--- a/Screener/ScreenResult/ScreenResult.xlsx
+++ b/Screener/ScreenResult/ScreenResult.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="231">
   <si>
     <t>Symbol</t>
   </si>
@@ -85,6 +85,9 @@
     <t>Code 33</t>
   </si>
   <si>
+    <t>PRFX</t>
+  </si>
+  <si>
     <t>OPRA</t>
   </si>
   <si>
@@ -100,235 +103,226 @@
     <t>RXST</t>
   </si>
   <si>
+    <t>RXDX</t>
+  </si>
+  <si>
     <t>ACLS</t>
   </si>
   <si>
-    <t>RXDX</t>
-  </si>
-  <si>
     <t>IOT</t>
   </si>
   <si>
     <t>ELF</t>
   </si>
   <si>
+    <t>VRT</t>
+  </si>
+  <si>
     <t>INTT</t>
   </si>
   <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>AEHR</t>
+  </si>
+  <si>
     <t>LI</t>
   </si>
   <si>
+    <t>MOD</t>
+  </si>
+  <si>
     <t>AMPH</t>
   </si>
   <si>
-    <t>VRT</t>
-  </si>
-  <si>
-    <t>AEHR</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
     <t>RCL</t>
   </si>
   <si>
-    <t>MOD</t>
-  </si>
-  <si>
     <t>XPO</t>
   </si>
   <si>
-    <t>BLBD</t>
-  </si>
-  <si>
     <t>STRL</t>
   </si>
   <si>
+    <t>AVGO</t>
+  </si>
+  <si>
     <t>TGLS</t>
   </si>
   <si>
-    <t>AVGO</t>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
+    <t>STVN</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>KRYS</t>
+  </si>
+  <si>
+    <t>DV</t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>ROIV</t>
+  </si>
+  <si>
+    <t>ABCM</t>
+  </si>
+  <si>
+    <t>IDCC</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>TOL</t>
+  </si>
+  <si>
+    <t>LTH</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>AN</t>
+  </si>
+  <si>
+    <t>BECN</t>
+  </si>
+  <si>
+    <t>KBH</t>
+  </si>
+  <si>
+    <t>MANH</t>
   </si>
   <si>
     <t>CELH</t>
   </si>
   <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>STVN</t>
-  </si>
-  <si>
-    <t>JBL</t>
-  </si>
-  <si>
-    <t>DV</t>
-  </si>
-  <si>
-    <t>ABCM</t>
-  </si>
-  <si>
-    <t>KRYS</t>
-  </si>
-  <si>
-    <t>ROIV</t>
-  </si>
-  <si>
-    <t>PHM</t>
-  </si>
-  <si>
-    <t>IDCC</t>
-  </si>
-  <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>BECN</t>
-  </si>
-  <si>
-    <t>LAD</t>
-  </si>
-  <si>
-    <t>TOL</t>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>RDNT</t>
   </si>
   <si>
     <t>FTAI</t>
   </si>
   <si>
-    <t>LTH</t>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>ENS</t>
+  </si>
+  <si>
+    <t>TMHC</t>
+  </si>
+  <si>
+    <t>PAG</t>
+  </si>
+  <si>
+    <t>DICE</t>
+  </si>
+  <si>
+    <t>APG</t>
+  </si>
+  <si>
+    <t>CNMD</t>
+  </si>
+  <si>
+    <t>VNT</t>
+  </si>
+  <si>
+    <t>ALGM</t>
+  </si>
+  <si>
+    <t>TPH</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>MPWR</t>
+  </si>
+  <si>
+    <t>LPG</t>
   </si>
   <si>
     <t>ONTO</t>
   </si>
   <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>KBH</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>AN</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>TMHC</t>
-  </si>
-  <si>
-    <t>ENS</t>
-  </si>
-  <si>
-    <t>TPH</t>
-  </si>
-  <si>
-    <t>RDNT</t>
-  </si>
-  <si>
     <t>PEN</t>
   </si>
   <si>
-    <t>DICE</t>
-  </si>
-  <si>
-    <t>ALGM</t>
-  </si>
-  <si>
-    <t>VNT</t>
-  </si>
-  <si>
-    <t>MPWR</t>
-  </si>
-  <si>
-    <t>CNMD</t>
+    <t>MTH</t>
+  </si>
+  <si>
+    <t>TMDX</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>FND</t>
+  </si>
+  <si>
+    <t>IGT</t>
+  </si>
+  <si>
+    <t>HUBB</t>
   </si>
   <si>
     <t>LRCX</t>
   </si>
   <si>
-    <t>PAG</t>
-  </si>
-  <si>
-    <t>ON</t>
-  </si>
-  <si>
-    <t>OC</t>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>CPRT</t>
+  </si>
+  <si>
+    <t>FDX</t>
+  </si>
+  <si>
+    <t>ORCL</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>MWA</t>
   </si>
   <si>
     <t>LSCC</t>
   </si>
   <si>
-    <t>MTH</t>
-  </si>
-  <si>
-    <t>APG</t>
-  </si>
-  <si>
-    <t>AMAT</t>
-  </si>
-  <si>
-    <t>TMDX</t>
+    <t>MTZ</t>
   </si>
   <si>
     <t>CLH</t>
   </si>
   <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>HUBB</t>
-  </si>
-  <si>
-    <t>WCC</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>CPRT</t>
-  </si>
-  <si>
-    <t>SNPS</t>
-  </si>
-  <si>
-    <t>MTZ</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>ORCL</t>
-  </si>
-  <si>
-    <t>CDNS</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>IGT</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>LEGN</t>
-  </si>
-  <si>
-    <t>NXPI</t>
+    <t>Healthcare</t>
   </si>
   <si>
     <t>Communication Services</t>
@@ -337,24 +331,24 @@
     <t>Technology</t>
   </si>
   <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
     <t>Consumer Defensive</t>
   </si>
   <si>
+    <t>Industrials</t>
+  </si>
+  <si>
     <t>Consumer Cyclical</t>
   </si>
   <si>
-    <t>Industrials</t>
-  </si>
-  <si>
     <t>Basic Materials</t>
   </si>
   <si>
     <t>Energy</t>
   </si>
   <si>
+    <t>Drug Manufacturers—Specialty &amp; Generic</t>
+  </si>
+  <si>
     <t>Internet Content &amp; Information</t>
   </si>
   <si>
@@ -370,36 +364,33 @@
     <t>Medical Devices</t>
   </si>
   <si>
+    <t>Biotechnology</t>
+  </si>
+  <si>
     <t>Semiconductor Equipment &amp; Materials</t>
   </si>
   <si>
-    <t>Biotechnology</t>
-  </si>
-  <si>
     <t>Software—Infrastructure</t>
   </si>
   <si>
     <t>Household &amp; Personal Products</t>
   </si>
   <si>
+    <t>Electrical Equipment &amp; Parts</t>
+  </si>
+  <si>
+    <t>Building Products &amp; Equipment</t>
+  </si>
+  <si>
     <t>Auto Manufacturers</t>
   </si>
   <si>
-    <t>Drug Manufacturers—Specialty &amp; Generic</t>
-  </si>
-  <si>
-    <t>Electrical Equipment &amp; Parts</t>
-  </si>
-  <si>
-    <t>Building Products &amp; Equipment</t>
+    <t>Auto Parts</t>
   </si>
   <si>
     <t>Travel Services</t>
   </si>
   <si>
-    <t>Auto Parts</t>
-  </si>
-  <si>
     <t>Trucking</t>
   </si>
   <si>
@@ -409,58 +400,73 @@
     <t>Building Materials</t>
   </si>
   <si>
+    <t>Electronic Components</t>
+  </si>
+  <si>
+    <t>Residential Construction</t>
+  </si>
+  <si>
+    <t>Medical Instruments &amp; Supplies</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas E&amp;P</t>
+  </si>
+  <si>
+    <t>Software—Application</t>
+  </si>
+  <si>
+    <t>Auto &amp; Truck Dealerships</t>
+  </si>
+  <si>
+    <t>Telecom Services</t>
+  </si>
+  <si>
+    <t>Leisure</t>
+  </si>
+  <si>
+    <t>Industrial Distribution</t>
+  </si>
+  <si>
     <t>Beverages—Non-Alcoholic</t>
   </si>
   <si>
-    <t>Residential Construction</t>
-  </si>
-  <si>
-    <t>Medical Instruments &amp; Supplies</t>
-  </si>
-  <si>
-    <t>Electronic Components</t>
-  </si>
-  <si>
-    <t>Software—Application</t>
-  </si>
-  <si>
-    <t>Telecom Services</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas E&amp;P</t>
-  </si>
-  <si>
-    <t>Industrial Distribution</t>
-  </si>
-  <si>
-    <t>Auto &amp; Truck Dealerships</t>
+    <t>Airlines</t>
+  </si>
+  <si>
+    <t>Diagnostics &amp; Research</t>
   </si>
   <si>
     <t>Rental &amp; Leasing Services</t>
   </si>
   <si>
-    <t>Leisure</t>
-  </si>
-  <si>
-    <t>Airlines</t>
-  </si>
-  <si>
-    <t>Diagnostics &amp; Research</t>
+    <t>Oil &amp; Gas Equipment &amp; Services</t>
   </si>
   <si>
     <t>Scientific &amp; Technical Instruments</t>
   </si>
   <si>
+    <t>Oil &amp; Gas Midstream</t>
+  </si>
+  <si>
+    <t>Home Improvement Retail</t>
+  </si>
+  <si>
+    <t>Gambling</t>
+  </si>
+  <si>
+    <t>Specialty Business Services</t>
+  </si>
+  <si>
+    <t>Integrated Freight &amp; Logistics</t>
+  </si>
+  <si>
+    <t>Specialty Industrial Machinery</t>
+  </si>
+  <si>
     <t>Waste Management</t>
   </si>
   <si>
-    <t>Oil &amp; Gas Equipment &amp; Services</t>
-  </si>
-  <si>
-    <t>Specialty Business Services</t>
-  </si>
-  <si>
-    <t>Gambling</t>
+    <t>2020-09-01</t>
   </si>
   <si>
     <t>2018-07-27</t>
@@ -478,229 +484,223 @@
     <t>2021-07-30</t>
   </si>
   <si>
+    <t>2021-03-12</t>
+  </si>
+  <si>
     <t>2000-07-11</t>
   </si>
   <si>
-    <t>2021-03-12</t>
-  </si>
-  <si>
     <t>2021-12-15</t>
   </si>
   <si>
     <t>2016-09-22</t>
   </si>
   <si>
+    <t>2018-08-02</t>
+  </si>
+  <si>
     <t>1997-06-17</t>
   </si>
   <si>
+    <t>2005-06-28</t>
+  </si>
+  <si>
+    <t>1997-08-15</t>
+  </si>
+  <si>
     <t>2020-07-30</t>
   </si>
   <si>
+    <t>1982-09-20</t>
+  </si>
+  <si>
     <t>2014-06-25</t>
   </si>
   <si>
-    <t>2018-08-02</t>
-  </si>
-  <si>
-    <t>1997-08-15</t>
-  </si>
-  <si>
-    <t>2005-06-28</t>
-  </si>
-  <si>
     <t>1993-04-28</t>
   </si>
   <si>
-    <t>1982-09-20</t>
-  </si>
-  <si>
     <t>2003-10-07</t>
   </si>
   <si>
-    <t>2014-03-20</t>
-  </si>
-  <si>
     <t>1991-07-12</t>
   </si>
   <si>
+    <t>2009-08-06</t>
+  </si>
+  <si>
     <t>2012-05-10</t>
   </si>
   <si>
-    <t>2009-08-06</t>
+    <t>1993-05-03</t>
+  </si>
+  <si>
+    <t>1993-11-03</t>
+  </si>
+  <si>
+    <t>2021-07-16</t>
+  </si>
+  <si>
+    <t>2019-07-26</t>
+  </si>
+  <si>
+    <t>2017-09-20</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>1996-12-18</t>
+  </si>
+  <si>
+    <t>1980-03-17</t>
+  </si>
+  <si>
+    <t>2020-12-08</t>
+  </si>
+  <si>
+    <t>2020-10-22</t>
+  </si>
+  <si>
+    <t>1981-11-12</t>
+  </si>
+  <si>
+    <t>2002-09-11</t>
+  </si>
+  <si>
+    <t>1986-07-08</t>
+  </si>
+  <si>
+    <t>2021-10-07</t>
+  </si>
+  <si>
+    <t>2012-07-20</t>
+  </si>
+  <si>
+    <t>1990-05-11</t>
+  </si>
+  <si>
+    <t>2004-09-23</t>
+  </si>
+  <si>
+    <t>1986-08-01</t>
+  </si>
+  <si>
+    <t>1998-04-23</t>
   </si>
   <si>
     <t>2007-01-22</t>
   </si>
   <si>
-    <t>1993-11-03</t>
-  </si>
-  <si>
-    <t>2021-07-16</t>
-  </si>
-  <si>
-    <t>1993-05-03</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>2020-10-22</t>
-  </si>
-  <si>
-    <t>2017-09-20</t>
-  </si>
-  <si>
-    <t>2020-12-08</t>
-  </si>
-  <si>
-    <t>1980-03-17</t>
-  </si>
-  <si>
-    <t>1981-11-12</t>
-  </si>
-  <si>
-    <t>2019-07-26</t>
-  </si>
-  <si>
-    <t>2004-09-23</t>
-  </si>
-  <si>
-    <t>1996-12-18</t>
-  </si>
-  <si>
-    <t>1986-07-08</t>
+    <t>2007-05-03</t>
+  </si>
+  <si>
+    <t>1997-01-03</t>
   </si>
   <si>
     <t>2015-05-14</t>
   </si>
   <si>
-    <t>2021-10-07</t>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>2004-08-02</t>
+  </si>
+  <si>
+    <t>2013-04-10</t>
+  </si>
+  <si>
+    <t>1996-10-23</t>
+  </si>
+  <si>
+    <t>2021-09-15</t>
+  </si>
+  <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
+    <t>1987-07-23</t>
+  </si>
+  <si>
+    <t>2020-09-24</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>2013-01-31</t>
+  </si>
+  <si>
+    <t>2006-11-01</t>
+  </si>
+  <si>
+    <t>2004-11-19</t>
+  </si>
+  <si>
+    <t>2014-05-08</t>
   </si>
   <si>
     <t>2019-10-28</t>
   </si>
   <si>
-    <t>2012-07-20</t>
-  </si>
-  <si>
-    <t>2002-09-11</t>
-  </si>
-  <si>
-    <t>1986-08-01</t>
-  </si>
-  <si>
-    <t>2007-05-03</t>
-  </si>
-  <si>
-    <t>1990-05-11</t>
-  </si>
-  <si>
-    <t>1998-04-23</t>
-  </si>
-  <si>
-    <t>2013-04-10</t>
-  </si>
-  <si>
-    <t>2004-08-02</t>
-  </si>
-  <si>
-    <t>2013-01-31</t>
-  </si>
-  <si>
-    <t>1997-01-03</t>
-  </si>
-  <si>
     <t>2015-09-18</t>
   </si>
   <si>
-    <t>2021-09-15</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>2020-09-24</t>
-  </si>
-  <si>
-    <t>2004-11-19</t>
-  </si>
-  <si>
-    <t>1987-07-23</t>
+    <t>1988-07-26</t>
+  </si>
+  <si>
+    <t>2019-05-02</t>
+  </si>
+  <si>
+    <t>2013-02-06</t>
+  </si>
+  <si>
+    <t>2000-05-02</t>
+  </si>
+  <si>
+    <t>2016-08-17</t>
+  </si>
+  <si>
+    <t>2009-11-18</t>
+  </si>
+  <si>
+    <t>2017-04-27</t>
+  </si>
+  <si>
+    <t>1990-03-26</t>
+  </si>
+  <si>
+    <t>1972-06-05</t>
   </si>
   <si>
     <t>1984-05-04</t>
   </si>
   <si>
-    <t>1996-10-23</t>
-  </si>
-  <si>
-    <t>2000-05-02</t>
-  </si>
-  <si>
-    <t>2006-11-01</t>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>1994-03-17</t>
+  </si>
+  <si>
+    <t>1978-04-12</t>
+  </si>
+  <si>
+    <t>1986-03-12</t>
+  </si>
+  <si>
+    <t>2012-06-29</t>
+  </si>
+  <si>
+    <t>2006-05-26</t>
   </si>
   <si>
     <t>1989-11-09</t>
   </si>
   <si>
-    <t>1988-07-26</t>
-  </si>
-  <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
-    <t>2019-05-02</t>
+    <t>1973-02-21</t>
   </si>
   <si>
     <t>1987-11-24</t>
-  </si>
-  <si>
-    <t>2012-06-29</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>1972-06-05</t>
-  </si>
-  <si>
-    <t>1999-05-12</t>
-  </si>
-  <si>
-    <t>2013-02-06</t>
-  </si>
-  <si>
-    <t>2009-11-18</t>
-  </si>
-  <si>
-    <t>1994-03-17</t>
-  </si>
-  <si>
-    <t>1992-02-26</t>
-  </si>
-  <si>
-    <t>1973-02-21</t>
-  </si>
-  <si>
-    <t>2016-08-17</t>
-  </si>
-  <si>
-    <t>1986-03-12</t>
-  </si>
-  <si>
-    <t>1987-06-10</t>
-  </si>
-  <si>
-    <t>1990-03-26</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>2020-06-05</t>
-  </si>
-  <si>
-    <t>2010-08-06</t>
   </si>
   <si>
     <t>F</t>
@@ -1064,7 +1064,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W83"/>
+  <dimension ref="A1:W80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
@@ -1143,67 +1143,67 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E2">
-        <v>24.47999954223633</v>
+        <v>16.5</v>
       </c>
       <c r="F2">
-        <v>1347496.666666667</v>
+        <v>603930</v>
       </c>
       <c r="G2">
-        <v>16.42780004501343</v>
+        <v>1.334840007424354</v>
       </c>
       <c r="H2">
-        <v>10.68693337440491</v>
+        <v>0.8076266684134801</v>
       </c>
       <c r="I2">
-        <v>9.165300034284591</v>
+        <v>0.7511750009655952</v>
       </c>
       <c r="J2">
-        <v>7.656050037145615</v>
+        <v>0.5763150002062321</v>
       </c>
       <c r="K2">
-        <v>3.970000028610229</v>
+        <v>0.3610000014305115</v>
       </c>
       <c r="L2">
-        <v>24.5</v>
+        <v>16.5</v>
       </c>
       <c r="M2">
-        <v>314.4204001179268</v>
+        <v>2948.165655424706</v>
       </c>
       <c r="N2">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>9384000</v>
+        <v>-7359000</v>
       </c>
       <c r="R2">
-        <v>20922000</v>
+        <v>-3166000</v>
       </c>
       <c r="S2">
-        <v>15478000</v>
+        <v>-2308000</v>
       </c>
       <c r="T2">
-        <v>10.99511406376322</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>21.73217550274223</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>17.7803816153749</v>
+        <v>0</v>
       </c>
       <c r="W2" t="s">
         <v>229</v>
@@ -1214,67 +1214,67 @@
         <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E3">
-        <v>269.9299926757812</v>
+        <v>25.44000053405762</v>
       </c>
       <c r="F3">
-        <v>3166170</v>
+        <v>1407013.333333333</v>
       </c>
       <c r="G3">
-        <v>197.291799621582</v>
+        <v>16.4524081993103</v>
       </c>
       <c r="H3">
-        <v>126.8952665710449</v>
+        <v>10.4475453154246</v>
       </c>
       <c r="I3">
-        <v>112.4695499038696</v>
+        <v>8.842341672182084</v>
       </c>
       <c r="J3">
-        <v>94.87589992523193</v>
+        <v>7.260309534072876</v>
       </c>
       <c r="K3">
-        <v>3.849999904632568</v>
+        <v>3.460049629211426</v>
       </c>
       <c r="L3">
-        <v>269.9299926757812</v>
+        <v>25.44000053405762</v>
       </c>
       <c r="M3">
-        <v>275.9478690241664</v>
+        <v>325.9014186056987</v>
       </c>
       <c r="N3">
-        <v>3.35</v>
+        <v>0.08</v>
       </c>
       <c r="O3">
-        <v>3.14</v>
+        <v>0.22</v>
       </c>
       <c r="P3">
-        <v>1.53</v>
+        <v>0.18</v>
       </c>
       <c r="Q3">
-        <v>184416000</v>
+        <v>9384000</v>
       </c>
       <c r="R3">
-        <v>176167000</v>
+        <v>20922000</v>
       </c>
       <c r="S3">
-        <v>85846000</v>
+        <v>15478000</v>
       </c>
       <c r="T3">
-        <v>9.956968463336807</v>
+        <v>10.99511406376322</v>
       </c>
       <c r="U3">
-        <v>9.769714312650601</v>
+        <v>21.73217550274223</v>
       </c>
       <c r="V3">
-        <v>6.689493304740293</v>
+        <v>17.7803816153749</v>
       </c>
       <c r="W3" t="s">
         <v>229</v>
@@ -1285,67 +1285,67 @@
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E4">
-        <v>11.30000019073486</v>
+        <v>270.9500122070312</v>
       </c>
       <c r="F4">
-        <v>716780</v>
+        <v>3026220</v>
       </c>
       <c r="G4">
-        <v>9.909600019454956</v>
+        <v>200.7391998291016</v>
       </c>
       <c r="H4">
-        <v>6.959266678492228</v>
+        <v>128.0981999715169</v>
       </c>
       <c r="I4">
-        <v>6.024900008440017</v>
+        <v>113.5491499710083</v>
       </c>
       <c r="J4">
-        <v>5.234550015926361</v>
+        <v>95.84584995269775</v>
       </c>
       <c r="K4">
-        <v>0.09375</v>
+        <v>3.849999904632568</v>
       </c>
       <c r="L4">
-        <v>13.27000045776367</v>
+        <v>270.9500122070312</v>
       </c>
       <c r="M4">
-        <v>236.6186016987529</v>
+        <v>266.5758812525153</v>
       </c>
       <c r="N4">
-        <v>-0.12</v>
+        <v>3.35</v>
       </c>
       <c r="O4">
-        <v>-0.07000000000000001</v>
+        <v>3.14</v>
       </c>
       <c r="P4">
-        <v>-0.08</v>
+        <v>1.53</v>
       </c>
       <c r="Q4">
-        <v>-3327000</v>
+        <v>184416000</v>
       </c>
       <c r="R4">
-        <v>-1960000</v>
+        <v>176167000</v>
       </c>
       <c r="S4">
-        <v>-2116000</v>
+        <v>85846000</v>
       </c>
       <c r="T4">
-        <v>-18.03545291917385</v>
+        <v>9.956968463336807</v>
       </c>
       <c r="U4">
-        <v>-10.11612903225806</v>
+        <v>9.769714312650601</v>
       </c>
       <c r="V4">
-        <v>-11.23201868464356</v>
+        <v>6.689493304740293</v>
       </c>
       <c r="W4" t="s">
         <v>229</v>
@@ -1356,70 +1356,70 @@
         <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E5">
-        <v>421.7999877929688</v>
+        <v>10.9399995803833</v>
       </c>
       <c r="F5">
-        <v>54112963.33333334</v>
+        <v>705150</v>
       </c>
       <c r="G5">
-        <v>361.8196008300781</v>
+        <v>9.99560001373291</v>
       </c>
       <c r="H5">
-        <v>263.4778666178385</v>
+        <v>7.009600008328755</v>
       </c>
       <c r="I5">
-        <v>231.7846499633789</v>
+        <v>6.06425000667572</v>
       </c>
       <c r="J5">
-        <v>204.4626495361328</v>
+        <v>5.267200013399124</v>
       </c>
       <c r="K5">
-        <v>0.3134739995002747</v>
+        <v>0.09375</v>
       </c>
       <c r="L5">
-        <v>438.0799865722656</v>
+        <v>13.27000045776367</v>
       </c>
       <c r="M5">
-        <v>216.4992247055354</v>
+        <v>226.7055263452704</v>
       </c>
       <c r="N5">
-        <v>0.27</v>
+        <v>-0.12</v>
       </c>
       <c r="O5">
-        <v>0.57</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="P5">
-        <v>0.82</v>
+        <v>-0.08</v>
       </c>
       <c r="Q5">
-        <v>680000000</v>
+        <v>-3327000</v>
       </c>
       <c r="R5">
-        <v>1414000000</v>
+        <v>-1960000</v>
       </c>
       <c r="S5">
-        <v>2043000000</v>
+        <v>-2116000</v>
       </c>
       <c r="T5">
-        <v>11.4651829371101</v>
+        <v>-18.03545291917385</v>
       </c>
       <c r="U5">
-        <v>23.36803834077012</v>
+        <v>-10.11612903225806</v>
       </c>
       <c r="V5">
-        <v>28.40656284760845</v>
+        <v>-11.23201868464356</v>
       </c>
       <c r="W5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -1427,67 +1427,67 @@
         <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E6">
-        <v>31.68000030517578</v>
+        <v>424.0499877929688</v>
       </c>
       <c r="F6">
-        <v>522520</v>
+        <v>49982716.66666666</v>
       </c>
       <c r="G6">
-        <v>24.6406999206543</v>
+        <v>364.8374389648437</v>
       </c>
       <c r="H6">
-        <v>17.7642333094279</v>
+        <v>265.1283240763346</v>
       </c>
       <c r="I6">
-        <v>16.30292498111725</v>
+        <v>233.1984477615356</v>
       </c>
       <c r="J6">
-        <v>14.89857500076294</v>
+        <v>205.4890301132202</v>
       </c>
       <c r="K6">
-        <v>8.970000267028809</v>
+        <v>0.3130019903182983</v>
       </c>
       <c r="L6">
-        <v>31.68000030517578</v>
+        <v>438.0799865722656</v>
       </c>
       <c r="M6">
-        <v>207.7500756598931</v>
+        <v>215.514735130629</v>
       </c>
       <c r="N6">
-        <v>-0.61</v>
+        <v>0.27</v>
       </c>
       <c r="O6">
-        <v>-0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="P6">
-        <v>-0.42</v>
+        <v>0.82</v>
       </c>
       <c r="Q6">
-        <v>-16818000</v>
+        <v>680000000</v>
       </c>
       <c r="R6">
-        <v>-15610000</v>
+        <v>1414000000</v>
       </c>
       <c r="S6">
-        <v>-13212000</v>
+        <v>2043000000</v>
       </c>
       <c r="T6">
-        <v>-133.3174791914388</v>
+        <v>11.4651829371101</v>
       </c>
       <c r="U6">
-        <v>-97.02884137245151</v>
+        <v>23.36803834077012</v>
       </c>
       <c r="V6">
-        <v>-75.54462805191835</v>
+        <v>28.40656284760845</v>
       </c>
       <c r="W6" t="s">
         <v>230</v>
@@ -1498,70 +1498,70 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E7">
-        <v>177.9299926757812</v>
+        <v>30.77000045776367</v>
       </c>
       <c r="F7">
-        <v>547396.6666666666</v>
+        <v>532353.3333333334</v>
       </c>
       <c r="G7">
-        <v>153.3342004394531</v>
+        <v>24.89089992523193</v>
       </c>
       <c r="H7">
-        <v>125.2645337931315</v>
+        <v>17.87749998092652</v>
       </c>
       <c r="I7">
-        <v>110.0636503219605</v>
+        <v>16.39802498340607</v>
       </c>
       <c r="J7">
-        <v>99.27110033035278</v>
+        <v>14.9612249994278</v>
       </c>
       <c r="K7">
-        <v>0.6800000071525574</v>
+        <v>8.970000267028809</v>
       </c>
       <c r="L7">
-        <v>183.3300018310547</v>
+        <v>31.68000030517578</v>
       </c>
       <c r="M7">
-        <v>193.2290239152157</v>
+        <v>199.2145124429223</v>
       </c>
       <c r="N7">
-        <v>1.21</v>
+        <v>-0.61</v>
       </c>
       <c r="O7">
-        <v>1.71</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="P7">
-        <v>1.43</v>
+        <v>-0.42</v>
       </c>
       <c r="Q7">
-        <v>40283000</v>
+        <v>-16818000</v>
       </c>
       <c r="R7">
-        <v>56992000</v>
+        <v>-15610000</v>
       </c>
       <c r="S7">
-        <v>47697000</v>
+        <v>-13212000</v>
       </c>
       <c r="T7">
-        <v>17.57739718555689</v>
+        <v>-133.3174791914388</v>
       </c>
       <c r="U7">
-        <v>21.42145678836013</v>
+        <v>-97.02884137245151</v>
       </c>
       <c r="V7">
-        <v>18.77686796315251</v>
+        <v>-75.54462805191835</v>
       </c>
       <c r="W7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -1569,13 +1569,13 @@
         <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E8">
         <v>199.9199981689453</v>
@@ -1602,7 +1602,7 @@
         <v>199.9199981689453</v>
       </c>
       <c r="M8">
-        <v>188.1703394893809</v>
+        <v>189.7452927007889</v>
       </c>
       <c r="N8">
         <v>-0.9</v>
@@ -1640,67 +1640,67 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E9">
-        <v>27.25</v>
+        <v>174.1199951171875</v>
       </c>
       <c r="F9">
-        <v>5023780</v>
+        <v>539016.6666666666</v>
       </c>
       <c r="G9">
-        <v>23.30379985809326</v>
+        <v>154.4884002685547</v>
       </c>
       <c r="H9">
-        <v>18.3365332921346</v>
+        <v>125.8972671000163</v>
       </c>
       <c r="I9">
-        <v>16.52669998168945</v>
+        <v>110.6287503051758</v>
       </c>
       <c r="J9">
-        <v>15.11625000476837</v>
+        <v>99.77305032730102</v>
       </c>
       <c r="K9">
-        <v>8.699999809265137</v>
+        <v>0.6800000071525574</v>
       </c>
       <c r="L9">
-        <v>30.6299991607666</v>
+        <v>183.3300018310547</v>
       </c>
       <c r="M9">
-        <v>174.4687727168251</v>
+        <v>186.7020197528608</v>
       </c>
       <c r="N9">
-        <v>-0.11</v>
+        <v>1.21</v>
       </c>
       <c r="O9">
-        <v>-0.1</v>
+        <v>1.71</v>
       </c>
       <c r="P9">
-        <v>-0.13</v>
+        <v>1.43</v>
       </c>
       <c r="Q9">
-        <v>-58555000</v>
+        <v>40283000</v>
       </c>
       <c r="R9">
-        <v>-53598000</v>
+        <v>56992000</v>
       </c>
       <c r="S9">
-        <v>-67856000</v>
+        <v>47697000</v>
       </c>
       <c r="T9">
-        <v>-34.48468786808009</v>
+        <v>17.57739718555689</v>
       </c>
       <c r="U9">
-        <v>-28.72701351184766</v>
+        <v>21.42145678836013</v>
       </c>
       <c r="V9">
-        <v>-33.21064996084574</v>
+        <v>18.77686796315251</v>
       </c>
       <c r="W9" t="s">
         <v>229</v>
@@ -1711,67 +1711,67 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E10">
-        <v>112.3399963378906</v>
+        <v>27.64999961853027</v>
       </c>
       <c r="F10">
-        <v>1173506.666666667</v>
+        <v>5021123.333333333</v>
       </c>
       <c r="G10">
-        <v>100.4213999938965</v>
+        <v>23.47579986572266</v>
       </c>
       <c r="H10">
-        <v>79.07499992370606</v>
+        <v>18.45486662546794</v>
       </c>
       <c r="I10">
-        <v>70.50664989471436</v>
+        <v>16.60234997749329</v>
       </c>
       <c r="J10">
-        <v>63.46984987258911</v>
+        <v>15.18460000038147</v>
       </c>
       <c r="K10">
-        <v>7.300000190734863</v>
+        <v>8.699999809265137</v>
       </c>
       <c r="L10">
-        <v>114.370002746582</v>
+        <v>30.6299991607666</v>
       </c>
       <c r="M10">
-        <v>174.418983046675</v>
+        <v>181.3191028228078</v>
       </c>
       <c r="N10">
-        <v>0.21</v>
+        <v>-0.11</v>
       </c>
       <c r="O10">
-        <v>0.34</v>
+        <v>-0.1</v>
       </c>
       <c r="P10">
-        <v>0.29</v>
+        <v>-0.13</v>
       </c>
       <c r="Q10">
-        <v>11710000</v>
+        <v>-58555000</v>
       </c>
       <c r="R10">
-        <v>19105000</v>
+        <v>-53598000</v>
       </c>
       <c r="S10">
-        <v>16246000</v>
+        <v>-67856000</v>
       </c>
       <c r="T10">
-        <v>9.570981372957686</v>
+        <v>-34.48468786808009</v>
       </c>
       <c r="U10">
-        <v>13.03766284283151</v>
+        <v>-28.72701351184766</v>
       </c>
       <c r="V10">
-        <v>8.671146527751832</v>
+        <v>-33.21064996084574</v>
       </c>
       <c r="W10" t="s">
         <v>229</v>
@@ -1782,67 +1782,67 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E11">
-        <v>23.25</v>
+        <v>113.4899978637695</v>
       </c>
       <c r="F11">
-        <v>333033.3333333333</v>
+        <v>1061740</v>
       </c>
       <c r="G11">
-        <v>22.84680004119873</v>
+        <v>100.8341999816895</v>
       </c>
       <c r="H11">
-        <v>17.58053329467774</v>
+        <v>79.46226656595866</v>
       </c>
       <c r="I11">
-        <v>15.33174998044968</v>
+        <v>70.87499988555908</v>
       </c>
       <c r="J11">
-        <v>13.66744995832443</v>
+        <v>63.80504987716674</v>
       </c>
       <c r="K11">
-        <v>0.1160330548882484</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="L11">
-        <v>26.90999984741211</v>
+        <v>114.370002746582</v>
       </c>
       <c r="M11">
-        <v>172.4094727159224</v>
+        <v>177.0189177543051</v>
       </c>
       <c r="N11">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="O11">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="P11">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="Q11">
-        <v>2524000</v>
+        <v>11710000</v>
       </c>
       <c r="R11">
-        <v>3244000</v>
+        <v>19105000</v>
       </c>
       <c r="S11">
-        <v>2817000</v>
+        <v>16246000</v>
       </c>
       <c r="T11">
-        <v>8.202528354619609</v>
+        <v>9.570981372957686</v>
       </c>
       <c r="U11">
-        <v>10.01080080234532</v>
+        <v>13.03766284283151</v>
       </c>
       <c r="V11">
-        <v>8.825464456906545</v>
+        <v>8.671146527751832</v>
       </c>
       <c r="W11" t="s">
         <v>229</v>
@@ -1853,67 +1853,67 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E12">
-        <v>35.84999847412109</v>
+        <v>25.30999946594238</v>
       </c>
       <c r="F12">
-        <v>7101793.333333333</v>
+        <v>5232390</v>
       </c>
       <c r="G12">
-        <v>30.36809993743897</v>
+        <v>19.66939994812012</v>
       </c>
       <c r="H12">
-        <v>25.49176666259766</v>
+        <v>15.94846665700277</v>
       </c>
       <c r="I12">
-        <v>23.90649998188019</v>
+        <v>15.1669499874115</v>
       </c>
       <c r="J12">
-        <v>23.21459998607635</v>
+        <v>14.02355000019073</v>
       </c>
       <c r="K12">
-        <v>13.61999988555908</v>
+        <v>5.564881324768066</v>
       </c>
       <c r="L12">
-        <v>43.95999908447266</v>
+        <v>28.57900047302246</v>
       </c>
       <c r="M12">
-        <v>171.7067482698571</v>
+        <v>171.8213109448897</v>
       </c>
       <c r="N12">
-        <v>-0.64</v>
+        <v>0.06</v>
       </c>
       <c r="O12">
-        <v>0.26</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="P12">
-        <v>0.9</v>
+        <v>0.12</v>
       </c>
       <c r="Q12">
-        <v>-1640321000</v>
+        <v>21200000</v>
       </c>
       <c r="R12">
-        <v>256938000</v>
+        <v>26600000</v>
       </c>
       <c r="S12">
-        <v>929668000</v>
+        <v>50300000</v>
       </c>
       <c r="T12">
-        <v>-17.55802782723927</v>
+        <v>1.431368577408683</v>
       </c>
       <c r="U12">
-        <v>1.455749769091836</v>
+        <v>1.607639308594222</v>
       </c>
       <c r="V12">
-        <v>4.948450403583787</v>
+        <v>3.306817434751167</v>
       </c>
       <c r="W12" t="s">
         <v>230</v>
@@ -1924,67 +1924,67 @@
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E13">
-        <v>56.93999862670898</v>
+        <v>23.63999938964844</v>
       </c>
       <c r="F13">
-        <v>473926.6666666667</v>
+        <v>311170</v>
       </c>
       <c r="G13">
-        <v>46.8379997253418</v>
+        <v>22.94860004425049</v>
       </c>
       <c r="H13">
-        <v>37.81073321024576</v>
+        <v>17.66299995422363</v>
       </c>
       <c r="I13">
-        <v>35.60979992866516</v>
+        <v>15.40949997663498</v>
       </c>
       <c r="J13">
-        <v>33.12369998931885</v>
+        <v>13.74904995679855</v>
       </c>
       <c r="K13">
-        <v>8.689999580383301</v>
+        <v>0.1160330548882484</v>
       </c>
       <c r="L13">
-        <v>58.38000106811523</v>
+        <v>26.90999984741211</v>
       </c>
       <c r="M13">
-        <v>171.5646357721439</v>
+        <v>168.0790200670218</v>
       </c>
       <c r="N13">
+        <v>0.23</v>
+      </c>
+      <c r="O13">
         <v>0.3</v>
       </c>
-      <c r="O13">
-        <v>0.66</v>
-      </c>
       <c r="P13">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="Q13">
-        <v>15874000</v>
+        <v>2524000</v>
       </c>
       <c r="R13">
-        <v>33913000</v>
+        <v>3244000</v>
       </c>
       <c r="S13">
-        <v>26032000</v>
+        <v>2817000</v>
       </c>
       <c r="T13">
-        <v>13.21412814557684</v>
+        <v>8.202528354619609</v>
       </c>
       <c r="U13">
-        <v>25.11646163986876</v>
+        <v>10.01080080234532</v>
       </c>
       <c r="V13">
-        <v>18.59136421419491</v>
+        <v>8.825464456906545</v>
       </c>
       <c r="W13" t="s">
         <v>229</v>
@@ -1995,70 +1995,70 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E14">
-        <v>25.3799991607666</v>
+        <v>135.4700012207031</v>
       </c>
       <c r="F14">
-        <v>6111130</v>
+        <v>2711756.666666667</v>
       </c>
       <c r="G14">
-        <v>19.45299995422363</v>
+        <v>120.9777996826172</v>
       </c>
       <c r="H14">
-        <v>15.87439999262492</v>
+        <v>92.80786649068196</v>
       </c>
       <c r="I14">
-        <v>15.09914999008179</v>
+        <v>84.70489982604981</v>
       </c>
       <c r="J14">
-        <v>13.97784999847412</v>
+        <v>77.58249979019165</v>
       </c>
       <c r="K14">
-        <v>5.564881324768066</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="L14">
-        <v>28.57900047302246</v>
+        <v>136.4700012207031</v>
       </c>
       <c r="M14">
-        <v>170.9425796010347</v>
+        <v>165.5519884010992</v>
       </c>
       <c r="N14">
-        <v>0.06</v>
+        <v>5.75</v>
       </c>
       <c r="O14">
-        <v>0.07000000000000001</v>
+        <v>4.72</v>
       </c>
       <c r="P14">
-        <v>0.12</v>
+        <v>2.41</v>
       </c>
       <c r="Q14">
-        <v>21200000</v>
+        <v>738007000</v>
       </c>
       <c r="R14">
-        <v>26600000</v>
+        <v>384513000</v>
       </c>
       <c r="S14">
-        <v>50300000</v>
+        <v>333786000</v>
       </c>
       <c r="T14">
-        <v>1.431368577408683</v>
+        <v>12.80936803725026</v>
       </c>
       <c r="U14">
-        <v>1.607639308594222</v>
+        <v>8.824033605924409</v>
       </c>
       <c r="V14">
-        <v>3.306817434751167</v>
+        <v>8.595390431986701</v>
       </c>
       <c r="W14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" spans="1:23">
@@ -2066,31 +2066,31 @@
         <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E15">
-        <v>39.77999877929688</v>
+        <v>38.70999908447266</v>
       </c>
       <c r="F15">
-        <v>1125330</v>
+        <v>1133333.333333333</v>
       </c>
       <c r="G15">
-        <v>35.07699993133545</v>
+        <v>35.36779991149902</v>
       </c>
       <c r="H15">
-        <v>31.44013324737549</v>
+        <v>31.51753323872884</v>
       </c>
       <c r="I15">
-        <v>28.46754991531372</v>
+        <v>28.5842999124527</v>
       </c>
       <c r="J15">
-        <v>25.93814990520477</v>
+        <v>26.05974991321564</v>
       </c>
       <c r="K15">
         <v>0.5</v>
@@ -2099,7 +2099,7 @@
         <v>44.2400016784668</v>
       </c>
       <c r="M15">
-        <v>166.7644048742971</v>
+        <v>164.5686930407567</v>
       </c>
       <c r="N15">
         <v>0.02</v>
@@ -2137,70 +2137,70 @@
         <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E16">
-        <v>135.2599945068359</v>
+        <v>37.06000137329102</v>
       </c>
       <c r="F16">
-        <v>2748706.666666667</v>
+        <v>7189086.666666667</v>
       </c>
       <c r="G16">
-        <v>120.1103996276856</v>
+        <v>30.64449996948242</v>
       </c>
       <c r="H16">
-        <v>92.32959981282552</v>
+        <v>25.59683334350586</v>
       </c>
       <c r="I16">
-        <v>84.31059982299804</v>
+        <v>23.97629998683929</v>
       </c>
       <c r="J16">
-        <v>77.29309976577758</v>
+        <v>23.22669998645782</v>
       </c>
       <c r="K16">
-        <v>0.8299999833106995</v>
+        <v>13.61999988555908</v>
       </c>
       <c r="L16">
-        <v>136.4700012207031</v>
+        <v>43.95999908447266</v>
       </c>
       <c r="M16">
-        <v>163.8988138492714</v>
+        <v>163.4535082713533</v>
       </c>
       <c r="N16">
-        <v>5.75</v>
+        <v>-0.64</v>
       </c>
       <c r="O16">
-        <v>4.72</v>
+        <v>0.26</v>
       </c>
       <c r="P16">
-        <v>2.41</v>
+        <v>0.9</v>
       </c>
       <c r="Q16">
-        <v>738007000</v>
+        <v>-1640321000</v>
       </c>
       <c r="R16">
-        <v>384513000</v>
+        <v>256938000</v>
       </c>
       <c r="S16">
-        <v>333786000</v>
+        <v>929668000</v>
       </c>
       <c r="T16">
-        <v>12.80936803725026</v>
+        <v>-17.55802782723927</v>
       </c>
       <c r="U16">
-        <v>8.824033605924409</v>
+        <v>1.455749769091836</v>
       </c>
       <c r="V16">
-        <v>8.595390431986701</v>
+        <v>4.948450403583787</v>
       </c>
       <c r="W16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -2208,67 +2208,67 @@
         <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E17">
-        <v>103.1999969482422</v>
+        <v>32.97000122070312</v>
       </c>
       <c r="F17">
-        <v>3915240</v>
+        <v>564273.3333333334</v>
       </c>
       <c r="G17">
-        <v>86.24379997253418</v>
+        <v>27.25860023498535</v>
       </c>
       <c r="H17">
-        <v>70.65800008138021</v>
+        <v>23.87653335571289</v>
       </c>
       <c r="I17">
-        <v>65.62190002441406</v>
+        <v>22.20725002288818</v>
       </c>
       <c r="J17">
-        <v>60.22510005950928</v>
+        <v>20.49624998569488</v>
       </c>
       <c r="K17">
-        <v>4.547188282012939</v>
+        <v>0.5703791379928589</v>
       </c>
       <c r="L17">
-        <v>133.7226409912109</v>
+        <v>34.61000061035156</v>
       </c>
       <c r="M17">
-        <v>163.8926870827923</v>
+        <v>161.4619054436921</v>
       </c>
       <c r="N17">
-        <v>0.13</v>
+        <v>0.46</v>
       </c>
       <c r="O17">
-        <v>-1.96</v>
+        <v>0.46</v>
       </c>
       <c r="P17">
-        <v>-0.19</v>
+        <v>1.69</v>
       </c>
       <c r="Q17">
-        <v>32968000</v>
+        <v>24400000</v>
       </c>
       <c r="R17">
-        <v>-500206000</v>
+        <v>24500000</v>
       </c>
       <c r="S17">
-        <v>-47910000</v>
+        <v>89900000</v>
       </c>
       <c r="T17">
-        <v>1.10147590688506</v>
+        <v>4.215618521078093</v>
       </c>
       <c r="U17">
-        <v>-19.20919879938187</v>
+        <v>4.375</v>
       </c>
       <c r="V17">
-        <v>-1.660574542848092</v>
+        <v>14.5445720757159</v>
       </c>
       <c r="W17" t="s">
         <v>229</v>
@@ -2279,67 +2279,67 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E18">
-        <v>32.90000152587891</v>
+        <v>55.06999969482422</v>
       </c>
       <c r="F18">
-        <v>584243.3333333334</v>
+        <v>482496.6666666667</v>
       </c>
       <c r="G18">
-        <v>27.0152001953125</v>
+        <v>47.21179969787597</v>
       </c>
       <c r="H18">
-        <v>23.79760000864665</v>
+        <v>37.9777332051595</v>
       </c>
       <c r="I18">
-        <v>22.1153000164032</v>
+        <v>35.74529993057251</v>
       </c>
       <c r="J18">
-        <v>20.41584997653961</v>
+        <v>33.18999998092652</v>
       </c>
       <c r="K18">
-        <v>0.5703791379928589</v>
+        <v>8.689999580383301</v>
       </c>
       <c r="L18">
-        <v>34.61000061035156</v>
+        <v>58.38000106811523</v>
       </c>
       <c r="M18">
-        <v>159.2822738705949</v>
+        <v>160.2053683329975</v>
       </c>
       <c r="N18">
-        <v>0.46</v>
+        <v>0.3</v>
       </c>
       <c r="O18">
-        <v>0.46</v>
+        <v>0.66</v>
       </c>
       <c r="P18">
-        <v>1.69</v>
+        <v>0.5</v>
       </c>
       <c r="Q18">
-        <v>24400000</v>
+        <v>15874000</v>
       </c>
       <c r="R18">
-        <v>24500000</v>
+        <v>33913000</v>
       </c>
       <c r="S18">
-        <v>89900000</v>
+        <v>26032000</v>
       </c>
       <c r="T18">
-        <v>4.215618521078093</v>
+        <v>13.21412814557684</v>
       </c>
       <c r="U18">
-        <v>4.375</v>
+        <v>25.11646163986876</v>
       </c>
       <c r="V18">
-        <v>14.5445720757159</v>
+        <v>18.59136421419491</v>
       </c>
       <c r="W18" t="s">
         <v>229</v>
@@ -2350,67 +2350,67 @@
         <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E19">
-        <v>60.04999923706055</v>
+        <v>101.2799987792969</v>
       </c>
       <c r="F19">
-        <v>1669190</v>
+        <v>3899783.333333333</v>
       </c>
       <c r="G19">
-        <v>50.06200012207032</v>
+        <v>87.03619995117188</v>
       </c>
       <c r="H19">
-        <v>40.58020008087158</v>
+        <v>70.92713340759278</v>
       </c>
       <c r="I19">
-        <v>38.34561850547791</v>
+        <v>65.89450002670289</v>
       </c>
       <c r="J19">
-        <v>35.98737289428711</v>
+        <v>60.48640007019043</v>
       </c>
       <c r="K19">
-        <v>0.6502050161361694</v>
+        <v>4.547188282012939</v>
       </c>
       <c r="L19">
-        <v>60.04999923706055</v>
+        <v>133.7226409912109</v>
       </c>
       <c r="M19">
-        <v>158.8872798948115</v>
+        <v>159.8288978874638</v>
       </c>
       <c r="N19">
-        <v>1.13</v>
+        <v>0.13</v>
       </c>
       <c r="O19">
-        <v>-0.8100000000000001</v>
+        <v>-1.96</v>
       </c>
       <c r="P19">
-        <v>0.13</v>
+        <v>-0.19</v>
       </c>
       <c r="Q19">
-        <v>131000000</v>
+        <v>32968000</v>
       </c>
       <c r="R19">
-        <v>-94000000</v>
+        <v>-500206000</v>
       </c>
       <c r="S19">
-        <v>14000000</v>
+        <v>-47910000</v>
       </c>
       <c r="T19">
-        <v>4.30637738330046</v>
+        <v>1.10147590688506</v>
       </c>
       <c r="U19">
-        <v>-5.133806663025669</v>
+        <v>-19.20919879938187</v>
       </c>
       <c r="V19">
-        <v>0.7341373885684321</v>
+        <v>-1.660574542848092</v>
       </c>
       <c r="W19" t="s">
         <v>229</v>
@@ -2421,70 +2421,70 @@
         <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E20">
-        <v>22.79000091552734</v>
+        <v>59.52000045776367</v>
       </c>
       <c r="F20">
-        <v>463810</v>
+        <v>1686066.666666667</v>
       </c>
       <c r="G20">
-        <v>22.3753999710083</v>
+        <v>50.4160001373291</v>
       </c>
       <c r="H20">
-        <v>18.49233331044515</v>
+        <v>40.72713342030843</v>
       </c>
       <c r="I20">
-        <v>16.21902499675751</v>
+        <v>38.50670632362366</v>
       </c>
       <c r="J20">
-        <v>15.15382500648499</v>
+        <v>36.07277248382568</v>
       </c>
       <c r="K20">
-        <v>7.369999885559082</v>
+        <v>0.6502050161361694</v>
       </c>
       <c r="L20">
-        <v>28.52000045776367</v>
+        <v>60.04999923706055</v>
       </c>
       <c r="M20">
-        <v>157.3222944623957</v>
+        <v>156.9924778239875</v>
       </c>
       <c r="N20">
-        <v>-0.72</v>
+        <v>1.13</v>
       </c>
       <c r="O20">
-        <v>-0.35</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P20">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="Q20">
-        <v>-23095000</v>
+        <v>131000000</v>
       </c>
       <c r="R20">
-        <v>-11294000</v>
+        <v>-94000000</v>
       </c>
       <c r="S20">
-        <v>7130000</v>
+        <v>14000000</v>
       </c>
       <c r="T20">
-        <v>-8.962945139557267</v>
+        <v>4.30637738330046</v>
       </c>
       <c r="U20">
-        <v>-4.791033885938269</v>
+        <v>-5.133806663025669</v>
       </c>
       <c r="V20">
-        <v>2.378141114157444</v>
+        <v>0.7341373885684321</v>
       </c>
       <c r="W20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -2492,40 +2492,40 @@
         <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D21" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E21">
-        <v>58.34000015258789</v>
+        <v>58.5099983215332</v>
       </c>
       <c r="F21">
-        <v>360130</v>
+        <v>359936.6666666667</v>
       </c>
       <c r="G21">
-        <v>48.35259994506836</v>
+        <v>48.79759994506836</v>
       </c>
       <c r="H21">
-        <v>39.80373338063558</v>
+        <v>39.97720002492269</v>
       </c>
       <c r="I21">
-        <v>36.62780000686646</v>
+        <v>36.80184999465942</v>
       </c>
       <c r="J21">
-        <v>33.69404998779297</v>
+        <v>33.83134999275207</v>
       </c>
       <c r="K21">
         <v>0.4209107160568237</v>
       </c>
       <c r="L21">
-        <v>58.43999862670898</v>
+        <v>58.5099983215332</v>
       </c>
       <c r="M21">
-        <v>156.1443324953716</v>
+        <v>156.9596804566893</v>
       </c>
       <c r="N21">
         <v>0.97</v>
@@ -2563,67 +2563,67 @@
         <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C22" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E22">
-        <v>52.40999984741211</v>
+        <v>882.0499877929688</v>
       </c>
       <c r="F22">
-        <v>460810</v>
+        <v>3832246.666666667</v>
       </c>
       <c r="G22">
-        <v>45.57539978027344</v>
+        <v>762.3998010253906</v>
       </c>
       <c r="H22">
-        <v>39.14846659342448</v>
+        <v>651.2884000651042</v>
       </c>
       <c r="I22">
-        <v>35.12744995117188</v>
+        <v>607.6588496398925</v>
       </c>
       <c r="J22">
-        <v>32.50509998321533</v>
+        <v>572.7052001953125</v>
       </c>
       <c r="K22">
-        <v>2.234822273254395</v>
+        <v>11.17089080810547</v>
       </c>
       <c r="L22">
-        <v>52.40999984741211</v>
+        <v>886.1799926757812</v>
       </c>
       <c r="M22">
-        <v>154.5965599773032</v>
+        <v>156.269461302709</v>
       </c>
       <c r="N22">
-        <v>0.98</v>
+        <v>7.810425</v>
       </c>
       <c r="O22">
-        <v>1.16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P22">
-        <v>1.01</v>
+        <v>8.15</v>
       </c>
       <c r="Q22">
-        <v>46726000</v>
+        <v>3359000000</v>
       </c>
       <c r="R22">
-        <v>54970000</v>
+        <v>3774000000</v>
       </c>
       <c r="S22">
-        <v>48235000</v>
+        <v>3481000000</v>
       </c>
       <c r="T22">
-        <v>23.15690355833085</v>
+        <v>37.61478163493841</v>
       </c>
       <c r="U22">
-        <v>26.03757140556466</v>
+        <v>42.3331463825014</v>
       </c>
       <c r="V22">
-        <v>23.8034139528916</v>
+        <v>39.86030001145082</v>
       </c>
       <c r="W22" t="s">
         <v>229</v>
@@ -2634,67 +2634,67 @@
         <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E23">
-        <v>877.72998046875</v>
+        <v>51.84000015258789</v>
       </c>
       <c r="F23">
-        <v>3911323.333333333</v>
+        <v>458223.3333333333</v>
       </c>
       <c r="G23">
-        <v>757.1270007324218</v>
+        <v>45.76999977111817</v>
       </c>
       <c r="H23">
-        <v>649.0797334798177</v>
+        <v>39.29159992218018</v>
       </c>
       <c r="I23">
-        <v>605.6592997741699</v>
+        <v>35.27864995002746</v>
       </c>
       <c r="J23">
-        <v>571.3310003662109</v>
+        <v>32.59619997978211</v>
       </c>
       <c r="K23">
-        <v>11.17089080810547</v>
+        <v>2.234822273254395</v>
       </c>
       <c r="L23">
-        <v>886.1799926757812</v>
+        <v>52.40999984741211</v>
       </c>
       <c r="M23">
-        <v>154.0793954262433</v>
+        <v>154.3948777935419</v>
       </c>
       <c r="N23">
-        <v>7.810425</v>
+        <v>0.98</v>
       </c>
       <c r="O23">
-        <v>8.800000000000001</v>
+        <v>1.16</v>
       </c>
       <c r="P23">
-        <v>8.15</v>
+        <v>1.01</v>
       </c>
       <c r="Q23">
-        <v>3359000000</v>
+        <v>46726000</v>
       </c>
       <c r="R23">
-        <v>3774000000</v>
+        <v>54970000</v>
       </c>
       <c r="S23">
-        <v>3481000000</v>
+        <v>48235000</v>
       </c>
       <c r="T23">
-        <v>37.61478163493841</v>
+        <v>23.15690355833085</v>
       </c>
       <c r="U23">
-        <v>42.3331463825014</v>
+        <v>26.03757140556466</v>
       </c>
       <c r="V23">
-        <v>39.86030001145082</v>
+        <v>23.8034139528916</v>
       </c>
       <c r="W23" t="s">
         <v>229</v>
@@ -2705,67 +2705,67 @@
         <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E24">
-        <v>149.5200042724609</v>
+        <v>111.6399993896484</v>
       </c>
       <c r="F24">
-        <v>1320956.666666667</v>
+        <v>1156100</v>
       </c>
       <c r="G24">
-        <v>132.4652008056641</v>
+        <v>92.84059951782227</v>
       </c>
       <c r="H24">
-        <v>108.7658002217611</v>
+        <v>83.40993321736654</v>
       </c>
       <c r="I24">
-        <v>104.4719500732422</v>
+        <v>78.39279985427856</v>
       </c>
       <c r="J24">
-        <v>100.2641499710083</v>
+        <v>73.84199991226197</v>
       </c>
       <c r="K24">
-        <v>0.1500000059604645</v>
+        <v>0.3787146806716919</v>
       </c>
       <c r="L24">
-        <v>150.7100067138672</v>
+        <v>111.6399993896484</v>
       </c>
       <c r="M24">
-        <v>152.1464460765735</v>
+        <v>152.2920661871823</v>
       </c>
       <c r="N24">
-        <v>0.12</v>
+        <v>1.61</v>
       </c>
       <c r="O24">
-        <v>-2.46</v>
+        <v>1.52</v>
       </c>
       <c r="P24">
-        <v>0.4</v>
+        <v>1.72</v>
       </c>
       <c r="Q24">
-        <v>-154116727</v>
+        <v>978000000</v>
       </c>
       <c r="R24">
-        <v>-21223000</v>
+        <v>207000000</v>
       </c>
       <c r="S24">
-        <v>41227000</v>
+        <v>233000000</v>
       </c>
       <c r="T24">
-        <v>-26.57668098589627</v>
+        <v>2.831007931453714</v>
       </c>
       <c r="U24">
-        <v>-11.92544559573846</v>
+        <v>2.544873371035161</v>
       </c>
       <c r="V24">
-        <v>15.86025952242641</v>
+        <v>2.749262536873156</v>
       </c>
       <c r="W24" t="s">
         <v>229</v>
@@ -2776,31 +2776,31 @@
         <v>46</v>
       </c>
       <c r="B25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D25" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E25">
-        <v>82.98000335693359</v>
+        <v>83.51999664306641</v>
       </c>
       <c r="F25">
-        <v>328806.6666666667</v>
+        <v>328350</v>
       </c>
       <c r="G25">
-        <v>74.66860031127929</v>
+        <v>74.99520019531251</v>
       </c>
       <c r="H25">
-        <v>62.23766677856445</v>
+        <v>62.48453341166179</v>
       </c>
       <c r="I25">
-        <v>56.88535013198852</v>
+        <v>57.10800010681152</v>
       </c>
       <c r="J25">
-        <v>52.95020011901855</v>
+        <v>53.10700012207031</v>
       </c>
       <c r="K25">
         <v>3.118403196334839</v>
@@ -2809,7 +2809,7 @@
         <v>87.20999908447266</v>
       </c>
       <c r="M25">
-        <v>151.3026948622085</v>
+        <v>151.7300167863497</v>
       </c>
       <c r="N25">
         <v>4.67</v>
@@ -2847,31 +2847,31 @@
         <v>47</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D26" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E26">
-        <v>31.8799991607666</v>
+        <v>31.76000022888184</v>
       </c>
       <c r="F26">
-        <v>300433.3333333333</v>
+        <v>290303.3333333333</v>
       </c>
       <c r="G26">
-        <v>29.03979991912842</v>
+        <v>29.16239994049072</v>
       </c>
       <c r="H26">
-        <v>23.93659994125366</v>
+        <v>24.04186660766602</v>
       </c>
       <c r="I26">
-        <v>22.07199998378753</v>
+        <v>22.14109998226166</v>
       </c>
       <c r="J26">
-        <v>20.64154999256134</v>
+        <v>20.70329999446869</v>
       </c>
       <c r="K26">
         <v>14.10000038146973</v>
@@ -2880,7 +2880,7 @@
         <v>32.86000061035156</v>
       </c>
       <c r="M26">
-        <v>150.9685591017775</v>
+        <v>151.708502569371</v>
       </c>
       <c r="N26">
         <v>0.14</v>
@@ -2918,67 +2918,67 @@
         <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D27" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E27">
-        <v>111.3099975585938</v>
+        <v>26.18000030517578</v>
       </c>
       <c r="F27">
-        <v>1169416.666666667</v>
+        <v>669986.6666666666</v>
       </c>
       <c r="G27">
-        <v>92.16479949951172</v>
+        <v>22.23420009613037</v>
       </c>
       <c r="H27">
-        <v>83.1493332417806</v>
+        <v>18.88553338368734</v>
       </c>
       <c r="I27">
-        <v>78.12909986495971</v>
+        <v>17.23650003910065</v>
       </c>
       <c r="J27">
-        <v>73.67929992675781</v>
+        <v>15.85175003528595</v>
       </c>
       <c r="K27">
-        <v>0.3787146806716919</v>
+        <v>1.899999976158142</v>
       </c>
       <c r="L27">
-        <v>111.3099975585938</v>
+        <v>26.18000030517578</v>
       </c>
       <c r="M27">
-        <v>150.5905981147945</v>
+        <v>151.3124496785799</v>
       </c>
       <c r="N27">
-        <v>1.61</v>
+        <v>0.75</v>
       </c>
       <c r="O27">
-        <v>1.52</v>
+        <v>0.762</v>
       </c>
       <c r="P27">
-        <v>1.72</v>
+        <v>1.315</v>
       </c>
       <c r="Q27">
-        <v>978000000</v>
+        <v>76661000</v>
       </c>
       <c r="R27">
-        <v>207000000</v>
+        <v>75504000</v>
       </c>
       <c r="S27">
-        <v>233000000</v>
+        <v>128734000</v>
       </c>
       <c r="T27">
-        <v>2.831007931453714</v>
+        <v>22.98177610298196</v>
       </c>
       <c r="U27">
-        <v>2.544873371035161</v>
+        <v>24.50593141948362</v>
       </c>
       <c r="V27">
-        <v>2.749262536873156</v>
+        <v>42.45662290205235</v>
       </c>
       <c r="W27" t="s">
         <v>229</v>
@@ -2989,67 +2989,67 @@
         <v>49</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E28">
-        <v>38.93999862670898</v>
+        <v>122.7399978637695</v>
       </c>
       <c r="F28">
-        <v>1433360</v>
+        <v>302600</v>
       </c>
       <c r="G28">
-        <v>33.55299983978271</v>
+        <v>110.5189999389648</v>
       </c>
       <c r="H28">
-        <v>28.80699996948242</v>
+        <v>89.67393341064454</v>
       </c>
       <c r="I28">
-        <v>28.37529997825623</v>
+        <v>85.43905012130737</v>
       </c>
       <c r="J28">
-        <v>27.31709999084473</v>
+        <v>80.34120012283326</v>
       </c>
       <c r="K28">
-        <v>18.28000068664551</v>
+        <v>8.189999580383301</v>
       </c>
       <c r="L28">
-        <v>47.06000137329102</v>
+        <v>130.3200073242188</v>
       </c>
       <c r="M28">
-        <v>149.8420154480939</v>
+        <v>150.1993502467734</v>
       </c>
       <c r="N28">
-        <v>0.06</v>
+        <v>-1.1</v>
       </c>
       <c r="O28">
-        <v>0.06</v>
+        <v>-1.17</v>
       </c>
       <c r="P28">
-        <v>0.07000000000000001</v>
+        <v>-1.76</v>
       </c>
       <c r="Q28">
-        <v>53508000</v>
+        <v>-129729000</v>
       </c>
       <c r="R28">
-        <v>18068000</v>
+        <v>-32052000</v>
       </c>
       <c r="S28">
-        <v>12175000</v>
+        <v>-45297000</v>
       </c>
       <c r="T28">
-        <v>12.61044271355007</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>13.52030889879972</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>9.931154868916913</v>
+        <v>0</v>
       </c>
       <c r="W28" t="s">
         <v>229</v>
@@ -3060,67 +3060,67 @@
         <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="D29" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E29">
-        <v>24.28000068664551</v>
+        <v>38.88999938964844</v>
       </c>
       <c r="F29">
-        <v>2394390</v>
+        <v>1413806.666666667</v>
       </c>
       <c r="G29">
-        <v>18.8945998954773</v>
+        <v>33.73199981689453</v>
       </c>
       <c r="H29">
-        <v>16.3089333152771</v>
+        <v>28.88519996643067</v>
       </c>
       <c r="I29">
-        <v>16.09835001468658</v>
+        <v>28.43584997177124</v>
       </c>
       <c r="J29">
-        <v>15.44270002365112</v>
+        <v>27.36609999656677</v>
       </c>
       <c r="K29">
-        <v>12.61999988555908</v>
+        <v>18.28000068664551</v>
       </c>
       <c r="L29">
-        <v>24.46999931335449</v>
+        <v>47.06000137329102</v>
       </c>
       <c r="M29">
-        <v>149.6003248189962</v>
+        <v>150.1477084628251</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>53508000</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>18068000</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>12175000</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>12.61044271355007</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>13.52030889879972</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>9.931154868916913</v>
       </c>
       <c r="W29" t="s">
         <v>229</v>
@@ -3134,64 +3134,64 @@
         <v>107</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="D30" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E30">
-        <v>123.3499984741211</v>
+        <v>325.260009765625</v>
       </c>
       <c r="F30">
-        <v>309493.3333333333</v>
+        <v>303986.6666666667</v>
       </c>
       <c r="G30">
-        <v>109.7416000366211</v>
+        <v>254.5346005249023</v>
       </c>
       <c r="H30">
-        <v>89.36900009155273</v>
+        <v>240.0925338745117</v>
       </c>
       <c r="I30">
-        <v>85.17165014266968</v>
+        <v>234.1027503967285</v>
       </c>
       <c r="J30">
-        <v>80.07830011367798</v>
+        <v>230.4159006500244</v>
       </c>
       <c r="K30">
-        <v>8.189999580383301</v>
+        <v>1.363492727279663</v>
       </c>
       <c r="L30">
-        <v>130.3200073242188</v>
+        <v>412.9100646972656</v>
       </c>
       <c r="M30">
-        <v>148.5855292328461</v>
+        <v>148.2450341450622</v>
       </c>
       <c r="N30">
-        <v>-1.1</v>
+        <v>11.92</v>
       </c>
       <c r="O30">
-        <v>-1.17</v>
+        <v>9</v>
       </c>
       <c r="P30">
-        <v>-1.76</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q30">
-        <v>-129729000</v>
+        <v>329600000</v>
       </c>
       <c r="R30">
-        <v>-32052000</v>
+        <v>247700000</v>
       </c>
       <c r="S30">
-        <v>-45297000</v>
+        <v>228700000</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>4.517729621557904</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>3.543532373894882</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>3.279417247411741</v>
       </c>
       <c r="W30" t="s">
         <v>229</v>
@@ -3205,64 +3205,64 @@
         <v>107</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E31">
-        <v>11.07999992370605</v>
+        <v>78.19999694824219</v>
       </c>
       <c r="F31">
-        <v>6123966.666666667</v>
+        <v>2759546.666666667</v>
       </c>
       <c r="G31">
-        <v>9.427799949645996</v>
+        <v>71.2034001159668</v>
       </c>
       <c r="H31">
-        <v>8.434866647720337</v>
+        <v>59.43019989013672</v>
       </c>
       <c r="I31">
-        <v>7.467399989366531</v>
+        <v>54.66484994888306</v>
       </c>
       <c r="J31">
-        <v>6.830949991941452</v>
+        <v>51.13139999389649</v>
       </c>
       <c r="K31">
-        <v>2.809999942779541</v>
+        <v>0.1027423962950706</v>
       </c>
       <c r="L31">
-        <v>13.52000045776367</v>
+        <v>78.66999816894531</v>
       </c>
       <c r="M31">
-        <v>147.2278414277113</v>
+        <v>148.1669075477361</v>
       </c>
       <c r="N31">
-        <v>-0.42</v>
+        <v>2.69</v>
       </c>
       <c r="O31">
-        <v>-0.49</v>
+        <v>3.85</v>
       </c>
       <c r="P31">
-        <v>-0.05</v>
+        <v>2.35</v>
       </c>
       <c r="Q31">
-        <v>-291590000</v>
+        <v>627928000</v>
       </c>
       <c r="R31">
-        <v>-352014000</v>
+        <v>882231000</v>
       </c>
       <c r="S31">
-        <v>-33617000</v>
+        <v>532259000</v>
       </c>
       <c r="T31">
-        <v>-2326.577834516876</v>
+        <v>15.92183813849328</v>
       </c>
       <c r="U31">
-        <v>-2064.356087262491</v>
+        <v>17.05988229829651</v>
       </c>
       <c r="V31">
-        <v>-122.7973407364115</v>
+        <v>14.88569462090853</v>
       </c>
       <c r="W31" t="s">
         <v>229</v>
@@ -3273,67 +3273,67 @@
         <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="D32" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E32">
-        <v>77.37999725341797</v>
+        <v>11.09000015258789</v>
       </c>
       <c r="F32">
-        <v>2755483.333333333</v>
+        <v>6189286.666666667</v>
       </c>
       <c r="G32">
-        <v>70.96480010986328</v>
+        <v>9.480999946594238</v>
       </c>
       <c r="H32">
-        <v>59.20986658732097</v>
+        <v>8.47013331413269</v>
       </c>
       <c r="I32">
-        <v>54.47054996490478</v>
+        <v>7.506949989795685</v>
       </c>
       <c r="J32">
-        <v>50.97720001220703</v>
+        <v>6.862849990129471</v>
       </c>
       <c r="K32">
-        <v>0.1027423962950706</v>
+        <v>2.809999942779541</v>
       </c>
       <c r="L32">
-        <v>78.66999816894531</v>
+        <v>13.52000045776367</v>
       </c>
       <c r="M32">
-        <v>146.7193950997101</v>
+        <v>147.7218641037902</v>
       </c>
       <c r="N32">
-        <v>2.69</v>
+        <v>-0.42</v>
       </c>
       <c r="O32">
-        <v>3.85</v>
+        <v>-0.49</v>
       </c>
       <c r="P32">
-        <v>2.35</v>
+        <v>-0.05</v>
       </c>
       <c r="Q32">
-        <v>627928000</v>
+        <v>-291590000</v>
       </c>
       <c r="R32">
-        <v>882231000</v>
+        <v>-352014000</v>
       </c>
       <c r="S32">
-        <v>532259000</v>
+        <v>-33617000</v>
       </c>
       <c r="T32">
-        <v>15.92183813849328</v>
+        <v>-2326.577834516876</v>
       </c>
       <c r="U32">
-        <v>17.05988229829651</v>
+        <v>-2064.356087262491</v>
       </c>
       <c r="V32">
-        <v>14.88569462090853</v>
+        <v>-122.7973407364115</v>
       </c>
       <c r="W32" t="s">
         <v>229</v>
@@ -3344,70 +3344,70 @@
         <v>54</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="D33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E33">
-        <v>95.27999877929688</v>
+        <v>24.07999992370605</v>
       </c>
       <c r="F33">
-        <v>409080</v>
+        <v>2425276.666666667</v>
       </c>
       <c r="G33">
-        <v>85.45779983520508</v>
+        <v>19.05719989776611</v>
       </c>
       <c r="H33">
-        <v>72.30326644897461</v>
+        <v>16.35779998143514</v>
       </c>
       <c r="I33">
-        <v>66.09839986801147</v>
+        <v>16.14085001468658</v>
       </c>
       <c r="J33">
-        <v>61.68469985961914</v>
+        <v>15.45365002155304</v>
       </c>
       <c r="K33">
-        <v>1.669681549072266</v>
+        <v>12.61999988555908</v>
       </c>
       <c r="L33">
-        <v>96.55000305175781</v>
+        <v>24.46999931335449</v>
       </c>
       <c r="M33">
-        <v>146.4474740806352</v>
+        <v>146.9470351554011</v>
       </c>
       <c r="N33">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>22222000</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>32408000</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>105259000</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>19.36321494545328</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>27.68613045149716</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>52.01237319207602</v>
+        <v>0</v>
       </c>
       <c r="W33" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="34" spans="1:23">
@@ -3415,70 +3415,70 @@
         <v>55</v>
       </c>
       <c r="B34" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C34" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D34" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E34">
-        <v>25.30999946594238</v>
+        <v>95.30000305175781</v>
       </c>
       <c r="F34">
-        <v>649596.6666666666</v>
+        <v>409736.6666666667</v>
       </c>
       <c r="G34">
-        <v>22.11760009765625</v>
+        <v>85.99759994506836</v>
       </c>
       <c r="H34">
-        <v>18.80580005009969</v>
+        <v>72.60026646931966</v>
       </c>
       <c r="I34">
-        <v>17.15330003738403</v>
+        <v>66.35374988555908</v>
       </c>
       <c r="J34">
-        <v>15.78295002937317</v>
+        <v>61.86034984588623</v>
       </c>
       <c r="K34">
-        <v>1.899999976158142</v>
+        <v>1.669681549072266</v>
       </c>
       <c r="L34">
-        <v>25.30999946594238</v>
+        <v>96.55000305175781</v>
       </c>
       <c r="M34">
-        <v>145.0637348273295</v>
+        <v>145.4778827199088</v>
       </c>
       <c r="N34">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="O34">
-        <v>0.762</v>
+        <v>1.08</v>
       </c>
       <c r="P34">
-        <v>1.315</v>
+        <v>3.58</v>
       </c>
       <c r="Q34">
-        <v>76661000</v>
+        <v>22222000</v>
       </c>
       <c r="R34">
-        <v>75504000</v>
+        <v>32408000</v>
       </c>
       <c r="S34">
-        <v>128734000</v>
+        <v>105259000</v>
       </c>
       <c r="T34">
-        <v>22.98177610298196</v>
+        <v>19.36321494545328</v>
       </c>
       <c r="U34">
-        <v>24.50593141948362</v>
+        <v>27.68613045149716</v>
       </c>
       <c r="V34">
-        <v>42.45662290205235</v>
+        <v>52.01237319207602</v>
       </c>
       <c r="W34" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="35" spans="1:23">
@@ -3486,67 +3486,67 @@
         <v>56</v>
       </c>
       <c r="B35" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C35" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="D35" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E35">
-        <v>84.54000091552734</v>
+        <v>358.8699951171875</v>
       </c>
       <c r="F35">
-        <v>531093.3333333334</v>
+        <v>529723.3333333334</v>
       </c>
       <c r="G35">
-        <v>70.33919998168945</v>
+        <v>303.9289996337891</v>
       </c>
       <c r="H35">
-        <v>62.09826657613119</v>
+        <v>273.5848001098633</v>
       </c>
       <c r="I35">
-        <v>60.61059995651245</v>
+        <v>258.0525497436523</v>
       </c>
       <c r="J35">
-        <v>58.17604995727539</v>
+        <v>245.5595498657227</v>
       </c>
       <c r="K35">
-        <v>7.03000020980835</v>
+        <v>4.533332824707031</v>
       </c>
       <c r="L35">
-        <v>84.54000091552734</v>
+        <v>364.4500122070312</v>
       </c>
       <c r="M35">
-        <v>144.3793005371247</v>
+        <v>145.3445901710574</v>
       </c>
       <c r="N35">
-        <v>1.95</v>
+        <v>3.67</v>
       </c>
       <c r="O35">
-        <v>0.88</v>
+        <v>2.65</v>
       </c>
       <c r="P35">
-        <v>0.25</v>
+        <v>2.85</v>
       </c>
       <c r="Q35">
-        <v>154800000</v>
+        <v>97891000</v>
       </c>
       <c r="R35">
-        <v>73300000</v>
+        <v>70862000</v>
       </c>
       <c r="S35">
-        <v>24800000</v>
+        <v>76097000</v>
       </c>
       <c r="T35">
-        <v>6.409407088439881</v>
+        <v>13.41779508498947</v>
       </c>
       <c r="U35">
-        <v>3.721945770285366</v>
+        <v>10.80664789866499</v>
       </c>
       <c r="V35">
-        <v>1.431622698146972</v>
+        <v>11.52050988971061</v>
       </c>
       <c r="W35" t="s">
         <v>229</v>
@@ -3557,67 +3557,67 @@
         <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C36" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D36" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E36">
-        <v>315.5499877929688</v>
+        <v>79.90000152587891</v>
       </c>
       <c r="F36">
-        <v>300346.6666666667</v>
+        <v>1760630</v>
       </c>
       <c r="G36">
-        <v>252.4708004760742</v>
+        <v>70.77319999694824</v>
       </c>
       <c r="H36">
-        <v>239.4930671183268</v>
+        <v>61.32293342590332</v>
       </c>
       <c r="I36">
-        <v>233.6086003112793</v>
+        <v>56.97220012664795</v>
       </c>
       <c r="J36">
-        <v>230.4890005493164</v>
+        <v>53.74840005874634</v>
       </c>
       <c r="K36">
-        <v>1.363492727279663</v>
+        <v>0.5319142937660217</v>
       </c>
       <c r="L36">
-        <v>412.9100646972656</v>
+        <v>79.90000152587891</v>
       </c>
       <c r="M36">
-        <v>143.2760351851946</v>
+        <v>144.9718432923428</v>
       </c>
       <c r="N36">
-        <v>11.92</v>
+        <v>5.63</v>
       </c>
       <c r="O36">
-        <v>9</v>
+        <v>1.7</v>
       </c>
       <c r="P36">
-        <v>8.300000000000001</v>
+        <v>2.85</v>
       </c>
       <c r="Q36">
-        <v>329600000</v>
+        <v>640536000</v>
       </c>
       <c r="R36">
-        <v>247700000</v>
+        <v>191530000</v>
       </c>
       <c r="S36">
-        <v>228700000</v>
+        <v>320216000</v>
       </c>
       <c r="T36">
-        <v>4.517729621557904</v>
+        <v>17.25519606781436</v>
       </c>
       <c r="U36">
-        <v>3.543532373894882</v>
+        <v>10.75909085036308</v>
       </c>
       <c r="V36">
-        <v>3.279417247411741</v>
+        <v>12.7729829408224</v>
       </c>
       <c r="W36" t="s">
         <v>229</v>
@@ -3628,67 +3628,67 @@
         <v>58</v>
       </c>
       <c r="B37" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C37" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D37" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E37">
-        <v>78.90000152587891</v>
+        <v>20.95999908447266</v>
       </c>
       <c r="F37">
-        <v>1853583.333333333</v>
+        <v>860880</v>
       </c>
       <c r="G37">
-        <v>70.43599998474122</v>
+        <v>19.88539993286133</v>
       </c>
       <c r="H37">
-        <v>61.11260007222494</v>
+        <v>17.47233329772949</v>
       </c>
       <c r="I37">
-        <v>56.7874001121521</v>
+        <v>15.80524997711182</v>
       </c>
       <c r="J37">
-        <v>53.60510005950928</v>
+        <v>15.07380000114441</v>
       </c>
       <c r="K37">
-        <v>0.5319142937660217</v>
+        <v>9.220000267028809</v>
       </c>
       <c r="L37">
-        <v>79.06999969482422</v>
+        <v>22.13999938964844</v>
       </c>
       <c r="M37">
-        <v>142.7243839431673</v>
+        <v>143.9441540201111</v>
       </c>
       <c r="N37">
-        <v>5.63</v>
+        <v>0.12</v>
       </c>
       <c r="O37">
-        <v>1.7</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="P37">
-        <v>2.85</v>
+        <v>0.14</v>
       </c>
       <c r="Q37">
-        <v>640536000</v>
+        <v>24732000</v>
       </c>
       <c r="R37">
-        <v>191530000</v>
+        <v>13726000</v>
       </c>
       <c r="S37">
-        <v>320216000</v>
+        <v>27460000</v>
       </c>
       <c r="T37">
-        <v>17.25519606781436</v>
+        <v>4.982463067683896</v>
       </c>
       <c r="U37">
-        <v>10.75909085036308</v>
+        <v>2.904020903195777</v>
       </c>
       <c r="V37">
-        <v>12.7729829408224</v>
+        <v>5.375344278468673</v>
       </c>
       <c r="W37" t="s">
         <v>229</v>
@@ -3699,67 +3699,67 @@
         <v>59</v>
       </c>
       <c r="B38" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C38" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="D38" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E38">
-        <v>31.94000053405762</v>
+        <v>250.2299957275391</v>
       </c>
       <c r="F38">
-        <v>1488206.666666667</v>
+        <v>6934630</v>
       </c>
       <c r="G38">
-        <v>28.97049991607666</v>
+        <v>218.6271997070313</v>
       </c>
       <c r="H38">
-        <v>24.92496664683024</v>
+        <v>186.5971332804362</v>
       </c>
       <c r="I38">
-        <v>22.78894999027252</v>
+        <v>180.9470998382568</v>
       </c>
       <c r="J38">
-        <v>21.51567502498627</v>
+        <v>174.496849899292</v>
       </c>
       <c r="K38">
-        <v>4.052896976470947</v>
+        <v>13.18666744232178</v>
       </c>
       <c r="L38">
-        <v>31.94000053405762</v>
+        <v>257.8800048828125</v>
       </c>
       <c r="M38">
-        <v>142.3935181723166</v>
+        <v>143.8215703284683</v>
       </c>
       <c r="N38">
-        <v>-0.23</v>
+        <v>0.06</v>
       </c>
       <c r="O38">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="P38">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="Q38">
-        <v>-16058000</v>
+        <v>20000000</v>
       </c>
       <c r="R38">
-        <v>26801000</v>
+        <v>84200000</v>
       </c>
       <c r="S38">
-        <v>29397000</v>
+        <v>107800000</v>
       </c>
       <c r="T38">
-        <v>-6.97067696915764</v>
+        <v>1.279263144428809</v>
       </c>
       <c r="U38">
-        <v>9.771009621168758</v>
+        <v>5.087305902966587</v>
       </c>
       <c r="V38">
-        <v>10.04277154121031</v>
+        <v>6.264164100180138</v>
       </c>
       <c r="W38" t="s">
         <v>230</v>
@@ -3770,67 +3770,67 @@
         <v>60</v>
       </c>
       <c r="B39" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D39" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E39">
-        <v>21.04999923706055</v>
+        <v>177.1699981689453</v>
       </c>
       <c r="F39">
-        <v>865560</v>
+        <v>634616.6666666666</v>
       </c>
       <c r="G39">
-        <v>19.86759994506836</v>
+        <v>145.0614001464844</v>
       </c>
       <c r="H39">
-        <v>17.41993330637614</v>
+        <v>132.174200592041</v>
       </c>
       <c r="I39">
-        <v>15.75579998016357</v>
+        <v>126.4774004364014</v>
       </c>
       <c r="J39">
-        <v>15.04244999885559</v>
+        <v>122.3506503295898</v>
       </c>
       <c r="K39">
-        <v>9.220000267028809</v>
+        <v>1.039746522903442</v>
       </c>
       <c r="L39">
-        <v>22.13999938964844</v>
+        <v>177.1699981689453</v>
       </c>
       <c r="M39">
-        <v>142.0221432201896</v>
+        <v>143.4652562835982</v>
       </c>
       <c r="N39">
-        <v>0.12</v>
+        <v>6.31</v>
       </c>
       <c r="O39">
-        <v>0.07000000000000001</v>
+        <v>5.716567</v>
       </c>
       <c r="P39">
-        <v>0.14</v>
+        <v>6.07</v>
       </c>
       <c r="Q39">
-        <v>24732000</v>
+        <v>352600000</v>
       </c>
       <c r="R39">
-        <v>13726000</v>
+        <v>286400000</v>
       </c>
       <c r="S39">
-        <v>27460000</v>
+        <v>288700000</v>
       </c>
       <c r="T39">
-        <v>4.982463067683896</v>
+        <v>5.28952895289529</v>
       </c>
       <c r="U39">
-        <v>2.904020903195777</v>
+        <v>4.276541735105271</v>
       </c>
       <c r="V39">
-        <v>5.375344278468673</v>
+        <v>4.511853970337725</v>
       </c>
       <c r="W39" t="s">
         <v>229</v>
@@ -3844,64 +3844,64 @@
         <v>106</v>
       </c>
       <c r="C40" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="D40" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E40">
-        <v>110.0400009155273</v>
+        <v>83.37000274658203</v>
       </c>
       <c r="F40">
-        <v>380480</v>
+        <v>526633.3333333334</v>
       </c>
       <c r="G40">
-        <v>101.4846000671387</v>
+        <v>70.82940002441406</v>
       </c>
       <c r="H40">
-        <v>86.8712000020345</v>
+        <v>62.2607332611084</v>
       </c>
       <c r="I40">
-        <v>82.74309991836547</v>
+        <v>60.75819997787475</v>
       </c>
       <c r="J40">
-        <v>78.88329996109009</v>
+        <v>58.24099994659424</v>
       </c>
       <c r="K40">
-        <v>20.81999969482422</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="L40">
-        <v>116.4700012207031</v>
+        <v>84.54000091552734</v>
       </c>
       <c r="M40">
-        <v>141.9695973795569</v>
+        <v>142.9079512128387</v>
       </c>
       <c r="N40">
-        <v>1.05</v>
+        <v>1.95</v>
       </c>
       <c r="O40">
-        <v>1.34</v>
+        <v>0.88</v>
       </c>
       <c r="P40">
-        <v>0.59</v>
+        <v>0.25</v>
       </c>
       <c r="Q40">
-        <v>52215000</v>
+        <v>154800000</v>
       </c>
       <c r="R40">
-        <v>66214000</v>
+        <v>73300000</v>
       </c>
       <c r="S40">
-        <v>29068000</v>
+        <v>24800000</v>
       </c>
       <c r="T40">
-        <v>20.53663083621432</v>
+        <v>6.409407088439881</v>
       </c>
       <c r="U40">
-        <v>26.14364117345126</v>
+        <v>3.721945770285366</v>
       </c>
       <c r="V40">
-        <v>14.59493384881882</v>
+        <v>1.431622698146972</v>
       </c>
       <c r="W40" t="s">
         <v>229</v>
@@ -3912,70 +3912,70 @@
         <v>62</v>
       </c>
       <c r="B41" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C41" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D41" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E41">
-        <v>247.4700012207031</v>
+        <v>51.20999908447266</v>
       </c>
       <c r="F41">
-        <v>7046970</v>
+        <v>1931023.333333333</v>
       </c>
       <c r="G41">
-        <v>217.3249996948242</v>
+        <v>47.42</v>
       </c>
       <c r="H41">
-        <v>186.1182666015625</v>
+        <v>39.96759995778402</v>
       </c>
       <c r="I41">
-        <v>180.5515498352051</v>
+        <v>37.11009996414185</v>
       </c>
       <c r="J41">
-        <v>174.3455332183838</v>
+        <v>34.91004997253418</v>
       </c>
       <c r="K41">
-        <v>13.18666744232178</v>
+        <v>1.498309969902039</v>
       </c>
       <c r="L41">
-        <v>257.8800048828125</v>
+        <v>66.26741027832031</v>
       </c>
       <c r="M41">
-        <v>141.7159359795624</v>
+        <v>141.3006451766136</v>
       </c>
       <c r="N41">
-        <v>0.06</v>
+        <v>2.47</v>
       </c>
       <c r="O41">
-        <v>0.25</v>
+        <v>1.45</v>
       </c>
       <c r="P41">
-        <v>0.31</v>
+        <v>1.94</v>
       </c>
       <c r="Q41">
-        <v>20000000</v>
+        <v>216410000</v>
       </c>
       <c r="R41">
-        <v>84200000</v>
+        <v>125500000</v>
       </c>
       <c r="S41">
-        <v>107800000</v>
+        <v>164442000</v>
       </c>
       <c r="T41">
-        <v>1.279263144428809</v>
+        <v>11.15498213945145</v>
       </c>
       <c r="U41">
-        <v>5.087305902966587</v>
+        <v>9.065862224899842</v>
       </c>
       <c r="V41">
-        <v>6.264164100180138</v>
+        <v>9.315159438876666</v>
       </c>
       <c r="W41" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="42" spans="1:23">
@@ -3983,67 +3983,67 @@
         <v>63</v>
       </c>
       <c r="B42" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C42" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D42" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E42">
-        <v>349.9500122070312</v>
+        <v>197.2700042724609</v>
       </c>
       <c r="F42">
-        <v>524623.3333333334</v>
+        <v>384186.6666666667</v>
       </c>
       <c r="G42">
-        <v>301.95</v>
+        <v>182.2733996582031</v>
       </c>
       <c r="H42">
-        <v>272.7774001057942</v>
+        <v>152.5387326558431</v>
       </c>
       <c r="I42">
-        <v>257.2050497436524</v>
+        <v>145.698599319458</v>
       </c>
       <c r="J42">
-        <v>245.1853998565674</v>
+        <v>140.5115492248535</v>
       </c>
       <c r="K42">
-        <v>4.533332824707031</v>
+        <v>0.8828129768371582</v>
       </c>
       <c r="L42">
-        <v>364.4500122070312</v>
+        <v>199.8800048828125</v>
       </c>
       <c r="M42">
-        <v>140.8550692950035</v>
+        <v>141.2256668516544</v>
       </c>
       <c r="N42">
-        <v>3.67</v>
+        <v>0.47</v>
       </c>
       <c r="O42">
-        <v>2.65</v>
+        <v>0.6</v>
       </c>
       <c r="P42">
-        <v>2.85</v>
+        <v>0.62</v>
       </c>
       <c r="Q42">
-        <v>97891000</v>
+        <v>29674000</v>
       </c>
       <c r="R42">
-        <v>70862000</v>
+        <v>37868000</v>
       </c>
       <c r="S42">
-        <v>76097000</v>
+        <v>38791000</v>
       </c>
       <c r="T42">
-        <v>13.41779508498947</v>
+        <v>14.97922776765387</v>
       </c>
       <c r="U42">
-        <v>10.80664789866499</v>
+        <v>19.11530870304841</v>
       </c>
       <c r="V42">
-        <v>11.52050988971061</v>
+        <v>17.55145624917991</v>
       </c>
       <c r="W42" t="s">
         <v>229</v>
@@ -4054,67 +4054,67 @@
         <v>64</v>
       </c>
       <c r="B43" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C43" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D43" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E43">
-        <v>50.86000061035156</v>
+        <v>145.7899932861328</v>
       </c>
       <c r="F43">
-        <v>1884523.333333333</v>
+        <v>1339783.333333333</v>
       </c>
       <c r="G43">
-        <v>47.24440002441406</v>
+        <v>133.5200006103516</v>
       </c>
       <c r="H43">
-        <v>39.83959995269775</v>
+        <v>108.9818668619792</v>
       </c>
       <c r="I43">
-        <v>36.9941499710083</v>
+        <v>104.7097500228882</v>
       </c>
       <c r="J43">
-        <v>34.81514996528625</v>
+        <v>100.3948999786377</v>
       </c>
       <c r="K43">
-        <v>1.498309969902039</v>
+        <v>0.1500000059604645</v>
       </c>
       <c r="L43">
-        <v>66.26741027832031</v>
+        <v>150.7100067138672</v>
       </c>
       <c r="M43">
-        <v>140.7824265539416</v>
+        <v>141.0569639842882</v>
       </c>
       <c r="N43">
-        <v>2.47</v>
+        <v>0.12</v>
       </c>
       <c r="O43">
-        <v>1.45</v>
+        <v>-2.46</v>
       </c>
       <c r="P43">
-        <v>1.94</v>
+        <v>0.4</v>
       </c>
       <c r="Q43">
-        <v>216410000</v>
+        <v>-154116727</v>
       </c>
       <c r="R43">
-        <v>125500000</v>
+        <v>-21223000</v>
       </c>
       <c r="S43">
-        <v>164442000</v>
+        <v>41227000</v>
       </c>
       <c r="T43">
-        <v>11.15498213945145</v>
+        <v>-26.57668098589627</v>
       </c>
       <c r="U43">
-        <v>9.065862224899842</v>
+        <v>-11.92544559573846</v>
       </c>
       <c r="V43">
-        <v>9.315159438876666</v>
+        <v>15.86025952242641</v>
       </c>
       <c r="W43" t="s">
         <v>229</v>
@@ -4125,31 +4125,31 @@
         <v>65</v>
       </c>
       <c r="B44" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C44" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D44" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E44">
-        <v>48.45999908447266</v>
+        <v>48.65999984741211</v>
       </c>
       <c r="F44">
-        <v>11840323.33333333</v>
+        <v>11942060</v>
       </c>
       <c r="G44">
-        <v>38.95140014648437</v>
+        <v>39.25800010681152</v>
       </c>
       <c r="H44">
-        <v>36.91006661732992</v>
+        <v>36.99859994252522</v>
       </c>
       <c r="I44">
-        <v>35.73919997215271</v>
+        <v>35.82669997215271</v>
       </c>
       <c r="J44">
-        <v>34.52229994773865</v>
+        <v>34.55434994697571</v>
       </c>
       <c r="K44">
         <v>3.490809917449951</v>
@@ -4158,7 +4158,7 @@
         <v>62.26396942138672</v>
       </c>
       <c r="M44">
-        <v>140.0255653767337</v>
+        <v>140.7356501155672</v>
       </c>
       <c r="N44">
         <v>1.08</v>
@@ -4196,67 +4196,67 @@
         <v>66</v>
       </c>
       <c r="B45" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C45" t="s">
         <v>139</v>
       </c>
       <c r="D45" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E45">
-        <v>173.3300018310547</v>
+        <v>31.70000076293945</v>
       </c>
       <c r="F45">
-        <v>624376.6666666666</v>
+        <v>813766.6666666666</v>
       </c>
       <c r="G45">
-        <v>144.1546002197266</v>
+        <v>30.07259983062744</v>
       </c>
       <c r="H45">
-        <v>131.8008672587077</v>
+        <v>24.86789993286133</v>
       </c>
       <c r="I45">
-        <v>126.1292504501343</v>
+        <v>23.23862494468689</v>
       </c>
       <c r="J45">
-        <v>122.2649003219605</v>
+        <v>22.0960749912262</v>
       </c>
       <c r="K45">
-        <v>1.039746522903442</v>
+        <v>0.1500000059604645</v>
       </c>
       <c r="L45">
-        <v>173.3300018310547</v>
+        <v>38.15000152587891</v>
       </c>
       <c r="M45">
-        <v>139.3020539666354</v>
+        <v>139.9960415506373</v>
       </c>
       <c r="N45">
-        <v>6.31</v>
+        <v>0.01</v>
       </c>
       <c r="O45">
-        <v>5.716567</v>
+        <v>-0.02</v>
       </c>
       <c r="P45">
-        <v>6.07</v>
+        <v>-0.36</v>
       </c>
       <c r="Q45">
-        <v>352600000</v>
+        <v>668000</v>
       </c>
       <c r="R45">
-        <v>286400000</v>
+        <v>-934000</v>
       </c>
       <c r="S45">
-        <v>288700000</v>
+        <v>-21005000</v>
       </c>
       <c r="T45">
-        <v>5.28952895289529</v>
+        <v>0.1908331524036978</v>
       </c>
       <c r="U45">
-        <v>4.276541735105271</v>
+        <v>-0.2433083686095734</v>
       </c>
       <c r="V45">
-        <v>4.511853970337725</v>
+        <v>-5.378119847195338</v>
       </c>
       <c r="W45" t="s">
         <v>229</v>
@@ -4270,67 +4270,67 @@
         <v>106</v>
       </c>
       <c r="C46" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D46" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E46">
-        <v>195.1999969482422</v>
+        <v>31.80999946594238</v>
       </c>
       <c r="F46">
-        <v>383666.6666666667</v>
+        <v>1497226.666666667</v>
       </c>
       <c r="G46">
-        <v>181.7007995605469</v>
+        <v>29.04249992370605</v>
       </c>
       <c r="H46">
-        <v>152.0705326334635</v>
+        <v>25.02323331197103</v>
       </c>
       <c r="I46">
-        <v>145.3798992919922</v>
+        <v>22.86844998836517</v>
       </c>
       <c r="J46">
-        <v>140.3048992156982</v>
+        <v>21.57317502498627</v>
       </c>
       <c r="K46">
-        <v>0.8828129768371582</v>
+        <v>4.052896976470947</v>
       </c>
       <c r="L46">
-        <v>199.8800048828125</v>
+        <v>31.94000053405762</v>
       </c>
       <c r="M46">
-        <v>138.9938848082165</v>
+        <v>139.906775555251</v>
       </c>
       <c r="N46">
-        <v>0.47</v>
+        <v>-0.23</v>
       </c>
       <c r="O46">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="P46">
-        <v>0.62</v>
+        <v>0.22</v>
       </c>
       <c r="Q46">
-        <v>29674000</v>
+        <v>-16058000</v>
       </c>
       <c r="R46">
-        <v>37868000</v>
+        <v>26801000</v>
       </c>
       <c r="S46">
-        <v>38791000</v>
+        <v>29397000</v>
       </c>
       <c r="T46">
-        <v>14.97922776765387</v>
+        <v>-6.97067696915764</v>
       </c>
       <c r="U46">
-        <v>19.11530870304841</v>
+        <v>9.771009621168758</v>
       </c>
       <c r="V46">
-        <v>17.55145624917991</v>
+        <v>10.04277154121031</v>
       </c>
       <c r="W46" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="47" spans="1:23">
@@ -4341,64 +4341,64 @@
         <v>109</v>
       </c>
       <c r="C47" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="D47" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E47">
-        <v>48.18999862670898</v>
+        <v>74.62999725341797</v>
       </c>
       <c r="F47">
-        <v>1256956.666666667</v>
+        <v>784123.3333333334</v>
       </c>
       <c r="G47">
-        <v>45.09459991455078</v>
+        <v>62.28579971313476</v>
       </c>
       <c r="H47">
-        <v>38.17013328552246</v>
+        <v>58.51693321228027</v>
       </c>
       <c r="I47">
-        <v>35.14690001487732</v>
+        <v>53.37334990501404</v>
       </c>
       <c r="J47">
-        <v>32.90820001602173</v>
+        <v>49.87364994049072</v>
       </c>
       <c r="K47">
-        <v>7.050000190734863</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="L47">
-        <v>48.77000045776367</v>
+        <v>74.62999725341797</v>
       </c>
       <c r="M47">
-        <v>138.3471213178586</v>
+        <v>139.8026609577829</v>
       </c>
       <c r="N47">
-        <v>2.72</v>
+        <v>0.39</v>
       </c>
       <c r="O47">
-        <v>2.51</v>
+        <v>0.99</v>
       </c>
       <c r="P47">
-        <v>1.74</v>
+        <v>0.97</v>
       </c>
       <c r="Q47">
-        <v>309779000</v>
+        <v>28000000</v>
       </c>
       <c r="R47">
-        <v>275331000</v>
+        <v>72000000</v>
       </c>
       <c r="S47">
-        <v>191051000</v>
+        <v>72000000</v>
       </c>
       <c r="T47">
-        <v>15.2252187606284</v>
+        <v>2.5</v>
       </c>
       <c r="U47">
-        <v>11.04803689701082</v>
+        <v>5.955334987593052</v>
       </c>
       <c r="V47">
-        <v>11.49623583737951</v>
+        <v>6.070826306913997</v>
       </c>
       <c r="W47" t="s">
         <v>229</v>
@@ -4409,40 +4409,40 @@
         <v>69</v>
       </c>
       <c r="B48" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C48" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D48" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E48">
-        <v>108.9000015258789</v>
+        <v>109.3000030517578</v>
       </c>
       <c r="F48">
-        <v>349333.3333333333</v>
+        <v>330960</v>
       </c>
       <c r="G48">
-        <v>95.99740020751953</v>
+        <v>96.5352001953125</v>
       </c>
       <c r="H48">
-        <v>86.55633316040038</v>
+        <v>86.77593317667643</v>
       </c>
       <c r="I48">
-        <v>81.44874982833862</v>
+        <v>81.68179985046386</v>
       </c>
       <c r="J48">
-        <v>77.28949989318848</v>
+        <v>77.47779987335205</v>
       </c>
       <c r="K48">
         <v>5.466728210449219</v>
       </c>
       <c r="L48">
-        <v>108.9000015258789</v>
+        <v>109.3000030517578</v>
       </c>
       <c r="M48">
-        <v>138.2025283365322</v>
+        <v>139.6430871945962</v>
       </c>
       <c r="N48">
         <v>0.84</v>
@@ -4480,67 +4480,67 @@
         <v>70</v>
       </c>
       <c r="B49" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C49" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D49" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E49">
-        <v>31.20999908447266</v>
+        <v>48.65000152587891</v>
       </c>
       <c r="F49">
-        <v>1198183.333333333</v>
+        <v>1229433.333333333</v>
       </c>
       <c r="G49">
-        <v>30.63020008087158</v>
+        <v>45.22599990844726</v>
       </c>
       <c r="H49">
-        <v>25.12433339436849</v>
+        <v>38.28939996083577</v>
       </c>
       <c r="I49">
-        <v>22.98470005512237</v>
+        <v>35.26940002441406</v>
       </c>
       <c r="J49">
-        <v>21.48095004558563</v>
+        <v>33.01105002403259</v>
       </c>
       <c r="K49">
-        <v>6.139999866485596</v>
+        <v>7.050000190734863</v>
       </c>
       <c r="L49">
-        <v>33.15999984741211</v>
+        <v>48.77000045776367</v>
       </c>
       <c r="M49">
-        <v>138.1100957343923</v>
+        <v>139.3553137449881</v>
       </c>
       <c r="N49">
-        <v>1.45</v>
+        <v>2.72</v>
       </c>
       <c r="O49">
-        <v>1.98</v>
+        <v>2.51</v>
       </c>
       <c r="P49">
-        <v>0.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q49">
-        <v>149226000</v>
+        <v>309779000</v>
       </c>
       <c r="R49">
-        <v>202973000</v>
+        <v>275331000</v>
       </c>
       <c r="S49">
-        <v>74742000</v>
+        <v>191051000</v>
       </c>
       <c r="T49">
-        <v>13.92298534422595</v>
+        <v>15.2252187606284</v>
       </c>
       <c r="U49">
-        <v>13.32889853191875</v>
+        <v>11.04803689701082</v>
       </c>
       <c r="V49">
-        <v>9.586474121445089</v>
+        <v>11.49623583737951</v>
       </c>
       <c r="W49" t="s">
         <v>229</v>
@@ -4554,64 +4554,64 @@
         <v>107</v>
       </c>
       <c r="C50" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D50" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E50">
-        <v>31.70999908447266</v>
+        <v>178.3699951171875</v>
       </c>
       <c r="F50">
-        <v>796810</v>
+        <v>300920</v>
       </c>
       <c r="G50">
-        <v>29.99339981079101</v>
+        <v>150.0002001953125</v>
       </c>
       <c r="H50">
-        <v>24.78809992472331</v>
+        <v>137.6920003763835</v>
       </c>
       <c r="I50">
-        <v>23.17387494087219</v>
+        <v>130.817250289917</v>
       </c>
       <c r="J50">
-        <v>22.04297499656677</v>
+        <v>125.8424003982544</v>
       </c>
       <c r="K50">
-        <v>0.1500000059604645</v>
+        <v>2.075098752975464</v>
       </c>
       <c r="L50">
-        <v>38.15000152587891</v>
+        <v>178.3699951171875</v>
       </c>
       <c r="M50">
-        <v>137.5215493880937</v>
+        <v>138.51020449617</v>
       </c>
       <c r="N50">
-        <v>0.01</v>
+        <v>4.61</v>
       </c>
       <c r="O50">
-        <v>-0.02</v>
+        <v>4.21</v>
       </c>
       <c r="P50">
-        <v>-0.36</v>
+        <v>4.31</v>
       </c>
       <c r="Q50">
-        <v>668000</v>
+        <v>340100000</v>
       </c>
       <c r="R50">
-        <v>-934000</v>
+        <v>298000000</v>
       </c>
       <c r="S50">
-        <v>-21005000</v>
+        <v>298300000</v>
       </c>
       <c r="T50">
-        <v>0.1908331524036978</v>
+        <v>4.914242778909648</v>
       </c>
       <c r="U50">
-        <v>-0.2433083686095734</v>
+        <v>4.24997860749023</v>
       </c>
       <c r="V50">
-        <v>-5.378119847195338</v>
+        <v>4.064586455920425</v>
       </c>
       <c r="W50" t="s">
         <v>229</v>
@@ -4622,70 +4622,70 @@
         <v>72</v>
       </c>
       <c r="B51" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C51" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D51" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E51">
-        <v>327.25</v>
+        <v>46.77000045776367</v>
       </c>
       <c r="F51">
-        <v>319770</v>
+        <v>2710540</v>
       </c>
       <c r="G51">
-        <v>319.0581988525391</v>
+        <v>37.80199996948242</v>
       </c>
       <c r="H51">
-        <v>274.2661998494466</v>
+        <v>32.7364999516805</v>
       </c>
       <c r="I51">
-        <v>251.6793000793457</v>
+        <v>32.22104994773865</v>
       </c>
       <c r="J51">
-        <v>236.3513500976563</v>
+        <v>29.75299998283386</v>
       </c>
       <c r="K51">
-        <v>36.5</v>
+        <v>13.1899995803833</v>
       </c>
       <c r="L51">
-        <v>344.0599975585938</v>
+        <v>46.91999816894531</v>
       </c>
       <c r="M51">
-        <v>137.3059790948429</v>
+        <v>137.6989336084455</v>
       </c>
       <c r="N51">
-        <v>-0.06</v>
+        <v>-0.55</v>
       </c>
       <c r="O51">
-        <v>0.1</v>
+        <v>-0.51</v>
       </c>
       <c r="P51">
-        <v>0.22</v>
+        <v>-0.54</v>
       </c>
       <c r="Q51">
-        <v>-2271000</v>
+        <v>-76858000</v>
       </c>
       <c r="R51">
-        <v>3877000</v>
+        <v>-23224000</v>
       </c>
       <c r="S51">
-        <v>8562000</v>
+        <v>-25646000</v>
       </c>
       <c r="T51">
-        <v>-1.062814140903603</v>
+        <v>0</v>
       </c>
       <c r="U51">
-        <v>1.752585708086214</v>
+        <v>0</v>
       </c>
       <c r="V51">
-        <v>3.546839658986404</v>
+        <v>0</v>
       </c>
       <c r="W51" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="52" spans="1:23">
@@ -4693,67 +4693,67 @@
         <v>73</v>
       </c>
       <c r="B52" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C52" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D52" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E52">
-        <v>46.91999816894531</v>
+        <v>27.65999984741211</v>
       </c>
       <c r="F52">
-        <v>2677996.666666667</v>
+        <v>1091536.666666667</v>
       </c>
       <c r="G52">
-        <v>37.52419998168946</v>
+        <v>24.25220005035401</v>
       </c>
       <c r="H52">
-        <v>32.66416660308838</v>
+        <v>22.07539994557699</v>
       </c>
       <c r="I52">
-        <v>32.08084994316101</v>
+        <v>20.61684997558594</v>
       </c>
       <c r="J52">
-        <v>29.6816999912262</v>
+        <v>19.55664995670319</v>
       </c>
       <c r="K52">
-        <v>13.1899995803833</v>
+        <v>9.090000152587891</v>
       </c>
       <c r="L52">
-        <v>46.91999816894531</v>
+        <v>27.65999984741211</v>
       </c>
       <c r="M52">
-        <v>137.1383258340364</v>
+        <v>137.6807078737178</v>
       </c>
       <c r="N52">
-        <v>-0.55</v>
+        <v>0.06</v>
       </c>
       <c r="O52">
-        <v>-0.51</v>
+        <v>0.04</v>
       </c>
       <c r="P52">
-        <v>-0.54</v>
+        <v>0.05</v>
       </c>
       <c r="Q52">
-        <v>-76858000</v>
+        <v>28000000</v>
       </c>
       <c r="R52">
-        <v>-23224000</v>
+        <v>22000000</v>
       </c>
       <c r="S52">
-        <v>-25646000</v>
+        <v>26000000</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>1.613832853025936</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>1.291837933059307</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.61090458488228</v>
       </c>
       <c r="W52" t="s">
         <v>229</v>
@@ -4764,67 +4764,67 @@
         <v>74</v>
       </c>
       <c r="B53" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C53" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D53" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E53">
-        <v>45.84000015258789</v>
+        <v>135.9100036621094</v>
       </c>
       <c r="F53">
-        <v>1293046.666666667</v>
+        <v>363716.6666666667</v>
       </c>
       <c r="G53">
-        <v>39.78940002441406</v>
+        <v>127.1771998596191</v>
       </c>
       <c r="H53">
-        <v>39.39020008087158</v>
+        <v>107.5080000305176</v>
       </c>
       <c r="I53">
-        <v>35.75940005302429</v>
+        <v>100.7709000015259</v>
       </c>
       <c r="J53">
-        <v>33.86330006599426</v>
+        <v>96.56470012664795</v>
       </c>
       <c r="K53">
-        <v>17.70000076293945</v>
+        <v>0.8630853891372681</v>
       </c>
       <c r="L53">
-        <v>47.9900016784668</v>
+        <v>156.8002166748047</v>
       </c>
       <c r="M53">
-        <v>136.8622751029824</v>
+        <v>137.2149423636228</v>
       </c>
       <c r="N53">
-        <v>0.26</v>
+        <v>1.48</v>
       </c>
       <c r="O53">
-        <v>0.33</v>
+        <v>0.86</v>
       </c>
       <c r="P53">
-        <v>0.32</v>
+        <v>0.06</v>
       </c>
       <c r="Q53">
-        <v>50614000</v>
+        <v>46150000</v>
       </c>
       <c r="R53">
-        <v>64519000</v>
+        <v>26584000</v>
       </c>
       <c r="S53">
-        <v>61977000</v>
+        <v>1819000</v>
       </c>
       <c r="T53">
-        <v>21.29627292082166</v>
+        <v>16.77644971790845</v>
       </c>
       <c r="U53">
-        <v>25.93322052019985</v>
+        <v>10.59685012377076</v>
       </c>
       <c r="V53">
-        <v>23.00172576963759</v>
+        <v>0.6156335034589194</v>
       </c>
       <c r="W53" t="s">
         <v>229</v>
@@ -4835,31 +4835,31 @@
         <v>75</v>
       </c>
       <c r="B54" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C54" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D54" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E54">
-        <v>32.31000137329102</v>
+        <v>32.43999862670898</v>
       </c>
       <c r="F54">
-        <v>1046280</v>
+        <v>1035336.666666667</v>
       </c>
       <c r="G54">
-        <v>29.82520023345947</v>
+        <v>29.9352001953125</v>
       </c>
       <c r="H54">
-        <v>25.62533340454102</v>
+        <v>25.71260005950928</v>
       </c>
       <c r="I54">
-        <v>23.83030002593994</v>
+        <v>23.89925002098083</v>
       </c>
       <c r="J54">
-        <v>22.83574997901917</v>
+        <v>22.87504998207092</v>
       </c>
       <c r="K54">
         <v>16.70999908447266</v>
@@ -4868,7 +4868,7 @@
         <v>36.84999847412109</v>
       </c>
       <c r="M54">
-        <v>136.7361507041445</v>
+        <v>137.1420559203621</v>
       </c>
       <c r="N54">
         <v>0.32</v>
@@ -4906,67 +4906,67 @@
         <v>76</v>
       </c>
       <c r="B55" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C55" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D55" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E55">
-        <v>534.3300170898438</v>
+        <v>46.36999893188477</v>
       </c>
       <c r="F55">
-        <v>667766.6666666666</v>
+        <v>1276853.333333333</v>
       </c>
       <c r="G55">
-        <v>480.7433990478515</v>
+        <v>40.00559997558594</v>
       </c>
       <c r="H55">
-        <v>455.5168662516276</v>
+        <v>39.49166674296061</v>
       </c>
       <c r="I55">
-        <v>431.1039994812012</v>
+        <v>35.88055005073547</v>
       </c>
       <c r="J55">
-        <v>423.4191494750976</v>
+        <v>33.93405005455017</v>
       </c>
       <c r="K55">
-        <v>5.184493541717529</v>
+        <v>17.70000076293945</v>
       </c>
       <c r="L55">
-        <v>575.969970703125</v>
+        <v>47.9900016784668</v>
       </c>
       <c r="M55">
-        <v>136.7267366446388</v>
+        <v>137.0375592317531</v>
       </c>
       <c r="N55">
-        <v>2.57</v>
+        <v>0.26</v>
       </c>
       <c r="O55">
-        <v>2.45</v>
+        <v>0.33</v>
       </c>
       <c r="P55">
-        <v>2.26</v>
+        <v>0.32</v>
       </c>
       <c r="Q55">
-        <v>124337000</v>
+        <v>50614000</v>
       </c>
       <c r="R55">
-        <v>119090000</v>
+        <v>64519000</v>
       </c>
       <c r="S55">
-        <v>109802000</v>
+        <v>61977000</v>
       </c>
       <c r="T55">
-        <v>25.09739250491504</v>
+        <v>21.29627292082166</v>
       </c>
       <c r="U55">
-        <v>25.88845508378042</v>
+        <v>25.93322052019985</v>
       </c>
       <c r="V55">
-        <v>24.34283307283873</v>
+        <v>23.00172576963759</v>
       </c>
       <c r="W55" t="s">
         <v>229</v>
@@ -4980,64 +4980,64 @@
         <v>107</v>
       </c>
       <c r="C56" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D56" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E56">
-        <v>133.6799926757812</v>
+        <v>31.17000007629395</v>
       </c>
       <c r="F56">
-        <v>359526.6666666667</v>
+        <v>1195853.333333333</v>
       </c>
       <c r="G56">
-        <v>127.0225996398926</v>
+        <v>30.71640007019043</v>
       </c>
       <c r="H56">
-        <v>107.185</v>
+        <v>25.20546672821045</v>
       </c>
       <c r="I56">
-        <v>100.5236999893188</v>
+        <v>23.06045005321503</v>
       </c>
       <c r="J56">
-        <v>96.36710010528564</v>
+        <v>21.55570004940033</v>
       </c>
       <c r="K56">
-        <v>0.8630853891372681</v>
+        <v>6.139999866485596</v>
       </c>
       <c r="L56">
-        <v>156.8002166748047</v>
+        <v>33.15999984741211</v>
       </c>
       <c r="M56">
-        <v>135.618279899029</v>
+        <v>137.0017119680191</v>
       </c>
       <c r="N56">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="O56">
-        <v>0.86</v>
+        <v>1.98</v>
       </c>
       <c r="P56">
-        <v>0.06</v>
+        <v>0.73</v>
       </c>
       <c r="Q56">
-        <v>46150000</v>
+        <v>149226000</v>
       </c>
       <c r="R56">
-        <v>26584000</v>
+        <v>202973000</v>
       </c>
       <c r="S56">
-        <v>1819000</v>
+        <v>74742000</v>
       </c>
       <c r="T56">
-        <v>16.77644971790845</v>
+        <v>13.92298534422595</v>
       </c>
       <c r="U56">
-        <v>10.59685012377076</v>
+        <v>13.32889853191875</v>
       </c>
       <c r="V56">
-        <v>0.6156335034589194</v>
+        <v>9.586474121445089</v>
       </c>
       <c r="W56" t="s">
         <v>229</v>
@@ -5051,64 +5051,64 @@
         <v>106</v>
       </c>
       <c r="C57" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D57" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E57">
-        <v>627.6400146484375</v>
+        <v>130.5700073242188</v>
       </c>
       <c r="F57">
-        <v>1337933.333333333</v>
+        <v>857743.3333333334</v>
       </c>
       <c r="G57">
-        <v>590.6740002441406</v>
+        <v>115.8842001342774</v>
       </c>
       <c r="H57">
-        <v>518.5123327636719</v>
+        <v>101.54420018514</v>
       </c>
       <c r="I57">
-        <v>489.5178492736816</v>
+        <v>97.50655010223389</v>
       </c>
       <c r="J57">
-        <v>470.5496490478516</v>
+        <v>93.27060009002686</v>
       </c>
       <c r="K57">
-        <v>0.5958155393600464</v>
+        <v>4.719488620758057</v>
       </c>
       <c r="L57">
-        <v>729.8200073242188</v>
+        <v>131.6100006103516</v>
       </c>
       <c r="M57">
-        <v>135.5605300596975</v>
+        <v>136.8625057143158</v>
       </c>
       <c r="N57">
-        <v>10.39</v>
+        <v>4.84</v>
       </c>
       <c r="O57">
-        <v>10.77</v>
+        <v>1.32</v>
       </c>
       <c r="P57">
-        <v>6.01</v>
+        <v>4.17</v>
       </c>
       <c r="Q57">
-        <v>1425879000</v>
+        <v>470000000</v>
       </c>
       <c r="R57">
-        <v>1468507000</v>
+        <v>124000000</v>
       </c>
       <c r="S57">
-        <v>814008000</v>
+        <v>383000000</v>
       </c>
       <c r="T57">
-        <v>28.10100508048586</v>
+        <v>18.58442071965204</v>
       </c>
       <c r="U57">
-        <v>27.82544387387451</v>
+        <v>5.426695842450766</v>
       </c>
       <c r="V57">
-        <v>21.03614123433385</v>
+        <v>16.43071643071643</v>
       </c>
       <c r="W57" t="s">
         <v>229</v>
@@ -5119,67 +5119,67 @@
         <v>79</v>
       </c>
       <c r="B58" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C58" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="D58" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E58">
-        <v>174.9199981689453</v>
+        <v>542.530029296875</v>
       </c>
       <c r="F58">
-        <v>295516.6666666667</v>
+        <v>611080</v>
       </c>
       <c r="G58">
-        <v>149.1960003662109</v>
+        <v>482.6217999267578</v>
       </c>
       <c r="H58">
-        <v>137.3345337422689</v>
+        <v>456.5865997314453</v>
       </c>
       <c r="I58">
-        <v>130.4440503311157</v>
+        <v>431.7973497009277</v>
       </c>
       <c r="J58">
-        <v>125.6870503616333</v>
+        <v>423.4409494018554</v>
       </c>
       <c r="K58">
-        <v>2.075098752975464</v>
+        <v>5.184493541717529</v>
       </c>
       <c r="L58">
-        <v>174.9199981689453</v>
+        <v>575.969970703125</v>
       </c>
       <c r="M58">
-        <v>135.3582461828401</v>
+        <v>136.5423472406811</v>
       </c>
       <c r="N58">
-        <v>4.61</v>
+        <v>2.57</v>
       </c>
       <c r="O58">
-        <v>4.21</v>
+        <v>2.45</v>
       </c>
       <c r="P58">
-        <v>4.31</v>
+        <v>2.26</v>
       </c>
       <c r="Q58">
-        <v>340100000</v>
+        <v>124337000</v>
       </c>
       <c r="R58">
-        <v>298000000</v>
+        <v>119090000</v>
       </c>
       <c r="S58">
-        <v>298300000</v>
+        <v>109802000</v>
       </c>
       <c r="T58">
-        <v>4.914242778909648</v>
+        <v>25.09739250491504</v>
       </c>
       <c r="U58">
-        <v>4.24997860749023</v>
+        <v>25.88845508378042</v>
       </c>
       <c r="V58">
-        <v>4.064586455920425</v>
+        <v>24.34283307283873</v>
       </c>
       <c r="W58" t="s">
         <v>229</v>
@@ -5190,70 +5190,70 @@
         <v>80</v>
       </c>
       <c r="B59" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C59" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="D59" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E59">
-        <v>95.98000335693359</v>
+        <v>25.93000030517578</v>
       </c>
       <c r="F59">
-        <v>6890880</v>
+        <v>494276.6666666667</v>
       </c>
       <c r="G59">
-        <v>86.04619979858398</v>
+        <v>23.64779987335205</v>
       </c>
       <c r="H59">
-        <v>78.10519971211751</v>
+        <v>21.39466663996378</v>
       </c>
       <c r="I59">
-        <v>75.13374982833862</v>
+        <v>20.23989997863769</v>
       </c>
       <c r="J59">
-        <v>72.94709993362427</v>
+        <v>19.20340000629425</v>
       </c>
       <c r="K59">
-        <v>0.9100000262260437</v>
+        <v>4.372677803039551</v>
       </c>
       <c r="L59">
-        <v>96.83000183105469</v>
+        <v>26.21999931335449</v>
       </c>
       <c r="M59">
-        <v>135.3549501790971</v>
+        <v>135.8850515203913</v>
       </c>
       <c r="N59">
-        <v>0.7</v>
+        <v>0.51</v>
       </c>
       <c r="O59">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="P59">
-        <v>1.03</v>
+        <v>1.89</v>
       </c>
       <c r="Q59">
-        <v>311900000</v>
+        <v>20311465</v>
       </c>
       <c r="R59">
-        <v>604300000</v>
+        <v>51263710</v>
       </c>
       <c r="S59">
-        <v>461700000</v>
+        <v>76021035</v>
       </c>
       <c r="T59">
-        <v>14.22512086107817</v>
+        <v>26.73680365703607</v>
       </c>
       <c r="U59">
-        <v>28.72694428598593</v>
+        <v>49.61536070215114</v>
       </c>
       <c r="V59">
-        <v>23.55972852987702</v>
+        <v>56.88704797132189</v>
       </c>
       <c r="W59" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="60" spans="1:23">
@@ -5261,67 +5261,67 @@
         <v>81</v>
       </c>
       <c r="B60" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C60" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D60" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E60">
-        <v>128.7700042724609</v>
+        <v>107.0599975585938</v>
       </c>
       <c r="F60">
-        <v>856276.6666666666</v>
+        <v>378833.3333333333</v>
       </c>
       <c r="G60">
-        <v>115.3508000183106</v>
+        <v>102.0441999816895</v>
       </c>
       <c r="H60">
-        <v>101.2743334452311</v>
+        <v>87.04593332926433</v>
       </c>
       <c r="I60">
-        <v>97.24990005493164</v>
+        <v>82.94034990310669</v>
       </c>
       <c r="J60">
-        <v>93.11410007476806</v>
+        <v>79.04674993515015</v>
       </c>
       <c r="K60">
-        <v>4.719488620758057</v>
+        <v>20.81999969482422</v>
       </c>
       <c r="L60">
-        <v>131.6100006103516</v>
+        <v>116.4700012207031</v>
       </c>
       <c r="M60">
-        <v>134.7659670129065</v>
+        <v>135.2549302624207</v>
       </c>
       <c r="N60">
-        <v>4.84</v>
+        <v>1.05</v>
       </c>
       <c r="O60">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P60">
-        <v>4.17</v>
+        <v>0.59</v>
       </c>
       <c r="Q60">
-        <v>470000000</v>
+        <v>52215000</v>
       </c>
       <c r="R60">
-        <v>124000000</v>
+        <v>66214000</v>
       </c>
       <c r="S60">
-        <v>383000000</v>
+        <v>29068000</v>
       </c>
       <c r="T60">
-        <v>18.58442071965204</v>
+        <v>20.53663083621432</v>
       </c>
       <c r="U60">
-        <v>5.426695842450766</v>
+        <v>26.14364117345126</v>
       </c>
       <c r="V60">
-        <v>16.43071643071643</v>
+        <v>14.59493384881882</v>
       </c>
       <c r="W60" t="s">
         <v>229</v>
@@ -5332,67 +5332,67 @@
         <v>82</v>
       </c>
       <c r="B61" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C61" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D61" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E61">
-        <v>95.23999786376953</v>
+        <v>321.3599853515625</v>
       </c>
       <c r="F61">
-        <v>2364280</v>
+        <v>324073.3333333333</v>
       </c>
       <c r="G61">
-        <v>85.03859970092773</v>
+        <v>319.8221984863281</v>
       </c>
       <c r="H61">
-        <v>82.33299975077311</v>
+        <v>275.007866414388</v>
       </c>
       <c r="I61">
-        <v>75.53054979324341</v>
+        <v>252.3559999847412</v>
       </c>
       <c r="J61">
-        <v>71.93954984664917</v>
+        <v>237.1800000762939</v>
       </c>
       <c r="K61">
-        <v>0.8958330154418945</v>
+        <v>36.5</v>
       </c>
       <c r="L61">
-        <v>96.06999969482422</v>
+        <v>344.0599975585938</v>
       </c>
       <c r="M61">
-        <v>134.5089402255208</v>
+        <v>135.1770809495814</v>
       </c>
       <c r="N61">
-        <v>0.33</v>
+        <v>-0.06</v>
       </c>
       <c r="O61">
-        <v>0.37</v>
+        <v>0.1</v>
       </c>
       <c r="P61">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="Q61">
-        <v>46359000</v>
+        <v>-2271000</v>
       </c>
       <c r="R61">
-        <v>51913000</v>
+        <v>3877000</v>
       </c>
       <c r="S61">
-        <v>55923000</v>
+        <v>8562000</v>
       </c>
       <c r="T61">
-        <v>26.87338051927726</v>
+        <v>-1.062814140903603</v>
       </c>
       <c r="U61">
-        <v>29.50272789270289</v>
+        <v>1.752585708086214</v>
       </c>
       <c r="V61">
-        <v>30.34181541967338</v>
+        <v>3.546839658986404</v>
       </c>
       <c r="W61" t="s">
         <v>230</v>
@@ -5403,31 +5403,31 @@
         <v>83</v>
       </c>
       <c r="B62" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C62" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D62" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E62">
-        <v>137.2200012207031</v>
+        <v>137.9199981689453</v>
       </c>
       <c r="F62">
-        <v>370433.3333333333</v>
+        <v>365793.3333333333</v>
       </c>
       <c r="G62">
-        <v>127.9676007080078</v>
+        <v>128.281400604248</v>
       </c>
       <c r="H62">
-        <v>113.4751335652669</v>
+        <v>113.8142668660482</v>
       </c>
       <c r="I62">
-        <v>104.015700302124</v>
+        <v>104.3352502822876</v>
       </c>
       <c r="J62">
-        <v>98.28510021209716</v>
+        <v>98.52790019989014</v>
       </c>
       <c r="K62">
         <v>0.577300488948822</v>
@@ -5436,7 +5436,7 @@
         <v>142.2700042724609</v>
       </c>
       <c r="M62">
-        <v>134.0907184415566</v>
+        <v>135.0001188985055</v>
       </c>
       <c r="N62">
         <v>7.1</v>
@@ -5474,70 +5474,70 @@
         <v>84</v>
       </c>
       <c r="B63" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C63" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="D63" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E63">
-        <v>27.07999992370605</v>
+        <v>86.76999664306641</v>
       </c>
       <c r="F63">
-        <v>1082503.333333333</v>
+        <v>503973.3333333333</v>
       </c>
       <c r="G63">
-        <v>24.14860004425049</v>
+        <v>77.78129989624023</v>
       </c>
       <c r="H63">
-        <v>22.01986661275228</v>
+        <v>71.55040008544921</v>
       </c>
       <c r="I63">
-        <v>20.55239997863769</v>
+        <v>65.87225004196166</v>
       </c>
       <c r="J63">
-        <v>19.51564995288849</v>
+        <v>62.83700006484985</v>
       </c>
       <c r="K63">
-        <v>9.090000152587891</v>
+        <v>10.5</v>
       </c>
       <c r="L63">
-        <v>27.26000022888184</v>
+        <v>88.73000335693359</v>
       </c>
       <c r="M63">
-        <v>133.9699338545227</v>
+        <v>134.9960291967982</v>
       </c>
       <c r="N63">
-        <v>0.06</v>
+        <v>-0.25</v>
       </c>
       <c r="O63">
-        <v>0.04</v>
+        <v>-0.21</v>
       </c>
       <c r="P63">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="Q63">
-        <v>28000000</v>
+        <v>-7426000</v>
       </c>
       <c r="R63">
-        <v>22000000</v>
+        <v>-6720000</v>
       </c>
       <c r="S63">
-        <v>26000000</v>
+        <v>-2636000</v>
       </c>
       <c r="T63">
-        <v>1.613832853025936</v>
+        <v>-28.91406767122221</v>
       </c>
       <c r="U63">
-        <v>1.291837933059307</v>
+        <v>-21.41832669322709</v>
       </c>
       <c r="V63">
-        <v>1.61090458488228</v>
+        <v>-6.343552967223371</v>
       </c>
       <c r="W63" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="64" spans="1:23">
@@ -5545,67 +5545,67 @@
         <v>85</v>
       </c>
       <c r="B64" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C64" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D64" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="E64">
-        <v>140.5599975585938</v>
+        <v>93.5</v>
       </c>
       <c r="F64">
-        <v>5931446.666666667</v>
+        <v>338983.3333333333</v>
       </c>
       <c r="G64">
-        <v>130.5195994567871</v>
+        <v>78.12240020751953</v>
       </c>
       <c r="H64">
-        <v>118.45079981486</v>
+        <v>71.96966702779135</v>
       </c>
       <c r="I64">
-        <v>111.5456999588013</v>
+        <v>70.37845024108887</v>
       </c>
       <c r="J64">
-        <v>106.871600112915</v>
+        <v>68.18270021438599</v>
       </c>
       <c r="K64">
-        <v>0.05741097033023834</v>
+        <v>11.37919998168945</v>
       </c>
       <c r="L64">
-        <v>167</v>
+        <v>93.5</v>
       </c>
       <c r="M64">
-        <v>133.9169893006235</v>
+        <v>134.9456555725604</v>
       </c>
       <c r="N64">
-        <v>1.85</v>
+        <v>5.52</v>
       </c>
       <c r="O64">
-        <v>2.02</v>
+        <v>2.95</v>
       </c>
       <c r="P64">
-        <v>1.86</v>
+        <v>2.43</v>
       </c>
       <c r="Q64">
-        <v>1591000000</v>
+        <v>219587000</v>
       </c>
       <c r="R64">
-        <v>1717000000</v>
+        <v>117360000</v>
       </c>
       <c r="S64">
-        <v>1575000000</v>
+        <v>96733000</v>
       </c>
       <c r="T64">
-        <v>23.57386279448807</v>
+        <v>10.19132136261764</v>
       </c>
       <c r="U64">
-        <v>25.47855764950289</v>
+        <v>7.207490483975371</v>
       </c>
       <c r="V64">
-        <v>23.75565610859728</v>
+        <v>6.263755974277502</v>
       </c>
       <c r="W64" t="s">
         <v>229</v>
@@ -5616,70 +5616,70 @@
         <v>86</v>
       </c>
       <c r="B65" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C65" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D65" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E65">
-        <v>86.44999694824219</v>
+        <v>96.63999938964844</v>
       </c>
       <c r="F65">
-        <v>500030</v>
+        <v>6704670</v>
       </c>
       <c r="G65">
-        <v>77.61789993286133</v>
+        <v>86.57939971923828</v>
       </c>
       <c r="H65">
-        <v>71.38366676330567</v>
+        <v>78.25619972229003</v>
       </c>
       <c r="I65">
-        <v>65.66820005416871</v>
+        <v>75.27524984359741</v>
       </c>
       <c r="J65">
-        <v>62.68890007019043</v>
+        <v>73.0359499168396</v>
       </c>
       <c r="K65">
-        <v>10.5</v>
+        <v>0.9100000262260437</v>
       </c>
       <c r="L65">
-        <v>88.73000335693359</v>
+        <v>96.83000183105469</v>
       </c>
       <c r="M65">
-        <v>133.4669688683025</v>
+        <v>134.8857080482051</v>
       </c>
       <c r="N65">
-        <v>-0.25</v>
+        <v>0.7</v>
       </c>
       <c r="O65">
-        <v>-0.21</v>
+        <v>1.35</v>
       </c>
       <c r="P65">
-        <v>-0.08</v>
+        <v>1.03</v>
       </c>
       <c r="Q65">
-        <v>-7426000</v>
+        <v>311900000</v>
       </c>
       <c r="R65">
-        <v>-6720000</v>
+        <v>604300000</v>
       </c>
       <c r="S65">
-        <v>-2636000</v>
+        <v>461700000</v>
       </c>
       <c r="T65">
-        <v>-28.91406767122221</v>
+        <v>14.22512086107817</v>
       </c>
       <c r="U65">
-        <v>-21.41832669322709</v>
+        <v>28.72694428598593</v>
       </c>
       <c r="V65">
-        <v>-6.343552967223371</v>
+        <v>23.55972852987702</v>
       </c>
       <c r="W65" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="66" spans="1:23">
@@ -5687,67 +5687,67 @@
         <v>87</v>
       </c>
       <c r="B66" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C66" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="D66" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E66">
-        <v>171.8699951171875</v>
+        <v>55.7400016784668</v>
       </c>
       <c r="F66">
-        <v>414293.3333333333</v>
+        <v>5420766.666666667</v>
       </c>
       <c r="G66">
-        <v>149.9799987792969</v>
+        <v>48.35939987182617</v>
       </c>
       <c r="H66">
-        <v>136.1195993041992</v>
+        <v>43.28706657409668</v>
       </c>
       <c r="I66">
-        <v>131.0672494888306</v>
+        <v>42.0682999420166</v>
       </c>
       <c r="J66">
-        <v>127.0039496231079</v>
+        <v>40.82479997634888</v>
       </c>
       <c r="K66">
-        <v>0.5625</v>
+        <v>11.99751472473145</v>
       </c>
       <c r="L66">
-        <v>171.8699951171875</v>
+        <v>60.77000045776367</v>
       </c>
       <c r="M66">
-        <v>133.2340922805791</v>
+        <v>134.2274858842702</v>
       </c>
       <c r="N66">
-        <v>2.5</v>
+        <v>0.33</v>
       </c>
       <c r="O66">
-        <v>1.52</v>
+        <v>0.84</v>
       </c>
       <c r="P66">
-        <v>1.33</v>
+        <v>0.79</v>
       </c>
       <c r="Q66">
-        <v>378263000</v>
+        <v>245000000</v>
       </c>
       <c r="R66">
-        <v>82474000</v>
+        <v>614000000</v>
       </c>
       <c r="S66">
-        <v>72401000</v>
+        <v>583000000</v>
       </c>
       <c r="T66">
-        <v>7.553193018833112</v>
+        <v>0.9910602321912545</v>
       </c>
       <c r="U66">
-        <v>6.452869811235132</v>
+        <v>2.452174607612125</v>
       </c>
       <c r="V66">
-        <v>5.537839981581582</v>
+        <v>2.786540483701367</v>
       </c>
       <c r="W66" t="s">
         <v>229</v>
@@ -5758,67 +5758,67 @@
         <v>88</v>
       </c>
       <c r="B67" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C67" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="D67" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E67">
-        <v>565.5999755859375</v>
+        <v>78.31999969482422</v>
       </c>
       <c r="F67">
-        <v>1398670</v>
+        <v>5536276.666666667</v>
       </c>
       <c r="G67">
-        <v>516.4586010742188</v>
+        <v>69.55319931030273</v>
       </c>
       <c r="H67">
-        <v>460.5484670003255</v>
+        <v>61.45006624857584</v>
       </c>
       <c r="I67">
-        <v>442.4088500976562</v>
+        <v>59.10594972610474</v>
       </c>
       <c r="J67">
-        <v>431.402000579834</v>
+        <v>56.8217497253418</v>
       </c>
       <c r="K67">
-        <v>23.73999977111816</v>
+        <v>1.5</v>
       </c>
       <c r="L67">
-        <v>701.72998046875</v>
+        <v>78.31999969482422</v>
       </c>
       <c r="M67">
-        <v>133.0570377765718</v>
+        <v>133.9592665205222</v>
       </c>
       <c r="N67">
-        <v>0.39</v>
+        <v>0.29</v>
       </c>
       <c r="O67">
-        <v>0.74</v>
+        <v>0.4</v>
       </c>
       <c r="P67">
-        <v>0.73</v>
+        <v>0.31</v>
       </c>
       <c r="Q67">
-        <v>80000000</v>
+        <v>231600000</v>
       </c>
       <c r="R67">
-        <v>150000000</v>
+        <v>313800000</v>
       </c>
       <c r="S67">
-        <v>150000000</v>
+        <v>247700000</v>
       </c>
       <c r="T67">
-        <v>4.369197160021846</v>
+        <v>20.14789038712484</v>
       </c>
       <c r="U67">
-        <v>7.731958762886598</v>
+        <v>24.45830085736555</v>
       </c>
       <c r="V67">
-        <v>7.15648854961832</v>
+        <v>19.62291056008873</v>
       </c>
       <c r="W67" t="s">
         <v>229</v>
@@ -5829,67 +5829,67 @@
         <v>89</v>
       </c>
       <c r="B68" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C68" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D68" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E68">
-        <v>71.73999786376953</v>
+        <v>109</v>
       </c>
       <c r="F68">
-        <v>772816.6666666666</v>
+        <v>1139393.333333333</v>
       </c>
       <c r="G68">
-        <v>62.06759979248047</v>
+        <v>95.95980010986328</v>
       </c>
       <c r="H68">
-        <v>58.3093332417806</v>
+        <v>90.63326675415038</v>
       </c>
       <c r="I68">
-        <v>53.1509499168396</v>
+        <v>86.02295001983643</v>
       </c>
       <c r="J68">
-        <v>49.6799999332428</v>
+        <v>84.1902001953125</v>
       </c>
       <c r="K68">
-        <v>5.739999771118164</v>
+        <v>24</v>
       </c>
       <c r="L68">
-        <v>71.73999786376953</v>
+        <v>143.3099975585938</v>
       </c>
       <c r="M68">
-        <v>133.0372350179966</v>
+        <v>133.7349871025708</v>
       </c>
       <c r="N68">
-        <v>0.39</v>
+        <v>0.71</v>
       </c>
       <c r="O68">
-        <v>0.99</v>
+        <v>0.64</v>
       </c>
       <c r="P68">
-        <v>0.97</v>
+        <v>0.66</v>
       </c>
       <c r="Q68">
-        <v>28000000</v>
+        <v>76175000</v>
       </c>
       <c r="R68">
-        <v>72000000</v>
+        <v>69237000</v>
       </c>
       <c r="S68">
-        <v>72000000</v>
+        <v>71524000</v>
       </c>
       <c r="T68">
-        <v>2.5</v>
+        <v>6.938726061736672</v>
       </c>
       <c r="U68">
-        <v>5.955334987593052</v>
+        <v>6.606149022631144</v>
       </c>
       <c r="V68">
-        <v>6.070826306913997</v>
+        <v>6.37439263064457</v>
       </c>
       <c r="W68" t="s">
         <v>229</v>
@@ -5900,67 +5900,67 @@
         <v>90</v>
       </c>
       <c r="B69" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C69" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="D69" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E69">
-        <v>335.4299926757812</v>
+        <v>31.77000045776367</v>
       </c>
       <c r="F69">
-        <v>395613.6333333334</v>
+        <v>1587213.333333333</v>
       </c>
       <c r="G69">
-        <v>296.9869995117188</v>
+        <v>28.39959991455078</v>
       </c>
       <c r="H69">
-        <v>258.2949327596029</v>
+        <v>26.47099994659424</v>
       </c>
       <c r="I69">
-        <v>252.6301493835449</v>
+        <v>24.87084998607635</v>
       </c>
       <c r="J69">
-        <v>242.0579493713379</v>
+        <v>23.5651500082016</v>
       </c>
       <c r="K69">
-        <v>0.03128649666905403</v>
+        <v>0.1598737090826035</v>
       </c>
       <c r="L69">
-        <v>335.4299926757812</v>
+        <v>32.02597808837891</v>
       </c>
       <c r="M69">
-        <v>133.0115536420186</v>
+        <v>132.9784173760003</v>
       </c>
       <c r="N69">
-        <v>2.57</v>
+        <v>-0.02</v>
       </c>
       <c r="O69">
-        <v>2.27</v>
+        <v>1.3</v>
       </c>
       <c r="P69">
-        <v>3.37</v>
+        <v>0.11</v>
       </c>
       <c r="Q69">
-        <v>139100000</v>
+        <v>359000000</v>
       </c>
       <c r="R69">
-        <v>122900000</v>
+        <v>-64000000</v>
       </c>
       <c r="S69">
-        <v>181900000</v>
+        <v>23000000</v>
       </c>
       <c r="T69">
-        <v>10.56830268956086</v>
+        <v>8.586462568763453</v>
       </c>
       <c r="U69">
-        <v>10.07707445063955</v>
+        <v>-5.85544373284538</v>
       </c>
       <c r="V69">
-        <v>14.15123696903688</v>
+        <v>2.167766258246937</v>
       </c>
       <c r="W69" t="s">
         <v>229</v>
@@ -5971,67 +5971,67 @@
         <v>91</v>
       </c>
       <c r="B70" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C70" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="D70" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E70">
-        <v>183.1000061035156</v>
+        <v>332.8699951171875</v>
       </c>
       <c r="F70">
-        <v>986850</v>
+        <v>392226.9666666667</v>
       </c>
       <c r="G70">
-        <v>150.9248004150391</v>
+        <v>298.304599609375</v>
       </c>
       <c r="H70">
-        <v>145.397533009847</v>
+        <v>258.8318660481771</v>
       </c>
       <c r="I70">
-        <v>140.4724998855591</v>
+        <v>253.1587993621826</v>
       </c>
       <c r="J70">
-        <v>136.8376498413086</v>
+        <v>242.4993492889404</v>
       </c>
       <c r="K70">
-        <v>3.140000104904175</v>
+        <v>0.03128649666905403</v>
       </c>
       <c r="L70">
-        <v>183.1000061035156</v>
+        <v>335.4299926757812</v>
       </c>
       <c r="M70">
-        <v>132.9599851253658</v>
+        <v>132.7518171058426</v>
       </c>
       <c r="N70">
-        <v>4.3</v>
+        <v>2.57</v>
       </c>
       <c r="O70">
-        <v>3.9</v>
+        <v>2.27</v>
       </c>
       <c r="P70">
-        <v>3.48</v>
+        <v>3.37</v>
       </c>
       <c r="Q70">
-        <v>239602000</v>
+        <v>139100000</v>
       </c>
       <c r="R70">
-        <v>218920000</v>
+        <v>122900000</v>
       </c>
       <c r="S70">
-        <v>197100000</v>
+        <v>181900000</v>
       </c>
       <c r="T70">
-        <v>4.399663894926033</v>
+        <v>10.56830268956086</v>
       </c>
       <c r="U70">
-        <v>3.938476860818776</v>
+        <v>10.07707445063955</v>
       </c>
       <c r="V70">
-        <v>3.569423567974792</v>
+        <v>14.15123696903688</v>
       </c>
       <c r="W70" t="s">
         <v>229</v>
@@ -6042,67 +6042,67 @@
         <v>92</v>
       </c>
       <c r="B71" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C71" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="D71" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E71">
-        <v>93.02999877929688</v>
+        <v>619.4199829101562</v>
       </c>
       <c r="F71">
-        <v>338433.3333333333</v>
+        <v>1309846.666666667</v>
       </c>
       <c r="G71">
-        <v>77.58380020141601</v>
+        <v>592.684599609375</v>
       </c>
       <c r="H71">
-        <v>71.83873369852702</v>
+        <v>519.55419921875</v>
       </c>
       <c r="I71">
-        <v>70.2084002494812</v>
+        <v>490.62169921875</v>
       </c>
       <c r="J71">
-        <v>68.14360021591186</v>
+        <v>471.2627491760254</v>
       </c>
       <c r="K71">
-        <v>11.37919998168945</v>
+        <v>0.5958155393600464</v>
       </c>
       <c r="L71">
-        <v>93.02999877929688</v>
+        <v>729.8200073242188</v>
       </c>
       <c r="M71">
-        <v>132.7107225812265</v>
+        <v>132.7425174485702</v>
       </c>
       <c r="N71">
-        <v>5.52</v>
+        <v>10.39</v>
       </c>
       <c r="O71">
-        <v>2.95</v>
+        <v>10.77</v>
       </c>
       <c r="P71">
-        <v>2.43</v>
+        <v>6.01</v>
       </c>
       <c r="Q71">
-        <v>219587000</v>
+        <v>1425879000</v>
       </c>
       <c r="R71">
-        <v>117360000</v>
+        <v>1468507000</v>
       </c>
       <c r="S71">
-        <v>96733000</v>
+        <v>814008000</v>
       </c>
       <c r="T71">
-        <v>10.19132136261764</v>
+        <v>28.10100508048586</v>
       </c>
       <c r="U71">
-        <v>7.207490483975371</v>
+        <v>27.82544387387451</v>
       </c>
       <c r="V71">
-        <v>6.263755974277502</v>
+        <v>21.03614123433385</v>
       </c>
       <c r="W71" t="s">
         <v>229</v>
@@ -6116,64 +6116,64 @@
         <v>106</v>
       </c>
       <c r="C72" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="D72" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E72">
-        <v>77.86000061035156</v>
+        <v>31.32999992370605</v>
       </c>
       <c r="F72">
-        <v>5678583.333333333</v>
+        <v>1564070</v>
       </c>
       <c r="G72">
-        <v>69.24799934387207</v>
+        <v>28.15919998168945</v>
       </c>
       <c r="H72">
-        <v>61.29713292439779</v>
+        <v>24.05266667683919</v>
       </c>
       <c r="I72">
-        <v>58.96334972381592</v>
+        <v>23.5480500125885</v>
       </c>
       <c r="J72">
-        <v>56.73464971542359</v>
+        <v>22.97485004425049</v>
       </c>
       <c r="K72">
-        <v>1.5</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="L72">
-        <v>77.86000061035156</v>
+        <v>31.5</v>
       </c>
       <c r="M72">
-        <v>132.3920078004651</v>
+        <v>132.2912562670783</v>
       </c>
       <c r="N72">
-        <v>0.29</v>
+        <v>0.65</v>
       </c>
       <c r="O72">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="P72">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="Q72">
-        <v>231600000</v>
+        <v>111000000</v>
       </c>
       <c r="R72">
-        <v>313800000</v>
+        <v>54000000</v>
       </c>
       <c r="S72">
-        <v>247700000</v>
+        <v>86000000</v>
       </c>
       <c r="T72">
-        <v>20.14789038712484</v>
+        <v>6.105610561056106</v>
       </c>
       <c r="U72">
-        <v>24.45830085736555</v>
+        <v>3.930131004366813</v>
       </c>
       <c r="V72">
-        <v>19.62291056008873</v>
+        <v>5.463786531130877</v>
       </c>
       <c r="W72" t="s">
         <v>229</v>
@@ -6184,31 +6184,31 @@
         <v>94</v>
       </c>
       <c r="B73" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C73" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D73" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E73">
-        <v>90.29000091552734</v>
+        <v>90.56999969482422</v>
       </c>
       <c r="F73">
-        <v>2307843.333333333</v>
+        <v>2286253.333333333</v>
       </c>
       <c r="G73">
-        <v>85.69580017089844</v>
+        <v>85.95200012207032</v>
       </c>
       <c r="H73">
-        <v>74.09893338521321</v>
+        <v>74.2516000620524</v>
       </c>
       <c r="I73">
-        <v>70.03782497406006</v>
+        <v>70.22097497940064</v>
       </c>
       <c r="J73">
-        <v>67.02572492599488</v>
+        <v>67.14374992370605</v>
       </c>
       <c r="K73">
         <v>0.2213539928197861</v>
@@ -6217,7 +6217,7 @@
         <v>91.20999908447266</v>
       </c>
       <c r="M73">
-        <v>131.8318607482259</v>
+        <v>132.2735329667315</v>
       </c>
       <c r="N73">
         <v>0.51</v>
@@ -6258,64 +6258,64 @@
         <v>106</v>
       </c>
       <c r="C74" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="D74" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E74">
-        <v>445.7200012207031</v>
+        <v>258.3999938964844</v>
       </c>
       <c r="F74">
-        <v>1270160</v>
+        <v>2481603.333333333</v>
       </c>
       <c r="G74">
-        <v>414.4143988037109</v>
+        <v>231.3467987060547</v>
       </c>
       <c r="H74">
-        <v>374.6397328694662</v>
+        <v>211.7326000976562</v>
       </c>
       <c r="I74">
-        <v>357.3930497741699</v>
+        <v>198.9669500732422</v>
       </c>
       <c r="J74">
-        <v>347.5749996948242</v>
+        <v>194.9998000335693</v>
       </c>
       <c r="K74">
-        <v>5.65625</v>
+        <v>0.8275843262672424</v>
       </c>
       <c r="L74">
-        <v>464.8299865722656</v>
+        <v>312.9627685546875</v>
       </c>
       <c r="M74">
-        <v>131.7621215225137</v>
+        <v>132.249905584196</v>
       </c>
       <c r="N74">
-        <v>0.99</v>
+        <v>3.07</v>
       </c>
       <c r="O74">
-        <v>1.75</v>
+        <v>3.047431</v>
       </c>
       <c r="P74">
-        <v>1.76</v>
+        <v>6.05</v>
       </c>
       <c r="Q74">
-        <v>153500000</v>
+        <v>3333000000</v>
       </c>
       <c r="R74">
-        <v>271536000</v>
+        <v>771000000</v>
       </c>
       <c r="S74">
-        <v>272910000</v>
+        <v>1538000000</v>
       </c>
       <c r="T74">
-        <v>11.95211057921407</v>
+        <v>3.542315418052736</v>
       </c>
       <c r="U74">
-        <v>19.94622945039447</v>
+        <v>3.477829401416392</v>
       </c>
       <c r="V74">
-        <v>19.565362333075</v>
+        <v>7.013223894208847</v>
       </c>
       <c r="W74" t="s">
         <v>229</v>
@@ -6326,70 +6326,70 @@
         <v>96</v>
       </c>
       <c r="B75" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C75" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D75" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E75">
-        <v>116.1999969482422</v>
+        <v>114.879997253418</v>
       </c>
       <c r="F75">
-        <v>657146.6666666666</v>
+        <v>13571253.33333333</v>
       </c>
       <c r="G75">
-        <v>102.9247994995117</v>
+        <v>107.901799621582</v>
       </c>
       <c r="H75">
-        <v>95.7443999226888</v>
+        <v>94.34693318684896</v>
       </c>
       <c r="I75">
-        <v>91.42304998397827</v>
+        <v>88.8469998550415</v>
       </c>
       <c r="J75">
-        <v>88.2594500541687</v>
+        <v>84.32745002746582</v>
       </c>
       <c r="K75">
-        <v>0.8245028257369995</v>
+        <v>0.03513695672154427</v>
       </c>
       <c r="L75">
-        <v>121.2600021362305</v>
+        <v>126.5500030517578</v>
       </c>
       <c r="M75">
-        <v>131.627284462856</v>
+        <v>131.8973423673471</v>
       </c>
       <c r="N75">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="O75">
-        <v>0.04</v>
+        <v>0.68</v>
       </c>
       <c r="P75">
-        <v>-1.05</v>
+        <v>1.19</v>
       </c>
       <c r="Q75">
-        <v>48896000</v>
+        <v>1741000000</v>
       </c>
       <c r="R75">
-        <v>3224000</v>
+        <v>1895000000</v>
       </c>
       <c r="S75">
-        <v>-80540000</v>
+        <v>3319000000</v>
       </c>
       <c r="T75">
-        <v>1.945347573328496</v>
+        <v>14.18329938900204</v>
       </c>
       <c r="U75">
-        <v>0.1071679894799859</v>
+        <v>15.28472334247459</v>
       </c>
       <c r="V75">
-        <v>-3.116078368558483</v>
+        <v>23.98641323986413</v>
       </c>
       <c r="W75" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="76" spans="1:23">
@@ -6397,67 +6397,67 @@
         <v>97</v>
       </c>
       <c r="B76" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C76" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="D76" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E76">
-        <v>54.86999893188477</v>
+        <v>561.4400024414062</v>
       </c>
       <c r="F76">
-        <v>5403586.666666667</v>
+        <v>1331036.666666667</v>
       </c>
       <c r="G76">
-        <v>48.10059982299805</v>
+        <v>518.6006011962891</v>
       </c>
       <c r="H76">
-        <v>43.21479990641276</v>
+        <v>461.4540669759115</v>
       </c>
       <c r="I76">
-        <v>41.97349992752075</v>
+        <v>443.2089001464844</v>
       </c>
       <c r="J76">
-        <v>40.82144996643066</v>
+        <v>431.7722007751465</v>
       </c>
       <c r="K76">
-        <v>11.99751472473145</v>
+        <v>23.73999977111816</v>
       </c>
       <c r="L76">
-        <v>60.77000045776367</v>
+        <v>701.72998046875</v>
       </c>
       <c r="M76">
-        <v>131.474687678503</v>
+        <v>131.6785135826206</v>
       </c>
       <c r="N76">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="O76">
-        <v>0.84</v>
+        <v>0.74</v>
       </c>
       <c r="P76">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="Q76">
-        <v>245000000</v>
+        <v>80000000</v>
       </c>
       <c r="R76">
-        <v>614000000</v>
+        <v>150000000</v>
       </c>
       <c r="S76">
-        <v>583000000</v>
+        <v>150000000</v>
       </c>
       <c r="T76">
-        <v>0.9910602321912545</v>
+        <v>4.369197160021846</v>
       </c>
       <c r="U76">
-        <v>2.452174607612125</v>
+        <v>7.731958762886598</v>
       </c>
       <c r="V76">
-        <v>2.786540483701367</v>
+        <v>7.15648854961832</v>
       </c>
       <c r="W76" t="s">
         <v>229</v>
@@ -6471,67 +6471,67 @@
         <v>106</v>
       </c>
       <c r="C77" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="D77" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E77">
-        <v>114.379997253418</v>
+        <v>16.3799991607666</v>
       </c>
       <c r="F77">
-        <v>13924950</v>
+        <v>931743.3333333334</v>
       </c>
       <c r="G77">
-        <v>107.5049996948242</v>
+        <v>14.74100002288818</v>
       </c>
       <c r="H77">
-        <v>94.14179987589519</v>
+        <v>13.39353335062663</v>
       </c>
       <c r="I77">
-        <v>88.60634986877442</v>
+        <v>12.80110000610352</v>
       </c>
       <c r="J77">
-        <v>84.16025005340576</v>
+        <v>12.33975001335144</v>
       </c>
       <c r="K77">
-        <v>0.03513695672154427</v>
+        <v>1.275554656982422</v>
       </c>
       <c r="L77">
-        <v>126.5500030517578</v>
+        <v>17.22677421569824</v>
       </c>
       <c r="M77">
-        <v>130.4695965536535</v>
+        <v>131.3772977476627</v>
       </c>
       <c r="N77">
-        <v>0.63</v>
+        <v>0.05</v>
       </c>
       <c r="O77">
-        <v>0.68</v>
+        <v>0.14</v>
       </c>
       <c r="P77">
-        <v>1.19</v>
+        <v>0.14</v>
       </c>
       <c r="Q77">
-        <v>1741000000</v>
+        <v>7100000</v>
       </c>
       <c r="R77">
-        <v>1895000000</v>
+        <v>22500000</v>
       </c>
       <c r="S77">
-        <v>3319000000</v>
+        <v>21300000</v>
       </c>
       <c r="T77">
-        <v>14.18329938900204</v>
+        <v>2.142426071213035</v>
       </c>
       <c r="U77">
-        <v>15.28472334247459</v>
+        <v>7.147395171537483</v>
       </c>
       <c r="V77">
-        <v>23.98641323986413</v>
+        <v>6.398317813157105</v>
       </c>
       <c r="W77" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="78" spans="1:23">
@@ -6539,70 +6539,70 @@
         <v>99</v>
       </c>
       <c r="B78" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C78" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="D78" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E78">
-        <v>234.4199981689453</v>
+        <v>93.61000061035156</v>
       </c>
       <c r="F78">
-        <v>2302210</v>
+        <v>2267223.333333333</v>
       </c>
       <c r="G78">
-        <v>221.087600402832</v>
+        <v>85.32439971923829</v>
       </c>
       <c r="H78">
-        <v>198.8321999104818</v>
+        <v>82.4832664235433</v>
       </c>
       <c r="I78">
-        <v>188.7999499511719</v>
+        <v>75.7415497970581</v>
       </c>
       <c r="J78">
-        <v>182.8911000061035</v>
+        <v>72.0442498588562</v>
       </c>
       <c r="K78">
-        <v>0.8611109852790833</v>
+        <v>0.8958330154418945</v>
       </c>
       <c r="L78">
-        <v>239</v>
+        <v>96.06999969482422</v>
       </c>
       <c r="M78">
-        <v>130.3899336678149</v>
+        <v>131.1754539126597</v>
       </c>
       <c r="N78">
-        <v>0.68</v>
+        <v>0.33</v>
       </c>
       <c r="O78">
-        <v>0.88</v>
+        <v>0.37</v>
       </c>
       <c r="P78">
-        <v>0.89</v>
+        <v>0.4</v>
       </c>
       <c r="Q78">
-        <v>186305000</v>
+        <v>46359000</v>
       </c>
       <c r="R78">
-        <v>240392000</v>
+        <v>51913000</v>
       </c>
       <c r="S78">
-        <v>241804000</v>
+        <v>55923000</v>
       </c>
       <c r="T78">
-        <v>20.64197820850609</v>
+        <v>26.87338051927726</v>
       </c>
       <c r="U78">
-        <v>26.71387311821504</v>
+        <v>29.50272789270289</v>
       </c>
       <c r="V78">
-        <v>23.66706143742231</v>
+        <v>30.34181541967338</v>
       </c>
       <c r="W78" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="79" spans="1:23">
@@ -6610,67 +6610,67 @@
         <v>100</v>
       </c>
       <c r="B79" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C79" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D79" t="s">
-        <v>179</v>
+        <v>227</v>
       </c>
       <c r="E79">
-        <v>377.2999877929688</v>
+        <v>115.370002746582</v>
       </c>
       <c r="F79">
-        <v>393250</v>
+        <v>665466.6666666666</v>
       </c>
       <c r="G79">
-        <v>358.7973999023437</v>
+        <v>103.4871995544434</v>
       </c>
       <c r="H79">
-        <v>314.1149330647787</v>
+        <v>95.91973327636718</v>
       </c>
       <c r="I79">
-        <v>295.4249997711182</v>
+        <v>91.60809999465943</v>
       </c>
       <c r="J79">
-        <v>288.1886498260498</v>
+        <v>88.39825006484985</v>
       </c>
       <c r="K79">
-        <v>0.2751234471797943</v>
+        <v>0.8245028257369995</v>
       </c>
       <c r="L79">
-        <v>471.1166076660156</v>
+        <v>121.2600021362305</v>
       </c>
       <c r="M79">
-        <v>130.2507194747586</v>
+        <v>131.1214552648555</v>
       </c>
       <c r="N79">
-        <v>1.59</v>
+        <v>0.65</v>
       </c>
       <c r="O79">
-        <v>1.36</v>
+        <v>0.04</v>
       </c>
       <c r="P79">
-        <v>1.85</v>
+        <v>-1.05</v>
       </c>
       <c r="Q79">
-        <v>120600000</v>
+        <v>48896000</v>
       </c>
       <c r="R79">
-        <v>103000000</v>
+        <v>3224000</v>
       </c>
       <c r="S79">
-        <v>140000000</v>
+        <v>-80540000</v>
       </c>
       <c r="T79">
-        <v>17.55714077740573</v>
+        <v>1.945347573328496</v>
       </c>
       <c r="U79">
-        <v>14.53365316777198</v>
+        <v>0.1071679894799859</v>
       </c>
       <c r="V79">
-        <v>19.53670108847335</v>
+        <v>-3.116078368558483</v>
       </c>
       <c r="W79" t="s">
         <v>229</v>
@@ -6681,282 +6681,69 @@
         <v>101</v>
       </c>
       <c r="B80" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C80" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D80" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E80">
-        <v>31.59000015258789</v>
+        <v>168.0800018310547</v>
       </c>
       <c r="F80">
-        <v>1594690</v>
+        <v>424380</v>
       </c>
       <c r="G80">
-        <v>28.31439990997314</v>
+        <v>150.4563989257813</v>
       </c>
       <c r="H80">
-        <v>26.42626660664876</v>
+        <v>136.435466003418</v>
       </c>
       <c r="I80">
-        <v>24.79499998569489</v>
+        <v>131.3291495132446</v>
       </c>
       <c r="J80">
-        <v>23.5116500043869</v>
+        <v>127.1992496490479</v>
       </c>
       <c r="K80">
-        <v>0.1598737090826035</v>
+        <v>0.5625</v>
       </c>
       <c r="L80">
-        <v>32.02597808837891</v>
+        <v>171.8699951171875</v>
       </c>
       <c r="M80">
-        <v>130.1654200669369</v>
+        <v>130.4868752401933</v>
       </c>
       <c r="N80">
-        <v>-0.02</v>
+        <v>2.5</v>
       </c>
       <c r="O80">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="P80">
-        <v>0.11</v>
+        <v>1.33</v>
       </c>
       <c r="Q80">
-        <v>359000000</v>
+        <v>378263000</v>
       </c>
       <c r="R80">
-        <v>-64000000</v>
+        <v>82474000</v>
       </c>
       <c r="S80">
-        <v>23000000</v>
+        <v>72401000</v>
       </c>
       <c r="T80">
-        <v>8.586462568763453</v>
+        <v>7.553193018833112</v>
       </c>
       <c r="U80">
-        <v>-5.85544373284538</v>
+        <v>6.452869811235132</v>
       </c>
       <c r="V80">
-        <v>2.167766258246937</v>
+        <v>5.537839981581582</v>
       </c>
       <c r="W80" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="81" spans="1:23">
-      <c r="A81" t="s">
-        <v>102</v>
-      </c>
-      <c r="B81" t="s">
-        <v>110</v>
-      </c>
-      <c r="C81" t="s">
-        <v>138</v>
-      </c>
-      <c r="D81" t="s">
-        <v>226</v>
-      </c>
-      <c r="E81">
-        <v>30.70999908447266</v>
-      </c>
-      <c r="F81">
-        <v>1567760</v>
-      </c>
-      <c r="G81">
-        <v>28.05379997253418</v>
-      </c>
-      <c r="H81">
-        <v>23.98180001576742</v>
-      </c>
-      <c r="I81">
-        <v>23.50525001525879</v>
-      </c>
-      <c r="J81">
-        <v>22.95600004196167</v>
-      </c>
-      <c r="K81">
-        <v>18.89999961853027</v>
-      </c>
-      <c r="L81">
-        <v>31.5</v>
-      </c>
-      <c r="M81">
-        <v>129.9525571302814</v>
-      </c>
-      <c r="N81">
-        <v>0.65</v>
-      </c>
-      <c r="O81">
-        <v>0.31</v>
-      </c>
-      <c r="P81">
-        <v>0.5</v>
-      </c>
-      <c r="Q81">
-        <v>111000000</v>
-      </c>
-      <c r="R81">
-        <v>54000000</v>
-      </c>
-      <c r="S81">
-        <v>86000000</v>
-      </c>
-      <c r="T81">
-        <v>6.105610561056106</v>
-      </c>
-      <c r="U81">
-        <v>3.930131004366813</v>
-      </c>
-      <c r="V81">
-        <v>5.463786531130877</v>
-      </c>
-      <c r="W81" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="82" spans="1:23">
-      <c r="A82" t="s">
-        <v>103</v>
-      </c>
-      <c r="B82" t="s">
-        <v>107</v>
-      </c>
-      <c r="C82" t="s">
-        <v>119</v>
-      </c>
-      <c r="D82" t="s">
-        <v>227</v>
-      </c>
-      <c r="E82">
-        <v>71.05000305175781</v>
-      </c>
-      <c r="F82">
-        <v>767633.3333333334</v>
-      </c>
-      <c r="G82">
-        <v>68.79360008239746</v>
-      </c>
-      <c r="H82">
-        <v>56.68366661071777</v>
-      </c>
-      <c r="I82">
-        <v>53.99239994049072</v>
-      </c>
-      <c r="J82">
-        <v>51.39659996032715</v>
-      </c>
-      <c r="K82">
-        <v>23.54999923706055</v>
-      </c>
-      <c r="L82">
-        <v>75.01000213623047</v>
-      </c>
-      <c r="M82">
-        <v>129.5747556567092</v>
-      </c>
-      <c r="N82">
-        <v>-0.68</v>
-      </c>
-      <c r="O82">
-        <v>-1.24</v>
-      </c>
-      <c r="P82">
-        <v>-0.68</v>
-      </c>
-      <c r="Q82">
-        <v>-526161000</v>
-      </c>
-      <c r="R82">
-        <v>-193228000</v>
-      </c>
-      <c r="S82">
-        <v>-112101000</v>
-      </c>
-      <c r="T82">
-        <v>-509.3474409734659</v>
-      </c>
-      <c r="U82">
-        <v>-1614.134157547406</v>
-      </c>
-      <c r="V82">
-        <v>-308.5122192866579</v>
-      </c>
-      <c r="W82" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="83" spans="1:23">
-      <c r="A83" t="s">
-        <v>104</v>
-      </c>
-      <c r="B83" t="s">
-        <v>106</v>
-      </c>
-      <c r="C83" t="s">
-        <v>116</v>
-      </c>
-      <c r="D83" t="s">
-        <v>228</v>
-      </c>
-      <c r="E83">
-        <v>210.4199981689453</v>
-      </c>
-      <c r="F83">
-        <v>2395850</v>
-      </c>
-      <c r="G83">
-        <v>182.5153997802734</v>
-      </c>
-      <c r="H83">
-        <v>176.9625334676107</v>
-      </c>
-      <c r="I83">
-        <v>171.5766502380371</v>
-      </c>
-      <c r="J83">
-        <v>168.3069003295898</v>
-      </c>
-      <c r="K83">
-        <v>10.29651737213135</v>
-      </c>
-      <c r="L83">
-        <v>238.8999938964844</v>
-      </c>
-      <c r="M83">
-        <v>129.5621637786964</v>
-      </c>
-      <c r="N83">
-        <v>2.79</v>
-      </c>
-      <c r="O83">
-        <v>2.76</v>
-      </c>
-      <c r="P83">
-        <v>2.35</v>
-      </c>
-      <c r="Q83">
-        <v>738000000</v>
-      </c>
-      <c r="R83">
-        <v>722000000</v>
-      </c>
-      <c r="S83">
-        <v>615000000</v>
-      </c>
-      <c r="T83">
-        <v>21.42235123367199</v>
-      </c>
-      <c r="U83">
-        <v>21.79951690821256</v>
-      </c>
-      <c r="V83">
-        <v>19.70522268503685</v>
-      </c>
-      <c r="W83" t="s">
         <v>229</v>
       </c>
     </row>

--- a/Screener/ScreenResult/ScreenResult.xlsx
+++ b/Screener/ScreenResult/ScreenResult.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="234">
   <si>
     <t>Symbol</t>
   </si>
@@ -85,7 +85,7 @@
     <t>Code 33</t>
   </si>
   <si>
-    <t>PRFX</t>
+    <t>EDTX</t>
   </si>
   <si>
     <t>OPRA</t>
@@ -94,325 +94,346 @@
     <t>SMCI</t>
   </si>
   <si>
-    <t>INOD</t>
-  </si>
-  <si>
     <t>NVDA</t>
   </si>
   <si>
+    <t>DFH</t>
+  </si>
+  <si>
     <t>RXST</t>
   </si>
   <si>
     <t>RXDX</t>
   </si>
   <si>
+    <t>IOT</t>
+  </si>
+  <si>
     <t>ACLS</t>
   </si>
   <si>
-    <t>IOT</t>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>SGH</t>
+  </si>
+  <si>
+    <t>BLDR</t>
   </si>
   <si>
     <t>ELF</t>
   </si>
   <si>
-    <t>VRT</t>
-  </si>
-  <si>
-    <t>INTT</t>
-  </si>
-  <si>
-    <t>BLDR</t>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>TTD</t>
   </si>
   <si>
     <t>AEHR</t>
   </si>
   <si>
+    <t>MHO</t>
+  </si>
+  <si>
     <t>LI</t>
   </si>
   <si>
-    <t>MOD</t>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>DV</t>
   </si>
   <si>
     <t>AMPH</t>
   </si>
   <si>
-    <t>RCL</t>
+    <t>FLNC</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>STRL</t>
   </si>
   <si>
     <t>XPO</t>
   </si>
   <si>
-    <t>STRL</t>
-  </si>
-  <si>
     <t>AVGO</t>
   </si>
   <si>
+    <t>KRYS</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>ABCM</t>
+  </si>
+  <si>
     <t>TGLS</t>
   </si>
   <si>
-    <t>JBL</t>
-  </si>
-  <si>
-    <t>MHO</t>
+    <t>BLD</t>
+  </si>
+  <si>
+    <t>PHM</t>
   </si>
   <si>
     <t>STVN</t>
   </si>
   <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>KRYS</t>
-  </si>
-  <si>
-    <t>DV</t>
+    <t>ALGM</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>LTH</t>
   </si>
   <si>
     <t>LAD</t>
   </si>
   <si>
-    <t>PHM</t>
+    <t>TOL</t>
+  </si>
+  <si>
+    <t>IDCC</t>
   </si>
   <si>
     <t>ROIV</t>
   </si>
   <si>
-    <t>ABCM</t>
-  </si>
-  <si>
-    <t>IDCC</t>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>MPWR</t>
+  </si>
+  <si>
+    <t>TMHC</t>
+  </si>
+  <si>
+    <t>DICE</t>
+  </si>
+  <si>
+    <t>MANH</t>
+  </si>
+  <si>
+    <t>AN</t>
+  </si>
+  <si>
+    <t>BECN</t>
+  </si>
+  <si>
+    <t>BCC</t>
   </si>
   <si>
     <t>SAIA</t>
   </si>
   <si>
-    <t>TOL</t>
-  </si>
-  <si>
-    <t>LTH</t>
+    <t>TPH</t>
+  </si>
+  <si>
+    <t>KBH</t>
+  </si>
+  <si>
+    <t>MRUS</t>
+  </si>
+  <si>
+    <t>WFRD</t>
   </si>
   <si>
     <t>PANW</t>
   </si>
   <si>
-    <t>AN</t>
-  </si>
-  <si>
-    <t>BECN</t>
-  </si>
-  <si>
-    <t>KBH</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>CELH</t>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>ENS</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>VNT</t>
+  </si>
+  <si>
+    <t>MTH</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>RDNT</t>
+  </si>
+  <si>
+    <t>ONTO</t>
+  </si>
+  <si>
+    <t>BSY</t>
+  </si>
+  <si>
+    <t>CNMD</t>
+  </si>
+  <si>
+    <t>BLBD</t>
   </si>
   <si>
     <t>DAL</t>
   </si>
   <si>
-    <t>RDNT</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>ENS</t>
-  </si>
-  <si>
-    <t>TMHC</t>
+    <t>APG</t>
+  </si>
+  <si>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>CNM</t>
   </si>
   <si>
     <t>PAG</t>
   </si>
   <si>
-    <t>DICE</t>
-  </si>
-  <si>
-    <t>APG</t>
-  </si>
-  <si>
-    <t>CNMD</t>
-  </si>
-  <si>
-    <t>VNT</t>
-  </si>
-  <si>
-    <t>ALGM</t>
-  </si>
-  <si>
-    <t>TPH</t>
-  </si>
-  <si>
-    <t>OC</t>
-  </si>
-  <si>
-    <t>MPWR</t>
-  </si>
-  <si>
-    <t>LPG</t>
-  </si>
-  <si>
-    <t>ONTO</t>
-  </si>
-  <si>
-    <t>PEN</t>
-  </si>
-  <si>
-    <t>MTH</t>
-  </si>
-  <si>
     <t>TMDX</t>
   </si>
   <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>ON</t>
+    <t>FND</t>
+  </si>
+  <si>
+    <t>CDNS</t>
+  </si>
+  <si>
+    <t>IGT</t>
+  </si>
+  <si>
+    <t>TSM</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>WCC</t>
   </si>
   <si>
     <t>DELL</t>
   </si>
   <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>FND</t>
-  </si>
-  <si>
-    <t>IGT</t>
-  </si>
-  <si>
-    <t>HUBB</t>
-  </si>
-  <si>
-    <t>LRCX</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>CPRT</t>
-  </si>
-  <si>
-    <t>FDX</t>
+    <t>LSCC</t>
+  </si>
+  <si>
+    <t>SNPS</t>
   </si>
   <si>
     <t>ORCL</t>
   </si>
   <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>MWA</t>
-  </si>
-  <si>
-    <t>LSCC</t>
-  </si>
-  <si>
-    <t>MTZ</t>
-  </si>
-  <si>
-    <t>CLH</t>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
   </si>
   <si>
     <t>Healthcare</t>
   </si>
   <si>
-    <t>Communication Services</t>
-  </si>
-  <si>
-    <t>Technology</t>
+    <t>Industrials</t>
   </si>
   <si>
     <t>Consumer Defensive</t>
   </si>
   <si>
-    <t>Industrials</t>
-  </si>
-  <si>
-    <t>Consumer Cyclical</t>
+    <t>Utilities</t>
+  </si>
+  <si>
+    <t>Energy</t>
   </si>
   <si>
     <t>Basic Materials</t>
   </si>
   <si>
-    <t>Energy</t>
+    <t>Shell Companies</t>
+  </si>
+  <si>
+    <t>Internet Content &amp; Information</t>
+  </si>
+  <si>
+    <t>Computer Hardware</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Residential Construction</t>
+  </si>
+  <si>
+    <t>Medical Devices</t>
+  </si>
+  <si>
+    <t>Biotechnology</t>
+  </si>
+  <si>
+    <t>Software—Infrastructure</t>
+  </si>
+  <si>
+    <t>Semiconductor Equipment &amp; Materials</t>
+  </si>
+  <si>
+    <t>Electrical Equipment &amp; Parts</t>
+  </si>
+  <si>
+    <t>Building Products &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Household &amp; Personal Products</t>
+  </si>
+  <si>
+    <t>Auto Parts</t>
+  </si>
+  <si>
+    <t>Software—Application</t>
+  </si>
+  <si>
+    <t>Auto Manufacturers</t>
   </si>
   <si>
     <t>Drug Manufacturers—Specialty &amp; Generic</t>
   </si>
   <si>
-    <t>Internet Content &amp; Information</t>
-  </si>
-  <si>
-    <t>Computer Hardware</t>
-  </si>
-  <si>
-    <t>Information Technology Services</t>
-  </si>
-  <si>
-    <t>Semiconductors</t>
-  </si>
-  <si>
-    <t>Medical Devices</t>
-  </si>
-  <si>
-    <t>Biotechnology</t>
-  </si>
-  <si>
-    <t>Semiconductor Equipment &amp; Materials</t>
-  </si>
-  <si>
-    <t>Software—Infrastructure</t>
-  </si>
-  <si>
-    <t>Household &amp; Personal Products</t>
-  </si>
-  <si>
-    <t>Electrical Equipment &amp; Parts</t>
-  </si>
-  <si>
-    <t>Building Products &amp; Equipment</t>
-  </si>
-  <si>
-    <t>Auto Manufacturers</t>
-  </si>
-  <si>
-    <t>Auto Parts</t>
-  </si>
-  <si>
-    <t>Travel Services</t>
+    <t>Utilities—Renewable</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas E&amp;P</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Construction</t>
   </si>
   <si>
     <t>Trucking</t>
   </si>
   <si>
-    <t>Engineering &amp; Construction</t>
+    <t>Electronic Components</t>
   </si>
   <si>
     <t>Building Materials</t>
   </si>
   <si>
-    <t>Electronic Components</t>
-  </si>
-  <si>
-    <t>Residential Construction</t>
-  </si>
-  <si>
     <t>Medical Instruments &amp; Supplies</t>
   </si>
   <si>
-    <t>Oil &amp; Gas E&amp;P</t>
-  </si>
-  <si>
-    <t>Software—Application</t>
+    <t>Leisure</t>
   </si>
   <si>
     <t>Auto &amp; Truck Dealerships</t>
@@ -421,52 +442,34 @@
     <t>Telecom Services</t>
   </si>
   <si>
-    <t>Leisure</t>
+    <t>Beverages—Non-Alcoholic</t>
   </si>
   <si>
     <t>Industrial Distribution</t>
   </si>
   <si>
-    <t>Beverages—Non-Alcoholic</t>
+    <t>Oil &amp; Gas Equipment &amp; Services</t>
+  </si>
+  <si>
+    <t>Rental &amp; Leasing Services</t>
+  </si>
+  <si>
+    <t>Scientific &amp; Technical Instruments</t>
+  </si>
+  <si>
+    <t>Diagnostics &amp; Research</t>
   </si>
   <si>
     <t>Airlines</t>
   </si>
   <si>
-    <t>Diagnostics &amp; Research</t>
-  </si>
-  <si>
-    <t>Rental &amp; Leasing Services</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Equipment &amp; Services</t>
-  </si>
-  <si>
-    <t>Scientific &amp; Technical Instruments</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Midstream</t>
-  </si>
-  <si>
     <t>Home Improvement Retail</t>
   </si>
   <si>
     <t>Gambling</t>
   </si>
   <si>
-    <t>Specialty Business Services</t>
-  </si>
-  <si>
-    <t>Integrated Freight &amp; Logistics</t>
-  </si>
-  <si>
-    <t>Specialty Industrial Machinery</t>
-  </si>
-  <si>
-    <t>Waste Management</t>
-  </si>
-  <si>
-    <t>2020-09-01</t>
+    <t>2021-01-04</t>
   </si>
   <si>
     <t>2018-07-27</t>
@@ -475,232 +478,238 @@
     <t>2007-03-29</t>
   </si>
   <si>
-    <t>1993-08-10</t>
-  </si>
-  <si>
     <t>1999-01-22</t>
   </si>
   <si>
+    <t>2021-01-21</t>
+  </si>
+  <si>
     <t>2021-07-30</t>
   </si>
   <si>
     <t>2021-03-12</t>
   </si>
   <si>
+    <t>2021-12-15</t>
+  </si>
+  <si>
     <t>2000-07-11</t>
   </si>
   <si>
-    <t>2021-12-15</t>
+    <t>2014-02-03</t>
+  </si>
+  <si>
+    <t>2018-08-02</t>
+  </si>
+  <si>
+    <t>2017-05-24</t>
+  </si>
+  <si>
+    <t>2005-06-28</t>
   </si>
   <si>
     <t>2016-09-22</t>
   </si>
   <si>
-    <t>2018-08-02</t>
-  </si>
-  <si>
-    <t>1997-06-17</t>
-  </si>
-  <si>
-    <t>2005-06-28</t>
+    <t>1982-09-20</t>
+  </si>
+  <si>
+    <t>2016-09-21</t>
   </si>
   <si>
     <t>1997-08-15</t>
   </si>
   <si>
+    <t>1993-11-03</t>
+  </si>
+  <si>
     <t>2020-07-30</t>
   </si>
   <si>
-    <t>1982-09-20</t>
+    <t>1986-08-13</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
   </si>
   <si>
     <t>2014-06-25</t>
   </si>
   <si>
-    <t>1993-04-28</t>
+    <t>2021-10-28</t>
+  </si>
+  <si>
+    <t>2019-07-26</t>
+  </si>
+  <si>
+    <t>1991-07-12</t>
   </si>
   <si>
     <t>2003-10-07</t>
   </si>
   <si>
-    <t>1991-07-12</t>
-  </si>
-  <si>
     <t>2009-08-06</t>
   </si>
   <si>
+    <t>2017-09-20</t>
+  </si>
+  <si>
+    <t>1993-05-03</t>
+  </si>
+  <si>
+    <t>2020-10-22</t>
+  </si>
+  <si>
     <t>2012-05-10</t>
   </si>
   <si>
-    <t>1993-05-03</t>
-  </si>
-  <si>
-    <t>1993-11-03</t>
+    <t>2015-06-17</t>
+  </si>
+  <si>
+    <t>1980-03-17</t>
   </si>
   <si>
     <t>2021-07-16</t>
   </si>
   <si>
-    <t>2019-07-26</t>
-  </si>
-  <si>
-    <t>2017-09-20</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>2021-07-28</t>
+  </si>
+  <si>
+    <t>2021-10-07</t>
   </si>
   <si>
     <t>1996-12-18</t>
   </si>
   <si>
-    <t>1980-03-17</t>
+    <t>1986-07-08</t>
+  </si>
+  <si>
+    <t>1981-11-12</t>
   </si>
   <si>
     <t>2020-12-08</t>
   </si>
   <si>
-    <t>2020-10-22</t>
-  </si>
-  <si>
-    <t>1981-11-12</t>
+    <t>2007-01-22</t>
+  </si>
+  <si>
+    <t>2004-11-19</t>
+  </si>
+  <si>
+    <t>2013-04-10</t>
+  </si>
+  <si>
+    <t>2021-09-15</t>
+  </si>
+  <si>
+    <t>1998-04-23</t>
+  </si>
+  <si>
+    <t>1990-05-11</t>
+  </si>
+  <si>
+    <t>2004-09-23</t>
+  </si>
+  <si>
+    <t>2013-02-06</t>
   </si>
   <si>
     <t>2002-09-11</t>
   </si>
   <si>
-    <t>1986-07-08</t>
-  </si>
-  <si>
-    <t>2021-10-07</t>
+    <t>2013-01-31</t>
+  </si>
+  <si>
+    <t>1986-08-01</t>
+  </si>
+  <si>
+    <t>2016-05-19</t>
   </si>
   <si>
     <t>2012-07-20</t>
   </si>
   <si>
-    <t>1990-05-11</t>
-  </si>
-  <si>
-    <t>2004-09-23</t>
-  </si>
-  <si>
-    <t>1986-08-01</t>
-  </si>
-  <si>
-    <t>1998-04-23</t>
-  </si>
-  <si>
-    <t>2007-01-22</t>
+    <t>2015-05-14</t>
+  </si>
+  <si>
+    <t>2004-08-02</t>
+  </si>
+  <si>
+    <t>2012-06-29</t>
+  </si>
+  <si>
+    <t>2000-05-02</t>
+  </si>
+  <si>
+    <t>2020-09-24</t>
+  </si>
+  <si>
+    <t>1988-07-26</t>
+  </si>
+  <si>
+    <t>2006-11-01</t>
+  </si>
+  <si>
+    <t>1997-01-03</t>
+  </si>
+  <si>
+    <t>2019-10-28</t>
+  </si>
+  <si>
+    <t>2020-09-23</t>
+  </si>
+  <si>
+    <t>1987-07-23</t>
+  </si>
+  <si>
+    <t>2014-03-20</t>
   </si>
   <si>
     <t>2007-05-03</t>
   </si>
   <si>
-    <t>1997-01-03</t>
-  </si>
-  <si>
-    <t>2015-05-14</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>2004-08-02</t>
-  </si>
-  <si>
-    <t>2013-04-10</t>
+    <t>2020-04-29</t>
+  </si>
+  <si>
+    <t>2009-11-18</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
   </si>
   <si>
     <t>1996-10-23</t>
   </si>
   <si>
-    <t>2021-09-15</t>
-  </si>
-  <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
-    <t>1987-07-23</t>
-  </si>
-  <si>
-    <t>2020-09-24</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>2013-01-31</t>
-  </si>
-  <si>
-    <t>2006-11-01</t>
-  </si>
-  <si>
-    <t>2004-11-19</t>
-  </si>
-  <si>
-    <t>2014-05-08</t>
-  </si>
-  <si>
-    <t>2019-10-28</t>
-  </si>
-  <si>
-    <t>2015-09-18</t>
-  </si>
-  <si>
-    <t>1988-07-26</t>
-  </si>
-  <si>
     <t>2019-05-02</t>
   </si>
   <si>
-    <t>2013-02-06</t>
-  </si>
-  <si>
-    <t>2000-05-02</t>
+    <t>2017-04-27</t>
+  </si>
+  <si>
+    <t>1987-06-10</t>
+  </si>
+  <si>
+    <t>1990-03-26</t>
+  </si>
+  <si>
+    <t>1997-10-09</t>
+  </si>
+  <si>
+    <t>1999-05-12</t>
   </si>
   <si>
     <t>2016-08-17</t>
   </si>
   <si>
-    <t>2009-11-18</t>
-  </si>
-  <si>
-    <t>2017-04-27</t>
-  </si>
-  <si>
-    <t>1990-03-26</t>
-  </si>
-  <si>
-    <t>1972-06-05</t>
-  </si>
-  <si>
-    <t>1984-05-04</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>1994-03-17</t>
-  </si>
-  <si>
-    <t>1978-04-12</t>
+    <t>1989-11-09</t>
+  </si>
+  <si>
+    <t>1992-02-26</t>
   </si>
   <si>
     <t>1986-03-12</t>
-  </si>
-  <si>
-    <t>2012-06-29</t>
-  </si>
-  <si>
-    <t>2006-05-26</t>
-  </si>
-  <si>
-    <t>1989-11-09</t>
-  </si>
-  <si>
-    <t>1973-02-21</t>
-  </si>
-  <si>
-    <t>1987-11-24</t>
   </si>
   <si>
     <t>F</t>
@@ -1064,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W80"/>
+  <dimension ref="A1:W84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
@@ -1143,58 +1152,58 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E2">
-        <v>16.5</v>
+        <v>43.22999954223633</v>
       </c>
       <c r="F2">
-        <v>603930</v>
+        <v>408576.6666666667</v>
       </c>
       <c r="G2">
-        <v>1.334840007424354</v>
+        <v>14.20694005966187</v>
       </c>
       <c r="H2">
-        <v>0.8076266684134801</v>
+        <v>11.81855339686076</v>
       </c>
       <c r="I2">
-        <v>0.7511750009655952</v>
+        <v>11.43621504306793</v>
       </c>
       <c r="J2">
-        <v>0.5763150002062321</v>
+        <v>10.53966502666473</v>
       </c>
       <c r="K2">
-        <v>0.3610000014305115</v>
+        <v>9.739999771118164</v>
       </c>
       <c r="L2">
-        <v>16.5</v>
+        <v>43.22999954223633</v>
       </c>
       <c r="M2">
-        <v>2948.165655424706</v>
+        <v>408.3573055448696</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.002796</v>
       </c>
       <c r="Q2">
-        <v>-7359000</v>
+        <v>4198372</v>
       </c>
       <c r="R2">
-        <v>-3166000</v>
+        <v>317981</v>
       </c>
       <c r="S2">
-        <v>-2308000</v>
+        <v>768</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -1206,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -1214,40 +1223,40 @@
         <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E3">
-        <v>25.44000053405762</v>
+        <v>27.82999992370605</v>
       </c>
       <c r="F3">
-        <v>1407013.333333333</v>
+        <v>1504113.333333333</v>
       </c>
       <c r="G3">
-        <v>16.4524081993103</v>
+        <v>17.35080005645752</v>
       </c>
       <c r="H3">
-        <v>10.4475453154246</v>
+        <v>11.11320004781087</v>
       </c>
       <c r="I3">
-        <v>8.842341672182084</v>
+        <v>9.501100038290025</v>
       </c>
       <c r="J3">
-        <v>7.260309534072876</v>
+        <v>7.865600045919418</v>
       </c>
       <c r="K3">
-        <v>3.460049629211426</v>
+        <v>3.970000028610229</v>
       </c>
       <c r="L3">
-        <v>25.44000053405762</v>
+        <v>27.82999992370605</v>
       </c>
       <c r="M3">
-        <v>325.9014186056987</v>
+        <v>355.1290127954948</v>
       </c>
       <c r="N3">
         <v>0.08</v>
@@ -1277,7 +1286,7 @@
         <v>17.7803816153749</v>
       </c>
       <c r="W3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -1285,40 +1294,40 @@
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E4">
-        <v>270.9500122070312</v>
+        <v>294.0499877929688</v>
       </c>
       <c r="F4">
-        <v>3026220</v>
+        <v>2893523.333333333</v>
       </c>
       <c r="G4">
-        <v>200.7391998291016</v>
+        <v>207.9421998596191</v>
       </c>
       <c r="H4">
-        <v>128.0981999715169</v>
+        <v>130.7694000244141</v>
       </c>
       <c r="I4">
-        <v>113.5491499710083</v>
+        <v>115.8644999885559</v>
       </c>
       <c r="J4">
-        <v>95.84584995269775</v>
+        <v>97.63699993133545</v>
       </c>
       <c r="K4">
         <v>3.849999904632568</v>
       </c>
       <c r="L4">
-        <v>270.9500122070312</v>
+        <v>294.0499877929688</v>
       </c>
       <c r="M4">
-        <v>266.5758812525153</v>
+        <v>297.2837277422557</v>
       </c>
       <c r="N4">
         <v>3.35</v>
@@ -1348,7 +1357,7 @@
         <v>6.689493304740293</v>
       </c>
       <c r="W4" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -1356,70 +1365,70 @@
         <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E5">
-        <v>10.9399995803833</v>
+        <v>459.7699890136719</v>
       </c>
       <c r="F5">
-        <v>705150</v>
+        <v>47714066.66666666</v>
       </c>
       <c r="G5">
-        <v>9.99560001373291</v>
+        <v>371.4994000244141</v>
       </c>
       <c r="H5">
-        <v>7.009600008328755</v>
+        <v>268.9220663452148</v>
       </c>
       <c r="I5">
-        <v>6.06425000667572</v>
+        <v>236.4819497680664</v>
       </c>
       <c r="J5">
-        <v>5.267200013399124</v>
+        <v>207.810549621582</v>
       </c>
       <c r="K5">
-        <v>0.09375</v>
+        <v>0.3134739995002747</v>
       </c>
       <c r="L5">
-        <v>13.27000045776367</v>
+        <v>459.7699890136719</v>
       </c>
       <c r="M5">
-        <v>226.7055263452704</v>
+        <v>231.7763632427629</v>
       </c>
       <c r="N5">
-        <v>-0.12</v>
+        <v>0.27</v>
       </c>
       <c r="O5">
-        <v>-0.07000000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="P5">
-        <v>-0.08</v>
+        <v>0.82</v>
       </c>
       <c r="Q5">
-        <v>-3327000</v>
+        <v>680000000</v>
       </c>
       <c r="R5">
-        <v>-1960000</v>
+        <v>1414000000</v>
       </c>
       <c r="S5">
-        <v>-2116000</v>
+        <v>2043000000</v>
       </c>
       <c r="T5">
-        <v>-18.03545291917385</v>
+        <v>11.4651829371101</v>
       </c>
       <c r="U5">
-        <v>-10.11612903225806</v>
+        <v>23.36803834077012</v>
       </c>
       <c r="V5">
-        <v>-11.23201868464356</v>
+        <v>28.40656284760845</v>
       </c>
       <c r="W5" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -1427,70 +1436,70 @@
         <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E6">
-        <v>424.0499877929688</v>
+        <v>25.67000007629395</v>
       </c>
       <c r="F6">
-        <v>49982716.66666666</v>
+        <v>376870</v>
       </c>
       <c r="G6">
-        <v>364.8374389648437</v>
+        <v>20.46920001983642</v>
       </c>
       <c r="H6">
-        <v>265.1283240763346</v>
+        <v>14.72479998906453</v>
       </c>
       <c r="I6">
-        <v>233.1984477615356</v>
+        <v>13.6255500125885</v>
       </c>
       <c r="J6">
-        <v>205.4890301132202</v>
+        <v>12.39560000896454</v>
       </c>
       <c r="K6">
-        <v>0.3130019903182983</v>
+        <v>8.369999885559082</v>
       </c>
       <c r="L6">
-        <v>438.0799865722656</v>
+        <v>34</v>
       </c>
       <c r="M6">
-        <v>215.514735130629</v>
+        <v>204.7653652253236</v>
       </c>
       <c r="N6">
-        <v>0.27</v>
+        <v>0.64</v>
       </c>
       <c r="O6">
-        <v>0.57</v>
+        <v>0.78</v>
       </c>
       <c r="P6">
-        <v>0.82</v>
+        <v>0.45</v>
       </c>
       <c r="Q6">
-        <v>680000000</v>
+        <v>69641000</v>
       </c>
       <c r="R6">
-        <v>1414000000</v>
+        <v>86332000</v>
       </c>
       <c r="S6">
-        <v>2043000000</v>
+        <v>49089000</v>
       </c>
       <c r="T6">
-        <v>11.4651829371101</v>
+        <v>8.863910883590927</v>
       </c>
       <c r="U6">
-        <v>23.36803834077012</v>
+        <v>7.852175510656992</v>
       </c>
       <c r="V6">
-        <v>28.40656284760845</v>
+        <v>6.380000519872111</v>
       </c>
       <c r="W6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -1498,31 +1507,31 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E7">
-        <v>30.77000045776367</v>
+        <v>30.95999908447266</v>
       </c>
       <c r="F7">
-        <v>532353.3333333334</v>
+        <v>512960</v>
       </c>
       <c r="G7">
-        <v>24.89089992523193</v>
+        <v>25.39089992523193</v>
       </c>
       <c r="H7">
-        <v>17.87749998092652</v>
+        <v>18.10196664174398</v>
       </c>
       <c r="I7">
-        <v>16.39802498340607</v>
+        <v>16.59097497940063</v>
       </c>
       <c r="J7">
-        <v>14.9612249994278</v>
+        <v>15.08832499980926</v>
       </c>
       <c r="K7">
         <v>8.970000267028809</v>
@@ -1531,7 +1540,7 @@
         <v>31.68000030517578</v>
       </c>
       <c r="M7">
-        <v>199.2145124429223</v>
+        <v>197.4678031685473</v>
       </c>
       <c r="N7">
         <v>-0.61</v>
@@ -1561,7 +1570,7 @@
         <v>-75.54462805191835</v>
       </c>
       <c r="W7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -1569,13 +1578,13 @@
         <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E8">
         <v>199.9199981689453</v>
@@ -1602,7 +1611,7 @@
         <v>199.9199981689453</v>
       </c>
       <c r="M8">
-        <v>189.7452927007889</v>
+        <v>194.968050850363</v>
       </c>
       <c r="N8">
         <v>-0.9</v>
@@ -1632,7 +1641,7 @@
         <v>-3699.185520361991</v>
       </c>
       <c r="W8" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:23">
@@ -1640,70 +1649,70 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E9">
-        <v>174.1199951171875</v>
+        <v>27.70000076293945</v>
       </c>
       <c r="F9">
-        <v>539016.6666666666</v>
+        <v>4991536.666666667</v>
       </c>
       <c r="G9">
-        <v>154.4884002685547</v>
+        <v>23.85759990692139</v>
       </c>
       <c r="H9">
-        <v>125.8972671000163</v>
+        <v>18.66699996948242</v>
       </c>
       <c r="I9">
-        <v>110.6287503051758</v>
+        <v>16.76044998168945</v>
       </c>
       <c r="J9">
-        <v>99.77305032730102</v>
+        <v>15.32794999599457</v>
       </c>
       <c r="K9">
-        <v>0.6800000071525574</v>
+        <v>8.699999809265137</v>
       </c>
       <c r="L9">
-        <v>183.3300018310547</v>
+        <v>30.6299991607666</v>
       </c>
       <c r="M9">
-        <v>186.7020197528608</v>
+        <v>193.7785972366965</v>
       </c>
       <c r="N9">
-        <v>1.21</v>
+        <v>-0.11</v>
       </c>
       <c r="O9">
-        <v>1.71</v>
+        <v>-0.1</v>
       </c>
       <c r="P9">
-        <v>1.43</v>
+        <v>-0.13</v>
       </c>
       <c r="Q9">
-        <v>40283000</v>
+        <v>-58555000</v>
       </c>
       <c r="R9">
-        <v>56992000</v>
+        <v>-53598000</v>
       </c>
       <c r="S9">
-        <v>47697000</v>
+        <v>-67856000</v>
       </c>
       <c r="T9">
-        <v>17.57739718555689</v>
+        <v>-34.48468786808009</v>
       </c>
       <c r="U9">
-        <v>21.42145678836013</v>
+        <v>-28.72701351184766</v>
       </c>
       <c r="V9">
-        <v>18.77686796315251</v>
+        <v>-33.21064996084574</v>
       </c>
       <c r="W9" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -1711,70 +1720,70 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E10">
-        <v>27.64999961853027</v>
+        <v>182.0700073242188</v>
       </c>
       <c r="F10">
-        <v>5021123.333333333</v>
+        <v>529126.6666666666</v>
       </c>
       <c r="G10">
-        <v>23.47579986572266</v>
+        <v>156.8090005493164</v>
       </c>
       <c r="H10">
-        <v>18.45486662546794</v>
+        <v>127.2209338378906</v>
       </c>
       <c r="I10">
-        <v>16.60234997749329</v>
+        <v>111.836800365448</v>
       </c>
       <c r="J10">
-        <v>15.18460000038147</v>
+        <v>100.8083003044128</v>
       </c>
       <c r="K10">
-        <v>8.699999809265137</v>
+        <v>0.6800000071525574</v>
       </c>
       <c r="L10">
-        <v>30.6299991607666</v>
+        <v>183.3300018310547</v>
       </c>
       <c r="M10">
-        <v>181.3191028228078</v>
+        <v>186.6565012692695</v>
       </c>
       <c r="N10">
-        <v>-0.11</v>
+        <v>1.21</v>
       </c>
       <c r="O10">
-        <v>-0.1</v>
+        <v>1.71</v>
       </c>
       <c r="P10">
-        <v>-0.13</v>
+        <v>1.43</v>
       </c>
       <c r="Q10">
-        <v>-58555000</v>
+        <v>40283000</v>
       </c>
       <c r="R10">
-        <v>-53598000</v>
+        <v>56992000</v>
       </c>
       <c r="S10">
-        <v>-67856000</v>
+        <v>47697000</v>
       </c>
       <c r="T10">
-        <v>-34.48468786808009</v>
+        <v>17.57739718555689</v>
       </c>
       <c r="U10">
-        <v>-28.72701351184766</v>
+        <v>21.42145678836013</v>
       </c>
       <c r="V10">
-        <v>-33.21064996084574</v>
+        <v>18.77686796315251</v>
       </c>
       <c r="W10" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -1782,70 +1791,70 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C11" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E11">
-        <v>113.4899978637695</v>
+        <v>11.81999969482422</v>
       </c>
       <c r="F11">
-        <v>1061740</v>
+        <v>2430963.333333333</v>
       </c>
       <c r="G11">
-        <v>100.8341999816895</v>
+        <v>9.506300010681151</v>
       </c>
       <c r="H11">
-        <v>79.46226656595866</v>
+        <v>8.322900021870931</v>
       </c>
       <c r="I11">
-        <v>70.87499988555908</v>
+        <v>7.102525014877319</v>
       </c>
       <c r="J11">
-        <v>63.80504987716674</v>
+        <v>6.51932501912117</v>
       </c>
       <c r="K11">
-        <v>7.300000190734863</v>
+        <v>0.9279999732971191</v>
       </c>
       <c r="L11">
-        <v>114.370002746582</v>
+        <v>15.15999984741211</v>
       </c>
       <c r="M11">
-        <v>177.0189177543051</v>
+        <v>186.3484364629211</v>
       </c>
       <c r="N11">
-        <v>0.21</v>
+        <v>-0.28</v>
       </c>
       <c r="O11">
-        <v>0.34</v>
+        <v>-0.3</v>
       </c>
       <c r="P11">
-        <v>0.29</v>
+        <v>-0.29</v>
       </c>
       <c r="Q11">
-        <v>11710000</v>
+        <v>-105911000</v>
       </c>
       <c r="R11">
-        <v>19105000</v>
+        <v>-26633000</v>
       </c>
       <c r="S11">
-        <v>16246000</v>
+        <v>-28778000</v>
       </c>
       <c r="T11">
-        <v>9.570981372957686</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>13.03766284283151</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>8.671146527751832</v>
+        <v>0</v>
       </c>
       <c r="W11" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" spans="1:23">
@@ -1853,31 +1862,31 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E12">
-        <v>25.30999946594238</v>
+        <v>26.51000022888184</v>
       </c>
       <c r="F12">
-        <v>5232390</v>
+        <v>4642626.666666667</v>
       </c>
       <c r="G12">
-        <v>19.66939994812012</v>
+        <v>20.11999996185303</v>
       </c>
       <c r="H12">
-        <v>15.94846665700277</v>
+        <v>16.10286665598552</v>
       </c>
       <c r="I12">
-        <v>15.1669499874115</v>
+        <v>15.32339999198914</v>
       </c>
       <c r="J12">
-        <v>14.02355000019073</v>
+        <v>14.11775000572205</v>
       </c>
       <c r="K12">
         <v>5.564881324768066</v>
@@ -1886,7 +1895,7 @@
         <v>28.57900047302246</v>
       </c>
       <c r="M12">
-        <v>171.8213109448897</v>
+        <v>182.3985777141801</v>
       </c>
       <c r="N12">
         <v>0.06</v>
@@ -1916,7 +1925,7 @@
         <v>3.306817434751167</v>
       </c>
       <c r="W12" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -1924,70 +1933,70 @@
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E13">
-        <v>23.63999938964844</v>
+        <v>27.68000030517578</v>
       </c>
       <c r="F13">
-        <v>311170</v>
+        <v>1151900</v>
       </c>
       <c r="G13">
-        <v>22.94860004425049</v>
+        <v>22.8202000617981</v>
       </c>
       <c r="H13">
-        <v>17.66299995422363</v>
+        <v>18.56460001627604</v>
       </c>
       <c r="I13">
-        <v>15.40949997663498</v>
+        <v>17.71044999599457</v>
       </c>
       <c r="J13">
-        <v>13.74904995679855</v>
+        <v>16.79100002765655</v>
       </c>
       <c r="K13">
-        <v>0.1160330548882484</v>
+        <v>6.489999771118164</v>
       </c>
       <c r="L13">
-        <v>26.90999984741211</v>
+        <v>36.5</v>
       </c>
       <c r="M13">
-        <v>168.0790200670218</v>
+        <v>176.9675882803405</v>
       </c>
       <c r="N13">
-        <v>0.23</v>
+        <v>0.4</v>
       </c>
       <c r="O13">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="P13">
-        <v>0.25</v>
+        <v>-0.55</v>
       </c>
       <c r="Q13">
-        <v>2524000</v>
+        <v>51522000</v>
       </c>
       <c r="R13">
-        <v>3244000</v>
+        <v>-27219000</v>
       </c>
       <c r="S13">
-        <v>2817000</v>
+        <v>-24455000</v>
       </c>
       <c r="T13">
-        <v>8.202528354619609</v>
+        <v>2.838855994260796</v>
       </c>
       <c r="U13">
-        <v>10.01080080234532</v>
+        <v>-6.342182890855458</v>
       </c>
       <c r="V13">
-        <v>8.825464456906545</v>
+        <v>-6.379620692353846</v>
       </c>
       <c r="W13" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -1995,40 +2004,40 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E14">
-        <v>135.4700012207031</v>
+        <v>139.8699951171875</v>
       </c>
       <c r="F14">
-        <v>2711756.666666667</v>
+        <v>2656886.666666667</v>
       </c>
       <c r="G14">
-        <v>120.9777996826172</v>
+        <v>122.7883996582031</v>
       </c>
       <c r="H14">
-        <v>92.80786649068196</v>
+        <v>93.83926643371582</v>
       </c>
       <c r="I14">
-        <v>84.70489982604981</v>
+        <v>85.55239980697633</v>
       </c>
       <c r="J14">
-        <v>77.58249979019165</v>
+        <v>78.18269979476929</v>
       </c>
       <c r="K14">
         <v>0.8299999833106995</v>
       </c>
       <c r="L14">
-        <v>136.4700012207031</v>
+        <v>139.8699951171875</v>
       </c>
       <c r="M14">
-        <v>165.5519884010992</v>
+        <v>173.5201968164739</v>
       </c>
       <c r="N14">
         <v>5.75</v>
@@ -2058,7 +2067,7 @@
         <v>8.595390431986701</v>
       </c>
       <c r="W14" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15" spans="1:23">
@@ -2066,70 +2075,70 @@
         <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C15" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E15">
-        <v>38.70999908447266</v>
+        <v>115.6100006103516</v>
       </c>
       <c r="F15">
-        <v>1133333.333333333</v>
+        <v>1004743.333333333</v>
       </c>
       <c r="G15">
-        <v>35.36779991149902</v>
+        <v>101.7255999755859</v>
       </c>
       <c r="H15">
-        <v>31.51753323872884</v>
+        <v>80.26799992879232</v>
       </c>
       <c r="I15">
-        <v>28.5842999124527</v>
+        <v>71.63489990234375</v>
       </c>
       <c r="J15">
-        <v>26.05974991321564</v>
+        <v>64.46224990844726</v>
       </c>
       <c r="K15">
-        <v>0.5</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="L15">
-        <v>44.2400016784668</v>
+        <v>115.6100006103516</v>
       </c>
       <c r="M15">
-        <v>164.5686930407567</v>
+        <v>171.8209673604115</v>
       </c>
       <c r="N15">
-        <v>0.02</v>
+        <v>0.21</v>
       </c>
       <c r="O15">
-        <v>0.13</v>
+        <v>0.34</v>
       </c>
       <c r="P15">
-        <v>0.14</v>
+        <v>0.29</v>
       </c>
       <c r="Q15">
-        <v>5794000</v>
+        <v>11710000</v>
       </c>
       <c r="R15">
-        <v>589000</v>
+        <v>19105000</v>
       </c>
       <c r="S15">
-        <v>4132000</v>
+        <v>16246000</v>
       </c>
       <c r="T15">
-        <v>28.55734634531027</v>
+        <v>9.570981372957686</v>
       </c>
       <c r="U15">
-        <v>5.519632649236248</v>
+        <v>13.03766284283151</v>
       </c>
       <c r="V15">
-        <v>24.01487853074509</v>
+        <v>8.671146527751832</v>
       </c>
       <c r="W15" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:23">
@@ -2137,70 +2146,70 @@
         <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E16">
-        <v>37.06000137329102</v>
+        <v>36.66999816894531</v>
       </c>
       <c r="F16">
-        <v>7189086.666666667</v>
+        <v>572870</v>
       </c>
       <c r="G16">
-        <v>30.64449996948242</v>
+        <v>27.85920017242432</v>
       </c>
       <c r="H16">
-        <v>25.59683334350586</v>
+        <v>24.07860000610351</v>
       </c>
       <c r="I16">
-        <v>23.97629998683929</v>
+        <v>22.42570001125336</v>
       </c>
       <c r="J16">
-        <v>23.22669998645782</v>
+        <v>20.6602999830246</v>
       </c>
       <c r="K16">
-        <v>13.61999988555908</v>
+        <v>0.5703791379928589</v>
       </c>
       <c r="L16">
-        <v>43.95999908447266</v>
+        <v>36.66999816894531</v>
       </c>
       <c r="M16">
-        <v>163.4535082713533</v>
+        <v>171.4245788359831</v>
       </c>
       <c r="N16">
-        <v>-0.64</v>
+        <v>0.46</v>
       </c>
       <c r="O16">
-        <v>0.26</v>
+        <v>0.46</v>
       </c>
       <c r="P16">
-        <v>0.9</v>
+        <v>1.69</v>
       </c>
       <c r="Q16">
-        <v>-1640321000</v>
+        <v>24400000</v>
       </c>
       <c r="R16">
-        <v>256938000</v>
+        <v>24500000</v>
       </c>
       <c r="S16">
-        <v>929668000</v>
+        <v>89900000</v>
       </c>
       <c r="T16">
-        <v>-17.55802782723927</v>
+        <v>4.215618521078093</v>
       </c>
       <c r="U16">
-        <v>1.455749769091836</v>
+        <v>4.375</v>
       </c>
       <c r="V16">
-        <v>4.948450403583787</v>
+        <v>14.5445720757159</v>
       </c>
       <c r="W16" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -2208,70 +2217,70 @@
         <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E17">
-        <v>32.97000122070312</v>
+        <v>87.01000213623047</v>
       </c>
       <c r="F17">
-        <v>564273.3333333334</v>
+        <v>3624056.666666667</v>
       </c>
       <c r="G17">
-        <v>27.25860023498535</v>
+        <v>72.08040031433106</v>
       </c>
       <c r="H17">
-        <v>23.87653335571289</v>
+        <v>59.81466679890951</v>
       </c>
       <c r="I17">
-        <v>22.20725002288818</v>
+        <v>58.12915006637573</v>
       </c>
       <c r="J17">
-        <v>20.49624998569488</v>
+        <v>56.60115001678466</v>
       </c>
       <c r="K17">
-        <v>0.5703791379928589</v>
+        <v>2.279999971389771</v>
       </c>
       <c r="L17">
-        <v>34.61000061035156</v>
+        <v>111.6399993896484</v>
       </c>
       <c r="M17">
-        <v>161.4619054436921</v>
+        <v>167.2588838695628</v>
       </c>
       <c r="N17">
-        <v>0.46</v>
+        <v>0.03</v>
       </c>
       <c r="O17">
-        <v>0.46</v>
+        <v>0.14</v>
       </c>
       <c r="P17">
-        <v>1.69</v>
+        <v>0.02</v>
       </c>
       <c r="Q17">
-        <v>24400000</v>
+        <v>15869000</v>
       </c>
       <c r="R17">
-        <v>24500000</v>
+        <v>71187000</v>
       </c>
       <c r="S17">
-        <v>89900000</v>
+        <v>9326000</v>
       </c>
       <c r="T17">
-        <v>4.215618521078093</v>
+        <v>4.019778454960192</v>
       </c>
       <c r="U17">
-        <v>4.375</v>
+        <v>14.50614076378997</v>
       </c>
       <c r="V17">
-        <v>14.5445720757159</v>
+        <v>2.436240050365332</v>
       </c>
       <c r="W17" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:23">
@@ -2279,70 +2288,70 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E18">
-        <v>55.06999969482422</v>
+        <v>41.43000030517578</v>
       </c>
       <c r="F18">
-        <v>482496.6666666667</v>
+        <v>1193266.666666667</v>
       </c>
       <c r="G18">
-        <v>47.21179969787597</v>
+        <v>35.98019989013672</v>
       </c>
       <c r="H18">
-        <v>37.9777332051595</v>
+        <v>31.71073323567708</v>
       </c>
       <c r="I18">
-        <v>35.74529993057251</v>
+        <v>28.84469991207123</v>
       </c>
       <c r="J18">
-        <v>33.18999998092652</v>
+        <v>26.313299908638</v>
       </c>
       <c r="K18">
-        <v>8.689999580383301</v>
+        <v>0.5</v>
       </c>
       <c r="L18">
-        <v>58.38000106811523</v>
+        <v>44.2400016784668</v>
       </c>
       <c r="M18">
-        <v>160.2053683329975</v>
+        <v>167.1012778048138</v>
       </c>
       <c r="N18">
-        <v>0.3</v>
+        <v>0.02</v>
       </c>
       <c r="O18">
-        <v>0.66</v>
+        <v>0.13</v>
       </c>
       <c r="P18">
-        <v>0.5</v>
+        <v>0.14</v>
       </c>
       <c r="Q18">
-        <v>15874000</v>
+        <v>5794000</v>
       </c>
       <c r="R18">
-        <v>33913000</v>
+        <v>589000</v>
       </c>
       <c r="S18">
-        <v>26032000</v>
+        <v>4132000</v>
       </c>
       <c r="T18">
-        <v>13.21412814557684</v>
+        <v>28.55734634531027</v>
       </c>
       <c r="U18">
-        <v>25.11646163986876</v>
+        <v>5.519632649236248</v>
       </c>
       <c r="V18">
-        <v>18.59136421419491</v>
+        <v>24.01487853074509</v>
       </c>
       <c r="W18" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" spans="1:23">
@@ -2350,70 +2359,70 @@
         <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E19">
-        <v>101.2799987792969</v>
+        <v>90.43000030517578</v>
       </c>
       <c r="F19">
-        <v>3899783.333333333</v>
+        <v>346263.3333333333</v>
       </c>
       <c r="G19">
-        <v>87.03619995117188</v>
+        <v>75.91020034790039</v>
       </c>
       <c r="H19">
-        <v>70.92713340759278</v>
+        <v>63.0909334564209</v>
       </c>
       <c r="I19">
-        <v>65.89450002670289</v>
+        <v>57.63415012359619</v>
       </c>
       <c r="J19">
-        <v>60.48640007019043</v>
+        <v>53.42870014190674</v>
       </c>
       <c r="K19">
-        <v>4.547188282012939</v>
+        <v>3.118403196334839</v>
       </c>
       <c r="L19">
-        <v>133.7226409912109</v>
+        <v>90.43000030517578</v>
       </c>
       <c r="M19">
-        <v>159.8288978874638</v>
+        <v>164.7862566176076</v>
       </c>
       <c r="N19">
-        <v>0.13</v>
+        <v>4.67</v>
       </c>
       <c r="O19">
-        <v>-1.96</v>
+        <v>4.65</v>
       </c>
       <c r="P19">
-        <v>-0.19</v>
+        <v>3.64</v>
       </c>
       <c r="Q19">
-        <v>32968000</v>
+        <v>131590000</v>
       </c>
       <c r="R19">
-        <v>-500206000</v>
+        <v>130395000</v>
       </c>
       <c r="S19">
-        <v>-47910000</v>
+        <v>103066000</v>
       </c>
       <c r="T19">
-        <v>1.10147590688506</v>
+        <v>12.99105168383143</v>
       </c>
       <c r="U19">
-        <v>-19.20919879938187</v>
+        <v>10.71446179129006</v>
       </c>
       <c r="V19">
-        <v>-1.660574542848092</v>
+        <v>10.30114039559034</v>
       </c>
       <c r="W19" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" spans="1:23">
@@ -2421,70 +2430,70 @@
         <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D20" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E20">
-        <v>59.52000045776367</v>
+        <v>37.36000061035156</v>
       </c>
       <c r="F20">
-        <v>1686066.666666667</v>
+        <v>7131050</v>
       </c>
       <c r="G20">
-        <v>50.4160001373291</v>
+        <v>31.21269992828369</v>
       </c>
       <c r="H20">
-        <v>40.72713342030843</v>
+        <v>25.80109999338786</v>
       </c>
       <c r="I20">
-        <v>38.50670632362366</v>
+        <v>24.1077999830246</v>
       </c>
       <c r="J20">
-        <v>36.07277248382568</v>
+        <v>23.23604998111725</v>
       </c>
       <c r="K20">
-        <v>0.6502050161361694</v>
+        <v>13.61999988555908</v>
       </c>
       <c r="L20">
-        <v>60.04999923706055</v>
+        <v>43.95999908447266</v>
       </c>
       <c r="M20">
-        <v>156.9924778239875</v>
+        <v>162.2340283588514</v>
       </c>
       <c r="N20">
-        <v>1.13</v>
+        <v>-0.64</v>
       </c>
       <c r="O20">
-        <v>-0.8100000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="P20">
-        <v>0.13</v>
+        <v>0.9</v>
       </c>
       <c r="Q20">
-        <v>131000000</v>
+        <v>-1640321000</v>
       </c>
       <c r="R20">
-        <v>-94000000</v>
+        <v>256938000</v>
       </c>
       <c r="S20">
-        <v>14000000</v>
+        <v>929668000</v>
       </c>
       <c r="T20">
-        <v>4.30637738330046</v>
+        <v>-17.55802782723927</v>
       </c>
       <c r="U20">
-        <v>-5.133806663025669</v>
+        <v>1.455749769091836</v>
       </c>
       <c r="V20">
-        <v>0.7341373885684321</v>
+        <v>4.948450403583787</v>
       </c>
       <c r="W20" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -2492,70 +2501,70 @@
         <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C21" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E21">
-        <v>58.5099983215332</v>
+        <v>517.280029296875</v>
       </c>
       <c r="F21">
-        <v>359936.6666666667</v>
+        <v>4469773.333333333</v>
       </c>
       <c r="G21">
-        <v>48.79759994506836</v>
+        <v>428.2163989257813</v>
       </c>
       <c r="H21">
-        <v>39.97720002492269</v>
+        <v>380.0418664550782</v>
       </c>
       <c r="I21">
-        <v>36.80184999465942</v>
+        <v>362.5753993225098</v>
       </c>
       <c r="J21">
-        <v>33.83134999275207</v>
+        <v>348.4745994567871</v>
       </c>
       <c r="K21">
-        <v>0.4209107160568237</v>
+        <v>0.1503329128026962</v>
       </c>
       <c r="L21">
-        <v>58.5099983215332</v>
+        <v>688.3699951171875</v>
       </c>
       <c r="M21">
-        <v>156.9596804566893</v>
+        <v>160.3951568308797</v>
       </c>
       <c r="N21">
-        <v>0.97</v>
+        <v>2.53</v>
       </c>
       <c r="O21">
-        <v>1.03</v>
+        <v>2.71</v>
       </c>
       <c r="P21">
-        <v>0.64</v>
+        <v>2.82</v>
       </c>
       <c r="Q21">
-        <v>29523000</v>
+        <v>4756000000</v>
       </c>
       <c r="R21">
-        <v>31725000</v>
+        <v>1247000000</v>
       </c>
       <c r="S21">
-        <v>19649000</v>
+        <v>1295000000</v>
       </c>
       <c r="T21">
-        <v>5.300911046392623</v>
+        <v>27.01351811882313</v>
       </c>
       <c r="U21">
-        <v>7.071891432813131</v>
+        <v>26.78839957035446</v>
       </c>
       <c r="V21">
-        <v>4.868687419315673</v>
+        <v>26.88953488372093</v>
       </c>
       <c r="W21" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -2563,70 +2572,70 @@
         <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E22">
-        <v>882.0499877929688</v>
+        <v>40.38999938964844</v>
       </c>
       <c r="F22">
-        <v>3832246.666666667</v>
+        <v>1467923.333333333</v>
       </c>
       <c r="G22">
-        <v>762.3998010253906</v>
+        <v>34.20039981842041</v>
       </c>
       <c r="H22">
-        <v>651.2884000651042</v>
+        <v>29.07053329467773</v>
       </c>
       <c r="I22">
-        <v>607.6588496398925</v>
+        <v>28.58174997329712</v>
       </c>
       <c r="J22">
-        <v>572.7052001953125</v>
+        <v>27.46369999885559</v>
       </c>
       <c r="K22">
-        <v>11.17089080810547</v>
+        <v>18.28000068664551</v>
       </c>
       <c r="L22">
-        <v>886.1799926757812</v>
+        <v>47.06000137329102</v>
       </c>
       <c r="M22">
-        <v>156.269461302709</v>
+        <v>160.3321714190521</v>
       </c>
       <c r="N22">
-        <v>7.810425</v>
+        <v>0.06</v>
       </c>
       <c r="O22">
-        <v>8.800000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="P22">
-        <v>8.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q22">
-        <v>3359000000</v>
+        <v>53508000</v>
       </c>
       <c r="R22">
-        <v>3774000000</v>
+        <v>18068000</v>
       </c>
       <c r="S22">
-        <v>3481000000</v>
+        <v>12175000</v>
       </c>
       <c r="T22">
-        <v>37.61478163493841</v>
+        <v>12.61044271355007</v>
       </c>
       <c r="U22">
-        <v>42.3331463825014</v>
+        <v>13.52030889879972</v>
       </c>
       <c r="V22">
-        <v>39.86030001145082</v>
+        <v>9.931154868916913</v>
       </c>
       <c r="W22" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="23" spans="1:23">
@@ -2634,70 +2643,70 @@
         <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E23">
-        <v>51.84000015258789</v>
+        <v>55.27999877929688</v>
       </c>
       <c r="F23">
-        <v>458223.3333333333</v>
+        <v>493696.6666666667</v>
       </c>
       <c r="G23">
-        <v>45.76999977111817</v>
+        <v>47.95419967651367</v>
       </c>
       <c r="H23">
-        <v>39.29159992218018</v>
+        <v>38.31506652832032</v>
       </c>
       <c r="I23">
-        <v>35.27864995002746</v>
+        <v>36.02039992332458</v>
       </c>
       <c r="J23">
-        <v>32.59619997978211</v>
+        <v>33.34484996795654</v>
       </c>
       <c r="K23">
-        <v>2.234822273254395</v>
+        <v>8.689999580383301</v>
       </c>
       <c r="L23">
-        <v>52.40999984741211</v>
+        <v>58.38000106811523</v>
       </c>
       <c r="M23">
-        <v>154.3948777935419</v>
+        <v>159.544380796584</v>
       </c>
       <c r="N23">
-        <v>0.98</v>
+        <v>0.3</v>
       </c>
       <c r="O23">
-        <v>1.16</v>
+        <v>0.66</v>
       </c>
       <c r="P23">
-        <v>1.01</v>
+        <v>0.5</v>
       </c>
       <c r="Q23">
-        <v>46726000</v>
+        <v>15874000</v>
       </c>
       <c r="R23">
-        <v>54970000</v>
+        <v>33913000</v>
       </c>
       <c r="S23">
-        <v>48235000</v>
+        <v>26032000</v>
       </c>
       <c r="T23">
-        <v>23.15690355833085</v>
+        <v>13.21412814557684</v>
       </c>
       <c r="U23">
-        <v>26.03757140556466</v>
+        <v>25.11646163986876</v>
       </c>
       <c r="V23">
-        <v>23.8034139528916</v>
+        <v>18.59136421419491</v>
       </c>
       <c r="W23" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:23">
@@ -2705,70 +2714,70 @@
         <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D24" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E24">
-        <v>111.6399993896484</v>
+        <v>28.6299991607666</v>
       </c>
       <c r="F24">
-        <v>1156100</v>
+        <v>1447250</v>
       </c>
       <c r="G24">
-        <v>92.84059951782227</v>
+        <v>23.95279998779297</v>
       </c>
       <c r="H24">
-        <v>83.40993321736654</v>
+        <v>20.97689996083577</v>
       </c>
       <c r="I24">
-        <v>78.39279985427856</v>
+        <v>19.45152498722076</v>
       </c>
       <c r="J24">
-        <v>73.84199991226197</v>
+        <v>18.69807501792908</v>
       </c>
       <c r="K24">
-        <v>0.3787146806716919</v>
+        <v>6.309999942779541</v>
       </c>
       <c r="L24">
-        <v>111.6399993896484</v>
+        <v>37.61000061035156</v>
       </c>
       <c r="M24">
-        <v>152.2920661871823</v>
+        <v>159.1537021783387</v>
       </c>
       <c r="N24">
-        <v>1.61</v>
+        <v>-0.32</v>
       </c>
       <c r="O24">
-        <v>1.52</v>
+        <v>-0.21</v>
       </c>
       <c r="P24">
-        <v>1.72</v>
+        <v>-0.21</v>
       </c>
       <c r="Q24">
-        <v>978000000</v>
+        <v>-37149000</v>
       </c>
       <c r="R24">
-        <v>207000000</v>
+        <v>-24642000</v>
       </c>
       <c r="S24">
-        <v>233000000</v>
+        <v>-24855000</v>
       </c>
       <c r="T24">
-        <v>2.831007931453714</v>
+        <v>-8.405093420094031</v>
       </c>
       <c r="U24">
-        <v>2.544873371035161</v>
+        <v>-7.937254396701668</v>
       </c>
       <c r="V24">
-        <v>2.749262536873156</v>
+        <v>-3.559939614945014</v>
       </c>
       <c r="W24" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:23">
@@ -2776,70 +2785,70 @@
         <v>46</v>
       </c>
       <c r="B25" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C25" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D25" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E25">
-        <v>83.51999664306641</v>
+        <v>27.38999938964844</v>
       </c>
       <c r="F25">
-        <v>328350</v>
+        <v>721873.3333333334</v>
       </c>
       <c r="G25">
-        <v>74.99520019531251</v>
+        <v>22.4988000869751</v>
       </c>
       <c r="H25">
-        <v>62.48453341166179</v>
+        <v>19.06573338826497</v>
       </c>
       <c r="I25">
-        <v>57.10800010681152</v>
+        <v>17.41760003566742</v>
       </c>
       <c r="J25">
-        <v>53.10700012207031</v>
+        <v>15.97405003547668</v>
       </c>
       <c r="K25">
-        <v>3.118403196334839</v>
+        <v>1.899999976158142</v>
       </c>
       <c r="L25">
-        <v>87.20999908447266</v>
+        <v>27.38999938964844</v>
       </c>
       <c r="M25">
-        <v>151.7300167863497</v>
+        <v>158.1967608879753</v>
       </c>
       <c r="N25">
-        <v>4.67</v>
+        <v>0.75</v>
       </c>
       <c r="O25">
-        <v>4.65</v>
+        <v>0.762</v>
       </c>
       <c r="P25">
-        <v>3.64</v>
+        <v>1.315</v>
       </c>
       <c r="Q25">
-        <v>131590000</v>
+        <v>76661000</v>
       </c>
       <c r="R25">
-        <v>130395000</v>
+        <v>75504000</v>
       </c>
       <c r="S25">
-        <v>103066000</v>
+        <v>128734000</v>
       </c>
       <c r="T25">
-        <v>12.99105168383143</v>
+        <v>22.98177610298196</v>
       </c>
       <c r="U25">
-        <v>10.71446179129006</v>
+        <v>24.50593141948362</v>
       </c>
       <c r="V25">
-        <v>10.30114039559034</v>
+        <v>42.45662290205235</v>
       </c>
       <c r="W25" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26" spans="1:23">
@@ -2847,70 +2856,70 @@
         <v>47</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C26" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E26">
-        <v>31.76000022888184</v>
+        <v>58.56000137329102</v>
       </c>
       <c r="F26">
-        <v>290303.3333333333</v>
+        <v>357543.3333333333</v>
       </c>
       <c r="G26">
-        <v>29.16239994049072</v>
+        <v>49.64</v>
       </c>
       <c r="H26">
-        <v>24.04186660766602</v>
+        <v>40.32546670277913</v>
       </c>
       <c r="I26">
-        <v>22.14109998226166</v>
+        <v>37.16305000305176</v>
       </c>
       <c r="J26">
-        <v>20.70329999446869</v>
+        <v>34.09489999771118</v>
       </c>
       <c r="K26">
-        <v>14.10000038146973</v>
+        <v>0.4209107160568237</v>
       </c>
       <c r="L26">
-        <v>32.86000061035156</v>
+        <v>58.56000137329102</v>
       </c>
       <c r="M26">
-        <v>151.708502569371</v>
+        <v>157.690312310653</v>
       </c>
       <c r="N26">
-        <v>0.14</v>
+        <v>0.97</v>
       </c>
       <c r="O26">
-        <v>0.18</v>
+        <v>1.03</v>
       </c>
       <c r="P26">
-        <v>0.11</v>
+        <v>0.64</v>
       </c>
       <c r="Q26">
-        <v>36215000</v>
+        <v>29523000</v>
       </c>
       <c r="R26">
-        <v>48300000</v>
+        <v>31725000</v>
       </c>
       <c r="S26">
-        <v>28265000</v>
+        <v>19649000</v>
       </c>
       <c r="T26">
-        <v>14.76590244678119</v>
+        <v>5.300911046392623</v>
       </c>
       <c r="U26">
-        <v>16.53543307086614</v>
+        <v>7.071891432813131</v>
       </c>
       <c r="V26">
-        <v>11.87644962855894</v>
+        <v>4.868687419315673</v>
       </c>
       <c r="W26" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="27" spans="1:23">
@@ -2918,70 +2927,70 @@
         <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C27" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E27">
-        <v>26.18000030517578</v>
+        <v>60.75</v>
       </c>
       <c r="F27">
-        <v>669986.6666666666</v>
+        <v>1807626.666666667</v>
       </c>
       <c r="G27">
-        <v>22.23420009613037</v>
+        <v>51.04740013122559</v>
       </c>
       <c r="H27">
-        <v>18.88553338368734</v>
+        <v>41.03300009409587</v>
       </c>
       <c r="I27">
-        <v>17.23650003910065</v>
+        <v>38.84759076118469</v>
       </c>
       <c r="J27">
-        <v>15.85175003528595</v>
+        <v>36.22838760375976</v>
       </c>
       <c r="K27">
-        <v>1.899999976158142</v>
+        <v>0.6502050161361694</v>
       </c>
       <c r="L27">
-        <v>26.18000030517578</v>
+        <v>60.75</v>
       </c>
       <c r="M27">
-        <v>151.3124496785799</v>
+        <v>156.8422495088006</v>
       </c>
       <c r="N27">
-        <v>0.75</v>
+        <v>1.13</v>
       </c>
       <c r="O27">
-        <v>0.762</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P27">
-        <v>1.315</v>
+        <v>0.13</v>
       </c>
       <c r="Q27">
-        <v>76661000</v>
+        <v>131000000</v>
       </c>
       <c r="R27">
-        <v>75504000</v>
+        <v>-94000000</v>
       </c>
       <c r="S27">
-        <v>128734000</v>
+        <v>14000000</v>
       </c>
       <c r="T27">
-        <v>22.98177610298196</v>
+        <v>4.30637738330046</v>
       </c>
       <c r="U27">
-        <v>24.50593141948362</v>
+        <v>-5.133806663025669</v>
       </c>
       <c r="V27">
-        <v>42.45662290205235</v>
+        <v>0.7341373885684321</v>
       </c>
       <c r="W27" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="28" spans="1:23">
@@ -2989,70 +2998,70 @@
         <v>49</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E28">
-        <v>122.7399978637695</v>
+        <v>890.3599853515625</v>
       </c>
       <c r="F28">
-        <v>302600</v>
+        <v>3347900</v>
       </c>
       <c r="G28">
-        <v>110.5189999389648</v>
+        <v>772.7170007324219</v>
       </c>
       <c r="H28">
-        <v>89.67393341064454</v>
+        <v>656.0142000325521</v>
       </c>
       <c r="I28">
-        <v>85.43905012130737</v>
+        <v>611.8289497375488</v>
       </c>
       <c r="J28">
-        <v>80.34120012283326</v>
+        <v>575.8327499389649</v>
       </c>
       <c r="K28">
-        <v>8.189999580383301</v>
+        <v>11.17089080810547</v>
       </c>
       <c r="L28">
-        <v>130.3200073242188</v>
+        <v>890.3599853515625</v>
       </c>
       <c r="M28">
-        <v>150.1993502467734</v>
+        <v>155.7719984672208</v>
       </c>
       <c r="N28">
-        <v>-1.1</v>
+        <v>7.810425</v>
       </c>
       <c r="O28">
-        <v>-1.17</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P28">
-        <v>-1.76</v>
+        <v>8.15</v>
       </c>
       <c r="Q28">
-        <v>-129729000</v>
+        <v>3359000000</v>
       </c>
       <c r="R28">
-        <v>-32052000</v>
+        <v>3774000000</v>
       </c>
       <c r="S28">
-        <v>-45297000</v>
+        <v>3481000000</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>37.61478163493841</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>42.3331463825014</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>39.86030001145082</v>
       </c>
       <c r="W28" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29" spans="1:23">
@@ -3060,70 +3069,70 @@
         <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C29" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D29" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E29">
-        <v>38.88999938964844</v>
+        <v>125.4100036621094</v>
       </c>
       <c r="F29">
-        <v>1413806.666666667</v>
+        <v>298270</v>
       </c>
       <c r="G29">
-        <v>33.73199981689453</v>
+        <v>112.1208000183105</v>
       </c>
       <c r="H29">
-        <v>28.88519996643067</v>
+        <v>90.32060012817382</v>
       </c>
       <c r="I29">
-        <v>28.43584997177124</v>
+        <v>85.99880014419556</v>
       </c>
       <c r="J29">
-        <v>27.36609999656677</v>
+        <v>80.8896001625061</v>
       </c>
       <c r="K29">
-        <v>18.28000068664551</v>
+        <v>8.189999580383301</v>
       </c>
       <c r="L29">
-        <v>47.06000137329102</v>
+        <v>130.3200073242188</v>
       </c>
       <c r="M29">
-        <v>150.1477084628251</v>
+        <v>155.7155336731865</v>
       </c>
       <c r="N29">
-        <v>0.06</v>
+        <v>-1.1</v>
       </c>
       <c r="O29">
-        <v>0.06</v>
+        <v>-1.17</v>
       </c>
       <c r="P29">
-        <v>0.07000000000000001</v>
+        <v>-1.76</v>
       </c>
       <c r="Q29">
-        <v>53508000</v>
+        <v>-129729000</v>
       </c>
       <c r="R29">
-        <v>18068000</v>
+        <v>-32052000</v>
       </c>
       <c r="S29">
-        <v>12175000</v>
+        <v>-45297000</v>
       </c>
       <c r="T29">
-        <v>12.61044271355007</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>13.52030889879972</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>9.931154868916913</v>
+        <v>0</v>
       </c>
       <c r="W29" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" spans="1:23">
@@ -3131,70 +3140,70 @@
         <v>51</v>
       </c>
       <c r="B30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C30" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D30" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E30">
-        <v>325.260009765625</v>
+        <v>112.8600006103516</v>
       </c>
       <c r="F30">
-        <v>303986.6666666667</v>
+        <v>1129976.666666667</v>
       </c>
       <c r="G30">
-        <v>254.5346005249023</v>
+        <v>94.164599609375</v>
       </c>
       <c r="H30">
-        <v>240.0925338745117</v>
+        <v>83.94999994913736</v>
       </c>
       <c r="I30">
-        <v>234.1027503967285</v>
+        <v>78.94209985733032</v>
       </c>
       <c r="J30">
-        <v>230.4159006500244</v>
+        <v>74.19649988174439</v>
       </c>
       <c r="K30">
-        <v>1.363492727279663</v>
+        <v>0.3787146806716919</v>
       </c>
       <c r="L30">
-        <v>412.9100646972656</v>
+        <v>112.8600006103516</v>
       </c>
       <c r="M30">
-        <v>148.2450341450622</v>
+        <v>152.7614276342225</v>
       </c>
       <c r="N30">
-        <v>11.92</v>
+        <v>1.61</v>
       </c>
       <c r="O30">
-        <v>9</v>
+        <v>1.52</v>
       </c>
       <c r="P30">
-        <v>8.300000000000001</v>
+        <v>1.72</v>
       </c>
       <c r="Q30">
-        <v>329600000</v>
+        <v>978000000</v>
       </c>
       <c r="R30">
-        <v>247700000</v>
+        <v>207000000</v>
       </c>
       <c r="S30">
-        <v>228700000</v>
+        <v>233000000</v>
       </c>
       <c r="T30">
-        <v>4.517729621557904</v>
+        <v>2.831007931453714</v>
       </c>
       <c r="U30">
-        <v>3.543532373894882</v>
+        <v>2.544873371035161</v>
       </c>
       <c r="V30">
-        <v>3.279417247411741</v>
+        <v>2.749262536873156</v>
       </c>
       <c r="W30" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="31" spans="1:23">
@@ -3202,70 +3211,70 @@
         <v>52</v>
       </c>
       <c r="B31" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C31" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D31" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E31">
-        <v>78.19999694824219</v>
+        <v>23.88999938964844</v>
       </c>
       <c r="F31">
-        <v>2759546.666666667</v>
+        <v>2466806.666666667</v>
       </c>
       <c r="G31">
-        <v>71.2034001159668</v>
+        <v>19.34219985961914</v>
       </c>
       <c r="H31">
-        <v>59.43019989013672</v>
+        <v>16.4557999865214</v>
       </c>
       <c r="I31">
-        <v>54.66484994888306</v>
+        <v>16.22995001316071</v>
       </c>
       <c r="J31">
-        <v>51.13139999389649</v>
+        <v>15.48470002174377</v>
       </c>
       <c r="K31">
-        <v>0.1027423962950706</v>
+        <v>12.61999988555908</v>
       </c>
       <c r="L31">
-        <v>78.66999816894531</v>
+        <v>24.46999931335449</v>
       </c>
       <c r="M31">
-        <v>148.1669075477361</v>
+        <v>152.4592499398751</v>
       </c>
       <c r="N31">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>627928000</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>882231000</v>
+        <v>0</v>
       </c>
       <c r="S31">
-        <v>532259000</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>15.92183813849328</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>17.05988229829651</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>14.88569462090853</v>
+        <v>0</v>
       </c>
       <c r="W31" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="32" spans="1:23">
@@ -3273,70 +3282,70 @@
         <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C32" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E32">
-        <v>11.09000015258789</v>
+        <v>53.59000015258789</v>
       </c>
       <c r="F32">
-        <v>6189286.666666667</v>
+        <v>447556.6666666667</v>
       </c>
       <c r="G32">
-        <v>9.480999946594238</v>
+        <v>46.12339981079101</v>
       </c>
       <c r="H32">
-        <v>8.47013331413269</v>
+        <v>39.58753323872884</v>
       </c>
       <c r="I32">
-        <v>7.506949989795685</v>
+        <v>35.61084994316101</v>
       </c>
       <c r="J32">
-        <v>6.862849990129471</v>
+        <v>32.79539998054504</v>
       </c>
       <c r="K32">
-        <v>2.809999942779541</v>
+        <v>2.234822273254395</v>
       </c>
       <c r="L32">
-        <v>13.52000045776367</v>
+        <v>53.59000015258789</v>
       </c>
       <c r="M32">
-        <v>147.7218641037902</v>
+        <v>152.4422426524919</v>
       </c>
       <c r="N32">
-        <v>-0.42</v>
+        <v>0.98</v>
       </c>
       <c r="O32">
-        <v>-0.49</v>
+        <v>1.16</v>
       </c>
       <c r="P32">
-        <v>-0.05</v>
+        <v>1.01</v>
       </c>
       <c r="Q32">
-        <v>-291590000</v>
+        <v>46726000</v>
       </c>
       <c r="R32">
-        <v>-352014000</v>
+        <v>54970000</v>
       </c>
       <c r="S32">
-        <v>-33617000</v>
+        <v>48235000</v>
       </c>
       <c r="T32">
-        <v>-2326.577834516876</v>
+        <v>23.15690355833085</v>
       </c>
       <c r="U32">
-        <v>-2064.356087262491</v>
+        <v>26.03757140556466</v>
       </c>
       <c r="V32">
-        <v>-122.7973407364115</v>
+        <v>23.8034139528916</v>
       </c>
       <c r="W32" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="33" spans="1:23">
@@ -3344,70 +3353,70 @@
         <v>54</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C33" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="D33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E33">
-        <v>24.07999992370605</v>
+        <v>277.010009765625</v>
       </c>
       <c r="F33">
-        <v>2425276.666666667</v>
+        <v>252616.6666666667</v>
       </c>
       <c r="G33">
-        <v>19.05719989776611</v>
+        <v>232.4763998413086</v>
       </c>
       <c r="H33">
-        <v>16.35779998143514</v>
+        <v>204.0643999226888</v>
       </c>
       <c r="I33">
-        <v>16.14085001468658</v>
+        <v>192.9860000610352</v>
       </c>
       <c r="J33">
-        <v>15.45365002155304</v>
+        <v>184.8533502960205</v>
       </c>
       <c r="K33">
-        <v>12.61999988555908</v>
+        <v>22.75</v>
       </c>
       <c r="L33">
-        <v>24.46999931335449</v>
+        <v>280.2300109863281</v>
       </c>
       <c r="M33">
-        <v>146.9470351554011</v>
+        <v>152.3298878902208</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>153746000</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>143834000</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>135870000</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>11.81754314764511</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>11.3743858453212</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>10.73869106049613</v>
       </c>
       <c r="W33" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" spans="1:23">
@@ -3415,70 +3424,70 @@
         <v>55</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="D34" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E34">
-        <v>95.30000305175781</v>
+        <v>80.34999847412109</v>
       </c>
       <c r="F34">
-        <v>409736.6666666667</v>
+        <v>2774480</v>
       </c>
       <c r="G34">
-        <v>85.99759994506836</v>
+        <v>71.7518000793457</v>
       </c>
       <c r="H34">
-        <v>72.60026646931966</v>
+        <v>59.91053321838379</v>
       </c>
       <c r="I34">
-        <v>66.35374988555908</v>
+        <v>55.07629993438721</v>
       </c>
       <c r="J34">
-        <v>61.86034984588623</v>
+        <v>51.43965000152588</v>
       </c>
       <c r="K34">
-        <v>1.669681549072266</v>
+        <v>0.1027423962950706</v>
       </c>
       <c r="L34">
-        <v>96.55000305175781</v>
+        <v>80.34999847412109</v>
       </c>
       <c r="M34">
-        <v>145.4778827199088</v>
+        <v>152.2883628158504</v>
       </c>
       <c r="N34">
-        <v>0.74</v>
+        <v>2.69</v>
       </c>
       <c r="O34">
-        <v>1.08</v>
+        <v>3.85</v>
       </c>
       <c r="P34">
-        <v>3.58</v>
+        <v>2.35</v>
       </c>
       <c r="Q34">
-        <v>22222000</v>
+        <v>627928000</v>
       </c>
       <c r="R34">
-        <v>32408000</v>
+        <v>882231000</v>
       </c>
       <c r="S34">
-        <v>105259000</v>
+        <v>532259000</v>
       </c>
       <c r="T34">
-        <v>19.36321494545328</v>
+        <v>15.92183813849328</v>
       </c>
       <c r="U34">
-        <v>27.68613045149716</v>
+        <v>17.05988229829651</v>
       </c>
       <c r="V34">
-        <v>52.01237319207602</v>
+        <v>14.88569462090853</v>
       </c>
       <c r="W34" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="35" spans="1:23">
@@ -3486,70 +3495,70 @@
         <v>56</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="D35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E35">
-        <v>358.8699951171875</v>
+        <v>32</v>
       </c>
       <c r="F35">
-        <v>529723.3333333334</v>
+        <v>300743.3333333333</v>
       </c>
       <c r="G35">
-        <v>303.9289996337891</v>
+        <v>29.36619995117188</v>
       </c>
       <c r="H35">
-        <v>273.5848001098633</v>
+        <v>24.25759993871053</v>
       </c>
       <c r="I35">
-        <v>258.0525497436523</v>
+        <v>22.28874998569488</v>
       </c>
       <c r="J35">
-        <v>245.5595498657227</v>
+        <v>20.83010000705719</v>
       </c>
       <c r="K35">
-        <v>4.533332824707031</v>
+        <v>14.10000038146973</v>
       </c>
       <c r="L35">
-        <v>364.4500122070312</v>
+        <v>32.86000061035156</v>
       </c>
       <c r="M35">
-        <v>145.3445901710574</v>
+        <v>151.8357553472608</v>
       </c>
       <c r="N35">
-        <v>3.67</v>
+        <v>0.14</v>
       </c>
       <c r="O35">
-        <v>2.65</v>
+        <v>0.18</v>
       </c>
       <c r="P35">
-        <v>2.85</v>
+        <v>0.11</v>
       </c>
       <c r="Q35">
-        <v>97891000</v>
+        <v>36215000</v>
       </c>
       <c r="R35">
-        <v>70862000</v>
+        <v>48300000</v>
       </c>
       <c r="S35">
-        <v>76097000</v>
+        <v>28265000</v>
       </c>
       <c r="T35">
-        <v>13.41779508498947</v>
+        <v>14.76590244678119</v>
       </c>
       <c r="U35">
-        <v>10.80664789866499</v>
+        <v>16.53543307086614</v>
       </c>
       <c r="V35">
-        <v>11.52050988971061</v>
+        <v>11.87644962855894</v>
       </c>
       <c r="W35" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="36" spans="1:23">
@@ -3557,70 +3566,70 @@
         <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C36" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D36" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E36">
-        <v>79.90000152587891</v>
+        <v>51.52999877929688</v>
       </c>
       <c r="F36">
-        <v>1760630</v>
+        <v>1359946.666666667</v>
       </c>
       <c r="G36">
-        <v>70.77319999694824</v>
+        <v>40.53039993286133</v>
       </c>
       <c r="H36">
-        <v>61.32293342590332</v>
+        <v>39.72273338317871</v>
       </c>
       <c r="I36">
-        <v>56.97220012664795</v>
+        <v>36.15615003585815</v>
       </c>
       <c r="J36">
-        <v>53.74840005874634</v>
+        <v>34.08510004997253</v>
       </c>
       <c r="K36">
-        <v>0.5319142937660217</v>
+        <v>17.70000076293945</v>
       </c>
       <c r="L36">
-        <v>79.90000152587891</v>
+        <v>51.52999877929688</v>
       </c>
       <c r="M36">
-        <v>144.9718432923428</v>
+        <v>151.1944962367647</v>
       </c>
       <c r="N36">
-        <v>5.63</v>
+        <v>0.26</v>
       </c>
       <c r="O36">
-        <v>1.7</v>
+        <v>0.33</v>
       </c>
       <c r="P36">
-        <v>2.85</v>
+        <v>0.32</v>
       </c>
       <c r="Q36">
-        <v>640536000</v>
+        <v>50614000</v>
       </c>
       <c r="R36">
-        <v>191530000</v>
+        <v>64519000</v>
       </c>
       <c r="S36">
-        <v>320216000</v>
+        <v>61977000</v>
       </c>
       <c r="T36">
-        <v>17.25519606781436</v>
+        <v>21.29627292082166</v>
       </c>
       <c r="U36">
-        <v>10.75909085036308</v>
+        <v>25.93322052019985</v>
       </c>
       <c r="V36">
-        <v>12.7729829408224</v>
+        <v>23.00172576963759</v>
       </c>
       <c r="W36" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="37" spans="1:23">
@@ -3628,70 +3637,70 @@
         <v>58</v>
       </c>
       <c r="B37" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C37" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D37" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E37">
-        <v>20.95999908447266</v>
+        <v>153.8899993896484</v>
       </c>
       <c r="F37">
-        <v>860880</v>
+        <v>582933.3333333334</v>
       </c>
       <c r="G37">
-        <v>19.88539993286133</v>
+        <v>145.5597998046875</v>
       </c>
       <c r="H37">
-        <v>17.47233329772949</v>
+        <v>117.8234331258138</v>
       </c>
       <c r="I37">
-        <v>15.80524997711182</v>
+        <v>108.963074836731</v>
       </c>
       <c r="J37">
-        <v>15.07380000114441</v>
+        <v>104.0745748901367</v>
       </c>
       <c r="K37">
-        <v>9.220000267028809</v>
+        <v>63</v>
       </c>
       <c r="L37">
-        <v>22.13999938964844</v>
+        <v>202.6900024414062</v>
       </c>
       <c r="M37">
-        <v>143.9441540201111</v>
+        <v>150.8990004468832</v>
       </c>
       <c r="N37">
-        <v>0.12</v>
+        <v>-0.46</v>
       </c>
       <c r="O37">
-        <v>0.07000000000000001</v>
+        <v>-0.35</v>
       </c>
       <c r="P37">
-        <v>0.14</v>
+        <v>-0.06</v>
       </c>
       <c r="Q37">
-        <v>24732000</v>
+        <v>-18445000</v>
       </c>
       <c r="R37">
-        <v>13726000</v>
+        <v>-13930000</v>
       </c>
       <c r="S37">
-        <v>27460000</v>
+        <v>-2582000</v>
       </c>
       <c r="T37">
-        <v>4.982463067683896</v>
+        <v>-19.20054130016135</v>
       </c>
       <c r="U37">
-        <v>2.904020903195777</v>
+        <v>-13.41693635382956</v>
       </c>
       <c r="V37">
-        <v>5.375344278468673</v>
+        <v>-2.232386024675561</v>
       </c>
       <c r="W37" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="38" spans="1:23">
@@ -3699,70 +3708,70 @@
         <v>59</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="D38" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E38">
-        <v>250.2299957275391</v>
+        <v>21.79999923706055</v>
       </c>
       <c r="F38">
-        <v>6934630</v>
+        <v>854906.6666666666</v>
       </c>
       <c r="G38">
-        <v>218.6271997070313</v>
+        <v>19.93279991149902</v>
       </c>
       <c r="H38">
-        <v>186.5971332804362</v>
+        <v>17.5938666343689</v>
       </c>
       <c r="I38">
-        <v>180.9470998382568</v>
+        <v>15.91784997940064</v>
       </c>
       <c r="J38">
-        <v>174.496849899292</v>
+        <v>15.14284999847412</v>
       </c>
       <c r="K38">
-        <v>13.18666744232178</v>
+        <v>9.220000267028809</v>
       </c>
       <c r="L38">
-        <v>257.8800048828125</v>
+        <v>22.13999938964844</v>
       </c>
       <c r="M38">
-        <v>143.8215703284683</v>
+        <v>149.4288426412054</v>
       </c>
       <c r="N38">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="O38">
-        <v>0.25</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="P38">
-        <v>0.31</v>
+        <v>0.14</v>
       </c>
       <c r="Q38">
-        <v>20000000</v>
+        <v>24732000</v>
       </c>
       <c r="R38">
-        <v>84200000</v>
+        <v>13726000</v>
       </c>
       <c r="S38">
-        <v>107800000</v>
+        <v>27460000</v>
       </c>
       <c r="T38">
-        <v>1.279263144428809</v>
+        <v>4.982463067683896</v>
       </c>
       <c r="U38">
-        <v>5.087305902966587</v>
+        <v>2.904020903195777</v>
       </c>
       <c r="V38">
-        <v>6.264164100180138</v>
+        <v>5.375344278468673</v>
       </c>
       <c r="W38" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="39" spans="1:23">
@@ -3770,70 +3779,70 @@
         <v>60</v>
       </c>
       <c r="B39" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D39" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E39">
-        <v>177.1699981689453</v>
+        <v>320.2099914550781</v>
       </c>
       <c r="F39">
-        <v>634616.6666666666</v>
+        <v>304383.3333333333</v>
       </c>
       <c r="G39">
-        <v>145.0614001464844</v>
+        <v>258.4278002929688</v>
       </c>
       <c r="H39">
-        <v>132.174200592041</v>
+        <v>241.3940004475911</v>
       </c>
       <c r="I39">
-        <v>126.4774004364014</v>
+        <v>235.0403003692627</v>
       </c>
       <c r="J39">
-        <v>122.3506503295898</v>
+        <v>230.2825006866455</v>
       </c>
       <c r="K39">
-        <v>1.039746522903442</v>
+        <v>1.363492727279663</v>
       </c>
       <c r="L39">
-        <v>177.1699981689453</v>
+        <v>412.9100646972656</v>
       </c>
       <c r="M39">
-        <v>143.4652562835982</v>
+        <v>148.9902393566263</v>
       </c>
       <c r="N39">
-        <v>6.31</v>
+        <v>11.92</v>
       </c>
       <c r="O39">
-        <v>5.716567</v>
+        <v>9</v>
       </c>
       <c r="P39">
-        <v>6.07</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q39">
-        <v>352600000</v>
+        <v>329600000</v>
       </c>
       <c r="R39">
-        <v>286400000</v>
+        <v>247700000</v>
       </c>
       <c r="S39">
-        <v>288700000</v>
+        <v>228700000</v>
       </c>
       <c r="T39">
-        <v>5.28952895289529</v>
+        <v>4.517729621557904</v>
       </c>
       <c r="U39">
-        <v>4.276541735105271</v>
+        <v>3.543532373894882</v>
       </c>
       <c r="V39">
-        <v>4.511853970337725</v>
+        <v>3.279417247411741</v>
       </c>
       <c r="W39" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="40" spans="1:23">
@@ -3841,70 +3850,70 @@
         <v>61</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D40" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E40">
-        <v>83.37000274658203</v>
+        <v>81.98000335693359</v>
       </c>
       <c r="F40">
-        <v>526633.3333333334</v>
+        <v>1766906.666666667</v>
       </c>
       <c r="G40">
-        <v>70.82940002441406</v>
+        <v>71.51440017700196</v>
       </c>
       <c r="H40">
-        <v>62.2607332611084</v>
+        <v>61.78553347269694</v>
       </c>
       <c r="I40">
-        <v>60.75819997787475</v>
+        <v>57.3703501701355</v>
       </c>
       <c r="J40">
-        <v>58.24099994659424</v>
+        <v>54.02715007781983</v>
       </c>
       <c r="K40">
-        <v>7.03000020980835</v>
+        <v>0.5319142937660217</v>
       </c>
       <c r="L40">
-        <v>84.54000091552734</v>
+        <v>82.16000366210938</v>
       </c>
       <c r="M40">
-        <v>142.9079512128387</v>
+        <v>148.8116249814337</v>
       </c>
       <c r="N40">
-        <v>1.95</v>
+        <v>5.63</v>
       </c>
       <c r="O40">
-        <v>0.88</v>
+        <v>1.7</v>
       </c>
       <c r="P40">
-        <v>0.25</v>
+        <v>2.85</v>
       </c>
       <c r="Q40">
-        <v>154800000</v>
+        <v>640536000</v>
       </c>
       <c r="R40">
-        <v>73300000</v>
+        <v>191530000</v>
       </c>
       <c r="S40">
-        <v>24800000</v>
+        <v>320216000</v>
       </c>
       <c r="T40">
-        <v>6.409407088439881</v>
+        <v>17.25519606781436</v>
       </c>
       <c r="U40">
-        <v>3.721945770285366</v>
+        <v>10.75909085036308</v>
       </c>
       <c r="V40">
-        <v>1.431622698146972</v>
+        <v>12.7729829408224</v>
       </c>
       <c r="W40" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="1:23">
@@ -3915,67 +3924,67 @@
         <v>107</v>
       </c>
       <c r="C41" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="D41" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E41">
-        <v>51.20999908447266</v>
+        <v>98.38999938964844</v>
       </c>
       <c r="F41">
-        <v>1931023.333333333</v>
+        <v>431203.3333333333</v>
       </c>
       <c r="G41">
-        <v>47.42</v>
+        <v>87.18839996337891</v>
       </c>
       <c r="H41">
-        <v>39.96759995778402</v>
+        <v>73.23539978027344</v>
       </c>
       <c r="I41">
-        <v>37.11009996414185</v>
+        <v>66.90064987182618</v>
       </c>
       <c r="J41">
-        <v>34.91004997253418</v>
+        <v>62.22584981918335</v>
       </c>
       <c r="K41">
-        <v>1.498309969902039</v>
+        <v>1.669681549072266</v>
       </c>
       <c r="L41">
-        <v>66.26741027832031</v>
+        <v>98.38999938964844</v>
       </c>
       <c r="M41">
-        <v>141.3006451766136</v>
+        <v>148.7165859347409</v>
       </c>
       <c r="N41">
-        <v>2.47</v>
+        <v>0.74</v>
       </c>
       <c r="O41">
-        <v>1.45</v>
+        <v>1.08</v>
       </c>
       <c r="P41">
-        <v>1.94</v>
+        <v>3.58</v>
       </c>
       <c r="Q41">
-        <v>216410000</v>
+        <v>22222000</v>
       </c>
       <c r="R41">
-        <v>125500000</v>
+        <v>32408000</v>
       </c>
       <c r="S41">
-        <v>164442000</v>
+        <v>105259000</v>
       </c>
       <c r="T41">
-        <v>11.15498213945145</v>
+        <v>19.36321494545328</v>
       </c>
       <c r="U41">
-        <v>9.065862224899842</v>
+        <v>27.68613045149716</v>
       </c>
       <c r="V41">
-        <v>9.315159438876666</v>
+        <v>52.01237319207602</v>
       </c>
       <c r="W41" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="42" spans="1:23">
@@ -3983,70 +3992,70 @@
         <v>63</v>
       </c>
       <c r="B42" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C42" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D42" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E42">
-        <v>197.2700042724609</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="F42">
-        <v>384186.6666666667</v>
+        <v>6555683.333333333</v>
       </c>
       <c r="G42">
-        <v>182.2733996582031</v>
+        <v>9.597999954223633</v>
       </c>
       <c r="H42">
-        <v>152.5387326558431</v>
+        <v>8.540399983723958</v>
       </c>
       <c r="I42">
-        <v>145.698599319458</v>
+        <v>7.591799992322922</v>
       </c>
       <c r="J42">
-        <v>140.5115492248535</v>
+        <v>6.919999989271164</v>
       </c>
       <c r="K42">
-        <v>0.8828129768371582</v>
+        <v>2.809999942779541</v>
       </c>
       <c r="L42">
-        <v>199.8800048828125</v>
+        <v>13.52000045776367</v>
       </c>
       <c r="M42">
-        <v>141.2256668516544</v>
+        <v>148.5227436888644</v>
       </c>
       <c r="N42">
-        <v>0.47</v>
+        <v>-0.42</v>
       </c>
       <c r="O42">
-        <v>0.6</v>
+        <v>-0.49</v>
       </c>
       <c r="P42">
-        <v>0.62</v>
+        <v>-0.05</v>
       </c>
       <c r="Q42">
-        <v>29674000</v>
+        <v>-291590000</v>
       </c>
       <c r="R42">
-        <v>37868000</v>
+        <v>-352014000</v>
       </c>
       <c r="S42">
-        <v>38791000</v>
+        <v>-33617000</v>
       </c>
       <c r="T42">
-        <v>14.97922776765387</v>
+        <v>-2326.577834516876</v>
       </c>
       <c r="U42">
-        <v>19.11530870304841</v>
+        <v>-2064.356087262491</v>
       </c>
       <c r="V42">
-        <v>17.55145624917991</v>
+        <v>-122.7973407364115</v>
       </c>
       <c r="W42" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="43" spans="1:23">
@@ -4054,31 +4063,31 @@
         <v>64</v>
       </c>
       <c r="B43" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C43" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D43" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E43">
-        <v>145.7899932861328</v>
+        <v>148.7100067138672</v>
       </c>
       <c r="F43">
-        <v>1339783.333333333</v>
+        <v>1351393.333333333</v>
       </c>
       <c r="G43">
-        <v>133.5200006103516</v>
+        <v>135.5126007080078</v>
       </c>
       <c r="H43">
-        <v>108.9818668619792</v>
+        <v>109.4322002156575</v>
       </c>
       <c r="I43">
-        <v>104.7097500228882</v>
+        <v>105.3104000473023</v>
       </c>
       <c r="J43">
-        <v>100.3948999786377</v>
+        <v>100.714700012207</v>
       </c>
       <c r="K43">
         <v>0.1500000059604645</v>
@@ -4087,7 +4096,7 @@
         <v>150.7100067138672</v>
       </c>
       <c r="M43">
-        <v>141.0569639842882</v>
+        <v>146.7136265496125</v>
       </c>
       <c r="N43">
         <v>0.12</v>
@@ -4117,7 +4126,7 @@
         <v>15.86025952242641</v>
       </c>
       <c r="W43" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="44" spans="1:23">
@@ -4125,70 +4134,70 @@
         <v>65</v>
       </c>
       <c r="B44" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C44" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="D44" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E44">
-        <v>48.65999984741211</v>
+        <v>576.6199951171875</v>
       </c>
       <c r="F44">
-        <v>11942060</v>
+        <v>545900</v>
       </c>
       <c r="G44">
-        <v>39.25800010681152</v>
+        <v>486.7007995605469</v>
       </c>
       <c r="H44">
-        <v>36.99859994252522</v>
+        <v>459.1158662923177</v>
       </c>
       <c r="I44">
-        <v>35.82669997215271</v>
+        <v>433.7208996582031</v>
       </c>
       <c r="J44">
-        <v>34.55434994697571</v>
+        <v>423.6927993774414</v>
       </c>
       <c r="K44">
-        <v>3.490809917449951</v>
+        <v>5.184493541717529</v>
       </c>
       <c r="L44">
-        <v>62.26396942138672</v>
+        <v>576.6199951171875</v>
       </c>
       <c r="M44">
-        <v>140.7356501155672</v>
+        <v>146.0291730023319</v>
       </c>
       <c r="N44">
-        <v>1.08</v>
+        <v>2.57</v>
       </c>
       <c r="O44">
-        <v>1.29</v>
+        <v>2.45</v>
       </c>
       <c r="P44">
-        <v>-0.57</v>
+        <v>2.26</v>
       </c>
       <c r="Q44">
-        <v>695000000</v>
+        <v>124337000</v>
       </c>
       <c r="R44">
-        <v>828000000</v>
+        <v>119090000</v>
       </c>
       <c r="S44">
-        <v>-363000000</v>
+        <v>109802000</v>
       </c>
       <c r="T44">
-        <v>4.973166368515206</v>
+        <v>25.09739250491504</v>
       </c>
       <c r="U44">
-        <v>6.163007071082992</v>
+        <v>25.88845508378042</v>
       </c>
       <c r="V44">
-        <v>-2.84505055255114</v>
+        <v>24.34283307283873</v>
       </c>
       <c r="W44" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="45" spans="1:23">
@@ -4196,70 +4205,70 @@
         <v>66</v>
       </c>
       <c r="B45" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C45" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="D45" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E45">
-        <v>31.70000076293945</v>
+        <v>50.79000091552734</v>
       </c>
       <c r="F45">
-        <v>813766.6666666666</v>
+        <v>1216286.666666667</v>
       </c>
       <c r="G45">
-        <v>30.07259983062744</v>
+        <v>45.53159988403321</v>
       </c>
       <c r="H45">
-        <v>24.86789993286133</v>
+        <v>38.55859995524089</v>
       </c>
       <c r="I45">
-        <v>23.23862494468689</v>
+        <v>35.53905002593994</v>
       </c>
       <c r="J45">
-        <v>22.0960749912262</v>
+        <v>33.21135003089905</v>
       </c>
       <c r="K45">
-        <v>0.1500000059604645</v>
+        <v>7.050000190734863</v>
       </c>
       <c r="L45">
-        <v>38.15000152587891</v>
+        <v>50.79000091552734</v>
       </c>
       <c r="M45">
-        <v>139.9960415506373</v>
+        <v>145.8673501442741</v>
       </c>
       <c r="N45">
-        <v>0.01</v>
+        <v>2.72</v>
       </c>
       <c r="O45">
-        <v>-0.02</v>
+        <v>2.51</v>
       </c>
       <c r="P45">
-        <v>-0.36</v>
+        <v>1.74</v>
       </c>
       <c r="Q45">
-        <v>668000</v>
+        <v>309779000</v>
       </c>
       <c r="R45">
-        <v>-934000</v>
+        <v>275331000</v>
       </c>
       <c r="S45">
-        <v>-21005000</v>
+        <v>191051000</v>
       </c>
       <c r="T45">
-        <v>0.1908331524036978</v>
+        <v>15.2252187606284</v>
       </c>
       <c r="U45">
-        <v>-0.2433083686095734</v>
+        <v>11.04803689701082</v>
       </c>
       <c r="V45">
-        <v>-5.378119847195338</v>
+        <v>11.49623583737951</v>
       </c>
       <c r="W45" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="46" spans="1:23">
@@ -4267,70 +4276,70 @@
         <v>67</v>
       </c>
       <c r="B46" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C46" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="D46" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E46">
-        <v>31.80999946594238</v>
+        <v>46.63000106811523</v>
       </c>
       <c r="F46">
-        <v>1497226.666666667</v>
+        <v>2810660</v>
       </c>
       <c r="G46">
-        <v>29.04249992370605</v>
+        <v>38.33180000305176</v>
       </c>
       <c r="H46">
-        <v>25.02323331197103</v>
+        <v>32.8854333114624</v>
       </c>
       <c r="I46">
-        <v>22.86844998836517</v>
+        <v>32.50314995765686</v>
       </c>
       <c r="J46">
-        <v>21.57317502498627</v>
+        <v>29.90734997749329</v>
       </c>
       <c r="K46">
-        <v>4.052896976470947</v>
+        <v>13.1899995803833</v>
       </c>
       <c r="L46">
-        <v>31.94000053405762</v>
+        <v>46.91999816894531</v>
       </c>
       <c r="M46">
-        <v>139.906775555251</v>
+        <v>145.7771804789558</v>
       </c>
       <c r="N46">
-        <v>-0.23</v>
+        <v>-0.55</v>
       </c>
       <c r="O46">
-        <v>0.2</v>
+        <v>-0.51</v>
       </c>
       <c r="P46">
-        <v>0.22</v>
+        <v>-0.54</v>
       </c>
       <c r="Q46">
-        <v>-16058000</v>
+        <v>-76858000</v>
       </c>
       <c r="R46">
-        <v>26801000</v>
+        <v>-23224000</v>
       </c>
       <c r="S46">
-        <v>29397000</v>
+        <v>-25646000</v>
       </c>
       <c r="T46">
-        <v>-6.97067696915764</v>
+        <v>0</v>
       </c>
       <c r="U46">
-        <v>9.771009621168758</v>
+        <v>0</v>
       </c>
       <c r="V46">
-        <v>10.04277154121031</v>
+        <v>0</v>
       </c>
       <c r="W46" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="47" spans="1:23">
@@ -4338,70 +4347,70 @@
         <v>68</v>
       </c>
       <c r="B47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C47" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="D47" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E47">
-        <v>74.62999725341797</v>
+        <v>199.75</v>
       </c>
       <c r="F47">
-        <v>784123.3333333334</v>
+        <v>372246.6666666667</v>
       </c>
       <c r="G47">
-        <v>62.28579971313476</v>
+        <v>183.542399597168</v>
       </c>
       <c r="H47">
-        <v>58.51693321228027</v>
+        <v>153.5413992818197</v>
       </c>
       <c r="I47">
-        <v>53.37334990501404</v>
+        <v>146.3852492523193</v>
       </c>
       <c r="J47">
-        <v>49.87364994049072</v>
+        <v>140.9472992706299</v>
       </c>
       <c r="K47">
-        <v>5.739999771118164</v>
+        <v>0.8828129768371582</v>
       </c>
       <c r="L47">
-        <v>74.62999725341797</v>
+        <v>199.8800048828125</v>
       </c>
       <c r="M47">
-        <v>139.8026609577829</v>
+        <v>145.5406891148138</v>
       </c>
       <c r="N47">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="O47">
-        <v>0.99</v>
+        <v>0.6</v>
       </c>
       <c r="P47">
-        <v>0.97</v>
+        <v>0.62</v>
       </c>
       <c r="Q47">
-        <v>28000000</v>
+        <v>29674000</v>
       </c>
       <c r="R47">
-        <v>72000000</v>
+        <v>37868000</v>
       </c>
       <c r="S47">
-        <v>72000000</v>
+        <v>38791000</v>
       </c>
       <c r="T47">
-        <v>2.5</v>
+        <v>14.97922776765387</v>
       </c>
       <c r="U47">
-        <v>5.955334987593052</v>
+        <v>19.11530870304841</v>
       </c>
       <c r="V47">
-        <v>6.070826306913997</v>
+        <v>17.55145624917991</v>
       </c>
       <c r="W47" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="48" spans="1:23">
@@ -4409,70 +4418,70 @@
         <v>69</v>
       </c>
       <c r="B48" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C48" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D48" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E48">
-        <v>109.3000030517578</v>
+        <v>178.1600036621094</v>
       </c>
       <c r="F48">
-        <v>330960</v>
+        <v>649970</v>
       </c>
       <c r="G48">
-        <v>96.5352001953125</v>
+        <v>146.8088000488281</v>
       </c>
       <c r="H48">
-        <v>86.77593317667643</v>
+        <v>132.9584672037761</v>
       </c>
       <c r="I48">
-        <v>81.68179985046386</v>
+        <v>127.1879504394531</v>
       </c>
       <c r="J48">
-        <v>77.47779987335205</v>
+        <v>122.5495503234863</v>
       </c>
       <c r="K48">
-        <v>5.466728210449219</v>
+        <v>1.039746522903442</v>
       </c>
       <c r="L48">
-        <v>109.3000030517578</v>
+        <v>178.1600036621094</v>
       </c>
       <c r="M48">
-        <v>139.6430871945962</v>
+        <v>145.4928880053916</v>
       </c>
       <c r="N48">
-        <v>0.84</v>
+        <v>6.31</v>
       </c>
       <c r="O48">
-        <v>1.08</v>
+        <v>5.716567</v>
       </c>
       <c r="P48">
-        <v>1.59</v>
+        <v>6.07</v>
       </c>
       <c r="Q48">
-        <v>34500</v>
+        <v>352600000</v>
       </c>
       <c r="R48">
-        <v>44410000</v>
+        <v>286400000</v>
       </c>
       <c r="S48">
-        <v>65900000</v>
+        <v>288700000</v>
       </c>
       <c r="T48">
-        <v>3.835890593729153</v>
+        <v>5.28952895289529</v>
       </c>
       <c r="U48">
-        <v>4.825983154156529</v>
+        <v>4.276541735105271</v>
       </c>
       <c r="V48">
-        <v>6.657238104859077</v>
+        <v>4.511853970337725</v>
       </c>
       <c r="W48" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="49" spans="1:23">
@@ -4480,70 +4489,70 @@
         <v>70</v>
       </c>
       <c r="B49" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C49" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="D49" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E49">
-        <v>48.65000152587891</v>
+        <v>84.91999816894531</v>
       </c>
       <c r="F49">
-        <v>1229433.333333333</v>
+        <v>534493.3333333334</v>
       </c>
       <c r="G49">
-        <v>45.22599990844726</v>
+        <v>71.79439994812012</v>
       </c>
       <c r="H49">
-        <v>38.28939996083577</v>
+        <v>62.61053324381511</v>
       </c>
       <c r="I49">
-        <v>35.26940002441406</v>
+        <v>61.08144996643066</v>
       </c>
       <c r="J49">
-        <v>33.01105002403259</v>
+        <v>58.39124994277954</v>
       </c>
       <c r="K49">
-        <v>7.050000190734863</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="L49">
-        <v>48.77000045776367</v>
+        <v>84.91999816894531</v>
       </c>
       <c r="M49">
-        <v>139.3553137449881</v>
+        <v>145.4521356941933</v>
       </c>
       <c r="N49">
-        <v>2.72</v>
+        <v>1.95</v>
       </c>
       <c r="O49">
-        <v>2.51</v>
+        <v>0.88</v>
       </c>
       <c r="P49">
-        <v>1.74</v>
+        <v>0.25</v>
       </c>
       <c r="Q49">
-        <v>309779000</v>
+        <v>154800000</v>
       </c>
       <c r="R49">
-        <v>275331000</v>
+        <v>73300000</v>
       </c>
       <c r="S49">
-        <v>191051000</v>
+        <v>24800000</v>
       </c>
       <c r="T49">
-        <v>15.2252187606284</v>
+        <v>6.409407088439881</v>
       </c>
       <c r="U49">
-        <v>11.04803689701082</v>
+        <v>3.721945770285366</v>
       </c>
       <c r="V49">
-        <v>11.49623583737951</v>
+        <v>1.431622698146972</v>
       </c>
       <c r="W49" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:23">
@@ -4551,70 +4560,70 @@
         <v>71</v>
       </c>
       <c r="B50" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C50" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D50" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E50">
-        <v>178.3699951171875</v>
+        <v>98.5</v>
       </c>
       <c r="F50">
-        <v>300920</v>
+        <v>348636.6666666667</v>
       </c>
       <c r="G50">
-        <v>150.0002001953125</v>
+        <v>79.24680023193359</v>
       </c>
       <c r="H50">
-        <v>137.6920003763835</v>
+        <v>72.29986701965332</v>
       </c>
       <c r="I50">
-        <v>130.817250289917</v>
+        <v>70.7708002281189</v>
       </c>
       <c r="J50">
-        <v>125.8424003982544</v>
+        <v>68.27780023574829</v>
       </c>
       <c r="K50">
-        <v>2.075098752975464</v>
+        <v>11.37919998168945</v>
       </c>
       <c r="L50">
-        <v>178.3699951171875</v>
+        <v>98.5</v>
       </c>
       <c r="M50">
-        <v>138.51020449617</v>
+        <v>145.2793893797502</v>
       </c>
       <c r="N50">
-        <v>4.61</v>
+        <v>5.52</v>
       </c>
       <c r="O50">
-        <v>4.21</v>
+        <v>2.95</v>
       </c>
       <c r="P50">
-        <v>4.31</v>
+        <v>2.43</v>
       </c>
       <c r="Q50">
-        <v>340100000</v>
+        <v>219587000</v>
       </c>
       <c r="R50">
-        <v>298000000</v>
+        <v>117360000</v>
       </c>
       <c r="S50">
-        <v>298300000</v>
+        <v>96733000</v>
       </c>
       <c r="T50">
-        <v>4.914242778909648</v>
+        <v>10.19132136261764</v>
       </c>
       <c r="U50">
-        <v>4.24997860749023</v>
+        <v>7.207490483975371</v>
       </c>
       <c r="V50">
-        <v>4.064586455920425</v>
+        <v>6.263755974277502</v>
       </c>
       <c r="W50" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51" spans="1:23">
@@ -4622,70 +4631,70 @@
         <v>72</v>
       </c>
       <c r="B51" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C51" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="D51" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E51">
-        <v>46.77000045776367</v>
+        <v>363.1199951171875</v>
       </c>
       <c r="F51">
-        <v>2710540</v>
+        <v>545840</v>
       </c>
       <c r="G51">
-        <v>37.80199996948242</v>
+        <v>306.5693994140625</v>
       </c>
       <c r="H51">
-        <v>32.7364999516805</v>
+        <v>275.2768666585287</v>
       </c>
       <c r="I51">
-        <v>32.22104994773865</v>
+        <v>259.8110997009277</v>
       </c>
       <c r="J51">
-        <v>29.75299998283386</v>
+        <v>246.3666498565674</v>
       </c>
       <c r="K51">
-        <v>13.1899995803833</v>
+        <v>4.533332824707031</v>
       </c>
       <c r="L51">
-        <v>46.91999816894531</v>
+        <v>364.4500122070312</v>
       </c>
       <c r="M51">
-        <v>137.6989336084455</v>
+        <v>145.2735781460551</v>
       </c>
       <c r="N51">
-        <v>-0.55</v>
+        <v>3.67</v>
       </c>
       <c r="O51">
-        <v>-0.51</v>
+        <v>2.65</v>
       </c>
       <c r="P51">
-        <v>-0.54</v>
+        <v>2.85</v>
       </c>
       <c r="Q51">
-        <v>-76858000</v>
+        <v>97891000</v>
       </c>
       <c r="R51">
-        <v>-23224000</v>
+        <v>70862000</v>
       </c>
       <c r="S51">
-        <v>-25646000</v>
+        <v>76097000</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>13.41779508498947</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>10.80664789866499</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>11.52050988971061</v>
       </c>
       <c r="W51" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="52" spans="1:23">
@@ -4693,70 +4702,70 @@
         <v>73</v>
       </c>
       <c r="B52" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C52" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D52" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E52">
-        <v>27.65999984741211</v>
+        <v>33.22999954223633</v>
       </c>
       <c r="F52">
-        <v>1091536.666666667</v>
+        <v>1223483.333333333</v>
       </c>
       <c r="G52">
-        <v>24.25220005035401</v>
+        <v>30.89240005493164</v>
       </c>
       <c r="H52">
-        <v>22.07539994557699</v>
+        <v>25.39820004781087</v>
       </c>
       <c r="I52">
-        <v>20.61684997558594</v>
+        <v>23.2330500459671</v>
       </c>
       <c r="J52">
-        <v>19.55664995670319</v>
+        <v>21.70435004711151</v>
       </c>
       <c r="K52">
-        <v>9.090000152587891</v>
+        <v>6.139999866485596</v>
       </c>
       <c r="L52">
-        <v>27.65999984741211</v>
+        <v>33.22999954223633</v>
       </c>
       <c r="M52">
-        <v>137.6807078737178</v>
+        <v>145.1313097846991</v>
       </c>
       <c r="N52">
-        <v>0.06</v>
+        <v>1.45</v>
       </c>
       <c r="O52">
-        <v>0.04</v>
+        <v>1.98</v>
       </c>
       <c r="P52">
-        <v>0.05</v>
+        <v>0.73</v>
       </c>
       <c r="Q52">
-        <v>28000000</v>
+        <v>149226000</v>
       </c>
       <c r="R52">
-        <v>22000000</v>
+        <v>202973000</v>
       </c>
       <c r="S52">
-        <v>26000000</v>
+        <v>74742000</v>
       </c>
       <c r="T52">
-        <v>1.613832853025936</v>
+        <v>13.92298534422595</v>
       </c>
       <c r="U52">
-        <v>1.291837933059307</v>
+        <v>13.32889853191875</v>
       </c>
       <c r="V52">
-        <v>1.61090458488228</v>
+        <v>9.586474121445089</v>
       </c>
       <c r="W52" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="53" spans="1:23">
@@ -4764,70 +4773,70 @@
         <v>74</v>
       </c>
       <c r="B53" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C53" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D53" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E53">
-        <v>135.9100036621094</v>
+        <v>52.95999908447266</v>
       </c>
       <c r="F53">
-        <v>363716.6666666667</v>
+        <v>1988386.666666667</v>
       </c>
       <c r="G53">
-        <v>127.1771998596191</v>
+        <v>47.78159996032715</v>
       </c>
       <c r="H53">
-        <v>107.5080000305176</v>
+        <v>40.257799949646</v>
       </c>
       <c r="I53">
-        <v>100.7709000015259</v>
+        <v>37.37069994926453</v>
       </c>
       <c r="J53">
-        <v>96.56470012664795</v>
+        <v>35.10489996910096</v>
       </c>
       <c r="K53">
-        <v>0.8630853891372681</v>
+        <v>1.498309969902039</v>
       </c>
       <c r="L53">
-        <v>156.8002166748047</v>
+        <v>66.26741027832031</v>
       </c>
       <c r="M53">
-        <v>137.2149423636228</v>
+        <v>145.1199216672256</v>
       </c>
       <c r="N53">
-        <v>1.48</v>
+        <v>2.47</v>
       </c>
       <c r="O53">
-        <v>0.86</v>
+        <v>1.45</v>
       </c>
       <c r="P53">
-        <v>0.06</v>
+        <v>1.94</v>
       </c>
       <c r="Q53">
-        <v>46150000</v>
+        <v>216410000</v>
       </c>
       <c r="R53">
-        <v>26584000</v>
+        <v>125500000</v>
       </c>
       <c r="S53">
-        <v>1819000</v>
+        <v>164442000</v>
       </c>
       <c r="T53">
-        <v>16.77644971790845</v>
+        <v>11.15498213945145</v>
       </c>
       <c r="U53">
-        <v>10.59685012377076</v>
+        <v>9.065862224899842</v>
       </c>
       <c r="V53">
-        <v>0.6156335034589194</v>
+        <v>9.315159438876666</v>
       </c>
       <c r="W53" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="54" spans="1:23">
@@ -4835,70 +4844,70 @@
         <v>75</v>
       </c>
       <c r="B54" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C54" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="D54" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E54">
-        <v>32.43999862670898</v>
+        <v>26.18000030517578</v>
       </c>
       <c r="F54">
-        <v>1035336.666666667</v>
+        <v>280770</v>
       </c>
       <c r="G54">
-        <v>29.9352001953125</v>
+        <v>23.37279987335205</v>
       </c>
       <c r="H54">
-        <v>25.71260005950928</v>
+        <v>19.33946664174398</v>
       </c>
       <c r="I54">
-        <v>23.89925002098083</v>
+        <v>19.27444994926453</v>
       </c>
       <c r="J54">
-        <v>22.87504998207092</v>
+        <v>18.89949993133545</v>
       </c>
       <c r="K54">
-        <v>16.70999908447266</v>
+        <v>7.619999885559082</v>
       </c>
       <c r="L54">
-        <v>36.84999847412109</v>
+        <v>32.29000091552734</v>
       </c>
       <c r="M54">
-        <v>137.1420559203621</v>
+        <v>144.8172267752956</v>
       </c>
       <c r="N54">
-        <v>0.32</v>
+        <v>-0.13</v>
       </c>
       <c r="O54">
-        <v>0.43</v>
+        <v>-0.53</v>
       </c>
       <c r="P54">
-        <v>0.53</v>
+        <v>-0.86</v>
       </c>
       <c r="Q54">
-        <v>50100000</v>
+        <v>-63643000</v>
       </c>
       <c r="R54">
-        <v>67700000</v>
+        <v>-81972000</v>
       </c>
       <c r="S54">
-        <v>82800000</v>
+        <v>-39741000</v>
       </c>
       <c r="T54">
-        <v>6.357868020304569</v>
+        <v>-139.4792785290057</v>
       </c>
       <c r="U54">
-        <v>7.764651909622663</v>
+        <v>-768.535533470842</v>
       </c>
       <c r="V54">
-        <v>10.66460587326121</v>
+        <v>-294.3995851544559</v>
       </c>
       <c r="W54" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="55" spans="1:23">
@@ -4906,70 +4915,70 @@
         <v>76</v>
       </c>
       <c r="B55" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C55" t="s">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="D55" t="s">
-        <v>203</v>
+        <v>151</v>
       </c>
       <c r="E55">
-        <v>46.36999893188477</v>
+        <v>76.41999816894531</v>
       </c>
       <c r="F55">
-        <v>1276853.333333333</v>
+        <v>781463.3333333334</v>
       </c>
       <c r="G55">
-        <v>40.00559997558594</v>
+        <v>62.71119979858398</v>
       </c>
       <c r="H55">
-        <v>39.49166674296061</v>
+        <v>58.95719985961914</v>
       </c>
       <c r="I55">
-        <v>35.88055005073547</v>
+        <v>53.82484990119934</v>
       </c>
       <c r="J55">
-        <v>33.93405005455017</v>
+        <v>50.22944993972779</v>
       </c>
       <c r="K55">
-        <v>17.70000076293945</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="L55">
-        <v>47.9900016784668</v>
+        <v>76.41999816894531</v>
       </c>
       <c r="M55">
-        <v>137.0375592317531</v>
+        <v>143.9628823579038</v>
       </c>
       <c r="N55">
-        <v>0.26</v>
+        <v>0.39</v>
       </c>
       <c r="O55">
-        <v>0.33</v>
+        <v>0.99</v>
       </c>
       <c r="P55">
-        <v>0.32</v>
+        <v>0.97</v>
       </c>
       <c r="Q55">
-        <v>50614000</v>
+        <v>28000000</v>
       </c>
       <c r="R55">
-        <v>64519000</v>
+        <v>72000000</v>
       </c>
       <c r="S55">
-        <v>61977000</v>
+        <v>72000000</v>
       </c>
       <c r="T55">
-        <v>21.29627292082166</v>
+        <v>2.5</v>
       </c>
       <c r="U55">
-        <v>25.93322052019985</v>
+        <v>5.955334987593052</v>
       </c>
       <c r="V55">
-        <v>23.00172576963759</v>
+        <v>6.070826306913997</v>
       </c>
       <c r="W55" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="56" spans="1:23">
@@ -4977,70 +4986,70 @@
         <v>77</v>
       </c>
       <c r="B56" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C56" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D56" t="s">
         <v>204</v>
       </c>
       <c r="E56">
-        <v>31.17000007629395</v>
+        <v>239.0099945068359</v>
       </c>
       <c r="F56">
-        <v>1195853.333333333</v>
+        <v>7440356.666666667</v>
       </c>
       <c r="G56">
-        <v>30.71640007019043</v>
+        <v>220.7449993896484</v>
       </c>
       <c r="H56">
-        <v>25.20546672821045</v>
+        <v>187.456933186849</v>
       </c>
       <c r="I56">
-        <v>23.06045005321503</v>
+        <v>181.6665998077393</v>
       </c>
       <c r="J56">
-        <v>21.55570004940033</v>
+        <v>174.9100498962402</v>
       </c>
       <c r="K56">
-        <v>6.139999866485596</v>
+        <v>13.18666744232178</v>
       </c>
       <c r="L56">
-        <v>33.15999984741211</v>
+        <v>257.8800048828125</v>
       </c>
       <c r="M56">
-        <v>137.0017119680191</v>
+        <v>142.7719647448292</v>
       </c>
       <c r="N56">
-        <v>1.45</v>
+        <v>0.06</v>
       </c>
       <c r="O56">
-        <v>1.98</v>
+        <v>0.25</v>
       </c>
       <c r="P56">
-        <v>0.73</v>
+        <v>0.31</v>
       </c>
       <c r="Q56">
-        <v>149226000</v>
+        <v>20000000</v>
       </c>
       <c r="R56">
-        <v>202973000</v>
+        <v>84200000</v>
       </c>
       <c r="S56">
-        <v>74742000</v>
+        <v>107800000</v>
       </c>
       <c r="T56">
-        <v>13.92298534422595</v>
+        <v>1.279263144428809</v>
       </c>
       <c r="U56">
-        <v>13.32889853191875</v>
+        <v>5.087305902966587</v>
       </c>
       <c r="V56">
-        <v>9.586474121445089</v>
+        <v>6.264164100180138</v>
       </c>
       <c r="W56" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="57" spans="1:23">
@@ -5048,70 +5057,70 @@
         <v>78</v>
       </c>
       <c r="B57" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C57" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="D57" t="s">
         <v>205</v>
       </c>
       <c r="E57">
-        <v>130.5700073242188</v>
+        <v>32.27999877929688</v>
       </c>
       <c r="F57">
-        <v>857743.3333333334</v>
+        <v>1499500</v>
       </c>
       <c r="G57">
-        <v>115.8842001342774</v>
+        <v>29.19569988250732</v>
       </c>
       <c r="H57">
-        <v>101.54420018514</v>
+        <v>25.22329996744792</v>
       </c>
       <c r="I57">
-        <v>97.50655010223389</v>
+        <v>23.03734998226166</v>
       </c>
       <c r="J57">
-        <v>93.27060009002686</v>
+        <v>21.6935750246048</v>
       </c>
       <c r="K57">
-        <v>4.719488620758057</v>
+        <v>4.052896976470947</v>
       </c>
       <c r="L57">
-        <v>131.6100006103516</v>
+        <v>32.27999877929688</v>
       </c>
       <c r="M57">
-        <v>136.8625057143158</v>
+        <v>142.6908856879183</v>
       </c>
       <c r="N57">
-        <v>4.84</v>
+        <v>-0.23</v>
       </c>
       <c r="O57">
-        <v>1.32</v>
+        <v>0.2</v>
       </c>
       <c r="P57">
-        <v>4.17</v>
+        <v>0.22</v>
       </c>
       <c r="Q57">
-        <v>470000000</v>
+        <v>-16058000</v>
       </c>
       <c r="R57">
-        <v>124000000</v>
+        <v>26801000</v>
       </c>
       <c r="S57">
-        <v>383000000</v>
+        <v>29397000</v>
       </c>
       <c r="T57">
-        <v>18.58442071965204</v>
+        <v>-6.97067696915764</v>
       </c>
       <c r="U57">
-        <v>5.426695842450766</v>
+        <v>9.771009621168758</v>
       </c>
       <c r="V57">
-        <v>16.43071643071643</v>
+        <v>10.04277154121031</v>
       </c>
       <c r="W57" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="58" spans="1:23">
@@ -5119,70 +5128,70 @@
         <v>79</v>
       </c>
       <c r="B58" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C58" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D58" t="s">
         <v>206</v>
       </c>
       <c r="E58">
-        <v>542.530029296875</v>
+        <v>110.9899978637695</v>
       </c>
       <c r="F58">
-        <v>611080</v>
+        <v>324503.3333333333</v>
       </c>
       <c r="G58">
-        <v>482.6217999267578</v>
+        <v>97.63220016479492</v>
       </c>
       <c r="H58">
-        <v>456.5865997314453</v>
+        <v>87.22346649169921</v>
       </c>
       <c r="I58">
-        <v>431.7973497009277</v>
+        <v>82.18749982833862</v>
       </c>
       <c r="J58">
-        <v>423.4409494018554</v>
+        <v>77.85634986877442</v>
       </c>
       <c r="K58">
-        <v>5.184493541717529</v>
+        <v>5.466728210449219</v>
       </c>
       <c r="L58">
-        <v>575.969970703125</v>
+        <v>110.9899978637695</v>
       </c>
       <c r="M58">
-        <v>136.5423472406811</v>
+        <v>142.5062305314136</v>
       </c>
       <c r="N58">
-        <v>2.57</v>
+        <v>0.84</v>
       </c>
       <c r="O58">
-        <v>2.45</v>
+        <v>1.08</v>
       </c>
       <c r="P58">
-        <v>2.26</v>
+        <v>1.59</v>
       </c>
       <c r="Q58">
-        <v>124337000</v>
+        <v>34500</v>
       </c>
       <c r="R58">
-        <v>119090000</v>
+        <v>44410000</v>
       </c>
       <c r="S58">
-        <v>109802000</v>
+        <v>65900000</v>
       </c>
       <c r="T58">
-        <v>25.09739250491504</v>
+        <v>3.835890593729153</v>
       </c>
       <c r="U58">
-        <v>25.88845508378042</v>
+        <v>4.825983154156529</v>
       </c>
       <c r="V58">
-        <v>24.34283307283873</v>
+        <v>6.657238104859077</v>
       </c>
       <c r="W58" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="59" spans="1:23">
@@ -5190,70 +5199,70 @@
         <v>80</v>
       </c>
       <c r="B59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C59" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="D59" t="s">
         <v>207</v>
       </c>
       <c r="E59">
-        <v>25.93000030517578</v>
+        <v>577.4500122070312</v>
       </c>
       <c r="F59">
-        <v>494276.6666666667</v>
+        <v>1278030</v>
       </c>
       <c r="G59">
-        <v>23.64779987335205</v>
+        <v>523.1798016357421</v>
       </c>
       <c r="H59">
-        <v>21.39466663996378</v>
+        <v>463.6784672037761</v>
       </c>
       <c r="I59">
-        <v>20.23989997863769</v>
+        <v>445.0828002929687</v>
       </c>
       <c r="J59">
-        <v>19.20340000629425</v>
+        <v>432.659800567627</v>
       </c>
       <c r="K59">
-        <v>4.372677803039551</v>
+        <v>23.73999977111816</v>
       </c>
       <c r="L59">
-        <v>26.21999931335449</v>
+        <v>701.72998046875</v>
       </c>
       <c r="M59">
-        <v>135.8850515203913</v>
+        <v>142.0004653050219</v>
       </c>
       <c r="N59">
-        <v>0.51</v>
+        <v>0.39</v>
       </c>
       <c r="O59">
-        <v>1.27</v>
+        <v>0.74</v>
       </c>
       <c r="P59">
-        <v>1.89</v>
+        <v>0.73</v>
       </c>
       <c r="Q59">
-        <v>20311465</v>
+        <v>80000000</v>
       </c>
       <c r="R59">
-        <v>51263710</v>
+        <v>150000000</v>
       </c>
       <c r="S59">
-        <v>76021035</v>
+        <v>150000000</v>
       </c>
       <c r="T59">
-        <v>26.73680365703607</v>
+        <v>4.369197160021846</v>
       </c>
       <c r="U59">
-        <v>49.61536070215114</v>
+        <v>7.731958762886598</v>
       </c>
       <c r="V59">
-        <v>56.88704797132189</v>
+        <v>7.15648854961832</v>
       </c>
       <c r="W59" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="60" spans="1:23">
@@ -5261,70 +5270,70 @@
         <v>81</v>
       </c>
       <c r="B60" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C60" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D60" t="s">
         <v>208</v>
       </c>
       <c r="E60">
-        <v>107.0599975585938</v>
+        <v>102.0400009155273</v>
       </c>
       <c r="F60">
-        <v>378833.3333333333</v>
+        <v>6426186.666666667</v>
       </c>
       <c r="G60">
-        <v>102.0441999816895</v>
+        <v>87.58699966430665</v>
       </c>
       <c r="H60">
-        <v>87.04593332926433</v>
+        <v>78.62993303934734</v>
       </c>
       <c r="I60">
-        <v>82.94034990310669</v>
+        <v>75.63724983215332</v>
       </c>
       <c r="J60">
-        <v>79.04674993515015</v>
+        <v>73.21089990615845</v>
       </c>
       <c r="K60">
-        <v>20.81999969482422</v>
+        <v>0.9100000262260437</v>
       </c>
       <c r="L60">
-        <v>116.4700012207031</v>
+        <v>102.0400009155273</v>
       </c>
       <c r="M60">
-        <v>135.2549302624207</v>
+        <v>141.1814826649681</v>
       </c>
       <c r="N60">
-        <v>1.05</v>
+        <v>0.7</v>
       </c>
       <c r="O60">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P60">
-        <v>0.59</v>
+        <v>1.03</v>
       </c>
       <c r="Q60">
-        <v>52215000</v>
+        <v>311900000</v>
       </c>
       <c r="R60">
-        <v>66214000</v>
+        <v>604300000</v>
       </c>
       <c r="S60">
-        <v>29068000</v>
+        <v>461700000</v>
       </c>
       <c r="T60">
-        <v>20.53663083621432</v>
+        <v>14.22512086107817</v>
       </c>
       <c r="U60">
-        <v>26.14364117345126</v>
+        <v>28.72694428598593</v>
       </c>
       <c r="V60">
-        <v>14.59493384881882</v>
+        <v>23.55972852987702</v>
       </c>
       <c r="W60" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="61" spans="1:23">
@@ -5332,70 +5341,70 @@
         <v>82</v>
       </c>
       <c r="B61" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C61" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="D61" t="s">
         <v>209</v>
       </c>
       <c r="E61">
-        <v>321.3599853515625</v>
+        <v>32.7599983215332</v>
       </c>
       <c r="F61">
-        <v>324073.3333333333</v>
+        <v>1015366.666666667</v>
       </c>
       <c r="G61">
-        <v>319.8221984863281</v>
+        <v>30.15640022277832</v>
       </c>
       <c r="H61">
-        <v>275.007866414388</v>
+        <v>25.89146672566732</v>
       </c>
       <c r="I61">
-        <v>252.3559999847412</v>
+        <v>24.04545001983643</v>
       </c>
       <c r="J61">
-        <v>237.1800000762939</v>
+        <v>22.95684998512268</v>
       </c>
       <c r="K61">
-        <v>36.5</v>
+        <v>16.70999908447266</v>
       </c>
       <c r="L61">
-        <v>344.0599975585938</v>
+        <v>36.84999847412109</v>
       </c>
       <c r="M61">
-        <v>135.1770809495814</v>
+        <v>140.8652637658371</v>
       </c>
       <c r="N61">
-        <v>-0.06</v>
+        <v>0.32</v>
       </c>
       <c r="O61">
-        <v>0.1</v>
+        <v>0.43</v>
       </c>
       <c r="P61">
-        <v>0.22</v>
+        <v>0.53</v>
       </c>
       <c r="Q61">
-        <v>-2271000</v>
+        <v>50100000</v>
       </c>
       <c r="R61">
-        <v>3877000</v>
+        <v>67700000</v>
       </c>
       <c r="S61">
-        <v>8562000</v>
+        <v>82800000</v>
       </c>
       <c r="T61">
-        <v>-1.062814140903603</v>
+        <v>6.357868020304569</v>
       </c>
       <c r="U61">
-        <v>1.752585708086214</v>
+        <v>7.764651909622663</v>
       </c>
       <c r="V61">
-        <v>3.546839658986404</v>
+        <v>10.66460587326121</v>
       </c>
       <c r="W61" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="62" spans="1:23">
@@ -5403,40 +5412,40 @@
         <v>83</v>
       </c>
       <c r="B62" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C62" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D62" t="s">
         <v>210</v>
       </c>
       <c r="E62">
-        <v>137.9199981689453</v>
+        <v>144.3600006103516</v>
       </c>
       <c r="F62">
-        <v>365793.3333333333</v>
+        <v>363786.6666666667</v>
       </c>
       <c r="G62">
-        <v>128.281400604248</v>
+        <v>128.9378005981445</v>
       </c>
       <c r="H62">
-        <v>113.8142668660482</v>
+        <v>114.5760668436686</v>
       </c>
       <c r="I62">
-        <v>104.3352502822876</v>
+        <v>105.0413502883911</v>
       </c>
       <c r="J62">
-        <v>98.52790019989014</v>
+        <v>99.01425022125244</v>
       </c>
       <c r="K62">
         <v>0.577300488948822</v>
       </c>
       <c r="L62">
-        <v>142.2700042724609</v>
+        <v>144.3600006103516</v>
       </c>
       <c r="M62">
-        <v>135.0001188985055</v>
+        <v>140.8376763186334</v>
       </c>
       <c r="N62">
         <v>7.1</v>
@@ -5466,7 +5475,7 @@
         <v>10.21560758672308</v>
       </c>
       <c r="W62" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="63" spans="1:23">
@@ -5474,70 +5483,70 @@
         <v>84</v>
       </c>
       <c r="B63" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C63" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D63" t="s">
         <v>211</v>
       </c>
       <c r="E63">
-        <v>86.76999664306641</v>
+        <v>133.4600067138672</v>
       </c>
       <c r="F63">
-        <v>503973.3333333333</v>
+        <v>862876.6666666666</v>
       </c>
       <c r="G63">
-        <v>77.78129989624023</v>
+        <v>116.9606002807617</v>
       </c>
       <c r="H63">
-        <v>71.55040008544921</v>
+        <v>102.1220002237956</v>
       </c>
       <c r="I63">
-        <v>65.87225004196166</v>
+        <v>98.06970012664794</v>
       </c>
       <c r="J63">
-        <v>62.83700006484985</v>
+        <v>93.59650012969971</v>
       </c>
       <c r="K63">
-        <v>10.5</v>
+        <v>4.719488620758057</v>
       </c>
       <c r="L63">
-        <v>88.73000335693359</v>
+        <v>133.4600067138672</v>
       </c>
       <c r="M63">
-        <v>134.9960291967982</v>
+        <v>140.8107844466733</v>
       </c>
       <c r="N63">
-        <v>-0.25</v>
+        <v>4.84</v>
       </c>
       <c r="O63">
-        <v>-0.21</v>
+        <v>1.32</v>
       </c>
       <c r="P63">
-        <v>-0.08</v>
+        <v>4.17</v>
       </c>
       <c r="Q63">
-        <v>-7426000</v>
+        <v>470000000</v>
       </c>
       <c r="R63">
-        <v>-6720000</v>
+        <v>124000000</v>
       </c>
       <c r="S63">
-        <v>-2636000</v>
+        <v>383000000</v>
       </c>
       <c r="T63">
-        <v>-28.91406767122221</v>
+        <v>18.58442071965204</v>
       </c>
       <c r="U63">
-        <v>-21.41832669322709</v>
+        <v>5.426695842450766</v>
       </c>
       <c r="V63">
-        <v>-6.343552967223371</v>
+        <v>16.43071643071643</v>
       </c>
       <c r="W63" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="64" spans="1:23">
@@ -5545,70 +5554,70 @@
         <v>85</v>
       </c>
       <c r="B64" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C64" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="D64" t="s">
         <v>212</v>
       </c>
       <c r="E64">
-        <v>93.5</v>
+        <v>30.59000015258789</v>
       </c>
       <c r="F64">
-        <v>338983.3333333333</v>
+        <v>824543.3333333334</v>
       </c>
       <c r="G64">
-        <v>78.12240020751953</v>
+        <v>30.18539981842041</v>
       </c>
       <c r="H64">
-        <v>71.96966702779135</v>
+        <v>25.00309993743896</v>
       </c>
       <c r="I64">
-        <v>70.37845024108887</v>
+        <v>23.37212493896484</v>
       </c>
       <c r="J64">
-        <v>68.18270021438599</v>
+        <v>22.20457497596741</v>
       </c>
       <c r="K64">
-        <v>11.37919998168945</v>
+        <v>0.1500000059604645</v>
       </c>
       <c r="L64">
-        <v>93.5</v>
+        <v>38.15000152587891</v>
       </c>
       <c r="M64">
-        <v>134.9456555725604</v>
+        <v>140.4424059594698</v>
       </c>
       <c r="N64">
-        <v>5.52</v>
+        <v>0.01</v>
       </c>
       <c r="O64">
-        <v>2.95</v>
+        <v>-0.02</v>
       </c>
       <c r="P64">
-        <v>2.43</v>
+        <v>-0.36</v>
       </c>
       <c r="Q64">
-        <v>219587000</v>
+        <v>668000</v>
       </c>
       <c r="R64">
-        <v>117360000</v>
+        <v>-934000</v>
       </c>
       <c r="S64">
-        <v>96733000</v>
+        <v>-21005000</v>
       </c>
       <c r="T64">
-        <v>10.19132136261764</v>
+        <v>0.1908331524036978</v>
       </c>
       <c r="U64">
-        <v>7.207490483975371</v>
+        <v>-0.2433083686095734</v>
       </c>
       <c r="V64">
-        <v>6.263755974277502</v>
+        <v>-5.378119847195338</v>
       </c>
       <c r="W64" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="65" spans="1:23">
@@ -5616,70 +5625,70 @@
         <v>86</v>
       </c>
       <c r="B65" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C65" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D65" t="s">
         <v>213</v>
       </c>
       <c r="E65">
-        <v>96.63999938964844</v>
+        <v>112.0899963378906</v>
       </c>
       <c r="F65">
-        <v>6704670</v>
+        <v>371016.6666666667</v>
       </c>
       <c r="G65">
-        <v>86.57939971923828</v>
+        <v>103.203999786377</v>
       </c>
       <c r="H65">
-        <v>78.25619972229003</v>
+        <v>87.46439997355144</v>
       </c>
       <c r="I65">
-        <v>75.27524984359741</v>
+        <v>83.38669988632202</v>
       </c>
       <c r="J65">
-        <v>73.0359499168396</v>
+        <v>79.37514993667602</v>
       </c>
       <c r="K65">
-        <v>0.9100000262260437</v>
+        <v>20.81999969482422</v>
       </c>
       <c r="L65">
-        <v>96.83000183105469</v>
+        <v>116.4700012207031</v>
       </c>
       <c r="M65">
-        <v>134.8857080482051</v>
+        <v>139.902384881612</v>
       </c>
       <c r="N65">
-        <v>0.7</v>
+        <v>1.05</v>
       </c>
       <c r="O65">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P65">
-        <v>1.03</v>
+        <v>0.59</v>
       </c>
       <c r="Q65">
-        <v>311900000</v>
+        <v>52215000</v>
       </c>
       <c r="R65">
-        <v>604300000</v>
+        <v>66214000</v>
       </c>
       <c r="S65">
-        <v>461700000</v>
+        <v>29068000</v>
       </c>
       <c r="T65">
-        <v>14.22512086107817</v>
+        <v>20.53663083621432</v>
       </c>
       <c r="U65">
-        <v>28.72694428598593</v>
+        <v>26.14364117345126</v>
       </c>
       <c r="V65">
-        <v>23.55972852987702</v>
+        <v>14.59493384881882</v>
       </c>
       <c r="W65" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="66" spans="1:23">
@@ -5687,70 +5696,70 @@
         <v>87</v>
       </c>
       <c r="B66" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C66" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="D66" t="s">
         <v>214</v>
       </c>
       <c r="E66">
-        <v>55.7400016784668</v>
+        <v>54.20000076293945</v>
       </c>
       <c r="F66">
-        <v>5420766.666666667</v>
+        <v>1056093.333333333</v>
       </c>
       <c r="G66">
-        <v>48.35939987182617</v>
+        <v>49.35900047302246</v>
       </c>
       <c r="H66">
-        <v>43.28706657409668</v>
+        <v>43.06820012410482</v>
       </c>
       <c r="I66">
-        <v>42.0682999420166</v>
+        <v>41.09615013122558</v>
       </c>
       <c r="J66">
-        <v>40.82479997634888</v>
+        <v>39.34195007324219</v>
       </c>
       <c r="K66">
-        <v>11.99751472473145</v>
+        <v>27.71999931335449</v>
       </c>
       <c r="L66">
-        <v>60.77000045776367</v>
+        <v>71.16999816894531</v>
       </c>
       <c r="M66">
-        <v>134.2274858842702</v>
+        <v>139.8322253529184</v>
       </c>
       <c r="N66">
-        <v>0.33</v>
+        <v>0.12</v>
       </c>
       <c r="O66">
-        <v>0.84</v>
+        <v>0.08</v>
       </c>
       <c r="P66">
-        <v>0.79</v>
+        <v>0.14</v>
       </c>
       <c r="Q66">
-        <v>245000000</v>
+        <v>36997000</v>
       </c>
       <c r="R66">
-        <v>614000000</v>
+        <v>25722000</v>
       </c>
       <c r="S66">
-        <v>583000000</v>
+        <v>45490000</v>
       </c>
       <c r="T66">
-        <v>0.9910602321912545</v>
+        <v>13.78777037401428</v>
       </c>
       <c r="U66">
-        <v>2.452174607612125</v>
+        <v>8.963993476169898</v>
       </c>
       <c r="V66">
-        <v>2.786540483701367</v>
+        <v>14.46832330929898</v>
       </c>
       <c r="W66" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67" spans="1:23">
@@ -5758,70 +5767,70 @@
         <v>88</v>
       </c>
       <c r="B67" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C67" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D67" t="s">
         <v>215</v>
       </c>
       <c r="E67">
-        <v>78.31999969482422</v>
+        <v>134.4299926757812</v>
       </c>
       <c r="F67">
-        <v>5536276.666666667</v>
+        <v>378520</v>
       </c>
       <c r="G67">
-        <v>69.55319931030273</v>
+        <v>127.5173997497559</v>
       </c>
       <c r="H67">
-        <v>61.45006624857584</v>
+        <v>108.1021333312988</v>
       </c>
       <c r="I67">
-        <v>59.10594972610474</v>
+        <v>101.2862999725342</v>
       </c>
       <c r="J67">
-        <v>56.8217497253418</v>
+        <v>96.91935009002685</v>
       </c>
       <c r="K67">
-        <v>1.5</v>
+        <v>0.8630853891372681</v>
       </c>
       <c r="L67">
-        <v>78.31999969482422</v>
+        <v>156.8002166748047</v>
       </c>
       <c r="M67">
-        <v>133.9592665205222</v>
+        <v>139.0980624397909</v>
       </c>
       <c r="N67">
-        <v>0.29</v>
+        <v>1.48</v>
       </c>
       <c r="O67">
-        <v>0.4</v>
+        <v>0.86</v>
       </c>
       <c r="P67">
-        <v>0.31</v>
+        <v>0.06</v>
       </c>
       <c r="Q67">
-        <v>231600000</v>
+        <v>46150000</v>
       </c>
       <c r="R67">
-        <v>313800000</v>
+        <v>26584000</v>
       </c>
       <c r="S67">
-        <v>247700000</v>
+        <v>1819000</v>
       </c>
       <c r="T67">
-        <v>20.14789038712484</v>
+        <v>16.77644971790845</v>
       </c>
       <c r="U67">
-        <v>24.45830085736555</v>
+        <v>10.59685012377076</v>
       </c>
       <c r="V67">
-        <v>19.62291056008873</v>
+        <v>0.6156335034589194</v>
       </c>
       <c r="W67" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="68" spans="1:23">
@@ -5829,70 +5838,70 @@
         <v>89</v>
       </c>
       <c r="B68" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C68" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="D68" t="s">
         <v>216</v>
       </c>
       <c r="E68">
-        <v>109</v>
+        <v>22.70999908447266</v>
       </c>
       <c r="F68">
-        <v>1139393.333333333</v>
+        <v>467663.3333333333</v>
       </c>
       <c r="G68">
-        <v>95.95980010986328</v>
+        <v>22.59979991912842</v>
       </c>
       <c r="H68">
-        <v>90.63326675415038</v>
+        <v>18.69719997406006</v>
       </c>
       <c r="I68">
-        <v>86.02295001983643</v>
+        <v>16.42369998931885</v>
       </c>
       <c r="J68">
-        <v>84.1902001953125</v>
+        <v>15.30272500038147</v>
       </c>
       <c r="K68">
-        <v>24</v>
+        <v>7.369999885559082</v>
       </c>
       <c r="L68">
-        <v>143.3099975585938</v>
+        <v>28.52000045776367</v>
       </c>
       <c r="M68">
-        <v>133.7349871025708</v>
+        <v>138.7206221345322</v>
       </c>
       <c r="N68">
-        <v>0.71</v>
+        <v>-0.72</v>
       </c>
       <c r="O68">
-        <v>0.64</v>
+        <v>-0.35</v>
       </c>
       <c r="P68">
-        <v>0.66</v>
+        <v>0.22</v>
       </c>
       <c r="Q68">
-        <v>76175000</v>
+        <v>-23095000</v>
       </c>
       <c r="R68">
-        <v>69237000</v>
+        <v>-11294000</v>
       </c>
       <c r="S68">
-        <v>71524000</v>
+        <v>7130000</v>
       </c>
       <c r="T68">
-        <v>6.938726061736672</v>
+        <v>-8.962945139557267</v>
       </c>
       <c r="U68">
-        <v>6.606149022631144</v>
+        <v>-4.791033885938269</v>
       </c>
       <c r="V68">
-        <v>6.37439263064457</v>
+        <v>2.378141114157444</v>
       </c>
       <c r="W68" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="69" spans="1:23">
@@ -5900,70 +5909,70 @@
         <v>90</v>
       </c>
       <c r="B69" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C69" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D69" t="s">
         <v>217</v>
       </c>
       <c r="E69">
-        <v>31.77000045776367</v>
+        <v>47.70999908447266</v>
       </c>
       <c r="F69">
-        <v>1587213.333333333</v>
+        <v>13039106.66666667</v>
       </c>
       <c r="G69">
-        <v>28.39959991455078</v>
+        <v>39.79060005187988</v>
       </c>
       <c r="H69">
-        <v>26.47099994659424</v>
+        <v>37.15966660817464</v>
       </c>
       <c r="I69">
-        <v>24.87084998607635</v>
+        <v>36.01009997367859</v>
       </c>
       <c r="J69">
-        <v>23.5651500082016</v>
+        <v>34.62664994239807</v>
       </c>
       <c r="K69">
-        <v>0.1598737090826035</v>
+        <v>3.490809917449951</v>
       </c>
       <c r="L69">
-        <v>32.02597808837891</v>
+        <v>62.26396942138672</v>
       </c>
       <c r="M69">
-        <v>132.9784173760003</v>
+        <v>138.6566111160424</v>
       </c>
       <c r="N69">
-        <v>-0.02</v>
+        <v>1.08</v>
       </c>
       <c r="O69">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P69">
-        <v>0.11</v>
+        <v>-0.57</v>
       </c>
       <c r="Q69">
-        <v>359000000</v>
+        <v>695000000</v>
       </c>
       <c r="R69">
-        <v>-64000000</v>
+        <v>828000000</v>
       </c>
       <c r="S69">
-        <v>23000000</v>
+        <v>-363000000</v>
       </c>
       <c r="T69">
-        <v>8.586462568763453</v>
+        <v>4.973166368515206</v>
       </c>
       <c r="U69">
-        <v>-5.85544373284538</v>
+        <v>6.163007071082992</v>
       </c>
       <c r="V69">
-        <v>2.167766258246937</v>
+        <v>-2.84505055255114</v>
       </c>
       <c r="W69" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="70" spans="1:23">
@@ -5971,70 +5980,70 @@
         <v>91</v>
       </c>
       <c r="B70" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C70" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="D70" t="s">
         <v>218</v>
       </c>
       <c r="E70">
-        <v>332.8699951171875</v>
+        <v>28.34000015258789</v>
       </c>
       <c r="F70">
-        <v>392226.9666666667</v>
+        <v>1109150</v>
       </c>
       <c r="G70">
-        <v>298.304599609375</v>
+        <v>24.46980003356934</v>
       </c>
       <c r="H70">
-        <v>258.8318660481771</v>
+        <v>22.19426661173503</v>
       </c>
       <c r="I70">
-        <v>253.1587993621826</v>
+        <v>20.75674997329712</v>
       </c>
       <c r="J70">
-        <v>242.4993492889404</v>
+        <v>19.64124995708466</v>
       </c>
       <c r="K70">
-        <v>0.03128649666905403</v>
+        <v>9.090000152587891</v>
       </c>
       <c r="L70">
-        <v>335.4299926757812</v>
+        <v>28.34000015258789</v>
       </c>
       <c r="M70">
-        <v>132.7518171058426</v>
+        <v>138.6466069282945</v>
       </c>
       <c r="N70">
-        <v>2.57</v>
+        <v>0.06</v>
       </c>
       <c r="O70">
-        <v>2.27</v>
+        <v>0.04</v>
       </c>
       <c r="P70">
-        <v>3.37</v>
+        <v>0.05</v>
       </c>
       <c r="Q70">
-        <v>139100000</v>
+        <v>28000000</v>
       </c>
       <c r="R70">
-        <v>122900000</v>
+        <v>22000000</v>
       </c>
       <c r="S70">
-        <v>181900000</v>
+        <v>26000000</v>
       </c>
       <c r="T70">
-        <v>10.56830268956086</v>
+        <v>1.613832853025936</v>
       </c>
       <c r="U70">
-        <v>10.07707445063955</v>
+        <v>1.291837933059307</v>
       </c>
       <c r="V70">
-        <v>14.15123696903688</v>
+        <v>1.61090458488228</v>
       </c>
       <c r="W70" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="71" spans="1:23">
@@ -6042,70 +6051,70 @@
         <v>92</v>
       </c>
       <c r="B71" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C71" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D71" t="s">
         <v>219</v>
       </c>
       <c r="E71">
-        <v>619.4199829101562</v>
+        <v>78.25</v>
       </c>
       <c r="F71">
-        <v>1309846.666666667</v>
+        <v>5572526.666666667</v>
       </c>
       <c r="G71">
-        <v>592.684599609375</v>
+        <v>70.13539932250977</v>
       </c>
       <c r="H71">
-        <v>519.55419921875</v>
+        <v>61.78133293151856</v>
       </c>
       <c r="I71">
-        <v>490.62169921875</v>
+        <v>59.39414972305298</v>
       </c>
       <c r="J71">
-        <v>471.2627491760254</v>
+        <v>57.01824970245362</v>
       </c>
       <c r="K71">
-        <v>0.5958155393600464</v>
+        <v>1.5</v>
       </c>
       <c r="L71">
-        <v>729.8200073242188</v>
+        <v>78.31999969482422</v>
       </c>
       <c r="M71">
-        <v>132.7425174485702</v>
+        <v>138.1886972162805</v>
       </c>
       <c r="N71">
-        <v>10.39</v>
+        <v>0.29</v>
       </c>
       <c r="O71">
-        <v>10.77</v>
+        <v>0.4</v>
       </c>
       <c r="P71">
-        <v>6.01</v>
+        <v>0.31</v>
       </c>
       <c r="Q71">
-        <v>1425879000</v>
+        <v>231600000</v>
       </c>
       <c r="R71">
-        <v>1468507000</v>
+        <v>313800000</v>
       </c>
       <c r="S71">
-        <v>814008000</v>
+        <v>247700000</v>
       </c>
       <c r="T71">
-        <v>28.10100508048586</v>
+        <v>20.14789038712484</v>
       </c>
       <c r="U71">
-        <v>27.82544387387451</v>
+        <v>24.45830085736555</v>
       </c>
       <c r="V71">
-        <v>21.03614123433385</v>
+        <v>19.62291056008873</v>
       </c>
       <c r="W71" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="72" spans="1:23">
@@ -6113,40 +6122,40 @@
         <v>93</v>
       </c>
       <c r="B72" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C72" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D72" t="s">
         <v>220</v>
       </c>
       <c r="E72">
-        <v>31.32999992370605</v>
+        <v>31.60000038146973</v>
       </c>
       <c r="F72">
-        <v>1564070</v>
+        <v>1589013.333333333</v>
       </c>
       <c r="G72">
-        <v>28.15919998168945</v>
+        <v>28.38100002288818</v>
       </c>
       <c r="H72">
-        <v>24.05266667683919</v>
+        <v>24.20380001068115</v>
       </c>
       <c r="I72">
-        <v>23.5480500125885</v>
+        <v>23.64300002098084</v>
       </c>
       <c r="J72">
-        <v>22.97485004425049</v>
+        <v>23.01185004234314</v>
       </c>
       <c r="K72">
         <v>18.89999961853027</v>
       </c>
       <c r="L72">
-        <v>31.5</v>
+        <v>31.79000091552734</v>
       </c>
       <c r="M72">
-        <v>132.2912562670783</v>
+        <v>137.7196691233726</v>
       </c>
       <c r="N72">
         <v>0.65</v>
@@ -6176,7 +6185,7 @@
         <v>5.463786531130877</v>
       </c>
       <c r="W72" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="73" spans="1:23">
@@ -6184,70 +6193,70 @@
         <v>94</v>
       </c>
       <c r="B73" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C73" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D73" t="s">
         <v>221</v>
       </c>
       <c r="E73">
-        <v>90.56999969482422</v>
+        <v>177.0899963378906</v>
       </c>
       <c r="F73">
-        <v>2286253.333333333</v>
+        <v>290463.3333333333</v>
       </c>
       <c r="G73">
-        <v>85.95200012207032</v>
+        <v>151.4844000244141</v>
       </c>
       <c r="H73">
-        <v>74.2516000620524</v>
+        <v>138.3993336486816</v>
       </c>
       <c r="I73">
-        <v>70.22097497940064</v>
+        <v>131.5756002426147</v>
       </c>
       <c r="J73">
-        <v>67.14374992370605</v>
+        <v>126.1549503707886</v>
       </c>
       <c r="K73">
-        <v>0.2213539928197861</v>
+        <v>2.075098752975464</v>
       </c>
       <c r="L73">
-        <v>91.20999908447266</v>
+        <v>178.4799957275391</v>
       </c>
       <c r="M73">
-        <v>132.2735329667315</v>
+        <v>137.702695166012</v>
       </c>
       <c r="N73">
-        <v>0.51</v>
+        <v>4.61</v>
       </c>
       <c r="O73">
-        <v>0.61</v>
+        <v>4.21</v>
       </c>
       <c r="P73">
-        <v>0.72</v>
+        <v>4.31</v>
       </c>
       <c r="Q73">
-        <v>245848000</v>
+        <v>340100000</v>
       </c>
       <c r="R73">
-        <v>293677000</v>
+        <v>298000000</v>
       </c>
       <c r="S73">
-        <v>350431000</v>
+        <v>298300000</v>
       </c>
       <c r="T73">
-        <v>27.51910738191929</v>
+        <v>4.914242778909648</v>
       </c>
       <c r="U73">
-        <v>30.69610462369502</v>
+        <v>4.24997860749023</v>
       </c>
       <c r="V73">
-        <v>34.29441854866411</v>
+        <v>4.064586455920425</v>
       </c>
       <c r="W73" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="74" spans="1:23">
@@ -6255,70 +6264,70 @@
         <v>95</v>
       </c>
       <c r="B74" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C74" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="D74" t="s">
         <v>222</v>
       </c>
       <c r="E74">
-        <v>258.3999938964844</v>
+        <v>90.16000366210938</v>
       </c>
       <c r="F74">
-        <v>2481603.333333333</v>
+        <v>519486.6666666667</v>
       </c>
       <c r="G74">
-        <v>231.3467987060547</v>
+        <v>78.22089996337891</v>
       </c>
       <c r="H74">
-        <v>211.7326000976562</v>
+        <v>71.90200007120768</v>
       </c>
       <c r="I74">
-        <v>198.9669500732422</v>
+        <v>66.34440004348755</v>
       </c>
       <c r="J74">
-        <v>194.9998000335693</v>
+        <v>63.13740005493164</v>
       </c>
       <c r="K74">
-        <v>0.8275843262672424</v>
+        <v>10.5</v>
       </c>
       <c r="L74">
-        <v>312.9627685546875</v>
+        <v>90.16000366210938</v>
       </c>
       <c r="M74">
-        <v>132.249905584196</v>
+        <v>137.5029928601381</v>
       </c>
       <c r="N74">
-        <v>3.07</v>
+        <v>-0.25</v>
       </c>
       <c r="O74">
-        <v>3.047431</v>
+        <v>-0.21</v>
       </c>
       <c r="P74">
-        <v>6.05</v>
+        <v>-0.08</v>
       </c>
       <c r="Q74">
-        <v>3333000000</v>
+        <v>-7426000</v>
       </c>
       <c r="R74">
-        <v>771000000</v>
+        <v>-6720000</v>
       </c>
       <c r="S74">
-        <v>1538000000</v>
+        <v>-2636000</v>
       </c>
       <c r="T74">
-        <v>3.542315418052736</v>
+        <v>-28.91406767122221</v>
       </c>
       <c r="U74">
-        <v>3.477829401416392</v>
+        <v>-21.41832669322709</v>
       </c>
       <c r="V74">
-        <v>7.013223894208847</v>
+        <v>-6.343552967223371</v>
       </c>
       <c r="W74" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="75" spans="1:23">
@@ -6326,70 +6335,70 @@
         <v>96</v>
       </c>
       <c r="B75" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C75" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="D75" t="s">
         <v>223</v>
       </c>
       <c r="E75">
-        <v>114.879997253418</v>
+        <v>113.25</v>
       </c>
       <c r="F75">
-        <v>13571253.33333333</v>
+        <v>1177340</v>
       </c>
       <c r="G75">
-        <v>107.901799621582</v>
+        <v>96.51000015258789</v>
       </c>
       <c r="H75">
-        <v>94.34693318684896</v>
+        <v>91.13373341878255</v>
       </c>
       <c r="I75">
-        <v>88.8469998550415</v>
+        <v>86.45640003204346</v>
       </c>
       <c r="J75">
-        <v>84.32745002746582</v>
+        <v>84.27410018920898</v>
       </c>
       <c r="K75">
-        <v>0.03513695672154427</v>
+        <v>24</v>
       </c>
       <c r="L75">
-        <v>126.5500030517578</v>
+        <v>143.3099975585938</v>
       </c>
       <c r="M75">
-        <v>131.8973423673471</v>
+        <v>137.0128111628075</v>
       </c>
       <c r="N75">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="O75">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="P75">
-        <v>1.19</v>
+        <v>0.66</v>
       </c>
       <c r="Q75">
-        <v>1741000000</v>
+        <v>76175000</v>
       </c>
       <c r="R75">
-        <v>1895000000</v>
+        <v>69237000</v>
       </c>
       <c r="S75">
-        <v>3319000000</v>
+        <v>71524000</v>
       </c>
       <c r="T75">
-        <v>14.18329938900204</v>
+        <v>6.938726061736672</v>
       </c>
       <c r="U75">
-        <v>15.28472334247459</v>
+        <v>6.606149022631144</v>
       </c>
       <c r="V75">
-        <v>23.98641323986413</v>
+        <v>6.37439263064457</v>
       </c>
       <c r="W75" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="76" spans="1:23">
@@ -6397,70 +6406,70 @@
         <v>97</v>
       </c>
       <c r="B76" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C76" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D76" t="s">
         <v>224</v>
       </c>
       <c r="E76">
-        <v>561.4400024414062</v>
+        <v>239.5099945068359</v>
       </c>
       <c r="F76">
-        <v>1331036.666666667</v>
+        <v>2131310</v>
       </c>
       <c r="G76">
-        <v>518.6006011962891</v>
+        <v>222.6108004760742</v>
       </c>
       <c r="H76">
-        <v>461.4540669759115</v>
+        <v>200.0885332234701</v>
       </c>
       <c r="I76">
-        <v>443.2089001464844</v>
+        <v>189.8738999176025</v>
       </c>
       <c r="J76">
-        <v>431.7722007751465</v>
+        <v>183.6434999847412</v>
       </c>
       <c r="K76">
-        <v>23.73999977111816</v>
+        <v>0.8611109852790833</v>
       </c>
       <c r="L76">
-        <v>701.72998046875</v>
+        <v>239.5099945068359</v>
       </c>
       <c r="M76">
-        <v>131.6785135826206</v>
+        <v>135.7459673196028</v>
       </c>
       <c r="N76">
-        <v>0.39</v>
+        <v>0.68</v>
       </c>
       <c r="O76">
-        <v>0.74</v>
+        <v>0.88</v>
       </c>
       <c r="P76">
-        <v>0.73</v>
+        <v>0.89</v>
       </c>
       <c r="Q76">
-        <v>80000000</v>
+        <v>186305000</v>
       </c>
       <c r="R76">
-        <v>150000000</v>
+        <v>240392000</v>
       </c>
       <c r="S76">
-        <v>150000000</v>
+        <v>241804000</v>
       </c>
       <c r="T76">
-        <v>4.369197160021846</v>
+        <v>20.64197820850609</v>
       </c>
       <c r="U76">
-        <v>7.731958762886598</v>
+        <v>26.71387311821504</v>
       </c>
       <c r="V76">
-        <v>7.15648854961832</v>
+        <v>23.66706143742231</v>
       </c>
       <c r="W76" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="77" spans="1:23">
@@ -6468,70 +6477,70 @@
         <v>98</v>
       </c>
       <c r="B77" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C77" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D77" t="s">
         <v>225</v>
       </c>
       <c r="E77">
-        <v>16.3799991607666</v>
+        <v>32.22000122070312</v>
       </c>
       <c r="F77">
-        <v>931743.3333333334</v>
+        <v>1583870</v>
       </c>
       <c r="G77">
-        <v>14.74100002288818</v>
+        <v>28.54999996185303</v>
       </c>
       <c r="H77">
-        <v>13.39353335062663</v>
+        <v>26.5659999593099</v>
       </c>
       <c r="I77">
-        <v>12.80110000610352</v>
+        <v>25.03539999008179</v>
       </c>
       <c r="J77">
-        <v>12.33975001335144</v>
+        <v>23.68150001049042</v>
       </c>
       <c r="K77">
-        <v>1.275554656982422</v>
+        <v>0.1598737090826035</v>
       </c>
       <c r="L77">
-        <v>17.22677421569824</v>
+        <v>32.22000122070312</v>
       </c>
       <c r="M77">
-        <v>131.3772977476627</v>
+        <v>135.7444515766796</v>
       </c>
       <c r="N77">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="O77">
-        <v>0.14</v>
+        <v>1.3</v>
       </c>
       <c r="P77">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="Q77">
-        <v>7100000</v>
+        <v>359000000</v>
       </c>
       <c r="R77">
-        <v>22500000</v>
+        <v>-64000000</v>
       </c>
       <c r="S77">
-        <v>21300000</v>
+        <v>23000000</v>
       </c>
       <c r="T77">
-        <v>2.142426071213035</v>
+        <v>8.586462568763453</v>
       </c>
       <c r="U77">
-        <v>7.147395171537483</v>
+        <v>-5.85544373284538</v>
       </c>
       <c r="V77">
-        <v>6.398317813157105</v>
+        <v>2.167766258246937</v>
       </c>
       <c r="W77" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="78" spans="1:23">
@@ -6539,70 +6548,70 @@
         <v>99</v>
       </c>
       <c r="B78" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C78" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D78" t="s">
         <v>226</v>
       </c>
       <c r="E78">
-        <v>93.61000061035156</v>
+        <v>105.5699996948242</v>
       </c>
       <c r="F78">
-        <v>2267223.333333333</v>
+        <v>11213003.33333333</v>
       </c>
       <c r="G78">
-        <v>85.32439971923829</v>
+        <v>96.80920028686523</v>
       </c>
       <c r="H78">
-        <v>82.4832664235433</v>
+        <v>90.27920018513997</v>
       </c>
       <c r="I78">
-        <v>75.7415497970581</v>
+        <v>85.31690015792847</v>
       </c>
       <c r="J78">
-        <v>72.0442498588562</v>
+        <v>83.07070009231568</v>
       </c>
       <c r="K78">
-        <v>0.8958330154418945</v>
+        <v>1.637526988983154</v>
       </c>
       <c r="L78">
-        <v>96.06999969482422</v>
+        <v>140.6600036621094</v>
       </c>
       <c r="M78">
-        <v>131.1754539126597</v>
+        <v>135.6524869215367</v>
       </c>
       <c r="N78">
-        <v>0.33</v>
+        <v>54.15</v>
       </c>
       <c r="O78">
-        <v>0.37</v>
+        <v>57.05</v>
       </c>
       <c r="P78">
-        <v>0.4</v>
+        <v>39.9</v>
       </c>
       <c r="Q78">
-        <v>46359000</v>
+        <v>280865780000</v>
       </c>
       <c r="R78">
-        <v>51913000</v>
+        <v>295904000000</v>
       </c>
       <c r="S78">
-        <v>55923000</v>
+        <v>206986561000</v>
       </c>
       <c r="T78">
-        <v>26.87338051927726</v>
+        <v>45.8075681734033</v>
       </c>
       <c r="U78">
-        <v>29.50272789270289</v>
+        <v>47.30452576215369</v>
       </c>
       <c r="V78">
-        <v>30.34181541967338</v>
+        <v>40.69468005173939</v>
       </c>
       <c r="W78" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="79" spans="1:23">
@@ -6610,70 +6619,70 @@
         <v>100</v>
       </c>
       <c r="B79" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C79" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="D79" t="s">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="E79">
-        <v>115.370002746582</v>
+        <v>383.6600036621094</v>
       </c>
       <c r="F79">
-        <v>665466.6666666666</v>
+        <v>380096.6666666667</v>
       </c>
       <c r="G79">
-        <v>103.4871995544434</v>
+        <v>359.9959997558594</v>
       </c>
       <c r="H79">
-        <v>95.91973327636718</v>
+        <v>316.8929995727539</v>
       </c>
       <c r="I79">
-        <v>91.60809999465943</v>
+        <v>297.3098496246338</v>
       </c>
       <c r="J79">
-        <v>88.39825006484985</v>
+        <v>288.8312500762939</v>
       </c>
       <c r="K79">
-        <v>0.8245028257369995</v>
+        <v>0.2751234471797943</v>
       </c>
       <c r="L79">
-        <v>121.2600021362305</v>
+        <v>471.1166076660156</v>
       </c>
       <c r="M79">
-        <v>131.1214552648555</v>
+        <v>135.615381869454</v>
       </c>
       <c r="N79">
-        <v>0.65</v>
+        <v>1.59</v>
       </c>
       <c r="O79">
-        <v>0.04</v>
+        <v>1.36</v>
       </c>
       <c r="P79">
-        <v>-1.05</v>
+        <v>1.85</v>
       </c>
       <c r="Q79">
-        <v>48896000</v>
+        <v>120600000</v>
       </c>
       <c r="R79">
-        <v>3224000</v>
+        <v>103000000</v>
       </c>
       <c r="S79">
-        <v>-80540000</v>
+        <v>140000000</v>
       </c>
       <c r="T79">
-        <v>1.945347573328496</v>
+        <v>17.55714077740573</v>
       </c>
       <c r="U79">
-        <v>0.1071679894799859</v>
+        <v>14.53365316777198</v>
       </c>
       <c r="V79">
-        <v>-3.116078368558483</v>
+        <v>19.53670108847335</v>
       </c>
       <c r="W79" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="80" spans="1:23">
@@ -6681,70 +6690,354 @@
         <v>101</v>
       </c>
       <c r="B80" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C80" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D80" t="s">
+        <v>227</v>
+      </c>
+      <c r="E80">
+        <v>178.1300048828125</v>
+      </c>
+      <c r="F80">
+        <v>974173.3333333334</v>
+      </c>
+      <c r="G80">
+        <v>153.0202005004883</v>
+      </c>
+      <c r="H80">
+        <v>146.4525997416178</v>
+      </c>
+      <c r="I80">
+        <v>141.3384999084473</v>
+      </c>
+      <c r="J80">
+        <v>137.195599899292</v>
+      </c>
+      <c r="K80">
+        <v>3.140000104904175</v>
+      </c>
+      <c r="L80">
+        <v>183.1000061035156</v>
+      </c>
+      <c r="M80">
+        <v>135.0922309856031</v>
+      </c>
+      <c r="N80">
+        <v>4.3</v>
+      </c>
+      <c r="O80">
+        <v>3.9</v>
+      </c>
+      <c r="P80">
+        <v>3.48</v>
+      </c>
+      <c r="Q80">
+        <v>239602000</v>
+      </c>
+      <c r="R80">
+        <v>218920000</v>
+      </c>
+      <c r="S80">
+        <v>197100000</v>
+      </c>
+      <c r="T80">
+        <v>4.399663894926033</v>
+      </c>
+      <c r="U80">
+        <v>3.938476860818776</v>
+      </c>
+      <c r="V80">
+        <v>3.569423567974792</v>
+      </c>
+      <c r="W80" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23">
+      <c r="A81" t="s">
+        <v>102</v>
+      </c>
+      <c r="B81" t="s">
+        <v>108</v>
+      </c>
+      <c r="C81" t="s">
+        <v>118</v>
+      </c>
+      <c r="D81" t="s">
         <v>228</v>
       </c>
-      <c r="E80">
-        <v>168.0800018310547</v>
-      </c>
-      <c r="F80">
-        <v>424380</v>
-      </c>
-      <c r="G80">
-        <v>150.4563989257813</v>
-      </c>
-      <c r="H80">
-        <v>136.435466003418</v>
-      </c>
-      <c r="I80">
-        <v>131.3291495132446</v>
-      </c>
-      <c r="J80">
-        <v>127.1992496490479</v>
-      </c>
-      <c r="K80">
-        <v>0.5625</v>
-      </c>
-      <c r="L80">
-        <v>171.8699951171875</v>
-      </c>
-      <c r="M80">
-        <v>130.4868752401933</v>
-      </c>
-      <c r="N80">
-        <v>2.5</v>
-      </c>
-      <c r="O80">
-        <v>1.52</v>
-      </c>
-      <c r="P80">
-        <v>1.33</v>
-      </c>
-      <c r="Q80">
-        <v>378263000</v>
-      </c>
-      <c r="R80">
-        <v>82474000</v>
-      </c>
-      <c r="S80">
-        <v>72401000</v>
-      </c>
-      <c r="T80">
-        <v>7.553193018833112</v>
-      </c>
-      <c r="U80">
-        <v>6.452869811235132</v>
-      </c>
-      <c r="V80">
-        <v>5.537839981581582</v>
-      </c>
-      <c r="W80" t="s">
+      <c r="E81">
+        <v>55.63999938964844</v>
+      </c>
+      <c r="F81">
+        <v>5470663.333333333</v>
+      </c>
+      <c r="G81">
+        <v>48.80939979553223</v>
+      </c>
+      <c r="H81">
+        <v>43.43506655375162</v>
+      </c>
+      <c r="I81">
+        <v>42.25834993362427</v>
+      </c>
+      <c r="J81">
+        <v>40.83654996871948</v>
+      </c>
+      <c r="K81">
+        <v>11.99751472473145</v>
+      </c>
+      <c r="L81">
+        <v>60.77000045776367</v>
+      </c>
+      <c r="M81">
+        <v>134.794220677352</v>
+      </c>
+      <c r="N81">
+        <v>0.33</v>
+      </c>
+      <c r="O81">
+        <v>0.84</v>
+      </c>
+      <c r="P81">
+        <v>0.79</v>
+      </c>
+      <c r="Q81">
+        <v>245000000</v>
+      </c>
+      <c r="R81">
+        <v>614000000</v>
+      </c>
+      <c r="S81">
+        <v>583000000</v>
+      </c>
+      <c r="T81">
+        <v>0.9910602321912545</v>
+      </c>
+      <c r="U81">
+        <v>2.452174607612125</v>
+      </c>
+      <c r="V81">
+        <v>2.786540483701367</v>
+      </c>
+      <c r="W81" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23">
+      <c r="A82" t="s">
+        <v>103</v>
+      </c>
+      <c r="B82" t="s">
+        <v>108</v>
+      </c>
+      <c r="C82" t="s">
+        <v>119</v>
+      </c>
+      <c r="D82" t="s">
         <v>229</v>
+      </c>
+      <c r="E82">
+        <v>95.93000030517578</v>
+      </c>
+      <c r="F82">
+        <v>2107956.666666667</v>
+      </c>
+      <c r="G82">
+        <v>85.92719985961914</v>
+      </c>
+      <c r="H82">
+        <v>82.81653312683106</v>
+      </c>
+      <c r="I82">
+        <v>76.20924982070923</v>
+      </c>
+      <c r="J82">
+        <v>72.33259983062744</v>
+      </c>
+      <c r="K82">
+        <v>0.8958330154418945</v>
+      </c>
+      <c r="L82">
+        <v>96.06999969482422</v>
+      </c>
+      <c r="M82">
+        <v>134.6267962054363</v>
+      </c>
+      <c r="N82">
+        <v>0.33</v>
+      </c>
+      <c r="O82">
+        <v>0.37</v>
+      </c>
+      <c r="P82">
+        <v>0.4</v>
+      </c>
+      <c r="Q82">
+        <v>46359000</v>
+      </c>
+      <c r="R82">
+        <v>51913000</v>
+      </c>
+      <c r="S82">
+        <v>55923000</v>
+      </c>
+      <c r="T82">
+        <v>26.87338051927726</v>
+      </c>
+      <c r="U82">
+        <v>29.50272789270289</v>
+      </c>
+      <c r="V82">
+        <v>30.34181541967338</v>
+      </c>
+      <c r="W82" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23">
+      <c r="A83" t="s">
+        <v>104</v>
+      </c>
+      <c r="B83" t="s">
+        <v>108</v>
+      </c>
+      <c r="C83" t="s">
+        <v>123</v>
+      </c>
+      <c r="D83" t="s">
+        <v>230</v>
+      </c>
+      <c r="E83">
+        <v>448.8399963378906</v>
+      </c>
+      <c r="F83">
+        <v>1115740</v>
+      </c>
+      <c r="G83">
+        <v>418.7655987548828</v>
+      </c>
+      <c r="H83">
+        <v>376.5837996419271</v>
+      </c>
+      <c r="I83">
+        <v>359.4206999206543</v>
+      </c>
+      <c r="J83">
+        <v>348.8439497375488</v>
+      </c>
+      <c r="K83">
+        <v>5.65625</v>
+      </c>
+      <c r="L83">
+        <v>464.8299865722656</v>
+      </c>
+      <c r="M83">
+        <v>134.4090806296152</v>
+      </c>
+      <c r="N83">
+        <v>0.99</v>
+      </c>
+      <c r="O83">
+        <v>1.75</v>
+      </c>
+      <c r="P83">
+        <v>1.76</v>
+      </c>
+      <c r="Q83">
+        <v>153500000</v>
+      </c>
+      <c r="R83">
+        <v>271536000</v>
+      </c>
+      <c r="S83">
+        <v>272910000</v>
+      </c>
+      <c r="T83">
+        <v>11.95211057921407</v>
+      </c>
+      <c r="U83">
+        <v>19.94622945039447</v>
+      </c>
+      <c r="V83">
+        <v>19.565362333075</v>
+      </c>
+      <c r="W83" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23">
+      <c r="A84" t="s">
+        <v>105</v>
+      </c>
+      <c r="B84" t="s">
+        <v>108</v>
+      </c>
+      <c r="C84" t="s">
+        <v>123</v>
+      </c>
+      <c r="D84" t="s">
+        <v>231</v>
+      </c>
+      <c r="E84">
+        <v>117.4499969482422</v>
+      </c>
+      <c r="F84">
+        <v>13440563.33333333</v>
+      </c>
+      <c r="G84">
+        <v>108.7793994140625</v>
+      </c>
+      <c r="H84">
+        <v>94.81819981892903</v>
+      </c>
+      <c r="I84">
+        <v>89.36144981384277</v>
+      </c>
+      <c r="J84">
+        <v>84.72770004272461</v>
+      </c>
+      <c r="K84">
+        <v>0.03513695672154427</v>
+      </c>
+      <c r="L84">
+        <v>126.5500030517578</v>
+      </c>
+      <c r="M84">
+        <v>134.2835236400988</v>
+      </c>
+      <c r="N84">
+        <v>0.63</v>
+      </c>
+      <c r="O84">
+        <v>0.68</v>
+      </c>
+      <c r="P84">
+        <v>1.19</v>
+      </c>
+      <c r="Q84">
+        <v>1741000000</v>
+      </c>
+      <c r="R84">
+        <v>1895000000</v>
+      </c>
+      <c r="S84">
+        <v>3319000000</v>
+      </c>
+      <c r="T84">
+        <v>14.18329938900204</v>
+      </c>
+      <c r="U84">
+        <v>15.28472334247459</v>
+      </c>
+      <c r="V84">
+        <v>23.98641323986413</v>
+      </c>
+      <c r="W84" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/ScreenResult/ScreenResult.xlsx
+++ b/Screener/ScreenResult/ScreenResult.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="238">
   <si>
     <t>Symbol</t>
   </si>
@@ -61,6 +61,9 @@
     <t>2nd qtr EPS</t>
   </si>
   <si>
+    <t>3rd qtr EPS</t>
+  </si>
+  <si>
     <t>Current qtr EPS</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t>2nd qtr Inc</t>
   </si>
   <si>
+    <t>3rd qtr Inc</t>
+  </si>
+  <si>
     <t>Current qtr Inc</t>
   </si>
   <si>
@@ -79,643 +85,649 @@
     <t>2nd qtr NPM</t>
   </si>
   <si>
-    <t>Current qtr NPM</t>
-  </si>
-  <si>
-    <t>Code 33</t>
-  </si>
-  <si>
     <t>EDTX</t>
   </si>
   <si>
-    <t>OPRA</t>
-  </si>
-  <si>
     <t>SMCI</t>
   </si>
   <si>
+    <t>INOD</t>
+  </si>
+  <si>
     <t>NVDA</t>
   </si>
   <si>
-    <t>DFH</t>
+    <t>IOT</t>
   </si>
   <si>
     <t>RXST</t>
   </si>
   <si>
-    <t>RXDX</t>
-  </si>
-  <si>
-    <t>IOT</t>
+    <t>AMPH</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>ELF</t>
+  </si>
+  <si>
+    <t>IAS</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>AEHR</t>
+  </si>
+  <si>
+    <t>LI</t>
   </si>
   <si>
     <t>ACLS</t>
   </si>
   <si>
-    <t>CBAY</t>
-  </si>
-  <si>
-    <t>VRT</t>
-  </si>
-  <si>
-    <t>SGH</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>ELF</t>
-  </si>
-  <si>
-    <t>MOD</t>
-  </si>
-  <si>
-    <t>TTD</t>
-  </si>
-  <si>
-    <t>AEHR</t>
+    <t>FLNC</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>SAIA</t>
   </si>
   <si>
     <t>MHO</t>
   </si>
   <si>
-    <t>LI</t>
+    <t>STVN</t>
+  </si>
+  <si>
+    <t>DV</t>
+  </si>
+  <si>
+    <t>RDNT</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>DICE</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>ABCM</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>KRYS</t>
   </si>
   <si>
     <t>ADBE</t>
   </si>
   <si>
-    <t>DV</t>
-  </si>
-  <si>
-    <t>AMPH</t>
-  </si>
-  <si>
-    <t>FLNC</t>
-  </si>
-  <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>STRL</t>
-  </si>
-  <si>
-    <t>XPO</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>KRYS</t>
-  </si>
-  <si>
-    <t>JBL</t>
-  </si>
-  <si>
-    <t>ABCM</t>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>AN</t>
+  </si>
+  <si>
+    <t>MANH</t>
+  </si>
+  <si>
+    <t>BECN</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>MRUS</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>IDCC</t>
+  </si>
+  <si>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>ALGM</t>
+  </si>
+  <si>
+    <t>CLBR</t>
+  </si>
+  <si>
+    <t>KBH</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>ENS</t>
+  </si>
+  <si>
+    <t>DAL</t>
+  </si>
+  <si>
+    <t>TMHC</t>
+  </si>
+  <si>
+    <t>LAD</t>
   </si>
   <si>
     <t>TGLS</t>
   </si>
   <si>
-    <t>BLD</t>
-  </si>
-  <si>
-    <t>PHM</t>
-  </si>
-  <si>
-    <t>STVN</t>
-  </si>
-  <si>
-    <t>ALGM</t>
-  </si>
-  <si>
-    <t>DUOL</t>
+    <t>PAG</t>
+  </si>
+  <si>
+    <t>ARGX</t>
+  </si>
+  <si>
+    <t>VMW</t>
+  </si>
+  <si>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>APG</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>ATKR</t>
+  </si>
+  <si>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>NUVL</t>
+  </si>
+  <si>
+    <t>NVT</t>
+  </si>
+  <si>
+    <t>ARCB</t>
+  </si>
+  <si>
+    <t>HUBB</t>
+  </si>
+  <si>
+    <t>IGT</t>
+  </si>
+  <si>
+    <t>ERII</t>
+  </si>
+  <si>
+    <t>CRS</t>
+  </si>
+  <si>
+    <t>EXP</t>
+  </si>
+  <si>
+    <t>CLH</t>
+  </si>
+  <si>
+    <t>CNMD</t>
+  </si>
+  <si>
+    <t>MTH</t>
+  </si>
+  <si>
+    <t>LECO</t>
+  </si>
+  <si>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>CPA</t>
+  </si>
+  <si>
+    <t>ALSN</t>
+  </si>
+  <si>
+    <t>AGRO</t>
+  </si>
+  <si>
+    <t>FND</t>
+  </si>
+  <si>
+    <t>NYCB</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>WCC</t>
   </si>
   <si>
     <t>LTH</t>
   </si>
   <si>
-    <t>LAD</t>
-  </si>
-  <si>
-    <t>TOL</t>
-  </si>
-  <si>
-    <t>IDCC</t>
-  </si>
-  <si>
-    <t>ROIV</t>
-  </si>
-  <si>
-    <t>CELH</t>
-  </si>
-  <si>
-    <t>MPWR</t>
-  </si>
-  <si>
-    <t>TMHC</t>
-  </si>
-  <si>
-    <t>DICE</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>AN</t>
-  </si>
-  <si>
-    <t>BECN</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>TPH</t>
-  </si>
-  <si>
-    <t>KBH</t>
-  </si>
-  <si>
-    <t>MRUS</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>ENS</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>ON</t>
-  </si>
-  <si>
-    <t>VNT</t>
-  </si>
-  <si>
-    <t>MTH</t>
-  </si>
-  <si>
-    <t>OC</t>
-  </si>
-  <si>
-    <t>RDNT</t>
-  </si>
-  <si>
-    <t>ONTO</t>
-  </si>
-  <si>
-    <t>BSY</t>
-  </si>
-  <si>
-    <t>CNMD</t>
-  </si>
-  <si>
-    <t>BLBD</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>APG</t>
-  </si>
-  <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>PAG</t>
-  </si>
-  <si>
-    <t>TMDX</t>
-  </si>
-  <si>
-    <t>FND</t>
-  </si>
-  <si>
-    <t>CDNS</t>
-  </si>
-  <si>
-    <t>IGT</t>
-  </si>
-  <si>
-    <t>TSM</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>WCC</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>LSCC</t>
-  </si>
-  <si>
-    <t>SNPS</t>
-  </si>
-  <si>
-    <t>ORCL</t>
-  </si>
-  <si>
     <t>Financial Services</t>
   </si>
   <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
+    <t>Consumer Defensive</t>
+  </si>
+  <si>
     <t>Communication Services</t>
   </si>
   <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Consumer Cyclical</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Industrials</t>
-  </si>
-  <si>
-    <t>Consumer Defensive</t>
-  </si>
-  <si>
     <t>Utilities</t>
   </si>
   <si>
+    <t>Basic Materials</t>
+  </si>
+  <si>
     <t>Energy</t>
   </si>
   <si>
-    <t>Basic Materials</t>
-  </si>
-  <si>
     <t>Shell Companies</t>
   </si>
   <si>
-    <t>Internet Content &amp; Information</t>
-  </si>
-  <si>
     <t>Computer Hardware</t>
   </si>
   <si>
+    <t>Information Technology Services</t>
+  </si>
+  <si>
     <t>Semiconductors</t>
   </si>
   <si>
+    <t>Software—Infrastructure</t>
+  </si>
+  <si>
+    <t>Medical Devices</t>
+  </si>
+  <si>
+    <t>Drug Manufacturers—Specialty &amp; Generic</t>
+  </si>
+  <si>
+    <t>Biotechnology</t>
+  </si>
+  <si>
+    <t>Electrical Equipment &amp; Parts</t>
+  </si>
+  <si>
+    <t>Trucking</t>
+  </si>
+  <si>
+    <t>Auto Parts</t>
+  </si>
+  <si>
+    <t>Household &amp; Personal Products</t>
+  </si>
+  <si>
+    <t>Advertising Agencies</t>
+  </si>
+  <si>
+    <t>Building Products &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Semiconductor Equipment &amp; Materials</t>
+  </si>
+  <si>
+    <t>Auto Manufacturers</t>
+  </si>
+  <si>
+    <t>Utilities—Renewable</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Construction</t>
+  </si>
+  <si>
     <t>Residential Construction</t>
   </si>
   <si>
-    <t>Medical Devices</t>
-  </si>
-  <si>
-    <t>Biotechnology</t>
-  </si>
-  <si>
-    <t>Software—Infrastructure</t>
-  </si>
-  <si>
-    <t>Semiconductor Equipment &amp; Materials</t>
-  </si>
-  <si>
-    <t>Electrical Equipment &amp; Parts</t>
-  </si>
-  <si>
-    <t>Building Products &amp; Equipment</t>
-  </si>
-  <si>
-    <t>Household &amp; Personal Products</t>
-  </si>
-  <si>
-    <t>Auto Parts</t>
+    <t>Medical Instruments &amp; Supplies</t>
   </si>
   <si>
     <t>Software—Application</t>
   </si>
   <si>
-    <t>Auto Manufacturers</t>
-  </si>
-  <si>
-    <t>Drug Manufacturers—Specialty &amp; Generic</t>
-  </si>
-  <si>
-    <t>Utilities—Renewable</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas E&amp;P</t>
-  </si>
-  <si>
-    <t>Engineering &amp; Construction</t>
-  </si>
-  <si>
-    <t>Trucking</t>
+    <t>Diagnostics &amp; Research</t>
+  </si>
+  <si>
+    <t>Travel Services</t>
   </si>
   <si>
     <t>Electronic Components</t>
   </si>
   <si>
+    <t>Auto &amp; Truck Dealerships</t>
+  </si>
+  <si>
+    <t>Industrial Distribution</t>
+  </si>
+  <si>
+    <t>Rental &amp; Leasing Services</t>
+  </si>
+  <si>
     <t>Building Materials</t>
   </si>
   <si>
-    <t>Medical Instruments &amp; Supplies</t>
+    <t>Insurance—Life</t>
+  </si>
+  <si>
+    <t>Telecom Services</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Equipment &amp; Services</t>
+  </si>
+  <si>
+    <t>Airlines</t>
+  </si>
+  <si>
+    <t>Beverages—Non-Alcoholic</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Drilling</t>
+  </si>
+  <si>
+    <t>Gambling</t>
+  </si>
+  <si>
+    <t>Pollution &amp; Treatment Controls</t>
+  </si>
+  <si>
+    <t>Metal Fabrication</t>
+  </si>
+  <si>
+    <t>Waste Management</t>
+  </si>
+  <si>
+    <t>Tools &amp; Accessories</t>
+  </si>
+  <si>
+    <t>Farm Products</t>
+  </si>
+  <si>
+    <t>Home Improvement Retail</t>
+  </si>
+  <si>
+    <t>Banks—Regional</t>
+  </si>
+  <si>
+    <t>Footwear &amp; Accessories</t>
   </si>
   <si>
     <t>Leisure</t>
   </si>
   <si>
-    <t>Auto &amp; Truck Dealerships</t>
-  </si>
-  <si>
-    <t>Telecom Services</t>
-  </si>
-  <si>
-    <t>Beverages—Non-Alcoholic</t>
-  </si>
-  <si>
-    <t>Industrial Distribution</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Equipment &amp; Services</t>
-  </si>
-  <si>
-    <t>Rental &amp; Leasing Services</t>
-  </si>
-  <si>
-    <t>Scientific &amp; Technical Instruments</t>
-  </si>
-  <si>
-    <t>Diagnostics &amp; Research</t>
-  </si>
-  <si>
-    <t>Airlines</t>
-  </si>
-  <si>
-    <t>Home Improvement Retail</t>
-  </si>
-  <si>
-    <t>Gambling</t>
-  </si>
-  <si>
     <t>2021-01-04</t>
   </si>
   <si>
-    <t>2018-07-27</t>
-  </si>
-  <si>
     <t>2007-03-29</t>
   </si>
   <si>
+    <t>1993-08-10</t>
+  </si>
+  <si>
     <t>1999-01-22</t>
   </si>
   <si>
-    <t>2021-01-21</t>
+    <t>2021-12-15</t>
   </si>
   <si>
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-03-12</t>
-  </si>
-  <si>
-    <t>2021-12-15</t>
+    <t>2014-06-25</t>
+  </si>
+  <si>
+    <t>2014-02-03</t>
+  </si>
+  <si>
+    <t>2018-08-02</t>
+  </si>
+  <si>
+    <t>2003-10-07</t>
+  </si>
+  <si>
+    <t>1982-09-20</t>
+  </si>
+  <si>
+    <t>2016-09-22</t>
+  </si>
+  <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
+    <t>2005-06-28</t>
+  </si>
+  <si>
+    <t>1997-08-15</t>
+  </si>
+  <si>
+    <t>2020-07-30</t>
   </si>
   <si>
     <t>2000-07-11</t>
   </si>
   <si>
-    <t>2014-02-03</t>
-  </si>
-  <si>
-    <t>2018-08-02</t>
-  </si>
-  <si>
-    <t>2017-05-24</t>
-  </si>
-  <si>
-    <t>2005-06-28</t>
-  </si>
-  <si>
-    <t>2016-09-22</t>
-  </si>
-  <si>
-    <t>1982-09-20</t>
-  </si>
-  <si>
-    <t>2016-09-21</t>
-  </si>
-  <si>
-    <t>1997-08-15</t>
+    <t>2021-10-28</t>
+  </si>
+  <si>
+    <t>1991-07-12</t>
+  </si>
+  <si>
+    <t>2002-09-11</t>
   </si>
   <si>
     <t>1993-11-03</t>
   </si>
   <si>
-    <t>2020-07-30</t>
+    <t>2021-07-16</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>1997-01-03</t>
+  </si>
+  <si>
+    <t>1993-04-28</t>
+  </si>
+  <si>
+    <t>2021-09-15</t>
+  </si>
+  <si>
+    <t>2009-08-06</t>
+  </si>
+  <si>
+    <t>2020-10-22</t>
+  </si>
+  <si>
+    <t>1993-05-03</t>
+  </si>
+  <si>
+    <t>2017-09-20</t>
   </si>
   <si>
     <t>1986-08-13</t>
   </si>
   <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>2014-06-25</t>
-  </si>
-  <si>
-    <t>2021-10-28</t>
-  </si>
-  <si>
-    <t>2019-07-26</t>
-  </si>
-  <si>
-    <t>1991-07-12</t>
-  </si>
-  <si>
-    <t>2003-10-07</t>
-  </si>
-  <si>
-    <t>2009-08-06</t>
-  </si>
-  <si>
-    <t>2017-09-20</t>
-  </si>
-  <si>
-    <t>1993-05-03</t>
-  </si>
-  <si>
-    <t>2020-10-22</t>
+    <t>2015-06-25</t>
+  </si>
+  <si>
+    <t>1990-05-11</t>
+  </si>
+  <si>
+    <t>1998-04-23</t>
+  </si>
+  <si>
+    <t>2004-09-23</t>
+  </si>
+  <si>
+    <t>2012-07-20</t>
+  </si>
+  <si>
+    <t>2015-05-14</t>
+  </si>
+  <si>
+    <t>2013-02-06</t>
+  </si>
+  <si>
+    <t>2016-05-19</t>
+  </si>
+  <si>
+    <t>2003-12-04</t>
+  </si>
+  <si>
+    <t>1981-11-12</t>
+  </si>
+  <si>
+    <t>1980-03-17</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>2021-07-07</t>
+  </si>
+  <si>
+    <t>1986-08-01</t>
+  </si>
+  <si>
+    <t>2004-08-02</t>
+  </si>
+  <si>
+    <t>2007-05-03</t>
+  </si>
+  <si>
+    <t>2013-04-10</t>
+  </si>
+  <si>
+    <t>1996-12-18</t>
   </si>
   <si>
     <t>2012-05-10</t>
   </si>
   <si>
-    <t>2015-06-17</t>
-  </si>
-  <si>
-    <t>1980-03-17</t>
-  </si>
-  <si>
-    <t>2021-07-16</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>2021-07-28</t>
+    <t>1996-10-23</t>
+  </si>
+  <si>
+    <t>2017-05-18</t>
+  </si>
+  <si>
+    <t>2007-08-15</t>
+  </si>
+  <si>
+    <t>2007-01-22</t>
+  </si>
+  <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
+    <t>2006-11-01</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>2016-06-10</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>2021-07-29</t>
+  </si>
+  <si>
+    <t>2018-04-24</t>
+  </si>
+  <si>
+    <t>1992-05-13</t>
+  </si>
+  <si>
+    <t>1972-06-05</t>
+  </si>
+  <si>
+    <t>1990-03-26</t>
+  </si>
+  <si>
+    <t>2008-07-02</t>
+  </si>
+  <si>
+    <t>1973-02-21</t>
+  </si>
+  <si>
+    <t>1994-04-12</t>
+  </si>
+  <si>
+    <t>1987-11-24</t>
+  </si>
+  <si>
+    <t>1987-07-23</t>
+  </si>
+  <si>
+    <t>1988-07-26</t>
+  </si>
+  <si>
+    <t>1994-04-07</t>
+  </si>
+  <si>
+    <t>2009-11-18</t>
+  </si>
+  <si>
+    <t>2005-12-15</t>
+  </si>
+  <si>
+    <t>2012-03-15</t>
+  </si>
+  <si>
+    <t>2011-01-28</t>
+  </si>
+  <si>
+    <t>2017-04-27</t>
+  </si>
+  <si>
+    <t>1993-11-23</t>
+  </si>
+  <si>
+    <t>1993-10-15</t>
+  </si>
+  <si>
+    <t>1999-05-12</t>
   </si>
   <si>
     <t>2021-10-07</t>
-  </si>
-  <si>
-    <t>1996-12-18</t>
-  </si>
-  <si>
-    <t>1986-07-08</t>
-  </si>
-  <si>
-    <t>1981-11-12</t>
-  </si>
-  <si>
-    <t>2020-12-08</t>
-  </si>
-  <si>
-    <t>2007-01-22</t>
-  </si>
-  <si>
-    <t>2004-11-19</t>
-  </si>
-  <si>
-    <t>2013-04-10</t>
-  </si>
-  <si>
-    <t>2021-09-15</t>
-  </si>
-  <si>
-    <t>1998-04-23</t>
-  </si>
-  <si>
-    <t>1990-05-11</t>
-  </si>
-  <si>
-    <t>2004-09-23</t>
-  </si>
-  <si>
-    <t>2013-02-06</t>
-  </si>
-  <si>
-    <t>2002-09-11</t>
-  </si>
-  <si>
-    <t>2013-01-31</t>
-  </si>
-  <si>
-    <t>1986-08-01</t>
-  </si>
-  <si>
-    <t>2016-05-19</t>
-  </si>
-  <si>
-    <t>2012-07-20</t>
-  </si>
-  <si>
-    <t>2015-05-14</t>
-  </si>
-  <si>
-    <t>2004-08-02</t>
-  </si>
-  <si>
-    <t>2012-06-29</t>
-  </si>
-  <si>
-    <t>2000-05-02</t>
-  </si>
-  <si>
-    <t>2020-09-24</t>
-  </si>
-  <si>
-    <t>1988-07-26</t>
-  </si>
-  <si>
-    <t>2006-11-01</t>
-  </si>
-  <si>
-    <t>1997-01-03</t>
-  </si>
-  <si>
-    <t>2019-10-28</t>
-  </si>
-  <si>
-    <t>2020-09-23</t>
-  </si>
-  <si>
-    <t>1987-07-23</t>
-  </si>
-  <si>
-    <t>2014-03-20</t>
-  </si>
-  <si>
-    <t>2007-05-03</t>
-  </si>
-  <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
-    <t>2009-11-18</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>1996-10-23</t>
-  </si>
-  <si>
-    <t>2019-05-02</t>
-  </si>
-  <si>
-    <t>2017-04-27</t>
-  </si>
-  <si>
-    <t>1987-06-10</t>
-  </si>
-  <si>
-    <t>1990-03-26</t>
-  </si>
-  <si>
-    <t>1997-10-09</t>
-  </si>
-  <si>
-    <t>1999-05-12</t>
-  </si>
-  <si>
-    <t>2016-08-17</t>
-  </si>
-  <si>
-    <t>1989-11-09</t>
-  </si>
-  <si>
-    <t>1992-02-26</t>
-  </si>
-  <si>
-    <t>1986-03-12</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>T</t>
   </si>
 </sst>
 </file>
@@ -1073,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W84"/>
+  <dimension ref="A1:W82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
@@ -1152,70 +1164,70 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="E2">
-        <v>43.22999954223633</v>
+        <v>63.2400016784668</v>
       </c>
       <c r="F2">
-        <v>408576.6666666667</v>
+        <v>428723.3333333333</v>
       </c>
       <c r="G2">
-        <v>14.20694005966187</v>
+        <v>18.3685401725769</v>
       </c>
       <c r="H2">
-        <v>11.81855339686076</v>
+        <v>13.22888677597046</v>
       </c>
       <c r="I2">
-        <v>11.43621504306793</v>
+        <v>12.4972650718689</v>
       </c>
       <c r="J2">
-        <v>10.53966502666473</v>
+        <v>10.80671504020691</v>
       </c>
       <c r="K2">
         <v>9.739999771118164</v>
       </c>
       <c r="L2">
-        <v>43.22999954223633</v>
+        <v>63.2400016784668</v>
       </c>
       <c r="M2">
-        <v>408.3573055448696</v>
+        <v>594.5424739133769</v>
       </c>
       <c r="N2">
+        <v>0.002796</v>
+      </c>
+      <c r="O2">
         <v>0.04</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>0.06</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>0.002796</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>4198372</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>317981</v>
       </c>
-      <c r="S2">
+      <c r="T2">
         <v>768</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>0</v>
+        <v>4563809</v>
       </c>
       <c r="V2">
         <v>0</v>
       </c>
-      <c r="W2" t="s">
-        <v>232</v>
+      <c r="W2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -1223,70 +1235,70 @@
         <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E3">
-        <v>27.82999992370605</v>
+        <v>298</v>
       </c>
       <c r="F3">
-        <v>1504113.333333333</v>
+        <v>2995693.966666667</v>
       </c>
       <c r="G3">
-        <v>17.35080005645752</v>
+        <v>225.3194000244141</v>
       </c>
       <c r="H3">
-        <v>11.11320004781087</v>
+        <v>138.0116000366211</v>
       </c>
       <c r="I3">
-        <v>9.501100038290025</v>
+        <v>122.0978999710083</v>
       </c>
       <c r="J3">
-        <v>7.865600045919418</v>
+        <v>101.8005499458313</v>
       </c>
       <c r="K3">
-        <v>3.970000028610229</v>
+        <v>3.849999904632568</v>
       </c>
       <c r="L3">
-        <v>27.82999992370605</v>
+        <v>318.3999938964844</v>
       </c>
       <c r="M3">
-        <v>355.1290127954948</v>
+        <v>280.1621561560102</v>
       </c>
       <c r="N3">
-        <v>0.08</v>
+        <v>2.6</v>
       </c>
       <c r="O3">
-        <v>0.22</v>
+        <v>3.35</v>
       </c>
       <c r="P3">
-        <v>0.18</v>
+        <v>3.14</v>
       </c>
       <c r="Q3">
-        <v>9384000</v>
+        <v>1.53</v>
       </c>
       <c r="R3">
-        <v>20922000</v>
+        <v>184416000</v>
       </c>
       <c r="S3">
-        <v>15478000</v>
+        <v>176167000</v>
       </c>
       <c r="T3">
-        <v>10.99511406376322</v>
+        <v>85846000</v>
       </c>
       <c r="U3">
-        <v>21.73217550274223</v>
+        <v>578377000</v>
       </c>
       <c r="V3">
-        <v>17.7803816153749</v>
-      </c>
-      <c r="W3" t="s">
-        <v>232</v>
+        <v>9.956968463336807</v>
+      </c>
+      <c r="W3">
+        <v>9.769714312650601</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -1294,70 +1306,70 @@
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E4">
-        <v>294.0499877929688</v>
+        <v>13.5</v>
       </c>
       <c r="F4">
-        <v>2893523.333333333</v>
+        <v>709886.6666666666</v>
       </c>
       <c r="G4">
-        <v>207.9421998596191</v>
+        <v>10.62200001716614</v>
       </c>
       <c r="H4">
-        <v>130.7694000244141</v>
+        <v>7.348933339118958</v>
       </c>
       <c r="I4">
-        <v>115.8644999885559</v>
+        <v>6.324550001621247</v>
       </c>
       <c r="J4">
-        <v>97.63699993133545</v>
+        <v>5.505250015258789</v>
       </c>
       <c r="K4">
-        <v>3.849999904632568</v>
+        <v>0.09375</v>
       </c>
       <c r="L4">
-        <v>294.0499877929688</v>
+        <v>13.5</v>
       </c>
       <c r="M4">
-        <v>297.2837277422557</v>
+        <v>226.9743659900273</v>
       </c>
       <c r="N4">
-        <v>3.35</v>
+        <v>-0.14</v>
       </c>
       <c r="O4">
-        <v>3.14</v>
+        <v>-0.12</v>
       </c>
       <c r="P4">
-        <v>1.53</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Q4">
-        <v>184416000</v>
+        <v>-0.08</v>
       </c>
       <c r="R4">
-        <v>176167000</v>
+        <v>-3327000</v>
       </c>
       <c r="S4">
-        <v>85846000</v>
+        <v>-1960000</v>
       </c>
       <c r="T4">
-        <v>9.956968463336807</v>
+        <v>-2116000</v>
       </c>
       <c r="U4">
-        <v>9.769714312650601</v>
+        <v>-11935000</v>
       </c>
       <c r="V4">
-        <v>6.689493304740293</v>
-      </c>
-      <c r="W4" t="s">
-        <v>232</v>
+        <v>-18.03545291917385</v>
+      </c>
+      <c r="W4">
+        <v>-10.11612903225806</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -1365,70 +1377,70 @@
         <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="E5">
-        <v>459.7699890136719</v>
+        <v>470.7699890136719</v>
       </c>
       <c r="F5">
-        <v>47714066.66666666</v>
+        <v>46920483.33333334</v>
       </c>
       <c r="G5">
-        <v>371.4994000244141</v>
+        <v>386.3488000488281</v>
       </c>
       <c r="H5">
-        <v>268.9220663452148</v>
+        <v>276.936999613444</v>
       </c>
       <c r="I5">
-        <v>236.4819497680664</v>
+        <v>243.3271496963501</v>
       </c>
       <c r="J5">
-        <v>207.810549621582</v>
+        <v>213.2868996429443</v>
       </c>
       <c r="K5">
         <v>0.3134739995002747</v>
       </c>
       <c r="L5">
-        <v>459.7699890136719</v>
+        <v>474.9400024414062</v>
       </c>
       <c r="M5">
-        <v>231.7763632427629</v>
+        <v>205.2429945071746</v>
       </c>
       <c r="N5">
+        <v>0.26</v>
+      </c>
+      <c r="O5">
         <v>0.27</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>0.57</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>0.82</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>680000000</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>1414000000</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>2043000000</v>
       </c>
-      <c r="T5">
+      <c r="U5">
+        <v>4368000000</v>
+      </c>
+      <c r="V5">
         <v>11.4651829371101</v>
       </c>
-      <c r="U5">
+      <c r="W5">
         <v>23.36803834077012</v>
-      </c>
-      <c r="V5">
-        <v>28.40656284760845</v>
-      </c>
-      <c r="W5" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -1436,70 +1448,70 @@
         <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="E6">
-        <v>25.67000007629395</v>
+        <v>27.57010078430176</v>
       </c>
       <c r="F6">
-        <v>376870</v>
+        <v>3712444.666666667</v>
       </c>
       <c r="G6">
-        <v>20.46920001983642</v>
+        <v>24.8874019241333</v>
       </c>
       <c r="H6">
-        <v>14.72479998906453</v>
+        <v>19.18566732406616</v>
       </c>
       <c r="I6">
-        <v>13.6255500125885</v>
+        <v>17.16300049304962</v>
       </c>
       <c r="J6">
-        <v>12.39560000896454</v>
+        <v>15.68729999065399</v>
       </c>
       <c r="K6">
-        <v>8.369999885559082</v>
+        <v>8.699999809265137</v>
       </c>
       <c r="L6">
-        <v>34</v>
+        <v>30.6299991607666</v>
       </c>
       <c r="M6">
-        <v>204.7653652253236</v>
+        <v>183.9838616740865</v>
       </c>
       <c r="N6">
-        <v>0.64</v>
+        <v>-0.13</v>
       </c>
       <c r="O6">
-        <v>0.78</v>
+        <v>-0.11</v>
       </c>
       <c r="P6">
-        <v>0.45</v>
+        <v>-0.1</v>
       </c>
       <c r="Q6">
-        <v>69641000</v>
+        <v>-0.13</v>
       </c>
       <c r="R6">
-        <v>86332000</v>
+        <v>-58555000</v>
       </c>
       <c r="S6">
-        <v>49089000</v>
+        <v>-53598000</v>
       </c>
       <c r="T6">
-        <v>8.863910883590927</v>
+        <v>-67856000</v>
       </c>
       <c r="U6">
-        <v>7.852175510656992</v>
+        <v>-247422000</v>
       </c>
       <c r="V6">
-        <v>6.380000519872111</v>
-      </c>
-      <c r="W6" t="s">
-        <v>232</v>
+        <v>-34.48468786808009</v>
+      </c>
+      <c r="W6">
+        <v>-28.72701351184766</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -1507,70 +1519,70 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="E7">
-        <v>30.95999908447266</v>
+        <v>30.94499969482422</v>
       </c>
       <c r="F7">
-        <v>512960</v>
+        <v>475774.9666666667</v>
       </c>
       <c r="G7">
-        <v>25.39089992523193</v>
+        <v>26.75359985351562</v>
       </c>
       <c r="H7">
-        <v>18.10196664174398</v>
+        <v>18.73333330154419</v>
       </c>
       <c r="I7">
-        <v>16.59097497940063</v>
+        <v>17.11084997177124</v>
       </c>
       <c r="J7">
-        <v>15.08832499980926</v>
+        <v>15.41987499713898</v>
       </c>
       <c r="K7">
         <v>8.970000267028809</v>
       </c>
       <c r="L7">
-        <v>31.68000030517578</v>
+        <v>32.77000045776367</v>
       </c>
       <c r="M7">
-        <v>197.4678031685473</v>
+        <v>182.1067917868554</v>
       </c>
       <c r="N7">
         <v>-0.61</v>
       </c>
       <c r="O7">
+        <v>-0.61</v>
+      </c>
+      <c r="P7">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>-0.42</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>-16818000</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <v>-15610000</v>
       </c>
-      <c r="S7">
+      <c r="T7">
         <v>-13212000</v>
       </c>
-      <c r="T7">
+      <c r="U7">
+        <v>-66756000</v>
+      </c>
+      <c r="V7">
         <v>-133.3174791914388</v>
       </c>
-      <c r="U7">
+      <c r="W7">
         <v>-97.02884137245151</v>
-      </c>
-      <c r="V7">
-        <v>-75.54462805191835</v>
-      </c>
-      <c r="W7" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -1578,70 +1590,70 @@
         <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="E8">
-        <v>199.9199981689453</v>
+        <v>62.56999969482422</v>
       </c>
       <c r="F8">
-        <v>1081147.333333333</v>
+        <v>487945.2</v>
       </c>
       <c r="G8">
-        <v>186.0122996520996</v>
+        <v>50.27139961242676</v>
       </c>
       <c r="H8">
-        <v>129.3656999969483</v>
+        <v>39.34173319498698</v>
       </c>
       <c r="I8">
-        <v>110.3482249641418</v>
+        <v>36.79789991378784</v>
       </c>
       <c r="J8">
-        <v>95.39312496185303</v>
+        <v>33.92774994850159</v>
       </c>
       <c r="K8">
-        <v>16.51000022888184</v>
+        <v>8.689999580383301</v>
       </c>
       <c r="L8">
-        <v>199.9199981689453</v>
+        <v>62.56999969482422</v>
       </c>
       <c r="M8">
-        <v>194.968050850363</v>
+        <v>177.9745074336391</v>
       </c>
       <c r="N8">
-        <v>-0.9</v>
+        <v>0.33</v>
       </c>
       <c r="O8">
-        <v>-0.9</v>
+        <v>0.3</v>
       </c>
       <c r="P8">
-        <v>-0.86</v>
+        <v>0.66</v>
       </c>
       <c r="Q8">
-        <v>-37275000</v>
+        <v>0.5</v>
       </c>
       <c r="R8">
-        <v>-38764000</v>
+        <v>15874000</v>
       </c>
       <c r="S8">
-        <v>-40876000</v>
+        <v>33913000</v>
       </c>
       <c r="T8">
-        <v>-3850.723140495868</v>
+        <v>26032000</v>
       </c>
       <c r="U8">
-        <v>-5936.294027565084</v>
+        <v>91386000</v>
       </c>
       <c r="V8">
-        <v>-3699.185520361991</v>
-      </c>
-      <c r="W8" t="s">
-        <v>232</v>
+        <v>13.21412814557684</v>
+      </c>
+      <c r="W8">
+        <v>25.11646163986876</v>
       </c>
     </row>
     <row r="9" spans="1:23">
@@ -1649,70 +1661,70 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="E9">
-        <v>27.70000076293945</v>
+        <v>11.45499992370605</v>
       </c>
       <c r="F9">
-        <v>4991536.666666667</v>
+        <v>2417736.533333333</v>
       </c>
       <c r="G9">
-        <v>23.85759990692139</v>
+        <v>9.642400016784668</v>
       </c>
       <c r="H9">
-        <v>18.66699996948242</v>
+        <v>8.577800022761027</v>
       </c>
       <c r="I9">
-        <v>16.76044998168945</v>
+        <v>7.30575001835823</v>
       </c>
       <c r="J9">
-        <v>15.32794999599457</v>
+        <v>6.639425020217896</v>
       </c>
       <c r="K9">
-        <v>8.699999809265137</v>
+        <v>0.9279999732971191</v>
       </c>
       <c r="L9">
-        <v>30.6299991607666</v>
+        <v>15.15999984741211</v>
       </c>
       <c r="M9">
-        <v>193.7785972366965</v>
+        <v>176.8736102167953</v>
       </c>
       <c r="N9">
-        <v>-0.11</v>
+        <v>-0.31</v>
       </c>
       <c r="O9">
-        <v>-0.1</v>
+        <v>-0.28</v>
       </c>
       <c r="P9">
-        <v>-0.13</v>
+        <v>-0.3</v>
       </c>
       <c r="Q9">
-        <v>-58555000</v>
+        <v>-0.29</v>
       </c>
       <c r="R9">
-        <v>-53598000</v>
+        <v>-105911000</v>
       </c>
       <c r="S9">
-        <v>-67856000</v>
+        <v>-26633000</v>
       </c>
       <c r="T9">
-        <v>-34.48468786808009</v>
+        <v>-28778000</v>
       </c>
       <c r="U9">
-        <v>-28.72701351184766</v>
+        <v>-106001000</v>
       </c>
       <c r="V9">
-        <v>-33.21064996084574</v>
-      </c>
-      <c r="W9" t="s">
-        <v>232</v>
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -1720,70 +1732,70 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D10" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="E10">
-        <v>182.0700073242188</v>
+        <v>26.21999931335449</v>
       </c>
       <c r="F10">
-        <v>529126.6666666666</v>
+        <v>4639601.466666667</v>
       </c>
       <c r="G10">
-        <v>156.8090005493164</v>
+        <v>21.28239995956421</v>
       </c>
       <c r="H10">
-        <v>127.2209338378906</v>
+        <v>16.52453332265218</v>
       </c>
       <c r="I10">
-        <v>111.836800365448</v>
+        <v>15.73899999141693</v>
       </c>
       <c r="J10">
-        <v>100.8083003044128</v>
+        <v>14.39535000801086</v>
       </c>
       <c r="K10">
-        <v>0.6800000071525574</v>
+        <v>5.564881324768066</v>
       </c>
       <c r="L10">
-        <v>183.3300018310547</v>
+        <v>28.57900047302246</v>
       </c>
       <c r="M10">
-        <v>186.6565012692695</v>
+        <v>176.4818509157336</v>
       </c>
       <c r="N10">
-        <v>1.21</v>
+        <v>0.05</v>
       </c>
       <c r="O10">
-        <v>1.71</v>
+        <v>0.06</v>
       </c>
       <c r="P10">
-        <v>1.43</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q10">
-        <v>40283000</v>
+        <v>0.12</v>
       </c>
       <c r="R10">
-        <v>56992000</v>
+        <v>21200000</v>
       </c>
       <c r="S10">
-        <v>47697000</v>
+        <v>26600000</v>
       </c>
       <c r="T10">
-        <v>17.57739718555689</v>
+        <v>50300000</v>
       </c>
       <c r="U10">
-        <v>21.42145678836013</v>
+        <v>76600000</v>
       </c>
       <c r="V10">
-        <v>18.77686796315251</v>
-      </c>
-      <c r="W10" t="s">
-        <v>232</v>
+        <v>1.431368577408683</v>
+      </c>
+      <c r="W10">
+        <v>1.607639308594222</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -1791,70 +1803,70 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="E11">
-        <v>11.81999969482422</v>
+        <v>68.17500305175781</v>
       </c>
       <c r="F11">
-        <v>2430963.333333333</v>
+        <v>1975441.533333333</v>
       </c>
       <c r="G11">
-        <v>9.506300010681151</v>
+        <v>52.92270011901856</v>
       </c>
       <c r="H11">
-        <v>8.322900021870931</v>
+        <v>41.99056677500407</v>
       </c>
       <c r="I11">
-        <v>7.102525014877319</v>
+        <v>39.81195527076721</v>
       </c>
       <c r="J11">
-        <v>6.51932501912117</v>
+        <v>36.73251899719239</v>
       </c>
       <c r="K11">
-        <v>0.9279999732971191</v>
+        <v>0.6502050161361694</v>
       </c>
       <c r="L11">
-        <v>15.15999984741211</v>
+        <v>68.44000244140625</v>
       </c>
       <c r="M11">
-        <v>186.3484364629211</v>
+        <v>171.5766682443286</v>
       </c>
       <c r="N11">
-        <v>-0.28</v>
+        <v>1.22</v>
       </c>
       <c r="O11">
-        <v>-0.3</v>
+        <v>1.13</v>
       </c>
       <c r="P11">
-        <v>-0.29</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="Q11">
-        <v>-105911000</v>
+        <v>0.13</v>
       </c>
       <c r="R11">
-        <v>-26633000</v>
+        <v>131000000</v>
       </c>
       <c r="S11">
-        <v>-28778000</v>
+        <v>-94000000</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>14000000</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>666000000</v>
       </c>
       <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11" t="s">
-        <v>232</v>
+        <v>4.30637738330046</v>
+      </c>
+      <c r="W11">
+        <v>-5.133806663025669</v>
       </c>
     </row>
     <row r="12" spans="1:23">
@@ -1862,70 +1874,70 @@
         <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D12" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="E12">
-        <v>26.51000022888184</v>
+        <v>37.34000015258789</v>
       </c>
       <c r="F12">
-        <v>4642626.666666667</v>
+        <v>600920</v>
       </c>
       <c r="G12">
-        <v>20.11999996185303</v>
+        <v>29.21940013885498</v>
       </c>
       <c r="H12">
-        <v>16.10286665598552</v>
+        <v>24.5393333307902</v>
       </c>
       <c r="I12">
-        <v>15.32339999198914</v>
+        <v>22.90545000553131</v>
       </c>
       <c r="J12">
-        <v>14.11775000572205</v>
+        <v>20.97914999008179</v>
       </c>
       <c r="K12">
-        <v>5.564881324768066</v>
+        <v>0.5703791379928589</v>
       </c>
       <c r="L12">
-        <v>28.57900047302246</v>
+        <v>37.97000122070312</v>
       </c>
       <c r="M12">
-        <v>182.3985777141801</v>
+        <v>170.963041427082</v>
       </c>
       <c r="N12">
-        <v>0.06</v>
+        <v>0.27</v>
       </c>
       <c r="O12">
-        <v>0.07000000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="P12">
-        <v>0.12</v>
+        <v>0.46</v>
       </c>
       <c r="Q12">
-        <v>21200000</v>
+        <v>1.69</v>
       </c>
       <c r="R12">
-        <v>26600000</v>
+        <v>24400000</v>
       </c>
       <c r="S12">
-        <v>50300000</v>
+        <v>24500000</v>
       </c>
       <c r="T12">
-        <v>1.431368577408683</v>
+        <v>89900000</v>
       </c>
       <c r="U12">
-        <v>1.607639308594222</v>
+        <v>71600000</v>
       </c>
       <c r="V12">
-        <v>3.306817434751167</v>
-      </c>
-      <c r="W12" t="s">
-        <v>233</v>
+        <v>4.215618521078093</v>
+      </c>
+      <c r="W12">
+        <v>4.375</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -1933,70 +1945,70 @@
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D13" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="E13">
-        <v>27.68000030517578</v>
+        <v>113.3199996948242</v>
       </c>
       <c r="F13">
-        <v>1151900</v>
+        <v>967465.2</v>
       </c>
       <c r="G13">
-        <v>22.8202000617981</v>
+        <v>104.2994000244141</v>
       </c>
       <c r="H13">
-        <v>18.56460001627604</v>
+        <v>82.32086659749349</v>
       </c>
       <c r="I13">
-        <v>17.71044999599457</v>
+        <v>73.58999992370606</v>
       </c>
       <c r="J13">
-        <v>16.79100002765655</v>
+        <v>66.16924993515015</v>
       </c>
       <c r="K13">
-        <v>6.489999771118164</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="L13">
-        <v>36.5</v>
+        <v>119.5100021362305</v>
       </c>
       <c r="M13">
-        <v>176.9675882803405</v>
+        <v>170.0064407452977</v>
       </c>
       <c r="N13">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="O13">
-        <v>0.1</v>
+        <v>0.21</v>
       </c>
       <c r="P13">
-        <v>-0.55</v>
+        <v>0.34</v>
       </c>
       <c r="Q13">
-        <v>51522000</v>
+        <v>0.29</v>
       </c>
       <c r="R13">
-        <v>-27219000</v>
+        <v>11710000</v>
       </c>
       <c r="S13">
-        <v>-24455000</v>
+        <v>19105000</v>
       </c>
       <c r="T13">
-        <v>2.838855994260796</v>
+        <v>16246000</v>
       </c>
       <c r="U13">
-        <v>-6.342182890855458</v>
+        <v>46840000</v>
       </c>
       <c r="V13">
-        <v>-6.379620692353846</v>
-      </c>
-      <c r="W13" t="s">
-        <v>232</v>
+        <v>9.570981372957686</v>
+      </c>
+      <c r="W13">
+        <v>13.03766284283151</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -2004,70 +2016,70 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C14" t="s">
         <v>126</v>
       </c>
       <c r="D14" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="E14">
-        <v>139.8699951171875</v>
+        <v>20.01000022888184</v>
       </c>
       <c r="F14">
-        <v>2656886.666666667</v>
+        <v>916925.8</v>
       </c>
       <c r="G14">
-        <v>122.7883996582031</v>
+        <v>18.06240009307861</v>
       </c>
       <c r="H14">
-        <v>93.83926643371582</v>
+        <v>14.00320000330607</v>
       </c>
       <c r="I14">
-        <v>85.55239980697633</v>
+        <v>12.60069999694824</v>
       </c>
       <c r="J14">
-        <v>78.18269979476929</v>
+        <v>11.53505000114441</v>
       </c>
       <c r="K14">
-        <v>0.8299999833106995</v>
+        <v>6.690000057220459</v>
       </c>
       <c r="L14">
-        <v>139.8699951171875</v>
+        <v>26.39999961853027</v>
       </c>
       <c r="M14">
-        <v>173.5201968164739</v>
+        <v>164.6609273103286</v>
       </c>
       <c r="N14">
-        <v>5.75</v>
+        <v>0.01</v>
       </c>
       <c r="O14">
-        <v>4.72</v>
+        <v>0.004895</v>
       </c>
       <c r="P14">
-        <v>2.41</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q14">
-        <v>738007000</v>
+        <v>0.02</v>
       </c>
       <c r="R14">
-        <v>384513000</v>
+        <v>767000</v>
       </c>
       <c r="S14">
-        <v>333786000</v>
+        <v>11487000</v>
       </c>
       <c r="T14">
-        <v>12.80936803725026</v>
+        <v>3146000</v>
       </c>
       <c r="U14">
-        <v>8.824033605924409</v>
+        <v>15373000</v>
       </c>
       <c r="V14">
-        <v>8.595390431986701</v>
-      </c>
-      <c r="W14" t="s">
-        <v>232</v>
+        <v>0.7568356965947327</v>
+      </c>
+      <c r="W14">
+        <v>9.781581300293778</v>
       </c>
     </row>
     <row r="15" spans="1:23">
@@ -2075,70 +2087,70 @@
         <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C15" t="s">
         <v>127</v>
       </c>
       <c r="D15" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="E15">
-        <v>115.6100006103516</v>
+        <v>138.7449951171875</v>
       </c>
       <c r="F15">
-        <v>1004743.333333333</v>
+        <v>2111214.766666667</v>
       </c>
       <c r="G15">
-        <v>101.7255999755859</v>
+        <v>126.3730999755859</v>
       </c>
       <c r="H15">
-        <v>80.26799992879232</v>
+        <v>96.42396644592286</v>
       </c>
       <c r="I15">
-        <v>71.63489990234375</v>
+        <v>87.70662487030029</v>
       </c>
       <c r="J15">
-        <v>64.46224990844726</v>
+        <v>79.79029989242554</v>
       </c>
       <c r="K15">
-        <v>7.300000190734863</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="L15">
-        <v>115.6100006103516</v>
+        <v>146.4199981689453</v>
       </c>
       <c r="M15">
-        <v>171.8209673604115</v>
+        <v>162.1359849282519</v>
       </c>
       <c r="N15">
-        <v>0.21</v>
+        <v>2.41</v>
       </c>
       <c r="O15">
-        <v>0.34</v>
+        <v>5.75</v>
       </c>
       <c r="P15">
-        <v>0.29</v>
+        <v>4.72</v>
       </c>
       <c r="Q15">
-        <v>11710000</v>
+        <v>2.41</v>
       </c>
       <c r="R15">
-        <v>19105000</v>
+        <v>738007000</v>
       </c>
       <c r="S15">
-        <v>16246000</v>
+        <v>384513000</v>
       </c>
       <c r="T15">
-        <v>9.570981372957686</v>
+        <v>333786000</v>
       </c>
       <c r="U15">
-        <v>13.03766284283151</v>
+        <v>2749369000</v>
       </c>
       <c r="V15">
-        <v>8.671146527751832</v>
-      </c>
-      <c r="W15" t="s">
-        <v>232</v>
+        <v>12.80936803725026</v>
+      </c>
+      <c r="W15">
+        <v>8.824033605924409</v>
       </c>
     </row>
     <row r="16" spans="1:23">
@@ -2146,70 +2158,70 @@
         <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
         <v>128</v>
       </c>
       <c r="D16" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="E16">
-        <v>36.66999816894531</v>
+        <v>47.82009887695312</v>
       </c>
       <c r="F16">
-        <v>572870</v>
+        <v>1418337.566666667</v>
       </c>
       <c r="G16">
-        <v>27.85920017242432</v>
+        <v>38.34760185241699</v>
       </c>
       <c r="H16">
-        <v>24.07860000610351</v>
+        <v>32.56580055236817</v>
       </c>
       <c r="I16">
-        <v>22.42570001125336</v>
+        <v>29.74360040187836</v>
       </c>
       <c r="J16">
-        <v>20.6602999830246</v>
+        <v>26.9578499174118</v>
       </c>
       <c r="K16">
-        <v>0.5703791379928589</v>
+        <v>0.5</v>
       </c>
       <c r="L16">
-        <v>36.66999816894531</v>
+        <v>52.16999816894531</v>
       </c>
       <c r="M16">
-        <v>171.4245788359831</v>
+        <v>159.2256496329512</v>
       </c>
       <c r="N16">
-        <v>0.46</v>
+        <v>0.02</v>
       </c>
       <c r="O16">
-        <v>0.46</v>
+        <v>0.13</v>
       </c>
       <c r="P16">
-        <v>1.69</v>
+        <v>0.14</v>
       </c>
       <c r="Q16">
-        <v>24400000</v>
+        <v>0.21</v>
       </c>
       <c r="R16">
-        <v>24500000</v>
+        <v>3725000</v>
       </c>
       <c r="S16">
-        <v>89900000</v>
+        <v>4132000</v>
       </c>
       <c r="T16">
-        <v>4.215618521078093</v>
+        <v>6111000</v>
       </c>
       <c r="U16">
-        <v>4.375</v>
+        <v>14240000</v>
       </c>
       <c r="V16">
-        <v>14.5445720757159</v>
-      </c>
-      <c r="W16" t="s">
-        <v>232</v>
+        <v>25.14343570705366</v>
+      </c>
+      <c r="W16">
+        <v>24.01487853074509</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -2223,64 +2235,64 @@
         <v>129</v>
       </c>
       <c r="D17" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="E17">
-        <v>87.01000213623047</v>
+        <v>37.58000183105469</v>
       </c>
       <c r="F17">
-        <v>3624056.666666667</v>
+        <v>6620912.066666666</v>
       </c>
       <c r="G17">
-        <v>72.08040031433106</v>
+        <v>32.59409988403321</v>
       </c>
       <c r="H17">
-        <v>59.81466679890951</v>
+        <v>26.30549996693929</v>
       </c>
       <c r="I17">
-        <v>58.12915006637573</v>
+        <v>24.42729997158051</v>
       </c>
       <c r="J17">
-        <v>56.60115001678466</v>
+        <v>23.36699998378754</v>
       </c>
       <c r="K17">
-        <v>2.279999971389771</v>
+        <v>13.61999988555908</v>
       </c>
       <c r="L17">
-        <v>111.6399993896484</v>
+        <v>43.95999908447266</v>
       </c>
       <c r="M17">
-        <v>167.2588838695628</v>
+        <v>157.6522101953819</v>
       </c>
       <c r="N17">
-        <v>0.03</v>
+        <v>0.9</v>
       </c>
       <c r="O17">
-        <v>0.14</v>
+        <v>-0.64</v>
       </c>
       <c r="P17">
-        <v>0.02</v>
+        <v>0.26</v>
       </c>
       <c r="Q17">
-        <v>15869000</v>
+        <v>0.9</v>
       </c>
       <c r="R17">
-        <v>71187000</v>
+        <v>-1640321000</v>
       </c>
       <c r="S17">
-        <v>9326000</v>
+        <v>256938000</v>
       </c>
       <c r="T17">
-        <v>4.019778454960192</v>
+        <v>929668000</v>
       </c>
       <c r="U17">
-        <v>14.50614076378997</v>
+        <v>-2012215000</v>
       </c>
       <c r="V17">
-        <v>2.436240050365332</v>
-      </c>
-      <c r="W17" t="s">
-        <v>232</v>
+        <v>-17.55802782723927</v>
+      </c>
+      <c r="W17">
+        <v>1.455749769091836</v>
       </c>
     </row>
     <row r="18" spans="1:23">
@@ -2288,70 +2300,70 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D18" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="E18">
-        <v>41.43000030517578</v>
+        <v>175.2299957275391</v>
       </c>
       <c r="F18">
-        <v>1193266.666666667</v>
+        <v>533022.3</v>
       </c>
       <c r="G18">
-        <v>35.98019989013672</v>
+        <v>163.3296003723144</v>
       </c>
       <c r="H18">
-        <v>31.71073323567708</v>
+        <v>130.6928004964193</v>
       </c>
       <c r="I18">
-        <v>28.84469991207123</v>
+        <v>114.9425503349304</v>
       </c>
       <c r="J18">
-        <v>26.313299908638</v>
+        <v>103.3325002670288</v>
       </c>
       <c r="K18">
-        <v>0.5</v>
+        <v>0.6800000071525574</v>
       </c>
       <c r="L18">
-        <v>44.2400016784668</v>
+        <v>192.2700042724609</v>
       </c>
       <c r="M18">
-        <v>167.1012778048138</v>
+        <v>157.6286106981774</v>
       </c>
       <c r="N18">
-        <v>0.02</v>
+        <v>1.32</v>
       </c>
       <c r="O18">
-        <v>0.13</v>
+        <v>1.21</v>
       </c>
       <c r="P18">
-        <v>0.14</v>
+        <v>1.71</v>
       </c>
       <c r="Q18">
-        <v>5794000</v>
+        <v>1.43</v>
       </c>
       <c r="R18">
-        <v>589000</v>
+        <v>40283000</v>
       </c>
       <c r="S18">
-        <v>4132000</v>
+        <v>56992000</v>
       </c>
       <c r="T18">
-        <v>28.55734634531027</v>
+        <v>47697000</v>
       </c>
       <c r="U18">
-        <v>5.519632649236248</v>
+        <v>183079000</v>
       </c>
       <c r="V18">
-        <v>24.01487853074509</v>
-      </c>
-      <c r="W18" t="s">
-        <v>232</v>
+        <v>17.57739718555689</v>
+      </c>
+      <c r="W18">
+        <v>21.42145678836013</v>
       </c>
     </row>
     <row r="19" spans="1:23">
@@ -2359,70 +2371,70 @@
         <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C19" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D19" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E19">
-        <v>90.43000030517578</v>
+        <v>29.15500068664551</v>
       </c>
       <c r="F19">
-        <v>346263.3333333333</v>
+        <v>1343585.8</v>
       </c>
       <c r="G19">
-        <v>75.91020034790039</v>
+        <v>25.16089996337891</v>
       </c>
       <c r="H19">
-        <v>63.0909334564209</v>
+        <v>21.43899996439616</v>
       </c>
       <c r="I19">
-        <v>57.63415012359619</v>
+        <v>19.82494998931885</v>
       </c>
       <c r="J19">
-        <v>53.42870014190674</v>
+        <v>18.88627500534058</v>
       </c>
       <c r="K19">
-        <v>3.118403196334839</v>
+        <v>6.309999942779541</v>
       </c>
       <c r="L19">
-        <v>90.43000030517578</v>
+        <v>37.61000061035156</v>
       </c>
       <c r="M19">
-        <v>164.7862566176076</v>
+        <v>156.2233337826705</v>
       </c>
       <c r="N19">
-        <v>4.67</v>
+        <v>-0.35</v>
       </c>
       <c r="O19">
-        <v>4.65</v>
+        <v>-0.32</v>
       </c>
       <c r="P19">
-        <v>3.64</v>
+        <v>-0.21</v>
       </c>
       <c r="Q19">
-        <v>131590000</v>
+        <v>-0.21</v>
       </c>
       <c r="R19">
-        <v>130395000</v>
+        <v>-37149000</v>
       </c>
       <c r="S19">
-        <v>103066000</v>
+        <v>-24642000</v>
       </c>
       <c r="T19">
-        <v>12.99105168383143</v>
+        <v>-24855000</v>
       </c>
       <c r="U19">
-        <v>10.71446179129006</v>
+        <v>-100322000</v>
       </c>
       <c r="V19">
-        <v>10.30114039559034</v>
-      </c>
-      <c r="W19" t="s">
-        <v>232</v>
+        <v>-8.405093420094031</v>
+      </c>
+      <c r="W19">
+        <v>-7.937254396701668</v>
       </c>
     </row>
     <row r="20" spans="1:23">
@@ -2430,70 +2442,70 @@
         <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D20" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="E20">
-        <v>37.36000061035156</v>
+        <v>58.29999923706055</v>
       </c>
       <c r="F20">
-        <v>7131050</v>
+        <v>336508.3333333333</v>
       </c>
       <c r="G20">
-        <v>31.21269992828369</v>
+        <v>51.38119995117187</v>
       </c>
       <c r="H20">
-        <v>25.80109999338786</v>
+        <v>41.22406667073567</v>
       </c>
       <c r="I20">
-        <v>24.1077999830246</v>
+        <v>38.10785000801086</v>
       </c>
       <c r="J20">
-        <v>23.23604998111725</v>
+        <v>34.76280000686646</v>
       </c>
       <c r="K20">
-        <v>13.61999988555908</v>
+        <v>0.4209107160568237</v>
       </c>
       <c r="L20">
-        <v>43.95999908447266</v>
+        <v>59.93999862670898</v>
       </c>
       <c r="M20">
-        <v>162.2340283588514</v>
+        <v>155.026275051384</v>
       </c>
       <c r="N20">
-        <v>-0.64</v>
+        <v>0.86</v>
       </c>
       <c r="O20">
-        <v>0.26</v>
+        <v>0.97</v>
       </c>
       <c r="P20">
-        <v>0.9</v>
+        <v>1.03</v>
       </c>
       <c r="Q20">
-        <v>-1640321000</v>
+        <v>0.64</v>
       </c>
       <c r="R20">
-        <v>256938000</v>
+        <v>29523000</v>
       </c>
       <c r="S20">
-        <v>929668000</v>
+        <v>31725000</v>
       </c>
       <c r="T20">
-        <v>-17.55802782723927</v>
+        <v>19649000</v>
       </c>
       <c r="U20">
-        <v>1.455749769091836</v>
+        <v>106461000</v>
       </c>
       <c r="V20">
-        <v>4.948450403583787</v>
-      </c>
-      <c r="W20" t="s">
-        <v>233</v>
+        <v>5.300911046392623</v>
+      </c>
+      <c r="W20">
+        <v>7.071891432813131</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -2501,70 +2513,70 @@
         <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
         <v>123</v>
       </c>
       <c r="D21" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="E21">
-        <v>517.280029296875</v>
+        <v>405.2049865722656</v>
       </c>
       <c r="F21">
-        <v>4469773.333333333</v>
+        <v>586684.6</v>
       </c>
       <c r="G21">
-        <v>428.2163989257813</v>
+        <v>315.7152996826172</v>
       </c>
       <c r="H21">
-        <v>380.0418664550782</v>
+        <v>280.4078331502279</v>
       </c>
       <c r="I21">
-        <v>362.5753993225098</v>
+        <v>264.6004747772217</v>
       </c>
       <c r="J21">
-        <v>348.4745994567871</v>
+        <v>248.8530498504639</v>
       </c>
       <c r="K21">
-        <v>0.1503329128026962</v>
+        <v>4.533332824707031</v>
       </c>
       <c r="L21">
-        <v>688.3699951171875</v>
+        <v>405.2049865722656</v>
       </c>
       <c r="M21">
-        <v>160.3951568308797</v>
+        <v>154.420228958684</v>
       </c>
       <c r="N21">
-        <v>2.53</v>
+        <v>4.1</v>
       </c>
       <c r="O21">
-        <v>2.71</v>
+        <v>3.67</v>
       </c>
       <c r="P21">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="Q21">
-        <v>4756000000</v>
+        <v>2.85</v>
       </c>
       <c r="R21">
-        <v>1247000000</v>
+        <v>97891000</v>
       </c>
       <c r="S21">
-        <v>1295000000</v>
+        <v>70862000</v>
       </c>
       <c r="T21">
-        <v>27.01351811882313</v>
+        <v>76097000</v>
       </c>
       <c r="U21">
-        <v>26.78839957035446</v>
+        <v>357422000</v>
       </c>
       <c r="V21">
-        <v>26.88953488372093</v>
-      </c>
-      <c r="W21" t="s">
-        <v>232</v>
+        <v>13.41779508498947</v>
+      </c>
+      <c r="W21">
+        <v>10.80664789866499</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -2575,67 +2587,67 @@
         <v>108</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D22" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="E22">
-        <v>40.38999938964844</v>
+        <v>90.30000305175781</v>
       </c>
       <c r="F22">
-        <v>1467923.333333333</v>
+        <v>339901.3666666666</v>
       </c>
       <c r="G22">
-        <v>34.20039981842041</v>
+        <v>78.41020034790039</v>
       </c>
       <c r="H22">
-        <v>29.07053329467773</v>
+        <v>64.67586680094401</v>
       </c>
       <c r="I22">
-        <v>28.58174997329712</v>
+        <v>59.01905014038086</v>
       </c>
       <c r="J22">
-        <v>27.46369999885559</v>
+        <v>54.30390008926392</v>
       </c>
       <c r="K22">
-        <v>18.28000068664551</v>
+        <v>3.118403196334839</v>
       </c>
       <c r="L22">
-        <v>47.06000137329102</v>
+        <v>93.88999938964844</v>
       </c>
       <c r="M22">
-        <v>160.3321714190521</v>
+        <v>154.0481122143651</v>
       </c>
       <c r="N22">
-        <v>0.06</v>
+        <v>4.79</v>
       </c>
       <c r="O22">
-        <v>0.06</v>
+        <v>4.67</v>
       </c>
       <c r="P22">
-        <v>0.07000000000000001</v>
+        <v>4.65</v>
       </c>
       <c r="Q22">
-        <v>53508000</v>
+        <v>3.64</v>
       </c>
       <c r="R22">
-        <v>18068000</v>
+        <v>131590000</v>
       </c>
       <c r="S22">
-        <v>12175000</v>
+        <v>130395000</v>
       </c>
       <c r="T22">
-        <v>12.61044271355007</v>
+        <v>103066000</v>
       </c>
       <c r="U22">
-        <v>13.52030889879972</v>
+        <v>490662000</v>
       </c>
       <c r="V22">
-        <v>9.931154868916913</v>
-      </c>
-      <c r="W22" t="s">
-        <v>232</v>
+        <v>12.99105168383143</v>
+      </c>
+      <c r="W22">
+        <v>10.71446179129006</v>
       </c>
     </row>
     <row r="23" spans="1:23">
@@ -2643,70 +2655,70 @@
         <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C23" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D23" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="E23">
-        <v>55.27999877929688</v>
+        <v>32.77000045776367</v>
       </c>
       <c r="F23">
-        <v>493696.6666666667</v>
+        <v>298733.1666666667</v>
       </c>
       <c r="G23">
-        <v>47.95419967651367</v>
+        <v>29.84819995880127</v>
       </c>
       <c r="H23">
-        <v>38.31506652832032</v>
+        <v>24.78993328094482</v>
       </c>
       <c r="I23">
-        <v>36.02039992332458</v>
+        <v>22.66164997577667</v>
       </c>
       <c r="J23">
-        <v>33.34484996795654</v>
+        <v>21.20379998683929</v>
       </c>
       <c r="K23">
-        <v>8.689999580383301</v>
+        <v>14.10000038146973</v>
       </c>
       <c r="L23">
-        <v>58.38000106811523</v>
+        <v>33.61000061035156</v>
       </c>
       <c r="M23">
-        <v>159.544380796584</v>
+        <v>153.4393796479383</v>
       </c>
       <c r="N23">
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="O23">
-        <v>0.66</v>
+        <v>0.14</v>
       </c>
       <c r="P23">
-        <v>0.5</v>
+        <v>0.18</v>
       </c>
       <c r="Q23">
-        <v>15874000</v>
+        <v>0.11</v>
       </c>
       <c r="R23">
-        <v>33913000</v>
+        <v>36215000</v>
       </c>
       <c r="S23">
-        <v>26032000</v>
+        <v>48300000</v>
       </c>
       <c r="T23">
-        <v>13.21412814557684</v>
+        <v>28265000</v>
       </c>
       <c r="U23">
-        <v>25.11646163986876</v>
+        <v>142849000</v>
       </c>
       <c r="V23">
-        <v>18.59136421419491</v>
-      </c>
-      <c r="W23" t="s">
-        <v>232</v>
+        <v>14.76590244678119</v>
+      </c>
+      <c r="W23">
+        <v>16.53543307086614</v>
       </c>
     </row>
     <row r="24" spans="1:23">
@@ -2714,70 +2726,70 @@
         <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D24" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="E24">
-        <v>28.6299991607666</v>
+        <v>40.69499969482422</v>
       </c>
       <c r="F24">
-        <v>1447250</v>
+        <v>1344397.433333333</v>
       </c>
       <c r="G24">
-        <v>23.95279998779297</v>
+        <v>35.55129978179932</v>
       </c>
       <c r="H24">
-        <v>20.97689996083577</v>
+        <v>29.58976660410563</v>
       </c>
       <c r="I24">
-        <v>19.45152498722076</v>
+        <v>28.91127495765686</v>
       </c>
       <c r="J24">
-        <v>18.69807501792908</v>
+        <v>27.75124997138977</v>
       </c>
       <c r="K24">
-        <v>6.309999942779541</v>
+        <v>18.28000068664551</v>
       </c>
       <c r="L24">
-        <v>37.61000061035156</v>
+        <v>47.06000137329102</v>
       </c>
       <c r="M24">
-        <v>159.1537021783387</v>
+        <v>151.1949273850225</v>
       </c>
       <c r="N24">
-        <v>-0.32</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O24">
-        <v>-0.21</v>
+        <v>0.06</v>
       </c>
       <c r="P24">
-        <v>-0.21</v>
+        <v>0.06</v>
       </c>
       <c r="Q24">
-        <v>-37149000</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R24">
-        <v>-24642000</v>
+        <v>53508000</v>
       </c>
       <c r="S24">
-        <v>-24855000</v>
+        <v>18068000</v>
       </c>
       <c r="T24">
-        <v>-8.405093420094031</v>
+        <v>12175000</v>
       </c>
       <c r="U24">
-        <v>-7.937254396701668</v>
+        <v>43268000</v>
       </c>
       <c r="V24">
-        <v>-3.559939614945014</v>
-      </c>
-      <c r="W24" t="s">
-        <v>232</v>
+        <v>12.61044271355007</v>
+      </c>
+      <c r="W24">
+        <v>13.52030889879972</v>
       </c>
     </row>
     <row r="25" spans="1:23">
@@ -2785,70 +2797,70 @@
         <v>46</v>
       </c>
       <c r="B25" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D25" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="E25">
-        <v>27.38999938964844</v>
+        <v>33.88999938964844</v>
       </c>
       <c r="F25">
-        <v>721873.3333333334</v>
+        <v>840301.0333333333</v>
       </c>
       <c r="G25">
-        <v>22.4988000869751</v>
+        <v>30.68399974822998</v>
       </c>
       <c r="H25">
-        <v>19.06573338826497</v>
+        <v>25.43969992319743</v>
       </c>
       <c r="I25">
-        <v>17.41760003566742</v>
+        <v>23.71327492713928</v>
       </c>
       <c r="J25">
-        <v>15.97405003547668</v>
+        <v>22.47212496757507</v>
       </c>
       <c r="K25">
-        <v>1.899999976158142</v>
+        <v>0.1500000059604645</v>
       </c>
       <c r="L25">
-        <v>27.38999938964844</v>
+        <v>38.15000152587891</v>
       </c>
       <c r="M25">
-        <v>158.1967608879753</v>
+        <v>151.070099883861</v>
       </c>
       <c r="N25">
-        <v>0.75</v>
+        <v>0.13</v>
       </c>
       <c r="O25">
-        <v>0.762</v>
+        <v>0.01</v>
       </c>
       <c r="P25">
-        <v>1.315</v>
+        <v>-0.02</v>
       </c>
       <c r="Q25">
-        <v>76661000</v>
+        <v>-0.36</v>
       </c>
       <c r="R25">
-        <v>75504000</v>
+        <v>668000</v>
       </c>
       <c r="S25">
-        <v>128734000</v>
+        <v>-934000</v>
       </c>
       <c r="T25">
-        <v>22.98177610298196</v>
+        <v>-21005000</v>
       </c>
       <c r="U25">
-        <v>24.50593141948362</v>
+        <v>10650000</v>
       </c>
       <c r="V25">
-        <v>42.45662290205235</v>
-      </c>
-      <c r="W25" t="s">
-        <v>232</v>
+        <v>0.1908331524036978</v>
+      </c>
+      <c r="W25">
+        <v>-0.2433083686095734</v>
       </c>
     </row>
     <row r="26" spans="1:23">
@@ -2856,70 +2868,70 @@
         <v>47</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C26" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D26" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="E26">
-        <v>58.56000137329102</v>
+        <v>101.4199981689453</v>
       </c>
       <c r="F26">
-        <v>357543.3333333333</v>
+        <v>3700452</v>
       </c>
       <c r="G26">
-        <v>49.64</v>
+        <v>91.07940002441406</v>
       </c>
       <c r="H26">
-        <v>40.32546670277913</v>
+        <v>72.86646677652995</v>
       </c>
       <c r="I26">
-        <v>37.16305000305176</v>
+        <v>67.82025005340576</v>
       </c>
       <c r="J26">
-        <v>34.09489999771118</v>
+        <v>62.36230012893677</v>
       </c>
       <c r="K26">
-        <v>0.4209107160568237</v>
+        <v>4.547188282012939</v>
       </c>
       <c r="L26">
-        <v>58.56000137329102</v>
+        <v>133.7226409912109</v>
       </c>
       <c r="M26">
-        <v>157.690312310653</v>
+        <v>150.5165850579068</v>
       </c>
       <c r="N26">
-        <v>0.97</v>
+        <v>-2.05</v>
       </c>
       <c r="O26">
-        <v>1.03</v>
+        <v>0.13</v>
       </c>
       <c r="P26">
-        <v>0.64</v>
+        <v>-1.96</v>
       </c>
       <c r="Q26">
-        <v>29523000</v>
+        <v>-0.19</v>
       </c>
       <c r="R26">
-        <v>31725000</v>
+        <v>32968000</v>
       </c>
       <c r="S26">
-        <v>19649000</v>
+        <v>-500206000</v>
       </c>
       <c r="T26">
-        <v>5.300911046392623</v>
+        <v>-47910000</v>
       </c>
       <c r="U26">
-        <v>7.071891432813131</v>
+        <v>-2155962000</v>
       </c>
       <c r="V26">
-        <v>4.868687419315673</v>
-      </c>
-      <c r="W26" t="s">
-        <v>232</v>
+        <v>1.10147590688506</v>
+      </c>
+      <c r="W26">
+        <v>-19.20919879938187</v>
       </c>
     </row>
     <row r="27" spans="1:23">
@@ -2927,70 +2939,70 @@
         <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="E27">
-        <v>60.75</v>
+        <v>46.72000122070312</v>
       </c>
       <c r="F27">
-        <v>1807626.666666667</v>
+        <v>2891136.566666667</v>
       </c>
       <c r="G27">
-        <v>51.04740013122559</v>
+        <v>39.32559997558594</v>
       </c>
       <c r="H27">
-        <v>41.03300009409587</v>
+        <v>33.34709997812907</v>
       </c>
       <c r="I27">
-        <v>38.84759076118469</v>
+        <v>33.20189993858337</v>
       </c>
       <c r="J27">
-        <v>36.22838760375976</v>
+        <v>30.47309996604919</v>
       </c>
       <c r="K27">
-        <v>0.6502050161361694</v>
+        <v>13.1899995803833</v>
       </c>
       <c r="L27">
-        <v>60.75</v>
+        <v>46.91999816894531</v>
       </c>
       <c r="M27">
-        <v>156.8422495088006</v>
+        <v>149.2954192871287</v>
       </c>
       <c r="N27">
-        <v>1.13</v>
+        <v>-0.58</v>
       </c>
       <c r="O27">
-        <v>-0.8100000000000001</v>
+        <v>-0.55</v>
       </c>
       <c r="P27">
-        <v>0.13</v>
+        <v>-0.51</v>
       </c>
       <c r="Q27">
-        <v>131000000</v>
+        <v>-0.54</v>
       </c>
       <c r="R27">
-        <v>-94000000</v>
+        <v>-76858000</v>
       </c>
       <c r="S27">
-        <v>14000000</v>
+        <v>-23224000</v>
       </c>
       <c r="T27">
-        <v>4.30637738330046</v>
+        <v>-25646000</v>
       </c>
       <c r="U27">
-        <v>-5.133806663025669</v>
+        <v>-83887000</v>
       </c>
       <c r="V27">
-        <v>0.7341373885684321</v>
-      </c>
-      <c r="W27" t="s">
-        <v>232</v>
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:23">
@@ -2998,70 +3010,70 @@
         <v>49</v>
       </c>
       <c r="B28" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="E28">
-        <v>890.3599853515625</v>
+        <v>901.9600219726562</v>
       </c>
       <c r="F28">
-        <v>3347900</v>
+        <v>2714493.833333333</v>
       </c>
       <c r="G28">
-        <v>772.7170007324219</v>
+        <v>800.9332006835938</v>
       </c>
       <c r="H28">
-        <v>656.0142000325521</v>
+        <v>668.2071333821615</v>
       </c>
       <c r="I28">
-        <v>611.8289497375488</v>
+        <v>622.9218496704102</v>
       </c>
       <c r="J28">
-        <v>575.8327499389649</v>
+        <v>584.9370498657227</v>
       </c>
       <c r="K28">
         <v>11.17089080810547</v>
       </c>
       <c r="L28">
-        <v>890.3599853515625</v>
+        <v>910.3499755859375</v>
       </c>
       <c r="M28">
-        <v>155.7719984672208</v>
+        <v>147.3335984920871</v>
       </c>
       <c r="N28">
+        <v>7.132125</v>
+      </c>
+      <c r="O28">
         <v>7.810425</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>8.800000000000001</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>8.15</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <v>3359000000</v>
       </c>
-      <c r="R28">
+      <c r="S28">
         <v>3774000000</v>
       </c>
-      <c r="S28">
+      <c r="T28">
         <v>3481000000</v>
       </c>
-      <c r="T28">
+      <c r="U28">
+        <v>12797000000</v>
+      </c>
+      <c r="V28">
         <v>37.61478163493841</v>
       </c>
-      <c r="U28">
+      <c r="W28">
         <v>42.3331463825014</v>
-      </c>
-      <c r="V28">
-        <v>39.86030001145082</v>
-      </c>
-      <c r="W28" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="29" spans="1:23">
@@ -3069,58 +3081,58 @@
         <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C29" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D29" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E29">
-        <v>125.4100036621094</v>
+        <v>23.39999961853027</v>
       </c>
       <c r="F29">
-        <v>298270</v>
+        <v>2371178.4</v>
       </c>
       <c r="G29">
-        <v>112.1208000183105</v>
+        <v>19.96039989471436</v>
       </c>
       <c r="H29">
-        <v>90.32060012817382</v>
+        <v>16.72733331680298</v>
       </c>
       <c r="I29">
-        <v>85.99880014419556</v>
+        <v>16.45255001544952</v>
       </c>
       <c r="J29">
-        <v>80.8896001625061</v>
+        <v>15.61825001239777</v>
       </c>
       <c r="K29">
-        <v>8.189999580383301</v>
+        <v>12.61999988555908</v>
       </c>
       <c r="L29">
-        <v>130.3200073242188</v>
+        <v>24.46999931335449</v>
       </c>
       <c r="M29">
-        <v>155.7155336731865</v>
+        <v>147.2667966495009</v>
       </c>
       <c r="N29">
-        <v>-1.1</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>-1.17</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>-1.76</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>-129729000</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>-32052000</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>-45297000</v>
+        <v>0</v>
       </c>
       <c r="T29">
         <v>0</v>
@@ -3131,8 +3143,8 @@
       <c r="V29">
         <v>0</v>
       </c>
-      <c r="W29" t="s">
-        <v>232</v>
+      <c r="W29">
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:23">
@@ -3140,70 +3152,70 @@
         <v>51</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C30" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="E30">
-        <v>112.8600006103516</v>
+        <v>112.9599990844727</v>
       </c>
       <c r="F30">
-        <v>1129976.666666667</v>
+        <v>1156765.166666667</v>
       </c>
       <c r="G30">
-        <v>94.164599609375</v>
+        <v>97.77379959106446</v>
       </c>
       <c r="H30">
-        <v>83.94999994913736</v>
+        <v>85.35459986368815</v>
       </c>
       <c r="I30">
-        <v>78.94209985733032</v>
+        <v>80.32604984283448</v>
       </c>
       <c r="J30">
-        <v>74.19649988174439</v>
+        <v>75.28169990539551</v>
       </c>
       <c r="K30">
         <v>0.3787146806716919</v>
       </c>
       <c r="L30">
-        <v>112.8600006103516</v>
+        <v>115.1399993896484</v>
       </c>
       <c r="M30">
-        <v>152.7614276342225</v>
+        <v>146.4094264237745</v>
       </c>
       <c r="N30">
+        <v>2.25</v>
+      </c>
+      <c r="O30">
         <v>1.61</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>1.52</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>1.72</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>978000000</v>
       </c>
-      <c r="R30">
+      <c r="S30">
         <v>207000000</v>
       </c>
-      <c r="S30">
+      <c r="T30">
         <v>233000000</v>
       </c>
-      <c r="T30">
+      <c r="U30">
+        <v>963000000</v>
+      </c>
+      <c r="V30">
         <v>2.831007931453714</v>
       </c>
-      <c r="U30">
+      <c r="W30">
         <v>2.544873371035161</v>
-      </c>
-      <c r="V30">
-        <v>2.749262536873156</v>
-      </c>
-      <c r="W30" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="31" spans="1:23">
@@ -3211,70 +3223,70 @@
         <v>52</v>
       </c>
       <c r="B31" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C31" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="E31">
-        <v>23.88999938964844</v>
+        <v>123.4000015258789</v>
       </c>
       <c r="F31">
-        <v>2466806.666666667</v>
+        <v>270677.7666666667</v>
       </c>
       <c r="G31">
-        <v>19.34219985961914</v>
+        <v>116.3551998901367</v>
       </c>
       <c r="H31">
-        <v>16.4557999865214</v>
+        <v>92.08486673990886</v>
       </c>
       <c r="I31">
-        <v>16.22995001316071</v>
+        <v>87.42130014419556</v>
       </c>
       <c r="J31">
-        <v>15.48470002174377</v>
+        <v>82.23655019760132</v>
       </c>
       <c r="K31">
-        <v>12.61999988555908</v>
+        <v>8.189999580383301</v>
       </c>
       <c r="L31">
-        <v>24.46999931335449</v>
+        <v>130.3200073242188</v>
       </c>
       <c r="M31">
-        <v>152.4592499398751</v>
+        <v>146.1780301231503</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>-1.76</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>-1.17</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>-1.76</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>-129729000</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>-32052000</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>-45297000</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>-139975000</v>
       </c>
       <c r="V31">
         <v>0</v>
       </c>
-      <c r="W31" t="s">
-        <v>232</v>
+      <c r="W31">
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:23">
@@ -3282,70 +3294,70 @@
         <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C32" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="D32" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E32">
-        <v>53.59000015258789</v>
+        <v>519.4000244140625</v>
       </c>
       <c r="F32">
-        <v>447556.6666666667</v>
+        <v>4290365.333333333</v>
       </c>
       <c r="G32">
-        <v>46.12339981079101</v>
+        <v>445.6849993896485</v>
       </c>
       <c r="H32">
-        <v>39.58753323872884</v>
+        <v>386.4179331461589</v>
       </c>
       <c r="I32">
-        <v>35.61084994316101</v>
+        <v>368.7066493225097</v>
       </c>
       <c r="J32">
-        <v>32.79539998054504</v>
+        <v>351.2427993774414</v>
       </c>
       <c r="K32">
-        <v>2.234822273254395</v>
+        <v>0.1503329128026962</v>
       </c>
       <c r="L32">
-        <v>53.59000015258789</v>
+        <v>688.3699951171875</v>
       </c>
       <c r="M32">
-        <v>152.4422426524919</v>
+        <v>145.2708806659446</v>
       </c>
       <c r="N32">
-        <v>0.98</v>
+        <v>2.42</v>
       </c>
       <c r="O32">
-        <v>1.16</v>
+        <v>2.53</v>
       </c>
       <c r="P32">
-        <v>1.01</v>
+        <v>2.71</v>
       </c>
       <c r="Q32">
-        <v>46726000</v>
+        <v>2.82</v>
       </c>
       <c r="R32">
-        <v>54970000</v>
+        <v>4756000000</v>
       </c>
       <c r="S32">
-        <v>48235000</v>
+        <v>1247000000</v>
       </c>
       <c r="T32">
-        <v>23.15690355833085</v>
+        <v>1295000000</v>
       </c>
       <c r="U32">
-        <v>26.03757140556466</v>
+        <v>4737000000</v>
       </c>
       <c r="V32">
-        <v>23.8034139528916</v>
-      </c>
-      <c r="W32" t="s">
-        <v>232</v>
+        <v>27.01351811882313</v>
+      </c>
+      <c r="W32">
+        <v>26.78839957035446</v>
       </c>
     </row>
     <row r="33" spans="1:23">
@@ -3353,70 +3365,70 @@
         <v>54</v>
       </c>
       <c r="B33" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C33" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="E33">
-        <v>277.010009765625</v>
+        <v>76.44999694824219</v>
       </c>
       <c r="F33">
-        <v>252616.6666666667</v>
+        <v>520026.4666666667</v>
       </c>
       <c r="G33">
-        <v>232.4763998413086</v>
+        <v>65.71579978942871</v>
       </c>
       <c r="H33">
-        <v>204.0643999226888</v>
+        <v>53.87093317667643</v>
       </c>
       <c r="I33">
-        <v>192.9860000610352</v>
+        <v>53.15014989852905</v>
       </c>
       <c r="J33">
-        <v>184.8533502960205</v>
+        <v>51.38469995498657</v>
       </c>
       <c r="K33">
-        <v>22.75</v>
+        <v>14.8100004196167</v>
       </c>
       <c r="L33">
-        <v>280.2300109863281</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="M33">
-        <v>152.3298878902208</v>
+        <v>144.9035588150722</v>
       </c>
       <c r="N33">
-        <v>4.76</v>
+        <v>-0.96</v>
       </c>
       <c r="O33">
-        <v>4.52</v>
+        <v>-0.58</v>
       </c>
       <c r="P33">
-        <v>4.28</v>
+        <v>-0.66</v>
       </c>
       <c r="Q33">
-        <v>153746000</v>
+        <v>-0.72</v>
       </c>
       <c r="R33">
-        <v>143834000</v>
+        <v>-27576000</v>
       </c>
       <c r="S33">
-        <v>135870000</v>
+        <v>-31460000</v>
       </c>
       <c r="T33">
-        <v>11.81754314764511</v>
+        <v>-34626000</v>
       </c>
       <c r="U33">
-        <v>11.3743858453212</v>
+        <v>-99195000</v>
       </c>
       <c r="V33">
-        <v>10.73869106049613</v>
-      </c>
-      <c r="W33" t="s">
-        <v>232</v>
+        <v>-38.69283980412241</v>
+      </c>
+      <c r="W33">
+        <v>-44.16864391312284</v>
       </c>
     </row>
     <row r="34" spans="1:23">
@@ -3424,70 +3436,70 @@
         <v>55</v>
       </c>
       <c r="B34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="D34" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="E34">
-        <v>80.34999847412109</v>
+        <v>177.5599975585938</v>
       </c>
       <c r="F34">
-        <v>2774480</v>
+        <v>629913.4666666667</v>
       </c>
       <c r="G34">
-        <v>71.7518000793457</v>
+        <v>151.3562002563476</v>
       </c>
       <c r="H34">
-        <v>59.91053321838379</v>
+        <v>134.967733968099</v>
       </c>
       <c r="I34">
-        <v>55.07629993438721</v>
+        <v>129.0079504776001</v>
       </c>
       <c r="J34">
-        <v>51.43965000152588</v>
+        <v>123.1665003967285</v>
       </c>
       <c r="K34">
-        <v>0.1027423962950706</v>
+        <v>1.039746522903442</v>
       </c>
       <c r="L34">
-        <v>80.34999847412109</v>
+        <v>181.4700012207031</v>
       </c>
       <c r="M34">
-        <v>152.2883628158504</v>
+        <v>142.8766548099713</v>
       </c>
       <c r="N34">
-        <v>2.69</v>
+        <v>6.48</v>
       </c>
       <c r="O34">
-        <v>3.85</v>
+        <v>6.31</v>
       </c>
       <c r="P34">
-        <v>2.35</v>
+        <v>5.716567</v>
       </c>
       <c r="Q34">
-        <v>627928000</v>
+        <v>6.07</v>
       </c>
       <c r="R34">
-        <v>882231000</v>
+        <v>352600000</v>
       </c>
       <c r="S34">
-        <v>532259000</v>
+        <v>286400000</v>
       </c>
       <c r="T34">
-        <v>15.92183813849328</v>
+        <v>288700000</v>
       </c>
       <c r="U34">
-        <v>17.05988229829651</v>
+        <v>1377400000</v>
       </c>
       <c r="V34">
-        <v>14.88569462090853</v>
-      </c>
-      <c r="W34" t="s">
-        <v>232</v>
+        <v>5.28952895289529</v>
+      </c>
+      <c r="W34">
+        <v>4.276541735105271</v>
       </c>
     </row>
     <row r="35" spans="1:23">
@@ -3495,70 +3507,70 @@
         <v>56</v>
       </c>
       <c r="B35" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C35" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D35" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="E35">
-        <v>32</v>
+        <v>206.4250030517578</v>
       </c>
       <c r="F35">
-        <v>300743.3333333333</v>
+        <v>360379.3</v>
       </c>
       <c r="G35">
-        <v>29.36619995117188</v>
+        <v>187.2066995239258</v>
       </c>
       <c r="H35">
-        <v>24.25759993871053</v>
+        <v>156.4088992818197</v>
       </c>
       <c r="I35">
-        <v>22.28874998569488</v>
+        <v>148.1944242858887</v>
       </c>
       <c r="J35">
-        <v>20.83010000705719</v>
+        <v>142.2101493835449</v>
       </c>
       <c r="K35">
-        <v>14.10000038146973</v>
+        <v>0.8828129768371582</v>
       </c>
       <c r="L35">
-        <v>32.86000061035156</v>
+        <v>207.8500061035156</v>
       </c>
       <c r="M35">
-        <v>151.8357553472608</v>
+        <v>142.6311346826648</v>
       </c>
       <c r="N35">
-        <v>0.14</v>
+        <v>0.49</v>
       </c>
       <c r="O35">
-        <v>0.18</v>
+        <v>0.47</v>
       </c>
       <c r="P35">
-        <v>0.11</v>
+        <v>0.6</v>
       </c>
       <c r="Q35">
-        <v>36215000</v>
+        <v>0.62</v>
       </c>
       <c r="R35">
-        <v>48300000</v>
+        <v>29674000</v>
       </c>
       <c r="S35">
-        <v>28265000</v>
+        <v>37868000</v>
       </c>
       <c r="T35">
-        <v>14.76590244678119</v>
+        <v>38791000</v>
       </c>
       <c r="U35">
-        <v>16.53543307086614</v>
+        <v>128959000</v>
       </c>
       <c r="V35">
-        <v>11.87644962855894</v>
-      </c>
-      <c r="W35" t="s">
-        <v>232</v>
+        <v>14.97922776765387</v>
+      </c>
+      <c r="W35">
+        <v>19.11530870304841</v>
       </c>
     </row>
     <row r="36" spans="1:23">
@@ -3566,70 +3578,70 @@
         <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C36" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D36" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E36">
-        <v>51.52999877929688</v>
+        <v>84.33999633789062</v>
       </c>
       <c r="F36">
-        <v>1359946.666666667</v>
+        <v>523129.6333333334</v>
       </c>
       <c r="G36">
-        <v>40.53039993286133</v>
+        <v>74.26579986572266</v>
       </c>
       <c r="H36">
-        <v>39.72273338317871</v>
+        <v>63.52093317667643</v>
       </c>
       <c r="I36">
-        <v>36.15615003585815</v>
+        <v>61.87104991912842</v>
       </c>
       <c r="J36">
-        <v>34.08510004997253</v>
+        <v>58.97664993286133</v>
       </c>
       <c r="K36">
-        <v>17.70000076293945</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="L36">
-        <v>51.52999877929688</v>
+        <v>85.40000152587891</v>
       </c>
       <c r="M36">
-        <v>151.1944962367647</v>
+        <v>141.4944955319837</v>
       </c>
       <c r="N36">
-        <v>0.26</v>
+        <v>2.12</v>
       </c>
       <c r="O36">
-        <v>0.33</v>
+        <v>1.95</v>
       </c>
       <c r="P36">
-        <v>0.32</v>
+        <v>0.88</v>
       </c>
       <c r="Q36">
-        <v>50614000</v>
+        <v>0.25</v>
       </c>
       <c r="R36">
-        <v>64519000</v>
+        <v>154800000</v>
       </c>
       <c r="S36">
-        <v>61977000</v>
+        <v>73300000</v>
       </c>
       <c r="T36">
-        <v>21.29627292082166</v>
+        <v>24800000</v>
       </c>
       <c r="U36">
-        <v>25.93322052019985</v>
+        <v>458400000</v>
       </c>
       <c r="V36">
-        <v>23.00172576963759</v>
-      </c>
-      <c r="W36" t="s">
-        <v>232</v>
+        <v>6.409407088439881</v>
+      </c>
+      <c r="W36">
+        <v>3.721945770285366</v>
       </c>
     </row>
     <row r="37" spans="1:23">
@@ -3637,70 +3649,70 @@
         <v>58</v>
       </c>
       <c r="B37" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D37" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="E37">
-        <v>153.8899993896484</v>
+        <v>242.5200042724609</v>
       </c>
       <c r="F37">
-        <v>582933.3333333334</v>
+        <v>6979044.5</v>
       </c>
       <c r="G37">
-        <v>145.5597998046875</v>
+        <v>227.1281994628906</v>
       </c>
       <c r="H37">
-        <v>117.8234331258138</v>
+        <v>190.2257998657226</v>
       </c>
       <c r="I37">
-        <v>108.963074836731</v>
+        <v>183.692449798584</v>
       </c>
       <c r="J37">
-        <v>104.0745748901367</v>
+        <v>176.321566619873</v>
       </c>
       <c r="K37">
-        <v>63</v>
+        <v>13.18666744232178</v>
       </c>
       <c r="L37">
-        <v>202.6900024414062</v>
+        <v>257.8800048828125</v>
       </c>
       <c r="M37">
-        <v>150.8990004468832</v>
+        <v>141.1498074200022</v>
       </c>
       <c r="N37">
-        <v>-0.46</v>
+        <v>0.01</v>
       </c>
       <c r="O37">
-        <v>-0.35</v>
+        <v>0.06</v>
       </c>
       <c r="P37">
-        <v>-0.06</v>
+        <v>0.25</v>
       </c>
       <c r="Q37">
-        <v>-18445000</v>
+        <v>0.31</v>
       </c>
       <c r="R37">
-        <v>-13930000</v>
+        <v>20000000</v>
       </c>
       <c r="S37">
-        <v>-2582000</v>
+        <v>84200000</v>
       </c>
       <c r="T37">
-        <v>-19.20054130016135</v>
+        <v>107800000</v>
       </c>
       <c r="U37">
-        <v>-13.41693635382956</v>
+        <v>34300000</v>
       </c>
       <c r="V37">
-        <v>-2.232386024675561</v>
-      </c>
-      <c r="W37" t="s">
-        <v>233</v>
+        <v>1.279263144428809</v>
+      </c>
+      <c r="W37">
+        <v>5.087305902966587</v>
       </c>
     </row>
     <row r="38" spans="1:23">
@@ -3708,70 +3720,70 @@
         <v>59</v>
       </c>
       <c r="B38" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C38" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D38" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="E38">
-        <v>21.79999923706055</v>
+        <v>33.38999938964844</v>
       </c>
       <c r="F38">
-        <v>854906.6666666666</v>
+        <v>1422687.7</v>
       </c>
       <c r="G38">
-        <v>19.93279991149902</v>
+        <v>29.75629978179932</v>
       </c>
       <c r="H38">
-        <v>17.5938666343689</v>
+        <v>25.76556660970052</v>
       </c>
       <c r="I38">
-        <v>15.91784997940064</v>
+        <v>23.48582496166229</v>
       </c>
       <c r="J38">
-        <v>15.14284999847412</v>
+        <v>22.01352501392364</v>
       </c>
       <c r="K38">
-        <v>9.220000267028809</v>
+        <v>4.052896976470947</v>
       </c>
       <c r="L38">
-        <v>22.13999938964844</v>
+        <v>33.38999938964844</v>
       </c>
       <c r="M38">
-        <v>149.4288426412054</v>
+        <v>140.8047689722629</v>
       </c>
       <c r="N38">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="O38">
-        <v>0.07000000000000001</v>
+        <v>-0.23</v>
       </c>
       <c r="P38">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="Q38">
-        <v>24732000</v>
+        <v>0.22</v>
       </c>
       <c r="R38">
-        <v>13726000</v>
+        <v>-16058000</v>
       </c>
       <c r="S38">
-        <v>27460000</v>
+        <v>26801000</v>
       </c>
       <c r="T38">
-        <v>4.982463067683896</v>
+        <v>29397000</v>
       </c>
       <c r="U38">
-        <v>2.904020903195777</v>
+        <v>-193210000</v>
       </c>
       <c r="V38">
-        <v>5.375344278468673</v>
-      </c>
-      <c r="W38" t="s">
-        <v>232</v>
+        <v>-6.97067696915764</v>
+      </c>
+      <c r="W38">
+        <v>9.771009621168758</v>
       </c>
     </row>
     <row r="39" spans="1:23">
@@ -3779,70 +3791,70 @@
         <v>60</v>
       </c>
       <c r="B39" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C39" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D39" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="E39">
-        <v>320.2099914550781</v>
+        <v>99.47000122070312</v>
       </c>
       <c r="F39">
-        <v>304383.3333333333</v>
+        <v>365182.3333333333</v>
       </c>
       <c r="G39">
-        <v>258.4278002929688</v>
+        <v>82.30600021362305</v>
       </c>
       <c r="H39">
-        <v>241.3940004475911</v>
+        <v>73.24180030822754</v>
       </c>
       <c r="I39">
-        <v>235.0403003692627</v>
+        <v>71.82290023803711</v>
       </c>
       <c r="J39">
-        <v>230.2825006866455</v>
+        <v>68.64230026245117</v>
       </c>
       <c r="K39">
-        <v>1.363492727279663</v>
+        <v>11.37919998168945</v>
       </c>
       <c r="L39">
-        <v>412.9100646972656</v>
+        <v>101.0999984741211</v>
       </c>
       <c r="M39">
-        <v>148.9902393566263</v>
+        <v>140.4886364878397</v>
       </c>
       <c r="N39">
-        <v>11.92</v>
+        <v>5.49</v>
       </c>
       <c r="O39">
-        <v>9</v>
+        <v>5.52</v>
       </c>
       <c r="P39">
-        <v>8.300000000000001</v>
+        <v>2.95</v>
       </c>
       <c r="Q39">
-        <v>329600000</v>
+        <v>2.43</v>
       </c>
       <c r="R39">
-        <v>247700000</v>
+        <v>219587000</v>
       </c>
       <c r="S39">
-        <v>228700000</v>
+        <v>117360000</v>
       </c>
       <c r="T39">
-        <v>4.517729621557904</v>
+        <v>96733000</v>
       </c>
       <c r="U39">
-        <v>3.543532373894882</v>
+        <v>857658000</v>
       </c>
       <c r="V39">
-        <v>3.279417247411741</v>
-      </c>
-      <c r="W39" t="s">
-        <v>232</v>
+        <v>10.19132136261764</v>
+      </c>
+      <c r="W39">
+        <v>7.207490483975371</v>
       </c>
     </row>
     <row r="40" spans="1:23">
@@ -3850,70 +3862,70 @@
         <v>61</v>
       </c>
       <c r="B40" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C40" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D40" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E40">
-        <v>81.98000335693359</v>
+        <v>26.79000091552734</v>
       </c>
       <c r="F40">
-        <v>1766906.666666667</v>
+        <v>275038.4333333333</v>
       </c>
       <c r="G40">
-        <v>71.51440017700196</v>
+        <v>24.1157999420166</v>
       </c>
       <c r="H40">
-        <v>61.78553347269694</v>
+        <v>19.78179998397827</v>
       </c>
       <c r="I40">
-        <v>57.3703501701355</v>
+        <v>19.45619996070862</v>
       </c>
       <c r="J40">
-        <v>54.02715007781983</v>
+        <v>18.97744994163513</v>
       </c>
       <c r="K40">
-        <v>0.5319142937660217</v>
+        <v>7.619999885559082</v>
       </c>
       <c r="L40">
-        <v>82.16000366210938</v>
+        <v>32.29000091552734</v>
       </c>
       <c r="M40">
-        <v>148.8116249814337</v>
+        <v>140.3016246725128</v>
       </c>
       <c r="N40">
-        <v>5.63</v>
+        <v>-0.86</v>
       </c>
       <c r="O40">
-        <v>1.7</v>
+        <v>-0.13</v>
       </c>
       <c r="P40">
-        <v>2.85</v>
+        <v>-0.53</v>
       </c>
       <c r="Q40">
-        <v>640536000</v>
+        <v>-0.86</v>
       </c>
       <c r="R40">
-        <v>191530000</v>
+        <v>-63643000</v>
       </c>
       <c r="S40">
-        <v>320216000</v>
+        <v>-81972000</v>
       </c>
       <c r="T40">
-        <v>17.25519606781436</v>
+        <v>-39741000</v>
       </c>
       <c r="U40">
-        <v>10.75909085036308</v>
+        <v>-131194000</v>
       </c>
       <c r="V40">
-        <v>12.7729829408224</v>
-      </c>
-      <c r="W40" t="s">
-        <v>232</v>
+        <v>-139.4792785290057</v>
+      </c>
+      <c r="W40">
+        <v>-768.535533470842</v>
       </c>
     </row>
     <row r="41" spans="1:23">
@@ -3921,70 +3933,70 @@
         <v>62</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C41" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D41" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E41">
-        <v>98.38999938964844</v>
+        <v>53.53499984741211</v>
       </c>
       <c r="F41">
-        <v>431203.3333333333</v>
+        <v>1160073.8</v>
       </c>
       <c r="G41">
-        <v>87.18839996337891</v>
+        <v>44.86150001525879</v>
       </c>
       <c r="H41">
-        <v>73.23539978027344</v>
+        <v>42.53483334859212</v>
       </c>
       <c r="I41">
-        <v>66.90064987182618</v>
+        <v>41.77437503814697</v>
       </c>
       <c r="J41">
-        <v>62.22584981918335</v>
+        <v>40.36830001831055</v>
       </c>
       <c r="K41">
-        <v>1.669681549072266</v>
+        <v>2.721946477890015</v>
       </c>
       <c r="L41">
-        <v>98.38999938964844</v>
+        <v>53.59000015258789</v>
       </c>
       <c r="M41">
-        <v>148.7165859347409</v>
+        <v>139.8974090851178</v>
       </c>
       <c r="N41">
-        <v>0.74</v>
+        <v>3.74</v>
       </c>
       <c r="O41">
-        <v>1.08</v>
+        <v>3.41</v>
       </c>
       <c r="P41">
-        <v>3.58</v>
+        <v>0.25</v>
       </c>
       <c r="Q41">
-        <v>22222000</v>
+        <v>-2</v>
       </c>
       <c r="R41">
-        <v>32408000</v>
+        <v>312600000</v>
       </c>
       <c r="S41">
-        <v>105259000</v>
+        <v>32572000</v>
       </c>
       <c r="T41">
-        <v>19.36321494545328</v>
+        <v>-155994000</v>
       </c>
       <c r="U41">
-        <v>27.68613045149716</v>
+        <v>1220944000</v>
       </c>
       <c r="V41">
-        <v>52.01237319207602</v>
-      </c>
-      <c r="W41" t="s">
-        <v>233</v>
+        <v>34.45664646224154</v>
+      </c>
+      <c r="W41">
+        <v>10.50950378957761</v>
       </c>
     </row>
     <row r="42" spans="1:23">
@@ -3995,67 +4007,67 @@
         <v>110</v>
       </c>
       <c r="C42" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="D42" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E42">
-        <v>11.60000038146973</v>
+        <v>93.76000213623047</v>
       </c>
       <c r="F42">
-        <v>6555683.333333333</v>
+        <v>429332</v>
       </c>
       <c r="G42">
-        <v>9.597999954223633</v>
+        <v>89.40300033569336</v>
       </c>
       <c r="H42">
-        <v>8.540399983723958</v>
+        <v>74.8109331258138</v>
       </c>
       <c r="I42">
-        <v>7.591799992322922</v>
+        <v>68.26989990234375</v>
       </c>
       <c r="J42">
-        <v>6.919999989271164</v>
+        <v>63.2559998512268</v>
       </c>
       <c r="K42">
-        <v>2.809999942779541</v>
+        <v>1.669681549072266</v>
       </c>
       <c r="L42">
-        <v>13.52000045776367</v>
+        <v>98.38999938964844</v>
       </c>
       <c r="M42">
-        <v>148.5227436888644</v>
+        <v>139.8646952363676</v>
       </c>
       <c r="N42">
-        <v>-0.42</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O42">
-        <v>-0.49</v>
+        <v>0.74</v>
       </c>
       <c r="P42">
-        <v>-0.05</v>
+        <v>1.08</v>
       </c>
       <c r="Q42">
-        <v>-291590000</v>
+        <v>3.58</v>
       </c>
       <c r="R42">
-        <v>-352014000</v>
+        <v>22222000</v>
       </c>
       <c r="S42">
-        <v>-33617000</v>
+        <v>32408000</v>
       </c>
       <c r="T42">
-        <v>-2326.577834516876</v>
+        <v>105259000</v>
       </c>
       <c r="U42">
-        <v>-2064.356087262491</v>
+        <v>93693000</v>
       </c>
       <c r="V42">
-        <v>-122.7973407364115</v>
-      </c>
-      <c r="W42" t="s">
-        <v>232</v>
+        <v>19.36321494545328</v>
+      </c>
+      <c r="W42">
+        <v>27.68613045149716</v>
       </c>
     </row>
     <row r="43" spans="1:23">
@@ -4063,70 +4075,70 @@
         <v>64</v>
       </c>
       <c r="B43" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C43" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D43" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E43">
-        <v>148.7100067138672</v>
+        <v>81.95999908447266</v>
       </c>
       <c r="F43">
-        <v>1351393.333333333</v>
+        <v>2652570</v>
       </c>
       <c r="G43">
-        <v>135.5126007080078</v>
+        <v>73.00260009765626</v>
       </c>
       <c r="H43">
-        <v>109.4322002156575</v>
+        <v>60.92306653340658</v>
       </c>
       <c r="I43">
-        <v>105.3104000473023</v>
+        <v>55.95209991455078</v>
       </c>
       <c r="J43">
-        <v>100.714700012207</v>
+        <v>52.09969999313355</v>
       </c>
       <c r="K43">
-        <v>0.1500000059604645</v>
+        <v>0.1027423962950706</v>
       </c>
       <c r="L43">
-        <v>150.7100067138672</v>
+        <v>82.51000213623047</v>
       </c>
       <c r="M43">
-        <v>146.7136265496125</v>
+        <v>138.5925791322447</v>
       </c>
       <c r="N43">
-        <v>0.12</v>
+        <v>2.73</v>
       </c>
       <c r="O43">
-        <v>-2.46</v>
+        <v>2.69</v>
       </c>
       <c r="P43">
-        <v>0.4</v>
+        <v>3.85</v>
       </c>
       <c r="Q43">
-        <v>-154116727</v>
+        <v>2.35</v>
       </c>
       <c r="R43">
-        <v>-21223000</v>
+        <v>627928000</v>
       </c>
       <c r="S43">
-        <v>41227000</v>
+        <v>882231000</v>
       </c>
       <c r="T43">
-        <v>-26.57668098589627</v>
+        <v>532259000</v>
       </c>
       <c r="U43">
-        <v>-11.92544559573846</v>
+        <v>2617317000</v>
       </c>
       <c r="V43">
-        <v>15.86025952242641</v>
-      </c>
-      <c r="W43" t="s">
-        <v>232</v>
+        <v>15.92183813849328</v>
+      </c>
+      <c r="W43">
+        <v>17.05988229829651</v>
       </c>
     </row>
     <row r="44" spans="1:23">
@@ -4134,70 +4146,70 @@
         <v>65</v>
       </c>
       <c r="B44" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C44" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D44" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="E44">
-        <v>576.6199951171875</v>
+        <v>50.20999908447266</v>
       </c>
       <c r="F44">
-        <v>545900</v>
+        <v>1409852.933333333</v>
       </c>
       <c r="G44">
-        <v>486.7007995605469</v>
+        <v>41.93479988098144</v>
       </c>
       <c r="H44">
-        <v>459.1158662923177</v>
+        <v>40.36080004374186</v>
       </c>
       <c r="I44">
-        <v>433.7208996582031</v>
+        <v>36.88510002136231</v>
       </c>
       <c r="J44">
-        <v>423.6927993774414</v>
+        <v>34.51845004081726</v>
       </c>
       <c r="K44">
-        <v>5.184493541717529</v>
+        <v>17.70000076293945</v>
       </c>
       <c r="L44">
-        <v>576.6199951171875</v>
+        <v>52.72000122070312</v>
       </c>
       <c r="M44">
-        <v>146.0291730023319</v>
+        <v>138.4859910937689</v>
       </c>
       <c r="N44">
-        <v>2.57</v>
+        <v>0.05</v>
       </c>
       <c r="O44">
-        <v>2.45</v>
+        <v>0.26</v>
       </c>
       <c r="P44">
-        <v>2.26</v>
+        <v>0.33</v>
       </c>
       <c r="Q44">
-        <v>124337000</v>
+        <v>0.32</v>
       </c>
       <c r="R44">
-        <v>119090000</v>
+        <v>50614000</v>
       </c>
       <c r="S44">
-        <v>109802000</v>
+        <v>64519000</v>
       </c>
       <c r="T44">
-        <v>25.09739250491504</v>
+        <v>61977000</v>
       </c>
       <c r="U44">
-        <v>25.88845508378042</v>
+        <v>150996000</v>
       </c>
       <c r="V44">
-        <v>24.34283307283873</v>
-      </c>
-      <c r="W44" t="s">
-        <v>232</v>
+        <v>21.29627292082166</v>
+      </c>
+      <c r="W44">
+        <v>25.93322052019985</v>
       </c>
     </row>
     <row r="45" spans="1:23">
@@ -4205,70 +4217,70 @@
         <v>66</v>
       </c>
       <c r="B45" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C45" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D45" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="E45">
-        <v>50.79000091552734</v>
+        <v>13.89000034332275</v>
       </c>
       <c r="F45">
-        <v>1216286.666666667</v>
+        <v>1247623.1</v>
       </c>
       <c r="G45">
-        <v>45.53159988403321</v>
+        <v>10.21729988098144</v>
       </c>
       <c r="H45">
-        <v>38.55859995524089</v>
+        <v>10.11725797017415</v>
       </c>
       <c r="I45">
-        <v>35.53905002593994</v>
+        <v>10.04098649501801</v>
       </c>
       <c r="J45">
-        <v>33.21135003089905</v>
+        <v>9.983236494064331</v>
       </c>
       <c r="K45">
-        <v>7.050000190734863</v>
+        <v>8.989999771118164</v>
       </c>
       <c r="L45">
-        <v>50.79000091552734</v>
+        <v>13.89000034332275</v>
       </c>
       <c r="M45">
-        <v>145.8673501442741</v>
+        <v>138.3628761265203</v>
       </c>
       <c r="N45">
-        <v>2.72</v>
+        <v>-0.08</v>
       </c>
       <c r="O45">
-        <v>2.51</v>
+        <v>0.090181</v>
       </c>
       <c r="P45">
-        <v>1.74</v>
+        <v>0.02</v>
       </c>
       <c r="Q45">
-        <v>309779000</v>
+        <v>-0.08</v>
       </c>
       <c r="R45">
-        <v>275331000</v>
+        <v>366476</v>
       </c>
       <c r="S45">
-        <v>191051000</v>
+        <v>900174</v>
       </c>
       <c r="T45">
-        <v>15.2252187606284</v>
+        <v>-1652348</v>
       </c>
       <c r="U45">
-        <v>11.04803689701082</v>
+        <v>5796203</v>
       </c>
       <c r="V45">
-        <v>11.49623583737951</v>
-      </c>
-      <c r="W45" t="s">
-        <v>232</v>
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:23">
@@ -4276,70 +4288,70 @@
         <v>67</v>
       </c>
       <c r="B46" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C46" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="D46" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E46">
-        <v>46.63000106811523</v>
+        <v>52.13000106811523</v>
       </c>
       <c r="F46">
-        <v>2810660</v>
+        <v>2066076.9</v>
       </c>
       <c r="G46">
-        <v>38.33180000305176</v>
+        <v>48.7866000366211</v>
       </c>
       <c r="H46">
-        <v>32.8854333114624</v>
+        <v>41.02146662394205</v>
       </c>
       <c r="I46">
-        <v>32.50314995765686</v>
+        <v>38.07124996185303</v>
       </c>
       <c r="J46">
-        <v>29.90734997749329</v>
+        <v>35.64789996147156</v>
       </c>
       <c r="K46">
-        <v>13.1899995803833</v>
+        <v>1.498309969902039</v>
       </c>
       <c r="L46">
-        <v>46.91999816894531</v>
+        <v>66.26741027832031</v>
       </c>
       <c r="M46">
-        <v>145.7771804789558</v>
+        <v>138.2355758941389</v>
       </c>
       <c r="N46">
-        <v>-0.55</v>
+        <v>2.86</v>
       </c>
       <c r="O46">
-        <v>-0.51</v>
+        <v>2.47</v>
       </c>
       <c r="P46">
-        <v>-0.54</v>
+        <v>1.45</v>
       </c>
       <c r="Q46">
-        <v>-76858000</v>
+        <v>1.94</v>
       </c>
       <c r="R46">
-        <v>-23224000</v>
+        <v>216410000</v>
       </c>
       <c r="S46">
-        <v>-25646000</v>
+        <v>125500000</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>164442000</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>807909000</v>
       </c>
       <c r="V46">
-        <v>0</v>
-      </c>
-      <c r="W46" t="s">
-        <v>232</v>
+        <v>11.15498213945145</v>
+      </c>
+      <c r="W46">
+        <v>9.065862224899842</v>
       </c>
     </row>
     <row r="47" spans="1:23">
@@ -4347,70 +4359,70 @@
         <v>68</v>
       </c>
       <c r="B47" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C47" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="D47" t="s">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="E47">
-        <v>199.75</v>
+        <v>73.18720245361328</v>
       </c>
       <c r="F47">
-        <v>372246.6666666667</v>
+        <v>772927.8333333334</v>
       </c>
       <c r="G47">
-        <v>183.542399597168</v>
+        <v>64.22914375305176</v>
       </c>
       <c r="H47">
-        <v>153.5413992818197</v>
+        <v>60.05584782918294</v>
       </c>
       <c r="I47">
-        <v>146.3852492523193</v>
+        <v>54.93008588790894</v>
       </c>
       <c r="J47">
-        <v>140.9472992706299</v>
+        <v>51.05864992141723</v>
       </c>
       <c r="K47">
-        <v>0.8828129768371582</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="L47">
-        <v>199.8800048828125</v>
+        <v>76.41999816894531</v>
       </c>
       <c r="M47">
-        <v>145.5406891148138</v>
+        <v>137.7799672732077</v>
       </c>
       <c r="N47">
-        <v>0.47</v>
+        <v>0.08</v>
       </c>
       <c r="O47">
-        <v>0.6</v>
+        <v>0.39</v>
       </c>
       <c r="P47">
-        <v>0.62</v>
+        <v>0.99</v>
       </c>
       <c r="Q47">
-        <v>29674000</v>
+        <v>0.97</v>
       </c>
       <c r="R47">
-        <v>37868000</v>
+        <v>28000000</v>
       </c>
       <c r="S47">
-        <v>38791000</v>
+        <v>72000000</v>
       </c>
       <c r="T47">
-        <v>14.97922776765387</v>
+        <v>72000000</v>
       </c>
       <c r="U47">
-        <v>19.11530870304841</v>
+        <v>26000000</v>
       </c>
       <c r="V47">
-        <v>17.55145624917991</v>
-      </c>
-      <c r="W47" t="s">
-        <v>232</v>
+        <v>2.5</v>
+      </c>
+      <c r="W47">
+        <v>5.955334987593052</v>
       </c>
     </row>
     <row r="48" spans="1:23">
@@ -4418,70 +4430,70 @@
         <v>69</v>
       </c>
       <c r="B48" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C48" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="D48" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E48">
-        <v>178.1600036621094</v>
+        <v>112.2249984741211</v>
       </c>
       <c r="F48">
-        <v>649970</v>
+        <v>297615.7</v>
       </c>
       <c r="G48">
-        <v>146.8088000488281</v>
+        <v>100.531300201416</v>
       </c>
       <c r="H48">
-        <v>132.9584672037761</v>
+        <v>88.45723322550455</v>
       </c>
       <c r="I48">
-        <v>127.1879504394531</v>
+        <v>83.50932485580444</v>
       </c>
       <c r="J48">
-        <v>122.5495503234863</v>
+        <v>78.87849985122681</v>
       </c>
       <c r="K48">
-        <v>1.039746522903442</v>
+        <v>5.466728210449219</v>
       </c>
       <c r="L48">
-        <v>178.1600036621094</v>
+        <v>112.9800033569336</v>
       </c>
       <c r="M48">
-        <v>145.4928880053916</v>
+        <v>137.4730221182488</v>
       </c>
       <c r="N48">
-        <v>6.31</v>
+        <v>0.75</v>
       </c>
       <c r="O48">
-        <v>5.716567</v>
+        <v>0.84</v>
       </c>
       <c r="P48">
-        <v>6.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q48">
-        <v>352600000</v>
+        <v>1.59</v>
       </c>
       <c r="R48">
-        <v>286400000</v>
+        <v>34500</v>
       </c>
       <c r="S48">
-        <v>288700000</v>
+        <v>44410000</v>
       </c>
       <c r="T48">
-        <v>5.28952895289529</v>
+        <v>65900000</v>
       </c>
       <c r="U48">
-        <v>4.276541735105271</v>
+        <v>137952000</v>
       </c>
       <c r="V48">
-        <v>4.511853970337725</v>
-      </c>
-      <c r="W48" t="s">
-        <v>232</v>
+        <v>3.835890593729153</v>
+      </c>
+      <c r="W48">
+        <v>4.825983154156529</v>
       </c>
     </row>
     <row r="49" spans="1:23">
@@ -4489,70 +4501,70 @@
         <v>70</v>
       </c>
       <c r="B49" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C49" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D49" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E49">
-        <v>84.91999816894531</v>
+        <v>48.55009841918945</v>
       </c>
       <c r="F49">
-        <v>534493.3333333334</v>
+        <v>13527924.53333333</v>
       </c>
       <c r="G49">
-        <v>71.79439994812012</v>
+        <v>41.16820198059082</v>
       </c>
       <c r="H49">
-        <v>62.61053324381511</v>
+        <v>37.6024672571818</v>
       </c>
       <c r="I49">
-        <v>61.08144996643066</v>
+        <v>36.49135046005249</v>
       </c>
       <c r="J49">
-        <v>58.39124994277954</v>
+        <v>34.89934995651245</v>
       </c>
       <c r="K49">
-        <v>7.03000020980835</v>
+        <v>3.490809917449951</v>
       </c>
       <c r="L49">
-        <v>84.91999816894531</v>
+        <v>62.26396942138672</v>
       </c>
       <c r="M49">
-        <v>145.4521356941933</v>
+        <v>137.3786489652296</v>
       </c>
       <c r="N49">
-        <v>1.95</v>
+        <v>1.08</v>
       </c>
       <c r="O49">
-        <v>0.88</v>
+        <v>1.29</v>
       </c>
       <c r="P49">
-        <v>0.25</v>
+        <v>-0.57</v>
       </c>
       <c r="Q49">
-        <v>154800000</v>
+        <v>2.84</v>
       </c>
       <c r="R49">
-        <v>73300000</v>
+        <v>1318000000</v>
       </c>
       <c r="S49">
-        <v>24800000</v>
+        <v>-363000000</v>
       </c>
       <c r="T49">
-        <v>6.409407088439881</v>
+        <v>1827000000</v>
       </c>
       <c r="U49">
-        <v>3.721945770285366</v>
+        <v>1895000000</v>
       </c>
       <c r="V49">
-        <v>1.431622698146972</v>
-      </c>
-      <c r="W49" t="s">
-        <v>232</v>
+        <v>2.605670001186193</v>
+      </c>
+      <c r="W49">
+        <v>-2.84505055255114</v>
       </c>
     </row>
     <row r="50" spans="1:23">
@@ -4560,70 +4572,70 @@
         <v>71</v>
       </c>
       <c r="B50" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C50" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D50" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="E50">
-        <v>98.5</v>
+        <v>49.65000152587891</v>
       </c>
       <c r="F50">
-        <v>348636.6666666667</v>
+        <v>1048986.433333333</v>
       </c>
       <c r="G50">
-        <v>79.24680023193359</v>
+        <v>46.41659996032715</v>
       </c>
       <c r="H50">
-        <v>72.29986701965332</v>
+        <v>39.26373332977295</v>
       </c>
       <c r="I50">
-        <v>70.7708002281189</v>
+        <v>36.2324000453949</v>
       </c>
       <c r="J50">
-        <v>68.27780023574829</v>
+        <v>33.74625001907349</v>
       </c>
       <c r="K50">
-        <v>11.37919998168945</v>
+        <v>7.050000190734863</v>
       </c>
       <c r="L50">
-        <v>98.5</v>
+        <v>51.63999938964844</v>
       </c>
       <c r="M50">
-        <v>145.2793893797502</v>
+        <v>137.2437111400247</v>
       </c>
       <c r="N50">
-        <v>5.52</v>
+        <v>2.45</v>
       </c>
       <c r="O50">
-        <v>2.95</v>
+        <v>2.72</v>
       </c>
       <c r="P50">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="Q50">
-        <v>219587000</v>
+        <v>1.74</v>
       </c>
       <c r="R50">
-        <v>117360000</v>
+        <v>309779000</v>
       </c>
       <c r="S50">
-        <v>96733000</v>
+        <v>275331000</v>
       </c>
       <c r="T50">
-        <v>10.19132136261764</v>
+        <v>191051000</v>
       </c>
       <c r="U50">
-        <v>7.207490483975371</v>
+        <v>1052800000</v>
       </c>
       <c r="V50">
-        <v>6.263755974277502</v>
-      </c>
-      <c r="W50" t="s">
-        <v>232</v>
+        <v>15.2252187606284</v>
+      </c>
+      <c r="W50">
+        <v>11.04803689701082</v>
       </c>
     </row>
     <row r="51" spans="1:23">
@@ -4631,70 +4643,70 @@
         <v>72</v>
       </c>
       <c r="B51" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C51" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D51" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E51">
-        <v>363.1199951171875</v>
+        <v>310.2749938964844</v>
       </c>
       <c r="F51">
-        <v>545840</v>
+        <v>289418.3</v>
       </c>
       <c r="G51">
-        <v>306.5693994140625</v>
+        <v>268.142900390625</v>
       </c>
       <c r="H51">
-        <v>275.2768666585287</v>
+        <v>244.4564339192708</v>
       </c>
       <c r="I51">
-        <v>259.8110997009277</v>
+        <v>237.3323754119873</v>
       </c>
       <c r="J51">
-        <v>246.3666498565674</v>
+        <v>230.3881008148193</v>
       </c>
       <c r="K51">
-        <v>4.533332824707031</v>
+        <v>1.363492727279663</v>
       </c>
       <c r="L51">
-        <v>364.4500122070312</v>
+        <v>412.9100646972656</v>
       </c>
       <c r="M51">
-        <v>145.2735781460551</v>
+        <v>136.896599543079</v>
       </c>
       <c r="N51">
-        <v>3.67</v>
+        <v>11.6</v>
       </c>
       <c r="O51">
-        <v>2.65</v>
+        <v>11.92</v>
       </c>
       <c r="P51">
-        <v>2.85</v>
+        <v>9</v>
       </c>
       <c r="Q51">
-        <v>97891000</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R51">
-        <v>70862000</v>
+        <v>329600000</v>
       </c>
       <c r="S51">
-        <v>76097000</v>
+        <v>247700000</v>
       </c>
       <c r="T51">
-        <v>13.41779508498947</v>
+        <v>228700000</v>
       </c>
       <c r="U51">
-        <v>10.80664789866499</v>
+        <v>1251000000</v>
       </c>
       <c r="V51">
-        <v>11.52050988971061</v>
-      </c>
-      <c r="W51" t="s">
-        <v>232</v>
+        <v>4.517729621557904</v>
+      </c>
+      <c r="W51">
+        <v>3.543532373894882</v>
       </c>
     </row>
     <row r="52" spans="1:23">
@@ -4702,70 +4714,70 @@
         <v>73</v>
       </c>
       <c r="B52" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C52" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="D52" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E52">
-        <v>33.22999954223633</v>
+        <v>47.06499862670898</v>
       </c>
       <c r="F52">
-        <v>1223483.333333333</v>
+        <v>444518.1666666667</v>
       </c>
       <c r="G52">
-        <v>30.89240005493164</v>
+        <v>46.80249984741211</v>
       </c>
       <c r="H52">
-        <v>25.39820004781087</v>
+        <v>40.29763324737549</v>
       </c>
       <c r="I52">
-        <v>23.2330500459671</v>
+        <v>36.38277493476868</v>
       </c>
       <c r="J52">
-        <v>21.70435004711151</v>
+        <v>33.43029998779297</v>
       </c>
       <c r="K52">
-        <v>6.139999866485596</v>
+        <v>2.234822273254395</v>
       </c>
       <c r="L52">
-        <v>33.22999954223633</v>
+        <v>53.88000106811523</v>
       </c>
       <c r="M52">
-        <v>145.1313097846991</v>
+        <v>136.5712369630736</v>
       </c>
       <c r="N52">
-        <v>1.45</v>
+        <v>0.7</v>
       </c>
       <c r="O52">
-        <v>1.98</v>
+        <v>0.98</v>
       </c>
       <c r="P52">
-        <v>0.73</v>
+        <v>1.16</v>
       </c>
       <c r="Q52">
-        <v>149226000</v>
+        <v>1.01</v>
       </c>
       <c r="R52">
-        <v>202973000</v>
+        <v>46726000</v>
       </c>
       <c r="S52">
-        <v>74742000</v>
+        <v>54970000</v>
       </c>
       <c r="T52">
-        <v>13.92298534422595</v>
+        <v>48235000</v>
       </c>
       <c r="U52">
-        <v>13.32889853191875</v>
+        <v>155743000</v>
       </c>
       <c r="V52">
-        <v>9.586474121445089</v>
-      </c>
-      <c r="W52" t="s">
-        <v>232</v>
+        <v>23.15690355833085</v>
+      </c>
+      <c r="W52">
+        <v>26.03757140556466</v>
       </c>
     </row>
     <row r="53" spans="1:23">
@@ -4773,70 +4785,70 @@
         <v>74</v>
       </c>
       <c r="B53" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C53" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="D53" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E53">
-        <v>52.95999908447266</v>
+        <v>176.8399963378906</v>
       </c>
       <c r="F53">
-        <v>1988386.666666667</v>
+        <v>263923.6</v>
       </c>
       <c r="G53">
-        <v>47.78159996032715</v>
+        <v>155.3287994384766</v>
       </c>
       <c r="H53">
-        <v>40.257799949646</v>
+        <v>140.1091335042318</v>
       </c>
       <c r="I53">
-        <v>37.37069994926453</v>
+        <v>133.4958001327515</v>
       </c>
       <c r="J53">
-        <v>35.10489996910096</v>
+        <v>127.0386003112793</v>
       </c>
       <c r="K53">
-        <v>1.498309969902039</v>
+        <v>2.075098752975464</v>
       </c>
       <c r="L53">
-        <v>66.26741027832031</v>
+        <v>179.6499938964844</v>
       </c>
       <c r="M53">
-        <v>145.1199216672256</v>
+        <v>136.0717000616034</v>
       </c>
       <c r="N53">
-        <v>2.47</v>
+        <v>4.93</v>
       </c>
       <c r="O53">
-        <v>1.45</v>
+        <v>4.61</v>
       </c>
       <c r="P53">
-        <v>1.94</v>
+        <v>4.21</v>
       </c>
       <c r="Q53">
-        <v>216410000</v>
+        <v>4.31</v>
       </c>
       <c r="R53">
-        <v>125500000</v>
+        <v>340100000</v>
       </c>
       <c r="S53">
-        <v>164442000</v>
+        <v>298000000</v>
       </c>
       <c r="T53">
-        <v>11.15498213945145</v>
+        <v>298300000</v>
       </c>
       <c r="U53">
-        <v>9.065862224899842</v>
+        <v>1380000000</v>
       </c>
       <c r="V53">
-        <v>9.315159438876666</v>
-      </c>
-      <c r="W53" t="s">
-        <v>232</v>
+        <v>4.914242778909648</v>
+      </c>
+      <c r="W53">
+        <v>4.24997860749023</v>
       </c>
     </row>
     <row r="54" spans="1:23">
@@ -4844,70 +4856,70 @@
         <v>75</v>
       </c>
       <c r="B54" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C54" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D54" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E54">
-        <v>26.18000030517578</v>
+        <v>530.64501953125</v>
       </c>
       <c r="F54">
-        <v>280770</v>
+        <v>338385.9333333333</v>
       </c>
       <c r="G54">
-        <v>23.37279987335205</v>
+        <v>404.7635009765625</v>
       </c>
       <c r="H54">
-        <v>19.33946664174398</v>
+        <v>384.9911336263021</v>
       </c>
       <c r="I54">
-        <v>19.27444994926453</v>
+        <v>381.8551501464844</v>
       </c>
       <c r="J54">
-        <v>18.89949993133545</v>
+        <v>377.8019747924805</v>
       </c>
       <c r="K54">
-        <v>7.619999885559082</v>
+        <v>19.76499938964844</v>
       </c>
       <c r="L54">
-        <v>32.29000091552734</v>
+        <v>530.64501953125</v>
       </c>
       <c r="M54">
-        <v>144.8172267752956</v>
+        <v>135.8865009065889</v>
       </c>
       <c r="N54">
-        <v>-0.13</v>
+        <v>-0.52</v>
       </c>
       <c r="O54">
-        <v>-0.53</v>
+        <v>-4.26</v>
       </c>
       <c r="P54">
-        <v>-0.86</v>
+        <v>-0.7</v>
       </c>
       <c r="Q54">
-        <v>-63643000</v>
+        <v>-0.52</v>
       </c>
       <c r="R54">
-        <v>-81972000</v>
+        <v>-235042000</v>
       </c>
       <c r="S54">
-        <v>-39741000</v>
+        <v>-38613000</v>
       </c>
       <c r="T54">
-        <v>-139.4792785290057</v>
+        <v>-28871000</v>
       </c>
       <c r="U54">
-        <v>-768.535533470842</v>
+        <v>-709594000</v>
       </c>
       <c r="V54">
-        <v>-294.3995851544559</v>
-      </c>
-      <c r="W54" t="s">
-        <v>232</v>
+        <v>-170.3437429791058</v>
+      </c>
+      <c r="W54">
+        <v>-22.17099219108865</v>
       </c>
     </row>
     <row r="55" spans="1:23">
@@ -4915,70 +4927,70 @@
         <v>76</v>
       </c>
       <c r="B55" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C55" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="D55" t="s">
-        <v>151</v>
+        <v>210</v>
       </c>
       <c r="E55">
-        <v>76.41999816894531</v>
+        <v>165.6549987792969</v>
       </c>
       <c r="F55">
-        <v>781463.3333333334</v>
+        <v>1587800.466666667</v>
       </c>
       <c r="G55">
-        <v>62.71119979858398</v>
+        <v>138.2420999145508</v>
       </c>
       <c r="H55">
-        <v>58.95719985961914</v>
+        <v>127.1056331380208</v>
       </c>
       <c r="I55">
-        <v>53.82484990119934</v>
+        <v>123.7244747924805</v>
       </c>
       <c r="J55">
-        <v>50.22944993972779</v>
+        <v>120.1378999328613</v>
       </c>
       <c r="K55">
-        <v>5.739999771118164</v>
+        <v>12.18373107910156</v>
       </c>
       <c r="L55">
-        <v>76.41999816894531</v>
+        <v>168.5816802978516</v>
       </c>
       <c r="M55">
-        <v>143.9628823579038</v>
+        <v>135.757906767528</v>
       </c>
       <c r="N55">
-        <v>0.39</v>
+        <v>0.82</v>
       </c>
       <c r="O55">
-        <v>0.99</v>
+        <v>0.54</v>
       </c>
       <c r="P55">
-        <v>0.97</v>
+        <v>1.15</v>
       </c>
       <c r="Q55">
-        <v>28000000</v>
+        <v>0.52</v>
       </c>
       <c r="R55">
-        <v>72000000</v>
+        <v>231000000</v>
       </c>
       <c r="S55">
-        <v>72000000</v>
+        <v>494000000</v>
       </c>
       <c r="T55">
-        <v>2.5</v>
+        <v>224000000</v>
       </c>
       <c r="U55">
-        <v>5.955334987593052</v>
+        <v>1314000000</v>
       </c>
       <c r="V55">
-        <v>6.070826306913997</v>
-      </c>
-      <c r="W55" t="s">
-        <v>232</v>
+        <v>7.194020554344441</v>
+      </c>
+      <c r="W55">
+        <v>13.30102315562736</v>
       </c>
     </row>
     <row r="56" spans="1:23">
@@ -4986,70 +4998,70 @@
         <v>77</v>
       </c>
       <c r="B56" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C56" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="D56" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E56">
-        <v>239.0099945068359</v>
+        <v>143.3399963378906</v>
       </c>
       <c r="F56">
-        <v>7440356.666666667</v>
+        <v>1266060.333333333</v>
       </c>
       <c r="G56">
-        <v>220.7449993896484</v>
+        <v>140.0660005187988</v>
       </c>
       <c r="H56">
-        <v>187.456933186849</v>
+        <v>110.536400197347</v>
       </c>
       <c r="I56">
-        <v>181.6665998077393</v>
+        <v>106.7394500350952</v>
       </c>
       <c r="J56">
-        <v>174.9100498962402</v>
+        <v>101.6711000061035</v>
       </c>
       <c r="K56">
-        <v>13.18666744232178</v>
+        <v>0.1500000059604645</v>
       </c>
       <c r="L56">
-        <v>257.8800048828125</v>
+        <v>153.1100006103516</v>
       </c>
       <c r="M56">
-        <v>142.7719647448292</v>
+        <v>134.7462261557664</v>
       </c>
       <c r="N56">
-        <v>0.06</v>
+        <v>0.4</v>
       </c>
       <c r="O56">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="P56">
-        <v>0.31</v>
+        <v>-2.46</v>
       </c>
       <c r="Q56">
-        <v>20000000</v>
+        <v>0.4</v>
       </c>
       <c r="R56">
-        <v>84200000</v>
+        <v>-154116727</v>
       </c>
       <c r="S56">
-        <v>107800000</v>
+        <v>-21223000</v>
       </c>
       <c r="T56">
-        <v>1.279263144428809</v>
+        <v>41227000</v>
       </c>
       <c r="U56">
-        <v>5.087305902966587</v>
+        <v>-187282000</v>
       </c>
       <c r="V56">
-        <v>6.264164100180138</v>
-      </c>
-      <c r="W56" t="s">
-        <v>233</v>
+        <v>-26.57668098589627</v>
+      </c>
+      <c r="W56">
+        <v>-11.92544559573846</v>
       </c>
     </row>
     <row r="57" spans="1:23">
@@ -5057,70 +5069,70 @@
         <v>78</v>
       </c>
       <c r="B57" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C57" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="D57" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E57">
-        <v>32.27999877929688</v>
+        <v>28.45000076293945</v>
       </c>
       <c r="F57">
-        <v>1499500</v>
+        <v>1004953.533333333</v>
       </c>
       <c r="G57">
-        <v>29.19569988250732</v>
+        <v>25.09500003814697</v>
       </c>
       <c r="H57">
-        <v>25.22329996744792</v>
+        <v>22.51619993845622</v>
       </c>
       <c r="I57">
-        <v>23.03734998226166</v>
+        <v>21.1289999628067</v>
       </c>
       <c r="J57">
-        <v>21.6935750246048</v>
+        <v>19.88759996414185</v>
       </c>
       <c r="K57">
-        <v>4.052896976470947</v>
+        <v>9.090000152587891</v>
       </c>
       <c r="L57">
-        <v>32.27999877929688</v>
+        <v>28.70999908447266</v>
       </c>
       <c r="M57">
-        <v>142.6908856879183</v>
+        <v>134.705240307926</v>
       </c>
       <c r="N57">
-        <v>-0.23</v>
+        <v>0.06</v>
       </c>
       <c r="O57">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
       <c r="P57">
-        <v>0.22</v>
+        <v>0.04</v>
       </c>
       <c r="Q57">
-        <v>-16058000</v>
+        <v>0.05</v>
       </c>
       <c r="R57">
-        <v>26801000</v>
+        <v>28000000</v>
       </c>
       <c r="S57">
-        <v>29397000</v>
+        <v>22000000</v>
       </c>
       <c r="T57">
-        <v>-6.97067696915764</v>
+        <v>26000000</v>
       </c>
       <c r="U57">
-        <v>9.771009621168758</v>
+        <v>73000000</v>
       </c>
       <c r="V57">
-        <v>10.04277154121031</v>
-      </c>
-      <c r="W57" t="s">
-        <v>233</v>
+        <v>1.613832853025936</v>
+      </c>
+      <c r="W57">
+        <v>1.291837933059307</v>
       </c>
     </row>
     <row r="58" spans="1:23">
@@ -5128,70 +5140,70 @@
         <v>79</v>
       </c>
       <c r="B58" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C58" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D58" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="E58">
-        <v>110.9899978637695</v>
+        <v>130.6300048828125</v>
       </c>
       <c r="F58">
-        <v>324503.3333333333</v>
+        <v>812807.8666666667</v>
       </c>
       <c r="G58">
-        <v>97.63220016479492</v>
+        <v>119.8672004699707</v>
       </c>
       <c r="H58">
-        <v>87.22346649169921</v>
+        <v>103.53966700236</v>
       </c>
       <c r="I58">
-        <v>82.18749982833862</v>
+        <v>99.48150020599365</v>
       </c>
       <c r="J58">
-        <v>77.85634986877442</v>
+        <v>94.59985008239747</v>
       </c>
       <c r="K58">
-        <v>5.466728210449219</v>
+        <v>4.719488620758057</v>
       </c>
       <c r="L58">
-        <v>110.9899978637695</v>
+        <v>137.5700073242188</v>
       </c>
       <c r="M58">
-        <v>142.5062305314136</v>
+        <v>134.5546856509591</v>
       </c>
       <c r="N58">
-        <v>0.84</v>
+        <v>3.49</v>
       </c>
       <c r="O58">
-        <v>1.08</v>
+        <v>4.84</v>
       </c>
       <c r="P58">
-        <v>1.59</v>
+        <v>1.32</v>
       </c>
       <c r="Q58">
-        <v>34500</v>
+        <v>4.17</v>
       </c>
       <c r="R58">
-        <v>44410000</v>
+        <v>470000000</v>
       </c>
       <c r="S58">
-        <v>65900000</v>
+        <v>124000000</v>
       </c>
       <c r="T58">
-        <v>3.835890593729153</v>
+        <v>383000000</v>
       </c>
       <c r="U58">
-        <v>4.825983154156529</v>
+        <v>1241000000</v>
       </c>
       <c r="V58">
-        <v>6.657238104859077</v>
-      </c>
-      <c r="W58" t="s">
-        <v>233</v>
+        <v>18.58442071965204</v>
+      </c>
+      <c r="W58">
+        <v>5.426695842450766</v>
       </c>
     </row>
     <row r="59" spans="1:23">
@@ -5199,70 +5211,70 @@
         <v>80</v>
       </c>
       <c r="B59" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C59" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="D59" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E59">
-        <v>577.4500122070312</v>
+        <v>50.81499862670898</v>
       </c>
       <c r="F59">
-        <v>1278030</v>
+        <v>1775399.633333333</v>
       </c>
       <c r="G59">
-        <v>523.1798016357421</v>
+        <v>40.97230003356933</v>
       </c>
       <c r="H59">
-        <v>463.6784672037761</v>
+        <v>39.72776674906413</v>
       </c>
       <c r="I59">
-        <v>445.0828002929687</v>
+        <v>38.63967506408692</v>
       </c>
       <c r="J59">
-        <v>432.659800567627</v>
+        <v>37.29460003852844</v>
       </c>
       <c r="K59">
-        <v>23.73999977111816</v>
+        <v>20.39999961853027</v>
       </c>
       <c r="L59">
-        <v>701.72998046875</v>
+        <v>51.9900016784668</v>
       </c>
       <c r="M59">
-        <v>142.0004653050219</v>
+        <v>133.8731011160293</v>
       </c>
       <c r="N59">
-        <v>0.39</v>
+        <v>0.74</v>
       </c>
       <c r="O59">
+        <v>0.41</v>
+      </c>
+      <c r="P59">
+        <v>0.92</v>
+      </c>
+      <c r="Q59">
         <v>0.74</v>
       </c>
-      <c r="P59">
-        <v>0.73</v>
-      </c>
-      <c r="Q59">
-        <v>80000000</v>
-      </c>
       <c r="R59">
-        <v>150000000</v>
+        <v>33585000</v>
       </c>
       <c r="S59">
-        <v>150000000</v>
+        <v>134962000</v>
       </c>
       <c r="T59">
-        <v>4.369197160021846</v>
+        <v>108063000</v>
       </c>
       <c r="U59">
-        <v>7.731958762886598</v>
+        <v>168948000</v>
       </c>
       <c r="V59">
-        <v>7.15648854961832</v>
-      </c>
-      <c r="W59" t="s">
-        <v>232</v>
+        <v>10.98008317204582</v>
+      </c>
+      <c r="W59">
+        <v>21.67743883634868</v>
       </c>
     </row>
     <row r="60" spans="1:23">
@@ -5270,70 +5282,70 @@
         <v>81</v>
       </c>
       <c r="B60" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C60" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D60" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E60">
-        <v>102.0400009155273</v>
+        <v>160.1499938964844</v>
       </c>
       <c r="F60">
-        <v>6426186.666666667</v>
+        <v>402718.1666666667</v>
       </c>
       <c r="G60">
-        <v>87.58699966430665</v>
+        <v>138.2774005126953</v>
       </c>
       <c r="H60">
-        <v>78.62993303934734</v>
+        <v>133.5429335021973</v>
       </c>
       <c r="I60">
-        <v>75.63724983215332</v>
+        <v>125.585700263977</v>
       </c>
       <c r="J60">
-        <v>73.21089990615845</v>
+        <v>118.3055001831055</v>
       </c>
       <c r="K60">
-        <v>0.9100000262260437</v>
+        <v>11.96000003814697</v>
       </c>
       <c r="L60">
-        <v>102.0400009155273</v>
+        <v>161.8300018310547</v>
       </c>
       <c r="M60">
-        <v>141.1814826649681</v>
+        <v>133.636013709772</v>
       </c>
       <c r="N60">
-        <v>0.7</v>
+        <v>5.74</v>
       </c>
       <c r="O60">
-        <v>1.35</v>
+        <v>5.18</v>
       </c>
       <c r="P60">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="Q60">
-        <v>311900000</v>
+        <v>4.31</v>
       </c>
       <c r="R60">
-        <v>604300000</v>
+        <v>220802000</v>
       </c>
       <c r="S60">
-        <v>461700000</v>
+        <v>173492000</v>
       </c>
       <c r="T60">
-        <v>14.22512086107817</v>
+        <v>174194000</v>
       </c>
       <c r="U60">
-        <v>28.72694428598593</v>
+        <v>882083000</v>
       </c>
       <c r="V60">
-        <v>23.55972852987702</v>
-      </c>
-      <c r="W60" t="s">
-        <v>232</v>
+        <v>21.45821225944765</v>
+      </c>
+      <c r="W60">
+        <v>20.80686382329061</v>
       </c>
     </row>
     <row r="61" spans="1:23">
@@ -5341,70 +5353,70 @@
         <v>82</v>
       </c>
       <c r="B61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C61" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D61" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E61">
-        <v>32.7599983215332</v>
+        <v>31.06999969482422</v>
       </c>
       <c r="F61">
-        <v>1015366.666666667</v>
+        <v>1452741.2</v>
       </c>
       <c r="G61">
-        <v>30.15640022277832</v>
+        <v>28.84740001678467</v>
       </c>
       <c r="H61">
-        <v>25.89146672566732</v>
+        <v>24.55973333994547</v>
       </c>
       <c r="I61">
-        <v>24.04545001983643</v>
+        <v>23.86375001907349</v>
       </c>
       <c r="J61">
-        <v>22.95684998512268</v>
+        <v>23.13375004768372</v>
       </c>
       <c r="K61">
-        <v>16.70999908447266</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="L61">
-        <v>36.84999847412109</v>
+        <v>31.79000091552734</v>
       </c>
       <c r="M61">
-        <v>140.8652637658371</v>
+        <v>133.5006517207393</v>
       </c>
       <c r="N61">
-        <v>0.32</v>
+        <v>0.67</v>
       </c>
       <c r="O61">
-        <v>0.43</v>
+        <v>0.65</v>
       </c>
       <c r="P61">
-        <v>0.53</v>
+        <v>0.31</v>
       </c>
       <c r="Q61">
-        <v>50100000</v>
+        <v>0.5</v>
       </c>
       <c r="R61">
-        <v>67700000</v>
+        <v>111000000</v>
       </c>
       <c r="S61">
-        <v>82800000</v>
+        <v>54000000</v>
       </c>
       <c r="T61">
-        <v>6.357868020304569</v>
+        <v>86000000</v>
       </c>
       <c r="U61">
-        <v>7.764651909622663</v>
+        <v>366000000</v>
       </c>
       <c r="V61">
-        <v>10.66460587326121</v>
-      </c>
-      <c r="W61" t="s">
-        <v>233</v>
+        <v>6.105610561056106</v>
+      </c>
+      <c r="W61">
+        <v>3.930131004366813</v>
       </c>
     </row>
     <row r="62" spans="1:23">
@@ -5412,70 +5424,70 @@
         <v>83</v>
       </c>
       <c r="B62" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C62" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D62" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="E62">
-        <v>144.3600006103516</v>
+        <v>45.00099945068359</v>
       </c>
       <c r="F62">
-        <v>363786.6666666667</v>
+        <v>305622.5333333333</v>
       </c>
       <c r="G62">
-        <v>128.9378005981445</v>
+        <v>41.85661979675293</v>
       </c>
       <c r="H62">
-        <v>114.5760668436686</v>
+        <v>34.0521399307251</v>
       </c>
       <c r="I62">
-        <v>105.0413502883911</v>
+        <v>32.40780494689941</v>
       </c>
       <c r="J62">
-        <v>99.01425022125244</v>
+        <v>29.95200001239776</v>
       </c>
       <c r="K62">
-        <v>0.577300488948822</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="L62">
-        <v>144.3600006103516</v>
+        <v>45.00099945068359</v>
       </c>
       <c r="M62">
-        <v>140.8376763186334</v>
+        <v>133.0969648937134</v>
       </c>
       <c r="N62">
-        <v>7.1</v>
+        <v>-0.38</v>
       </c>
       <c r="O62">
-        <v>7.09</v>
+        <v>-0.41</v>
       </c>
       <c r="P62">
-        <v>3.54</v>
+        <v>-0.49</v>
       </c>
       <c r="Q62">
-        <v>262489000</v>
+        <v>-0.44</v>
       </c>
       <c r="R62">
-        <v>262365000</v>
+        <v>-73020000</v>
       </c>
       <c r="S62">
-        <v>131301000</v>
+        <v>-26123000</v>
       </c>
       <c r="T62">
-        <v>16.55385399330376</v>
+        <v>-25192000</v>
       </c>
       <c r="U62">
-        <v>13.11388307693538</v>
+        <v>-81854000</v>
       </c>
       <c r="V62">
-        <v>10.21560758672308</v>
-      </c>
-      <c r="W62" t="s">
-        <v>232</v>
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:23">
@@ -5483,70 +5495,70 @@
         <v>84</v>
       </c>
       <c r="B63" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C63" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D63" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E63">
-        <v>133.4600067138672</v>
+        <v>54.10499954223633</v>
       </c>
       <c r="F63">
-        <v>862876.6666666666</v>
+        <v>1163668.433333333</v>
       </c>
       <c r="G63">
-        <v>116.9606002807617</v>
+        <v>47.37389991760254</v>
       </c>
       <c r="H63">
-        <v>102.1220002237956</v>
+        <v>43.62756665547689</v>
       </c>
       <c r="I63">
-        <v>98.06970012664794</v>
+        <v>41.87902499198913</v>
       </c>
       <c r="J63">
-        <v>93.59650012969971</v>
+        <v>40.00040001869202</v>
       </c>
       <c r="K63">
-        <v>4.719488620758057</v>
+        <v>11.8095235824585</v>
       </c>
       <c r="L63">
-        <v>133.4600067138672</v>
+        <v>55.52000045776367</v>
       </c>
       <c r="M63">
-        <v>140.8107844466733</v>
+        <v>132.9399198677628</v>
       </c>
       <c r="N63">
-        <v>4.84</v>
+        <v>0.48</v>
       </c>
       <c r="O63">
-        <v>1.32</v>
+        <v>0.55</v>
       </c>
       <c r="P63">
-        <v>4.17</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q63">
-        <v>470000000</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R63">
-        <v>124000000</v>
+        <v>93400000</v>
       </c>
       <c r="S63">
-        <v>383000000</v>
+        <v>158700000</v>
       </c>
       <c r="T63">
-        <v>18.58442071965204</v>
+        <v>93800000</v>
       </c>
       <c r="U63">
-        <v>5.426695842450766</v>
+        <v>399800000</v>
       </c>
       <c r="V63">
-        <v>16.43071643071643</v>
-      </c>
-      <c r="W63" t="s">
-        <v>232</v>
+        <v>12.53354804079442</v>
+      </c>
+      <c r="W63">
+        <v>21.39967637540453</v>
       </c>
     </row>
     <row r="64" spans="1:23">
@@ -5554,70 +5566,70 @@
         <v>85</v>
       </c>
       <c r="B64" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C64" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="D64" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="E64">
-        <v>30.59000015258789</v>
+        <v>111.5999984741211</v>
       </c>
       <c r="F64">
-        <v>824543.3333333334</v>
+        <v>386218.2</v>
       </c>
       <c r="G64">
-        <v>30.18539981842041</v>
+        <v>90.75079956054688</v>
       </c>
       <c r="H64">
-        <v>25.00309993743896</v>
+        <v>89.03079981486003</v>
       </c>
       <c r="I64">
-        <v>23.37212493896484</v>
+        <v>86.35574989318847</v>
       </c>
       <c r="J64">
-        <v>22.20457497596741</v>
+        <v>84.08969997406005</v>
       </c>
       <c r="K64">
-        <v>0.1500000059604645</v>
+        <v>3.099249601364136</v>
       </c>
       <c r="L64">
-        <v>38.15000152587891</v>
+        <v>121.8199996948242</v>
       </c>
       <c r="M64">
-        <v>140.4424059594698</v>
+        <v>132.2656353334257</v>
       </c>
       <c r="N64">
-        <v>0.01</v>
+        <v>4</v>
       </c>
       <c r="O64">
-        <v>-0.02</v>
+        <v>3.5</v>
       </c>
       <c r="P64">
-        <v>-0.36</v>
+        <v>1.48</v>
       </c>
       <c r="Q64">
-        <v>668000</v>
+        <v>2.84</v>
       </c>
       <c r="R64">
-        <v>-934000</v>
+        <v>88842000</v>
       </c>
       <c r="S64">
-        <v>-21005000</v>
+        <v>37337000</v>
       </c>
       <c r="T64">
-        <v>0.1908331524036978</v>
+        <v>71283000</v>
       </c>
       <c r="U64">
-        <v>-0.2433083686095734</v>
+        <v>298209000</v>
       </c>
       <c r="V64">
-        <v>-5.378119847195338</v>
-      </c>
-      <c r="W64" t="s">
-        <v>232</v>
+        <v>6.57197534307173</v>
+      </c>
+      <c r="W64">
+        <v>3.000840688689603</v>
       </c>
     </row>
     <row r="65" spans="1:23">
@@ -5625,70 +5637,70 @@
         <v>86</v>
       </c>
       <c r="B65" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C65" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D65" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="E65">
-        <v>112.0899963378906</v>
+        <v>336.2799987792969</v>
       </c>
       <c r="F65">
-        <v>371016.6666666667</v>
+        <v>372318.9666666667</v>
       </c>
       <c r="G65">
-        <v>103.203999786377</v>
+        <v>306.9073999023437</v>
       </c>
       <c r="H65">
-        <v>87.46439997355144</v>
+        <v>262.7856659952799</v>
       </c>
       <c r="I65">
-        <v>83.38669988632202</v>
+        <v>257.1242993927002</v>
       </c>
       <c r="J65">
-        <v>79.37514993667602</v>
+        <v>246.2250492858887</v>
       </c>
       <c r="K65">
-        <v>20.81999969482422</v>
+        <v>0.03128649666905403</v>
       </c>
       <c r="L65">
-        <v>116.4700012207031</v>
+        <v>337.3200073242188</v>
       </c>
       <c r="M65">
-        <v>139.902384881612</v>
+        <v>132.0441989208849</v>
       </c>
       <c r="N65">
-        <v>1.05</v>
+        <v>2.26</v>
       </c>
       <c r="O65">
-        <v>1.34</v>
+        <v>2.57</v>
       </c>
       <c r="P65">
-        <v>0.59</v>
+        <v>2.27</v>
       </c>
       <c r="Q65">
-        <v>52215000</v>
+        <v>3.37</v>
       </c>
       <c r="R65">
-        <v>66214000</v>
+        <v>139100000</v>
       </c>
       <c r="S65">
-        <v>29068000</v>
+        <v>122900000</v>
       </c>
       <c r="T65">
-        <v>20.53663083621432</v>
+        <v>181900000</v>
       </c>
       <c r="U65">
-        <v>26.14364117345126</v>
+        <v>545900000</v>
       </c>
       <c r="V65">
-        <v>14.59493384881882</v>
-      </c>
-      <c r="W65" t="s">
-        <v>232</v>
+        <v>10.56830268956086</v>
+      </c>
+      <c r="W65">
+        <v>10.07707445063955</v>
       </c>
     </row>
     <row r="66" spans="1:23">
@@ -5699,67 +5711,67 @@
         <v>108</v>
       </c>
       <c r="C66" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="D66" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E66">
-        <v>54.20000076293945</v>
+        <v>32.98500061035156</v>
       </c>
       <c r="F66">
-        <v>1056093.333333333</v>
+        <v>1589067.666666667</v>
       </c>
       <c r="G66">
-        <v>49.35900047302246</v>
+        <v>29.12629997253418</v>
       </c>
       <c r="H66">
-        <v>43.06820012410482</v>
+        <v>26.85169995625814</v>
       </c>
       <c r="I66">
-        <v>41.09615013122558</v>
+        <v>25.46452498435974</v>
       </c>
       <c r="J66">
-        <v>39.34195007324219</v>
+        <v>23.99785000324249</v>
       </c>
       <c r="K66">
-        <v>27.71999931335449</v>
+        <v>0.1598737090826035</v>
       </c>
       <c r="L66">
-        <v>71.16999816894531</v>
+        <v>33.22999954223633</v>
       </c>
       <c r="M66">
-        <v>139.8322253529184</v>
+        <v>131.8958813002955</v>
       </c>
       <c r="N66">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="O66">
-        <v>0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="P66">
-        <v>0.14</v>
+        <v>1.3</v>
       </c>
       <c r="Q66">
-        <v>36997000</v>
+        <v>0.11</v>
       </c>
       <c r="R66">
-        <v>25722000</v>
+        <v>359000000</v>
       </c>
       <c r="S66">
-        <v>45490000</v>
+        <v>-64000000</v>
       </c>
       <c r="T66">
-        <v>13.78777037401428</v>
+        <v>23000000</v>
       </c>
       <c r="U66">
-        <v>8.963993476169898</v>
+        <v>275000000</v>
       </c>
       <c r="V66">
-        <v>14.46832330929898</v>
-      </c>
-      <c r="W66" t="s">
-        <v>232</v>
+        <v>8.586462568763453</v>
+      </c>
+      <c r="W66">
+        <v>-5.85544373284538</v>
       </c>
     </row>
     <row r="67" spans="1:23">
@@ -5767,70 +5779,70 @@
         <v>88</v>
       </c>
       <c r="B67" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C67" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="D67" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E67">
-        <v>134.4299926757812</v>
+        <v>29.92499923706055</v>
       </c>
       <c r="F67">
-        <v>378520</v>
+        <v>400926.2666666667</v>
       </c>
       <c r="G67">
-        <v>127.5173997497559</v>
+        <v>26.75349987030029</v>
       </c>
       <c r="H67">
-        <v>108.1021333312988</v>
+        <v>23.72803328196208</v>
       </c>
       <c r="I67">
-        <v>101.2862999725342</v>
+        <v>23.31557494163513</v>
       </c>
       <c r="J67">
-        <v>96.91935009002685</v>
+        <v>22.8875999546051</v>
       </c>
       <c r="K67">
-        <v>0.8630853891372681</v>
+        <v>1.970000028610229</v>
       </c>
       <c r="L67">
-        <v>156.8002166748047</v>
+        <v>30.61000061035156</v>
       </c>
       <c r="M67">
-        <v>139.0980624397909</v>
+        <v>131.3394859647028</v>
       </c>
       <c r="N67">
-        <v>1.48</v>
+        <v>-0.04</v>
       </c>
       <c r="O67">
-        <v>0.86</v>
+        <v>0.08</v>
       </c>
       <c r="P67">
-        <v>0.06</v>
+        <v>0.24</v>
       </c>
       <c r="Q67">
-        <v>46150000</v>
+        <v>-0.11</v>
       </c>
       <c r="R67">
-        <v>26584000</v>
+        <v>4789000</v>
       </c>
       <c r="S67">
-        <v>1819000</v>
+        <v>13725000</v>
       </c>
       <c r="T67">
-        <v>16.77644971790845</v>
+        <v>-6296000</v>
       </c>
       <c r="U67">
-        <v>10.59685012377076</v>
+        <v>24049000</v>
       </c>
       <c r="V67">
-        <v>0.6156335034589194</v>
-      </c>
-      <c r="W67" t="s">
-        <v>232</v>
+        <v>15.72122644606395</v>
+      </c>
+      <c r="W67">
+        <v>32.45371355607575</v>
       </c>
     </row>
     <row r="68" spans="1:23">
@@ -5838,70 +5850,70 @@
         <v>89</v>
       </c>
       <c r="B68" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C68" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="D68" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="E68">
-        <v>22.70999908447266</v>
+        <v>56.93999862670898</v>
       </c>
       <c r="F68">
-        <v>467663.3333333333</v>
+        <v>345775.3666666666</v>
       </c>
       <c r="G68">
-        <v>22.59979991912842</v>
+        <v>51.56600006103515</v>
       </c>
       <c r="H68">
-        <v>18.69719997406006</v>
+        <v>47.21719998677572</v>
       </c>
       <c r="I68">
-        <v>16.42369998931885</v>
+        <v>44.94595005035401</v>
       </c>
       <c r="J68">
-        <v>15.30272500038147</v>
+        <v>42.90430004119873</v>
       </c>
       <c r="K68">
-        <v>7.369999885559082</v>
+        <v>0.07982486486434937</v>
       </c>
       <c r="L68">
-        <v>28.52000045776367</v>
+        <v>59.70568466186523</v>
       </c>
       <c r="M68">
-        <v>138.7206221345322</v>
+        <v>131.2882493284291</v>
       </c>
       <c r="N68">
-        <v>-0.72</v>
+        <v>0.05</v>
       </c>
       <c r="O68">
-        <v>-0.35</v>
+        <v>-0.14</v>
       </c>
       <c r="P68">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="Q68">
-        <v>-23095000</v>
+        <v>0.38</v>
       </c>
       <c r="R68">
-        <v>-11294000</v>
+        <v>-6900000</v>
       </c>
       <c r="S68">
-        <v>7130000</v>
+        <v>6200000</v>
       </c>
       <c r="T68">
-        <v>-8.962945139557267</v>
+        <v>18600000</v>
       </c>
       <c r="U68">
-        <v>-4.791033885938269</v>
+        <v>-5600000</v>
       </c>
       <c r="V68">
-        <v>2.378141114157444</v>
-      </c>
-      <c r="W68" t="s">
-        <v>233</v>
+        <v>-1.31956397016638</v>
+      </c>
+      <c r="W68">
+        <v>1.070626834743567</v>
       </c>
     </row>
     <row r="69" spans="1:23">
@@ -5909,70 +5921,70 @@
         <v>90</v>
       </c>
       <c r="B69" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C69" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D69" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="E69">
-        <v>47.70999908447266</v>
+        <v>192.4299926757812</v>
       </c>
       <c r="F69">
-        <v>13039106.66666667</v>
+        <v>353621.3666666666</v>
       </c>
       <c r="G69">
-        <v>39.79060005187988</v>
+        <v>172.7073992919922</v>
       </c>
       <c r="H69">
-        <v>37.15966660817464</v>
+        <v>152.2213995361328</v>
       </c>
       <c r="I69">
-        <v>36.01009997367859</v>
+        <v>145.2323494720459</v>
       </c>
       <c r="J69">
-        <v>34.62664994239807</v>
+        <v>138.0792495727539</v>
       </c>
       <c r="K69">
-        <v>3.490809917449951</v>
+        <v>2.138945579528809</v>
       </c>
       <c r="L69">
-        <v>62.26396942138672</v>
+        <v>192.9400024414062</v>
       </c>
       <c r="M69">
-        <v>138.6566111160424</v>
+        <v>131.285423583404</v>
       </c>
       <c r="N69">
-        <v>1.08</v>
+        <v>2.75</v>
       </c>
       <c r="O69">
-        <v>1.29</v>
+        <v>3.72</v>
       </c>
       <c r="P69">
-        <v>-0.57</v>
+        <v>3.2</v>
       </c>
       <c r="Q69">
-        <v>695000000</v>
+        <v>2.79</v>
       </c>
       <c r="R69">
-        <v>828000000</v>
+        <v>138995000</v>
       </c>
       <c r="S69">
-        <v>-363000000</v>
+        <v>117184000</v>
       </c>
       <c r="T69">
-        <v>4.973166368515206</v>
+        <v>100356000</v>
       </c>
       <c r="U69">
-        <v>6.163007071082992</v>
+        <v>435500000</v>
       </c>
       <c r="V69">
-        <v>-2.84505055255114</v>
-      </c>
-      <c r="W69" t="s">
-        <v>232</v>
+        <v>22.97179821111015</v>
+      </c>
+      <c r="W69">
+        <v>22.910455202185</v>
       </c>
     </row>
     <row r="70" spans="1:23">
@@ -5980,70 +5992,70 @@
         <v>91</v>
       </c>
       <c r="B70" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C70" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="D70" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="E70">
-        <v>28.34000015258789</v>
+        <v>168.7100067138672</v>
       </c>
       <c r="F70">
-        <v>1109150</v>
+        <v>385770.3666666666</v>
       </c>
       <c r="G70">
-        <v>24.46980003356934</v>
+        <v>154.0547994995117</v>
       </c>
       <c r="H70">
-        <v>22.19426661173503</v>
+        <v>138.6586661275228</v>
       </c>
       <c r="I70">
-        <v>20.75674997329712</v>
+        <v>133.3046495437622</v>
       </c>
       <c r="J70">
-        <v>19.64124995708466</v>
+        <v>128.5147996520996</v>
       </c>
       <c r="K70">
-        <v>9.090000152587891</v>
+        <v>0.5625</v>
       </c>
       <c r="L70">
-        <v>28.34000015258789</v>
+        <v>171.8699951171875</v>
       </c>
       <c r="M70">
-        <v>138.6466069282945</v>
+        <v>130.8676609889043</v>
       </c>
       <c r="N70">
-        <v>0.06</v>
+        <v>2.71</v>
       </c>
       <c r="O70">
-        <v>0.04</v>
+        <v>2.5</v>
       </c>
       <c r="P70">
-        <v>0.05</v>
+        <v>1.52</v>
       </c>
       <c r="Q70">
-        <v>28000000</v>
+        <v>1.33</v>
       </c>
       <c r="R70">
-        <v>22000000</v>
+        <v>378263000</v>
       </c>
       <c r="S70">
-        <v>26000000</v>
+        <v>82474000</v>
       </c>
       <c r="T70">
-        <v>1.613832853025936</v>
+        <v>72401000</v>
       </c>
       <c r="U70">
-        <v>1.291837933059307</v>
+        <v>411744000</v>
       </c>
       <c r="V70">
-        <v>1.61090458488228</v>
-      </c>
-      <c r="W70" t="s">
-        <v>232</v>
+        <v>7.553193018833112</v>
+      </c>
+      <c r="W70">
+        <v>6.452869811235132</v>
       </c>
     </row>
     <row r="71" spans="1:23">
@@ -6051,70 +6063,70 @@
         <v>92</v>
       </c>
       <c r="B71" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C71" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D71" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E71">
-        <v>78.25</v>
+        <v>132.6799926757812</v>
       </c>
       <c r="F71">
-        <v>5572526.666666667</v>
+        <v>367205.5666666667</v>
       </c>
       <c r="G71">
-        <v>70.13539932250977</v>
+        <v>128.4299993896484</v>
       </c>
       <c r="H71">
-        <v>61.78133293151856</v>
+        <v>109.5805332438151</v>
       </c>
       <c r="I71">
-        <v>59.39414972305298</v>
+        <v>102.6233499145508</v>
       </c>
       <c r="J71">
-        <v>57.01824970245362</v>
+        <v>98.05700012207031</v>
       </c>
       <c r="K71">
-        <v>1.5</v>
+        <v>0.8630853891372681</v>
       </c>
       <c r="L71">
-        <v>78.31999969482422</v>
+        <v>156.8002166748047</v>
       </c>
       <c r="M71">
-        <v>138.1886972162805</v>
+        <v>130.8667562300924</v>
       </c>
       <c r="N71">
-        <v>0.29</v>
+        <v>-5.65</v>
       </c>
       <c r="O71">
-        <v>0.4</v>
+        <v>1.48</v>
       </c>
       <c r="P71">
-        <v>0.31</v>
+        <v>0.86</v>
       </c>
       <c r="Q71">
-        <v>231600000</v>
+        <v>0.06</v>
       </c>
       <c r="R71">
-        <v>313800000</v>
+        <v>46150000</v>
       </c>
       <c r="S71">
-        <v>247700000</v>
+        <v>26584000</v>
       </c>
       <c r="T71">
-        <v>20.14789038712484</v>
+        <v>1819000</v>
       </c>
       <c r="U71">
-        <v>24.45830085736555</v>
+        <v>-80582000</v>
       </c>
       <c r="V71">
-        <v>19.62291056008873</v>
-      </c>
-      <c r="W71" t="s">
-        <v>232</v>
+        <v>16.77644971790845</v>
+      </c>
+      <c r="W71">
+        <v>10.59685012377076</v>
       </c>
     </row>
     <row r="72" spans="1:23">
@@ -6122,70 +6134,70 @@
         <v>93</v>
       </c>
       <c r="B72" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C72" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D72" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E72">
-        <v>31.60000038146973</v>
+        <v>138.8549957275391</v>
       </c>
       <c r="F72">
-        <v>1589013.333333333</v>
+        <v>354861.8</v>
       </c>
       <c r="G72">
-        <v>28.38100002288818</v>
+        <v>130.8047003173828</v>
       </c>
       <c r="H72">
-        <v>24.20380001068115</v>
+        <v>116.471166788737</v>
       </c>
       <c r="I72">
-        <v>23.64300002098084</v>
+        <v>106.8654752731323</v>
       </c>
       <c r="J72">
-        <v>23.01185004234314</v>
+        <v>100.3206002807617</v>
       </c>
       <c r="K72">
-        <v>18.89999961853027</v>
+        <v>0.577300488948822</v>
       </c>
       <c r="L72">
-        <v>31.79000091552734</v>
+        <v>146.2899932861328</v>
       </c>
       <c r="M72">
-        <v>137.7196691233726</v>
+        <v>130.8533008730499</v>
       </c>
       <c r="N72">
-        <v>0.65</v>
+        <v>6.77</v>
       </c>
       <c r="O72">
-        <v>0.31</v>
+        <v>7.1</v>
       </c>
       <c r="P72">
-        <v>0.5</v>
+        <v>7.09</v>
       </c>
       <c r="Q72">
-        <v>111000000</v>
+        <v>3.54</v>
       </c>
       <c r="R72">
-        <v>54000000</v>
+        <v>262489000</v>
       </c>
       <c r="S72">
-        <v>86000000</v>
+        <v>262365000</v>
       </c>
       <c r="T72">
-        <v>6.105610561056106</v>
+        <v>131301000</v>
       </c>
       <c r="U72">
-        <v>3.930131004366813</v>
+        <v>992192000</v>
       </c>
       <c r="V72">
-        <v>5.463786531130877</v>
-      </c>
-      <c r="W72" t="s">
-        <v>232</v>
+        <v>16.55385399330376</v>
+      </c>
+      <c r="W72">
+        <v>13.11388307693538</v>
       </c>
     </row>
     <row r="73" spans="1:23">
@@ -6193,70 +6205,70 @@
         <v>94</v>
       </c>
       <c r="B73" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C73" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="D73" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="E73">
-        <v>177.0899963378906</v>
+        <v>209.5399932861328</v>
       </c>
       <c r="F73">
-        <v>290463.3333333333</v>
+        <v>336530</v>
       </c>
       <c r="G73">
-        <v>151.4844000244141</v>
+        <v>186.7177993774414</v>
       </c>
       <c r="H73">
-        <v>138.3993336486816</v>
+        <v>169.9723326619466</v>
       </c>
       <c r="I73">
-        <v>131.5756002426147</v>
+        <v>162.2991495132446</v>
       </c>
       <c r="J73">
-        <v>126.1549503707886</v>
+        <v>155.8767495346069</v>
       </c>
       <c r="K73">
-        <v>2.075098752975464</v>
+        <v>2.624907255172729</v>
       </c>
       <c r="L73">
-        <v>178.4799957275391</v>
+        <v>209.5399932861328</v>
       </c>
       <c r="M73">
-        <v>137.702695166012</v>
+        <v>130.8122296140773</v>
       </c>
       <c r="N73">
-        <v>4.61</v>
+        <v>2.18</v>
       </c>
       <c r="O73">
-        <v>4.21</v>
+        <v>1.87</v>
       </c>
       <c r="P73">
-        <v>4.31</v>
+        <v>1.87</v>
       </c>
       <c r="Q73">
-        <v>340100000</v>
+        <v>2.09</v>
       </c>
       <c r="R73">
-        <v>298000000</v>
+        <v>109225000</v>
       </c>
       <c r="S73">
-        <v>298300000</v>
+        <v>109146000</v>
       </c>
       <c r="T73">
-        <v>4.914242778909648</v>
+        <v>121931000</v>
       </c>
       <c r="U73">
-        <v>4.24997860749023</v>
+        <v>472224000</v>
       </c>
       <c r="V73">
-        <v>4.064586455920425</v>
-      </c>
-      <c r="W73" t="s">
-        <v>232</v>
+        <v>11.6788204097344</v>
+      </c>
+      <c r="W73">
+        <v>11.72435425067728</v>
       </c>
     </row>
     <row r="74" spans="1:23">
@@ -6264,70 +6276,70 @@
         <v>95</v>
       </c>
       <c r="B74" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C74" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D74" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E74">
-        <v>90.16000366210938</v>
+        <v>78.69000244140625</v>
       </c>
       <c r="F74">
-        <v>519486.6666666667</v>
+        <v>5413226.666666667</v>
       </c>
       <c r="G74">
-        <v>78.22089996337891</v>
+        <v>71.54399932861328</v>
       </c>
       <c r="H74">
-        <v>71.90200007120768</v>
+        <v>62.51893292744955</v>
       </c>
       <c r="I74">
-        <v>66.34440004348755</v>
+        <v>60.00284969329834</v>
       </c>
       <c r="J74">
-        <v>63.13740005493164</v>
+        <v>57.48584972381592</v>
       </c>
       <c r="K74">
-        <v>10.5</v>
+        <v>1.5</v>
       </c>
       <c r="L74">
-        <v>90.16000366210938</v>
+        <v>80.27999877929688</v>
       </c>
       <c r="M74">
-        <v>137.5029928601381</v>
+        <v>130.6708815481005</v>
       </c>
       <c r="N74">
-        <v>-0.25</v>
+        <v>0.21</v>
       </c>
       <c r="O74">
-        <v>-0.21</v>
+        <v>0.29</v>
       </c>
       <c r="P74">
-        <v>-0.08</v>
+        <v>0.4</v>
       </c>
       <c r="Q74">
-        <v>-7426000</v>
+        <v>0.31</v>
       </c>
       <c r="R74">
-        <v>-6720000</v>
+        <v>231600000</v>
       </c>
       <c r="S74">
-        <v>-2636000</v>
+        <v>313800000</v>
       </c>
       <c r="T74">
-        <v>-28.91406767122221</v>
+        <v>247700000</v>
       </c>
       <c r="U74">
-        <v>-21.41832669322709</v>
+        <v>857300000</v>
       </c>
       <c r="V74">
-        <v>-6.343552967223371</v>
-      </c>
-      <c r="W74" t="s">
-        <v>233</v>
+        <v>20.14789038712484</v>
+      </c>
+      <c r="W74">
+        <v>24.45830085736555</v>
       </c>
     </row>
     <row r="75" spans="1:23">
@@ -6335,70 +6347,70 @@
         <v>96</v>
       </c>
       <c r="B75" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C75" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D75" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E75">
-        <v>113.25</v>
+        <v>119.9700012207031</v>
       </c>
       <c r="F75">
-        <v>1177340</v>
+        <v>643386.6666666666</v>
       </c>
       <c r="G75">
-        <v>96.51000015258789</v>
+        <v>108.4141995239258</v>
       </c>
       <c r="H75">
-        <v>91.13373341878255</v>
+        <v>95.68799962361653</v>
       </c>
       <c r="I75">
-        <v>86.45640003204346</v>
+        <v>91.07164974212647</v>
       </c>
       <c r="J75">
-        <v>84.27410018920898</v>
+        <v>87.09129978179932</v>
       </c>
       <c r="K75">
-        <v>24</v>
+        <v>13.45347881317139</v>
       </c>
       <c r="L75">
-        <v>143.3099975585938</v>
+        <v>131.5730438232422</v>
       </c>
       <c r="M75">
-        <v>137.0128111628075</v>
+        <v>130.5898247616127</v>
       </c>
       <c r="N75">
-        <v>0.71</v>
+        <v>3.01</v>
       </c>
       <c r="O75">
-        <v>0.64</v>
+        <v>2.93</v>
       </c>
       <c r="P75">
-        <v>0.66</v>
+        <v>2.23</v>
       </c>
       <c r="Q75">
-        <v>76175000</v>
+        <v>3.07</v>
       </c>
       <c r="R75">
-        <v>69237000</v>
+        <v>115939000</v>
       </c>
       <c r="S75">
-        <v>71524000</v>
+        <v>88280000</v>
       </c>
       <c r="T75">
-        <v>6.938726061736672</v>
+        <v>121521000</v>
       </c>
       <c r="U75">
-        <v>6.606149022631144</v>
+        <v>348054000</v>
       </c>
       <c r="V75">
-        <v>6.37439263064457</v>
-      </c>
-      <c r="W75" t="s">
-        <v>232</v>
+        <v>14.32327088313597</v>
+      </c>
+      <c r="W75">
+        <v>9.912285035458764</v>
       </c>
     </row>
     <row r="76" spans="1:23">
@@ -6409,67 +6421,67 @@
         <v>108</v>
       </c>
       <c r="C76" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D76" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E76">
-        <v>239.5099945068359</v>
+        <v>58.79999923706055</v>
       </c>
       <c r="F76">
-        <v>2131310</v>
+        <v>690966.2333333333</v>
       </c>
       <c r="G76">
-        <v>222.6108004760742</v>
+        <v>52.92919998168945</v>
       </c>
       <c r="H76">
-        <v>200.0885332234701</v>
+        <v>47.56979998270671</v>
       </c>
       <c r="I76">
-        <v>189.8738999176025</v>
+        <v>45.87789995193481</v>
       </c>
       <c r="J76">
-        <v>183.6434999847412</v>
+        <v>43.70914993286133</v>
       </c>
       <c r="K76">
-        <v>0.8611109852790833</v>
+        <v>13.7691478729248</v>
       </c>
       <c r="L76">
-        <v>239.5099945068359</v>
+        <v>59.22999954223633</v>
       </c>
       <c r="M76">
-        <v>135.7459673196028</v>
+        <v>130.4462988901802</v>
       </c>
       <c r="N76">
-        <v>0.68</v>
+        <v>1.26</v>
       </c>
       <c r="O76">
-        <v>0.88</v>
+        <v>1.45</v>
       </c>
       <c r="P76">
-        <v>0.89</v>
+        <v>1.52</v>
       </c>
       <c r="Q76">
-        <v>186305000</v>
+        <v>1.85</v>
       </c>
       <c r="R76">
-        <v>240392000</v>
+        <v>139000000</v>
       </c>
       <c r="S76">
-        <v>241804000</v>
+        <v>141000000</v>
       </c>
       <c r="T76">
-        <v>20.64197820850609</v>
+        <v>170000000</v>
       </c>
       <c r="U76">
-        <v>26.71387311821504</v>
+        <v>531000000</v>
       </c>
       <c r="V76">
-        <v>23.66706143742231</v>
-      </c>
-      <c r="W76" t="s">
-        <v>232</v>
+        <v>19.57746478873239</v>
+      </c>
+      <c r="W76">
+        <v>19.63788300835655</v>
       </c>
     </row>
     <row r="77" spans="1:23">
@@ -6480,67 +6492,67 @@
         <v>109</v>
       </c>
       <c r="C77" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D77" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E77">
-        <v>32.22000122070312</v>
+        <v>10.6850004196167</v>
       </c>
       <c r="F77">
-        <v>1583870</v>
+        <v>482947.5</v>
       </c>
       <c r="G77">
-        <v>28.54999996185303</v>
+        <v>9.368899993896484</v>
       </c>
       <c r="H77">
-        <v>26.5659999593099</v>
+        <v>8.523833322525025</v>
       </c>
       <c r="I77">
-        <v>25.03539999008179</v>
+        <v>8.457524998188019</v>
       </c>
       <c r="J77">
-        <v>23.68150001049042</v>
+        <v>8.321950001716614</v>
       </c>
       <c r="K77">
-        <v>0.1598737090826035</v>
+        <v>3.549999952316284</v>
       </c>
       <c r="L77">
-        <v>32.22000122070312</v>
+        <v>13.5</v>
       </c>
       <c r="M77">
-        <v>135.7444515766796</v>
+        <v>130.4110664730868</v>
       </c>
       <c r="N77">
-        <v>-0.02</v>
+        <v>0.168</v>
       </c>
       <c r="O77">
-        <v>1.3</v>
+        <v>0.205</v>
       </c>
       <c r="P77">
-        <v>0.11</v>
+        <v>0.024961</v>
       </c>
       <c r="Q77">
-        <v>359000000</v>
+        <v>0.2</v>
       </c>
       <c r="R77">
-        <v>-64000000</v>
+        <v>22548000</v>
       </c>
       <c r="S77">
-        <v>23000000</v>
+        <v>2732000</v>
       </c>
       <c r="T77">
-        <v>8.586462568763453</v>
+        <v>21569000</v>
       </c>
       <c r="U77">
-        <v>-5.85544373284538</v>
+        <v>108138000</v>
       </c>
       <c r="V77">
-        <v>2.167766258246937</v>
-      </c>
-      <c r="W77" t="s">
-        <v>232</v>
+        <v>5.84049753537635</v>
+      </c>
+      <c r="W77">
+        <v>0.7351516586657482</v>
       </c>
     </row>
     <row r="78" spans="1:23">
@@ -6551,67 +6563,67 @@
         <v>108</v>
       </c>
       <c r="C78" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="D78" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="E78">
-        <v>105.5699996948242</v>
+        <v>113.2602996826172</v>
       </c>
       <c r="F78">
-        <v>11213003.33333333</v>
+        <v>1178803.5</v>
       </c>
       <c r="G78">
-        <v>96.80920028686523</v>
+        <v>98.1878059387207</v>
       </c>
       <c r="H78">
-        <v>90.27920018513997</v>
+        <v>92.39066869099935</v>
       </c>
       <c r="I78">
-        <v>85.31690015792847</v>
+        <v>87.47645153045654</v>
       </c>
       <c r="J78">
-        <v>83.07070009231568</v>
+        <v>84.61285011291504</v>
       </c>
       <c r="K78">
-        <v>1.637526988983154</v>
+        <v>24</v>
       </c>
       <c r="L78">
-        <v>140.6600036621094</v>
+        <v>143.3099975585938</v>
       </c>
       <c r="M78">
-        <v>135.6524869215367</v>
+        <v>130.1841690912718</v>
       </c>
       <c r="N78">
-        <v>54.15</v>
+        <v>0.76</v>
       </c>
       <c r="O78">
-        <v>57.05</v>
+        <v>0.71</v>
       </c>
       <c r="P78">
-        <v>39.9</v>
+        <v>0.64</v>
       </c>
       <c r="Q78">
-        <v>280865780000</v>
+        <v>0.66</v>
       </c>
       <c r="R78">
-        <v>295904000000</v>
+        <v>76175000</v>
       </c>
       <c r="S78">
-        <v>206986561000</v>
+        <v>69237000</v>
       </c>
       <c r="T78">
-        <v>45.8075681734033</v>
+        <v>71524000</v>
       </c>
       <c r="U78">
-        <v>47.30452576215369</v>
+        <v>298195000</v>
       </c>
       <c r="V78">
-        <v>40.69468005173939</v>
-      </c>
-      <c r="W78" t="s">
-        <v>232</v>
+        <v>6.938726061736672</v>
+      </c>
+      <c r="W78">
+        <v>6.606149022631144</v>
       </c>
     </row>
     <row r="79" spans="1:23">
@@ -6619,70 +6631,70 @@
         <v>100</v>
       </c>
       <c r="B79" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C79" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="D79" t="s">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="E79">
-        <v>383.6600036621094</v>
+        <v>12.13000011444092</v>
       </c>
       <c r="F79">
-        <v>380096.6666666667</v>
+        <v>8931185.366666667</v>
       </c>
       <c r="G79">
-        <v>359.9959997558594</v>
+        <v>10.92239999771118</v>
       </c>
       <c r="H79">
-        <v>316.8929995727539</v>
+        <v>9.669533332188925</v>
       </c>
       <c r="I79">
-        <v>297.3098496246338</v>
+        <v>9.498600013256073</v>
       </c>
       <c r="J79">
-        <v>288.8312500762939</v>
+        <v>9.29365000963211</v>
       </c>
       <c r="K79">
-        <v>0.2751234471797943</v>
+        <v>0.3049550950527191</v>
       </c>
       <c r="L79">
-        <v>471.1166076660156</v>
+        <v>13.71520042419434</v>
       </c>
       <c r="M79">
-        <v>135.615381869454</v>
+        <v>129.975827554942</v>
       </c>
       <c r="N79">
-        <v>1.59</v>
+        <v>0.34</v>
       </c>
       <c r="O79">
-        <v>1.36</v>
+        <v>0.3</v>
       </c>
       <c r="P79">
-        <v>1.85</v>
+        <v>0.3</v>
       </c>
       <c r="Q79">
-        <v>120600000</v>
+        <v>2.87</v>
       </c>
       <c r="R79">
-        <v>103000000</v>
+        <v>152000000</v>
       </c>
       <c r="S79">
-        <v>140000000</v>
+        <v>172000000</v>
       </c>
       <c r="T79">
-        <v>17.55714077740573</v>
+        <v>2006000000</v>
       </c>
       <c r="U79">
-        <v>14.53365316777198</v>
+        <v>650000000</v>
       </c>
       <c r="V79">
-        <v>19.53670108847335</v>
-      </c>
-      <c r="W79" t="s">
-        <v>232</v>
+        <v>44.31486880466473</v>
+      </c>
+      <c r="W79">
+        <v>41.14832535885167</v>
       </c>
     </row>
     <row r="80" spans="1:23">
@@ -6690,70 +6702,70 @@
         <v>101</v>
       </c>
       <c r="B80" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C80" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="D80" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="E80">
-        <v>178.1300048828125</v>
+        <v>534.010009765625</v>
       </c>
       <c r="F80">
-        <v>974173.3333333334</v>
+        <v>352947.7666666667</v>
       </c>
       <c r="G80">
-        <v>153.0202005004883</v>
+        <v>502.3063989257813</v>
       </c>
       <c r="H80">
-        <v>146.4525997416178</v>
+        <v>452.8440661621094</v>
       </c>
       <c r="I80">
-        <v>141.3384999084473</v>
+        <v>428.9887496948242</v>
       </c>
       <c r="J80">
-        <v>137.195599899292</v>
+        <v>409.0641505432129</v>
       </c>
       <c r="K80">
-        <v>3.140000104904175</v>
+        <v>0.4583329856395721</v>
       </c>
       <c r="L80">
-        <v>183.1000061035156</v>
+        <v>553.3200073242188</v>
       </c>
       <c r="M80">
-        <v>135.0922309856031</v>
+        <v>129.8882548185674</v>
       </c>
       <c r="N80">
-        <v>4.3</v>
+        <v>1.66</v>
       </c>
       <c r="O80">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P80">
-        <v>3.48</v>
+        <v>10.48</v>
       </c>
       <c r="Q80">
-        <v>239602000</v>
+        <v>3.46</v>
       </c>
       <c r="R80">
-        <v>218920000</v>
+        <v>101524000</v>
       </c>
       <c r="S80">
-        <v>197100000</v>
+        <v>278662000</v>
       </c>
       <c r="T80">
-        <v>4.399663894926033</v>
+        <v>91787000</v>
       </c>
       <c r="U80">
-        <v>3.938476860818776</v>
+        <v>493854000</v>
       </c>
       <c r="V80">
-        <v>3.569423567974792</v>
-      </c>
-      <c r="W80" t="s">
-        <v>232</v>
+        <v>11.59460675594497</v>
+      </c>
+      <c r="W80">
+        <v>20.7085104485598</v>
       </c>
     </row>
     <row r="81" spans="1:23">
@@ -6761,70 +6773,70 @@
         <v>102</v>
       </c>
       <c r="B81" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C81" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="D81" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E81">
-        <v>55.63999938964844</v>
+        <v>175.4600067138672</v>
       </c>
       <c r="F81">
-        <v>5470663.333333333</v>
+        <v>911975.9333333333</v>
       </c>
       <c r="G81">
-        <v>48.80939979553223</v>
+        <v>157.0382005310059</v>
       </c>
       <c r="H81">
-        <v>43.43506655375162</v>
+        <v>148.1705331420899</v>
       </c>
       <c r="I81">
-        <v>42.25834993362427</v>
+        <v>142.7805499649048</v>
       </c>
       <c r="J81">
-        <v>40.83654996871948</v>
+        <v>138.0801998901367</v>
       </c>
       <c r="K81">
-        <v>11.99751472473145</v>
+        <v>3.140000104904175</v>
       </c>
       <c r="L81">
-        <v>60.77000045776367</v>
+        <v>183.1000061035156</v>
       </c>
       <c r="M81">
-        <v>134.794220677352</v>
+        <v>129.8066822040929</v>
       </c>
       <c r="N81">
-        <v>0.33</v>
+        <v>3.95</v>
       </c>
       <c r="O81">
-        <v>0.84</v>
+        <v>4.3</v>
       </c>
       <c r="P81">
-        <v>0.79</v>
+        <v>3.9</v>
       </c>
       <c r="Q81">
-        <v>245000000</v>
+        <v>3.48</v>
       </c>
       <c r="R81">
-        <v>614000000</v>
+        <v>239602000</v>
       </c>
       <c r="S81">
-        <v>583000000</v>
+        <v>218920000</v>
       </c>
       <c r="T81">
-        <v>0.9910602321912545</v>
+        <v>197100000</v>
       </c>
       <c r="U81">
-        <v>2.452174607612125</v>
+        <v>860471000</v>
       </c>
       <c r="V81">
-        <v>2.786540483701367</v>
-      </c>
-      <c r="W81" t="s">
-        <v>232</v>
+        <v>4.399663894926033</v>
+      </c>
+      <c r="W81">
+        <v>3.938476860818776</v>
       </c>
     </row>
     <row r="82" spans="1:23">
@@ -6835,209 +6847,67 @@
         <v>108</v>
       </c>
       <c r="C82" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="D82" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E82">
-        <v>95.93000030517578</v>
+        <v>21.3799991607666</v>
       </c>
       <c r="F82">
-        <v>2107956.666666667</v>
+        <v>743574.5333333333</v>
       </c>
       <c r="G82">
-        <v>85.92719985961914</v>
+        <v>20.12559993743896</v>
       </c>
       <c r="H82">
-        <v>82.81653312683106</v>
+        <v>17.88173329671224</v>
       </c>
       <c r="I82">
-        <v>76.20924982070923</v>
+        <v>16.20729998111725</v>
       </c>
       <c r="J82">
-        <v>72.33259983062744</v>
+        <v>15.33244999885559</v>
       </c>
       <c r="K82">
-        <v>0.8958330154418945</v>
+        <v>9.220000267028809</v>
       </c>
       <c r="L82">
-        <v>96.06999969482422</v>
+        <v>22.13999938964844</v>
       </c>
       <c r="M82">
-        <v>134.6267962054363</v>
+        <v>129.4868683213205</v>
       </c>
       <c r="N82">
-        <v>0.33</v>
+        <v>-0.01</v>
       </c>
       <c r="O82">
-        <v>0.37</v>
+        <v>0.12</v>
       </c>
       <c r="P82">
-        <v>0.4</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q82">
-        <v>46359000</v>
+        <v>0.14</v>
       </c>
       <c r="R82">
-        <v>51913000</v>
+        <v>24732000</v>
       </c>
       <c r="S82">
-        <v>55923000</v>
+        <v>13726000</v>
       </c>
       <c r="T82">
-        <v>26.87338051927726</v>
+        <v>27460000</v>
       </c>
       <c r="U82">
-        <v>29.50272789270289</v>
+        <v>-1793000</v>
       </c>
       <c r="V82">
-        <v>30.34181541967338</v>
-      </c>
-      <c r="W82" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="83" spans="1:23">
-      <c r="A83" t="s">
-        <v>104</v>
-      </c>
-      <c r="B83" t="s">
-        <v>108</v>
-      </c>
-      <c r="C83" t="s">
-        <v>123</v>
-      </c>
-      <c r="D83" t="s">
-        <v>230</v>
-      </c>
-      <c r="E83">
-        <v>448.8399963378906</v>
-      </c>
-      <c r="F83">
-        <v>1115740</v>
-      </c>
-      <c r="G83">
-        <v>418.7655987548828</v>
-      </c>
-      <c r="H83">
-        <v>376.5837996419271</v>
-      </c>
-      <c r="I83">
-        <v>359.4206999206543</v>
-      </c>
-      <c r="J83">
-        <v>348.8439497375488</v>
-      </c>
-      <c r="K83">
-        <v>5.65625</v>
-      </c>
-      <c r="L83">
-        <v>464.8299865722656</v>
-      </c>
-      <c r="M83">
-        <v>134.4090806296152</v>
-      </c>
-      <c r="N83">
-        <v>0.99</v>
-      </c>
-      <c r="O83">
-        <v>1.75</v>
-      </c>
-      <c r="P83">
-        <v>1.76</v>
-      </c>
-      <c r="Q83">
-        <v>153500000</v>
-      </c>
-      <c r="R83">
-        <v>271536000</v>
-      </c>
-      <c r="S83">
-        <v>272910000</v>
-      </c>
-      <c r="T83">
-        <v>11.95211057921407</v>
-      </c>
-      <c r="U83">
-        <v>19.94622945039447</v>
-      </c>
-      <c r="V83">
-        <v>19.565362333075</v>
-      </c>
-      <c r="W83" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="84" spans="1:23">
-      <c r="A84" t="s">
-        <v>105</v>
-      </c>
-      <c r="B84" t="s">
-        <v>108</v>
-      </c>
-      <c r="C84" t="s">
-        <v>123</v>
-      </c>
-      <c r="D84" t="s">
-        <v>231</v>
-      </c>
-      <c r="E84">
-        <v>117.4499969482422</v>
-      </c>
-      <c r="F84">
-        <v>13440563.33333333</v>
-      </c>
-      <c r="G84">
-        <v>108.7793994140625</v>
-      </c>
-      <c r="H84">
-        <v>94.81819981892903</v>
-      </c>
-      <c r="I84">
-        <v>89.36144981384277</v>
-      </c>
-      <c r="J84">
-        <v>84.72770004272461</v>
-      </c>
-      <c r="K84">
-        <v>0.03513695672154427</v>
-      </c>
-      <c r="L84">
-        <v>126.5500030517578</v>
-      </c>
-      <c r="M84">
-        <v>134.2835236400988</v>
-      </c>
-      <c r="N84">
-        <v>0.63</v>
-      </c>
-      <c r="O84">
-        <v>0.68</v>
-      </c>
-      <c r="P84">
-        <v>1.19</v>
-      </c>
-      <c r="Q84">
-        <v>1741000000</v>
-      </c>
-      <c r="R84">
-        <v>1895000000</v>
-      </c>
-      <c r="S84">
-        <v>3319000000</v>
-      </c>
-      <c r="T84">
-        <v>14.18329938900204</v>
-      </c>
-      <c r="U84">
-        <v>15.28472334247459</v>
-      </c>
-      <c r="V84">
-        <v>23.98641323986413</v>
-      </c>
-      <c r="W84" t="s">
-        <v>233</v>
+        <v>4.982463067683896</v>
+      </c>
+      <c r="W82">
+        <v>2.904020903195777</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/ScreenResult/ScreenResult.xlsx
+++ b/Screener/ScreenResult/ScreenResult.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="269">
   <si>
     <t>Symbol</t>
   </si>
@@ -85,276 +85,282 @@
     <t>EDTX</t>
   </si>
   <si>
+    <t>AURC</t>
+  </si>
+  <si>
     <t>SMCI</t>
   </si>
   <si>
     <t>INOD</t>
   </si>
   <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>RXST</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>RXDX</t>
+  </si>
+  <si>
     <t>NVDA</t>
   </si>
   <si>
-    <t>RXDX</t>
-  </si>
-  <si>
-    <t>RXST</t>
-  </si>
-  <si>
     <t>IOT</t>
   </si>
   <si>
-    <t>CBAY</t>
+    <t>LI</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>ACLS</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>MHO</t>
   </si>
   <si>
     <t>AMPH</t>
   </si>
   <si>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>ROIV</t>
+  </si>
+  <si>
+    <t>AEHR</t>
+  </si>
+  <si>
+    <t>IAS</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>TTD</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>ELF</t>
+  </si>
+  <si>
     <t>MOD</t>
   </si>
   <si>
-    <t>VRT</t>
-  </si>
-  <si>
-    <t>ELF</t>
-  </si>
-  <si>
-    <t>XPO</t>
-  </si>
-  <si>
-    <t>IAS</t>
-  </si>
-  <si>
-    <t>AEHR</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>LI</t>
+    <t>COCO</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>UBER</t>
+  </si>
+  <si>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>ABCM</t>
+  </si>
+  <si>
+    <t>NUVL</t>
+  </si>
+  <si>
+    <t>DICE</t>
+  </si>
+  <si>
+    <t>SPOK</t>
+  </si>
+  <si>
+    <t>FLNC</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>DV</t>
+  </si>
+  <si>
+    <t>STVN</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>BCC</t>
   </si>
   <si>
     <t>RDNT</t>
   </si>
   <si>
-    <t>STRL</t>
-  </si>
-  <si>
-    <t>ACLS</t>
-  </si>
-  <si>
-    <t>STVN</t>
-  </si>
-  <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>FLNC</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>DV</t>
-  </si>
-  <si>
-    <t>ABCM</t>
-  </si>
-  <si>
-    <t>TTD</t>
-  </si>
-  <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>DICE</t>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>KRYS</t>
+  </si>
+  <si>
+    <t>NYCB</t>
+  </si>
+  <si>
+    <t>BECN</t>
+  </si>
+  <si>
+    <t>MATX</t>
+  </si>
+  <si>
+    <t>MTH</t>
+  </si>
+  <si>
+    <t>THO</t>
+  </si>
+  <si>
+    <t>KBH</t>
+  </si>
+  <si>
+    <t>FTAI</t>
   </si>
   <si>
     <t>AVGO</t>
   </si>
   <si>
-    <t>ADBE</t>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>LII</t>
+  </si>
+  <si>
+    <t>ALGM</t>
+  </si>
+  <si>
+    <t>CARR</t>
+  </si>
+  <si>
+    <t>CSAN</t>
+  </si>
+  <si>
+    <t>ONTO</t>
+  </si>
+  <si>
+    <t>CRS</t>
+  </si>
+  <si>
+    <t>LEGN</t>
+  </si>
+  <si>
+    <t>CLBR</t>
+  </si>
+  <si>
+    <t>BUR</t>
+  </si>
+  <si>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>TOL</t>
+  </si>
+  <si>
+    <t>MDC</t>
+  </si>
+  <si>
+    <t>IGT</t>
+  </si>
+  <si>
+    <t>ZGN</t>
+  </si>
+  <si>
+    <t>TMDX</t>
+  </si>
+  <si>
+    <t>LRCX</t>
+  </si>
+  <si>
+    <t>ARCB</t>
+  </si>
+  <si>
+    <t>CCJ</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>IDCC</t>
+  </si>
+  <si>
+    <t>TPH</t>
+  </si>
+  <si>
+    <t>EME</t>
+  </si>
+  <si>
+    <t>APG</t>
+  </si>
+  <si>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>AGRO</t>
+  </si>
+  <si>
+    <t>ERII</t>
+  </si>
+  <si>
+    <t>AEL</t>
   </si>
   <si>
     <t>JBL</t>
   </si>
   <si>
-    <t>KBH</t>
-  </si>
-  <si>
-    <t>PHM</t>
-  </si>
-  <si>
-    <t>GKOS</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>PANW</t>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>TMHC</t>
+  </si>
+  <si>
+    <t>CRH</t>
+  </si>
+  <si>
+    <t>PNR</t>
+  </si>
+  <si>
+    <t>TNET</t>
+  </si>
+  <si>
+    <t>ODFL</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>NTES</t>
   </si>
   <si>
     <t>ARGX</t>
   </si>
   <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>BECN</t>
-  </si>
-  <si>
-    <t>TMHC</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>TOL</t>
-  </si>
-  <si>
-    <t>CLBR</t>
-  </si>
-  <si>
-    <t>IDCC</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>TPH</t>
-  </si>
-  <si>
-    <t>ROIV</t>
-  </si>
-  <si>
-    <t>ALGM</t>
-  </si>
-  <si>
-    <t>MRUS</t>
-  </si>
-  <si>
-    <t>CELH</t>
-  </si>
-  <si>
-    <t>MTH</t>
-  </si>
-  <si>
-    <t>TGLS</t>
-  </si>
-  <si>
-    <t>KRYS</t>
-  </si>
-  <si>
-    <t>OC</t>
-  </si>
-  <si>
-    <t>PFSI</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>APG</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>TMDX</t>
-  </si>
-  <si>
-    <t>ENS</t>
-  </si>
-  <si>
-    <t>VMW</t>
-  </si>
-  <si>
-    <t>CPA</t>
-  </si>
-  <si>
-    <t>DHI</t>
-  </si>
-  <si>
-    <t>DECK</t>
-  </si>
-  <si>
-    <t>LEGN</t>
-  </si>
-  <si>
-    <t>CSAN</t>
-  </si>
-  <si>
-    <t>AGRO</t>
-  </si>
-  <si>
-    <t>ERII</t>
-  </si>
-  <si>
-    <t>ABR</t>
-  </si>
-  <si>
-    <t>THO</t>
-  </si>
-  <si>
-    <t>EXP</t>
-  </si>
-  <si>
-    <t>IGT</t>
-  </si>
-  <si>
-    <t>HUBB</t>
-  </si>
-  <si>
-    <t>ATKR</t>
-  </si>
-  <si>
-    <t>RYI</t>
-  </si>
-  <si>
-    <t>APAM</t>
-  </si>
-  <si>
-    <t>ALSN</t>
-  </si>
-  <si>
-    <t>ORCL</t>
-  </si>
-  <si>
-    <t>NUVL</t>
-  </si>
-  <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>ARCB</t>
-  </si>
-  <si>
-    <t>CLH</t>
-  </si>
-  <si>
-    <t>VNT</t>
-  </si>
-  <si>
-    <t>WCC</t>
-  </si>
-  <si>
-    <t>NVT</t>
-  </si>
-  <si>
-    <t>PAG</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>NE</t>
-  </si>
-  <si>
     <t>Financial Services</t>
   </si>
   <si>
@@ -364,30 +370,27 @@
     <t>Healthcare</t>
   </si>
   <si>
+    <t>Basic Materials</t>
+  </si>
+  <si>
     <t>Consumer Cyclical</t>
   </si>
   <si>
     <t>Industrials</t>
   </si>
   <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
     <t>Consumer Defensive</t>
   </si>
   <si>
-    <t>Communication Services</t>
+    <t>Energy</t>
   </si>
   <si>
     <t>Utilities</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>Basic Materials</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
-  </si>
-  <si>
     <t>Shell Companies</t>
   </si>
   <si>
@@ -397,406 +400,421 @@
     <t>Information Technology Services</t>
   </si>
   <si>
+    <t>Biotechnology</t>
+  </si>
+  <si>
+    <t>Medical Devices</t>
+  </si>
+  <si>
+    <t>Steel</t>
+  </si>
+  <si>
     <t>Semiconductors</t>
   </si>
   <si>
-    <t>Biotechnology</t>
-  </si>
-  <si>
-    <t>Medical Devices</t>
-  </si>
-  <si>
     <t>Software—Infrastructure</t>
   </si>
   <si>
+    <t>Auto Manufacturers</t>
+  </si>
+  <si>
+    <t>Semiconductor Equipment &amp; Materials</t>
+  </si>
+  <si>
+    <t>Trucking</t>
+  </si>
+  <si>
+    <t>Building Products &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Residential Construction</t>
+  </si>
+  <si>
     <t>Drug Manufacturers—Specialty &amp; Generic</t>
   </si>
   <si>
+    <t>Electrical Equipment &amp; Parts</t>
+  </si>
+  <si>
+    <t>Advertising Agencies</t>
+  </si>
+  <si>
+    <t>Travel Services</t>
+  </si>
+  <si>
+    <t>Software—Application</t>
+  </si>
+  <si>
+    <t>Household &amp; Personal Products</t>
+  </si>
+  <si>
     <t>Auto Parts</t>
   </si>
   <si>
-    <t>Electrical Equipment &amp; Parts</t>
-  </si>
-  <si>
-    <t>Household &amp; Personal Products</t>
-  </si>
-  <si>
-    <t>Trucking</t>
-  </si>
-  <si>
-    <t>Advertising Agencies</t>
-  </si>
-  <si>
-    <t>Semiconductor Equipment &amp; Materials</t>
-  </si>
-  <si>
-    <t>Building Products &amp; Equipment</t>
-  </si>
-  <si>
-    <t>Residential Construction</t>
-  </si>
-  <si>
-    <t>Auto Manufacturers</t>
+    <t>Beverages—Non-Alcoholic</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Construction</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Equipment &amp; Services</t>
+  </si>
+  <si>
+    <t>Health Information Services</t>
+  </si>
+  <si>
+    <t>Utilities—Renewable</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas E&amp;P</t>
+  </si>
+  <si>
+    <t>Medical Instruments &amp; Supplies</t>
+  </si>
+  <si>
+    <t>Building Materials</t>
   </si>
   <si>
     <t>Diagnostics &amp; Research</t>
   </si>
   <si>
-    <t>Engineering &amp; Construction</t>
-  </si>
-  <si>
-    <t>Medical Instruments &amp; Supplies</t>
-  </si>
-  <si>
-    <t>Utilities—Renewable</t>
-  </si>
-  <si>
-    <t>Travel Services</t>
-  </si>
-  <si>
-    <t>Software—Application</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas E&amp;P</t>
+    <t>Oil &amp; Gas Midstream</t>
+  </si>
+  <si>
+    <t>Banks—Regional</t>
+  </si>
+  <si>
+    <t>Industrial Distribution</t>
+  </si>
+  <si>
+    <t>Marine Shipping</t>
+  </si>
+  <si>
+    <t>Recreational Vehicles</t>
+  </si>
+  <si>
+    <t>Rental &amp; Leasing Services</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Refining &amp; Marketing</t>
+  </si>
+  <si>
+    <t>Metal Fabrication</t>
+  </si>
+  <si>
+    <t>Asset Management</t>
+  </si>
+  <si>
+    <t>Gambling</t>
+  </si>
+  <si>
+    <t>Apparel Manufacturing</t>
+  </si>
+  <si>
+    <t>Uranium</t>
+  </si>
+  <si>
+    <t>Telecom Services</t>
+  </si>
+  <si>
+    <t>Farm Products</t>
+  </si>
+  <si>
+    <t>Pollution &amp; Treatment Controls</t>
+  </si>
+  <si>
+    <t>Insurance—Life</t>
   </si>
   <si>
     <t>Electronic Components</t>
   </si>
   <si>
-    <t>Rental &amp; Leasing Services</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Equipment &amp; Services</t>
-  </si>
-  <si>
-    <t>Insurance—Life</t>
-  </si>
-  <si>
-    <t>Industrial Distribution</t>
-  </si>
-  <si>
-    <t>Building Materials</t>
-  </si>
-  <si>
-    <t>Telecom Services</t>
-  </si>
-  <si>
-    <t>Airlines</t>
-  </si>
-  <si>
-    <t>Beverages—Non-Alcoholic</t>
-  </si>
-  <si>
-    <t>Mortgage Finance</t>
-  </si>
-  <si>
-    <t>Footwear &amp; Accessories</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Refining &amp; Marketing</t>
-  </si>
-  <si>
-    <t>Farm Products</t>
-  </si>
-  <si>
-    <t>Pollution &amp; Treatment Controls</t>
-  </si>
-  <si>
-    <t>REIT—Mortgage</t>
-  </si>
-  <si>
-    <t>Recreational Vehicles</t>
-  </si>
-  <si>
-    <t>Gambling</t>
-  </si>
-  <si>
-    <t>Metal Fabrication</t>
-  </si>
-  <si>
-    <t>Asset Management</t>
-  </si>
-  <si>
-    <t>Waste Management</t>
-  </si>
-  <si>
-    <t>Scientific &amp; Technical Instruments</t>
-  </si>
-  <si>
     <t>Auto &amp; Truck Dealerships</t>
   </si>
   <si>
+    <t>Specialty Industrial Machinery</t>
+  </si>
+  <si>
+    <t>Staffing &amp; Employment Services</t>
+  </si>
+  <si>
     <t>Oil &amp; Gas Drilling</t>
   </si>
   <si>
+    <t>Electronic Gaming &amp; Multimedia</t>
+  </si>
+  <si>
     <t>2021-01-04</t>
   </si>
   <si>
+    <t>2021-04-30</t>
+  </si>
+  <si>
     <t>2007-03-29</t>
   </si>
   <si>
     <t>1993-08-10</t>
   </si>
   <si>
+    <t>2014-02-03</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>1994-10-14</t>
+  </si>
+  <si>
+    <t>2021-03-12</t>
+  </si>
+  <si>
     <t>1999-01-22</t>
   </si>
   <si>
-    <t>2021-03-12</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
     <t>2021-12-15</t>
   </si>
   <si>
-    <t>2014-02-03</t>
+    <t>2020-07-30</t>
+  </si>
+  <si>
+    <t>2000-07-28</t>
+  </si>
+  <si>
+    <t>2003-10-07</t>
+  </si>
+  <si>
+    <t>2000-07-11</t>
+  </si>
+  <si>
+    <t>2005-06-28</t>
+  </si>
+  <si>
+    <t>1993-11-03</t>
   </si>
   <si>
     <t>2014-06-25</t>
   </si>
   <si>
+    <t>2018-08-02</t>
+  </si>
+  <si>
+    <t>2020-12-08</t>
+  </si>
+  <si>
+    <t>1997-08-15</t>
+  </si>
+  <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
+    <t>1993-04-28</t>
+  </si>
+  <si>
+    <t>2016-09-21</t>
+  </si>
+  <si>
+    <t>2002-09-11</t>
+  </si>
+  <si>
+    <t>2016-09-22</t>
+  </si>
+  <si>
     <t>1982-09-20</t>
   </si>
   <si>
-    <t>2018-08-02</t>
-  </si>
-  <si>
-    <t>2016-09-22</t>
-  </si>
-  <si>
-    <t>2003-10-07</t>
-  </si>
-  <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
-    <t>1997-08-15</t>
-  </si>
-  <si>
-    <t>2005-06-28</t>
-  </si>
-  <si>
-    <t>1993-11-03</t>
-  </si>
-  <si>
-    <t>2020-07-30</t>
+    <t>2021-10-21</t>
+  </si>
+  <si>
+    <t>1991-07-12</t>
+  </si>
+  <si>
+    <t>2019-05-10</t>
+  </si>
+  <si>
+    <t>1980-03-17</t>
+  </si>
+  <si>
+    <t>2015-06-25</t>
+  </si>
+  <si>
+    <t>2020-10-22</t>
+  </si>
+  <si>
+    <t>2021-07-29</t>
+  </si>
+  <si>
+    <t>2021-09-15</t>
+  </si>
+  <si>
+    <t>2004-11-17</t>
+  </si>
+  <si>
+    <t>2021-10-28</t>
+  </si>
+  <si>
+    <t>2019-07-26</t>
+  </si>
+  <si>
+    <t>2021-07-28</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>2021-07-16</t>
+  </si>
+  <si>
+    <t>1986-08-13</t>
+  </si>
+  <si>
+    <t>2013-02-06</t>
   </si>
   <si>
     <t>1997-01-03</t>
   </si>
   <si>
-    <t>1991-07-12</t>
-  </si>
-  <si>
-    <t>2000-07-11</t>
-  </si>
-  <si>
-    <t>2021-07-16</t>
-  </si>
-  <si>
-    <t>2002-09-11</t>
-  </si>
-  <si>
-    <t>2021-10-28</t>
-  </si>
-  <si>
-    <t>1993-04-28</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>2020-10-22</t>
-  </si>
-  <si>
-    <t>2016-09-21</t>
-  </si>
-  <si>
-    <t>2019-07-26</t>
-  </si>
-  <si>
-    <t>2021-09-15</t>
+    <t>2006-11-01</t>
+  </si>
+  <si>
+    <t>2014-05-08</t>
+  </si>
+  <si>
+    <t>2017-09-20</t>
+  </si>
+  <si>
+    <t>1993-11-23</t>
+  </si>
+  <si>
+    <t>2004-09-23</t>
+  </si>
+  <si>
+    <t>1973-05-03</t>
+  </si>
+  <si>
+    <t>1988-07-26</t>
+  </si>
+  <si>
+    <t>1984-01-10</t>
+  </si>
+  <si>
+    <t>1986-08-01</t>
+  </si>
+  <si>
+    <t>2015-05-14</t>
   </si>
   <si>
     <t>2009-08-06</t>
   </si>
   <si>
-    <t>1986-08-13</t>
+    <t>2000-05-02</t>
+  </si>
+  <si>
+    <t>1999-07-29</t>
+  </si>
+  <si>
+    <t>2020-10-29</t>
+  </si>
+  <si>
+    <t>2020-03-19</t>
+  </si>
+  <si>
+    <t>2021-03-08</t>
+  </si>
+  <si>
+    <t>2019-10-28</t>
+  </si>
+  <si>
+    <t>1973-02-21</t>
+  </si>
+  <si>
+    <t>2020-06-05</t>
+  </si>
+  <si>
+    <t>2021-07-07</t>
+  </si>
+  <si>
+    <t>2020-10-19</t>
+  </si>
+  <si>
+    <t>2007-01-22</t>
+  </si>
+  <si>
+    <t>1986-07-08</t>
+  </si>
+  <si>
+    <t>1980-03-11</t>
+  </si>
+  <si>
+    <t>1990-03-26</t>
+  </si>
+  <si>
+    <t>2021-12-20</t>
+  </si>
+  <si>
+    <t>2019-05-02</t>
+  </si>
+  <si>
+    <t>1984-05-04</t>
+  </si>
+  <si>
+    <t>1992-05-13</t>
+  </si>
+  <si>
+    <t>1996-03-14</t>
+  </si>
+  <si>
+    <t>2012-07-20</t>
+  </si>
+  <si>
+    <t>1981-11-12</t>
+  </si>
+  <si>
+    <t>2013-01-31</t>
+  </si>
+  <si>
+    <t>1995-01-10</t>
+  </si>
+  <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>2011-01-28</t>
+  </si>
+  <si>
+    <t>2008-07-02</t>
+  </si>
+  <si>
+    <t>2003-12-04</t>
   </si>
   <si>
     <t>1993-05-03</t>
   </si>
   <si>
-    <t>1986-08-01</t>
-  </si>
-  <si>
-    <t>1980-03-17</t>
-  </si>
-  <si>
-    <t>2015-06-25</t>
-  </si>
-  <si>
-    <t>2015-05-14</t>
-  </si>
-  <si>
-    <t>2012-07-20</t>
+    <t>1996-12-18</t>
+  </si>
+  <si>
+    <t>2013-04-10</t>
+  </si>
+  <si>
+    <t>1989-07-13</t>
+  </si>
+  <si>
+    <t>2014-03-27</t>
+  </si>
+  <si>
+    <t>1991-10-24</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>2000-06-30</t>
   </si>
   <si>
     <t>2017-05-18</t>
-  </si>
-  <si>
-    <t>2003-12-04</t>
-  </si>
-  <si>
-    <t>2004-09-23</t>
-  </si>
-  <si>
-    <t>2013-04-10</t>
-  </si>
-  <si>
-    <t>2013-02-06</t>
-  </si>
-  <si>
-    <t>1986-07-08</t>
-  </si>
-  <si>
-    <t>2021-07-07</t>
-  </si>
-  <si>
-    <t>1981-11-12</t>
-  </si>
-  <si>
-    <t>2007-05-03</t>
-  </si>
-  <si>
-    <t>2013-01-31</t>
-  </si>
-  <si>
-    <t>2020-12-08</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>2016-05-19</t>
-  </si>
-  <si>
-    <t>2007-01-22</t>
-  </si>
-  <si>
-    <t>1988-07-26</t>
-  </si>
-  <si>
-    <t>2012-05-10</t>
-  </si>
-  <si>
-    <t>2017-09-20</t>
-  </si>
-  <si>
-    <t>2006-11-01</t>
-  </si>
-  <si>
-    <t>2013-05-09</t>
-  </si>
-  <si>
-    <t>1998-04-23</t>
-  </si>
-  <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>2019-05-02</t>
-  </si>
-  <si>
-    <t>2004-08-02</t>
-  </si>
-  <si>
-    <t>2007-08-15</t>
-  </si>
-  <si>
-    <t>2005-12-15</t>
-  </si>
-  <si>
-    <t>1992-06-05</t>
-  </si>
-  <si>
-    <t>1993-10-15</t>
-  </si>
-  <si>
-    <t>2020-06-05</t>
-  </si>
-  <si>
-    <t>2021-03-08</t>
-  </si>
-  <si>
-    <t>2011-01-28</t>
-  </si>
-  <si>
-    <t>2008-07-02</t>
-  </si>
-  <si>
-    <t>2004-04-07</t>
-  </si>
-  <si>
-    <t>1984-01-10</t>
-  </si>
-  <si>
-    <t>1994-04-12</t>
-  </si>
-  <si>
-    <t>1990-03-26</t>
-  </si>
-  <si>
-    <t>1972-06-05</t>
-  </si>
-  <si>
-    <t>2016-06-10</t>
-  </si>
-  <si>
-    <t>2014-08-08</t>
-  </si>
-  <si>
-    <t>2013-03-07</t>
-  </si>
-  <si>
-    <t>2012-03-15</t>
-  </si>
-  <si>
-    <t>1986-03-12</t>
-  </si>
-  <si>
-    <t>2021-07-29</t>
-  </si>
-  <si>
-    <t>2009-11-18</t>
-  </si>
-  <si>
-    <t>1992-05-13</t>
-  </si>
-  <si>
-    <t>1987-11-24</t>
-  </si>
-  <si>
-    <t>2020-09-24</t>
-  </si>
-  <si>
-    <t>1999-05-12</t>
-  </si>
-  <si>
-    <t>2018-04-24</t>
-  </si>
-  <si>
-    <t>1996-10-23</t>
-  </si>
-  <si>
-    <t>2012-06-29</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
   </si>
   <si>
     <t>F</t>
@@ -1160,7 +1178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V92"/>
+  <dimension ref="A1:V94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
@@ -1236,31 +1254,31 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E2">
         <v>63.2400016784668</v>
       </c>
       <c r="F2">
-        <v>427963.3333333333</v>
+        <v>254533.3333333333</v>
       </c>
       <c r="G2">
-        <v>20.46354022979736</v>
+        <v>26.76828042984009</v>
       </c>
       <c r="H2">
-        <v>13.92808013280233</v>
+        <v>16.05221351623535</v>
       </c>
       <c r="I2">
-        <v>13.0273650932312</v>
+        <v>14.61806515693664</v>
       </c>
       <c r="J2">
-        <v>10.92269002914429</v>
+        <v>11.05911502838135</v>
       </c>
       <c r="K2">
         <v>9.739999771118164</v>
@@ -1269,7 +1287,7 @@
         <v>63.2400016784668</v>
       </c>
       <c r="M2">
-        <v>594.6581873627458</v>
+        <v>581.5698777251038</v>
       </c>
       <c r="N2">
         <v>0.002796</v>
@@ -1296,7 +1314,7 @@
         <v>4563809</v>
       </c>
       <c r="V2" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -1304,67 +1322,67 @@
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C3" t="s">
         <v>125</v>
       </c>
       <c r="D3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E3">
-        <v>303.1499938964844</v>
+        <v>46.0099983215332</v>
       </c>
       <c r="F3">
-        <v>3017206.666666667</v>
+        <v>462473.3333333333</v>
       </c>
       <c r="G3">
-        <v>228.8364001464844</v>
+        <v>12.63671977996826</v>
       </c>
       <c r="H3">
-        <v>139.465533396403</v>
+        <v>10.97828661600749</v>
       </c>
       <c r="I3">
-        <v>123.3530500030518</v>
+        <v>10.72397996902466</v>
       </c>
       <c r="J3">
-        <v>102.610149974823</v>
+        <v>10.10458000183105</v>
       </c>
       <c r="K3">
-        <v>3.849999904632568</v>
+        <v>9.789999961853027</v>
       </c>
       <c r="L3">
-        <v>318.3999938964844</v>
+        <v>46.0099983215332</v>
       </c>
       <c r="M3">
-        <v>280.5909856384841</v>
+        <v>453.6179757064314</v>
       </c>
       <c r="N3">
-        <v>2.6</v>
+        <v>-0.01</v>
       </c>
       <c r="O3">
-        <v>3.35</v>
+        <v>0.05</v>
       </c>
       <c r="P3">
-        <v>3.14</v>
+        <v>-0.03</v>
       </c>
       <c r="Q3">
-        <v>1.53</v>
+        <v>-0.01</v>
       </c>
       <c r="R3">
-        <v>184416000</v>
+        <v>4245973</v>
       </c>
       <c r="S3">
-        <v>176167000</v>
+        <v>6905230</v>
       </c>
       <c r="T3">
-        <v>85846000</v>
+        <v>-127955</v>
       </c>
       <c r="U3">
-        <v>578377000</v>
+        <v>8735542</v>
       </c>
       <c r="V3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -1372,67 +1390,67 @@
         <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s">
         <v>126</v>
       </c>
       <c r="D4" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E4">
-        <v>11.75</v>
+        <v>330.2699890136719</v>
       </c>
       <c r="F4">
-        <v>718776.6666666666</v>
+        <v>2863040</v>
       </c>
       <c r="G4">
-        <v>10.78460000038147</v>
+        <v>250.7761999511719</v>
       </c>
       <c r="H4">
-        <v>7.469266668955485</v>
+        <v>149.0879998270671</v>
       </c>
       <c r="I4">
-        <v>6.412649999856949</v>
+        <v>131.2884498405457</v>
       </c>
       <c r="J4">
-        <v>5.603400018215179</v>
+        <v>107.5752499008179</v>
       </c>
       <c r="K4">
-        <v>0.09375</v>
+        <v>3.849999904632568</v>
       </c>
       <c r="L4">
-        <v>13.5</v>
+        <v>334.5</v>
       </c>
       <c r="M4">
-        <v>219.2488041077693</v>
+        <v>280.4146651000763</v>
       </c>
       <c r="N4">
-        <v>-0.14</v>
+        <v>2.6</v>
       </c>
       <c r="O4">
-        <v>-0.12</v>
+        <v>3.35</v>
       </c>
       <c r="P4">
-        <v>-0.07000000000000001</v>
+        <v>3.14</v>
       </c>
       <c r="Q4">
-        <v>-0.08</v>
+        <v>1.53</v>
       </c>
       <c r="R4">
-        <v>-3327000</v>
+        <v>184416000</v>
       </c>
       <c r="S4">
-        <v>-1960000</v>
+        <v>176167000</v>
       </c>
       <c r="T4">
-        <v>-2116000</v>
+        <v>85846000</v>
       </c>
       <c r="U4">
-        <v>-11935000</v>
+        <v>578377000</v>
       </c>
       <c r="V4" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -1440,67 +1458,67 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
         <v>127</v>
       </c>
       <c r="D5" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E5">
-        <v>443.0899963378906</v>
+        <v>12.82999992370605</v>
       </c>
       <c r="F5">
-        <v>48931930</v>
+        <v>674073.3333333334</v>
       </c>
       <c r="G5">
-        <v>392.7569287109375</v>
+        <v>11.19279998779297</v>
       </c>
       <c r="H5">
-        <v>280.5200569661458</v>
+        <v>7.834866666793824</v>
       </c>
       <c r="I5">
-        <v>246.5452746582031</v>
+        <v>6.673949999809265</v>
       </c>
       <c r="J5">
-        <v>216.1633061218262</v>
+        <v>5.834350011348724</v>
       </c>
       <c r="K5">
-        <v>0.3130019009113312</v>
+        <v>0.09375</v>
       </c>
       <c r="L5">
-        <v>474.9400024414062</v>
+        <v>13.5</v>
       </c>
       <c r="M5">
-        <v>195.5101448557973</v>
+        <v>239.0767061813042</v>
       </c>
       <c r="N5">
-        <v>0.26</v>
+        <v>-0.14</v>
       </c>
       <c r="O5">
-        <v>0.27</v>
+        <v>-0.12</v>
       </c>
       <c r="P5">
-        <v>0.57</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Q5">
-        <v>0.82</v>
+        <v>-0.08</v>
       </c>
       <c r="R5">
-        <v>680000000</v>
+        <v>-3327000</v>
       </c>
       <c r="S5">
-        <v>1414000000</v>
+        <v>-1960000</v>
       </c>
       <c r="T5">
-        <v>2043000000</v>
+        <v>-2116000</v>
       </c>
       <c r="U5">
-        <v>4368000000</v>
+        <v>-11935000</v>
       </c>
       <c r="V5" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1508,67 +1526,67 @@
         <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C6" t="s">
         <v>128</v>
       </c>
       <c r="D6" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E6">
-        <v>199.9199981689453</v>
+        <v>13.05000019073486</v>
       </c>
       <c r="F6">
-        <v>1081147.333333333</v>
+        <v>2547540</v>
       </c>
       <c r="G6">
-        <v>186.0122996520996</v>
+        <v>9.899000015258789</v>
       </c>
       <c r="H6">
-        <v>129.3656999969483</v>
+        <v>8.927566693623861</v>
       </c>
       <c r="I6">
-        <v>110.3482249641418</v>
+        <v>7.604175020456314</v>
       </c>
       <c r="J6">
-        <v>95.39312496185303</v>
+        <v>6.80387501835823</v>
       </c>
       <c r="K6">
-        <v>16.51000022888184</v>
+        <v>0.9279999732971191</v>
       </c>
       <c r="L6">
-        <v>199.9199981689453</v>
+        <v>15.15999984741211</v>
       </c>
       <c r="M6">
-        <v>190.3591316243511</v>
+        <v>202.5312354104882</v>
       </c>
       <c r="N6">
-        <v>-0.86</v>
+        <v>-0.31</v>
       </c>
       <c r="O6">
-        <v>-0.9</v>
+        <v>-0.28</v>
       </c>
       <c r="P6">
-        <v>-0.9</v>
+        <v>-0.3</v>
       </c>
       <c r="Q6">
-        <v>-0.86</v>
+        <v>-0.29</v>
       </c>
       <c r="R6">
-        <v>-37275000</v>
+        <v>-105911000</v>
       </c>
       <c r="S6">
-        <v>-38764000</v>
+        <v>-26633000</v>
       </c>
       <c r="T6">
-        <v>-40876000</v>
+        <v>-28778000</v>
       </c>
       <c r="U6">
-        <v>-141752000</v>
+        <v>-106001000</v>
       </c>
       <c r="V6" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1576,40 +1594,40 @@
         <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
         <v>129</v>
       </c>
       <c r="D7" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E7">
-        <v>31.05999946594238</v>
+        <v>33.36999893188477</v>
       </c>
       <c r="F7">
-        <v>469836.6666666667</v>
+        <v>398626.6666666667</v>
       </c>
       <c r="G7">
-        <v>26.97789985656738</v>
+        <v>28.10849990844726</v>
       </c>
       <c r="H7">
-        <v>18.85183330535889</v>
+        <v>19.67496662775676</v>
       </c>
       <c r="I7">
-        <v>17.20297497272491</v>
+        <v>17.83387496948242</v>
       </c>
       <c r="J7">
-        <v>15.48982499599457</v>
+        <v>15.88287498950958</v>
       </c>
       <c r="K7">
         <v>8.970000267028809</v>
       </c>
       <c r="L7">
-        <v>32.77000045776367</v>
+        <v>33.36999893188477</v>
       </c>
       <c r="M7">
-        <v>180.2701622626164</v>
+        <v>199.3021960308955</v>
       </c>
       <c r="N7">
         <v>-0.61</v>
@@ -1636,7 +1654,7 @@
         <v>-66756000</v>
       </c>
       <c r="V7" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1644,67 +1662,67 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
         <v>130</v>
       </c>
       <c r="D8" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E8">
-        <v>27.07999992370605</v>
+        <v>125.4899978637695</v>
       </c>
       <c r="F8">
-        <v>3588116.666666667</v>
+        <v>505070</v>
       </c>
       <c r="G8">
-        <v>25.03399990081787</v>
+        <v>82.79600006103516</v>
       </c>
       <c r="H8">
-        <v>19.27286664962769</v>
+        <v>70.69606661478679</v>
       </c>
       <c r="I8">
-        <v>17.23649998664856</v>
+        <v>65.59124990463256</v>
       </c>
       <c r="J8">
-        <v>15.76159998893738</v>
+        <v>59.89694986343384</v>
       </c>
       <c r="K8">
-        <v>8.699999809265137</v>
+        <v>5.792013168334961</v>
       </c>
       <c r="L8">
-        <v>30.6299991607666</v>
+        <v>132.4752044677734</v>
       </c>
       <c r="M8">
-        <v>179.5037574449794</v>
+        <v>198.2365190893374</v>
       </c>
       <c r="N8">
-        <v>-0.13</v>
+        <v>2394.25</v>
       </c>
       <c r="O8">
-        <v>-0.11</v>
+        <v>4830.25</v>
       </c>
       <c r="P8">
-        <v>-0.1</v>
+        <v>1680.75</v>
       </c>
       <c r="Q8">
-        <v>-0.13</v>
+        <v>2394.25</v>
       </c>
       <c r="R8">
-        <v>-58555000</v>
+        <v>509914000000</v>
       </c>
       <c r="S8">
-        <v>-53598000</v>
+        <v>-665869000000</v>
       </c>
       <c r="T8">
-        <v>-67856000</v>
+        <v>726419000000</v>
       </c>
       <c r="U8">
-        <v>-247422000</v>
+        <v>3144087000000</v>
       </c>
       <c r="V8" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1712,67 +1730,67 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C9" t="s">
         <v>128</v>
       </c>
       <c r="D9" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E9">
-        <v>11.57999992370605</v>
+        <v>199.9199981689453</v>
       </c>
       <c r="F9">
-        <v>2432943.333333333</v>
+        <v>1081147.333333333</v>
       </c>
       <c r="G9">
-        <v>9.661700019836426</v>
+        <v>186.0122996520996</v>
       </c>
       <c r="H9">
-        <v>8.626566692988078</v>
+        <v>129.3656999969483</v>
       </c>
       <c r="I9">
-        <v>7.34562502026558</v>
+        <v>110.3482249641418</v>
       </c>
       <c r="J9">
-        <v>6.664025020599365</v>
+        <v>95.39312496185303</v>
       </c>
       <c r="K9">
-        <v>0.9279999732971191</v>
+        <v>16.51000022888184</v>
       </c>
       <c r="L9">
-        <v>15.15999984741211</v>
+        <v>199.9199981689453</v>
       </c>
       <c r="M9">
-        <v>175.4941320170654</v>
+        <v>196.7962603205521</v>
       </c>
       <c r="N9">
-        <v>-0.31</v>
+        <v>-0.86</v>
       </c>
       <c r="O9">
-        <v>-0.28</v>
+        <v>-0.9</v>
       </c>
       <c r="P9">
-        <v>-0.3</v>
+        <v>-0.9</v>
       </c>
       <c r="Q9">
-        <v>-0.29</v>
+        <v>-0.86</v>
       </c>
       <c r="R9">
-        <v>-105911000</v>
+        <v>-37275000</v>
       </c>
       <c r="S9">
-        <v>-26633000</v>
+        <v>-38764000</v>
       </c>
       <c r="T9">
-        <v>-28778000</v>
+        <v>-40876000</v>
       </c>
       <c r="U9">
-        <v>-106001000</v>
+        <v>-141752000</v>
       </c>
       <c r="V9" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1780,67 +1798,67 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" t="s">
         <v>131</v>
       </c>
       <c r="D10" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E10">
-        <v>61.61999893188477</v>
+        <v>467.2900085449219</v>
       </c>
       <c r="F10">
-        <v>500956.6666666667</v>
+        <v>45517723.33333334</v>
       </c>
       <c r="G10">
-        <v>50.78859962463379</v>
+        <v>412.9652001953125</v>
       </c>
       <c r="H10">
-        <v>39.56519985198975</v>
+        <v>292.2241328938802</v>
       </c>
       <c r="I10">
-        <v>36.96739991188049</v>
+        <v>256.60024974823</v>
       </c>
       <c r="J10">
-        <v>34.0750999546051</v>
+        <v>224.4994998931885</v>
       </c>
       <c r="K10">
-        <v>8.689999580383301</v>
+        <v>0.3134739995002747</v>
       </c>
       <c r="L10">
-        <v>63.25</v>
+        <v>474.9400024414062</v>
       </c>
       <c r="M10">
-        <v>174.8399856620773</v>
+        <v>188.7717042022524</v>
       </c>
       <c r="N10">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="O10">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="P10">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="Q10">
-        <v>0.5</v>
+        <v>0.82</v>
       </c>
       <c r="R10">
-        <v>15874000</v>
+        <v>680000000</v>
       </c>
       <c r="S10">
-        <v>33913000</v>
+        <v>1414000000</v>
       </c>
       <c r="T10">
-        <v>26032000</v>
+        <v>2043000000</v>
       </c>
       <c r="U10">
-        <v>91386000</v>
+        <v>4368000000</v>
       </c>
       <c r="V10" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1854,61 +1872,61 @@
         <v>132</v>
       </c>
       <c r="D11" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E11">
-        <v>36.63000106811523</v>
+        <v>27.94000053405762</v>
       </c>
       <c r="F11">
-        <v>589273.3333333334</v>
+        <v>2995076.666666667</v>
       </c>
       <c r="G11">
-        <v>29.86880016326904</v>
+        <v>25.90059989929199</v>
       </c>
       <c r="H11">
-        <v>24.75853333791097</v>
+        <v>19.83413331985474</v>
       </c>
       <c r="I11">
-        <v>23.13930001735687</v>
+        <v>17.65249998569488</v>
       </c>
       <c r="J11">
-        <v>21.14869999885559</v>
+        <v>16.16999999046326</v>
       </c>
       <c r="K11">
-        <v>0.7788501977920532</v>
+        <v>8.699999809265137</v>
       </c>
       <c r="L11">
-        <v>37.97000122070312</v>
+        <v>30.6299991607666</v>
       </c>
       <c r="M11">
-        <v>170.1413980151002</v>
+        <v>188.549891559784</v>
       </c>
       <c r="N11">
-        <v>0.27</v>
+        <v>-0.13</v>
       </c>
       <c r="O11">
-        <v>0.46</v>
+        <v>-0.11</v>
       </c>
       <c r="P11">
-        <v>0.46</v>
+        <v>-0.1</v>
       </c>
       <c r="Q11">
-        <v>1.69</v>
+        <v>-0.13</v>
       </c>
       <c r="R11">
-        <v>24400000</v>
+        <v>-58555000</v>
       </c>
       <c r="S11">
-        <v>24500000</v>
+        <v>-53598000</v>
       </c>
       <c r="T11">
-        <v>89900000</v>
+        <v>-67856000</v>
       </c>
       <c r="U11">
-        <v>71600000</v>
+        <v>-247422000</v>
       </c>
       <c r="V11" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1916,67 +1934,67 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C12" t="s">
         <v>133</v>
       </c>
       <c r="D12" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E12">
-        <v>25.68000030517578</v>
+        <v>42.79999923706055</v>
       </c>
       <c r="F12">
-        <v>4712500</v>
+        <v>6536786.666666667</v>
       </c>
       <c r="G12">
-        <v>21.48979997634888</v>
+        <v>34.12079998016358</v>
       </c>
       <c r="H12">
-        <v>16.60153333028158</v>
+        <v>27.20136664072673</v>
       </c>
       <c r="I12">
-        <v>15.80892131328583</v>
+        <v>25.05569999217987</v>
       </c>
       <c r="J12">
-        <v>14.45298980236053</v>
+        <v>23.6458499956131</v>
       </c>
       <c r="K12">
-        <v>5.560633659362793</v>
+        <v>13.61999988555908</v>
       </c>
       <c r="L12">
-        <v>28.55718421936035</v>
+        <v>43.95999908447266</v>
       </c>
       <c r="M12">
-        <v>169.7991514246532</v>
+        <v>181.1259662745777</v>
       </c>
       <c r="N12">
-        <v>0.05</v>
+        <v>0.9</v>
       </c>
       <c r="O12">
-        <v>0.06</v>
+        <v>-0.64</v>
       </c>
       <c r="P12">
-        <v>0.07000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="Q12">
-        <v>0.12</v>
+        <v>0.9</v>
       </c>
       <c r="R12">
-        <v>21200000</v>
+        <v>-1640321000</v>
       </c>
       <c r="S12">
-        <v>26600000</v>
+        <v>256938000</v>
       </c>
       <c r="T12">
-        <v>50300000</v>
+        <v>929668000</v>
       </c>
       <c r="U12">
-        <v>76600000</v>
+        <v>-2012215000</v>
       </c>
       <c r="V12" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1984,67 +2002,67 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C13" t="s">
         <v>134</v>
       </c>
       <c r="D13" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E13">
-        <v>111.620002746582</v>
+        <v>47.61000061035156</v>
       </c>
       <c r="F13">
-        <v>974946.6666666666</v>
+        <v>279350</v>
       </c>
       <c r="G13">
-        <v>104.8088000488281</v>
+        <v>34.8135998916626</v>
       </c>
       <c r="H13">
-        <v>82.69559995015462</v>
+        <v>29.11713334401449</v>
       </c>
       <c r="I13">
-        <v>73.95714994430541</v>
+        <v>27.63789999961853</v>
       </c>
       <c r="J13">
-        <v>66.541699924469</v>
+        <v>25.9875</v>
       </c>
       <c r="K13">
-        <v>7.300000190734863</v>
+        <v>0.2220596075057983</v>
       </c>
       <c r="L13">
-        <v>119.5100021362305</v>
+        <v>48.31999969482422</v>
       </c>
       <c r="M13">
-        <v>168.0379970789592</v>
+        <v>175.1066591801561</v>
       </c>
       <c r="N13">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="O13">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
       <c r="P13">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="Q13">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
       <c r="R13">
-        <v>11710000</v>
+        <v>20715000</v>
       </c>
       <c r="S13">
-        <v>19105000</v>
+        <v>21673000</v>
       </c>
       <c r="T13">
-        <v>16246000</v>
+        <v>17245000</v>
       </c>
       <c r="U13">
-        <v>46840000</v>
+        <v>79949000</v>
       </c>
       <c r="V13" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -2052,40 +2070,40 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
         <v>135</v>
       </c>
       <c r="D14" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E14">
-        <v>65.83999633789062</v>
+        <v>69.23999786376953</v>
       </c>
       <c r="F14">
-        <v>2051446.666666667</v>
+        <v>2215236.666666667</v>
       </c>
       <c r="G14">
-        <v>53.29880004882813</v>
+        <v>55.95459999084473</v>
       </c>
       <c r="H14">
-        <v>42.18140008290609</v>
+        <v>43.51686672210693</v>
       </c>
       <c r="I14">
-        <v>40.00347107887268</v>
+        <v>41.2029078578949</v>
       </c>
       <c r="J14">
-        <v>36.84364750862122</v>
+        <v>37.58414888381958</v>
       </c>
       <c r="K14">
         <v>0.6502050161361694</v>
       </c>
       <c r="L14">
-        <v>68.44000244140625</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="M14">
-        <v>166.2590691865597</v>
+        <v>175.0301828025447</v>
       </c>
       <c r="N14">
         <v>1.22</v>
@@ -2112,7 +2130,7 @@
         <v>666000000</v>
       </c>
       <c r="V14" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2120,67 +2138,67 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C15" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D15" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E15">
-        <v>20.31999969482422</v>
+        <v>200.4799957275391</v>
       </c>
       <c r="F15">
-        <v>934533.3333333334</v>
+        <v>517223.3333333333</v>
       </c>
       <c r="G15">
-        <v>18.12500007629394</v>
+        <v>171.173200378418</v>
       </c>
       <c r="H15">
-        <v>14.07686666488647</v>
+        <v>135.3816004435221</v>
       </c>
       <c r="I15">
-        <v>12.66614999055862</v>
+        <v>119.1451003265381</v>
       </c>
       <c r="J15">
-        <v>11.58550000429153</v>
+        <v>107.1865002822876</v>
       </c>
       <c r="K15">
-        <v>6.690000057220459</v>
+        <v>0.6800000071525574</v>
       </c>
       <c r="L15">
-        <v>26.39999961853027</v>
+        <v>200.4799957275391</v>
       </c>
       <c r="M15">
-        <v>166.2453553767382</v>
+        <v>170.2688435410465</v>
       </c>
       <c r="N15">
-        <v>0.01</v>
+        <v>1.32</v>
       </c>
       <c r="O15">
-        <v>0.004895</v>
+        <v>1.21</v>
       </c>
       <c r="P15">
-        <v>0.07000000000000001</v>
+        <v>1.71</v>
       </c>
       <c r="Q15">
-        <v>0.02</v>
+        <v>1.43</v>
       </c>
       <c r="R15">
-        <v>767000</v>
+        <v>40283000</v>
       </c>
       <c r="S15">
-        <v>11487000</v>
+        <v>56992000</v>
       </c>
       <c r="T15">
-        <v>3146000</v>
+        <v>47697000</v>
       </c>
       <c r="U15">
-        <v>15373000</v>
+        <v>183079000</v>
       </c>
       <c r="V15" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -2188,67 +2206,67 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D16" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E16">
-        <v>48.34000015258789</v>
+        <v>144.4299926757812</v>
       </c>
       <c r="F16">
-        <v>1437663.333333333</v>
+        <v>1773470</v>
       </c>
       <c r="G16">
-        <v>38.75679985046386</v>
+        <v>129.753999786377</v>
       </c>
       <c r="H16">
-        <v>32.72879988352458</v>
+        <v>99.90946637471517</v>
       </c>
       <c r="I16">
-        <v>29.91229990005493</v>
+        <v>90.44699979782105</v>
       </c>
       <c r="J16">
-        <v>27.09774991512299</v>
+        <v>82.34769983291626</v>
       </c>
       <c r="K16">
-        <v>0.5</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="L16">
-        <v>52.16999816894531</v>
+        <v>146.4199981689453</v>
       </c>
       <c r="M16">
-        <v>163.2518567240724</v>
+        <v>170.0038695596177</v>
       </c>
       <c r="N16">
-        <v>0.02</v>
+        <v>2.41</v>
       </c>
       <c r="O16">
-        <v>0.13</v>
+        <v>5.75</v>
       </c>
       <c r="P16">
-        <v>0.14</v>
+        <v>4.72</v>
       </c>
       <c r="Q16">
-        <v>0.21</v>
+        <v>2.41</v>
       </c>
       <c r="R16">
-        <v>3725000</v>
+        <v>738007000</v>
       </c>
       <c r="S16">
-        <v>4132000</v>
+        <v>384513000</v>
       </c>
       <c r="T16">
-        <v>6111000</v>
+        <v>333786000</v>
       </c>
       <c r="U16">
-        <v>14240000</v>
+        <v>2749369000</v>
       </c>
       <c r="V16" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2256,67 +2274,67 @@
         <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D17" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E17">
-        <v>138.7299957275391</v>
+        <v>100</v>
       </c>
       <c r="F17">
-        <v>2064546.666666667</v>
+        <v>381440</v>
       </c>
       <c r="G17">
-        <v>126.8625999450684</v>
+        <v>82.0918000793457</v>
       </c>
       <c r="H17">
-        <v>96.9021997833252</v>
+        <v>66.97753339131673</v>
       </c>
       <c r="I17">
-        <v>88.10084987640381</v>
+        <v>60.96090005874634</v>
       </c>
       <c r="J17">
-        <v>80.13499990463256</v>
+        <v>55.79695011138916</v>
       </c>
       <c r="K17">
-        <v>0.8299999833106995</v>
+        <v>3.118403196334839</v>
       </c>
       <c r="L17">
-        <v>146.4199981689453</v>
+        <v>100</v>
       </c>
       <c r="M17">
-        <v>162.7442720400813</v>
+        <v>169.7756640412077</v>
       </c>
       <c r="N17">
-        <v>2.41</v>
+        <v>4.67</v>
       </c>
       <c r="O17">
-        <v>5.75</v>
+        <v>4.65</v>
       </c>
       <c r="P17">
-        <v>4.72</v>
+        <v>3.64</v>
       </c>
       <c r="Q17">
-        <v>2.41</v>
+        <v>4.12</v>
       </c>
       <c r="R17">
-        <v>738007000</v>
+        <v>490662000</v>
       </c>
       <c r="S17">
-        <v>384513000</v>
+        <v>103066000</v>
       </c>
       <c r="T17">
-        <v>333786000</v>
+        <v>118001000</v>
       </c>
       <c r="U17">
-        <v>2749369000</v>
+        <v>501889000</v>
       </c>
       <c r="V17" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -2324,67 +2342,67 @@
         <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D18" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E18">
-        <v>91.22000122070312</v>
+        <v>60.68999862670898</v>
       </c>
       <c r="F18">
-        <v>344403.3333333333</v>
+        <v>451820</v>
       </c>
       <c r="G18">
-        <v>78.86340026855468</v>
+        <v>53.0621997833252</v>
       </c>
       <c r="H18">
-        <v>64.98153345743815</v>
+        <v>40.85613320668539</v>
       </c>
       <c r="I18">
-        <v>59.28370012283325</v>
+        <v>37.94209991455078</v>
       </c>
       <c r="J18">
-        <v>54.50440010070801</v>
+        <v>34.90739994049072</v>
       </c>
       <c r="K18">
-        <v>3.118402242660522</v>
+        <v>8.689999580383301</v>
       </c>
       <c r="L18">
-        <v>93.88999938964844</v>
+        <v>63.25</v>
       </c>
       <c r="M18">
-        <v>158.7937128666052</v>
+        <v>168.407444260123</v>
       </c>
       <c r="N18">
-        <v>4.79</v>
+        <v>0.33</v>
       </c>
       <c r="O18">
-        <v>4.67</v>
+        <v>0.3</v>
       </c>
       <c r="P18">
-        <v>4.65</v>
+        <v>0.66</v>
       </c>
       <c r="Q18">
-        <v>3.64</v>
+        <v>0.5</v>
       </c>
       <c r="R18">
-        <v>131590000</v>
+        <v>15874000</v>
       </c>
       <c r="S18">
-        <v>130395000</v>
+        <v>33913000</v>
       </c>
       <c r="T18">
-        <v>103066000</v>
+        <v>26032000</v>
       </c>
       <c r="U18">
-        <v>490662000</v>
+        <v>91386000</v>
       </c>
       <c r="V18" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -2392,67 +2410,67 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D19" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E19">
-        <v>36.97000122070312</v>
+        <v>26.01000022888184</v>
       </c>
       <c r="F19">
-        <v>6549130</v>
+        <v>4674690</v>
       </c>
       <c r="G19">
-        <v>32.83629989624023</v>
+        <v>22.74159999847412</v>
       </c>
       <c r="H19">
-        <v>26.41576663970947</v>
+        <v>17.1043333307902</v>
       </c>
       <c r="I19">
-        <v>24.49439998149872</v>
+        <v>16.23745000839233</v>
       </c>
       <c r="J19">
-        <v>23.4060999917984</v>
+        <v>14.79835000038147</v>
       </c>
       <c r="K19">
-        <v>13.61999988555908</v>
+        <v>5.564881324768066</v>
       </c>
       <c r="L19">
-        <v>43.95999908447266</v>
+        <v>28.57900047302246</v>
       </c>
       <c r="M19">
-        <v>157.5805582354955</v>
+        <v>162.8174828123756</v>
       </c>
       <c r="N19">
-        <v>0.9</v>
+        <v>0.05</v>
       </c>
       <c r="O19">
-        <v>-0.64</v>
+        <v>0.06</v>
       </c>
       <c r="P19">
-        <v>0.26</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q19">
-        <v>0.9</v>
+        <v>0.12</v>
       </c>
       <c r="R19">
-        <v>-1640321000</v>
+        <v>21200000</v>
       </c>
       <c r="S19">
-        <v>256938000</v>
+        <v>26600000</v>
       </c>
       <c r="T19">
-        <v>929668000</v>
+        <v>50300000</v>
       </c>
       <c r="U19">
-        <v>-2012215000</v>
+        <v>76600000</v>
       </c>
       <c r="V19" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -2460,67 +2478,67 @@
         <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="D20" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E20">
-        <v>34.9900016784668</v>
+        <v>11.97999954223633</v>
       </c>
       <c r="F20">
-        <v>862323.3333333334</v>
+        <v>6916610</v>
       </c>
       <c r="G20">
-        <v>30.81039978027344</v>
+        <v>10.1889999961853</v>
       </c>
       <c r="H20">
-        <v>25.5382332611084</v>
+        <v>8.888399982452393</v>
       </c>
       <c r="I20">
-        <v>23.78567493438721</v>
+        <v>8.048599989414216</v>
       </c>
       <c r="J20">
-        <v>22.53527496337891</v>
+        <v>7.28754998922348</v>
       </c>
       <c r="K20">
-        <v>0.1500000059604645</v>
+        <v>2.809999942779541</v>
       </c>
       <c r="L20">
-        <v>38.15000152587891</v>
+        <v>13.52000045776367</v>
       </c>
       <c r="M20">
-        <v>157.2876128717563</v>
+        <v>161.9594467559942</v>
       </c>
       <c r="N20">
-        <v>0.13</v>
+        <v>-0.48</v>
       </c>
       <c r="O20">
-        <v>0.01</v>
+        <v>-0.42</v>
       </c>
       <c r="P20">
-        <v>-0.02</v>
+        <v>-0.49</v>
       </c>
       <c r="Q20">
-        <v>-0.36</v>
+        <v>-0.05</v>
       </c>
       <c r="R20">
-        <v>668000</v>
+        <v>-291590000</v>
       </c>
       <c r="S20">
-        <v>-934000</v>
+        <v>-352014000</v>
       </c>
       <c r="T20">
-        <v>-21005000</v>
+        <v>-33617000</v>
       </c>
       <c r="U20">
-        <v>10650000</v>
+        <v>-1245475000</v>
       </c>
       <c r="V20" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -2528,67 +2546,67 @@
         <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C21" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D21" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E21">
-        <v>57.95999908447266</v>
+        <v>52.15999984741211</v>
       </c>
       <c r="F21">
-        <v>335010</v>
+        <v>1460763.333333333</v>
       </c>
       <c r="G21">
-        <v>51.68519996643067</v>
+        <v>41.38399997711181</v>
       </c>
       <c r="H21">
-        <v>41.39866666158041</v>
+        <v>33.83793326059977</v>
       </c>
       <c r="I21">
-        <v>38.28505000114441</v>
+        <v>30.96719992637634</v>
       </c>
       <c r="J21">
-        <v>34.90540001869201</v>
+        <v>27.85994991779327</v>
       </c>
       <c r="K21">
-        <v>0.421875</v>
+        <v>0.5</v>
       </c>
       <c r="L21">
-        <v>59.93999862670898</v>
+        <v>52.16999816894531</v>
       </c>
       <c r="M21">
-        <v>156.6337107524481</v>
+        <v>161.7948314334095</v>
       </c>
       <c r="N21">
-        <v>0.86</v>
+        <v>0.02</v>
       </c>
       <c r="O21">
-        <v>0.97</v>
+        <v>0.13</v>
       </c>
       <c r="P21">
-        <v>1.03</v>
+        <v>0.14</v>
       </c>
       <c r="Q21">
-        <v>0.64</v>
+        <v>0.21</v>
       </c>
       <c r="R21">
-        <v>29523000</v>
+        <v>3725000</v>
       </c>
       <c r="S21">
-        <v>31725000</v>
+        <v>4132000</v>
       </c>
       <c r="T21">
-        <v>19649000</v>
+        <v>6111000</v>
       </c>
       <c r="U21">
-        <v>106461000</v>
+        <v>14240000</v>
       </c>
       <c r="V21" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2596,67 +2614,67 @@
         <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C22" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D22" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E22">
-        <v>175.5200042724609</v>
+        <v>20.85000038146973</v>
       </c>
       <c r="F22">
-        <v>532873.3333333334</v>
+        <v>908953.3333333334</v>
       </c>
       <c r="G22">
-        <v>164.4536004638672</v>
+        <v>18.63200008392334</v>
       </c>
       <c r="H22">
-        <v>131.2900005594889</v>
+        <v>14.51826667149862</v>
       </c>
       <c r="I22">
-        <v>115.506800365448</v>
+        <v>13.03574999332428</v>
       </c>
       <c r="J22">
-        <v>103.865700263977</v>
+        <v>11.87699999570847</v>
       </c>
       <c r="K22">
-        <v>0.6800000071525574</v>
+        <v>6.690000057220459</v>
       </c>
       <c r="L22">
-        <v>192.2700042724609</v>
+        <v>26.39999961853027</v>
       </c>
       <c r="M22">
-        <v>155.8126763513131</v>
+        <v>161.4197255402331</v>
       </c>
       <c r="N22">
-        <v>1.32</v>
+        <v>0.01</v>
       </c>
       <c r="O22">
-        <v>1.21</v>
+        <v>0.004895</v>
       </c>
       <c r="P22">
-        <v>1.71</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q22">
-        <v>1.43</v>
+        <v>0.02</v>
       </c>
       <c r="R22">
-        <v>40283000</v>
+        <v>767000</v>
       </c>
       <c r="S22">
-        <v>56992000</v>
+        <v>11487000</v>
       </c>
       <c r="T22">
-        <v>47697000</v>
+        <v>3146000</v>
       </c>
       <c r="U22">
-        <v>183079000</v>
+        <v>15373000</v>
       </c>
       <c r="V22" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2664,67 +2682,67 @@
         <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C23" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D23" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E23">
-        <v>32.88000106811523</v>
+        <v>109.1100006103516</v>
       </c>
       <c r="F23">
-        <v>305216.6666666667</v>
+        <v>3705826.666666667</v>
       </c>
       <c r="G23">
-        <v>29.94499992370605</v>
+        <v>95.02160003662109</v>
       </c>
       <c r="H23">
-        <v>24.88726660410563</v>
+        <v>75.2770667775472</v>
       </c>
       <c r="I23">
-        <v>22.73614997386932</v>
+        <v>70.0234500694275</v>
       </c>
       <c r="J23">
-        <v>21.28594998836518</v>
+        <v>64.30695007324219</v>
       </c>
       <c r="K23">
-        <v>14.10000038146973</v>
+        <v>4.547188282012939</v>
       </c>
       <c r="L23">
-        <v>33.61000061035156</v>
+        <v>133.7226409912109</v>
       </c>
       <c r="M23">
-        <v>154.3822503406911</v>
+        <v>160.8687788574994</v>
       </c>
       <c r="N23">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="O23">
-        <v>0.14</v>
+        <v>-1.96</v>
       </c>
       <c r="P23">
-        <v>0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="Q23">
-        <v>0.11</v>
+        <v>1.7</v>
       </c>
       <c r="R23">
-        <v>36215000</v>
+        <v>-2155962000</v>
       </c>
       <c r="S23">
-        <v>48300000</v>
+        <v>-47910000</v>
       </c>
       <c r="T23">
-        <v>28265000</v>
+        <v>458761000</v>
       </c>
       <c r="U23">
-        <v>142849000</v>
+        <v>-1036730000</v>
       </c>
       <c r="V23" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2732,67 +2750,67 @@
         <v>44</v>
       </c>
       <c r="B24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D24" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E24">
-        <v>402.7200012207031</v>
+        <v>91.26000213623047</v>
       </c>
       <c r="F24">
-        <v>606876.6666666666</v>
+        <v>5117183.333333333</v>
       </c>
       <c r="G24">
-        <v>318.1853997802734</v>
+        <v>77.61980026245118</v>
       </c>
       <c r="H24">
-        <v>281.5550665283203</v>
+        <v>62.92940012613932</v>
       </c>
       <c r="I24">
-        <v>265.6470497894287</v>
+        <v>59.77360006332398</v>
       </c>
       <c r="J24">
-        <v>249.3961497497559</v>
+        <v>57.40695003509521</v>
       </c>
       <c r="K24">
-        <v>4.533332824707031</v>
+        <v>2.279999971389771</v>
       </c>
       <c r="L24">
-        <v>410.0499877929688</v>
+        <v>111.6399993896484</v>
       </c>
       <c r="M24">
-        <v>153.9990183026713</v>
+        <v>159.5575279760833</v>
       </c>
       <c r="N24">
-        <v>4.1</v>
+        <v>-0.04</v>
       </c>
       <c r="O24">
-        <v>3.67</v>
+        <v>0.03</v>
       </c>
       <c r="P24">
-        <v>2.65</v>
+        <v>0.14</v>
       </c>
       <c r="Q24">
-        <v>2.85</v>
+        <v>0.02</v>
       </c>
       <c r="R24">
-        <v>97891000</v>
+        <v>15869000</v>
       </c>
       <c r="S24">
-        <v>70862000</v>
+        <v>71187000</v>
       </c>
       <c r="T24">
-        <v>76097000</v>
+        <v>9326000</v>
       </c>
       <c r="U24">
-        <v>357422000</v>
+        <v>53385000</v>
       </c>
       <c r="V24" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2803,64 +2821,64 @@
         <v>120</v>
       </c>
       <c r="C25" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D25" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E25">
-        <v>28.8700008392334</v>
+        <v>423.1400146484375</v>
       </c>
       <c r="F25">
-        <v>1322183.333333333</v>
+        <v>653590</v>
       </c>
       <c r="G25">
-        <v>25.35479995727539</v>
+        <v>334.1879998779297</v>
       </c>
       <c r="H25">
-        <v>21.49043329874674</v>
+        <v>288.9743999226888</v>
       </c>
       <c r="I25">
-        <v>19.89432498931885</v>
+        <v>271.9603997802735</v>
       </c>
       <c r="J25">
-        <v>18.92462500572205</v>
+        <v>253.3839996337891</v>
       </c>
       <c r="K25">
-        <v>6.309999942779541</v>
+        <v>4.533332824707031</v>
       </c>
       <c r="L25">
-        <v>37.61000061035156</v>
+        <v>425.8900146484375</v>
       </c>
       <c r="M25">
-        <v>152.0138559852837</v>
+        <v>159.1793745647682</v>
       </c>
       <c r="N25">
-        <v>-0.35</v>
+        <v>3.67</v>
       </c>
       <c r="O25">
-        <v>-0.32</v>
+        <v>2.65</v>
       </c>
       <c r="P25">
-        <v>-0.21</v>
+        <v>2.85</v>
       </c>
       <c r="Q25">
-        <v>-0.21</v>
+        <v>3.42</v>
       </c>
       <c r="R25">
-        <v>-37149000</v>
+        <v>357422000</v>
       </c>
       <c r="S25">
-        <v>-24642000</v>
+        <v>76097000</v>
       </c>
       <c r="T25">
-        <v>-24855000</v>
+        <v>91319000</v>
       </c>
       <c r="U25">
-        <v>-100322000</v>
+        <v>354095000</v>
       </c>
       <c r="V25" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2868,67 +2886,67 @@
         <v>46</v>
       </c>
       <c r="B26" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C26" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="E26">
-        <v>102.379997253418</v>
+        <v>116.7200012207031</v>
       </c>
       <c r="F26">
-        <v>3699543.333333333</v>
+        <v>1020153.333333333</v>
       </c>
       <c r="G26">
-        <v>91.5816000366211</v>
+        <v>107.6404000854492</v>
       </c>
       <c r="H26">
-        <v>73.17520011901856</v>
+        <v>85.0457999420166</v>
       </c>
       <c r="I26">
-        <v>68.14265005111695</v>
+        <v>76.19599992752075</v>
       </c>
       <c r="J26">
-        <v>62.64435014724732</v>
+        <v>68.69774990081787</v>
       </c>
       <c r="K26">
-        <v>4.621691703796387</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="L26">
-        <v>133.7226409912109</v>
+        <v>119.5100021362305</v>
       </c>
       <c r="M26">
-        <v>151.530272903834</v>
+        <v>159.0995762233708</v>
       </c>
       <c r="N26">
-        <v>-2.05</v>
+        <v>0.27</v>
       </c>
       <c r="O26">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="P26">
-        <v>-1.96</v>
+        <v>0.34</v>
       </c>
       <c r="Q26">
-        <v>-0.19</v>
+        <v>0.29</v>
       </c>
       <c r="R26">
-        <v>32968000</v>
+        <v>11710000</v>
       </c>
       <c r="S26">
-        <v>-500206000</v>
+        <v>19105000</v>
       </c>
       <c r="T26">
-        <v>-47910000</v>
+        <v>16246000</v>
       </c>
       <c r="U26">
-        <v>-2155962000</v>
+        <v>46840000</v>
       </c>
       <c r="V26" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -2936,67 +2954,67 @@
         <v>47</v>
       </c>
       <c r="B27" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D27" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E27">
-        <v>41.18999862670898</v>
+        <v>37.56000137329102</v>
       </c>
       <c r="F27">
-        <v>1336873.333333333</v>
+        <v>589126.6666666666</v>
       </c>
       <c r="G27">
-        <v>35.83559978485108</v>
+        <v>31.73180015563965</v>
       </c>
       <c r="H27">
-        <v>29.69559993743896</v>
+        <v>25.38173334757487</v>
       </c>
       <c r="I27">
-        <v>28.97879995346069</v>
+        <v>23.81255001544952</v>
       </c>
       <c r="J27">
-        <v>27.81194997787476</v>
+        <v>21.66294999599457</v>
       </c>
       <c r="K27">
-        <v>18.28000068664551</v>
+        <v>0.5703791379928589</v>
       </c>
       <c r="L27">
-        <v>47.06000137329102</v>
+        <v>37.97000122070312</v>
       </c>
       <c r="M27">
-        <v>150.8002880020072</v>
+        <v>155.9803190100494</v>
       </c>
       <c r="N27">
-        <v>0.07000000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="O27">
-        <v>0.06</v>
+        <v>0.46</v>
       </c>
       <c r="P27">
-        <v>0.06</v>
+        <v>0.46</v>
       </c>
       <c r="Q27">
-        <v>0.07000000000000001</v>
+        <v>1.69</v>
       </c>
       <c r="R27">
-        <v>53508000</v>
+        <v>24400000</v>
       </c>
       <c r="S27">
-        <v>18068000</v>
+        <v>24500000</v>
       </c>
       <c r="T27">
-        <v>12175000</v>
+        <v>89900000</v>
       </c>
       <c r="U27">
-        <v>43268000</v>
+        <v>71600000</v>
       </c>
       <c r="V27" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -3004,67 +3022,67 @@
         <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C28" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="D28" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E28">
-        <v>23.88999938964844</v>
+        <v>26.42000007629395</v>
       </c>
       <c r="F28">
-        <v>2504550</v>
+        <v>527773.3333333334</v>
       </c>
       <c r="G28">
-        <v>20.0861999130249</v>
+        <v>26.32530002593994</v>
       </c>
       <c r="H28">
-        <v>16.78139998753866</v>
+        <v>20.4942333539327</v>
       </c>
       <c r="I28">
-        <v>16.49380001544952</v>
+        <v>18.22015003204346</v>
       </c>
       <c r="J28">
-        <v>15.64875001430512</v>
+        <v>16.91220003128052</v>
       </c>
       <c r="K28">
-        <v>12.61999988555908</v>
+        <v>7.559999942779541</v>
       </c>
       <c r="L28">
-        <v>24.46999931335449</v>
+        <v>29.29999923706055</v>
       </c>
       <c r="M28">
-        <v>150.6253082630952</v>
+        <v>155.4577213152232</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>7258000</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>-2810000</v>
       </c>
       <c r="T28">
-        <v>-8500000</v>
+        <v>6705000</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>7814000</v>
       </c>
       <c r="V28" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -3072,67 +3090,67 @@
         <v>49</v>
       </c>
       <c r="B29" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C29" t="s">
         <v>146</v>
       </c>
       <c r="D29" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E29">
-        <v>84.16000366210938</v>
+        <v>59.9900016784668</v>
       </c>
       <c r="F29">
-        <v>4848546.666666667</v>
+        <v>336000</v>
       </c>
       <c r="G29">
-        <v>75.00180038452149</v>
+        <v>53.57799995422364</v>
       </c>
       <c r="H29">
-        <v>61.35726682027181</v>
+        <v>42.49166667938233</v>
       </c>
       <c r="I29">
-        <v>58.94245008468628</v>
+        <v>39.35090001106262</v>
       </c>
       <c r="J29">
-        <v>57.02534999847412</v>
+        <v>35.78235000610351</v>
       </c>
       <c r="K29">
-        <v>2.279999971389771</v>
+        <v>0.4209107160568237</v>
       </c>
       <c r="L29">
-        <v>111.6399993896484</v>
+        <v>59.9900016784668</v>
       </c>
       <c r="M29">
-        <v>149.7455280997524</v>
+        <v>154.7057237025718</v>
       </c>
       <c r="N29">
-        <v>-0.04</v>
+        <v>0.86</v>
       </c>
       <c r="O29">
-        <v>0.03</v>
+        <v>0.97</v>
       </c>
       <c r="P29">
-        <v>0.14</v>
+        <v>1.03</v>
       </c>
       <c r="Q29">
-        <v>0.02</v>
+        <v>0.64</v>
       </c>
       <c r="R29">
-        <v>15869000</v>
+        <v>29523000</v>
       </c>
       <c r="S29">
-        <v>71187000</v>
+        <v>31725000</v>
       </c>
       <c r="T29">
-        <v>9326000</v>
+        <v>19649000</v>
       </c>
       <c r="U29">
-        <v>53385000</v>
+        <v>106461000</v>
       </c>
       <c r="V29" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -3140,67 +3158,67 @@
         <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C30" t="s">
         <v>147</v>
       </c>
       <c r="D30" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="E30">
-        <v>26.18000030517578</v>
+        <v>83.09999847412109</v>
       </c>
       <c r="F30">
-        <v>887523.3333333334</v>
+        <v>872560</v>
       </c>
       <c r="G30">
-        <v>23.19740005493164</v>
+        <v>67.1121997833252</v>
       </c>
       <c r="H30">
-        <v>19.61866671880086</v>
+        <v>61.64046648661296</v>
       </c>
       <c r="I30">
-        <v>17.92635003566742</v>
+        <v>56.51844987869263</v>
       </c>
       <c r="J30">
-        <v>16.38410003662109</v>
+        <v>52.25719989776611</v>
       </c>
       <c r="K30">
-        <v>1.899999976158142</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="L30">
-        <v>27.38999938964844</v>
+        <v>83.09999847412109</v>
       </c>
       <c r="M30">
-        <v>149.5480256104833</v>
+        <v>154.2114616029173</v>
       </c>
       <c r="N30">
-        <v>0.75</v>
+        <v>0.39</v>
       </c>
       <c r="O30">
-        <v>0.762</v>
+        <v>0.99</v>
       </c>
       <c r="P30">
-        <v>1.315</v>
+        <v>0.97</v>
       </c>
       <c r="Q30">
-        <v>0.519</v>
+        <v>1.12</v>
       </c>
       <c r="R30">
-        <v>269535000</v>
+        <v>26000000</v>
       </c>
       <c r="S30">
-        <v>128734000</v>
+        <v>72000000</v>
       </c>
       <c r="T30">
-        <v>52181000</v>
+        <v>82000000</v>
       </c>
       <c r="U30">
-        <v>382735000</v>
+        <v>178000000</v>
       </c>
       <c r="V30" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -3208,67 +3226,67 @@
         <v>51</v>
       </c>
       <c r="B31" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D31" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E31">
-        <v>46.65000152587891</v>
+        <v>49.45999908447266</v>
       </c>
       <c r="F31">
-        <v>2927433.333333333</v>
+        <v>22335443.33333333</v>
       </c>
       <c r="G31">
-        <v>39.49479995727539</v>
+        <v>42.78839996337891</v>
       </c>
       <c r="H31">
-        <v>33.43283331553141</v>
+        <v>35.55140009562174</v>
       </c>
       <c r="I31">
-        <v>33.33499994277954</v>
+        <v>33.5685000705719</v>
       </c>
       <c r="J31">
-        <v>30.61604996681213</v>
+        <v>31.89245009422302</v>
       </c>
       <c r="K31">
-        <v>13.1899995803833</v>
+        <v>14.81999969482422</v>
       </c>
       <c r="L31">
-        <v>46.91999816894531</v>
+        <v>63.18000030517578</v>
       </c>
       <c r="M31">
-        <v>148.9975435545929</v>
+        <v>153.8479977014528</v>
       </c>
       <c r="N31">
-        <v>-0.58</v>
+        <v>-1.33</v>
       </c>
       <c r="O31">
-        <v>-0.55</v>
+        <v>-0.61</v>
       </c>
       <c r="P31">
-        <v>-0.51</v>
+        <v>0.29</v>
       </c>
       <c r="Q31">
-        <v>-0.54</v>
+        <v>-0.08</v>
       </c>
       <c r="R31">
-        <v>-76858000</v>
+        <v>-1206000000</v>
       </c>
       <c r="S31">
-        <v>-23224000</v>
+        <v>595000000</v>
       </c>
       <c r="T31">
-        <v>-25646000</v>
+        <v>-157000000</v>
       </c>
       <c r="U31">
-        <v>-83887000</v>
+        <v>-9141000000</v>
       </c>
       <c r="V31" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -3276,67 +3294,67 @@
         <v>52</v>
       </c>
       <c r="B32" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E32">
-        <v>896.75</v>
+        <v>84.38999938964844</v>
       </c>
       <c r="F32">
-        <v>2914250</v>
+        <v>2801106.666666667</v>
       </c>
       <c r="G32">
-        <v>803.9798400878906</v>
+        <v>75.1513996887207</v>
       </c>
       <c r="H32">
-        <v>665.5057332356771</v>
+        <v>62.84839981079102</v>
       </c>
       <c r="I32">
-        <v>618.9494375610352</v>
+        <v>57.62679985046387</v>
       </c>
       <c r="J32">
-        <v>579.3134098815918</v>
+        <v>53.550299949646</v>
       </c>
       <c r="K32">
-        <v>10.54332065582275</v>
+        <v>0.1027423962950706</v>
       </c>
       <c r="L32">
-        <v>910.3499755859375</v>
+        <v>84.81999969482422</v>
       </c>
       <c r="M32">
-        <v>148.4027206241158</v>
+        <v>151.3797681659705</v>
       </c>
       <c r="N32">
-        <v>7.132125</v>
+        <v>2.69</v>
       </c>
       <c r="O32">
-        <v>7.810425</v>
+        <v>3.85</v>
       </c>
       <c r="P32">
-        <v>8.800000000000001</v>
+        <v>2.35</v>
       </c>
       <c r="Q32">
-        <v>8.15</v>
+        <v>3.21</v>
       </c>
       <c r="R32">
-        <v>3359000000</v>
+        <v>2617317000</v>
       </c>
       <c r="S32">
-        <v>3774000000</v>
+        <v>532259000</v>
       </c>
       <c r="T32">
-        <v>3481000000</v>
+        <v>720345000</v>
       </c>
       <c r="U32">
-        <v>12797000000</v>
+        <v>2694853000</v>
       </c>
       <c r="V32" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -3344,67 +3362,67 @@
         <v>53</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D33" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E33">
-        <v>520.22998046875</v>
+        <v>77.13999938964844</v>
       </c>
       <c r="F33">
-        <v>4446163.333333333</v>
+        <v>523273.3333333333</v>
       </c>
       <c r="G33">
-        <v>449.1861987304687</v>
+        <v>68.01819976806641</v>
       </c>
       <c r="H33">
-        <v>387.5862662760417</v>
+        <v>55.37139984130859</v>
       </c>
       <c r="I33">
-        <v>369.8689991760254</v>
+        <v>53.8719998550415</v>
       </c>
       <c r="J33">
-        <v>351.7899992370606</v>
+        <v>51.89414989471435</v>
       </c>
       <c r="K33">
-        <v>0.1943886876106262</v>
+        <v>14.8100004196167</v>
       </c>
       <c r="L33">
-        <v>688.3699951171875</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="M33">
-        <v>145.3845312890374</v>
+        <v>151.2972453723136</v>
       </c>
       <c r="N33">
-        <v>2.42</v>
+        <v>-0.96</v>
       </c>
       <c r="O33">
-        <v>2.53</v>
+        <v>-0.58</v>
       </c>
       <c r="P33">
-        <v>2.71</v>
+        <v>-0.66</v>
       </c>
       <c r="Q33">
-        <v>2.82</v>
+        <v>-0.72</v>
       </c>
       <c r="R33">
-        <v>4756000000</v>
+        <v>-27576000</v>
       </c>
       <c r="S33">
-        <v>1247000000</v>
+        <v>-31460000</v>
       </c>
       <c r="T33">
-        <v>1295000000</v>
+        <v>-34626000</v>
       </c>
       <c r="U33">
-        <v>4737000000</v>
+        <v>-99195000</v>
       </c>
       <c r="V33" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -3412,67 +3430,67 @@
         <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C34" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D34" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E34">
-        <v>112.4000015258789</v>
+        <v>23.44000053405762</v>
       </c>
       <c r="F34">
-        <v>1212340</v>
+        <v>2336916.666666667</v>
       </c>
       <c r="G34">
-        <v>98.4724169921875</v>
+        <v>20.80739997863769</v>
       </c>
       <c r="H34">
-        <v>85.54724034627279</v>
+        <v>17.09813332239787</v>
       </c>
       <c r="I34">
-        <v>80.49789468765259</v>
+        <v>16.73040001392365</v>
       </c>
       <c r="J34">
-        <v>75.39480707168579</v>
+        <v>15.90505000591278</v>
       </c>
       <c r="K34">
-        <v>0.3779089450836182</v>
+        <v>12.61999988555908</v>
       </c>
       <c r="L34">
-        <v>115.1399993896484</v>
+        <v>24.46999931335449</v>
       </c>
       <c r="M34">
-        <v>143.3792457521962</v>
+        <v>150.6272401455155</v>
       </c>
       <c r="N34">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O34">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="P34">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>978000000</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>207000000</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>233000000</v>
+        <v>-8500000</v>
       </c>
       <c r="U34">
-        <v>963000000</v>
+        <v>0</v>
       </c>
       <c r="V34" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -3480,67 +3498,67 @@
         <v>55</v>
       </c>
       <c r="B35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C35" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="D35" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E35">
-        <v>52.63999938964844</v>
+        <v>49.84999847412109</v>
       </c>
       <c r="F35">
-        <v>2095946.666666667</v>
+        <v>329790</v>
       </c>
       <c r="G35">
-        <v>48.9342000579834</v>
+        <v>42.8303997039795</v>
       </c>
       <c r="H35">
-        <v>41.04854695638021</v>
+        <v>34.84246660868327</v>
       </c>
       <c r="I35">
-        <v>38.04266626358032</v>
+        <v>33.37989994049072</v>
       </c>
       <c r="J35">
-        <v>35.57566363334656</v>
+        <v>30.83634998321533</v>
       </c>
       <c r="K35">
-        <v>1.604377269744873</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="L35">
-        <v>64.82536315917969</v>
+        <v>49.84999847412109</v>
       </c>
       <c r="M35">
-        <v>142.0374083714284</v>
+        <v>149.8612624272533</v>
       </c>
       <c r="N35">
-        <v>2.86</v>
+        <v>-0.38</v>
       </c>
       <c r="O35">
-        <v>2.47</v>
+        <v>-0.41</v>
       </c>
       <c r="P35">
-        <v>1.45</v>
+        <v>-0.49</v>
       </c>
       <c r="Q35">
-        <v>1.94</v>
+        <v>-0.44</v>
       </c>
       <c r="R35">
-        <v>216410000</v>
+        <v>-73020000</v>
       </c>
       <c r="S35">
-        <v>125500000</v>
+        <v>-26123000</v>
       </c>
       <c r="T35">
-        <v>164442000</v>
+        <v>-25192000</v>
       </c>
       <c r="U35">
-        <v>807909000</v>
+        <v>-81854000</v>
       </c>
       <c r="V35" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3548,67 +3566,67 @@
         <v>56</v>
       </c>
       <c r="B36" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C36" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="D36" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E36">
-        <v>78.08999633789062</v>
+        <v>47</v>
       </c>
       <c r="F36">
-        <v>2665606.666666667</v>
+        <v>2990553.333333333</v>
       </c>
       <c r="G36">
-        <v>73.32662551879883</v>
+        <v>40.88279998779297</v>
       </c>
       <c r="H36">
-        <v>61.18830678304037</v>
+        <v>34.01770001729329</v>
       </c>
       <c r="I36">
-        <v>56.13264078140259</v>
+        <v>33.99429996490478</v>
       </c>
       <c r="J36">
-        <v>52.19785215377808</v>
+        <v>31.40409996032715</v>
       </c>
       <c r="K36">
-        <v>0.1049395576119423</v>
+        <v>13.1899995803833</v>
       </c>
       <c r="L36">
-        <v>82.51000213623047</v>
+        <v>47</v>
       </c>
       <c r="M36">
-        <v>141.8633122806268</v>
+        <v>149.75595124966</v>
       </c>
       <c r="N36">
-        <v>2.73</v>
+        <v>-0.58</v>
       </c>
       <c r="O36">
-        <v>2.69</v>
+        <v>-0.55</v>
       </c>
       <c r="P36">
-        <v>3.85</v>
+        <v>-0.51</v>
       </c>
       <c r="Q36">
-        <v>2.35</v>
+        <v>-0.54</v>
       </c>
       <c r="R36">
-        <v>627928000</v>
+        <v>-76858000</v>
       </c>
       <c r="S36">
-        <v>882231000</v>
+        <v>-23224000</v>
       </c>
       <c r="T36">
-        <v>532259000</v>
+        <v>-25646000</v>
       </c>
       <c r="U36">
-        <v>2617317000</v>
+        <v>-83887000</v>
       </c>
       <c r="V36" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -3616,67 +3634,67 @@
         <v>57</v>
       </c>
       <c r="B37" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="D37" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E37">
-        <v>74.86000061035156</v>
+        <v>14.65999984741211</v>
       </c>
       <c r="F37">
-        <v>528080</v>
+        <v>343066.6666666667</v>
       </c>
       <c r="G37">
-        <v>66.05439987182618</v>
+        <v>12.41979999542236</v>
       </c>
       <c r="H37">
-        <v>54.06433321634928</v>
+        <v>10.87140001296997</v>
       </c>
       <c r="I37">
-        <v>53.2574499130249</v>
+        <v>10.19300000429153</v>
       </c>
       <c r="J37">
-        <v>51.47619993209839</v>
+        <v>9.75465000152588</v>
       </c>
       <c r="K37">
-        <v>14.8100004196167</v>
+        <v>2.79044508934021</v>
       </c>
       <c r="L37">
-        <v>97.69999694824219</v>
+        <v>18.82888412475586</v>
       </c>
       <c r="M37">
-        <v>141.5275681285418</v>
+        <v>149.3396503066246</v>
       </c>
       <c r="N37">
-        <v>-0.96</v>
+        <v>0.15</v>
       </c>
       <c r="O37">
-        <v>-0.58</v>
+        <v>1.21</v>
       </c>
       <c r="P37">
-        <v>-0.66</v>
+        <v>0.15</v>
       </c>
       <c r="Q37">
-        <v>-0.72</v>
+        <v>0.23</v>
       </c>
       <c r="R37">
-        <v>-27576000</v>
+        <v>21856000</v>
       </c>
       <c r="S37">
-        <v>-31460000</v>
+        <v>3117000</v>
       </c>
       <c r="T37">
-        <v>-34626000</v>
+        <v>4733000</v>
       </c>
       <c r="U37">
-        <v>-99195000</v>
+        <v>32187000</v>
       </c>
       <c r="V37" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -3684,67 +3702,67 @@
         <v>58</v>
       </c>
       <c r="B38" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C38" t="s">
         <v>149</v>
       </c>
       <c r="D38" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E38">
-        <v>33.56000137329102</v>
+        <v>29.23999977111816</v>
       </c>
       <c r="F38">
-        <v>1392733.333333333</v>
+        <v>1173076.666666667</v>
       </c>
       <c r="G38">
-        <v>29.8598998260498</v>
+        <v>26.03839992523193</v>
       </c>
       <c r="H38">
-        <v>25.60150034586589</v>
+        <v>21.80983328501383</v>
       </c>
       <c r="I38">
-        <v>23.24529892444611</v>
+        <v>20.2836749792099</v>
       </c>
       <c r="J38">
-        <v>21.68372899055481</v>
+        <v>19.11597499847412</v>
       </c>
       <c r="K38">
-        <v>3.907924652099609</v>
+        <v>6.309999942779541</v>
       </c>
       <c r="L38">
-        <v>33.56000137329102</v>
+        <v>37.61000061035156</v>
       </c>
       <c r="M38">
-        <v>141.255027362186</v>
+        <v>148.9346750832101</v>
       </c>
       <c r="N38">
-        <v>0.11</v>
+        <v>-0.35</v>
       </c>
       <c r="O38">
-        <v>-0.23</v>
+        <v>-0.32</v>
       </c>
       <c r="P38">
-        <v>0.2</v>
+        <v>-0.21</v>
       </c>
       <c r="Q38">
-        <v>0.22</v>
+        <v>-0.21</v>
       </c>
       <c r="R38">
-        <v>-16058000</v>
+        <v>-37149000</v>
       </c>
       <c r="S38">
-        <v>26801000</v>
+        <v>-24642000</v>
       </c>
       <c r="T38">
-        <v>29397000</v>
+        <v>-24855000</v>
       </c>
       <c r="U38">
-        <v>-193210000</v>
+        <v>-100322000</v>
       </c>
       <c r="V38" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -3752,67 +3770,67 @@
         <v>59</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C39" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="D39" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E39">
-        <v>243.8200073242188</v>
+        <v>26.10000038146973</v>
       </c>
       <c r="F39">
-        <v>7024473.333333333</v>
+        <v>841553.3333333334</v>
       </c>
       <c r="G39">
-        <v>228.0783996582031</v>
+        <v>23.80580005645752</v>
       </c>
       <c r="H39">
-        <v>190.7764665730794</v>
+        <v>20.11440005620321</v>
       </c>
       <c r="I39">
-        <v>184.0607498168945</v>
+        <v>18.36485003471374</v>
       </c>
       <c r="J39">
-        <v>176.6686499023438</v>
+        <v>16.79595004081726</v>
       </c>
       <c r="K39">
-        <v>13.18666744232178</v>
+        <v>1.899999976158142</v>
       </c>
       <c r="L39">
-        <v>257.8800048828125</v>
+        <v>27.38999938964844</v>
       </c>
       <c r="M39">
-        <v>141.0015768298448</v>
+        <v>148.1029962769371</v>
       </c>
       <c r="N39">
-        <v>0.01</v>
+        <v>0.75</v>
       </c>
       <c r="O39">
-        <v>0.06</v>
+        <v>0.762</v>
       </c>
       <c r="P39">
-        <v>0.25</v>
+        <v>1.315</v>
       </c>
       <c r="Q39">
-        <v>0.31</v>
+        <v>0.519</v>
       </c>
       <c r="R39">
-        <v>20000000</v>
+        <v>269535000</v>
       </c>
       <c r="S39">
-        <v>84200000</v>
+        <v>128734000</v>
       </c>
       <c r="T39">
-        <v>107800000</v>
+        <v>52181000</v>
       </c>
       <c r="U39">
-        <v>34300000</v>
+        <v>382735000</v>
       </c>
       <c r="V39" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -3820,67 +3838,67 @@
         <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C40" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D40" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E40">
-        <v>548.4299926757812</v>
+        <v>155.1900024414062</v>
       </c>
       <c r="F40">
-        <v>360253.3333333333</v>
+        <v>529663.3333333334</v>
       </c>
       <c r="G40">
-        <v>407.7878009033203</v>
+        <v>149.5631994628906</v>
       </c>
       <c r="H40">
-        <v>386.111366780599</v>
+        <v>124.2378331502279</v>
       </c>
       <c r="I40">
-        <v>382.8641250610352</v>
+        <v>112.2017247009277</v>
       </c>
       <c r="J40">
-        <v>377.9283248901367</v>
+        <v>107.1025748062134</v>
       </c>
       <c r="K40">
-        <v>19.76499938964844</v>
+        <v>63</v>
       </c>
       <c r="L40">
-        <v>548.4299926757812</v>
+        <v>202.6900024414062</v>
       </c>
       <c r="M40">
-        <v>140.2991611482426</v>
+        <v>145.8814235137661</v>
       </c>
       <c r="N40">
-        <v>-0.52</v>
+        <v>-0.38</v>
       </c>
       <c r="O40">
-        <v>-4.26</v>
+        <v>-0.46</v>
       </c>
       <c r="P40">
-        <v>-0.7</v>
+        <v>-0.35</v>
       </c>
       <c r="Q40">
-        <v>-0.52</v>
+        <v>-0.06</v>
       </c>
       <c r="R40">
-        <v>-235042000</v>
+        <v>-18445000</v>
       </c>
       <c r="S40">
-        <v>-38613000</v>
+        <v>-13930000</v>
       </c>
       <c r="T40">
-        <v>-28871000</v>
+        <v>-2582000</v>
       </c>
       <c r="U40">
-        <v>-709594000</v>
+        <v>-59574000</v>
       </c>
       <c r="V40" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -3888,67 +3906,67 @@
         <v>61</v>
       </c>
       <c r="B41" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C41" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="D41" t="s">
-        <v>171</v>
+        <v>214</v>
       </c>
       <c r="E41">
-        <v>75.04000091552734</v>
+        <v>42.09999847412109</v>
       </c>
       <c r="F41">
-        <v>780180</v>
+        <v>1330196.666666667</v>
       </c>
       <c r="G41">
-        <v>64.53719970703125</v>
+        <v>37.33999973297119</v>
       </c>
       <c r="H41">
-        <v>60.27293314615886</v>
+        <v>30.39579992930095</v>
       </c>
       <c r="I41">
-        <v>55.14074987411499</v>
+        <v>29.37819993972778</v>
       </c>
       <c r="J41">
-        <v>51.21924991607666</v>
+        <v>28.1043999671936</v>
       </c>
       <c r="K41">
-        <v>5.739999771118164</v>
+        <v>18.28000068664551</v>
       </c>
       <c r="L41">
-        <v>76.41999816894531</v>
+        <v>47.06000137329102</v>
       </c>
       <c r="M41">
-        <v>140.0336240038694</v>
+        <v>145.8019098650194</v>
       </c>
       <c r="N41">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O41">
-        <v>0.39</v>
+        <v>0.06</v>
       </c>
       <c r="P41">
-        <v>0.99</v>
+        <v>0.06</v>
       </c>
       <c r="Q41">
-        <v>0.97</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R41">
-        <v>28000000</v>
+        <v>53508000</v>
       </c>
       <c r="S41">
-        <v>72000000</v>
+        <v>18068000</v>
       </c>
       <c r="T41">
-        <v>72000000</v>
+        <v>12175000</v>
       </c>
       <c r="U41">
-        <v>26000000</v>
+        <v>43268000</v>
       </c>
       <c r="V41" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -3956,67 +3974,67 @@
         <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C42" t="s">
         <v>151</v>
       </c>
       <c r="D42" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E42">
-        <v>53.91999816894531</v>
+        <v>31.22999954223633</v>
       </c>
       <c r="F42">
-        <v>1180690</v>
+        <v>313073.3333333333</v>
       </c>
       <c r="G42">
-        <v>45.13219993591309</v>
+        <v>30.44779998779297</v>
       </c>
       <c r="H42">
-        <v>42.62833333333333</v>
+        <v>25.44939994812012</v>
       </c>
       <c r="I42">
-        <v>41.78840232849121</v>
+        <v>23.16209997653961</v>
       </c>
       <c r="J42">
-        <v>40.28770523071289</v>
+        <v>21.71155000209808</v>
       </c>
       <c r="K42">
-        <v>2.697069406509399</v>
+        <v>14.10000038146973</v>
       </c>
       <c r="L42">
-        <v>53.91999816894531</v>
+        <v>33.61000061035156</v>
       </c>
       <c r="M42">
-        <v>139.9984411375982</v>
+        <v>145.5658292896496</v>
       </c>
       <c r="N42">
-        <v>3.74</v>
+        <v>0.14</v>
       </c>
       <c r="O42">
-        <v>3.41</v>
+        <v>0.18</v>
       </c>
       <c r="P42">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="Q42">
-        <v>-2</v>
+        <v>0.13</v>
       </c>
       <c r="R42">
-        <v>312600000</v>
+        <v>142849000</v>
       </c>
       <c r="S42">
-        <v>32572000</v>
+        <v>28265000</v>
       </c>
       <c r="T42">
-        <v>-155994000</v>
+        <v>34300000</v>
       </c>
       <c r="U42">
-        <v>1220944000</v>
+        <v>143391000</v>
       </c>
       <c r="V42" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -4024,67 +4042,67 @@
         <v>63</v>
       </c>
       <c r="B43" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C43" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="D43" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E43">
-        <v>83.29000091552734</v>
+        <v>546.1699829101562</v>
       </c>
       <c r="F43">
-        <v>527913.3333333334</v>
+        <v>3574453.333333333</v>
       </c>
       <c r="G43">
-        <v>74.73680000305175</v>
+        <v>470.8721978759766</v>
       </c>
       <c r="H43">
-        <v>63.68446655273438</v>
+        <v>395.1677990722656</v>
       </c>
       <c r="I43">
-        <v>62.00339994430542</v>
+        <v>376.8823989868164</v>
       </c>
       <c r="J43">
-        <v>59.10889991760254</v>
+        <v>354.8775491333008</v>
       </c>
       <c r="K43">
-        <v>7.03000020980835</v>
+        <v>0.1503329128026962</v>
       </c>
       <c r="L43">
-        <v>85.40000152587891</v>
+        <v>688.3699951171875</v>
       </c>
       <c r="M43">
-        <v>139.5773766729721</v>
+        <v>144.8630208083272</v>
       </c>
       <c r="N43">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="O43">
-        <v>1.95</v>
+        <v>2.53</v>
       </c>
       <c r="P43">
-        <v>0.88</v>
+        <v>2.71</v>
       </c>
       <c r="Q43">
-        <v>0.25</v>
+        <v>2.82</v>
       </c>
       <c r="R43">
-        <v>154800000</v>
+        <v>4756000000</v>
       </c>
       <c r="S43">
-        <v>73300000</v>
+        <v>1247000000</v>
       </c>
       <c r="T43">
-        <v>24800000</v>
+        <v>1295000000</v>
       </c>
       <c r="U43">
-        <v>458400000</v>
+        <v>4737000000</v>
       </c>
       <c r="V43" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -4092,67 +4110,67 @@
         <v>64</v>
       </c>
       <c r="B44" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C44" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="D44" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="E44">
-        <v>49.34999847412109</v>
+        <v>103.4899978637695</v>
       </c>
       <c r="F44">
-        <v>1041823.333333333</v>
+        <v>376260</v>
       </c>
       <c r="G44">
-        <v>46.5265998840332</v>
+        <v>85.92039993286133</v>
       </c>
       <c r="H44">
-        <v>39.38659998575847</v>
+        <v>74.55886695861817</v>
       </c>
       <c r="I44">
-        <v>36.35565003395081</v>
+        <v>73.10430025100707</v>
       </c>
       <c r="J44">
-        <v>33.86040000915527</v>
+        <v>69.43105028152466</v>
       </c>
       <c r="K44">
-        <v>7.050000190734863</v>
+        <v>11.37919998168945</v>
       </c>
       <c r="L44">
-        <v>51.63999938964844</v>
+        <v>103.4899978637695</v>
       </c>
       <c r="M44">
-        <v>139.5528490673355</v>
+        <v>144.2791675123891</v>
       </c>
       <c r="N44">
-        <v>2.45</v>
+        <v>5.49</v>
       </c>
       <c r="O44">
-        <v>2.72</v>
+        <v>5.52</v>
       </c>
       <c r="P44">
-        <v>2.51</v>
+        <v>2.95</v>
       </c>
       <c r="Q44">
-        <v>1.74</v>
+        <v>2.43</v>
       </c>
       <c r="R44">
-        <v>309779000</v>
+        <v>219587000</v>
       </c>
       <c r="S44">
-        <v>275331000</v>
+        <v>117360000</v>
       </c>
       <c r="T44">
-        <v>191051000</v>
+        <v>96733000</v>
       </c>
       <c r="U44">
-        <v>1052800000</v>
+        <v>857658000</v>
       </c>
       <c r="V44" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -4160,67 +4178,67 @@
         <v>65</v>
       </c>
       <c r="B45" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C45" t="s">
         <v>153</v>
       </c>
       <c r="D45" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E45">
-        <v>98.41000366210938</v>
+        <v>33.08000183105469</v>
       </c>
       <c r="F45">
-        <v>370883.3333333333</v>
+        <v>755920</v>
       </c>
       <c r="G45">
-        <v>81.93850189208985</v>
+        <v>31.49399982452393</v>
       </c>
       <c r="H45">
-        <v>71.21264709472656</v>
+        <v>26.081233253479</v>
       </c>
       <c r="I45">
-        <v>69.43418756484985</v>
+        <v>24.19652495384216</v>
       </c>
       <c r="J45">
-        <v>65.81490358352661</v>
+        <v>22.89752494812012</v>
       </c>
       <c r="K45">
-        <v>10.32766056060791</v>
+        <v>0.1500000059604645</v>
       </c>
       <c r="L45">
-        <v>101.0999984741211</v>
+        <v>38.15000152587891</v>
       </c>
       <c r="M45">
-        <v>139.4100820864048</v>
+        <v>144.1963885214341</v>
       </c>
       <c r="N45">
-        <v>5.49</v>
+        <v>0.13</v>
       </c>
       <c r="O45">
-        <v>5.52</v>
+        <v>0.01</v>
       </c>
       <c r="P45">
-        <v>2.95</v>
+        <v>-0.02</v>
       </c>
       <c r="Q45">
-        <v>2.43</v>
+        <v>-0.36</v>
       </c>
       <c r="R45">
-        <v>219587000</v>
+        <v>668000</v>
       </c>
       <c r="S45">
-        <v>117360000</v>
+        <v>-934000</v>
       </c>
       <c r="T45">
-        <v>96733000</v>
+        <v>-21005000</v>
       </c>
       <c r="U45">
-        <v>857658000</v>
+        <v>10650000</v>
       </c>
       <c r="V45" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="46" spans="1:22">
@@ -4228,67 +4246,67 @@
         <v>66</v>
       </c>
       <c r="B46" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C46" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D46" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E46">
-        <v>78.72000122070312</v>
+        <v>139.9900054931641</v>
       </c>
       <c r="F46">
-        <v>1742633.333333333</v>
+        <v>923976.6666666666</v>
       </c>
       <c r="G46">
-        <v>73.49621383666992</v>
+        <v>123.9638008117676</v>
       </c>
       <c r="H46">
-        <v>62.8092975362142</v>
+        <v>105.6282670593262</v>
       </c>
       <c r="I46">
-        <v>58.22762813568115</v>
+        <v>101.2659502410889</v>
       </c>
       <c r="J46">
-        <v>54.55701274871826</v>
+        <v>96.09600006103516</v>
       </c>
       <c r="K46">
-        <v>0.5197567343711853</v>
+        <v>4.719488620758057</v>
       </c>
       <c r="L46">
-        <v>83.51999664306641</v>
+        <v>140.0700073242188</v>
       </c>
       <c r="M46">
-        <v>138.790548646384</v>
+        <v>143.5475586451923</v>
       </c>
       <c r="N46">
-        <v>2.35</v>
+        <v>4.84</v>
       </c>
       <c r="O46">
-        <v>5.63</v>
+        <v>1.32</v>
       </c>
       <c r="P46">
-        <v>1.7</v>
+        <v>4.17</v>
       </c>
       <c r="Q46">
-        <v>2.85</v>
+        <v>3.78</v>
       </c>
       <c r="R46">
-        <v>640536000</v>
+        <v>1241000000</v>
       </c>
       <c r="S46">
-        <v>191530000</v>
+        <v>383000000</v>
       </c>
       <c r="T46">
-        <v>320216000</v>
+        <v>345000000</v>
       </c>
       <c r="U46">
-        <v>1326126000</v>
+        <v>1320000000</v>
       </c>
       <c r="V46" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -4296,67 +4314,67 @@
         <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C47" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="D47" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E47">
-        <v>13.89000034332275</v>
+        <v>29.73999977111816</v>
       </c>
       <c r="F47">
-        <v>1247623.1</v>
+        <v>545486.6666666666</v>
       </c>
       <c r="G47">
-        <v>10.21729988098144</v>
+        <v>24.98899993896485</v>
       </c>
       <c r="H47">
-        <v>10.11725797017415</v>
+        <v>22.08066665013631</v>
       </c>
       <c r="I47">
-        <v>10.04098649501801</v>
+        <v>21.12449999809265</v>
       </c>
       <c r="J47">
-        <v>9.983236494064331</v>
+        <v>19.89394999027252</v>
       </c>
       <c r="K47">
-        <v>8.989999771118164</v>
+        <v>4.372677803039551</v>
       </c>
       <c r="L47">
-        <v>13.89000034332275</v>
+        <v>29.73999977111816</v>
       </c>
       <c r="M47">
-        <v>138.3680107024486</v>
+        <v>143.438543036451</v>
       </c>
       <c r="N47">
-        <v>-0.08</v>
+        <v>0.62</v>
       </c>
       <c r="O47">
-        <v>0.090181</v>
+        <v>0.51</v>
       </c>
       <c r="P47">
-        <v>0.02</v>
+        <v>1.27</v>
       </c>
       <c r="Q47">
-        <v>-0.08</v>
+        <v>1.89</v>
       </c>
       <c r="R47">
-        <v>366476</v>
+        <v>20311465</v>
       </c>
       <c r="S47">
-        <v>900174</v>
+        <v>51263710</v>
       </c>
       <c r="T47">
-        <v>-1652348</v>
+        <v>76021035</v>
       </c>
       <c r="U47">
-        <v>5796203</v>
+        <v>131806125</v>
       </c>
       <c r="V47" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="48" spans="1:22">
@@ -4364,67 +4382,67 @@
         <v>68</v>
       </c>
       <c r="B48" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C48" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D48" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E48">
-        <v>93.41999816894531</v>
+        <v>129.1000061035156</v>
       </c>
       <c r="F48">
-        <v>435476.6666666667</v>
+        <v>258240</v>
       </c>
       <c r="G48">
-        <v>89.41626190185546</v>
+        <v>120.8787998962402</v>
       </c>
       <c r="H48">
-        <v>74.65004641215006</v>
+        <v>94.18380020141602</v>
       </c>
       <c r="I48">
-        <v>67.97378040313721</v>
+        <v>89.31995018005371</v>
       </c>
       <c r="J48">
-        <v>62.87370779037476</v>
+        <v>83.91300016403198</v>
       </c>
       <c r="K48">
-        <v>1.604847550392151</v>
+        <v>8.189999580383301</v>
       </c>
       <c r="L48">
-        <v>98.38999938964844</v>
+        <v>130.3200073242188</v>
       </c>
       <c r="M48">
-        <v>138.157100233013</v>
+        <v>141.8728480770349</v>
       </c>
       <c r="N48">
-        <v>0.6899999999999999</v>
+        <v>-1.76</v>
       </c>
       <c r="O48">
-        <v>0.74</v>
+        <v>-1.1</v>
       </c>
       <c r="P48">
-        <v>1.08</v>
+        <v>-1.17</v>
       </c>
       <c r="Q48">
-        <v>3.58</v>
+        <v>-1.76</v>
       </c>
       <c r="R48">
-        <v>22222000</v>
+        <v>-129729000</v>
       </c>
       <c r="S48">
-        <v>32408000</v>
+        <v>-32052000</v>
       </c>
       <c r="T48">
-        <v>105259000</v>
+        <v>-45297000</v>
       </c>
       <c r="U48">
-        <v>93693000</v>
+        <v>-139975000</v>
       </c>
       <c r="V48" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="49" spans="1:22">
@@ -4432,67 +4450,67 @@
         <v>69</v>
       </c>
       <c r="B49" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C49" t="s">
         <v>155</v>
       </c>
       <c r="D49" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E49">
-        <v>48.54999923706055</v>
+        <v>13.86999988555908</v>
       </c>
       <c r="F49">
-        <v>13610256.66666667</v>
+        <v>9684486.666666666</v>
       </c>
       <c r="G49">
-        <v>41.38315391540527</v>
+        <v>11.2803999710083</v>
       </c>
       <c r="H49">
-        <v>37.62952124277751</v>
+        <v>9.856399997075398</v>
       </c>
       <c r="I49">
-        <v>36.51981247901917</v>
+        <v>9.639600007534026</v>
       </c>
       <c r="J49">
-        <v>34.88607515335083</v>
+        <v>9.333800013065337</v>
       </c>
       <c r="K49">
-        <v>3.483493328094482</v>
+        <v>0.3049550950527191</v>
       </c>
       <c r="L49">
-        <v>62.13346481323242</v>
+        <v>13.86999988555908</v>
       </c>
       <c r="M49">
-        <v>137.4356364370926</v>
+        <v>141.4043040609131</v>
       </c>
       <c r="N49">
-        <v>1.08</v>
+        <v>0.3</v>
       </c>
       <c r="O49">
-        <v>1.29</v>
+        <v>0.3</v>
       </c>
       <c r="P49">
-        <v>-0.57</v>
+        <v>2.87</v>
       </c>
       <c r="Q49">
-        <v>2.84</v>
+        <v>0.55</v>
       </c>
       <c r="R49">
-        <v>1318000000</v>
+        <v>650000000</v>
       </c>
       <c r="S49">
-        <v>-363000000</v>
+        <v>2006000000</v>
       </c>
       <c r="T49">
-        <v>1827000000</v>
+        <v>413000000</v>
       </c>
       <c r="U49">
-        <v>1895000000</v>
+        <v>2501000000</v>
       </c>
       <c r="V49" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="50" spans="1:22">
@@ -4500,67 +4518,67 @@
         <v>70</v>
       </c>
       <c r="B50" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C50" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="D50" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E50">
-        <v>32.20000076293945</v>
+        <v>85.66999816894531</v>
       </c>
       <c r="F50">
-        <v>1129416.666666667</v>
+        <v>479136.6666666667</v>
       </c>
       <c r="G50">
-        <v>31.387200050354</v>
+        <v>77.42539985656738</v>
       </c>
       <c r="H50">
-        <v>25.98313337961833</v>
+        <v>64.79126653035482</v>
       </c>
       <c r="I50">
-        <v>23.76420005321503</v>
+        <v>62.75734991073608</v>
       </c>
       <c r="J50">
-        <v>22.1375500535965</v>
+        <v>59.90284996032715</v>
       </c>
       <c r="K50">
-        <v>6.139999866485596</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="L50">
-        <v>33.66999816894531</v>
+        <v>85.66999816894531</v>
       </c>
       <c r="M50">
-        <v>137.2029525483879</v>
+        <v>141.3977580125558</v>
       </c>
       <c r="N50">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="O50">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="P50">
-        <v>1.98</v>
+        <v>0.88</v>
       </c>
       <c r="Q50">
-        <v>0.73</v>
+        <v>0.25</v>
       </c>
       <c r="R50">
-        <v>149226000</v>
+        <v>154800000</v>
       </c>
       <c r="S50">
-        <v>202973000</v>
+        <v>73300000</v>
       </c>
       <c r="T50">
-        <v>74742000</v>
+        <v>24800000</v>
       </c>
       <c r="U50">
-        <v>576060000</v>
+        <v>458400000</v>
       </c>
       <c r="V50" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -4568,67 +4586,67 @@
         <v>71</v>
       </c>
       <c r="B51" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C51" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="D51" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E51">
-        <v>11.09000015258789</v>
+        <v>93.45999908447266</v>
       </c>
       <c r="F51">
-        <v>7038933.333333333</v>
+        <v>282540</v>
       </c>
       <c r="G51">
-        <v>9.938799991607667</v>
+        <v>77.34000015258789</v>
       </c>
       <c r="H51">
-        <v>8.727599989573161</v>
+        <v>68.58740018208822</v>
       </c>
       <c r="I51">
-        <v>7.841299997568131</v>
+        <v>68.05275018692016</v>
       </c>
       <c r="J51">
-        <v>7.105399988889694</v>
+        <v>66.30505018234253</v>
       </c>
       <c r="K51">
-        <v>2.809999942779541</v>
+        <v>0.2077736556529999</v>
       </c>
       <c r="L51">
-        <v>13.52000045776367</v>
+        <v>124.5500030517578</v>
       </c>
       <c r="M51">
-        <v>136.9102226201362</v>
+        <v>141.3126199421443</v>
       </c>
       <c r="N51">
-        <v>-0.48</v>
+        <v>9.49</v>
       </c>
       <c r="O51">
-        <v>-0.42</v>
+        <v>6.89</v>
       </c>
       <c r="P51">
-        <v>-0.49</v>
+        <v>2.1</v>
       </c>
       <c r="Q51">
-        <v>-0.05</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="R51">
-        <v>-291590000</v>
+        <v>266000000</v>
       </c>
       <c r="S51">
-        <v>-352014000</v>
+        <v>78000000</v>
       </c>
       <c r="T51">
-        <v>-33617000</v>
+        <v>34000000</v>
       </c>
       <c r="U51">
-        <v>-1245475000</v>
+        <v>1063900000</v>
       </c>
       <c r="V51" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="52" spans="1:22">
@@ -4636,67 +4654,67 @@
         <v>72</v>
       </c>
       <c r="B52" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C52" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="D52" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E52">
-        <v>49.54999923706055</v>
+        <v>148.9499969482422</v>
       </c>
       <c r="F52">
-        <v>1472623.333333333</v>
+        <v>393160</v>
       </c>
       <c r="G52">
-        <v>42.17899993896484</v>
+        <v>133.3744003295898</v>
       </c>
       <c r="H52">
-        <v>40.46720006306966</v>
+        <v>118.8800667317708</v>
       </c>
       <c r="I52">
-        <v>37.01715003013611</v>
+        <v>109.2658002090454</v>
       </c>
       <c r="J52">
-        <v>34.61910004615784</v>
+        <v>102.4714002227783</v>
       </c>
       <c r="K52">
-        <v>17.70000076293945</v>
+        <v>0.577300488948822</v>
       </c>
       <c r="L52">
-        <v>52.72000122070312</v>
+        <v>150.4900054931641</v>
       </c>
       <c r="M52">
-        <v>135.6260725025899</v>
+        <v>140.8694707054412</v>
       </c>
       <c r="N52">
-        <v>0.05</v>
+        <v>7.1</v>
       </c>
       <c r="O52">
-        <v>0.26</v>
+        <v>7.09</v>
       </c>
       <c r="P52">
-        <v>0.33</v>
+        <v>3.54</v>
       </c>
       <c r="Q52">
-        <v>0.32</v>
+        <v>5.02</v>
       </c>
       <c r="R52">
-        <v>50614000</v>
+        <v>992192000</v>
       </c>
       <c r="S52">
-        <v>64519000</v>
+        <v>131301000</v>
       </c>
       <c r="T52">
-        <v>61977000</v>
+        <v>186836000</v>
       </c>
       <c r="U52">
-        <v>150996000</v>
+        <v>906239000</v>
       </c>
       <c r="V52" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -4704,67 +4722,67 @@
         <v>73</v>
       </c>
       <c r="B53" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C53" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="D53" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E53">
-        <v>26.04000091552734</v>
+        <v>115.4899978637695</v>
       </c>
       <c r="F53">
-        <v>278070</v>
+        <v>587270</v>
       </c>
       <c r="G53">
-        <v>24.22859996795654</v>
+        <v>97.49600006103516</v>
       </c>
       <c r="H53">
-        <v>19.86346665700277</v>
+        <v>88.86606689453124</v>
       </c>
       <c r="I53">
-        <v>19.48649996757507</v>
+        <v>87.12745002746583</v>
       </c>
       <c r="J53">
-        <v>18.99234993934631</v>
+        <v>83.57795017242432</v>
       </c>
       <c r="K53">
-        <v>7.619999885559082</v>
+        <v>0.3318000435829163</v>
       </c>
       <c r="L53">
-        <v>32.29000091552734</v>
+        <v>149.9608459472656</v>
       </c>
       <c r="M53">
-        <v>135.3487446386117</v>
+        <v>140.4870794589808</v>
       </c>
       <c r="N53">
-        <v>-0.86</v>
+        <v>5.15</v>
       </c>
       <c r="O53">
-        <v>-0.13</v>
+        <v>2.53</v>
       </c>
       <c r="P53">
-        <v>-0.53</v>
+        <v>0.5</v>
       </c>
       <c r="Q53">
-        <v>-0.86</v>
+        <v>2.24</v>
       </c>
       <c r="R53">
-        <v>-63643000</v>
+        <v>136185000</v>
       </c>
       <c r="S53">
-        <v>-81972000</v>
+        <v>27080000</v>
       </c>
       <c r="T53">
-        <v>-39741000</v>
+        <v>120719000</v>
       </c>
       <c r="U53">
-        <v>-131194000</v>
+        <v>792259000</v>
       </c>
       <c r="V53" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -4772,67 +4790,67 @@
         <v>74</v>
       </c>
       <c r="B54" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C54" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="D54" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E54">
-        <v>143.3800048828125</v>
+        <v>53.97000122070312</v>
       </c>
       <c r="F54">
-        <v>1253746.666666667</v>
+        <v>2079556.666666667</v>
       </c>
       <c r="G54">
-        <v>140.7946005249023</v>
+        <v>49.89520004272461</v>
       </c>
       <c r="H54">
-        <v>110.7220669047038</v>
+        <v>42.02586659749349</v>
       </c>
       <c r="I54">
-        <v>107.0011000442505</v>
+        <v>38.96089994430542</v>
       </c>
       <c r="J54">
-        <v>101.9286499786377</v>
+        <v>36.45464996337891</v>
       </c>
       <c r="K54">
-        <v>0.1500000059604645</v>
+        <v>1.498309969902039</v>
       </c>
       <c r="L54">
-        <v>153.1100006103516</v>
+        <v>66.26741027832031</v>
       </c>
       <c r="M54">
-        <v>134.8321626036516</v>
+        <v>140.2491428624017</v>
       </c>
       <c r="N54">
-        <v>0.4</v>
+        <v>2.86</v>
       </c>
       <c r="O54">
-        <v>0.12</v>
+        <v>2.47</v>
       </c>
       <c r="P54">
-        <v>-2.46</v>
+        <v>1.45</v>
       </c>
       <c r="Q54">
-        <v>0.4</v>
+        <v>1.94</v>
       </c>
       <c r="R54">
-        <v>-154116727</v>
+        <v>216410000</v>
       </c>
       <c r="S54">
-        <v>-21223000</v>
+        <v>125500000</v>
       </c>
       <c r="T54">
-        <v>41227000</v>
+        <v>164442000</v>
       </c>
       <c r="U54">
-        <v>-187282000</v>
+        <v>807909000</v>
       </c>
       <c r="V54" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="55" spans="1:22">
@@ -4840,67 +4858,67 @@
         <v>75</v>
       </c>
       <c r="B55" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C55" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D55" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="E55">
-        <v>140.5099945068359</v>
+        <v>32.20999908447266</v>
       </c>
       <c r="F55">
-        <v>355830</v>
+        <v>1359243.333333333</v>
       </c>
       <c r="G55">
-        <v>130.9504643249512</v>
+        <v>30.41409976959228</v>
       </c>
       <c r="H55">
-        <v>116.4943358357747</v>
+        <v>26.47843327840169</v>
       </c>
       <c r="I55">
-        <v>106.8863802337647</v>
+        <v>24.06857495784759</v>
       </c>
       <c r="J55">
-        <v>100.2626465606689</v>
+        <v>22.43542500019073</v>
       </c>
       <c r="K55">
-        <v>0.5746307373046875</v>
+        <v>4.052896976470947</v>
       </c>
       <c r="L55">
-        <v>146.2899932861328</v>
+        <v>33.56000137329102</v>
       </c>
       <c r="M55">
-        <v>134.7560234718916</v>
+        <v>139.9336183503602</v>
       </c>
       <c r="N55">
-        <v>6.77</v>
+        <v>-0.23</v>
       </c>
       <c r="O55">
-        <v>7.1</v>
+        <v>0.2</v>
       </c>
       <c r="P55">
-        <v>7.09</v>
+        <v>0.22</v>
       </c>
       <c r="Q55">
-        <v>3.54</v>
+        <v>0.46</v>
       </c>
       <c r="R55">
-        <v>262489000</v>
+        <v>-193210000</v>
       </c>
       <c r="S55">
-        <v>262365000</v>
+        <v>29397000</v>
       </c>
       <c r="T55">
-        <v>131301000</v>
+        <v>54753000</v>
       </c>
       <c r="U55">
-        <v>992192000</v>
+        <v>58380000</v>
       </c>
       <c r="V55" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="56" spans="1:22">
@@ -4908,67 +4926,67 @@
         <v>76</v>
       </c>
       <c r="B56" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C56" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="D56" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E56">
-        <v>47.65000152587891</v>
+        <v>898.6500244140625</v>
       </c>
       <c r="F56">
-        <v>449590</v>
+        <v>2604360</v>
       </c>
       <c r="G56">
-        <v>46.78674140930175</v>
+        <v>837.84240234375</v>
       </c>
       <c r="H56">
-        <v>40.30638880411784</v>
+        <v>684.0304675292969</v>
       </c>
       <c r="I56">
-        <v>36.39699301719666</v>
+        <v>638.2113000488281</v>
       </c>
       <c r="J56">
-        <v>33.42364406585693</v>
+        <v>596.646849975586</v>
       </c>
       <c r="K56">
-        <v>2.19098949432373</v>
+        <v>11.17089080810547</v>
       </c>
       <c r="L56">
-        <v>53.88000106811523</v>
+        <v>917.989990234375</v>
       </c>
       <c r="M56">
-        <v>134.6681814640669</v>
+        <v>139.6360267235086</v>
       </c>
       <c r="N56">
-        <v>0.7</v>
+        <v>7.132125</v>
       </c>
       <c r="O56">
-        <v>0.98</v>
+        <v>7.810425</v>
       </c>
       <c r="P56">
-        <v>1.16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q56">
-        <v>1.01</v>
+        <v>8.15</v>
       </c>
       <c r="R56">
-        <v>46726000</v>
+        <v>3359000000</v>
       </c>
       <c r="S56">
-        <v>54970000</v>
+        <v>3774000000</v>
       </c>
       <c r="T56">
-        <v>48235000</v>
+        <v>3481000000</v>
       </c>
       <c r="U56">
-        <v>155743000</v>
+        <v>12797000000</v>
       </c>
       <c r="V56" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -4976,67 +4994,67 @@
         <v>77</v>
       </c>
       <c r="B57" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C57" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D57" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E57">
-        <v>120.3099975585938</v>
+        <v>107.75</v>
       </c>
       <c r="F57">
-        <v>272946.6666666667</v>
+        <v>6746123.333333333</v>
       </c>
       <c r="G57">
-        <v>116.9219998168945</v>
+        <v>92.58759994506836</v>
       </c>
       <c r="H57">
-        <v>92.39340006510416</v>
+        <v>81.31779980977376</v>
       </c>
       <c r="I57">
-        <v>87.67545011520386</v>
+        <v>77.84369983673096</v>
       </c>
       <c r="J57">
-        <v>82.48270017623901</v>
+        <v>74.49689985275269</v>
       </c>
       <c r="K57">
-        <v>8.189999580383301</v>
+        <v>0.9100000262260437</v>
       </c>
       <c r="L57">
-        <v>130.3200073242188</v>
+        <v>107.75</v>
       </c>
       <c r="M57">
-        <v>134.0711538924853</v>
+        <v>139.4616192467998</v>
       </c>
       <c r="N57">
-        <v>-1.76</v>
+        <v>1.02</v>
       </c>
       <c r="O57">
-        <v>-1.1</v>
+        <v>0.7</v>
       </c>
       <c r="P57">
-        <v>-1.17</v>
+        <v>1.35</v>
       </c>
       <c r="Q57">
-        <v>-1.76</v>
+        <v>1.03</v>
       </c>
       <c r="R57">
-        <v>-129729000</v>
+        <v>311900000</v>
       </c>
       <c r="S57">
-        <v>-32052000</v>
+        <v>604300000</v>
       </c>
       <c r="T57">
-        <v>-45297000</v>
+        <v>461700000</v>
       </c>
       <c r="U57">
-        <v>-139975000</v>
+        <v>1902200000</v>
       </c>
       <c r="V57" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="58" spans="1:22">
@@ -5044,67 +5062,67 @@
         <v>78</v>
       </c>
       <c r="B58" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C58" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D58" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E58">
-        <v>130.3200073242188</v>
+        <v>367.4400024414062</v>
       </c>
       <c r="F58">
-        <v>827413.3333333334</v>
+        <v>283440</v>
       </c>
       <c r="G58">
-        <v>119.958151550293</v>
+        <v>314.5678009033203</v>
       </c>
       <c r="H58">
-        <v>103.1741015625</v>
+        <v>275.5302675374349</v>
       </c>
       <c r="I58">
-        <v>98.93110095977784</v>
+        <v>268.503800201416</v>
       </c>
       <c r="J58">
-        <v>93.89969982147217</v>
+        <v>258.0759503173828</v>
       </c>
       <c r="K58">
-        <v>4.60856294631958</v>
+        <v>4.775613307952881</v>
       </c>
       <c r="L58">
-        <v>137.5700073242188</v>
+        <v>367.4400024414062</v>
       </c>
       <c r="M58">
-        <v>133.7351266929983</v>
+        <v>139.4311498054925</v>
       </c>
       <c r="N58">
-        <v>3.49</v>
+        <v>3.99</v>
       </c>
       <c r="O58">
-        <v>4.84</v>
+        <v>2.65</v>
       </c>
       <c r="P58">
-        <v>1.32</v>
+        <v>2.75</v>
       </c>
       <c r="Q58">
-        <v>4.17</v>
+        <v>6.1</v>
       </c>
       <c r="R58">
-        <v>470000000</v>
+        <v>497100000</v>
       </c>
       <c r="S58">
-        <v>124000000</v>
+        <v>98000000</v>
       </c>
       <c r="T58">
-        <v>383000000</v>
+        <v>217200000</v>
       </c>
       <c r="U58">
-        <v>1241000000</v>
+        <v>511500000</v>
       </c>
       <c r="V58" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="59" spans="1:22">
@@ -5112,67 +5130,67 @@
         <v>79</v>
       </c>
       <c r="B59" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C59" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="D59" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E59">
-        <v>80.01999664306641</v>
+        <v>51.61000061035156</v>
       </c>
       <c r="F59">
-        <v>320550</v>
+        <v>1566246.666666667</v>
       </c>
       <c r="G59">
-        <v>67.19960739135742</v>
+        <v>43.54999992370605</v>
       </c>
       <c r="H59">
-        <v>62.94471112569173</v>
+        <v>41.23020005544026</v>
       </c>
       <c r="I59">
-        <v>60.17488185882569</v>
+        <v>37.81840002059936</v>
       </c>
       <c r="J59">
-        <v>57.90384149551392</v>
+        <v>35.20355004310608</v>
       </c>
       <c r="K59">
-        <v>10.08381271362305</v>
+        <v>17.70000076293945</v>
       </c>
       <c r="L59">
-        <v>81.51999664306641</v>
+        <v>52.72000122070312</v>
       </c>
       <c r="M59">
-        <v>133.1632653398787</v>
+        <v>139.1903097788406</v>
       </c>
       <c r="N59">
-        <v>2.28</v>
+        <v>0.05</v>
       </c>
       <c r="O59">
-        <v>2.46</v>
+        <v>0.26</v>
       </c>
       <c r="P59">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="Q59">
-        <v>0.57</v>
+        <v>0.32</v>
       </c>
       <c r="R59">
-        <v>135134000</v>
+        <v>50614000</v>
       </c>
       <c r="S59">
-        <v>37617000</v>
+        <v>64519000</v>
       </c>
       <c r="T59">
-        <v>30378000</v>
+        <v>61977000</v>
       </c>
       <c r="U59">
-        <v>475507000</v>
+        <v>150996000</v>
       </c>
       <c r="V59" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -5180,67 +5198,67 @@
         <v>80</v>
       </c>
       <c r="B60" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C60" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D60" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E60">
-        <v>193.9700012207031</v>
+        <v>59.54999923706055</v>
       </c>
       <c r="F60">
-        <v>386076.6666666667</v>
+        <v>5628960</v>
       </c>
       <c r="G60">
-        <v>187.6647994995117</v>
+        <v>48.56000015258789</v>
       </c>
       <c r="H60">
-        <v>156.8656659444173</v>
+        <v>45.50286671956381</v>
       </c>
       <c r="I60">
-        <v>148.4755493164062</v>
+        <v>44.37769998550415</v>
       </c>
       <c r="J60">
-        <v>142.4777493286133</v>
+        <v>42.71944999694824</v>
       </c>
       <c r="K60">
-        <v>0.8828129768371582</v>
+        <v>11.31525421142578</v>
       </c>
       <c r="L60">
-        <v>207.8500061035156</v>
+        <v>59.54999923706055</v>
       </c>
       <c r="M60">
-        <v>133.0840597101596</v>
+        <v>138.9872154111048</v>
       </c>
       <c r="N60">
-        <v>0.49</v>
+        <v>1.53</v>
       </c>
       <c r="O60">
-        <v>0.47</v>
+        <v>0.32</v>
       </c>
       <c r="P60">
-        <v>0.6</v>
+        <v>0.44</v>
       </c>
       <c r="Q60">
-        <v>0.62</v>
+        <v>0.23</v>
       </c>
       <c r="R60">
-        <v>29674000</v>
+        <v>3534000000</v>
       </c>
       <c r="S60">
-        <v>37868000</v>
+        <v>373000000</v>
       </c>
       <c r="T60">
-        <v>38791000</v>
+        <v>199000000</v>
       </c>
       <c r="U60">
-        <v>128959000</v>
+        <v>2528000000</v>
       </c>
       <c r="V60" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="61" spans="1:22">
@@ -5248,67 +5266,67 @@
         <v>81</v>
       </c>
       <c r="B61" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C61" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="D61" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E61">
-        <v>28.28000068664551</v>
+        <v>16.78000068664551</v>
       </c>
       <c r="F61">
-        <v>996290</v>
+        <v>461046.6666666667</v>
       </c>
       <c r="G61">
-        <v>25.2196000289917</v>
+        <v>14.74340003967285</v>
       </c>
       <c r="H61">
-        <v>22.57673327128093</v>
+        <v>13.00906667709351</v>
       </c>
       <c r="I61">
-        <v>21.20119996070862</v>
+        <v>12.95140000343323</v>
       </c>
       <c r="J61">
-        <v>19.94009996891022</v>
+        <v>12.69070001125336</v>
       </c>
       <c r="K61">
-        <v>9.090000152587891</v>
+        <v>10.27999973297119</v>
       </c>
       <c r="L61">
-        <v>28.70999908447266</v>
+        <v>21.03000068664551</v>
       </c>
       <c r="M61">
-        <v>132.79375217751</v>
+        <v>138.6523379055089</v>
       </c>
       <c r="N61">
-        <v>0.06</v>
+        <v>-1.9552</v>
       </c>
       <c r="O61">
-        <v>0.06</v>
+        <v>-0.2692</v>
       </c>
       <c r="P61">
-        <v>0.04</v>
+        <v>-0.0328</v>
       </c>
       <c r="Q61">
-        <v>0.05</v>
+        <v>-1.9552</v>
       </c>
       <c r="R61">
-        <v>28000000</v>
+        <v>-201907000</v>
       </c>
       <c r="S61">
-        <v>22000000</v>
+        <v>993042000</v>
       </c>
       <c r="T61">
-        <v>26000000</v>
+        <v>-904131000</v>
       </c>
       <c r="U61">
-        <v>73000000</v>
+        <v>1176032000</v>
       </c>
       <c r="V61" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="62" spans="1:22">
@@ -5316,67 +5334,67 @@
         <v>82</v>
       </c>
       <c r="B62" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C62" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="D62" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E62">
-        <v>30.79000091552734</v>
+        <v>124.3199996948242</v>
       </c>
       <c r="F62">
-        <v>1449116.666666667</v>
+        <v>349993.3333333333</v>
       </c>
       <c r="G62">
-        <v>28.92540004730225</v>
+        <v>109.1179997253418</v>
       </c>
       <c r="H62">
-        <v>24.62460001627604</v>
+        <v>90.55213322957357</v>
       </c>
       <c r="I62">
-        <v>23.90160002708435</v>
+        <v>86.11849992752076</v>
       </c>
       <c r="J62">
-        <v>23.16205004692078</v>
+        <v>81.69059991836548</v>
       </c>
       <c r="K62">
-        <v>18.89999961853027</v>
+        <v>20.81999969482422</v>
       </c>
       <c r="L62">
-        <v>31.79000091552734</v>
+        <v>124.3199996948242</v>
       </c>
       <c r="M62">
-        <v>132.7275798955153</v>
+        <v>138.5104684789908</v>
       </c>
       <c r="N62">
-        <v>0.67</v>
+        <v>1.03</v>
       </c>
       <c r="O62">
-        <v>0.65</v>
+        <v>1.05</v>
       </c>
       <c r="P62">
-        <v>0.31</v>
+        <v>1.34</v>
       </c>
       <c r="Q62">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="R62">
-        <v>111000000</v>
+        <v>52215000</v>
       </c>
       <c r="S62">
-        <v>54000000</v>
+        <v>66214000</v>
       </c>
       <c r="T62">
-        <v>86000000</v>
+        <v>29068000</v>
       </c>
       <c r="U62">
-        <v>366000000</v>
+        <v>223334000</v>
       </c>
       <c r="V62" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="63" spans="1:22">
@@ -5384,67 +5402,67 @@
         <v>83</v>
       </c>
       <c r="B63" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C63" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="D63" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E63">
-        <v>90.61000061035156</v>
+        <v>59.86000061035156</v>
       </c>
       <c r="F63">
-        <v>504030</v>
+        <v>358796.6666666667</v>
       </c>
       <c r="G63">
-        <v>80.5011001586914</v>
+        <v>52.81380012512207</v>
       </c>
       <c r="H63">
-        <v>73.20286677042644</v>
+        <v>48.1241333770752</v>
       </c>
       <c r="I63">
-        <v>67.87350004196168</v>
+        <v>45.76340009689331</v>
       </c>
       <c r="J63">
-        <v>63.98875005722046</v>
+        <v>43.54930004119873</v>
       </c>
       <c r="K63">
-        <v>10.5</v>
+        <v>0.07982486486434937</v>
       </c>
       <c r="L63">
-        <v>96.06999969482422</v>
+        <v>59.86000061035156</v>
       </c>
       <c r="M63">
-        <v>132.4402992601575</v>
+        <v>138.4862618209644</v>
       </c>
       <c r="N63">
-        <v>-0.41</v>
+        <v>0.05</v>
       </c>
       <c r="O63">
-        <v>-0.25</v>
+        <v>-0.14</v>
       </c>
       <c r="P63">
-        <v>-0.21</v>
+        <v>0.13</v>
       </c>
       <c r="Q63">
-        <v>-0.08</v>
+        <v>0.38</v>
       </c>
       <c r="R63">
-        <v>-7426000</v>
+        <v>-6900000</v>
       </c>
       <c r="S63">
-        <v>-6720000</v>
+        <v>6200000</v>
       </c>
       <c r="T63">
-        <v>-2636000</v>
+        <v>18600000</v>
       </c>
       <c r="U63">
-        <v>-36231000</v>
+        <v>-5600000</v>
       </c>
       <c r="V63" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -5455,64 +5473,64 @@
         <v>117</v>
       </c>
       <c r="C64" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D64" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E64">
-        <v>109.0699996948242</v>
+        <v>75.51999664306641</v>
       </c>
       <c r="F64">
-        <v>297310</v>
+        <v>677023.3333333334</v>
       </c>
       <c r="G64">
-        <v>100.9205131530762</v>
+        <v>69.94299995422364</v>
       </c>
       <c r="H64">
-        <v>88.46315073649089</v>
+        <v>58.79373321533203</v>
       </c>
       <c r="I64">
-        <v>83.50324123382569</v>
+        <v>56.46784992218018</v>
       </c>
       <c r="J64">
-        <v>78.79475458145141</v>
+        <v>53.32889993667602</v>
       </c>
       <c r="K64">
-        <v>5.390120983123779</v>
+        <v>23.54999923706055</v>
       </c>
       <c r="L64">
-        <v>112.9800033569336</v>
+        <v>76.5</v>
       </c>
       <c r="M64">
-        <v>132.1881413205918</v>
+        <v>138.2292759605373</v>
       </c>
       <c r="N64">
-        <v>0.75</v>
+        <v>-1.24</v>
       </c>
       <c r="O64">
-        <v>0.84</v>
+        <v>-0.68</v>
       </c>
       <c r="P64">
-        <v>1.08</v>
+        <v>-1.24</v>
       </c>
       <c r="Q64">
-        <v>1.59</v>
+        <v>-0.68</v>
       </c>
       <c r="R64">
-        <v>34500</v>
+        <v>-526161000</v>
       </c>
       <c r="S64">
-        <v>44410000</v>
+        <v>-193228000</v>
       </c>
       <c r="T64">
-        <v>65900000</v>
+        <v>-112101000</v>
       </c>
       <c r="U64">
-        <v>137952000</v>
+        <v>-446349000</v>
       </c>
       <c r="V64" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5520,67 +5538,67 @@
         <v>85</v>
       </c>
       <c r="B65" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C65" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D65" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E65">
-        <v>160.3800048828125</v>
+        <v>13.89000034332275</v>
       </c>
       <c r="F65">
-        <v>1656166.666666667</v>
+        <v>1247623.1</v>
       </c>
       <c r="G65">
-        <v>138.9756001281738</v>
+        <v>10.21729988098144</v>
       </c>
       <c r="H65">
-        <v>127.3375998942057</v>
+        <v>10.11725797017415</v>
       </c>
       <c r="I65">
-        <v>123.9741498565674</v>
+        <v>10.04098649501801</v>
       </c>
       <c r="J65">
-        <v>120.2457498931885</v>
+        <v>9.983236494064331</v>
       </c>
       <c r="K65">
-        <v>12.18373107910156</v>
+        <v>8.989999771118164</v>
       </c>
       <c r="L65">
-        <v>168.5816802978516</v>
+        <v>13.89000034332275</v>
       </c>
       <c r="M65">
-        <v>132.090161416676</v>
+        <v>138.2251659760368</v>
       </c>
       <c r="N65">
-        <v>0.82</v>
+        <v>-0.08</v>
       </c>
       <c r="O65">
-        <v>0.54</v>
+        <v>0.090181</v>
       </c>
       <c r="P65">
-        <v>1.15</v>
+        <v>0.02</v>
       </c>
       <c r="Q65">
-        <v>0.52</v>
+        <v>-0.08</v>
       </c>
       <c r="R65">
-        <v>231000000</v>
+        <v>366476</v>
       </c>
       <c r="S65">
-        <v>494000000</v>
+        <v>900174</v>
       </c>
       <c r="T65">
-        <v>224000000</v>
+        <v>-1652348</v>
       </c>
       <c r="U65">
-        <v>1314000000</v>
+        <v>5796203</v>
       </c>
       <c r="V65" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5588,67 +5606,67 @@
         <v>86</v>
       </c>
       <c r="B66" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C66" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="D66" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E66">
-        <v>118.1500015258789</v>
+        <v>13.47999954223633</v>
       </c>
       <c r="F66">
-        <v>735240</v>
+        <v>513820</v>
       </c>
       <c r="G66">
-        <v>109.1914739990234</v>
+        <v>12.79540002822876</v>
       </c>
       <c r="H66">
-        <v>95.24147847493489</v>
+        <v>10.76886667251587</v>
       </c>
       <c r="I66">
-        <v>90.56054180145264</v>
+        <v>10.16819999694824</v>
       </c>
       <c r="J66">
-        <v>86.34651136398315</v>
+        <v>9.689499990940094</v>
       </c>
       <c r="K66">
-        <v>13.2287483215332</v>
+        <v>6.639999866485596</v>
       </c>
       <c r="L66">
-        <v>129.3752899169922</v>
+        <v>13.81999969482422</v>
       </c>
       <c r="M66">
-        <v>131.7506249114107</v>
+        <v>137.9516076787338</v>
       </c>
       <c r="N66">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O66">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P66">
-        <v>2.23</v>
+        <v>1.17</v>
       </c>
       <c r="Q66">
-        <v>3.07</v>
+        <v>1.17</v>
       </c>
       <c r="R66">
-        <v>115939000</v>
+        <v>-77781000</v>
       </c>
       <c r="S66">
-        <v>88280000</v>
+        <v>-64977000</v>
       </c>
       <c r="T66">
-        <v>121521000</v>
+        <v>259425000</v>
       </c>
       <c r="U66">
-        <v>348054000</v>
+        <v>30506000</v>
       </c>
       <c r="V66" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -5656,67 +5674,67 @@
         <v>87</v>
       </c>
       <c r="B67" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C67" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D67" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E67">
-        <v>127.5800018310547</v>
+        <v>144.6999969482422</v>
       </c>
       <c r="F67">
-        <v>3250226.666666667</v>
+        <v>1207866.666666667</v>
       </c>
       <c r="G67">
-        <v>116.1387998962402</v>
+        <v>142.5690002441406</v>
       </c>
       <c r="H67">
-        <v>103.0374997965495</v>
+        <v>112.2022001647949</v>
       </c>
       <c r="I67">
-        <v>96.69355331420898</v>
+        <v>108.7000500106812</v>
       </c>
       <c r="J67">
-        <v>91.43230499267578</v>
+        <v>103.3562500762939</v>
       </c>
       <c r="K67">
-        <v>0.7455874085426331</v>
+        <v>0.1500000059604645</v>
       </c>
       <c r="L67">
-        <v>130.3099975585938</v>
+        <v>153.1100006103516</v>
       </c>
       <c r="M67">
-        <v>131.6921247062887</v>
+        <v>137.7039096910782</v>
       </c>
       <c r="N67">
-        <v>4.67</v>
+        <v>0.4</v>
       </c>
       <c r="O67">
-        <v>2.76</v>
+        <v>0.12</v>
       </c>
       <c r="P67">
-        <v>2.73</v>
+        <v>-2.46</v>
       </c>
       <c r="Q67">
-        <v>3.9</v>
+        <v>0.4</v>
       </c>
       <c r="R67">
-        <v>5674600000</v>
+        <v>-154116727</v>
       </c>
       <c r="S67">
-        <v>942200000</v>
+        <v>-21223000</v>
       </c>
       <c r="T67">
-        <v>1335100000</v>
+        <v>41227000</v>
       </c>
       <c r="U67">
-        <v>5180500000</v>
+        <v>-187282000</v>
       </c>
       <c r="V67" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5724,67 +5742,67 @@
         <v>88</v>
       </c>
       <c r="B68" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C68" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="D68" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="E68">
-        <v>537.5499877929688</v>
+        <v>80.33000183105469</v>
       </c>
       <c r="F68">
-        <v>350370</v>
+        <v>1640953.333333333</v>
       </c>
       <c r="G68">
-        <v>503.1475982666016</v>
+        <v>75.4352001953125</v>
       </c>
       <c r="H68">
-        <v>453.902666015625</v>
+        <v>64.24980013529459</v>
       </c>
       <c r="I68">
-        <v>430.068649597168</v>
+        <v>59.59305017471313</v>
       </c>
       <c r="J68">
-        <v>409.9953004455567</v>
+        <v>55.93175008773804</v>
       </c>
       <c r="K68">
-        <v>0.4583329856395721</v>
+        <v>0.5319142937660217</v>
       </c>
       <c r="L68">
-        <v>553.3200073242188</v>
+        <v>83.51999664306641</v>
       </c>
       <c r="M68">
-        <v>131.5599533617691</v>
+        <v>137.6168911600767</v>
       </c>
       <c r="N68">
-        <v>1.66</v>
+        <v>2.35</v>
       </c>
       <c r="O68">
-        <v>3.8</v>
+        <v>5.63</v>
       </c>
       <c r="P68">
-        <v>10.48</v>
+        <v>1.7</v>
       </c>
       <c r="Q68">
-        <v>3.46</v>
+        <v>2.85</v>
       </c>
       <c r="R68">
-        <v>101524000</v>
+        <v>640536000</v>
       </c>
       <c r="S68">
-        <v>278662000</v>
+        <v>191530000</v>
       </c>
       <c r="T68">
-        <v>91787000</v>
+        <v>320216000</v>
       </c>
       <c r="U68">
-        <v>493854000</v>
+        <v>1326126000</v>
       </c>
       <c r="V68" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="69" spans="1:22">
@@ -5792,67 +5810,67 @@
         <v>89</v>
       </c>
       <c r="B69" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C69" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D69" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E69">
-        <v>74.66000366210938</v>
+        <v>51.27999877929688</v>
       </c>
       <c r="F69">
-        <v>745603.3333333334</v>
+        <v>802423.3333333334</v>
       </c>
       <c r="G69">
-        <v>69.48740013122558</v>
+        <v>45.07120002746582</v>
       </c>
       <c r="H69">
-        <v>57.81919993082682</v>
+        <v>40.07406661987304</v>
       </c>
       <c r="I69">
-        <v>55.41689994812012</v>
+        <v>37.81209995269776</v>
       </c>
       <c r="J69">
-        <v>52.50504995346069</v>
+        <v>35.95589994430542</v>
       </c>
       <c r="K69">
-        <v>23.54999923706055</v>
+        <v>0.02175931446254253</v>
       </c>
       <c r="L69">
-        <v>76.01000213623047</v>
+        <v>59.96058654785156</v>
       </c>
       <c r="M69">
-        <v>131.2217491777038</v>
+        <v>137.3209600504246</v>
       </c>
       <c r="N69">
-        <v>-1.24</v>
+        <v>1.98</v>
       </c>
       <c r="O69">
-        <v>-0.68</v>
+        <v>1.08</v>
       </c>
       <c r="P69">
-        <v>-1.24</v>
+        <v>1.08</v>
       </c>
       <c r="Q69">
-        <v>-0.68</v>
+        <v>1.24</v>
       </c>
       <c r="R69">
-        <v>-526161000</v>
+        <v>562139000</v>
       </c>
       <c r="S69">
-        <v>-193228000</v>
+        <v>80700000</v>
       </c>
       <c r="T69">
-        <v>-112101000</v>
+        <v>93493000</v>
       </c>
       <c r="U69">
-        <v>-446349000</v>
+        <v>494418000</v>
       </c>
       <c r="V69" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5860,67 +5878,67 @@
         <v>90</v>
       </c>
       <c r="B70" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C70" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D70" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="E70">
-        <v>16.45999908447266</v>
+        <v>33.83000183105469</v>
       </c>
       <c r="F70">
-        <v>467666.6666666667</v>
+        <v>1265050</v>
       </c>
       <c r="G70">
-        <v>14.23367879867554</v>
+        <v>30.13739994049072</v>
       </c>
       <c r="H70">
-        <v>12.59488197962443</v>
+        <v>27.30466659545898</v>
       </c>
       <c r="I70">
-        <v>12.5812768983841</v>
+        <v>26.02739996910095</v>
       </c>
       <c r="J70">
-        <v>12.3854549741745</v>
+        <v>24.4575999879837</v>
       </c>
       <c r="K70">
-        <v>10.00760269165039</v>
+        <v>0.1598737090826035</v>
       </c>
       <c r="L70">
-        <v>19.65240669250488</v>
+        <v>33.83000183105469</v>
       </c>
       <c r="M70">
-        <v>131.1528715465286</v>
+        <v>136.7497833782667</v>
       </c>
       <c r="N70">
-        <v>-1.9552</v>
+        <v>0.11</v>
       </c>
       <c r="O70">
-        <v>-0.2692</v>
+        <v>-0.02</v>
       </c>
       <c r="P70">
-        <v>-0.0328</v>
+        <v>1.3</v>
       </c>
       <c r="Q70">
-        <v>-1.9552</v>
+        <v>0.11</v>
       </c>
       <c r="R70">
-        <v>-201907000</v>
+        <v>359000000</v>
       </c>
       <c r="S70">
-        <v>993042000</v>
+        <v>-64000000</v>
       </c>
       <c r="T70">
-        <v>-904131000</v>
+        <v>23000000</v>
       </c>
       <c r="U70">
-        <v>1176032000</v>
+        <v>275000000</v>
       </c>
       <c r="V70" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -5928,67 +5946,67 @@
         <v>91</v>
       </c>
       <c r="B71" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C71" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D71" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E71">
-        <v>10.6899995803833</v>
+        <v>15.86999988555908</v>
       </c>
       <c r="F71">
-        <v>490886.6666666667</v>
+        <v>912300</v>
       </c>
       <c r="G71">
-        <v>9.41019998550415</v>
+        <v>12.8510000038147</v>
       </c>
       <c r="H71">
-        <v>8.443274218241374</v>
+        <v>12.55400000890096</v>
       </c>
       <c r="I71">
-        <v>8.338653690814972</v>
+        <v>12.1385000038147</v>
       </c>
       <c r="J71">
-        <v>8.164685616493225</v>
+        <v>11.76915000915527</v>
       </c>
       <c r="K71">
-        <v>3.371170282363892</v>
+        <v>9.039999961853027</v>
       </c>
       <c r="L71">
-        <v>12.81994342803955</v>
+        <v>15.86999988555908</v>
       </c>
       <c r="M71">
-        <v>131.1129378658328</v>
+        <v>136.5836952936951</v>
       </c>
       <c r="N71">
-        <v>0.168</v>
+        <v>0</v>
       </c>
       <c r="O71">
-        <v>0.205</v>
+        <v>0</v>
       </c>
       <c r="P71">
-        <v>0.024961</v>
+        <v>0</v>
       </c>
       <c r="Q71">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R71">
-        <v>22548000</v>
+        <v>0</v>
       </c>
       <c r="S71">
-        <v>2732000</v>
+        <v>-150120000</v>
       </c>
       <c r="T71">
-        <v>21569000</v>
+        <v>-150120000</v>
       </c>
       <c r="U71">
-        <v>108138000</v>
+        <v>51482000</v>
       </c>
       <c r="V71" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5999,64 +6017,64 @@
         <v>117</v>
       </c>
       <c r="C72" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="D72" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E72">
-        <v>29.92000007629395</v>
+        <v>93.18000030517578</v>
       </c>
       <c r="F72">
-        <v>415013.3333333333</v>
+        <v>402826.6666666667</v>
       </c>
       <c r="G72">
-        <v>26.8639998626709</v>
+        <v>82.33840011596679</v>
       </c>
       <c r="H72">
-        <v>23.77906661987305</v>
+        <v>74.50480010986328</v>
       </c>
       <c r="I72">
-        <v>23.35464994430542</v>
+        <v>69.33780006408692</v>
       </c>
       <c r="J72">
-        <v>22.91094995498657</v>
+        <v>64.86175004959107</v>
       </c>
       <c r="K72">
-        <v>1.970000028610229</v>
+        <v>10.5</v>
       </c>
       <c r="L72">
-        <v>30.61000061035156</v>
+        <v>96.06999969482422</v>
       </c>
       <c r="M72">
-        <v>131.0944142963648</v>
+        <v>136.4452698276311</v>
       </c>
       <c r="N72">
-        <v>-0.04</v>
+        <v>-0.41</v>
       </c>
       <c r="O72">
-        <v>0.08</v>
+        <v>-0.25</v>
       </c>
       <c r="P72">
-        <v>0.24</v>
+        <v>-0.21</v>
       </c>
       <c r="Q72">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="R72">
-        <v>4789000</v>
+        <v>-7426000</v>
       </c>
       <c r="S72">
-        <v>13725000</v>
+        <v>-6720000</v>
       </c>
       <c r="T72">
-        <v>-6296000</v>
+        <v>-2636000</v>
       </c>
       <c r="U72">
-        <v>24049000</v>
+        <v>-36231000</v>
       </c>
       <c r="V72" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -6064,67 +6082,67 @@
         <v>93</v>
       </c>
       <c r="B73" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C73" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="D73" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="E73">
-        <v>16.54000091552734</v>
+        <v>718.489990234375</v>
       </c>
       <c r="F73">
-        <v>5285310</v>
+        <v>1336443.333333333</v>
       </c>
       <c r="G73">
-        <v>13.99048812866211</v>
+        <v>627.3242004394531</v>
       </c>
       <c r="H73">
-        <v>12.94481492360433</v>
+        <v>538.5065325927734</v>
       </c>
       <c r="I73">
-        <v>12.85846347332001</v>
+        <v>510.0912493896485</v>
       </c>
       <c r="J73">
-        <v>12.58797719478607</v>
+        <v>484.072649230957</v>
       </c>
       <c r="K73">
-        <v>0.2171852588653564</v>
+        <v>0.5958155393600464</v>
       </c>
       <c r="L73">
-        <v>17.37691307067871</v>
+        <v>729.8200073242188</v>
       </c>
       <c r="M73">
-        <v>131.0332404735889</v>
+        <v>136.2603888711199</v>
       </c>
       <c r="N73">
-        <v>0.41</v>
+        <v>10.39</v>
       </c>
       <c r="O73">
-        <v>0.36</v>
+        <v>10.77</v>
       </c>
       <c r="P73">
-        <v>0.49</v>
+        <v>6.01</v>
       </c>
       <c r="Q73">
-        <v>0.46</v>
+        <v>5.97</v>
       </c>
       <c r="R73">
-        <v>73052000</v>
+        <v>5125098000</v>
       </c>
       <c r="S73">
-        <v>98494000</v>
+        <v>814008000</v>
       </c>
       <c r="T73">
-        <v>94661000</v>
+        <v>802537000</v>
       </c>
       <c r="U73">
-        <v>325783000</v>
+        <v>4917328000</v>
       </c>
       <c r="V73" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -6132,67 +6150,67 @@
         <v>94</v>
       </c>
       <c r="B74" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C74" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="D74" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E74">
-        <v>109.8099975585938</v>
+        <v>116.3199996948242</v>
       </c>
       <c r="F74">
-        <v>631520</v>
+        <v>455450</v>
       </c>
       <c r="G74">
-        <v>93.22016235351562</v>
+        <v>94.72599975585938</v>
       </c>
       <c r="H74">
-        <v>86.91152938842774</v>
+        <v>90.89619979858398</v>
       </c>
       <c r="I74">
-        <v>85.12941860198974</v>
+        <v>87.67859992980956</v>
       </c>
       <c r="J74">
-        <v>81.98432586669922</v>
+        <v>84.63469993591309</v>
       </c>
       <c r="K74">
-        <v>0.3210051953792572</v>
+        <v>3.099249601364136</v>
       </c>
       <c r="L74">
-        <v>145.0883178710938</v>
+        <v>121.8199996948242</v>
       </c>
       <c r="M74">
-        <v>130.8406668280275</v>
+        <v>136.2020114899823</v>
       </c>
       <c r="N74">
-        <v>5.15</v>
+        <v>3.5</v>
       </c>
       <c r="O74">
-        <v>2.53</v>
+        <v>1.48</v>
       </c>
       <c r="P74">
-        <v>0.5</v>
+        <v>2.84</v>
       </c>
       <c r="Q74">
-        <v>2.24</v>
+        <v>1.64</v>
       </c>
       <c r="R74">
-        <v>136185000</v>
+        <v>298209000</v>
       </c>
       <c r="S74">
-        <v>27080000</v>
+        <v>71283000</v>
       </c>
       <c r="T74">
-        <v>120719000</v>
+        <v>40443000</v>
       </c>
       <c r="U74">
-        <v>792259000</v>
+        <v>299923000</v>
       </c>
       <c r="V74" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -6200,67 +6218,67 @@
         <v>95</v>
       </c>
       <c r="B75" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C75" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D75" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E75">
-        <v>190.9100036621094</v>
+        <v>35.15999984741211</v>
       </c>
       <c r="F75">
-        <v>351960</v>
+        <v>3874016.666666667</v>
       </c>
       <c r="G75">
-        <v>173.2293246459961</v>
+        <v>30.74520004272461</v>
       </c>
       <c r="H75">
-        <v>152.2605650838216</v>
+        <v>27.72946669260661</v>
       </c>
       <c r="I75">
-        <v>145.2514926528931</v>
+        <v>26.59060001373291</v>
       </c>
       <c r="J75">
-        <v>137.9174468612671</v>
+        <v>26.09935001373291</v>
       </c>
       <c r="K75">
-        <v>2.114836454391479</v>
+        <v>1.243403434753418</v>
       </c>
       <c r="L75">
-        <v>192.9400024414062</v>
+        <v>44.90747833251953</v>
       </c>
       <c r="M75">
-        <v>130.797735246736</v>
+        <v>136.1365227108579</v>
       </c>
       <c r="N75">
-        <v>2.75</v>
+        <v>0.27</v>
       </c>
       <c r="O75">
-        <v>3.72</v>
+        <v>0.21</v>
       </c>
       <c r="P75">
-        <v>3.2</v>
+        <v>-0.05</v>
       </c>
       <c r="Q75">
-        <v>2.79</v>
+        <v>0.27</v>
       </c>
       <c r="R75">
-        <v>138995000</v>
+        <v>-19530000</v>
       </c>
       <c r="S75">
-        <v>117184000</v>
+        <v>-15417000</v>
       </c>
       <c r="T75">
-        <v>100356000</v>
+        <v>118969000</v>
       </c>
       <c r="U75">
-        <v>435500000</v>
+        <v>89382000</v>
       </c>
       <c r="V75" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -6271,64 +6289,64 @@
         <v>116</v>
       </c>
       <c r="C76" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="D76" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E76">
-        <v>33</v>
+        <v>249.9600067138672</v>
       </c>
       <c r="F76">
-        <v>1629473.333333333</v>
+        <v>6436760</v>
       </c>
       <c r="G76">
-        <v>29.20825660705566</v>
+        <v>234.1404000854492</v>
       </c>
       <c r="H76">
-        <v>26.67294521331787</v>
+        <v>194.5357333374023</v>
       </c>
       <c r="I76">
-        <v>25.25476930618286</v>
+        <v>186.3620999145508</v>
       </c>
       <c r="J76">
-        <v>23.72711111068726</v>
+        <v>178.6773498535156</v>
       </c>
       <c r="K76">
-        <v>0.1737031638622284</v>
+        <v>13.18666744232178</v>
       </c>
       <c r="L76">
-        <v>33.22999954223633</v>
+        <v>257.8800048828125</v>
       </c>
       <c r="M76">
-        <v>130.7137570071686</v>
+        <v>135.4600862620373</v>
       </c>
       <c r="N76">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="O76">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="P76">
-        <v>1.3</v>
+        <v>0.25</v>
       </c>
       <c r="Q76">
-        <v>0.11</v>
+        <v>0.31</v>
       </c>
       <c r="R76">
-        <v>359000000</v>
+        <v>20000000</v>
       </c>
       <c r="S76">
-        <v>-64000000</v>
+        <v>84200000</v>
       </c>
       <c r="T76">
-        <v>23000000</v>
+        <v>107800000</v>
       </c>
       <c r="U76">
-        <v>275000000</v>
+        <v>34300000</v>
       </c>
       <c r="V76" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="77" spans="1:22">
@@ -6336,67 +6354,67 @@
         <v>97</v>
       </c>
       <c r="B77" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C77" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="D77" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E77">
-        <v>333.739990234375</v>
+        <v>92.69000244140625</v>
       </c>
       <c r="F77">
-        <v>377993.3666666666</v>
+        <v>414790</v>
       </c>
       <c r="G77">
-        <v>307.9165447998047</v>
+        <v>90.72000030517579</v>
       </c>
       <c r="H77">
-        <v>262.2637711588542</v>
+        <v>76.85306650797526</v>
       </c>
       <c r="I77">
-        <v>256.1731450653076</v>
+        <v>69.83994993209839</v>
       </c>
       <c r="J77">
-        <v>245.02783203125</v>
+        <v>64.86389987945557</v>
       </c>
       <c r="K77">
-        <v>0.1523502618074417</v>
+        <v>1.669681549072266</v>
       </c>
       <c r="L77">
-        <v>337.8099975585938</v>
+        <v>98.38999938964844</v>
       </c>
       <c r="M77">
-        <v>130.6846452065481</v>
+        <v>135.4186105577915</v>
       </c>
       <c r="N77">
-        <v>2.26</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O77">
-        <v>2.57</v>
+        <v>0.74</v>
       </c>
       <c r="P77">
-        <v>2.27</v>
+        <v>1.08</v>
       </c>
       <c r="Q77">
-        <v>3.37</v>
+        <v>3.58</v>
       </c>
       <c r="R77">
-        <v>139100000</v>
+        <v>22222000</v>
       </c>
       <c r="S77">
-        <v>122900000</v>
+        <v>32408000</v>
       </c>
       <c r="T77">
-        <v>181900000</v>
+        <v>105259000</v>
       </c>
       <c r="U77">
-        <v>545900000</v>
+        <v>93693000</v>
       </c>
       <c r="V77" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -6404,67 +6422,67 @@
         <v>98</v>
       </c>
       <c r="B78" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C78" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D78" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E78">
-        <v>157.6300048828125</v>
+        <v>31.8799991607666</v>
       </c>
       <c r="F78">
-        <v>398693.3333333333</v>
+        <v>1132396.666666667</v>
       </c>
       <c r="G78">
-        <v>138.8632006835938</v>
+        <v>31.64800003051758</v>
       </c>
       <c r="H78">
-        <v>133.7584002685547</v>
+        <v>26.50473337809245</v>
       </c>
       <c r="I78">
-        <v>125.9633003234863</v>
+        <v>24.23160004615784</v>
       </c>
       <c r="J78">
-        <v>118.6123501968384</v>
+        <v>22.60275006771088</v>
       </c>
       <c r="K78">
-        <v>11.96000003814697</v>
+        <v>6.139999866485596</v>
       </c>
       <c r="L78">
-        <v>161.8300018310547</v>
+        <v>33.66999816894531</v>
       </c>
       <c r="M78">
-        <v>130.4018084857356</v>
+        <v>134.454367680038</v>
       </c>
       <c r="N78">
-        <v>5.74</v>
+        <v>1.45</v>
       </c>
       <c r="O78">
-        <v>5.18</v>
+        <v>1.98</v>
       </c>
       <c r="P78">
-        <v>4.2</v>
+        <v>0.73</v>
       </c>
       <c r="Q78">
-        <v>4.31</v>
+        <v>0.6</v>
       </c>
       <c r="R78">
-        <v>220802000</v>
+        <v>576060000</v>
       </c>
       <c r="S78">
-        <v>173492000</v>
+        <v>74742000</v>
       </c>
       <c r="T78">
-        <v>174194000</v>
+        <v>60724000</v>
       </c>
       <c r="U78">
-        <v>882083000</v>
+        <v>563324000</v>
       </c>
       <c r="V78" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -6472,67 +6490,67 @@
         <v>99</v>
       </c>
       <c r="B79" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C79" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="D79" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E79">
-        <v>42.31000137329102</v>
+        <v>215.0399932861328</v>
       </c>
       <c r="F79">
-        <v>305753.3333333333</v>
+        <v>566250</v>
       </c>
       <c r="G79">
-        <v>38.63574943542481</v>
+        <v>180.3333999633789</v>
       </c>
       <c r="H79">
-        <v>36.52129384358724</v>
+        <v>164.1136000569661</v>
       </c>
       <c r="I79">
-        <v>34.67694772720337</v>
+        <v>159.0799996566772</v>
       </c>
       <c r="J79">
-        <v>33.17396993637085</v>
+        <v>151.846849861145</v>
       </c>
       <c r="K79">
-        <v>2.540576934814453</v>
+        <v>0.9346818327903748</v>
       </c>
       <c r="L79">
-        <v>44.08000183105469</v>
+        <v>215.0399932861328</v>
       </c>
       <c r="M79">
-        <v>130.2012318739947</v>
+        <v>134.3884700644366</v>
       </c>
       <c r="N79">
-        <v>5.1</v>
+        <v>2.16</v>
       </c>
       <c r="O79">
-        <v>1.46</v>
+        <v>2.63</v>
       </c>
       <c r="P79">
-        <v>-0.65</v>
+        <v>2.32</v>
       </c>
       <c r="Q79">
-        <v>1.27</v>
+        <v>2.95</v>
       </c>
       <c r="R79">
-        <v>55100000</v>
+        <v>406122000</v>
       </c>
       <c r="S79">
-        <v>-24100000</v>
+        <v>111473000</v>
       </c>
       <c r="T79">
-        <v>47300000</v>
+        <v>140595000</v>
       </c>
       <c r="U79">
-        <v>391000000</v>
+        <v>444209000</v>
       </c>
       <c r="V79" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6540,67 +6558,67 @@
         <v>100</v>
       </c>
       <c r="B80" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C80" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="D80" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E80">
-        <v>42.25</v>
+        <v>28.76000022888184</v>
       </c>
       <c r="F80">
-        <v>1314786.666666667</v>
+        <v>916220</v>
       </c>
       <c r="G80">
-        <v>36.67029335021973</v>
+        <v>25.90520004272461</v>
       </c>
       <c r="H80">
-        <v>33.84036380767822</v>
+        <v>22.95959995269775</v>
       </c>
       <c r="I80">
-        <v>32.69622779846191</v>
+        <v>21.61889996528625</v>
       </c>
       <c r="J80">
-        <v>31.6199667930603</v>
+        <v>20.26214997768402</v>
       </c>
       <c r="K80">
-        <v>12.00996017456055</v>
+        <v>9.090000152587891</v>
       </c>
       <c r="L80">
-        <v>46.59550094604492</v>
+        <v>28.76000022888184</v>
       </c>
       <c r="M80">
-        <v>129.9448220482373</v>
+        <v>134.3080848914423</v>
       </c>
       <c r="N80">
-        <v>0.62</v>
+        <v>0.06</v>
       </c>
       <c r="O80">
-        <v>0.65</v>
+        <v>0.06</v>
       </c>
       <c r="P80">
-        <v>0.76</v>
+        <v>0.04</v>
       </c>
       <c r="Q80">
-        <v>0.72</v>
+        <v>0.05</v>
       </c>
       <c r="R80">
-        <v>44200000</v>
+        <v>28000000</v>
       </c>
       <c r="S80">
-        <v>52900000</v>
+        <v>22000000</v>
       </c>
       <c r="T80">
-        <v>50800000</v>
+        <v>26000000</v>
       </c>
       <c r="U80">
-        <v>206755000</v>
+        <v>73000000</v>
       </c>
       <c r="V80" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -6608,67 +6626,67 @@
         <v>101</v>
       </c>
       <c r="B81" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C81" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="D81" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E81">
-        <v>58.25</v>
+        <v>31.61000061035156</v>
       </c>
       <c r="F81">
-        <v>687316.6666666666</v>
+        <v>1021096.666666667</v>
       </c>
       <c r="G81">
-        <v>53.12515365600586</v>
+        <v>29.46780006408692</v>
       </c>
       <c r="H81">
-        <v>47.4527102915446</v>
+        <v>25.10673337300619</v>
       </c>
       <c r="I81">
-        <v>45.70288629531861</v>
+        <v>24.14995003700257</v>
       </c>
       <c r="J81">
-        <v>43.45442472457886</v>
+        <v>23.33990002632141</v>
       </c>
       <c r="K81">
-        <v>13.3568058013916</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="L81">
-        <v>59.22999954223633</v>
+        <v>32.33000183105469</v>
       </c>
       <c r="M81">
-        <v>129.9080589662269</v>
+        <v>134.0992295488805</v>
       </c>
       <c r="N81">
-        <v>1.26</v>
+        <v>0.67</v>
       </c>
       <c r="O81">
-        <v>1.45</v>
+        <v>0.65</v>
       </c>
       <c r="P81">
-        <v>1.52</v>
+        <v>0.31</v>
       </c>
       <c r="Q81">
-        <v>1.85</v>
+        <v>0.5</v>
       </c>
       <c r="R81">
-        <v>139000000</v>
+        <v>111000000</v>
       </c>
       <c r="S81">
-        <v>141000000</v>
+        <v>54000000</v>
       </c>
       <c r="T81">
-        <v>170000000</v>
+        <v>86000000</v>
       </c>
       <c r="U81">
-        <v>531000000</v>
+        <v>366000000</v>
       </c>
       <c r="V81" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -6676,67 +6694,67 @@
         <v>102</v>
       </c>
       <c r="B82" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C82" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="D82" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E82">
-        <v>117.6500015258789</v>
+        <v>11.10000038146973</v>
       </c>
       <c r="F82">
-        <v>13391793.33333333</v>
+        <v>462506.6666666667</v>
       </c>
       <c r="G82">
-        <v>111.1975273132324</v>
+        <v>9.66459997177124</v>
       </c>
       <c r="H82">
-        <v>95.83018442789714</v>
+        <v>8.672733322779338</v>
       </c>
       <c r="I82">
-        <v>90.42385684967041</v>
+        <v>8.536149990558624</v>
       </c>
       <c r="J82">
-        <v>85.47608320236206</v>
+        <v>8.341499996185302</v>
       </c>
       <c r="K82">
-        <v>0.03427219390869141</v>
+        <v>3.549999952316284</v>
       </c>
       <c r="L82">
-        <v>126.1074447631836</v>
+        <v>13.5</v>
       </c>
       <c r="M82">
-        <v>129.8205806021168</v>
+        <v>134.0927143052481</v>
       </c>
       <c r="N82">
-        <v>0.5600000000000001</v>
+        <v>0.168</v>
       </c>
       <c r="O82">
-        <v>0.63</v>
+        <v>0.205</v>
       </c>
       <c r="P82">
-        <v>0.68</v>
+        <v>0.024961</v>
       </c>
       <c r="Q82">
-        <v>1.19</v>
+        <v>0.2</v>
       </c>
       <c r="R82">
-        <v>1741000000</v>
+        <v>22548000</v>
       </c>
       <c r="S82">
-        <v>1895000000</v>
+        <v>2732000</v>
       </c>
       <c r="T82">
-        <v>3319000000</v>
+        <v>21569000</v>
       </c>
       <c r="U82">
-        <v>8373000000</v>
+        <v>108138000</v>
       </c>
       <c r="V82" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="83" spans="1:22">
@@ -6744,67 +6762,67 @@
         <v>103</v>
       </c>
       <c r="B83" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C83" t="s">
-        <v>128</v>
+        <v>168</v>
       </c>
       <c r="D83" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E83">
-        <v>44.72999954223633</v>
+        <v>30.47999954223633</v>
       </c>
       <c r="F83">
-        <v>311746.6666666667</v>
+        <v>404350</v>
       </c>
       <c r="G83">
-        <v>41.95399978637695</v>
+        <v>27.5565998840332</v>
       </c>
       <c r="H83">
-        <v>34.14253326416016</v>
+        <v>24.13193328857422</v>
       </c>
       <c r="I83">
-        <v>32.53409995079041</v>
+        <v>23.60934995651245</v>
       </c>
       <c r="J83">
-        <v>30.07860001087189</v>
+        <v>22.99069995880127</v>
       </c>
       <c r="K83">
-        <v>7.400000095367432</v>
+        <v>1.970000028610229</v>
       </c>
       <c r="L83">
-        <v>44.95000076293945</v>
+        <v>30.61000061035156</v>
       </c>
       <c r="M83">
-        <v>129.7338095871469</v>
+        <v>133.927745362198</v>
       </c>
       <c r="N83">
-        <v>-0.38</v>
+        <v>-0.04</v>
       </c>
       <c r="O83">
-        <v>-0.41</v>
+        <v>0.08</v>
       </c>
       <c r="P83">
-        <v>-0.49</v>
+        <v>0.24</v>
       </c>
       <c r="Q83">
-        <v>-0.44</v>
+        <v>-0.11</v>
       </c>
       <c r="R83">
-        <v>-73020000</v>
+        <v>4789000</v>
       </c>
       <c r="S83">
-        <v>-26123000</v>
+        <v>13725000</v>
       </c>
       <c r="T83">
-        <v>-25192000</v>
+        <v>-6296000</v>
       </c>
       <c r="U83">
-        <v>-81854000</v>
+        <v>24049000</v>
       </c>
       <c r="V83" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="84" spans="1:22">
@@ -6812,67 +6830,67 @@
         <v>104</v>
       </c>
       <c r="B84" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C84" t="s">
-        <v>130</v>
+        <v>169</v>
       </c>
       <c r="D84" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E84">
-        <v>78.16000366210938</v>
+        <v>53.66999816894531</v>
       </c>
       <c r="F84">
-        <v>5586643.333333333</v>
+        <v>1173240</v>
       </c>
       <c r="G84">
-        <v>72.01159927368164</v>
+        <v>46.90399978637695</v>
       </c>
       <c r="H84">
-        <v>62.83566627502442</v>
+        <v>43.12819999694824</v>
       </c>
       <c r="I84">
-        <v>60.28169969558716</v>
+        <v>42.28294998168946</v>
       </c>
       <c r="J84">
-        <v>57.71494974136353</v>
+        <v>40.74560003280639</v>
       </c>
       <c r="K84">
-        <v>1.5</v>
+        <v>2.721946477890015</v>
       </c>
       <c r="L84">
-        <v>80.27999877929688</v>
+        <v>53.91999816894531</v>
       </c>
       <c r="M84">
-        <v>129.72982125931</v>
+        <v>133.8993498886863</v>
       </c>
       <c r="N84">
-        <v>0.21</v>
+        <v>3.74</v>
       </c>
       <c r="O84">
-        <v>0.29</v>
+        <v>3.41</v>
       </c>
       <c r="P84">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="Q84">
-        <v>0.31</v>
+        <v>-2</v>
       </c>
       <c r="R84">
-        <v>231600000</v>
+        <v>312600000</v>
       </c>
       <c r="S84">
-        <v>313800000</v>
+        <v>32572000</v>
       </c>
       <c r="T84">
-        <v>247700000</v>
+        <v>-155994000</v>
       </c>
       <c r="U84">
-        <v>857300000</v>
+        <v>1220944000</v>
       </c>
       <c r="V84" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="85" spans="1:22">
@@ -6880,67 +6898,67 @@
         <v>105</v>
       </c>
       <c r="B85" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C85" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="D85" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E85">
-        <v>109.0999984741211</v>
+        <v>110.6699981689453</v>
       </c>
       <c r="F85">
-        <v>392150</v>
+        <v>1113550</v>
       </c>
       <c r="G85">
-        <v>91.20339965820312</v>
+        <v>102.1255996704102</v>
       </c>
       <c r="H85">
-        <v>89.23613316853842</v>
+        <v>87.25533320109049</v>
       </c>
       <c r="I85">
-        <v>86.52179988861084</v>
+        <v>82.09754981994629</v>
       </c>
       <c r="J85">
-        <v>84.13499996185303</v>
+        <v>76.87339988708496</v>
       </c>
       <c r="K85">
-        <v>3.099249601364136</v>
+        <v>0.3787146806716919</v>
       </c>
       <c r="L85">
-        <v>121.8199996948242</v>
+        <v>115.1399993896484</v>
       </c>
       <c r="M85">
-        <v>129.6553316219292</v>
+        <v>133.8220223489677</v>
       </c>
       <c r="N85">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="O85">
-        <v>3.5</v>
+        <v>1.61</v>
       </c>
       <c r="P85">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Q85">
-        <v>2.84</v>
+        <v>1.72</v>
       </c>
       <c r="R85">
-        <v>88842000</v>
+        <v>978000000</v>
       </c>
       <c r="S85">
-        <v>37337000</v>
+        <v>207000000</v>
       </c>
       <c r="T85">
-        <v>71283000</v>
+        <v>233000000</v>
       </c>
       <c r="U85">
-        <v>298209000</v>
+        <v>963000000</v>
       </c>
       <c r="V85" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="86" spans="1:22">
@@ -6948,67 +6966,67 @@
         <v>106</v>
       </c>
       <c r="B86" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C86" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D86" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E86">
-        <v>169.1399993896484</v>
+        <v>310.5299987792969</v>
       </c>
       <c r="F86">
-        <v>396200</v>
+        <v>322336.6666666667</v>
       </c>
       <c r="G86">
-        <v>154.6841995239258</v>
+        <v>280.5541995239258</v>
       </c>
       <c r="H86">
-        <v>138.9940661112468</v>
+        <v>248.9095338948568</v>
       </c>
       <c r="I86">
-        <v>133.5820495223999</v>
+        <v>240.5363003540039</v>
       </c>
       <c r="J86">
-        <v>128.7021996307373</v>
+        <v>231.8691004943848</v>
       </c>
       <c r="K86">
-        <v>0.5625</v>
+        <v>1.363492727279663</v>
       </c>
       <c r="L86">
-        <v>171.8699951171875</v>
+        <v>412.9100646972656</v>
       </c>
       <c r="M86">
-        <v>129.5557468372629</v>
+        <v>133.5122787335413</v>
       </c>
       <c r="N86">
-        <v>2.71</v>
+        <v>11.92</v>
       </c>
       <c r="O86">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="P86">
-        <v>1.52</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q86">
-        <v>1.33</v>
+        <v>10.78</v>
       </c>
       <c r="R86">
-        <v>378263000</v>
+        <v>1251000000</v>
       </c>
       <c r="S86">
-        <v>82474000</v>
+        <v>228700000</v>
       </c>
       <c r="T86">
-        <v>72401000</v>
+        <v>297200000</v>
       </c>
       <c r="U86">
-        <v>411744000</v>
+        <v>1137500000</v>
       </c>
       <c r="V86" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="87" spans="1:22">
@@ -7016,67 +7034,67 @@
         <v>107</v>
       </c>
       <c r="B87" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C87" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="D87" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E87">
-        <v>31.80999946594238</v>
+        <v>48.41999816894531</v>
       </c>
       <c r="F87">
-        <v>920946.6666666666</v>
+        <v>1058410</v>
       </c>
       <c r="G87">
-        <v>30.74820018768311</v>
+        <v>47.09019989013672</v>
       </c>
       <c r="H87">
-        <v>26.41926672617594</v>
+        <v>40.09586666107177</v>
       </c>
       <c r="I87">
-        <v>24.49810003280639</v>
+        <v>37.03420002937317</v>
       </c>
       <c r="J87">
-        <v>23.23484999656677</v>
+        <v>34.55645001411438</v>
       </c>
       <c r="K87">
-        <v>16.70999908447266</v>
+        <v>7.050000190734863</v>
       </c>
       <c r="L87">
-        <v>36.84999847412109</v>
+        <v>51.63999938964844</v>
       </c>
       <c r="M87">
-        <v>129.487426634305</v>
+        <v>133.5122565754114</v>
       </c>
       <c r="N87">
-        <v>0.21</v>
+        <v>2.72</v>
       </c>
       <c r="O87">
-        <v>0.32</v>
+        <v>2.51</v>
       </c>
       <c r="P87">
-        <v>0.43</v>
+        <v>1.74</v>
       </c>
       <c r="Q87">
-        <v>0.53</v>
+        <v>2.12</v>
       </c>
       <c r="R87">
-        <v>50100000</v>
+        <v>1052800000</v>
       </c>
       <c r="S87">
-        <v>67700000</v>
+        <v>191051000</v>
       </c>
       <c r="T87">
-        <v>82800000</v>
+        <v>234602000</v>
       </c>
       <c r="U87">
-        <v>401300000</v>
+        <v>1067148000</v>
       </c>
       <c r="V87" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="88" spans="1:22">
@@ -7084,67 +7102,67 @@
         <v>108</v>
       </c>
       <c r="B88" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C88" t="s">
         <v>152</v>
       </c>
       <c r="D88" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E88">
-        <v>174.6900024414062</v>
+        <v>60.29999923706055</v>
       </c>
       <c r="F88">
-        <v>908116.6666666666</v>
+        <v>1583686.666666667</v>
       </c>
       <c r="G88">
-        <v>157.9318003845215</v>
+        <v>53.45320014953613</v>
       </c>
       <c r="H88">
-        <v>148.485066426595</v>
+        <v>49.44633336385091</v>
       </c>
       <c r="I88">
-        <v>143.043099899292</v>
+        <v>46.51530003547668</v>
       </c>
       <c r="J88">
-        <v>138.2588999176025</v>
+        <v>44.13330001831055</v>
       </c>
       <c r="K88">
-        <v>3.140000104904175</v>
+        <v>1.326302051544189</v>
       </c>
       <c r="L88">
-        <v>183.1000061035156</v>
+        <v>60.29999923706055</v>
       </c>
       <c r="M88">
-        <v>129.3666034014301</v>
+        <v>132.7802772224183</v>
       </c>
       <c r="N88">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O88">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P88">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q88">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R88">
-        <v>239602000</v>
+        <v>0</v>
       </c>
       <c r="S88">
-        <v>218920000</v>
+        <v>0</v>
       </c>
       <c r="T88">
-        <v>197100000</v>
+        <v>3847000000</v>
       </c>
       <c r="U88">
-        <v>860471000</v>
+        <v>0</v>
       </c>
       <c r="V88" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="89" spans="1:22">
@@ -7152,67 +7170,67 @@
         <v>109</v>
       </c>
       <c r="B89" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C89" t="s">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="D89" t="s">
-        <v>257</v>
+        <v>224</v>
       </c>
       <c r="E89">
-        <v>53.36000061035156</v>
+        <v>69.5</v>
       </c>
       <c r="F89">
-        <v>1193250</v>
+        <v>1420840</v>
       </c>
       <c r="G89">
-        <v>47.60119995117188</v>
+        <v>62.20980003356934</v>
       </c>
       <c r="H89">
-        <v>43.7200666809082</v>
+        <v>56.32693328857422</v>
       </c>
       <c r="I89">
-        <v>41.98140000343323</v>
+        <v>53.14079992294312</v>
       </c>
       <c r="J89">
-        <v>40.07630002021789</v>
+        <v>50.7285499382019</v>
       </c>
       <c r="K89">
-        <v>11.8095235824585</v>
+        <v>0.1557042300701141</v>
       </c>
       <c r="L89">
-        <v>55.52000045776367</v>
+        <v>79.82826232910156</v>
       </c>
       <c r="M89">
-        <v>129.2540680974793</v>
+        <v>132.7059363108922</v>
       </c>
       <c r="N89">
-        <v>0.48</v>
+        <v>0.7</v>
       </c>
       <c r="O89">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="P89">
-        <v>0.9399999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="Q89">
-        <v>0.5600000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="R89">
-        <v>93400000</v>
+        <v>480900000</v>
       </c>
       <c r="S89">
-        <v>158700000</v>
+        <v>129700000</v>
       </c>
       <c r="T89">
-        <v>93800000</v>
+        <v>152900000</v>
       </c>
       <c r="U89">
-        <v>399800000</v>
+        <v>493000000</v>
       </c>
       <c r="V89" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="90" spans="1:22">
@@ -7220,67 +7238,67 @@
         <v>110</v>
       </c>
       <c r="B90" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C90" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D90" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E90">
-        <v>169.3399963378906</v>
+        <v>105.2300033569336</v>
       </c>
       <c r="F90">
-        <v>272893.3333333333</v>
+        <v>286210</v>
       </c>
       <c r="G90">
-        <v>155.897399597168</v>
+        <v>95.62000015258789</v>
       </c>
       <c r="H90">
-        <v>140.4282001749675</v>
+        <v>85.45493362426758</v>
       </c>
       <c r="I90">
-        <v>133.833800163269</v>
+        <v>81.27605020523072</v>
       </c>
       <c r="J90">
-        <v>127.2487002944946</v>
+        <v>79.04170022964477</v>
       </c>
       <c r="K90">
-        <v>2.075098752975464</v>
+        <v>12.27999973297119</v>
       </c>
       <c r="L90">
-        <v>179.6499938964844</v>
+        <v>108.4400024414062</v>
       </c>
       <c r="M90">
-        <v>129.1884133486842</v>
+        <v>132.6341144798291</v>
       </c>
       <c r="N90">
-        <v>4.93</v>
+        <v>1.22</v>
       </c>
       <c r="O90">
-        <v>4.61</v>
+        <v>0.78</v>
       </c>
       <c r="P90">
-        <v>4.21</v>
+        <v>2.17</v>
       </c>
       <c r="Q90">
-        <v>4.31</v>
+        <v>1.38</v>
       </c>
       <c r="R90">
-        <v>340100000</v>
+        <v>355000000</v>
       </c>
       <c r="S90">
-        <v>298000000</v>
+        <v>131000000</v>
       </c>
       <c r="T90">
-        <v>298300000</v>
+        <v>83000000</v>
       </c>
       <c r="U90">
-        <v>1380000000</v>
+        <v>340000000</v>
       </c>
       <c r="V90" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="91" spans="1:22">
@@ -7288,67 +7306,67 @@
         <v>111</v>
       </c>
       <c r="B91" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C91" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D91" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E91">
-        <v>582.02001953125</v>
+        <v>419.489990234375</v>
       </c>
       <c r="F91">
-        <v>1180293.333333333</v>
+        <v>984203.3333333334</v>
       </c>
       <c r="G91">
-        <v>541.3316027832032</v>
+        <v>349.1213995361328</v>
       </c>
       <c r="H91">
-        <v>471.3368007405599</v>
+        <v>335.5441998291016</v>
       </c>
       <c r="I91">
-        <v>451.2894004821777</v>
+        <v>323.2082997131347</v>
       </c>
       <c r="J91">
-        <v>436.3914002990722</v>
+        <v>310.0965498352051</v>
       </c>
       <c r="K91">
-        <v>23.73999977111816</v>
+        <v>0.6462651491165161</v>
       </c>
       <c r="L91">
-        <v>701.72998046875</v>
+        <v>427.5899963378906</v>
       </c>
       <c r="M91">
-        <v>129.1786661590297</v>
+        <v>132.6021110088814</v>
       </c>
       <c r="N91">
-        <v>0.1</v>
+        <v>3.36</v>
       </c>
       <c r="O91">
-        <v>0.39</v>
+        <v>2.92</v>
       </c>
       <c r="P91">
-        <v>0.74</v>
+        <v>2.58</v>
       </c>
       <c r="Q91">
-        <v>0.73</v>
+        <v>2.65</v>
       </c>
       <c r="R91">
-        <v>80000000</v>
+        <v>1377159000</v>
       </c>
       <c r="S91">
-        <v>150000000</v>
+        <v>285038000</v>
       </c>
       <c r="T91">
-        <v>150000000</v>
+        <v>292362000</v>
       </c>
       <c r="U91">
-        <v>325000000</v>
+        <v>1362446000</v>
       </c>
       <c r="V91" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="92" spans="1:22">
@@ -7356,40 +7374,40 @@
         <v>112</v>
       </c>
       <c r="B92" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C92" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D92" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E92">
-        <v>51.2400016784668</v>
+        <v>52.27000045776367</v>
       </c>
       <c r="F92">
-        <v>1782530</v>
+        <v>1738190</v>
       </c>
       <c r="G92">
-        <v>41.25720008850098</v>
+        <v>43.03980003356934</v>
       </c>
       <c r="H92">
-        <v>39.83313344319662</v>
+        <v>40.49606671651205</v>
       </c>
       <c r="I92">
-        <v>38.74440008163452</v>
+        <v>39.40570006370545</v>
       </c>
       <c r="J92">
-        <v>37.32985004425049</v>
+        <v>37.5139000415802</v>
       </c>
       <c r="K92">
         <v>20.39999961853027</v>
       </c>
       <c r="L92">
-        <v>51.9900016784668</v>
+        <v>52.36999893188477</v>
       </c>
       <c r="M92">
-        <v>129.0741997172067</v>
+        <v>132.5868141233705</v>
       </c>
       <c r="N92">
         <v>0.74</v>
@@ -7416,7 +7434,143 @@
         <v>168948000</v>
       </c>
       <c r="V92" t="s">
-        <v>261</v>
+        <v>267</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22">
+      <c r="A93" t="s">
+        <v>113</v>
+      </c>
+      <c r="B93" t="s">
+        <v>121</v>
+      </c>
+      <c r="C93" t="s">
+        <v>175</v>
+      </c>
+      <c r="D93" t="s">
+        <v>265</v>
+      </c>
+      <c r="E93">
+        <v>108.7399978637695</v>
+      </c>
+      <c r="F93">
+        <v>1102046.666666667</v>
+      </c>
+      <c r="G93">
+        <v>96.09559982299805</v>
+      </c>
+      <c r="H93">
+        <v>89.58886637369791</v>
+      </c>
+      <c r="I93">
+        <v>83.74624977111816</v>
+      </c>
+      <c r="J93">
+        <v>81.35399982452392</v>
+      </c>
+      <c r="K93">
+        <v>0.02227001264691353</v>
+      </c>
+      <c r="L93">
+        <v>132.0598602294922</v>
+      </c>
+      <c r="M93">
+        <v>132.5513518035199</v>
+      </c>
+      <c r="N93">
+        <v>8</v>
+      </c>
+      <c r="O93">
+        <v>10.15</v>
+      </c>
+      <c r="P93">
+        <v>6.05</v>
+      </c>
+      <c r="Q93">
+        <v>10.35</v>
+      </c>
+      <c r="R93">
+        <v>6699364000</v>
+      </c>
+      <c r="S93">
+        <v>3952737000</v>
+      </c>
+      <c r="T93">
+        <v>6754634000</v>
+      </c>
+      <c r="U93">
+        <v>20337600000</v>
+      </c>
+      <c r="V93" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22">
+      <c r="A94" t="s">
+        <v>114</v>
+      </c>
+      <c r="B94" t="s">
+        <v>117</v>
+      </c>
+      <c r="C94" t="s">
+        <v>128</v>
+      </c>
+      <c r="D94" t="s">
+        <v>266</v>
+      </c>
+      <c r="E94">
+        <v>504.4800109863281</v>
+      </c>
+      <c r="F94">
+        <v>414890</v>
+      </c>
+      <c r="G94">
+        <v>420.98</v>
+      </c>
+      <c r="H94">
+        <v>391.4035001627604</v>
+      </c>
+      <c r="I94">
+        <v>387.5528250122071</v>
+      </c>
+      <c r="J94">
+        <v>377.9874749755859</v>
+      </c>
+      <c r="K94">
+        <v>19.76499938964844</v>
+      </c>
+      <c r="L94">
+        <v>548.4299926757812</v>
+      </c>
+      <c r="M94">
+        <v>132.4804150761046</v>
+      </c>
+      <c r="N94">
+        <v>-0.52</v>
+      </c>
+      <c r="O94">
+        <v>-4.26</v>
+      </c>
+      <c r="P94">
+        <v>-0.7</v>
+      </c>
+      <c r="Q94">
+        <v>-0.52</v>
+      </c>
+      <c r="R94">
+        <v>-709594000</v>
+      </c>
+      <c r="S94">
+        <v>-28871000</v>
+      </c>
+      <c r="T94">
+        <v>-94368000</v>
+      </c>
+      <c r="U94">
+        <v>-511278000</v>
+      </c>
+      <c r="V94" t="s">
+        <v>267</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/ScreenResult/ScreenResult.xlsx
+++ b/Screener/ScreenResult/ScreenResult.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="241">
   <si>
     <t>Symbol</t>
   </si>
@@ -82,739 +82,655 @@
     <t>Code 33</t>
   </si>
   <si>
-    <t>EDTX</t>
-  </si>
-  <si>
     <t>AURC</t>
   </si>
   <si>
     <t>SMCI</t>
   </si>
   <si>
+    <t>VRT</t>
+  </si>
+  <si>
     <t>INOD</t>
   </si>
   <si>
+    <t>RXDX</t>
+  </si>
+  <si>
+    <t>LI</t>
+  </si>
+  <si>
     <t>CBAY</t>
   </si>
   <si>
     <t>RXST</t>
   </si>
   <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>ELF</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>AMPH</t>
+  </si>
+  <si>
     <t>PKX</t>
   </si>
   <si>
-    <t>RXDX</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>LI</t>
-  </si>
-  <si>
-    <t>CAMT</t>
-  </si>
-  <si>
     <t>XPO</t>
   </si>
   <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>DICE</t>
+  </si>
+  <si>
     <t>ACLS</t>
   </si>
   <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>AMPH</t>
-  </si>
-  <si>
-    <t>VRT</t>
+    <t>SAIA</t>
   </si>
   <si>
     <t>ROIV</t>
   </si>
   <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>STVN</t>
+  </si>
+  <si>
+    <t>ABCM</t>
+  </si>
+  <si>
     <t>AEHR</t>
   </si>
   <si>
-    <t>IAS</t>
-  </si>
-  <si>
-    <t>RCL</t>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>OC</t>
   </si>
   <si>
     <t>TTD</t>
   </si>
   <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>ELF</t>
-  </si>
-  <si>
-    <t>MOD</t>
-  </si>
-  <si>
-    <t>COCO</t>
-  </si>
-  <si>
-    <t>STRL</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>UBER</t>
-  </si>
-  <si>
-    <t>PHM</t>
-  </si>
-  <si>
     <t>GKOS</t>
   </si>
   <si>
-    <t>ABCM</t>
+    <t>BECN</t>
+  </si>
+  <si>
+    <t>CLBR</t>
+  </si>
+  <si>
+    <t>LII</t>
+  </si>
+  <si>
+    <t>RDNT</t>
+  </si>
+  <si>
+    <t>NYCB</t>
+  </si>
+  <si>
+    <t>LEGN</t>
+  </si>
+  <si>
+    <t>ARCB</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>THO</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>KBH</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>EME</t>
+  </si>
+  <si>
+    <t>NE</t>
   </si>
   <si>
     <t>NUVL</t>
   </si>
   <si>
-    <t>DICE</t>
-  </si>
-  <si>
-    <t>SPOK</t>
-  </si>
-  <si>
-    <t>FLNC</t>
-  </si>
-  <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>DUOL</t>
-  </si>
-  <si>
-    <t>DV</t>
-  </si>
-  <si>
-    <t>STVN</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>RDNT</t>
-  </si>
-  <si>
-    <t>OC</t>
-  </si>
-  <si>
-    <t>LPG</t>
-  </si>
-  <si>
-    <t>KRYS</t>
-  </si>
-  <si>
-    <t>NYCB</t>
-  </si>
-  <si>
-    <t>BECN</t>
-  </si>
-  <si>
-    <t>MATX</t>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>CARR</t>
+  </si>
+  <si>
+    <t>NTES</t>
   </si>
   <si>
     <t>MTH</t>
   </si>
   <si>
-    <t>THO</t>
-  </si>
-  <si>
-    <t>KBH</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>AVGO</t>
+    <t>ONTO</t>
+  </si>
+  <si>
+    <t>ZGN</t>
+  </si>
+  <si>
+    <t>COOP</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>LRCX</t>
+  </si>
+  <si>
+    <t>APG</t>
+  </si>
+  <si>
+    <t>PNR</t>
+  </si>
+  <si>
+    <t>NVT</t>
+  </si>
+  <si>
+    <t>ARGX</t>
+  </si>
+  <si>
+    <t>PARR</t>
+  </si>
+  <si>
+    <t>TOL</t>
+  </si>
+  <si>
+    <t>MDC</t>
+  </si>
+  <si>
+    <t>PAG</t>
+  </si>
+  <si>
+    <t>PH</t>
+  </si>
+  <si>
+    <t>FDX</t>
+  </si>
+  <si>
+    <t>CSAN</t>
+  </si>
+  <si>
+    <t>TMHC</t>
+  </si>
+  <si>
+    <t>ODFL</t>
+  </si>
+  <si>
+    <t>TNET</t>
+  </si>
+  <si>
+    <t>AGRO</t>
   </si>
   <si>
     <t>ON</t>
   </si>
   <si>
-    <t>LII</t>
-  </si>
-  <si>
-    <t>ALGM</t>
-  </si>
-  <si>
-    <t>CARR</t>
-  </si>
-  <si>
-    <t>CSAN</t>
-  </si>
-  <si>
-    <t>ONTO</t>
-  </si>
-  <si>
-    <t>CRS</t>
-  </si>
-  <si>
-    <t>LEGN</t>
-  </si>
-  <si>
-    <t>CLBR</t>
+    <t>APO</t>
   </si>
   <si>
     <t>BUR</t>
   </si>
   <si>
-    <t>CELH</t>
-  </si>
-  <si>
-    <t>TOL</t>
-  </si>
-  <si>
-    <t>MDC</t>
+    <t>GMS</t>
+  </si>
+  <si>
+    <t>URBN</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>CRH</t>
   </si>
   <si>
     <t>IGT</t>
   </si>
   <si>
-    <t>ZGN</t>
-  </si>
-  <si>
-    <t>TMDX</t>
-  </si>
-  <si>
-    <t>LRCX</t>
-  </si>
-  <si>
-    <t>ARCB</t>
-  </si>
-  <si>
-    <t>CCJ</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>IDCC</t>
-  </si>
-  <si>
     <t>TPH</t>
   </si>
   <si>
-    <t>EME</t>
-  </si>
-  <si>
-    <t>APG</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>AGRO</t>
-  </si>
-  <si>
-    <t>ERII</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>JBL</t>
-  </si>
-  <si>
-    <t>LAD</t>
-  </si>
-  <si>
-    <t>TMHC</t>
-  </si>
-  <si>
-    <t>CRH</t>
-  </si>
-  <si>
-    <t>PNR</t>
-  </si>
-  <si>
-    <t>TNET</t>
-  </si>
-  <si>
-    <t>ODFL</t>
-  </si>
-  <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>NTES</t>
-  </si>
-  <si>
-    <t>ARGX</t>
-  </si>
-  <si>
     <t>Financial Services</t>
   </si>
   <si>
     <t>Technology</t>
   </si>
   <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
     <t>Healthcare</t>
   </si>
   <si>
+    <t>Consumer Defensive</t>
+  </si>
+  <si>
     <t>Basic Materials</t>
   </si>
   <si>
-    <t>Consumer Cyclical</t>
-  </si>
-  <si>
-    <t>Industrials</t>
+    <t>Energy</t>
   </si>
   <si>
     <t>Communication Services</t>
   </si>
   <si>
-    <t>Consumer Defensive</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>Utilities</t>
-  </si>
-  <si>
     <t>Shell Companies</t>
   </si>
   <si>
     <t>Computer Hardware</t>
   </si>
   <si>
+    <t>Electrical Equipment &amp; Parts</t>
+  </si>
+  <si>
     <t>Information Technology Services</t>
   </si>
   <si>
+    <t>Auto Manufacturers</t>
+  </si>
+  <si>
     <t>Biotechnology</t>
   </si>
   <si>
     <t>Medical Devices</t>
   </si>
   <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Household &amp; Personal Products</t>
+  </si>
+  <si>
+    <t>Semiconductor Equipment &amp; Materials</t>
+  </si>
+  <si>
+    <t>Drug Manufacturers—Specialty &amp; Generic</t>
+  </si>
+  <si>
     <t>Steel</t>
   </si>
   <si>
-    <t>Semiconductors</t>
+    <t>Trucking</t>
+  </si>
+  <si>
+    <t>Building Products &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Residential Construction</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Construction</t>
+  </si>
+  <si>
+    <t>Building Materials</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Equipment &amp; Services</t>
+  </si>
+  <si>
+    <t>Travel Services</t>
+  </si>
+  <si>
+    <t>Medical Instruments &amp; Supplies</t>
+  </si>
+  <si>
+    <t>Software—Application</t>
+  </si>
+  <si>
+    <t>Industrial Distribution</t>
+  </si>
+  <si>
+    <t>Diagnostics &amp; Research</t>
+  </si>
+  <si>
+    <t>Banks—Regional</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas E&amp;P</t>
+  </si>
+  <si>
+    <t>Recreational Vehicles</t>
+  </si>
+  <si>
+    <t>Rental &amp; Leasing Services</t>
   </si>
   <si>
     <t>Software—Infrastructure</t>
   </si>
   <si>
-    <t>Auto Manufacturers</t>
-  </si>
-  <si>
-    <t>Semiconductor Equipment &amp; Materials</t>
-  </si>
-  <si>
-    <t>Trucking</t>
-  </si>
-  <si>
-    <t>Building Products &amp; Equipment</t>
-  </si>
-  <si>
-    <t>Residential Construction</t>
-  </si>
-  <si>
-    <t>Drug Manufacturers—Specialty &amp; Generic</t>
-  </si>
-  <si>
-    <t>Electrical Equipment &amp; Parts</t>
-  </si>
-  <si>
-    <t>Advertising Agencies</t>
-  </si>
-  <si>
-    <t>Travel Services</t>
-  </si>
-  <si>
-    <t>Software—Application</t>
-  </si>
-  <si>
-    <t>Household &amp; Personal Products</t>
-  </si>
-  <si>
-    <t>Auto Parts</t>
-  </si>
-  <si>
-    <t>Beverages—Non-Alcoholic</t>
-  </si>
-  <si>
-    <t>Engineering &amp; Construction</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Equipment &amp; Services</t>
-  </si>
-  <si>
-    <t>Health Information Services</t>
-  </si>
-  <si>
-    <t>Utilities—Renewable</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas E&amp;P</t>
-  </si>
-  <si>
-    <t>Medical Instruments &amp; Supplies</t>
-  </si>
-  <si>
-    <t>Building Materials</t>
-  </si>
-  <si>
-    <t>Diagnostics &amp; Research</t>
-  </si>
-  <si>
     <t>Oil &amp; Gas Midstream</t>
   </si>
   <si>
-    <t>Banks—Regional</t>
-  </si>
-  <si>
-    <t>Industrial Distribution</t>
-  </si>
-  <si>
-    <t>Marine Shipping</t>
-  </si>
-  <si>
-    <t>Recreational Vehicles</t>
-  </si>
-  <si>
-    <t>Rental &amp; Leasing Services</t>
+    <t>Oil &amp; Gas Drilling</t>
+  </si>
+  <si>
+    <t>Insurance—Life</t>
+  </si>
+  <si>
+    <t>Electronic Gaming &amp; Multimedia</t>
+  </si>
+  <si>
+    <t>Apparel Manufacturing</t>
+  </si>
+  <si>
+    <t>Mortgage Finance</t>
+  </si>
+  <si>
+    <t>Electronic Components</t>
+  </si>
+  <si>
+    <t>Specialty Industrial Machinery</t>
   </si>
   <si>
     <t>Oil &amp; Gas Refining &amp; Marketing</t>
   </si>
   <si>
-    <t>Metal Fabrication</t>
+    <t>Auto &amp; Truck Dealerships</t>
+  </si>
+  <si>
+    <t>Integrated Freight &amp; Logistics</t>
+  </si>
+  <si>
+    <t>Staffing &amp; Employment Services</t>
+  </si>
+  <si>
+    <t>Farm Products</t>
   </si>
   <si>
     <t>Asset Management</t>
   </si>
   <si>
+    <t>Apparel Retail</t>
+  </si>
+  <si>
+    <t>Footwear &amp; Accessories</t>
+  </si>
+  <si>
     <t>Gambling</t>
   </si>
   <si>
-    <t>Apparel Manufacturing</t>
-  </si>
-  <si>
-    <t>Uranium</t>
-  </si>
-  <si>
-    <t>Telecom Services</t>
-  </si>
-  <si>
-    <t>Farm Products</t>
-  </si>
-  <si>
-    <t>Pollution &amp; Treatment Controls</t>
-  </si>
-  <si>
-    <t>Insurance—Life</t>
-  </si>
-  <si>
-    <t>Electronic Components</t>
-  </si>
-  <si>
-    <t>Auto &amp; Truck Dealerships</t>
-  </si>
-  <si>
-    <t>Specialty Industrial Machinery</t>
-  </si>
-  <si>
-    <t>Staffing &amp; Employment Services</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Drilling</t>
-  </si>
-  <si>
-    <t>Electronic Gaming &amp; Multimedia</t>
+    <t>2021-04-30</t>
+  </si>
+  <si>
+    <t>2007-03-29</t>
+  </si>
+  <si>
+    <t>2018-08-02</t>
+  </si>
+  <si>
+    <t>1993-08-10</t>
+  </si>
+  <si>
+    <t>2021-03-12</t>
+  </si>
+  <si>
+    <t>2020-07-30</t>
+  </si>
+  <si>
+    <t>2014-02-03</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>1999-01-22</t>
+  </si>
+  <si>
+    <t>2016-09-22</t>
+  </si>
+  <si>
+    <t>2000-07-28</t>
+  </si>
+  <si>
+    <t>2014-06-25</t>
+  </si>
+  <si>
+    <t>1994-10-14</t>
+  </si>
+  <si>
+    <t>2003-10-07</t>
+  </si>
+  <si>
+    <t>2005-06-28</t>
+  </si>
+  <si>
+    <t>1993-11-03</t>
+  </si>
+  <si>
+    <t>1991-07-12</t>
+  </si>
+  <si>
+    <t>2021-09-15</t>
+  </si>
+  <si>
+    <t>2000-07-11</t>
+  </si>
+  <si>
+    <t>2002-09-11</t>
+  </si>
+  <si>
+    <t>2020-12-08</t>
+  </si>
+  <si>
+    <t>2013-02-06</t>
   </si>
   <si>
     <t>2021-01-04</t>
   </si>
   <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>2007-03-29</t>
-  </si>
-  <si>
-    <t>1993-08-10</t>
-  </si>
-  <si>
-    <t>2014-02-03</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>1994-10-14</t>
-  </si>
-  <si>
-    <t>2021-03-12</t>
-  </si>
-  <si>
-    <t>1999-01-22</t>
-  </si>
-  <si>
-    <t>2021-12-15</t>
-  </si>
-  <si>
-    <t>2020-07-30</t>
-  </si>
-  <si>
-    <t>2000-07-28</t>
-  </si>
-  <si>
-    <t>2003-10-07</t>
-  </si>
-  <si>
-    <t>2000-07-11</t>
-  </si>
-  <si>
-    <t>2005-06-28</t>
-  </si>
-  <si>
-    <t>1993-11-03</t>
-  </si>
-  <si>
-    <t>2014-06-25</t>
-  </si>
-  <si>
-    <t>2018-08-02</t>
-  </si>
-  <si>
-    <t>2020-12-08</t>
+    <t>1993-04-28</t>
+  </si>
+  <si>
+    <t>2021-07-16</t>
+  </si>
+  <si>
+    <t>2020-10-22</t>
   </si>
   <si>
     <t>1997-08-15</t>
   </si>
   <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
-    <t>1993-04-28</t>
+    <t>1980-03-17</t>
+  </si>
+  <si>
+    <t>2006-11-01</t>
   </si>
   <si>
     <t>2016-09-21</t>
   </si>
   <si>
-    <t>2002-09-11</t>
-  </si>
-  <si>
-    <t>2016-09-22</t>
-  </si>
-  <si>
-    <t>1982-09-20</t>
-  </si>
-  <si>
-    <t>2021-10-21</t>
-  </si>
-  <si>
-    <t>1991-07-12</t>
-  </si>
-  <si>
-    <t>2019-05-10</t>
-  </si>
-  <si>
-    <t>1980-03-17</t>
-  </si>
-  <si>
     <t>2015-06-25</t>
   </si>
   <si>
-    <t>2020-10-22</t>
+    <t>2004-09-23</t>
+  </si>
+  <si>
+    <t>2021-07-07</t>
+  </si>
+  <si>
+    <t>1999-07-29</t>
+  </si>
+  <si>
+    <t>1997-01-03</t>
+  </si>
+  <si>
+    <t>1993-11-23</t>
+  </si>
+  <si>
+    <t>2020-06-05</t>
+  </si>
+  <si>
+    <t>1992-05-13</t>
+  </si>
+  <si>
+    <t>2019-07-26</t>
+  </si>
+  <si>
+    <t>1984-01-10</t>
+  </si>
+  <si>
+    <t>2015-05-14</t>
+  </si>
+  <si>
+    <t>1986-08-01</t>
+  </si>
+  <si>
+    <t>2009-08-06</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>1986-08-13</t>
+  </si>
+  <si>
+    <t>2014-05-08</t>
+  </si>
+  <si>
+    <t>1995-01-10</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
   </si>
   <si>
     <t>2021-07-29</t>
   </si>
   <si>
-    <t>2021-09-15</t>
-  </si>
-  <si>
-    <t>2004-11-17</t>
-  </si>
-  <si>
-    <t>2021-10-28</t>
-  </si>
-  <si>
-    <t>2019-07-26</t>
-  </si>
-  <si>
-    <t>2021-07-28</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>2021-07-16</t>
-  </si>
-  <si>
-    <t>1986-08-13</t>
-  </si>
-  <si>
-    <t>2013-02-06</t>
-  </si>
-  <si>
-    <t>1997-01-03</t>
-  </si>
-  <si>
-    <t>2006-11-01</t>
-  </si>
-  <si>
-    <t>2014-05-08</t>
-  </si>
-  <si>
-    <t>2017-09-20</t>
-  </si>
-  <si>
-    <t>1993-11-23</t>
-  </si>
-  <si>
-    <t>2004-09-23</t>
+    <t>2003-12-04</t>
+  </si>
+  <si>
+    <t>2020-03-19</t>
+  </si>
+  <si>
+    <t>2000-06-30</t>
+  </si>
+  <si>
+    <t>1988-07-26</t>
+  </si>
+  <si>
+    <t>2019-10-28</t>
+  </si>
+  <si>
+    <t>2021-12-20</t>
+  </si>
+  <si>
+    <t>2012-03-28</t>
+  </si>
+  <si>
+    <t>1993-05-03</t>
+  </si>
+  <si>
+    <t>1984-05-04</t>
+  </si>
+  <si>
+    <t>2020-04-29</t>
   </si>
   <si>
     <t>1973-05-03</t>
   </si>
   <si>
-    <t>1988-07-26</t>
-  </si>
-  <si>
-    <t>1984-01-10</t>
-  </si>
-  <si>
-    <t>1986-08-01</t>
-  </si>
-  <si>
-    <t>2015-05-14</t>
-  </si>
-  <si>
-    <t>2009-08-06</t>
+    <t>2018-04-24</t>
+  </si>
+  <si>
+    <t>2017-05-18</t>
+  </si>
+  <si>
+    <t>2012-09-05</t>
+  </si>
+  <si>
+    <t>1986-07-08</t>
+  </si>
+  <si>
+    <t>1980-03-11</t>
+  </si>
+  <si>
+    <t>1996-10-23</t>
+  </si>
+  <si>
+    <t>1978-04-12</t>
+  </si>
+  <si>
+    <t>2021-03-08</t>
+  </si>
+  <si>
+    <t>2013-04-10</t>
+  </si>
+  <si>
+    <t>1991-10-24</t>
+  </si>
+  <si>
+    <t>2014-03-27</t>
+  </si>
+  <si>
+    <t>2011-01-28</t>
   </si>
   <si>
     <t>2000-05-02</t>
   </si>
   <si>
-    <t>1999-07-29</t>
-  </si>
-  <si>
-    <t>2020-10-29</t>
-  </si>
-  <si>
-    <t>2020-03-19</t>
-  </si>
-  <si>
-    <t>2021-03-08</t>
-  </si>
-  <si>
-    <t>2019-10-28</t>
-  </si>
-  <si>
-    <t>1973-02-21</t>
-  </si>
-  <si>
-    <t>2020-06-05</t>
-  </si>
-  <si>
-    <t>2021-07-07</t>
+    <t>2011-03-30</t>
   </si>
   <si>
     <t>2020-10-19</t>
   </si>
   <si>
-    <t>2007-01-22</t>
-  </si>
-  <si>
-    <t>1986-07-08</t>
-  </si>
-  <si>
-    <t>1980-03-11</t>
+    <t>2016-05-26</t>
+  </si>
+  <si>
+    <t>1993-11-09</t>
+  </si>
+  <si>
+    <t>1993-10-15</t>
+  </si>
+  <si>
+    <t>1989-07-13</t>
   </si>
   <si>
     <t>1990-03-26</t>
   </si>
   <si>
-    <t>2021-12-20</t>
-  </si>
-  <si>
-    <t>2019-05-02</t>
-  </si>
-  <si>
-    <t>1984-05-04</t>
-  </si>
-  <si>
-    <t>1992-05-13</t>
-  </si>
-  <si>
-    <t>1996-03-14</t>
-  </si>
-  <si>
-    <t>2012-07-20</t>
-  </si>
-  <si>
-    <t>1981-11-12</t>
-  </si>
-  <si>
     <t>2013-01-31</t>
-  </si>
-  <si>
-    <t>1995-01-10</t>
-  </si>
-  <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>2011-01-28</t>
-  </si>
-  <si>
-    <t>2008-07-02</t>
-  </si>
-  <si>
-    <t>2003-12-04</t>
-  </si>
-  <si>
-    <t>1993-05-03</t>
-  </si>
-  <si>
-    <t>1996-12-18</t>
-  </si>
-  <si>
-    <t>2013-04-10</t>
-  </si>
-  <si>
-    <t>1989-07-13</t>
-  </si>
-  <si>
-    <t>2014-03-27</t>
-  </si>
-  <si>
-    <t>1991-10-24</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>2000-06-30</t>
-  </si>
-  <si>
-    <t>2017-05-18</t>
   </si>
   <si>
     <t>F</t>
@@ -1178,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V94"/>
+  <dimension ref="A1:V83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
@@ -1254,67 +1170,67 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="E2">
-        <v>63.2400016784668</v>
+        <v>42.2400016784668</v>
       </c>
       <c r="F2">
-        <v>254533.3333333333</v>
+        <v>523787.1333333334</v>
       </c>
       <c r="G2">
-        <v>26.76828042984009</v>
+        <v>14.48171987533569</v>
       </c>
       <c r="H2">
-        <v>16.05221351623535</v>
+        <v>11.59568663914998</v>
       </c>
       <c r="I2">
-        <v>14.61806515693664</v>
+        <v>11.1895049905777</v>
       </c>
       <c r="J2">
-        <v>11.05911502838135</v>
+        <v>10.11328000068665</v>
       </c>
       <c r="K2">
-        <v>9.739999771118164</v>
+        <v>9.789999961853027</v>
       </c>
       <c r="L2">
-        <v>63.2400016784668</v>
+        <v>49.58000183105469</v>
       </c>
       <c r="M2">
-        <v>581.5698777251038</v>
+        <v>428.7292142613572</v>
       </c>
       <c r="N2">
-        <v>0.002796</v>
+        <v>-0.01</v>
       </c>
       <c r="O2">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="P2">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="Q2">
-        <v>0.002796</v>
+        <v>-0.01</v>
       </c>
       <c r="R2">
-        <v>4198372</v>
+        <v>1785906</v>
       </c>
       <c r="S2">
-        <v>317981</v>
+        <v>-965634</v>
       </c>
       <c r="T2">
-        <v>768</v>
+        <v>6905230</v>
       </c>
       <c r="U2">
-        <v>4563809</v>
+        <v>-127955</v>
       </c>
       <c r="V2" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -1322,67 +1238,67 @@
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="E3">
-        <v>46.0099983215332</v>
+        <v>320.2731018066406</v>
       </c>
       <c r="F3">
-        <v>462473.3333333333</v>
+        <v>2764303.466666667</v>
       </c>
       <c r="G3">
-        <v>12.63671977996826</v>
+        <v>260.453861694336</v>
       </c>
       <c r="H3">
-        <v>10.97828661600749</v>
+        <v>153.9570870463053</v>
       </c>
       <c r="I3">
-        <v>10.72397996902466</v>
+        <v>135.3677152633667</v>
       </c>
       <c r="J3">
-        <v>10.10458000183105</v>
+        <v>110.3886998939514</v>
       </c>
       <c r="K3">
-        <v>9.789999961853027</v>
+        <v>3.849999904632568</v>
       </c>
       <c r="L3">
-        <v>46.0099983215332</v>
+        <v>337.5599975585938</v>
       </c>
       <c r="M3">
-        <v>453.6179757064314</v>
+        <v>272.1951199024072</v>
       </c>
       <c r="N3">
-        <v>-0.01</v>
+        <v>2.6</v>
       </c>
       <c r="O3">
-        <v>0.05</v>
+        <v>3.35</v>
       </c>
       <c r="P3">
-        <v>-0.03</v>
+        <v>3.14</v>
       </c>
       <c r="Q3">
-        <v>-0.01</v>
+        <v>1.53</v>
       </c>
       <c r="R3">
-        <v>4245973</v>
+        <v>140822000</v>
       </c>
       <c r="S3">
-        <v>6905230</v>
+        <v>184416000</v>
       </c>
       <c r="T3">
-        <v>-127955</v>
+        <v>176167000</v>
       </c>
       <c r="U3">
-        <v>8735542</v>
+        <v>85846000</v>
       </c>
       <c r="V3" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -1390,67 +1306,67 @@
         <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="E4">
-        <v>330.2699890136719</v>
+        <v>34.29000091552734</v>
       </c>
       <c r="F4">
-        <v>2863040</v>
+        <v>5861290</v>
       </c>
       <c r="G4">
-        <v>250.7761999511719</v>
+        <v>23.3276000213623</v>
       </c>
       <c r="H4">
-        <v>149.0879998270671</v>
+        <v>17.33913334528605</v>
       </c>
       <c r="I4">
-        <v>131.2884498405457</v>
+        <v>16.43260001659393</v>
       </c>
       <c r="J4">
-        <v>107.5752499008179</v>
+        <v>14.91379999637604</v>
       </c>
       <c r="K4">
-        <v>3.849999904632568</v>
+        <v>5.564881324768066</v>
       </c>
       <c r="L4">
-        <v>334.5</v>
+        <v>34.29000091552734</v>
       </c>
       <c r="M4">
-        <v>280.4146651000763</v>
+        <v>214.6132208388158</v>
       </c>
       <c r="N4">
-        <v>2.6</v>
+        <v>0.05</v>
       </c>
       <c r="O4">
-        <v>3.35</v>
+        <v>0.06</v>
       </c>
       <c r="P4">
-        <v>3.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q4">
-        <v>1.53</v>
+        <v>0.12</v>
       </c>
       <c r="R4">
-        <v>184416000</v>
+        <v>20300000</v>
       </c>
       <c r="S4">
-        <v>176167000</v>
+        <v>21200000</v>
       </c>
       <c r="T4">
-        <v>85846000</v>
+        <v>26600000</v>
       </c>
       <c r="U4">
-        <v>578377000</v>
+        <v>50300000</v>
       </c>
       <c r="V4" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -1458,31 +1374,31 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" t="s">
         <v>116</v>
       </c>
-      <c r="C5" t="s">
-        <v>127</v>
-      </c>
       <c r="D5" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="E5">
-        <v>12.82999992370605</v>
+        <v>11.87849998474121</v>
       </c>
       <c r="F5">
-        <v>674073.3333333334</v>
+        <v>620152.1666666666</v>
       </c>
       <c r="G5">
-        <v>11.19279998779297</v>
+        <v>11.33876996994019</v>
       </c>
       <c r="H5">
-        <v>7.834866666793824</v>
+        <v>8.023989993731181</v>
       </c>
       <c r="I5">
-        <v>6.673949999809265</v>
+        <v>6.808692495822907</v>
       </c>
       <c r="J5">
-        <v>5.834350011348724</v>
+        <v>5.94755000948906</v>
       </c>
       <c r="K5">
         <v>0.09375</v>
@@ -1491,7 +1407,7 @@
         <v>13.5</v>
       </c>
       <c r="M5">
-        <v>239.0767061813042</v>
+        <v>201.7373700215835</v>
       </c>
       <c r="N5">
         <v>-0.14</v>
@@ -1506,87 +1422,81 @@
         <v>-0.08</v>
       </c>
       <c r="R5">
+        <v>-3833000</v>
+      </c>
+      <c r="S5">
         <v>-3327000</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>-1960000</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>-2116000</v>
       </c>
-      <c r="U5">
-        <v>-11935000</v>
-      </c>
       <c r="V5" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" t="s">
-        <v>128</v>
-      </c>
       <c r="D6" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="E6">
-        <v>13.05000019073486</v>
+        <v>199.9199981689453</v>
       </c>
       <c r="F6">
-        <v>2547540</v>
+        <v>1081147.333333333</v>
       </c>
       <c r="G6">
-        <v>9.899000015258789</v>
+        <v>186.0122996520996</v>
       </c>
       <c r="H6">
-        <v>8.927566693623861</v>
+        <v>129.3656999969483</v>
       </c>
       <c r="I6">
-        <v>7.604175020456314</v>
+        <v>110.3482249641418</v>
       </c>
       <c r="J6">
-        <v>6.80387501835823</v>
+        <v>95.39312496185303</v>
       </c>
       <c r="K6">
-        <v>0.9279999732971191</v>
+        <v>16.51000022888184</v>
       </c>
       <c r="L6">
-        <v>15.15999984741211</v>
+        <v>199.9199981689453</v>
       </c>
       <c r="M6">
-        <v>202.5312354104882</v>
+        <v>201.2990990610614</v>
       </c>
       <c r="N6">
-        <v>-0.31</v>
+        <v>-0.86</v>
       </c>
       <c r="O6">
-        <v>-0.28</v>
+        <v>-0.9</v>
       </c>
       <c r="P6">
-        <v>-0.3</v>
+        <v>-0.9</v>
       </c>
       <c r="Q6">
-        <v>-0.29</v>
+        <v>-0.86</v>
       </c>
       <c r="R6">
-        <v>-105911000</v>
+        <v>-33647000</v>
       </c>
       <c r="S6">
-        <v>-26633000</v>
+        <v>-37275000</v>
       </c>
       <c r="T6">
-        <v>-28778000</v>
+        <v>-38764000</v>
       </c>
       <c r="U6">
-        <v>-106001000</v>
+        <v>-40876000</v>
       </c>
       <c r="V6" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1594,67 +1504,67 @@
         <v>27</v>
       </c>
       <c r="B7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" t="s">
         <v>117</v>
       </c>
-      <c r="C7" t="s">
-        <v>129</v>
-      </c>
       <c r="D7" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="E7">
-        <v>33.36999893188477</v>
+        <v>44.40000152587891</v>
       </c>
       <c r="F7">
-        <v>398626.6666666667</v>
+        <v>6596970</v>
       </c>
       <c r="G7">
-        <v>28.10849990844726</v>
+        <v>34.74059997558594</v>
       </c>
       <c r="H7">
-        <v>19.67496662775676</v>
+        <v>27.53183330535889</v>
       </c>
       <c r="I7">
-        <v>17.83387496948242</v>
+        <v>25.29739999294281</v>
       </c>
       <c r="J7">
-        <v>15.88287498950958</v>
+        <v>23.74369999408722</v>
       </c>
       <c r="K7">
-        <v>8.970000267028809</v>
+        <v>13.61999988555908</v>
       </c>
       <c r="L7">
-        <v>33.36999893188477</v>
+        <v>44.40000152587891</v>
       </c>
       <c r="M7">
-        <v>199.3021960308955</v>
+        <v>192.442073150157</v>
       </c>
       <c r="N7">
-        <v>-0.61</v>
+        <v>0.9</v>
       </c>
       <c r="O7">
-        <v>-0.61</v>
+        <v>-0.64</v>
       </c>
       <c r="P7">
-        <v>-0.5600000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="Q7">
-        <v>-0.42</v>
+        <v>0.9</v>
       </c>
       <c r="R7">
-        <v>-16818000</v>
+        <v>-617966000</v>
       </c>
       <c r="S7">
-        <v>-15610000</v>
+        <v>-1640321000</v>
       </c>
       <c r="T7">
-        <v>-13212000</v>
+        <v>256938000</v>
       </c>
       <c r="U7">
-        <v>-66756000</v>
+        <v>929668000</v>
       </c>
       <c r="V7" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1662,67 +1572,67 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" t="s">
         <v>118</v>
       </c>
-      <c r="C8" t="s">
-        <v>130</v>
-      </c>
       <c r="D8" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="E8">
-        <v>125.4899978637695</v>
+        <v>12.32999992370605</v>
       </c>
       <c r="F8">
-        <v>505070</v>
+        <v>2501457.833333333</v>
       </c>
       <c r="G8">
-        <v>82.79600006103516</v>
+        <v>10.11659999847412</v>
       </c>
       <c r="H8">
-        <v>70.69606661478679</v>
+        <v>9.072833353678385</v>
       </c>
       <c r="I8">
-        <v>65.59124990463256</v>
+        <v>7.743275017738342</v>
       </c>
       <c r="J8">
-        <v>59.89694986343384</v>
+        <v>6.915375020503998</v>
       </c>
       <c r="K8">
-        <v>5.792013168334961</v>
+        <v>0.9279999732971191</v>
       </c>
       <c r="L8">
-        <v>132.4752044677734</v>
+        <v>15.15999984741211</v>
       </c>
       <c r="M8">
-        <v>198.2365190893374</v>
+        <v>185.7454276117793</v>
       </c>
       <c r="N8">
-        <v>2394.25</v>
+        <v>-0.31</v>
       </c>
       <c r="O8">
-        <v>4830.25</v>
+        <v>-0.28</v>
       </c>
       <c r="P8">
-        <v>1680.75</v>
+        <v>-0.3</v>
       </c>
       <c r="Q8">
-        <v>2394.25</v>
+        <v>-0.29</v>
       </c>
       <c r="R8">
-        <v>509914000000</v>
+        <v>-27094000</v>
       </c>
       <c r="S8">
-        <v>-665869000000</v>
+        <v>-24505000</v>
       </c>
       <c r="T8">
-        <v>726419000000</v>
+        <v>-26633000</v>
       </c>
       <c r="U8">
-        <v>3144087000000</v>
+        <v>-28778000</v>
       </c>
       <c r="V8" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1730,67 +1640,67 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="E9">
-        <v>199.9199981689453</v>
+        <v>32.75</v>
       </c>
       <c r="F9">
-        <v>1081147.333333333</v>
+        <v>409280</v>
       </c>
       <c r="G9">
-        <v>186.0122996520996</v>
+        <v>28.42529987335205</v>
       </c>
       <c r="H9">
-        <v>129.3656999969483</v>
+        <v>19.95229995091756</v>
       </c>
       <c r="I9">
-        <v>110.3482249641418</v>
+        <v>18.06062496185303</v>
       </c>
       <c r="J9">
-        <v>95.39312496185303</v>
+        <v>16.03497498512268</v>
       </c>
       <c r="K9">
-        <v>16.51000022888184</v>
+        <v>8.970000267028809</v>
       </c>
       <c r="L9">
-        <v>199.9199981689453</v>
+        <v>33.36999893188477</v>
       </c>
       <c r="M9">
-        <v>196.7962603205521</v>
+        <v>185.008419431494</v>
       </c>
       <c r="N9">
-        <v>-0.86</v>
+        <v>-0.61</v>
       </c>
       <c r="O9">
-        <v>-0.9</v>
+        <v>-0.61</v>
       </c>
       <c r="P9">
-        <v>-0.9</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="Q9">
-        <v>-0.86</v>
+        <v>-0.42</v>
       </c>
       <c r="R9">
-        <v>-37275000</v>
+        <v>-16732000</v>
       </c>
       <c r="S9">
-        <v>-38764000</v>
+        <v>-16818000</v>
       </c>
       <c r="T9">
-        <v>-40876000</v>
+        <v>-15610000</v>
       </c>
       <c r="U9">
-        <v>-141752000</v>
+        <v>-13212000</v>
       </c>
       <c r="V9" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1798,31 +1708,31 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D10" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="E10">
-        <v>467.2900085449219</v>
+        <v>442.6900024414062</v>
       </c>
       <c r="F10">
-        <v>45517723.33333334</v>
+        <v>44391006.66666666</v>
       </c>
       <c r="G10">
-        <v>412.9652001953125</v>
+        <v>418.5320001220703</v>
       </c>
       <c r="H10">
-        <v>292.2241328938802</v>
+        <v>296.2395329793295</v>
       </c>
       <c r="I10">
-        <v>256.60024974823</v>
+        <v>259.9660498046875</v>
       </c>
       <c r="J10">
-        <v>224.4994998931885</v>
+        <v>227.4331500244141</v>
       </c>
       <c r="K10">
         <v>0.3134739995002747</v>
@@ -1831,7 +1741,7 @@
         <v>474.9400024414062</v>
       </c>
       <c r="M10">
-        <v>188.7717042022524</v>
+        <v>175.1944072066</v>
       </c>
       <c r="N10">
         <v>0.26</v>
@@ -1846,19 +1756,19 @@
         <v>0.82</v>
       </c>
       <c r="R10">
+        <v>656000000</v>
+      </c>
+      <c r="S10">
         <v>680000000</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>1414000000</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <v>2043000000</v>
       </c>
-      <c r="U10">
-        <v>4368000000</v>
-      </c>
       <c r="V10" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1866,67 +1776,67 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D11" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="E11">
-        <v>27.94000053405762</v>
+        <v>133.1900024414062</v>
       </c>
       <c r="F11">
-        <v>2995076.666666667</v>
+        <v>1136150</v>
       </c>
       <c r="G11">
-        <v>25.90059989929199</v>
+        <v>109.0258001708984</v>
       </c>
       <c r="H11">
-        <v>19.83413331985474</v>
+        <v>85.98039995829264</v>
       </c>
       <c r="I11">
-        <v>17.65249998569488</v>
+        <v>77.04499992370606</v>
       </c>
       <c r="J11">
-        <v>16.16999999046326</v>
+        <v>69.4314499092102</v>
       </c>
       <c r="K11">
-        <v>8.699999809265137</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="L11">
-        <v>30.6299991607666</v>
+        <v>133.1900024414062</v>
       </c>
       <c r="M11">
-        <v>188.549891559784</v>
+        <v>174.9091188014804</v>
       </c>
       <c r="N11">
-        <v>-0.13</v>
+        <v>0.27</v>
       </c>
       <c r="O11">
-        <v>-0.11</v>
+        <v>0.21</v>
       </c>
       <c r="P11">
-        <v>-0.1</v>
+        <v>0.34</v>
       </c>
       <c r="Q11">
-        <v>-0.13</v>
+        <v>0.29</v>
       </c>
       <c r="R11">
-        <v>-58555000</v>
+        <v>14469000</v>
       </c>
       <c r="S11">
-        <v>-53598000</v>
+        <v>11710000</v>
       </c>
       <c r="T11">
-        <v>-67856000</v>
+        <v>19105000</v>
       </c>
       <c r="U11">
-        <v>-247422000</v>
+        <v>16246000</v>
       </c>
       <c r="V11" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1934,67 +1844,67 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C12" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="D12" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="E12">
-        <v>42.79999923706055</v>
+        <v>47.06000137329102</v>
       </c>
       <c r="F12">
-        <v>6536786.666666667</v>
+        <v>300010.1666666667</v>
       </c>
       <c r="G12">
-        <v>34.12079998016358</v>
+        <v>35.89179992675781</v>
       </c>
       <c r="H12">
-        <v>27.20136664072673</v>
+        <v>29.61733334859212</v>
       </c>
       <c r="I12">
-        <v>25.05569999217987</v>
+        <v>28.00144999504089</v>
       </c>
       <c r="J12">
-        <v>23.6458499956131</v>
+        <v>26.12255000114441</v>
       </c>
       <c r="K12">
-        <v>13.61999988555908</v>
+        <v>0.2220596075057983</v>
       </c>
       <c r="L12">
-        <v>43.95999908447266</v>
+        <v>48.31999969482422</v>
       </c>
       <c r="M12">
-        <v>181.1259662745777</v>
+        <v>173.7016879582047</v>
       </c>
       <c r="N12">
-        <v>0.9</v>
+        <v>0.43</v>
       </c>
       <c r="O12">
-        <v>-0.64</v>
+        <v>0.45</v>
       </c>
       <c r="P12">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="Q12">
-        <v>0.9</v>
+        <v>0.38</v>
       </c>
       <c r="R12">
-        <v>-1640321000</v>
+        <v>20715000</v>
       </c>
       <c r="S12">
-        <v>256938000</v>
+        <v>21673000</v>
       </c>
       <c r="T12">
-        <v>929668000</v>
+        <v>17245000</v>
       </c>
       <c r="U12">
-        <v>-2012215000</v>
+        <v>18539000</v>
       </c>
       <c r="V12" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -2002,67 +1912,67 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C13" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="D13" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="E13">
-        <v>47.61000061035156</v>
+        <v>63.25</v>
       </c>
       <c r="F13">
-        <v>279350</v>
+        <v>386060.3666666666</v>
       </c>
       <c r="G13">
-        <v>34.8135998916626</v>
+        <v>54.12839973449707</v>
       </c>
       <c r="H13">
-        <v>29.11713334401449</v>
+        <v>41.52266653696696</v>
       </c>
       <c r="I13">
-        <v>27.63789999961853</v>
+        <v>38.44569990158081</v>
       </c>
       <c r="J13">
-        <v>25.9875</v>
+        <v>35.329049949646</v>
       </c>
       <c r="K13">
-        <v>0.2220596075057983</v>
+        <v>8.689999580383301</v>
       </c>
       <c r="L13">
-        <v>48.31999969482422</v>
+        <v>63.25</v>
       </c>
       <c r="M13">
-        <v>175.1066591801561</v>
+        <v>172.559088590271</v>
       </c>
       <c r="N13">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="O13">
-        <v>0.43</v>
+        <v>0.3</v>
       </c>
       <c r="P13">
-        <v>0.45</v>
+        <v>0.66</v>
       </c>
       <c r="Q13">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="R13">
-        <v>20715000</v>
+        <v>17346000</v>
       </c>
       <c r="S13">
-        <v>21673000</v>
+        <v>15874000</v>
       </c>
       <c r="T13">
-        <v>17245000</v>
+        <v>33913000</v>
       </c>
       <c r="U13">
-        <v>79949000</v>
+        <v>26032000</v>
       </c>
       <c r="V13" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -2070,67 +1980,67 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C14" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="D14" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="E14">
-        <v>69.23999786376953</v>
+        <v>113.5</v>
       </c>
       <c r="F14">
-        <v>2215236.666666667</v>
+        <v>525799.7333333333</v>
       </c>
       <c r="G14">
-        <v>55.95459999084473</v>
+        <v>85.52700012207032</v>
       </c>
       <c r="H14">
-        <v>43.51686672210693</v>
+        <v>71.87653330485026</v>
       </c>
       <c r="I14">
-        <v>41.2029078578949</v>
+        <v>66.6894499206543</v>
       </c>
       <c r="J14">
-        <v>37.58414888381958</v>
+        <v>60.40894987106324</v>
       </c>
       <c r="K14">
-        <v>0.6502050161361694</v>
+        <v>5.792013168334961</v>
       </c>
       <c r="L14">
-        <v>71.65000152587891</v>
+        <v>132.4752044677734</v>
       </c>
       <c r="M14">
-        <v>175.0301828025447</v>
+        <v>171.6050524420866</v>
       </c>
       <c r="N14">
-        <v>1.22</v>
+        <v>2394.25</v>
       </c>
       <c r="O14">
-        <v>1.13</v>
+        <v>4830.25</v>
       </c>
       <c r="P14">
-        <v>-0.8100000000000001</v>
+        <v>1680.75</v>
       </c>
       <c r="Q14">
-        <v>0.13</v>
+        <v>2394.25</v>
       </c>
       <c r="R14">
-        <v>131000000</v>
+        <v>1588430000000</v>
       </c>
       <c r="S14">
-        <v>-94000000</v>
+        <v>509914000000</v>
       </c>
       <c r="T14">
-        <v>14000000</v>
+        <v>-665869000000</v>
       </c>
       <c r="U14">
-        <v>666000000</v>
+        <v>726419000000</v>
       </c>
       <c r="V14" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2138,67 +2048,67 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C15" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D15" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="E15">
-        <v>200.4799957275391</v>
+        <v>68.29000091552734</v>
       </c>
       <c r="F15">
-        <v>517223.3333333333</v>
+        <v>2247446.666666667</v>
       </c>
       <c r="G15">
-        <v>171.173200378418</v>
+        <v>56.81000007629395</v>
       </c>
       <c r="H15">
-        <v>135.3816004435221</v>
+        <v>43.96980007171631</v>
       </c>
       <c r="I15">
-        <v>119.1451003265381</v>
+        <v>41.59836042404175</v>
       </c>
       <c r="J15">
-        <v>107.1865002822876</v>
+        <v>37.87534955978393</v>
       </c>
       <c r="K15">
-        <v>0.6800000071525574</v>
+        <v>0.6502050161361694</v>
       </c>
       <c r="L15">
-        <v>200.4799957275391</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="M15">
-        <v>170.2688435410465</v>
+        <v>169.5139099417947</v>
       </c>
       <c r="N15">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="O15">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="P15">
-        <v>1.71</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="Q15">
-        <v>1.43</v>
+        <v>0.13</v>
       </c>
       <c r="R15">
-        <v>40283000</v>
+        <v>141000000</v>
       </c>
       <c r="S15">
-        <v>56992000</v>
+        <v>131000000</v>
       </c>
       <c r="T15">
-        <v>47697000</v>
+        <v>-94000000</v>
       </c>
       <c r="U15">
-        <v>183079000</v>
+        <v>14000000</v>
       </c>
       <c r="V15" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -2206,52 +2116,52 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C16" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D16" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="E16">
-        <v>144.4299926757812</v>
+        <v>148.6399993896484</v>
       </c>
       <c r="F16">
-        <v>1773470</v>
+        <v>1554080</v>
       </c>
       <c r="G16">
-        <v>129.753999786377</v>
+        <v>130.8109997558594</v>
       </c>
       <c r="H16">
-        <v>99.90946637471517</v>
+        <v>101.0099329884847</v>
       </c>
       <c r="I16">
-        <v>90.44699979782105</v>
+        <v>91.29804977416993</v>
       </c>
       <c r="J16">
-        <v>82.34769983291626</v>
+        <v>83.15909984588623</v>
       </c>
       <c r="K16">
         <v>0.8299999833106995</v>
       </c>
       <c r="L16">
-        <v>146.4199981689453</v>
+        <v>148.6399993896484</v>
       </c>
       <c r="M16">
-        <v>170.0038695596177</v>
+        <v>166.479777541394</v>
       </c>
       <c r="N16">
+        <v>5.75</v>
+      </c>
+      <c r="O16">
+        <v>4.72</v>
+      </c>
+      <c r="P16">
         <v>2.41</v>
       </c>
-      <c r="O16">
-        <v>5.75</v>
-      </c>
-      <c r="P16">
-        <v>4.72</v>
-      </c>
       <c r="Q16">
-        <v>2.41</v>
+        <v>3.16</v>
       </c>
       <c r="R16">
         <v>738007000</v>
@@ -2263,10 +2173,10 @@
         <v>333786000</v>
       </c>
       <c r="U16">
-        <v>2749369000</v>
+        <v>404619000</v>
       </c>
       <c r="V16" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2274,31 +2184,31 @@
         <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D17" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="E17">
-        <v>100</v>
+        <v>98.30999755859375</v>
       </c>
       <c r="F17">
-        <v>381440</v>
+        <v>364553.3333333333</v>
       </c>
       <c r="G17">
-        <v>82.0918000793457</v>
+        <v>83.14060012817383</v>
       </c>
       <c r="H17">
-        <v>66.97753339131673</v>
+        <v>67.66980005900065</v>
       </c>
       <c r="I17">
-        <v>60.96090005874634</v>
+        <v>61.54945003509521</v>
       </c>
       <c r="J17">
-        <v>55.79695011138916</v>
+        <v>56.25710010528564</v>
       </c>
       <c r="K17">
         <v>3.118403196334839</v>
@@ -2307,7 +2217,7 @@
         <v>100</v>
       </c>
       <c r="M17">
-        <v>169.7756640412077</v>
+        <v>155.9731081513379</v>
       </c>
       <c r="N17">
         <v>4.67</v>
@@ -2322,19 +2232,19 @@
         <v>4.12</v>
       </c>
       <c r="R17">
-        <v>490662000</v>
+        <v>131590000</v>
       </c>
       <c r="S17">
+        <v>130395000</v>
+      </c>
+      <c r="T17">
         <v>103066000</v>
       </c>
-      <c r="T17">
+      <c r="U17">
         <v>118001000</v>
       </c>
-      <c r="U17">
-        <v>501889000</v>
-      </c>
       <c r="V17" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -2342,67 +2252,67 @@
         <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D18" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="E18">
-        <v>60.68999862670898</v>
+        <v>61.41999816894531</v>
       </c>
       <c r="F18">
-        <v>451820</v>
+        <v>334966.0333333333</v>
       </c>
       <c r="G18">
-        <v>53.0621997833252</v>
+        <v>54.66399993896484</v>
       </c>
       <c r="H18">
-        <v>40.85613320668539</v>
+        <v>43.08020000457763</v>
       </c>
       <c r="I18">
-        <v>37.94209991455078</v>
+        <v>39.92875</v>
       </c>
       <c r="J18">
-        <v>34.90739994049072</v>
+        <v>36.28819999694824</v>
       </c>
       <c r="K18">
-        <v>8.689999580383301</v>
+        <v>0.4209107160568237</v>
       </c>
       <c r="L18">
-        <v>63.25</v>
+        <v>62.97999954223633</v>
       </c>
       <c r="M18">
-        <v>168.407444260123</v>
+        <v>155.9099931669256</v>
       </c>
       <c r="N18">
-        <v>0.33</v>
+        <v>0.86</v>
       </c>
       <c r="O18">
-        <v>0.3</v>
+        <v>0.97</v>
       </c>
       <c r="P18">
-        <v>0.66</v>
+        <v>1.03</v>
       </c>
       <c r="Q18">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="R18">
-        <v>15874000</v>
+        <v>25961000</v>
       </c>
       <c r="S18">
-        <v>33913000</v>
+        <v>29523000</v>
       </c>
       <c r="T18">
-        <v>26032000</v>
+        <v>31725000</v>
       </c>
       <c r="U18">
-        <v>91386000</v>
+        <v>19649000</v>
       </c>
       <c r="V18" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -2410,67 +2320,67 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C19" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="E19">
-        <v>26.01000022888184</v>
+        <v>47.38000106811523</v>
       </c>
       <c r="F19">
-        <v>4674690</v>
+        <v>1991166.666666667</v>
       </c>
       <c r="G19">
-        <v>22.74159999847412</v>
+        <v>41.46540000915527</v>
       </c>
       <c r="H19">
-        <v>17.1043333307902</v>
+        <v>34.22250002543132</v>
       </c>
       <c r="I19">
-        <v>16.23745000839233</v>
+        <v>34.06104997634888</v>
       </c>
       <c r="J19">
-        <v>14.79835000038147</v>
+        <v>31.67024994850159</v>
       </c>
       <c r="K19">
-        <v>5.564881324768066</v>
+        <v>13.1899995803833</v>
       </c>
       <c r="L19">
-        <v>28.57900047302246</v>
+        <v>47.38000106811523</v>
       </c>
       <c r="M19">
-        <v>162.8174828123756</v>
+        <v>154.9268505712554</v>
       </c>
       <c r="N19">
-        <v>0.05</v>
+        <v>-0.58</v>
       </c>
       <c r="O19">
-        <v>0.06</v>
+        <v>-0.55</v>
       </c>
       <c r="P19">
-        <v>0.07000000000000001</v>
+        <v>-0.51</v>
       </c>
       <c r="Q19">
-        <v>0.12</v>
+        <v>-0.54</v>
       </c>
       <c r="R19">
-        <v>21200000</v>
+        <v>-21522000</v>
       </c>
       <c r="S19">
-        <v>26600000</v>
+        <v>-20550000</v>
       </c>
       <c r="T19">
-        <v>50300000</v>
+        <v>-23224000</v>
       </c>
       <c r="U19">
-        <v>76600000</v>
+        <v>-25646000</v>
       </c>
       <c r="V19" t="s">
-        <v>268</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -2478,67 +2388,67 @@
         <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D20" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="E20">
-        <v>11.97999954223633</v>
+        <v>186.4400024414062</v>
       </c>
       <c r="F20">
-        <v>6916610</v>
+        <v>511499.3333333333</v>
       </c>
       <c r="G20">
-        <v>10.1889999961853</v>
+        <v>174.0048007202148</v>
       </c>
       <c r="H20">
-        <v>8.888399982452393</v>
+        <v>137.5932672119141</v>
       </c>
       <c r="I20">
-        <v>8.048599989414216</v>
+        <v>121.1951503944397</v>
       </c>
       <c r="J20">
-        <v>7.28754998922348</v>
+        <v>108.9223503303528</v>
       </c>
       <c r="K20">
-        <v>2.809999942779541</v>
+        <v>0.6800000071525574</v>
       </c>
       <c r="L20">
-        <v>13.52000045776367</v>
+        <v>200.4799957275391</v>
       </c>
       <c r="M20">
-        <v>161.9594467559942</v>
+        <v>154.9227533137995</v>
       </c>
       <c r="N20">
-        <v>-0.48</v>
+        <v>1.32</v>
       </c>
       <c r="O20">
-        <v>-0.42</v>
+        <v>1.21</v>
       </c>
       <c r="P20">
-        <v>-0.49</v>
+        <v>1.71</v>
       </c>
       <c r="Q20">
-        <v>-0.05</v>
+        <v>1.43</v>
       </c>
       <c r="R20">
-        <v>-291590000</v>
+        <v>44189000</v>
       </c>
       <c r="S20">
-        <v>-352014000</v>
+        <v>40283000</v>
       </c>
       <c r="T20">
-        <v>-33617000</v>
+        <v>56992000</v>
       </c>
       <c r="U20">
-        <v>-1245475000</v>
+        <v>47697000</v>
       </c>
       <c r="V20" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -2546,67 +2456,67 @@
         <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="E21">
-        <v>52.15999984741211</v>
+        <v>425.1300048828125</v>
       </c>
       <c r="F21">
-        <v>1460763.333333333</v>
+        <v>652400</v>
       </c>
       <c r="G21">
-        <v>41.38399997711181</v>
+        <v>340.0053997802734</v>
       </c>
       <c r="H21">
-        <v>33.83793326059977</v>
+        <v>291.7941999308268</v>
       </c>
       <c r="I21">
-        <v>30.96719992637634</v>
+        <v>274.1866498565674</v>
       </c>
       <c r="J21">
-        <v>27.85994991779327</v>
+        <v>254.8489495849609</v>
       </c>
       <c r="K21">
-        <v>0.5</v>
+        <v>4.533332824707031</v>
       </c>
       <c r="L21">
-        <v>52.16999816894531</v>
+        <v>425.8900146484375</v>
       </c>
       <c r="M21">
-        <v>161.7948314334095</v>
+        <v>154.0928205532058</v>
       </c>
       <c r="N21">
-        <v>0.02</v>
+        <v>3.67</v>
       </c>
       <c r="O21">
-        <v>0.13</v>
+        <v>2.65</v>
       </c>
       <c r="P21">
-        <v>0.14</v>
+        <v>2.85</v>
       </c>
       <c r="Q21">
-        <v>0.21</v>
+        <v>3.42</v>
       </c>
       <c r="R21">
-        <v>3725000</v>
+        <v>97891000</v>
       </c>
       <c r="S21">
-        <v>4132000</v>
+        <v>70862000</v>
       </c>
       <c r="T21">
-        <v>6111000</v>
+        <v>76097000</v>
       </c>
       <c r="U21">
-        <v>14240000</v>
+        <v>91319000</v>
       </c>
       <c r="V21" t="s">
-        <v>268</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2614,67 +2524,67 @@
         <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C22" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="D22" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="E22">
-        <v>20.85000038146973</v>
+        <v>11.57999992370605</v>
       </c>
       <c r="F22">
-        <v>908953.3333333334</v>
+        <v>6701876.266666667</v>
       </c>
       <c r="G22">
-        <v>18.63200008392334</v>
+        <v>10.33400001525879</v>
       </c>
       <c r="H22">
-        <v>14.51826667149862</v>
+        <v>8.978799985249838</v>
       </c>
       <c r="I22">
-        <v>13.03574999332428</v>
+        <v>8.157199993133545</v>
       </c>
       <c r="J22">
-        <v>11.87699999570847</v>
+        <v>7.390599988698959</v>
       </c>
       <c r="K22">
-        <v>6.690000057220459</v>
+        <v>2.809999942779541</v>
       </c>
       <c r="L22">
-        <v>26.39999961853027</v>
+        <v>13.52000045776367</v>
       </c>
       <c r="M22">
-        <v>161.4197255402331</v>
+        <v>152.4871659079732</v>
       </c>
       <c r="N22">
-        <v>0.01</v>
+        <v>-0.48</v>
       </c>
       <c r="O22">
-        <v>0.004895</v>
+        <v>-0.42</v>
       </c>
       <c r="P22">
-        <v>0.07000000000000001</v>
+        <v>-0.49</v>
       </c>
       <c r="Q22">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="R22">
-        <v>767000</v>
+        <v>-331809000</v>
       </c>
       <c r="S22">
-        <v>11487000</v>
+        <v>-291590000</v>
       </c>
       <c r="T22">
-        <v>3146000</v>
+        <v>-352014000</v>
       </c>
       <c r="U22">
-        <v>15373000</v>
+        <v>-33617000</v>
       </c>
       <c r="V22" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2682,67 +2592,67 @@
         <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C23" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="D23" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="E23">
-        <v>109.1100006103516</v>
+        <v>109.3899993896484</v>
       </c>
       <c r="F23">
-        <v>3705826.666666667</v>
+        <v>376483.8333333333</v>
       </c>
       <c r="G23">
-        <v>95.02160003662109</v>
+        <v>87.84979980468751</v>
       </c>
       <c r="H23">
-        <v>75.2770667775472</v>
+        <v>75.30733360290527</v>
       </c>
       <c r="I23">
-        <v>70.0234500694275</v>
+        <v>73.81795021057128</v>
       </c>
       <c r="J23">
-        <v>64.30695007324219</v>
+        <v>69.8934002494812</v>
       </c>
       <c r="K23">
-        <v>4.547188282012939</v>
+        <v>11.37919998168945</v>
       </c>
       <c r="L23">
-        <v>133.7226409912109</v>
+        <v>109.3899993896484</v>
       </c>
       <c r="M23">
-        <v>160.8687788574994</v>
+        <v>152.0271840825212</v>
       </c>
       <c r="N23">
-        <v>0.13</v>
+        <v>5.52</v>
       </c>
       <c r="O23">
-        <v>-1.96</v>
+        <v>2.95</v>
       </c>
       <c r="P23">
-        <v>-0.19</v>
+        <v>2.43</v>
       </c>
       <c r="Q23">
-        <v>1.7</v>
+        <v>3.67</v>
       </c>
       <c r="R23">
-        <v>-2155962000</v>
+        <v>219587000</v>
       </c>
       <c r="S23">
-        <v>-47910000</v>
+        <v>117360000</v>
       </c>
       <c r="T23">
-        <v>458761000</v>
+        <v>96733000</v>
       </c>
       <c r="U23">
-        <v>-1036730000</v>
+        <v>146320000</v>
       </c>
       <c r="V23" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2750,67 +2660,67 @@
         <v>44</v>
       </c>
       <c r="B24" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C24" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="D24" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="E24">
-        <v>91.26000213623047</v>
+        <v>83.08000183105469</v>
       </c>
       <c r="F24">
-        <v>5117183.333333333</v>
+        <v>869886.4666666667</v>
       </c>
       <c r="G24">
-        <v>77.61980026245118</v>
+        <v>68.52439971923827</v>
       </c>
       <c r="H24">
-        <v>62.92940012613932</v>
+        <v>62.31113311767578</v>
       </c>
       <c r="I24">
-        <v>59.77360006332398</v>
+        <v>57.27264987945556</v>
       </c>
       <c r="J24">
-        <v>57.40695003509521</v>
+        <v>52.76229991912842</v>
       </c>
       <c r="K24">
-        <v>2.279999971389771</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="L24">
-        <v>111.6399993896484</v>
+        <v>84.09999847412109</v>
       </c>
       <c r="M24">
-        <v>159.5575279760833</v>
+        <v>149.2301440582534</v>
       </c>
       <c r="N24">
-        <v>-0.04</v>
+        <v>0.39</v>
       </c>
       <c r="O24">
-        <v>0.03</v>
+        <v>0.99</v>
       </c>
       <c r="P24">
-        <v>0.14</v>
+        <v>0.97</v>
       </c>
       <c r="Q24">
-        <v>0.02</v>
+        <v>1.12</v>
       </c>
       <c r="R24">
-        <v>15869000</v>
+        <v>28000000</v>
       </c>
       <c r="S24">
-        <v>71187000</v>
+        <v>72000000</v>
       </c>
       <c r="T24">
-        <v>9326000</v>
+        <v>72000000</v>
       </c>
       <c r="U24">
-        <v>53385000</v>
+        <v>82000000</v>
       </c>
       <c r="V24" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2818,67 +2728,67 @@
         <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C25" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D25" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="E25">
-        <v>423.1400146484375</v>
+        <v>104.3649978637695</v>
       </c>
       <c r="F25">
-        <v>653590</v>
+        <v>3705553.5</v>
       </c>
       <c r="G25">
-        <v>334.1879998779297</v>
+        <v>96.56050003051757</v>
       </c>
       <c r="H25">
-        <v>288.9743999226888</v>
+        <v>76.40250007629395</v>
       </c>
       <c r="I25">
-        <v>271.9603997802735</v>
+        <v>70.93487504959107</v>
       </c>
       <c r="J25">
-        <v>253.3839996337891</v>
+        <v>65.09695003509522</v>
       </c>
       <c r="K25">
-        <v>4.533332824707031</v>
+        <v>4.547188282012939</v>
       </c>
       <c r="L25">
-        <v>425.8900146484375</v>
+        <v>133.7226409912109</v>
       </c>
       <c r="M25">
-        <v>159.1793745647682</v>
+        <v>147.9284171317249</v>
       </c>
       <c r="N25">
-        <v>3.67</v>
+        <v>0.13</v>
       </c>
       <c r="O25">
-        <v>2.65</v>
+        <v>-1.96</v>
       </c>
       <c r="P25">
-        <v>2.85</v>
+        <v>-0.19</v>
       </c>
       <c r="Q25">
-        <v>3.42</v>
+        <v>1.7</v>
       </c>
       <c r="R25">
-        <v>357422000</v>
+        <v>32968000</v>
       </c>
       <c r="S25">
-        <v>76097000</v>
+        <v>-500206000</v>
       </c>
       <c r="T25">
-        <v>91319000</v>
+        <v>-47910000</v>
       </c>
       <c r="U25">
-        <v>354095000</v>
+        <v>458761000</v>
       </c>
       <c r="V25" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2886,67 +2796,67 @@
         <v>46</v>
       </c>
       <c r="B26" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C26" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D26" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="E26">
-        <v>116.7200012207031</v>
+        <v>32.46500015258789</v>
       </c>
       <c r="F26">
-        <v>1020153.333333333</v>
+        <v>273520.3666666666</v>
       </c>
       <c r="G26">
-        <v>107.6404000854492</v>
+        <v>30.78349994659424</v>
       </c>
       <c r="H26">
-        <v>85.0457999420166</v>
+        <v>25.74629993438721</v>
       </c>
       <c r="I26">
-        <v>76.19599992752075</v>
+        <v>23.37732496738434</v>
       </c>
       <c r="J26">
-        <v>68.69774990081787</v>
+        <v>21.92749999523163</v>
       </c>
       <c r="K26">
-        <v>7.300000190734863</v>
+        <v>14.10000038146973</v>
       </c>
       <c r="L26">
-        <v>119.5100021362305</v>
+        <v>33.61000061035156</v>
       </c>
       <c r="M26">
-        <v>159.0995762233708</v>
+        <v>146.1653343675191</v>
       </c>
       <c r="N26">
-        <v>0.27</v>
+        <v>0.14</v>
       </c>
       <c r="O26">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="P26">
-        <v>0.34</v>
+        <v>0.11</v>
       </c>
       <c r="Q26">
-        <v>0.29</v>
+        <v>0.13</v>
       </c>
       <c r="R26">
-        <v>11710000</v>
+        <v>36215000</v>
       </c>
       <c r="S26">
-        <v>19105000</v>
+        <v>48300000</v>
       </c>
       <c r="T26">
-        <v>16246000</v>
+        <v>28265000</v>
       </c>
       <c r="U26">
-        <v>46840000</v>
+        <v>34300000</v>
       </c>
       <c r="V26" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -2954,67 +2864,67 @@
         <v>47</v>
       </c>
       <c r="B27" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="C27" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="E27">
-        <v>37.56000137329102</v>
+        <v>22.8799991607666</v>
       </c>
       <c r="F27">
-        <v>589126.6666666666</v>
+        <v>2064013.1</v>
       </c>
       <c r="G27">
-        <v>31.73180015563965</v>
+        <v>21.17999996185303</v>
       </c>
       <c r="H27">
-        <v>25.38173334757487</v>
+        <v>17.24499998092652</v>
       </c>
       <c r="I27">
-        <v>23.81255001544952</v>
+        <v>16.85110000610351</v>
       </c>
       <c r="J27">
-        <v>21.66294999599457</v>
+        <v>16.01930000782013</v>
       </c>
       <c r="K27">
-        <v>0.5703791379928589</v>
+        <v>12.61999988555908</v>
       </c>
       <c r="L27">
-        <v>37.97000122070312</v>
+        <v>24.46999931335449</v>
       </c>
       <c r="M27">
-        <v>155.9803190100494</v>
+        <v>144.8231704721786</v>
       </c>
       <c r="N27">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>24400000</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>24500000</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>71600000</v>
+        <v>0</v>
       </c>
       <c r="V27" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -3022,40 +2932,40 @@
         <v>48</v>
       </c>
       <c r="B28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" t="s">
         <v>122</v>
       </c>
-      <c r="C28" t="s">
-        <v>145</v>
-      </c>
       <c r="D28" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="E28">
-        <v>26.42000007629395</v>
+        <v>50.04999923706055</v>
       </c>
       <c r="F28">
-        <v>527773.3333333334</v>
+        <v>1463973.333333333</v>
       </c>
       <c r="G28">
-        <v>26.32530002593994</v>
+        <v>42.16179996490479</v>
       </c>
       <c r="H28">
-        <v>20.4942333539327</v>
+        <v>34.25059991200765</v>
       </c>
       <c r="I28">
-        <v>18.22015003204346</v>
+        <v>31.33024991989136</v>
       </c>
       <c r="J28">
-        <v>16.91220003128052</v>
+        <v>28.11069992542267</v>
       </c>
       <c r="K28">
-        <v>7.559999942779541</v>
+        <v>0.5</v>
       </c>
       <c r="L28">
-        <v>29.29999923706055</v>
+        <v>53.68999862670898</v>
       </c>
       <c r="M28">
-        <v>155.4577213152232</v>
+        <v>142.7663481001454</v>
       </c>
       <c r="N28">
         <v>0.02</v>
@@ -3064,25 +2974,25 @@
         <v>0.13</v>
       </c>
       <c r="P28">
-        <v>-0.05</v>
+        <v>0.14</v>
       </c>
       <c r="Q28">
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="R28">
-        <v>7258000</v>
+        <v>589000</v>
       </c>
       <c r="S28">
-        <v>-2810000</v>
+        <v>3725000</v>
       </c>
       <c r="T28">
-        <v>6705000</v>
+        <v>4132000</v>
       </c>
       <c r="U28">
-        <v>7814000</v>
+        <v>6111000</v>
       </c>
       <c r="V28" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -3090,67 +3000,67 @@
         <v>49</v>
       </c>
       <c r="B29" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C29" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="E29">
-        <v>59.9900016784668</v>
+        <v>83.55999755859375</v>
       </c>
       <c r="F29">
-        <v>336000</v>
+        <v>2660183.333333333</v>
       </c>
       <c r="G29">
-        <v>53.57799995422364</v>
+        <v>75.72839965820313</v>
       </c>
       <c r="H29">
-        <v>42.49166667938233</v>
+        <v>63.35746648152669</v>
       </c>
       <c r="I29">
-        <v>39.35090001106262</v>
+        <v>58.07844985961914</v>
       </c>
       <c r="J29">
-        <v>35.78235000610351</v>
+        <v>53.93349996566772</v>
       </c>
       <c r="K29">
-        <v>0.4209107160568237</v>
+        <v>0.1027423962950706</v>
       </c>
       <c r="L29">
-        <v>59.9900016784668</v>
+        <v>84.81999969482422</v>
       </c>
       <c r="M29">
-        <v>154.7057237025718</v>
+        <v>141.5486644685861</v>
       </c>
       <c r="N29">
-        <v>0.86</v>
+        <v>2.69</v>
       </c>
       <c r="O29">
-        <v>0.97</v>
+        <v>3.85</v>
       </c>
       <c r="P29">
-        <v>1.03</v>
+        <v>2.35</v>
       </c>
       <c r="Q29">
-        <v>0.64</v>
+        <v>3.21</v>
       </c>
       <c r="R29">
-        <v>29523000</v>
+        <v>627928000</v>
       </c>
       <c r="S29">
-        <v>31725000</v>
+        <v>882231000</v>
       </c>
       <c r="T29">
-        <v>19649000</v>
+        <v>532259000</v>
       </c>
       <c r="U29">
-        <v>106461000</v>
+        <v>720345000</v>
       </c>
       <c r="V29" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -3158,67 +3068,67 @@
         <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="D30" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="E30">
-        <v>83.09999847412109</v>
+        <v>141.9100036621094</v>
       </c>
       <c r="F30">
-        <v>872560</v>
+        <v>872776.6666666666</v>
       </c>
       <c r="G30">
-        <v>67.1121997833252</v>
+        <v>125.1906007385254</v>
       </c>
       <c r="H30">
-        <v>61.64046648661296</v>
+        <v>106.3447336832682</v>
       </c>
       <c r="I30">
-        <v>56.51844987869263</v>
+        <v>101.8252001953125</v>
       </c>
       <c r="J30">
-        <v>52.25719989776611</v>
+        <v>96.56130004882813</v>
       </c>
       <c r="K30">
-        <v>5.739999771118164</v>
+        <v>4.719488620758057</v>
       </c>
       <c r="L30">
-        <v>83.09999847412109</v>
+        <v>141.9100036621094</v>
       </c>
       <c r="M30">
-        <v>154.2114616029173</v>
+        <v>140.6375885910446</v>
       </c>
       <c r="N30">
-        <v>0.39</v>
+        <v>4.84</v>
       </c>
       <c r="O30">
-        <v>0.99</v>
+        <v>1.32</v>
       </c>
       <c r="P30">
-        <v>0.97</v>
+        <v>4.17</v>
       </c>
       <c r="Q30">
-        <v>1.12</v>
+        <v>3.78</v>
       </c>
       <c r="R30">
-        <v>26000000</v>
+        <v>470000000</v>
       </c>
       <c r="S30">
-        <v>72000000</v>
+        <v>124000000</v>
       </c>
       <c r="T30">
-        <v>82000000</v>
+        <v>383000000</v>
       </c>
       <c r="U30">
-        <v>178000000</v>
+        <v>345000000</v>
       </c>
       <c r="V30" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -3226,67 +3136,67 @@
         <v>51</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C31" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D31" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="E31">
-        <v>49.45999908447266</v>
+        <v>84.54000091552734</v>
       </c>
       <c r="F31">
-        <v>22335443.33333333</v>
+        <v>5068079.666666667</v>
       </c>
       <c r="G31">
-        <v>42.78839996337891</v>
+        <v>78.7872004699707</v>
       </c>
       <c r="H31">
-        <v>35.55140009562174</v>
+        <v>63.78026679992676</v>
       </c>
       <c r="I31">
-        <v>33.5685000705719</v>
+        <v>60.3013000869751</v>
       </c>
       <c r="J31">
-        <v>31.89245009422302</v>
+        <v>57.61540000915527</v>
       </c>
       <c r="K31">
-        <v>14.81999969482422</v>
+        <v>2.279999971389771</v>
       </c>
       <c r="L31">
-        <v>63.18000030517578</v>
+        <v>111.6399993896484</v>
       </c>
       <c r="M31">
-        <v>153.8479977014528</v>
+        <v>140.0888905157719</v>
       </c>
       <c r="N31">
-        <v>-1.33</v>
+        <v>-0.04</v>
       </c>
       <c r="O31">
-        <v>-0.61</v>
+        <v>0.03</v>
       </c>
       <c r="P31">
-        <v>0.29</v>
+        <v>0.14</v>
       </c>
       <c r="Q31">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="R31">
-        <v>-1206000000</v>
+        <v>-19073000</v>
       </c>
       <c r="S31">
-        <v>595000000</v>
+        <v>15869000</v>
       </c>
       <c r="T31">
-        <v>-157000000</v>
+        <v>71187000</v>
       </c>
       <c r="U31">
-        <v>-9141000000</v>
+        <v>9326000</v>
       </c>
       <c r="V31" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -3294,67 +3204,67 @@
         <v>52</v>
       </c>
       <c r="B32" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" t="s">
         <v>119</v>
       </c>
-      <c r="C32" t="s">
-        <v>137</v>
-      </c>
       <c r="D32" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="E32">
-        <v>84.38999938964844</v>
+        <v>74.31999969482422</v>
       </c>
       <c r="F32">
-        <v>2801106.666666667</v>
+        <v>500034.2</v>
       </c>
       <c r="G32">
-        <v>75.1513996887207</v>
+        <v>68.97379974365235</v>
       </c>
       <c r="H32">
-        <v>62.84839981079102</v>
+        <v>56.03279980977376</v>
       </c>
       <c r="I32">
-        <v>57.62679985046387</v>
+        <v>54.20469984054566</v>
       </c>
       <c r="J32">
-        <v>53.550299949646</v>
+        <v>52.08049989700317</v>
       </c>
       <c r="K32">
-        <v>0.1027423962950706</v>
+        <v>14.8100004196167</v>
       </c>
       <c r="L32">
-        <v>84.81999969482422</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="M32">
-        <v>151.3797681659705</v>
+        <v>139.8058017366882</v>
       </c>
       <c r="N32">
-        <v>2.69</v>
+        <v>-0.96</v>
       </c>
       <c r="O32">
-        <v>3.85</v>
+        <v>-0.58</v>
       </c>
       <c r="P32">
-        <v>2.35</v>
+        <v>-0.66</v>
       </c>
       <c r="Q32">
-        <v>3.21</v>
+        <v>-0.72</v>
       </c>
       <c r="R32">
-        <v>2617317000</v>
+        <v>-45536000</v>
       </c>
       <c r="S32">
-        <v>532259000</v>
+        <v>-27576000</v>
       </c>
       <c r="T32">
-        <v>720345000</v>
+        <v>-31460000</v>
       </c>
       <c r="U32">
-        <v>2694853000</v>
+        <v>-34626000</v>
       </c>
       <c r="V32" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -3362,135 +3272,129 @@
         <v>53</v>
       </c>
       <c r="B33" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C33" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D33" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="E33">
-        <v>77.13999938964844</v>
+        <v>84.87999725341797</v>
       </c>
       <c r="F33">
-        <v>523273.3333333333</v>
+        <v>462880.9666666667</v>
       </c>
       <c r="G33">
-        <v>68.01819976806641</v>
+        <v>78.67159980773926</v>
       </c>
       <c r="H33">
-        <v>55.37139984130859</v>
+        <v>65.44779986063639</v>
       </c>
       <c r="I33">
-        <v>53.8719998550415</v>
+        <v>63.20009990692139</v>
       </c>
       <c r="J33">
-        <v>51.89414989471435</v>
+        <v>60.32039995193482</v>
       </c>
       <c r="K33">
-        <v>14.8100004196167</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="L33">
-        <v>97.69999694824219</v>
+        <v>86.93000030517578</v>
       </c>
       <c r="M33">
-        <v>151.2972453723136</v>
+        <v>138.9625394173734</v>
       </c>
       <c r="N33">
-        <v>-0.96</v>
+        <v>2.12</v>
       </c>
       <c r="O33">
-        <v>-0.58</v>
+        <v>1.95</v>
       </c>
       <c r="P33">
-        <v>-0.66</v>
+        <v>0.88</v>
       </c>
       <c r="Q33">
-        <v>-0.72</v>
+        <v>0.25</v>
       </c>
       <c r="R33">
-        <v>-27576000</v>
+        <v>174500000</v>
       </c>
       <c r="S33">
-        <v>-31460000</v>
+        <v>154800000</v>
       </c>
       <c r="T33">
-        <v>-34626000</v>
+        <v>73300000</v>
       </c>
       <c r="U33">
-        <v>-99195000</v>
+        <v>24800000</v>
       </c>
       <c r="V33" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
         <v>54</v>
       </c>
-      <c r="B34" t="s">
-        <v>117</v>
-      </c>
-      <c r="C34" t="s">
-        <v>128</v>
-      </c>
       <c r="D34" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="E34">
-        <v>23.44000053405762</v>
+        <v>13.89000034332275</v>
       </c>
       <c r="F34">
-        <v>2336916.666666667</v>
+        <v>1247623.1</v>
       </c>
       <c r="G34">
-        <v>20.80739997863769</v>
+        <v>10.21729988098144</v>
       </c>
       <c r="H34">
-        <v>17.09813332239787</v>
+        <v>10.11725797017415</v>
       </c>
       <c r="I34">
-        <v>16.73040001392365</v>
+        <v>10.04098649501801</v>
       </c>
       <c r="J34">
-        <v>15.90505000591278</v>
+        <v>9.983236494064331</v>
       </c>
       <c r="K34">
-        <v>12.61999988555908</v>
+        <v>8.989999771118164</v>
       </c>
       <c r="L34">
-        <v>24.46999931335449</v>
+        <v>13.89000034332275</v>
       </c>
       <c r="M34">
-        <v>150.6272401455155</v>
+        <v>138.2820215626973</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>0.090181</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>1944526</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>366476</v>
       </c>
       <c r="T34">
-        <v>-8500000</v>
+        <v>900174</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>-1652348</v>
       </c>
       <c r="V34" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -3498,67 +3402,67 @@
         <v>55</v>
       </c>
       <c r="B35" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C35" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D35" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="E35">
-        <v>49.84999847412109</v>
+        <v>372.75</v>
       </c>
       <c r="F35">
-        <v>329790</v>
+        <v>284896.6666666667</v>
       </c>
       <c r="G35">
-        <v>42.8303997039795</v>
+        <v>317.9118011474609</v>
       </c>
       <c r="H35">
-        <v>34.84246660868327</v>
+        <v>277.2842008463542</v>
       </c>
       <c r="I35">
-        <v>33.37989994049072</v>
+        <v>270.0473502349853</v>
       </c>
       <c r="J35">
-        <v>30.83634998321533</v>
+        <v>258.8177003479004</v>
       </c>
       <c r="K35">
-        <v>7.400000095367432</v>
+        <v>4.775613307952881</v>
       </c>
       <c r="L35">
-        <v>49.84999847412109</v>
+        <v>374.9800109863281</v>
       </c>
       <c r="M35">
-        <v>149.8612624272533</v>
+        <v>137.7453677797959</v>
       </c>
       <c r="N35">
-        <v>-0.38</v>
+        <v>3.99</v>
       </c>
       <c r="O35">
-        <v>-0.41</v>
+        <v>2.65</v>
       </c>
       <c r="P35">
-        <v>-0.49</v>
+        <v>2.75</v>
       </c>
       <c r="Q35">
-        <v>-0.44</v>
+        <v>6.1</v>
       </c>
       <c r="R35">
-        <v>-73020000</v>
+        <v>141900000</v>
       </c>
       <c r="S35">
-        <v>-26123000</v>
+        <v>94400000</v>
       </c>
       <c r="T35">
-        <v>-25192000</v>
+        <v>98000000</v>
       </c>
       <c r="U35">
-        <v>-81854000</v>
+        <v>217200000</v>
       </c>
       <c r="V35" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3566,67 +3470,67 @@
         <v>56</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C36" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D36" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="E36">
-        <v>47</v>
+        <v>32.45000076293945</v>
       </c>
       <c r="F36">
-        <v>2990553.333333333</v>
+        <v>661651.8333333334</v>
       </c>
       <c r="G36">
-        <v>40.88279998779297</v>
+        <v>31.78019989013672</v>
       </c>
       <c r="H36">
-        <v>34.01770001729329</v>
+        <v>26.36056660970052</v>
       </c>
       <c r="I36">
-        <v>33.99429996490478</v>
+        <v>24.41387496948242</v>
       </c>
       <c r="J36">
-        <v>31.40409996032715</v>
+        <v>23.05657493591309</v>
       </c>
       <c r="K36">
-        <v>13.1899995803833</v>
+        <v>0.1500000059604645</v>
       </c>
       <c r="L36">
-        <v>47</v>
+        <v>38.15000152587891</v>
       </c>
       <c r="M36">
-        <v>149.75595124966</v>
+        <v>137.3209029552308</v>
       </c>
       <c r="N36">
-        <v>-0.58</v>
+        <v>0.13</v>
       </c>
       <c r="O36">
-        <v>-0.55</v>
+        <v>0.01</v>
       </c>
       <c r="P36">
-        <v>-0.51</v>
+        <v>-0.02</v>
       </c>
       <c r="Q36">
-        <v>-0.54</v>
+        <v>-0.36</v>
       </c>
       <c r="R36">
-        <v>-76858000</v>
+        <v>7905000</v>
       </c>
       <c r="S36">
-        <v>-23224000</v>
+        <v>668000</v>
       </c>
       <c r="T36">
-        <v>-25646000</v>
+        <v>-934000</v>
       </c>
       <c r="U36">
-        <v>-83887000</v>
+        <v>-21005000</v>
       </c>
       <c r="V36" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -3634,67 +3538,67 @@
         <v>57</v>
       </c>
       <c r="B37" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C37" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="D37" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="E37">
-        <v>14.65999984741211</v>
+        <v>13.44999980926514</v>
       </c>
       <c r="F37">
-        <v>343066.6666666667</v>
+        <v>8962973.333333334</v>
       </c>
       <c r="G37">
-        <v>12.41979999542236</v>
+        <v>11.38319995880127</v>
       </c>
       <c r="H37">
-        <v>10.87140001296997</v>
+        <v>9.921999991734822</v>
       </c>
       <c r="I37">
-        <v>10.19300000429153</v>
+        <v>9.689950006008148</v>
       </c>
       <c r="J37">
-        <v>9.75465000152588</v>
+        <v>9.350900013446807</v>
       </c>
       <c r="K37">
-        <v>2.79044508934021</v>
+        <v>0.3049550950527191</v>
       </c>
       <c r="L37">
-        <v>18.82888412475586</v>
+        <v>13.86999988555908</v>
       </c>
       <c r="M37">
-        <v>149.3396503066246</v>
+        <v>136.8856279875857</v>
       </c>
       <c r="N37">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="O37">
-        <v>1.21</v>
+        <v>0.3</v>
       </c>
       <c r="P37">
-        <v>0.15</v>
+        <v>2.87</v>
       </c>
       <c r="Q37">
-        <v>0.23</v>
+        <v>0.55</v>
       </c>
       <c r="R37">
-        <v>21856000</v>
+        <v>152000000</v>
       </c>
       <c r="S37">
-        <v>3117000</v>
+        <v>172000000</v>
       </c>
       <c r="T37">
-        <v>4733000</v>
+        <v>2006000000</v>
       </c>
       <c r="U37">
-        <v>32187000</v>
+        <v>413000000</v>
       </c>
       <c r="V37" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -3702,67 +3606,67 @@
         <v>58</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="C38" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="D38" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="E38">
-        <v>29.23999977111816</v>
+        <v>74.30500030517578</v>
       </c>
       <c r="F38">
-        <v>1173076.666666667</v>
+        <v>612486.0333333333</v>
       </c>
       <c r="G38">
-        <v>26.03839992523193</v>
+        <v>70.26869987487792</v>
       </c>
       <c r="H38">
-        <v>21.80983328501383</v>
+        <v>59.29403322855632</v>
       </c>
       <c r="I38">
-        <v>20.2836749792099</v>
+        <v>57.00207492828369</v>
       </c>
       <c r="J38">
-        <v>19.11597499847412</v>
+        <v>53.70964992523194</v>
       </c>
       <c r="K38">
-        <v>6.309999942779541</v>
+        <v>23.54999923706055</v>
       </c>
       <c r="L38">
-        <v>37.61000061035156</v>
+        <v>76.5</v>
       </c>
       <c r="M38">
-        <v>148.9346750832101</v>
+        <v>136.7515713199409</v>
       </c>
       <c r="N38">
-        <v>-0.35</v>
+        <v>-1.24</v>
       </c>
       <c r="O38">
-        <v>-0.32</v>
+        <v>-0.68</v>
       </c>
       <c r="P38">
-        <v>-0.21</v>
+        <v>-1.24</v>
       </c>
       <c r="Q38">
-        <v>-0.21</v>
+        <v>-0.68</v>
       </c>
       <c r="R38">
-        <v>-37149000</v>
+        <v>-193228000</v>
       </c>
       <c r="S38">
-        <v>-24642000</v>
+        <v>-112101000</v>
       </c>
       <c r="T38">
-        <v>-24855000</v>
+        <v>-193228000</v>
       </c>
       <c r="U38">
-        <v>-100322000</v>
+        <v>-112101000</v>
       </c>
       <c r="V38" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -3770,67 +3674,67 @@
         <v>59</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="C39" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="D39" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="E39">
-        <v>26.10000038146973</v>
+        <v>117.870002746582</v>
       </c>
       <c r="F39">
-        <v>841553.3333333334</v>
+        <v>451402.2333333333</v>
       </c>
       <c r="G39">
-        <v>23.80580005645752</v>
+        <v>96.53739990234375</v>
       </c>
       <c r="H39">
-        <v>20.11440005620321</v>
+        <v>91.81693318684896</v>
       </c>
       <c r="I39">
-        <v>18.36485003471374</v>
+        <v>88.27379997253418</v>
       </c>
       <c r="J39">
-        <v>16.79595004081726</v>
+        <v>84.97219993591308</v>
       </c>
       <c r="K39">
-        <v>1.899999976158142</v>
+        <v>3.099249601364136</v>
       </c>
       <c r="L39">
-        <v>27.38999938964844</v>
+        <v>121.8199996948242</v>
       </c>
       <c r="M39">
-        <v>148.1029962769371</v>
+        <v>136.6228468789908</v>
       </c>
       <c r="N39">
-        <v>0.75</v>
+        <v>3.5</v>
       </c>
       <c r="O39">
-        <v>0.762</v>
+        <v>1.48</v>
       </c>
       <c r="P39">
-        <v>1.315</v>
+        <v>2.84</v>
       </c>
       <c r="Q39">
-        <v>0.519</v>
+        <v>1.64</v>
       </c>
       <c r="R39">
-        <v>269535000</v>
+        <v>88842000</v>
       </c>
       <c r="S39">
-        <v>128734000</v>
+        <v>37337000</v>
       </c>
       <c r="T39">
-        <v>52181000</v>
+        <v>71283000</v>
       </c>
       <c r="U39">
-        <v>382735000</v>
+        <v>40443000</v>
       </c>
       <c r="V39" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -3838,67 +3742,67 @@
         <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C40" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D40" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="E40">
-        <v>155.1900024414062</v>
+        <v>24.6299991607666</v>
       </c>
       <c r="F40">
-        <v>529663.3333333334</v>
+        <v>816992.1</v>
       </c>
       <c r="G40">
-        <v>149.5631994628906</v>
+        <v>24.09440002441406</v>
       </c>
       <c r="H40">
-        <v>124.2378331502279</v>
+        <v>20.30826672236125</v>
       </c>
       <c r="I40">
-        <v>112.2017247009277</v>
+        <v>18.57120003223419</v>
       </c>
       <c r="J40">
-        <v>107.1025748062134</v>
+        <v>17.0039000415802</v>
       </c>
       <c r="K40">
-        <v>63</v>
+        <v>1.899999976158142</v>
       </c>
       <c r="L40">
-        <v>202.6900024414062</v>
+        <v>27.38999938964844</v>
       </c>
       <c r="M40">
-        <v>145.8814235137661</v>
+        <v>136.434090002839</v>
       </c>
       <c r="N40">
-        <v>-0.38</v>
+        <v>0.75</v>
       </c>
       <c r="O40">
-        <v>-0.46</v>
+        <v>0.762</v>
       </c>
       <c r="P40">
-        <v>-0.35</v>
+        <v>1.315</v>
       </c>
       <c r="Q40">
-        <v>-0.06</v>
+        <v>0.519</v>
       </c>
       <c r="R40">
-        <v>-18445000</v>
+        <v>76661000</v>
       </c>
       <c r="S40">
-        <v>-13930000</v>
+        <v>75504000</v>
       </c>
       <c r="T40">
-        <v>-2582000</v>
+        <v>128734000</v>
       </c>
       <c r="U40">
-        <v>-59574000</v>
+        <v>52181000</v>
       </c>
       <c r="V40" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -3906,67 +3810,67 @@
         <v>61</v>
       </c>
       <c r="B41" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C41" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D41" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="E41">
-        <v>42.09999847412109</v>
+        <v>114.3399963378906</v>
       </c>
       <c r="F41">
-        <v>1330196.666666667</v>
+        <v>568353.7666666667</v>
       </c>
       <c r="G41">
-        <v>37.33999973297119</v>
+        <v>99.53900009155274</v>
       </c>
       <c r="H41">
-        <v>30.39579992930095</v>
+        <v>89.64213353474935</v>
       </c>
       <c r="I41">
-        <v>29.37819993972778</v>
+        <v>87.67495002746583</v>
       </c>
       <c r="J41">
-        <v>28.1043999671936</v>
+        <v>83.97660015106202</v>
       </c>
       <c r="K41">
-        <v>18.28000068664551</v>
+        <v>0.3318000435829163</v>
       </c>
       <c r="L41">
-        <v>47.06000137329102</v>
+        <v>149.9608459472656</v>
       </c>
       <c r="M41">
-        <v>145.8019098650194</v>
+        <v>135.6252202007354</v>
       </c>
       <c r="N41">
-        <v>0.07000000000000001</v>
+        <v>5.15</v>
       </c>
       <c r="O41">
-        <v>0.06</v>
+        <v>2.53</v>
       </c>
       <c r="P41">
-        <v>0.06</v>
+        <v>0.5</v>
       </c>
       <c r="Q41">
-        <v>0.07000000000000001</v>
+        <v>2.24</v>
       </c>
       <c r="R41">
-        <v>53508000</v>
+        <v>280943000</v>
       </c>
       <c r="S41">
-        <v>18068000</v>
+        <v>136185000</v>
       </c>
       <c r="T41">
-        <v>12175000</v>
+        <v>27080000</v>
       </c>
       <c r="U41">
-        <v>43268000</v>
+        <v>120719000</v>
       </c>
       <c r="V41" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -3974,67 +3878,67 @@
         <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C42" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D42" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="E42">
-        <v>31.22999954223633</v>
+        <v>32.70999908447266</v>
       </c>
       <c r="F42">
-        <v>313073.3333333333</v>
+        <v>1320385.033333333</v>
       </c>
       <c r="G42">
-        <v>30.44779998779297</v>
+        <v>30.6104997253418</v>
       </c>
       <c r="H42">
-        <v>25.44939994812012</v>
+        <v>26.78123326619466</v>
       </c>
       <c r="I42">
-        <v>23.16209997653961</v>
+        <v>24.3245249414444</v>
       </c>
       <c r="J42">
-        <v>21.71155000209808</v>
+        <v>22.6387999868393</v>
       </c>
       <c r="K42">
-        <v>14.10000038146973</v>
+        <v>4.052896976470947</v>
       </c>
       <c r="L42">
-        <v>33.61000061035156</v>
+        <v>33.56000137329102</v>
       </c>
       <c r="M42">
-        <v>145.5658292896496</v>
+        <v>135.4950686890014</v>
       </c>
       <c r="N42">
-        <v>0.14</v>
+        <v>-0.23</v>
       </c>
       <c r="O42">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="P42">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="Q42">
-        <v>0.13</v>
+        <v>0.46</v>
       </c>
       <c r="R42">
-        <v>142849000</v>
+        <v>-16058000</v>
       </c>
       <c r="S42">
-        <v>28265000</v>
+        <v>26801000</v>
       </c>
       <c r="T42">
-        <v>34300000</v>
+        <v>29397000</v>
       </c>
       <c r="U42">
-        <v>143391000</v>
+        <v>54753000</v>
       </c>
       <c r="V42" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -4042,67 +3946,67 @@
         <v>63</v>
       </c>
       <c r="B43" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C43" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D43" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="E43">
-        <v>546.1699829101562</v>
+        <v>54.36000061035156</v>
       </c>
       <c r="F43">
-        <v>3574453.333333333</v>
+        <v>2010083.333333333</v>
       </c>
       <c r="G43">
-        <v>470.8721978759766</v>
+        <v>50.26000007629395</v>
       </c>
       <c r="H43">
-        <v>395.1677990722656</v>
+        <v>42.32339993794759</v>
       </c>
       <c r="I43">
-        <v>376.8823989868164</v>
+        <v>39.23189993858337</v>
       </c>
       <c r="J43">
-        <v>354.8775491333008</v>
+        <v>36.68854996681213</v>
       </c>
       <c r="K43">
-        <v>0.1503329128026962</v>
+        <v>1.498309969902039</v>
       </c>
       <c r="L43">
-        <v>688.3699951171875</v>
+        <v>66.26741027832031</v>
       </c>
       <c r="M43">
-        <v>144.8630208083272</v>
+        <v>134.7699533557918</v>
       </c>
       <c r="N43">
-        <v>2.42</v>
+        <v>2.86</v>
       </c>
       <c r="O43">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="P43">
-        <v>2.71</v>
+        <v>1.45</v>
       </c>
       <c r="Q43">
-        <v>2.82</v>
+        <v>1.94</v>
       </c>
       <c r="R43">
-        <v>4756000000</v>
+        <v>255329000</v>
       </c>
       <c r="S43">
-        <v>1247000000</v>
+        <v>216410000</v>
       </c>
       <c r="T43">
-        <v>1295000000</v>
+        <v>125500000</v>
       </c>
       <c r="U43">
-        <v>4737000000</v>
+        <v>164442000</v>
       </c>
       <c r="V43" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -4110,67 +4014,67 @@
         <v>64</v>
       </c>
       <c r="B44" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="C44" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="D44" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="E44">
-        <v>103.4899978637695</v>
+        <v>886.1099853515625</v>
       </c>
       <c r="F44">
-        <v>376260</v>
+        <v>2398529.166666667</v>
       </c>
       <c r="G44">
-        <v>85.92039993286133</v>
+        <v>851.0402014160156</v>
       </c>
       <c r="H44">
-        <v>74.55886695861817</v>
+        <v>690.9594673665365</v>
       </c>
       <c r="I44">
-        <v>73.10430025100707</v>
+        <v>645.2251498413086</v>
       </c>
       <c r="J44">
-        <v>69.43105028152466</v>
+        <v>602.0113998413086</v>
       </c>
       <c r="K44">
-        <v>11.37919998168945</v>
+        <v>11.17089080810547</v>
       </c>
       <c r="L44">
-        <v>103.4899978637695</v>
+        <v>920</v>
       </c>
       <c r="M44">
-        <v>144.2791675123891</v>
+        <v>134.6926311357979</v>
       </c>
       <c r="N44">
-        <v>5.49</v>
+        <v>7.132125</v>
       </c>
       <c r="O44">
-        <v>5.52</v>
+        <v>7.810425</v>
       </c>
       <c r="P44">
-        <v>2.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q44">
-        <v>2.43</v>
+        <v>8.15</v>
       </c>
       <c r="R44">
-        <v>219587000</v>
+        <v>3074000000</v>
       </c>
       <c r="S44">
-        <v>117360000</v>
+        <v>3359000000</v>
       </c>
       <c r="T44">
-        <v>96733000</v>
+        <v>3774000000</v>
       </c>
       <c r="U44">
-        <v>857658000</v>
+        <v>3481000000</v>
       </c>
       <c r="V44" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -4178,67 +4082,67 @@
         <v>65</v>
       </c>
       <c r="B45" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C45" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="D45" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="E45">
-        <v>33.08000183105469</v>
+        <v>32.08000183105469</v>
       </c>
       <c r="F45">
-        <v>755920</v>
+        <v>916923.3</v>
       </c>
       <c r="G45">
-        <v>31.49399982452393</v>
+        <v>29.73980007171631</v>
       </c>
       <c r="H45">
-        <v>26.081233253479</v>
+        <v>25.36000003814697</v>
       </c>
       <c r="I45">
-        <v>24.19652495384216</v>
+        <v>24.28695004463196</v>
       </c>
       <c r="J45">
-        <v>22.89752494812012</v>
+        <v>23.43525002479553</v>
       </c>
       <c r="K45">
-        <v>0.1500000059604645</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="L45">
-        <v>38.15000152587891</v>
+        <v>32.33000183105469</v>
       </c>
       <c r="M45">
-        <v>144.1963885214341</v>
+        <v>134.6781611475295</v>
       </c>
       <c r="N45">
-        <v>0.13</v>
+        <v>0.67</v>
       </c>
       <c r="O45">
-        <v>0.01</v>
+        <v>0.65</v>
       </c>
       <c r="P45">
-        <v>-0.02</v>
+        <v>0.31</v>
       </c>
       <c r="Q45">
-        <v>-0.36</v>
+        <v>0.5</v>
       </c>
       <c r="R45">
-        <v>668000</v>
+        <v>115000000</v>
       </c>
       <c r="S45">
-        <v>-934000</v>
+        <v>111000000</v>
       </c>
       <c r="T45">
-        <v>-21005000</v>
+        <v>54000000</v>
       </c>
       <c r="U45">
-        <v>10650000</v>
+        <v>86000000</v>
       </c>
       <c r="V45" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="46" spans="1:22">
@@ -4246,67 +4150,67 @@
         <v>66</v>
       </c>
       <c r="B46" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C46" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D46" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="E46">
-        <v>139.9900054931641</v>
+        <v>530.2999877929688</v>
       </c>
       <c r="F46">
-        <v>923976.6666666666</v>
+        <v>3127053.333333333</v>
       </c>
       <c r="G46">
-        <v>123.9638008117676</v>
+        <v>477.826597290039</v>
       </c>
       <c r="H46">
-        <v>105.6282670593262</v>
+        <v>397.863998819987</v>
       </c>
       <c r="I46">
-        <v>101.2659502410889</v>
+        <v>379.3749488830566</v>
       </c>
       <c r="J46">
-        <v>96.09600006103516</v>
+        <v>356.3366491699219</v>
       </c>
       <c r="K46">
-        <v>4.719488620758057</v>
+        <v>0.1503329128026962</v>
       </c>
       <c r="L46">
-        <v>140.0700073242188</v>
+        <v>688.3699951171875</v>
       </c>
       <c r="M46">
-        <v>143.5475586451923</v>
+        <v>134.5504957247051</v>
       </c>
       <c r="N46">
-        <v>4.84</v>
+        <v>2.42</v>
       </c>
       <c r="O46">
-        <v>1.32</v>
+        <v>2.53</v>
       </c>
       <c r="P46">
-        <v>4.17</v>
+        <v>2.71</v>
       </c>
       <c r="Q46">
-        <v>3.78</v>
+        <v>2.82</v>
       </c>
       <c r="R46">
-        <v>1241000000</v>
+        <v>1136000000</v>
       </c>
       <c r="S46">
-        <v>383000000</v>
+        <v>1176000000</v>
       </c>
       <c r="T46">
-        <v>345000000</v>
+        <v>1247000000</v>
       </c>
       <c r="U46">
-        <v>1320000000</v>
+        <v>1295000000</v>
       </c>
       <c r="V46" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -4314,31 +4218,31 @@
         <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="D47" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="E47">
-        <v>29.73999977111816</v>
+        <v>28.15999984741211</v>
       </c>
       <c r="F47">
-        <v>545486.6666666666</v>
+        <v>586794.9333333333</v>
       </c>
       <c r="G47">
-        <v>24.98899993896485</v>
+        <v>25.29979991912842</v>
       </c>
       <c r="H47">
-        <v>22.08066665013631</v>
+        <v>22.26499998092651</v>
       </c>
       <c r="I47">
-        <v>21.12449999809265</v>
+        <v>21.33194999694824</v>
       </c>
       <c r="J47">
-        <v>19.89394999027252</v>
+        <v>20.06444998264313</v>
       </c>
       <c r="K47">
         <v>4.372677803039551</v>
@@ -4347,7 +4251,7 @@
         <v>29.73999977111816</v>
       </c>
       <c r="M47">
-        <v>143.438543036451</v>
+        <v>134.2322376025219</v>
       </c>
       <c r="N47">
         <v>0.62</v>
@@ -4362,19 +4266,19 @@
         <v>1.89</v>
       </c>
       <c r="R47">
+        <v>24847720</v>
+      </c>
+      <c r="S47">
         <v>20311465</v>
       </c>
-      <c r="S47">
+      <c r="T47">
         <v>51263710</v>
       </c>
-      <c r="T47">
+      <c r="U47">
         <v>76021035</v>
       </c>
-      <c r="U47">
-        <v>131806125</v>
-      </c>
       <c r="V47" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="48" spans="1:22">
@@ -4382,67 +4286,67 @@
         <v>68</v>
       </c>
       <c r="B48" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C48" t="s">
         <v>128</v>
       </c>
       <c r="D48" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="E48">
-        <v>129.1000061035156</v>
+        <v>215.2400054931641</v>
       </c>
       <c r="F48">
-        <v>258240</v>
+        <v>561638.4</v>
       </c>
       <c r="G48">
-        <v>120.8787998962402</v>
+        <v>183.3179998779297</v>
       </c>
       <c r="H48">
-        <v>94.18380020141602</v>
+        <v>165.4255333455404</v>
       </c>
       <c r="I48">
-        <v>89.31995018005371</v>
+        <v>160.4737496948242</v>
       </c>
       <c r="J48">
-        <v>83.91300016403198</v>
+        <v>152.8209998321533</v>
       </c>
       <c r="K48">
-        <v>8.189999580383301</v>
+        <v>0.9346818327903748</v>
       </c>
       <c r="L48">
-        <v>130.3200073242188</v>
+        <v>216.1799926757812</v>
       </c>
       <c r="M48">
-        <v>141.8728480770349</v>
+        <v>133.1615765956707</v>
       </c>
       <c r="N48">
-        <v>-1.76</v>
+        <v>2.16</v>
       </c>
       <c r="O48">
-        <v>-1.1</v>
+        <v>2.63</v>
       </c>
       <c r="P48">
-        <v>-1.17</v>
+        <v>2.32</v>
       </c>
       <c r="Q48">
-        <v>-1.76</v>
+        <v>2.95</v>
       </c>
       <c r="R48">
-        <v>-129729000</v>
+        <v>105772000</v>
       </c>
       <c r="S48">
-        <v>-32052000</v>
+        <v>126300000</v>
       </c>
       <c r="T48">
-        <v>-45297000</v>
+        <v>111473000</v>
       </c>
       <c r="U48">
-        <v>-139975000</v>
+        <v>140595000</v>
       </c>
       <c r="V48" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="49" spans="1:22">
@@ -4450,67 +4354,67 @@
         <v>69</v>
       </c>
       <c r="B49" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C49" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="D49" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="E49">
-        <v>13.86999988555908</v>
+        <v>52.38999938964844</v>
       </c>
       <c r="F49">
-        <v>9684486.666666666</v>
+        <v>1734528.166666667</v>
       </c>
       <c r="G49">
-        <v>11.2803999710083</v>
+        <v>43.86760002136231</v>
       </c>
       <c r="H49">
-        <v>9.856399997075398</v>
+        <v>40.78753339131674</v>
       </c>
       <c r="I49">
-        <v>9.639600007534026</v>
+        <v>39.71880006790161</v>
       </c>
       <c r="J49">
-        <v>9.333800013065337</v>
+        <v>37.65400006294251</v>
       </c>
       <c r="K49">
-        <v>0.3049550950527191</v>
+        <v>20.39999961853027</v>
       </c>
       <c r="L49">
-        <v>13.86999988555908</v>
+        <v>52.38999938964844</v>
       </c>
       <c r="M49">
-        <v>141.4043040609131</v>
+        <v>132.4579367657776</v>
       </c>
       <c r="N49">
-        <v>0.3</v>
+        <v>0.74</v>
       </c>
       <c r="O49">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
       <c r="P49">
-        <v>2.87</v>
+        <v>0.92</v>
       </c>
       <c r="Q49">
-        <v>0.55</v>
+        <v>0.74</v>
       </c>
       <c r="R49">
-        <v>650000000</v>
+        <v>108063000</v>
       </c>
       <c r="S49">
-        <v>2006000000</v>
+        <v>33585000</v>
       </c>
       <c r="T49">
-        <v>413000000</v>
+        <v>134962000</v>
       </c>
       <c r="U49">
-        <v>2501000000</v>
+        <v>108063000</v>
       </c>
       <c r="V49" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="50" spans="1:22">
@@ -4518,67 +4422,67 @@
         <v>70</v>
       </c>
       <c r="B50" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C50" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="D50" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="E50">
-        <v>85.66999816894531</v>
+        <v>45.57500076293945</v>
       </c>
       <c r="F50">
-        <v>479136.6666666667</v>
+        <v>325471.4333333333</v>
       </c>
       <c r="G50">
-        <v>77.42539985656738</v>
+        <v>43.28029983520508</v>
       </c>
       <c r="H50">
-        <v>64.79126653035482</v>
+        <v>35.21656661987305</v>
       </c>
       <c r="I50">
-        <v>62.75734991073608</v>
+        <v>33.7736749458313</v>
       </c>
       <c r="J50">
-        <v>59.90284996032715</v>
+        <v>31.17694996833801</v>
       </c>
       <c r="K50">
-        <v>7.03000020980835</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="L50">
-        <v>85.66999816894531</v>
+        <v>49.84999847412109</v>
       </c>
       <c r="M50">
-        <v>141.3977580125558</v>
+        <v>132.2661442102612</v>
       </c>
       <c r="N50">
-        <v>2.12</v>
+        <v>-0.38</v>
       </c>
       <c r="O50">
-        <v>1.95</v>
+        <v>-0.41</v>
       </c>
       <c r="P50">
-        <v>0.88</v>
+        <v>-0.49</v>
       </c>
       <c r="Q50">
-        <v>0.25</v>
+        <v>-0.44</v>
       </c>
       <c r="R50">
-        <v>154800000</v>
+        <v>-18466000</v>
       </c>
       <c r="S50">
-        <v>73300000</v>
+        <v>-19716000</v>
       </c>
       <c r="T50">
-        <v>24800000</v>
+        <v>-26123000</v>
       </c>
       <c r="U50">
-        <v>458400000</v>
+        <v>-25192000</v>
       </c>
       <c r="V50" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -4586,67 +4490,67 @@
         <v>71</v>
       </c>
       <c r="B51" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="C51" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="D51" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="E51">
-        <v>93.45999908447266</v>
+        <v>53.52000045776367</v>
       </c>
       <c r="F51">
-        <v>282540</v>
+        <v>1075266.666666667</v>
       </c>
       <c r="G51">
-        <v>77.34000015258789</v>
+        <v>47.48739974975586</v>
       </c>
       <c r="H51">
-        <v>68.58740018208822</v>
+        <v>43.2299333190918</v>
       </c>
       <c r="I51">
-        <v>68.05275018692016</v>
+        <v>42.42324996948242</v>
       </c>
       <c r="J51">
-        <v>66.30505018234253</v>
+        <v>40.89590003967285</v>
       </c>
       <c r="K51">
-        <v>0.2077736556529999</v>
+        <v>2.721946477890015</v>
       </c>
       <c r="L51">
-        <v>124.5500030517578</v>
+        <v>53.91999816894531</v>
       </c>
       <c r="M51">
-        <v>141.3126199421443</v>
+        <v>132.1821638423702</v>
       </c>
       <c r="N51">
-        <v>9.49</v>
+        <v>3.74</v>
       </c>
       <c r="O51">
-        <v>6.89</v>
+        <v>3.41</v>
       </c>
       <c r="P51">
-        <v>2.1</v>
+        <v>0.25</v>
       </c>
       <c r="Q51">
-        <v>0.9399999999999999</v>
+        <v>-2</v>
       </c>
       <c r="R51">
-        <v>266000000</v>
+        <v>360580000</v>
       </c>
       <c r="S51">
-        <v>78000000</v>
+        <v>312600000</v>
       </c>
       <c r="T51">
-        <v>34000000</v>
+        <v>32572000</v>
       </c>
       <c r="U51">
-        <v>1063900000</v>
+        <v>-155994000</v>
       </c>
       <c r="V51" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="52" spans="1:22">
@@ -4654,67 +4558,67 @@
         <v>72</v>
       </c>
       <c r="B52" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="C52" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D52" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="E52">
-        <v>148.9499969482422</v>
+        <v>58.97999954223633</v>
       </c>
       <c r="F52">
-        <v>393160</v>
+        <v>5388316.666666667</v>
       </c>
       <c r="G52">
-        <v>133.3744003295898</v>
+        <v>49.214400100708</v>
       </c>
       <c r="H52">
-        <v>118.8800667317708</v>
+        <v>45.73826670328776</v>
       </c>
       <c r="I52">
-        <v>109.2658002090454</v>
+        <v>44.62294998168945</v>
       </c>
       <c r="J52">
-        <v>102.4714002227783</v>
+        <v>42.81295000076294</v>
       </c>
       <c r="K52">
-        <v>0.577300488948822</v>
+        <v>11.31525421142578</v>
       </c>
       <c r="L52">
-        <v>150.4900054931641</v>
+        <v>59.79999923706055</v>
       </c>
       <c r="M52">
-        <v>140.8694707054412</v>
+        <v>132.0594763273835</v>
       </c>
       <c r="N52">
-        <v>7.1</v>
+        <v>1.53</v>
       </c>
       <c r="O52">
-        <v>7.09</v>
+        <v>0.32</v>
       </c>
       <c r="P52">
-        <v>3.54</v>
+        <v>0.44</v>
       </c>
       <c r="Q52">
-        <v>5.02</v>
+        <v>0.23</v>
       </c>
       <c r="R52">
-        <v>992192000</v>
+        <v>1312000000</v>
       </c>
       <c r="S52">
-        <v>131301000</v>
+        <v>270000000</v>
       </c>
       <c r="T52">
-        <v>186836000</v>
+        <v>373000000</v>
       </c>
       <c r="U52">
-        <v>906239000</v>
+        <v>199000000</v>
       </c>
       <c r="V52" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -4722,67 +4626,67 @@
         <v>73</v>
       </c>
       <c r="B53" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C53" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="D53" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="E53">
-        <v>115.4899978637695</v>
+        <v>109.0599975585938</v>
       </c>
       <c r="F53">
-        <v>587270</v>
+        <v>1064856.8</v>
       </c>
       <c r="G53">
-        <v>97.49600006103516</v>
+        <v>97.34639968872071</v>
       </c>
       <c r="H53">
-        <v>88.86606689453124</v>
+        <v>90.31639968872071</v>
       </c>
       <c r="I53">
-        <v>87.12745002746583</v>
+        <v>84.31564975738526</v>
       </c>
       <c r="J53">
-        <v>83.57795017242432</v>
+        <v>81.55844982147217</v>
       </c>
       <c r="K53">
-        <v>0.3318000435829163</v>
+        <v>0.02227001264691353</v>
       </c>
       <c r="L53">
-        <v>149.9608459472656</v>
+        <v>132.0598602294922</v>
       </c>
       <c r="M53">
-        <v>140.4870794589808</v>
+        <v>132.0532977514115</v>
       </c>
       <c r="N53">
-        <v>5.15</v>
+        <v>8</v>
       </c>
       <c r="O53">
-        <v>2.53</v>
+        <v>10.15</v>
       </c>
       <c r="P53">
-        <v>0.5</v>
+        <v>6.05</v>
       </c>
       <c r="Q53">
-        <v>2.24</v>
+        <v>10.35</v>
       </c>
       <c r="R53">
-        <v>136185000</v>
+        <v>5291476000</v>
       </c>
       <c r="S53">
-        <v>27080000</v>
+        <v>6699364000</v>
       </c>
       <c r="T53">
-        <v>120719000</v>
+        <v>3952737000</v>
       </c>
       <c r="U53">
-        <v>792259000</v>
+        <v>6754634000</v>
       </c>
       <c r="V53" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -4790,67 +4694,67 @@
         <v>74</v>
       </c>
       <c r="B54" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C54" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D54" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="E54">
-        <v>53.97000122070312</v>
+        <v>143.8999938964844</v>
       </c>
       <c r="F54">
-        <v>2079556.666666667</v>
+        <v>366311.0666666667</v>
       </c>
       <c r="G54">
-        <v>49.89520004272461</v>
+        <v>134.8834001159668</v>
       </c>
       <c r="H54">
-        <v>42.02586659749349</v>
+        <v>119.9737999979655</v>
       </c>
       <c r="I54">
-        <v>38.96089994430542</v>
+        <v>110.4302001190186</v>
       </c>
       <c r="J54">
-        <v>36.45464996337891</v>
+        <v>103.4217502975464</v>
       </c>
       <c r="K54">
-        <v>1.498309969902039</v>
+        <v>0.577300488948822</v>
       </c>
       <c r="L54">
-        <v>66.26741027832031</v>
+        <v>150.4900054931641</v>
       </c>
       <c r="M54">
-        <v>140.2491428624017</v>
+        <v>131.755657470813</v>
       </c>
       <c r="N54">
-        <v>2.86</v>
+        <v>7.1</v>
       </c>
       <c r="O54">
-        <v>2.47</v>
+        <v>7.09</v>
       </c>
       <c r="P54">
-        <v>1.45</v>
+        <v>3.54</v>
       </c>
       <c r="Q54">
-        <v>1.94</v>
+        <v>5.02</v>
       </c>
       <c r="R54">
-        <v>216410000</v>
+        <v>262489000</v>
       </c>
       <c r="S54">
-        <v>125500000</v>
+        <v>262365000</v>
       </c>
       <c r="T54">
-        <v>164442000</v>
+        <v>131301000</v>
       </c>
       <c r="U54">
-        <v>807909000</v>
+        <v>186836000</v>
       </c>
       <c r="V54" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="55" spans="1:22">
@@ -4858,67 +4762,67 @@
         <v>75</v>
       </c>
       <c r="B55" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C55" t="s">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="D55" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="E55">
-        <v>32.20999908447266</v>
+        <v>118.9599990844727</v>
       </c>
       <c r="F55">
-        <v>1359243.333333333</v>
+        <v>320661.6333333334</v>
       </c>
       <c r="G55">
-        <v>30.41409976959228</v>
+        <v>110.3507995605469</v>
       </c>
       <c r="H55">
-        <v>26.47843327840169</v>
+        <v>91.61526657104493</v>
       </c>
       <c r="I55">
-        <v>24.06857495784759</v>
+        <v>87.02514989852905</v>
       </c>
       <c r="J55">
-        <v>22.43542500019073</v>
+        <v>82.33244993209838</v>
       </c>
       <c r="K55">
-        <v>4.052896976470947</v>
+        <v>20.81999969482422</v>
       </c>
       <c r="L55">
-        <v>33.56000137329102</v>
+        <v>124.3199996948242</v>
       </c>
       <c r="M55">
-        <v>139.9336183503602</v>
+        <v>131.5081729109738</v>
       </c>
       <c r="N55">
-        <v>-0.23</v>
+        <v>1.03</v>
       </c>
       <c r="O55">
-        <v>0.2</v>
+        <v>1.05</v>
       </c>
       <c r="P55">
-        <v>0.22</v>
+        <v>1.34</v>
       </c>
       <c r="Q55">
-        <v>0.46</v>
+        <v>0.59</v>
       </c>
       <c r="R55">
-        <v>-193210000</v>
+        <v>51575000</v>
       </c>
       <c r="S55">
-        <v>29397000</v>
+        <v>52215000</v>
       </c>
       <c r="T55">
-        <v>54753000</v>
+        <v>66214000</v>
       </c>
       <c r="U55">
-        <v>58380000</v>
+        <v>29068000</v>
       </c>
       <c r="V55" t="s">
-        <v>268</v>
+        <v>239</v>
       </c>
     </row>
     <row r="56" spans="1:22">
@@ -4926,67 +4830,67 @@
         <v>76</v>
       </c>
       <c r="B56" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C56" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="D56" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="E56">
-        <v>898.6500244140625</v>
+        <v>15.58500003814697</v>
       </c>
       <c r="F56">
-        <v>2604360</v>
+        <v>886388.9</v>
       </c>
       <c r="G56">
-        <v>837.84240234375</v>
+        <v>13.05909999847412</v>
       </c>
       <c r="H56">
-        <v>684.0304675292969</v>
+        <v>12.66563334147135</v>
       </c>
       <c r="I56">
-        <v>638.2113000488281</v>
+        <v>12.21347500324249</v>
       </c>
       <c r="J56">
-        <v>596.646849975586</v>
+        <v>11.80485000610352</v>
       </c>
       <c r="K56">
-        <v>11.17089080810547</v>
+        <v>9.039999961853027</v>
       </c>
       <c r="L56">
-        <v>917.989990234375</v>
+        <v>15.89999961853027</v>
       </c>
       <c r="M56">
-        <v>139.6360267235086</v>
+        <v>130.9738666142341</v>
       </c>
       <c r="N56">
-        <v>7.132125</v>
+        <v>0</v>
       </c>
       <c r="O56">
-        <v>7.810425</v>
+        <v>0</v>
       </c>
       <c r="P56">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q56">
-        <v>8.15</v>
+        <v>0</v>
       </c>
       <c r="R56">
-        <v>3359000000</v>
+        <v>0</v>
       </c>
       <c r="S56">
-        <v>3774000000</v>
+        <v>0</v>
       </c>
       <c r="T56">
-        <v>3481000000</v>
+        <v>0</v>
       </c>
       <c r="U56">
-        <v>12797000000</v>
+        <v>0</v>
       </c>
       <c r="V56" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -4994,67 +4898,67 @@
         <v>77</v>
       </c>
       <c r="B57" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C57" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="D57" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="E57">
-        <v>107.75</v>
+        <v>59.29000091552734</v>
       </c>
       <c r="F57">
-        <v>6746123.333333333</v>
+        <v>689176.7</v>
       </c>
       <c r="G57">
-        <v>92.58759994506836</v>
+        <v>50.93819984436035</v>
       </c>
       <c r="H57">
-        <v>81.31779980977376</v>
+        <v>46.17119997660319</v>
       </c>
       <c r="I57">
-        <v>77.84369983673096</v>
+        <v>45.18180002212524</v>
       </c>
       <c r="J57">
-        <v>74.49689985275269</v>
+        <v>43.92014999389649</v>
       </c>
       <c r="K57">
-        <v>0.9100000262260437</v>
+        <v>5.159999847412109</v>
       </c>
       <c r="L57">
-        <v>107.75</v>
+        <v>59.40999984741211</v>
       </c>
       <c r="M57">
-        <v>139.4616192467998</v>
+        <v>130.7909113705638</v>
       </c>
       <c r="N57">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="O57">
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="P57">
-        <v>1.35</v>
+        <v>0.52</v>
       </c>
       <c r="Q57">
-        <v>1.03</v>
+        <v>2.07</v>
       </c>
       <c r="R57">
-        <v>311900000</v>
+        <v>113000000</v>
       </c>
       <c r="S57">
-        <v>604300000</v>
+        <v>1000000</v>
       </c>
       <c r="T57">
-        <v>461700000</v>
+        <v>37000000</v>
       </c>
       <c r="U57">
-        <v>1902200000</v>
+        <v>142000000</v>
       </c>
       <c r="V57" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="58" spans="1:22">
@@ -5062,67 +4966,67 @@
         <v>78</v>
       </c>
       <c r="B58" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C58" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="D58" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="E58">
-        <v>367.4400024414062</v>
+        <v>108.1999969482422</v>
       </c>
       <c r="F58">
-        <v>283440</v>
+        <v>1063030</v>
       </c>
       <c r="G58">
-        <v>314.5678009033203</v>
+        <v>103.1107995605469</v>
       </c>
       <c r="H58">
-        <v>275.5302675374349</v>
+        <v>87.78066650390625</v>
       </c>
       <c r="I58">
-        <v>268.503800201416</v>
+        <v>82.60159980773926</v>
       </c>
       <c r="J58">
-        <v>258.0759503173828</v>
+        <v>77.37124988555908</v>
       </c>
       <c r="K58">
-        <v>4.775613307952881</v>
+        <v>0.3787146806716919</v>
       </c>
       <c r="L58">
-        <v>367.4400024414062</v>
+        <v>115.1399993896484</v>
       </c>
       <c r="M58">
-        <v>139.4311498054925</v>
+        <v>130.7831613826413</v>
       </c>
       <c r="N58">
-        <v>3.99</v>
+        <v>2.25</v>
       </c>
       <c r="O58">
-        <v>2.65</v>
+        <v>1.61</v>
       </c>
       <c r="P58">
-        <v>2.75</v>
+        <v>1.52</v>
       </c>
       <c r="Q58">
-        <v>6.1</v>
+        <v>1.72</v>
       </c>
       <c r="R58">
-        <v>497100000</v>
+        <v>315000000</v>
       </c>
       <c r="S58">
-        <v>98000000</v>
+        <v>223000000</v>
       </c>
       <c r="T58">
-        <v>217200000</v>
+        <v>207000000</v>
       </c>
       <c r="U58">
-        <v>511500000</v>
+        <v>233000000</v>
       </c>
       <c r="V58" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="59" spans="1:22">
@@ -5130,67 +5034,67 @@
         <v>79</v>
       </c>
       <c r="B59" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C59" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D59" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="E59">
-        <v>51.61000061035156</v>
+        <v>691.6300048828125</v>
       </c>
       <c r="F59">
-        <v>1566246.666666667</v>
+        <v>1293747.133333333</v>
       </c>
       <c r="G59">
-        <v>43.54999992370605</v>
+        <v>633.7390014648438</v>
       </c>
       <c r="H59">
-        <v>41.23020005544026</v>
+        <v>544.2846663411458</v>
       </c>
       <c r="I59">
-        <v>37.81840002059936</v>
+        <v>515.6605995178222</v>
       </c>
       <c r="J59">
-        <v>35.20355004310608</v>
+        <v>487.3533992004395</v>
       </c>
       <c r="K59">
-        <v>17.70000076293945</v>
+        <v>0.5958155393600464</v>
       </c>
       <c r="L59">
-        <v>52.72000122070312</v>
+        <v>729.8200073242188</v>
       </c>
       <c r="M59">
-        <v>139.1903097788406</v>
+        <v>130.2812167710583</v>
       </c>
       <c r="N59">
-        <v>0.05</v>
+        <v>10.39</v>
       </c>
       <c r="O59">
-        <v>0.26</v>
+        <v>10.77</v>
       </c>
       <c r="P59">
-        <v>0.33</v>
+        <v>6.01</v>
       </c>
       <c r="Q59">
-        <v>0.32</v>
+        <v>5.97</v>
       </c>
       <c r="R59">
-        <v>50614000</v>
+        <v>1425879000</v>
       </c>
       <c r="S59">
-        <v>64519000</v>
+        <v>1468507000</v>
       </c>
       <c r="T59">
-        <v>61977000</v>
+        <v>814008000</v>
       </c>
       <c r="U59">
-        <v>150996000</v>
+        <v>802537000</v>
       </c>
       <c r="V59" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -5198,67 +5102,67 @@
         <v>80</v>
       </c>
       <c r="B60" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="C60" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D60" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="E60">
-        <v>59.54999923706055</v>
+        <v>28.88999938964844</v>
       </c>
       <c r="F60">
-        <v>5628960</v>
+        <v>883493.3333333334</v>
       </c>
       <c r="G60">
-        <v>48.56000015258789</v>
+        <v>26.13320003509521</v>
       </c>
       <c r="H60">
-        <v>45.50286671956381</v>
+        <v>23.09926661173503</v>
       </c>
       <c r="I60">
-        <v>44.37769998550415</v>
+        <v>21.76979996204376</v>
       </c>
       <c r="J60">
-        <v>42.71944999694824</v>
+        <v>20.37919998168945</v>
       </c>
       <c r="K60">
-        <v>11.31525421142578</v>
+        <v>9.090000152587891</v>
       </c>
       <c r="L60">
-        <v>59.54999923706055</v>
+        <v>29.15999984741211</v>
       </c>
       <c r="M60">
-        <v>138.9872154111048</v>
+        <v>130.1711409472614</v>
       </c>
       <c r="N60">
-        <v>1.53</v>
+        <v>0.06</v>
       </c>
       <c r="O60">
-        <v>0.32</v>
+        <v>0.06</v>
       </c>
       <c r="P60">
-        <v>0.44</v>
+        <v>0.04</v>
       </c>
       <c r="Q60">
-        <v>0.23</v>
+        <v>0.05</v>
       </c>
       <c r="R60">
-        <v>3534000000</v>
+        <v>30000000</v>
       </c>
       <c r="S60">
-        <v>373000000</v>
+        <v>28000000</v>
       </c>
       <c r="T60">
-        <v>199000000</v>
+        <v>22000000</v>
       </c>
       <c r="U60">
-        <v>2528000000</v>
+        <v>26000000</v>
       </c>
       <c r="V60" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="61" spans="1:22">
@@ -5266,67 +5170,67 @@
         <v>81</v>
       </c>
       <c r="B61" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="C61" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="D61" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="E61">
-        <v>16.78000068664551</v>
+        <v>69.40000152587891</v>
       </c>
       <c r="F61">
-        <v>461046.6666666667</v>
+        <v>1387912.733333333</v>
       </c>
       <c r="G61">
-        <v>14.74340003967285</v>
+        <v>62.82020011901855</v>
       </c>
       <c r="H61">
-        <v>13.00906667709351</v>
+        <v>56.82666664123535</v>
       </c>
       <c r="I61">
-        <v>12.95140000343323</v>
+        <v>53.56769994735718</v>
       </c>
       <c r="J61">
-        <v>12.69070001125336</v>
+        <v>51.02379997253418</v>
       </c>
       <c r="K61">
-        <v>10.27999973297119</v>
+        <v>0.1557042300701141</v>
       </c>
       <c r="L61">
-        <v>21.03000068664551</v>
+        <v>79.82826232910156</v>
       </c>
       <c r="M61">
-        <v>138.6523379055089</v>
+        <v>129.5236368294642</v>
       </c>
       <c r="N61">
-        <v>-1.9552</v>
+        <v>0.7</v>
       </c>
       <c r="O61">
-        <v>-0.2692</v>
+        <v>0.57</v>
       </c>
       <c r="P61">
-        <v>-0.0328</v>
+        <v>0.79</v>
       </c>
       <c r="Q61">
-        <v>-1.9552</v>
+        <v>0.92</v>
       </c>
       <c r="R61">
-        <v>-201907000</v>
+        <v>115400000</v>
       </c>
       <c r="S61">
-        <v>993042000</v>
+        <v>95000000</v>
       </c>
       <c r="T61">
-        <v>-904131000</v>
+        <v>129700000</v>
       </c>
       <c r="U61">
-        <v>1176032000</v>
+        <v>152900000</v>
       </c>
       <c r="V61" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="62" spans="1:22">
@@ -5334,67 +5238,67 @@
         <v>82</v>
       </c>
       <c r="B62" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C62" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="D62" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="E62">
-        <v>124.3199996948242</v>
+        <v>56.15000152587891</v>
       </c>
       <c r="F62">
-        <v>349993.3333333333</v>
+        <v>1479613.333333333</v>
       </c>
       <c r="G62">
-        <v>109.1179997253418</v>
+        <v>49.50940010070801</v>
       </c>
       <c r="H62">
-        <v>90.55213322957357</v>
+        <v>44.54780001322428</v>
       </c>
       <c r="I62">
-        <v>86.11849992752076</v>
+        <v>42.80825002670288</v>
       </c>
       <c r="J62">
-        <v>81.69059991836548</v>
+        <v>40.73250000953674</v>
       </c>
       <c r="K62">
-        <v>20.81999969482422</v>
+        <v>11.8095235824585</v>
       </c>
       <c r="L62">
-        <v>124.3199996948242</v>
+        <v>56.15000152587891</v>
       </c>
       <c r="M62">
-        <v>138.5104684789908</v>
+        <v>129.1571037060192</v>
       </c>
       <c r="N62">
-        <v>1.03</v>
+        <v>0.55</v>
       </c>
       <c r="O62">
-        <v>1.05</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P62">
-        <v>1.34</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q62">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="R62">
-        <v>52215000</v>
+        <v>93400000</v>
       </c>
       <c r="S62">
-        <v>66214000</v>
+        <v>158700000</v>
       </c>
       <c r="T62">
-        <v>29068000</v>
+        <v>93800000</v>
       </c>
       <c r="U62">
-        <v>223334000</v>
+        <v>112900000</v>
       </c>
       <c r="V62" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="63" spans="1:22">
@@ -5402,67 +5306,67 @@
         <v>83</v>
       </c>
       <c r="B63" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C63" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="D63" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="E63">
-        <v>59.86000061035156</v>
+        <v>495.5299987792969</v>
       </c>
       <c r="F63">
-        <v>358796.6666666667</v>
+        <v>416651.0666666667</v>
       </c>
       <c r="G63">
-        <v>52.81380012512207</v>
+        <v>425.8608001708984</v>
       </c>
       <c r="H63">
-        <v>48.1241333770752</v>
+        <v>393.860767211914</v>
       </c>
       <c r="I63">
-        <v>45.76340009689331</v>
+        <v>389.8113252258301</v>
       </c>
       <c r="J63">
-        <v>43.54930004119873</v>
+        <v>378.0562748718262</v>
       </c>
       <c r="K63">
-        <v>0.07982486486434937</v>
+        <v>19.76499938964844</v>
       </c>
       <c r="L63">
-        <v>59.86000061035156</v>
+        <v>548.4299926757812</v>
       </c>
       <c r="M63">
-        <v>138.4862618209644</v>
+        <v>129.1447575418808</v>
       </c>
       <c r="N63">
-        <v>0.05</v>
+        <v>-0.52</v>
       </c>
       <c r="O63">
-        <v>-0.14</v>
+        <v>-4.26</v>
       </c>
       <c r="P63">
-        <v>0.13</v>
+        <v>-0.7</v>
       </c>
       <c r="Q63">
-        <v>0.38</v>
+        <v>-0.52</v>
       </c>
       <c r="R63">
-        <v>-6900000</v>
+        <v>-235042000</v>
       </c>
       <c r="S63">
-        <v>6200000</v>
+        <v>-38613000</v>
       </c>
       <c r="T63">
-        <v>18600000</v>
+        <v>-28871000</v>
       </c>
       <c r="U63">
-        <v>-5600000</v>
+        <v>-94368000</v>
       </c>
       <c r="V63" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -5470,67 +5374,67 @@
         <v>84</v>
       </c>
       <c r="B64" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C64" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="D64" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="E64">
-        <v>75.51999664306641</v>
+        <v>31.90999984741211</v>
       </c>
       <c r="F64">
-        <v>677023.3333333334</v>
+        <v>745569.7333333333</v>
       </c>
       <c r="G64">
-        <v>69.94299995422364</v>
+        <v>25.96280014038086</v>
       </c>
       <c r="H64">
-        <v>58.79373321533203</v>
+        <v>25.69033339182536</v>
       </c>
       <c r="I64">
-        <v>56.46784992218018</v>
+        <v>24.86230004310608</v>
       </c>
       <c r="J64">
-        <v>53.32889993667602</v>
+        <v>23.67315005302429</v>
       </c>
       <c r="K64">
-        <v>23.54999923706055</v>
+        <v>0.6000000238418579</v>
       </c>
       <c r="L64">
-        <v>76.5</v>
+        <v>31.90999984741211</v>
       </c>
       <c r="M64">
-        <v>138.2292759605373</v>
+        <v>128.9200542805826</v>
       </c>
       <c r="N64">
-        <v>-1.24</v>
+        <v>2.5</v>
       </c>
       <c r="O64">
-        <v>-0.68</v>
+        <v>4.47</v>
       </c>
       <c r="P64">
-        <v>-1.24</v>
+        <v>1.4</v>
       </c>
       <c r="Q64">
-        <v>-0.68</v>
+        <v>3.9</v>
       </c>
       <c r="R64">
-        <v>-526161000</v>
+        <v>149125000</v>
       </c>
       <c r="S64">
-        <v>-193228000</v>
+        <v>267396000</v>
       </c>
       <c r="T64">
-        <v>-112101000</v>
+        <v>84719000</v>
       </c>
       <c r="U64">
-        <v>-446349000</v>
+        <v>237890000</v>
       </c>
       <c r="V64" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5538,67 +5442,67 @@
         <v>85</v>
       </c>
       <c r="B65" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C65" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D65" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="E65">
-        <v>13.89000034332275</v>
+        <v>77.12999725341797</v>
       </c>
       <c r="F65">
-        <v>1247623.1</v>
+        <v>1535791.233333333</v>
       </c>
       <c r="G65">
-        <v>10.21729988098144</v>
+        <v>76.21000030517578</v>
       </c>
       <c r="H65">
-        <v>10.11725797017415</v>
+        <v>64.81606679280598</v>
       </c>
       <c r="I65">
-        <v>10.04098649501801</v>
+        <v>60.14440019607544</v>
       </c>
       <c r="J65">
-        <v>9.983236494064331</v>
+        <v>56.44925012588501</v>
       </c>
       <c r="K65">
-        <v>8.989999771118164</v>
+        <v>0.5319142937660217</v>
       </c>
       <c r="L65">
-        <v>13.89000034332275</v>
+        <v>83.51999664306641</v>
       </c>
       <c r="M65">
-        <v>138.2251659760368</v>
+        <v>128.7475335240506</v>
       </c>
       <c r="N65">
-        <v>-0.08</v>
+        <v>2.35</v>
       </c>
       <c r="O65">
-        <v>0.090181</v>
+        <v>5.63</v>
       </c>
       <c r="P65">
-        <v>0.02</v>
+        <v>1.7</v>
       </c>
       <c r="Q65">
-        <v>-0.08</v>
+        <v>2.85</v>
       </c>
       <c r="R65">
-        <v>366476</v>
+        <v>273467000</v>
       </c>
       <c r="S65">
-        <v>900174</v>
+        <v>640536000</v>
       </c>
       <c r="T65">
-        <v>-1652348</v>
+        <v>191530000</v>
       </c>
       <c r="U65">
-        <v>5796203</v>
+        <v>320216000</v>
       </c>
       <c r="V65" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5606,67 +5510,67 @@
         <v>86</v>
       </c>
       <c r="B66" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C66" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="D66" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="E66">
-        <v>13.47999954223633</v>
+        <v>49.45999908447266</v>
       </c>
       <c r="F66">
-        <v>513820</v>
+        <v>699466.1666666666</v>
       </c>
       <c r="G66">
-        <v>12.79540002822876</v>
+        <v>45.5818000793457</v>
       </c>
       <c r="H66">
-        <v>10.76886667251587</v>
+        <v>40.45573328653971</v>
       </c>
       <c r="I66">
-        <v>10.16819999694824</v>
+        <v>38.14824995040894</v>
       </c>
       <c r="J66">
-        <v>9.689499990940094</v>
+        <v>36.20504995346069</v>
       </c>
       <c r="K66">
-        <v>6.639999866485596</v>
+        <v>0.02175931446254253</v>
       </c>
       <c r="L66">
-        <v>13.81999969482422</v>
+        <v>59.96058654785156</v>
       </c>
       <c r="M66">
-        <v>137.9516076787338</v>
+        <v>128.5911648524974</v>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P66">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Q66">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="R66">
-        <v>-77781000</v>
+        <v>144400000</v>
       </c>
       <c r="S66">
-        <v>-64977000</v>
+        <v>79776000</v>
       </c>
       <c r="T66">
-        <v>259425000</v>
+        <v>80700000</v>
       </c>
       <c r="U66">
-        <v>30506000</v>
+        <v>93493000</v>
       </c>
       <c r="V66" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -5674,67 +5578,67 @@
         <v>87</v>
       </c>
       <c r="B67" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C67" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D67" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="E67">
-        <v>144.6999969482422</v>
+        <v>173.2700042724609</v>
       </c>
       <c r="F67">
-        <v>1207866.666666667</v>
+        <v>333383.3333333333</v>
       </c>
       <c r="G67">
-        <v>142.5690002441406</v>
+        <v>159.8541998291016</v>
       </c>
       <c r="H67">
-        <v>112.2022001647949</v>
+        <v>143.0354002380371</v>
       </c>
       <c r="I67">
-        <v>108.7000500106812</v>
+        <v>136.3687001800537</v>
       </c>
       <c r="J67">
-        <v>103.3562500762939</v>
+        <v>129.4414003372192</v>
       </c>
       <c r="K67">
-        <v>0.1500000059604645</v>
+        <v>2.075098752975464</v>
       </c>
       <c r="L67">
-        <v>153.1100006103516</v>
+        <v>179.6499938964844</v>
       </c>
       <c r="M67">
-        <v>137.7039096910782</v>
+        <v>127.8041030511158</v>
       </c>
       <c r="N67">
-        <v>0.4</v>
+        <v>4.61</v>
       </c>
       <c r="O67">
-        <v>0.12</v>
+        <v>4.21</v>
       </c>
       <c r="P67">
-        <v>-2.46</v>
+        <v>4.31</v>
       </c>
       <c r="Q67">
-        <v>0.4</v>
+        <v>4.41</v>
       </c>
       <c r="R67">
-        <v>-154116727</v>
+        <v>340100000</v>
       </c>
       <c r="S67">
-        <v>-21223000</v>
+        <v>298000000</v>
       </c>
       <c r="T67">
-        <v>41227000</v>
+        <v>298300000</v>
       </c>
       <c r="U67">
-        <v>-187282000</v>
+        <v>300800000</v>
       </c>
       <c r="V67" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5742,67 +5646,67 @@
         <v>88</v>
       </c>
       <c r="B68" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="C68" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="D68" t="s">
-        <v>241</v>
+        <v>185</v>
       </c>
       <c r="E68">
-        <v>80.33000183105469</v>
+        <v>419.3110961914062</v>
       </c>
       <c r="F68">
-        <v>1640953.333333333</v>
+        <v>740604.4666666667</v>
       </c>
       <c r="G68">
-        <v>75.4352001953125</v>
+        <v>375.8520245361328</v>
       </c>
       <c r="H68">
-        <v>64.24980013529459</v>
+        <v>343.680141398112</v>
       </c>
       <c r="I68">
-        <v>59.59305017471313</v>
+        <v>330.7309060668945</v>
       </c>
       <c r="J68">
-        <v>55.93175008773804</v>
+        <v>315.944700088501</v>
       </c>
       <c r="K68">
-        <v>0.5319142937660217</v>
+        <v>1.31995165348053</v>
       </c>
       <c r="L68">
-        <v>83.51999664306641</v>
+        <v>419.3110961914062</v>
       </c>
       <c r="M68">
-        <v>137.6168911600767</v>
+        <v>127.7868839661596</v>
       </c>
       <c r="N68">
-        <v>2.35</v>
+        <v>0.99</v>
       </c>
       <c r="O68">
-        <v>5.63</v>
+        <v>2.98</v>
       </c>
       <c r="P68">
-        <v>1.7</v>
+        <v>3.04</v>
       </c>
       <c r="Q68">
-        <v>2.85</v>
+        <v>4.54</v>
       </c>
       <c r="R68">
-        <v>640536000</v>
+        <v>128831000</v>
       </c>
       <c r="S68">
-        <v>191530000</v>
+        <v>387854000</v>
       </c>
       <c r="T68">
-        <v>320216000</v>
+        <v>395237000</v>
       </c>
       <c r="U68">
-        <v>1326126000</v>
+        <v>590889000</v>
       </c>
       <c r="V68" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
     </row>
     <row r="69" spans="1:22">
@@ -5810,67 +5714,67 @@
         <v>89</v>
       </c>
       <c r="B69" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="C69" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="D69" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="E69">
-        <v>51.27999877929688</v>
+        <v>265.4500122070312</v>
       </c>
       <c r="F69">
-        <v>802423.3333333334</v>
+        <v>2300726.666666667</v>
       </c>
       <c r="G69">
-        <v>45.07120002746582</v>
+        <v>242.7173999023437</v>
       </c>
       <c r="H69">
-        <v>40.07406661987304</v>
+        <v>221.2159335327148</v>
       </c>
       <c r="I69">
-        <v>37.81209995269776</v>
+        <v>207.807250289917</v>
       </c>
       <c r="J69">
-        <v>35.95589994430542</v>
+        <v>197.0947500610351</v>
       </c>
       <c r="K69">
-        <v>0.02175931446254253</v>
+        <v>0.8275843262672424</v>
       </c>
       <c r="L69">
-        <v>59.96058654785156</v>
+        <v>312.9627685546875</v>
       </c>
       <c r="M69">
-        <v>137.3209600504246</v>
+        <v>127.6254711441808</v>
       </c>
       <c r="N69">
-        <v>1.98</v>
+        <v>3.33</v>
       </c>
       <c r="O69">
-        <v>1.08</v>
+        <v>3.07</v>
       </c>
       <c r="P69">
-        <v>1.08</v>
+        <v>3.05</v>
       </c>
       <c r="Q69">
-        <v>1.24</v>
+        <v>6.05</v>
       </c>
       <c r="R69">
-        <v>562139000</v>
+        <v>875000000</v>
       </c>
       <c r="S69">
-        <v>80700000</v>
+        <v>788000000</v>
       </c>
       <c r="T69">
-        <v>93493000</v>
+        <v>771000000</v>
       </c>
       <c r="U69">
-        <v>494418000</v>
+        <v>1538000000</v>
       </c>
       <c r="V69" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5878,67 +5782,67 @@
         <v>90</v>
       </c>
       <c r="B70" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C70" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="D70" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="E70">
-        <v>33.83000183105469</v>
+        <v>16.28000068664551</v>
       </c>
       <c r="F70">
-        <v>1265050</v>
+        <v>402072.8333333333</v>
       </c>
       <c r="G70">
-        <v>30.13739994049072</v>
+        <v>14.96080005645752</v>
       </c>
       <c r="H70">
-        <v>27.30466659545898</v>
+        <v>13.07600001653035</v>
       </c>
       <c r="I70">
-        <v>26.02739996910095</v>
+        <v>13.02175000667572</v>
       </c>
       <c r="J70">
-        <v>24.4575999879837</v>
+        <v>12.70985001087189</v>
       </c>
       <c r="K70">
-        <v>0.1598737090826035</v>
+        <v>10.27999973297119</v>
       </c>
       <c r="L70">
-        <v>33.83000183105469</v>
+        <v>21.03000068664551</v>
       </c>
       <c r="M70">
-        <v>136.7497833782667</v>
+        <v>127.4969527508918</v>
       </c>
       <c r="N70">
-        <v>0.11</v>
+        <v>-1.9552</v>
       </c>
       <c r="O70">
-        <v>-0.02</v>
+        <v>-0.2692</v>
       </c>
       <c r="P70">
-        <v>1.3</v>
+        <v>-0.0328</v>
       </c>
       <c r="Q70">
-        <v>0.11</v>
+        <v>-1.9552</v>
       </c>
       <c r="R70">
-        <v>359000000</v>
+        <v>-125294000</v>
       </c>
       <c r="S70">
-        <v>-64000000</v>
+        <v>-201907000</v>
       </c>
       <c r="T70">
-        <v>23000000</v>
+        <v>993042000</v>
       </c>
       <c r="U70">
-        <v>275000000</v>
+        <v>-904131000</v>
       </c>
       <c r="V70" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -5946,67 +5850,67 @@
         <v>91</v>
       </c>
       <c r="B71" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C71" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="D71" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="E71">
-        <v>15.86999988555908</v>
+        <v>48.77999877929688</v>
       </c>
       <c r="F71">
-        <v>912300</v>
+        <v>1011090</v>
       </c>
       <c r="G71">
-        <v>12.8510000038147</v>
+        <v>47.26279991149902</v>
       </c>
       <c r="H71">
-        <v>12.55400000890096</v>
+        <v>40.33906665802002</v>
       </c>
       <c r="I71">
-        <v>12.1385000038147</v>
+        <v>37.26875001907349</v>
       </c>
       <c r="J71">
-        <v>11.76915000915527</v>
+        <v>34.80835000991821</v>
       </c>
       <c r="K71">
-        <v>9.039999961853027</v>
+        <v>7.050000190734863</v>
       </c>
       <c r="L71">
-        <v>15.86999988555908</v>
+        <v>51.63999938964844</v>
       </c>
       <c r="M71">
-        <v>136.5836952936951</v>
+        <v>127.3767151230392</v>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>309779000</v>
       </c>
       <c r="S71">
-        <v>-150120000</v>
+        <v>275331000</v>
       </c>
       <c r="T71">
-        <v>-150120000</v>
+        <v>191051000</v>
       </c>
       <c r="U71">
-        <v>51482000</v>
+        <v>234602000</v>
       </c>
       <c r="V71" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -6014,67 +5918,67 @@
         <v>92</v>
       </c>
       <c r="B72" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C72" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D72" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="E72">
-        <v>93.18000030517578</v>
+        <v>408.239990234375</v>
       </c>
       <c r="F72">
-        <v>402826.6666666667</v>
+        <v>972792.8666666667</v>
       </c>
       <c r="G72">
-        <v>82.33840011596679</v>
+        <v>355.5105993652344</v>
       </c>
       <c r="H72">
-        <v>74.50480010986328</v>
+        <v>338.0415997314453</v>
       </c>
       <c r="I72">
-        <v>69.33780006408692</v>
+        <v>325.3418496704102</v>
       </c>
       <c r="J72">
-        <v>64.86175004959107</v>
+        <v>311.7542498779297</v>
       </c>
       <c r="K72">
-        <v>10.5</v>
+        <v>0.6462651491165161</v>
       </c>
       <c r="L72">
-        <v>96.06999969482422</v>
+        <v>427.5899963378906</v>
       </c>
       <c r="M72">
-        <v>136.4452698276311</v>
+        <v>127.3644032535261</v>
       </c>
       <c r="N72">
-        <v>-0.41</v>
+        <v>3.36</v>
       </c>
       <c r="O72">
-        <v>-0.25</v>
+        <v>2.92</v>
       </c>
       <c r="P72">
-        <v>-0.21</v>
+        <v>2.58</v>
       </c>
       <c r="Q72">
-        <v>-0.08</v>
+        <v>2.65</v>
       </c>
       <c r="R72">
-        <v>-7426000</v>
+        <v>377401000</v>
       </c>
       <c r="S72">
-        <v>-6720000</v>
+        <v>323929000</v>
       </c>
       <c r="T72">
-        <v>-2636000</v>
+        <v>285038000</v>
       </c>
       <c r="U72">
-        <v>-36231000</v>
+        <v>292362000</v>
       </c>
       <c r="V72" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -6082,67 +5986,67 @@
         <v>93</v>
       </c>
       <c r="B73" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C73" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="D73" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="E73">
-        <v>718.489990234375</v>
+        <v>104.1699981689453</v>
       </c>
       <c r="F73">
-        <v>1336443.333333333</v>
+        <v>284311.6666666667</v>
       </c>
       <c r="G73">
-        <v>627.3242004394531</v>
+        <v>96.30060012817383</v>
       </c>
       <c r="H73">
-        <v>538.5065325927734</v>
+        <v>86.2268669128418</v>
       </c>
       <c r="I73">
-        <v>510.0912493896485</v>
+        <v>81.76900022506715</v>
       </c>
       <c r="J73">
-        <v>484.072649230957</v>
+        <v>79.30515024185181</v>
       </c>
       <c r="K73">
-        <v>0.5958155393600464</v>
+        <v>12.27999973297119</v>
       </c>
       <c r="L73">
-        <v>729.8200073242188</v>
+        <v>108.4400024414062</v>
       </c>
       <c r="M73">
-        <v>136.2603888711199</v>
+        <v>127.145499222131</v>
       </c>
       <c r="N73">
-        <v>10.39</v>
+        <v>1.22</v>
       </c>
       <c r="O73">
-        <v>10.77</v>
+        <v>0.78</v>
       </c>
       <c r="P73">
-        <v>6.01</v>
+        <v>2.17</v>
       </c>
       <c r="Q73">
-        <v>5.97</v>
+        <v>1.38</v>
       </c>
       <c r="R73">
-        <v>5125098000</v>
+        <v>77000000</v>
       </c>
       <c r="S73">
-        <v>814008000</v>
+        <v>49000000</v>
       </c>
       <c r="T73">
-        <v>802537000</v>
+        <v>131000000</v>
       </c>
       <c r="U73">
-        <v>4917328000</v>
+        <v>83000000</v>
       </c>
       <c r="V73" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -6150,67 +6054,67 @@
         <v>94</v>
       </c>
       <c r="B74" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C74" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="D74" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="E74">
-        <v>116.3199996948242</v>
+        <v>10.86989974975586</v>
       </c>
       <c r="F74">
-        <v>455450</v>
+        <v>444014.2333333333</v>
       </c>
       <c r="G74">
-        <v>94.72599975585938</v>
+        <v>9.791197967529296</v>
       </c>
       <c r="H74">
-        <v>90.89619979858398</v>
+        <v>8.724799318313599</v>
       </c>
       <c r="I74">
-        <v>87.67859992980956</v>
+        <v>8.575049488544463</v>
       </c>
       <c r="J74">
-        <v>84.63469993591309</v>
+        <v>8.358299994468689</v>
       </c>
       <c r="K74">
-        <v>3.099249601364136</v>
+        <v>3.549999952316284</v>
       </c>
       <c r="L74">
-        <v>121.8199996948242</v>
+        <v>13.5</v>
       </c>
       <c r="M74">
-        <v>136.2020114899823</v>
+        <v>126.8588001506004</v>
       </c>
       <c r="N74">
-        <v>3.5</v>
+        <v>0.168</v>
       </c>
       <c r="O74">
-        <v>1.48</v>
+        <v>0.205</v>
       </c>
       <c r="P74">
-        <v>2.84</v>
+        <v>0.024961</v>
       </c>
       <c r="Q74">
-        <v>1.64</v>
+        <v>0.2</v>
       </c>
       <c r="R74">
-        <v>298209000</v>
+        <v>19087000</v>
       </c>
       <c r="S74">
-        <v>71283000</v>
+        <v>22548000</v>
       </c>
       <c r="T74">
-        <v>40443000</v>
+        <v>2732000</v>
       </c>
       <c r="U74">
-        <v>299923000</v>
+        <v>21569000</v>
       </c>
       <c r="V74" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -6218,67 +6122,67 @@
         <v>95</v>
       </c>
       <c r="B75" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C75" t="s">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="D75" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="E75">
-        <v>35.15999984741211</v>
+        <v>103.5699996948242</v>
       </c>
       <c r="F75">
-        <v>3874016.666666667</v>
+        <v>6025520</v>
       </c>
       <c r="G75">
-        <v>30.74520004272461</v>
+        <v>93.40379989624023</v>
       </c>
       <c r="H75">
-        <v>27.72946669260661</v>
+        <v>81.89879979451497</v>
       </c>
       <c r="I75">
-        <v>26.59060001373291</v>
+        <v>78.30409980773926</v>
       </c>
       <c r="J75">
-        <v>26.09935001373291</v>
+        <v>74.76219984054565</v>
       </c>
       <c r="K75">
-        <v>1.243403434753418</v>
+        <v>0.9100000262260437</v>
       </c>
       <c r="L75">
-        <v>44.90747833251953</v>
+        <v>108.0899963378906</v>
       </c>
       <c r="M75">
-        <v>136.1365227108579</v>
+        <v>126.8170257536855</v>
       </c>
       <c r="N75">
-        <v>0.27</v>
+        <v>0.7</v>
       </c>
       <c r="O75">
-        <v>0.21</v>
+        <v>1.35</v>
       </c>
       <c r="P75">
-        <v>-0.05</v>
+        <v>1.03</v>
       </c>
       <c r="Q75">
-        <v>0.27</v>
+        <v>1.29</v>
       </c>
       <c r="R75">
-        <v>-19530000</v>
+        <v>311900000</v>
       </c>
       <c r="S75">
-        <v>-15417000</v>
+        <v>604300000</v>
       </c>
       <c r="T75">
-        <v>118969000</v>
+        <v>461700000</v>
       </c>
       <c r="U75">
-        <v>89382000</v>
+        <v>576600000</v>
       </c>
       <c r="V75" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -6286,67 +6190,67 @@
         <v>96</v>
       </c>
       <c r="B76" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C76" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="D76" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="E76">
-        <v>249.9600067138672</v>
+        <v>81.33000183105469</v>
       </c>
       <c r="F76">
-        <v>6436760</v>
+        <v>2087616.666666667</v>
       </c>
       <c r="G76">
-        <v>234.1404000854492</v>
+        <v>75.29920043945313</v>
       </c>
       <c r="H76">
-        <v>194.5357333374023</v>
+        <v>68.70426684061687</v>
       </c>
       <c r="I76">
-        <v>186.3620999145508</v>
+        <v>66.74480020523072</v>
       </c>
       <c r="J76">
-        <v>178.6773498535156</v>
+        <v>63.76200012207031</v>
       </c>
       <c r="K76">
-        <v>13.18666744232178</v>
+        <v>4.15140962600708</v>
       </c>
       <c r="L76">
-        <v>257.8800048828125</v>
+        <v>82.45999908447266</v>
       </c>
       <c r="M76">
-        <v>135.4600862620373</v>
+        <v>126.7716456050033</v>
       </c>
       <c r="N76">
-        <v>0.01</v>
+        <v>-3.53</v>
       </c>
       <c r="O76">
-        <v>0.06</v>
+        <v>-1.52</v>
       </c>
       <c r="P76">
-        <v>0.25</v>
+        <v>0.025016</v>
       </c>
       <c r="Q76">
-        <v>0.31</v>
+        <v>0.366974</v>
       </c>
       <c r="R76">
-        <v>20000000</v>
+        <v>-2051000000</v>
       </c>
       <c r="S76">
-        <v>84200000</v>
+        <v>-876000000</v>
       </c>
       <c r="T76">
-        <v>107800000</v>
+        <v>23430000</v>
       </c>
       <c r="U76">
-        <v>34300000</v>
+        <v>217383000</v>
       </c>
       <c r="V76" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
     </row>
     <row r="77" spans="1:22">
@@ -6354,67 +6258,67 @@
         <v>97</v>
       </c>
       <c r="B77" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C77" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D77" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="E77">
-        <v>92.69000244140625</v>
+        <v>13.71000003814697</v>
       </c>
       <c r="F77">
-        <v>414790</v>
+        <v>495449.5</v>
       </c>
       <c r="G77">
-        <v>90.72000030517579</v>
+        <v>12.81000001907349</v>
       </c>
       <c r="H77">
-        <v>76.85306650797526</v>
+        <v>10.88553333918254</v>
       </c>
       <c r="I77">
-        <v>69.83994993209839</v>
+        <v>10.26634999752045</v>
       </c>
       <c r="J77">
-        <v>64.86389987945557</v>
+        <v>9.751249988079071</v>
       </c>
       <c r="K77">
-        <v>1.669681549072266</v>
+        <v>6.639999866485596</v>
       </c>
       <c r="L77">
-        <v>98.38999938964844</v>
+        <v>13.89000034332275</v>
       </c>
       <c r="M77">
-        <v>135.4186105577915</v>
+        <v>126.3842058001431</v>
       </c>
       <c r="N77">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="O77">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="P77">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Q77">
-        <v>3.58</v>
+        <v>1.17</v>
       </c>
       <c r="R77">
-        <v>22222000</v>
+        <v>-77781000</v>
       </c>
       <c r="S77">
-        <v>32408000</v>
+        <v>259425000</v>
       </c>
       <c r="T77">
-        <v>105259000</v>
+        <v>-77781000</v>
       </c>
       <c r="U77">
-        <v>93693000</v>
+        <v>259425000</v>
       </c>
       <c r="V77" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -6422,67 +6326,67 @@
         <v>98</v>
       </c>
       <c r="B78" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="C78" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D78" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="E78">
-        <v>31.8799991607666</v>
+        <v>73.99500274658203</v>
       </c>
       <c r="F78">
-        <v>1132396.666666667</v>
+        <v>418487.8666666666</v>
       </c>
       <c r="G78">
-        <v>31.64800003051758</v>
+        <v>69.13009971618652</v>
       </c>
       <c r="H78">
-        <v>26.50473337809245</v>
+        <v>60.95249994913737</v>
       </c>
       <c r="I78">
-        <v>24.23160004615784</v>
+        <v>57.91302499771118</v>
       </c>
       <c r="J78">
-        <v>22.60275006771088</v>
+        <v>54.89604997634888</v>
       </c>
       <c r="K78">
-        <v>6.139999866485596</v>
+        <v>10.73999977111816</v>
       </c>
       <c r="L78">
-        <v>33.66999816894531</v>
+        <v>74.80000305175781</v>
       </c>
       <c r="M78">
-        <v>134.454367680038</v>
+        <v>126.3386576001221</v>
       </c>
       <c r="N78">
-        <v>1.45</v>
+        <v>2.07</v>
       </c>
       <c r="O78">
-        <v>1.98</v>
+        <v>2.41</v>
       </c>
       <c r="P78">
-        <v>0.73</v>
+        <v>1.53</v>
       </c>
       <c r="Q78">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="R78">
-        <v>576060000</v>
+        <v>89470000</v>
       </c>
       <c r="S78">
-        <v>74742000</v>
+        <v>103153000</v>
       </c>
       <c r="T78">
-        <v>60724000</v>
+        <v>64775000</v>
       </c>
       <c r="U78">
-        <v>563324000</v>
+        <v>75593000</v>
       </c>
       <c r="V78" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -6490,67 +6394,67 @@
         <v>99</v>
       </c>
       <c r="B79" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C79" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="D79" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="E79">
-        <v>215.0399932861328</v>
+        <v>36.68999862670898</v>
       </c>
       <c r="F79">
-        <v>566250</v>
+        <v>1234259.5</v>
       </c>
       <c r="G79">
-        <v>180.3333999633789</v>
+        <v>33.19919990539551</v>
       </c>
       <c r="H79">
-        <v>164.1136000569661</v>
+        <v>29.00599997202555</v>
       </c>
       <c r="I79">
-        <v>159.0799996566772</v>
+        <v>28.15485001564026</v>
       </c>
       <c r="J79">
-        <v>151.846849861145</v>
+        <v>26.77610004425049</v>
       </c>
       <c r="K79">
-        <v>0.9346818327903748</v>
+        <v>0.8671879768371582</v>
       </c>
       <c r="L79">
-        <v>215.0399932861328</v>
+        <v>48.7400016784668</v>
       </c>
       <c r="M79">
-        <v>134.3884700644366</v>
+        <v>126.2308646934236</v>
       </c>
       <c r="N79">
-        <v>2.16</v>
+        <v>0.64</v>
       </c>
       <c r="O79">
-        <v>2.63</v>
+        <v>0.4</v>
       </c>
       <c r="P79">
-        <v>2.32</v>
+        <v>0.34</v>
       </c>
       <c r="Q79">
-        <v>2.95</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R79">
-        <v>406122000</v>
+        <v>59473000</v>
       </c>
       <c r="S79">
-        <v>111473000</v>
+        <v>37231000</v>
       </c>
       <c r="T79">
-        <v>140595000</v>
+        <v>31462000</v>
       </c>
       <c r="U79">
-        <v>444209000</v>
+        <v>52817000</v>
       </c>
       <c r="V79" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6558,67 +6462,67 @@
         <v>100</v>
       </c>
       <c r="B80" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C80" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="D80" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="E80">
-        <v>28.76000022888184</v>
+        <v>553.7150268554688</v>
       </c>
       <c r="F80">
-        <v>916220</v>
+        <v>366854.8666666666</v>
       </c>
       <c r="G80">
-        <v>25.90520004272461</v>
+        <v>515.5296978759766</v>
       </c>
       <c r="H80">
-        <v>22.95959995269775</v>
+        <v>463.8291658528646</v>
       </c>
       <c r="I80">
-        <v>21.61889996528625</v>
+        <v>439.4328742980957</v>
       </c>
       <c r="J80">
-        <v>20.26214997768402</v>
+        <v>418.1029501342774</v>
       </c>
       <c r="K80">
-        <v>9.090000152587891</v>
+        <v>0.4583329856395721</v>
       </c>
       <c r="L80">
-        <v>28.76000022888184</v>
+        <v>558</v>
       </c>
       <c r="M80">
-        <v>134.3080848914423</v>
+        <v>126.140502577076</v>
       </c>
       <c r="N80">
-        <v>0.06</v>
+        <v>3.8</v>
       </c>
       <c r="O80">
-        <v>0.06</v>
+        <v>10.48</v>
       </c>
       <c r="P80">
-        <v>0.04</v>
+        <v>3.46</v>
       </c>
       <c r="Q80">
-        <v>0.05</v>
+        <v>2.41</v>
       </c>
       <c r="R80">
-        <v>28000000</v>
+        <v>101524000</v>
       </c>
       <c r="S80">
-        <v>22000000</v>
+        <v>278662000</v>
       </c>
       <c r="T80">
-        <v>26000000</v>
+        <v>91787000</v>
       </c>
       <c r="U80">
-        <v>73000000</v>
+        <v>63552000</v>
       </c>
       <c r="V80" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -6626,67 +6530,67 @@
         <v>101</v>
       </c>
       <c r="B81" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C81" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="D81" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="E81">
-        <v>31.61000061035156</v>
+        <v>58.68999862670898</v>
       </c>
       <c r="F81">
-        <v>1021096.666666667</v>
+        <v>1583600</v>
       </c>
       <c r="G81">
-        <v>29.46780006408692</v>
+        <v>53.81780014038086</v>
       </c>
       <c r="H81">
-        <v>25.10673337300619</v>
+        <v>49.70693336486816</v>
       </c>
       <c r="I81">
-        <v>24.14995003700257</v>
+        <v>46.78275003433227</v>
       </c>
       <c r="J81">
-        <v>23.33990002632141</v>
+        <v>44.33255002975464</v>
       </c>
       <c r="K81">
-        <v>18.89999961853027</v>
+        <v>1.326302051544189</v>
       </c>
       <c r="L81">
-        <v>32.33000183105469</v>
+        <v>60.29999923706055</v>
       </c>
       <c r="M81">
-        <v>134.0992295488805</v>
+        <v>126.0024384509456</v>
       </c>
       <c r="N81">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="O81">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="P81">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="Q81">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R81">
-        <v>111000000</v>
+        <v>0</v>
       </c>
       <c r="S81">
-        <v>54000000</v>
+        <v>0</v>
       </c>
       <c r="T81">
-        <v>86000000</v>
+        <v>0</v>
       </c>
       <c r="U81">
-        <v>366000000</v>
+        <v>0</v>
       </c>
       <c r="V81" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -6694,67 +6598,67 @@
         <v>102</v>
       </c>
       <c r="B82" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C82" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="D82" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="E82">
-        <v>11.10000038146973</v>
+        <v>32.49499893188477</v>
       </c>
       <c r="F82">
-        <v>462506.6666666667</v>
+        <v>1334094</v>
       </c>
       <c r="G82">
-        <v>9.66459997177124</v>
+        <v>30.52249992370605</v>
       </c>
       <c r="H82">
-        <v>8.672733322779338</v>
+        <v>27.50869992574056</v>
       </c>
       <c r="I82">
-        <v>8.536149990558624</v>
+        <v>26.25192496299744</v>
       </c>
       <c r="J82">
-        <v>8.341499996185302</v>
+        <v>24.65844998836517</v>
       </c>
       <c r="K82">
-        <v>3.549999952316284</v>
+        <v>0.1598737090826035</v>
       </c>
       <c r="L82">
-        <v>13.5</v>
+        <v>33.83000183105469</v>
       </c>
       <c r="M82">
-        <v>134.0927143052481</v>
+        <v>125.7623768225628</v>
       </c>
       <c r="N82">
-        <v>0.168</v>
+        <v>0.11</v>
       </c>
       <c r="O82">
-        <v>0.205</v>
+        <v>-0.02</v>
       </c>
       <c r="P82">
-        <v>0.024961</v>
+        <v>1.3</v>
       </c>
       <c r="Q82">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="R82">
-        <v>22548000</v>
+        <v>-4000000</v>
       </c>
       <c r="S82">
-        <v>2732000</v>
+        <v>264000000</v>
       </c>
       <c r="T82">
-        <v>21569000</v>
+        <v>-64000000</v>
       </c>
       <c r="U82">
-        <v>108138000</v>
+        <v>23000000</v>
       </c>
       <c r="V82" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
     <row r="83" spans="1:22">
@@ -6762,815 +6666,67 @@
         <v>103</v>
       </c>
       <c r="B83" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C83" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="D83" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="E83">
-        <v>30.47999954223633</v>
+        <v>32.02000045776367</v>
       </c>
       <c r="F83">
-        <v>404350</v>
+        <v>1077573.333333333</v>
       </c>
       <c r="G83">
-        <v>27.5565998840332</v>
+        <v>31.71100006103516</v>
       </c>
       <c r="H83">
-        <v>24.13193328857422</v>
+        <v>26.68313337961833</v>
       </c>
       <c r="I83">
-        <v>23.60934995651245</v>
+        <v>24.39620005130768</v>
       </c>
       <c r="J83">
-        <v>22.99069995880127</v>
+        <v>22.76790006160736</v>
       </c>
       <c r="K83">
-        <v>1.970000028610229</v>
+        <v>6.139999866485596</v>
       </c>
       <c r="L83">
-        <v>30.61000061035156</v>
+        <v>33.66999816894531</v>
       </c>
       <c r="M83">
-        <v>133.927745362198</v>
+        <v>125.4154569860466</v>
       </c>
       <c r="N83">
-        <v>-0.04</v>
+        <v>1.45</v>
       </c>
       <c r="O83">
-        <v>0.08</v>
+        <v>1.98</v>
       </c>
       <c r="P83">
-        <v>0.24</v>
+        <v>0.73</v>
       </c>
       <c r="Q83">
-        <v>-0.11</v>
+        <v>0.6</v>
       </c>
       <c r="R83">
-        <v>4789000</v>
+        <v>149226000</v>
       </c>
       <c r="S83">
-        <v>13725000</v>
+        <v>202973000</v>
       </c>
       <c r="T83">
-        <v>-6296000</v>
+        <v>74742000</v>
       </c>
       <c r="U83">
-        <v>24049000</v>
+        <v>60724000</v>
       </c>
       <c r="V83" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="84" spans="1:22">
-      <c r="A84" t="s">
-        <v>104</v>
-      </c>
-      <c r="B84" t="s">
-        <v>115</v>
-      </c>
-      <c r="C84" t="s">
-        <v>169</v>
-      </c>
-      <c r="D84" t="s">
-        <v>257</v>
-      </c>
-      <c r="E84">
-        <v>53.66999816894531</v>
-      </c>
-      <c r="F84">
-        <v>1173240</v>
-      </c>
-      <c r="G84">
-        <v>46.90399978637695</v>
-      </c>
-      <c r="H84">
-        <v>43.12819999694824</v>
-      </c>
-      <c r="I84">
-        <v>42.28294998168946</v>
-      </c>
-      <c r="J84">
-        <v>40.74560003280639</v>
-      </c>
-      <c r="K84">
-        <v>2.721946477890015</v>
-      </c>
-      <c r="L84">
-        <v>53.91999816894531</v>
-      </c>
-      <c r="M84">
-        <v>133.8993498886863</v>
-      </c>
-      <c r="N84">
-        <v>3.74</v>
-      </c>
-      <c r="O84">
-        <v>3.41</v>
-      </c>
-      <c r="P84">
-        <v>0.25</v>
-      </c>
-      <c r="Q84">
-        <v>-2</v>
-      </c>
-      <c r="R84">
-        <v>312600000</v>
-      </c>
-      <c r="S84">
-        <v>32572000</v>
-      </c>
-      <c r="T84">
-        <v>-155994000</v>
-      </c>
-      <c r="U84">
-        <v>1220944000</v>
-      </c>
-      <c r="V84" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="85" spans="1:22">
-      <c r="A85" t="s">
-        <v>105</v>
-      </c>
-      <c r="B85" t="s">
-        <v>116</v>
-      </c>
-      <c r="C85" t="s">
-        <v>170</v>
-      </c>
-      <c r="D85" t="s">
-        <v>258</v>
-      </c>
-      <c r="E85">
-        <v>110.6699981689453</v>
-      </c>
-      <c r="F85">
-        <v>1113550</v>
-      </c>
-      <c r="G85">
-        <v>102.1255996704102</v>
-      </c>
-      <c r="H85">
-        <v>87.25533320109049</v>
-      </c>
-      <c r="I85">
-        <v>82.09754981994629</v>
-      </c>
-      <c r="J85">
-        <v>76.87339988708496</v>
-      </c>
-      <c r="K85">
-        <v>0.3787146806716919</v>
-      </c>
-      <c r="L85">
-        <v>115.1399993896484</v>
-      </c>
-      <c r="M85">
-        <v>133.8220223489677</v>
-      </c>
-      <c r="N85">
-        <v>2.25</v>
-      </c>
-      <c r="O85">
-        <v>1.61</v>
-      </c>
-      <c r="P85">
-        <v>1.52</v>
-      </c>
-      <c r="Q85">
-        <v>1.72</v>
-      </c>
-      <c r="R85">
-        <v>978000000</v>
-      </c>
-      <c r="S85">
-        <v>207000000</v>
-      </c>
-      <c r="T85">
-        <v>233000000</v>
-      </c>
-      <c r="U85">
-        <v>963000000</v>
-      </c>
-      <c r="V85" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="86" spans="1:22">
-      <c r="A86" t="s">
-        <v>106</v>
-      </c>
-      <c r="B86" t="s">
-        <v>119</v>
-      </c>
-      <c r="C86" t="s">
-        <v>171</v>
-      </c>
-      <c r="D86" t="s">
-        <v>259</v>
-      </c>
-      <c r="E86">
-        <v>310.5299987792969</v>
-      </c>
-      <c r="F86">
-        <v>322336.6666666667</v>
-      </c>
-      <c r="G86">
-        <v>280.5541995239258</v>
-      </c>
-      <c r="H86">
-        <v>248.9095338948568</v>
-      </c>
-      <c r="I86">
-        <v>240.5363003540039</v>
-      </c>
-      <c r="J86">
-        <v>231.8691004943848</v>
-      </c>
-      <c r="K86">
-        <v>1.363492727279663</v>
-      </c>
-      <c r="L86">
-        <v>412.9100646972656</v>
-      </c>
-      <c r="M86">
-        <v>133.5122787335413</v>
-      </c>
-      <c r="N86">
-        <v>11.92</v>
-      </c>
-      <c r="O86">
-        <v>9</v>
-      </c>
-      <c r="P86">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Q86">
-        <v>10.78</v>
-      </c>
-      <c r="R86">
-        <v>1251000000</v>
-      </c>
-      <c r="S86">
-        <v>228700000</v>
-      </c>
-      <c r="T86">
-        <v>297200000</v>
-      </c>
-      <c r="U86">
-        <v>1137500000</v>
-      </c>
-      <c r="V86" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="87" spans="1:22">
-      <c r="A87" t="s">
-        <v>107</v>
-      </c>
-      <c r="B87" t="s">
-        <v>119</v>
-      </c>
-      <c r="C87" t="s">
-        <v>137</v>
-      </c>
-      <c r="D87" t="s">
-        <v>260</v>
-      </c>
-      <c r="E87">
-        <v>48.41999816894531</v>
-      </c>
-      <c r="F87">
-        <v>1058410</v>
-      </c>
-      <c r="G87">
-        <v>47.09019989013672</v>
-      </c>
-      <c r="H87">
-        <v>40.09586666107177</v>
-      </c>
-      <c r="I87">
-        <v>37.03420002937317</v>
-      </c>
-      <c r="J87">
-        <v>34.55645001411438</v>
-      </c>
-      <c r="K87">
-        <v>7.050000190734863</v>
-      </c>
-      <c r="L87">
-        <v>51.63999938964844</v>
-      </c>
-      <c r="M87">
-        <v>133.5122565754114</v>
-      </c>
-      <c r="N87">
-        <v>2.72</v>
-      </c>
-      <c r="O87">
-        <v>2.51</v>
-      </c>
-      <c r="P87">
-        <v>1.74</v>
-      </c>
-      <c r="Q87">
-        <v>2.12</v>
-      </c>
-      <c r="R87">
-        <v>1052800000</v>
-      </c>
-      <c r="S87">
-        <v>191051000</v>
-      </c>
-      <c r="T87">
-        <v>234602000</v>
-      </c>
-      <c r="U87">
-        <v>1067148000</v>
-      </c>
-      <c r="V87" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="88" spans="1:22">
-      <c r="A88" t="s">
-        <v>108</v>
-      </c>
-      <c r="B88" t="s">
-        <v>118</v>
-      </c>
-      <c r="C88" t="s">
-        <v>152</v>
-      </c>
-      <c r="D88" t="s">
-        <v>261</v>
-      </c>
-      <c r="E88">
-        <v>60.29999923706055</v>
-      </c>
-      <c r="F88">
-        <v>1583686.666666667</v>
-      </c>
-      <c r="G88">
-        <v>53.45320014953613</v>
-      </c>
-      <c r="H88">
-        <v>49.44633336385091</v>
-      </c>
-      <c r="I88">
-        <v>46.51530003547668</v>
-      </c>
-      <c r="J88">
-        <v>44.13330001831055</v>
-      </c>
-      <c r="K88">
-        <v>1.326302051544189</v>
-      </c>
-      <c r="L88">
-        <v>60.29999923706055</v>
-      </c>
-      <c r="M88">
-        <v>132.7802772224183</v>
-      </c>
-      <c r="N88">
-        <v>0</v>
-      </c>
-      <c r="O88">
-        <v>0</v>
-      </c>
-      <c r="P88">
-        <v>0</v>
-      </c>
-      <c r="Q88">
-        <v>0</v>
-      </c>
-      <c r="R88">
-        <v>0</v>
-      </c>
-      <c r="S88">
-        <v>0</v>
-      </c>
-      <c r="T88">
-        <v>3847000000</v>
-      </c>
-      <c r="U88">
-        <v>0</v>
-      </c>
-      <c r="V88" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="89" spans="1:22">
-      <c r="A89" t="s">
-        <v>109</v>
-      </c>
-      <c r="B89" t="s">
-        <v>120</v>
-      </c>
-      <c r="C89" t="s">
-        <v>172</v>
-      </c>
-      <c r="D89" t="s">
-        <v>224</v>
-      </c>
-      <c r="E89">
-        <v>69.5</v>
-      </c>
-      <c r="F89">
-        <v>1420840</v>
-      </c>
-      <c r="G89">
-        <v>62.20980003356934</v>
-      </c>
-      <c r="H89">
-        <v>56.32693328857422</v>
-      </c>
-      <c r="I89">
-        <v>53.14079992294312</v>
-      </c>
-      <c r="J89">
-        <v>50.7285499382019</v>
-      </c>
-      <c r="K89">
-        <v>0.1557042300701141</v>
-      </c>
-      <c r="L89">
-        <v>79.82826232910156</v>
-      </c>
-      <c r="M89">
-        <v>132.7059363108922</v>
-      </c>
-      <c r="N89">
-        <v>0.7</v>
-      </c>
-      <c r="O89">
-        <v>0.57</v>
-      </c>
-      <c r="P89">
-        <v>0.79</v>
-      </c>
-      <c r="Q89">
-        <v>0.92</v>
-      </c>
-      <c r="R89">
-        <v>480900000</v>
-      </c>
-      <c r="S89">
-        <v>129700000</v>
-      </c>
-      <c r="T89">
-        <v>152900000</v>
-      </c>
-      <c r="U89">
-        <v>493000000</v>
-      </c>
-      <c r="V89" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="90" spans="1:22">
-      <c r="A90" t="s">
-        <v>110</v>
-      </c>
-      <c r="B90" t="s">
-        <v>120</v>
-      </c>
-      <c r="C90" t="s">
-        <v>173</v>
-      </c>
-      <c r="D90" t="s">
-        <v>262</v>
-      </c>
-      <c r="E90">
-        <v>105.2300033569336</v>
-      </c>
-      <c r="F90">
-        <v>286210</v>
-      </c>
-      <c r="G90">
-        <v>95.62000015258789</v>
-      </c>
-      <c r="H90">
-        <v>85.45493362426758</v>
-      </c>
-      <c r="I90">
-        <v>81.27605020523072</v>
-      </c>
-      <c r="J90">
-        <v>79.04170022964477</v>
-      </c>
-      <c r="K90">
-        <v>12.27999973297119</v>
-      </c>
-      <c r="L90">
-        <v>108.4400024414062</v>
-      </c>
-      <c r="M90">
-        <v>132.6341144798291</v>
-      </c>
-      <c r="N90">
-        <v>1.22</v>
-      </c>
-      <c r="O90">
-        <v>0.78</v>
-      </c>
-      <c r="P90">
-        <v>2.17</v>
-      </c>
-      <c r="Q90">
-        <v>1.38</v>
-      </c>
-      <c r="R90">
-        <v>355000000</v>
-      </c>
-      <c r="S90">
-        <v>131000000</v>
-      </c>
-      <c r="T90">
-        <v>83000000</v>
-      </c>
-      <c r="U90">
-        <v>340000000</v>
-      </c>
-      <c r="V90" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="91" spans="1:22">
-      <c r="A91" t="s">
-        <v>111</v>
-      </c>
-      <c r="B91" t="s">
-        <v>120</v>
-      </c>
-      <c r="C91" t="s">
-        <v>135</v>
-      </c>
-      <c r="D91" t="s">
-        <v>263</v>
-      </c>
-      <c r="E91">
-        <v>419.489990234375</v>
-      </c>
-      <c r="F91">
-        <v>984203.3333333334</v>
-      </c>
-      <c r="G91">
-        <v>349.1213995361328</v>
-      </c>
-      <c r="H91">
-        <v>335.5441998291016</v>
-      </c>
-      <c r="I91">
-        <v>323.2082997131347</v>
-      </c>
-      <c r="J91">
-        <v>310.0965498352051</v>
-      </c>
-      <c r="K91">
-        <v>0.6462651491165161</v>
-      </c>
-      <c r="L91">
-        <v>427.5899963378906</v>
-      </c>
-      <c r="M91">
-        <v>132.6021110088814</v>
-      </c>
-      <c r="N91">
-        <v>3.36</v>
-      </c>
-      <c r="O91">
-        <v>2.92</v>
-      </c>
-      <c r="P91">
-        <v>2.58</v>
-      </c>
-      <c r="Q91">
-        <v>2.65</v>
-      </c>
-      <c r="R91">
-        <v>1377159000</v>
-      </c>
-      <c r="S91">
-        <v>285038000</v>
-      </c>
-      <c r="T91">
-        <v>292362000</v>
-      </c>
-      <c r="U91">
-        <v>1362446000</v>
-      </c>
-      <c r="V91" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="92" spans="1:22">
-      <c r="A92" t="s">
-        <v>112</v>
-      </c>
-      <c r="B92" t="s">
-        <v>123</v>
-      </c>
-      <c r="C92" t="s">
-        <v>174</v>
-      </c>
-      <c r="D92" t="s">
-        <v>264</v>
-      </c>
-      <c r="E92">
-        <v>52.27000045776367</v>
-      </c>
-      <c r="F92">
-        <v>1738190</v>
-      </c>
-      <c r="G92">
-        <v>43.03980003356934</v>
-      </c>
-      <c r="H92">
-        <v>40.49606671651205</v>
-      </c>
-      <c r="I92">
-        <v>39.40570006370545</v>
-      </c>
-      <c r="J92">
-        <v>37.5139000415802</v>
-      </c>
-      <c r="K92">
-        <v>20.39999961853027</v>
-      </c>
-      <c r="L92">
-        <v>52.36999893188477</v>
-      </c>
-      <c r="M92">
-        <v>132.5868141233705</v>
-      </c>
-      <c r="N92">
-        <v>0.74</v>
-      </c>
-      <c r="O92">
-        <v>0.41</v>
-      </c>
-      <c r="P92">
-        <v>0.92</v>
-      </c>
-      <c r="Q92">
-        <v>0.74</v>
-      </c>
-      <c r="R92">
-        <v>33585000</v>
-      </c>
-      <c r="S92">
-        <v>134962000</v>
-      </c>
-      <c r="T92">
-        <v>108063000</v>
-      </c>
-      <c r="U92">
-        <v>168948000</v>
-      </c>
-      <c r="V92" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="93" spans="1:22">
-      <c r="A93" t="s">
-        <v>113</v>
-      </c>
-      <c r="B93" t="s">
-        <v>121</v>
-      </c>
-      <c r="C93" t="s">
-        <v>175</v>
-      </c>
-      <c r="D93" t="s">
-        <v>265</v>
-      </c>
-      <c r="E93">
-        <v>108.7399978637695</v>
-      </c>
-      <c r="F93">
-        <v>1102046.666666667</v>
-      </c>
-      <c r="G93">
-        <v>96.09559982299805</v>
-      </c>
-      <c r="H93">
-        <v>89.58886637369791</v>
-      </c>
-      <c r="I93">
-        <v>83.74624977111816</v>
-      </c>
-      <c r="J93">
-        <v>81.35399982452392</v>
-      </c>
-      <c r="K93">
-        <v>0.02227001264691353</v>
-      </c>
-      <c r="L93">
-        <v>132.0598602294922</v>
-      </c>
-      <c r="M93">
-        <v>132.5513518035199</v>
-      </c>
-      <c r="N93">
-        <v>8</v>
-      </c>
-      <c r="O93">
-        <v>10.15</v>
-      </c>
-      <c r="P93">
-        <v>6.05</v>
-      </c>
-      <c r="Q93">
-        <v>10.35</v>
-      </c>
-      <c r="R93">
-        <v>6699364000</v>
-      </c>
-      <c r="S93">
-        <v>3952737000</v>
-      </c>
-      <c r="T93">
-        <v>6754634000</v>
-      </c>
-      <c r="U93">
-        <v>20337600000</v>
-      </c>
-      <c r="V93" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="94" spans="1:22">
-      <c r="A94" t="s">
-        <v>114</v>
-      </c>
-      <c r="B94" t="s">
-        <v>117</v>
-      </c>
-      <c r="C94" t="s">
-        <v>128</v>
-      </c>
-      <c r="D94" t="s">
-        <v>266</v>
-      </c>
-      <c r="E94">
-        <v>504.4800109863281</v>
-      </c>
-      <c r="F94">
-        <v>414890</v>
-      </c>
-      <c r="G94">
-        <v>420.98</v>
-      </c>
-      <c r="H94">
-        <v>391.4035001627604</v>
-      </c>
-      <c r="I94">
-        <v>387.5528250122071</v>
-      </c>
-      <c r="J94">
-        <v>377.9874749755859</v>
-      </c>
-      <c r="K94">
-        <v>19.76499938964844</v>
-      </c>
-      <c r="L94">
-        <v>548.4299926757812</v>
-      </c>
-      <c r="M94">
-        <v>132.4804150761046</v>
-      </c>
-      <c r="N94">
-        <v>-0.52</v>
-      </c>
-      <c r="O94">
-        <v>-4.26</v>
-      </c>
-      <c r="P94">
-        <v>-0.7</v>
-      </c>
-      <c r="Q94">
-        <v>-0.52</v>
-      </c>
-      <c r="R94">
-        <v>-709594000</v>
-      </c>
-      <c r="S94">
-        <v>-28871000</v>
-      </c>
-      <c r="T94">
-        <v>-94368000</v>
-      </c>
-      <c r="U94">
-        <v>-511278000</v>
-      </c>
-      <c r="V94" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/ScreenResult/ScreenResult.xlsx
+++ b/Screener/ScreenResult/ScreenResult.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="262">
   <si>
     <t>Symbol</t>
   </si>
@@ -91,241 +91,274 @@
     <t>VRT</t>
   </si>
   <si>
-    <t>INOD</t>
+    <t>DFH</t>
   </si>
   <si>
     <t>RXDX</t>
   </si>
   <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>FOR</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>AMPH</t>
+  </si>
+  <si>
+    <t>ELF</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>RXST</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
     <t>LI</t>
   </si>
   <si>
-    <t>CBAY</t>
-  </si>
-  <si>
-    <t>RXST</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>ELF</t>
-  </si>
-  <si>
-    <t>CAMT</t>
-  </si>
-  <si>
-    <t>AMPH</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>XPO</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>MHO</t>
-  </si>
-  <si>
-    <t>STRL</t>
+    <t>STVN</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>SAIA</t>
   </si>
   <si>
     <t>DICE</t>
   </si>
   <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>COCO</t>
+  </si>
+  <si>
+    <t>ROIV</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>ABCM</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>AEHR</t>
+  </si>
+  <si>
+    <t>PHM</t>
+  </si>
+  <si>
     <t>ACLS</t>
   </si>
   <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>ROIV</t>
-  </si>
-  <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>STVN</t>
-  </si>
-  <si>
-    <t>ABCM</t>
-  </si>
-  <si>
-    <t>AEHR</t>
-  </si>
-  <si>
-    <t>PHM</t>
+    <t>SOVO</t>
+  </si>
+  <si>
+    <t>TTD</t>
   </si>
   <si>
     <t>OC</t>
   </si>
   <si>
-    <t>TTD</t>
+    <t>PARR</t>
+  </si>
+  <si>
+    <t>LII</t>
   </si>
   <si>
     <t>GKOS</t>
   </si>
   <si>
+    <t>CLBR</t>
+  </si>
+  <si>
+    <t>EME</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>KBH</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>NUVL</t>
+  </si>
+  <si>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>ZGN</t>
+  </si>
+  <si>
+    <t>MTH</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>NYCB</t>
+  </si>
+  <si>
     <t>BECN</t>
   </si>
   <si>
-    <t>CLBR</t>
-  </si>
-  <si>
-    <t>LII</t>
-  </si>
-  <si>
-    <t>RDNT</t>
-  </si>
-  <si>
-    <t>NYCB</t>
-  </si>
-  <si>
-    <t>LEGN</t>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>TOL</t>
+  </si>
+  <si>
+    <t>MDC</t>
+  </si>
+  <si>
+    <t>ONTO</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>HCCI</t>
+  </si>
+  <si>
+    <t>BKNG</t>
+  </si>
+  <si>
+    <t>PNR</t>
+  </si>
+  <si>
+    <t>CRH</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>TPH</t>
+  </si>
+  <si>
+    <t>NVO</t>
+  </si>
+  <si>
+    <t>LRCX</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>CARR</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>PH</t>
+  </si>
+  <si>
+    <t>NVT</t>
+  </si>
+  <si>
+    <t>GMS</t>
+  </si>
+  <si>
+    <t>APG</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>TMHC</t>
+  </si>
+  <si>
+    <t>FDX</t>
+  </si>
+  <si>
+    <t>AEL</t>
   </si>
   <si>
     <t>ARCB</t>
   </si>
   <si>
-    <t>VIST</t>
-  </si>
-  <si>
-    <t>THO</t>
-  </si>
-  <si>
-    <t>FTAI</t>
-  </si>
-  <si>
-    <t>KBH</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>LPG</t>
-  </si>
-  <si>
-    <t>EME</t>
-  </si>
-  <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>NUVL</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>CARR</t>
-  </si>
-  <si>
-    <t>NTES</t>
-  </si>
-  <si>
-    <t>MTH</t>
-  </si>
-  <si>
-    <t>ONTO</t>
-  </si>
-  <si>
-    <t>ZGN</t>
+    <t>DVA</t>
+  </si>
+  <si>
+    <t>SUM</t>
+  </si>
+  <si>
+    <t>EXP</t>
+  </si>
+  <si>
+    <t>ODFL</t>
+  </si>
+  <si>
+    <t>TNET</t>
+  </si>
+  <si>
+    <t>DHI</t>
+  </si>
+  <si>
+    <t>ARGX</t>
+  </si>
+  <si>
+    <t>CRS</t>
+  </si>
+  <si>
+    <t>URBN</t>
+  </si>
+  <si>
+    <t>VMW</t>
+  </si>
+  <si>
+    <t>TBBK</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>DECK</t>
   </si>
   <si>
     <t>COOP</t>
   </si>
   <si>
-    <t>JBL</t>
-  </si>
-  <si>
-    <t>LRCX</t>
-  </si>
-  <si>
-    <t>APG</t>
-  </si>
-  <si>
-    <t>PNR</t>
-  </si>
-  <si>
-    <t>NVT</t>
-  </si>
-  <si>
-    <t>ARGX</t>
-  </si>
-  <si>
-    <t>PARR</t>
-  </si>
-  <si>
-    <t>TOL</t>
-  </si>
-  <si>
-    <t>MDC</t>
-  </si>
-  <si>
-    <t>PAG</t>
-  </si>
-  <si>
-    <t>PH</t>
-  </si>
-  <si>
-    <t>FDX</t>
-  </si>
-  <si>
-    <t>CSAN</t>
-  </si>
-  <si>
-    <t>TMHC</t>
-  </si>
-  <si>
-    <t>ODFL</t>
-  </si>
-  <si>
-    <t>TNET</t>
-  </si>
-  <si>
-    <t>AGRO</t>
-  </si>
-  <si>
     <t>ON</t>
   </si>
   <si>
-    <t>APO</t>
-  </si>
-  <si>
-    <t>BUR</t>
-  </si>
-  <si>
-    <t>GMS</t>
-  </si>
-  <si>
-    <t>URBN</t>
-  </si>
-  <si>
-    <t>DECK</t>
-  </si>
-  <si>
-    <t>CRH</t>
-  </si>
-  <si>
-    <t>IGT</t>
-  </si>
-  <si>
-    <t>TPH</t>
+    <t>ALSN</t>
   </si>
   <si>
     <t>Financial Services</t>
@@ -343,6 +376,9 @@
     <t>Healthcare</t>
   </si>
   <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
     <t>Consumer Defensive</t>
   </si>
   <si>
@@ -352,9 +388,6 @@
     <t>Energy</t>
   </si>
   <si>
-    <t>Communication Services</t>
-  </si>
-  <si>
     <t>Shell Companies</t>
   </si>
   <si>
@@ -364,43 +397,49 @@
     <t>Electrical Equipment &amp; Parts</t>
   </si>
   <si>
-    <t>Information Technology Services</t>
+    <t>Residential Construction</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Construction</t>
+  </si>
+  <si>
+    <t>Biotechnology</t>
+  </si>
+  <si>
+    <t>Auto Parts</t>
+  </si>
+  <si>
+    <t>Real Estate—Development</t>
+  </si>
+  <si>
+    <t>Trucking</t>
+  </si>
+  <si>
+    <t>Drug Manufacturers—Specialty &amp; Generic</t>
+  </si>
+  <si>
+    <t>Household &amp; Personal Products</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Semiconductor Equipment &amp; Materials</t>
+  </si>
+  <si>
+    <t>Medical Devices</t>
+  </si>
+  <si>
+    <t>Building Products &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Steel</t>
   </si>
   <si>
     <t>Auto Manufacturers</t>
   </si>
   <si>
-    <t>Biotechnology</t>
-  </si>
-  <si>
-    <t>Medical Devices</t>
-  </si>
-  <si>
-    <t>Semiconductors</t>
-  </si>
-  <si>
-    <t>Household &amp; Personal Products</t>
-  </si>
-  <si>
-    <t>Semiconductor Equipment &amp; Materials</t>
-  </si>
-  <si>
-    <t>Drug Manufacturers—Specialty &amp; Generic</t>
-  </si>
-  <si>
-    <t>Steel</t>
-  </si>
-  <si>
-    <t>Trucking</t>
-  </si>
-  <si>
-    <t>Building Products &amp; Equipment</t>
-  </si>
-  <si>
-    <t>Residential Construction</t>
-  </si>
-  <si>
-    <t>Engineering &amp; Construction</t>
+    <t>Medical Instruments &amp; Supplies</t>
   </si>
   <si>
     <t>Building Materials</t>
@@ -409,87 +448,84 @@
     <t>Oil &amp; Gas Equipment &amp; Services</t>
   </si>
   <si>
+    <t>Beverages—Non-Alcoholic</t>
+  </si>
+  <si>
     <t>Travel Services</t>
   </si>
   <si>
-    <t>Medical Instruments &amp; Supplies</t>
+    <t>Rental &amp; Leasing Services</t>
+  </si>
+  <si>
+    <t>Packaged Foods</t>
   </si>
   <si>
     <t>Software—Application</t>
   </si>
   <si>
+    <t>Oil &amp; Gas Refining &amp; Marketing</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas E&amp;P</t>
+  </si>
+  <si>
+    <t>Drug Manufacturers—General</t>
+  </si>
+  <si>
     <t>Industrial Distribution</t>
   </si>
   <si>
-    <t>Diagnostics &amp; Research</t>
+    <t>Software—Infrastructure</t>
+  </si>
+  <si>
+    <t>Apparel Manufacturing</t>
   </si>
   <si>
     <t>Banks—Regional</t>
   </si>
   <si>
-    <t>Oil &amp; Gas E&amp;P</t>
-  </si>
-  <si>
-    <t>Recreational Vehicles</t>
-  </si>
-  <si>
-    <t>Rental &amp; Leasing Services</t>
-  </si>
-  <si>
-    <t>Software—Infrastructure</t>
+    <t>Oil &amp; Gas Drilling</t>
   </si>
   <si>
     <t>Oil &amp; Gas Midstream</t>
   </si>
   <si>
-    <t>Oil &amp; Gas Drilling</t>
+    <t>Waste Management</t>
+  </si>
+  <si>
+    <t>Specialty Industrial Machinery</t>
+  </si>
+  <si>
+    <t>Internet Retail</t>
+  </si>
+  <si>
+    <t>Electronic Components</t>
+  </si>
+  <si>
+    <t>Integrated Freight &amp; Logistics</t>
   </si>
   <si>
     <t>Insurance—Life</t>
   </si>
   <si>
-    <t>Electronic Gaming &amp; Multimedia</t>
-  </si>
-  <si>
-    <t>Apparel Manufacturing</t>
+    <t>Medical Care Facilities</t>
+  </si>
+  <si>
+    <t>Staffing &amp; Employment Services</t>
+  </si>
+  <si>
+    <t>Metal Fabrication</t>
+  </si>
+  <si>
+    <t>Apparel Retail</t>
+  </si>
+  <si>
+    <t>Footwear &amp; Accessories</t>
   </si>
   <si>
     <t>Mortgage Finance</t>
   </si>
   <si>
-    <t>Electronic Components</t>
-  </si>
-  <si>
-    <t>Specialty Industrial Machinery</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Refining &amp; Marketing</t>
-  </si>
-  <si>
-    <t>Auto &amp; Truck Dealerships</t>
-  </si>
-  <si>
-    <t>Integrated Freight &amp; Logistics</t>
-  </si>
-  <si>
-    <t>Staffing &amp; Employment Services</t>
-  </si>
-  <si>
-    <t>Farm Products</t>
-  </si>
-  <si>
-    <t>Asset Management</t>
-  </si>
-  <si>
-    <t>Apparel Retail</t>
-  </si>
-  <si>
-    <t>Footwear &amp; Accessories</t>
-  </si>
-  <si>
-    <t>Gambling</t>
-  </si>
-  <si>
     <t>2021-04-30</t>
   </si>
   <si>
@@ -499,238 +535,265 @@
     <t>2018-08-02</t>
   </si>
   <si>
-    <t>1993-08-10</t>
+    <t>2021-01-21</t>
   </si>
   <si>
     <t>2021-03-12</t>
   </si>
   <si>
+    <t>1991-07-12</t>
+  </si>
+  <si>
+    <t>2014-02-03</t>
+  </si>
+  <si>
+    <t>1982-09-20</t>
+  </si>
+  <si>
+    <t>2007-12-13</t>
+  </si>
+  <si>
+    <t>2003-10-07</t>
+  </si>
+  <si>
+    <t>2014-06-25</t>
+  </si>
+  <si>
+    <t>2016-09-22</t>
+  </si>
+  <si>
+    <t>1999-01-22</t>
+  </si>
+  <si>
+    <t>2000-07-28</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>2005-06-28</t>
+  </si>
+  <si>
+    <t>1994-10-14</t>
+  </si>
+  <si>
+    <t>1993-11-03</t>
+  </si>
+  <si>
     <t>2020-07-30</t>
   </si>
   <si>
-    <t>2014-02-03</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>1999-01-22</t>
-  </si>
-  <si>
-    <t>2016-09-22</t>
-  </si>
-  <si>
-    <t>2000-07-28</t>
-  </si>
-  <si>
-    <t>2014-06-25</t>
-  </si>
-  <si>
-    <t>1994-10-14</t>
-  </si>
-  <si>
-    <t>2003-10-07</t>
-  </si>
-  <si>
-    <t>2005-06-28</t>
-  </si>
-  <si>
-    <t>1993-11-03</t>
-  </si>
-  <si>
-    <t>1991-07-12</t>
+    <t>2021-07-16</t>
+  </si>
+  <si>
+    <t>2013-02-06</t>
+  </si>
+  <si>
+    <t>2002-09-11</t>
   </si>
   <si>
     <t>2021-09-15</t>
   </si>
   <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>2021-10-21</t>
+  </si>
+  <si>
+    <t>2020-12-08</t>
+  </si>
+  <si>
+    <t>1993-04-28</t>
+  </si>
+  <si>
+    <t>2020-10-22</t>
+  </si>
+  <si>
+    <t>2015-05-14</t>
+  </si>
+  <si>
+    <t>1997-08-15</t>
+  </si>
+  <si>
+    <t>1980-03-17</t>
+  </si>
+  <si>
     <t>2000-07-11</t>
   </si>
   <si>
-    <t>2002-09-11</t>
-  </si>
-  <si>
-    <t>2020-12-08</t>
-  </si>
-  <si>
-    <t>2013-02-06</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>1993-04-28</t>
-  </si>
-  <si>
-    <t>2021-07-16</t>
-  </si>
-  <si>
-    <t>2020-10-22</t>
-  </si>
-  <si>
-    <t>1997-08-15</t>
-  </si>
-  <si>
-    <t>1980-03-17</t>
+    <t>2021-09-23</t>
+  </si>
+  <si>
+    <t>2016-09-21</t>
   </si>
   <si>
     <t>2006-11-01</t>
   </si>
   <si>
-    <t>2016-09-21</t>
+    <t>2012-09-05</t>
+  </si>
+  <si>
+    <t>1999-07-29</t>
   </si>
   <si>
     <t>2015-06-25</t>
   </si>
   <si>
+    <t>2021-07-07</t>
+  </si>
+  <si>
+    <t>1995-01-10</t>
+  </si>
+  <si>
+    <t>2019-07-26</t>
+  </si>
+  <si>
+    <t>1986-08-01</t>
+  </si>
+  <si>
+    <t>2009-08-06</t>
+  </si>
+  <si>
+    <t>1972-06-01</t>
+  </si>
+  <si>
+    <t>2021-07-29</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>1986-08-13</t>
+  </si>
+  <si>
+    <t>2021-12-20</t>
+  </si>
+  <si>
+    <t>1988-07-26</t>
+  </si>
+  <si>
+    <t>1993-11-23</t>
+  </si>
+  <si>
     <t>2004-09-23</t>
   </si>
   <si>
-    <t>2021-07-07</t>
-  </si>
-  <si>
-    <t>1999-07-29</t>
-  </si>
-  <si>
-    <t>1997-01-03</t>
-  </si>
-  <si>
-    <t>1993-11-23</t>
-  </si>
-  <si>
-    <t>2020-06-05</t>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>1986-07-08</t>
+  </si>
+  <si>
+    <t>1980-03-11</t>
+  </si>
+  <si>
+    <t>2019-10-28</t>
+  </si>
+  <si>
+    <t>2014-05-08</t>
+  </si>
+  <si>
+    <t>2008-03-12</t>
+  </si>
+  <si>
+    <t>1999-03-31</t>
+  </si>
+  <si>
+    <t>1973-05-03</t>
+  </si>
+  <si>
+    <t>1989-07-13</t>
+  </si>
+  <si>
+    <t>2016-08-17</t>
+  </si>
+  <si>
+    <t>2013-01-31</t>
+  </si>
+  <si>
+    <t>1981-04-30</t>
+  </si>
+  <si>
+    <t>1984-05-04</t>
+  </si>
+  <si>
+    <t>1997-05-15</t>
+  </si>
+  <si>
+    <t>2020-03-19</t>
+  </si>
+  <si>
+    <t>1993-05-03</t>
+  </si>
+  <si>
+    <t>2018-04-24</t>
+  </si>
+  <si>
+    <t>2016-05-26</t>
+  </si>
+  <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
+    <t>2013-04-10</t>
+  </si>
+  <si>
+    <t>1978-04-12</t>
+  </si>
+  <si>
+    <t>2003-12-04</t>
   </si>
   <si>
     <t>1992-05-13</t>
   </si>
   <si>
-    <t>2019-07-26</t>
-  </si>
-  <si>
-    <t>1984-01-10</t>
-  </si>
-  <si>
-    <t>2015-05-14</t>
-  </si>
-  <si>
-    <t>1986-08-01</t>
-  </si>
-  <si>
-    <t>2009-08-06</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>1986-08-13</t>
-  </si>
-  <si>
-    <t>2014-05-08</t>
-  </si>
-  <si>
-    <t>1995-01-10</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>2021-07-29</t>
-  </si>
-  <si>
-    <t>2003-12-04</t>
-  </si>
-  <si>
-    <t>2020-03-19</t>
-  </si>
-  <si>
-    <t>2000-06-30</t>
-  </si>
-  <si>
-    <t>1988-07-26</t>
-  </si>
-  <si>
-    <t>2019-10-28</t>
-  </si>
-  <si>
-    <t>2021-12-20</t>
+    <t>1995-10-31</t>
+  </si>
+  <si>
+    <t>2015-03-12</t>
+  </si>
+  <si>
+    <t>1994-04-12</t>
+  </si>
+  <si>
+    <t>1991-10-24</t>
+  </si>
+  <si>
+    <t>2014-03-27</t>
+  </si>
+  <si>
+    <t>1992-06-05</t>
+  </si>
+  <si>
+    <t>2017-05-18</t>
+  </si>
+  <si>
+    <t>1973-02-21</t>
+  </si>
+  <si>
+    <t>1993-11-09</t>
+  </si>
+  <si>
+    <t>2007-08-15</t>
+  </si>
+  <si>
+    <t>2004-02-03</t>
+  </si>
+  <si>
+    <t>1997-12-18</t>
+  </si>
+  <si>
+    <t>1993-10-15</t>
   </si>
   <si>
     <t>2012-03-28</t>
   </si>
   <si>
-    <t>1993-05-03</t>
-  </si>
-  <si>
-    <t>1984-05-04</t>
-  </si>
-  <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
-    <t>1973-05-03</t>
-  </si>
-  <si>
-    <t>2018-04-24</t>
-  </si>
-  <si>
-    <t>2017-05-18</t>
-  </si>
-  <si>
-    <t>2012-09-05</t>
-  </si>
-  <si>
-    <t>1986-07-08</t>
-  </si>
-  <si>
-    <t>1980-03-11</t>
-  </si>
-  <si>
-    <t>1996-10-23</t>
-  </si>
-  <si>
-    <t>1978-04-12</t>
-  </si>
-  <si>
-    <t>2021-03-08</t>
-  </si>
-  <si>
-    <t>2013-04-10</t>
-  </si>
-  <si>
-    <t>1991-10-24</t>
-  </si>
-  <si>
-    <t>2014-03-27</t>
-  </si>
-  <si>
-    <t>2011-01-28</t>
-  </si>
-  <si>
     <t>2000-05-02</t>
   </si>
   <si>
-    <t>2011-03-30</t>
-  </si>
-  <si>
-    <t>2020-10-19</t>
-  </si>
-  <si>
-    <t>2016-05-26</t>
-  </si>
-  <si>
-    <t>1993-11-09</t>
-  </si>
-  <si>
-    <t>1993-10-15</t>
-  </si>
-  <si>
-    <t>1989-07-13</t>
-  </si>
-  <si>
-    <t>1990-03-26</t>
-  </si>
-  <si>
-    <t>2013-01-31</t>
+    <t>2012-03-15</t>
   </si>
   <si>
     <t>F</t>
@@ -1094,7 +1157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V83"/>
+  <dimension ref="A1:V94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
@@ -1170,31 +1233,31 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D2" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="E2">
-        <v>42.2400016784668</v>
+        <v>42.27000045776367</v>
       </c>
       <c r="F2">
-        <v>523787.1333333334</v>
+        <v>541610</v>
       </c>
       <c r="G2">
-        <v>14.48171987533569</v>
+        <v>16.50261980056763</v>
       </c>
       <c r="H2">
-        <v>11.59568663914998</v>
+        <v>12.2728199450175</v>
       </c>
       <c r="I2">
-        <v>11.1895049905777</v>
+        <v>11.69967997074127</v>
       </c>
       <c r="J2">
-        <v>10.11328000068665</v>
+        <v>10.12095499515534</v>
       </c>
       <c r="K2">
         <v>9.789999961853027</v>
@@ -1203,34 +1266,34 @@
         <v>49.58000183105469</v>
       </c>
       <c r="M2">
-        <v>428.7292142613572</v>
+        <v>414.7981944984094</v>
       </c>
       <c r="N2">
+        <v>0.051392</v>
+      </c>
+      <c r="O2">
+        <v>-0.03</v>
+      </c>
+      <c r="P2">
         <v>-0.01</v>
       </c>
-      <c r="O2">
-        <v>0.05</v>
-      </c>
-      <c r="P2">
-        <v>-0.03</v>
-      </c>
       <c r="Q2">
-        <v>-0.01</v>
+        <v>-0.094594</v>
       </c>
       <c r="R2">
-        <v>1785906</v>
+        <v>-965634</v>
       </c>
       <c r="S2">
-        <v>-965634</v>
+        <v>6905230</v>
       </c>
       <c r="T2">
-        <v>6905230</v>
+        <v>-127955</v>
       </c>
       <c r="U2">
-        <v>-127955</v>
+        <v>-831131</v>
       </c>
       <c r="V2" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -1238,40 +1301,40 @@
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D3" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="E3">
-        <v>320.2731018066406</v>
+        <v>347.3999938964844</v>
       </c>
       <c r="F3">
-        <v>2764303.466666667</v>
+        <v>2840063.333333333</v>
       </c>
       <c r="G3">
-        <v>260.453861694336</v>
+        <v>270.5203994750976</v>
       </c>
       <c r="H3">
-        <v>153.9570870463053</v>
+        <v>159.2577996317546</v>
       </c>
       <c r="I3">
-        <v>135.3677152633667</v>
+        <v>139.7309497070312</v>
       </c>
       <c r="J3">
-        <v>110.3886998939514</v>
+        <v>113.5491499710083</v>
       </c>
       <c r="K3">
         <v>3.849999904632568</v>
       </c>
       <c r="L3">
-        <v>337.5599975585938</v>
+        <v>353.2900085449219</v>
       </c>
       <c r="M3">
-        <v>272.1951199024072</v>
+        <v>286.4049839345308</v>
       </c>
       <c r="N3">
         <v>2.6</v>
@@ -1298,7 +1361,7 @@
         <v>85846000</v>
       </c>
       <c r="V3" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -1306,67 +1369,67 @@
         <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="E4">
-        <v>34.29000091552734</v>
+        <v>36.22000122070312</v>
       </c>
       <c r="F4">
-        <v>5861290</v>
+        <v>6582323.333333333</v>
       </c>
       <c r="G4">
-        <v>23.3276000213623</v>
+        <v>24.8196000289917</v>
       </c>
       <c r="H4">
-        <v>17.33913334528605</v>
+        <v>17.93933335622152</v>
       </c>
       <c r="I4">
-        <v>16.43260001659393</v>
+        <v>16.92355002880096</v>
       </c>
       <c r="J4">
-        <v>14.91379999637604</v>
+        <v>15.1669499874115</v>
       </c>
       <c r="K4">
         <v>5.564881324768066</v>
       </c>
       <c r="L4">
-        <v>34.29000091552734</v>
+        <v>36.22000122070312</v>
       </c>
       <c r="M4">
-        <v>214.6132208388158</v>
+        <v>228.1172065735038</v>
       </c>
       <c r="N4">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="O4">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="P4">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="Q4">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="R4">
-        <v>20300000</v>
+        <v>21200000</v>
       </c>
       <c r="S4">
-        <v>21200000</v>
+        <v>26600000</v>
       </c>
       <c r="T4">
-        <v>26600000</v>
+        <v>50300000</v>
       </c>
       <c r="U4">
-        <v>50300000</v>
+        <v>83200000</v>
       </c>
       <c r="V4" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -1374,67 +1437,67 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D5" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="E5">
-        <v>11.87849998474121</v>
+        <v>30.48999977111816</v>
       </c>
       <c r="F5">
-        <v>620152.1666666666</v>
+        <v>331650</v>
       </c>
       <c r="G5">
-        <v>11.33876996994019</v>
+        <v>23.86120002746582</v>
       </c>
       <c r="H5">
-        <v>8.023989993731181</v>
+        <v>16.75259998957316</v>
       </c>
       <c r="I5">
-        <v>6.808692495822907</v>
+        <v>15.02200000286102</v>
       </c>
       <c r="J5">
-        <v>5.94755000948906</v>
+        <v>13.47445001602173</v>
       </c>
       <c r="K5">
-        <v>0.09375</v>
+        <v>8.369999885559082</v>
       </c>
       <c r="L5">
-        <v>13.5</v>
+        <v>34</v>
       </c>
       <c r="M5">
-        <v>201.7373700215835</v>
+        <v>216.2559771279986</v>
       </c>
       <c r="N5">
-        <v>-0.14</v>
+        <v>0.64</v>
       </c>
       <c r="O5">
-        <v>-0.12</v>
+        <v>0.78</v>
       </c>
       <c r="P5">
-        <v>-0.07000000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="Q5">
-        <v>-0.08</v>
+        <v>0.65</v>
       </c>
       <c r="R5">
-        <v>-3833000</v>
+        <v>69641000</v>
       </c>
       <c r="S5">
-        <v>-3327000</v>
+        <v>86332000</v>
       </c>
       <c r="T5">
-        <v>-1960000</v>
+        <v>49089000</v>
       </c>
       <c r="U5">
-        <v>-2116000</v>
+        <v>68764000</v>
       </c>
       <c r="V5" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1442,7 +1505,7 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="E6">
         <v>199.9199981689453</v>
@@ -1469,7 +1532,7 @@
         <v>199.9199981689453</v>
       </c>
       <c r="M6">
-        <v>201.2990990610614</v>
+        <v>210.7611920516861</v>
       </c>
       <c r="N6">
         <v>-0.86</v>
@@ -1496,7 +1559,7 @@
         <v>-40876000</v>
       </c>
       <c r="V6" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1504,67 +1567,67 @@
         <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="D7" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E7">
-        <v>44.40000152587891</v>
+        <v>75.58000183105469</v>
       </c>
       <c r="F7">
-        <v>6596970</v>
+        <v>374306.6666666667</v>
       </c>
       <c r="G7">
-        <v>34.74059997558594</v>
+        <v>55.88160003662109</v>
       </c>
       <c r="H7">
-        <v>27.53183330535889</v>
+        <v>43.75146671295166</v>
       </c>
       <c r="I7">
-        <v>25.29739999294281</v>
+        <v>40.55170001983642</v>
       </c>
       <c r="J7">
-        <v>23.74369999408722</v>
+        <v>36.80184999465942</v>
       </c>
       <c r="K7">
-        <v>13.61999988555908</v>
+        <v>0.4209107160568237</v>
       </c>
       <c r="L7">
-        <v>44.40000152587891</v>
+        <v>75.58000183105469</v>
       </c>
       <c r="M7">
-        <v>192.442073150157</v>
+        <v>187.2934803997703</v>
       </c>
       <c r="N7">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="O7">
-        <v>-0.64</v>
+        <v>1.03</v>
       </c>
       <c r="P7">
-        <v>0.26</v>
+        <v>0.64</v>
       </c>
       <c r="Q7">
-        <v>0.9</v>
+        <v>1.27</v>
       </c>
       <c r="R7">
-        <v>-617966000</v>
+        <v>29523000</v>
       </c>
       <c r="S7">
-        <v>-1640321000</v>
+        <v>31725000</v>
       </c>
       <c r="T7">
-        <v>256938000</v>
+        <v>19649000</v>
       </c>
       <c r="U7">
-        <v>929668000</v>
+        <v>39480000</v>
       </c>
       <c r="V7" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1572,31 +1635,31 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D8" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="E8">
-        <v>12.32999992370605</v>
+        <v>12.39999961853027</v>
       </c>
       <c r="F8">
-        <v>2501457.833333333</v>
+        <v>2001853.333333333</v>
       </c>
       <c r="G8">
-        <v>10.11659999847412</v>
+        <v>10.34180000305176</v>
       </c>
       <c r="H8">
-        <v>9.072833353678385</v>
+        <v>9.199900019963582</v>
       </c>
       <c r="I8">
-        <v>7.743275017738342</v>
+        <v>7.877575018405914</v>
       </c>
       <c r="J8">
-        <v>6.915375020503998</v>
+        <v>7.022925016880035</v>
       </c>
       <c r="K8">
         <v>0.9279999732971191</v>
@@ -1605,7 +1668,7 @@
         <v>15.15999984741211</v>
       </c>
       <c r="M8">
-        <v>185.7454276117793</v>
+        <v>183.7362501843911</v>
       </c>
       <c r="N8">
         <v>-0.31</v>
@@ -1632,7 +1695,7 @@
         <v>-28778000</v>
       </c>
       <c r="V8" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1640,67 +1703,67 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D9" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="E9">
-        <v>32.75</v>
+        <v>45.83000183105469</v>
       </c>
       <c r="F9">
-        <v>409280</v>
+        <v>612536.6666666666</v>
       </c>
       <c r="G9">
-        <v>28.42529987335205</v>
+        <v>34.23880023956299</v>
       </c>
       <c r="H9">
-        <v>19.95229995091756</v>
+        <v>26.28233337402344</v>
       </c>
       <c r="I9">
-        <v>18.06062496185303</v>
+        <v>24.65300003528595</v>
       </c>
       <c r="J9">
-        <v>16.03497498512268</v>
+        <v>22.20725002288818</v>
       </c>
       <c r="K9">
-        <v>8.970000267028809</v>
+        <v>0.5703791379928589</v>
       </c>
       <c r="L9">
-        <v>33.36999893188477</v>
+        <v>45.83000183105469</v>
       </c>
       <c r="M9">
-        <v>185.008419431494</v>
+        <v>182.7092600818787</v>
       </c>
       <c r="N9">
-        <v>-0.61</v>
+        <v>0.46</v>
       </c>
       <c r="O9">
-        <v>-0.61</v>
+        <v>0.46</v>
       </c>
       <c r="P9">
-        <v>-0.5600000000000001</v>
+        <v>1.69</v>
       </c>
       <c r="Q9">
-        <v>-0.42</v>
+        <v>0.85</v>
       </c>
       <c r="R9">
-        <v>-16732000</v>
+        <v>24400000</v>
       </c>
       <c r="S9">
-        <v>-16818000</v>
+        <v>24500000</v>
       </c>
       <c r="T9">
-        <v>-15610000</v>
+        <v>89900000</v>
       </c>
       <c r="U9">
-        <v>-13212000</v>
+        <v>44800000</v>
       </c>
       <c r="V9" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1708,67 +1771,67 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D10" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="E10">
-        <v>442.6900024414062</v>
+        <v>30.94000053405762</v>
       </c>
       <c r="F10">
-        <v>44391006.66666666</v>
+        <v>251216.6666666667</v>
       </c>
       <c r="G10">
-        <v>418.5320001220703</v>
+        <v>23.91540000915527</v>
       </c>
       <c r="H10">
-        <v>296.2395329793295</v>
+        <v>18.74906671524048</v>
       </c>
       <c r="I10">
-        <v>259.9660498046875</v>
+        <v>17.50595004558563</v>
       </c>
       <c r="J10">
-        <v>227.4331500244141</v>
+        <v>15.85880003452301</v>
       </c>
       <c r="K10">
-        <v>0.3134739995002747</v>
+        <v>2.950000047683716</v>
       </c>
       <c r="L10">
-        <v>474.9400024414062</v>
+        <v>31.03000068664551</v>
       </c>
       <c r="M10">
-        <v>175.1944072066</v>
+        <v>181.8520538734474</v>
       </c>
       <c r="N10">
-        <v>0.26</v>
+        <v>1.02</v>
       </c>
       <c r="O10">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="P10">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="Q10">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="R10">
-        <v>656000000</v>
+        <v>50800000</v>
       </c>
       <c r="S10">
-        <v>680000000</v>
+        <v>20800000</v>
       </c>
       <c r="T10">
-        <v>1414000000</v>
+        <v>26900000</v>
       </c>
       <c r="U10">
-        <v>2043000000</v>
+        <v>46800000</v>
       </c>
       <c r="V10" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1776,67 +1839,67 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="D11" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E11">
-        <v>133.1900024414062</v>
+        <v>73.05999755859375</v>
       </c>
       <c r="F11">
-        <v>1136150</v>
+        <v>2332623.333333333</v>
       </c>
       <c r="G11">
-        <v>109.0258001708984</v>
+        <v>58.73259994506836</v>
       </c>
       <c r="H11">
-        <v>85.98039995829264</v>
+        <v>44.96326669057211</v>
       </c>
       <c r="I11">
-        <v>77.04499992370606</v>
+        <v>42.46587018013</v>
       </c>
       <c r="J11">
-        <v>69.4314499092102</v>
+        <v>38.50670632362366</v>
       </c>
       <c r="K11">
-        <v>7.300000190734863</v>
+        <v>0.6502050161361694</v>
       </c>
       <c r="L11">
-        <v>133.1900024414062</v>
+        <v>73.05999755859375</v>
       </c>
       <c r="M11">
-        <v>174.9091188014804</v>
+        <v>179.9528708860766</v>
       </c>
       <c r="N11">
-        <v>0.27</v>
+        <v>1.13</v>
       </c>
       <c r="O11">
-        <v>0.21</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P11">
-        <v>0.34</v>
+        <v>0.13</v>
       </c>
       <c r="Q11">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="R11">
-        <v>14469000</v>
+        <v>131000000</v>
       </c>
       <c r="S11">
-        <v>11710000</v>
+        <v>-94000000</v>
       </c>
       <c r="T11">
-        <v>19105000</v>
+        <v>14000000</v>
       </c>
       <c r="U11">
-        <v>16246000</v>
+        <v>33000000</v>
       </c>
       <c r="V11" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1844,67 +1907,67 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="D12" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="E12">
-        <v>47.06000137329102</v>
+        <v>65</v>
       </c>
       <c r="F12">
-        <v>300010.1666666667</v>
+        <v>358823.3333333333</v>
       </c>
       <c r="G12">
-        <v>35.89179992675781</v>
+        <v>55.30579986572265</v>
       </c>
       <c r="H12">
-        <v>29.61733334859212</v>
+        <v>42.23106657663981</v>
       </c>
       <c r="I12">
-        <v>28.00144999504089</v>
+        <v>38.95714993476868</v>
       </c>
       <c r="J12">
-        <v>26.12255000114441</v>
+        <v>35.74529993057251</v>
       </c>
       <c r="K12">
-        <v>0.2220596075057983</v>
+        <v>8.689999580383301</v>
       </c>
       <c r="L12">
-        <v>48.31999969482422</v>
+        <v>65</v>
       </c>
       <c r="M12">
-        <v>173.7016879582047</v>
+        <v>176.5697582215314</v>
       </c>
       <c r="N12">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="O12">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="P12">
-        <v>0.36</v>
+        <v>0.66</v>
       </c>
       <c r="Q12">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="R12">
-        <v>20715000</v>
+        <v>17346000</v>
       </c>
       <c r="S12">
-        <v>21673000</v>
+        <v>15874000</v>
       </c>
       <c r="T12">
-        <v>17245000</v>
+        <v>33913000</v>
       </c>
       <c r="U12">
-        <v>18539000</v>
+        <v>26032000</v>
       </c>
       <c r="V12" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1912,67 +1975,67 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="D13" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="E13">
-        <v>63.25</v>
+        <v>131.5299987792969</v>
       </c>
       <c r="F13">
-        <v>386060.3666666666</v>
+        <v>1126750</v>
       </c>
       <c r="G13">
-        <v>54.12839973449707</v>
+        <v>112.2473999023437</v>
       </c>
       <c r="H13">
-        <v>41.52266653696696</v>
+        <v>87.98433319091797</v>
       </c>
       <c r="I13">
-        <v>38.44569990158081</v>
+        <v>78.84369985580445</v>
       </c>
       <c r="J13">
-        <v>35.329049949646</v>
+        <v>70.87499988555908</v>
       </c>
       <c r="K13">
-        <v>8.689999580383301</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="L13">
-        <v>63.25</v>
+        <v>133.1900024414062</v>
       </c>
       <c r="M13">
-        <v>172.559088590271</v>
+        <v>176.3934583053485</v>
       </c>
       <c r="N13">
-        <v>0.33</v>
+        <v>0.21</v>
       </c>
       <c r="O13">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="P13">
-        <v>0.66</v>
+        <v>0.29</v>
       </c>
       <c r="Q13">
-        <v>0.5</v>
+        <v>0.93</v>
       </c>
       <c r="R13">
-        <v>17346000</v>
+        <v>11710000</v>
       </c>
       <c r="S13">
-        <v>15874000</v>
+        <v>19105000</v>
       </c>
       <c r="T13">
-        <v>33913000</v>
+        <v>16246000</v>
       </c>
       <c r="U13">
-        <v>26032000</v>
+        <v>52977000</v>
       </c>
       <c r="V13" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1980,67 +2043,67 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="D14" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="E14">
-        <v>113.5</v>
+        <v>446.6400146484375</v>
       </c>
       <c r="F14">
-        <v>525799.7333333333</v>
+        <v>42533890</v>
       </c>
       <c r="G14">
-        <v>85.52700012207032</v>
+        <v>428.3108001708985</v>
       </c>
       <c r="H14">
-        <v>71.87653330485026</v>
+        <v>304.3663330078125</v>
       </c>
       <c r="I14">
-        <v>66.6894499206543</v>
+        <v>266.5731998825073</v>
       </c>
       <c r="J14">
-        <v>60.40894987106324</v>
+        <v>233.241849899292</v>
       </c>
       <c r="K14">
-        <v>5.792013168334961</v>
+        <v>0.3134739995002747</v>
       </c>
       <c r="L14">
-        <v>132.4752044677734</v>
+        <v>474.9400024414062</v>
       </c>
       <c r="M14">
-        <v>171.6050524420866</v>
+        <v>176.3421800122788</v>
       </c>
       <c r="N14">
-        <v>2394.25</v>
+        <v>0.26</v>
       </c>
       <c r="O14">
-        <v>4830.25</v>
+        <v>0.27</v>
       </c>
       <c r="P14">
-        <v>1680.75</v>
+        <v>0.57</v>
       </c>
       <c r="Q14">
-        <v>2394.25</v>
+        <v>0.82</v>
       </c>
       <c r="R14">
-        <v>1588430000000</v>
+        <v>656000000</v>
       </c>
       <c r="S14">
-        <v>509914000000</v>
+        <v>680000000</v>
       </c>
       <c r="T14">
-        <v>-665869000000</v>
+        <v>1414000000</v>
       </c>
       <c r="U14">
-        <v>726419000000</v>
+        <v>2043000000</v>
       </c>
       <c r="V14" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2048,67 +2111,67 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C15" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="D15" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="E15">
-        <v>68.29000091552734</v>
+        <v>47.47999954223633</v>
       </c>
       <c r="F15">
-        <v>2247446.666666667</v>
+        <v>317286.6666666667</v>
       </c>
       <c r="G15">
-        <v>56.81000007629395</v>
+        <v>37.07279991149903</v>
       </c>
       <c r="H15">
-        <v>43.96980007171631</v>
+        <v>30.13060001373291</v>
       </c>
       <c r="I15">
-        <v>41.59836042404175</v>
+        <v>28.37784998893738</v>
       </c>
       <c r="J15">
-        <v>37.87534955978393</v>
+        <v>26.25704998970032</v>
       </c>
       <c r="K15">
-        <v>0.6502050161361694</v>
+        <v>0.2220596075057983</v>
       </c>
       <c r="L15">
-        <v>71.65000152587891</v>
+        <v>48.31999969482422</v>
       </c>
       <c r="M15">
-        <v>169.5139099417947</v>
+        <v>171.3834076715913</v>
       </c>
       <c r="N15">
-        <v>1.22</v>
+        <v>0.43</v>
       </c>
       <c r="O15">
-        <v>1.13</v>
+        <v>0.45</v>
       </c>
       <c r="P15">
-        <v>-0.8100000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="Q15">
-        <v>0.13</v>
+        <v>0.38</v>
       </c>
       <c r="R15">
-        <v>141000000</v>
+        <v>20715000</v>
       </c>
       <c r="S15">
-        <v>131000000</v>
+        <v>21673000</v>
       </c>
       <c r="T15">
-        <v>-94000000</v>
+        <v>17245000</v>
       </c>
       <c r="U15">
-        <v>14000000</v>
+        <v>18539000</v>
       </c>
       <c r="V15" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -2116,67 +2179,67 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C16" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="D16" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="E16">
-        <v>148.6399993896484</v>
+        <v>29.6299991607666</v>
       </c>
       <c r="F16">
-        <v>1554080</v>
+        <v>450613.3333333333</v>
       </c>
       <c r="G16">
-        <v>130.8109997558594</v>
+        <v>28.76209987640381</v>
       </c>
       <c r="H16">
-        <v>101.0099329884847</v>
+        <v>20.43576661427816</v>
       </c>
       <c r="I16">
-        <v>91.29804977416993</v>
+        <v>18.44777495861053</v>
       </c>
       <c r="J16">
-        <v>83.15909984588623</v>
+        <v>16.39802498340607</v>
       </c>
       <c r="K16">
-        <v>0.8299999833106995</v>
+        <v>8.970000267028809</v>
       </c>
       <c r="L16">
-        <v>148.6399993896484</v>
+        <v>33.36999893188477</v>
       </c>
       <c r="M16">
-        <v>166.479777541394</v>
+        <v>171.3610885443715</v>
       </c>
       <c r="N16">
-        <v>5.75</v>
+        <v>-0.61</v>
       </c>
       <c r="O16">
-        <v>4.72</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="P16">
-        <v>2.41</v>
+        <v>-0.42</v>
       </c>
       <c r="Q16">
-        <v>3.16</v>
+        <v>-0.4</v>
       </c>
       <c r="R16">
-        <v>738007000</v>
+        <v>-16818000</v>
       </c>
       <c r="S16">
-        <v>384513000</v>
+        <v>-15610000</v>
       </c>
       <c r="T16">
-        <v>333786000</v>
+        <v>-13212000</v>
       </c>
       <c r="U16">
-        <v>404619000</v>
+        <v>-13804000</v>
       </c>
       <c r="V16" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2184,67 +2247,67 @@
         <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C17" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="D17" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="E17">
-        <v>98.30999755859375</v>
+        <v>151.6999969482422</v>
       </c>
       <c r="F17">
-        <v>364553.3333333333</v>
+        <v>1493653.333333333</v>
       </c>
       <c r="G17">
-        <v>83.14060012817383</v>
+        <v>133.4949995422363</v>
       </c>
       <c r="H17">
-        <v>67.66980005900065</v>
+        <v>103.2729996236165</v>
       </c>
       <c r="I17">
-        <v>61.54945003509521</v>
+        <v>93.11944972991944</v>
       </c>
       <c r="J17">
-        <v>56.25710010528564</v>
+        <v>84.70489982604981</v>
       </c>
       <c r="K17">
-        <v>3.118403196334839</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>152.2200012207031</v>
       </c>
       <c r="M17">
-        <v>155.9731081513379</v>
+        <v>169.569958645074</v>
       </c>
       <c r="N17">
-        <v>4.67</v>
+        <v>5.75</v>
       </c>
       <c r="O17">
-        <v>4.65</v>
+        <v>4.72</v>
       </c>
       <c r="P17">
-        <v>3.64</v>
+        <v>2.41</v>
       </c>
       <c r="Q17">
-        <v>4.12</v>
+        <v>3.16</v>
       </c>
       <c r="R17">
-        <v>131590000</v>
+        <v>738007000</v>
       </c>
       <c r="S17">
-        <v>130395000</v>
+        <v>384513000</v>
       </c>
       <c r="T17">
-        <v>103066000</v>
+        <v>333786000</v>
       </c>
       <c r="U17">
-        <v>118001000</v>
+        <v>404619000</v>
       </c>
       <c r="V17" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -2252,67 +2315,67 @@
         <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="C18" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="D18" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="E18">
-        <v>61.41999816894531</v>
+        <v>112.9700012207031</v>
       </c>
       <c r="F18">
-        <v>334966.0333333333</v>
+        <v>546546.6666666666</v>
       </c>
       <c r="G18">
-        <v>54.66399993896484</v>
+        <v>88.03700012207031</v>
       </c>
       <c r="H18">
-        <v>43.08020000457763</v>
+        <v>72.99779998779297</v>
       </c>
       <c r="I18">
-        <v>39.92875</v>
+        <v>67.70669992446899</v>
       </c>
       <c r="J18">
-        <v>36.28819999694824</v>
+        <v>60.92844989776611</v>
       </c>
       <c r="K18">
-        <v>0.4209107160568237</v>
+        <v>5.792013168334961</v>
       </c>
       <c r="L18">
-        <v>62.97999954223633</v>
+        <v>132.4752044677734</v>
       </c>
       <c r="M18">
-        <v>155.9099931669256</v>
+        <v>168.5830618040611</v>
       </c>
       <c r="N18">
-        <v>0.86</v>
+        <v>2394.25</v>
       </c>
       <c r="O18">
-        <v>0.97</v>
+        <v>4830.25</v>
       </c>
       <c r="P18">
-        <v>1.03</v>
+        <v>1680.75</v>
       </c>
       <c r="Q18">
-        <v>0.64</v>
+        <v>2394.25</v>
       </c>
       <c r="R18">
-        <v>25961000</v>
+        <v>1588430000000</v>
       </c>
       <c r="S18">
-        <v>29523000</v>
+        <v>509914000000</v>
       </c>
       <c r="T18">
-        <v>31725000</v>
+        <v>-665869000000</v>
       </c>
       <c r="U18">
-        <v>19649000</v>
+        <v>726419000000</v>
       </c>
       <c r="V18" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -2320,67 +2383,67 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D19" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="E19">
-        <v>47.38000106811523</v>
+        <v>99.59999847412109</v>
       </c>
       <c r="F19">
-        <v>1991166.666666667</v>
+        <v>350080</v>
       </c>
       <c r="G19">
-        <v>41.46540000915527</v>
+        <v>85.37059982299805</v>
       </c>
       <c r="H19">
-        <v>34.22250002543132</v>
+        <v>69.05573336283366</v>
       </c>
       <c r="I19">
-        <v>34.06104997634888</v>
+        <v>62.72905002593994</v>
       </c>
       <c r="J19">
-        <v>31.67024994850159</v>
+        <v>57.10800010681152</v>
       </c>
       <c r="K19">
-        <v>13.1899995803833</v>
+        <v>3.118403196334839</v>
       </c>
       <c r="L19">
-        <v>47.38000106811523</v>
+        <v>100</v>
       </c>
       <c r="M19">
-        <v>154.9268505712554</v>
+        <v>161.9399478198272</v>
       </c>
       <c r="N19">
-        <v>-0.58</v>
+        <v>4.67</v>
       </c>
       <c r="O19">
-        <v>-0.55</v>
+        <v>4.65</v>
       </c>
       <c r="P19">
-        <v>-0.51</v>
+        <v>3.64</v>
       </c>
       <c r="Q19">
-        <v>-0.54</v>
+        <v>4.12</v>
       </c>
       <c r="R19">
-        <v>-21522000</v>
+        <v>131590000</v>
       </c>
       <c r="S19">
-        <v>-20550000</v>
+        <v>130395000</v>
       </c>
       <c r="T19">
-        <v>-23224000</v>
+        <v>103066000</v>
       </c>
       <c r="U19">
-        <v>-25646000</v>
+        <v>118001000</v>
       </c>
       <c r="V19" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -2388,67 +2451,67 @@
         <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="D20" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="E20">
-        <v>186.4400024414062</v>
+        <v>42.63000106811523</v>
       </c>
       <c r="F20">
-        <v>511499.3333333333</v>
+        <v>7316120</v>
       </c>
       <c r="G20">
-        <v>174.0048007202148</v>
+        <v>36.06900005340576</v>
       </c>
       <c r="H20">
-        <v>137.5932672119141</v>
+        <v>28.23049999237061</v>
       </c>
       <c r="I20">
-        <v>121.1951503944397</v>
+        <v>25.83875001430512</v>
       </c>
       <c r="J20">
-        <v>108.9223503303528</v>
+        <v>23.97629998683929</v>
       </c>
       <c r="K20">
-        <v>0.6800000071525574</v>
+        <v>13.61999988555908</v>
       </c>
       <c r="L20">
-        <v>200.4799957275391</v>
+        <v>46.65000152587891</v>
       </c>
       <c r="M20">
-        <v>154.9227533137995</v>
+        <v>161.59057559473</v>
       </c>
       <c r="N20">
-        <v>1.32</v>
+        <v>0.9</v>
       </c>
       <c r="O20">
-        <v>1.21</v>
+        <v>-0.64</v>
       </c>
       <c r="P20">
-        <v>1.71</v>
+        <v>0.26</v>
       </c>
       <c r="Q20">
-        <v>1.43</v>
+        <v>0.9</v>
       </c>
       <c r="R20">
-        <v>44189000</v>
+        <v>-617966000</v>
       </c>
       <c r="S20">
-        <v>40283000</v>
+        <v>-1640321000</v>
       </c>
       <c r="T20">
-        <v>56992000</v>
+        <v>256938000</v>
       </c>
       <c r="U20">
-        <v>47697000</v>
+        <v>929668000</v>
       </c>
       <c r="V20" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -2456,67 +2519,67 @@
         <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="D21" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="E21">
-        <v>425.1300048828125</v>
+        <v>35.4900016784668</v>
       </c>
       <c r="F21">
-        <v>652400</v>
+        <v>279640</v>
       </c>
       <c r="G21">
-        <v>340.0053997802734</v>
+        <v>31.17499992370605</v>
       </c>
       <c r="H21">
-        <v>291.7941999308268</v>
+        <v>26.0589332707723</v>
       </c>
       <c r="I21">
-        <v>274.1866498565674</v>
+        <v>23.60619995594025</v>
       </c>
       <c r="J21">
-        <v>254.8489495849609</v>
+        <v>22.14109998226166</v>
       </c>
       <c r="K21">
-        <v>4.533332824707031</v>
+        <v>14.10000038146973</v>
       </c>
       <c r="L21">
-        <v>425.8900146484375</v>
+        <v>35.4900016784668</v>
       </c>
       <c r="M21">
-        <v>154.0928205532058</v>
+        <v>161.1319262980886</v>
       </c>
       <c r="N21">
-        <v>3.67</v>
+        <v>0.14</v>
       </c>
       <c r="O21">
-        <v>2.65</v>
+        <v>0.18</v>
       </c>
       <c r="P21">
-        <v>2.85</v>
+        <v>0.11</v>
       </c>
       <c r="Q21">
-        <v>3.42</v>
+        <v>0.13</v>
       </c>
       <c r="R21">
-        <v>97891000</v>
+        <v>36215000</v>
       </c>
       <c r="S21">
-        <v>70862000</v>
+        <v>48300000</v>
       </c>
       <c r="T21">
-        <v>76097000</v>
+        <v>28265000</v>
       </c>
       <c r="U21">
-        <v>91319000</v>
+        <v>34300000</v>
       </c>
       <c r="V21" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2524,67 +2587,67 @@
         <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="D22" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="E22">
-        <v>11.57999992370605</v>
+        <v>110.8600006103516</v>
       </c>
       <c r="F22">
-        <v>6701876.266666667</v>
+        <v>374813.3333333333</v>
       </c>
       <c r="G22">
-        <v>10.33400001525879</v>
+        <v>90.02179977416992</v>
       </c>
       <c r="H22">
-        <v>8.978799985249838</v>
+        <v>76.14213361104329</v>
       </c>
       <c r="I22">
-        <v>8.157199993133545</v>
+        <v>74.55895021438599</v>
       </c>
       <c r="J22">
-        <v>7.390599988698959</v>
+        <v>70.37845024108887</v>
       </c>
       <c r="K22">
-        <v>2.809999942779541</v>
+        <v>11.37919998168945</v>
       </c>
       <c r="L22">
-        <v>13.52000045776367</v>
+        <v>111.7799987792969</v>
       </c>
       <c r="M22">
-        <v>152.4871659079732</v>
+        <v>155.6875435756648</v>
       </c>
       <c r="N22">
-        <v>-0.48</v>
+        <v>5.52</v>
       </c>
       <c r="O22">
-        <v>-0.42</v>
+        <v>2.95</v>
       </c>
       <c r="P22">
-        <v>-0.49</v>
+        <v>2.43</v>
       </c>
       <c r="Q22">
-        <v>-0.05</v>
+        <v>3.67</v>
       </c>
       <c r="R22">
-        <v>-331809000</v>
+        <v>219587000</v>
       </c>
       <c r="S22">
-        <v>-291590000</v>
+        <v>117360000</v>
       </c>
       <c r="T22">
-        <v>-352014000</v>
+        <v>96733000</v>
       </c>
       <c r="U22">
-        <v>-33617000</v>
+        <v>146320000</v>
       </c>
       <c r="V22" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2592,67 +2655,67 @@
         <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C23" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D23" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="E23">
-        <v>109.3899993896484</v>
+        <v>425.3299865722656</v>
       </c>
       <c r="F23">
-        <v>376483.8333333333</v>
+        <v>538533.3333333334</v>
       </c>
       <c r="G23">
-        <v>87.84979980468751</v>
+        <v>352.0355993652344</v>
       </c>
       <c r="H23">
-        <v>75.30733360290527</v>
+        <v>297.5350665283203</v>
       </c>
       <c r="I23">
-        <v>73.81795021057128</v>
+        <v>278.7000997924804</v>
       </c>
       <c r="J23">
-        <v>69.8934002494812</v>
+        <v>258.0525497436523</v>
       </c>
       <c r="K23">
-        <v>11.37919998168945</v>
+        <v>4.533332824707031</v>
       </c>
       <c r="L23">
-        <v>109.3899993896484</v>
+        <v>429.0599975585938</v>
       </c>
       <c r="M23">
-        <v>152.0271840825212</v>
+        <v>153.1918861074822</v>
       </c>
       <c r="N23">
-        <v>5.52</v>
+        <v>3.67</v>
       </c>
       <c r="O23">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="P23">
-        <v>2.43</v>
+        <v>2.85</v>
       </c>
       <c r="Q23">
-        <v>3.67</v>
+        <v>3.42</v>
       </c>
       <c r="R23">
-        <v>219587000</v>
+        <v>97891000</v>
       </c>
       <c r="S23">
-        <v>117360000</v>
+        <v>70862000</v>
       </c>
       <c r="T23">
-        <v>96733000</v>
+        <v>76097000</v>
       </c>
       <c r="U23">
-        <v>146320000</v>
+        <v>91319000</v>
       </c>
       <c r="V23" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2660,67 +2723,67 @@
         <v>44</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D24" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E24">
-        <v>83.08000183105469</v>
+        <v>47.54999923706055</v>
       </c>
       <c r="F24">
-        <v>869886.4666666667</v>
+        <v>1630586.666666667</v>
       </c>
       <c r="G24">
-        <v>68.52439971923827</v>
+        <v>42.54879997253418</v>
       </c>
       <c r="H24">
-        <v>62.31113311767578</v>
+        <v>34.65803335825602</v>
       </c>
       <c r="I24">
-        <v>57.27264987945556</v>
+        <v>34.30534997940063</v>
       </c>
       <c r="J24">
-        <v>52.76229991912842</v>
+        <v>32.22104994773865</v>
       </c>
       <c r="K24">
-        <v>5.739999771118164</v>
+        <v>13.1899995803833</v>
       </c>
       <c r="L24">
-        <v>84.09999847412109</v>
+        <v>47.54999923706055</v>
       </c>
       <c r="M24">
-        <v>149.2301440582534</v>
+        <v>152.0154751570682</v>
       </c>
       <c r="N24">
-        <v>0.39</v>
+        <v>-0.58</v>
       </c>
       <c r="O24">
-        <v>0.99</v>
+        <v>-0.55</v>
       </c>
       <c r="P24">
-        <v>0.97</v>
+        <v>-0.51</v>
       </c>
       <c r="Q24">
-        <v>1.12</v>
+        <v>-0.54</v>
       </c>
       <c r="R24">
-        <v>28000000</v>
+        <v>-21522000</v>
       </c>
       <c r="S24">
-        <v>72000000</v>
+        <v>-20550000</v>
       </c>
       <c r="T24">
-        <v>72000000</v>
+        <v>-23224000</v>
       </c>
       <c r="U24">
-        <v>82000000</v>
+        <v>-25646000</v>
       </c>
       <c r="V24" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2728,67 +2791,67 @@
         <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="C25" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D25" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="E25">
-        <v>104.3649978637695</v>
+        <v>85.44000244140625</v>
       </c>
       <c r="F25">
-        <v>3705553.5</v>
+        <v>859646.6666666666</v>
       </c>
       <c r="G25">
-        <v>96.56050003051757</v>
+        <v>69.97639961242676</v>
       </c>
       <c r="H25">
-        <v>76.40250007629395</v>
+        <v>62.98713307698568</v>
       </c>
       <c r="I25">
-        <v>70.93487504959107</v>
+        <v>58.03229986190796</v>
       </c>
       <c r="J25">
-        <v>65.09695003509522</v>
+        <v>53.37334990501404</v>
       </c>
       <c r="K25">
-        <v>4.547188282012939</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="L25">
-        <v>133.7226409912109</v>
+        <v>85.44000244140625</v>
       </c>
       <c r="M25">
-        <v>147.9284171317249</v>
+        <v>151.0845127302103</v>
       </c>
       <c r="N25">
-        <v>0.13</v>
+        <v>0.39</v>
       </c>
       <c r="O25">
-        <v>-1.96</v>
+        <v>0.99</v>
       </c>
       <c r="P25">
-        <v>-0.19</v>
+        <v>0.97</v>
       </c>
       <c r="Q25">
-        <v>1.7</v>
+        <v>1.12</v>
       </c>
       <c r="R25">
-        <v>32968000</v>
+        <v>28000000</v>
       </c>
       <c r="S25">
-        <v>-500206000</v>
+        <v>72000000</v>
       </c>
       <c r="T25">
-        <v>-47910000</v>
+        <v>72000000</v>
       </c>
       <c r="U25">
-        <v>458761000</v>
+        <v>82000000</v>
       </c>
       <c r="V25" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2796,67 +2859,67 @@
         <v>46</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D26" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="E26">
-        <v>32.46500015258789</v>
+        <v>26.64999961853027</v>
       </c>
       <c r="F26">
-        <v>273520.3666666666</v>
+        <v>692000</v>
       </c>
       <c r="G26">
-        <v>30.78349994659424</v>
+        <v>26.49939998626709</v>
       </c>
       <c r="H26">
-        <v>25.74629993438721</v>
+        <v>20.975366675059</v>
       </c>
       <c r="I26">
-        <v>23.37732496738434</v>
+        <v>18.65167502403259</v>
       </c>
       <c r="J26">
-        <v>21.92749999523163</v>
+        <v>17.28280003070831</v>
       </c>
       <c r="K26">
-        <v>14.10000038146973</v>
+        <v>7.559999942779541</v>
       </c>
       <c r="L26">
-        <v>33.61000061035156</v>
+        <v>29.29999923706055</v>
       </c>
       <c r="M26">
-        <v>146.1653343675191</v>
+        <v>150.1304132260817</v>
       </c>
       <c r="N26">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="O26">
-        <v>0.18</v>
+        <v>-0.05</v>
       </c>
       <c r="P26">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="Q26">
-        <v>0.13</v>
+        <v>0.31</v>
       </c>
       <c r="R26">
-        <v>36215000</v>
+        <v>7258000</v>
       </c>
       <c r="S26">
-        <v>48300000</v>
+        <v>-2810000</v>
       </c>
       <c r="T26">
-        <v>28265000</v>
+        <v>6705000</v>
       </c>
       <c r="U26">
-        <v>34300000</v>
+        <v>17987000</v>
       </c>
       <c r="V26" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -2864,67 +2927,67 @@
         <v>47</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D27" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="E27">
-        <v>22.8799991607666</v>
+        <v>11.39000034332275</v>
       </c>
       <c r="F27">
-        <v>2064013.1</v>
+        <v>5218893.333333333</v>
       </c>
       <c r="G27">
-        <v>21.17999996185303</v>
+        <v>10.46000001907349</v>
       </c>
       <c r="H27">
-        <v>17.24499998092652</v>
+        <v>9.049733320871988</v>
       </c>
       <c r="I27">
-        <v>16.85110000610351</v>
+        <v>8.261599993705749</v>
       </c>
       <c r="J27">
-        <v>16.01930000782013</v>
+        <v>7.506949989795685</v>
       </c>
       <c r="K27">
-        <v>12.61999988555908</v>
+        <v>2.809999942779541</v>
       </c>
       <c r="L27">
-        <v>24.46999931335449</v>
+        <v>13.52000045776367</v>
       </c>
       <c r="M27">
-        <v>144.8231704721786</v>
+        <v>147.9420622676186</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>-0.48</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>-0.49</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>-331809000</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>-291590000</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>-352014000</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>-33617000</v>
       </c>
       <c r="V27" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -2932,67 +2995,67 @@
         <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="D28" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="E28">
-        <v>50.04999923706055</v>
+        <v>106.1500015258789</v>
       </c>
       <c r="F28">
-        <v>1463973.333333333</v>
+        <v>3468263.333333333</v>
       </c>
       <c r="G28">
-        <v>42.16179996490479</v>
+        <v>98.25</v>
       </c>
       <c r="H28">
-        <v>34.25059991200765</v>
+        <v>77.54420008341471</v>
       </c>
       <c r="I28">
-        <v>31.33024991989136</v>
+        <v>71.82570005416871</v>
       </c>
       <c r="J28">
-        <v>28.11069992542267</v>
+        <v>65.89450002670289</v>
       </c>
       <c r="K28">
-        <v>0.5</v>
+        <v>4.547188282012939</v>
       </c>
       <c r="L28">
-        <v>53.68999862670898</v>
+        <v>133.7226409912109</v>
       </c>
       <c r="M28">
-        <v>142.7663481001454</v>
+        <v>147.885724236739</v>
       </c>
       <c r="N28">
-        <v>0.02</v>
+        <v>0.13</v>
       </c>
       <c r="O28">
-        <v>0.13</v>
+        <v>-1.96</v>
       </c>
       <c r="P28">
-        <v>0.14</v>
+        <v>-0.19</v>
       </c>
       <c r="Q28">
-        <v>0.21</v>
+        <v>1.7</v>
       </c>
       <c r="R28">
-        <v>589000</v>
+        <v>32968000</v>
       </c>
       <c r="S28">
-        <v>3725000</v>
+        <v>-500206000</v>
       </c>
       <c r="T28">
-        <v>4132000</v>
+        <v>-47910000</v>
       </c>
       <c r="U28">
-        <v>6111000</v>
+        <v>458761000</v>
       </c>
       <c r="V28" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -3000,67 +3063,67 @@
         <v>49</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D29" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="E29">
-        <v>83.55999755859375</v>
+        <v>22.47999954223633</v>
       </c>
       <c r="F29">
-        <v>2660183.333333333</v>
+        <v>1715910</v>
       </c>
       <c r="G29">
-        <v>75.72839965820313</v>
+        <v>21.54480003356933</v>
       </c>
       <c r="H29">
-        <v>63.35746648152669</v>
+        <v>17.38686665852865</v>
       </c>
       <c r="I29">
-        <v>58.07844985961914</v>
+        <v>16.96290001392364</v>
       </c>
       <c r="J29">
-        <v>53.93349996566772</v>
+        <v>16.14085001468658</v>
       </c>
       <c r="K29">
-        <v>0.1027423962950706</v>
+        <v>12.61999988555908</v>
       </c>
       <c r="L29">
-        <v>84.81999969482422</v>
+        <v>24.46999931335449</v>
       </c>
       <c r="M29">
-        <v>141.5486644685861</v>
+        <v>147.7943906181666</v>
       </c>
       <c r="N29">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>627928000</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>882231000</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>532259000</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>720345000</v>
+        <v>0</v>
       </c>
       <c r="V29" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -3068,67 +3131,67 @@
         <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C30" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="D30" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="E30">
-        <v>141.9100036621094</v>
+        <v>35.09999847412109</v>
       </c>
       <c r="F30">
-        <v>872776.6666666666</v>
+        <v>884000</v>
       </c>
       <c r="G30">
-        <v>125.1906007385254</v>
+        <v>30.99769969940186</v>
       </c>
       <c r="H30">
-        <v>106.3447336832682</v>
+        <v>27.1356999206543</v>
       </c>
       <c r="I30">
-        <v>101.8252001953125</v>
+        <v>24.61477493286133</v>
       </c>
       <c r="J30">
-        <v>96.56130004882813</v>
+        <v>22.86844998836517</v>
       </c>
       <c r="K30">
-        <v>4.719488620758057</v>
+        <v>4.052896976470947</v>
       </c>
       <c r="L30">
-        <v>141.9100036621094</v>
+        <v>35.09999847412109</v>
       </c>
       <c r="M30">
-        <v>140.6375885910446</v>
+        <v>147.6927667342856</v>
       </c>
       <c r="N30">
-        <v>4.84</v>
+        <v>-0.23</v>
       </c>
       <c r="O30">
-        <v>1.32</v>
+        <v>0.2</v>
       </c>
       <c r="P30">
-        <v>4.17</v>
+        <v>0.22</v>
       </c>
       <c r="Q30">
-        <v>3.78</v>
+        <v>0.46</v>
       </c>
       <c r="R30">
-        <v>470000000</v>
+        <v>-16058000</v>
       </c>
       <c r="S30">
-        <v>124000000</v>
+        <v>26801000</v>
       </c>
       <c r="T30">
-        <v>383000000</v>
+        <v>29397000</v>
       </c>
       <c r="U30">
-        <v>345000000</v>
+        <v>54753000</v>
       </c>
       <c r="V30" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -3136,67 +3199,67 @@
         <v>51</v>
       </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D31" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="E31">
-        <v>84.54000091552734</v>
+        <v>48.04999923706055</v>
       </c>
       <c r="F31">
-        <v>5068079.666666667</v>
+        <v>1337796.666666667</v>
       </c>
       <c r="G31">
-        <v>78.7872004699707</v>
+        <v>43.55699996948242</v>
       </c>
       <c r="H31">
-        <v>63.78026679992676</v>
+        <v>35.00859991709391</v>
       </c>
       <c r="I31">
-        <v>60.3013000869751</v>
+        <v>31.95659992218017</v>
       </c>
       <c r="J31">
-        <v>57.61540000915527</v>
+        <v>28.5842999124527</v>
       </c>
       <c r="K31">
-        <v>2.279999971389771</v>
+        <v>0.5</v>
       </c>
       <c r="L31">
-        <v>111.6399993896484</v>
+        <v>53.68999862670898</v>
       </c>
       <c r="M31">
-        <v>140.0888905157719</v>
+        <v>145.7507952465374</v>
       </c>
       <c r="N31">
-        <v>-0.04</v>
+        <v>0.02</v>
       </c>
       <c r="O31">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="P31">
         <v>0.14</v>
       </c>
       <c r="Q31">
-        <v>0.02</v>
+        <v>0.21</v>
       </c>
       <c r="R31">
-        <v>-19073000</v>
+        <v>589000</v>
       </c>
       <c r="S31">
-        <v>15869000</v>
+        <v>3725000</v>
       </c>
       <c r="T31">
-        <v>71187000</v>
+        <v>4132000</v>
       </c>
       <c r="U31">
-        <v>9326000</v>
+        <v>6111000</v>
       </c>
       <c r="V31" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -3204,67 +3267,67 @@
         <v>52</v>
       </c>
       <c r="B32" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D32" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="E32">
-        <v>74.31999969482422</v>
+        <v>86.01000213623047</v>
       </c>
       <c r="F32">
-        <v>500034.2</v>
+        <v>2562490</v>
       </c>
       <c r="G32">
-        <v>68.97379974365235</v>
+        <v>77.16939956665038</v>
       </c>
       <c r="H32">
-        <v>56.03279980977376</v>
+        <v>64.39299980163574</v>
       </c>
       <c r="I32">
-        <v>54.20469984054566</v>
+        <v>59.00214981079102</v>
       </c>
       <c r="J32">
-        <v>52.08049989700317</v>
+        <v>54.66484994888306</v>
       </c>
       <c r="K32">
-        <v>14.8100004196167</v>
+        <v>0.1027423962950706</v>
       </c>
       <c r="L32">
-        <v>97.69999694824219</v>
+        <v>86.01000213623047</v>
       </c>
       <c r="M32">
-        <v>139.8058017366882</v>
+        <v>145.2601429697899</v>
       </c>
       <c r="N32">
-        <v>-0.96</v>
+        <v>2.69</v>
       </c>
       <c r="O32">
-        <v>-0.58</v>
+        <v>3.85</v>
       </c>
       <c r="P32">
-        <v>-0.66</v>
+        <v>2.35</v>
       </c>
       <c r="Q32">
-        <v>-0.72</v>
+        <v>3.21</v>
       </c>
       <c r="R32">
-        <v>-45536000</v>
+        <v>627928000</v>
       </c>
       <c r="S32">
-        <v>-27576000</v>
+        <v>882231000</v>
       </c>
       <c r="T32">
-        <v>-31460000</v>
+        <v>532259000</v>
       </c>
       <c r="U32">
-        <v>-34626000</v>
+        <v>720345000</v>
       </c>
       <c r="V32" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -3272,129 +3335,135 @@
         <v>53</v>
       </c>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D33" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="E33">
-        <v>84.87999725341797</v>
+        <v>177.3300018310547</v>
       </c>
       <c r="F33">
-        <v>462880.9666666667</v>
+        <v>531286.6666666666</v>
       </c>
       <c r="G33">
-        <v>78.67159980773926</v>
+        <v>175.9778005981445</v>
       </c>
       <c r="H33">
-        <v>65.44779986063639</v>
+        <v>139.5797338867187</v>
       </c>
       <c r="I33">
-        <v>63.20009990692139</v>
+        <v>123.0961503982544</v>
       </c>
       <c r="J33">
-        <v>60.32039995193482</v>
+        <v>110.6287503051758</v>
       </c>
       <c r="K33">
-        <v>7.03000020980835</v>
+        <v>0.6800000071525574</v>
       </c>
       <c r="L33">
-        <v>86.93000030517578</v>
+        <v>200.4799957275391</v>
       </c>
       <c r="M33">
-        <v>138.9625394173734</v>
+        <v>144.7559778973308</v>
       </c>
       <c r="N33">
-        <v>2.12</v>
+        <v>1.21</v>
       </c>
       <c r="O33">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="P33">
-        <v>0.88</v>
+        <v>1.43</v>
       </c>
       <c r="Q33">
-        <v>0.25</v>
+        <v>1.86</v>
       </c>
       <c r="R33">
-        <v>174500000</v>
+        <v>40283000</v>
       </c>
       <c r="S33">
-        <v>154800000</v>
+        <v>56992000</v>
       </c>
       <c r="T33">
-        <v>73300000</v>
+        <v>47697000</v>
       </c>
       <c r="U33">
-        <v>24800000</v>
+        <v>61579000</v>
       </c>
       <c r="V33" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" t="s">
         <v>54</v>
       </c>
+      <c r="B34" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" t="s">
+        <v>147</v>
+      </c>
       <c r="D34" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="E34">
-        <v>13.89000034332275</v>
+        <v>22.52000045776367</v>
       </c>
       <c r="F34">
-        <v>1247623.1</v>
+        <v>1097706.666666667</v>
       </c>
       <c r="G34">
-        <v>10.21729988098144</v>
+        <v>18.83639995574951</v>
       </c>
       <c r="H34">
-        <v>10.11725797017415</v>
+        <v>16.53653329849243</v>
       </c>
       <c r="I34">
-        <v>10.04098649501801</v>
+        <v>15.89694997310638</v>
       </c>
       <c r="J34">
-        <v>9.983236494064331</v>
+        <v>15.42824997425079</v>
       </c>
       <c r="K34">
-        <v>8.989999771118164</v>
+        <v>10.84000015258789</v>
       </c>
       <c r="L34">
-        <v>13.89000034332275</v>
+        <v>22.55999946594238</v>
       </c>
       <c r="M34">
-        <v>138.2820215626973</v>
+        <v>140.8003600350384</v>
       </c>
       <c r="N34">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="O34">
-        <v>0.090181</v>
+        <v>-0.28</v>
       </c>
       <c r="P34">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="Q34">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="R34">
-        <v>1944526</v>
+        <v>1464000</v>
       </c>
       <c r="S34">
-        <v>366476</v>
+        <v>-28687000</v>
       </c>
       <c r="T34">
-        <v>900174</v>
+        <v>7846000</v>
       </c>
       <c r="U34">
-        <v>-1652348</v>
+        <v>5389000</v>
       </c>
       <c r="V34" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -3402,67 +3471,67 @@
         <v>55</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="D35" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="E35">
-        <v>372.75</v>
+        <v>85.30000305175781</v>
       </c>
       <c r="F35">
-        <v>284896.6666666667</v>
+        <v>5131773.333333333</v>
       </c>
       <c r="G35">
-        <v>317.9118011474609</v>
+        <v>79.92280044555665</v>
       </c>
       <c r="H35">
-        <v>277.2842008463542</v>
+        <v>64.59806681315104</v>
       </c>
       <c r="I35">
-        <v>270.0473502349853</v>
+        <v>60.75095010757446</v>
       </c>
       <c r="J35">
-        <v>258.8177003479004</v>
+        <v>57.85625005722046</v>
       </c>
       <c r="K35">
-        <v>4.775613307952881</v>
+        <v>2.279999971389771</v>
       </c>
       <c r="L35">
-        <v>374.9800109863281</v>
+        <v>111.6399993896484</v>
       </c>
       <c r="M35">
-        <v>137.7453677797959</v>
+        <v>140.7465741597917</v>
       </c>
       <c r="N35">
-        <v>3.99</v>
+        <v>-0.04</v>
       </c>
       <c r="O35">
-        <v>2.65</v>
+        <v>0.03</v>
       </c>
       <c r="P35">
-        <v>2.75</v>
+        <v>0.14</v>
       </c>
       <c r="Q35">
-        <v>6.1</v>
+        <v>0.02</v>
       </c>
       <c r="R35">
-        <v>141900000</v>
+        <v>-19073000</v>
       </c>
       <c r="S35">
-        <v>94400000</v>
+        <v>15869000</v>
       </c>
       <c r="T35">
-        <v>98000000</v>
+        <v>71187000</v>
       </c>
       <c r="U35">
-        <v>217200000</v>
+        <v>9326000</v>
       </c>
       <c r="V35" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3470,67 +3539,67 @@
         <v>56</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C36" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D36" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="E36">
-        <v>32.45000076293945</v>
+        <v>142.8500061035156</v>
       </c>
       <c r="F36">
-        <v>661651.8333333334</v>
+        <v>872520</v>
       </c>
       <c r="G36">
-        <v>31.78019989013672</v>
+        <v>127.809600982666</v>
       </c>
       <c r="H36">
-        <v>26.36056660970052</v>
+        <v>107.8191337585449</v>
       </c>
       <c r="I36">
-        <v>24.41387496948242</v>
+        <v>102.9858502578735</v>
       </c>
       <c r="J36">
-        <v>23.05657493591309</v>
+        <v>97.50655010223389</v>
       </c>
       <c r="K36">
-        <v>0.1500000059604645</v>
+        <v>4.719488620758057</v>
       </c>
       <c r="L36">
-        <v>38.15000152587891</v>
+        <v>142.8500061035156</v>
       </c>
       <c r="M36">
-        <v>137.3209029552308</v>
+        <v>140.2716330985683</v>
       </c>
       <c r="N36">
-        <v>0.13</v>
+        <v>4.84</v>
       </c>
       <c r="O36">
-        <v>0.01</v>
+        <v>1.32</v>
       </c>
       <c r="P36">
-        <v>-0.02</v>
+        <v>4.17</v>
       </c>
       <c r="Q36">
-        <v>-0.36</v>
+        <v>3.78</v>
       </c>
       <c r="R36">
-        <v>7905000</v>
+        <v>470000000</v>
       </c>
       <c r="S36">
-        <v>668000</v>
+        <v>124000000</v>
       </c>
       <c r="T36">
-        <v>-934000</v>
+        <v>383000000</v>
       </c>
       <c r="U36">
-        <v>-21005000</v>
+        <v>345000000</v>
       </c>
       <c r="V36" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -3538,67 +3607,67 @@
         <v>57</v>
       </c>
       <c r="B37" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="C37" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="D37" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="E37">
-        <v>13.44999980926514</v>
+        <v>35.06000137329102</v>
       </c>
       <c r="F37">
-        <v>8962973.333333334</v>
+        <v>676190</v>
       </c>
       <c r="G37">
-        <v>11.38319995880127</v>
+        <v>26.68940013885498</v>
       </c>
       <c r="H37">
-        <v>9.921999991734822</v>
+        <v>25.90026672363281</v>
       </c>
       <c r="I37">
-        <v>9.689950006008148</v>
+        <v>25.06940004348755</v>
       </c>
       <c r="J37">
-        <v>9.350900013446807</v>
+        <v>23.83420004844665</v>
       </c>
       <c r="K37">
-        <v>0.3049550950527191</v>
+        <v>0.6000000238418579</v>
       </c>
       <c r="L37">
-        <v>13.86999988555908</v>
+        <v>35.06000137329102</v>
       </c>
       <c r="M37">
-        <v>136.8856279875857</v>
+        <v>139.4357928260872</v>
       </c>
       <c r="N37">
-        <v>0.3</v>
+        <v>4.47</v>
       </c>
       <c r="O37">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="P37">
-        <v>2.87</v>
+        <v>3.9</v>
       </c>
       <c r="Q37">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
       <c r="R37">
-        <v>152000000</v>
+        <v>267396000</v>
       </c>
       <c r="S37">
-        <v>172000000</v>
+        <v>84719000</v>
       </c>
       <c r="T37">
-        <v>2006000000</v>
+        <v>237890000</v>
       </c>
       <c r="U37">
-        <v>413000000</v>
+        <v>30013000</v>
       </c>
       <c r="V37" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -3606,67 +3675,67 @@
         <v>58</v>
       </c>
       <c r="B38" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C38" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="D38" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="E38">
-        <v>74.30500030517578</v>
+        <v>377.3800048828125</v>
       </c>
       <c r="F38">
-        <v>612486.0333333333</v>
+        <v>282690</v>
       </c>
       <c r="G38">
-        <v>70.26869987487792</v>
+        <v>325.7794006347656</v>
       </c>
       <c r="H38">
-        <v>59.29403322855632</v>
+        <v>280.8597340901693</v>
       </c>
       <c r="I38">
-        <v>57.00207492828369</v>
+        <v>273.1459002685547</v>
       </c>
       <c r="J38">
-        <v>53.70964992523194</v>
+        <v>260.4802004241943</v>
       </c>
       <c r="K38">
-        <v>23.54999923706055</v>
+        <v>4.775613307952881</v>
       </c>
       <c r="L38">
-        <v>76.5</v>
+        <v>377.3800048828125</v>
       </c>
       <c r="M38">
-        <v>136.7515713199409</v>
+        <v>138.2195730214023</v>
       </c>
       <c r="N38">
-        <v>-1.24</v>
+        <v>3.99</v>
       </c>
       <c r="O38">
-        <v>-0.68</v>
+        <v>2.65</v>
       </c>
       <c r="P38">
-        <v>-1.24</v>
+        <v>2.75</v>
       </c>
       <c r="Q38">
-        <v>-0.68</v>
+        <v>6.1</v>
       </c>
       <c r="R38">
-        <v>-193228000</v>
+        <v>141900000</v>
       </c>
       <c r="S38">
-        <v>-112101000</v>
+        <v>94400000</v>
       </c>
       <c r="T38">
-        <v>-193228000</v>
+        <v>98000000</v>
       </c>
       <c r="U38">
-        <v>-112101000</v>
+        <v>217200000</v>
       </c>
       <c r="V38" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -3674,135 +3743,129 @@
         <v>59</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C39" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D39" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="E39">
-        <v>117.870002746582</v>
+        <v>74.77999877929688</v>
       </c>
       <c r="F39">
-        <v>451402.2333333333</v>
+        <v>508506.6666666667</v>
       </c>
       <c r="G39">
-        <v>96.53739990234375</v>
+        <v>70.0605997467041</v>
       </c>
       <c r="H39">
-        <v>91.81693318684896</v>
+        <v>56.67946647644043</v>
       </c>
       <c r="I39">
-        <v>88.27379997253418</v>
+        <v>54.51254983901978</v>
       </c>
       <c r="J39">
-        <v>84.97219993591308</v>
+        <v>52.2969499206543</v>
       </c>
       <c r="K39">
-        <v>3.099249601364136</v>
+        <v>14.8100004196167</v>
       </c>
       <c r="L39">
-        <v>121.8199996948242</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="M39">
-        <v>136.6228468789908</v>
+        <v>138.1663907436597</v>
       </c>
       <c r="N39">
-        <v>3.5</v>
+        <v>-0.58</v>
       </c>
       <c r="O39">
-        <v>1.48</v>
+        <v>-0.66</v>
       </c>
       <c r="P39">
-        <v>2.84</v>
+        <v>-0.72</v>
       </c>
       <c r="Q39">
-        <v>1.64</v>
+        <v>-0.68</v>
       </c>
       <c r="R39">
-        <v>88842000</v>
+        <v>-27576000</v>
       </c>
       <c r="S39">
-        <v>37337000</v>
+        <v>-31460000</v>
       </c>
       <c r="T39">
-        <v>71283000</v>
+        <v>-34626000</v>
       </c>
       <c r="U39">
-        <v>40443000</v>
+        <v>-32812000</v>
       </c>
       <c r="V39" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="40" spans="1:22">
       <c r="A40" t="s">
         <v>60</v>
       </c>
-      <c r="B40" t="s">
-        <v>111</v>
-      </c>
-      <c r="C40" t="s">
-        <v>137</v>
-      </c>
       <c r="D40" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="E40">
-        <v>24.6299991607666</v>
+        <v>13.89000034332275</v>
       </c>
       <c r="F40">
-        <v>816992.1</v>
+        <v>1247623.1</v>
       </c>
       <c r="G40">
-        <v>24.09440002441406</v>
+        <v>10.21729988098144</v>
       </c>
       <c r="H40">
-        <v>20.30826672236125</v>
+        <v>10.11725797017415</v>
       </c>
       <c r="I40">
-        <v>18.57120003223419</v>
+        <v>10.04098649501801</v>
       </c>
       <c r="J40">
-        <v>17.0039000415802</v>
+        <v>9.983236494064331</v>
       </c>
       <c r="K40">
-        <v>1.899999976158142</v>
+        <v>8.989999771118164</v>
       </c>
       <c r="L40">
-        <v>27.38999938964844</v>
+        <v>13.89000034332275</v>
       </c>
       <c r="M40">
-        <v>136.434090002839</v>
+        <v>137.8945695997145</v>
       </c>
       <c r="N40">
-        <v>0.75</v>
+        <v>-0.08</v>
       </c>
       <c r="O40">
-        <v>0.762</v>
+        <v>0.090181</v>
       </c>
       <c r="P40">
-        <v>1.315</v>
+        <v>0.02</v>
       </c>
       <c r="Q40">
-        <v>0.519</v>
+        <v>-0.08</v>
       </c>
       <c r="R40">
-        <v>76661000</v>
+        <v>1944526</v>
       </c>
       <c r="S40">
-        <v>75504000</v>
+        <v>366476</v>
       </c>
       <c r="T40">
-        <v>128734000</v>
+        <v>900174</v>
       </c>
       <c r="U40">
-        <v>52181000</v>
+        <v>-1652348</v>
       </c>
       <c r="V40" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -3810,67 +3873,67 @@
         <v>61</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C41" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D41" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="E41">
-        <v>114.3399963378906</v>
+        <v>221.1799926757812</v>
       </c>
       <c r="F41">
-        <v>568353.7666666667</v>
+        <v>372000</v>
       </c>
       <c r="G41">
-        <v>99.53900009155274</v>
+        <v>186.6495999145508</v>
       </c>
       <c r="H41">
-        <v>89.64213353474935</v>
+        <v>166.8522666422526</v>
       </c>
       <c r="I41">
-        <v>87.67495002746583</v>
+        <v>161.8516996765137</v>
       </c>
       <c r="J41">
-        <v>83.97660015106202</v>
+        <v>153.8178998184204</v>
       </c>
       <c r="K41">
-        <v>0.3318000435829163</v>
+        <v>0.9346818327903748</v>
       </c>
       <c r="L41">
-        <v>149.9608459472656</v>
+        <v>221.1799926757812</v>
       </c>
       <c r="M41">
-        <v>135.6252202007354</v>
+        <v>136.9737893920463</v>
       </c>
       <c r="N41">
-        <v>5.15</v>
+        <v>2.16</v>
       </c>
       <c r="O41">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="P41">
-        <v>0.5</v>
+        <v>2.32</v>
       </c>
       <c r="Q41">
-        <v>2.24</v>
+        <v>2.95</v>
       </c>
       <c r="R41">
-        <v>280943000</v>
+        <v>105772000</v>
       </c>
       <c r="S41">
-        <v>136185000</v>
+        <v>126300000</v>
       </c>
       <c r="T41">
-        <v>27080000</v>
+        <v>111473000</v>
       </c>
       <c r="U41">
-        <v>120719000</v>
+        <v>140595000</v>
       </c>
       <c r="V41" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -3878,67 +3941,67 @@
         <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D42" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E42">
-        <v>32.70999908447266</v>
+        <v>25.79000091552734</v>
       </c>
       <c r="F42">
-        <v>1320385.033333333</v>
+        <v>792403.3333333334</v>
       </c>
       <c r="G42">
-        <v>30.6104997253418</v>
+        <v>24.32139999389648</v>
       </c>
       <c r="H42">
-        <v>26.78123326619466</v>
+        <v>20.50406672159831</v>
       </c>
       <c r="I42">
-        <v>24.3245249414444</v>
+        <v>18.77715003490448</v>
       </c>
       <c r="J42">
-        <v>22.6387999868393</v>
+        <v>17.23650003910065</v>
       </c>
       <c r="K42">
-        <v>4.052896976470947</v>
+        <v>1.899999976158142</v>
       </c>
       <c r="L42">
-        <v>33.56000137329102</v>
+        <v>27.38999938964844</v>
       </c>
       <c r="M42">
-        <v>135.4950686890014</v>
+        <v>136.9735154571766</v>
       </c>
       <c r="N42">
-        <v>-0.23</v>
+        <v>0.75</v>
       </c>
       <c r="O42">
-        <v>0.2</v>
+        <v>0.762</v>
       </c>
       <c r="P42">
-        <v>0.22</v>
+        <v>1.315</v>
       </c>
       <c r="Q42">
-        <v>0.46</v>
+        <v>0.519</v>
       </c>
       <c r="R42">
-        <v>-16058000</v>
+        <v>76661000</v>
       </c>
       <c r="S42">
-        <v>26801000</v>
+        <v>75504000</v>
       </c>
       <c r="T42">
-        <v>29397000</v>
+        <v>128734000</v>
       </c>
       <c r="U42">
-        <v>54753000</v>
+        <v>52181000</v>
       </c>
       <c r="V42" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -3946,31 +4009,31 @@
         <v>63</v>
       </c>
       <c r="B43" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="C43" t="s">
         <v>127</v>
       </c>
       <c r="D43" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="E43">
-        <v>54.36000061035156</v>
+        <v>54.81999969482422</v>
       </c>
       <c r="F43">
-        <v>2010083.333333333</v>
+        <v>1653563.333333333</v>
       </c>
       <c r="G43">
-        <v>50.26000007629395</v>
+        <v>51.10480003356933</v>
       </c>
       <c r="H43">
-        <v>42.32339993794759</v>
+        <v>42.92266660054525</v>
       </c>
       <c r="I43">
-        <v>39.23189993858337</v>
+        <v>39.77599993705749</v>
       </c>
       <c r="J43">
-        <v>36.68854996681213</v>
+        <v>37.11009996414185</v>
       </c>
       <c r="K43">
         <v>1.498309969902039</v>
@@ -3979,7 +4042,7 @@
         <v>66.26741027832031</v>
       </c>
       <c r="M43">
-        <v>134.7699533557918</v>
+        <v>135.9624801810163</v>
       </c>
       <c r="N43">
         <v>2.86</v>
@@ -4006,7 +4069,7 @@
         <v>164442000</v>
       </c>
       <c r="V43" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -4014,31 +4077,31 @@
         <v>64</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C44" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="D44" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="E44">
-        <v>886.1099853515625</v>
+        <v>883.1599731445312</v>
       </c>
       <c r="F44">
-        <v>2398529.166666667</v>
+        <v>2304100</v>
       </c>
       <c r="G44">
-        <v>851.0402014160156</v>
+        <v>862.3584008789062</v>
       </c>
       <c r="H44">
-        <v>690.9594673665365</v>
+        <v>697.6188671875</v>
       </c>
       <c r="I44">
-        <v>645.2251498413086</v>
+        <v>652.0013499450683</v>
       </c>
       <c r="J44">
-        <v>602.0113998413086</v>
+        <v>607.6588496398925</v>
       </c>
       <c r="K44">
         <v>11.17089080810547</v>
@@ -4047,7 +4110,7 @@
         <v>920</v>
       </c>
       <c r="M44">
-        <v>134.6926311357979</v>
+        <v>135.4375103024965</v>
       </c>
       <c r="N44">
         <v>7.132125</v>
@@ -4074,7 +4137,7 @@
         <v>3481000000</v>
       </c>
       <c r="V44" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -4082,67 +4145,67 @@
         <v>65</v>
       </c>
       <c r="B45" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C45" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="D45" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="E45">
-        <v>32.08000183105469</v>
+        <v>521.5999755859375</v>
       </c>
       <c r="F45">
-        <v>916923.3</v>
+        <v>2834053.333333333</v>
       </c>
       <c r="G45">
-        <v>29.73980007171631</v>
+        <v>452.1170007324219</v>
       </c>
       <c r="H45">
-        <v>25.36000003814697</v>
+        <v>391.7923337809245</v>
       </c>
       <c r="I45">
-        <v>24.28695004463196</v>
+        <v>384.1324501037598</v>
       </c>
       <c r="J45">
-        <v>23.43525002479553</v>
+        <v>371.0586505126953</v>
       </c>
       <c r="K45">
-        <v>18.89999961853027</v>
+        <v>0.5143532752990723</v>
       </c>
       <c r="L45">
-        <v>32.33000183105469</v>
+        <v>521.5999755859375</v>
       </c>
       <c r="M45">
-        <v>134.6781611475295</v>
+        <v>135.1759247283216</v>
       </c>
       <c r="N45">
-        <v>0.67</v>
+        <v>1.05</v>
       </c>
       <c r="O45">
-        <v>0.65</v>
+        <v>1.61</v>
       </c>
       <c r="P45">
-        <v>0.31</v>
+        <v>2.039294</v>
       </c>
       <c r="Q45">
-        <v>0.5</v>
+        <v>1.416777</v>
       </c>
       <c r="R45">
-        <v>115000000</v>
+        <v>952500000</v>
       </c>
       <c r="S45">
-        <v>111000000</v>
+        <v>1451700000</v>
       </c>
       <c r="T45">
-        <v>54000000</v>
+        <v>1937700000</v>
       </c>
       <c r="U45">
-        <v>86000000</v>
+        <v>1344900000</v>
       </c>
       <c r="V45" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="46" spans="1:22">
@@ -4150,67 +4213,67 @@
         <v>66</v>
       </c>
       <c r="B46" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="C46" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D46" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="E46">
-        <v>530.2999877929688</v>
+        <v>44.04000091552734</v>
       </c>
       <c r="F46">
-        <v>3127053.333333333</v>
+        <v>296346.6666666667</v>
       </c>
       <c r="G46">
-        <v>477.826597290039</v>
+        <v>43.57499984741211</v>
       </c>
       <c r="H46">
-        <v>397.863998819987</v>
+        <v>35.52153327941895</v>
       </c>
       <c r="I46">
-        <v>379.3749488830566</v>
+        <v>34.12624994277954</v>
       </c>
       <c r="J46">
-        <v>356.3366491699219</v>
+        <v>31.53129996299744</v>
       </c>
       <c r="K46">
-        <v>0.1503329128026962</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="L46">
-        <v>688.3699951171875</v>
+        <v>49.84999847412109</v>
       </c>
       <c r="M46">
-        <v>134.5504957247051</v>
+        <v>135.1312624139452</v>
       </c>
       <c r="N46">
-        <v>2.42</v>
+        <v>-0.38</v>
       </c>
       <c r="O46">
-        <v>2.53</v>
+        <v>-0.41</v>
       </c>
       <c r="P46">
-        <v>2.71</v>
+        <v>-0.49</v>
       </c>
       <c r="Q46">
-        <v>2.82</v>
+        <v>-0.44</v>
       </c>
       <c r="R46">
-        <v>1136000000</v>
+        <v>-18466000</v>
       </c>
       <c r="S46">
-        <v>1176000000</v>
+        <v>-19716000</v>
       </c>
       <c r="T46">
-        <v>1247000000</v>
+        <v>-26123000</v>
       </c>
       <c r="U46">
-        <v>1295000000</v>
+        <v>-25192000</v>
       </c>
       <c r="V46" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -4218,67 +4281,67 @@
         <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C47" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D47" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E47">
-        <v>28.15999984741211</v>
+        <v>32.5099983215332</v>
       </c>
       <c r="F47">
-        <v>586794.9333333333</v>
+        <v>895333.3333333334</v>
       </c>
       <c r="G47">
-        <v>25.29979991912842</v>
+        <v>30.07680000305176</v>
       </c>
       <c r="H47">
-        <v>22.26499998092651</v>
+        <v>25.62233336130778</v>
       </c>
       <c r="I47">
-        <v>21.33194999694824</v>
+        <v>24.43005002975464</v>
       </c>
       <c r="J47">
-        <v>20.06444998264313</v>
+        <v>23.5480500125885</v>
       </c>
       <c r="K47">
-        <v>4.372677803039551</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="L47">
-        <v>29.73999977111816</v>
+        <v>32.58000183105469</v>
       </c>
       <c r="M47">
-        <v>134.2322376025219</v>
+        <v>134.9736723172544</v>
       </c>
       <c r="N47">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O47">
-        <v>0.51</v>
+        <v>0.65</v>
       </c>
       <c r="P47">
-        <v>1.27</v>
+        <v>0.31</v>
       </c>
       <c r="Q47">
-        <v>1.89</v>
+        <v>0.5</v>
       </c>
       <c r="R47">
-        <v>24847720</v>
+        <v>115000000</v>
       </c>
       <c r="S47">
-        <v>20311465</v>
+        <v>111000000</v>
       </c>
       <c r="T47">
-        <v>51263710</v>
+        <v>54000000</v>
       </c>
       <c r="U47">
-        <v>76021035</v>
+        <v>86000000</v>
       </c>
       <c r="V47" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="48" spans="1:22">
@@ -4286,67 +4349,67 @@
         <v>68</v>
       </c>
       <c r="B48" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C48" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="D48" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="E48">
-        <v>215.2400054931641</v>
+        <v>520.5999755859375</v>
       </c>
       <c r="F48">
-        <v>561638.4</v>
+        <v>2879326.666666667</v>
       </c>
       <c r="G48">
-        <v>183.3179998779297</v>
+        <v>489.8401965332031</v>
       </c>
       <c r="H48">
-        <v>165.4255333455404</v>
+        <v>402.953598836263</v>
       </c>
       <c r="I48">
-        <v>160.4737496948242</v>
+        <v>384.0085487365723</v>
       </c>
       <c r="J48">
-        <v>152.8209998321533</v>
+        <v>360.3102992248535</v>
       </c>
       <c r="K48">
-        <v>0.9346818327903748</v>
+        <v>0.1503329128026962</v>
       </c>
       <c r="L48">
-        <v>216.1799926757812</v>
+        <v>688.3699951171875</v>
       </c>
       <c r="M48">
-        <v>133.1615765956707</v>
+        <v>134.3412516983596</v>
       </c>
       <c r="N48">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="O48">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="P48">
-        <v>2.32</v>
+        <v>2.71</v>
       </c>
       <c r="Q48">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="R48">
-        <v>105772000</v>
+        <v>1136000000</v>
       </c>
       <c r="S48">
-        <v>126300000</v>
+        <v>1176000000</v>
       </c>
       <c r="T48">
-        <v>111473000</v>
+        <v>1247000000</v>
       </c>
       <c r="U48">
-        <v>140595000</v>
+        <v>1295000000</v>
       </c>
       <c r="V48" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
     </row>
     <row r="49" spans="1:22">
@@ -4354,67 +4417,67 @@
         <v>69</v>
       </c>
       <c r="B49" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C49" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="D49" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="E49">
-        <v>52.38999938964844</v>
+        <v>15.81999969482422</v>
       </c>
       <c r="F49">
-        <v>1734528.166666667</v>
+        <v>510526.6666666667</v>
       </c>
       <c r="G49">
-        <v>43.86760002136231</v>
+        <v>13.26059999465942</v>
       </c>
       <c r="H49">
-        <v>40.78753339131674</v>
+        <v>12.77213333765666</v>
       </c>
       <c r="I49">
-        <v>39.71880006790161</v>
+        <v>12.28575000286102</v>
       </c>
       <c r="J49">
-        <v>37.65400006294251</v>
+        <v>11.8549000120163</v>
       </c>
       <c r="K49">
-        <v>20.39999961853027</v>
+        <v>9.039999961853027</v>
       </c>
       <c r="L49">
-        <v>52.38999938964844</v>
+        <v>15.89999961853027</v>
       </c>
       <c r="M49">
-        <v>132.4579367657776</v>
+        <v>133.6994029608328</v>
       </c>
       <c r="N49">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>108063000</v>
+        <v>0</v>
       </c>
       <c r="S49">
-        <v>33585000</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>134962000</v>
+        <v>0</v>
       </c>
       <c r="U49">
-        <v>108063000</v>
+        <v>0</v>
       </c>
       <c r="V49" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="50" spans="1:22">
@@ -4422,67 +4485,67 @@
         <v>70</v>
       </c>
       <c r="B50" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C50" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D50" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="E50">
-        <v>45.57500076293945</v>
+        <v>149.2400054931641</v>
       </c>
       <c r="F50">
-        <v>325471.4333333333</v>
+        <v>339186.6666666667</v>
       </c>
       <c r="G50">
-        <v>43.28029983520508</v>
+        <v>136.7890003967285</v>
       </c>
       <c r="H50">
-        <v>35.21656661987305</v>
+        <v>121.1256001790365</v>
       </c>
       <c r="I50">
-        <v>33.7736749458313</v>
+        <v>111.6251002120972</v>
       </c>
       <c r="J50">
-        <v>31.17694996833801</v>
+        <v>104.3352502822876</v>
       </c>
       <c r="K50">
-        <v>7.400000095367432</v>
+        <v>0.577300488948822</v>
       </c>
       <c r="L50">
-        <v>49.84999847412109</v>
+        <v>150.4900054931641</v>
       </c>
       <c r="M50">
-        <v>132.2661442102612</v>
+        <v>133.2237848789503</v>
       </c>
       <c r="N50">
-        <v>-0.38</v>
+        <v>7.1</v>
       </c>
       <c r="O50">
-        <v>-0.41</v>
+        <v>7.09</v>
       </c>
       <c r="P50">
-        <v>-0.49</v>
+        <v>3.54</v>
       </c>
       <c r="Q50">
-        <v>-0.44</v>
+        <v>5.02</v>
       </c>
       <c r="R50">
-        <v>-18466000</v>
+        <v>262489000</v>
       </c>
       <c r="S50">
-        <v>-19716000</v>
+        <v>262365000</v>
       </c>
       <c r="T50">
-        <v>-26123000</v>
+        <v>131301000</v>
       </c>
       <c r="U50">
-        <v>-25192000</v>
+        <v>186836000</v>
       </c>
       <c r="V50" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -4490,67 +4553,67 @@
         <v>71</v>
       </c>
       <c r="B51" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="C51" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D51" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="E51">
-        <v>53.52000045776367</v>
+        <v>399.8699951171875</v>
       </c>
       <c r="F51">
-        <v>1075266.666666667</v>
+        <v>365353.3333333333</v>
       </c>
       <c r="G51">
-        <v>47.48739974975586</v>
+        <v>367.1920001220703</v>
       </c>
       <c r="H51">
-        <v>43.2299333190918</v>
+        <v>333.7755997721354</v>
       </c>
       <c r="I51">
-        <v>42.42324996948242</v>
+        <v>308.6507496643067</v>
       </c>
       <c r="J51">
-        <v>40.89590003967285</v>
+        <v>296.0106996917725</v>
       </c>
       <c r="K51">
-        <v>2.721946477890015</v>
+        <v>0.2751234471797943</v>
       </c>
       <c r="L51">
-        <v>53.91999816894531</v>
+        <v>471.1166076660156</v>
       </c>
       <c r="M51">
-        <v>132.1821638423702</v>
+        <v>132.9899978290975</v>
       </c>
       <c r="N51">
-        <v>3.74</v>
+        <v>1.59</v>
       </c>
       <c r="O51">
-        <v>3.41</v>
+        <v>1.36</v>
       </c>
       <c r="P51">
-        <v>0.25</v>
+        <v>1.85</v>
       </c>
       <c r="Q51">
-        <v>-2</v>
+        <v>2.06</v>
       </c>
       <c r="R51">
-        <v>360580000</v>
+        <v>120600000</v>
       </c>
       <c r="S51">
-        <v>312600000</v>
+        <v>103000000</v>
       </c>
       <c r="T51">
-        <v>32572000</v>
+        <v>140000000</v>
       </c>
       <c r="U51">
-        <v>-155994000</v>
+        <v>155100000</v>
       </c>
       <c r="V51" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="52" spans="1:22">
@@ -4558,67 +4621,67 @@
         <v>72</v>
       </c>
       <c r="B52" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C52" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="D52" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="E52">
-        <v>58.97999954223633</v>
+        <v>13.27000045776367</v>
       </c>
       <c r="F52">
-        <v>5388316.666666667</v>
+        <v>8936656.666666666</v>
       </c>
       <c r="G52">
-        <v>49.214400100708</v>
+        <v>11.60799997329712</v>
       </c>
       <c r="H52">
-        <v>45.73826670328776</v>
+        <v>10.05093332608541</v>
       </c>
       <c r="I52">
-        <v>44.62294998168945</v>
+        <v>9.785900003910065</v>
       </c>
       <c r="J52">
-        <v>42.81295000076294</v>
+        <v>9.390100014209747</v>
       </c>
       <c r="K52">
-        <v>11.31525421142578</v>
+        <v>0.3049550950527191</v>
       </c>
       <c r="L52">
-        <v>59.79999923706055</v>
+        <v>13.86999988555908</v>
       </c>
       <c r="M52">
-        <v>132.0594763273835</v>
+        <v>132.8223821631663</v>
       </c>
       <c r="N52">
-        <v>1.53</v>
+        <v>0.3</v>
       </c>
       <c r="O52">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="P52">
-        <v>0.44</v>
+        <v>2.87</v>
       </c>
       <c r="Q52">
-        <v>0.23</v>
+        <v>0.55</v>
       </c>
       <c r="R52">
-        <v>1312000000</v>
+        <v>152000000</v>
       </c>
       <c r="S52">
-        <v>270000000</v>
+        <v>172000000</v>
       </c>
       <c r="T52">
-        <v>373000000</v>
+        <v>2006000000</v>
       </c>
       <c r="U52">
-        <v>199000000</v>
+        <v>413000000</v>
       </c>
       <c r="V52" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -4626,67 +4689,67 @@
         <v>73</v>
       </c>
       <c r="B53" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C53" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D53" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="E53">
-        <v>109.0599975585938</v>
+        <v>82.58999633789062</v>
       </c>
       <c r="F53">
-        <v>1064856.8</v>
+        <v>545993.3333333334</v>
       </c>
       <c r="G53">
-        <v>97.34639968872071</v>
+        <v>79.75639991760254</v>
       </c>
       <c r="H53">
-        <v>90.31639968872071</v>
+        <v>66.07173319498698</v>
       </c>
       <c r="I53">
-        <v>84.31564975738526</v>
+        <v>63.63964992523194</v>
       </c>
       <c r="J53">
-        <v>81.55844982147217</v>
+        <v>60.75819997787475</v>
       </c>
       <c r="K53">
-        <v>0.02227001264691353</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="L53">
-        <v>132.0598602294922</v>
+        <v>86.93000030517578</v>
       </c>
       <c r="M53">
-        <v>132.0532977514115</v>
+        <v>132.3943461258388</v>
       </c>
       <c r="N53">
-        <v>8</v>
+        <v>1.95</v>
       </c>
       <c r="O53">
-        <v>10.15</v>
+        <v>0.88</v>
       </c>
       <c r="P53">
-        <v>6.05</v>
+        <v>0.25</v>
       </c>
       <c r="Q53">
-        <v>10.35</v>
+        <v>1.97</v>
       </c>
       <c r="R53">
-        <v>5291476000</v>
+        <v>154800000</v>
       </c>
       <c r="S53">
-        <v>6699364000</v>
+        <v>73300000</v>
       </c>
       <c r="T53">
-        <v>3952737000</v>
+        <v>24800000</v>
       </c>
       <c r="U53">
-        <v>6754634000</v>
+        <v>153800000</v>
       </c>
       <c r="V53" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -4694,67 +4757,67 @@
         <v>74</v>
       </c>
       <c r="B54" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="C54" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="D54" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="E54">
-        <v>143.8999938964844</v>
+        <v>52.2400016784668</v>
       </c>
       <c r="F54">
-        <v>366311.0666666667</v>
+        <v>1589146.666666667</v>
       </c>
       <c r="G54">
-        <v>134.8834001159668</v>
+        <v>44.63120010375977</v>
       </c>
       <c r="H54">
-        <v>119.9737999979655</v>
+        <v>41.08480008443197</v>
       </c>
       <c r="I54">
-        <v>110.4302001190186</v>
+        <v>40.01090007781983</v>
       </c>
       <c r="J54">
-        <v>103.4217502975464</v>
+        <v>37.89395005226135</v>
       </c>
       <c r="K54">
-        <v>0.577300488948822</v>
+        <v>20.39999961853027</v>
       </c>
       <c r="L54">
-        <v>150.4900054931641</v>
+        <v>52.68000030517578</v>
       </c>
       <c r="M54">
-        <v>131.755657470813</v>
+        <v>132.3638191578668</v>
       </c>
       <c r="N54">
-        <v>7.1</v>
+        <v>0.41</v>
       </c>
       <c r="O54">
-        <v>7.09</v>
+        <v>0.92</v>
       </c>
       <c r="P54">
-        <v>3.54</v>
+        <v>0.74</v>
       </c>
       <c r="Q54">
-        <v>5.02</v>
+        <v>0.45</v>
       </c>
       <c r="R54">
-        <v>262489000</v>
+        <v>33585000</v>
       </c>
       <c r="S54">
-        <v>262365000</v>
+        <v>134962000</v>
       </c>
       <c r="T54">
-        <v>131301000</v>
+        <v>108063000</v>
       </c>
       <c r="U54">
-        <v>186836000</v>
+        <v>65816000</v>
       </c>
       <c r="V54" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="55" spans="1:22">
@@ -4762,67 +4825,67 @@
         <v>75</v>
       </c>
       <c r="B55" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C55" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D55" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="E55">
-        <v>118.9599990844727</v>
+        <v>80.76000213623047</v>
       </c>
       <c r="F55">
-        <v>320661.6333333334</v>
+        <v>1475296.666666667</v>
       </c>
       <c r="G55">
-        <v>110.3507995605469</v>
+        <v>77.09020050048828</v>
       </c>
       <c r="H55">
-        <v>91.61526657104493</v>
+        <v>65.42453348795573</v>
       </c>
       <c r="I55">
-        <v>87.02514989852905</v>
+        <v>60.71920019149781</v>
       </c>
       <c r="J55">
-        <v>82.33244993209838</v>
+        <v>56.97220012664795</v>
       </c>
       <c r="K55">
-        <v>20.81999969482422</v>
+        <v>0.5319142937660217</v>
       </c>
       <c r="L55">
-        <v>124.3199996948242</v>
+        <v>83.51999664306641</v>
       </c>
       <c r="M55">
-        <v>131.5081729109738</v>
+        <v>131.7932215214609</v>
       </c>
       <c r="N55">
-        <v>1.03</v>
+        <v>2.35</v>
       </c>
       <c r="O55">
-        <v>1.05</v>
+        <v>5.63</v>
       </c>
       <c r="P55">
-        <v>1.34</v>
+        <v>1.7</v>
       </c>
       <c r="Q55">
-        <v>0.59</v>
+        <v>2.85</v>
       </c>
       <c r="R55">
-        <v>51575000</v>
+        <v>273467000</v>
       </c>
       <c r="S55">
-        <v>52215000</v>
+        <v>640536000</v>
       </c>
       <c r="T55">
-        <v>66214000</v>
+        <v>191530000</v>
       </c>
       <c r="U55">
-        <v>29068000</v>
+        <v>320216000</v>
       </c>
       <c r="V55" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="56" spans="1:22">
@@ -4830,67 +4893,67 @@
         <v>76</v>
       </c>
       <c r="B56" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="C56" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="D56" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="E56">
-        <v>15.58500003814697</v>
+        <v>51.5099983215332</v>
       </c>
       <c r="F56">
-        <v>886388.9</v>
+        <v>688150</v>
       </c>
       <c r="G56">
-        <v>13.05909999847412</v>
+        <v>46.24440002441406</v>
       </c>
       <c r="H56">
-        <v>12.66563334147135</v>
+        <v>40.85913327534993</v>
       </c>
       <c r="I56">
-        <v>12.21347500324249</v>
+        <v>38.48434993743896</v>
       </c>
       <c r="J56">
-        <v>11.80485000610352</v>
+        <v>36.43699994087219</v>
       </c>
       <c r="K56">
-        <v>9.039999961853027</v>
+        <v>0.02175931446254253</v>
       </c>
       <c r="L56">
-        <v>15.89999961853027</v>
+        <v>59.96058654785156</v>
       </c>
       <c r="M56">
-        <v>130.9738666142341</v>
+        <v>131.5834964933555</v>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>144400000</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>79776000</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>80700000</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>93493000</v>
       </c>
       <c r="V56" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -4898,67 +4961,67 @@
         <v>77</v>
       </c>
       <c r="B57" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="C57" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D57" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="E57">
-        <v>59.29000091552734</v>
+        <v>120.25</v>
       </c>
       <c r="F57">
-        <v>689176.7</v>
+        <v>306303.3333333333</v>
       </c>
       <c r="G57">
-        <v>50.93819984436035</v>
+        <v>111.5819995117187</v>
       </c>
       <c r="H57">
-        <v>46.17119997660319</v>
+        <v>92.67013320922851</v>
       </c>
       <c r="I57">
-        <v>45.18180002212524</v>
+        <v>87.92689987182617</v>
       </c>
       <c r="J57">
-        <v>43.92014999389649</v>
+        <v>82.94034990310669</v>
       </c>
       <c r="K57">
-        <v>5.159999847412109</v>
+        <v>20.81999969482422</v>
       </c>
       <c r="L57">
-        <v>59.40999984741211</v>
+        <v>124.3199996948242</v>
       </c>
       <c r="M57">
-        <v>130.7909113705638</v>
+        <v>131.3232784295469</v>
       </c>
       <c r="N57">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="O57">
-        <v>0.01</v>
+        <v>1.05</v>
       </c>
       <c r="P57">
-        <v>0.52</v>
+        <v>1.34</v>
       </c>
       <c r="Q57">
-        <v>2.07</v>
+        <v>0.59</v>
       </c>
       <c r="R57">
-        <v>113000000</v>
+        <v>51575000</v>
       </c>
       <c r="S57">
-        <v>1000000</v>
+        <v>52215000</v>
       </c>
       <c r="T57">
-        <v>37000000</v>
+        <v>66214000</v>
       </c>
       <c r="U57">
-        <v>142000000</v>
+        <v>29068000</v>
       </c>
       <c r="V57" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="58" spans="1:22">
@@ -4966,67 +5029,67 @@
         <v>78</v>
       </c>
       <c r="B58" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="C58" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D58" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="E58">
-        <v>108.1999969482422</v>
+        <v>28.36000061035156</v>
       </c>
       <c r="F58">
-        <v>1063030</v>
+        <v>617966.6666666666</v>
       </c>
       <c r="G58">
-        <v>103.1107995605469</v>
+        <v>25.58259994506836</v>
       </c>
       <c r="H58">
-        <v>87.78066650390625</v>
+        <v>22.4570666440328</v>
       </c>
       <c r="I58">
-        <v>82.60159980773926</v>
+        <v>21.52535000324249</v>
       </c>
       <c r="J58">
-        <v>77.37124988555908</v>
+        <v>20.23989997863769</v>
       </c>
       <c r="K58">
-        <v>0.3787146806716919</v>
+        <v>4.372677803039551</v>
       </c>
       <c r="L58">
-        <v>115.1399993896484</v>
+        <v>29.73999977111816</v>
       </c>
       <c r="M58">
-        <v>130.7831613826413</v>
+        <v>131.27547443351</v>
       </c>
       <c r="N58">
-        <v>2.25</v>
+        <v>0.51</v>
       </c>
       <c r="O58">
-        <v>1.61</v>
+        <v>1.27</v>
       </c>
       <c r="P58">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="Q58">
-        <v>1.72</v>
+        <v>1.28</v>
       </c>
       <c r="R58">
-        <v>315000000</v>
+        <v>20311465</v>
       </c>
       <c r="S58">
-        <v>223000000</v>
+        <v>51263710</v>
       </c>
       <c r="T58">
-        <v>207000000</v>
+        <v>76021035</v>
       </c>
       <c r="U58">
-        <v>233000000</v>
+        <v>51721137</v>
       </c>
       <c r="V58" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="59" spans="1:22">
@@ -5034,67 +5097,67 @@
         <v>79</v>
       </c>
       <c r="B59" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C59" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="D59" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="E59">
-        <v>691.6300048828125</v>
+        <v>46</v>
       </c>
       <c r="F59">
-        <v>1293747.133333333</v>
+        <v>277470</v>
       </c>
       <c r="G59">
-        <v>633.7390014648438</v>
+        <v>39.94239974975586</v>
       </c>
       <c r="H59">
-        <v>544.2846663411458</v>
+        <v>36.94793333689372</v>
       </c>
       <c r="I59">
-        <v>515.6605995178222</v>
+        <v>35.22249998092651</v>
       </c>
       <c r="J59">
-        <v>487.3533992004395</v>
+        <v>33.71200003623962</v>
       </c>
       <c r="K59">
-        <v>0.5958155393600464</v>
+        <v>6.900000095367432</v>
       </c>
       <c r="L59">
-        <v>729.8200073242188</v>
+        <v>47.5</v>
       </c>
       <c r="M59">
-        <v>130.2812167710583</v>
+        <v>131.2752860153809</v>
       </c>
       <c r="N59">
-        <v>10.39</v>
+        <v>0.89</v>
       </c>
       <c r="O59">
-        <v>10.77</v>
+        <v>0.98</v>
       </c>
       <c r="P59">
-        <v>6.01</v>
+        <v>1.16</v>
       </c>
       <c r="Q59">
-        <v>5.97</v>
+        <v>0.7</v>
       </c>
       <c r="R59">
-        <v>1425879000</v>
+        <v>21107000</v>
       </c>
       <c r="S59">
-        <v>1468507000</v>
+        <v>23201000</v>
       </c>
       <c r="T59">
-        <v>814008000</v>
+        <v>27570000</v>
       </c>
       <c r="U59">
-        <v>802537000</v>
+        <v>16589000</v>
       </c>
       <c r="V59" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -5102,67 +5165,67 @@
         <v>80</v>
       </c>
       <c r="B60" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="C60" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="D60" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="E60">
-        <v>28.88999938964844</v>
+        <v>3225.969970703125</v>
       </c>
       <c r="F60">
-        <v>883493.3333333334</v>
+        <v>335270</v>
       </c>
       <c r="G60">
-        <v>26.13320003509521</v>
+        <v>2768.298779296875</v>
       </c>
       <c r="H60">
-        <v>23.09926661173503</v>
+        <v>2599.471334635416</v>
       </c>
       <c r="I60">
-        <v>21.76979996204376</v>
+        <v>2436.522850952148</v>
       </c>
       <c r="J60">
-        <v>20.37919998168945</v>
+        <v>2310.925403442383</v>
       </c>
       <c r="K60">
-        <v>9.090000152587891</v>
+        <v>6.599999904632568</v>
       </c>
       <c r="L60">
-        <v>29.15999984741211</v>
+        <v>3243.010009765625</v>
       </c>
       <c r="M60">
-        <v>130.1711409472614</v>
+        <v>130.875680939457</v>
       </c>
       <c r="N60">
-        <v>0.06</v>
+        <v>41.98</v>
       </c>
       <c r="O60">
-        <v>0.06</v>
+        <v>31.92</v>
       </c>
       <c r="P60">
-        <v>0.04</v>
+        <v>7</v>
       </c>
       <c r="Q60">
-        <v>0.05</v>
+        <v>34.89</v>
       </c>
       <c r="R60">
-        <v>30000000</v>
+        <v>1666000000</v>
       </c>
       <c r="S60">
-        <v>28000000</v>
+        <v>1235000000</v>
       </c>
       <c r="T60">
-        <v>22000000</v>
+        <v>266000000</v>
       </c>
       <c r="U60">
-        <v>26000000</v>
+        <v>1290000000</v>
       </c>
       <c r="V60" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="61" spans="1:22">
@@ -5170,31 +5233,31 @@
         <v>81</v>
       </c>
       <c r="B61" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C61" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="D61" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E61">
-        <v>69.40000152587891</v>
+        <v>71.72000122070312</v>
       </c>
       <c r="F61">
-        <v>1387912.733333333</v>
+        <v>1439993.333333333</v>
       </c>
       <c r="G61">
-        <v>62.82020011901855</v>
+        <v>63.64360000610352</v>
       </c>
       <c r="H61">
-        <v>56.82666664123535</v>
+        <v>57.35073328653971</v>
       </c>
       <c r="I61">
-        <v>53.56769994735718</v>
+        <v>54.01249992370605</v>
       </c>
       <c r="J61">
-        <v>51.02379997253418</v>
+        <v>51.35089996337891</v>
       </c>
       <c r="K61">
         <v>0.1557042300701141</v>
@@ -5203,7 +5266,7 @@
         <v>79.82826232910156</v>
       </c>
       <c r="M61">
-        <v>129.5236368294642</v>
+        <v>130.8335549968744</v>
       </c>
       <c r="N61">
         <v>0.7</v>
@@ -5230,7 +5293,7 @@
         <v>152900000</v>
       </c>
       <c r="V61" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="62" spans="1:22">
@@ -5238,67 +5301,67 @@
         <v>82</v>
       </c>
       <c r="B62" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="C62" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="D62" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="E62">
-        <v>56.15000152587891</v>
+        <v>59.77999877929688</v>
       </c>
       <c r="F62">
-        <v>1479613.333333333</v>
+        <v>1514740</v>
       </c>
       <c r="G62">
-        <v>49.50940010070801</v>
+        <v>54.67240005493164</v>
       </c>
       <c r="H62">
-        <v>44.54780001322428</v>
+        <v>50.23466669718425</v>
       </c>
       <c r="I62">
-        <v>42.80825002670288</v>
+        <v>47.31055002212524</v>
       </c>
       <c r="J62">
-        <v>40.73250000953674</v>
+        <v>44.71335000991822</v>
       </c>
       <c r="K62">
-        <v>11.8095235824585</v>
+        <v>1.326302051544189</v>
       </c>
       <c r="L62">
-        <v>56.15000152587891</v>
+        <v>60.29999923706055</v>
       </c>
       <c r="M62">
-        <v>129.1571037060192</v>
+        <v>130.3101842471494</v>
       </c>
       <c r="N62">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="O62">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="P62">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q62">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="R62">
-        <v>93400000</v>
+        <v>0</v>
       </c>
       <c r="S62">
-        <v>158700000</v>
+        <v>0</v>
       </c>
       <c r="T62">
-        <v>93800000</v>
+        <v>0</v>
       </c>
       <c r="U62">
-        <v>112900000</v>
+        <v>0</v>
       </c>
       <c r="V62" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="63" spans="1:22">
@@ -5306,67 +5369,67 @@
         <v>83</v>
       </c>
       <c r="B63" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C63" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D63" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="E63">
-        <v>495.5299987792969</v>
+        <v>57.58000183105469</v>
       </c>
       <c r="F63">
-        <v>416651.0666666667</v>
+        <v>3771426.666666667</v>
       </c>
       <c r="G63">
-        <v>425.8608001708984</v>
+        <v>51.73339973449707</v>
       </c>
       <c r="H63">
-        <v>393.860767211914</v>
+        <v>45.06086654663086</v>
       </c>
       <c r="I63">
-        <v>389.8113252258301</v>
+        <v>43.96159990310669</v>
       </c>
       <c r="J63">
-        <v>378.0562748718262</v>
+        <v>42.0682999420166</v>
       </c>
       <c r="K63">
-        <v>19.76499938964844</v>
+        <v>11.99751472473145</v>
       </c>
       <c r="L63">
-        <v>548.4299926757812</v>
+        <v>60.77000045776367</v>
       </c>
       <c r="M63">
-        <v>129.1447575418808</v>
+        <v>130.1933490976917</v>
       </c>
       <c r="N63">
-        <v>-0.52</v>
+        <v>0.68</v>
       </c>
       <c r="O63">
-        <v>-4.26</v>
+        <v>0.33</v>
       </c>
       <c r="P63">
-        <v>-0.7</v>
+        <v>0.84</v>
       </c>
       <c r="Q63">
-        <v>-0.52</v>
+        <v>0.79</v>
       </c>
       <c r="R63">
-        <v>-235042000</v>
+        <v>511000000</v>
       </c>
       <c r="S63">
-        <v>-38613000</v>
+        <v>245000000</v>
       </c>
       <c r="T63">
-        <v>-28871000</v>
+        <v>614000000</v>
       </c>
       <c r="U63">
-        <v>-94368000</v>
+        <v>583000000</v>
       </c>
       <c r="V63" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -5374,67 +5437,67 @@
         <v>84</v>
       </c>
       <c r="B64" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C64" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="D64" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="E64">
-        <v>31.90999984741211</v>
+        <v>32.47000122070312</v>
       </c>
       <c r="F64">
-        <v>745569.7333333333</v>
+        <v>1035340</v>
       </c>
       <c r="G64">
-        <v>25.96280014038086</v>
+        <v>31.92340007781982</v>
       </c>
       <c r="H64">
-        <v>25.69033339182536</v>
+        <v>27.03586671193441</v>
       </c>
       <c r="I64">
-        <v>24.86230004310608</v>
+        <v>24.72665006160736</v>
       </c>
       <c r="J64">
-        <v>23.67315005302429</v>
+        <v>23.06045005321503</v>
       </c>
       <c r="K64">
-        <v>0.6000000238418579</v>
+        <v>6.139999866485596</v>
       </c>
       <c r="L64">
-        <v>31.90999984741211</v>
+        <v>33.66999816894531</v>
       </c>
       <c r="M64">
-        <v>128.9200542805826</v>
+        <v>129.8881568220512</v>
       </c>
       <c r="N64">
-        <v>2.5</v>
+        <v>1.45</v>
       </c>
       <c r="O64">
-        <v>4.47</v>
+        <v>1.98</v>
       </c>
       <c r="P64">
-        <v>1.4</v>
+        <v>0.73</v>
       </c>
       <c r="Q64">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="R64">
-        <v>149125000</v>
+        <v>149226000</v>
       </c>
       <c r="S64">
-        <v>267396000</v>
+        <v>202973000</v>
       </c>
       <c r="T64">
-        <v>84719000</v>
+        <v>74742000</v>
       </c>
       <c r="U64">
-        <v>237890000</v>
+        <v>60724000</v>
       </c>
       <c r="V64" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5442,67 +5505,67 @@
         <v>85</v>
       </c>
       <c r="B65" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C65" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D65" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="E65">
-        <v>77.12999725341797</v>
+        <v>189.1699981689453</v>
       </c>
       <c r="F65">
-        <v>1535791.233333333</v>
+        <v>1452200</v>
       </c>
       <c r="G65">
-        <v>76.21000030517578</v>
+        <v>159.8356002807617</v>
       </c>
       <c r="H65">
-        <v>64.81606679280598</v>
+        <v>153.9478668212891</v>
       </c>
       <c r="I65">
-        <v>60.14440019607544</v>
+        <v>145.5855501174927</v>
       </c>
       <c r="J65">
-        <v>56.44925012588501</v>
+        <v>139.6980000305176</v>
       </c>
       <c r="K65">
-        <v>0.5319142937660217</v>
+        <v>-8.571051876060665E-05</v>
       </c>
       <c r="L65">
-        <v>83.51999664306641</v>
+        <v>189.1699981689453</v>
       </c>
       <c r="M65">
-        <v>128.7475335240506</v>
+        <v>129.5621745414584</v>
       </c>
       <c r="N65">
-        <v>2.35</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="O65">
-        <v>5.63</v>
+        <v>5.86</v>
       </c>
       <c r="P65">
-        <v>1.7</v>
+        <v>6.34</v>
       </c>
       <c r="Q65">
-        <v>2.85</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="R65">
-        <v>273467000</v>
+        <v>13318000000</v>
       </c>
       <c r="S65">
-        <v>640536000</v>
+        <v>14405000000</v>
       </c>
       <c r="T65">
-        <v>191530000</v>
+        <v>13592000000</v>
       </c>
       <c r="U65">
-        <v>320216000</v>
+        <v>19814000000</v>
       </c>
       <c r="V65" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5510,67 +5573,67 @@
         <v>86</v>
       </c>
       <c r="B66" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C66" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="D66" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="E66">
-        <v>49.45999908447266</v>
+        <v>696</v>
       </c>
       <c r="F66">
-        <v>699466.1666666666</v>
+        <v>1258723.333333333</v>
       </c>
       <c r="G66">
-        <v>45.5818000793457</v>
+        <v>640.7808020019531</v>
       </c>
       <c r="H66">
-        <v>40.45573328653971</v>
+        <v>549.9502665201823</v>
       </c>
       <c r="I66">
-        <v>38.14824995040894</v>
+        <v>521.2905494689942</v>
       </c>
       <c r="J66">
-        <v>36.20504995346069</v>
+        <v>490.62169921875</v>
       </c>
       <c r="K66">
-        <v>0.02175931446254253</v>
+        <v>0.5958155393600464</v>
       </c>
       <c r="L66">
-        <v>59.96058654785156</v>
+        <v>729.8200073242188</v>
       </c>
       <c r="M66">
-        <v>128.5911648524974</v>
+        <v>129.507961092539</v>
       </c>
       <c r="N66">
-        <v>1.98</v>
+        <v>10.39</v>
       </c>
       <c r="O66">
-        <v>1.08</v>
+        <v>10.77</v>
       </c>
       <c r="P66">
-        <v>1.08</v>
+        <v>6.01</v>
       </c>
       <c r="Q66">
-        <v>1.24</v>
+        <v>5.97</v>
       </c>
       <c r="R66">
-        <v>144400000</v>
+        <v>1425879000</v>
       </c>
       <c r="S66">
-        <v>79776000</v>
+        <v>1468507000</v>
       </c>
       <c r="T66">
-        <v>80700000</v>
+        <v>814008000</v>
       </c>
       <c r="U66">
-        <v>93493000</v>
+        <v>802537000</v>
       </c>
       <c r="V66" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -5578,67 +5641,67 @@
         <v>87</v>
       </c>
       <c r="B67" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="C67" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="D67" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="E67">
-        <v>173.2700042724609</v>
+        <v>139.9400024414062</v>
       </c>
       <c r="F67">
-        <v>333383.3333333333</v>
+        <v>57009920</v>
       </c>
       <c r="G67">
-        <v>159.8541998291016</v>
+        <v>128.864800567627</v>
       </c>
       <c r="H67">
-        <v>143.0354002380371</v>
+        <v>109.9811336263021</v>
       </c>
       <c r="I67">
-        <v>136.3687001800537</v>
+        <v>106.1211002349853</v>
       </c>
       <c r="J67">
-        <v>129.4414003372192</v>
+        <v>104.3732000732422</v>
       </c>
       <c r="K67">
-        <v>2.075098752975464</v>
+        <v>0.0697920024394989</v>
       </c>
       <c r="L67">
-        <v>179.6499938964844</v>
+        <v>186.5704956054688</v>
       </c>
       <c r="M67">
-        <v>127.8041030511158</v>
+        <v>129.4651771430167</v>
       </c>
       <c r="N67">
-        <v>4.61</v>
+        <v>0.28</v>
       </c>
       <c r="O67">
-        <v>4.21</v>
+        <v>0.03</v>
       </c>
       <c r="P67">
-        <v>4.31</v>
+        <v>0.31</v>
       </c>
       <c r="Q67">
-        <v>4.41</v>
+        <v>0.65</v>
       </c>
       <c r="R67">
-        <v>340100000</v>
+        <v>2872000000</v>
       </c>
       <c r="S67">
-        <v>298000000</v>
+        <v>278000000</v>
       </c>
       <c r="T67">
-        <v>298300000</v>
+        <v>3172000000</v>
       </c>
       <c r="U67">
-        <v>300800000</v>
+        <v>6750000000</v>
       </c>
       <c r="V67" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5646,67 +5709,67 @@
         <v>88</v>
       </c>
       <c r="B68" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C68" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D68" t="s">
-        <v>185</v>
+        <v>235</v>
       </c>
       <c r="E68">
-        <v>419.3110961914062</v>
+        <v>57.38999938964844</v>
       </c>
       <c r="F68">
-        <v>740604.4666666667</v>
+        <v>5234083.333333333</v>
       </c>
       <c r="G68">
-        <v>375.8520245361328</v>
+        <v>50.49900009155274</v>
       </c>
       <c r="H68">
-        <v>343.680141398112</v>
+        <v>46.16986671447754</v>
       </c>
       <c r="I68">
-        <v>330.7309060668945</v>
+        <v>45.06964998245239</v>
       </c>
       <c r="J68">
-        <v>315.944700088501</v>
+        <v>43.06335000991821</v>
       </c>
       <c r="K68">
-        <v>1.31995165348053</v>
+        <v>11.31525421142578</v>
       </c>
       <c r="L68">
-        <v>419.3110961914062</v>
+        <v>59.79999923706055</v>
       </c>
       <c r="M68">
-        <v>127.7868839661596</v>
+        <v>129.3462862966608</v>
       </c>
       <c r="N68">
-        <v>0.99</v>
+        <v>1.53</v>
       </c>
       <c r="O68">
-        <v>2.98</v>
+        <v>0.32</v>
       </c>
       <c r="P68">
-        <v>3.04</v>
+        <v>0.44</v>
       </c>
       <c r="Q68">
-        <v>4.54</v>
+        <v>0.23</v>
       </c>
       <c r="R68">
-        <v>128831000</v>
+        <v>1312000000</v>
       </c>
       <c r="S68">
-        <v>387854000</v>
+        <v>270000000</v>
       </c>
       <c r="T68">
-        <v>395237000</v>
+        <v>373000000</v>
       </c>
       <c r="U68">
-        <v>590889000</v>
+        <v>199000000</v>
       </c>
       <c r="V68" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
     </row>
     <row r="69" spans="1:22">
@@ -5714,67 +5777,67 @@
         <v>89</v>
       </c>
       <c r="B69" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C69" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="D69" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E69">
-        <v>265.4500122070312</v>
+        <v>108.3099975585938</v>
       </c>
       <c r="F69">
-        <v>2300726.666666667</v>
+        <v>1012466.666666667</v>
       </c>
       <c r="G69">
-        <v>242.7173999023437</v>
+        <v>104.9469995117187</v>
       </c>
       <c r="H69">
-        <v>221.2159335327148</v>
+        <v>88.85879989624023</v>
       </c>
       <c r="I69">
-        <v>207.807250289917</v>
+        <v>83.5732998085022</v>
       </c>
       <c r="J69">
-        <v>197.0947500610351</v>
+        <v>78.39279985427856</v>
       </c>
       <c r="K69">
-        <v>0.8275843262672424</v>
+        <v>0.3787146806716919</v>
       </c>
       <c r="L69">
-        <v>312.9627685546875</v>
+        <v>115.1399993896484</v>
       </c>
       <c r="M69">
-        <v>127.6254711441808</v>
+        <v>129.3410642721542</v>
       </c>
       <c r="N69">
-        <v>3.33</v>
+        <v>2.25</v>
       </c>
       <c r="O69">
-        <v>3.07</v>
+        <v>1.61</v>
       </c>
       <c r="P69">
-        <v>3.05</v>
+        <v>1.52</v>
       </c>
       <c r="Q69">
-        <v>6.05</v>
+        <v>1.72</v>
       </c>
       <c r="R69">
-        <v>875000000</v>
+        <v>315000000</v>
       </c>
       <c r="S69">
-        <v>788000000</v>
+        <v>223000000</v>
       </c>
       <c r="T69">
-        <v>771000000</v>
+        <v>207000000</v>
       </c>
       <c r="U69">
-        <v>1538000000</v>
+        <v>233000000</v>
       </c>
       <c r="V69" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5782,67 +5845,67 @@
         <v>90</v>
       </c>
       <c r="B70" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C70" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D70" t="s">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="E70">
-        <v>16.28000068664551</v>
+        <v>425.1199951171875</v>
       </c>
       <c r="F70">
-        <v>402072.8333333333</v>
+        <v>744006.6666666666</v>
       </c>
       <c r="G70">
-        <v>14.96080005645752</v>
+        <v>381.5554022216797</v>
       </c>
       <c r="H70">
-        <v>13.07600001653035</v>
+        <v>346.3016007486979</v>
       </c>
       <c r="I70">
-        <v>13.02175000667572</v>
+        <v>333.0744006347657</v>
       </c>
       <c r="J70">
-        <v>12.70985001087189</v>
+        <v>317.908500289917</v>
       </c>
       <c r="K70">
-        <v>10.27999973297119</v>
+        <v>1.31995165348053</v>
       </c>
       <c r="L70">
-        <v>21.03000068664551</v>
+        <v>425.1199951171875</v>
       </c>
       <c r="M70">
-        <v>127.4969527508918</v>
+        <v>128.8851268634323</v>
       </c>
       <c r="N70">
-        <v>-1.9552</v>
+        <v>2.98</v>
       </c>
       <c r="O70">
-        <v>-0.2692</v>
+        <v>3.04</v>
       </c>
       <c r="P70">
-        <v>-0.0328</v>
+        <v>4.54</v>
       </c>
       <c r="Q70">
-        <v>-1.9552</v>
+        <v>5.44</v>
       </c>
       <c r="R70">
-        <v>-125294000</v>
+        <v>387854000</v>
       </c>
       <c r="S70">
-        <v>-201907000</v>
+        <v>395237000</v>
       </c>
       <c r="T70">
-        <v>993042000</v>
+        <v>590889000</v>
       </c>
       <c r="U70">
-        <v>-904131000</v>
+        <v>708956000</v>
       </c>
       <c r="V70" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -5850,67 +5913,67 @@
         <v>91</v>
       </c>
       <c r="B71" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C71" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D71" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="E71">
-        <v>48.77999877929688</v>
+        <v>55.20000076293945</v>
       </c>
       <c r="F71">
-        <v>1011090</v>
+        <v>1526166.666666667</v>
       </c>
       <c r="G71">
-        <v>47.26279991149902</v>
+        <v>50.52380012512207</v>
       </c>
       <c r="H71">
-        <v>40.33906665802002</v>
+        <v>44.99580004374186</v>
       </c>
       <c r="I71">
-        <v>37.26875001907349</v>
+        <v>43.24800004959106</v>
       </c>
       <c r="J71">
-        <v>34.80835000991821</v>
+        <v>41.09634999275207</v>
       </c>
       <c r="K71">
-        <v>7.050000190734863</v>
+        <v>11.8095235824585</v>
       </c>
       <c r="L71">
-        <v>51.63999938964844</v>
+        <v>56.15000152587891</v>
       </c>
       <c r="M71">
-        <v>127.3767151230392</v>
+        <v>128.5758769746884</v>
       </c>
       <c r="N71">
-        <v>2.72</v>
+        <v>0.55</v>
       </c>
       <c r="O71">
-        <v>2.51</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P71">
-        <v>1.74</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q71">
-        <v>2.12</v>
+        <v>0.67</v>
       </c>
       <c r="R71">
-        <v>309779000</v>
+        <v>93400000</v>
       </c>
       <c r="S71">
-        <v>275331000</v>
+        <v>158700000</v>
       </c>
       <c r="T71">
-        <v>191051000</v>
+        <v>93800000</v>
       </c>
       <c r="U71">
-        <v>234602000</v>
+        <v>112900000</v>
       </c>
       <c r="V71" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5918,67 +5981,67 @@
         <v>92</v>
       </c>
       <c r="B72" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C72" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="D72" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="E72">
-        <v>408.239990234375</v>
+        <v>75.19999694824219</v>
       </c>
       <c r="F72">
-        <v>972792.8666666667</v>
+        <v>316386.6666666667</v>
       </c>
       <c r="G72">
-        <v>355.5105993652344</v>
+        <v>69.77279960632325</v>
       </c>
       <c r="H72">
-        <v>338.0415997314453</v>
+        <v>61.45339991251628</v>
       </c>
       <c r="I72">
-        <v>325.3418496704102</v>
+        <v>58.39519996643067</v>
       </c>
       <c r="J72">
-        <v>311.7542498779297</v>
+        <v>55.28369998931885</v>
       </c>
       <c r="K72">
-        <v>0.6462651491165161</v>
+        <v>10.73999977111816</v>
       </c>
       <c r="L72">
-        <v>427.5899963378906</v>
+        <v>76.09999847412109</v>
       </c>
       <c r="M72">
-        <v>127.3644032535261</v>
+        <v>128.5525964359129</v>
       </c>
       <c r="N72">
-        <v>3.36</v>
+        <v>2.07</v>
       </c>
       <c r="O72">
-        <v>2.92</v>
+        <v>2.41</v>
       </c>
       <c r="P72">
-        <v>2.58</v>
+        <v>1.53</v>
       </c>
       <c r="Q72">
-        <v>2.65</v>
+        <v>1.8</v>
       </c>
       <c r="R72">
-        <v>377401000</v>
+        <v>89470000</v>
       </c>
       <c r="S72">
-        <v>323929000</v>
+        <v>103153000</v>
       </c>
       <c r="T72">
-        <v>285038000</v>
+        <v>64775000</v>
       </c>
       <c r="U72">
-        <v>292362000</v>
+        <v>75593000</v>
       </c>
       <c r="V72" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -5986,67 +6049,67 @@
         <v>93</v>
       </c>
       <c r="B73" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C73" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="D73" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="E73">
-        <v>104.1699981689453</v>
+        <v>28.44000053405762</v>
       </c>
       <c r="F73">
-        <v>284311.6666666667</v>
+        <v>718096.6666666666</v>
       </c>
       <c r="G73">
-        <v>96.30060012817383</v>
+        <v>26.57020004272461</v>
       </c>
       <c r="H73">
-        <v>86.2268669128418</v>
+        <v>23.35806662241618</v>
       </c>
       <c r="I73">
-        <v>81.76900022506715</v>
+        <v>22.04144996166229</v>
       </c>
       <c r="J73">
-        <v>79.30515024185181</v>
+        <v>20.61684997558594</v>
       </c>
       <c r="K73">
-        <v>12.27999973297119</v>
+        <v>9.090000152587891</v>
       </c>
       <c r="L73">
-        <v>108.4400024414062</v>
+        <v>29.15999984741211</v>
       </c>
       <c r="M73">
-        <v>127.145499222131</v>
+        <v>128.4947166298838</v>
       </c>
       <c r="N73">
-        <v>1.22</v>
+        <v>0.06</v>
       </c>
       <c r="O73">
-        <v>0.78</v>
+        <v>0.04</v>
       </c>
       <c r="P73">
-        <v>2.17</v>
+        <v>0.05</v>
       </c>
       <c r="Q73">
-        <v>1.38</v>
+        <v>0.12</v>
       </c>
       <c r="R73">
-        <v>77000000</v>
+        <v>28000000</v>
       </c>
       <c r="S73">
-        <v>49000000</v>
+        <v>22000000</v>
       </c>
       <c r="T73">
-        <v>131000000</v>
+        <v>26000000</v>
       </c>
       <c r="U73">
-        <v>83000000</v>
+        <v>48000000</v>
       </c>
       <c r="V73" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -6054,67 +6117,67 @@
         <v>94</v>
       </c>
       <c r="B74" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C74" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="D74" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="E74">
-        <v>10.86989974975586</v>
+        <v>220.1999969482422</v>
       </c>
       <c r="F74">
-        <v>444014.2333333333</v>
+        <v>2104996.666666667</v>
       </c>
       <c r="G74">
-        <v>9.791197967529296</v>
+        <v>199.2880004882813</v>
       </c>
       <c r="H74">
-        <v>8.724799318313599</v>
+        <v>177.4793339029948</v>
       </c>
       <c r="I74">
-        <v>8.575049488544463</v>
+        <v>172.3828505706787</v>
       </c>
       <c r="J74">
-        <v>8.358299994468689</v>
+        <v>165.1082005310058</v>
       </c>
       <c r="K74">
-        <v>3.549999952316284</v>
+        <v>0.004536735825240612</v>
       </c>
       <c r="L74">
-        <v>13.5</v>
+        <v>221.0899963378906</v>
       </c>
       <c r="M74">
-        <v>126.8588001506004</v>
+        <v>128.3989458739862</v>
       </c>
       <c r="N74">
-        <v>0.168</v>
+        <v>1.52</v>
       </c>
       <c r="O74">
-        <v>0.205</v>
+        <v>1.8</v>
       </c>
       <c r="P74">
-        <v>0.024961</v>
+        <v>1.59</v>
       </c>
       <c r="Q74">
-        <v>0.2</v>
+        <v>1.86</v>
       </c>
       <c r="R74">
-        <v>19087000</v>
+        <v>607000000</v>
       </c>
       <c r="S74">
-        <v>22548000</v>
+        <v>721000000</v>
       </c>
       <c r="T74">
-        <v>2732000</v>
+        <v>638000000</v>
       </c>
       <c r="U74">
-        <v>21569000</v>
+        <v>744000000</v>
       </c>
       <c r="V74" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -6122,67 +6185,67 @@
         <v>95</v>
       </c>
       <c r="B75" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C75" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D75" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E75">
-        <v>103.5699996948242</v>
+        <v>49.11000061035156</v>
       </c>
       <c r="F75">
-        <v>6025520</v>
+        <v>989426.6666666666</v>
       </c>
       <c r="G75">
-        <v>93.40379989624023</v>
+        <v>47.70439994812012</v>
       </c>
       <c r="H75">
-        <v>81.89879979451497</v>
+        <v>40.81919999440511</v>
       </c>
       <c r="I75">
-        <v>78.30409980773926</v>
+        <v>37.73965003013611</v>
       </c>
       <c r="J75">
-        <v>74.76219984054565</v>
+        <v>35.26940002441406</v>
       </c>
       <c r="K75">
-        <v>0.9100000262260437</v>
+        <v>7.050000190734863</v>
       </c>
       <c r="L75">
-        <v>108.0899963378906</v>
+        <v>51.63999938964844</v>
       </c>
       <c r="M75">
-        <v>126.8170257536855</v>
+        <v>127.7669202303683</v>
       </c>
       <c r="N75">
-        <v>0.7</v>
+        <v>2.72</v>
       </c>
       <c r="O75">
-        <v>1.35</v>
+        <v>2.51</v>
       </c>
       <c r="P75">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="Q75">
-        <v>1.29</v>
+        <v>2.12</v>
       </c>
       <c r="R75">
-        <v>311900000</v>
+        <v>309779000</v>
       </c>
       <c r="S75">
-        <v>604300000</v>
+        <v>275331000</v>
       </c>
       <c r="T75">
-        <v>461700000</v>
+        <v>191051000</v>
       </c>
       <c r="U75">
-        <v>576600000</v>
+        <v>234602000</v>
       </c>
       <c r="V75" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -6190,67 +6253,67 @@
         <v>96</v>
       </c>
       <c r="B76" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C76" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D76" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="E76">
-        <v>81.33000183105469</v>
+        <v>268.260009765625</v>
       </c>
       <c r="F76">
-        <v>2087616.666666667</v>
+        <v>2000650</v>
       </c>
       <c r="G76">
-        <v>75.29920043945313</v>
+        <v>245.8211996459961</v>
       </c>
       <c r="H76">
-        <v>68.70426684061687</v>
+        <v>223.6178667195638</v>
       </c>
       <c r="I76">
-        <v>66.74480020523072</v>
+        <v>209.9869501495361</v>
       </c>
       <c r="J76">
-        <v>63.76200012207031</v>
+        <v>198.9669500732422</v>
       </c>
       <c r="K76">
-        <v>4.15140962600708</v>
+        <v>0.8275843262672424</v>
       </c>
       <c r="L76">
-        <v>82.45999908447266</v>
+        <v>312.9627685546875</v>
       </c>
       <c r="M76">
-        <v>126.7716456050033</v>
+        <v>127.0991331832926</v>
       </c>
       <c r="N76">
-        <v>-3.53</v>
+        <v>3.33</v>
       </c>
       <c r="O76">
-        <v>-1.52</v>
+        <v>3.07</v>
       </c>
       <c r="P76">
-        <v>0.025016</v>
+        <v>3.05</v>
       </c>
       <c r="Q76">
-        <v>0.366974</v>
+        <v>6.05</v>
       </c>
       <c r="R76">
-        <v>-2051000000</v>
+        <v>875000000</v>
       </c>
       <c r="S76">
-        <v>-876000000</v>
+        <v>788000000</v>
       </c>
       <c r="T76">
-        <v>23430000</v>
+        <v>771000000</v>
       </c>
       <c r="U76">
-        <v>217383000</v>
+        <v>1538000000</v>
       </c>
       <c r="V76" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" spans="1:22">
@@ -6258,67 +6321,67 @@
         <v>97</v>
       </c>
       <c r="B77" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="C77" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="D77" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="E77">
-        <v>13.71000003814697</v>
+        <v>53</v>
       </c>
       <c r="F77">
-        <v>495449.5</v>
+        <v>989476.6666666666</v>
       </c>
       <c r="G77">
-        <v>12.81000001907349</v>
+        <v>48.57159980773926</v>
       </c>
       <c r="H77">
-        <v>10.88553333918254</v>
+        <v>43.43153330485026</v>
       </c>
       <c r="I77">
-        <v>10.26634999752045</v>
+        <v>42.68644998550415</v>
       </c>
       <c r="J77">
-        <v>9.751249988079071</v>
+        <v>41.19375003814697</v>
       </c>
       <c r="K77">
-        <v>6.639999866485596</v>
+        <v>2.721946477890015</v>
       </c>
       <c r="L77">
-        <v>13.89000034332275</v>
+        <v>53.91999816894531</v>
       </c>
       <c r="M77">
-        <v>126.3842058001431</v>
+        <v>127.0379439859438</v>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P77">
-        <v>1.17</v>
+        <v>-2</v>
       </c>
       <c r="Q77">
-        <v>1.17</v>
+        <v>4.36</v>
       </c>
       <c r="R77">
-        <v>-77781000</v>
+        <v>312600000</v>
       </c>
       <c r="S77">
-        <v>259425000</v>
+        <v>32572000</v>
       </c>
       <c r="T77">
-        <v>-77781000</v>
+        <v>-155994000</v>
       </c>
       <c r="U77">
-        <v>259425000</v>
+        <v>355363000</v>
       </c>
       <c r="V77" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -6326,67 +6389,67 @@
         <v>98</v>
       </c>
       <c r="B78" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C78" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D78" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="E78">
-        <v>73.99500274658203</v>
+        <v>110.0500030517578</v>
       </c>
       <c r="F78">
-        <v>418487.8666666666</v>
+        <v>453360</v>
       </c>
       <c r="G78">
-        <v>69.13009971618652</v>
+        <v>98.12099990844726</v>
       </c>
       <c r="H78">
-        <v>60.95249994913737</v>
+        <v>92.66893320719402</v>
       </c>
       <c r="I78">
-        <v>57.91302499771118</v>
+        <v>88.79639995574951</v>
       </c>
       <c r="J78">
-        <v>54.89604997634888</v>
+        <v>85.35319995880127</v>
       </c>
       <c r="K78">
-        <v>10.73999977111816</v>
+        <v>3.099249601364136</v>
       </c>
       <c r="L78">
-        <v>74.80000305175781</v>
+        <v>121.8199996948242</v>
       </c>
       <c r="M78">
-        <v>126.3386576001221</v>
+        <v>126.9739429973167</v>
       </c>
       <c r="N78">
-        <v>2.07</v>
+        <v>3.5</v>
       </c>
       <c r="O78">
-        <v>2.41</v>
+        <v>1.48</v>
       </c>
       <c r="P78">
-        <v>1.53</v>
+        <v>2.84</v>
       </c>
       <c r="Q78">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="R78">
-        <v>89470000</v>
+        <v>88842000</v>
       </c>
       <c r="S78">
-        <v>103153000</v>
+        <v>37337000</v>
       </c>
       <c r="T78">
-        <v>64775000</v>
+        <v>71283000</v>
       </c>
       <c r="U78">
-        <v>75593000</v>
+        <v>40443000</v>
       </c>
       <c r="V78" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -6394,67 +6457,67 @@
         <v>99</v>
       </c>
       <c r="B79" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C79" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="D79" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E79">
-        <v>36.68999862670898</v>
+        <v>110.7900009155273</v>
       </c>
       <c r="F79">
-        <v>1234259.5</v>
+        <v>681433.3333333334</v>
       </c>
       <c r="G79">
-        <v>33.19919990539551</v>
+        <v>100.7503999328613</v>
       </c>
       <c r="H79">
-        <v>29.00599997202555</v>
+        <v>89.45133321126302</v>
       </c>
       <c r="I79">
-        <v>28.15485001564026</v>
+        <v>85.78439998626709</v>
       </c>
       <c r="J79">
-        <v>26.77610004425049</v>
+        <v>84.10275001525879</v>
       </c>
       <c r="K79">
-        <v>0.8671879768371582</v>
+        <v>0.8541669845581055</v>
       </c>
       <c r="L79">
-        <v>48.7400016784668</v>
+        <v>133.7799987792969</v>
       </c>
       <c r="M79">
-        <v>126.2308646934236</v>
+        <v>126.9644429324393</v>
       </c>
       <c r="N79">
-        <v>0.64</v>
+        <v>1.13</v>
       </c>
       <c r="O79">
-        <v>0.4</v>
+        <v>0.74</v>
       </c>
       <c r="P79">
-        <v>0.34</v>
+        <v>1.25</v>
       </c>
       <c r="Q79">
-        <v>0.5600000000000001</v>
+        <v>1.91</v>
       </c>
       <c r="R79">
-        <v>59473000</v>
+        <v>105366000</v>
       </c>
       <c r="S79">
-        <v>37231000</v>
+        <v>68103000</v>
       </c>
       <c r="T79">
-        <v>31462000</v>
+        <v>115547000</v>
       </c>
       <c r="U79">
-        <v>52817000</v>
+        <v>178691000</v>
       </c>
       <c r="V79" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6462,67 +6525,67 @@
         <v>100</v>
       </c>
       <c r="B80" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="C80" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="D80" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E80">
-        <v>553.7150268554688</v>
+        <v>39.52000045776367</v>
       </c>
       <c r="F80">
-        <v>366854.8666666666</v>
+        <v>754643.3333333334</v>
       </c>
       <c r="G80">
-        <v>515.5296978759766</v>
+        <v>35.68639999389649</v>
       </c>
       <c r="H80">
-        <v>463.8291658528646</v>
+        <v>31.69933340708415</v>
       </c>
       <c r="I80">
-        <v>439.4328742980957</v>
+        <v>30.86958533287048</v>
       </c>
       <c r="J80">
-        <v>418.1029501342774</v>
+        <v>29.58462300300598</v>
       </c>
       <c r="K80">
-        <v>0.4583329856395721</v>
+        <v>8.338250160217285</v>
       </c>
       <c r="L80">
-        <v>558</v>
+        <v>40.52114105224609</v>
       </c>
       <c r="M80">
-        <v>126.140502577076</v>
+        <v>126.5707330014932</v>
       </c>
       <c r="N80">
-        <v>3.8</v>
+        <v>0.717797</v>
       </c>
       <c r="O80">
-        <v>10.48</v>
+        <v>0.25</v>
       </c>
       <c r="P80">
-        <v>3.46</v>
+        <v>-0.26</v>
       </c>
       <c r="Q80">
-        <v>2.41</v>
+        <v>0.7</v>
       </c>
       <c r="R80">
-        <v>101524000</v>
+        <v>86489000</v>
       </c>
       <c r="S80">
-        <v>278662000</v>
+        <v>29835000</v>
       </c>
       <c r="T80">
-        <v>91787000</v>
+        <v>-30804000</v>
       </c>
       <c r="U80">
-        <v>63552000</v>
+        <v>83637000</v>
       </c>
       <c r="V80" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -6530,67 +6593,67 @@
         <v>101</v>
       </c>
       <c r="B81" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="C81" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="D81" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="E81">
-        <v>58.68999862670898</v>
+        <v>189.5200042724609</v>
       </c>
       <c r="F81">
-        <v>1583600</v>
+        <v>316470</v>
       </c>
       <c r="G81">
-        <v>53.81780014038086</v>
+        <v>179.3099996948242</v>
       </c>
       <c r="H81">
-        <v>49.70693336486816</v>
+        <v>156.8586662801107</v>
       </c>
       <c r="I81">
-        <v>46.78275003433227</v>
+        <v>150.0432495498657</v>
       </c>
       <c r="J81">
-        <v>44.33255002975464</v>
+        <v>142.300199584961</v>
       </c>
       <c r="K81">
-        <v>1.326302051544189</v>
+        <v>2.138945579528809</v>
       </c>
       <c r="L81">
-        <v>60.29999923706055</v>
+        <v>192.9400024414062</v>
       </c>
       <c r="M81">
-        <v>126.0024384509456</v>
+        <v>126.4652698265689</v>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>138995000</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>117184000</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>100356000</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>120849000</v>
       </c>
       <c r="V81" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -6598,67 +6661,67 @@
         <v>102</v>
       </c>
       <c r="B82" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C82" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="D82" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="E82">
-        <v>32.49499893188477</v>
+        <v>409.1000061035156</v>
       </c>
       <c r="F82">
-        <v>1334094</v>
+        <v>964433.3333333334</v>
       </c>
       <c r="G82">
-        <v>30.52249992370605</v>
+        <v>361.878599243164</v>
       </c>
       <c r="H82">
-        <v>27.50869992574056</v>
+        <v>340.5599997965495</v>
       </c>
       <c r="I82">
-        <v>26.25192496299744</v>
+        <v>327.5111996459961</v>
       </c>
       <c r="J82">
-        <v>24.65844998836517</v>
+        <v>313.5499498748779</v>
       </c>
       <c r="K82">
-        <v>0.1598737090826035</v>
+        <v>0.6462651491165161</v>
       </c>
       <c r="L82">
-        <v>33.83000183105469</v>
+        <v>427.5899963378906</v>
       </c>
       <c r="M82">
-        <v>125.7623768225628</v>
+        <v>126.2409187568156</v>
       </c>
       <c r="N82">
-        <v>0.11</v>
+        <v>3.36</v>
       </c>
       <c r="O82">
-        <v>-0.02</v>
+        <v>2.92</v>
       </c>
       <c r="P82">
-        <v>1.3</v>
+        <v>2.58</v>
       </c>
       <c r="Q82">
-        <v>0.11</v>
+        <v>2.65</v>
       </c>
       <c r="R82">
-        <v>-4000000</v>
+        <v>377401000</v>
       </c>
       <c r="S82">
-        <v>264000000</v>
+        <v>323929000</v>
       </c>
       <c r="T82">
-        <v>-64000000</v>
+        <v>285038000</v>
       </c>
       <c r="U82">
-        <v>23000000</v>
+        <v>292362000</v>
       </c>
       <c r="V82" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="83" spans="1:22">
@@ -6666,67 +6729,815 @@
         <v>103</v>
       </c>
       <c r="B83" t="s">
+        <v>117</v>
+      </c>
+      <c r="C83" t="s">
+        <v>165</v>
+      </c>
+      <c r="D83" t="s">
+        <v>248</v>
+      </c>
+      <c r="E83">
+        <v>105.2600021362305</v>
+      </c>
+      <c r="F83">
+        <v>302803.3333333333</v>
+      </c>
+      <c r="G83">
+        <v>97.16740005493165</v>
+      </c>
+      <c r="H83">
+        <v>86.98053354899089</v>
+      </c>
+      <c r="I83">
+        <v>82.23810022354127</v>
+      </c>
+      <c r="J83">
+        <v>79.53270017623902</v>
+      </c>
+      <c r="K83">
+        <v>12.27999973297119</v>
+      </c>
+      <c r="L83">
+        <v>108.4400024414062</v>
+      </c>
+      <c r="M83">
+        <v>126.2051213363564</v>
+      </c>
+      <c r="N83">
+        <v>1.22</v>
+      </c>
+      <c r="O83">
+        <v>0.78</v>
+      </c>
+      <c r="P83">
+        <v>2.17</v>
+      </c>
+      <c r="Q83">
+        <v>1.38</v>
+      </c>
+      <c r="R83">
+        <v>77000000</v>
+      </c>
+      <c r="S83">
+        <v>49000000</v>
+      </c>
+      <c r="T83">
+        <v>131000000</v>
+      </c>
+      <c r="U83">
+        <v>83000000</v>
+      </c>
+      <c r="V83" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22">
+      <c r="A84" t="s">
+        <v>104</v>
+      </c>
+      <c r="B84" t="s">
+        <v>118</v>
+      </c>
+      <c r="C84" t="s">
+        <v>127</v>
+      </c>
+      <c r="D84" t="s">
+        <v>249</v>
+      </c>
+      <c r="E84">
+        <v>127.5299987792969</v>
+      </c>
+      <c r="F84">
+        <v>3120883.333333333</v>
+      </c>
+      <c r="G84">
+        <v>120.5093994140625</v>
+      </c>
+      <c r="H84">
+        <v>106.3039998881022</v>
+      </c>
+      <c r="I84">
+        <v>100.3326497650147</v>
+      </c>
+      <c r="J84">
+        <v>94.67129981994628</v>
+      </c>
+      <c r="K84">
+        <v>0.7500790357589722</v>
+      </c>
+      <c r="L84">
+        <v>131</v>
+      </c>
+      <c r="M84">
+        <v>126.1462210850073</v>
+      </c>
+      <c r="N84">
+        <v>4.67</v>
+      </c>
+      <c r="O84">
+        <v>2.76</v>
+      </c>
+      <c r="P84">
+        <v>2.73</v>
+      </c>
+      <c r="Q84">
+        <v>3.9</v>
+      </c>
+      <c r="R84">
+        <v>1631900000</v>
+      </c>
+      <c r="S84">
+        <v>958700000</v>
+      </c>
+      <c r="T84">
+        <v>942200000</v>
+      </c>
+      <c r="U84">
+        <v>1335100000</v>
+      </c>
+      <c r="V84" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22">
+      <c r="A85" t="s">
+        <v>105</v>
+      </c>
+      <c r="B85" t="s">
+        <v>119</v>
+      </c>
+      <c r="C85" t="s">
+        <v>129</v>
+      </c>
+      <c r="D85" t="s">
+        <v>250</v>
+      </c>
+      <c r="E85">
+        <v>487.8900146484375</v>
+      </c>
+      <c r="F85">
+        <v>427803.3333333333</v>
+      </c>
+      <c r="G85">
+        <v>430.6778002929688</v>
+      </c>
+      <c r="H85">
+        <v>396.0918339029948</v>
+      </c>
+      <c r="I85">
+        <v>391.6183253479004</v>
+      </c>
+      <c r="J85">
+        <v>378.3193751525879</v>
+      </c>
+      <c r="K85">
+        <v>19.76499938964844</v>
+      </c>
+      <c r="L85">
+        <v>548.4299926757812</v>
+      </c>
+      <c r="M85">
+        <v>126.0959969014464</v>
+      </c>
+      <c r="N85">
+        <v>-0.52</v>
+      </c>
+      <c r="O85">
+        <v>-4.26</v>
+      </c>
+      <c r="P85">
+        <v>-0.7</v>
+      </c>
+      <c r="Q85">
+        <v>-0.52</v>
+      </c>
+      <c r="R85">
+        <v>-235042000</v>
+      </c>
+      <c r="S85">
+        <v>-38613000</v>
+      </c>
+      <c r="T85">
+        <v>-28871000</v>
+      </c>
+      <c r="U85">
+        <v>-94368000</v>
+      </c>
+      <c r="V85" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22">
+      <c r="A86" t="s">
+        <v>106</v>
+      </c>
+      <c r="B86" t="s">
+        <v>117</v>
+      </c>
+      <c r="C86" t="s">
+        <v>166</v>
+      </c>
+      <c r="D86" t="s">
+        <v>251</v>
+      </c>
+      <c r="E86">
+        <v>58.68000030517578</v>
+      </c>
+      <c r="F86">
+        <v>332193.3333333333</v>
+      </c>
+      <c r="G86">
+        <v>54.24320022583008</v>
+      </c>
+      <c r="H86">
+        <v>48.98246673583984</v>
+      </c>
+      <c r="I86">
+        <v>46.4926501083374</v>
+      </c>
+      <c r="J86">
+        <v>44.10395004272461</v>
+      </c>
+      <c r="K86">
+        <v>0.07982486486434937</v>
+      </c>
+      <c r="L86">
+        <v>60.29000091552734</v>
+      </c>
+      <c r="M86">
+        <v>125.4720128070037</v>
+      </c>
+      <c r="N86">
+        <v>-0.14</v>
+      </c>
+      <c r="O86">
+        <v>0.13</v>
+      </c>
+      <c r="P86">
+        <v>0.38</v>
+      </c>
+      <c r="Q86">
+        <v>0.78</v>
+      </c>
+      <c r="R86">
+        <v>-6900000</v>
+      </c>
+      <c r="S86">
+        <v>6200000</v>
+      </c>
+      <c r="T86">
+        <v>18600000</v>
+      </c>
+      <c r="U86">
+        <v>38400000</v>
+      </c>
+      <c r="V86" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22">
+      <c r="A87" t="s">
         <v>107</v>
       </c>
-      <c r="C83" t="s">
-        <v>127</v>
-      </c>
-      <c r="D83" t="s">
-        <v>238</v>
-      </c>
-      <c r="E83">
-        <v>32.02000045776367</v>
-      </c>
-      <c r="F83">
-        <v>1077573.333333333</v>
-      </c>
-      <c r="G83">
-        <v>31.71100006103516</v>
-      </c>
-      <c r="H83">
-        <v>26.68313337961833</v>
-      </c>
-      <c r="I83">
-        <v>24.39620005130768</v>
-      </c>
-      <c r="J83">
-        <v>22.76790006160736</v>
-      </c>
-      <c r="K83">
-        <v>6.139999866485596</v>
-      </c>
-      <c r="L83">
-        <v>33.66999816894531</v>
-      </c>
-      <c r="M83">
-        <v>125.4154569860466</v>
-      </c>
-      <c r="N83">
+      <c r="B87" t="s">
+        <v>118</v>
+      </c>
+      <c r="C87" t="s">
+        <v>167</v>
+      </c>
+      <c r="D87" t="s">
+        <v>252</v>
+      </c>
+      <c r="E87">
+        <v>36.95000076293945</v>
+      </c>
+      <c r="F87">
+        <v>1113593.333333333</v>
+      </c>
+      <c r="G87">
+        <v>33.64479999542236</v>
+      </c>
+      <c r="H87">
+        <v>29.26586667378744</v>
+      </c>
+      <c r="I87">
+        <v>28.36335003852844</v>
+      </c>
+      <c r="J87">
+        <v>26.97315003395081</v>
+      </c>
+      <c r="K87">
+        <v>0.8671879768371582</v>
+      </c>
+      <c r="L87">
+        <v>48.7400016784668</v>
+      </c>
+      <c r="M87">
+        <v>125.4506226960056</v>
+      </c>
+      <c r="N87">
+        <v>0.64</v>
+      </c>
+      <c r="O87">
+        <v>0.4</v>
+      </c>
+      <c r="P87">
+        <v>0.34</v>
+      </c>
+      <c r="Q87">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="R87">
+        <v>59473000</v>
+      </c>
+      <c r="S87">
+        <v>37231000</v>
+      </c>
+      <c r="T87">
+        <v>31462000</v>
+      </c>
+      <c r="U87">
+        <v>52817000</v>
+      </c>
+      <c r="V87" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22">
+      <c r="A88" t="s">
+        <v>108</v>
+      </c>
+      <c r="B88" t="s">
+        <v>116</v>
+      </c>
+      <c r="C88" t="s">
+        <v>153</v>
+      </c>
+      <c r="D88" t="s">
+        <v>253</v>
+      </c>
+      <c r="E88">
+        <v>158.3800048828125</v>
+      </c>
+      <c r="F88">
+        <v>1504263.333333333</v>
+      </c>
+      <c r="G88">
+        <v>147.1948001098633</v>
+      </c>
+      <c r="H88">
+        <v>130.2936665344238</v>
+      </c>
+      <c r="I88">
+        <v>126.985899887085</v>
+      </c>
+      <c r="J88">
+        <v>121.925899772644</v>
+      </c>
+      <c r="K88">
+        <v>12.18373107910156</v>
+      </c>
+      <c r="L88">
+        <v>168.5816802978516</v>
+      </c>
+      <c r="M88">
+        <v>125.4289676630226</v>
+      </c>
+      <c r="N88">
+        <v>0.82</v>
+      </c>
+      <c r="O88">
+        <v>0.54</v>
+      </c>
+      <c r="P88">
+        <v>1.15</v>
+      </c>
+      <c r="Q88">
+        <v>0.52</v>
+      </c>
+      <c r="R88">
+        <v>347000000</v>
+      </c>
+      <c r="S88">
+        <v>231000000</v>
+      </c>
+      <c r="T88">
+        <v>494000000</v>
+      </c>
+      <c r="U88">
+        <v>224000000</v>
+      </c>
+      <c r="V88" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22">
+      <c r="A89" t="s">
+        <v>109</v>
+      </c>
+      <c r="B89" t="s">
+        <v>115</v>
+      </c>
+      <c r="C89" t="s">
+        <v>155</v>
+      </c>
+      <c r="D89" t="s">
+        <v>254</v>
+      </c>
+      <c r="E89">
+        <v>40.20000076293945</v>
+      </c>
+      <c r="F89">
+        <v>353300</v>
+      </c>
+      <c r="G89">
+        <v>35.48599987030029</v>
+      </c>
+      <c r="H89">
+        <v>32.29853326161702</v>
+      </c>
+      <c r="I89">
+        <v>31.38714990615845</v>
+      </c>
+      <c r="J89">
+        <v>29.86539988517761</v>
+      </c>
+      <c r="K89">
+        <v>2.220000028610229</v>
+      </c>
+      <c r="L89">
+        <v>40.59000015258789</v>
+      </c>
+      <c r="M89">
+        <v>125.3766515840249</v>
+      </c>
+      <c r="N89">
+        <v>0.54</v>
+      </c>
+      <c r="O89">
+        <v>0.71</v>
+      </c>
+      <c r="P89">
+        <v>0.88</v>
+      </c>
+      <c r="Q89">
+        <v>0.89</v>
+      </c>
+      <c r="R89">
+        <v>30604000</v>
+      </c>
+      <c r="S89">
+        <v>40241000</v>
+      </c>
+      <c r="T89">
+        <v>49122000</v>
+      </c>
+      <c r="U89">
+        <v>49009000</v>
+      </c>
+      <c r="V89" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22">
+      <c r="A90" t="s">
+        <v>110</v>
+      </c>
+      <c r="B90" t="s">
+        <v>117</v>
+      </c>
+      <c r="C90" t="s">
+        <v>146</v>
+      </c>
+      <c r="D90" t="s">
+        <v>255</v>
+      </c>
+      <c r="E90">
+        <v>480.5499877929688</v>
+      </c>
+      <c r="F90">
+        <v>784813.3333333334</v>
+      </c>
+      <c r="G90">
+        <v>425.4125994873047</v>
+      </c>
+      <c r="H90">
+        <v>405.7753328450521</v>
+      </c>
+      <c r="I90">
+        <v>389.267200012207</v>
+      </c>
+      <c r="J90">
+        <v>371.261849975586</v>
+      </c>
+      <c r="K90">
+        <v>3.029999971389771</v>
+      </c>
+      <c r="L90">
+        <v>486.5599975585938</v>
+      </c>
+      <c r="M90">
+        <v>125.3140746608057</v>
+      </c>
+      <c r="N90">
+        <v>8.66</v>
+      </c>
+      <c r="O90">
+        <v>9.15</v>
+      </c>
+      <c r="P90">
+        <v>6.47</v>
+      </c>
+      <c r="Q90">
+        <v>8.58</v>
+      </c>
+      <c r="R90">
+        <v>606000000</v>
+      </c>
+      <c r="S90">
+        <v>639000000</v>
+      </c>
+      <c r="T90">
+        <v>451000000</v>
+      </c>
+      <c r="U90">
+        <v>591000000</v>
+      </c>
+      <c r="V90" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22">
+      <c r="A91" t="s">
+        <v>111</v>
+      </c>
+      <c r="B91" t="s">
+        <v>118</v>
+      </c>
+      <c r="C91" t="s">
+        <v>168</v>
+      </c>
+      <c r="D91" t="s">
+        <v>256</v>
+      </c>
+      <c r="E91">
+        <v>565.0900268554688</v>
+      </c>
+      <c r="F91">
+        <v>371600</v>
+      </c>
+      <c r="G91">
+        <v>522.4417974853516</v>
+      </c>
+      <c r="H91">
+        <v>467.1251324462891</v>
+      </c>
+      <c r="I91">
+        <v>442.5118492126465</v>
+      </c>
+      <c r="J91">
+        <v>421.152449798584</v>
+      </c>
+      <c r="K91">
+        <v>0.4583329856395721</v>
+      </c>
+      <c r="L91">
+        <v>565.5499877929688</v>
+      </c>
+      <c r="M91">
+        <v>125.2537440814427</v>
+      </c>
+      <c r="N91">
+        <v>3.8</v>
+      </c>
+      <c r="O91">
+        <v>10.48</v>
+      </c>
+      <c r="P91">
+        <v>3.46</v>
+      </c>
+      <c r="Q91">
+        <v>2.41</v>
+      </c>
+      <c r="R91">
+        <v>101524000</v>
+      </c>
+      <c r="S91">
+        <v>278662000</v>
+      </c>
+      <c r="T91">
+        <v>91787000</v>
+      </c>
+      <c r="U91">
+        <v>63552000</v>
+      </c>
+      <c r="V91" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22">
+      <c r="A92" t="s">
+        <v>112</v>
+      </c>
+      <c r="B92" t="s">
+        <v>115</v>
+      </c>
+      <c r="C92" t="s">
+        <v>169</v>
+      </c>
+      <c r="D92" t="s">
+        <v>257</v>
+      </c>
+      <c r="E92">
+        <v>57.68999862670898</v>
+      </c>
+      <c r="F92">
+        <v>678486.6666666666</v>
+      </c>
+      <c r="G92">
+        <v>51.7513998413086</v>
+      </c>
+      <c r="H92">
+        <v>46.54799995422363</v>
+      </c>
+      <c r="I92">
+        <v>45.42030000686646</v>
+      </c>
+      <c r="J92">
+        <v>44.0164999961853</v>
+      </c>
+      <c r="K92">
+        <v>5.159999847412109</v>
+      </c>
+      <c r="L92">
+        <v>59.47999954223633</v>
+      </c>
+      <c r="M92">
+        <v>125.1606336601367</v>
+      </c>
+      <c r="N92">
+        <v>1.55</v>
+      </c>
+      <c r="O92">
+        <v>0.01</v>
+      </c>
+      <c r="P92">
+        <v>0.52</v>
+      </c>
+      <c r="Q92">
+        <v>2.07</v>
+      </c>
+      <c r="R92">
+        <v>113000000</v>
+      </c>
+      <c r="S92">
+        <v>1000000</v>
+      </c>
+      <c r="T92">
+        <v>37000000</v>
+      </c>
+      <c r="U92">
+        <v>142000000</v>
+      </c>
+      <c r="V92" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22">
+      <c r="A93" t="s">
+        <v>113</v>
+      </c>
+      <c r="B93" t="s">
+        <v>116</v>
+      </c>
+      <c r="C93" t="s">
+        <v>135</v>
+      </c>
+      <c r="D93" t="s">
+        <v>258</v>
+      </c>
+      <c r="E93">
+        <v>101.379997253418</v>
+      </c>
+      <c r="F93">
+        <v>5952446.666666667</v>
+      </c>
+      <c r="G93">
+        <v>95.01199966430664</v>
+      </c>
+      <c r="H93">
+        <v>82.98719973246257</v>
+      </c>
+      <c r="I93">
+        <v>79.15869974136352</v>
+      </c>
+      <c r="J93">
+        <v>75.27524984359741</v>
+      </c>
+      <c r="K93">
+        <v>0.9100000262260437</v>
+      </c>
+      <c r="L93">
+        <v>108.0899963378906</v>
+      </c>
+      <c r="M93">
+        <v>124.9432997325041</v>
+      </c>
+      <c r="N93">
+        <v>0.7</v>
+      </c>
+      <c r="O93">
+        <v>1.35</v>
+      </c>
+      <c r="P93">
+        <v>1.03</v>
+      </c>
+      <c r="Q93">
+        <v>1.29</v>
+      </c>
+      <c r="R93">
+        <v>311900000</v>
+      </c>
+      <c r="S93">
+        <v>604300000</v>
+      </c>
+      <c r="T93">
+        <v>461700000</v>
+      </c>
+      <c r="U93">
+        <v>576600000</v>
+      </c>
+      <c r="V93" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22">
+      <c r="A94" t="s">
+        <v>114</v>
+      </c>
+      <c r="B94" t="s">
+        <v>118</v>
+      </c>
+      <c r="C94" t="s">
+        <v>130</v>
+      </c>
+      <c r="D94" t="s">
+        <v>259</v>
+      </c>
+      <c r="E94">
+        <v>59.02000045776367</v>
+      </c>
+      <c r="F94">
+        <v>642246.6666666666</v>
+      </c>
+      <c r="G94">
+        <v>55.59919982910156</v>
+      </c>
+      <c r="H94">
+        <v>48.99173332214355</v>
+      </c>
+      <c r="I94">
+        <v>47.35439992904663</v>
+      </c>
+      <c r="J94">
+        <v>45.01294994354248</v>
+      </c>
+      <c r="K94">
+        <v>13.7691478729248</v>
+      </c>
+      <c r="L94">
+        <v>59.68000030517578</v>
+      </c>
+      <c r="M94">
+        <v>124.6837062415044</v>
+      </c>
+      <c r="N94">
         <v>1.45</v>
       </c>
-      <c r="O83">
-        <v>1.98</v>
-      </c>
-      <c r="P83">
-        <v>0.73</v>
-      </c>
-      <c r="Q83">
-        <v>0.6</v>
-      </c>
-      <c r="R83">
-        <v>149226000</v>
-      </c>
-      <c r="S83">
-        <v>202973000</v>
-      </c>
-      <c r="T83">
-        <v>74742000</v>
-      </c>
-      <c r="U83">
-        <v>60724000</v>
-      </c>
-      <c r="V83" t="s">
-        <v>239</v>
+      <c r="O94">
+        <v>1.52</v>
+      </c>
+      <c r="P94">
+        <v>1.85</v>
+      </c>
+      <c r="Q94">
+        <v>1.92</v>
+      </c>
+      <c r="R94">
+        <v>139000000</v>
+      </c>
+      <c r="S94">
+        <v>141000000</v>
+      </c>
+      <c r="T94">
+        <v>170000000</v>
+      </c>
+      <c r="U94">
+        <v>175000000</v>
+      </c>
+      <c r="V94" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/ScreenResult/ScreenResult.xlsx
+++ b/Screener/ScreenResult/ScreenResult.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="240">
   <si>
     <t>Symbol</t>
   </si>
@@ -82,718 +82,652 @@
     <t>Code 33</t>
   </si>
   <si>
-    <t>AURC</t>
-  </si>
-  <si>
-    <t>SMCI</t>
+    <t>INOD</t>
+  </si>
+  <si>
+    <t>RXDX</t>
   </si>
   <si>
     <t>VRT</t>
   </si>
   <si>
+    <t>STRL</t>
+  </si>
+  <si>
     <t>DFH</t>
   </si>
   <si>
-    <t>RXDX</t>
-  </si>
-  <si>
-    <t>STRL</t>
-  </si>
-  <si>
     <t>CBAY</t>
   </si>
   <si>
     <t>MOD</t>
   </si>
   <si>
+    <t>XPO</t>
+  </si>
+  <si>
     <t>FOR</t>
   </si>
   <si>
-    <t>XPO</t>
-  </si>
-  <si>
-    <t>AMPH</t>
-  </si>
-  <si>
     <t>ELF</t>
   </si>
   <si>
-    <t>NVDA</t>
+    <t>BLDR</t>
   </si>
   <si>
     <t>CAMT</t>
   </si>
   <si>
-    <t>RXST</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
     <t>PKX</t>
   </si>
   <si>
     <t>MHO</t>
   </si>
   <si>
+    <t>WFRD</t>
+  </si>
+  <si>
     <t>LI</t>
   </si>
   <si>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>PARR</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>DICE</t>
+  </si>
+  <si>
+    <t>ABCM</t>
+  </si>
+  <si>
+    <t>ROIV</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>BSAQ</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
     <t>STVN</t>
   </si>
   <si>
-    <t>BCC</t>
-  </si>
-  <si>
-    <t>SAIA</t>
-  </si>
-  <si>
-    <t>DICE</t>
-  </si>
-  <si>
-    <t>WFRD</t>
-  </si>
-  <si>
-    <t>COCO</t>
-  </si>
-  <si>
-    <t>ROIV</t>
-  </si>
-  <si>
-    <t>RCL</t>
-  </si>
-  <si>
-    <t>ABCM</t>
-  </si>
-  <si>
-    <t>FTAI</t>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>SPOK</t>
+  </si>
+  <si>
+    <t>SOVO</t>
+  </si>
+  <si>
+    <t>EME</t>
+  </si>
+  <si>
+    <t>CLBR</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>LII</t>
+  </si>
+  <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>ZGN</t>
   </si>
   <si>
     <t>AEHR</t>
   </si>
   <si>
-    <t>PHM</t>
-  </si>
-  <si>
-    <t>ACLS</t>
-  </si>
-  <si>
-    <t>SOVO</t>
-  </si>
-  <si>
-    <t>TTD</t>
-  </si>
-  <si>
-    <t>OC</t>
-  </si>
-  <si>
-    <t>PARR</t>
-  </si>
-  <si>
-    <t>LII</t>
-  </si>
-  <si>
-    <t>GKOS</t>
-  </si>
-  <si>
-    <t>CLBR</t>
-  </si>
-  <si>
-    <t>EME</t>
-  </si>
-  <si>
-    <t>VIST</t>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>IDYA</t>
+  </si>
+  <si>
+    <t>BKNG</t>
+  </si>
+  <si>
+    <t>NYCB</t>
+  </si>
+  <si>
+    <t>TOL</t>
+  </si>
+  <si>
+    <t>BUR</t>
   </si>
   <si>
     <t>KBH</t>
   </si>
   <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>LLY</t>
-  </si>
-  <si>
-    <t>NUVL</t>
-  </si>
-  <si>
-    <t>CNM</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>ZGN</t>
+    <t>CHX</t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>SCPL</t>
   </si>
   <si>
     <t>MTH</t>
   </si>
   <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>NYCB</t>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>ODFL</t>
+  </si>
+  <si>
+    <t>AEL</t>
   </si>
   <si>
     <t>BECN</t>
   </si>
   <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>TOL</t>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>HCCI</t>
+  </si>
+  <si>
+    <t>PNR</t>
   </si>
   <si>
     <t>MDC</t>
   </si>
   <si>
-    <t>ONTO</t>
-  </si>
-  <si>
-    <t>LPG</t>
-  </si>
-  <si>
-    <t>HCCI</t>
-  </si>
-  <si>
-    <t>BKNG</t>
-  </si>
-  <si>
-    <t>PNR</t>
+    <t>RDY</t>
+  </si>
+  <si>
+    <t>CCJ</t>
+  </si>
+  <si>
+    <t>ARGX</t>
+  </si>
+  <si>
+    <t>LEGN</t>
+  </si>
+  <si>
+    <t>NMIH</t>
+  </si>
+  <si>
+    <t>COOP</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>ARCB</t>
+  </si>
+  <si>
+    <t>APG</t>
+  </si>
+  <si>
+    <t>CLH</t>
+  </si>
+  <si>
+    <t>DVA</t>
+  </si>
+  <si>
+    <t>MEDP</t>
+  </si>
+  <si>
+    <t>TMHC</t>
   </si>
   <si>
     <t>CRH</t>
   </si>
   <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>TPH</t>
-  </si>
-  <si>
-    <t>NVO</t>
-  </si>
-  <si>
-    <t>LRCX</t>
-  </si>
-  <si>
-    <t>AMZN</t>
+    <t>FDX</t>
+  </si>
+  <si>
+    <t>VST</t>
+  </si>
+  <si>
+    <t>PH</t>
+  </si>
+  <si>
+    <t>PAG</t>
   </si>
   <si>
     <t>CARR</t>
   </si>
   <si>
-    <t>JBL</t>
-  </si>
-  <si>
-    <t>PH</t>
-  </si>
-  <si>
-    <t>NVT</t>
-  </si>
-  <si>
-    <t>GMS</t>
-  </si>
-  <si>
-    <t>APG</t>
-  </si>
-  <si>
-    <t>ETN</t>
-  </si>
-  <si>
-    <t>TMHC</t>
-  </si>
-  <si>
-    <t>FDX</t>
-  </si>
-  <si>
-    <t>AEL</t>
-  </si>
-  <si>
-    <t>ARCB</t>
-  </si>
-  <si>
-    <t>DVA</t>
-  </si>
-  <si>
-    <t>SUM</t>
-  </si>
-  <si>
-    <t>EXP</t>
-  </si>
-  <si>
-    <t>ODFL</t>
+    <t>ALSN</t>
   </si>
   <si>
     <t>TNET</t>
   </si>
   <si>
-    <t>DHI</t>
-  </si>
-  <si>
-    <t>ARGX</t>
-  </si>
-  <si>
-    <t>CRS</t>
-  </si>
-  <si>
-    <t>URBN</t>
-  </si>
-  <si>
-    <t>VMW</t>
-  </si>
-  <si>
-    <t>TBBK</t>
-  </si>
-  <si>
-    <t>URI</t>
-  </si>
-  <si>
-    <t>DECK</t>
-  </si>
-  <si>
-    <t>COOP</t>
-  </si>
-  <si>
-    <t>ON</t>
-  </si>
-  <si>
-    <t>ALSN</t>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Consumer Defensive</t>
+  </si>
+  <si>
+    <t>Basic Materials</t>
+  </si>
+  <si>
+    <t>Energy</t>
   </si>
   <si>
     <t>Financial Services</t>
   </si>
   <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Industrials</t>
-  </si>
-  <si>
-    <t>Consumer Cyclical</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
-  </si>
-  <si>
-    <t>Consumer Defensive</t>
-  </si>
-  <si>
-    <t>Basic Materials</t>
-  </si>
-  <si>
-    <t>Energy</t>
+    <t>Communication Services</t>
+  </si>
+  <si>
+    <t>Utilities</t>
+  </si>
+  <si>
+    <t>Information Technology Services</t>
+  </si>
+  <si>
+    <t>Electrical Equipment &amp; Parts</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Construction</t>
+  </si>
+  <si>
+    <t>Residential Construction</t>
+  </si>
+  <si>
+    <t>Biotechnology</t>
+  </si>
+  <si>
+    <t>Auto Parts</t>
+  </si>
+  <si>
+    <t>Trucking</t>
+  </si>
+  <si>
+    <t>Real Estate—Development</t>
+  </si>
+  <si>
+    <t>Household &amp; Personal Products</t>
+  </si>
+  <si>
+    <t>Building Products &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Semiconductor Equipment &amp; Materials</t>
+  </si>
+  <si>
+    <t>Steel</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Equipment &amp; Services</t>
+  </si>
+  <si>
+    <t>Auto Manufacturers</t>
+  </si>
+  <si>
+    <t>Beverages—Non-Alcoholic</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Refining &amp; Marketing</t>
+  </si>
+  <si>
+    <t>Building Materials</t>
+  </si>
+  <si>
+    <t>Rental &amp; Leasing Services</t>
   </si>
   <si>
     <t>Shell Companies</t>
   </si>
   <si>
+    <t>Oil &amp; Gas E&amp;P</t>
+  </si>
+  <si>
+    <t>Travel Services</t>
+  </si>
+  <si>
+    <t>Medical Instruments &amp; Supplies</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Drilling</t>
+  </si>
+  <si>
+    <t>Health Information Services</t>
+  </si>
+  <si>
+    <t>Packaged Foods</t>
+  </si>
+  <si>
+    <t>Medical Devices</t>
+  </si>
+  <si>
+    <t>Drug Manufacturers—General</t>
+  </si>
+  <si>
+    <t>Apparel Manufacturing</t>
+  </si>
+  <si>
+    <t>Industrial Distribution</t>
+  </si>
+  <si>
+    <t>Banks—Regional</t>
+  </si>
+  <si>
+    <t>Asset Management</t>
+  </si>
+  <si>
+    <t>Auto &amp; Truck Dealerships</t>
+  </si>
+  <si>
+    <t>Electronic Gaming &amp; Multimedia</t>
+  </si>
+  <si>
     <t>Computer Hardware</t>
   </si>
   <si>
-    <t>Electrical Equipment &amp; Parts</t>
-  </si>
-  <si>
-    <t>Residential Construction</t>
-  </si>
-  <si>
-    <t>Engineering &amp; Construction</t>
-  </si>
-  <si>
-    <t>Biotechnology</t>
-  </si>
-  <si>
-    <t>Auto Parts</t>
-  </si>
-  <si>
-    <t>Real Estate—Development</t>
-  </si>
-  <si>
-    <t>Trucking</t>
+    <t>Insurance—Life</t>
+  </si>
+  <si>
+    <t>Specialty Industrial Machinery</t>
+  </si>
+  <si>
+    <t>Waste Management</t>
   </si>
   <si>
     <t>Drug Manufacturers—Specialty &amp; Generic</t>
   </si>
   <si>
-    <t>Household &amp; Personal Products</t>
-  </si>
-  <si>
-    <t>Semiconductors</t>
-  </si>
-  <si>
-    <t>Semiconductor Equipment &amp; Materials</t>
-  </si>
-  <si>
-    <t>Medical Devices</t>
-  </si>
-  <si>
-    <t>Building Products &amp; Equipment</t>
-  </si>
-  <si>
-    <t>Steel</t>
-  </si>
-  <si>
-    <t>Auto Manufacturers</t>
-  </si>
-  <si>
-    <t>Medical Instruments &amp; Supplies</t>
-  </si>
-  <si>
-    <t>Building Materials</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Equipment &amp; Services</t>
-  </si>
-  <si>
-    <t>Beverages—Non-Alcoholic</t>
-  </si>
-  <si>
-    <t>Travel Services</t>
-  </si>
-  <si>
-    <t>Rental &amp; Leasing Services</t>
-  </si>
-  <si>
-    <t>Packaged Foods</t>
-  </si>
-  <si>
-    <t>Software—Application</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Refining &amp; Marketing</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas E&amp;P</t>
-  </si>
-  <si>
-    <t>Drug Manufacturers—General</t>
-  </si>
-  <si>
-    <t>Industrial Distribution</t>
-  </si>
-  <si>
-    <t>Software—Infrastructure</t>
-  </si>
-  <si>
-    <t>Apparel Manufacturing</t>
-  </si>
-  <si>
-    <t>Banks—Regional</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Drilling</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Midstream</t>
-  </si>
-  <si>
-    <t>Waste Management</t>
-  </si>
-  <si>
-    <t>Specialty Industrial Machinery</t>
-  </si>
-  <si>
-    <t>Internet Retail</t>
-  </si>
-  <si>
-    <t>Electronic Components</t>
+    <t>Uranium</t>
+  </si>
+  <si>
+    <t>Insurance—Specialty</t>
+  </si>
+  <si>
+    <t>Mortgage Finance</t>
+  </si>
+  <si>
+    <t>Medical Care Facilities</t>
+  </si>
+  <si>
+    <t>Diagnostics &amp; Research</t>
   </si>
   <si>
     <t>Integrated Freight &amp; Logistics</t>
   </si>
   <si>
-    <t>Insurance—Life</t>
-  </si>
-  <si>
-    <t>Medical Care Facilities</t>
+    <t>Utilities—Independent Power Producers</t>
   </si>
   <si>
     <t>Staffing &amp; Employment Services</t>
   </si>
   <si>
-    <t>Metal Fabrication</t>
-  </si>
-  <si>
-    <t>Apparel Retail</t>
-  </si>
-  <si>
-    <t>Footwear &amp; Accessories</t>
-  </si>
-  <si>
-    <t>Mortgage Finance</t>
-  </si>
-  <si>
-    <t>2021-04-30</t>
-  </si>
-  <si>
-    <t>2007-03-29</t>
+    <t>1993-08-10</t>
+  </si>
+  <si>
+    <t>2021-03-12</t>
   </si>
   <si>
     <t>2018-08-02</t>
   </si>
   <si>
+    <t>1991-07-12</t>
+  </si>
+  <si>
     <t>2021-01-21</t>
   </si>
   <si>
-    <t>2021-03-12</t>
-  </si>
-  <si>
-    <t>1991-07-12</t>
-  </si>
-  <si>
     <t>2014-02-03</t>
   </si>
   <si>
     <t>1982-09-20</t>
   </si>
   <si>
+    <t>2003-10-07</t>
+  </si>
+  <si>
     <t>2007-12-13</t>
   </si>
   <si>
-    <t>2003-10-07</t>
-  </si>
-  <si>
-    <t>2014-06-25</t>
-  </si>
-  <si>
     <t>2016-09-22</t>
   </si>
   <si>
-    <t>1999-01-22</t>
+    <t>2005-06-28</t>
   </si>
   <si>
     <t>2000-07-28</t>
   </si>
   <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>2005-06-28</t>
-  </si>
-  <si>
     <t>1994-10-14</t>
   </si>
   <si>
     <t>1993-11-03</t>
   </si>
   <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
     <t>2020-07-30</t>
   </si>
   <si>
+    <t>2007-01-22</t>
+  </si>
+  <si>
+    <t>2002-09-11</t>
+  </si>
+  <si>
+    <t>2012-09-05</t>
+  </si>
+  <si>
+    <t>2013-02-06</t>
+  </si>
+  <si>
+    <t>2021-09-15</t>
+  </si>
+  <si>
+    <t>2020-10-22</t>
+  </si>
+  <si>
+    <t>2020-12-08</t>
+  </si>
+  <si>
+    <t>2015-05-14</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>2019-07-26</t>
+  </si>
+  <si>
+    <t>1993-04-28</t>
+  </si>
+  <si>
     <t>2021-07-16</t>
   </si>
   <si>
-    <t>2013-02-06</t>
-  </si>
-  <si>
-    <t>2002-09-11</t>
-  </si>
-  <si>
-    <t>2021-09-15</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>2021-10-21</t>
-  </si>
-  <si>
-    <t>2020-12-08</t>
-  </si>
-  <si>
-    <t>1993-04-28</t>
-  </si>
-  <si>
-    <t>2020-10-22</t>
-  </si>
-  <si>
-    <t>2015-05-14</t>
+    <t>1980-03-17</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>2004-11-17</t>
+  </si>
+  <si>
+    <t>2021-09-23</t>
+  </si>
+  <si>
+    <t>1995-01-10</t>
+  </si>
+  <si>
+    <t>2021-07-07</t>
+  </si>
+  <si>
+    <t>2015-06-25</t>
+  </si>
+  <si>
+    <t>2006-11-01</t>
+  </si>
+  <si>
+    <t>1999-07-29</t>
+  </si>
+  <si>
+    <t>1972-06-01</t>
+  </si>
+  <si>
+    <t>2021-12-20</t>
   </si>
   <si>
     <t>1997-08-15</t>
   </si>
   <si>
-    <t>1980-03-17</t>
-  </si>
-  <si>
-    <t>2000-07-11</t>
-  </si>
-  <si>
-    <t>2021-09-23</t>
-  </si>
-  <si>
-    <t>2016-09-21</t>
-  </si>
-  <si>
-    <t>2006-11-01</t>
-  </si>
-  <si>
-    <t>2012-09-05</t>
-  </si>
-  <si>
-    <t>1999-07-29</t>
-  </si>
-  <si>
-    <t>2015-06-25</t>
-  </si>
-  <si>
-    <t>2021-07-07</t>
-  </si>
-  <si>
-    <t>1995-01-10</t>
-  </si>
-  <si>
-    <t>2019-07-26</t>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>2019-05-23</t>
+  </si>
+  <si>
+    <t>1999-03-31</t>
+  </si>
+  <si>
+    <t>1993-11-23</t>
+  </si>
+  <si>
+    <t>1986-07-08</t>
+  </si>
+  <si>
+    <t>2020-10-19</t>
   </si>
   <si>
     <t>1986-08-01</t>
   </si>
   <si>
-    <t>2009-08-06</t>
-  </si>
-  <si>
-    <t>1972-06-01</t>
-  </si>
-  <si>
-    <t>2021-07-29</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>1986-08-13</t>
-  </si>
-  <si>
-    <t>2021-12-20</t>
+    <t>2018-04-27</t>
+  </si>
+  <si>
+    <t>1996-12-18</t>
+  </si>
+  <si>
+    <t>2019-05-03</t>
   </si>
   <si>
     <t>1988-07-26</t>
   </si>
   <si>
-    <t>1993-11-23</t>
+    <t>2016-08-17</t>
+  </si>
+  <si>
+    <t>1991-10-24</t>
+  </si>
+  <si>
+    <t>2003-12-04</t>
   </si>
   <si>
     <t>2004-09-23</t>
   </si>
   <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>1986-07-08</t>
+    <t>2008-03-12</t>
+  </si>
+  <si>
+    <t>1973-05-03</t>
   </si>
   <si>
     <t>1980-03-11</t>
   </si>
   <si>
-    <t>2019-10-28</t>
-  </si>
-  <si>
-    <t>2014-05-08</t>
-  </si>
-  <si>
-    <t>2008-03-12</t>
-  </si>
-  <si>
-    <t>1999-03-31</t>
-  </si>
-  <si>
-    <t>1973-05-03</t>
+    <t>2001-04-11</t>
+  </si>
+  <si>
+    <t>1996-03-14</t>
+  </si>
+  <si>
+    <t>2017-05-18</t>
+  </si>
+  <si>
+    <t>2020-06-05</t>
+  </si>
+  <si>
+    <t>2013-11-08</t>
+  </si>
+  <si>
+    <t>2012-03-28</t>
+  </si>
+  <si>
+    <t>1997-12-18</t>
+  </si>
+  <si>
+    <t>1992-05-13</t>
+  </si>
+  <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
+    <t>1987-11-24</t>
+  </si>
+  <si>
+    <t>1995-10-31</t>
+  </si>
+  <si>
+    <t>2016-08-11</t>
+  </si>
+  <si>
+    <t>2013-04-10</t>
   </si>
   <si>
     <t>1989-07-13</t>
   </si>
   <si>
-    <t>2016-08-17</t>
-  </si>
-  <si>
-    <t>2013-01-31</t>
-  </si>
-  <si>
-    <t>1981-04-30</t>
-  </si>
-  <si>
-    <t>1984-05-04</t>
-  </si>
-  <si>
-    <t>1997-05-15</t>
+    <t>1978-04-12</t>
+  </si>
+  <si>
+    <t>2016-10-05</t>
+  </si>
+  <si>
+    <t>1996-10-23</t>
   </si>
   <si>
     <t>2020-03-19</t>
   </si>
   <si>
-    <t>1993-05-03</t>
-  </si>
-  <si>
-    <t>2018-04-24</t>
-  </si>
-  <si>
-    <t>2016-05-26</t>
-  </si>
-  <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
-    <t>2013-04-10</t>
-  </si>
-  <si>
-    <t>1978-04-12</t>
-  </si>
-  <si>
-    <t>2003-12-04</t>
-  </si>
-  <si>
-    <t>1992-05-13</t>
-  </si>
-  <si>
-    <t>1995-10-31</t>
-  </si>
-  <si>
-    <t>2015-03-12</t>
-  </si>
-  <si>
-    <t>1994-04-12</t>
-  </si>
-  <si>
-    <t>1991-10-24</t>
+    <t>2012-03-15</t>
   </si>
   <si>
     <t>2014-03-27</t>
-  </si>
-  <si>
-    <t>1992-06-05</t>
-  </si>
-  <si>
-    <t>2017-05-18</t>
-  </si>
-  <si>
-    <t>1973-02-21</t>
-  </si>
-  <si>
-    <t>1993-11-09</t>
-  </si>
-  <si>
-    <t>2007-08-15</t>
-  </si>
-  <si>
-    <t>2004-02-03</t>
-  </si>
-  <si>
-    <t>1997-12-18</t>
-  </si>
-  <si>
-    <t>1993-10-15</t>
-  </si>
-  <si>
-    <t>2012-03-28</t>
-  </si>
-  <si>
-    <t>2000-05-02</t>
-  </si>
-  <si>
-    <t>2012-03-15</t>
   </si>
   <si>
     <t>F</t>
@@ -1157,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V94"/>
+  <dimension ref="A1:V82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
@@ -1233,135 +1167,129 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D2" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E2">
-        <v>42.27000045776367</v>
+        <v>13.34000015258789</v>
       </c>
       <c r="F2">
-        <v>541610</v>
+        <v>520490</v>
       </c>
       <c r="G2">
-        <v>16.50261980056763</v>
+        <v>11.49299995422363</v>
       </c>
       <c r="H2">
-        <v>12.2728199450175</v>
+        <v>8.362666662534078</v>
       </c>
       <c r="I2">
-        <v>11.69967997074127</v>
+        <v>7.045549995899201</v>
       </c>
       <c r="J2">
-        <v>10.12095499515534</v>
+        <v>6.181600004434586</v>
       </c>
       <c r="K2">
-        <v>9.789999961853027</v>
+        <v>0.09375</v>
       </c>
       <c r="L2">
-        <v>49.58000183105469</v>
+        <v>13.5</v>
       </c>
       <c r="M2">
-        <v>414.7981944984094</v>
+        <v>220.9878353105352</v>
       </c>
       <c r="N2">
-        <v>0.051392</v>
+        <v>-0.14</v>
       </c>
       <c r="O2">
-        <v>-0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="P2">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Q2">
-        <v>-0.094594</v>
+        <v>-0.08</v>
       </c>
       <c r="R2">
-        <v>-965634</v>
+        <v>-3833000</v>
       </c>
       <c r="S2">
-        <v>6905230</v>
+        <v>-3327000</v>
       </c>
       <c r="T2">
-        <v>-127955</v>
+        <v>-1960000</v>
       </c>
       <c r="U2">
-        <v>-831131</v>
+        <v>-2116000</v>
       </c>
       <c r="V2" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C3" t="s">
-        <v>125</v>
-      </c>
       <c r="D3" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="E3">
-        <v>347.3999938964844</v>
+        <v>199.9199981689453</v>
       </c>
       <c r="F3">
-        <v>2840063.333333333</v>
+        <v>1081147.333333333</v>
       </c>
       <c r="G3">
-        <v>270.5203994750976</v>
+        <v>186.0122996520996</v>
       </c>
       <c r="H3">
-        <v>159.2577996317546</v>
+        <v>129.3656999969483</v>
       </c>
       <c r="I3">
-        <v>139.7309497070312</v>
+        <v>110.3482249641418</v>
       </c>
       <c r="J3">
-        <v>113.5491499710083</v>
+        <v>95.39312496185303</v>
       </c>
       <c r="K3">
-        <v>3.849999904632568</v>
+        <v>16.51000022888184</v>
       </c>
       <c r="L3">
-        <v>353.2900085449219</v>
+        <v>199.9199981689453</v>
       </c>
       <c r="M3">
-        <v>286.4049839345308</v>
+        <v>218.5788222250409</v>
       </c>
       <c r="N3">
-        <v>2.6</v>
+        <v>-0.86</v>
       </c>
       <c r="O3">
-        <v>3.35</v>
+        <v>-0.9</v>
       </c>
       <c r="P3">
-        <v>3.14</v>
+        <v>-0.9</v>
       </c>
       <c r="Q3">
-        <v>1.53</v>
+        <v>-0.86</v>
       </c>
       <c r="R3">
-        <v>140822000</v>
+        <v>-33647000</v>
       </c>
       <c r="S3">
-        <v>184416000</v>
+        <v>-37275000</v>
       </c>
       <c r="T3">
-        <v>176167000</v>
+        <v>-38764000</v>
       </c>
       <c r="U3">
-        <v>85846000</v>
+        <v>-40876000</v>
       </c>
       <c r="V3" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -1369,31 +1297,31 @@
         <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E4">
-        <v>36.22000122070312</v>
+        <v>33.5099983215332</v>
       </c>
       <c r="F4">
-        <v>6582323.333333333</v>
+        <v>6825480</v>
       </c>
       <c r="G4">
-        <v>24.8196000289917</v>
+        <v>25.68</v>
       </c>
       <c r="H4">
-        <v>17.93933335622152</v>
+        <v>18.35180000305176</v>
       </c>
       <c r="I4">
-        <v>16.92355002880096</v>
+        <v>17.23775001525879</v>
       </c>
       <c r="J4">
-        <v>15.1669499874115</v>
+        <v>15.40619999408722</v>
       </c>
       <c r="K4">
         <v>5.564881324768066</v>
@@ -1402,7 +1330,7 @@
         <v>36.22000122070312</v>
       </c>
       <c r="M4">
-        <v>228.1172065735038</v>
+        <v>210.7993659480594</v>
       </c>
       <c r="N4">
         <v>0.06</v>
@@ -1429,7 +1357,7 @@
         <v>83200000</v>
       </c>
       <c r="V4" t="s">
-        <v>261</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -1437,129 +1365,135 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E5">
-        <v>30.48999977111816</v>
+        <v>80.79000091552734</v>
       </c>
       <c r="F5">
-        <v>331650</v>
+        <v>430450</v>
       </c>
       <c r="G5">
-        <v>23.86120002746582</v>
+        <v>57.84500007629394</v>
       </c>
       <c r="H5">
-        <v>16.75259998957316</v>
+        <v>44.68886669158935</v>
       </c>
       <c r="I5">
-        <v>15.02200000286102</v>
+        <v>41.37520001411438</v>
       </c>
       <c r="J5">
-        <v>13.47445001602173</v>
+        <v>37.3522500038147</v>
       </c>
       <c r="K5">
-        <v>8.369999885559082</v>
+        <v>0.4209107160568237</v>
       </c>
       <c r="L5">
-        <v>34</v>
+        <v>80.79000091552734</v>
       </c>
       <c r="M5">
-        <v>216.2559771279986</v>
+        <v>202.1545778035803</v>
       </c>
       <c r="N5">
+        <v>0.97</v>
+      </c>
+      <c r="O5">
+        <v>1.03</v>
+      </c>
+      <c r="P5">
         <v>0.64</v>
       </c>
-      <c r="O5">
-        <v>0.78</v>
-      </c>
-      <c r="P5">
-        <v>0.45</v>
-      </c>
       <c r="Q5">
-        <v>0.65</v>
+        <v>1.27</v>
       </c>
       <c r="R5">
-        <v>69641000</v>
+        <v>29523000</v>
       </c>
       <c r="S5">
-        <v>86332000</v>
+        <v>31725000</v>
       </c>
       <c r="T5">
-        <v>49089000</v>
+        <v>19649000</v>
       </c>
       <c r="U5">
-        <v>68764000</v>
+        <v>39480000</v>
       </c>
       <c r="V5" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
         <v>26</v>
       </c>
+      <c r="B6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" t="s">
+        <v>117</v>
+      </c>
       <c r="D6" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="E6">
-        <v>199.9199981689453</v>
+        <v>28.93000030517578</v>
       </c>
       <c r="F6">
-        <v>1081147.333333333</v>
+        <v>331726.6666666667</v>
       </c>
       <c r="G6">
-        <v>186.0122996520996</v>
+        <v>24.55619998931885</v>
       </c>
       <c r="H6">
-        <v>129.3656999969483</v>
+        <v>17.14973332087199</v>
       </c>
       <c r="I6">
-        <v>110.3482249641418</v>
+        <v>15.31810000419617</v>
       </c>
       <c r="J6">
-        <v>95.39312496185303</v>
+        <v>13.70660001277924</v>
       </c>
       <c r="K6">
-        <v>16.51000022888184</v>
+        <v>8.369999885559082</v>
       </c>
       <c r="L6">
-        <v>199.9199981689453</v>
+        <v>34</v>
       </c>
       <c r="M6">
-        <v>210.7611920516861</v>
+        <v>202.1041236781414</v>
       </c>
       <c r="N6">
-        <v>-0.86</v>
+        <v>0.64</v>
       </c>
       <c r="O6">
-        <v>-0.9</v>
+        <v>0.78</v>
       </c>
       <c r="P6">
-        <v>-0.9</v>
+        <v>0.45</v>
       </c>
       <c r="Q6">
-        <v>-0.86</v>
+        <v>0.65</v>
       </c>
       <c r="R6">
-        <v>-33647000</v>
+        <v>69641000</v>
       </c>
       <c r="S6">
-        <v>-37275000</v>
+        <v>86332000</v>
       </c>
       <c r="T6">
-        <v>-38764000</v>
+        <v>49089000</v>
       </c>
       <c r="U6">
-        <v>-40876000</v>
+        <v>68764000</v>
       </c>
       <c r="V6" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1567,67 +1501,67 @@
         <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D7" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E7">
-        <v>75.58000183105469</v>
+        <v>13.47000026702881</v>
       </c>
       <c r="F7">
-        <v>374306.6666666667</v>
+        <v>2035886.666666667</v>
       </c>
       <c r="G7">
-        <v>55.88160003662109</v>
+        <v>10.59160001754761</v>
       </c>
       <c r="H7">
-        <v>43.75146671295166</v>
+        <v>9.339766689936321</v>
       </c>
       <c r="I7">
-        <v>40.55170001983642</v>
+        <v>8.023325021266936</v>
       </c>
       <c r="J7">
-        <v>36.80184999465942</v>
+        <v>7.143175015449524</v>
       </c>
       <c r="K7">
-        <v>0.4209107160568237</v>
+        <v>0.9279999732971191</v>
       </c>
       <c r="L7">
-        <v>75.58000183105469</v>
+        <v>15.15999984741211</v>
       </c>
       <c r="M7">
-        <v>187.2934803997703</v>
+        <v>186.5350455563866</v>
       </c>
       <c r="N7">
-        <v>0.97</v>
+        <v>-0.31</v>
       </c>
       <c r="O7">
-        <v>1.03</v>
+        <v>-0.28</v>
       </c>
       <c r="P7">
-        <v>0.64</v>
+        <v>-0.3</v>
       </c>
       <c r="Q7">
-        <v>1.27</v>
+        <v>-0.29</v>
       </c>
       <c r="R7">
-        <v>29523000</v>
+        <v>-27094000</v>
       </c>
       <c r="S7">
-        <v>31725000</v>
+        <v>-24505000</v>
       </c>
       <c r="T7">
-        <v>19649000</v>
+        <v>-26633000</v>
       </c>
       <c r="U7">
-        <v>39480000</v>
+        <v>-28778000</v>
       </c>
       <c r="V7" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1635,67 +1569,67 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" t="s">
         <v>119</v>
       </c>
-      <c r="C8" t="s">
-        <v>129</v>
-      </c>
       <c r="D8" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="E8">
-        <v>12.39999961853027</v>
+        <v>46.25</v>
       </c>
       <c r="F8">
-        <v>2001853.333333333</v>
+        <v>654556.6666666666</v>
       </c>
       <c r="G8">
-        <v>10.34180000305176</v>
+        <v>35.36500022888183</v>
       </c>
       <c r="H8">
-        <v>9.199900019963582</v>
+        <v>26.80340003967285</v>
       </c>
       <c r="I8">
-        <v>7.877575018405914</v>
+        <v>25.12240003585815</v>
       </c>
       <c r="J8">
-        <v>7.022925016880035</v>
+        <v>22.54410000324249</v>
       </c>
       <c r="K8">
-        <v>0.9279999732971191</v>
+        <v>0.5703791379928589</v>
       </c>
       <c r="L8">
-        <v>15.15999984741211</v>
+        <v>46.86000061035156</v>
       </c>
       <c r="M8">
-        <v>183.7362501843911</v>
+        <v>185.1023422931817</v>
       </c>
       <c r="N8">
-        <v>-0.31</v>
+        <v>0.46</v>
       </c>
       <c r="O8">
-        <v>-0.28</v>
+        <v>0.46</v>
       </c>
       <c r="P8">
-        <v>-0.3</v>
+        <v>1.69</v>
       </c>
       <c r="Q8">
-        <v>-0.29</v>
+        <v>0.85</v>
       </c>
       <c r="R8">
-        <v>-27094000</v>
+        <v>24400000</v>
       </c>
       <c r="S8">
-        <v>-24505000</v>
+        <v>24500000</v>
       </c>
       <c r="T8">
-        <v>-26633000</v>
+        <v>89900000</v>
       </c>
       <c r="U8">
-        <v>-28778000</v>
+        <v>44800000</v>
       </c>
       <c r="V8" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1703,67 +1637,67 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D9" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="E9">
-        <v>45.83000183105469</v>
+        <v>73.22000122070312</v>
       </c>
       <c r="F9">
-        <v>612536.6666666666</v>
+        <v>2179686.666666667</v>
       </c>
       <c r="G9">
-        <v>34.23880023956299</v>
+        <v>60.26139991760254</v>
       </c>
       <c r="H9">
-        <v>26.28233337402344</v>
+        <v>45.76626669565837</v>
       </c>
       <c r="I9">
-        <v>24.65300003528595</v>
+        <v>43.15720538139343</v>
       </c>
       <c r="J9">
-        <v>22.20725002288818</v>
+        <v>39.02543319702148</v>
       </c>
       <c r="K9">
-        <v>0.5703791379928589</v>
+        <v>0.6502050161361694</v>
       </c>
       <c r="L9">
-        <v>45.83000183105469</v>
+        <v>73.73999786376953</v>
       </c>
       <c r="M9">
-        <v>182.7092600818787</v>
+        <v>182.7114409443364</v>
       </c>
       <c r="N9">
-        <v>0.46</v>
+        <v>1.13</v>
       </c>
       <c r="O9">
-        <v>0.46</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P9">
-        <v>1.69</v>
+        <v>0.13</v>
       </c>
       <c r="Q9">
-        <v>0.85</v>
+        <v>0.28</v>
       </c>
       <c r="R9">
-        <v>24400000</v>
+        <v>131000000</v>
       </c>
       <c r="S9">
-        <v>24500000</v>
+        <v>-94000000</v>
       </c>
       <c r="T9">
-        <v>89900000</v>
+        <v>14000000</v>
       </c>
       <c r="U9">
-        <v>44800000</v>
+        <v>33000000</v>
       </c>
       <c r="V9" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1771,31 +1705,31 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C10" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E10">
-        <v>30.94000053405762</v>
+        <v>30.64999961853027</v>
       </c>
       <c r="F10">
-        <v>251216.6666666667</v>
+        <v>258533.3333333333</v>
       </c>
       <c r="G10">
-        <v>23.91540000915527</v>
+        <v>24.55739997863769</v>
       </c>
       <c r="H10">
-        <v>18.74906671524048</v>
+        <v>19.04780004501343</v>
       </c>
       <c r="I10">
-        <v>17.50595004558563</v>
+        <v>17.8079000377655</v>
       </c>
       <c r="J10">
-        <v>15.85880003452301</v>
+        <v>16.04035003662109</v>
       </c>
       <c r="K10">
         <v>2.950000047683716</v>
@@ -1804,7 +1738,7 @@
         <v>31.03000068664551</v>
       </c>
       <c r="M10">
-        <v>181.8520538734474</v>
+        <v>180.0827365568298</v>
       </c>
       <c r="N10">
         <v>1.02</v>
@@ -1831,7 +1765,7 @@
         <v>46800000</v>
       </c>
       <c r="V10" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1839,67 +1773,67 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C11" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D11" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="E11">
-        <v>73.05999755859375</v>
+        <v>132.4600067138672</v>
       </c>
       <c r="F11">
-        <v>2332623.333333333</v>
+        <v>1131040</v>
       </c>
       <c r="G11">
-        <v>58.73259994506836</v>
+        <v>113.9756002807617</v>
       </c>
       <c r="H11">
-        <v>44.96326669057211</v>
+        <v>89.5157999420166</v>
       </c>
       <c r="I11">
-        <v>42.46587018013</v>
+        <v>80.21039991378784</v>
       </c>
       <c r="J11">
-        <v>38.50670632362366</v>
+        <v>72.01914989471436</v>
       </c>
       <c r="K11">
-        <v>0.6502050161361694</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="L11">
-        <v>73.05999755859375</v>
+        <v>133.2200012207031</v>
       </c>
       <c r="M11">
-        <v>179.9528708860766</v>
+        <v>169.4788705640971</v>
       </c>
       <c r="N11">
-        <v>1.13</v>
+        <v>0.21</v>
       </c>
       <c r="O11">
-        <v>-0.8100000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="P11">
-        <v>0.13</v>
+        <v>0.29</v>
       </c>
       <c r="Q11">
-        <v>0.28</v>
+        <v>0.93</v>
       </c>
       <c r="R11">
-        <v>131000000</v>
+        <v>11710000</v>
       </c>
       <c r="S11">
-        <v>-94000000</v>
+        <v>19105000</v>
       </c>
       <c r="T11">
-        <v>14000000</v>
+        <v>16246000</v>
       </c>
       <c r="U11">
-        <v>33000000</v>
+        <v>52977000</v>
       </c>
       <c r="V11" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1907,67 +1841,67 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="C12" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D12" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="E12">
-        <v>65</v>
+        <v>147.8899993896484</v>
       </c>
       <c r="F12">
-        <v>358823.3333333333</v>
+        <v>1415100</v>
       </c>
       <c r="G12">
-        <v>55.30579986572265</v>
+        <v>135.4775996398926</v>
       </c>
       <c r="H12">
-        <v>42.23106657663981</v>
+        <v>104.9383329772949</v>
       </c>
       <c r="I12">
-        <v>38.95714993476868</v>
+        <v>94.51844974517822</v>
       </c>
       <c r="J12">
-        <v>35.74529993057251</v>
+        <v>85.99374982833862</v>
       </c>
       <c r="K12">
-        <v>8.689999580383301</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="L12">
-        <v>65</v>
+        <v>152.2200012207031</v>
       </c>
       <c r="M12">
-        <v>176.5697582215314</v>
+        <v>165.5071257169221</v>
       </c>
       <c r="N12">
-        <v>0.33</v>
+        <v>5.75</v>
       </c>
       <c r="O12">
-        <v>0.3</v>
+        <v>4.72</v>
       </c>
       <c r="P12">
-        <v>0.66</v>
+        <v>2.41</v>
       </c>
       <c r="Q12">
-        <v>0.5</v>
+        <v>3.16</v>
       </c>
       <c r="R12">
-        <v>17346000</v>
+        <v>738007000</v>
       </c>
       <c r="S12">
-        <v>15874000</v>
+        <v>384513000</v>
       </c>
       <c r="T12">
-        <v>33913000</v>
+        <v>333786000</v>
       </c>
       <c r="U12">
-        <v>26032000</v>
+        <v>404619000</v>
       </c>
       <c r="V12" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1975,67 +1909,67 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="D13" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="E13">
-        <v>131.5299987792969</v>
+        <v>46.15999984741211</v>
       </c>
       <c r="F13">
-        <v>1126750</v>
+        <v>317553.3333333333</v>
       </c>
       <c r="G13">
-        <v>112.2473999023437</v>
+        <v>38.1481999206543</v>
       </c>
       <c r="H13">
-        <v>87.98433319091797</v>
+        <v>30.62400001525879</v>
       </c>
       <c r="I13">
-        <v>78.84369985580445</v>
+        <v>28.74099999427795</v>
       </c>
       <c r="J13">
-        <v>70.87499988555908</v>
+        <v>26.47349998474121</v>
       </c>
       <c r="K13">
-        <v>7.300000190734863</v>
+        <v>0.2220596075057983</v>
       </c>
       <c r="L13">
-        <v>133.1900024414062</v>
+        <v>48.31999969482422</v>
       </c>
       <c r="M13">
-        <v>176.3934583053485</v>
+        <v>163.7094643231712</v>
       </c>
       <c r="N13">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
       <c r="O13">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="P13">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
       <c r="Q13">
-        <v>0.93</v>
+        <v>0.38</v>
       </c>
       <c r="R13">
-        <v>11710000</v>
+        <v>20715000</v>
       </c>
       <c r="S13">
-        <v>19105000</v>
+        <v>21673000</v>
       </c>
       <c r="T13">
-        <v>16246000</v>
+        <v>17245000</v>
       </c>
       <c r="U13">
-        <v>52977000</v>
+        <v>18539000</v>
       </c>
       <c r="V13" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -2043,67 +1977,67 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D14" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E14">
-        <v>446.6400146484375</v>
+        <v>108.5599975585938</v>
       </c>
       <c r="F14">
-        <v>42533890</v>
+        <v>546423.3333333334</v>
       </c>
       <c r="G14">
-        <v>428.3108001708985</v>
+        <v>90.59300018310547</v>
       </c>
       <c r="H14">
-        <v>304.3663330078125</v>
+        <v>74.12739995320638</v>
       </c>
       <c r="I14">
-        <v>266.5731998825073</v>
+        <v>68.71219991683959</v>
       </c>
       <c r="J14">
-        <v>233.241849899292</v>
+        <v>61.5851999092102</v>
       </c>
       <c r="K14">
-        <v>0.3134739995002747</v>
+        <v>5.792013168334961</v>
       </c>
       <c r="L14">
-        <v>474.9400024414062</v>
+        <v>132.4752044677734</v>
       </c>
       <c r="M14">
-        <v>176.3421800122788</v>
+        <v>162.0177366423817</v>
       </c>
       <c r="N14">
-        <v>0.26</v>
+        <v>2394.25</v>
       </c>
       <c r="O14">
-        <v>0.27</v>
+        <v>4830.25</v>
       </c>
       <c r="P14">
-        <v>0.57</v>
+        <v>1680.75</v>
       </c>
       <c r="Q14">
-        <v>0.82</v>
+        <v>2394.25</v>
       </c>
       <c r="R14">
-        <v>656000000</v>
+        <v>1588430000000</v>
       </c>
       <c r="S14">
-        <v>680000000</v>
+        <v>509914000000</v>
       </c>
       <c r="T14">
-        <v>1414000000</v>
+        <v>-665869000000</v>
       </c>
       <c r="U14">
-        <v>2043000000</v>
+        <v>726419000000</v>
       </c>
       <c r="V14" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2111,67 +2045,67 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C15" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="D15" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E15">
-        <v>47.47999954223633</v>
+        <v>97.55000305175781</v>
       </c>
       <c r="F15">
-        <v>317286.6666666667</v>
+        <v>345700</v>
       </c>
       <c r="G15">
-        <v>37.07279991149903</v>
+        <v>86.97940002441406</v>
       </c>
       <c r="H15">
-        <v>30.13060001373291</v>
+        <v>70.03706675211589</v>
       </c>
       <c r="I15">
-        <v>28.37784998893738</v>
+        <v>63.60600006103515</v>
       </c>
       <c r="J15">
-        <v>26.25704998970032</v>
+        <v>57.91305011749267</v>
       </c>
       <c r="K15">
-        <v>0.2220596075057983</v>
+        <v>3.118403196334839</v>
       </c>
       <c r="L15">
-        <v>48.31999969482422</v>
+        <v>100</v>
       </c>
       <c r="M15">
-        <v>171.3834076715913</v>
+        <v>159.4495990989138</v>
       </c>
       <c r="N15">
-        <v>0.43</v>
+        <v>4.67</v>
       </c>
       <c r="O15">
-        <v>0.45</v>
+        <v>4.65</v>
       </c>
       <c r="P15">
-        <v>0.36</v>
+        <v>3.64</v>
       </c>
       <c r="Q15">
-        <v>0.38</v>
+        <v>4.12</v>
       </c>
       <c r="R15">
-        <v>20715000</v>
+        <v>131590000</v>
       </c>
       <c r="S15">
-        <v>21673000</v>
+        <v>130395000</v>
       </c>
       <c r="T15">
-        <v>17245000</v>
+        <v>103066000</v>
       </c>
       <c r="U15">
-        <v>18539000</v>
+        <v>118001000</v>
       </c>
       <c r="V15" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -2179,67 +2113,67 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C16" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D16" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="E16">
-        <v>29.6299991607666</v>
+        <v>87.15000152587891</v>
       </c>
       <c r="F16">
-        <v>450613.3333333333</v>
+        <v>833550</v>
       </c>
       <c r="G16">
-        <v>28.76209987640381</v>
+        <v>71.67479957580566</v>
       </c>
       <c r="H16">
-        <v>20.43576661427816</v>
+        <v>63.74953305562337</v>
       </c>
       <c r="I16">
-        <v>18.44777495861053</v>
+        <v>58.7902498626709</v>
       </c>
       <c r="J16">
-        <v>16.39802498340607</v>
+        <v>54.06199988365174</v>
       </c>
       <c r="K16">
-        <v>8.970000267028809</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="L16">
-        <v>33.36999893188477</v>
+        <v>87.15000152587891</v>
       </c>
       <c r="M16">
-        <v>171.3610885443715</v>
+        <v>157.6979241085656</v>
       </c>
       <c r="N16">
-        <v>-0.61</v>
+        <v>0.39</v>
       </c>
       <c r="O16">
-        <v>-0.5600000000000001</v>
+        <v>0.99</v>
       </c>
       <c r="P16">
-        <v>-0.42</v>
+        <v>0.97</v>
       </c>
       <c r="Q16">
-        <v>-0.4</v>
+        <v>1.12</v>
       </c>
       <c r="R16">
-        <v>-16818000</v>
+        <v>28000000</v>
       </c>
       <c r="S16">
-        <v>-15610000</v>
+        <v>72000000</v>
       </c>
       <c r="T16">
-        <v>-13212000</v>
+        <v>72000000</v>
       </c>
       <c r="U16">
-        <v>-13804000</v>
+        <v>82000000</v>
       </c>
       <c r="V16" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2247,67 +2181,67 @@
         <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D17" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="E17">
-        <v>151.6999969482422</v>
+        <v>40.47000122070312</v>
       </c>
       <c r="F17">
-        <v>1493653.333333333</v>
+        <v>7787463.333333333</v>
       </c>
       <c r="G17">
-        <v>133.4949995422363</v>
+        <v>36.84500007629394</v>
       </c>
       <c r="H17">
-        <v>103.2729996236165</v>
+        <v>28.61823332468668</v>
       </c>
       <c r="I17">
-        <v>93.11944972991944</v>
+        <v>26.21580001354218</v>
       </c>
       <c r="J17">
-        <v>84.70489982604981</v>
+        <v>24.16084998607635</v>
       </c>
       <c r="K17">
-        <v>0.8299999833106995</v>
+        <v>13.61999988555908</v>
       </c>
       <c r="L17">
-        <v>152.2200012207031</v>
+        <v>46.65000152587891</v>
       </c>
       <c r="M17">
-        <v>169.569958645074</v>
+        <v>155.1789599824439</v>
       </c>
       <c r="N17">
-        <v>5.75</v>
+        <v>0.9</v>
       </c>
       <c r="O17">
-        <v>4.72</v>
+        <v>-0.64</v>
       </c>
       <c r="P17">
-        <v>2.41</v>
+        <v>0.26</v>
       </c>
       <c r="Q17">
-        <v>3.16</v>
+        <v>0.9</v>
       </c>
       <c r="R17">
-        <v>738007000</v>
+        <v>-1640321000</v>
       </c>
       <c r="S17">
-        <v>384513000</v>
+        <v>256938000</v>
       </c>
       <c r="T17">
-        <v>333786000</v>
+        <v>929668000</v>
       </c>
       <c r="U17">
-        <v>404619000</v>
+        <v>2293153000</v>
       </c>
       <c r="V17" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -2315,67 +2249,67 @@
         <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="D18" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="E18">
-        <v>112.9700012207031</v>
+        <v>175.0599975585938</v>
       </c>
       <c r="F18">
-        <v>546546.6666666666</v>
+        <v>1247480</v>
       </c>
       <c r="G18">
-        <v>88.03700012207031</v>
+        <v>146.8105999755859</v>
       </c>
       <c r="H18">
-        <v>72.99779998779297</v>
+        <v>115.1619333394368</v>
       </c>
       <c r="I18">
-        <v>67.70669992446899</v>
+        <v>111.675599899292</v>
       </c>
       <c r="J18">
-        <v>60.92844989776611</v>
+        <v>105.6346500396728</v>
       </c>
       <c r="K18">
-        <v>5.792013168334961</v>
+        <v>0.1500000059604645</v>
       </c>
       <c r="L18">
-        <v>132.4752044677734</v>
+        <v>175.0599975585938</v>
       </c>
       <c r="M18">
-        <v>168.5830618040611</v>
+        <v>154.9093034705795</v>
       </c>
       <c r="N18">
-        <v>2394.25</v>
+        <v>0.12</v>
       </c>
       <c r="O18">
-        <v>4830.25</v>
+        <v>-2.46</v>
       </c>
       <c r="P18">
-        <v>1680.75</v>
+        <v>0.4</v>
       </c>
       <c r="Q18">
-        <v>2394.25</v>
+        <v>0.52</v>
       </c>
       <c r="R18">
-        <v>1588430000000</v>
+        <v>-181896000</v>
       </c>
       <c r="S18">
-        <v>509914000000</v>
+        <v>-21223000</v>
       </c>
       <c r="T18">
-        <v>-665869000000</v>
+        <v>41227000</v>
       </c>
       <c r="U18">
-        <v>726419000000</v>
+        <v>51509000</v>
       </c>
       <c r="V18" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -2383,67 +2317,67 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D19" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="E19">
-        <v>99.59999847412109</v>
+        <v>424.4599914550781</v>
       </c>
       <c r="F19">
-        <v>350080</v>
+        <v>508163.3333333333</v>
       </c>
       <c r="G19">
-        <v>85.37059982299805</v>
+        <v>360.1867987060547</v>
       </c>
       <c r="H19">
-        <v>69.05573336283366</v>
+        <v>301.7637996419271</v>
       </c>
       <c r="I19">
-        <v>62.72905002593994</v>
+        <v>282.1707996368408</v>
       </c>
       <c r="J19">
-        <v>57.10800010681152</v>
+        <v>260.7041997528076</v>
       </c>
       <c r="K19">
-        <v>3.118403196334839</v>
+        <v>4.533332824707031</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>429.0599975585938</v>
       </c>
       <c r="M19">
-        <v>161.9399478198272</v>
+        <v>153.3900893469971</v>
       </c>
       <c r="N19">
-        <v>4.67</v>
+        <v>3.67</v>
       </c>
       <c r="O19">
-        <v>4.65</v>
+        <v>2.65</v>
       </c>
       <c r="P19">
-        <v>3.64</v>
+        <v>2.85</v>
       </c>
       <c r="Q19">
-        <v>4.12</v>
+        <v>3.42</v>
       </c>
       <c r="R19">
-        <v>131590000</v>
+        <v>97891000</v>
       </c>
       <c r="S19">
-        <v>130395000</v>
+        <v>70862000</v>
       </c>
       <c r="T19">
-        <v>103066000</v>
+        <v>76097000</v>
       </c>
       <c r="U19">
-        <v>118001000</v>
+        <v>91319000</v>
       </c>
       <c r="V19" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -2451,67 +2385,67 @@
         <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C20" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D20" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="E20">
-        <v>42.63000106811523</v>
+        <v>37.02000045776367</v>
       </c>
       <c r="F20">
-        <v>7316120</v>
+        <v>728936.6666666666</v>
       </c>
       <c r="G20">
-        <v>36.06900005340576</v>
+        <v>27.5902001953125</v>
       </c>
       <c r="H20">
-        <v>28.23049999237061</v>
+        <v>26.19026674906413</v>
       </c>
       <c r="I20">
-        <v>25.83875001430512</v>
+        <v>25.27605006217956</v>
       </c>
       <c r="J20">
-        <v>23.97629998683929</v>
+        <v>24.00750005245209</v>
       </c>
       <c r="K20">
-        <v>13.61999988555908</v>
+        <v>0.6000000238418579</v>
       </c>
       <c r="L20">
-        <v>46.65000152587891</v>
+        <v>37.02000045776367</v>
       </c>
       <c r="M20">
-        <v>161.59057559473</v>
+        <v>152.3855231195887</v>
       </c>
       <c r="N20">
-        <v>0.9</v>
+        <v>4.47</v>
       </c>
       <c r="O20">
-        <v>-0.64</v>
+        <v>1.4</v>
       </c>
       <c r="P20">
-        <v>0.26</v>
+        <v>3.9</v>
       </c>
       <c r="Q20">
-        <v>0.9</v>
+        <v>0.49</v>
       </c>
       <c r="R20">
-        <v>-617966000</v>
+        <v>267396000</v>
       </c>
       <c r="S20">
-        <v>-1640321000</v>
+        <v>84719000</v>
       </c>
       <c r="T20">
-        <v>256938000</v>
+        <v>237890000</v>
       </c>
       <c r="U20">
-        <v>929668000</v>
+        <v>30013000</v>
       </c>
       <c r="V20" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -2519,67 +2453,67 @@
         <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D21" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="E21">
-        <v>35.4900016784668</v>
+        <v>109.9700012207031</v>
       </c>
       <c r="F21">
-        <v>279640</v>
+        <v>353863.3333333333</v>
       </c>
       <c r="G21">
-        <v>31.17499992370605</v>
+        <v>92.10499969482422</v>
       </c>
       <c r="H21">
-        <v>26.0589332707723</v>
+        <v>76.95133354187011</v>
       </c>
       <c r="I21">
-        <v>23.60619995594025</v>
+        <v>75.27365020751954</v>
       </c>
       <c r="J21">
-        <v>22.14109998226166</v>
+        <v>70.98900022506714</v>
       </c>
       <c r="K21">
-        <v>14.10000038146973</v>
+        <v>11.37919998168945</v>
       </c>
       <c r="L21">
-        <v>35.4900016784668</v>
+        <v>111.7799987792969</v>
       </c>
       <c r="M21">
-        <v>161.1319262980886</v>
+        <v>150.9652225945763</v>
       </c>
       <c r="N21">
-        <v>0.14</v>
+        <v>5.52</v>
       </c>
       <c r="O21">
-        <v>0.18</v>
+        <v>2.95</v>
       </c>
       <c r="P21">
-        <v>0.11</v>
+        <v>2.43</v>
       </c>
       <c r="Q21">
-        <v>0.13</v>
+        <v>3.67</v>
       </c>
       <c r="R21">
-        <v>36215000</v>
+        <v>219587000</v>
       </c>
       <c r="S21">
-        <v>48300000</v>
+        <v>117360000</v>
       </c>
       <c r="T21">
-        <v>28265000</v>
+        <v>96733000</v>
       </c>
       <c r="U21">
-        <v>34300000</v>
+        <v>146320000</v>
       </c>
       <c r="V21" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -2587,67 +2521,67 @@
         <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C22" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="D22" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="E22">
-        <v>110.8600006103516</v>
+        <v>47.54999923706055</v>
       </c>
       <c r="F22">
-        <v>374813.3333333333</v>
+        <v>1301073.333333333</v>
       </c>
       <c r="G22">
-        <v>90.02179977416992</v>
+        <v>43.48419990539551</v>
       </c>
       <c r="H22">
-        <v>76.14213361104329</v>
+        <v>34.97816668192546</v>
       </c>
       <c r="I22">
-        <v>74.55895021438599</v>
+        <v>34.49874996185303</v>
       </c>
       <c r="J22">
-        <v>70.37845024108887</v>
+        <v>32.64969995498657</v>
       </c>
       <c r="K22">
-        <v>11.37919998168945</v>
+        <v>13.1899995803833</v>
       </c>
       <c r="L22">
-        <v>111.7799987792969</v>
+        <v>47.54999923706055</v>
       </c>
       <c r="M22">
-        <v>155.6875435756648</v>
+        <v>149.1204312994956</v>
       </c>
       <c r="N22">
-        <v>5.52</v>
+        <v>-0.55</v>
       </c>
       <c r="O22">
-        <v>2.95</v>
+        <v>-0.51</v>
       </c>
       <c r="P22">
-        <v>2.43</v>
+        <v>-0.54</v>
       </c>
       <c r="Q22">
-        <v>3.67</v>
+        <v>-0.74</v>
       </c>
       <c r="R22">
-        <v>219587000</v>
+        <v>-20550000</v>
       </c>
       <c r="S22">
-        <v>117360000</v>
+        <v>-23224000</v>
       </c>
       <c r="T22">
-        <v>96733000</v>
+        <v>-25646000</v>
       </c>
       <c r="U22">
-        <v>146320000</v>
+        <v>-34816000</v>
       </c>
       <c r="V22" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2655,67 +2589,67 @@
         <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C23" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="E23">
-        <v>425.3299865722656</v>
+        <v>23.29999923706055</v>
       </c>
       <c r="F23">
-        <v>538533.3333333334</v>
+        <v>1636416.666666667</v>
       </c>
       <c r="G23">
-        <v>352.0355993652344</v>
+        <v>21.92819999694824</v>
       </c>
       <c r="H23">
-        <v>297.5350665283203</v>
+        <v>17.51066665013631</v>
       </c>
       <c r="I23">
-        <v>278.7000997924804</v>
+        <v>17.08850000858307</v>
       </c>
       <c r="J23">
-        <v>258.0525497436523</v>
+        <v>16.27560000896454</v>
       </c>
       <c r="K23">
-        <v>4.533332824707031</v>
+        <v>12.61999988555908</v>
       </c>
       <c r="L23">
-        <v>429.0599975585938</v>
+        <v>24.46999931335449</v>
       </c>
       <c r="M23">
-        <v>153.1918861074822</v>
+        <v>148.6746919920275</v>
       </c>
       <c r="N23">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>97891000</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>70862000</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>76097000</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>91319000</v>
+        <v>0</v>
       </c>
       <c r="V23" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2723,67 +2657,67 @@
         <v>44</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D24" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="E24">
-        <v>47.54999923706055</v>
+        <v>11.56999969482422</v>
       </c>
       <c r="F24">
-        <v>1630586.666666667</v>
+        <v>4689390</v>
       </c>
       <c r="G24">
-        <v>42.54879997253418</v>
+        <v>10.59540000915527</v>
       </c>
       <c r="H24">
-        <v>34.65803335825602</v>
+        <v>9.125666650136312</v>
       </c>
       <c r="I24">
-        <v>34.30534997940063</v>
+        <v>8.36659999370575</v>
       </c>
       <c r="J24">
-        <v>32.22104994773865</v>
+        <v>7.635399992465973</v>
       </c>
       <c r="K24">
-        <v>13.1899995803833</v>
+        <v>2.809999942779541</v>
       </c>
       <c r="L24">
-        <v>47.54999923706055</v>
+        <v>13.52000045776367</v>
       </c>
       <c r="M24">
-        <v>152.0154751570682</v>
+        <v>148.1367650581797</v>
       </c>
       <c r="N24">
-        <v>-0.58</v>
+        <v>-0.48</v>
       </c>
       <c r="O24">
-        <v>-0.55</v>
+        <v>-0.42</v>
       </c>
       <c r="P24">
-        <v>-0.51</v>
+        <v>-0.49</v>
       </c>
       <c r="Q24">
-        <v>-0.54</v>
+        <v>-0.05</v>
       </c>
       <c r="R24">
-        <v>-21522000</v>
+        <v>-331809000</v>
       </c>
       <c r="S24">
-        <v>-20550000</v>
+        <v>-291590000</v>
       </c>
       <c r="T24">
-        <v>-23224000</v>
+        <v>-352014000</v>
       </c>
       <c r="U24">
-        <v>-25646000</v>
+        <v>-33617000</v>
       </c>
       <c r="V24" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2791,67 +2725,67 @@
         <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="D25" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E25">
-        <v>85.44000244140625</v>
+        <v>34.95000076293945</v>
       </c>
       <c r="F25">
-        <v>859646.6666666666</v>
+        <v>843180</v>
       </c>
       <c r="G25">
-        <v>69.97639961242676</v>
+        <v>31.40649974822998</v>
       </c>
       <c r="H25">
-        <v>62.98713307698568</v>
+        <v>27.46016660054525</v>
       </c>
       <c r="I25">
-        <v>58.03229986190796</v>
+        <v>24.90777494430542</v>
       </c>
       <c r="J25">
-        <v>53.37334990501404</v>
+        <v>23.12464997291565</v>
       </c>
       <c r="K25">
-        <v>5.739999771118164</v>
+        <v>4.052896976470947</v>
       </c>
       <c r="L25">
-        <v>85.44000244140625</v>
+        <v>35.09999847412109</v>
       </c>
       <c r="M25">
-        <v>151.0845127302103</v>
+        <v>145.4208761694426</v>
       </c>
       <c r="N25">
-        <v>0.39</v>
+        <v>-0.23</v>
       </c>
       <c r="O25">
-        <v>0.99</v>
+        <v>0.2</v>
       </c>
       <c r="P25">
-        <v>0.97</v>
+        <v>0.22</v>
       </c>
       <c r="Q25">
-        <v>1.12</v>
+        <v>0.46</v>
       </c>
       <c r="R25">
-        <v>28000000</v>
+        <v>-16058000</v>
       </c>
       <c r="S25">
-        <v>72000000</v>
+        <v>26801000</v>
       </c>
       <c r="T25">
-        <v>72000000</v>
+        <v>29397000</v>
       </c>
       <c r="U25">
-        <v>82000000</v>
+        <v>54753000</v>
       </c>
       <c r="V25" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2859,67 +2793,67 @@
         <v>46</v>
       </c>
       <c r="B26" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C26" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="D26" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E26">
-        <v>26.64999961853027</v>
+        <v>14.81999969482422</v>
       </c>
       <c r="F26">
-        <v>692000</v>
+        <v>279003.3333333333</v>
       </c>
       <c r="G26">
-        <v>26.49939998626709</v>
+        <v>10.67445995330811</v>
       </c>
       <c r="H26">
-        <v>20.975366675059</v>
+        <v>10.3564133199056</v>
       </c>
       <c r="I26">
-        <v>18.65167502403259</v>
+        <v>10.25780498027802</v>
       </c>
       <c r="J26">
-        <v>17.28280003070831</v>
+        <v>10.12067999839783</v>
       </c>
       <c r="K26">
-        <v>7.559999942779541</v>
+        <v>9.600000381469727</v>
       </c>
       <c r="L26">
-        <v>29.29999923706055</v>
+        <v>18.5</v>
       </c>
       <c r="M26">
-        <v>150.1304132260817</v>
+        <v>145.2886458421303</v>
       </c>
       <c r="N26">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="O26">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="P26">
-        <v>0.12</v>
+        <v>0.02</v>
       </c>
       <c r="Q26">
-        <v>0.31</v>
+        <v>0.05</v>
       </c>
       <c r="R26">
-        <v>7258000</v>
+        <v>1359247</v>
       </c>
       <c r="S26">
-        <v>-2810000</v>
+        <v>505538</v>
       </c>
       <c r="T26">
-        <v>6705000</v>
+        <v>2531258</v>
       </c>
       <c r="U26">
-        <v>17987000</v>
+        <v>1034088</v>
       </c>
       <c r="V26" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -2927,67 +2861,67 @@
         <v>47</v>
       </c>
       <c r="B27" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D27" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E27">
-        <v>11.39000034332275</v>
+        <v>25.8700008392334</v>
       </c>
       <c r="F27">
-        <v>5218893.333333333</v>
+        <v>796076.6666666666</v>
       </c>
       <c r="G27">
-        <v>10.46000001907349</v>
+        <v>24.59259998321533</v>
       </c>
       <c r="H27">
-        <v>9.049733320871988</v>
+        <v>20.7260667292277</v>
       </c>
       <c r="I27">
-        <v>8.261599993705749</v>
+        <v>18.97265003681183</v>
       </c>
       <c r="J27">
-        <v>7.506949989795685</v>
+        <v>17.50080004215241</v>
       </c>
       <c r="K27">
-        <v>2.809999942779541</v>
+        <v>1.899999976158142</v>
       </c>
       <c r="L27">
-        <v>13.52000045776367</v>
+        <v>27.38999938964844</v>
       </c>
       <c r="M27">
-        <v>147.9420622676186</v>
+        <v>142.3700664691631</v>
       </c>
       <c r="N27">
-        <v>-0.48</v>
+        <v>0.75</v>
       </c>
       <c r="O27">
-        <v>-0.42</v>
+        <v>0.762</v>
       </c>
       <c r="P27">
-        <v>-0.49</v>
+        <v>1.315</v>
       </c>
       <c r="Q27">
-        <v>-0.05</v>
+        <v>0.519</v>
       </c>
       <c r="R27">
-        <v>-331809000</v>
+        <v>76661000</v>
       </c>
       <c r="S27">
-        <v>-291590000</v>
+        <v>75504000</v>
       </c>
       <c r="T27">
-        <v>-352014000</v>
+        <v>128734000</v>
       </c>
       <c r="U27">
-        <v>-33617000</v>
+        <v>52181000</v>
       </c>
       <c r="V27" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -2995,31 +2929,31 @@
         <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="C28" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="D28" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="E28">
-        <v>106.1500015258789</v>
+        <v>102.8199996948242</v>
       </c>
       <c r="F28">
-        <v>3468263.333333333</v>
+        <v>3196210</v>
       </c>
       <c r="G28">
-        <v>98.25</v>
+        <v>99.6365998840332</v>
       </c>
       <c r="H28">
-        <v>77.54420008341471</v>
+        <v>78.57640007019043</v>
       </c>
       <c r="I28">
-        <v>71.82570005416871</v>
+        <v>72.64125003814698</v>
       </c>
       <c r="J28">
-        <v>65.89450002670289</v>
+        <v>66.69890001296997</v>
       </c>
       <c r="K28">
         <v>4.547188282012939</v>
@@ -3028,7 +2962,7 @@
         <v>133.7226409912109</v>
       </c>
       <c r="M28">
-        <v>147.885724236739</v>
+        <v>141.3124687109154</v>
       </c>
       <c r="N28">
         <v>0.13</v>
@@ -3055,7 +2989,7 @@
         <v>458761000</v>
       </c>
       <c r="V28" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -3063,67 +2997,67 @@
         <v>49</v>
       </c>
       <c r="B29" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="C29" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D29" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="E29">
-        <v>22.47999954223633</v>
+        <v>32.0099983215332</v>
       </c>
       <c r="F29">
-        <v>1715910</v>
+        <v>287123.3333333333</v>
       </c>
       <c r="G29">
-        <v>21.54480003356933</v>
+        <v>31.54879989624023</v>
       </c>
       <c r="H29">
-        <v>17.38686665852865</v>
+        <v>26.35253326416016</v>
       </c>
       <c r="I29">
-        <v>16.96290001392364</v>
+        <v>23.82684995174408</v>
       </c>
       <c r="J29">
-        <v>16.14085001468658</v>
+        <v>22.35984998226166</v>
       </c>
       <c r="K29">
-        <v>12.61999988555908</v>
+        <v>14.10000038146973</v>
       </c>
       <c r="L29">
-        <v>24.46999931335449</v>
+        <v>35.4900016784668</v>
       </c>
       <c r="M29">
-        <v>147.7943906181666</v>
+        <v>141.1130969592363</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>36215000</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>48300000</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>28265000</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>34300000</v>
       </c>
       <c r="V29" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -3131,67 +3065,67 @@
         <v>50</v>
       </c>
       <c r="B30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" t="s">
         <v>117</v>
       </c>
-      <c r="C30" t="s">
-        <v>146</v>
-      </c>
       <c r="D30" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E30">
-        <v>35.09999847412109</v>
+        <v>82.76999664306641</v>
       </c>
       <c r="F30">
-        <v>884000</v>
+        <v>2494003.333333333</v>
       </c>
       <c r="G30">
-        <v>30.99769969940186</v>
+        <v>78.2125993347168</v>
       </c>
       <c r="H30">
-        <v>27.1356999206543</v>
+        <v>65.12313311258951</v>
       </c>
       <c r="I30">
-        <v>24.61477493286133</v>
+        <v>59.6959497833252</v>
       </c>
       <c r="J30">
-        <v>22.86844998836517</v>
+        <v>55.2992999458313</v>
       </c>
       <c r="K30">
-        <v>4.052896976470947</v>
+        <v>0.1027423962950706</v>
       </c>
       <c r="L30">
-        <v>35.09999847412109</v>
+        <v>86.01000213623047</v>
       </c>
       <c r="M30">
-        <v>147.6927667342856</v>
+        <v>140.4674616564985</v>
       </c>
       <c r="N30">
-        <v>-0.23</v>
+        <v>2.69</v>
       </c>
       <c r="O30">
-        <v>0.2</v>
+        <v>3.85</v>
       </c>
       <c r="P30">
-        <v>0.22</v>
+        <v>2.35</v>
       </c>
       <c r="Q30">
-        <v>0.46</v>
+        <v>3.21</v>
       </c>
       <c r="R30">
-        <v>-16058000</v>
+        <v>627928000</v>
       </c>
       <c r="S30">
-        <v>26801000</v>
+        <v>882231000</v>
       </c>
       <c r="T30">
-        <v>29397000</v>
+        <v>532259000</v>
       </c>
       <c r="U30">
-        <v>54753000</v>
+        <v>720345000</v>
       </c>
       <c r="V30" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -3199,67 +3133,67 @@
         <v>51</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C31" t="s">
         <v>136</v>
       </c>
       <c r="D31" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="E31">
-        <v>48.04999923706055</v>
+        <v>53.11999893188477</v>
       </c>
       <c r="F31">
-        <v>1337796.666666667</v>
+        <v>1646193.333333333</v>
       </c>
       <c r="G31">
-        <v>43.55699996948242</v>
+        <v>45.43160003662109</v>
       </c>
       <c r="H31">
-        <v>35.00859991709391</v>
+        <v>41.41553342183431</v>
       </c>
       <c r="I31">
-        <v>31.95659992218017</v>
+        <v>40.2892000579834</v>
       </c>
       <c r="J31">
-        <v>28.5842999124527</v>
+        <v>38.20370006561279</v>
       </c>
       <c r="K31">
-        <v>0.5</v>
+        <v>20.39999961853027</v>
       </c>
       <c r="L31">
-        <v>53.68999862670898</v>
+        <v>53.11999893188477</v>
       </c>
       <c r="M31">
-        <v>145.7507952465374</v>
+        <v>140.4228397423457</v>
       </c>
       <c r="N31">
-        <v>0.02</v>
+        <v>0.41</v>
       </c>
       <c r="O31">
-        <v>0.13</v>
+        <v>0.92</v>
       </c>
       <c r="P31">
-        <v>0.14</v>
+        <v>0.74</v>
       </c>
       <c r="Q31">
-        <v>0.21</v>
+        <v>0.45</v>
       </c>
       <c r="R31">
-        <v>589000</v>
+        <v>33585000</v>
       </c>
       <c r="S31">
-        <v>3725000</v>
+        <v>134962000</v>
       </c>
       <c r="T31">
-        <v>4132000</v>
+        <v>108063000</v>
       </c>
       <c r="U31">
-        <v>6111000</v>
+        <v>65816000</v>
       </c>
       <c r="V31" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -3267,67 +3201,67 @@
         <v>52</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="C32" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="E32">
-        <v>86.01000213623047</v>
+        <v>14.28999996185303</v>
       </c>
       <c r="F32">
-        <v>2562490</v>
+        <v>273240</v>
       </c>
       <c r="G32">
-        <v>77.16939956665038</v>
+        <v>12.65199996948242</v>
       </c>
       <c r="H32">
-        <v>64.39299980163574</v>
+        <v>11.21040002187093</v>
       </c>
       <c r="I32">
-        <v>59.00214981079102</v>
+        <v>10.46995000839233</v>
       </c>
       <c r="J32">
-        <v>54.66484994888306</v>
+        <v>9.954250004291534</v>
       </c>
       <c r="K32">
-        <v>0.1027423962950706</v>
+        <v>2.79044508934021</v>
       </c>
       <c r="L32">
-        <v>86.01000213623047</v>
+        <v>18.82888412475586</v>
       </c>
       <c r="M32">
-        <v>145.2601429697899</v>
+        <v>140.4219181576626</v>
       </c>
       <c r="N32">
-        <v>2.69</v>
+        <v>0.15</v>
       </c>
       <c r="O32">
-        <v>3.85</v>
+        <v>1.21</v>
       </c>
       <c r="P32">
-        <v>2.35</v>
+        <v>0.15</v>
       </c>
       <c r="Q32">
-        <v>3.21</v>
+        <v>0.23</v>
       </c>
       <c r="R32">
-        <v>627928000</v>
+        <v>2920000</v>
       </c>
       <c r="S32">
-        <v>882231000</v>
+        <v>24226000</v>
       </c>
       <c r="T32">
-        <v>532259000</v>
+        <v>3117000</v>
       </c>
       <c r="U32">
-        <v>720345000</v>
+        <v>4733000</v>
       </c>
       <c r="V32" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -3335,67 +3269,67 @@
         <v>53</v>
       </c>
       <c r="B33" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D33" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="E33">
-        <v>177.3300018310547</v>
+        <v>22.54000091552734</v>
       </c>
       <c r="F33">
-        <v>531286.6666666666</v>
+        <v>1219340</v>
       </c>
       <c r="G33">
-        <v>175.9778005981445</v>
+        <v>19.07240001678467</v>
       </c>
       <c r="H33">
-        <v>139.5797338867187</v>
+        <v>16.71699998219808</v>
       </c>
       <c r="I33">
-        <v>123.0961503982544</v>
+        <v>16.02879998207092</v>
       </c>
       <c r="J33">
-        <v>110.6287503051758</v>
+        <v>15.49339997291565</v>
       </c>
       <c r="K33">
-        <v>0.6800000071525574</v>
+        <v>10.84000015258789</v>
       </c>
       <c r="L33">
-        <v>200.4799957275391</v>
+        <v>22.6200008392334</v>
       </c>
       <c r="M33">
-        <v>144.7559778973308</v>
+        <v>139.7904698268517</v>
       </c>
       <c r="N33">
-        <v>1.21</v>
+        <v>0.01</v>
       </c>
       <c r="O33">
-        <v>1.71</v>
+        <v>-0.28</v>
       </c>
       <c r="P33">
-        <v>1.43</v>
+        <v>0.08</v>
       </c>
       <c r="Q33">
-        <v>1.86</v>
+        <v>0.05</v>
       </c>
       <c r="R33">
-        <v>40283000</v>
+        <v>1464000</v>
       </c>
       <c r="S33">
-        <v>56992000</v>
+        <v>-28687000</v>
       </c>
       <c r="T33">
-        <v>47697000</v>
+        <v>7846000</v>
       </c>
       <c r="U33">
-        <v>61579000</v>
+        <v>5389000</v>
       </c>
       <c r="V33" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -3403,135 +3337,129 @@
         <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C34" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="D34" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="E34">
-        <v>22.52000045776367</v>
+        <v>220.9700012207031</v>
       </c>
       <c r="F34">
-        <v>1097706.666666667</v>
+        <v>362340</v>
       </c>
       <c r="G34">
-        <v>18.83639995574951</v>
+        <v>189.6723999023438</v>
       </c>
       <c r="H34">
-        <v>16.53653329849243</v>
+        <v>168.3303333536784</v>
       </c>
       <c r="I34">
-        <v>15.89694997310638</v>
+        <v>163.243049697876</v>
       </c>
       <c r="J34">
-        <v>15.42824997425079</v>
+        <v>154.8937997436524</v>
       </c>
       <c r="K34">
-        <v>10.84000015258789</v>
+        <v>0.9346818327903748</v>
       </c>
       <c r="L34">
-        <v>22.55999946594238</v>
+        <v>221.1799926757812</v>
       </c>
       <c r="M34">
-        <v>140.8003600350384</v>
+        <v>138.4076502903102</v>
       </c>
       <c r="N34">
-        <v>0.01</v>
+        <v>2.16</v>
       </c>
       <c r="O34">
-        <v>-0.28</v>
+        <v>2.63</v>
       </c>
       <c r="P34">
-        <v>0.08</v>
+        <v>2.32</v>
       </c>
       <c r="Q34">
-        <v>0.05</v>
+        <v>2.95</v>
       </c>
       <c r="R34">
-        <v>1464000</v>
+        <v>105772000</v>
       </c>
       <c r="S34">
-        <v>-28687000</v>
+        <v>126300000</v>
       </c>
       <c r="T34">
-        <v>7846000</v>
+        <v>111473000</v>
       </c>
       <c r="U34">
-        <v>5389000</v>
+        <v>140595000</v>
       </c>
       <c r="V34" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="35" spans="1:22">
       <c r="A35" t="s">
         <v>55</v>
       </c>
-      <c r="B35" t="s">
-        <v>116</v>
-      </c>
-      <c r="C35" t="s">
-        <v>148</v>
-      </c>
       <c r="D35" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="E35">
-        <v>85.30000305175781</v>
+        <v>13.89000034332275</v>
       </c>
       <c r="F35">
-        <v>5131773.333333333</v>
+        <v>1247623.1</v>
       </c>
       <c r="G35">
-        <v>79.92280044555665</v>
+        <v>10.21729988098144</v>
       </c>
       <c r="H35">
-        <v>64.59806681315104</v>
+        <v>10.11725797017415</v>
       </c>
       <c r="I35">
-        <v>60.75095010757446</v>
+        <v>10.04098649501801</v>
       </c>
       <c r="J35">
-        <v>57.85625005722046</v>
+        <v>9.983236494064331</v>
       </c>
       <c r="K35">
-        <v>2.279999971389771</v>
+        <v>8.989999771118164</v>
       </c>
       <c r="L35">
-        <v>111.6399993896484</v>
+        <v>13.89000034332275</v>
       </c>
       <c r="M35">
-        <v>140.7465741597917</v>
+        <v>137.4754157399989</v>
       </c>
       <c r="N35">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="O35">
-        <v>0.03</v>
+        <v>0.090181</v>
       </c>
       <c r="P35">
-        <v>0.14</v>
+        <v>0.02</v>
       </c>
       <c r="Q35">
-        <v>0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="R35">
-        <v>-19073000</v>
+        <v>1944526</v>
       </c>
       <c r="S35">
-        <v>15869000</v>
+        <v>366476</v>
       </c>
       <c r="T35">
-        <v>71187000</v>
+        <v>900174</v>
       </c>
       <c r="U35">
-        <v>9326000</v>
+        <v>-1652348</v>
       </c>
       <c r="V35" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3539,67 +3467,67 @@
         <v>56</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C36" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D36" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="E36">
-        <v>142.8500061035156</v>
+        <v>74.38999938964844</v>
       </c>
       <c r="F36">
-        <v>872520</v>
+        <v>488146.6666666667</v>
       </c>
       <c r="G36">
-        <v>127.809600982666</v>
+        <v>71.12479972839355</v>
       </c>
       <c r="H36">
-        <v>107.8191337585449</v>
+        <v>57.26506647745768</v>
       </c>
       <c r="I36">
-        <v>102.9858502578735</v>
+        <v>54.79729982376099</v>
       </c>
       <c r="J36">
-        <v>97.50655010223389</v>
+        <v>52.65039991378784</v>
       </c>
       <c r="K36">
-        <v>4.719488620758057</v>
+        <v>14.8100004196167</v>
       </c>
       <c r="L36">
-        <v>142.8500061035156</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="M36">
-        <v>140.2716330985683</v>
+        <v>137.2527013094927</v>
       </c>
       <c r="N36">
-        <v>4.84</v>
+        <v>-0.58</v>
       </c>
       <c r="O36">
-        <v>1.32</v>
+        <v>-0.66</v>
       </c>
       <c r="P36">
-        <v>4.17</v>
+        <v>-0.72</v>
       </c>
       <c r="Q36">
-        <v>3.78</v>
+        <v>-0.68</v>
       </c>
       <c r="R36">
-        <v>470000000</v>
+        <v>-27576000</v>
       </c>
       <c r="S36">
-        <v>124000000</v>
+        <v>-31460000</v>
       </c>
       <c r="T36">
-        <v>383000000</v>
+        <v>-34626000</v>
       </c>
       <c r="U36">
-        <v>345000000</v>
+        <v>-32812000</v>
       </c>
       <c r="V36" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -3607,67 +3535,67 @@
         <v>57</v>
       </c>
       <c r="B37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" t="s">
         <v>123</v>
       </c>
-      <c r="C37" t="s">
-        <v>149</v>
-      </c>
       <c r="D37" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="E37">
-        <v>35.06000137329102</v>
+        <v>141.1799926757812</v>
       </c>
       <c r="F37">
-        <v>676190</v>
+        <v>865213.3333333334</v>
       </c>
       <c r="G37">
-        <v>26.68940013885498</v>
+        <v>129.7924006652832</v>
       </c>
       <c r="H37">
-        <v>25.90026672363281</v>
+        <v>108.8904003397624</v>
       </c>
       <c r="I37">
-        <v>25.06940004348755</v>
+        <v>103.8380001831055</v>
       </c>
       <c r="J37">
-        <v>23.83420004844665</v>
+        <v>98.35630016326904</v>
       </c>
       <c r="K37">
-        <v>0.6000000238418579</v>
+        <v>4.719488620758057</v>
       </c>
       <c r="L37">
-        <v>35.06000137329102</v>
+        <v>142.8500061035156</v>
       </c>
       <c r="M37">
-        <v>139.4357928260872</v>
+        <v>136.4639098814952</v>
       </c>
       <c r="N37">
-        <v>4.47</v>
+        <v>4.84</v>
       </c>
       <c r="O37">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="P37">
-        <v>3.9</v>
+        <v>4.17</v>
       </c>
       <c r="Q37">
-        <v>0.49</v>
+        <v>3.78</v>
       </c>
       <c r="R37">
-        <v>267396000</v>
+        <v>470000000</v>
       </c>
       <c r="S37">
-        <v>84719000</v>
+        <v>124000000</v>
       </c>
       <c r="T37">
-        <v>237890000</v>
+        <v>383000000</v>
       </c>
       <c r="U37">
-        <v>30013000</v>
+        <v>345000000</v>
       </c>
       <c r="V37" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -3675,31 +3603,31 @@
         <v>58</v>
       </c>
       <c r="B38" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C38" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D38" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="E38">
-        <v>377.3800048828125</v>
+        <v>371.010009765625</v>
       </c>
       <c r="F38">
-        <v>282690</v>
+        <v>275250</v>
       </c>
       <c r="G38">
-        <v>325.7794006347656</v>
+        <v>331.331000366211</v>
       </c>
       <c r="H38">
-        <v>280.8597340901693</v>
+        <v>283.5012007649739</v>
       </c>
       <c r="I38">
-        <v>273.1459002685547</v>
+        <v>275.3892002868652</v>
       </c>
       <c r="J38">
-        <v>260.4802004241943</v>
+        <v>262.1775503540039</v>
       </c>
       <c r="K38">
         <v>4.775613307952881</v>
@@ -3708,7 +3636,7 @@
         <v>377.3800048828125</v>
       </c>
       <c r="M38">
-        <v>138.2195730214023</v>
+        <v>136.147424272235</v>
       </c>
       <c r="N38">
         <v>3.99</v>
@@ -3735,7 +3663,7 @@
         <v>217200000</v>
       </c>
       <c r="V38" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -3743,129 +3671,135 @@
         <v>59</v>
       </c>
       <c r="B39" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="C39" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D39" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="E39">
-        <v>74.77999877929688</v>
+        <v>528.280029296875</v>
       </c>
       <c r="F39">
-        <v>508506.6666666667</v>
+        <v>2931353.333333333</v>
       </c>
       <c r="G39">
-        <v>70.0605997467041</v>
+        <v>457.9842016601563</v>
       </c>
       <c r="H39">
-        <v>56.67946647644043</v>
+        <v>395.0512672932942</v>
       </c>
       <c r="I39">
-        <v>54.51254983901978</v>
+        <v>386.9230003356934</v>
       </c>
       <c r="J39">
-        <v>52.2969499206543</v>
+        <v>373.0333006286621</v>
       </c>
       <c r="K39">
-        <v>14.8100004196167</v>
+        <v>0.5143532752990723</v>
       </c>
       <c r="L39">
-        <v>97.69999694824219</v>
+        <v>528.280029296875</v>
       </c>
       <c r="M39">
-        <v>138.1663907436597</v>
+        <v>136.1431177762248</v>
       </c>
       <c r="N39">
-        <v>-0.58</v>
+        <v>1.61</v>
       </c>
       <c r="O39">
-        <v>-0.66</v>
+        <v>2.039294</v>
       </c>
       <c r="P39">
-        <v>-0.72</v>
+        <v>1.49</v>
       </c>
       <c r="Q39">
-        <v>-0.68</v>
+        <v>1.95</v>
       </c>
       <c r="R39">
-        <v>-27576000</v>
+        <v>1451700000</v>
       </c>
       <c r="S39">
-        <v>-31460000</v>
+        <v>1937700000</v>
       </c>
       <c r="T39">
-        <v>-34626000</v>
+        <v>1344900000</v>
       </c>
       <c r="U39">
-        <v>-32812000</v>
+        <v>1763200000</v>
       </c>
       <c r="V39" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="40" spans="1:22">
       <c r="A40" t="s">
         <v>60</v>
       </c>
+      <c r="B40" t="s">
+        <v>105</v>
+      </c>
+      <c r="C40" t="s">
+        <v>141</v>
+      </c>
       <c r="D40" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="E40">
-        <v>13.89000034332275</v>
+        <v>16.02000045776367</v>
       </c>
       <c r="F40">
-        <v>1247623.1</v>
+        <v>463816.6666666667</v>
       </c>
       <c r="G40">
-        <v>10.21729988098144</v>
+        <v>13.52480001449585</v>
       </c>
       <c r="H40">
-        <v>10.11725797017415</v>
+        <v>12.88340000788371</v>
       </c>
       <c r="I40">
-        <v>10.04098649501801</v>
+        <v>12.36385000705719</v>
       </c>
       <c r="J40">
-        <v>9.983236494064331</v>
+        <v>11.92120000839233</v>
       </c>
       <c r="K40">
-        <v>8.989999771118164</v>
+        <v>9.039999961853027</v>
       </c>
       <c r="L40">
-        <v>13.89000034332275</v>
+        <v>16.02000045776367</v>
       </c>
       <c r="M40">
-        <v>137.8945695997145</v>
+        <v>134.5764056541234</v>
       </c>
       <c r="N40">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>0.090181</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>1944526</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>366476</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>900174</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>-1652348</v>
+        <v>0</v>
       </c>
       <c r="V40" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -3873,67 +3807,67 @@
         <v>61</v>
       </c>
       <c r="B41" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="C41" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D41" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="E41">
-        <v>221.1799926757812</v>
+        <v>45.68999862670898</v>
       </c>
       <c r="F41">
-        <v>372000</v>
+        <v>1367750</v>
       </c>
       <c r="G41">
-        <v>186.6495999145508</v>
+        <v>44.39959999084473</v>
       </c>
       <c r="H41">
-        <v>166.8522666422526</v>
+        <v>35.59893324534098</v>
       </c>
       <c r="I41">
-        <v>161.8516996765137</v>
+        <v>32.3594499206543</v>
       </c>
       <c r="J41">
-        <v>153.8178998184204</v>
+        <v>29.02394990921021</v>
       </c>
       <c r="K41">
-        <v>0.9346818327903748</v>
+        <v>0.5</v>
       </c>
       <c r="L41">
-        <v>221.1799926757812</v>
+        <v>53.68999862670898</v>
       </c>
       <c r="M41">
-        <v>136.9737893920463</v>
+        <v>134.4818075635634</v>
       </c>
       <c r="N41">
-        <v>2.16</v>
+        <v>0.02</v>
       </c>
       <c r="O41">
-        <v>2.63</v>
+        <v>0.13</v>
       </c>
       <c r="P41">
-        <v>2.32</v>
+        <v>0.14</v>
       </c>
       <c r="Q41">
-        <v>2.95</v>
+        <v>0.21</v>
       </c>
       <c r="R41">
-        <v>105772000</v>
+        <v>589000</v>
       </c>
       <c r="S41">
-        <v>126300000</v>
+        <v>3725000</v>
       </c>
       <c r="T41">
-        <v>111473000</v>
+        <v>4132000</v>
       </c>
       <c r="U41">
-        <v>140595000</v>
+        <v>6111000</v>
       </c>
       <c r="V41" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -3941,67 +3875,67 @@
         <v>62</v>
       </c>
       <c r="B42" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="C42" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="D42" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E42">
-        <v>25.79000091552734</v>
+        <v>31.93000030517578</v>
       </c>
       <c r="F42">
-        <v>792403.3333333334</v>
+        <v>830420</v>
       </c>
       <c r="G42">
-        <v>24.32139999389648</v>
+        <v>30.36959999084473</v>
       </c>
       <c r="H42">
-        <v>20.50406672159831</v>
+        <v>25.86100002288818</v>
       </c>
       <c r="I42">
-        <v>18.77715003490448</v>
+        <v>24.58240002632141</v>
       </c>
       <c r="J42">
-        <v>17.23650003910065</v>
+        <v>23.68895002365112</v>
       </c>
       <c r="K42">
-        <v>1.899999976158142</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="L42">
-        <v>27.38999938964844</v>
+        <v>32.58000183105469</v>
       </c>
       <c r="M42">
-        <v>136.9735154571766</v>
+        <v>133.8076164573903</v>
       </c>
       <c r="N42">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O42">
-        <v>0.762</v>
+        <v>0.65</v>
       </c>
       <c r="P42">
-        <v>1.315</v>
+        <v>0.31</v>
       </c>
       <c r="Q42">
-        <v>0.519</v>
+        <v>0.5</v>
       </c>
       <c r="R42">
-        <v>76661000</v>
+        <v>115000000</v>
       </c>
       <c r="S42">
-        <v>75504000</v>
+        <v>111000000</v>
       </c>
       <c r="T42">
-        <v>128734000</v>
+        <v>54000000</v>
       </c>
       <c r="U42">
-        <v>52181000</v>
+        <v>86000000</v>
       </c>
       <c r="V42" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -4009,67 +3943,67 @@
         <v>63</v>
       </c>
       <c r="B43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" t="s">
         <v>118</v>
       </c>
-      <c r="C43" t="s">
-        <v>127</v>
-      </c>
       <c r="D43" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="E43">
-        <v>54.81999969482422</v>
+        <v>25.11000061035156</v>
       </c>
       <c r="F43">
-        <v>1653563.333333333</v>
+        <v>413863.3333333333</v>
       </c>
       <c r="G43">
-        <v>51.10480003356933</v>
+        <v>23.33959999084473</v>
       </c>
       <c r="H43">
-        <v>42.92266660054525</v>
+        <v>19.38233335494995</v>
       </c>
       <c r="I43">
-        <v>39.77599993705749</v>
+        <v>18.85460000514984</v>
       </c>
       <c r="J43">
-        <v>37.11009996414185</v>
+        <v>18.14239999771118</v>
       </c>
       <c r="K43">
-        <v>1.498309969902039</v>
+        <v>3.029999971389771</v>
       </c>
       <c r="L43">
-        <v>66.26741027832031</v>
+        <v>27.07999992370605</v>
       </c>
       <c r="M43">
-        <v>135.9624801810163</v>
+        <v>132.729673947039</v>
       </c>
       <c r="N43">
-        <v>2.86</v>
+        <v>0.04</v>
       </c>
       <c r="O43">
-        <v>2.47</v>
+        <v>-0.5</v>
       </c>
       <c r="P43">
-        <v>1.45</v>
+        <v>-0.49</v>
       </c>
       <c r="Q43">
-        <v>1.94</v>
+        <v>-0.5</v>
       </c>
       <c r="R43">
-        <v>255329000</v>
+        <v>1615000</v>
       </c>
       <c r="S43">
-        <v>216410000</v>
+        <v>-24201000</v>
       </c>
       <c r="T43">
-        <v>125500000</v>
+        <v>-23640000</v>
       </c>
       <c r="U43">
-        <v>164442000</v>
+        <v>-27926000</v>
       </c>
       <c r="V43" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -4077,67 +4011,67 @@
         <v>64</v>
       </c>
       <c r="B44" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C44" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D44" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="E44">
-        <v>883.1599731445312</v>
+        <v>3206.22998046875</v>
       </c>
       <c r="F44">
-        <v>2304100</v>
+        <v>332526.6666666667</v>
       </c>
       <c r="G44">
-        <v>862.3584008789062</v>
+        <v>2808.406977539063</v>
       </c>
       <c r="H44">
-        <v>697.6188671875</v>
+        <v>2621.781267903646</v>
       </c>
       <c r="I44">
-        <v>652.0013499450683</v>
+        <v>2457.668399658203</v>
       </c>
       <c r="J44">
-        <v>607.6588496398925</v>
+        <v>2328.07645324707</v>
       </c>
       <c r="K44">
-        <v>11.17089080810547</v>
+        <v>6.599999904632568</v>
       </c>
       <c r="L44">
-        <v>920</v>
+        <v>3243.010009765625</v>
       </c>
       <c r="M44">
-        <v>135.4375103024965</v>
+        <v>131.2948143616237</v>
       </c>
       <c r="N44">
-        <v>7.132125</v>
+        <v>41.98</v>
       </c>
       <c r="O44">
-        <v>7.810425</v>
+        <v>31.92</v>
       </c>
       <c r="P44">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="Q44">
-        <v>8.15</v>
+        <v>34.89</v>
       </c>
       <c r="R44">
-        <v>3074000000</v>
+        <v>1666000000</v>
       </c>
       <c r="S44">
-        <v>3359000000</v>
+        <v>1235000000</v>
       </c>
       <c r="T44">
-        <v>3774000000</v>
+        <v>266000000</v>
       </c>
       <c r="U44">
-        <v>3481000000</v>
+        <v>1290000000</v>
       </c>
       <c r="V44" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -4145,67 +4079,67 @@
         <v>65</v>
       </c>
       <c r="B45" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C45" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D45" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="E45">
-        <v>521.5999755859375</v>
+        <v>12.72999954223633</v>
       </c>
       <c r="F45">
-        <v>2834053.333333333</v>
+        <v>8940533.333333334</v>
       </c>
       <c r="G45">
-        <v>452.1170007324219</v>
+        <v>11.75459997177124</v>
       </c>
       <c r="H45">
-        <v>391.7923337809245</v>
+        <v>10.134399989446</v>
       </c>
       <c r="I45">
-        <v>384.1324501037598</v>
+        <v>9.851600005626679</v>
       </c>
       <c r="J45">
-        <v>371.0586505126953</v>
+        <v>9.431450011730194</v>
       </c>
       <c r="K45">
-        <v>0.5143532752990723</v>
+        <v>0.3049550950527191</v>
       </c>
       <c r="L45">
-        <v>521.5999755859375</v>
+        <v>13.86999988555908</v>
       </c>
       <c r="M45">
-        <v>135.1759247283216</v>
+        <v>130.749804244786</v>
       </c>
       <c r="N45">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="O45">
-        <v>1.61</v>
+        <v>0.3</v>
       </c>
       <c r="P45">
-        <v>2.039294</v>
+        <v>2.87</v>
       </c>
       <c r="Q45">
-        <v>1.416777</v>
+        <v>0.55</v>
       </c>
       <c r="R45">
-        <v>952500000</v>
+        <v>152000000</v>
       </c>
       <c r="S45">
-        <v>1451700000</v>
+        <v>172000000</v>
       </c>
       <c r="T45">
-        <v>1937700000</v>
+        <v>2006000000</v>
       </c>
       <c r="U45">
-        <v>1344900000</v>
+        <v>413000000</v>
       </c>
       <c r="V45" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="46" spans="1:22">
@@ -4213,67 +4147,67 @@
         <v>66</v>
       </c>
       <c r="B46" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C46" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="D46" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="E46">
-        <v>44.04000091552734</v>
+        <v>79.47000122070312</v>
       </c>
       <c r="F46">
-        <v>296346.6666666667</v>
+        <v>1400503.333333333</v>
       </c>
       <c r="G46">
-        <v>43.57499984741211</v>
+        <v>77.79500045776368</v>
       </c>
       <c r="H46">
-        <v>35.52153327941895</v>
+        <v>65.99046679178873</v>
       </c>
       <c r="I46">
-        <v>34.12624994277954</v>
+        <v>61.29690017700195</v>
       </c>
       <c r="J46">
-        <v>31.53129996299744</v>
+        <v>57.5823501586914</v>
       </c>
       <c r="K46">
-        <v>7.400000095367432</v>
+        <v>0.5319142937660217</v>
       </c>
       <c r="L46">
-        <v>49.84999847412109</v>
+        <v>83.51999664306641</v>
       </c>
       <c r="M46">
-        <v>135.1312624139452</v>
+        <v>130.4338572917512</v>
       </c>
       <c r="N46">
-        <v>-0.38</v>
+        <v>2.35</v>
       </c>
       <c r="O46">
-        <v>-0.41</v>
+        <v>5.63</v>
       </c>
       <c r="P46">
-        <v>-0.49</v>
+        <v>1.7</v>
       </c>
       <c r="Q46">
-        <v>-0.44</v>
+        <v>2.85</v>
       </c>
       <c r="R46">
-        <v>-18466000</v>
+        <v>273467000</v>
       </c>
       <c r="S46">
-        <v>-19716000</v>
+        <v>640536000</v>
       </c>
       <c r="T46">
-        <v>-26123000</v>
+        <v>191530000</v>
       </c>
       <c r="U46">
-        <v>-25192000</v>
+        <v>320216000</v>
       </c>
       <c r="V46" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -4281,67 +4215,67 @@
         <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D47" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="E47">
-        <v>32.5099983215332</v>
+        <v>13.93000030517578</v>
       </c>
       <c r="F47">
-        <v>895333.3333333334</v>
+        <v>539723.3333333334</v>
       </c>
       <c r="G47">
-        <v>30.07680000305176</v>
+        <v>12.87540000915527</v>
       </c>
       <c r="H47">
-        <v>25.62233336130778</v>
+        <v>11.11013334274292</v>
       </c>
       <c r="I47">
-        <v>24.43005002975464</v>
+        <v>10.45255000114441</v>
       </c>
       <c r="J47">
-        <v>23.5480500125885</v>
+        <v>9.884999992847442</v>
       </c>
       <c r="K47">
-        <v>18.89999961853027</v>
+        <v>6.639999866485596</v>
       </c>
       <c r="L47">
-        <v>32.58000183105469</v>
+        <v>14.38000011444092</v>
       </c>
       <c r="M47">
-        <v>134.9736723172544</v>
+        <v>129.8806525371881</v>
       </c>
       <c r="N47">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="O47">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="P47">
-        <v>0.31</v>
+        <v>1.17</v>
       </c>
       <c r="Q47">
-        <v>0.5</v>
+        <v>1.17</v>
       </c>
       <c r="R47">
-        <v>115000000</v>
+        <v>-77781000</v>
       </c>
       <c r="S47">
-        <v>111000000</v>
+        <v>259425000</v>
       </c>
       <c r="T47">
-        <v>54000000</v>
+        <v>-77781000</v>
       </c>
       <c r="U47">
-        <v>86000000</v>
+        <v>259425000</v>
       </c>
       <c r="V47" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="48" spans="1:22">
@@ -4349,67 +4283,67 @@
         <v>68</v>
       </c>
       <c r="B48" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C48" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="D48" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="E48">
-        <v>520.5999755859375</v>
+        <v>52.40999984741211</v>
       </c>
       <c r="F48">
-        <v>2879326.666666667</v>
+        <v>1537816.666666667</v>
       </c>
       <c r="G48">
-        <v>489.8401965332031</v>
+        <v>51.65040000915528</v>
       </c>
       <c r="H48">
-        <v>402.953598836263</v>
+        <v>43.31999994913737</v>
       </c>
       <c r="I48">
-        <v>384.0085487365723</v>
+        <v>40.16489994049072</v>
       </c>
       <c r="J48">
-        <v>360.3102992248535</v>
+        <v>37.51334995269775</v>
       </c>
       <c r="K48">
-        <v>0.1503329128026962</v>
+        <v>1.498309969902039</v>
       </c>
       <c r="L48">
-        <v>688.3699951171875</v>
+        <v>66.26741027832031</v>
       </c>
       <c r="M48">
-        <v>134.3412516983596</v>
+        <v>129.8489324369625</v>
       </c>
       <c r="N48">
-        <v>2.42</v>
+        <v>2.86</v>
       </c>
       <c r="O48">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="P48">
-        <v>2.71</v>
+        <v>1.45</v>
       </c>
       <c r="Q48">
-        <v>2.82</v>
+        <v>1.94</v>
       </c>
       <c r="R48">
-        <v>1136000000</v>
+        <v>255329000</v>
       </c>
       <c r="S48">
-        <v>1176000000</v>
+        <v>216410000</v>
       </c>
       <c r="T48">
-        <v>1247000000</v>
+        <v>125500000</v>
       </c>
       <c r="U48">
-        <v>1295000000</v>
+        <v>164442000</v>
       </c>
       <c r="V48" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
     </row>
     <row r="49" spans="1:22">
@@ -4417,67 +4351,67 @@
         <v>69</v>
       </c>
       <c r="B49" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C49" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="D49" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="E49">
-        <v>15.81999969482422</v>
+        <v>36.79999923706055</v>
       </c>
       <c r="F49">
-        <v>510526.6666666667</v>
+        <v>1561900</v>
       </c>
       <c r="G49">
-        <v>13.26059999465942</v>
+        <v>31.89650001525879</v>
       </c>
       <c r="H49">
-        <v>12.77213333765666</v>
+        <v>29.83143333435059</v>
       </c>
       <c r="I49">
-        <v>12.28575000286102</v>
+        <v>29.74722499847412</v>
       </c>
       <c r="J49">
-        <v>11.8549000120163</v>
+        <v>28.34730000495911</v>
       </c>
       <c r="K49">
-        <v>9.039999961853027</v>
+        <v>3.019999980926514</v>
       </c>
       <c r="L49">
-        <v>15.89999961853027</v>
+        <v>45.52999877929688</v>
       </c>
       <c r="M49">
-        <v>133.6994029608328</v>
+        <v>129.7620497359756</v>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>23068000</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>67857000</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>63532000</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>95797000</v>
       </c>
       <c r="V49" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="50" spans="1:22">
@@ -4485,67 +4419,67 @@
         <v>70</v>
       </c>
       <c r="B50" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="C50" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="D50" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="E50">
-        <v>149.2400054931641</v>
+        <v>316.3399963378906</v>
       </c>
       <c r="F50">
-        <v>339186.6666666667</v>
+        <v>279336.6666666667</v>
       </c>
       <c r="G50">
-        <v>136.7890003967285</v>
+        <v>293.1111987304687</v>
       </c>
       <c r="H50">
-        <v>121.1256001790365</v>
+        <v>255.0672003173828</v>
       </c>
       <c r="I50">
-        <v>111.6251002120972</v>
+        <v>245.1805002593994</v>
       </c>
       <c r="J50">
-        <v>104.3352502822876</v>
+        <v>235.4927503967285</v>
       </c>
       <c r="K50">
-        <v>0.577300488948822</v>
+        <v>1.363492727279663</v>
       </c>
       <c r="L50">
-        <v>150.4900054931641</v>
+        <v>412.9100646972656</v>
       </c>
       <c r="M50">
-        <v>133.2237848789503</v>
+        <v>129.7403585985813</v>
       </c>
       <c r="N50">
-        <v>7.1</v>
+        <v>11.92</v>
       </c>
       <c r="O50">
-        <v>7.09</v>
+        <v>9</v>
       </c>
       <c r="P50">
-        <v>3.54</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q50">
-        <v>5.02</v>
+        <v>10.78</v>
       </c>
       <c r="R50">
-        <v>262489000</v>
+        <v>329600000</v>
       </c>
       <c r="S50">
-        <v>262365000</v>
+        <v>247700000</v>
       </c>
       <c r="T50">
-        <v>131301000</v>
+        <v>228700000</v>
       </c>
       <c r="U50">
-        <v>186836000</v>
+        <v>297200000</v>
       </c>
       <c r="V50" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -4553,31 +4487,31 @@
         <v>71</v>
       </c>
       <c r="B51" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="C51" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D51" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E51">
-        <v>399.8699951171875</v>
+        <v>394.739990234375</v>
       </c>
       <c r="F51">
-        <v>365353.3333333333</v>
+        <v>369953.3333333333</v>
       </c>
       <c r="G51">
-        <v>367.1920001220703</v>
+        <v>370.8051995849609</v>
       </c>
       <c r="H51">
-        <v>333.7755997721354</v>
+        <v>337.0148663330078</v>
       </c>
       <c r="I51">
-        <v>308.6507496643067</v>
+        <v>311.1224495697022</v>
       </c>
       <c r="J51">
-        <v>296.0106996917725</v>
+        <v>297.9713496398926</v>
       </c>
       <c r="K51">
         <v>0.2751234471797943</v>
@@ -4586,7 +4520,7 @@
         <v>471.1166076660156</v>
       </c>
       <c r="M51">
-        <v>132.9899978290975</v>
+        <v>129.1618824936386</v>
       </c>
       <c r="N51">
         <v>1.59</v>
@@ -4613,7 +4547,7 @@
         <v>155100000</v>
       </c>
       <c r="V51" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="52" spans="1:22">
@@ -4621,67 +4555,67 @@
         <v>72</v>
       </c>
       <c r="B52" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C52" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D52" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="E52">
-        <v>13.27000045776367</v>
+        <v>22.68000030517578</v>
       </c>
       <c r="F52">
-        <v>8936656.666666666</v>
+        <v>505010</v>
       </c>
       <c r="G52">
-        <v>11.60799997329712</v>
+        <v>19.7838000869751</v>
       </c>
       <c r="H52">
-        <v>10.05093332608541</v>
+        <v>17.84460003534953</v>
       </c>
       <c r="I52">
-        <v>9.785900003910065</v>
+        <v>17.16760002613067</v>
       </c>
       <c r="J52">
-        <v>9.390100014209747</v>
+        <v>16.40125003814697</v>
       </c>
       <c r="K52">
-        <v>0.3049550950527191</v>
+        <v>6.340000152587891</v>
       </c>
       <c r="L52">
-        <v>13.86999988555908</v>
+        <v>22.70000076293945</v>
       </c>
       <c r="M52">
-        <v>132.8223821631663</v>
+        <v>129.073264833155</v>
       </c>
       <c r="N52">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="O52">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="P52">
-        <v>2.87</v>
+        <v>0.24</v>
       </c>
       <c r="Q52">
-        <v>0.55</v>
+        <v>0.25</v>
       </c>
       <c r="R52">
-        <v>152000000</v>
+        <v>4800000</v>
       </c>
       <c r="S52">
-        <v>172000000</v>
+        <v>7500000</v>
       </c>
       <c r="T52">
-        <v>2006000000</v>
+        <v>5500000</v>
       </c>
       <c r="U52">
-        <v>413000000</v>
+        <v>5600000</v>
       </c>
       <c r="V52" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -4689,67 +4623,67 @@
         <v>73</v>
       </c>
       <c r="B53" t="s">
+        <v>105</v>
+      </c>
+      <c r="C53" t="s">
         <v>117</v>
       </c>
-      <c r="C53" t="s">
-        <v>152</v>
-      </c>
       <c r="D53" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="E53">
-        <v>82.58999633789062</v>
+        <v>144.3999938964844</v>
       </c>
       <c r="F53">
-        <v>545993.3333333334</v>
+        <v>330896.6666666667</v>
       </c>
       <c r="G53">
-        <v>79.75639991760254</v>
+        <v>138.5230001831055</v>
       </c>
       <c r="H53">
-        <v>66.07173319498698</v>
+        <v>122.120866800944</v>
       </c>
       <c r="I53">
-        <v>63.63964992523194</v>
+        <v>112.7901002120972</v>
       </c>
       <c r="J53">
-        <v>60.75819997787475</v>
+        <v>105.4165503311157</v>
       </c>
       <c r="K53">
-        <v>7.03000020980835</v>
+        <v>0.577300488948822</v>
       </c>
       <c r="L53">
-        <v>86.93000030517578</v>
+        <v>150.4900054931641</v>
       </c>
       <c r="M53">
-        <v>132.3943461258388</v>
+        <v>128.9038489400424</v>
       </c>
       <c r="N53">
-        <v>1.95</v>
+        <v>7.1</v>
       </c>
       <c r="O53">
-        <v>0.88</v>
+        <v>7.09</v>
       </c>
       <c r="P53">
-        <v>0.25</v>
+        <v>3.54</v>
       </c>
       <c r="Q53">
-        <v>1.97</v>
+        <v>5.02</v>
       </c>
       <c r="R53">
-        <v>154800000</v>
+        <v>262489000</v>
       </c>
       <c r="S53">
-        <v>73300000</v>
+        <v>262365000</v>
       </c>
       <c r="T53">
-        <v>24800000</v>
+        <v>131301000</v>
       </c>
       <c r="U53">
-        <v>153800000</v>
+        <v>186836000</v>
       </c>
       <c r="V53" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -4757,67 +4691,67 @@
         <v>74</v>
       </c>
       <c r="B54" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="C54" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D54" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="E54">
-        <v>52.2400016784668</v>
+        <v>56.84000015258789</v>
       </c>
       <c r="F54">
-        <v>1589146.666666667</v>
+        <v>3724300</v>
       </c>
       <c r="G54">
-        <v>44.63120010375977</v>
+        <v>52.30879974365234</v>
       </c>
       <c r="H54">
-        <v>41.08480008443197</v>
+        <v>45.37219988505046</v>
       </c>
       <c r="I54">
-        <v>40.01090007781983</v>
+        <v>44.2636999130249</v>
       </c>
       <c r="J54">
-        <v>37.89395005226135</v>
+        <v>42.3619499206543</v>
       </c>
       <c r="K54">
-        <v>20.39999961853027</v>
+        <v>11.99751472473145</v>
       </c>
       <c r="L54">
-        <v>52.68000030517578</v>
+        <v>60.77000045776367</v>
       </c>
       <c r="M54">
-        <v>132.3638191578668</v>
+        <v>128.8848941264693</v>
       </c>
       <c r="N54">
-        <v>0.41</v>
+        <v>0.68</v>
       </c>
       <c r="O54">
-        <v>0.92</v>
+        <v>0.33</v>
       </c>
       <c r="P54">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="Q54">
-        <v>0.45</v>
+        <v>0.79</v>
       </c>
       <c r="R54">
-        <v>33585000</v>
+        <v>511000000</v>
       </c>
       <c r="S54">
-        <v>134962000</v>
+        <v>245000000</v>
       </c>
       <c r="T54">
-        <v>108063000</v>
+        <v>614000000</v>
       </c>
       <c r="U54">
-        <v>65816000</v>
+        <v>583000000</v>
       </c>
       <c r="V54" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="55" spans="1:22">
@@ -4825,67 +4759,67 @@
         <v>75</v>
       </c>
       <c r="B55" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C55" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D55" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="E55">
-        <v>80.76000213623047</v>
+        <v>410.7799987792969</v>
       </c>
       <c r="F55">
-        <v>1475296.666666667</v>
+        <v>894546.6666666666</v>
       </c>
       <c r="G55">
-        <v>77.09020050048828</v>
+        <v>367.365</v>
       </c>
       <c r="H55">
-        <v>65.42453348795573</v>
+        <v>342.9958664957682</v>
       </c>
       <c r="I55">
-        <v>60.71920019149781</v>
+        <v>329.6655497741699</v>
       </c>
       <c r="J55">
-        <v>56.97220012664795</v>
+        <v>315.5028498077393</v>
       </c>
       <c r="K55">
-        <v>0.5319142937660217</v>
+        <v>0.6462651491165161</v>
       </c>
       <c r="L55">
-        <v>83.51999664306641</v>
+        <v>427.5899963378906</v>
       </c>
       <c r="M55">
-        <v>131.7932215214609</v>
+        <v>128.7950124664951</v>
       </c>
       <c r="N55">
-        <v>2.35</v>
+        <v>3.36</v>
       </c>
       <c r="O55">
-        <v>5.63</v>
+        <v>2.92</v>
       </c>
       <c r="P55">
-        <v>1.7</v>
+        <v>2.58</v>
       </c>
       <c r="Q55">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="R55">
-        <v>273467000</v>
+        <v>377401000</v>
       </c>
       <c r="S55">
-        <v>640536000</v>
+        <v>323929000</v>
       </c>
       <c r="T55">
-        <v>191530000</v>
+        <v>285038000</v>
       </c>
       <c r="U55">
-        <v>320216000</v>
+        <v>292362000</v>
       </c>
       <c r="V55" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="56" spans="1:22">
@@ -4893,67 +4827,67 @@
         <v>76</v>
       </c>
       <c r="B56" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C56" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="D56" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="E56">
-        <v>51.5099983215332</v>
+        <v>53.59999847412109</v>
       </c>
       <c r="F56">
-        <v>688150</v>
+        <v>762723.3333333334</v>
       </c>
       <c r="G56">
-        <v>46.24440002441406</v>
+        <v>49.37919982910157</v>
       </c>
       <c r="H56">
-        <v>40.85913327534993</v>
+        <v>43.57313331604004</v>
       </c>
       <c r="I56">
-        <v>38.48434993743896</v>
+        <v>42.8860000038147</v>
       </c>
       <c r="J56">
-        <v>36.43699994087219</v>
+        <v>41.44685005187988</v>
       </c>
       <c r="K56">
-        <v>0.02175931446254253</v>
+        <v>2.721946477890015</v>
       </c>
       <c r="L56">
-        <v>59.96058654785156</v>
+        <v>53.91999816894531</v>
       </c>
       <c r="M56">
-        <v>131.5834964933555</v>
+        <v>128.7887322138049</v>
       </c>
       <c r="N56">
-        <v>1.98</v>
+        <v>3.41</v>
       </c>
       <c r="O56">
-        <v>1.08</v>
+        <v>0.25</v>
       </c>
       <c r="P56">
-        <v>1.08</v>
+        <v>-2</v>
       </c>
       <c r="Q56">
-        <v>1.24</v>
+        <v>4.36</v>
       </c>
       <c r="R56">
-        <v>144400000</v>
+        <v>312600000</v>
       </c>
       <c r="S56">
-        <v>79776000</v>
+        <v>32572000</v>
       </c>
       <c r="T56">
-        <v>80700000</v>
+        <v>-155994000</v>
       </c>
       <c r="U56">
-        <v>93493000</v>
+        <v>355363000</v>
       </c>
       <c r="V56" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -4961,67 +4895,67 @@
         <v>77</v>
       </c>
       <c r="B57" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C57" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D57" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="E57">
-        <v>120.25</v>
+        <v>82.01999664306641</v>
       </c>
       <c r="F57">
-        <v>306303.3333333333</v>
+        <v>616630</v>
       </c>
       <c r="G57">
-        <v>111.5819995117187</v>
+        <v>80.76759994506835</v>
       </c>
       <c r="H57">
-        <v>92.67013320922851</v>
+        <v>66.675066502889</v>
       </c>
       <c r="I57">
-        <v>87.92689987182617</v>
+        <v>64.08049989700318</v>
       </c>
       <c r="J57">
-        <v>82.94034990310669</v>
+        <v>61.24854995727539</v>
       </c>
       <c r="K57">
-        <v>20.81999969482422</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="L57">
-        <v>124.3199996948242</v>
+        <v>86.93000030517578</v>
       </c>
       <c r="M57">
-        <v>131.3232784295469</v>
+        <v>128.6541892318087</v>
       </c>
       <c r="N57">
-        <v>1.03</v>
+        <v>1.95</v>
       </c>
       <c r="O57">
-        <v>1.05</v>
+        <v>0.88</v>
       </c>
       <c r="P57">
-        <v>1.34</v>
+        <v>0.25</v>
       </c>
       <c r="Q57">
-        <v>0.59</v>
+        <v>1.97</v>
       </c>
       <c r="R57">
-        <v>51575000</v>
+        <v>154800000</v>
       </c>
       <c r="S57">
-        <v>52215000</v>
+        <v>73300000</v>
       </c>
       <c r="T57">
-        <v>66214000</v>
+        <v>24800000</v>
       </c>
       <c r="U57">
-        <v>29068000</v>
+        <v>153800000</v>
       </c>
       <c r="V57" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="58" spans="1:22">
@@ -5029,67 +4963,67 @@
         <v>78</v>
       </c>
       <c r="B58" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="C58" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D58" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="E58">
-        <v>28.36000061035156</v>
+        <v>218.3600006103516</v>
       </c>
       <c r="F58">
-        <v>617966.6666666666</v>
+        <v>2012790</v>
       </c>
       <c r="G58">
-        <v>25.58259994506836</v>
+        <v>201.5470004272461</v>
       </c>
       <c r="H58">
-        <v>22.4570666440328</v>
+        <v>178.6750005086263</v>
       </c>
       <c r="I58">
-        <v>21.52535000324249</v>
+        <v>173.5676505279541</v>
       </c>
       <c r="J58">
-        <v>20.23989997863769</v>
+        <v>166.1429005432129</v>
       </c>
       <c r="K58">
-        <v>4.372677803039551</v>
+        <v>0.004536735825240612</v>
       </c>
       <c r="L58">
-        <v>29.73999977111816</v>
+        <v>221.0899963378906</v>
       </c>
       <c r="M58">
-        <v>131.27547443351</v>
+        <v>127.9521132948472</v>
       </c>
       <c r="N58">
-        <v>0.51</v>
+        <v>1.52</v>
       </c>
       <c r="O58">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
       <c r="P58">
-        <v>1.89</v>
+        <v>1.59</v>
       </c>
       <c r="Q58">
-        <v>1.28</v>
+        <v>1.86</v>
       </c>
       <c r="R58">
-        <v>20311465</v>
+        <v>607000000</v>
       </c>
       <c r="S58">
-        <v>51263710</v>
+        <v>721000000</v>
       </c>
       <c r="T58">
-        <v>76021035</v>
+        <v>638000000</v>
       </c>
       <c r="U58">
-        <v>51721137</v>
+        <v>744000000</v>
       </c>
       <c r="V58" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="59" spans="1:22">
@@ -5097,31 +5031,31 @@
         <v>79</v>
       </c>
       <c r="B59" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C59" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D59" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="E59">
-        <v>46</v>
+        <v>45.18000030517578</v>
       </c>
       <c r="F59">
-        <v>277470</v>
+        <v>316406.6666666667</v>
       </c>
       <c r="G59">
-        <v>39.94239974975586</v>
+        <v>40.65359977722168</v>
       </c>
       <c r="H59">
-        <v>36.94793333689372</v>
+        <v>37.21333333333333</v>
       </c>
       <c r="I59">
-        <v>35.22249998092651</v>
+        <v>35.49319997787475</v>
       </c>
       <c r="J59">
-        <v>33.71200003623962</v>
+        <v>33.88315003395081</v>
       </c>
       <c r="K59">
         <v>6.900000095367432</v>
@@ -5130,34 +5064,34 @@
         <v>47.5</v>
       </c>
       <c r="M59">
-        <v>131.2752860153809</v>
+        <v>127.9371654894457</v>
       </c>
       <c r="N59">
-        <v>0.89</v>
+        <v>0.98</v>
       </c>
       <c r="O59">
-        <v>0.98</v>
+        <v>1.16</v>
       </c>
       <c r="P59">
-        <v>1.16</v>
+        <v>0.7</v>
       </c>
       <c r="Q59">
-        <v>0.7</v>
+        <v>0.36</v>
       </c>
       <c r="R59">
-        <v>21107000</v>
+        <v>23201000</v>
       </c>
       <c r="S59">
-        <v>23201000</v>
+        <v>27570000</v>
       </c>
       <c r="T59">
-        <v>27570000</v>
+        <v>16589000</v>
       </c>
       <c r="U59">
-        <v>16589000</v>
+        <v>8642000</v>
       </c>
       <c r="V59" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -5165,67 +5099,67 @@
         <v>80</v>
       </c>
       <c r="B60" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C60" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D60" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="E60">
-        <v>3225.969970703125</v>
+        <v>69.76999664306641</v>
       </c>
       <c r="F60">
-        <v>335270</v>
+        <v>1435426.666666667</v>
       </c>
       <c r="G60">
-        <v>2768.298779296875</v>
+        <v>64.4713998413086</v>
       </c>
       <c r="H60">
-        <v>2599.471334635416</v>
+        <v>57.84126655578613</v>
       </c>
       <c r="I60">
-        <v>2436.522850952148</v>
+        <v>54.47364990234375</v>
       </c>
       <c r="J60">
-        <v>2310.925403442383</v>
+        <v>51.73309995651245</v>
       </c>
       <c r="K60">
-        <v>6.599999904632568</v>
+        <v>0.1557042300701141</v>
       </c>
       <c r="L60">
-        <v>3243.010009765625</v>
+        <v>79.82826232910156</v>
       </c>
       <c r="M60">
-        <v>130.875680939457</v>
+        <v>127.7870506305755</v>
       </c>
       <c r="N60">
-        <v>41.98</v>
+        <v>0.7</v>
       </c>
       <c r="O60">
-        <v>31.92</v>
+        <v>0.57</v>
       </c>
       <c r="P60">
-        <v>7</v>
+        <v>0.79</v>
       </c>
       <c r="Q60">
-        <v>34.89</v>
+        <v>0.92</v>
       </c>
       <c r="R60">
-        <v>1666000000</v>
+        <v>115400000</v>
       </c>
       <c r="S60">
-        <v>1235000000</v>
+        <v>95000000</v>
       </c>
       <c r="T60">
-        <v>266000000</v>
+        <v>129700000</v>
       </c>
       <c r="U60">
-        <v>1290000000</v>
+        <v>152900000</v>
       </c>
       <c r="V60" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="61" spans="1:22">
@@ -5233,67 +5167,67 @@
         <v>81</v>
       </c>
       <c r="B61" t="s">
+        <v>105</v>
+      </c>
+      <c r="C61" t="s">
         <v>117</v>
       </c>
-      <c r="C61" t="s">
-        <v>159</v>
-      </c>
       <c r="D61" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="E61">
-        <v>71.72000122070312</v>
+        <v>49.90999984741211</v>
       </c>
       <c r="F61">
-        <v>1439993.333333333</v>
+        <v>656293.3333333334</v>
       </c>
       <c r="G61">
-        <v>63.64360000610352</v>
+        <v>46.83460006713867</v>
       </c>
       <c r="H61">
-        <v>57.35073328653971</v>
+        <v>41.20239995320638</v>
       </c>
       <c r="I61">
-        <v>54.01249992370605</v>
+        <v>38.80014993667603</v>
       </c>
       <c r="J61">
-        <v>51.35089996337891</v>
+        <v>36.7322999382019</v>
       </c>
       <c r="K61">
-        <v>0.1557042300701141</v>
+        <v>0.02175931446254253</v>
       </c>
       <c r="L61">
-        <v>79.82826232910156</v>
+        <v>59.96058654785156</v>
       </c>
       <c r="M61">
-        <v>130.8335549968744</v>
+        <v>127.7241253795214</v>
       </c>
       <c r="N61">
-        <v>0.7</v>
+        <v>1.98</v>
       </c>
       <c r="O61">
-        <v>0.57</v>
+        <v>1.08</v>
       </c>
       <c r="P61">
-        <v>0.79</v>
+        <v>1.08</v>
       </c>
       <c r="Q61">
-        <v>0.92</v>
+        <v>1.24</v>
       </c>
       <c r="R61">
-        <v>115400000</v>
+        <v>144400000</v>
       </c>
       <c r="S61">
-        <v>95000000</v>
+        <v>79776000</v>
       </c>
       <c r="T61">
-        <v>129700000</v>
+        <v>80700000</v>
       </c>
       <c r="U61">
-        <v>152900000</v>
+        <v>93493000</v>
       </c>
       <c r="V61" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="62" spans="1:22">
@@ -5301,67 +5235,67 @@
         <v>82</v>
       </c>
       <c r="B62" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C62" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="D62" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E62">
-        <v>59.77999877929688</v>
+        <v>71.52999877929688</v>
       </c>
       <c r="F62">
-        <v>1514740</v>
+        <v>255323.3333333333</v>
       </c>
       <c r="G62">
-        <v>54.67240005493164</v>
+        <v>63.21380004882813</v>
       </c>
       <c r="H62">
-        <v>50.23466669718425</v>
+        <v>58.18286677042643</v>
       </c>
       <c r="I62">
-        <v>47.31055002212524</v>
+        <v>57.2014001083374</v>
       </c>
       <c r="J62">
-        <v>44.71335000991822</v>
+        <v>55.67100017547607</v>
       </c>
       <c r="K62">
-        <v>1.326302051544189</v>
+        <v>4.32618522644043</v>
       </c>
       <c r="L62">
-        <v>60.29999923706055</v>
+        <v>74.94632720947266</v>
       </c>
       <c r="M62">
-        <v>130.3101842471494</v>
+        <v>127.6061577399607</v>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>66.89</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>75.080879</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>57.68</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>84.206165</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>11128000000</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>12471000000</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>9601000000</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>14025000000</v>
       </c>
       <c r="V62" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="63" spans="1:22">
@@ -5369,67 +5303,67 @@
         <v>83</v>
       </c>
       <c r="B63" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C63" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="D63" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E63">
-        <v>57.58000183105469</v>
+        <v>34.79999923706055</v>
       </c>
       <c r="F63">
-        <v>3771426.666666667</v>
+        <v>3999536.666666667</v>
       </c>
       <c r="G63">
-        <v>51.73339973449707</v>
+        <v>31.90979999542236</v>
       </c>
       <c r="H63">
-        <v>45.06086654663086</v>
+        <v>28.41520001729329</v>
       </c>
       <c r="I63">
-        <v>43.96159990310669</v>
+        <v>27.09365000724792</v>
       </c>
       <c r="J63">
-        <v>42.0682999420166</v>
+        <v>26.23995001792908</v>
       </c>
       <c r="K63">
-        <v>11.99751472473145</v>
+        <v>1.243403434753418</v>
       </c>
       <c r="L63">
-        <v>60.77000045776367</v>
+        <v>44.90747833251953</v>
       </c>
       <c r="M63">
-        <v>130.1933490976917</v>
+        <v>127.3725443809172</v>
       </c>
       <c r="N63">
-        <v>0.68</v>
+        <v>0.21</v>
       </c>
       <c r="O63">
-        <v>0.33</v>
+        <v>-0.05</v>
       </c>
       <c r="P63">
-        <v>0.84</v>
+        <v>0.27</v>
       </c>
       <c r="Q63">
-        <v>0.79</v>
+        <v>0.03</v>
       </c>
       <c r="R63">
-        <v>511000000</v>
+        <v>-19530000</v>
       </c>
       <c r="S63">
-        <v>245000000</v>
+        <v>-15417000</v>
       </c>
       <c r="T63">
-        <v>614000000</v>
+        <v>118969000</v>
       </c>
       <c r="U63">
-        <v>583000000</v>
+        <v>13693000</v>
       </c>
       <c r="V63" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -5437,67 +5371,67 @@
         <v>84</v>
       </c>
       <c r="B64" t="s">
+        <v>106</v>
+      </c>
+      <c r="C64" t="s">
         <v>118</v>
       </c>
-      <c r="C64" t="s">
-        <v>127</v>
-      </c>
       <c r="D64" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E64">
-        <v>32.47000122070312</v>
+        <v>493.5</v>
       </c>
       <c r="F64">
-        <v>1035340</v>
+        <v>435466.6666666667</v>
       </c>
       <c r="G64">
-        <v>31.92340007781982</v>
+        <v>436.9094006347656</v>
       </c>
       <c r="H64">
-        <v>27.03586671193441</v>
+        <v>398.5611006673177</v>
       </c>
       <c r="I64">
-        <v>24.72665006160736</v>
+        <v>393.4876753234863</v>
       </c>
       <c r="J64">
-        <v>23.06045005321503</v>
+        <v>378.7003251647949</v>
       </c>
       <c r="K64">
-        <v>6.139999866485596</v>
+        <v>19.76499938964844</v>
       </c>
       <c r="L64">
-        <v>33.66999816894531</v>
+        <v>548.4299926757812</v>
       </c>
       <c r="M64">
-        <v>129.8881568220512</v>
+        <v>127.292972785944</v>
       </c>
       <c r="N64">
-        <v>1.45</v>
+        <v>-0.52</v>
       </c>
       <c r="O64">
-        <v>1.98</v>
+        <v>-4.26</v>
       </c>
       <c r="P64">
-        <v>0.73</v>
+        <v>-0.7</v>
       </c>
       <c r="Q64">
-        <v>0.6</v>
+        <v>-0.52</v>
       </c>
       <c r="R64">
-        <v>149226000</v>
+        <v>-235042000</v>
       </c>
       <c r="S64">
-        <v>202973000</v>
+        <v>-38613000</v>
       </c>
       <c r="T64">
-        <v>74742000</v>
+        <v>-28871000</v>
       </c>
       <c r="U64">
-        <v>60724000</v>
+        <v>-94368000</v>
       </c>
       <c r="V64" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -5505,67 +5439,67 @@
         <v>85</v>
       </c>
       <c r="B65" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="C65" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D65" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E65">
-        <v>189.1699981689453</v>
+        <v>71.27999877929688</v>
       </c>
       <c r="F65">
-        <v>1452200</v>
+        <v>610086.6666666666</v>
       </c>
       <c r="G65">
-        <v>159.8356002807617</v>
+        <v>70.96399978637696</v>
       </c>
       <c r="H65">
-        <v>153.9478668212891</v>
+        <v>60.14653325398763</v>
       </c>
       <c r="I65">
-        <v>145.5855501174927</v>
+        <v>57.75849990844726</v>
       </c>
       <c r="J65">
-        <v>139.6980000305176</v>
+        <v>54.60509992599487</v>
       </c>
       <c r="K65">
-        <v>-8.571051876060665E-05</v>
+        <v>23.54999923706055</v>
       </c>
       <c r="L65">
-        <v>189.1699981689453</v>
+        <v>76.5</v>
       </c>
       <c r="M65">
-        <v>129.5621745414584</v>
+        <v>127.0549911254336</v>
       </c>
       <c r="N65">
-        <v>8.779999999999999</v>
+        <v>-1.24</v>
       </c>
       <c r="O65">
-        <v>5.86</v>
+        <v>-0.68</v>
       </c>
       <c r="P65">
-        <v>6.34</v>
+        <v>-1.24</v>
       </c>
       <c r="Q65">
-        <v>8.779999999999999</v>
+        <v>-0.68</v>
       </c>
       <c r="R65">
-        <v>13318000000</v>
+        <v>-193228000</v>
       </c>
       <c r="S65">
-        <v>14405000000</v>
+        <v>-112101000</v>
       </c>
       <c r="T65">
-        <v>13592000000</v>
+        <v>-193228000</v>
       </c>
       <c r="U65">
-        <v>19814000000</v>
+        <v>-112101000</v>
       </c>
       <c r="V65" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -5573,67 +5507,67 @@
         <v>86</v>
       </c>
       <c r="B66" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C66" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="D66" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E66">
-        <v>696</v>
+        <v>29.29999923706055</v>
       </c>
       <c r="F66">
-        <v>1258723.333333333</v>
+        <v>437153.3333333333</v>
       </c>
       <c r="G66">
-        <v>640.7808020019531</v>
+        <v>26.57620006561279</v>
       </c>
       <c r="H66">
-        <v>549.9502665201823</v>
+        <v>24.13760004679362</v>
       </c>
       <c r="I66">
-        <v>521.2905494689942</v>
+        <v>23.32915004730225</v>
       </c>
       <c r="J66">
-        <v>490.62169921875</v>
+        <v>22.62730007171631</v>
       </c>
       <c r="K66">
-        <v>0.5958155393600464</v>
+        <v>4.409999847412109</v>
       </c>
       <c r="L66">
-        <v>729.8200073242188</v>
+        <v>35.56999969482422</v>
       </c>
       <c r="M66">
-        <v>129.507961092539</v>
+        <v>126.8589835319579</v>
       </c>
       <c r="N66">
-        <v>10.39</v>
+        <v>0.9</v>
       </c>
       <c r="O66">
-        <v>10.77</v>
+        <v>0.86</v>
       </c>
       <c r="P66">
-        <v>6.01</v>
+        <v>0.88</v>
       </c>
       <c r="Q66">
-        <v>5.97</v>
+        <v>0.95</v>
       </c>
       <c r="R66">
-        <v>1425879000</v>
+        <v>76838000</v>
       </c>
       <c r="S66">
-        <v>1468507000</v>
+        <v>72940000</v>
       </c>
       <c r="T66">
-        <v>814008000</v>
+        <v>74458000</v>
       </c>
       <c r="U66">
-        <v>802537000</v>
+        <v>80284000</v>
       </c>
       <c r="V66" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -5641,67 +5575,67 @@
         <v>87</v>
       </c>
       <c r="B67" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C67" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D67" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="E67">
-        <v>139.9400024414062</v>
+        <v>57.43000030517578</v>
       </c>
       <c r="F67">
-        <v>57009920</v>
+        <v>645213.3333333334</v>
       </c>
       <c r="G67">
-        <v>128.864800567627</v>
+        <v>52.42139984130859</v>
       </c>
       <c r="H67">
-        <v>109.9811336263021</v>
+        <v>46.87633328755697</v>
       </c>
       <c r="I67">
-        <v>106.1211002349853</v>
+        <v>45.64379999160766</v>
       </c>
       <c r="J67">
-        <v>104.3732000732422</v>
+        <v>44.18715000152588</v>
       </c>
       <c r="K67">
-        <v>0.0697920024394989</v>
+        <v>5.159999847412109</v>
       </c>
       <c r="L67">
-        <v>186.5704956054688</v>
+        <v>59.47999954223633</v>
       </c>
       <c r="M67">
-        <v>129.4651771430167</v>
+        <v>126.6382257651476</v>
       </c>
       <c r="N67">
-        <v>0.28</v>
+        <v>1.55</v>
       </c>
       <c r="O67">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="P67">
-        <v>0.31</v>
+        <v>0.52</v>
       </c>
       <c r="Q67">
-        <v>0.65</v>
+        <v>2.07</v>
       </c>
       <c r="R67">
-        <v>2872000000</v>
+        <v>113000000</v>
       </c>
       <c r="S67">
-        <v>278000000</v>
+        <v>1000000</v>
       </c>
       <c r="T67">
-        <v>3172000000</v>
+        <v>37000000</v>
       </c>
       <c r="U67">
-        <v>6750000000</v>
+        <v>142000000</v>
       </c>
       <c r="V67" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -5709,67 +5643,67 @@
         <v>88</v>
       </c>
       <c r="B68" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C68" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D68" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="E68">
-        <v>57.38999938964844</v>
+        <v>488.2000122070312</v>
       </c>
       <c r="F68">
-        <v>5234083.333333333</v>
+        <v>780466.6666666666</v>
       </c>
       <c r="G68">
-        <v>50.49900009155274</v>
+        <v>433.7717999267578</v>
       </c>
       <c r="H68">
-        <v>46.16986671447754</v>
+        <v>408.1915329996745</v>
       </c>
       <c r="I68">
-        <v>45.06964998245239</v>
+        <v>392.2594500732422</v>
       </c>
       <c r="J68">
-        <v>43.06335000991821</v>
+        <v>374.1338500976562</v>
       </c>
       <c r="K68">
-        <v>11.31525421142578</v>
+        <v>3.029999971389771</v>
       </c>
       <c r="L68">
-        <v>59.79999923706055</v>
+        <v>488.2000122070312</v>
       </c>
       <c r="M68">
-        <v>129.3462862966608</v>
+        <v>126.5103662728782</v>
       </c>
       <c r="N68">
-        <v>1.53</v>
+        <v>8.66</v>
       </c>
       <c r="O68">
-        <v>0.32</v>
+        <v>9.15</v>
       </c>
       <c r="P68">
-        <v>0.44</v>
+        <v>6.47</v>
       </c>
       <c r="Q68">
-        <v>0.23</v>
+        <v>8.58</v>
       </c>
       <c r="R68">
-        <v>1312000000</v>
+        <v>606000000</v>
       </c>
       <c r="S68">
-        <v>270000000</v>
+        <v>639000000</v>
       </c>
       <c r="T68">
-        <v>373000000</v>
+        <v>451000000</v>
       </c>
       <c r="U68">
-        <v>199000000</v>
+        <v>591000000</v>
       </c>
       <c r="V68" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="69" spans="1:22">
@@ -5777,67 +5711,67 @@
         <v>89</v>
       </c>
       <c r="B69" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C69" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="D69" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="E69">
-        <v>108.3099975585938</v>
+        <v>108.2200012207031</v>
       </c>
       <c r="F69">
-        <v>1012466.666666667</v>
+        <v>436423.3333333333</v>
       </c>
       <c r="G69">
-        <v>104.9469995117187</v>
+        <v>99.54179992675782</v>
       </c>
       <c r="H69">
-        <v>88.85879989624023</v>
+        <v>93.46513326009115</v>
       </c>
       <c r="I69">
-        <v>83.5732998085022</v>
+        <v>89.32974994659423</v>
       </c>
       <c r="J69">
-        <v>78.39279985427856</v>
+        <v>85.73799995422364</v>
       </c>
       <c r="K69">
-        <v>0.3787146806716919</v>
+        <v>3.099249601364136</v>
       </c>
       <c r="L69">
-        <v>115.1399993896484</v>
+        <v>121.8199996948242</v>
       </c>
       <c r="M69">
-        <v>129.3410642721542</v>
+        <v>126.3763339426322</v>
       </c>
       <c r="N69">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="O69">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="P69">
-        <v>1.52</v>
+        <v>2.84</v>
       </c>
       <c r="Q69">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="R69">
-        <v>315000000</v>
+        <v>88842000</v>
       </c>
       <c r="S69">
-        <v>223000000</v>
+        <v>37337000</v>
       </c>
       <c r="T69">
-        <v>207000000</v>
+        <v>71283000</v>
       </c>
       <c r="U69">
-        <v>233000000</v>
+        <v>40443000</v>
       </c>
       <c r="V69" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -5845,67 +5779,67 @@
         <v>90</v>
       </c>
       <c r="B70" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C70" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="D70" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="E70">
-        <v>425.1199951171875</v>
+        <v>28.02000045776367</v>
       </c>
       <c r="F70">
-        <v>744006.6666666666</v>
+        <v>687193.3333333334</v>
       </c>
       <c r="G70">
-        <v>381.5554022216797</v>
+        <v>26.88580005645752</v>
       </c>
       <c r="H70">
-        <v>346.3016007486979</v>
+        <v>23.547799949646</v>
       </c>
       <c r="I70">
-        <v>333.0744006347657</v>
+        <v>22.23749996185303</v>
       </c>
       <c r="J70">
-        <v>317.908500289917</v>
+        <v>20.8303999710083</v>
       </c>
       <c r="K70">
-        <v>1.31995165348053</v>
+        <v>9.090000152587891</v>
       </c>
       <c r="L70">
-        <v>425.1199951171875</v>
+        <v>29.15999984741211</v>
       </c>
       <c r="M70">
-        <v>128.8851268634323</v>
+        <v>126.301647300819</v>
       </c>
       <c r="N70">
-        <v>2.98</v>
+        <v>0.06</v>
       </c>
       <c r="O70">
-        <v>3.04</v>
+        <v>0.04</v>
       </c>
       <c r="P70">
-        <v>4.54</v>
+        <v>0.05</v>
       </c>
       <c r="Q70">
-        <v>5.44</v>
+        <v>0.12</v>
       </c>
       <c r="R70">
-        <v>387854000</v>
+        <v>28000000</v>
       </c>
       <c r="S70">
-        <v>395237000</v>
+        <v>22000000</v>
       </c>
       <c r="T70">
-        <v>590889000</v>
+        <v>26000000</v>
       </c>
       <c r="U70">
-        <v>708956000</v>
+        <v>48000000</v>
       </c>
       <c r="V70" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -5913,67 +5847,67 @@
         <v>91</v>
       </c>
       <c r="B71" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C71" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="D71" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E71">
-        <v>55.20000076293945</v>
+        <v>174.7299957275391</v>
       </c>
       <c r="F71">
-        <v>1526166.666666667</v>
+        <v>377573.3333333333</v>
       </c>
       <c r="G71">
-        <v>50.52380012512207</v>
+        <v>162.8563998413086</v>
       </c>
       <c r="H71">
-        <v>44.99580004374186</v>
+        <v>144.449066212972</v>
       </c>
       <c r="I71">
-        <v>43.24800004959106</v>
+        <v>137.522399559021</v>
       </c>
       <c r="J71">
-        <v>41.09634999275207</v>
+        <v>132.1643995666504</v>
       </c>
       <c r="K71">
-        <v>11.8095235824585</v>
+        <v>0.5625</v>
       </c>
       <c r="L71">
-        <v>56.15000152587891</v>
+        <v>174.7299957275391</v>
       </c>
       <c r="M71">
-        <v>128.5758769746884</v>
+        <v>126.2005892570191</v>
       </c>
       <c r="N71">
-        <v>0.55</v>
+        <v>2.5</v>
       </c>
       <c r="O71">
-        <v>0.9399999999999999</v>
+        <v>1.52</v>
       </c>
       <c r="P71">
-        <v>0.5600000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="Q71">
-        <v>0.67</v>
+        <v>2.13</v>
       </c>
       <c r="R71">
-        <v>93400000</v>
+        <v>135799000</v>
       </c>
       <c r="S71">
-        <v>158700000</v>
+        <v>82474000</v>
       </c>
       <c r="T71">
-        <v>93800000</v>
+        <v>72401000</v>
       </c>
       <c r="U71">
-        <v>112900000</v>
+        <v>115766000</v>
       </c>
       <c r="V71" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -5981,67 +5915,67 @@
         <v>92</v>
       </c>
       <c r="B72" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C72" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="D72" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="E72">
-        <v>75.19999694824219</v>
+        <v>108.3499984741211</v>
       </c>
       <c r="F72">
-        <v>316386.6666666667</v>
+        <v>661436.6666666666</v>
       </c>
       <c r="G72">
-        <v>69.77279960632325</v>
+        <v>101.677799987793</v>
       </c>
       <c r="H72">
-        <v>61.45339991251628</v>
+        <v>90.09299987792969</v>
       </c>
       <c r="I72">
-        <v>58.39519996643067</v>
+        <v>86.04994998931885</v>
       </c>
       <c r="J72">
-        <v>55.28369998931885</v>
+        <v>84.36800003051758</v>
       </c>
       <c r="K72">
-        <v>10.73999977111816</v>
+        <v>0.8541669845581055</v>
       </c>
       <c r="L72">
-        <v>76.09999847412109</v>
+        <v>133.7799987792969</v>
       </c>
       <c r="M72">
-        <v>128.5525964359129</v>
+        <v>126.1581889062703</v>
       </c>
       <c r="N72">
-        <v>2.07</v>
+        <v>1.13</v>
       </c>
       <c r="O72">
-        <v>2.41</v>
+        <v>0.74</v>
       </c>
       <c r="P72">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="Q72">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="R72">
-        <v>89470000</v>
+        <v>105366000</v>
       </c>
       <c r="S72">
-        <v>103153000</v>
+        <v>68103000</v>
       </c>
       <c r="T72">
-        <v>64775000</v>
+        <v>115547000</v>
       </c>
       <c r="U72">
-        <v>75593000</v>
+        <v>178691000</v>
       </c>
       <c r="V72" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -6049,67 +5983,67 @@
         <v>93</v>
       </c>
       <c r="B73" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C73" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="D73" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="E73">
-        <v>28.44000053405762</v>
+        <v>266.8900146484375</v>
       </c>
       <c r="F73">
-        <v>718096.6666666666</v>
+        <v>308690</v>
       </c>
       <c r="G73">
-        <v>26.57020004272461</v>
+        <v>238.1524005126953</v>
       </c>
       <c r="H73">
-        <v>23.35806662241618</v>
+        <v>215.551133219401</v>
       </c>
       <c r="I73">
-        <v>22.04144996166229</v>
+        <v>214.9397998046875</v>
       </c>
       <c r="J73">
-        <v>20.61684997558594</v>
+        <v>205.2881997680664</v>
       </c>
       <c r="K73">
-        <v>9.090000152587891</v>
+        <v>22.18000030517578</v>
       </c>
       <c r="L73">
-        <v>29.15999984741211</v>
+        <v>267.6499938964844</v>
       </c>
       <c r="M73">
-        <v>128.4947166298838</v>
+        <v>125.9646078006813</v>
       </c>
       <c r="N73">
-        <v>0.06</v>
+        <v>2.05</v>
       </c>
       <c r="O73">
-        <v>0.04</v>
+        <v>2.12</v>
       </c>
       <c r="P73">
-        <v>0.05</v>
+        <v>2.27</v>
       </c>
       <c r="Q73">
-        <v>0.12</v>
+        <v>1.93</v>
       </c>
       <c r="R73">
-        <v>28000000</v>
+        <v>66027000</v>
       </c>
       <c r="S73">
-        <v>22000000</v>
+        <v>68670000</v>
       </c>
       <c r="T73">
-        <v>26000000</v>
+        <v>72894000</v>
       </c>
       <c r="U73">
-        <v>48000000</v>
+        <v>61068000</v>
       </c>
       <c r="V73" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -6117,67 +6051,67 @@
         <v>94</v>
       </c>
       <c r="B74" t="s">
+        <v>105</v>
+      </c>
+      <c r="C74" t="s">
         <v>117</v>
       </c>
-      <c r="C74" t="s">
-        <v>159</v>
-      </c>
       <c r="D74" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="E74">
-        <v>220.1999969482422</v>
+        <v>48.04999923706055</v>
       </c>
       <c r="F74">
-        <v>2104996.666666667</v>
+        <v>918153.3333333334</v>
       </c>
       <c r="G74">
-        <v>199.2880004882813</v>
+        <v>48.00459991455078</v>
       </c>
       <c r="H74">
-        <v>177.4793339029948</v>
+        <v>41.14193331400553</v>
       </c>
       <c r="I74">
-        <v>172.3828505706787</v>
+        <v>38.0915500164032</v>
       </c>
       <c r="J74">
-        <v>165.1082005310058</v>
+        <v>35.68215003013611</v>
       </c>
       <c r="K74">
-        <v>0.004536735825240612</v>
+        <v>7.050000190734863</v>
       </c>
       <c r="L74">
-        <v>221.0899963378906</v>
+        <v>51.63999938964844</v>
       </c>
       <c r="M74">
-        <v>128.3989458739862</v>
+        <v>125.7526541370251</v>
       </c>
       <c r="N74">
-        <v>1.52</v>
+        <v>2.72</v>
       </c>
       <c r="O74">
-        <v>1.8</v>
+        <v>2.51</v>
       </c>
       <c r="P74">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="Q74">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="R74">
-        <v>607000000</v>
+        <v>309779000</v>
       </c>
       <c r="S74">
-        <v>721000000</v>
+        <v>275331000</v>
       </c>
       <c r="T74">
-        <v>638000000</v>
+        <v>191051000</v>
       </c>
       <c r="U74">
-        <v>744000000</v>
+        <v>234602000</v>
       </c>
       <c r="V74" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -6185,67 +6119,67 @@
         <v>95</v>
       </c>
       <c r="B75" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C75" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D75" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="E75">
-        <v>49.11000061035156</v>
+        <v>58.09999847412109</v>
       </c>
       <c r="F75">
-        <v>989426.6666666666</v>
+        <v>1410860</v>
       </c>
       <c r="G75">
-        <v>47.70439994812012</v>
+        <v>55.28260002136231</v>
       </c>
       <c r="H75">
-        <v>40.81919999440511</v>
+        <v>50.56140004475912</v>
       </c>
       <c r="I75">
-        <v>37.73965003013611</v>
+        <v>47.67705001831055</v>
       </c>
       <c r="J75">
-        <v>35.26940002441406</v>
+        <v>45.07990002632141</v>
       </c>
       <c r="K75">
-        <v>7.050000190734863</v>
+        <v>1.326302051544189</v>
       </c>
       <c r="L75">
-        <v>51.63999938964844</v>
+        <v>60.29999923706055</v>
       </c>
       <c r="M75">
-        <v>127.7669202303683</v>
+        <v>125.7326378419124</v>
       </c>
       <c r="N75">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O75">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="P75">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q75">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="R75">
-        <v>309779000</v>
+        <v>0</v>
       </c>
       <c r="S75">
-        <v>275331000</v>
+        <v>0</v>
       </c>
       <c r="T75">
-        <v>191051000</v>
+        <v>0</v>
       </c>
       <c r="U75">
-        <v>234602000</v>
+        <v>0</v>
       </c>
       <c r="V75" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -6253,31 +6187,31 @@
         <v>96</v>
       </c>
       <c r="B76" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C76" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D76" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="E76">
-        <v>268.260009765625</v>
+        <v>265.7699890136719</v>
       </c>
       <c r="F76">
-        <v>2000650</v>
+        <v>1802413.333333333</v>
       </c>
       <c r="G76">
-        <v>245.8211996459961</v>
+        <v>248.4113998413086</v>
       </c>
       <c r="H76">
-        <v>223.6178667195638</v>
+        <v>225.3364000447591</v>
       </c>
       <c r="I76">
-        <v>209.9869501495361</v>
+        <v>211.6852001953125</v>
       </c>
       <c r="J76">
-        <v>198.9669500732422</v>
+        <v>200.6207000732422</v>
       </c>
       <c r="K76">
         <v>0.8275843262672424</v>
@@ -6286,7 +6220,7 @@
         <v>312.9627685546875</v>
       </c>
       <c r="M76">
-        <v>127.0991331832926</v>
+        <v>125.6324980204941</v>
       </c>
       <c r="N76">
         <v>3.33</v>
@@ -6313,7 +6247,7 @@
         <v>1538000000</v>
       </c>
       <c r="V76" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="77" spans="1:22">
@@ -6321,67 +6255,67 @@
         <v>97</v>
       </c>
       <c r="B77" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C77" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D77" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="E77">
-        <v>53</v>
+        <v>30.13999938964844</v>
       </c>
       <c r="F77">
-        <v>989476.6666666666</v>
+        <v>2940276.666666667</v>
       </c>
       <c r="G77">
-        <v>48.57159980773926</v>
+        <v>26.67139995574951</v>
       </c>
       <c r="H77">
-        <v>43.43153330485026</v>
+        <v>24.59960000356038</v>
       </c>
       <c r="I77">
-        <v>42.68644998550415</v>
+        <v>24.3180500125885</v>
       </c>
       <c r="J77">
-        <v>41.19375003814697</v>
+        <v>23.68060000419617</v>
       </c>
       <c r="K77">
-        <v>2.721946477890015</v>
+        <v>10.74393081665039</v>
       </c>
       <c r="L77">
-        <v>53.91999816894531</v>
+        <v>30.69000053405762</v>
       </c>
       <c r="M77">
-        <v>127.0379439859438</v>
+        <v>125.4540464617075</v>
       </c>
       <c r="N77">
-        <v>3.41</v>
+        <v>-3.27</v>
       </c>
       <c r="O77">
-        <v>0.25</v>
+        <v>1.51</v>
       </c>
       <c r="P77">
-        <v>-2</v>
+        <v>1.71</v>
       </c>
       <c r="Q77">
-        <v>4.36</v>
+        <v>1.17</v>
       </c>
       <c r="R77">
-        <v>312600000</v>
+        <v>668000000</v>
       </c>
       <c r="S77">
-        <v>32572000</v>
+        <v>-246000000</v>
       </c>
       <c r="T77">
-        <v>-155994000</v>
+        <v>699000000</v>
       </c>
       <c r="U77">
-        <v>355363000</v>
+        <v>476000000</v>
       </c>
       <c r="V77" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -6389,67 +6323,67 @@
         <v>98</v>
       </c>
       <c r="B78" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C78" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D78" t="s">
-        <v>243</v>
+        <v>188</v>
       </c>
       <c r="E78">
-        <v>110.0500030517578</v>
+        <v>416.510009765625</v>
       </c>
       <c r="F78">
-        <v>453360</v>
+        <v>749463.3333333334</v>
       </c>
       <c r="G78">
-        <v>98.12099990844726</v>
+        <v>386.9146026611328</v>
       </c>
       <c r="H78">
-        <v>92.66893320719402</v>
+        <v>348.7334674072266</v>
       </c>
       <c r="I78">
-        <v>88.79639995574951</v>
+        <v>335.3001007080078</v>
       </c>
       <c r="J78">
-        <v>85.35319995880127</v>
+        <v>320.1931004333496</v>
       </c>
       <c r="K78">
-        <v>3.099249601364136</v>
+        <v>1.31995165348053</v>
       </c>
       <c r="L78">
-        <v>121.8199996948242</v>
+        <v>425.1199951171875</v>
       </c>
       <c r="M78">
-        <v>126.9739429973167</v>
+        <v>125.2044676154203</v>
       </c>
       <c r="N78">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="O78">
-        <v>1.48</v>
+        <v>3.04</v>
       </c>
       <c r="P78">
-        <v>2.84</v>
+        <v>4.54</v>
       </c>
       <c r="Q78">
-        <v>1.64</v>
+        <v>5.44</v>
       </c>
       <c r="R78">
-        <v>88842000</v>
+        <v>387854000</v>
       </c>
       <c r="S78">
-        <v>37337000</v>
+        <v>395237000</v>
       </c>
       <c r="T78">
-        <v>71283000</v>
+        <v>590889000</v>
       </c>
       <c r="U78">
-        <v>40443000</v>
+        <v>708956000</v>
       </c>
       <c r="V78" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -6457,67 +6391,67 @@
         <v>99</v>
       </c>
       <c r="B79" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C79" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="D79" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="E79">
-        <v>110.7900009155273</v>
+        <v>173.6100006103516</v>
       </c>
       <c r="F79">
-        <v>681433.3333333334</v>
+        <v>501676.6666666667</v>
       </c>
       <c r="G79">
-        <v>100.7503999328613</v>
+        <v>163.5755999755859</v>
       </c>
       <c r="H79">
-        <v>89.45133321126302</v>
+        <v>145.5776003011068</v>
       </c>
       <c r="I79">
-        <v>85.78439998626709</v>
+        <v>138.7782502365112</v>
       </c>
       <c r="J79">
-        <v>84.10275001525879</v>
+        <v>131.9672502136231</v>
       </c>
       <c r="K79">
-        <v>0.8541669845581055</v>
+        <v>2.075098752975464</v>
       </c>
       <c r="L79">
-        <v>133.7799987792969</v>
+        <v>179.6499938964844</v>
       </c>
       <c r="M79">
-        <v>126.9644429324393</v>
+        <v>124.9229016502065</v>
       </c>
       <c r="N79">
-        <v>1.13</v>
+        <v>4.61</v>
       </c>
       <c r="O79">
-        <v>0.74</v>
+        <v>4.21</v>
       </c>
       <c r="P79">
-        <v>1.25</v>
+        <v>4.31</v>
       </c>
       <c r="Q79">
-        <v>1.91</v>
+        <v>4.41</v>
       </c>
       <c r="R79">
-        <v>105366000</v>
+        <v>340100000</v>
       </c>
       <c r="S79">
-        <v>68103000</v>
+        <v>298000000</v>
       </c>
       <c r="T79">
-        <v>115547000</v>
+        <v>298300000</v>
       </c>
       <c r="U79">
-        <v>178691000</v>
+        <v>300800000</v>
       </c>
       <c r="V79" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -6525,67 +6459,67 @@
         <v>100</v>
       </c>
       <c r="B80" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C80" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="D80" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E80">
-        <v>39.52000045776367</v>
+        <v>55.54000091552734</v>
       </c>
       <c r="F80">
-        <v>754643.3333333334</v>
+        <v>5208796.666666667</v>
       </c>
       <c r="G80">
-        <v>35.68639999389649</v>
+        <v>51.37020011901856</v>
       </c>
       <c r="H80">
-        <v>31.69933340708415</v>
+        <v>46.44940007527669</v>
       </c>
       <c r="I80">
-        <v>30.86958533287048</v>
+        <v>45.37965000152588</v>
       </c>
       <c r="J80">
-        <v>29.58462300300598</v>
+        <v>43.32579999923706</v>
       </c>
       <c r="K80">
-        <v>8.338250160217285</v>
+        <v>11.31525421142578</v>
       </c>
       <c r="L80">
-        <v>40.52114105224609</v>
+        <v>59.79999923706055</v>
       </c>
       <c r="M80">
-        <v>126.5707330014932</v>
+        <v>124.7971295256411</v>
       </c>
       <c r="N80">
-        <v>0.717797</v>
+        <v>1.53</v>
       </c>
       <c r="O80">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="P80">
-        <v>-0.26</v>
+        <v>0.44</v>
       </c>
       <c r="Q80">
-        <v>0.7</v>
+        <v>0.23</v>
       </c>
       <c r="R80">
-        <v>86489000</v>
+        <v>1312000000</v>
       </c>
       <c r="S80">
-        <v>29835000</v>
+        <v>270000000</v>
       </c>
       <c r="T80">
-        <v>-30804000</v>
+        <v>373000000</v>
       </c>
       <c r="U80">
-        <v>83637000</v>
+        <v>199000000</v>
       </c>
       <c r="V80" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -6593,67 +6527,67 @@
         <v>101</v>
       </c>
       <c r="B81" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="C81" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="D81" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="E81">
-        <v>189.5200042724609</v>
+        <v>59.02999877929688</v>
       </c>
       <c r="F81">
-        <v>316470</v>
+        <v>624663.3333333334</v>
       </c>
       <c r="G81">
-        <v>179.3099996948242</v>
+        <v>56.2389998626709</v>
       </c>
       <c r="H81">
-        <v>156.8586662801107</v>
+        <v>49.33726666768392</v>
       </c>
       <c r="I81">
-        <v>150.0432495498657</v>
+        <v>47.67714992523193</v>
       </c>
       <c r="J81">
-        <v>142.300199584961</v>
+        <v>45.38119995117187</v>
       </c>
       <c r="K81">
-        <v>2.138945579528809</v>
+        <v>13.7691478729248</v>
       </c>
       <c r="L81">
-        <v>192.9400024414062</v>
+        <v>59.68000030517578</v>
       </c>
       <c r="M81">
-        <v>126.4652698265689</v>
+        <v>124.4859210501041</v>
       </c>
       <c r="N81">
-        <v>3.72</v>
+        <v>1.45</v>
       </c>
       <c r="O81">
-        <v>3.2</v>
+        <v>1.52</v>
       </c>
       <c r="P81">
-        <v>2.79</v>
+        <v>1.85</v>
       </c>
       <c r="Q81">
-        <v>3.4</v>
+        <v>1.92</v>
       </c>
       <c r="R81">
-        <v>138995000</v>
+        <v>139000000</v>
       </c>
       <c r="S81">
-        <v>117184000</v>
+        <v>141000000</v>
       </c>
       <c r="T81">
-        <v>100356000</v>
+        <v>170000000</v>
       </c>
       <c r="U81">
-        <v>120849000</v>
+        <v>175000000</v>
       </c>
       <c r="V81" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -6661,883 +6595,67 @@
         <v>102</v>
       </c>
       <c r="B82" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C82" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="D82" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="E82">
-        <v>409.1000061035156</v>
+        <v>105.9400024414062</v>
       </c>
       <c r="F82">
-        <v>964433.3333333334</v>
+        <v>305673.3333333333</v>
       </c>
       <c r="G82">
-        <v>361.878599243164</v>
+        <v>98.14280014038086</v>
       </c>
       <c r="H82">
-        <v>340.5599997965495</v>
+        <v>87.69133356730143</v>
       </c>
       <c r="I82">
-        <v>327.5111996459961</v>
+        <v>82.71200021743775</v>
       </c>
       <c r="J82">
-        <v>313.5499498748779</v>
+        <v>79.83680017471313</v>
       </c>
       <c r="K82">
-        <v>0.6462651491165161</v>
+        <v>12.27999973297119</v>
       </c>
       <c r="L82">
-        <v>427.5899963378906</v>
+        <v>108.4400024414062</v>
       </c>
       <c r="M82">
-        <v>126.2409187568156</v>
+        <v>124.2317786739443</v>
       </c>
       <c r="N82">
-        <v>3.36</v>
+        <v>1.22</v>
       </c>
       <c r="O82">
-        <v>2.92</v>
+        <v>0.78</v>
       </c>
       <c r="P82">
-        <v>2.58</v>
+        <v>2.17</v>
       </c>
       <c r="Q82">
-        <v>2.65</v>
+        <v>1.38</v>
       </c>
       <c r="R82">
-        <v>377401000</v>
+        <v>77000000</v>
       </c>
       <c r="S82">
-        <v>323929000</v>
+        <v>49000000</v>
       </c>
       <c r="T82">
-        <v>285038000</v>
+        <v>131000000</v>
       </c>
       <c r="U82">
-        <v>292362000</v>
+        <v>83000000</v>
       </c>
       <c r="V82" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="83" spans="1:22">
-      <c r="A83" t="s">
-        <v>103</v>
-      </c>
-      <c r="B83" t="s">
-        <v>117</v>
-      </c>
-      <c r="C83" t="s">
-        <v>165</v>
-      </c>
-      <c r="D83" t="s">
-        <v>248</v>
-      </c>
-      <c r="E83">
-        <v>105.2600021362305</v>
-      </c>
-      <c r="F83">
-        <v>302803.3333333333</v>
-      </c>
-      <c r="G83">
-        <v>97.16740005493165</v>
-      </c>
-      <c r="H83">
-        <v>86.98053354899089</v>
-      </c>
-      <c r="I83">
-        <v>82.23810022354127</v>
-      </c>
-      <c r="J83">
-        <v>79.53270017623902</v>
-      </c>
-      <c r="K83">
-        <v>12.27999973297119</v>
-      </c>
-      <c r="L83">
-        <v>108.4400024414062</v>
-      </c>
-      <c r="M83">
-        <v>126.2051213363564</v>
-      </c>
-      <c r="N83">
-        <v>1.22</v>
-      </c>
-      <c r="O83">
-        <v>0.78</v>
-      </c>
-      <c r="P83">
-        <v>2.17</v>
-      </c>
-      <c r="Q83">
-        <v>1.38</v>
-      </c>
-      <c r="R83">
-        <v>77000000</v>
-      </c>
-      <c r="S83">
-        <v>49000000</v>
-      </c>
-      <c r="T83">
-        <v>131000000</v>
-      </c>
-      <c r="U83">
-        <v>83000000</v>
-      </c>
-      <c r="V83" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="84" spans="1:22">
-      <c r="A84" t="s">
-        <v>104</v>
-      </c>
-      <c r="B84" t="s">
-        <v>118</v>
-      </c>
-      <c r="C84" t="s">
-        <v>127</v>
-      </c>
-      <c r="D84" t="s">
-        <v>249</v>
-      </c>
-      <c r="E84">
-        <v>127.5299987792969</v>
-      </c>
-      <c r="F84">
-        <v>3120883.333333333</v>
-      </c>
-      <c r="G84">
-        <v>120.5093994140625</v>
-      </c>
-      <c r="H84">
-        <v>106.3039998881022</v>
-      </c>
-      <c r="I84">
-        <v>100.3326497650147</v>
-      </c>
-      <c r="J84">
-        <v>94.67129981994628</v>
-      </c>
-      <c r="K84">
-        <v>0.7500790357589722</v>
-      </c>
-      <c r="L84">
-        <v>131</v>
-      </c>
-      <c r="M84">
-        <v>126.1462210850073</v>
-      </c>
-      <c r="N84">
-        <v>4.67</v>
-      </c>
-      <c r="O84">
-        <v>2.76</v>
-      </c>
-      <c r="P84">
-        <v>2.73</v>
-      </c>
-      <c r="Q84">
-        <v>3.9</v>
-      </c>
-      <c r="R84">
-        <v>1631900000</v>
-      </c>
-      <c r="S84">
-        <v>958700000</v>
-      </c>
-      <c r="T84">
-        <v>942200000</v>
-      </c>
-      <c r="U84">
-        <v>1335100000</v>
-      </c>
-      <c r="V84" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="85" spans="1:22">
-      <c r="A85" t="s">
-        <v>105</v>
-      </c>
-      <c r="B85" t="s">
-        <v>119</v>
-      </c>
-      <c r="C85" t="s">
-        <v>129</v>
-      </c>
-      <c r="D85" t="s">
-        <v>250</v>
-      </c>
-      <c r="E85">
-        <v>487.8900146484375</v>
-      </c>
-      <c r="F85">
-        <v>427803.3333333333</v>
-      </c>
-      <c r="G85">
-        <v>430.6778002929688</v>
-      </c>
-      <c r="H85">
-        <v>396.0918339029948</v>
-      </c>
-      <c r="I85">
-        <v>391.6183253479004</v>
-      </c>
-      <c r="J85">
-        <v>378.3193751525879</v>
-      </c>
-      <c r="K85">
-        <v>19.76499938964844</v>
-      </c>
-      <c r="L85">
-        <v>548.4299926757812</v>
-      </c>
-      <c r="M85">
-        <v>126.0959969014464</v>
-      </c>
-      <c r="N85">
-        <v>-0.52</v>
-      </c>
-      <c r="O85">
-        <v>-4.26</v>
-      </c>
-      <c r="P85">
-        <v>-0.7</v>
-      </c>
-      <c r="Q85">
-        <v>-0.52</v>
-      </c>
-      <c r="R85">
-        <v>-235042000</v>
-      </c>
-      <c r="S85">
-        <v>-38613000</v>
-      </c>
-      <c r="T85">
-        <v>-28871000</v>
-      </c>
-      <c r="U85">
-        <v>-94368000</v>
-      </c>
-      <c r="V85" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="86" spans="1:22">
-      <c r="A86" t="s">
-        <v>106</v>
-      </c>
-      <c r="B86" t="s">
-        <v>117</v>
-      </c>
-      <c r="C86" t="s">
-        <v>166</v>
-      </c>
-      <c r="D86" t="s">
-        <v>251</v>
-      </c>
-      <c r="E86">
-        <v>58.68000030517578</v>
-      </c>
-      <c r="F86">
-        <v>332193.3333333333</v>
-      </c>
-      <c r="G86">
-        <v>54.24320022583008</v>
-      </c>
-      <c r="H86">
-        <v>48.98246673583984</v>
-      </c>
-      <c r="I86">
-        <v>46.4926501083374</v>
-      </c>
-      <c r="J86">
-        <v>44.10395004272461</v>
-      </c>
-      <c r="K86">
-        <v>0.07982486486434937</v>
-      </c>
-      <c r="L86">
-        <v>60.29000091552734</v>
-      </c>
-      <c r="M86">
-        <v>125.4720128070037</v>
-      </c>
-      <c r="N86">
-        <v>-0.14</v>
-      </c>
-      <c r="O86">
-        <v>0.13</v>
-      </c>
-      <c r="P86">
-        <v>0.38</v>
-      </c>
-      <c r="Q86">
-        <v>0.78</v>
-      </c>
-      <c r="R86">
-        <v>-6900000</v>
-      </c>
-      <c r="S86">
-        <v>6200000</v>
-      </c>
-      <c r="T86">
-        <v>18600000</v>
-      </c>
-      <c r="U86">
-        <v>38400000</v>
-      </c>
-      <c r="V86" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="87" spans="1:22">
-      <c r="A87" t="s">
-        <v>107</v>
-      </c>
-      <c r="B87" t="s">
-        <v>118</v>
-      </c>
-      <c r="C87" t="s">
-        <v>167</v>
-      </c>
-      <c r="D87" t="s">
-        <v>252</v>
-      </c>
-      <c r="E87">
-        <v>36.95000076293945</v>
-      </c>
-      <c r="F87">
-        <v>1113593.333333333</v>
-      </c>
-      <c r="G87">
-        <v>33.64479999542236</v>
-      </c>
-      <c r="H87">
-        <v>29.26586667378744</v>
-      </c>
-      <c r="I87">
-        <v>28.36335003852844</v>
-      </c>
-      <c r="J87">
-        <v>26.97315003395081</v>
-      </c>
-      <c r="K87">
-        <v>0.8671879768371582</v>
-      </c>
-      <c r="L87">
-        <v>48.7400016784668</v>
-      </c>
-      <c r="M87">
-        <v>125.4506226960056</v>
-      </c>
-      <c r="N87">
-        <v>0.64</v>
-      </c>
-      <c r="O87">
-        <v>0.4</v>
-      </c>
-      <c r="P87">
-        <v>0.34</v>
-      </c>
-      <c r="Q87">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="R87">
-        <v>59473000</v>
-      </c>
-      <c r="S87">
-        <v>37231000</v>
-      </c>
-      <c r="T87">
-        <v>31462000</v>
-      </c>
-      <c r="U87">
-        <v>52817000</v>
-      </c>
-      <c r="V87" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="88" spans="1:22">
-      <c r="A88" t="s">
-        <v>108</v>
-      </c>
-      <c r="B88" t="s">
-        <v>116</v>
-      </c>
-      <c r="C88" t="s">
-        <v>153</v>
-      </c>
-      <c r="D88" t="s">
-        <v>253</v>
-      </c>
-      <c r="E88">
-        <v>158.3800048828125</v>
-      </c>
-      <c r="F88">
-        <v>1504263.333333333</v>
-      </c>
-      <c r="G88">
-        <v>147.1948001098633</v>
-      </c>
-      <c r="H88">
-        <v>130.2936665344238</v>
-      </c>
-      <c r="I88">
-        <v>126.985899887085</v>
-      </c>
-      <c r="J88">
-        <v>121.925899772644</v>
-      </c>
-      <c r="K88">
-        <v>12.18373107910156</v>
-      </c>
-      <c r="L88">
-        <v>168.5816802978516</v>
-      </c>
-      <c r="M88">
-        <v>125.4289676630226</v>
-      </c>
-      <c r="N88">
-        <v>0.82</v>
-      </c>
-      <c r="O88">
-        <v>0.54</v>
-      </c>
-      <c r="P88">
-        <v>1.15</v>
-      </c>
-      <c r="Q88">
-        <v>0.52</v>
-      </c>
-      <c r="R88">
-        <v>347000000</v>
-      </c>
-      <c r="S88">
-        <v>231000000</v>
-      </c>
-      <c r="T88">
-        <v>494000000</v>
-      </c>
-      <c r="U88">
-        <v>224000000</v>
-      </c>
-      <c r="V88" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="89" spans="1:22">
-      <c r="A89" t="s">
-        <v>109</v>
-      </c>
-      <c r="B89" t="s">
-        <v>115</v>
-      </c>
-      <c r="C89" t="s">
-        <v>155</v>
-      </c>
-      <c r="D89" t="s">
-        <v>254</v>
-      </c>
-      <c r="E89">
-        <v>40.20000076293945</v>
-      </c>
-      <c r="F89">
-        <v>353300</v>
-      </c>
-      <c r="G89">
-        <v>35.48599987030029</v>
-      </c>
-      <c r="H89">
-        <v>32.29853326161702</v>
-      </c>
-      <c r="I89">
-        <v>31.38714990615845</v>
-      </c>
-      <c r="J89">
-        <v>29.86539988517761</v>
-      </c>
-      <c r="K89">
-        <v>2.220000028610229</v>
-      </c>
-      <c r="L89">
-        <v>40.59000015258789</v>
-      </c>
-      <c r="M89">
-        <v>125.3766515840249</v>
-      </c>
-      <c r="N89">
-        <v>0.54</v>
-      </c>
-      <c r="O89">
-        <v>0.71</v>
-      </c>
-      <c r="P89">
-        <v>0.88</v>
-      </c>
-      <c r="Q89">
-        <v>0.89</v>
-      </c>
-      <c r="R89">
-        <v>30604000</v>
-      </c>
-      <c r="S89">
-        <v>40241000</v>
-      </c>
-      <c r="T89">
-        <v>49122000</v>
-      </c>
-      <c r="U89">
-        <v>49009000</v>
-      </c>
-      <c r="V89" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="90" spans="1:22">
-      <c r="A90" t="s">
-        <v>110</v>
-      </c>
-      <c r="B90" t="s">
-        <v>117</v>
-      </c>
-      <c r="C90" t="s">
-        <v>146</v>
-      </c>
-      <c r="D90" t="s">
-        <v>255</v>
-      </c>
-      <c r="E90">
-        <v>480.5499877929688</v>
-      </c>
-      <c r="F90">
-        <v>784813.3333333334</v>
-      </c>
-      <c r="G90">
-        <v>425.4125994873047</v>
-      </c>
-      <c r="H90">
-        <v>405.7753328450521</v>
-      </c>
-      <c r="I90">
-        <v>389.267200012207</v>
-      </c>
-      <c r="J90">
-        <v>371.261849975586</v>
-      </c>
-      <c r="K90">
-        <v>3.029999971389771</v>
-      </c>
-      <c r="L90">
-        <v>486.5599975585938</v>
-      </c>
-      <c r="M90">
-        <v>125.3140746608057</v>
-      </c>
-      <c r="N90">
-        <v>8.66</v>
-      </c>
-      <c r="O90">
-        <v>9.15</v>
-      </c>
-      <c r="P90">
-        <v>6.47</v>
-      </c>
-      <c r="Q90">
-        <v>8.58</v>
-      </c>
-      <c r="R90">
-        <v>606000000</v>
-      </c>
-      <c r="S90">
-        <v>639000000</v>
-      </c>
-      <c r="T90">
-        <v>451000000</v>
-      </c>
-      <c r="U90">
-        <v>591000000</v>
-      </c>
-      <c r="V90" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="91" spans="1:22">
-      <c r="A91" t="s">
-        <v>111</v>
-      </c>
-      <c r="B91" t="s">
-        <v>118</v>
-      </c>
-      <c r="C91" t="s">
-        <v>168</v>
-      </c>
-      <c r="D91" t="s">
-        <v>256</v>
-      </c>
-      <c r="E91">
-        <v>565.0900268554688</v>
-      </c>
-      <c r="F91">
-        <v>371600</v>
-      </c>
-      <c r="G91">
-        <v>522.4417974853516</v>
-      </c>
-      <c r="H91">
-        <v>467.1251324462891</v>
-      </c>
-      <c r="I91">
-        <v>442.5118492126465</v>
-      </c>
-      <c r="J91">
-        <v>421.152449798584</v>
-      </c>
-      <c r="K91">
-        <v>0.4583329856395721</v>
-      </c>
-      <c r="L91">
-        <v>565.5499877929688</v>
-      </c>
-      <c r="M91">
-        <v>125.2537440814427</v>
-      </c>
-      <c r="N91">
-        <v>3.8</v>
-      </c>
-      <c r="O91">
-        <v>10.48</v>
-      </c>
-      <c r="P91">
-        <v>3.46</v>
-      </c>
-      <c r="Q91">
-        <v>2.41</v>
-      </c>
-      <c r="R91">
-        <v>101524000</v>
-      </c>
-      <c r="S91">
-        <v>278662000</v>
-      </c>
-      <c r="T91">
-        <v>91787000</v>
-      </c>
-      <c r="U91">
-        <v>63552000</v>
-      </c>
-      <c r="V91" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="92" spans="1:22">
-      <c r="A92" t="s">
-        <v>112</v>
-      </c>
-      <c r="B92" t="s">
-        <v>115</v>
-      </c>
-      <c r="C92" t="s">
-        <v>169</v>
-      </c>
-      <c r="D92" t="s">
-        <v>257</v>
-      </c>
-      <c r="E92">
-        <v>57.68999862670898</v>
-      </c>
-      <c r="F92">
-        <v>678486.6666666666</v>
-      </c>
-      <c r="G92">
-        <v>51.7513998413086</v>
-      </c>
-      <c r="H92">
-        <v>46.54799995422363</v>
-      </c>
-      <c r="I92">
-        <v>45.42030000686646</v>
-      </c>
-      <c r="J92">
-        <v>44.0164999961853</v>
-      </c>
-      <c r="K92">
-        <v>5.159999847412109</v>
-      </c>
-      <c r="L92">
-        <v>59.47999954223633</v>
-      </c>
-      <c r="M92">
-        <v>125.1606336601367</v>
-      </c>
-      <c r="N92">
-        <v>1.55</v>
-      </c>
-      <c r="O92">
-        <v>0.01</v>
-      </c>
-      <c r="P92">
-        <v>0.52</v>
-      </c>
-      <c r="Q92">
-        <v>2.07</v>
-      </c>
-      <c r="R92">
-        <v>113000000</v>
-      </c>
-      <c r="S92">
-        <v>1000000</v>
-      </c>
-      <c r="T92">
-        <v>37000000</v>
-      </c>
-      <c r="U92">
-        <v>142000000</v>
-      </c>
-      <c r="V92" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="93" spans="1:22">
-      <c r="A93" t="s">
-        <v>113</v>
-      </c>
-      <c r="B93" t="s">
-        <v>116</v>
-      </c>
-      <c r="C93" t="s">
-        <v>135</v>
-      </c>
-      <c r="D93" t="s">
-        <v>258</v>
-      </c>
-      <c r="E93">
-        <v>101.379997253418</v>
-      </c>
-      <c r="F93">
-        <v>5952446.666666667</v>
-      </c>
-      <c r="G93">
-        <v>95.01199966430664</v>
-      </c>
-      <c r="H93">
-        <v>82.98719973246257</v>
-      </c>
-      <c r="I93">
-        <v>79.15869974136352</v>
-      </c>
-      <c r="J93">
-        <v>75.27524984359741</v>
-      </c>
-      <c r="K93">
-        <v>0.9100000262260437</v>
-      </c>
-      <c r="L93">
-        <v>108.0899963378906</v>
-      </c>
-      <c r="M93">
-        <v>124.9432997325041</v>
-      </c>
-      <c r="N93">
-        <v>0.7</v>
-      </c>
-      <c r="O93">
-        <v>1.35</v>
-      </c>
-      <c r="P93">
-        <v>1.03</v>
-      </c>
-      <c r="Q93">
-        <v>1.29</v>
-      </c>
-      <c r="R93">
-        <v>311900000</v>
-      </c>
-      <c r="S93">
-        <v>604300000</v>
-      </c>
-      <c r="T93">
-        <v>461700000</v>
-      </c>
-      <c r="U93">
-        <v>576600000</v>
-      </c>
-      <c r="V93" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="94" spans="1:22">
-      <c r="A94" t="s">
-        <v>114</v>
-      </c>
-      <c r="B94" t="s">
-        <v>118</v>
-      </c>
-      <c r="C94" t="s">
-        <v>130</v>
-      </c>
-      <c r="D94" t="s">
-        <v>259</v>
-      </c>
-      <c r="E94">
-        <v>59.02000045776367</v>
-      </c>
-      <c r="F94">
-        <v>642246.6666666666</v>
-      </c>
-      <c r="G94">
-        <v>55.59919982910156</v>
-      </c>
-      <c r="H94">
-        <v>48.99173332214355</v>
-      </c>
-      <c r="I94">
-        <v>47.35439992904663</v>
-      </c>
-      <c r="J94">
-        <v>45.01294994354248</v>
-      </c>
-      <c r="K94">
-        <v>13.7691478729248</v>
-      </c>
-      <c r="L94">
-        <v>59.68000030517578</v>
-      </c>
-      <c r="M94">
-        <v>124.6837062415044</v>
-      </c>
-      <c r="N94">
-        <v>1.45</v>
-      </c>
-      <c r="O94">
-        <v>1.52</v>
-      </c>
-      <c r="P94">
-        <v>1.85</v>
-      </c>
-      <c r="Q94">
-        <v>1.92</v>
-      </c>
-      <c r="R94">
-        <v>139000000</v>
-      </c>
-      <c r="S94">
-        <v>141000000</v>
-      </c>
-      <c r="T94">
-        <v>170000000</v>
-      </c>
-      <c r="U94">
-        <v>175000000</v>
-      </c>
-      <c r="V94" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/ScreenResult/ScreenResult.xlsx
+++ b/Screener/ScreenResult/ScreenResult.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="297">
   <si>
     <t>Symbol</t>
   </si>
@@ -82,76 +82,829 @@
     <t>Code 33</t>
   </si>
   <si>
+    <t>LMB</t>
+  </si>
+  <si>
+    <t>CAMT</t>
+  </si>
+  <si>
+    <t>ANF</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>PARR</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>CORT</t>
+  </si>
+  <si>
+    <t>SOVO</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>IDYA</t>
+  </si>
+  <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>ARGX</t>
+  </si>
+  <si>
+    <t>AMR</t>
+  </si>
+  <si>
+    <t>BKI</t>
+  </si>
+  <si>
+    <t>NVO</t>
+  </si>
+  <si>
+    <t>MPC</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>TW</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>FOR</t>
+  </si>
+  <si>
+    <t>FRHC</t>
+  </si>
+  <si>
+    <t>SCPL</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>EME</t>
+  </si>
+  <si>
+    <t>VST</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>INOD</t>
+  </si>
+  <si>
+    <t>BCC</t>
+  </si>
+  <si>
+    <t>BRBR</t>
+  </si>
+  <si>
+    <t>BR</t>
+  </si>
+  <si>
+    <t>QLYS</t>
+  </si>
+  <si>
+    <t>ODFL</t>
+  </si>
+  <si>
+    <t>RDY</t>
+  </si>
+  <si>
+    <t>PBF</t>
+  </si>
+  <si>
+    <t>CCJ</t>
+  </si>
+  <si>
+    <t>TFII</t>
+  </si>
+  <si>
+    <t>BKNG</t>
+  </si>
+  <si>
+    <t>PRIM</t>
+  </si>
+  <si>
+    <t>AEL</t>
+  </si>
+  <si>
+    <t>TRGP</t>
+  </si>
+  <si>
+    <t>HCCI</t>
+  </si>
+  <si>
+    <t>CHX</t>
+  </si>
+  <si>
+    <t>DFH</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>WWE</t>
+  </si>
+  <si>
+    <t>PDCO</t>
+  </si>
+  <si>
+    <t>CBOE</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>COCO</t>
+  </si>
+  <si>
+    <t>GBDC</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>ACT</t>
+  </si>
+  <si>
+    <t>TNET</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>FWRG</t>
+  </si>
+  <si>
+    <t>IBKR</t>
+  </si>
+  <si>
+    <t>VAL</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>CDW</t>
+  </si>
+  <si>
     <t>MANU</t>
   </si>
   <si>
-    <t>IDYA</t>
+    <t>NYT</t>
+  </si>
+  <si>
+    <t>SFM</t>
+  </si>
+  <si>
+    <t>VMW</t>
+  </si>
+  <si>
+    <t>CSCO</t>
+  </si>
+  <si>
+    <t>CSWC</t>
+  </si>
+  <si>
+    <t>ATR</t>
+  </si>
+  <si>
+    <t>NWS</t>
+  </si>
+  <si>
+    <t>BDX</t>
   </si>
   <si>
     <t>BLMN</t>
   </si>
   <si>
-    <t>AVT</t>
-  </si>
-  <si>
-    <t>COCO</t>
-  </si>
-  <si>
-    <t>DFH</t>
+    <t>ZGN</t>
+  </si>
+  <si>
+    <t>CME</t>
+  </si>
+  <si>
+    <t>BRO</t>
+  </si>
+  <si>
+    <t>FLT</t>
+  </si>
+  <si>
+    <t>MAR</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>TJX</t>
+  </si>
+  <si>
+    <t>CNQ</t>
+  </si>
+  <si>
+    <t>FMX</t>
+  </si>
+  <si>
+    <t>COOP</t>
+  </si>
+  <si>
+    <t>BWXT</t>
+  </si>
+  <si>
+    <t>MHO</t>
+  </si>
+  <si>
+    <t>CHH</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>LII</t>
+  </si>
+  <si>
+    <t>ESNT</t>
+  </si>
+  <si>
+    <t>ROAD</t>
+  </si>
+  <si>
+    <t>ARCB</t>
+  </si>
+  <si>
+    <t>ATVI</t>
+  </si>
+  <si>
+    <t>PFGC</t>
+  </si>
+  <si>
+    <t>ICLR</t>
+  </si>
+  <si>
+    <t>LYB</t>
+  </si>
+  <si>
+    <t>WLK</t>
+  </si>
+  <si>
+    <t>RYAN</t>
+  </si>
+  <si>
+    <t>MEDP</t>
+  </si>
+  <si>
+    <t>NMIH</t>
+  </si>
+  <si>
+    <t>GOLF</t>
+  </si>
+  <si>
+    <t>IRM</t>
+  </si>
+  <si>
+    <t>MMP</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Consumer Defensive</t>
+  </si>
+  <si>
+    <t>Basic Materials</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
   </si>
   <si>
     <t>Communication Services</t>
   </si>
   <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Consumer Cyclical</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Consumer Defensive</t>
+    <t>Utilities</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Construction</t>
+  </si>
+  <si>
+    <t>Semiconductor Equipment &amp; Materials</t>
+  </si>
+  <si>
+    <t>Apparel Retail</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Refining &amp; Marketing</t>
+  </si>
+  <si>
+    <t>Biotechnology</t>
+  </si>
+  <si>
+    <t>Electrical Equipment &amp; Parts</t>
+  </si>
+  <si>
+    <t>Packaged Foods</t>
+  </si>
+  <si>
+    <t>Auto Parts</t>
+  </si>
+  <si>
+    <t>Beverages—Non-Alcoholic</t>
+  </si>
+  <si>
+    <t>Drug Manufacturers—General</t>
+  </si>
+  <si>
+    <t>Steel</t>
+  </si>
+  <si>
+    <t>Coking Coal</t>
+  </si>
+  <si>
+    <t>Software—Application</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Equipment &amp; Services</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>Trucking</t>
+  </si>
+  <si>
+    <t>Real Estate—Development</t>
+  </si>
+  <si>
+    <t>Electronic Gaming &amp; Multimedia</t>
+  </si>
+  <si>
+    <t>Utilities—Independent Power Producers</t>
+  </si>
+  <si>
+    <t>Rental &amp; Leasing Services</t>
+  </si>
+  <si>
+    <t>Information Technology Services</t>
+  </si>
+  <si>
+    <t>Building Materials</t>
+  </si>
+  <si>
+    <t>Software—Infrastructure</t>
+  </si>
+  <si>
+    <t>Drug Manufacturers—Specialty &amp; Generic</t>
+  </si>
+  <si>
+    <t>Uranium</t>
+  </si>
+  <si>
+    <t>Travel Services</t>
+  </si>
+  <si>
+    <t>Insurance—Life</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Midstream</t>
+  </si>
+  <si>
+    <t>Waste Management</t>
+  </si>
+  <si>
+    <t>Residential Construction</t>
+  </si>
+  <si>
+    <t>Computer Hardware</t>
   </si>
   <si>
     <t>Entertainment</t>
   </si>
   <si>
-    <t>Biotechnology</t>
+    <t>Medical Distribution</t>
+  </si>
+  <si>
+    <t>Financial Data &amp; Stock Exchanges</t>
+  </si>
+  <si>
+    <t>Asset Management</t>
+  </si>
+  <si>
+    <t>Specialty Industrial Machinery</t>
+  </si>
+  <si>
+    <t>Insurance—Specialty</t>
+  </si>
+  <si>
+    <t>Staffing &amp; Employment Services</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Drilling</t>
   </si>
   <si>
     <t>Restaurants</t>
   </si>
   <si>
-    <t>Electronics &amp; Computer Distribution</t>
-  </si>
-  <si>
-    <t>Beverages—Non-Alcoholic</t>
-  </si>
-  <si>
-    <t>Residential Construction</t>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Publishing</t>
+  </si>
+  <si>
+    <t>Grocery Stores</t>
+  </si>
+  <si>
+    <t>Communication Equipment</t>
+  </si>
+  <si>
+    <t>Medical Instruments &amp; Supplies</t>
+  </si>
+  <si>
+    <t>Apparel Manufacturing</t>
+  </si>
+  <si>
+    <t>Insurance Brokers</t>
+  </si>
+  <si>
+    <t>Lodging</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas E&amp;P</t>
+  </si>
+  <si>
+    <t>Beverages—Brewers</t>
+  </si>
+  <si>
+    <t>Mortgage Finance</t>
+  </si>
+  <si>
+    <t>Aerospace &amp; Defense</t>
+  </si>
+  <si>
+    <t>Internet Content &amp; Information</t>
+  </si>
+  <si>
+    <t>Building Products &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Food Distribution</t>
+  </si>
+  <si>
+    <t>Diagnostics &amp; Research</t>
+  </si>
+  <si>
+    <t>Specialty Chemicals</t>
+  </si>
+  <si>
+    <t>Leisure</t>
+  </si>
+  <si>
+    <t>REIT—Specialty</t>
+  </si>
+  <si>
+    <t>2014-08-08</t>
+  </si>
+  <si>
+    <t>2000-07-28</t>
+  </si>
+  <si>
+    <t>1996-09-26</t>
+  </si>
+  <si>
+    <t>1991-07-12</t>
+  </si>
+  <si>
+    <t>2012-09-05</t>
+  </si>
+  <si>
+    <t>2014-02-03</t>
+  </si>
+  <si>
+    <t>2018-08-02</t>
+  </si>
+  <si>
+    <t>2004-04-14</t>
+  </si>
+  <si>
+    <t>2021-09-23</t>
+  </si>
+  <si>
+    <t>1982-09-20</t>
+  </si>
+  <si>
+    <t>2007-01-22</t>
+  </si>
+  <si>
+    <t>2019-05-23</t>
+  </si>
+  <si>
+    <t>1972-06-01</t>
+  </si>
+  <si>
+    <t>1994-10-14</t>
+  </si>
+  <si>
+    <t>2017-05-18</t>
+  </si>
+  <si>
+    <t>2021-02-08</t>
+  </si>
+  <si>
+    <t>2015-05-20</t>
+  </si>
+  <si>
+    <t>1981-04-30</t>
+  </si>
+  <si>
+    <t>2011-06-24</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>2019-04-04</t>
+  </si>
+  <si>
+    <t>2003-10-07</t>
+  </si>
+  <si>
+    <t>2007-12-13</t>
+  </si>
+  <si>
+    <t>2018-02-07</t>
+  </si>
+  <si>
+    <t>2019-05-03</t>
+  </si>
+  <si>
+    <t>2002-09-11</t>
+  </si>
+  <si>
+    <t>1995-01-10</t>
+  </si>
+  <si>
+    <t>2016-10-05</t>
+  </si>
+  <si>
+    <t>2015-05-14</t>
+  </si>
+  <si>
+    <t>1993-08-10</t>
+  </si>
+  <si>
+    <t>2013-02-06</t>
+  </si>
+  <si>
+    <t>2019-10-18</t>
+  </si>
+  <si>
+    <t>2007-03-22</t>
+  </si>
+  <si>
+    <t>2012-09-28</t>
+  </si>
+  <si>
+    <t>1991-10-24</t>
+  </si>
+  <si>
+    <t>2001-04-11</t>
+  </si>
+  <si>
+    <t>2012-12-13</t>
+  </si>
+  <si>
+    <t>1996-03-14</t>
+  </si>
+  <si>
+    <t>2005-11-15</t>
+  </si>
+  <si>
+    <t>1999-03-31</t>
+  </si>
+  <si>
+    <t>2008-08-06</t>
+  </si>
+  <si>
+    <t>2003-12-04</t>
+  </si>
+  <si>
+    <t>2010-12-07</t>
+  </si>
+  <si>
+    <t>2008-03-12</t>
+  </si>
+  <si>
+    <t>2018-04-27</t>
+  </si>
+  <si>
+    <t>2021-01-21</t>
+  </si>
+  <si>
+    <t>2016-08-17</t>
+  </si>
+  <si>
+    <t>1999-10-19</t>
+  </si>
+  <si>
+    <t>1992-10-28</t>
+  </si>
+  <si>
+    <t>2010-06-15</t>
+  </si>
+  <si>
+    <t>2014-06-06</t>
+  </si>
+  <si>
+    <t>2021-10-21</t>
+  </si>
+  <si>
+    <t>2010-04-15</t>
+  </si>
+  <si>
+    <t>2021-09-16</t>
+  </si>
+  <si>
+    <t>2014-03-27</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>1980-01-02</t>
+  </si>
+  <si>
+    <t>2021-10-01</t>
+  </si>
+  <si>
+    <t>2007-05-04</t>
+  </si>
+  <si>
+    <t>2021-05-03</t>
+  </si>
+  <si>
+    <t>1999-01-22</t>
+  </si>
+  <si>
+    <t>2013-06-27</t>
   </si>
   <si>
     <t>2012-08-10</t>
   </si>
   <si>
-    <t>2019-05-23</t>
+    <t>1973-05-03</t>
+  </si>
+  <si>
+    <t>2013-08-01</t>
+  </si>
+  <si>
+    <t>2007-08-15</t>
+  </si>
+  <si>
+    <t>1990-02-16</t>
+  </si>
+  <si>
+    <t>1980-03-17</t>
+  </si>
+  <si>
+    <t>1993-04-23</t>
+  </si>
+  <si>
+    <t>2013-06-19</t>
+  </si>
+  <si>
+    <t>1973-02-21</t>
   </si>
   <si>
     <t>2012-08-08</t>
   </si>
   <si>
-    <t>1973-05-03</t>
-  </si>
-  <si>
-    <t>2021-10-21</t>
-  </si>
-  <si>
-    <t>2021-01-21</t>
+    <t>2021-12-20</t>
+  </si>
+  <si>
+    <t>2002-12-06</t>
+  </si>
+  <si>
+    <t>1981-02-11</t>
+  </si>
+  <si>
+    <t>2010-12-15</t>
+  </si>
+  <si>
+    <t>1998-03-23</t>
+  </si>
+  <si>
+    <t>1987-06-26</t>
+  </si>
+  <si>
+    <t>2000-07-31</t>
+  </si>
+  <si>
+    <t>1998-05-11</t>
+  </si>
+  <si>
+    <t>2012-03-28</t>
+  </si>
+  <si>
+    <t>2010-08-02</t>
+  </si>
+  <si>
+    <t>1993-11-03</t>
+  </si>
+  <si>
+    <t>1996-10-16</t>
+  </si>
+  <si>
+    <t>2004-08-19</t>
+  </si>
+  <si>
+    <t>1999-07-29</t>
+  </si>
+  <si>
+    <t>2013-10-31</t>
+  </si>
+  <si>
+    <t>2018-05-04</t>
+  </si>
+  <si>
+    <t>1992-05-13</t>
+  </si>
+  <si>
+    <t>1993-10-25</t>
+  </si>
+  <si>
+    <t>2015-09-30</t>
+  </si>
+  <si>
+    <t>1998-05-15</t>
+  </si>
+  <si>
+    <t>2010-04-28</t>
+  </si>
+  <si>
+    <t>2004-08-12</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>2016-08-11</t>
+  </si>
+  <si>
+    <t>2013-11-08</t>
+  </si>
+  <si>
+    <t>2016-10-28</t>
+  </si>
+  <si>
+    <t>1996-02-01</t>
+  </si>
+  <si>
+    <t>2001-03-19</t>
   </si>
   <si>
     <t>F</t>
+  </si>
+  <si>
+    <t>T</t>
   </si>
 </sst>
 </file>
@@ -509,7 +1262,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
@@ -585,67 +1338,67 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>125</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>195</v>
       </c>
       <c r="E2">
-        <v>23.05999946594238</v>
+        <v>36.04000091552734</v>
       </c>
       <c r="F2">
-        <v>1229706.666666667</v>
+        <v>250010</v>
       </c>
       <c r="G2">
-        <v>22.89739994049072</v>
+        <v>27.25780002593994</v>
       </c>
       <c r="H2">
-        <v>21.83846661885579</v>
+        <v>20.18083338419596</v>
       </c>
       <c r="I2">
-        <v>21.39544996738434</v>
+        <v>17.83602504491806</v>
       </c>
       <c r="J2">
-        <v>20.44749999046326</v>
+        <v>15.578875041008</v>
       </c>
       <c r="K2">
-        <v>10.51000022888184</v>
+        <v>2.529999971389771</v>
       </c>
       <c r="L2">
-        <v>26.84000015258789</v>
+        <v>36.04000091552734</v>
       </c>
       <c r="M2">
-        <v>33.60742780942049</v>
+        <v>142.1745394788033</v>
       </c>
       <c r="N2">
-        <v>-0.4346</v>
+        <v>0.34</v>
       </c>
       <c r="O2">
-        <v>-0.1626</v>
+        <v>0.35</v>
       </c>
       <c r="P2">
-        <v>0.0385</v>
+        <v>0.27</v>
       </c>
       <c r="Q2">
-        <v>-0.034</v>
+        <v>0.46</v>
       </c>
       <c r="R2">
-        <v>-70842000</v>
+        <v>3641000</v>
       </c>
       <c r="S2">
-        <v>-26516000</v>
+        <v>3808000</v>
       </c>
       <c r="T2">
-        <v>6306000</v>
+        <v>2993000</v>
       </c>
       <c r="U2">
-        <v>-5547000</v>
+        <v>5320000</v>
       </c>
       <c r="V2" t="s">
-        <v>45</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -653,67 +1406,67 @@
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>126</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>196</v>
       </c>
       <c r="E3">
-        <v>28.06999969482422</v>
+        <v>52.09999847412109</v>
       </c>
       <c r="F3">
-        <v>476913.3333333333</v>
+        <v>410090</v>
       </c>
       <c r="G3">
-        <v>23.60920001983643</v>
+        <v>41.26540004730224</v>
       </c>
       <c r="H3">
-        <v>19.89920005162557</v>
+        <v>32.0128000386556</v>
       </c>
       <c r="I3">
-        <v>19.28160003185272</v>
+        <v>29.87625001907348</v>
       </c>
       <c r="J3">
-        <v>18.47179999828339</v>
+        <v>27.38434999465942</v>
       </c>
       <c r="K3">
-        <v>3.029999971389771</v>
+        <v>0.2220596075057983</v>
       </c>
       <c r="L3">
-        <v>28.11000061035156</v>
+        <v>52.54000091552734</v>
       </c>
       <c r="M3">
-        <v>33.52485335906608</v>
+        <v>138.4981942286498</v>
       </c>
       <c r="N3">
-        <v>0.04</v>
+        <v>0.43</v>
       </c>
       <c r="O3">
-        <v>-0.5</v>
+        <v>0.45</v>
       </c>
       <c r="P3">
-        <v>-0.49</v>
+        <v>0.36</v>
       </c>
       <c r="Q3">
-        <v>-0.5</v>
+        <v>0.38</v>
       </c>
       <c r="R3">
-        <v>1615000</v>
+        <v>20715000</v>
       </c>
       <c r="S3">
-        <v>-24201000</v>
+        <v>21673000</v>
       </c>
       <c r="T3">
-        <v>-23640000</v>
+        <v>17245000</v>
       </c>
       <c r="U3">
-        <v>-27926000</v>
+        <v>18539000</v>
       </c>
       <c r="V3" t="s">
-        <v>45</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -721,67 +1474,67 @@
         <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>127</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>197</v>
       </c>
       <c r="E4">
-        <v>27.45999908447266</v>
+        <v>50.45999908447266</v>
       </c>
       <c r="F4">
-        <v>1931340</v>
+        <v>2182096.666666667</v>
       </c>
       <c r="G4">
-        <v>26.71140007019043</v>
+        <v>38.535</v>
       </c>
       <c r="H4">
-        <v>25.59860001881917</v>
+        <v>31.06793334960938</v>
       </c>
       <c r="I4">
-        <v>24.72430004119873</v>
+        <v>28.99609997749329</v>
       </c>
       <c r="J4">
-        <v>24.26184997558594</v>
+        <v>26.55339999198914</v>
       </c>
       <c r="K4">
-        <v>4.829999923706055</v>
+        <v>4.195813655853271</v>
       </c>
       <c r="L4">
-        <v>31.60000038146973</v>
+        <v>58.59574890136719</v>
       </c>
       <c r="M4">
-        <v>33.47701982023085</v>
+        <v>136.4092185411029</v>
       </c>
       <c r="N4">
-        <v>0.34</v>
+        <v>-0.33</v>
       </c>
       <c r="O4">
-        <v>0.61</v>
+        <v>-0.04</v>
       </c>
       <c r="P4">
-        <v>0.93</v>
+        <v>0.75</v>
       </c>
       <c r="Q4">
-        <v>0.7</v>
+        <v>0.32</v>
       </c>
       <c r="R4">
-        <v>31986000</v>
+        <v>-16834000</v>
       </c>
       <c r="S4">
-        <v>58045000</v>
+        <v>-2214000</v>
       </c>
       <c r="T4">
-        <v>91311000</v>
+        <v>38333000</v>
       </c>
       <c r="U4">
-        <v>68277000</v>
+        <v>16571000</v>
       </c>
       <c r="V4" t="s">
-        <v>45</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -789,67 +1542,67 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>198</v>
       </c>
       <c r="E5">
-        <v>48.81999969482422</v>
+        <v>77.87000274658203</v>
       </c>
       <c r="F5">
-        <v>752043.3333333334</v>
+        <v>458866.6666666667</v>
       </c>
       <c r="G5">
-        <v>48.08320030212403</v>
+        <v>62.74319999694824</v>
       </c>
       <c r="H5">
-        <v>45.34640012105306</v>
+        <v>47.45766672770182</v>
       </c>
       <c r="I5">
-        <v>44.83070009231567</v>
+        <v>43.62904999732971</v>
       </c>
       <c r="J5">
-        <v>44.01900007247925</v>
+        <v>38.98454999923706</v>
       </c>
       <c r="K5">
-        <v>0.5667726397514343</v>
+        <v>0.4209107160568237</v>
       </c>
       <c r="L5">
-        <v>50.61000061035156</v>
+        <v>82.29000091552734</v>
       </c>
       <c r="M5">
-        <v>33.47481385214371</v>
+        <v>135.4455427563442</v>
       </c>
       <c r="N5">
-        <v>1.93</v>
+        <v>0.97</v>
       </c>
       <c r="O5">
-        <v>2.63</v>
+        <v>1.03</v>
       </c>
       <c r="P5">
-        <v>2.03</v>
+        <v>0.64</v>
       </c>
       <c r="Q5">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="R5">
-        <v>184261000</v>
+        <v>29523000</v>
       </c>
       <c r="S5">
-        <v>243886000</v>
+        <v>31725000</v>
       </c>
       <c r="T5">
-        <v>187426000</v>
+        <v>19649000</v>
       </c>
       <c r="U5">
-        <v>155255000</v>
+        <v>39480000</v>
       </c>
       <c r="V5" t="s">
-        <v>45</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -857,67 +1610,67 @@
         <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>199</v>
       </c>
       <c r="E6">
-        <v>27.19000053405762</v>
+        <v>36.02999877929688</v>
       </c>
       <c r="F6">
-        <v>648503.3333333334</v>
+        <v>810273.3333333334</v>
       </c>
       <c r="G6">
-        <v>26.50699989318848</v>
+        <v>29.74120014190674</v>
       </c>
       <c r="H6">
-        <v>22.05496665318807</v>
+        <v>26.90493338267008</v>
       </c>
       <c r="I6">
-        <v>19.65242500782013</v>
+        <v>25.81090004920959</v>
       </c>
       <c r="J6">
-        <v>18.0758500289917</v>
+        <v>24.53600005149841</v>
       </c>
       <c r="K6">
-        <v>7.559999942779541</v>
+        <v>0.6000000238418579</v>
       </c>
       <c r="L6">
-        <v>29.29999923706055</v>
+        <v>37.02000045776367</v>
       </c>
       <c r="M6">
-        <v>33.44181710531121</v>
+        <v>131.0192561741487</v>
       </c>
       <c r="N6">
-        <v>0.13</v>
+        <v>4.47</v>
       </c>
       <c r="O6">
-        <v>-0.05</v>
+        <v>1.4</v>
       </c>
       <c r="P6">
-        <v>0.12</v>
+        <v>3.9</v>
       </c>
       <c r="Q6">
-        <v>0.31</v>
+        <v>0.49</v>
       </c>
       <c r="R6">
-        <v>7258000</v>
+        <v>267396000</v>
       </c>
       <c r="S6">
-        <v>-2810000</v>
+        <v>84719000</v>
       </c>
       <c r="T6">
-        <v>6705000</v>
+        <v>237890000</v>
       </c>
       <c r="U6">
-        <v>17987000</v>
+        <v>30013000</v>
       </c>
       <c r="V6" t="s">
-        <v>45</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -925,67 +1678,6663 @@
         <v>27</v>
       </c>
       <c r="B7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E7">
+        <v>13.56999969482422</v>
+      </c>
+      <c r="F7">
+        <v>1485836.666666667</v>
+      </c>
+      <c r="G7">
+        <v>11.1810000038147</v>
+      </c>
+      <c r="H7">
+        <v>9.716100021998088</v>
+      </c>
+      <c r="I7">
+        <v>8.434575021266937</v>
+      </c>
+      <c r="J7">
+        <v>7.510575020313263</v>
+      </c>
+      <c r="K7">
+        <v>0.9279999732971191</v>
+      </c>
+      <c r="L7">
+        <v>15.15999984741211</v>
+      </c>
+      <c r="M7">
+        <v>129.1620129457897</v>
+      </c>
+      <c r="N7">
+        <v>-0.28</v>
+      </c>
+      <c r="O7">
+        <v>-0.3</v>
+      </c>
+      <c r="P7">
+        <v>-0.29</v>
+      </c>
+      <c r="Q7">
+        <v>-0.01</v>
+      </c>
+      <c r="R7">
+        <v>-24505000</v>
+      </c>
+      <c r="S7">
+        <v>-26633000</v>
+      </c>
+      <c r="T7">
+        <v>-28778000</v>
+      </c>
+      <c r="U7">
+        <v>-808000</v>
+      </c>
+      <c r="V7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D8" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8">
+        <v>35.0099983215332</v>
+      </c>
+      <c r="F8">
+        <v>7665256.666666667</v>
+      </c>
+      <c r="G8">
+        <v>28.19160011291504</v>
+      </c>
+      <c r="H8">
+        <v>19.54720004399617</v>
+      </c>
+      <c r="I8">
+        <v>18.14240003585816</v>
+      </c>
+      <c r="J8">
+        <v>16.08925000190735</v>
+      </c>
+      <c r="K8">
+        <v>5.564881324768066</v>
+      </c>
+      <c r="L8">
+        <v>36.22000122070312</v>
+      </c>
+      <c r="M8">
+        <v>126.3638131611164</v>
+      </c>
+      <c r="N8">
+        <v>0.06</v>
+      </c>
+      <c r="O8">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P8">
+        <v>0.12</v>
+      </c>
+      <c r="Q8">
+        <v>0.22</v>
+      </c>
+      <c r="R8">
+        <v>21200000</v>
+      </c>
+      <c r="S8">
+        <v>26600000</v>
+      </c>
+      <c r="T8">
+        <v>50300000</v>
+      </c>
+      <c r="U8">
+        <v>83200000</v>
+      </c>
+      <c r="V8" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" t="s">
+        <v>202</v>
+      </c>
+      <c r="E9">
+        <v>31.77000045776367</v>
+      </c>
+      <c r="F9">
+        <v>723183.3333333334</v>
+      </c>
+      <c r="G9">
+        <v>25.60880001068115</v>
+      </c>
+      <c r="H9">
+        <v>23.60793329874674</v>
+      </c>
+      <c r="I9">
+        <v>23.43869998931885</v>
+      </c>
+      <c r="J9">
+        <v>23.25004998207092</v>
+      </c>
+      <c r="K9">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="L9">
+        <v>31.80999946594238</v>
+      </c>
+      <c r="M9">
+        <v>124.2670048723938</v>
+      </c>
+      <c r="N9">
+        <v>0.3</v>
+      </c>
+      <c r="O9">
+        <v>0.14</v>
+      </c>
+      <c r="P9">
+        <v>0.14</v>
+      </c>
+      <c r="Q9">
+        <v>0.25</v>
+      </c>
+      <c r="R9">
+        <v>34608000</v>
+      </c>
+      <c r="S9">
+        <v>16601000</v>
+      </c>
+      <c r="T9">
+        <v>15879000</v>
+      </c>
+      <c r="U9">
+        <v>27528000</v>
+      </c>
+      <c r="V9" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="A10" t="s">
         <v>30</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" t="s">
+        <v>142</v>
+      </c>
+      <c r="D10" t="s">
+        <v>203</v>
+      </c>
+      <c r="E10">
+        <v>22.53000068664551</v>
+      </c>
+      <c r="F10">
+        <v>1496773.333333333</v>
+      </c>
+      <c r="G10">
+        <v>19.78820007324219</v>
+      </c>
+      <c r="H10">
+        <v>17.23306666692098</v>
+      </c>
+      <c r="I10">
+        <v>16.41129999637604</v>
+      </c>
+      <c r="J10">
+        <v>15.69779996871948</v>
+      </c>
+      <c r="K10">
+        <v>10.84000015258789</v>
+      </c>
+      <c r="L10">
+        <v>22.6200008392334</v>
+      </c>
+      <c r="M10">
+        <v>123.305205781116</v>
+      </c>
+      <c r="N10">
+        <v>0.01</v>
+      </c>
+      <c r="O10">
+        <v>-0.28</v>
+      </c>
+      <c r="P10">
+        <v>0.08</v>
+      </c>
+      <c r="Q10">
+        <v>0.05</v>
+      </c>
+      <c r="R10">
+        <v>1464000</v>
+      </c>
+      <c r="S10">
+        <v>-28687000</v>
+      </c>
+      <c r="T10">
+        <v>7846000</v>
+      </c>
+      <c r="U10">
+        <v>5389000</v>
+      </c>
+      <c r="V10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D11" t="s">
+        <v>204</v>
+      </c>
+      <c r="E11">
+        <v>44.84999847412109</v>
+      </c>
+      <c r="F11">
+        <v>738236.6666666666</v>
+      </c>
+      <c r="G11">
+        <v>37.64040019989014</v>
+      </c>
+      <c r="H11">
+        <v>28.09826671600342</v>
+      </c>
+      <c r="I11">
+        <v>26.29715002059936</v>
+      </c>
+      <c r="J11">
+        <v>23.57960000991821</v>
+      </c>
+      <c r="K11">
+        <v>0.5703791379928589</v>
+      </c>
+      <c r="L11">
+        <v>46.86000061035156</v>
+      </c>
+      <c r="M11">
+        <v>122.9398176389222</v>
+      </c>
+      <c r="N11">
+        <v>0.46</v>
+      </c>
+      <c r="O11">
+        <v>0.46</v>
+      </c>
+      <c r="P11">
+        <v>1.69</v>
+      </c>
+      <c r="Q11">
+        <v>0.85</v>
+      </c>
+      <c r="R11">
+        <v>24400000</v>
+      </c>
+      <c r="S11">
+        <v>24500000</v>
+      </c>
+      <c r="T11">
+        <v>89900000</v>
+      </c>
+      <c r="U11">
+        <v>44800000</v>
+      </c>
+      <c r="V11" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" t="s">
+        <v>144</v>
+      </c>
+      <c r="D12" t="s">
+        <v>205</v>
+      </c>
+      <c r="E12">
+        <v>177.6199951171875</v>
+      </c>
+      <c r="F12">
+        <v>1358566.666666667</v>
+      </c>
+      <c r="G12">
+        <v>153.4727996826172</v>
+      </c>
+      <c r="H12">
+        <v>119.6345999654134</v>
+      </c>
+      <c r="I12">
+        <v>115.6717998886108</v>
+      </c>
+      <c r="J12">
+        <v>108.1169000244141</v>
+      </c>
+      <c r="K12">
+        <v>0.1500000059604645</v>
+      </c>
+      <c r="L12">
+        <v>183</v>
+      </c>
+      <c r="M12">
+        <v>122.8163278130604</v>
+      </c>
+      <c r="N12">
+        <v>-2.46</v>
+      </c>
+      <c r="O12">
+        <v>-0.37</v>
+      </c>
+      <c r="P12">
+        <v>0.4</v>
+      </c>
+      <c r="Q12">
+        <v>0.52</v>
+      </c>
+      <c r="R12">
+        <v>-181896000</v>
+      </c>
+      <c r="S12">
+        <v>-21223000</v>
+      </c>
+      <c r="T12">
+        <v>41227000</v>
+      </c>
+      <c r="U12">
+        <v>51509000</v>
+      </c>
+      <c r="V12" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" t="s">
+        <v>206</v>
+      </c>
+      <c r="E13">
+        <v>28.06999969482422</v>
+      </c>
+      <c r="F13">
+        <v>476913.3333333333</v>
+      </c>
+      <c r="G13">
+        <v>23.60920001983643</v>
+      </c>
+      <c r="H13">
+        <v>19.89920005162557</v>
+      </c>
+      <c r="I13">
+        <v>19.28160003185272</v>
+      </c>
+      <c r="J13">
+        <v>18.47179999828339</v>
+      </c>
+      <c r="K13">
+        <v>3.029999971389771</v>
+      </c>
+      <c r="L13">
+        <v>28.11000061035156</v>
+      </c>
+      <c r="M13">
+        <v>122.6336917575704</v>
+      </c>
+      <c r="N13">
+        <v>0.04</v>
+      </c>
+      <c r="O13">
+        <v>-0.5</v>
+      </c>
+      <c r="P13">
+        <v>-0.49</v>
+      </c>
+      <c r="Q13">
+        <v>-0.5</v>
+      </c>
+      <c r="R13">
+        <v>1615000</v>
+      </c>
+      <c r="S13">
+        <v>-24201000</v>
+      </c>
+      <c r="T13">
+        <v>-23640000</v>
+      </c>
+      <c r="U13">
+        <v>-27926000</v>
+      </c>
+      <c r="V13" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" t="s">
+        <v>145</v>
+      </c>
+      <c r="D14" t="s">
+        <v>207</v>
+      </c>
+      <c r="E14">
+        <v>548</v>
+      </c>
+      <c r="F14">
+        <v>2897153.333333333</v>
+      </c>
+      <c r="G14">
+        <v>476.679599609375</v>
+      </c>
+      <c r="H14">
+        <v>406.468066813151</v>
+      </c>
+      <c r="I14">
+        <v>395.4525001525879</v>
+      </c>
+      <c r="J14">
+        <v>378.8409506225586</v>
+      </c>
+      <c r="K14">
+        <v>0.5143532752990723</v>
+      </c>
+      <c r="L14">
+        <v>553.6599731445312</v>
+      </c>
+      <c r="M14">
+        <v>122.4906672805949</v>
+      </c>
+      <c r="N14">
+        <v>1.61</v>
+      </c>
+      <c r="O14">
+        <v>2.039294</v>
+      </c>
+      <c r="P14">
+        <v>1.49</v>
+      </c>
+      <c r="Q14">
+        <v>1.95</v>
+      </c>
+      <c r="R14">
+        <v>1451700000</v>
+      </c>
+      <c r="S14">
+        <v>1937700000</v>
+      </c>
+      <c r="T14">
+        <v>1344900000</v>
+      </c>
+      <c r="U14">
+        <v>1763200000</v>
+      </c>
+      <c r="V14" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15" t="s">
+        <v>208</v>
+      </c>
+      <c r="E15">
+        <v>107.9899978637695</v>
+      </c>
+      <c r="F15">
+        <v>556676.6666666666</v>
+      </c>
+      <c r="G15">
+        <v>96.08199981689454</v>
+      </c>
+      <c r="H15">
+        <v>76.82233324686686</v>
+      </c>
+      <c r="I15">
+        <v>71.45849988937378</v>
+      </c>
+      <c r="J15">
+        <v>64.75504991531372</v>
+      </c>
+      <c r="K15">
+        <v>5.792013168334961</v>
+      </c>
+      <c r="L15">
+        <v>132.4752044677734</v>
+      </c>
+      <c r="M15">
+        <v>121.0610917081422</v>
+      </c>
+      <c r="N15">
+        <v>4830.25</v>
+      </c>
+      <c r="O15">
+        <v>1680.75</v>
+      </c>
+      <c r="P15">
+        <v>-2153.25</v>
+      </c>
+      <c r="Q15">
+        <v>2394.25</v>
+      </c>
+      <c r="R15">
+        <v>1588430000000</v>
+      </c>
+      <c r="S15">
+        <v>509914000000</v>
+      </c>
+      <c r="T15">
+        <v>-665869000000</v>
+      </c>
+      <c r="U15">
+        <v>726419000000</v>
+      </c>
+      <c r="V15" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" t="s">
+        <v>140</v>
+      </c>
+      <c r="D16" t="s">
+        <v>209</v>
+      </c>
+      <c r="E16">
+        <v>507.3299865722656</v>
+      </c>
+      <c r="F16">
+        <v>406943.3333333333</v>
+      </c>
+      <c r="G16">
+        <v>455.91</v>
+      </c>
+      <c r="H16">
+        <v>405.2869669596354</v>
+      </c>
+      <c r="I16">
+        <v>398.9779751586914</v>
+      </c>
+      <c r="J16">
+        <v>385.9086749267578</v>
+      </c>
+      <c r="K16">
+        <v>19.76499938964844</v>
+      </c>
+      <c r="L16">
+        <v>548.4299926757812</v>
+      </c>
+      <c r="M16">
+        <v>120.2356704812904</v>
+      </c>
+      <c r="N16">
+        <v>-4.26</v>
+      </c>
+      <c r="O16">
+        <v>-0.7</v>
+      </c>
+      <c r="P16">
+        <v>-0.52</v>
+      </c>
+      <c r="Q16">
+        <v>-1.69</v>
+      </c>
+      <c r="R16">
+        <v>-235042000</v>
+      </c>
+      <c r="S16">
+        <v>-38613000</v>
+      </c>
+      <c r="T16">
+        <v>-28871000</v>
+      </c>
+      <c r="U16">
+        <v>-94368000</v>
+      </c>
+      <c r="V16" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" t="s">
+        <v>210</v>
+      </c>
+      <c r="E17">
+        <v>192.3300018310547</v>
+      </c>
+      <c r="F17">
+        <v>261953.3333333333</v>
+      </c>
+      <c r="G17">
+        <v>170.7063989257813</v>
+      </c>
+      <c r="H17">
+        <v>161.1744659423828</v>
+      </c>
+      <c r="I17">
+        <v>159.9658995056152</v>
+      </c>
+      <c r="J17">
+        <v>157.5402998352051</v>
+      </c>
+      <c r="K17">
+        <v>11.44999980926514</v>
+      </c>
+      <c r="L17">
+        <v>196.9600067138672</v>
+      </c>
+      <c r="M17">
+        <v>117.9723674874725</v>
+      </c>
+      <c r="N17">
+        <v>14.27</v>
+      </c>
+      <c r="O17">
+        <v>13.37</v>
+      </c>
+      <c r="P17">
+        <v>17.01</v>
+      </c>
+      <c r="Q17">
+        <v>12.16</v>
+      </c>
+      <c r="R17">
+        <v>252817000</v>
+      </c>
+      <c r="S17">
+        <v>220680000</v>
+      </c>
+      <c r="T17">
+        <v>270771000</v>
+      </c>
+      <c r="U17">
+        <v>181355000</v>
+      </c>
+      <c r="V17" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
+      <c r="A18" t="s">
         <v>38</v>
       </c>
-      <c r="D7" t="s">
+      <c r="B18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" t="s">
+        <v>211</v>
+      </c>
+      <c r="E18">
+        <v>74.83999633789062</v>
+      </c>
+      <c r="F18">
+        <v>3466340</v>
+      </c>
+      <c r="G18">
+        <v>66.78840011596679</v>
+      </c>
+      <c r="H18">
+        <v>60.68106658935547</v>
+      </c>
+      <c r="I18">
+        <v>60.54634992599487</v>
+      </c>
+      <c r="J18">
+        <v>59.32654993057251</v>
+      </c>
+      <c r="K18">
+        <v>26</v>
+      </c>
+      <c r="L18">
+        <v>95.48000335693359</v>
+      </c>
+      <c r="M18">
+        <v>117.7905544865506</v>
+      </c>
+      <c r="N18">
+        <v>0.19</v>
+      </c>
+      <c r="O18">
+        <v>0.11</v>
+      </c>
+      <c r="P18">
+        <v>0.91</v>
+      </c>
+      <c r="Q18">
+        <v>0.35</v>
+      </c>
+      <c r="R18">
+        <v>30000000</v>
+      </c>
+      <c r="S18">
+        <v>17600000</v>
+      </c>
+      <c r="T18">
+        <v>141800000</v>
+      </c>
+      <c r="U18">
+        <v>55300000</v>
+      </c>
+      <c r="V18" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
+      <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D19" t="s">
+        <v>212</v>
+      </c>
+      <c r="E19">
+        <v>185.3500061035156</v>
+      </c>
+      <c r="F19">
+        <v>1769603.333333333</v>
+      </c>
+      <c r="G19">
+        <v>165.96</v>
+      </c>
+      <c r="H19">
+        <v>157.7690000406901</v>
+      </c>
+      <c r="I19">
+        <v>150.1528000640869</v>
+      </c>
+      <c r="J19">
+        <v>143.2581000900269</v>
+      </c>
+      <c r="K19">
+        <v>-8.571051876060665E-05</v>
+      </c>
+      <c r="L19">
+        <v>190.0399932861328</v>
+      </c>
+      <c r="M19">
+        <v>117.3903407418821</v>
+      </c>
+      <c r="N19">
+        <v>6.34</v>
+      </c>
+      <c r="O19">
+        <v>6.02</v>
+      </c>
+      <c r="P19">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="Q19">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="R19">
+        <v>14405000000</v>
+      </c>
+      <c r="S19">
+        <v>13592000000</v>
+      </c>
+      <c r="T19">
+        <v>19814000000</v>
+      </c>
+      <c r="U19">
+        <v>19428000000</v>
+      </c>
+      <c r="V19" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
+      <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" t="s">
+        <v>213</v>
+      </c>
+      <c r="E20">
+        <v>143.6000061035156</v>
+      </c>
+      <c r="F20">
+        <v>3398390</v>
+      </c>
+      <c r="G20">
+        <v>127.4149998474121</v>
+      </c>
+      <c r="H20">
+        <v>123.7573337300618</v>
+      </c>
+      <c r="I20">
+        <v>122.0329503631592</v>
+      </c>
+      <c r="J20">
+        <v>119.0048004150391</v>
+      </c>
+      <c r="K20">
+        <v>9.75969409942627</v>
+      </c>
+      <c r="L20">
+        <v>149.75</v>
+      </c>
+      <c r="M20">
+        <v>116.910858301572</v>
+      </c>
+      <c r="N20">
+        <v>9.06</v>
+      </c>
+      <c r="O20">
+        <v>7.09</v>
+      </c>
+      <c r="P20">
+        <v>6.09</v>
+      </c>
+      <c r="Q20">
+        <v>5.32</v>
+      </c>
+      <c r="R20">
+        <v>4477000000</v>
+      </c>
+      <c r="S20">
+        <v>3321000000</v>
+      </c>
+      <c r="T20">
+        <v>2724000000</v>
+      </c>
+      <c r="U20">
+        <v>2226000000</v>
+      </c>
+      <c r="V20" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
+      <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D21" t="s">
+        <v>214</v>
+      </c>
+      <c r="E21">
+        <v>83.91999816894531</v>
+      </c>
+      <c r="F21">
+        <v>755123.3333333334</v>
+      </c>
+      <c r="G21">
+        <v>75.58839950561523</v>
+      </c>
+      <c r="H21">
+        <v>65.65753303527832</v>
+      </c>
+      <c r="I21">
+        <v>60.77389982223511</v>
+      </c>
+      <c r="J21">
+        <v>56.02249988555909</v>
+      </c>
+      <c r="K21">
+        <v>5.739999771118164</v>
+      </c>
+      <c r="L21">
+        <v>87.15000152587891</v>
+      </c>
+      <c r="M21">
+        <v>116.5486099173818</v>
+      </c>
+      <c r="N21">
+        <v>0.39</v>
+      </c>
+      <c r="O21">
+        <v>0.99</v>
+      </c>
+      <c r="P21">
+        <v>0.97</v>
+      </c>
+      <c r="Q21">
+        <v>1.12</v>
+      </c>
+      <c r="R21">
+        <v>28000000</v>
+      </c>
+      <c r="S21">
+        <v>72000000</v>
+      </c>
+      <c r="T21">
+        <v>72000000</v>
+      </c>
+      <c r="U21">
+        <v>82000000</v>
+      </c>
+      <c r="V21" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D22" t="s">
+        <v>215</v>
+      </c>
+      <c r="E22">
+        <v>85.58000183105469</v>
+      </c>
+      <c r="F22">
+        <v>845063.3333333334</v>
+      </c>
+      <c r="G22">
+        <v>75.11779998779296</v>
+      </c>
+      <c r="H22">
+        <v>73.17980010986328</v>
+      </c>
+      <c r="I22">
+        <v>70.67280002593994</v>
+      </c>
+      <c r="J22">
+        <v>67.82844993591308</v>
+      </c>
+      <c r="K22">
+        <v>35.33981704711914</v>
+      </c>
+      <c r="L22">
+        <v>101.9899978637695</v>
+      </c>
+      <c r="M22">
+        <v>116.4343472947386</v>
+      </c>
+      <c r="N22">
+        <v>0.33</v>
+      </c>
+      <c r="O22">
+        <v>0.42</v>
+      </c>
+      <c r="P22">
+        <v>0.42</v>
+      </c>
+      <c r="Q22">
+        <v>0.42</v>
+      </c>
+      <c r="R22">
+        <v>69083000</v>
+      </c>
+      <c r="S22">
+        <v>88946000</v>
+      </c>
+      <c r="T22">
+        <v>87856000</v>
+      </c>
+      <c r="U22">
+        <v>89082000</v>
+      </c>
+      <c r="V22" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
+      <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
+        <v>125</v>
+      </c>
+      <c r="C23" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23" t="s">
+        <v>216</v>
+      </c>
+      <c r="E23">
+        <v>69.33999633789062</v>
+      </c>
+      <c r="F23">
+        <v>1992653.333333333</v>
+      </c>
+      <c r="G23">
+        <v>64.20479988098144</v>
+      </c>
+      <c r="H23">
+        <v>47.77280002593994</v>
+      </c>
+      <c r="I23">
+        <v>44.94285004615784</v>
+      </c>
+      <c r="J23">
+        <v>40.79169657707214</v>
+      </c>
+      <c r="K23">
+        <v>0.6502050161361694</v>
+      </c>
+      <c r="L23">
+        <v>73.73999786376953</v>
+      </c>
+      <c r="M23">
+        <v>116.1551532574323</v>
+      </c>
+      <c r="N23">
+        <v>1.13</v>
+      </c>
+      <c r="O23">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="P23">
+        <v>0.13</v>
+      </c>
+      <c r="Q23">
+        <v>0.28</v>
+      </c>
+      <c r="R23">
+        <v>131000000</v>
+      </c>
+      <c r="S23">
+        <v>-94000000</v>
+      </c>
+      <c r="T23">
+        <v>14000000</v>
+      </c>
+      <c r="U23">
+        <v>33000000</v>
+      </c>
+      <c r="V23" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
+      <c r="A24" t="s">
         <v>44</v>
       </c>
-      <c r="E7">
+      <c r="B24" t="s">
+        <v>133</v>
+      </c>
+      <c r="C24" t="s">
+        <v>152</v>
+      </c>
+      <c r="D24" t="s">
+        <v>217</v>
+      </c>
+      <c r="E24">
+        <v>28.60000038146973</v>
+      </c>
+      <c r="F24">
+        <v>273066.6666666667</v>
+      </c>
+      <c r="G24">
+        <v>25.9873999786377</v>
+      </c>
+      <c r="H24">
+        <v>19.7976000658671</v>
+      </c>
+      <c r="I24">
+        <v>18.60350004673004</v>
+      </c>
+      <c r="J24">
+        <v>16.72505004405975</v>
+      </c>
+      <c r="K24">
+        <v>2.950000047683716</v>
+      </c>
+      <c r="L24">
+        <v>31.03000068664551</v>
+      </c>
+      <c r="M24">
+        <v>115.6351988252011</v>
+      </c>
+      <c r="N24">
+        <v>1.02</v>
+      </c>
+      <c r="O24">
+        <v>0.42</v>
+      </c>
+      <c r="P24">
+        <v>0.54</v>
+      </c>
+      <c r="Q24">
+        <v>0.93</v>
+      </c>
+      <c r="R24">
+        <v>50800000</v>
+      </c>
+      <c r="S24">
+        <v>20800000</v>
+      </c>
+      <c r="T24">
+        <v>26900000</v>
+      </c>
+      <c r="U24">
+        <v>46800000</v>
+      </c>
+      <c r="V24" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
+      <c r="A25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" t="s">
+        <v>150</v>
+      </c>
+      <c r="D25" t="s">
+        <v>218</v>
+      </c>
+      <c r="E25">
+        <v>92.97000122070312</v>
+      </c>
+      <c r="F25">
+        <v>344083.3333333333</v>
+      </c>
+      <c r="G25">
+        <v>80.88990005493164</v>
+      </c>
+      <c r="H25">
+        <v>75.93363321940105</v>
+      </c>
+      <c r="I25">
+        <v>72.08847484588622</v>
+      </c>
+      <c r="J25">
+        <v>69.41554983139038</v>
+      </c>
+      <c r="K25">
+        <v>5.980000019073486</v>
+      </c>
+      <c r="L25">
+        <v>92.97000122070312</v>
+      </c>
+      <c r="M25">
+        <v>115.5107720195065</v>
+      </c>
+      <c r="N25">
+        <v>1.03</v>
+      </c>
+      <c r="O25">
+        <v>0.44</v>
+      </c>
+      <c r="P25">
+        <v>1.36</v>
+      </c>
+      <c r="Q25">
+        <v>0.64</v>
+      </c>
+      <c r="R25">
+        <v>61067000</v>
+      </c>
+      <c r="S25">
+        <v>26262000</v>
+      </c>
+      <c r="T25">
+        <v>62864000</v>
+      </c>
+      <c r="U25">
+        <v>54949000</v>
+      </c>
+      <c r="V25" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
+      <c r="A26" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" t="s">
+        <v>153</v>
+      </c>
+      <c r="D26" t="s">
+        <v>219</v>
+      </c>
+      <c r="E26">
+        <v>22.70999908447266</v>
+      </c>
+      <c r="F26">
+        <v>562033.3333333334</v>
+      </c>
+      <c r="G26">
+        <v>20.37940002441406</v>
+      </c>
+      <c r="H26">
+        <v>18.24786668777466</v>
+      </c>
+      <c r="I26">
+        <v>17.56880001544953</v>
+      </c>
+      <c r="J26">
+        <v>16.74490004062653</v>
+      </c>
+      <c r="K26">
+        <v>6.340000152587891</v>
+      </c>
+      <c r="L26">
+        <v>22.72999954223633</v>
+      </c>
+      <c r="M26">
+        <v>115.314608805732</v>
+      </c>
+      <c r="N26">
+        <v>0.2</v>
+      </c>
+      <c r="O26">
+        <v>0.32</v>
+      </c>
+      <c r="P26">
+        <v>0.24</v>
+      </c>
+      <c r="Q26">
+        <v>0.25</v>
+      </c>
+      <c r="R26">
+        <v>4800000</v>
+      </c>
+      <c r="S26">
+        <v>7500000</v>
+      </c>
+      <c r="T26">
+        <v>5500000</v>
+      </c>
+      <c r="U26">
+        <v>5600000</v>
+      </c>
+      <c r="V26" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
+      <c r="A27" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" t="s">
+        <v>151</v>
+      </c>
+      <c r="D27" t="s">
+        <v>220</v>
+      </c>
+      <c r="E27">
+        <v>412.9500122070312</v>
+      </c>
+      <c r="F27">
+        <v>471160</v>
+      </c>
+      <c r="G27">
+        <v>380.5465985107422</v>
+      </c>
+      <c r="H27">
+        <v>312.4603329467773</v>
+      </c>
+      <c r="I27">
+        <v>291.8582997131348</v>
+      </c>
+      <c r="J27">
+        <v>269.7179996490478</v>
+      </c>
+      <c r="K27">
+        <v>4.533332824707031</v>
+      </c>
+      <c r="L27">
+        <v>429.0599975585938</v>
+      </c>
+      <c r="M27">
+        <v>113.8476688478566</v>
+      </c>
+      <c r="N27">
+        <v>3.67</v>
+      </c>
+      <c r="O27">
+        <v>2.65</v>
+      </c>
+      <c r="P27">
+        <v>2.85</v>
+      </c>
+      <c r="Q27">
+        <v>3.42</v>
+      </c>
+      <c r="R27">
+        <v>97891000</v>
+      </c>
+      <c r="S27">
+        <v>70862000</v>
+      </c>
+      <c r="T27">
+        <v>76097000</v>
+      </c>
+      <c r="U27">
+        <v>91319000</v>
+      </c>
+      <c r="V27" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
+      <c r="A28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" t="s">
+        <v>136</v>
+      </c>
+      <c r="D28" t="s">
+        <v>221</v>
+      </c>
+      <c r="E28">
+        <v>217.9400024414062</v>
+      </c>
+      <c r="F28">
+        <v>355763.3333333333</v>
+      </c>
+      <c r="G28">
+        <v>197.5399993896484</v>
+      </c>
+      <c r="H28">
+        <v>172.4967333984375</v>
+      </c>
+      <c r="I28">
+        <v>166.7955996704102</v>
+      </c>
+      <c r="J28">
+        <v>158.170249671936</v>
+      </c>
+      <c r="K28">
+        <v>0.9346818327903748</v>
+      </c>
+      <c r="L28">
+        <v>223.4100036621094</v>
+      </c>
+      <c r="M28">
+        <v>112.777743452436</v>
+      </c>
+      <c r="N28">
+        <v>2.16</v>
+      </c>
+      <c r="O28">
+        <v>2.63</v>
+      </c>
+      <c r="P28">
+        <v>2.32</v>
+      </c>
+      <c r="Q28">
+        <v>2.95</v>
+      </c>
+      <c r="R28">
+        <v>105772000</v>
+      </c>
+      <c r="S28">
+        <v>126300000</v>
+      </c>
+      <c r="T28">
+        <v>111473000</v>
+      </c>
+      <c r="U28">
+        <v>140595000</v>
+      </c>
+      <c r="V28" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
+      <c r="A29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" t="s">
+        <v>135</v>
+      </c>
+      <c r="C29" t="s">
+        <v>154</v>
+      </c>
+      <c r="D29" t="s">
+        <v>222</v>
+      </c>
+      <c r="E29">
+        <v>30.01000022888184</v>
+      </c>
+      <c r="F29">
+        <v>3402133.333333333</v>
+      </c>
+      <c r="G29">
+        <v>27.60759998321533</v>
+      </c>
+      <c r="H29">
+        <v>25.0656666692098</v>
+      </c>
+      <c r="I29">
+        <v>24.65085000991821</v>
+      </c>
+      <c r="J29">
+        <v>23.93190002441406</v>
+      </c>
+      <c r="K29">
+        <v>10.74393081665039</v>
+      </c>
+      <c r="L29">
+        <v>30.69000053405762</v>
+      </c>
+      <c r="M29">
+        <v>112.6622580188997</v>
+      </c>
+      <c r="N29">
+        <v>1.51</v>
+      </c>
+      <c r="O29">
+        <v>-0.73</v>
+      </c>
+      <c r="P29">
+        <v>1.71</v>
+      </c>
+      <c r="Q29">
+        <v>1.17</v>
+      </c>
+      <c r="R29">
+        <v>668000000</v>
+      </c>
+      <c r="S29">
+        <v>-246000000</v>
+      </c>
+      <c r="T29">
+        <v>699000000</v>
+      </c>
+      <c r="U29">
+        <v>476000000</v>
+      </c>
+      <c r="V29" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
+      <c r="A30" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" t="s">
+        <v>125</v>
+      </c>
+      <c r="C30" t="s">
+        <v>155</v>
+      </c>
+      <c r="D30" t="s">
+        <v>223</v>
+      </c>
+      <c r="E30">
+        <v>35.29000091552734</v>
+      </c>
+      <c r="F30">
+        <v>837543.3333333334</v>
+      </c>
+      <c r="G30">
+        <v>32.50729972839355</v>
+      </c>
+      <c r="H30">
+        <v>28.27216660817464</v>
+      </c>
+      <c r="I30">
+        <v>25.71932494163513</v>
+      </c>
+      <c r="J30">
+        <v>23.90032495975494</v>
+      </c>
+      <c r="K30">
+        <v>4.052896976470947</v>
+      </c>
+      <c r="L30">
+        <v>36.36000061035156</v>
+      </c>
+      <c r="M30">
+        <v>112.3906411292103</v>
+      </c>
+      <c r="N30">
+        <v>-0.23</v>
+      </c>
+      <c r="O30">
+        <v>0.2</v>
+      </c>
+      <c r="P30">
+        <v>0.22</v>
+      </c>
+      <c r="Q30">
+        <v>0.46</v>
+      </c>
+      <c r="R30">
+        <v>-16058000</v>
+      </c>
+      <c r="S30">
+        <v>26801000</v>
+      </c>
+      <c r="T30">
+        <v>29397000</v>
+      </c>
+      <c r="U30">
+        <v>54753000</v>
+      </c>
+      <c r="V30" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
+      <c r="A31" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" t="s">
+        <v>156</v>
+      </c>
+      <c r="D31" t="s">
+        <v>224</v>
+      </c>
+      <c r="E31">
+        <v>13.02000045776367</v>
+      </c>
+      <c r="F31">
+        <v>583143.3333333334</v>
+      </c>
+      <c r="G31">
+        <v>11.9457999420166</v>
+      </c>
+      <c r="H31">
+        <v>8.97206666469574</v>
+      </c>
+      <c r="I31">
+        <v>7.499149996042251</v>
+      </c>
+      <c r="J31">
+        <v>6.583499997854233</v>
+      </c>
+      <c r="K31">
+        <v>0.09375</v>
+      </c>
+      <c r="L31">
+        <v>14.22999954223633</v>
+      </c>
+      <c r="M31">
+        <v>112.2457426124794</v>
+      </c>
+      <c r="N31">
+        <v>-0.12</v>
+      </c>
+      <c r="O31">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="P31">
+        <v>-0.08</v>
+      </c>
+      <c r="Q31">
+        <v>-0.03</v>
+      </c>
+      <c r="R31">
+        <v>-3327000</v>
+      </c>
+      <c r="S31">
+        <v>-1960000</v>
+      </c>
+      <c r="T31">
+        <v>-2116000</v>
+      </c>
+      <c r="U31">
+        <v>-815000</v>
+      </c>
+      <c r="V31" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
+      <c r="A32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" t="s">
+        <v>131</v>
+      </c>
+      <c r="C32" t="s">
+        <v>157</v>
+      </c>
+      <c r="D32" t="s">
+        <v>225</v>
+      </c>
+      <c r="E32">
+        <v>105.8300018310547</v>
+      </c>
+      <c r="F32">
+        <v>336816.6666666667</v>
+      </c>
+      <c r="G32">
+        <v>97.46539978027344</v>
+      </c>
+      <c r="H32">
+        <v>79.20193356831868</v>
+      </c>
+      <c r="I32">
+        <v>77.12615018844605</v>
+      </c>
+      <c r="J32">
+        <v>72.72415025711059</v>
+      </c>
+      <c r="K32">
+        <v>11.37919998168945</v>
+      </c>
+      <c r="L32">
+        <v>111.7799987792969</v>
+      </c>
+      <c r="M32">
+        <v>111.8558510564928</v>
+      </c>
+      <c r="N32">
+        <v>5.52</v>
+      </c>
+      <c r="O32">
+        <v>2.95</v>
+      </c>
+      <c r="P32">
+        <v>2.43</v>
+      </c>
+      <c r="Q32">
+        <v>3.67</v>
+      </c>
+      <c r="R32">
+        <v>219587000</v>
+      </c>
+      <c r="S32">
+        <v>117360000</v>
+      </c>
+      <c r="T32">
+        <v>96733000</v>
+      </c>
+      <c r="U32">
+        <v>146320000</v>
+      </c>
+      <c r="V32" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
+      <c r="A33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33" t="s">
+        <v>142</v>
+      </c>
+      <c r="D33" t="s">
+        <v>226</v>
+      </c>
+      <c r="E33">
+        <v>39.90999984741211</v>
+      </c>
+      <c r="F33">
+        <v>891680</v>
+      </c>
+      <c r="G33">
+        <v>36.5715998840332</v>
+      </c>
+      <c r="H33">
+        <v>34.22126660664876</v>
+      </c>
+      <c r="I33">
+        <v>31.99829997062683</v>
+      </c>
+      <c r="J33">
+        <v>30.51949998855591</v>
+      </c>
+      <c r="K33">
+        <v>14.4399995803833</v>
+      </c>
+      <c r="L33">
+        <v>40.84000015258789</v>
+      </c>
+      <c r="M33">
+        <v>111.7263230745141</v>
+      </c>
+      <c r="N33">
+        <v>0.25</v>
+      </c>
+      <c r="O33">
+        <v>0.33</v>
+      </c>
+      <c r="P33">
+        <v>0.23</v>
+      </c>
+      <c r="Q33">
+        <v>0.33</v>
+      </c>
+      <c r="R33">
+        <v>33700000</v>
+      </c>
+      <c r="S33">
+        <v>44200000</v>
+      </c>
+      <c r="T33">
+        <v>30900000</v>
+      </c>
+      <c r="U33">
+        <v>44300000</v>
+      </c>
+      <c r="V33" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22">
+      <c r="A34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" t="s">
+        <v>126</v>
+      </c>
+      <c r="C34" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" t="s">
+        <v>227</v>
+      </c>
+      <c r="E34">
+        <v>182.5099945068359</v>
+      </c>
+      <c r="F34">
+        <v>540810</v>
+      </c>
+      <c r="G34">
+        <v>168.9504000854492</v>
+      </c>
+      <c r="H34">
+        <v>153.9550002034505</v>
+      </c>
+      <c r="I34">
+        <v>150.678600769043</v>
+      </c>
+      <c r="J34">
+        <v>147.3883506774902</v>
+      </c>
+      <c r="K34">
+        <v>7.301512241363525</v>
+      </c>
+      <c r="L34">
+        <v>184.4799957275391</v>
+      </c>
+      <c r="M34">
+        <v>111.3789935550132</v>
+      </c>
+      <c r="N34">
+        <v>0.42</v>
+      </c>
+      <c r="O34">
+        <v>0.48</v>
+      </c>
+      <c r="P34">
+        <v>1.67</v>
+      </c>
+      <c r="Q34">
+        <v>2.72</v>
+      </c>
+      <c r="R34">
+        <v>50400000</v>
+      </c>
+      <c r="S34">
+        <v>57500000</v>
+      </c>
+      <c r="T34">
+        <v>198500000</v>
+      </c>
+      <c r="U34">
+        <v>324100000</v>
+      </c>
+      <c r="V34" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22">
+      <c r="A35" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" t="s">
+        <v>126</v>
+      </c>
+      <c r="C35" t="s">
+        <v>158</v>
+      </c>
+      <c r="D35" t="s">
+        <v>228</v>
+      </c>
+      <c r="E35">
+        <v>146.1300048828125</v>
+      </c>
+      <c r="F35">
+        <v>301170</v>
+      </c>
+      <c r="G35">
+        <v>135.316600189209</v>
+      </c>
+      <c r="H35">
+        <v>125.713866780599</v>
+      </c>
+      <c r="I35">
+        <v>123.146600112915</v>
+      </c>
+      <c r="J35">
+        <v>121.9746002197266</v>
+      </c>
+      <c r="K35">
+        <v>10.75</v>
+      </c>
+      <c r="L35">
+        <v>160.0200042724609</v>
+      </c>
+      <c r="M35">
+        <v>110.5926902412967</v>
+      </c>
+      <c r="N35">
+        <v>0.71</v>
+      </c>
+      <c r="O35">
+        <v>0.74</v>
+      </c>
+      <c r="P35">
+        <v>0.77</v>
+      </c>
+      <c r="Q35">
+        <v>0.95</v>
+      </c>
+      <c r="R35">
+        <v>27660000</v>
+      </c>
+      <c r="S35">
+        <v>28326000</v>
+      </c>
+      <c r="T35">
+        <v>29105000</v>
+      </c>
+      <c r="U35">
+        <v>35382000</v>
+      </c>
+      <c r="V35" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22">
+      <c r="A36" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" t="s">
+        <v>125</v>
+      </c>
+      <c r="C36" t="s">
+        <v>151</v>
+      </c>
+      <c r="D36" t="s">
+        <v>229</v>
+      </c>
+      <c r="E36">
+        <v>408.7000122070312</v>
+      </c>
+      <c r="F36">
+        <v>867000</v>
+      </c>
+      <c r="G36">
+        <v>384.044799194336</v>
+      </c>
+      <c r="H36">
+        <v>348.6859999593099</v>
+      </c>
+      <c r="I36">
+        <v>335.7830996704101</v>
+      </c>
+      <c r="J36">
+        <v>321.6509498596191</v>
+      </c>
+      <c r="K36">
+        <v>0.6462651491165161</v>
+      </c>
+      <c r="L36">
+        <v>427.5899963378906</v>
+      </c>
+      <c r="M36">
+        <v>110.4523000389414</v>
+      </c>
+      <c r="N36">
+        <v>3.36</v>
+      </c>
+      <c r="O36">
+        <v>2.92</v>
+      </c>
+      <c r="P36">
+        <v>2.58</v>
+      </c>
+      <c r="Q36">
+        <v>2.65</v>
+      </c>
+      <c r="R36">
+        <v>377401000</v>
+      </c>
+      <c r="S36">
+        <v>323929000</v>
+      </c>
+      <c r="T36">
+        <v>285038000</v>
+      </c>
+      <c r="U36">
+        <v>292362000</v>
+      </c>
+      <c r="V36" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22">
+      <c r="A37" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" t="s">
+        <v>129</v>
+      </c>
+      <c r="C37" t="s">
+        <v>159</v>
+      </c>
+      <c r="D37" t="s">
+        <v>230</v>
+      </c>
+      <c r="E37">
+        <v>70.98000335693359</v>
+      </c>
+      <c r="F37">
+        <v>321973.3333333333</v>
+      </c>
+      <c r="G37">
+        <v>65.83360008239747</v>
+      </c>
+      <c r="H37">
+        <v>59.26800015767415</v>
+      </c>
+      <c r="I37">
+        <v>57.94370010375977</v>
+      </c>
+      <c r="J37">
+        <v>56.22815019607544</v>
+      </c>
+      <c r="K37">
+        <v>4.32618522644043</v>
+      </c>
+      <c r="L37">
+        <v>74.94632720947266</v>
+      </c>
+      <c r="M37">
+        <v>110.4124233963192</v>
+      </c>
+      <c r="N37">
+        <v>66.89</v>
+      </c>
+      <c r="O37">
+        <v>75.080879</v>
+      </c>
+      <c r="P37">
+        <v>57.68</v>
+      </c>
+      <c r="Q37">
+        <v>84.22</v>
+      </c>
+      <c r="R37">
+        <v>11128000000</v>
+      </c>
+      <c r="S37">
+        <v>12471000000</v>
+      </c>
+      <c r="T37">
+        <v>9601000000</v>
+      </c>
+      <c r="U37">
+        <v>14025000000</v>
+      </c>
+      <c r="V37" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22">
+      <c r="A38" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" t="s">
+        <v>128</v>
+      </c>
+      <c r="C38" t="s">
+        <v>139</v>
+      </c>
+      <c r="D38" t="s">
+        <v>231</v>
+      </c>
+      <c r="E38">
+        <v>46.18000030517578</v>
+      </c>
+      <c r="F38">
+        <v>2155346.666666667</v>
+      </c>
+      <c r="G38">
+        <v>43.72720016479492</v>
+      </c>
+      <c r="H38">
+        <v>41.33446657816569</v>
+      </c>
+      <c r="I38">
+        <v>41.13819992065429</v>
+      </c>
+      <c r="J38">
+        <v>40.74434991836548</v>
+      </c>
+      <c r="K38">
+        <v>4.269999980926514</v>
+      </c>
+      <c r="L38">
+        <v>50.28766250610352</v>
+      </c>
+      <c r="M38">
+        <v>110.1128008794736</v>
+      </c>
+      <c r="N38">
+        <v>8.4</v>
+      </c>
+      <c r="O38">
+        <v>4.86</v>
+      </c>
+      <c r="P38">
+        <v>2.86</v>
+      </c>
+      <c r="Q38">
+        <v>7.88</v>
+      </c>
+      <c r="R38">
+        <v>1056400000</v>
+      </c>
+      <c r="S38">
+        <v>637800000</v>
+      </c>
+      <c r="T38">
+        <v>382100000</v>
+      </c>
+      <c r="U38">
+        <v>1020400000</v>
+      </c>
+      <c r="V38" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22">
+      <c r="A39" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" t="s">
+        <v>128</v>
+      </c>
+      <c r="C39" t="s">
+        <v>160</v>
+      </c>
+      <c r="D39" t="s">
+        <v>232</v>
+      </c>
+      <c r="E39">
+        <v>35.72999954223633</v>
+      </c>
+      <c r="F39">
+        <v>4017723.333333333</v>
+      </c>
+      <c r="G39">
+        <v>32.6857999420166</v>
+      </c>
+      <c r="H39">
+        <v>29.00773333231608</v>
+      </c>
+      <c r="I39">
+        <v>27.60040000915527</v>
+      </c>
+      <c r="J39">
+        <v>26.5010000038147</v>
+      </c>
+      <c r="K39">
+        <v>1.243403434753418</v>
+      </c>
+      <c r="L39">
+        <v>44.90747833251953</v>
+      </c>
+      <c r="M39">
+        <v>110.0163037460615</v>
+      </c>
+      <c r="N39">
+        <v>-0.05</v>
+      </c>
+      <c r="O39">
+        <v>-0.04</v>
+      </c>
+      <c r="P39">
+        <v>0.27</v>
+      </c>
+      <c r="Q39">
+        <v>0.03</v>
+      </c>
+      <c r="R39">
+        <v>-19530000</v>
+      </c>
+      <c r="S39">
+        <v>-15417000</v>
+      </c>
+      <c r="T39">
+        <v>118969000</v>
+      </c>
+      <c r="U39">
+        <v>13693000</v>
+      </c>
+      <c r="V39" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22">
+      <c r="A40" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" t="s">
+        <v>125</v>
+      </c>
+      <c r="C40" t="s">
+        <v>151</v>
+      </c>
+      <c r="D40" t="s">
+        <v>233</v>
+      </c>
+      <c r="E40">
+        <v>127.4199981689453</v>
+      </c>
+      <c r="F40">
+        <v>320696.6666666667</v>
+      </c>
+      <c r="G40">
+        <v>120.3039999389649</v>
+      </c>
+      <c r="H40">
+        <v>116.5299999491374</v>
+      </c>
+      <c r="I40">
+        <v>113.2896500396728</v>
+      </c>
+      <c r="J40">
+        <v>109.6499000549316</v>
+      </c>
+      <c r="K40">
+        <v>1.774946093559265</v>
+      </c>
+      <c r="L40">
+        <v>132.9199981689453</v>
+      </c>
+      <c r="M40">
+        <v>109.9697141025042</v>
+      </c>
+      <c r="N40">
+        <v>2.72</v>
+      </c>
+      <c r="O40">
+        <v>1.75</v>
+      </c>
+      <c r="P40">
+        <v>1.27</v>
+      </c>
+      <c r="Q40">
+        <v>1.47</v>
+      </c>
+      <c r="R40">
+        <v>245190000</v>
+      </c>
+      <c r="S40">
+        <v>153494000</v>
+      </c>
+      <c r="T40">
+        <v>111918000</v>
+      </c>
+      <c r="U40">
+        <v>128234000</v>
+      </c>
+      <c r="V40" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22">
+      <c r="A41" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" t="s">
+        <v>127</v>
+      </c>
+      <c r="C41" t="s">
+        <v>161</v>
+      </c>
+      <c r="D41" t="s">
+        <v>234</v>
+      </c>
+      <c r="E41">
+        <v>3026.389892578125</v>
+      </c>
+      <c r="F41">
+        <v>313700</v>
+      </c>
+      <c r="G41">
+        <v>2896.00498046875</v>
+      </c>
+      <c r="H41">
+        <v>2673.209069010416</v>
+      </c>
+      <c r="I41">
+        <v>2514.58174987793</v>
+      </c>
+      <c r="J41">
+        <v>2383.938450927734</v>
+      </c>
+      <c r="K41">
+        <v>6.599999904632568</v>
+      </c>
+      <c r="L41">
+        <v>3243.010009765625</v>
+      </c>
+      <c r="M41">
+        <v>109.6207351585819</v>
+      </c>
+      <c r="N41">
+        <v>41.98</v>
+      </c>
+      <c r="O41">
+        <v>31.92</v>
+      </c>
+      <c r="P41">
+        <v>7</v>
+      </c>
+      <c r="Q41">
+        <v>34.89</v>
+      </c>
+      <c r="R41">
+        <v>1666000000</v>
+      </c>
+      <c r="S41">
+        <v>1235000000</v>
+      </c>
+      <c r="T41">
+        <v>266000000</v>
+      </c>
+      <c r="U41">
+        <v>1290000000</v>
+      </c>
+      <c r="V41" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22">
+      <c r="A42" t="s">
+        <v>62</v>
+      </c>
+      <c r="B42" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42" t="s">
+        <v>136</v>
+      </c>
+      <c r="D42" t="s">
+        <v>235</v>
+      </c>
+      <c r="E42">
+        <v>33.88999938964844</v>
+      </c>
+      <c r="F42">
+        <v>264863.3333333333</v>
+      </c>
+      <c r="G42">
+        <v>31.46980003356934</v>
+      </c>
+      <c r="H42">
+        <v>27.72813334147136</v>
+      </c>
+      <c r="I42">
+        <v>26.29460000991821</v>
+      </c>
+      <c r="J42">
+        <v>24.80269998550415</v>
+      </c>
+      <c r="K42">
+        <v>2.853151798248291</v>
+      </c>
+      <c r="L42">
+        <v>40.95831680297852</v>
+      </c>
+      <c r="M42">
+        <v>109.4152720123788</v>
+      </c>
+      <c r="N42">
+        <v>0.8</v>
+      </c>
+      <c r="O42">
+        <v>0.77</v>
+      </c>
+      <c r="P42">
+        <v>0.02</v>
+      </c>
+      <c r="Q42">
+        <v>0.72</v>
+      </c>
+      <c r="R42">
+        <v>43040000</v>
+      </c>
+      <c r="S42">
+        <v>41501000</v>
+      </c>
+      <c r="T42">
+        <v>1310000</v>
+      </c>
+      <c r="U42">
+        <v>39032000</v>
+      </c>
+      <c r="V42" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22">
+      <c r="A43" t="s">
+        <v>63</v>
+      </c>
+      <c r="B43" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" t="s">
+        <v>162</v>
+      </c>
+      <c r="D43" t="s">
+        <v>236</v>
+      </c>
+      <c r="E43">
+        <v>53.47999954223633</v>
+      </c>
+      <c r="F43">
+        <v>530996.6666666666</v>
+      </c>
+      <c r="G43">
+        <v>51.43739982604981</v>
+      </c>
+      <c r="H43">
+        <v>44.0011333211263</v>
+      </c>
+      <c r="I43">
+        <v>43.40879997253418</v>
+      </c>
+      <c r="J43">
+        <v>42.13769998550415</v>
+      </c>
+      <c r="K43">
+        <v>2.721946477890015</v>
+      </c>
+      <c r="L43">
+        <v>53.91999816894531</v>
+      </c>
+      <c r="M43">
+        <v>108.7500257791994</v>
+      </c>
+      <c r="N43">
+        <v>3.41</v>
+      </c>
+      <c r="O43">
+        <v>0.25</v>
+      </c>
+      <c r="P43">
+        <v>-2</v>
+      </c>
+      <c r="Q43">
+        <v>4.36</v>
+      </c>
+      <c r="R43">
+        <v>312600000</v>
+      </c>
+      <c r="S43">
+        <v>32572000</v>
+      </c>
+      <c r="T43">
+        <v>-155994000</v>
+      </c>
+      <c r="U43">
+        <v>355363000</v>
+      </c>
+      <c r="V43" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22">
+      <c r="A44" t="s">
+        <v>64</v>
+      </c>
+      <c r="B44" t="s">
+        <v>128</v>
+      </c>
+      <c r="C44" t="s">
+        <v>163</v>
+      </c>
+      <c r="D44" t="s">
+        <v>237</v>
+      </c>
+      <c r="E44">
+        <v>84.08999633789062</v>
+      </c>
+      <c r="F44">
+        <v>1465496.666666667</v>
+      </c>
+      <c r="G44">
+        <v>79.03499923706055</v>
+      </c>
+      <c r="H44">
+        <v>75.13439966837565</v>
+      </c>
+      <c r="I44">
+        <v>74.43144969940185</v>
+      </c>
+      <c r="J44">
+        <v>72.81244983673096</v>
+      </c>
+      <c r="K44">
+        <v>4.560298919677734</v>
+      </c>
+      <c r="L44">
+        <v>95.13722229003906</v>
+      </c>
+      <c r="M44">
+        <v>108.6006414279477</v>
+      </c>
+      <c r="N44">
+        <v>0.84</v>
+      </c>
+      <c r="O44">
+        <v>1.38</v>
+      </c>
+      <c r="P44">
+        <v>0.03</v>
+      </c>
+      <c r="Q44">
+        <v>1.44</v>
+      </c>
+      <c r="R44">
+        <v>193100000</v>
+      </c>
+      <c r="S44">
+        <v>318000000</v>
+      </c>
+      <c r="T44">
+        <v>497000000</v>
+      </c>
+      <c r="U44">
+        <v>329300000</v>
+      </c>
+      <c r="V44" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22">
+      <c r="A45" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" t="s">
+        <v>125</v>
+      </c>
+      <c r="C45" t="s">
+        <v>164</v>
+      </c>
+      <c r="D45" t="s">
+        <v>238</v>
+      </c>
+      <c r="E45">
+        <v>45.0099983215332</v>
+      </c>
+      <c r="F45">
+        <v>380413.3333333333</v>
+      </c>
+      <c r="G45">
+        <v>42.39179977416993</v>
+      </c>
+      <c r="H45">
+        <v>37.83453333536784</v>
+      </c>
+      <c r="I45">
+        <v>36.30459997177124</v>
+      </c>
+      <c r="J45">
+        <v>34.57114999771118</v>
+      </c>
+      <c r="K45">
+        <v>6.900000095367432</v>
+      </c>
+      <c r="L45">
+        <v>47.5</v>
+      </c>
+      <c r="M45">
+        <v>108.5280400573414</v>
+      </c>
+      <c r="N45">
+        <v>0.98</v>
+      </c>
+      <c r="O45">
+        <v>1.16</v>
+      </c>
+      <c r="P45">
+        <v>0.7</v>
+      </c>
+      <c r="Q45">
+        <v>0.36</v>
+      </c>
+      <c r="R45">
+        <v>23201000</v>
+      </c>
+      <c r="S45">
+        <v>27570000</v>
+      </c>
+      <c r="T45">
+        <v>16589000</v>
+      </c>
+      <c r="U45">
+        <v>8642000</v>
+      </c>
+      <c r="V45" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22">
+      <c r="A46" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" t="s">
+        <v>128</v>
+      </c>
+      <c r="C46" t="s">
+        <v>149</v>
+      </c>
+      <c r="D46" t="s">
+        <v>239</v>
+      </c>
+      <c r="E46">
+        <v>35.31000137329102</v>
+      </c>
+      <c r="F46">
+        <v>1291286.666666667</v>
+      </c>
+      <c r="G46">
+        <v>33.29990009307861</v>
+      </c>
+      <c r="H46">
+        <v>30.09536668141683</v>
+      </c>
+      <c r="I46">
+        <v>30.06122501373291</v>
+      </c>
+      <c r="J46">
+        <v>28.98610001564026</v>
+      </c>
+      <c r="K46">
+        <v>3.019999980926514</v>
+      </c>
+      <c r="L46">
+        <v>45.52999877929688</v>
+      </c>
+      <c r="M46">
+        <v>108.5040302130104</v>
+      </c>
+      <c r="N46">
+        <v>0.11</v>
+      </c>
+      <c r="O46">
+        <v>0.33</v>
+      </c>
+      <c r="P46">
+        <v>0.31</v>
+      </c>
+      <c r="Q46">
+        <v>0.48</v>
+      </c>
+      <c r="R46">
+        <v>23068000</v>
+      </c>
+      <c r="S46">
+        <v>67857000</v>
+      </c>
+      <c r="T46">
+        <v>63532000</v>
+      </c>
+      <c r="U46">
+        <v>95797000</v>
+      </c>
+      <c r="V46" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22">
+      <c r="A47" t="s">
+        <v>67</v>
+      </c>
+      <c r="B47" t="s">
+        <v>127</v>
+      </c>
+      <c r="C47" t="s">
+        <v>165</v>
+      </c>
+      <c r="D47" t="s">
+        <v>240</v>
+      </c>
+      <c r="E47">
         <v>26.59000015258789</v>
       </c>
-      <c r="F7">
+      <c r="F47">
         <v>300946.6666666667</v>
       </c>
-      <c r="G7">
+      <c r="G47">
         <v>25.76240001678467</v>
       </c>
-      <c r="H7">
+      <c r="H47">
         <v>18.18693333307902</v>
       </c>
-      <c r="I7">
+      <c r="I47">
         <v>16.06944999694824</v>
       </c>
-      <c r="J7">
+      <c r="J47">
         <v>14.37110000133514</v>
       </c>
-      <c r="K7">
+      <c r="K47">
         <v>8.369999885559082</v>
       </c>
-      <c r="L7">
+      <c r="L47">
         <v>34</v>
       </c>
-      <c r="M7">
-        <v>33.42319142586498</v>
-      </c>
-      <c r="N7">
+      <c r="M47">
+        <v>108.4453449889561</v>
+      </c>
+      <c r="N47">
         <v>0.64</v>
       </c>
-      <c r="O7">
+      <c r="O47">
         <v>0.78</v>
       </c>
-      <c r="P7">
+      <c r="P47">
         <v>0.45</v>
       </c>
-      <c r="Q7">
+      <c r="Q47">
         <v>0.65</v>
       </c>
-      <c r="R7">
+      <c r="R47">
         <v>69641000</v>
       </c>
-      <c r="S7">
+      <c r="S47">
         <v>86332000</v>
       </c>
-      <c r="T7">
+      <c r="T47">
         <v>49089000</v>
       </c>
-      <c r="U7">
+      <c r="U47">
         <v>68764000</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
+      <c r="V47" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22">
+      <c r="A48" t="s">
+        <v>68</v>
+      </c>
+      <c r="B48" t="s">
+        <v>126</v>
+      </c>
+      <c r="C48" t="s">
+        <v>166</v>
+      </c>
+      <c r="D48" t="s">
+        <v>241</v>
+      </c>
+      <c r="E48">
+        <v>56.70999908447266</v>
+      </c>
+      <c r="F48">
+        <v>3321353.333333333</v>
+      </c>
+      <c r="G48">
+        <v>53.8647998046875</v>
+      </c>
+      <c r="H48">
+        <v>46.2742665608724</v>
+      </c>
+      <c r="I48">
+        <v>45.05804990768433</v>
+      </c>
+      <c r="J48">
+        <v>43.18229991912842</v>
+      </c>
+      <c r="K48">
+        <v>11.99751472473145</v>
+      </c>
+      <c r="L48">
+        <v>60.77000045776367</v>
+      </c>
+      <c r="M48">
+        <v>108.2868993667295</v>
+      </c>
+      <c r="N48">
+        <v>0.68</v>
+      </c>
+      <c r="O48">
+        <v>0.33</v>
+      </c>
+      <c r="P48">
+        <v>0.84</v>
+      </c>
+      <c r="Q48">
+        <v>0.79</v>
+      </c>
+      <c r="R48">
+        <v>511000000</v>
+      </c>
+      <c r="S48">
+        <v>245000000</v>
+      </c>
+      <c r="T48">
+        <v>614000000</v>
+      </c>
+      <c r="U48">
+        <v>583000000</v>
+      </c>
+      <c r="V48" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22">
+      <c r="A49" t="s">
+        <v>69</v>
+      </c>
+      <c r="B49" t="s">
+        <v>134</v>
+      </c>
+      <c r="C49" t="s">
+        <v>167</v>
+      </c>
+      <c r="D49" t="s">
+        <v>242</v>
+      </c>
+      <c r="E49">
+        <v>113.7600021362305</v>
+      </c>
+      <c r="F49">
+        <v>544080</v>
+      </c>
+      <c r="G49">
+        <v>107.6630000305176</v>
+      </c>
+      <c r="H49">
+        <v>98.92013341267904</v>
+      </c>
+      <c r="I49">
+        <v>93.5428999710083</v>
+      </c>
+      <c r="J49">
+        <v>90.21079994201661</v>
+      </c>
+      <c r="K49">
+        <v>3.054112195968628</v>
+      </c>
+      <c r="L49">
+        <v>115.1399993896484</v>
+      </c>
+      <c r="M49">
+        <v>108.0135970624105</v>
+      </c>
+      <c r="N49">
+        <v>0.49</v>
+      </c>
+      <c r="O49">
+        <v>0.45</v>
+      </c>
+      <c r="P49">
+        <v>0.43</v>
+      </c>
+      <c r="Q49">
+        <v>0.67</v>
+      </c>
+      <c r="R49">
+        <v>41620000</v>
+      </c>
+      <c r="S49">
+        <v>38800000</v>
+      </c>
+      <c r="T49">
+        <v>36700000</v>
+      </c>
+      <c r="U49">
+        <v>52000000</v>
+      </c>
+      <c r="V49" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22">
+      <c r="A50" t="s">
+        <v>70</v>
+      </c>
+      <c r="B50" t="s">
+        <v>129</v>
+      </c>
+      <c r="C50" t="s">
+        <v>168</v>
+      </c>
+      <c r="D50" t="s">
+        <v>243</v>
+      </c>
+      <c r="E50">
+        <v>33.81000137329102</v>
+      </c>
+      <c r="F50">
+        <v>745200</v>
+      </c>
+      <c r="G50">
+        <v>32.43459972381592</v>
+      </c>
+      <c r="H50">
+        <v>29.09106658935547</v>
+      </c>
+      <c r="I50">
+        <v>28.92354996681213</v>
+      </c>
+      <c r="J50">
+        <v>28.22679993629455</v>
+      </c>
+      <c r="K50">
+        <v>1.370828747749329</v>
+      </c>
+      <c r="L50">
+        <v>41.53372192382812</v>
+      </c>
+      <c r="M50">
+        <v>107.9526742912932</v>
+      </c>
+      <c r="N50">
+        <v>0.25</v>
+      </c>
+      <c r="O50">
+        <v>0.55</v>
+      </c>
+      <c r="P50">
+        <v>0.55</v>
+      </c>
+      <c r="Q50">
+        <v>0.77</v>
+      </c>
+      <c r="R50">
+        <v>24590000</v>
+      </c>
+      <c r="S50">
+        <v>54073000</v>
+      </c>
+      <c r="T50">
+        <v>53929000</v>
+      </c>
+      <c r="U50">
+        <v>74965000</v>
+      </c>
+      <c r="V50" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22">
+      <c r="A51" t="s">
+        <v>71</v>
+      </c>
+      <c r="B51" t="s">
+        <v>132</v>
+      </c>
+      <c r="C51" t="s">
+        <v>169</v>
+      </c>
+      <c r="D51" t="s">
+        <v>244</v>
+      </c>
+      <c r="E51">
+        <v>148.8699951171875</v>
+      </c>
+      <c r="F51">
+        <v>644796.6666666666</v>
+      </c>
+      <c r="G51">
+        <v>141.6813995361328</v>
+      </c>
+      <c r="H51">
+        <v>134.7178001912435</v>
+      </c>
+      <c r="I51">
+        <v>132.1200001525879</v>
+      </c>
+      <c r="J51">
+        <v>129.6870003128052</v>
+      </c>
+      <c r="K51">
+        <v>16.98513031005859</v>
+      </c>
+      <c r="L51">
+        <v>150.5899963378906</v>
+      </c>
+      <c r="M51">
+        <v>107.8873643560209</v>
+      </c>
+      <c r="N51">
+        <v>1.41</v>
+      </c>
+      <c r="O51">
+        <v>1.49</v>
+      </c>
+      <c r="P51">
+        <v>1.63</v>
+      </c>
+      <c r="Q51">
+        <v>1.57</v>
+      </c>
+      <c r="R51">
+        <v>150200000</v>
+      </c>
+      <c r="S51">
+        <v>159700000</v>
+      </c>
+      <c r="T51">
+        <v>173400000</v>
+      </c>
+      <c r="U51">
+        <v>167800000</v>
+      </c>
+      <c r="V51" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22">
+      <c r="A52" t="s">
+        <v>72</v>
+      </c>
+      <c r="B52" t="s">
+        <v>126</v>
+      </c>
+      <c r="C52" t="s">
+        <v>166</v>
+      </c>
+      <c r="D52" t="s">
+        <v>245</v>
+      </c>
+      <c r="E52">
+        <v>179.1900024414062</v>
+      </c>
+      <c r="F52">
+        <v>3300416.666666667</v>
+      </c>
+      <c r="G52">
+        <v>168.5997991943359</v>
+      </c>
+      <c r="H52">
+        <v>155.2138665262858</v>
+      </c>
+      <c r="I52">
+        <v>147.8172999572754</v>
+      </c>
+      <c r="J52">
+        <v>141.3070000839233</v>
+      </c>
+      <c r="K52">
+        <v>13.25</v>
+      </c>
+      <c r="L52">
+        <v>189.8300018310547</v>
+      </c>
+      <c r="M52">
+        <v>107.8866266839896</v>
+      </c>
+      <c r="N52">
+        <v>1.13</v>
+      </c>
+      <c r="O52">
+        <v>1.35</v>
+      </c>
+      <c r="P52">
+        <v>1.38</v>
+      </c>
+      <c r="Q52">
+        <v>1.55</v>
+      </c>
+      <c r="R52">
+        <v>353999000</v>
+      </c>
+      <c r="S52">
+        <v>427089000</v>
+      </c>
+      <c r="T52">
+        <v>436473000</v>
+      </c>
+      <c r="U52">
+        <v>491885000</v>
+      </c>
+      <c r="V52" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22">
+      <c r="A53" t="s">
+        <v>73</v>
+      </c>
+      <c r="B53" t="s">
+        <v>130</v>
+      </c>
+      <c r="C53" t="s">
+        <v>144</v>
+      </c>
+      <c r="D53" t="s">
+        <v>246</v>
+      </c>
+      <c r="E53">
+        <v>27.19000053405762</v>
+      </c>
+      <c r="F53">
+        <v>648503.3333333334</v>
+      </c>
+      <c r="G53">
+        <v>26.50699989318848</v>
+      </c>
+      <c r="H53">
+        <v>22.05496665318807</v>
+      </c>
+      <c r="I53">
+        <v>19.65242500782013</v>
+      </c>
+      <c r="J53">
+        <v>18.0758500289917</v>
+      </c>
+      <c r="K53">
+        <v>7.559999942779541</v>
+      </c>
+      <c r="L53">
+        <v>29.29999923706055</v>
+      </c>
+      <c r="M53">
+        <v>107.8754235247931</v>
+      </c>
+      <c r="N53">
+        <v>0.13</v>
+      </c>
+      <c r="O53">
+        <v>-0.05</v>
+      </c>
+      <c r="P53">
+        <v>0.12</v>
+      </c>
+      <c r="Q53">
+        <v>0.31</v>
+      </c>
+      <c r="R53">
+        <v>7258000</v>
+      </c>
+      <c r="S53">
+        <v>-2810000</v>
+      </c>
+      <c r="T53">
+        <v>6705000</v>
+      </c>
+      <c r="U53">
+        <v>17987000</v>
+      </c>
+      <c r="V53" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22">
+      <c r="A54" t="s">
+        <v>74</v>
+      </c>
+      <c r="B54" t="s">
+        <v>132</v>
+      </c>
+      <c r="C54" t="s">
+        <v>170</v>
+      </c>
+      <c r="D54" t="s">
+        <v>247</v>
+      </c>
+      <c r="E54">
+        <v>14.69999980926514</v>
+      </c>
+      <c r="F54">
+        <v>627073.3333333334</v>
+      </c>
+      <c r="G54">
+        <v>13.88720001220703</v>
+      </c>
+      <c r="H54">
+        <v>13.53693333307902</v>
+      </c>
+      <c r="I54">
+        <v>13.49949998855591</v>
+      </c>
+      <c r="J54">
+        <v>13.34704998970032</v>
+      </c>
+      <c r="K54">
+        <v>5.130780220031738</v>
+      </c>
+      <c r="L54">
+        <v>16.10000038146973</v>
+      </c>
+      <c r="M54">
+        <v>107.8421986733093</v>
+      </c>
+      <c r="N54">
+        <v>0.05</v>
+      </c>
+      <c r="O54">
+        <v>0.15</v>
+      </c>
+      <c r="P54">
+        <v>0.34</v>
+      </c>
+      <c r="Q54">
+        <v>0.43</v>
+      </c>
+      <c r="R54">
+        <v>8083000</v>
+      </c>
+      <c r="S54">
+        <v>25581000</v>
+      </c>
+      <c r="T54">
+        <v>58503000</v>
+      </c>
+      <c r="U54">
+        <v>72983000</v>
+      </c>
+      <c r="V54" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22">
+      <c r="A55" t="s">
+        <v>75</v>
+      </c>
+      <c r="B55" t="s">
+        <v>125</v>
+      </c>
+      <c r="C55" t="s">
+        <v>171</v>
+      </c>
+      <c r="D55" t="s">
+        <v>207</v>
+      </c>
+      <c r="E55">
+        <v>220.9100036621094</v>
+      </c>
+      <c r="F55">
+        <v>2001693.333333333</v>
+      </c>
+      <c r="G55">
+        <v>207.1006002807617</v>
+      </c>
+      <c r="H55">
+        <v>182.0743336995443</v>
+      </c>
+      <c r="I55">
+        <v>176.5836504364014</v>
+      </c>
+      <c r="J55">
+        <v>169.2715505981445</v>
+      </c>
+      <c r="K55">
+        <v>0.004536735825240612</v>
+      </c>
+      <c r="L55">
+        <v>221.3000030517578</v>
+      </c>
+      <c r="M55">
+        <v>107.6442843714625</v>
+      </c>
+      <c r="N55">
+        <v>1.52</v>
+      </c>
+      <c r="O55">
+        <v>1.8</v>
+      </c>
+      <c r="P55">
+        <v>1.59</v>
+      </c>
+      <c r="Q55">
+        <v>1.86</v>
+      </c>
+      <c r="R55">
+        <v>607000000</v>
+      </c>
+      <c r="S55">
+        <v>721000000</v>
+      </c>
+      <c r="T55">
+        <v>638000000</v>
+      </c>
+      <c r="U55">
+        <v>744000000</v>
+      </c>
+      <c r="V55" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22">
+      <c r="A56" t="s">
+        <v>76</v>
+      </c>
+      <c r="B56" t="s">
+        <v>132</v>
+      </c>
+      <c r="C56" t="s">
+        <v>172</v>
+      </c>
+      <c r="D56" t="s">
+        <v>248</v>
+      </c>
+      <c r="E56">
+        <v>28.8700008392334</v>
+      </c>
+      <c r="F56">
+        <v>263830</v>
+      </c>
+      <c r="G56">
+        <v>26.95440002441406</v>
+      </c>
+      <c r="H56">
+        <v>24.98733334859212</v>
+      </c>
+      <c r="I56">
+        <v>24.84765001296997</v>
+      </c>
+      <c r="J56">
+        <v>24.42760001182556</v>
+      </c>
+      <c r="K56">
+        <v>19.29999923706055</v>
+      </c>
+      <c r="L56">
+        <v>29.56999969482422</v>
+      </c>
+      <c r="M56">
+        <v>107.4843324345364</v>
+      </c>
+      <c r="N56">
+        <v>1.17</v>
+      </c>
+      <c r="O56">
+        <v>0.88</v>
+      </c>
+      <c r="P56">
+        <v>1.08</v>
+      </c>
+      <c r="Q56">
+        <v>1.04</v>
+      </c>
+      <c r="R56">
+        <v>190986000</v>
+      </c>
+      <c r="S56">
+        <v>143806000</v>
+      </c>
+      <c r="T56">
+        <v>175988000</v>
+      </c>
+      <c r="U56">
+        <v>168020000</v>
+      </c>
+      <c r="V56" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22">
+      <c r="A57" t="s">
+        <v>77</v>
+      </c>
+      <c r="B57" t="s">
+        <v>125</v>
+      </c>
+      <c r="C57" t="s">
+        <v>173</v>
+      </c>
+      <c r="D57" t="s">
+        <v>249</v>
+      </c>
+      <c r="E57">
+        <v>105.5800018310547</v>
+      </c>
+      <c r="F57">
+        <v>429753.3333333333</v>
+      </c>
+      <c r="G57">
+        <v>99.50380020141601</v>
+      </c>
+      <c r="H57">
+        <v>89.61720016479492</v>
+      </c>
+      <c r="I57">
+        <v>84.52940021514893</v>
+      </c>
+      <c r="J57">
+        <v>80.95705015182494</v>
+      </c>
+      <c r="K57">
+        <v>12.27999973297119</v>
+      </c>
+      <c r="L57">
+        <v>108.4400024414062</v>
+      </c>
+      <c r="M57">
+        <v>107.3106870293134</v>
+      </c>
+      <c r="N57">
+        <v>1.22</v>
+      </c>
+      <c r="O57">
+        <v>0.78</v>
+      </c>
+      <c r="P57">
+        <v>2.17</v>
+      </c>
+      <c r="Q57">
+        <v>1.38</v>
+      </c>
+      <c r="R57">
+        <v>77000000</v>
+      </c>
+      <c r="S57">
+        <v>49000000</v>
+      </c>
+      <c r="T57">
+        <v>131000000</v>
+      </c>
+      <c r="U57">
+        <v>83000000</v>
+      </c>
+      <c r="V57" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22">
+      <c r="A58" t="s">
+        <v>78</v>
+      </c>
+      <c r="B58" t="s">
+        <v>128</v>
+      </c>
+      <c r="C58" t="s">
+        <v>174</v>
+      </c>
+      <c r="D58" t="s">
+        <v>250</v>
+      </c>
+      <c r="E58">
+        <v>49.97000122070312</v>
+      </c>
+      <c r="F58">
+        <v>1259633.333333333</v>
+      </c>
+      <c r="G58">
+        <v>47.53819999694824</v>
+      </c>
+      <c r="H58">
+        <v>42.16840001424153</v>
+      </c>
+      <c r="I58">
+        <v>40.98290004730224</v>
+      </c>
+      <c r="J58">
+        <v>39.17195006370545</v>
+      </c>
+      <c r="K58">
+        <v>20.39999961853027</v>
+      </c>
+      <c r="L58">
+        <v>53.11999893188477</v>
+      </c>
+      <c r="M58">
+        <v>107.1776592051601</v>
+      </c>
+      <c r="N58">
+        <v>0.41</v>
+      </c>
+      <c r="O58">
+        <v>0.92</v>
+      </c>
+      <c r="P58">
+        <v>0.74</v>
+      </c>
+      <c r="Q58">
+        <v>0.45</v>
+      </c>
+      <c r="R58">
+        <v>33585000</v>
+      </c>
+      <c r="S58">
+        <v>134962000</v>
+      </c>
+      <c r="T58">
+        <v>108063000</v>
+      </c>
+      <c r="U58">
+        <v>65816000</v>
+      </c>
+      <c r="V58" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22">
+      <c r="A59" t="s">
+        <v>79</v>
+      </c>
+      <c r="B59" t="s">
+        <v>125</v>
+      </c>
+      <c r="C59" t="s">
+        <v>155</v>
+      </c>
+      <c r="D59" t="s">
+        <v>251</v>
+      </c>
+      <c r="E59">
+        <v>96.02999877929688</v>
+      </c>
+      <c r="F59">
+        <v>369060</v>
+      </c>
+      <c r="G59">
+        <v>91.81219970703125</v>
+      </c>
+      <c r="H59">
+        <v>89.06580017089844</v>
+      </c>
+      <c r="I59">
+        <v>88.61320014953613</v>
+      </c>
+      <c r="J59">
+        <v>86.55120014190673</v>
+      </c>
+      <c r="K59">
+        <v>1.423831343650818</v>
+      </c>
+      <c r="L59">
+        <v>102.7399978637695</v>
+      </c>
+      <c r="M59">
+        <v>107.174362194882</v>
+      </c>
+      <c r="N59">
+        <v>4.82</v>
+      </c>
+      <c r="O59">
+        <v>4.18</v>
+      </c>
+      <c r="P59">
+        <v>2.94</v>
+      </c>
+      <c r="Q59">
+        <v>-0.4</v>
+      </c>
+      <c r="R59">
+        <v>246000000</v>
+      </c>
+      <c r="S59">
+        <v>206000000</v>
+      </c>
+      <c r="T59">
+        <v>139000000</v>
+      </c>
+      <c r="U59">
+        <v>-18000000</v>
+      </c>
+      <c r="V59" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22">
+      <c r="A60" t="s">
+        <v>80</v>
+      </c>
+      <c r="B60" t="s">
+        <v>127</v>
+      </c>
+      <c r="C60" t="s">
+        <v>175</v>
+      </c>
+      <c r="D60" t="s">
+        <v>252</v>
+      </c>
+      <c r="E60">
+        <v>19.14999961853027</v>
+      </c>
+      <c r="F60">
+        <v>350683.3333333333</v>
+      </c>
+      <c r="G60">
+        <v>17.92260009765625</v>
+      </c>
+      <c r="H60">
+        <v>16.76616671880086</v>
+      </c>
+      <c r="I60">
+        <v>16.27922503948212</v>
+      </c>
+      <c r="J60">
+        <v>16.01252504825592</v>
+      </c>
+      <c r="K60">
+        <v>11.81999969482422</v>
+      </c>
+      <c r="L60">
+        <v>22.52000045776367</v>
+      </c>
+      <c r="M60">
+        <v>107.1305780736901</v>
+      </c>
+      <c r="N60">
+        <v>0.000761</v>
+      </c>
+      <c r="O60">
+        <v>-0.01</v>
+      </c>
+      <c r="P60">
+        <v>0.15</v>
+      </c>
+      <c r="Q60">
+        <v>0.13</v>
+      </c>
+      <c r="R60">
+        <v>46000</v>
+      </c>
+      <c r="S60">
+        <v>-486000</v>
+      </c>
+      <c r="T60">
+        <v>9360000</v>
+      </c>
+      <c r="U60">
+        <v>7959000</v>
+      </c>
+      <c r="V60" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22">
+      <c r="A61" t="s">
+        <v>81</v>
+      </c>
+      <c r="B61" t="s">
+        <v>132</v>
+      </c>
+      <c r="C61" t="s">
+        <v>150</v>
+      </c>
+      <c r="D61" t="s">
+        <v>253</v>
+      </c>
+      <c r="E61">
+        <v>91.80999755859375</v>
+      </c>
+      <c r="F61">
+        <v>1051863.333333333</v>
+      </c>
+      <c r="G61">
+        <v>85.99859985351563</v>
+      </c>
+      <c r="H61">
+        <v>82.46300003051758</v>
+      </c>
+      <c r="I61">
+        <v>80.66120006561279</v>
+      </c>
+      <c r="J61">
+        <v>79.15225009918213</v>
+      </c>
+      <c r="K61">
+        <v>10.15009593963623</v>
+      </c>
+      <c r="L61">
+        <v>93.11000061035156</v>
+      </c>
+      <c r="M61">
+        <v>106.9844110734444</v>
+      </c>
+      <c r="N61">
+        <v>0.97</v>
+      </c>
+      <c r="O61">
+        <v>1.31</v>
+      </c>
+      <c r="P61">
+        <v>1.42</v>
+      </c>
+      <c r="Q61">
+        <v>1.2</v>
+      </c>
+      <c r="R61">
+        <v>99000000</v>
+      </c>
+      <c r="S61">
+        <v>136000000</v>
+      </c>
+      <c r="T61">
+        <v>148000000</v>
+      </c>
+      <c r="U61">
+        <v>125000000</v>
+      </c>
+      <c r="V61" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22">
+      <c r="A62" t="s">
+        <v>82</v>
+      </c>
+      <c r="B62" t="s">
+        <v>128</v>
+      </c>
+      <c r="C62" t="s">
+        <v>149</v>
+      </c>
+      <c r="D62" t="s">
+        <v>254</v>
+      </c>
+      <c r="E62">
+        <v>72.58999633789062</v>
+      </c>
+      <c r="F62">
+        <v>993063.3333333334</v>
+      </c>
+      <c r="G62">
+        <v>69.19499999999999</v>
+      </c>
+      <c r="H62">
+        <v>66.64866650899252</v>
+      </c>
+      <c r="I62">
+        <v>66.34409994125366</v>
+      </c>
+      <c r="J62">
+        <v>64.89755002975464</v>
+      </c>
+      <c r="K62">
+        <v>20.65999984741211</v>
+      </c>
+      <c r="L62">
+        <v>79.01000213623047</v>
+      </c>
+      <c r="M62">
+        <v>106.9327690335236</v>
+      </c>
+      <c r="N62">
+        <v>0.98</v>
+      </c>
+      <c r="O62">
+        <v>0.38</v>
+      </c>
+      <c r="P62">
+        <v>0.61</v>
+      </c>
+      <c r="Q62">
+        <v>-0.39</v>
+      </c>
+      <c r="R62">
+        <v>74300000</v>
+      </c>
+      <c r="S62">
+        <v>29200000</v>
+      </c>
+      <c r="T62">
+        <v>46700000</v>
+      </c>
+      <c r="U62">
+        <v>-29400000</v>
+      </c>
+      <c r="V62" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22">
+      <c r="A63" t="s">
+        <v>83</v>
+      </c>
+      <c r="B63" t="s">
+        <v>126</v>
+      </c>
+      <c r="C63" t="s">
+        <v>176</v>
+      </c>
+      <c r="D63" t="s">
+        <v>255</v>
+      </c>
+      <c r="E63">
+        <v>471.6300048828125</v>
+      </c>
+      <c r="F63">
+        <v>53216766.66666666</v>
+      </c>
+      <c r="G63">
+        <v>440.6029998779297</v>
+      </c>
+      <c r="H63">
+        <v>327.0031996663411</v>
+      </c>
+      <c r="I63">
+        <v>285.1867498016358</v>
+      </c>
+      <c r="J63">
+        <v>253.0890996932984</v>
+      </c>
+      <c r="K63">
+        <v>0.3134739995002747</v>
+      </c>
+      <c r="L63">
+        <v>474.9400024414062</v>
+      </c>
+      <c r="M63">
+        <v>106.9053240006801</v>
+      </c>
+      <c r="N63">
+        <v>0.27</v>
+      </c>
+      <c r="O63">
+        <v>0.57</v>
+      </c>
+      <c r="P63">
+        <v>0.82</v>
+      </c>
+      <c r="Q63">
+        <v>2.48</v>
+      </c>
+      <c r="R63">
+        <v>680000000</v>
+      </c>
+      <c r="S63">
+        <v>1414000000</v>
+      </c>
+      <c r="T63">
+        <v>2043000000</v>
+      </c>
+      <c r="U63">
+        <v>6188000000</v>
+      </c>
+      <c r="V63" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22">
+      <c r="A64" t="s">
+        <v>84</v>
+      </c>
+      <c r="B64" t="s">
+        <v>126</v>
+      </c>
+      <c r="C64" t="s">
+        <v>156</v>
+      </c>
+      <c r="D64" t="s">
+        <v>256</v>
+      </c>
+      <c r="E64">
+        <v>201.2799987792969</v>
+      </c>
+      <c r="F64">
+        <v>592353.3333333334</v>
+      </c>
+      <c r="G64">
+        <v>190.0861996459961</v>
+      </c>
+      <c r="H64">
+        <v>187.3907333374023</v>
+      </c>
+      <c r="I64">
+        <v>186.7413500976562</v>
+      </c>
+      <c r="J64">
+        <v>183.1892500305176</v>
+      </c>
+      <c r="K64">
+        <v>16.89643859863281</v>
+      </c>
+      <c r="L64">
+        <v>214.25</v>
+      </c>
+      <c r="M64">
+        <v>106.8295121422154</v>
+      </c>
+      <c r="N64">
+        <v>2.17</v>
+      </c>
+      <c r="O64">
+        <v>2.09</v>
+      </c>
+      <c r="P64">
+        <v>1.68</v>
+      </c>
+      <c r="Q64">
+        <v>1.92</v>
+      </c>
+      <c r="R64">
+        <v>297800000</v>
+      </c>
+      <c r="S64">
+        <v>287200000</v>
+      </c>
+      <c r="T64">
+        <v>230100000</v>
+      </c>
+      <c r="U64">
+        <v>262600000</v>
+      </c>
+      <c r="V64" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22">
+      <c r="A65" t="s">
+        <v>85</v>
+      </c>
+      <c r="B65" t="s">
+        <v>134</v>
+      </c>
+      <c r="C65" t="s">
+        <v>167</v>
+      </c>
+      <c r="D65" t="s">
+        <v>257</v>
+      </c>
+      <c r="E65">
+        <v>23.05999946594238</v>
+      </c>
+      <c r="F65">
+        <v>1229706.666666667</v>
+      </c>
+      <c r="G65">
+        <v>22.89739994049072</v>
+      </c>
+      <c r="H65">
+        <v>21.83846661885579</v>
+      </c>
+      <c r="I65">
+        <v>21.39544996738434</v>
+      </c>
+      <c r="J65">
+        <v>20.44749999046326</v>
+      </c>
+      <c r="K65">
+        <v>10.51000022888184</v>
+      </c>
+      <c r="L65">
+        <v>26.84000015258789</v>
+      </c>
+      <c r="M65">
+        <v>106.7748386718829</v>
+      </c>
+      <c r="N65">
+        <v>-0.4346</v>
+      </c>
+      <c r="O65">
+        <v>-0.1626</v>
+      </c>
+      <c r="P65">
+        <v>0.0385</v>
+      </c>
+      <c r="Q65">
+        <v>-0.034</v>
+      </c>
+      <c r="R65">
+        <v>-70842000</v>
+      </c>
+      <c r="S65">
+        <v>-26516000</v>
+      </c>
+      <c r="T65">
+        <v>6306000</v>
+      </c>
+      <c r="U65">
+        <v>-5547000</v>
+      </c>
+      <c r="V65" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22">
+      <c r="A66" t="s">
+        <v>86</v>
+      </c>
+      <c r="B66" t="s">
+        <v>134</v>
+      </c>
+      <c r="C66" t="s">
+        <v>177</v>
+      </c>
+      <c r="D66" t="s">
+        <v>258</v>
+      </c>
+      <c r="E66">
+        <v>42.47999954223633</v>
+      </c>
+      <c r="F66">
+        <v>1290903.333333333</v>
+      </c>
+      <c r="G66">
+        <v>40.78620002746582</v>
+      </c>
+      <c r="H66">
+        <v>38.79026664733887</v>
+      </c>
+      <c r="I66">
+        <v>37.65774995803833</v>
+      </c>
+      <c r="J66">
+        <v>36.41559993743896</v>
+      </c>
+      <c r="K66">
+        <v>0.3258776962757111</v>
+      </c>
+      <c r="L66">
+        <v>55.83219528198242</v>
+      </c>
+      <c r="M66">
+        <v>106.7413965088057</v>
+      </c>
+      <c r="N66">
+        <v>0.22</v>
+      </c>
+      <c r="O66">
+        <v>0.43</v>
+      </c>
+      <c r="P66">
+        <v>0.13</v>
+      </c>
+      <c r="Q66">
+        <v>0.28</v>
+      </c>
+      <c r="R66">
+        <v>36617000</v>
+      </c>
+      <c r="S66">
+        <v>70786000</v>
+      </c>
+      <c r="T66">
+        <v>22321000</v>
+      </c>
+      <c r="U66">
+        <v>46574000</v>
+      </c>
+      <c r="V66" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22">
+      <c r="A67" t="s">
+        <v>87</v>
+      </c>
+      <c r="B67" t="s">
+        <v>130</v>
+      </c>
+      <c r="C67" t="s">
+        <v>178</v>
+      </c>
+      <c r="D67" t="s">
+        <v>259</v>
+      </c>
+      <c r="E67">
+        <v>38.97000122070312</v>
+      </c>
+      <c r="F67">
+        <v>1531106.666666667</v>
+      </c>
+      <c r="G67">
+        <v>37.49819961547851</v>
+      </c>
+      <c r="H67">
+        <v>34.99926657358805</v>
+      </c>
+      <c r="I67">
+        <v>34.44154994010925</v>
+      </c>
+      <c r="J67">
+        <v>33.42304998397827</v>
+      </c>
+      <c r="K67">
+        <v>13.31999969482422</v>
+      </c>
+      <c r="L67">
+        <v>49.11000061035156</v>
+      </c>
+      <c r="M67">
+        <v>106.619699106584</v>
+      </c>
+      <c r="N67">
+        <v>0.61</v>
+      </c>
+      <c r="O67">
+        <v>0.42</v>
+      </c>
+      <c r="P67">
+        <v>0.73</v>
+      </c>
+      <c r="Q67">
+        <v>0.65</v>
+      </c>
+      <c r="R67">
+        <v>65740000</v>
+      </c>
+      <c r="S67">
+        <v>45120000</v>
+      </c>
+      <c r="T67">
+        <v>76160000</v>
+      </c>
+      <c r="U67">
+        <v>67334000</v>
+      </c>
+      <c r="V67" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22">
+      <c r="A68" t="s">
+        <v>88</v>
+      </c>
+      <c r="B68" t="s">
+        <v>126</v>
+      </c>
+      <c r="C68" t="s">
+        <v>158</v>
+      </c>
+      <c r="D68" t="s">
+        <v>260</v>
+      </c>
+      <c r="E68">
+        <v>162</v>
+      </c>
+      <c r="F68">
+        <v>1485316.666666667</v>
+      </c>
+      <c r="G68">
+        <v>152.654599609375</v>
+      </c>
+      <c r="H68">
+        <v>133.0127330525716</v>
+      </c>
+      <c r="I68">
+        <v>129.8147997665405</v>
+      </c>
+      <c r="J68">
+        <v>124.9295998001099</v>
+      </c>
+      <c r="K68">
+        <v>12.18373107910156</v>
+      </c>
+      <c r="L68">
+        <v>168.5816802978516</v>
+      </c>
+      <c r="M68">
+        <v>106.5018111581585</v>
+      </c>
+      <c r="N68">
+        <v>0.82</v>
+      </c>
+      <c r="O68">
+        <v>0.54</v>
+      </c>
+      <c r="P68">
+        <v>1.15</v>
+      </c>
+      <c r="Q68">
+        <v>0.52</v>
+      </c>
+      <c r="R68">
+        <v>347000000</v>
+      </c>
+      <c r="S68">
+        <v>231000000</v>
+      </c>
+      <c r="T68">
+        <v>494000000</v>
+      </c>
+      <c r="U68">
+        <v>224000000</v>
+      </c>
+      <c r="V68" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22">
+      <c r="A69" t="s">
+        <v>89</v>
+      </c>
+      <c r="B69" t="s">
+        <v>126</v>
+      </c>
+      <c r="C69" t="s">
+        <v>179</v>
+      </c>
+      <c r="D69" t="s">
+        <v>261</v>
+      </c>
+      <c r="E69">
+        <v>55.2400016784668</v>
+      </c>
+      <c r="F69">
+        <v>19939320</v>
+      </c>
+      <c r="G69">
+        <v>52.42320014953614</v>
+      </c>
+      <c r="H69">
+        <v>50.05533327738444</v>
+      </c>
+      <c r="I69">
+        <v>49.45140003204346</v>
+      </c>
+      <c r="J69">
+        <v>48.36015001296997</v>
+      </c>
+      <c r="K69">
+        <v>0.05248657986521721</v>
+      </c>
+      <c r="L69">
+        <v>63.95999908447266</v>
+      </c>
+      <c r="M69">
+        <v>106.3809607643407</v>
+      </c>
+      <c r="N69">
+        <v>0.65</v>
+      </c>
+      <c r="O69">
+        <v>0.67</v>
+      </c>
+      <c r="P69">
+        <v>0.78</v>
+      </c>
+      <c r="Q69">
+        <v>0.97</v>
+      </c>
+      <c r="R69">
+        <v>2670000000</v>
+      </c>
+      <c r="S69">
+        <v>2773000000</v>
+      </c>
+      <c r="T69">
+        <v>3212000000</v>
+      </c>
+      <c r="U69">
+        <v>3958000000</v>
+      </c>
+      <c r="V69" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22">
+      <c r="A70" t="s">
+        <v>90</v>
+      </c>
+      <c r="B70" t="s">
+        <v>132</v>
+      </c>
+      <c r="C70" t="s">
+        <v>170</v>
+      </c>
+      <c r="D70" t="s">
+        <v>262</v>
+      </c>
+      <c r="E70">
+        <v>21.71999931335449</v>
+      </c>
+      <c r="F70">
+        <v>344750</v>
+      </c>
+      <c r="G70">
+        <v>20.75879997253418</v>
+      </c>
+      <c r="H70">
+        <v>19.15379993438721</v>
+      </c>
+      <c r="I70">
+        <v>18.8730499458313</v>
+      </c>
+      <c r="J70">
+        <v>18.48304992675781</v>
+      </c>
+      <c r="K70">
+        <v>0.01849654316902161</v>
+      </c>
+      <c r="L70">
+        <v>28.34000015258789</v>
+      </c>
+      <c r="M70">
+        <v>106.236636832187</v>
+      </c>
+      <c r="N70">
+        <v>0.34</v>
+      </c>
+      <c r="O70">
+        <v>0.09</v>
+      </c>
+      <c r="P70">
+        <v>0.57</v>
+      </c>
+      <c r="Q70">
+        <v>0.63</v>
+      </c>
+      <c r="R70">
+        <v>9458000</v>
+      </c>
+      <c r="S70">
+        <v>2949000</v>
+      </c>
+      <c r="T70">
+        <v>18176000</v>
+      </c>
+      <c r="U70">
+        <v>23812000</v>
+      </c>
+      <c r="V70" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22">
+      <c r="A71" t="s">
+        <v>91</v>
+      </c>
+      <c r="B71" t="s">
+        <v>129</v>
+      </c>
+      <c r="C71" t="s">
+        <v>180</v>
+      </c>
+      <c r="D71" t="s">
+        <v>263</v>
+      </c>
+      <c r="E71">
+        <v>125.1100006103516</v>
+      </c>
+      <c r="F71">
+        <v>284170</v>
+      </c>
+      <c r="G71">
+        <v>118.7648004150391</v>
+      </c>
+      <c r="H71">
+        <v>116.8342668660482</v>
+      </c>
+      <c r="I71">
+        <v>114.6003002548218</v>
+      </c>
+      <c r="J71">
+        <v>112.0718502044678</v>
+      </c>
+      <c r="K71">
+        <v>2.89168906211853</v>
+      </c>
+      <c r="L71">
+        <v>156.1253356933594</v>
+      </c>
+      <c r="M71">
+        <v>106.196301800066</v>
+      </c>
+      <c r="N71">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="O71">
+        <v>0.89</v>
+      </c>
+      <c r="P71">
+        <v>0.82</v>
+      </c>
+      <c r="Q71">
+        <v>1.24</v>
+      </c>
+      <c r="R71">
+        <v>54244000</v>
+      </c>
+      <c r="S71">
+        <v>58996000</v>
+      </c>
+      <c r="T71">
+        <v>54764000</v>
+      </c>
+      <c r="U71">
+        <v>83072000</v>
+      </c>
+      <c r="V71" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22">
+      <c r="A72" t="s">
+        <v>92</v>
+      </c>
+      <c r="B72" t="s">
+        <v>134</v>
+      </c>
+      <c r="C72" t="s">
+        <v>167</v>
+      </c>
+      <c r="D72" t="s">
+        <v>264</v>
+      </c>
+      <c r="E72">
+        <v>21.11000061035156</v>
+      </c>
+      <c r="F72">
+        <v>787126.6666666666</v>
+      </c>
+      <c r="G72">
+        <v>20.21899997711182</v>
+      </c>
+      <c r="H72">
+        <v>18.83066669464111</v>
+      </c>
+      <c r="I72">
+        <v>18.75924998283386</v>
+      </c>
+      <c r="J72">
+        <v>18.34329997062683</v>
+      </c>
+      <c r="K72">
+        <v>8.053735733032227</v>
+      </c>
+      <c r="L72">
+        <v>25.95000076293945</v>
+      </c>
+      <c r="M72">
+        <v>105.8062087332248</v>
+      </c>
+      <c r="N72">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O72">
+        <v>0.12</v>
+      </c>
+      <c r="P72">
+        <v>0.09</v>
+      </c>
+      <c r="Q72">
+        <v>-0.01</v>
+      </c>
+      <c r="R72">
+        <v>40000000</v>
+      </c>
+      <c r="S72">
+        <v>67000000</v>
+      </c>
+      <c r="T72">
+        <v>50000000</v>
+      </c>
+      <c r="U72">
+        <v>-8000000</v>
+      </c>
+      <c r="V72" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22">
+      <c r="A73" t="s">
+        <v>93</v>
+      </c>
+      <c r="B73" t="s">
+        <v>129</v>
+      </c>
+      <c r="C73" t="s">
+        <v>180</v>
+      </c>
+      <c r="D73" t="s">
+        <v>265</v>
+      </c>
+      <c r="E73">
+        <v>277</v>
+      </c>
+      <c r="F73">
+        <v>1409940</v>
+      </c>
+      <c r="G73">
+        <v>267.9556008911133</v>
+      </c>
+      <c r="H73">
+        <v>254.3462000528971</v>
+      </c>
+      <c r="I73">
+        <v>251.99375</v>
+      </c>
+      <c r="J73">
+        <v>246.9507498168945</v>
+      </c>
+      <c r="K73">
+        <v>0.6767919063568115</v>
+      </c>
+      <c r="L73">
+        <v>283.5899963378906</v>
+      </c>
+      <c r="M73">
+        <v>105.7641433702202</v>
+      </c>
+      <c r="N73">
+        <v>0.92</v>
+      </c>
+      <c r="O73">
+        <v>1.7</v>
+      </c>
+      <c r="P73">
+        <v>1.53</v>
+      </c>
+      <c r="Q73">
+        <v>1.36</v>
+      </c>
+      <c r="R73">
+        <v>287000000</v>
+      </c>
+      <c r="S73">
+        <v>509000000</v>
+      </c>
+      <c r="T73">
+        <v>460000000</v>
+      </c>
+      <c r="U73">
+        <v>407000000</v>
+      </c>
+      <c r="V73" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22">
+      <c r="A74" t="s">
+        <v>94</v>
+      </c>
+      <c r="B74" t="s">
+        <v>127</v>
+      </c>
+      <c r="C74" t="s">
+        <v>175</v>
+      </c>
+      <c r="D74" t="s">
+        <v>266</v>
+      </c>
+      <c r="E74">
+        <v>27.45999908447266</v>
+      </c>
+      <c r="F74">
+        <v>1931340</v>
+      </c>
+      <c r="G74">
+        <v>26.71140007019043</v>
+      </c>
+      <c r="H74">
+        <v>25.59860001881917</v>
+      </c>
+      <c r="I74">
+        <v>24.72430004119873</v>
+      </c>
+      <c r="J74">
+        <v>24.26184997558594</v>
+      </c>
+      <c r="K74">
+        <v>4.829999923706055</v>
+      </c>
+      <c r="L74">
+        <v>31.60000038146973</v>
+      </c>
+      <c r="M74">
+        <v>105.5597458206934</v>
+      </c>
+      <c r="N74">
+        <v>0.34</v>
+      </c>
+      <c r="O74">
+        <v>0.61</v>
+      </c>
+      <c r="P74">
+        <v>0.93</v>
+      </c>
+      <c r="Q74">
+        <v>0.7</v>
+      </c>
+      <c r="R74">
+        <v>31986000</v>
+      </c>
+      <c r="S74">
+        <v>58045000</v>
+      </c>
+      <c r="T74">
+        <v>91311000</v>
+      </c>
+      <c r="U74">
+        <v>68277000</v>
+      </c>
+      <c r="V74" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22">
+      <c r="A75" t="s">
+        <v>95</v>
+      </c>
+      <c r="B75" t="s">
+        <v>127</v>
+      </c>
+      <c r="C75" t="s">
+        <v>181</v>
+      </c>
+      <c r="D75" t="s">
+        <v>267</v>
+      </c>
+      <c r="E75">
+        <v>14.64000034332275</v>
+      </c>
+      <c r="F75">
+        <v>388986.6666666667</v>
+      </c>
+      <c r="G75">
+        <v>14.16659999847412</v>
+      </c>
+      <c r="H75">
+        <v>13.13653334299723</v>
+      </c>
+      <c r="I75">
+        <v>12.55985000610351</v>
+      </c>
+      <c r="J75">
+        <v>12.08455000400543</v>
+      </c>
+      <c r="K75">
+        <v>9.039999961853027</v>
+      </c>
+      <c r="L75">
+        <v>16.02000045776367</v>
+      </c>
+      <c r="M75">
+        <v>105.5049401655169</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>0</v>
+      </c>
+      <c r="T75">
+        <v>0</v>
+      </c>
+      <c r="U75">
+        <v>0</v>
+      </c>
+      <c r="V75" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22">
+      <c r="A76" t="s">
+        <v>96</v>
+      </c>
+      <c r="B76" t="s">
+        <v>132</v>
+      </c>
+      <c r="C76" t="s">
+        <v>169</v>
+      </c>
+      <c r="D76" t="s">
+        <v>268</v>
+      </c>
+      <c r="E76">
+        <v>200.1100006103516</v>
+      </c>
+      <c r="F76">
+        <v>1473126.666666667</v>
+      </c>
+      <c r="G76">
+        <v>192.2942007446289</v>
+      </c>
+      <c r="H76">
+        <v>186.7160670979818</v>
+      </c>
+      <c r="I76">
+        <v>183.5623002624512</v>
+      </c>
+      <c r="J76">
+        <v>180.4765001678467</v>
+      </c>
+      <c r="K76">
+        <v>4.878548622131348</v>
+      </c>
+      <c r="L76">
+        <v>250.7599945068359</v>
+      </c>
+      <c r="M76">
+        <v>105.4329235796929</v>
+      </c>
+      <c r="N76">
+        <v>1.87</v>
+      </c>
+      <c r="O76">
+        <v>1.75</v>
+      </c>
+      <c r="P76">
+        <v>2.43</v>
+      </c>
+      <c r="Q76">
+        <v>2.14</v>
+      </c>
+      <c r="R76">
+        <v>679600000</v>
+      </c>
+      <c r="S76">
+        <v>637900000</v>
+      </c>
+      <c r="T76">
+        <v>883800000</v>
+      </c>
+      <c r="U76">
+        <v>777600000</v>
+      </c>
+      <c r="V76" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22">
+      <c r="A77" t="s">
+        <v>97</v>
+      </c>
+      <c r="B77" t="s">
+        <v>132</v>
+      </c>
+      <c r="C77" t="s">
+        <v>182</v>
+      </c>
+      <c r="D77" t="s">
+        <v>269</v>
+      </c>
+      <c r="E77">
+        <v>72.30000305175781</v>
+      </c>
+      <c r="F77">
+        <v>1039560</v>
+      </c>
+      <c r="G77">
+        <v>69.40300018310546</v>
+      </c>
+      <c r="H77">
+        <v>63.08726659138998</v>
+      </c>
+      <c r="I77">
+        <v>61.78879991531372</v>
+      </c>
+      <c r="J77">
+        <v>60.64319993972779</v>
+      </c>
+      <c r="K77">
+        <v>0.03246002644300461</v>
+      </c>
+      <c r="L77">
+        <v>73.40000152587891</v>
+      </c>
+      <c r="M77">
+        <v>105.3807756364774</v>
+      </c>
+      <c r="N77">
+        <v>0.57</v>
+      </c>
+      <c r="O77">
+        <v>0.51</v>
+      </c>
+      <c r="P77">
+        <v>0.83</v>
+      </c>
+      <c r="Q77">
+        <v>0.67</v>
+      </c>
+      <c r="R77">
+        <v>161100000</v>
+      </c>
+      <c r="S77">
+        <v>145200000</v>
+      </c>
+      <c r="T77">
+        <v>235500000</v>
+      </c>
+      <c r="U77">
+        <v>190400000</v>
+      </c>
+      <c r="V77" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22">
+      <c r="A78" t="s">
+        <v>98</v>
+      </c>
+      <c r="B78" t="s">
+        <v>126</v>
+      </c>
+      <c r="C78" t="s">
+        <v>158</v>
+      </c>
+      <c r="D78" t="s">
+        <v>270</v>
+      </c>
+      <c r="E78">
+        <v>262.0299987792969</v>
+      </c>
+      <c r="F78">
+        <v>487563.3333333333</v>
+      </c>
+      <c r="G78">
+        <v>252.7934008789063</v>
+      </c>
+      <c r="H78">
+        <v>227.6959339396159</v>
+      </c>
+      <c r="I78">
+        <v>217.7480503845215</v>
+      </c>
+      <c r="J78">
+        <v>209.5973002624512</v>
+      </c>
+      <c r="K78">
+        <v>25.25</v>
+      </c>
+      <c r="L78">
+        <v>328.8500061035156</v>
+      </c>
+      <c r="M78">
+        <v>105.3355464761853</v>
+      </c>
+      <c r="N78">
+        <v>3.29</v>
+      </c>
+      <c r="O78">
+        <v>3.03</v>
+      </c>
+      <c r="P78">
+        <v>2.88</v>
+      </c>
+      <c r="Q78">
+        <v>3.2</v>
+      </c>
+      <c r="R78">
+        <v>248885000</v>
+      </c>
+      <c r="S78">
+        <v>225319000</v>
+      </c>
+      <c r="T78">
+        <v>214835000</v>
+      </c>
+      <c r="U78">
+        <v>239702000</v>
+      </c>
+      <c r="V78" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22">
+      <c r="A79" t="s">
+        <v>99</v>
+      </c>
+      <c r="B79" t="s">
+        <v>127</v>
+      </c>
+      <c r="C79" t="s">
+        <v>183</v>
+      </c>
+      <c r="D79" t="s">
+        <v>271</v>
+      </c>
+      <c r="E79">
+        <v>198.7899932861328</v>
+      </c>
+      <c r="F79">
+        <v>2389010</v>
+      </c>
+      <c r="G79">
+        <v>192.5491986083984</v>
+      </c>
+      <c r="H79">
+        <v>178.1313327026367</v>
+      </c>
+      <c r="I79">
+        <v>172.7971997833252</v>
+      </c>
+      <c r="J79">
+        <v>167.4446499633789</v>
+      </c>
+      <c r="K79">
+        <v>7.491692066192627</v>
+      </c>
+      <c r="L79">
+        <v>208.5099945068359</v>
+      </c>
+      <c r="M79">
+        <v>105.2915371468971</v>
+      </c>
+      <c r="N79">
+        <v>1.94</v>
+      </c>
+      <c r="O79">
+        <v>2.12</v>
+      </c>
+      <c r="P79">
+        <v>2.43</v>
+      </c>
+      <c r="Q79">
+        <v>2.38</v>
+      </c>
+      <c r="R79">
+        <v>630000000</v>
+      </c>
+      <c r="S79">
+        <v>673000000</v>
+      </c>
+      <c r="T79">
+        <v>757000000</v>
+      </c>
+      <c r="U79">
+        <v>726000000</v>
+      </c>
+      <c r="V79" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22">
+      <c r="A80" t="s">
+        <v>100</v>
+      </c>
+      <c r="B80" t="s">
+        <v>129</v>
+      </c>
+      <c r="C80" t="s">
+        <v>180</v>
+      </c>
+      <c r="D80" t="s">
+        <v>262</v>
+      </c>
+      <c r="E80">
+        <v>391.7200012207031</v>
+      </c>
+      <c r="F80">
+        <v>390816.6666666667</v>
+      </c>
+      <c r="G80">
+        <v>379.1649987792969</v>
+      </c>
+      <c r="H80">
+        <v>345.8093330891927</v>
+      </c>
+      <c r="I80">
+        <v>318.6043995666504</v>
+      </c>
+      <c r="J80">
+        <v>303.5658995819092</v>
+      </c>
+      <c r="K80">
+        <v>0.2751234471797943</v>
+      </c>
+      <c r="L80">
+        <v>471.1166076660156</v>
+      </c>
+      <c r="M80">
+        <v>105.1201583447916</v>
+      </c>
+      <c r="N80">
+        <v>1.59</v>
+      </c>
+      <c r="O80">
+        <v>1.36</v>
+      </c>
+      <c r="P80">
+        <v>1.85</v>
+      </c>
+      <c r="Q80">
+        <v>2.06</v>
+      </c>
+      <c r="R80">
+        <v>120600000</v>
+      </c>
+      <c r="S80">
+        <v>103000000</v>
+      </c>
+      <c r="T80">
+        <v>140000000</v>
+      </c>
+      <c r="U80">
+        <v>155100000</v>
+      </c>
+      <c r="V80" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22">
+      <c r="A81" t="s">
+        <v>101</v>
+      </c>
+      <c r="B81" t="s">
+        <v>127</v>
+      </c>
+      <c r="C81" t="s">
+        <v>138</v>
+      </c>
+      <c r="D81" t="s">
+        <v>272</v>
+      </c>
+      <c r="E81">
+        <v>88.30999755859375</v>
+      </c>
+      <c r="F81">
+        <v>4686530</v>
+      </c>
+      <c r="G81">
+        <v>85.20799972534179</v>
+      </c>
+      <c r="H81">
+        <v>80.49139999389648</v>
+      </c>
+      <c r="I81">
+        <v>80.04880004882813</v>
+      </c>
+      <c r="J81">
+        <v>78.15100017547607</v>
+      </c>
+      <c r="K81">
+        <v>1.578974479343742E-05</v>
+      </c>
+      <c r="L81">
+        <v>90.01000213623047</v>
+      </c>
+      <c r="M81">
+        <v>105.0972919185189</v>
+      </c>
+      <c r="N81">
+        <v>0.91</v>
+      </c>
+      <c r="O81">
+        <v>0.89</v>
+      </c>
+      <c r="P81">
+        <v>0.76</v>
+      </c>
+      <c r="Q81">
+        <v>0.85</v>
+      </c>
+      <c r="R81">
+        <v>1062806000</v>
+      </c>
+      <c r="S81">
+        <v>1038000000</v>
+      </c>
+      <c r="T81">
+        <v>891000000</v>
+      </c>
+      <c r="U81">
+        <v>989000000</v>
+      </c>
+      <c r="V81" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22">
+      <c r="A82" t="s">
+        <v>102</v>
+      </c>
+      <c r="B82" t="s">
+        <v>128</v>
+      </c>
+      <c r="C82" t="s">
+        <v>184</v>
+      </c>
+      <c r="D82" t="s">
+        <v>273</v>
+      </c>
+      <c r="E82">
+        <v>60.06000137329102</v>
+      </c>
+      <c r="F82">
+        <v>1567086.666666667</v>
+      </c>
+      <c r="G82">
+        <v>58.15279991149902</v>
+      </c>
+      <c r="H82">
+        <v>57.55793324788412</v>
+      </c>
+      <c r="I82">
+        <v>57.45959991455078</v>
+      </c>
+      <c r="J82">
+        <v>57.09769994735718</v>
+      </c>
+      <c r="K82">
+        <v>1.790570735931396</v>
+      </c>
+      <c r="L82">
+        <v>67.36532592773438</v>
+      </c>
+      <c r="M82">
+        <v>105.0577261019518</v>
+      </c>
+      <c r="N82">
+        <v>2.49</v>
+      </c>
+      <c r="O82">
+        <v>1.36</v>
+      </c>
+      <c r="P82">
+        <v>1.62</v>
+      </c>
+      <c r="Q82">
+        <v>1.32</v>
+      </c>
+      <c r="R82">
+        <v>2814000000</v>
+      </c>
+      <c r="S82">
+        <v>1520000000</v>
+      </c>
+      <c r="T82">
+        <v>1799000000</v>
+      </c>
+      <c r="U82">
+        <v>1463000000</v>
+      </c>
+      <c r="V82" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22">
+      <c r="A83" t="s">
+        <v>103</v>
+      </c>
+      <c r="B83" t="s">
+        <v>130</v>
+      </c>
+      <c r="C83" t="s">
+        <v>185</v>
+      </c>
+      <c r="D83" t="s">
+        <v>274</v>
+      </c>
+      <c r="E83">
+        <v>115.1900024414062</v>
+      </c>
+      <c r="F83">
+        <v>485606.6666666667</v>
+      </c>
+      <c r="G83">
+        <v>111.0426000976562</v>
+      </c>
+      <c r="H83">
+        <v>99.38306681315105</v>
+      </c>
+      <c r="I83">
+        <v>94.26455005645752</v>
+      </c>
+      <c r="J83">
+        <v>89.68999990463257</v>
+      </c>
+      <c r="K83">
+        <v>3.7671959400177</v>
+      </c>
+      <c r="L83">
+        <v>116.620002746582</v>
+      </c>
+      <c r="M83">
+        <v>105.0226492214299</v>
+      </c>
+      <c r="N83">
+        <v>6.007446</v>
+      </c>
+      <c r="O83">
+        <v>2.692395</v>
+      </c>
+      <c r="P83">
+        <v>26.872532</v>
+      </c>
+      <c r="Q83">
+        <v>3.445282</v>
+      </c>
+      <c r="R83">
+        <v>10748000000</v>
+      </c>
+      <c r="S83">
+        <v>4817000000</v>
+      </c>
+      <c r="T83">
+        <v>48078000000</v>
+      </c>
+      <c r="U83">
+        <v>6164000000</v>
+      </c>
+      <c r="V83" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22">
+      <c r="A84" t="s">
+        <v>104</v>
+      </c>
+      <c r="B84" t="s">
+        <v>132</v>
+      </c>
+      <c r="C84" t="s">
+        <v>186</v>
+      </c>
+      <c r="D84" t="s">
+        <v>275</v>
+      </c>
+      <c r="E84">
+        <v>56.11000061035156</v>
+      </c>
+      <c r="F84">
+        <v>585523.3333333334</v>
+      </c>
+      <c r="G84">
+        <v>53.89139991760254</v>
+      </c>
+      <c r="H84">
+        <v>47.65319999694825</v>
+      </c>
+      <c r="I84">
+        <v>46.38929998397827</v>
+      </c>
+      <c r="J84">
+        <v>44.78490001678467</v>
+      </c>
+      <c r="K84">
+        <v>5.159999847412109</v>
+      </c>
+      <c r="L84">
+        <v>59.47999954223633</v>
+      </c>
+      <c r="M84">
+        <v>104.9983361047902</v>
+      </c>
+      <c r="N84">
+        <v>1.55</v>
+      </c>
+      <c r="O84">
+        <v>0.01</v>
+      </c>
+      <c r="P84">
+        <v>0.52</v>
+      </c>
+      <c r="Q84">
+        <v>2.07</v>
+      </c>
+      <c r="R84">
+        <v>113000000</v>
+      </c>
+      <c r="S84">
+        <v>1000000</v>
+      </c>
+      <c r="T84">
+        <v>37000000</v>
+      </c>
+      <c r="U84">
+        <v>142000000</v>
+      </c>
+      <c r="V84" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22">
+      <c r="A85" t="s">
+        <v>105</v>
+      </c>
+      <c r="B85" t="s">
+        <v>125</v>
+      </c>
+      <c r="C85" t="s">
+        <v>187</v>
+      </c>
+      <c r="D85" t="s">
+        <v>276</v>
+      </c>
+      <c r="E85">
+        <v>72.77999877929688</v>
+      </c>
+      <c r="F85">
+        <v>646973.3333333334</v>
+      </c>
+      <c r="G85">
+        <v>70.71040008544922</v>
+      </c>
+      <c r="H85">
+        <v>65.35706693013509</v>
+      </c>
+      <c r="I85">
+        <v>63.74355010986328</v>
+      </c>
+      <c r="J85">
+        <v>62.04700019836426</v>
+      </c>
+      <c r="K85">
+        <v>11.89461898803711</v>
+      </c>
+      <c r="L85">
+        <v>75.69999694824219</v>
+      </c>
+      <c r="M85">
+        <v>104.9689306974707</v>
+      </c>
+      <c r="N85">
+        <v>0.67</v>
+      </c>
+      <c r="O85">
+        <v>0.47</v>
+      </c>
+      <c r="P85">
+        <v>0.67</v>
+      </c>
+      <c r="Q85">
+        <v>0.64</v>
+      </c>
+      <c r="R85">
+        <v>61603000</v>
+      </c>
+      <c r="S85">
+        <v>42965000</v>
+      </c>
+      <c r="T85">
+        <v>61092000</v>
+      </c>
+      <c r="U85">
+        <v>58597000</v>
+      </c>
+      <c r="V85" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22">
+      <c r="A86" t="s">
+        <v>106</v>
+      </c>
+      <c r="B86" t="s">
+        <v>127</v>
+      </c>
+      <c r="C86" t="s">
+        <v>165</v>
+      </c>
+      <c r="D86" t="s">
+        <v>277</v>
+      </c>
+      <c r="E86">
+        <v>92.47000122070312</v>
+      </c>
+      <c r="F86">
+        <v>347113.3333333333</v>
+      </c>
+      <c r="G86">
+        <v>90.63320022583008</v>
+      </c>
+      <c r="H86">
+        <v>72.59106686909993</v>
+      </c>
+      <c r="I86">
+        <v>66.03260013580322</v>
+      </c>
+      <c r="J86">
+        <v>60.36480007171631</v>
+      </c>
+      <c r="K86">
+        <v>3.118403196334839</v>
+      </c>
+      <c r="L86">
+        <v>100</v>
+      </c>
+      <c r="M86">
+        <v>104.9358479984597</v>
+      </c>
+      <c r="N86">
+        <v>4.67</v>
+      </c>
+      <c r="O86">
+        <v>4.65</v>
+      </c>
+      <c r="P86">
+        <v>3.64</v>
+      </c>
+      <c r="Q86">
+        <v>4.12</v>
+      </c>
+      <c r="R86">
+        <v>131590000</v>
+      </c>
+      <c r="S86">
+        <v>130395000</v>
+      </c>
+      <c r="T86">
+        <v>103066000</v>
+      </c>
+      <c r="U86">
+        <v>118001000</v>
+      </c>
+      <c r="V86" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22">
+      <c r="A87" t="s">
+        <v>107</v>
+      </c>
+      <c r="B87" t="s">
+        <v>127</v>
+      </c>
+      <c r="C87" t="s">
+        <v>183</v>
+      </c>
+      <c r="D87" t="s">
+        <v>278</v>
+      </c>
+      <c r="E87">
+        <v>125.9199981689453</v>
+      </c>
+      <c r="F87">
+        <v>475033.3333333333</v>
+      </c>
+      <c r="G87">
+        <v>123.3025996398926</v>
+      </c>
+      <c r="H87">
+        <v>121.787533416748</v>
+      </c>
+      <c r="I87">
+        <v>120.7465002059937</v>
+      </c>
+      <c r="J87">
+        <v>120.0813003921509</v>
+      </c>
+      <c r="K87">
+        <v>2.157197952270508</v>
+      </c>
+      <c r="L87">
+        <v>155.7525024414062</v>
+      </c>
+      <c r="M87">
+        <v>104.8787987073611</v>
+      </c>
+      <c r="N87">
+        <v>1.85</v>
+      </c>
+      <c r="O87">
+        <v>1.04</v>
+      </c>
+      <c r="P87">
+        <v>1.02</v>
+      </c>
+      <c r="Q87">
+        <v>1.65</v>
+      </c>
+      <c r="R87">
+        <v>103080000</v>
+      </c>
+      <c r="S87">
+        <v>55513000</v>
+      </c>
+      <c r="T87">
+        <v>52820000</v>
+      </c>
+      <c r="U87">
+        <v>84710000</v>
+      </c>
+      <c r="V87" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22">
+      <c r="A88" t="s">
+        <v>108</v>
+      </c>
+      <c r="B88" t="s">
+        <v>134</v>
+      </c>
+      <c r="C88" t="s">
+        <v>188</v>
+      </c>
+      <c r="D88" t="s">
+        <v>279</v>
+      </c>
+      <c r="E88">
+        <v>130.4199981689453</v>
+      </c>
+      <c r="F88">
+        <v>23184020</v>
+      </c>
+      <c r="G88">
+        <v>125.6327998352051</v>
+      </c>
+      <c r="H88">
+        <v>112.6160334777832</v>
+      </c>
+      <c r="I88">
+        <v>107.773175163269</v>
+      </c>
+      <c r="J88">
+        <v>104.3753751754761</v>
+      </c>
+      <c r="K88">
+        <v>2.490912914276123</v>
+      </c>
+      <c r="L88">
+        <v>150.7089996337891</v>
+      </c>
+      <c r="M88">
+        <v>104.8125569841868</v>
+      </c>
+      <c r="N88">
+        <v>1.06</v>
+      </c>
+      <c r="O88">
+        <v>1.05</v>
+      </c>
+      <c r="P88">
+        <v>1.17</v>
+      </c>
+      <c r="Q88">
+        <v>1.44</v>
+      </c>
+      <c r="R88">
+        <v>13910000000</v>
+      </c>
+      <c r="S88">
+        <v>13624000000</v>
+      </c>
+      <c r="T88">
+        <v>15051000000</v>
+      </c>
+      <c r="U88">
+        <v>18368000000</v>
+      </c>
+      <c r="V88" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22">
+      <c r="A89" t="s">
+        <v>109</v>
+      </c>
+      <c r="B89" t="s">
+        <v>134</v>
+      </c>
+      <c r="C89" t="s">
+        <v>188</v>
+      </c>
+      <c r="D89" t="s">
+        <v>279</v>
+      </c>
+      <c r="E89">
+        <v>129.7799987792969</v>
+      </c>
+      <c r="F89">
+        <v>31041993.33333333</v>
+      </c>
+      <c r="G89">
+        <v>125.065799407959</v>
+      </c>
+      <c r="H89">
+        <v>112.021866607666</v>
+      </c>
+      <c r="I89">
+        <v>107.2197500228882</v>
+      </c>
+      <c r="J89">
+        <v>103.8281000518799</v>
+      </c>
+      <c r="K89">
+        <v>2.502753019332886</v>
+      </c>
+      <c r="L89">
+        <v>149.8385009765625</v>
+      </c>
+      <c r="M89">
+        <v>104.7790180415666</v>
+      </c>
+      <c r="N89">
+        <v>1.06</v>
+      </c>
+      <c r="O89">
+        <v>1.05</v>
+      </c>
+      <c r="P89">
+        <v>1.17</v>
+      </c>
+      <c r="Q89">
+        <v>1.44</v>
+      </c>
+      <c r="R89">
+        <v>13910000000</v>
+      </c>
+      <c r="S89">
+        <v>13624000000</v>
+      </c>
+      <c r="T89">
+        <v>15051000000</v>
+      </c>
+      <c r="U89">
+        <v>18368000000</v>
+      </c>
+      <c r="V89" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22">
+      <c r="A90" t="s">
+        <v>110</v>
+      </c>
+      <c r="B90" t="s">
+        <v>125</v>
+      </c>
+      <c r="C90" t="s">
+        <v>189</v>
+      </c>
+      <c r="D90" t="s">
+        <v>280</v>
+      </c>
+      <c r="E90">
+        <v>357.6700134277344</v>
+      </c>
+      <c r="F90">
+        <v>282586.6666666667</v>
+      </c>
+      <c r="G90">
+        <v>341.8116003417969</v>
+      </c>
+      <c r="H90">
+        <v>290.209067586263</v>
+      </c>
+      <c r="I90">
+        <v>281.0186503601074</v>
+      </c>
+      <c r="J90">
+        <v>267.09255027771</v>
+      </c>
+      <c r="K90">
+        <v>4.775613307952881</v>
+      </c>
+      <c r="L90">
+        <v>377.3800048828125</v>
+      </c>
+      <c r="M90">
+        <v>104.76324824368</v>
+      </c>
+      <c r="N90">
+        <v>3.99</v>
+      </c>
+      <c r="O90">
+        <v>2.65</v>
+      </c>
+      <c r="P90">
+        <v>2.75</v>
+      </c>
+      <c r="Q90">
+        <v>6.1</v>
+      </c>
+      <c r="R90">
+        <v>141900000</v>
+      </c>
+      <c r="S90">
+        <v>94400000</v>
+      </c>
+      <c r="T90">
+        <v>98000000</v>
+      </c>
+      <c r="U90">
+        <v>217200000</v>
+      </c>
+      <c r="V90" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22">
+      <c r="A91" t="s">
+        <v>111</v>
+      </c>
+      <c r="B91" t="s">
+        <v>132</v>
+      </c>
+      <c r="C91" t="s">
+        <v>172</v>
+      </c>
+      <c r="D91" t="s">
+        <v>281</v>
+      </c>
+      <c r="E91">
+        <v>50.41999816894531</v>
+      </c>
+      <c r="F91">
+        <v>430553.3333333333</v>
+      </c>
+      <c r="G91">
+        <v>48.64859985351563</v>
+      </c>
+      <c r="H91">
+        <v>44.43579996744791</v>
+      </c>
+      <c r="I91">
+        <v>43.02159999847412</v>
+      </c>
+      <c r="J91">
+        <v>41.63230001449585</v>
+      </c>
+      <c r="K91">
+        <v>16.02964210510254</v>
+      </c>
+      <c r="L91">
+        <v>53.82002639770508</v>
+      </c>
+      <c r="M91">
+        <v>104.7227794095532</v>
+      </c>
+      <c r="N91">
+        <v>1.66</v>
+      </c>
+      <c r="O91">
+        <v>1.37</v>
+      </c>
+      <c r="P91">
+        <v>1.59</v>
+      </c>
+      <c r="Q91">
+        <v>1.61</v>
+      </c>
+      <c r="R91">
+        <v>178051000</v>
+      </c>
+      <c r="S91">
+        <v>147366000</v>
+      </c>
+      <c r="T91">
+        <v>170827000</v>
+      </c>
+      <c r="U91">
+        <v>172233000</v>
+      </c>
+      <c r="V91" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22">
+      <c r="A92" t="s">
+        <v>112</v>
+      </c>
+      <c r="B92" t="s">
+        <v>125</v>
+      </c>
+      <c r="C92" t="s">
+        <v>136</v>
+      </c>
+      <c r="D92" t="s">
+        <v>282</v>
+      </c>
+      <c r="E92">
+        <v>33.40000152587891</v>
+      </c>
+      <c r="F92">
+        <v>277236.6666666667</v>
+      </c>
+      <c r="G92">
+        <v>31.8068000793457</v>
+      </c>
+      <c r="H92">
+        <v>28.90386661529541</v>
+      </c>
+      <c r="I92">
+        <v>28.66559995651245</v>
+      </c>
+      <c r="J92">
+        <v>28.2903999710083</v>
+      </c>
+      <c r="K92">
+        <v>8.170000076293945</v>
+      </c>
+      <c r="L92">
+        <v>42.15000152587891</v>
+      </c>
+      <c r="M92">
+        <v>104.6647527521165</v>
+      </c>
+      <c r="N92">
+        <v>0.25</v>
+      </c>
+      <c r="O92">
+        <v>0.04</v>
+      </c>
+      <c r="P92">
+        <v>-0.11</v>
+      </c>
+      <c r="Q92">
+        <v>0.41</v>
+      </c>
+      <c r="R92">
+        <v>13115000</v>
+      </c>
+      <c r="S92">
+        <v>1892000</v>
+      </c>
+      <c r="T92">
+        <v>-5481000</v>
+      </c>
+      <c r="U92">
+        <v>21677000</v>
+      </c>
+      <c r="V92" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22">
+      <c r="A93" t="s">
+        <v>113</v>
+      </c>
+      <c r="B93" t="s">
+        <v>125</v>
+      </c>
+      <c r="C93" t="s">
+        <v>151</v>
+      </c>
+      <c r="D93" t="s">
+        <v>283</v>
+      </c>
+      <c r="E93">
+        <v>104.629997253418</v>
+      </c>
+      <c r="F93">
+        <v>476700</v>
+      </c>
+      <c r="G93">
+        <v>102.9543998718262</v>
+      </c>
+      <c r="H93">
+        <v>95.12453308105469</v>
+      </c>
+      <c r="I93">
+        <v>90.6306498336792</v>
+      </c>
+      <c r="J93">
+        <v>87.26699989318848</v>
+      </c>
+      <c r="K93">
+        <v>3.099249601364136</v>
+      </c>
+      <c r="L93">
+        <v>121.8199996948242</v>
+      </c>
+      <c r="M93">
+        <v>104.5689609783173</v>
+      </c>
+      <c r="N93">
+        <v>3.5</v>
+      </c>
+      <c r="O93">
+        <v>1.48</v>
+      </c>
+      <c r="P93">
+        <v>2.84</v>
+      </c>
+      <c r="Q93">
+        <v>1.64</v>
+      </c>
+      <c r="R93">
+        <v>88842000</v>
+      </c>
+      <c r="S93">
+        <v>37337000</v>
+      </c>
+      <c r="T93">
+        <v>71283000</v>
+      </c>
+      <c r="U93">
+        <v>40443000</v>
+      </c>
+      <c r="V93" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22">
+      <c r="A94" t="s">
+        <v>114</v>
+      </c>
+      <c r="B94" t="s">
+        <v>134</v>
+      </c>
+      <c r="C94" t="s">
+        <v>153</v>
+      </c>
+      <c r="D94" t="s">
+        <v>284</v>
+      </c>
+      <c r="E94">
+        <v>91.41000366210938</v>
+      </c>
+      <c r="F94">
+        <v>12174390</v>
+      </c>
+      <c r="G94">
+        <v>88.51100021362305</v>
+      </c>
+      <c r="H94">
+        <v>82.34526636759441</v>
+      </c>
+      <c r="I94">
+        <v>80.6103998184204</v>
+      </c>
+      <c r="J94">
+        <v>78.73784984588623</v>
+      </c>
+      <c r="K94">
+        <v>0.2601212561130524</v>
+      </c>
+      <c r="L94">
+        <v>103.3097839355469</v>
+      </c>
+      <c r="M94">
+        <v>104.5297710479697</v>
+      </c>
+      <c r="N94">
+        <v>0.55</v>
+      </c>
+      <c r="O94">
+        <v>0.51</v>
+      </c>
+      <c r="P94">
+        <v>0.93</v>
+      </c>
+      <c r="Q94">
+        <v>0.74</v>
+      </c>
+      <c r="R94">
+        <v>435000000</v>
+      </c>
+      <c r="S94">
+        <v>403000000</v>
+      </c>
+      <c r="T94">
+        <v>740000000</v>
+      </c>
+      <c r="U94">
+        <v>587000000</v>
+      </c>
+      <c r="V94" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22">
+      <c r="A95" t="s">
+        <v>115</v>
+      </c>
+      <c r="B95" t="s">
+        <v>130</v>
+      </c>
+      <c r="C95" t="s">
+        <v>190</v>
+      </c>
+      <c r="D95" t="s">
+        <v>285</v>
+      </c>
+      <c r="E95">
+        <v>61.25</v>
+      </c>
+      <c r="F95">
+        <v>881170</v>
+      </c>
+      <c r="G95">
+        <v>59.88620025634766</v>
+      </c>
+      <c r="H95">
+        <v>59.13993344624837</v>
+      </c>
+      <c r="I95">
+        <v>59.05084997177124</v>
+      </c>
+      <c r="J95">
+        <v>57.88059997558594</v>
+      </c>
+      <c r="K95">
+        <v>11.42000007629395</v>
+      </c>
+      <c r="L95">
+        <v>63</v>
+      </c>
+      <c r="M95">
+        <v>104.5212119210419</v>
+      </c>
+      <c r="N95">
+        <v>0.62</v>
+      </c>
+      <c r="O95">
+        <v>0.46</v>
+      </c>
+      <c r="P95">
+        <v>0.51</v>
+      </c>
+      <c r="Q95">
+        <v>0.96</v>
+      </c>
+      <c r="R95">
+        <v>95700000</v>
+      </c>
+      <c r="S95">
+        <v>71100000</v>
+      </c>
+      <c r="T95">
+        <v>80300000</v>
+      </c>
+      <c r="U95">
+        <v>150100000</v>
+      </c>
+      <c r="V95" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22">
+      <c r="A96" t="s">
+        <v>116</v>
+      </c>
+      <c r="B96" t="s">
+        <v>129</v>
+      </c>
+      <c r="C96" t="s">
+        <v>191</v>
+      </c>
+      <c r="D96" t="s">
+        <v>286</v>
+      </c>
+      <c r="E96">
+        <v>252.9600067138672</v>
+      </c>
+      <c r="F96">
+        <v>622660</v>
+      </c>
+      <c r="G96">
+        <v>245.2760000610351</v>
+      </c>
+      <c r="H96">
+        <v>225.7370673624675</v>
+      </c>
+      <c r="I96">
+        <v>221.0199006652832</v>
+      </c>
+      <c r="J96">
+        <v>214.4346504211426</v>
+      </c>
+      <c r="K96">
+        <v>3</v>
+      </c>
+      <c r="L96">
+        <v>309.7000122070312</v>
+      </c>
+      <c r="M96">
+        <v>104.4692056608185</v>
+      </c>
+      <c r="N96">
+        <v>1.94</v>
+      </c>
+      <c r="O96">
+        <v>1.42</v>
+      </c>
+      <c r="P96">
+        <v>1.41</v>
+      </c>
+      <c r="Q96">
+        <v>1.4</v>
+      </c>
+      <c r="R96">
+        <v>160154000</v>
+      </c>
+      <c r="S96">
+        <v>117445000</v>
+      </c>
+      <c r="T96">
+        <v>116654000</v>
+      </c>
+      <c r="U96">
+        <v>115598000</v>
+      </c>
+      <c r="V96" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22">
+      <c r="A97" t="s">
+        <v>117</v>
+      </c>
+      <c r="B97" t="s">
+        <v>131</v>
+      </c>
+      <c r="C97" t="s">
+        <v>192</v>
+      </c>
+      <c r="D97" t="s">
+        <v>287</v>
+      </c>
+      <c r="E97">
+        <v>97.27999877929688</v>
+      </c>
+      <c r="F97">
+        <v>2078720</v>
+      </c>
+      <c r="G97">
+        <v>93.84759979248047</v>
+      </c>
+      <c r="H97">
+        <v>93.06926666259766</v>
+      </c>
+      <c r="I97">
+        <v>91.07365005493165</v>
+      </c>
+      <c r="J97">
+        <v>89.24980014801025</v>
+      </c>
+      <c r="K97">
+        <v>6.756211280822754</v>
+      </c>
+      <c r="L97">
+        <v>117.0800018310547</v>
+      </c>
+      <c r="M97">
+        <v>104.325574406182</v>
+      </c>
+      <c r="N97">
+        <v>1.75</v>
+      </c>
+      <c r="O97">
+        <v>1.07</v>
+      </c>
+      <c r="P97">
+        <v>1.44</v>
+      </c>
+      <c r="Q97">
+        <v>2.18</v>
+      </c>
+      <c r="R97">
+        <v>570000000</v>
+      </c>
+      <c r="S97">
+        <v>351000000</v>
+      </c>
+      <c r="T97">
+        <v>472000000</v>
+      </c>
+      <c r="U97">
+        <v>714000000</v>
+      </c>
+      <c r="V97" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22">
+      <c r="A98" t="s">
+        <v>118</v>
+      </c>
+      <c r="B98" t="s">
+        <v>131</v>
+      </c>
+      <c r="C98" t="s">
+        <v>192</v>
+      </c>
+      <c r="D98" t="s">
+        <v>288</v>
+      </c>
+      <c r="E98">
+        <v>129.7100067138672</v>
+      </c>
+      <c r="F98">
+        <v>451346.6666666667</v>
+      </c>
+      <c r="G98">
+        <v>125.962799987793</v>
+      </c>
+      <c r="H98">
+        <v>119.1023336283366</v>
+      </c>
+      <c r="I98">
+        <v>115.9125003051758</v>
+      </c>
+      <c r="J98">
+        <v>112.0677002716064</v>
+      </c>
+      <c r="K98">
+        <v>4.27363109588623</v>
+      </c>
+      <c r="L98">
+        <v>140.3300018310547</v>
+      </c>
+      <c r="M98">
+        <v>104.2689329825687</v>
+      </c>
+      <c r="N98">
+        <v>3.1</v>
+      </c>
+      <c r="O98">
+        <v>1.79</v>
+      </c>
+      <c r="P98">
+        <v>3.05</v>
+      </c>
+      <c r="Q98">
+        <v>2.31</v>
+      </c>
+      <c r="R98">
+        <v>401000000</v>
+      </c>
+      <c r="S98">
+        <v>232000000</v>
+      </c>
+      <c r="T98">
+        <v>394000000</v>
+      </c>
+      <c r="U98">
+        <v>297000000</v>
+      </c>
+      <c r="V98" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="99" spans="1:22">
+      <c r="A99" t="s">
+        <v>119</v>
+      </c>
+      <c r="B99" t="s">
+        <v>132</v>
+      </c>
+      <c r="C99" t="s">
+        <v>172</v>
+      </c>
+      <c r="D99" t="s">
+        <v>289</v>
+      </c>
+      <c r="E99">
+        <v>45.95999908447266</v>
+      </c>
+      <c r="F99">
+        <v>685226.6666666666</v>
+      </c>
+      <c r="G99">
+        <v>44.40040000915528</v>
+      </c>
+      <c r="H99">
+        <v>42.34513348897298</v>
+      </c>
+      <c r="I99">
+        <v>41.86675012588501</v>
+      </c>
+      <c r="J99">
+        <v>41.70055011749267</v>
+      </c>
+      <c r="K99">
+        <v>27.5</v>
+      </c>
+      <c r="L99">
+        <v>46.25</v>
+      </c>
+      <c r="M99">
+        <v>104.2592688209265</v>
+      </c>
+      <c r="N99">
+        <v>0.09</v>
+      </c>
+      <c r="O99">
+        <v>0.14</v>
+      </c>
+      <c r="P99">
+        <v>0.11</v>
+      </c>
+      <c r="Q99">
+        <v>0.26</v>
+      </c>
+      <c r="R99">
+        <v>11745000</v>
+      </c>
+      <c r="S99">
+        <v>45782000</v>
+      </c>
+      <c r="T99">
+        <v>36457000</v>
+      </c>
+      <c r="U99">
+        <v>30078000</v>
+      </c>
+      <c r="V99" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="100" spans="1:22">
+      <c r="A100" t="s">
+        <v>120</v>
+      </c>
+      <c r="B100" t="s">
+        <v>129</v>
+      </c>
+      <c r="C100" t="s">
+        <v>191</v>
+      </c>
+      <c r="D100" t="s">
+        <v>290</v>
+      </c>
+      <c r="E100">
+        <v>252.8200073242188</v>
+      </c>
+      <c r="F100">
+        <v>291326.6666666667</v>
+      </c>
+      <c r="G100">
+        <v>245.003200378418</v>
+      </c>
+      <c r="H100">
+        <v>217.3592001342773</v>
+      </c>
+      <c r="I100">
+        <v>216.5760998535156</v>
+      </c>
+      <c r="J100">
+        <v>209.3181497192383</v>
+      </c>
+      <c r="K100">
+        <v>22.18000030517578</v>
+      </c>
+      <c r="L100">
+        <v>267.6499938964844</v>
+      </c>
+      <c r="M100">
+        <v>104.2214179717905</v>
+      </c>
+      <c r="N100">
+        <v>2.05</v>
+      </c>
+      <c r="O100">
+        <v>2.12</v>
+      </c>
+      <c r="P100">
+        <v>2.27</v>
+      </c>
+      <c r="Q100">
+        <v>1.93</v>
+      </c>
+      <c r="R100">
+        <v>66027000</v>
+      </c>
+      <c r="S100">
+        <v>68670000</v>
+      </c>
+      <c r="T100">
+        <v>72894000</v>
+      </c>
+      <c r="U100">
+        <v>61068000</v>
+      </c>
+      <c r="V100" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="101" spans="1:22">
+      <c r="A101" t="s">
+        <v>121</v>
+      </c>
+      <c r="B101" t="s">
+        <v>132</v>
+      </c>
+      <c r="C101" t="s">
+        <v>172</v>
+      </c>
+      <c r="D101" t="s">
+        <v>291</v>
+      </c>
+      <c r="E101">
+        <v>28.10000038146973</v>
+      </c>
+      <c r="F101">
+        <v>468516.6666666667</v>
+      </c>
+      <c r="G101">
+        <v>27.02740001678467</v>
+      </c>
+      <c r="H101">
+        <v>24.58300005594889</v>
+      </c>
+      <c r="I101">
+        <v>23.63855003356933</v>
+      </c>
+      <c r="J101">
+        <v>22.9000000667572</v>
+      </c>
+      <c r="K101">
+        <v>4.409999847412109</v>
+      </c>
+      <c r="L101">
+        <v>35.56999969482422</v>
+      </c>
+      <c r="M101">
+        <v>104.0109540297533</v>
+      </c>
+      <c r="N101">
+        <v>0.9</v>
+      </c>
+      <c r="O101">
+        <v>0.86</v>
+      </c>
+      <c r="P101">
+        <v>0.88</v>
+      </c>
+      <c r="Q101">
+        <v>0.95</v>
+      </c>
+      <c r="R101">
+        <v>76838000</v>
+      </c>
+      <c r="S101">
+        <v>72940000</v>
+      </c>
+      <c r="T101">
+        <v>74458000</v>
+      </c>
+      <c r="U101">
+        <v>80284000</v>
+      </c>
+      <c r="V101" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="102" spans="1:22">
+      <c r="A102" t="s">
+        <v>122</v>
+      </c>
+      <c r="B102" t="s">
+        <v>127</v>
+      </c>
+      <c r="C102" t="s">
+        <v>193</v>
+      </c>
+      <c r="D102" t="s">
+        <v>292</v>
+      </c>
+      <c r="E102">
+        <v>57.08000183105469</v>
+      </c>
+      <c r="F102">
+        <v>397736.6666666667</v>
+      </c>
+      <c r="G102">
+        <v>55.32300033569336</v>
+      </c>
+      <c r="H102">
+        <v>51.14853352864584</v>
+      </c>
+      <c r="I102">
+        <v>49.64360012054443</v>
+      </c>
+      <c r="J102">
+        <v>48.44965002059936</v>
+      </c>
+      <c r="K102">
+        <v>14.26579666137695</v>
+      </c>
+      <c r="L102">
+        <v>59.63000106811523</v>
+      </c>
+      <c r="M102">
+        <v>103.9694122601321</v>
+      </c>
+      <c r="N102">
+        <v>0.72</v>
+      </c>
+      <c r="O102">
+        <v>-0.000831</v>
+      </c>
+      <c r="P102">
+        <v>1.36</v>
+      </c>
+      <c r="Q102">
+        <v>1.09</v>
+      </c>
+      <c r="R102">
+        <v>51837000</v>
+      </c>
+      <c r="S102">
+        <v>-58000</v>
+      </c>
+      <c r="T102">
+        <v>93275000</v>
+      </c>
+      <c r="U102">
+        <v>74655000</v>
+      </c>
+      <c r="V102" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="103" spans="1:22">
+      <c r="A103" t="s">
+        <v>123</v>
+      </c>
+      <c r="B103" t="s">
+        <v>133</v>
+      </c>
+      <c r="C103" t="s">
+        <v>194</v>
+      </c>
+      <c r="D103" t="s">
+        <v>293</v>
+      </c>
+      <c r="E103">
+        <v>60.54000091552734</v>
+      </c>
+      <c r="F103">
+        <v>1361870</v>
+      </c>
+      <c r="G103">
+        <v>59.20880020141602</v>
+      </c>
+      <c r="H103">
+        <v>55.47686681111654</v>
+      </c>
+      <c r="I103">
+        <v>54.64310009002686</v>
+      </c>
+      <c r="J103">
+        <v>53.37655006408691</v>
+      </c>
+      <c r="K103">
+        <v>1.152155995368958</v>
+      </c>
+      <c r="L103">
+        <v>62.43000030517578</v>
+      </c>
+      <c r="M103">
+        <v>103.8503344101329</v>
+      </c>
+      <c r="N103">
+        <v>0.66</v>
+      </c>
+      <c r="O103">
+        <v>0.41</v>
+      </c>
+      <c r="P103">
+        <v>0.22</v>
+      </c>
+      <c r="Q103">
+        <v>0.000388</v>
+      </c>
+      <c r="R103">
+        <v>192164000</v>
+      </c>
+      <c r="S103">
+        <v>122437000</v>
+      </c>
+      <c r="T103">
+        <v>64595000</v>
+      </c>
+      <c r="U103">
+        <v>114000</v>
+      </c>
+      <c r="V103" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="104" spans="1:22">
+      <c r="A104" t="s">
+        <v>124</v>
+      </c>
+      <c r="B104" t="s">
+        <v>128</v>
+      </c>
+      <c r="C104" t="s">
+        <v>163</v>
+      </c>
+      <c r="D104" t="s">
+        <v>294</v>
+      </c>
+      <c r="E104">
+        <v>65.41999816894531</v>
+      </c>
+      <c r="F104">
+        <v>942670</v>
+      </c>
+      <c r="G104">
+        <v>63.6939998626709</v>
+      </c>
+      <c r="H104">
+        <v>58.27446670532227</v>
+      </c>
+      <c r="I104">
+        <v>56.51910007476807</v>
+      </c>
+      <c r="J104">
+        <v>55.07675018310547</v>
+      </c>
+      <c r="K104">
+        <v>1.894549012184143</v>
+      </c>
+      <c r="L104">
+        <v>66.26999664306641</v>
+      </c>
+      <c r="M104">
+        <v>103.8212301082223</v>
+      </c>
+      <c r="N104">
+        <v>1.59</v>
+      </c>
+      <c r="O104">
+        <v>0.91</v>
+      </c>
+      <c r="P104">
+        <v>1.34</v>
+      </c>
+      <c r="Q104">
+        <v>1.18</v>
+      </c>
+      <c r="R104">
+        <v>330000000</v>
+      </c>
+      <c r="S104">
+        <v>187000000</v>
+      </c>
+      <c r="T104">
+        <v>273900000</v>
+      </c>
+      <c r="U104">
+        <v>238700000</v>
+      </c>
+      <c r="V104" t="s">
+        <v>295</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/ScreenResult/ScreenResult.xlsx
+++ b/Screener/ScreenResult/ScreenResult.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
   <si>
     <t>Symbol</t>
   </si>
@@ -82,25 +82,58 @@
     <t>Code 33</t>
   </si>
   <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>APO</t>
+  </si>
+  <si>
     <t>ADBE</t>
   </si>
   <si>
-    <t>AVGO</t>
+    <t>AJG</t>
+  </si>
+  <si>
+    <t>ATVI</t>
   </si>
   <si>
     <t>Technology</t>
   </si>
   <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
+    <t>Computer Hardware</t>
+  </si>
+  <si>
+    <t>Asset Management</t>
+  </si>
+  <si>
     <t>Software—Infrastructure</t>
   </si>
   <si>
-    <t>Semiconductors</t>
+    <t>Insurance Brokers</t>
+  </si>
+  <si>
+    <t>Electronic Gaming &amp; Multimedia</t>
+  </si>
+  <si>
+    <t>2014-06-06</t>
+  </si>
+  <si>
+    <t>2011-03-30</t>
   </si>
   <si>
     <t>1986-08-13</t>
   </si>
   <si>
-    <t>2009-08-06</t>
+    <t>1984-06-20</t>
+  </si>
+  <si>
+    <t>1993-10-25</t>
   </si>
   <si>
     <t>T</t>
@@ -464,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
@@ -540,67 +573,67 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E2">
-        <v>544.2849731445312</v>
+        <v>187.1000061035156</v>
       </c>
       <c r="F2">
-        <v>2485491.2</v>
+        <v>3167036.666666667</v>
       </c>
       <c r="G2">
-        <v>512.6240966796875</v>
+        <v>170.4111993408203</v>
       </c>
       <c r="H2">
-        <v>421.7209649658203</v>
+        <v>156.9325998942057</v>
       </c>
       <c r="I2">
-        <v>400.9320736694336</v>
+        <v>148.9463999557495</v>
       </c>
       <c r="J2">
-        <v>379.3749488830566</v>
+        <v>142.5318999862671</v>
       </c>
       <c r="K2">
-        <v>0.1503329128026962</v>
+        <v>13.25</v>
       </c>
       <c r="L2">
-        <v>688.3699951171875</v>
+        <v>189.8300018310547</v>
       </c>
       <c r="M2">
-        <v>115.4508138824493</v>
+        <v>120.2036448358768</v>
       </c>
       <c r="N2">
-        <v>2.42</v>
+        <v>1.13</v>
       </c>
       <c r="O2">
-        <v>2.53</v>
+        <v>1.35</v>
       </c>
       <c r="P2">
-        <v>2.71</v>
+        <v>1.38</v>
       </c>
       <c r="Q2">
-        <v>2.82</v>
+        <v>1.55</v>
       </c>
       <c r="R2">
-        <v>1136000000</v>
+        <v>353999000</v>
       </c>
       <c r="S2">
-        <v>1176000000</v>
+        <v>427089000</v>
       </c>
       <c r="T2">
-        <v>1247000000</v>
+        <v>436473000</v>
       </c>
       <c r="U2">
-        <v>1295000000</v>
+        <v>491885000</v>
       </c>
       <c r="V2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -608,67 +641,271 @@
         <v>23</v>
       </c>
       <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3">
+        <v>85.09999847412109</v>
+      </c>
+      <c r="F3">
+        <v>2260016.666666667</v>
+      </c>
+      <c r="G3">
+        <v>79.8472785949707</v>
+      </c>
+      <c r="H3">
+        <v>70.3119756825765</v>
+      </c>
+      <c r="I3">
+        <v>68.68916883468628</v>
+      </c>
+      <c r="J3">
+        <v>65.87708797454835</v>
+      </c>
+      <c r="K3">
+        <v>3.99648118019104</v>
+      </c>
+      <c r="L3">
+        <v>85.80780029296875</v>
+      </c>
+      <c r="M3">
+        <v>116.0053880386057</v>
+      </c>
+      <c r="N3">
+        <v>-1.52</v>
+      </c>
+      <c r="O3">
+        <v>0.025016</v>
+      </c>
+      <c r="P3">
+        <v>1.66</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>-876000000</v>
+      </c>
+      <c r="S3">
+        <v>23430000</v>
+      </c>
+      <c r="T3">
+        <v>217383000</v>
+      </c>
+      <c r="U3">
+        <v>599000000</v>
+      </c>
+      <c r="V3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" t="s">
         <v>24</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4">
+        <v>545.3599853515625</v>
+      </c>
+      <c r="F4">
+        <v>2521470</v>
+      </c>
+      <c r="G4">
+        <v>512.6455969238282</v>
+      </c>
+      <c r="H4">
+        <v>421.7281317138672</v>
+      </c>
+      <c r="I4">
+        <v>400.9374487304688</v>
+      </c>
+      <c r="J4">
+        <v>379.3749488830566</v>
+      </c>
+      <c r="K4">
+        <v>0.1943887174129486</v>
+      </c>
+      <c r="L4">
+        <v>688.3699951171875</v>
+      </c>
+      <c r="M4">
+        <v>115.5843379752632</v>
+      </c>
+      <c r="N4">
+        <v>2.42</v>
+      </c>
+      <c r="O4">
+        <v>2.53</v>
+      </c>
+      <c r="P4">
+        <v>2.71</v>
+      </c>
+      <c r="Q4">
+        <v>2.82</v>
+      </c>
+      <c r="R4">
+        <v>1136000000</v>
+      </c>
+      <c r="S4">
+        <v>1176000000</v>
+      </c>
+      <c r="T4">
+        <v>1247000000</v>
+      </c>
+      <c r="U4">
+        <v>1295000000</v>
+      </c>
+      <c r="V4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5">
+        <v>230.8300018310547</v>
+      </c>
+      <c r="F5">
+        <v>673910</v>
+      </c>
+      <c r="G5">
+        <v>219.1876007080078</v>
+      </c>
+      <c r="H5">
+        <v>205.123842976888</v>
+      </c>
+      <c r="I5">
+        <v>201.6767900085449</v>
+      </c>
+      <c r="J5">
+        <v>197.3334227752686</v>
+      </c>
+      <c r="K5">
+        <v>0.5987211465835571</v>
+      </c>
+      <c r="L5">
+        <v>230.8300018310547</v>
+      </c>
+      <c r="M5">
+        <v>109.8073800614181</v>
+      </c>
+      <c r="N5">
+        <v>1.19</v>
+      </c>
+      <c r="O5">
+        <v>0.63</v>
+      </c>
+      <c r="P5">
+        <v>2.24</v>
+      </c>
+      <c r="Q5">
+        <v>1.07</v>
+      </c>
+      <c r="R5">
+        <v>255800000</v>
+      </c>
+      <c r="S5">
+        <v>135500000</v>
+      </c>
+      <c r="T5">
+        <v>486500000</v>
+      </c>
+      <c r="U5">
+        <v>234500000</v>
+      </c>
+      <c r="V5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="A6" t="s">
         <v>26</v>
       </c>
-      <c r="D3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3">
-        <v>893.6749877929688</v>
-      </c>
-      <c r="F3">
-        <v>2177326.9</v>
-      </c>
-      <c r="G3">
-        <v>870.8075012207031</v>
-      </c>
-      <c r="H3">
-        <v>727.3953674316406</v>
-      </c>
-      <c r="I3">
-        <v>683.1587254333496</v>
-      </c>
-      <c r="J3">
-        <v>642.9300999450684</v>
-      </c>
-      <c r="K3">
-        <v>11.17089080810547</v>
-      </c>
-      <c r="L3">
-        <v>920</v>
-      </c>
-      <c r="M3">
-        <v>107.6387464561719</v>
-      </c>
-      <c r="N3">
-        <v>7.132125</v>
-      </c>
-      <c r="O3">
-        <v>7.810425</v>
-      </c>
-      <c r="P3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Q3">
-        <v>8.15</v>
-      </c>
-      <c r="R3">
-        <v>3074000000</v>
-      </c>
-      <c r="S3">
-        <v>3359000000</v>
-      </c>
-      <c r="T3">
-        <v>3774000000</v>
-      </c>
-      <c r="U3">
-        <v>3481000000</v>
-      </c>
-      <c r="V3" t="s">
-        <v>30</v>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6">
+        <v>91.98000335693359</v>
+      </c>
+      <c r="F6">
+        <v>7397483.333333333</v>
+      </c>
+      <c r="G6">
+        <v>88.80375366210937</v>
+      </c>
+      <c r="H6">
+        <v>82.06178253173829</v>
+      </c>
+      <c r="I6">
+        <v>80.24818447113037</v>
+      </c>
+      <c r="J6">
+        <v>78.27775188446044</v>
+      </c>
+      <c r="K6">
+        <v>0.2558244168758392</v>
+      </c>
+      <c r="L6">
+        <v>101.6032562255859</v>
+      </c>
+      <c r="M6">
+        <v>109.6120061433241</v>
+      </c>
+      <c r="N6">
+        <v>0.55</v>
+      </c>
+      <c r="O6">
+        <v>0.51</v>
+      </c>
+      <c r="P6">
+        <v>0.93</v>
+      </c>
+      <c r="Q6">
+        <v>0.74</v>
+      </c>
+      <c r="R6">
+        <v>435000000</v>
+      </c>
+      <c r="S6">
+        <v>403000000</v>
+      </c>
+      <c r="T6">
+        <v>740000000</v>
+      </c>
+      <c r="U6">
+        <v>587000000</v>
+      </c>
+      <c r="V6" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/ScreenResult/ScreenResult.xlsx
+++ b/Screener/ScreenResult/ScreenResult.xlsx
@@ -13,10 +13,242 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="73">
+  <si>
+    <t>Symbol</t>
+  </si>
+  <si>
+    <t>IPO Date</t>
+  </si>
+  <si>
+    <t>Current price</t>
+  </si>
+  <si>
+    <t>30D Avg Vol</t>
+  </si>
+  <si>
+    <t>SMA 50</t>
+  </si>
+  <si>
+    <t>SMA 150</t>
+  </si>
+  <si>
+    <t>SMA 200</t>
+  </si>
+  <si>
+    <t>Month ago SMA 200</t>
+  </si>
+  <si>
+    <t>Week 52 low</t>
+  </si>
+  <si>
+    <t>Week 52 high</t>
+  </si>
+  <si>
+    <t>RS Rating</t>
+  </si>
+  <si>
+    <t>1st qtr EPS</t>
+  </si>
+  <si>
+    <t>2nd qtr EPS</t>
+  </si>
+  <si>
+    <t>3rd qtr EPS</t>
+  </si>
+  <si>
+    <t>Current qtr EPS</t>
+  </si>
+  <si>
+    <t>1st qtr Inc</t>
+  </si>
+  <si>
+    <t>2nd qtr Inc</t>
+  </si>
+  <si>
+    <t>3rd qtr Inc</t>
+  </si>
+  <si>
+    <t>Current qtr Inc</t>
+  </si>
+  <si>
+    <t>1st qtr Rev</t>
+  </si>
+  <si>
+    <t>2nd qtr Rev</t>
+  </si>
+  <si>
+    <t>3rd qtr Rev</t>
+  </si>
+  <si>
+    <t>Current qtr Rev</t>
+  </si>
+  <si>
+    <t>1st qtr Profit Margin</t>
+  </si>
+  <si>
+    <t>2nd qtr Profit Margin</t>
+  </si>
+  <si>
+    <t>3rd qtr Profit Margin</t>
+  </si>
+  <si>
+    <t>Current qtr Profit Margin</t>
+  </si>
+  <si>
+    <t>Code 33</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>APO</t>
+  </si>
+  <si>
+    <t>ACN</t>
+  </si>
+  <si>
+    <t>AER</t>
+  </si>
+  <si>
+    <t>AMGN</t>
+  </si>
+  <si>
+    <t>AOS</t>
+  </si>
+  <si>
+    <t>APH</t>
+  </si>
+  <si>
+    <t>ASML</t>
+  </si>
+  <si>
+    <t>AMP</t>
+  </si>
+  <si>
+    <t>AXP</t>
+  </si>
+  <si>
+    <t>ADI</t>
+  </si>
+  <si>
+    <t>ABBV</t>
+  </si>
+  <si>
+    <t>AFL</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>AME</t>
+  </si>
+  <si>
+    <t>AVY</t>
+  </si>
+  <si>
+    <t>AJG</t>
+  </si>
+  <si>
+    <t>ACGL</t>
+  </si>
+  <si>
+    <t>1980-03-17</t>
+  </si>
+  <si>
+    <t>2009-08-06</t>
+  </si>
+  <si>
+    <t>2014-06-06</t>
+  </si>
+  <si>
+    <t>1997-05-15</t>
+  </si>
+  <si>
+    <t>1993-06-03</t>
+  </si>
+  <si>
+    <t>2011-03-30</t>
+  </si>
+  <si>
+    <t>2001-07-19</t>
+  </si>
+  <si>
+    <t>2006-11-21</t>
+  </si>
+  <si>
+    <t>1983-06-17</t>
+  </si>
+  <si>
+    <t>1983-09-30</t>
+  </si>
+  <si>
+    <t>1991-11-08</t>
+  </si>
+  <si>
+    <t>1995-03-15</t>
+  </si>
+  <si>
+    <t>2005-09-15</t>
+  </si>
+  <si>
+    <t>1972-06-01</t>
+  </si>
+  <si>
+    <t>2013-01-02</t>
+  </si>
+  <si>
+    <t>1980-12-12</t>
+  </si>
+  <si>
+    <t>1984-07-19</t>
+  </si>
+  <si>
+    <t>1973-02-21</t>
+  </si>
+  <si>
+    <t>1984-06-20</t>
+  </si>
+  <si>
+    <t>1995-09-14</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -32,7 +264,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -40,12 +272,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -340,9 +590,2074 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:AB24"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:28">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2">
+        <v>168.4199981689453</v>
+      </c>
+      <c r="D2">
+        <v>74512060</v>
+      </c>
+      <c r="E2">
+        <v>135.6265995788574</v>
+      </c>
+      <c r="F2">
+        <v>116.9890663146973</v>
+      </c>
+      <c r="G2">
+        <v>113.5309998703003</v>
+      </c>
+      <c r="H2">
+        <v>107.8922998046875</v>
+      </c>
+      <c r="I2">
+        <v>1.620000004768372</v>
+      </c>
+      <c r="J2">
+        <v>174.2299957275391</v>
+      </c>
+      <c r="K2">
+        <v>179.7762190137093</v>
+      </c>
+      <c r="L2">
+        <v>0.01</v>
+      </c>
+      <c r="M2">
+        <v>-0.09</v>
+      </c>
+      <c r="N2">
+        <v>0.02</v>
+      </c>
+      <c r="O2">
+        <v>0.18</v>
+      </c>
+      <c r="P2">
+        <v>21000000</v>
+      </c>
+      <c r="Q2">
+        <v>-139000000</v>
+      </c>
+      <c r="R2">
+        <v>27000000</v>
+      </c>
+      <c r="S2">
+        <v>299000000</v>
+      </c>
+      <c r="T2">
+        <v>5599000000</v>
+      </c>
+      <c r="U2">
+        <v>5353000000</v>
+      </c>
+      <c r="V2">
+        <v>5359000000</v>
+      </c>
+      <c r="W2">
+        <v>5800000000</v>
+      </c>
+      <c r="X2">
+        <v>0.003750669762457582</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.005038253405486098</v>
+      </c>
+      <c r="AA2">
+        <v>0.05155172413793103</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3">
+        <v>1226.31005859375</v>
+      </c>
+      <c r="D3">
+        <v>3938226.666666667</v>
+      </c>
+      <c r="E3">
+        <v>1041.742729492187</v>
+      </c>
+      <c r="F3">
+        <v>918.5223860677083</v>
+      </c>
+      <c r="G3">
+        <v>859.6645104980469</v>
+      </c>
+      <c r="H3">
+        <v>810.0158731079101</v>
+      </c>
+      <c r="I3">
+        <v>10.4382152557373</v>
+      </c>
+      <c r="J3">
+        <v>1226.31005859375</v>
+      </c>
+      <c r="K3">
+        <v>166.3697893120211</v>
+      </c>
+      <c r="L3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M3">
+        <v>8.15</v>
+      </c>
+      <c r="N3">
+        <v>7.74</v>
+      </c>
+      <c r="O3">
+        <v>8.25</v>
+      </c>
+      <c r="P3">
+        <v>3774000000</v>
+      </c>
+      <c r="Q3">
+        <v>3481000000</v>
+      </c>
+      <c r="R3">
+        <v>3303000000</v>
+      </c>
+      <c r="S3">
+        <v>3524000000</v>
+      </c>
+      <c r="T3">
+        <v>8915000000</v>
+      </c>
+      <c r="U3">
+        <v>8733000000</v>
+      </c>
+      <c r="V3">
+        <v>8876000000</v>
+      </c>
+      <c r="W3">
+        <v>9295000000</v>
+      </c>
+      <c r="X3">
+        <v>0.423331463825014</v>
+      </c>
+      <c r="Y3">
+        <v>0.3986030001145082</v>
+      </c>
+      <c r="Z3">
+        <v>0.3721270842721947</v>
+      </c>
+      <c r="AA3">
+        <v>0.3791285637439484</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4">
+        <v>262.0400085449219</v>
+      </c>
+      <c r="D4">
+        <v>1601666.666666667</v>
+      </c>
+      <c r="E4">
+        <v>230.5708004760742</v>
+      </c>
+      <c r="F4">
+        <v>197.150266418457</v>
+      </c>
+      <c r="G4">
+        <v>186.353099899292</v>
+      </c>
+      <c r="H4">
+        <v>177.9942999267578</v>
+      </c>
+      <c r="I4">
+        <v>13.25</v>
+      </c>
+      <c r="J4">
+        <v>266.6000061035156</v>
+      </c>
+      <c r="K4">
+        <v>162.5838417464409</v>
+      </c>
+      <c r="L4">
+        <v>1.35</v>
+      </c>
+      <c r="M4">
+        <v>1.38</v>
+      </c>
+      <c r="N4">
+        <v>1.55</v>
+      </c>
+      <c r="O4">
+        <v>1.72</v>
+      </c>
+      <c r="P4">
+        <v>427089000</v>
+      </c>
+      <c r="Q4">
+        <v>436473000</v>
+      </c>
+      <c r="R4">
+        <v>491885000</v>
+      </c>
+      <c r="S4">
+        <v>545327000</v>
+      </c>
+      <c r="T4">
+        <v>1275552000</v>
+      </c>
+      <c r="U4">
+        <v>1351351000</v>
+      </c>
+      <c r="V4">
+        <v>1458924000</v>
+      </c>
+      <c r="W4">
+        <v>1509456000</v>
+      </c>
+      <c r="X4">
+        <v>0.3348268043952736</v>
+      </c>
+      <c r="Y4">
+        <v>0.3229901039774271</v>
+      </c>
+      <c r="Z4">
+        <v>0.3371560136100304</v>
+      </c>
+      <c r="AA4">
+        <v>0.3612738629016016</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5">
+        <v>167.0500030517578</v>
+      </c>
+      <c r="D5">
+        <v>5645716.666666667</v>
+      </c>
+      <c r="E5">
+        <v>154.40515625</v>
+      </c>
+      <c r="F5">
+        <v>145.6192967732747</v>
+      </c>
+      <c r="G5">
+        <v>139.6888213729858</v>
+      </c>
+      <c r="H5">
+        <v>135.8602177429199</v>
+      </c>
+      <c r="I5">
+        <v>0.05632543936371803</v>
+      </c>
+      <c r="J5">
+        <v>168.3000030517578</v>
+      </c>
+      <c r="K5">
+        <v>132.6954828704281</v>
+      </c>
+      <c r="L5">
+        <v>2.02</v>
+      </c>
+      <c r="M5">
+        <v>1.86</v>
+      </c>
+      <c r="N5">
+        <v>1.85</v>
+      </c>
+      <c r="O5">
+        <v>2.38</v>
+      </c>
+      <c r="P5">
+        <v>1717000000</v>
+      </c>
+      <c r="Q5">
+        <v>1575000000</v>
+      </c>
+      <c r="R5">
+        <v>1560000000</v>
+      </c>
+      <c r="S5">
+        <v>2004000000</v>
+      </c>
+      <c r="T5">
+        <v>6739000000</v>
+      </c>
+      <c r="U5">
+        <v>6630000000</v>
+      </c>
+      <c r="V5">
+        <v>6425000000</v>
+      </c>
+      <c r="W5">
+        <v>6723000000</v>
+      </c>
+      <c r="X5">
+        <v>0.2547855764950289</v>
+      </c>
+      <c r="Y5">
+        <v>0.2375565610859728</v>
+      </c>
+      <c r="Z5">
+        <v>0.2428015564202335</v>
+      </c>
+      <c r="AA5">
+        <v>0.2980812137438644</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6">
+        <v>156.0200042724609</v>
+      </c>
+      <c r="D6">
+        <v>45776650</v>
+      </c>
+      <c r="E6">
+        <v>148.952200012207</v>
+      </c>
+      <c r="F6">
+        <v>138.0236670939128</v>
+      </c>
+      <c r="G6">
+        <v>131.6117004394531</v>
+      </c>
+      <c r="H6">
+        <v>126.2387503433227</v>
+      </c>
+      <c r="I6">
+        <v>0.0697920024394989</v>
+      </c>
+      <c r="J6">
+        <v>186.5704956054688</v>
+      </c>
+      <c r="K6">
+        <v>131.8085923746759</v>
+      </c>
+      <c r="L6">
+        <v>0.03</v>
+      </c>
+      <c r="M6">
+        <v>0.31</v>
+      </c>
+      <c r="N6">
+        <v>0.65</v>
+      </c>
+      <c r="O6">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="P6">
+        <v>278000000</v>
+      </c>
+      <c r="Q6">
+        <v>3172000000</v>
+      </c>
+      <c r="R6">
+        <v>6750000000</v>
+      </c>
+      <c r="S6">
+        <v>9879000000</v>
+      </c>
+      <c r="T6">
+        <v>149204000000</v>
+      </c>
+      <c r="U6">
+        <v>127358000000</v>
+      </c>
+      <c r="V6">
+        <v>134383000000</v>
+      </c>
+      <c r="W6">
+        <v>143083000000</v>
+      </c>
+      <c r="X6">
+        <v>0.00186322082517895</v>
+      </c>
+      <c r="Y6">
+        <v>0.02490617000895115</v>
+      </c>
+      <c r="Z6">
+        <v>0.05022956772806084</v>
+      </c>
+      <c r="AA6">
+        <v>0.06904384168629397</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7">
+        <v>154.1100006103516</v>
+      </c>
+      <c r="D7">
+        <v>1598613.333333333</v>
+      </c>
+      <c r="E7">
+        <v>140.8771063232422</v>
+      </c>
+      <c r="F7">
+        <v>121.3101370747884</v>
+      </c>
+      <c r="G7">
+        <v>118.9531686782837</v>
+      </c>
+      <c r="H7">
+        <v>115.0300895690918</v>
+      </c>
+      <c r="I7">
+        <v>5.702027797698975</v>
+      </c>
+      <c r="J7">
+        <v>155.3899993896484</v>
+      </c>
+      <c r="K7">
+        <v>129.8785902344811</v>
+      </c>
+      <c r="L7">
+        <v>-1.17</v>
+      </c>
+      <c r="M7">
+        <v>-1.31</v>
+      </c>
+      <c r="N7">
+        <v>-5.29</v>
+      </c>
+      <c r="O7">
+        <v>-0.16</v>
+      </c>
+      <c r="P7">
+        <v>-284000000</v>
+      </c>
+      <c r="Q7">
+        <v>-320000000</v>
+      </c>
+      <c r="R7">
+        <v>-1352000000</v>
+      </c>
+      <c r="S7">
+        <v>-5000000</v>
+      </c>
+      <c r="T7">
+        <v>13647000000</v>
+      </c>
+      <c r="U7">
+        <v>13786000000</v>
+      </c>
+      <c r="V7">
+        <v>13979000000</v>
+      </c>
+      <c r="W7">
+        <v>14497000000</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8">
+        <v>95.30999755859375</v>
+      </c>
+      <c r="D8">
+        <v>2171783.333333333</v>
+      </c>
+      <c r="E8">
+        <v>92.10132141113282</v>
+      </c>
+      <c r="F8">
+        <v>86.04308639526367</v>
+      </c>
+      <c r="G8">
+        <v>80.71470485687256</v>
+      </c>
+      <c r="H8">
+        <v>77.12546491622925</v>
+      </c>
+      <c r="I8">
+        <v>3.976721048355103</v>
+      </c>
+      <c r="J8">
+        <v>98.94000244140625</v>
+      </c>
+      <c r="K8">
+        <v>127.9384791872041</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>1.66</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>0.677267</v>
+      </c>
+      <c r="P8">
+        <v>584000000</v>
+      </c>
+      <c r="Q8">
+        <v>1010000000</v>
+      </c>
+      <c r="R8">
+        <v>599000000</v>
+      </c>
+      <c r="S8">
+        <v>682000000</v>
+      </c>
+      <c r="T8">
+        <v>4842000000</v>
+      </c>
+      <c r="U8">
+        <v>5301000000</v>
+      </c>
+      <c r="V8">
+        <v>13702000000</v>
+      </c>
+      <c r="W8">
+        <v>2595000000</v>
+      </c>
+      <c r="X8">
+        <v>0.1206113176373399</v>
+      </c>
+      <c r="Y8">
+        <v>0.1905300886625165</v>
+      </c>
+      <c r="Z8">
+        <v>0.04371624580353233</v>
+      </c>
+      <c r="AA8">
+        <v>0.2628131021194605</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9">
+        <v>369.8599853515625</v>
+      </c>
+      <c r="D9">
+        <v>2209990</v>
+      </c>
+      <c r="E9">
+        <v>339.7002386474609</v>
+      </c>
+      <c r="F9">
+        <v>319.2420255533854</v>
+      </c>
+      <c r="G9">
+        <v>310.6489520263672</v>
+      </c>
+      <c r="H9">
+        <v>301.8332396697998</v>
+      </c>
+      <c r="I9">
+        <v>8.505037307739258</v>
+      </c>
+      <c r="J9">
+        <v>401.9517211914062</v>
+      </c>
+      <c r="K9">
+        <v>127.7852006101587</v>
+      </c>
+      <c r="L9">
+        <v>2.39</v>
+      </c>
+      <c r="M9">
+        <v>3.15</v>
+      </c>
+      <c r="N9">
+        <v>2.15</v>
+      </c>
+      <c r="O9">
+        <v>3.1</v>
+      </c>
+      <c r="P9">
+        <v>1523648000</v>
+      </c>
+      <c r="Q9">
+        <v>2009996000</v>
+      </c>
+      <c r="R9">
+        <v>1372963000</v>
+      </c>
+      <c r="S9">
+        <v>1973444000</v>
+      </c>
+      <c r="T9">
+        <v>15814158000</v>
+      </c>
+      <c r="U9">
+        <v>16564585000</v>
+      </c>
+      <c r="V9">
+        <v>15985200000</v>
+      </c>
+      <c r="W9">
+        <v>16224303000</v>
+      </c>
+      <c r="X9">
+        <v>0.0963470834172771</v>
+      </c>
+      <c r="Y9">
+        <v>0.1213429735788732</v>
+      </c>
+      <c r="Z9">
+        <v>0.08588963541275681</v>
+      </c>
+      <c r="AA9">
+        <v>0.1216350557555539</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10">
+        <v>75.29000091552734</v>
+      </c>
+      <c r="D10">
+        <v>1561073.333333333</v>
+      </c>
+      <c r="E10">
+        <v>71.32120010375976</v>
+      </c>
+      <c r="F10">
+        <v>65.24900004069011</v>
+      </c>
+      <c r="G10">
+        <v>63.22025007247925</v>
+      </c>
+      <c r="H10">
+        <v>61.19465005874634</v>
+      </c>
+      <c r="I10">
+        <v>1.830000042915344</v>
+      </c>
+      <c r="J10">
+        <v>75.66000366210938</v>
+      </c>
+      <c r="K10">
+        <v>124.7877622598451</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>1.79</v>
+      </c>
+      <c r="N10">
+        <v>2.12</v>
+      </c>
+      <c r="O10">
+        <v>4.86</v>
+      </c>
+      <c r="P10">
+        <v>495007000</v>
+      </c>
+      <c r="Q10">
+        <v>432105000</v>
+      </c>
+      <c r="R10">
+        <v>492894000</v>
+      </c>
+      <c r="S10">
+        <v>1105254000</v>
+      </c>
+      <c r="T10">
+        <v>1798969000</v>
+      </c>
+      <c r="U10">
+        <v>1865722000</v>
+      </c>
+      <c r="V10">
+        <v>1923052000</v>
+      </c>
+      <c r="W10">
+        <v>1891667000</v>
+      </c>
+      <c r="X10">
+        <v>0.2751614952786846</v>
+      </c>
+      <c r="Y10">
+        <v>0.2316020285980441</v>
+      </c>
+      <c r="Z10">
+        <v>0.2563082017542948</v>
+      </c>
+      <c r="AA10">
+        <v>0.5842751393347773</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11">
+        <v>309.9100036621094</v>
+      </c>
+      <c r="D11">
+        <v>2534970</v>
+      </c>
+      <c r="E11">
+        <v>282.2089520263672</v>
+      </c>
+      <c r="F11">
+        <v>261.3540735880534</v>
+      </c>
+      <c r="G11">
+        <v>252.8730815124512</v>
+      </c>
+      <c r="H11">
+        <v>245.8953923797608</v>
+      </c>
+      <c r="I11">
+        <v>0.05471450462937355</v>
+      </c>
+      <c r="J11">
+        <v>310.8800048828125</v>
+      </c>
+      <c r="K11">
+        <v>123.6597227981528</v>
+      </c>
+      <c r="L11">
+        <v>3</v>
+      </c>
+      <c r="M11">
+        <v>5.28</v>
+      </c>
+      <c r="N11">
+        <v>2.57</v>
+      </c>
+      <c r="O11">
+        <v>3.22</v>
+      </c>
+      <c r="P11">
+        <v>1616000000</v>
+      </c>
+      <c r="Q11">
+        <v>2841000000</v>
+      </c>
+      <c r="R11">
+        <v>1379000000</v>
+      </c>
+      <c r="S11">
+        <v>1730000000</v>
+      </c>
+      <c r="T11">
+        <v>6839000000</v>
+      </c>
+      <c r="U11">
+        <v>6105000000</v>
+      </c>
+      <c r="V11">
+        <v>6986000000</v>
+      </c>
+      <c r="W11">
+        <v>6903000000</v>
+      </c>
+      <c r="X11">
+        <v>0.2362918555344349</v>
+      </c>
+      <c r="Y11">
+        <v>0.4653562653562653</v>
+      </c>
+      <c r="Z11">
+        <v>0.1973947895791583</v>
+      </c>
+      <c r="AA11">
+        <v>0.2506156743444879</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12">
+        <v>81.84999847412109</v>
+      </c>
+      <c r="D12">
+        <v>852530</v>
+      </c>
+      <c r="E12">
+        <v>78.51139999389649</v>
+      </c>
+      <c r="F12">
+        <v>72.83482554117839</v>
+      </c>
+      <c r="G12">
+        <v>71.48783201217651</v>
+      </c>
+      <c r="H12">
+        <v>70.0144832611084</v>
+      </c>
+      <c r="I12">
+        <v>0.227985218167305</v>
+      </c>
+      <c r="J12">
+        <v>82.74479675292969</v>
+      </c>
+      <c r="K12">
+        <v>123.4851114321863</v>
+      </c>
+      <c r="L12">
+        <v>-0.794422</v>
+      </c>
+      <c r="M12">
+        <v>0.84</v>
+      </c>
+      <c r="N12">
+        <v>1.04</v>
+      </c>
+      <c r="O12">
+        <v>0.9</v>
+      </c>
+      <c r="P12">
+        <v>-120100000</v>
+      </c>
+      <c r="Q12">
+        <v>126900000</v>
+      </c>
+      <c r="R12">
+        <v>157000000</v>
+      </c>
+      <c r="S12">
+        <v>135400000</v>
+      </c>
+      <c r="T12">
+        <v>936100000</v>
+      </c>
+      <c r="U12">
+        <v>966400000</v>
+      </c>
+      <c r="V12">
+        <v>960800000</v>
+      </c>
+      <c r="W12">
+        <v>937500000</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0.1313120860927152</v>
+      </c>
+      <c r="Z12">
+        <v>0.1634054954204829</v>
+      </c>
+      <c r="AA12">
+        <v>0.1444266666666667</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13">
+        <v>97.94000244140625</v>
+      </c>
+      <c r="D13">
+        <v>2654386.666666667</v>
+      </c>
+      <c r="E13">
+        <v>94.0489747619629</v>
+      </c>
+      <c r="F13">
+        <v>87.53117436726887</v>
+      </c>
+      <c r="G13">
+        <v>84.71083255767822</v>
+      </c>
+      <c r="H13">
+        <v>82.77795116424561</v>
+      </c>
+      <c r="I13">
+        <v>0.1448503583669662</v>
+      </c>
+      <c r="J13">
+        <v>99.48999786376953</v>
+      </c>
+      <c r="K13">
+        <v>123.2422985909084</v>
+      </c>
+      <c r="L13">
+        <v>0.82</v>
+      </c>
+      <c r="M13">
+        <v>0.71</v>
+      </c>
+      <c r="N13">
+        <v>0.74</v>
+      </c>
+      <c r="O13">
+        <v>0.83</v>
+      </c>
+      <c r="P13">
+        <v>507500000</v>
+      </c>
+      <c r="Q13">
+        <v>439200000</v>
+      </c>
+      <c r="R13">
+        <v>460500000</v>
+      </c>
+      <c r="S13">
+        <v>513900000</v>
+      </c>
+      <c r="T13">
+        <v>3239200000</v>
+      </c>
+      <c r="U13">
+        <v>2974000000</v>
+      </c>
+      <c r="V13">
+        <v>3053900000</v>
+      </c>
+      <c r="W13">
+        <v>3199200000</v>
+      </c>
+      <c r="X13">
+        <v>0.1566744875277847</v>
+      </c>
+      <c r="Y13">
+        <v>0.147679892400807</v>
+      </c>
+      <c r="Z13">
+        <v>0.1507907921019025</v>
+      </c>
+      <c r="AA13">
+        <v>0.1606339084771193</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14">
+        <v>778.3900146484375</v>
+      </c>
+      <c r="D14">
+        <v>964293.3333333334</v>
+      </c>
+      <c r="E14">
+        <v>712.8210021972657</v>
+      </c>
+      <c r="F14">
+        <v>670.3661861165365</v>
+      </c>
+      <c r="G14">
+        <v>670.3379873657227</v>
+      </c>
+      <c r="H14">
+        <v>660.7379364013672</v>
+      </c>
+      <c r="I14">
+        <v>1.309289693832397</v>
+      </c>
+      <c r="J14">
+        <v>867.1241455078125</v>
+      </c>
+      <c r="K14">
+        <v>122.5433026214375</v>
+      </c>
+      <c r="L14">
+        <v>4.6</v>
+      </c>
+      <c r="M14">
+        <v>4.95</v>
+      </c>
+      <c r="N14">
+        <v>4.93</v>
+      </c>
+      <c r="O14">
+        <v>4.81</v>
+      </c>
+      <c r="P14">
+        <v>1816500000</v>
+      </c>
+      <c r="Q14">
+        <v>1955800000</v>
+      </c>
+      <c r="R14">
+        <v>1941700000</v>
+      </c>
+      <c r="S14">
+        <v>1893400000</v>
+      </c>
+      <c r="T14">
+        <v>6430200000</v>
+      </c>
+      <c r="U14">
+        <v>6746200000</v>
+      </c>
+      <c r="V14">
+        <v>6902300000</v>
+      </c>
+      <c r="W14">
+        <v>6673000000</v>
+      </c>
+      <c r="X14">
+        <v>0.282495101241019</v>
+      </c>
+      <c r="Y14">
+        <v>0.2899113575049658</v>
+      </c>
+      <c r="Z14">
+        <v>0.281312026425974</v>
+      </c>
+      <c r="AA14">
+        <v>0.283740446575753</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15">
+        <v>387.7999877929688</v>
+      </c>
+      <c r="D15">
+        <v>521716.6666666667</v>
+      </c>
+      <c r="E15">
+        <v>365.1679998779297</v>
+      </c>
+      <c r="F15">
+        <v>343.5869940185547</v>
+      </c>
+      <c r="G15">
+        <v>333.1170553588867</v>
+      </c>
+      <c r="H15">
+        <v>324.5161172485352</v>
+      </c>
+      <c r="I15">
+        <v>8.841096878051758</v>
+      </c>
+      <c r="J15">
+        <v>387.7999877929688</v>
+      </c>
+      <c r="K15">
+        <v>120.9783151603196</v>
+      </c>
+      <c r="L15">
+        <v>4.43</v>
+      </c>
+      <c r="M15">
+        <v>3.79</v>
+      </c>
+      <c r="N15">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="O15">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="P15">
+        <v>494000000</v>
+      </c>
+      <c r="Q15">
+        <v>417000000</v>
+      </c>
+      <c r="R15">
+        <v>890000000</v>
+      </c>
+      <c r="S15">
+        <v>872000000</v>
+      </c>
+      <c r="T15">
+        <v>3617000000</v>
+      </c>
+      <c r="U15">
+        <v>3742000000</v>
+      </c>
+      <c r="V15">
+        <v>3876000000</v>
+      </c>
+      <c r="W15">
+        <v>3925000000</v>
+      </c>
+      <c r="X15">
+        <v>0.1365772739839646</v>
+      </c>
+      <c r="Y15">
+        <v>0.1114377338321753</v>
+      </c>
+      <c r="Z15">
+        <v>0.2296181630546956</v>
+      </c>
+      <c r="AA15">
+        <v>0.2221656050955414</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28">
+      <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16">
+        <v>185.4700012207031</v>
+      </c>
+      <c r="D16">
+        <v>3018950</v>
+      </c>
+      <c r="E16">
+        <v>174.7672314453125</v>
+      </c>
+      <c r="F16">
+        <v>164.1123129272461</v>
+      </c>
+      <c r="G16">
+        <v>162.6122047424316</v>
+      </c>
+      <c r="H16">
+        <v>160.0920462036133</v>
+      </c>
+      <c r="I16">
+        <v>0.3842804133892059</v>
+      </c>
+      <c r="J16">
+        <v>192.8470458984375</v>
+      </c>
+      <c r="K16">
+        <v>119.8801607244577</v>
+      </c>
+      <c r="L16">
+        <v>2.07</v>
+      </c>
+      <c r="M16">
+        <v>2.4</v>
+      </c>
+      <c r="N16">
+        <v>2.89</v>
+      </c>
+      <c r="O16">
+        <v>3.3</v>
+      </c>
+      <c r="P16">
+        <v>1572000000</v>
+      </c>
+      <c r="Q16">
+        <v>1816000000</v>
+      </c>
+      <c r="R16">
+        <v>2174000000</v>
+      </c>
+      <c r="S16">
+        <v>2451000000</v>
+      </c>
+      <c r="T16">
+        <v>13942000000</v>
+      </c>
+      <c r="U16">
+        <v>14186000000</v>
+      </c>
+      <c r="V16">
+        <v>15043000000</v>
+      </c>
+      <c r="W16">
+        <v>15342000000</v>
+      </c>
+      <c r="X16">
+        <v>0.1127528331659733</v>
+      </c>
+      <c r="Y16">
+        <v>0.1280135344706048</v>
+      </c>
+      <c r="Z16">
+        <v>0.1445190454031776</v>
+      </c>
+      <c r="AA16">
+        <v>0.1597575283535393</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28">
+      <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17">
+        <v>201.3699951171875</v>
+      </c>
+      <c r="D17">
+        <v>3060616.666666667</v>
+      </c>
+      <c r="E17">
+        <v>187.7404077148437</v>
+      </c>
+      <c r="F17">
+        <v>181.8594775390625</v>
+      </c>
+      <c r="G17">
+        <v>181.8014987945557</v>
+      </c>
+      <c r="H17">
+        <v>181.0833441925049</v>
+      </c>
+      <c r="I17">
+        <v>0.3827064335346222</v>
+      </c>
+      <c r="J17">
+        <v>201.3699951171875</v>
+      </c>
+      <c r="K17">
+        <v>116.8925334935554</v>
+      </c>
+      <c r="L17">
+        <v>1.88</v>
+      </c>
+      <c r="M17">
+        <v>1.92</v>
+      </c>
+      <c r="N17">
+        <v>1.74</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>961474000</v>
+      </c>
+      <c r="Q17">
+        <v>977656000</v>
+      </c>
+      <c r="R17">
+        <v>877019000</v>
+      </c>
+      <c r="S17">
+        <v>498430000</v>
+      </c>
+      <c r="T17">
+        <v>3249630000</v>
+      </c>
+      <c r="U17">
+        <v>3262930000</v>
+      </c>
+      <c r="V17">
+        <v>3076495000</v>
+      </c>
+      <c r="W17">
+        <v>2716484000</v>
+      </c>
+      <c r="X17">
+        <v>0.2958718377169093</v>
+      </c>
+      <c r="Y17">
+        <v>0.2996251835007187</v>
+      </c>
+      <c r="Z17">
+        <v>0.2850708354799861</v>
+      </c>
+      <c r="AA17">
+        <v>0.1834835029398296</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28">
+      <c r="A18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18">
+        <v>167.5</v>
+      </c>
+      <c r="D18">
+        <v>5629946.666666667</v>
+      </c>
+      <c r="E18">
+        <v>149.8244808959961</v>
+      </c>
+      <c r="F18">
+        <v>145.0444269816081</v>
+      </c>
+      <c r="G18">
+        <v>144.618323059082</v>
+      </c>
+      <c r="H18">
+        <v>143.6155020904541</v>
+      </c>
+      <c r="I18">
+        <v>21.3160572052002</v>
+      </c>
+      <c r="J18">
+        <v>167.5</v>
+      </c>
+      <c r="K18">
+        <v>116.2062472450079</v>
+      </c>
+      <c r="L18">
+        <v>1.38</v>
+      </c>
+      <c r="M18">
+        <v>0.13</v>
+      </c>
+      <c r="N18">
+        <v>1.14</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>2473000000</v>
+      </c>
+      <c r="Q18">
+        <v>239000000</v>
+      </c>
+      <c r="R18">
+        <v>2024000000</v>
+      </c>
+      <c r="S18">
+        <v>1778000000</v>
+      </c>
+      <c r="T18">
+        <v>15121000000</v>
+      </c>
+      <c r="U18">
+        <v>12225000000</v>
+      </c>
+      <c r="V18">
+        <v>13865000000</v>
+      </c>
+      <c r="W18">
+        <v>13927000000</v>
+      </c>
+      <c r="X18">
+        <v>0.1635473844322465</v>
+      </c>
+      <c r="Y18">
+        <v>0.01955010224948875</v>
+      </c>
+      <c r="Z18">
+        <v>0.1459790840245222</v>
+      </c>
+      <c r="AA18">
+        <v>0.1276656853593739</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28">
+      <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19">
+        <v>84.63999938964844</v>
+      </c>
+      <c r="D19">
+        <v>1993900</v>
+      </c>
+      <c r="E19">
+        <v>82.27285003662109</v>
+      </c>
+      <c r="F19">
+        <v>77.03068913777669</v>
+      </c>
+      <c r="G19">
+        <v>74.25226202011109</v>
+      </c>
+      <c r="H19">
+        <v>72.21122352600098</v>
+      </c>
+      <c r="I19">
+        <v>0.04394812136888504</v>
+      </c>
+      <c r="J19">
+        <v>84.63999938964844</v>
+      </c>
+      <c r="K19">
+        <v>116.0634020999849</v>
+      </c>
+      <c r="L19">
+        <v>0.31</v>
+      </c>
+      <c r="M19">
+        <v>1.94</v>
+      </c>
+      <c r="N19">
+        <v>2.71</v>
+      </c>
+      <c r="O19">
+        <v>2.64</v>
+      </c>
+      <c r="P19">
+        <v>185000000</v>
+      </c>
+      <c r="Q19">
+        <v>1188000000</v>
+      </c>
+      <c r="R19">
+        <v>1634000000</v>
+      </c>
+      <c r="S19">
+        <v>1569000000</v>
+      </c>
+      <c r="T19">
+        <v>4018000000</v>
+      </c>
+      <c r="U19">
+        <v>4828000000</v>
+      </c>
+      <c r="V19">
+        <v>5173000000</v>
+      </c>
+      <c r="W19">
+        <v>4979000000</v>
+      </c>
+      <c r="X19">
+        <v>0.04604280736684918</v>
+      </c>
+      <c r="Y19">
+        <v>0.2460646230323115</v>
+      </c>
+      <c r="Z19">
+        <v>0.3158708679682969</v>
+      </c>
+      <c r="AA19">
+        <v>0.3151235187788712</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28">
+      <c r="A20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20">
+        <v>195.1799926757812</v>
+      </c>
+      <c r="D20">
+        <v>56471820</v>
+      </c>
+      <c r="E20">
+        <v>190.2843997192383</v>
+      </c>
+      <c r="F20">
+        <v>184.2515041097005</v>
+      </c>
+      <c r="G20">
+        <v>181.1409587097168</v>
+      </c>
+      <c r="H20">
+        <v>178.0588411712646</v>
+      </c>
+      <c r="I20">
+        <v>0.03800013288855553</v>
+      </c>
+      <c r="J20">
+        <v>198.1100006103516</v>
+      </c>
+      <c r="K20">
+        <v>115.5024516844622</v>
+      </c>
+      <c r="L20">
+        <v>1.88</v>
+      </c>
+      <c r="M20">
+        <v>1.52</v>
+      </c>
+      <c r="N20">
+        <v>1.26</v>
+      </c>
+      <c r="O20">
+        <v>1.46</v>
+      </c>
+      <c r="P20">
+        <v>29998000000</v>
+      </c>
+      <c r="Q20">
+        <v>24160000000</v>
+      </c>
+      <c r="R20">
+        <v>19881000000</v>
+      </c>
+      <c r="S20">
+        <v>22956000000</v>
+      </c>
+      <c r="T20">
+        <v>117154000000</v>
+      </c>
+      <c r="U20">
+        <v>94836000000</v>
+      </c>
+      <c r="V20">
+        <v>81797000000</v>
+      </c>
+      <c r="W20">
+        <v>89498000000</v>
+      </c>
+      <c r="X20">
+        <v>0.2560561312460522</v>
+      </c>
+      <c r="Y20">
+        <v>0.2547555780505293</v>
+      </c>
+      <c r="Z20">
+        <v>0.2430529237013583</v>
+      </c>
+      <c r="AA20">
+        <v>0.2564973518961318</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21">
+        <v>165.1199951171875</v>
+      </c>
+      <c r="D21">
+        <v>896596.6666666666</v>
+      </c>
+      <c r="E21">
+        <v>159.1805725097656</v>
+      </c>
+      <c r="F21">
+        <v>155.0577189127604</v>
+      </c>
+      <c r="G21">
+        <v>152.1976529693603</v>
+      </c>
+      <c r="H21">
+        <v>149.7187301635742</v>
+      </c>
+      <c r="I21">
+        <v>0.8383815884590149</v>
+      </c>
+      <c r="J21">
+        <v>165.1199951171875</v>
+      </c>
+      <c r="K21">
+        <v>115.1772436043297</v>
+      </c>
+      <c r="L21">
+        <v>1.33</v>
+      </c>
+      <c r="M21">
+        <v>1.32</v>
+      </c>
+      <c r="N21">
+        <v>1.4</v>
+      </c>
+      <c r="O21">
+        <v>1.47</v>
+      </c>
+      <c r="P21">
+        <v>307081000</v>
+      </c>
+      <c r="Q21">
+        <v>305712000</v>
+      </c>
+      <c r="R21">
+        <v>324242000</v>
+      </c>
+      <c r="S21">
+        <v>340370000</v>
+      </c>
+      <c r="T21">
+        <v>1625667000</v>
+      </c>
+      <c r="U21">
+        <v>1597117000</v>
+      </c>
+      <c r="V21">
+        <v>1646111000</v>
+      </c>
+      <c r="W21">
+        <v>1622837000</v>
+      </c>
+      <c r="X21">
+        <v>0.1888953887850341</v>
+      </c>
+      <c r="Y21">
+        <v>0.1914149057332681</v>
+      </c>
+      <c r="Z21">
+        <v>0.1969745661137068</v>
+      </c>
+      <c r="AA21">
+        <v>0.2097376384689282</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28">
+      <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22">
+        <v>201.0299987792969</v>
+      </c>
+      <c r="D22">
+        <v>371716.6666666667</v>
+      </c>
+      <c r="E22">
+        <v>194.4694479370117</v>
+      </c>
+      <c r="F22">
+        <v>183.5479522705078</v>
+      </c>
+      <c r="G22">
+        <v>179.8839754486084</v>
+      </c>
+      <c r="H22">
+        <v>177.0523614501953</v>
+      </c>
+      <c r="I22">
+        <v>0.6416138410568237</v>
+      </c>
+      <c r="J22">
+        <v>219.1539916992188</v>
+      </c>
+      <c r="K22">
+        <v>114.6256851982266</v>
+      </c>
+      <c r="L22">
+        <v>1.51</v>
+      </c>
+      <c r="M22">
+        <v>1.49</v>
+      </c>
+      <c r="N22">
+        <v>1.24</v>
+      </c>
+      <c r="O22">
+        <v>1.71</v>
+      </c>
+      <c r="P22">
+        <v>122900000</v>
+      </c>
+      <c r="Q22">
+        <v>121200000</v>
+      </c>
+      <c r="R22">
+        <v>100400000</v>
+      </c>
+      <c r="S22">
+        <v>138300000</v>
+      </c>
+      <c r="T22">
+        <v>2025900000</v>
+      </c>
+      <c r="U22">
+        <v>2065000000</v>
+      </c>
+      <c r="V22">
+        <v>2090500000</v>
+      </c>
+      <c r="W22">
+        <v>2098300000</v>
+      </c>
+      <c r="X22">
+        <v>0.06066439607088208</v>
+      </c>
+      <c r="Y22">
+        <v>0.05869249394673123</v>
+      </c>
+      <c r="Z22">
+        <v>0.0480267878497967</v>
+      </c>
+      <c r="AA22">
+        <v>0.06591049897536101</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28">
+      <c r="A23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23">
+        <v>239.6799926757812</v>
+      </c>
+      <c r="D23">
+        <v>1023420</v>
+      </c>
+      <c r="E23">
+        <v>236.8199746704101</v>
+      </c>
+      <c r="F23">
+        <v>228.86365234375</v>
+      </c>
+      <c r="G23">
+        <v>223.3077913665771</v>
+      </c>
+      <c r="H23">
+        <v>218.7920514678955</v>
+      </c>
+      <c r="I23">
+        <v>0.5959535837173462</v>
+      </c>
+      <c r="J23">
+        <v>252.3522644042969</v>
+      </c>
+      <c r="K23">
+        <v>111.826441934746</v>
+      </c>
+      <c r="L23">
+        <v>0.63</v>
+      </c>
+      <c r="M23">
+        <v>2.24</v>
+      </c>
+      <c r="N23">
+        <v>1.07</v>
+      </c>
+      <c r="O23">
+        <v>1.28</v>
+      </c>
+      <c r="P23">
+        <v>135500000</v>
+      </c>
+      <c r="Q23">
+        <v>486500000</v>
+      </c>
+      <c r="R23">
+        <v>234500000</v>
+      </c>
+      <c r="S23">
+        <v>280700000</v>
+      </c>
+      <c r="T23">
+        <v>2018200000</v>
+      </c>
+      <c r="U23">
+        <v>2705800000</v>
+      </c>
+      <c r="V23">
+        <v>2436800000</v>
+      </c>
+      <c r="W23">
+        <v>2491500000</v>
+      </c>
+      <c r="X23">
+        <v>0.06713903478347041</v>
+      </c>
+      <c r="Y23">
+        <v>0.1797989504028384</v>
+      </c>
+      <c r="Z23">
+        <v>0.0962327642810243</v>
+      </c>
+      <c r="AA23">
+        <v>0.1126630543849087</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28">
+      <c r="A24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24">
+        <v>80.33999633789062</v>
+      </c>
+      <c r="D24">
+        <v>1762646.666666667</v>
+      </c>
+      <c r="E24">
+        <v>79.60059951782226</v>
+      </c>
+      <c r="F24">
+        <v>79.13879999796549</v>
+      </c>
+      <c r="G24">
+        <v>77.49629993438721</v>
+      </c>
+      <c r="H24">
+        <v>76.4592999458313</v>
+      </c>
+      <c r="I24">
+        <v>1.263888955116272</v>
+      </c>
+      <c r="J24">
+        <v>90</v>
+      </c>
+      <c r="K24">
+        <v>105.5228447459459</v>
+      </c>
+      <c r="L24">
+        <v>2.26</v>
+      </c>
+      <c r="M24">
+        <v>1.87</v>
+      </c>
+      <c r="N24">
+        <v>1.75</v>
+      </c>
+      <c r="O24">
+        <v>1.88</v>
+      </c>
+      <c r="P24">
+        <v>859688000</v>
+      </c>
+      <c r="Q24">
+        <v>715000000</v>
+      </c>
+      <c r="R24">
+        <v>671000000</v>
+      </c>
+      <c r="S24">
+        <v>723000000</v>
+      </c>
+      <c r="T24">
+        <v>2951721000</v>
+      </c>
+      <c r="U24">
+        <v>3118000000</v>
+      </c>
+      <c r="V24">
+        <v>3096000000</v>
+      </c>
+      <c r="W24">
+        <v>3293000000</v>
+      </c>
+      <c r="X24">
+        <v>0.2912497488753171</v>
+      </c>
+      <c r="Y24">
+        <v>0.2293136626042335</v>
+      </c>
+      <c r="Z24">
+        <v>0.2167312661498708</v>
+      </c>
+      <c r="AA24">
+        <v>0.2195566352869724</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Screener/ScreenResult/ScreenResult.xlsx
+++ b/Screener/ScreenResult/ScreenResult.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="243">
   <si>
     <t>Symbol</t>
   </si>
@@ -208,6 +208,150 @@
     <t>ONTO</t>
   </si>
   <si>
+    <t>INFA</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>PCVX</t>
+  </si>
+  <si>
+    <t>VST</t>
+  </si>
+  <si>
+    <t>GFF</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>CABA</t>
+  </si>
+  <si>
+    <t>WING</t>
+  </si>
+  <si>
+    <t>KKR</t>
+  </si>
+  <si>
+    <t>WOR</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>HCC</t>
+  </si>
+  <si>
+    <t>PGTI</t>
+  </si>
+  <si>
+    <t>MDC</t>
+  </si>
+  <si>
+    <t>CYBR</t>
+  </si>
+  <si>
+    <t>SBS</t>
+  </si>
+  <si>
+    <t>CCJ</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>BRBR</t>
+  </si>
+  <si>
+    <t>ASND</t>
+  </si>
+  <si>
+    <t>CNM</t>
+  </si>
+  <si>
+    <t>RCL</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>PHM</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>PRCT</t>
+  </si>
+  <si>
+    <t>GDDY</t>
+  </si>
+  <si>
+    <t>TNK</t>
+  </si>
+  <si>
+    <t>JBI</t>
+  </si>
+  <si>
+    <t>AZEK</t>
+  </si>
+  <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>NFLX</t>
+  </si>
+  <si>
+    <t>CVLT</t>
+  </si>
+  <si>
+    <t>RYAAY</t>
+  </si>
+  <si>
+    <t>WDAY</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>APPF</t>
+  </si>
+  <si>
+    <t>EXP</t>
+  </si>
+  <si>
+    <t>TOL</t>
+  </si>
+  <si>
+    <t>ROAD</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>PLAY</t>
+  </si>
+  <si>
+    <t>COLL</t>
+  </si>
+  <si>
+    <t>DV</t>
+  </si>
+  <si>
+    <t>AYI</t>
+  </si>
+  <si>
     <t>Healthcare</t>
   </si>
   <si>
@@ -226,6 +370,18 @@
     <t>Consumer Defensive</t>
   </si>
   <si>
+    <t>Utilities</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
     <t>Biotechnology</t>
   </si>
   <si>
@@ -247,39 +403,105 @@
     <t>Semiconductor Equipment &amp; Materials</t>
   </si>
   <si>
+    <t>Software—Infrastructure</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Coking Coal</t>
+  </si>
+  <si>
+    <t>Rental &amp; Leasing Services</t>
+  </si>
+  <si>
+    <t>Travel Services</t>
+  </si>
+  <si>
+    <t>Electronic Components</t>
+  </si>
+  <si>
+    <t>Residential Construction</t>
+  </si>
+  <si>
+    <t>Household &amp; Personal Products</t>
+  </si>
+  <si>
+    <t>Airlines</t>
+  </si>
+  <si>
     <t>Software - Infrastructure</t>
   </si>
   <si>
-    <t>Semiconductors</t>
-  </si>
-  <si>
-    <t>Coking Coal</t>
-  </si>
-  <si>
-    <t>Rental &amp; Leasing Services</t>
-  </si>
-  <si>
-    <t>Travel Services</t>
-  </si>
-  <si>
-    <t>Electronic Components</t>
-  </si>
-  <si>
-    <t>Residential Construction</t>
-  </si>
-  <si>
-    <t>Household &amp; Personal Products</t>
-  </si>
-  <si>
-    <t>Airlines</t>
-  </si>
-  <si>
     <t>Packaging &amp; Containers</t>
   </si>
   <si>
     <t>Software - Application</t>
   </si>
   <si>
+    <t>Building Products &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Utilities - Independent Power Producers</t>
+  </si>
+  <si>
+    <t>Conglomerates</t>
+  </si>
+  <si>
+    <t>Restaurants</t>
+  </si>
+  <si>
+    <t>Asset Management</t>
+  </si>
+  <si>
+    <t>Metal Fabrication</t>
+  </si>
+  <si>
+    <t>Utilities - Regulated Water</t>
+  </si>
+  <si>
+    <t>Uranium</t>
+  </si>
+  <si>
+    <t>Packaged Foods</t>
+  </si>
+  <si>
+    <t>Industrial Distribution</t>
+  </si>
+  <si>
+    <t>Software—Application</t>
+  </si>
+  <si>
+    <t>Footwear &amp; Accessories</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Construction</t>
+  </si>
+  <si>
+    <t>Utilities—Independent Power Producers</t>
+  </si>
+  <si>
+    <t>Trucking</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Midstream</t>
+  </si>
+  <si>
+    <t>Drug Manufacturers - General</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas E&amp;P</t>
+  </si>
+  <si>
+    <t>Building Materials</t>
+  </si>
+  <si>
+    <t>Drug Manufacturers - Specialty &amp; Generic</t>
+  </si>
+  <si>
     <t>2021-05-14</t>
   </si>
   <si>
@@ -380,6 +602,141 @@
   </si>
   <si>
     <t>2019-10-28</t>
+  </si>
+  <si>
+    <t>2021-10-27</t>
+  </si>
+  <si>
+    <t>2005-06-28</t>
+  </si>
+  <si>
+    <t>2020-06-12</t>
+  </si>
+  <si>
+    <t>2016-10-05</t>
+  </si>
+  <si>
+    <t>1973-05-03</t>
+  </si>
+  <si>
+    <t>2014-06-06</t>
+  </si>
+  <si>
+    <t>2019-10-25</t>
+  </si>
+  <si>
+    <t>2015-06-12</t>
+  </si>
+  <si>
+    <t>2010-07-15</t>
+  </si>
+  <si>
+    <t>1997-12-18</t>
+  </si>
+  <si>
+    <t>2017-04-13</t>
+  </si>
+  <si>
+    <t>2006-06-28</t>
+  </si>
+  <si>
+    <t>1980-03-11</t>
+  </si>
+  <si>
+    <t>2014-09-24</t>
+  </si>
+  <si>
+    <t>2002-05-10</t>
+  </si>
+  <si>
+    <t>1996-03-14</t>
+  </si>
+  <si>
+    <t>2015-06-25</t>
+  </si>
+  <si>
+    <t>2019-10-18</t>
+  </si>
+  <si>
+    <t>2015-01-28</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>1993-04-28</t>
+  </si>
+  <si>
+    <t>2012-06-29</t>
+  </si>
+  <si>
+    <t>1993-10-15</t>
+  </si>
+  <si>
+    <t>1991-07-12</t>
+  </si>
+  <si>
+    <t>2003-12-02</t>
+  </si>
+  <si>
+    <t>2003-10-07</t>
+  </si>
+  <si>
+    <t>2021-09-15</t>
+  </si>
+  <si>
+    <t>2015-03-31</t>
+  </si>
+  <si>
+    <t>2007-12-13</t>
+  </si>
+  <si>
+    <t>2019-12-20</t>
+  </si>
+  <si>
+    <t>1972-06-01</t>
+  </si>
+  <si>
+    <t>2002-05-23</t>
+  </si>
+  <si>
+    <t>2006-09-22</t>
+  </si>
+  <si>
+    <t>1997-05-29</t>
+  </si>
+  <si>
+    <t>2012-10-12</t>
+  </si>
+  <si>
+    <t>2019-07-26</t>
+  </si>
+  <si>
+    <t>2015-06-26</t>
+  </si>
+  <si>
+    <t>1994-04-12</t>
+  </si>
+  <si>
+    <t>1986-07-08</t>
+  </si>
+  <si>
+    <t>2018-05-04</t>
+  </si>
+  <si>
+    <t>2004-06-23</t>
+  </si>
+  <si>
+    <t>2014-10-10</t>
+  </si>
+  <si>
+    <t>2015-05-07</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>2001-12-03</t>
   </si>
   <si>
     <t>F</t>
@@ -743,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD35"/>
+  <dimension ref="A1:AD83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:30">
@@ -843,13 +1200,13 @@
         <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>162</v>
       </c>
       <c r="E2">
         <v>38</v>
@@ -927,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:30">
@@ -935,13 +1292,13 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>163</v>
       </c>
       <c r="E3">
         <v>583.5</v>
@@ -1019,7 +1376,7 @@
         <v>0.07406570450522533</v>
       </c>
       <c r="AD3" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:30">
@@ -1027,13 +1384,13 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="E4">
         <v>21.14999961853027</v>
@@ -1111,7 +1468,7 @@
         <v>0</v>
       </c>
       <c r="AD4" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:30">
@@ -1119,13 +1476,13 @@
         <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>165</v>
       </c>
       <c r="E5">
         <v>106.5800018310547</v>
@@ -1146,7 +1503,7 @@
         <v>47.42455002784729</v>
       </c>
       <c r="K5">
-        <v>4.19581413269043</v>
+        <v>4.195814609527588</v>
       </c>
       <c r="L5">
         <v>106.5800018310547</v>
@@ -1203,7 +1560,7 @@
         <v>0.0910717311400366</v>
       </c>
       <c r="AD5" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" spans="1:30">
@@ -1211,13 +1568,13 @@
         <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="E6">
         <v>59.45999908447266</v>
@@ -1226,19 +1583,19 @@
         <v>4770306.666666667</v>
       </c>
       <c r="G6">
-        <v>48.39249633789063</v>
+        <v>48.39880004882812</v>
       </c>
       <c r="H6">
-        <v>39.55638404846191</v>
+        <v>39.571466700236</v>
       </c>
       <c r="I6">
-        <v>34.10642806529999</v>
+        <v>34.12020001888275</v>
       </c>
       <c r="J6">
-        <v>30.23635217666626</v>
+        <v>30.2508500289917</v>
       </c>
       <c r="K6">
-        <v>5.557553291320801</v>
+        <v>5.564881324768066</v>
       </c>
       <c r="L6">
         <v>59.45999908447266</v>
@@ -1295,7 +1652,7 @@
         <v>0.05399977045793641</v>
       </c>
       <c r="AD6" t="s">
-        <v>123</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:30">
@@ -1303,13 +1660,13 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="E7">
         <v>49.79999923706055</v>
@@ -1387,7 +1744,7 @@
         <v>0</v>
       </c>
       <c r="AD7" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:30">
@@ -1395,13 +1752,13 @@
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="E8">
         <v>71.26000213623047</v>
@@ -1422,7 +1779,7 @@
         <v>38.05255004882812</v>
       </c>
       <c r="K8">
-        <v>0.7788500785827637</v>
+        <v>0.5703791379928589</v>
       </c>
       <c r="L8">
         <v>71.26000213623047</v>
@@ -1479,7 +1836,7 @@
         <v>0.07908799429996438</v>
       </c>
       <c r="AD8" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:30">
@@ -1487,13 +1844,13 @@
         <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="E9">
         <v>81.25</v>
@@ -1571,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="AD9" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:30">
@@ -1579,13 +1936,13 @@
         <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>170</v>
       </c>
       <c r="E10">
         <v>45</v>
@@ -1663,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="AD10" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" spans="1:30">
@@ -1671,13 +2028,13 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="C11" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="E11">
         <v>79.63999938964844</v>
@@ -1698,7 +2055,7 @@
         <v>45.65655004501343</v>
       </c>
       <c r="K11">
-        <v>0.2303776293992996</v>
+        <v>0.2220596075057983</v>
       </c>
       <c r="L11">
         <v>80.80000305175781</v>
@@ -1755,7 +2112,7 @@
         <v>0.274114576860942</v>
       </c>
       <c r="AD11" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12" spans="1:30">
@@ -1763,13 +2120,13 @@
         <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="E12">
         <v>24.38999938964844</v>
@@ -1847,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="AD12" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:30">
@@ -1855,13 +2212,13 @@
         <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="E13">
         <v>299.3699951171875</v>
@@ -1939,7 +2296,7 @@
         <v>0.03392433213657772</v>
       </c>
       <c r="AD13" t="s">
-        <v>123</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14" spans="1:30">
@@ -1947,13 +2304,13 @@
         <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>174</v>
       </c>
       <c r="E14">
         <v>46.33000183105469</v>
@@ -2031,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="AD14" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15" spans="1:30">
@@ -2039,13 +2396,13 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>175</v>
       </c>
       <c r="E15">
         <v>44.52999877929688</v>
@@ -2123,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="AD15" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" spans="1:30">
@@ -2131,13 +2488,13 @@
         <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="E16">
         <v>77.68000030517578</v>
@@ -2215,7 +2572,7 @@
         <v>0</v>
       </c>
       <c r="AD16" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="17" spans="1:30">
@@ -2223,13 +2580,13 @@
         <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>177</v>
       </c>
       <c r="E17">
         <v>630.27001953125</v>
@@ -2238,19 +2595,19 @@
         <v>41995640</v>
       </c>
       <c r="G17">
-        <v>518.7311590576172</v>
+        <v>518.7396002197265</v>
       </c>
       <c r="H17">
-        <v>471.2738641357422</v>
+        <v>471.3145336914063</v>
       </c>
       <c r="I17">
-        <v>438.6611726379394</v>
+        <v>438.7118006896973</v>
       </c>
       <c r="J17">
-        <v>408.1383532714844</v>
+        <v>408.196350402832</v>
       </c>
       <c r="K17">
-        <v>0.3129485249519348</v>
+        <v>0.3134739995002747</v>
       </c>
       <c r="L17">
         <v>630.27001953125</v>
@@ -2307,7 +2664,7 @@
         <v>0.5100993377483444</v>
       </c>
       <c r="AD17" t="s">
-        <v>123</v>
+        <v>242</v>
       </c>
     </row>
     <row r="18" spans="1:30">
@@ -2315,13 +2672,13 @@
         <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="D18" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="E18">
         <v>57.08000183105469</v>
@@ -2399,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="AD18" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:30">
@@ -2407,13 +2764,13 @@
         <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="D19" t="s">
-        <v>105</v>
+        <v>179</v>
       </c>
       <c r="E19">
         <v>18.95000076293945</v>
@@ -2428,19 +2785,19 @@
         <v>12.54828420639038</v>
       </c>
       <c r="I19">
-        <v>11.48964963674545</v>
+        <v>11.48964965581894</v>
       </c>
       <c r="J19">
-        <v>10.35613589525223</v>
+        <v>10.35613594293594</v>
       </c>
       <c r="K19">
-        <v>1.793278098106384</v>
+        <v>1.793278217315674</v>
       </c>
       <c r="L19">
         <v>22.39999961853027</v>
       </c>
       <c r="M19">
-        <v>182.3930432366508</v>
+        <v>182.3930432682599</v>
       </c>
       <c r="N19">
         <v>0.32</v>
@@ -2491,7 +2848,7 @@
         <v>0.104093792454243</v>
       </c>
       <c r="AD19" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" spans="1:30">
@@ -2499,13 +2856,13 @@
         <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="D20" t="s">
-        <v>106</v>
+        <v>180</v>
       </c>
       <c r="E20">
         <v>55.40000152587891</v>
@@ -2526,13 +2883,13 @@
         <v>33.53442879676819</v>
       </c>
       <c r="K20">
-        <v>3.845682859420776</v>
+        <v>3.845683097839355</v>
       </c>
       <c r="L20">
         <v>55.40000152587891</v>
       </c>
       <c r="M20">
-        <v>179.3338571368868</v>
+        <v>179.3338612942247</v>
       </c>
       <c r="N20">
         <v>0.2</v>
@@ -2583,7 +2940,7 @@
         <v>0.1419016406958529</v>
       </c>
       <c r="AD20" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" spans="1:30">
@@ -2591,13 +2948,13 @@
         <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>181</v>
       </c>
       <c r="E21">
         <v>57.0099983215332</v>
@@ -2675,7 +3032,7 @@
         <v>0.1132595137618105</v>
       </c>
       <c r="AD21" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="22" spans="1:30">
@@ -2683,13 +3040,13 @@
         <v>50</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>182</v>
       </c>
       <c r="E22">
         <v>221.7899932861328</v>
@@ -2767,7 +3124,7 @@
         <v>0.0949543164832664</v>
       </c>
       <c r="AD22" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="23" spans="1:30">
@@ -2775,13 +3132,13 @@
         <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="D23" t="s">
-        <v>109</v>
+        <v>183</v>
       </c>
       <c r="E23">
         <v>34</v>
@@ -2859,7 +3216,7 @@
         <v>0.08494580444950493</v>
       </c>
       <c r="AD23" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" spans="1:30">
@@ -2867,13 +3224,13 @@
         <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>110</v>
+        <v>184</v>
       </c>
       <c r="E24">
         <v>36.09000015258789</v>
@@ -2951,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="AD24" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" spans="1:30">
@@ -2959,13 +3316,13 @@
         <v>53</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="D25" t="s">
-        <v>111</v>
+        <v>185</v>
       </c>
       <c r="E25">
         <v>162.5</v>
@@ -3043,7 +3400,7 @@
         <v>0.1543847763645728</v>
       </c>
       <c r="AD25" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="26" spans="1:30">
@@ -3051,13 +3408,13 @@
         <v>54</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="C26" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="D26" t="s">
-        <v>112</v>
+        <v>186</v>
       </c>
       <c r="E26">
         <v>54.09000015258789</v>
@@ -3078,7 +3435,7 @@
         <v>38.07694995880127</v>
       </c>
       <c r="K26">
-        <v>0.4534775018692017</v>
+        <v>0.4534776210784912</v>
       </c>
       <c r="L26">
         <v>65.85888671875</v>
@@ -3135,7 +3492,7 @@
         <v>0.03064328981389272</v>
       </c>
       <c r="AD26" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27" spans="1:30">
@@ -3143,13 +3500,13 @@
         <v>55</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="D27" t="s">
-        <v>113</v>
+        <v>187</v>
       </c>
       <c r="E27">
         <v>170.4799957275391</v>
@@ -3227,7 +3584,7 @@
         <v>0.1081387808041505</v>
       </c>
       <c r="AD27" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28" spans="1:30">
@@ -3235,13 +3592,13 @@
         <v>56</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="D28" t="s">
-        <v>114</v>
+        <v>188</v>
       </c>
       <c r="E28">
         <v>339.9700012207031</v>
@@ -3319,7 +3676,7 @@
         <v>0.1034023747404292</v>
       </c>
       <c r="AD28" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29" spans="1:30">
@@ -3327,13 +3684,13 @@
         <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>139</v>
       </c>
       <c r="D29" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="E29">
         <v>14.65999984741211</v>
@@ -3345,22 +3702,22 @@
         <v>13.30081823348999</v>
       </c>
       <c r="H29">
-        <v>9.997125701904297</v>
+        <v>9.997125692367554</v>
       </c>
       <c r="I29">
-        <v>9.331780562400818</v>
+        <v>9.331780552864075</v>
       </c>
       <c r="J29">
-        <v>8.652675030231476</v>
+        <v>8.652675011157989</v>
       </c>
       <c r="K29">
         <v>6.708024024963379</v>
       </c>
       <c r="L29">
-        <v>16.82963562011719</v>
+        <v>16.82963371276855</v>
       </c>
       <c r="M29">
-        <v>162.3958211028741</v>
+        <v>162.3958192067563</v>
       </c>
       <c r="N29">
         <v>0.15</v>
@@ -3411,7 +3768,7 @@
         <v>0.02102973168963017</v>
       </c>
       <c r="AD29" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="30" spans="1:30">
@@ -3419,13 +3776,13 @@
         <v>58</v>
       </c>
       <c r="B30" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s">
-        <v>116</v>
+        <v>190</v>
       </c>
       <c r="E30">
         <v>128.8800048828125</v>
@@ -3446,7 +3803,7 @@
         <v>86.92170007705688</v>
       </c>
       <c r="K30">
-        <v>3.118401765823364</v>
+        <v>3.118402242660522</v>
       </c>
       <c r="L30">
         <v>138.8600006103516</v>
@@ -3503,7 +3860,7 @@
         <v>0.1328553639196805</v>
       </c>
       <c r="AD30" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31" spans="1:30">
@@ -3511,13 +3868,13 @@
         <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="C31" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="D31" t="s">
-        <v>117</v>
+        <v>191</v>
       </c>
       <c r="E31">
         <v>85.77999877929688</v>
@@ -3529,13 +3886,13 @@
         <v>75.90841674804688</v>
       </c>
       <c r="H31">
-        <v>66.70531318664551</v>
+        <v>66.70531290690104</v>
       </c>
       <c r="I31">
-        <v>61.46624073028565</v>
+        <v>61.46624048233032</v>
       </c>
       <c r="J31">
-        <v>57.3254907989502</v>
+        <v>57.32549049377442</v>
       </c>
       <c r="K31">
         <v>11.3210620880127</v>
@@ -3544,7 +3901,7 @@
         <v>85.77999877929688</v>
       </c>
       <c r="M31">
-        <v>161.7993707729368</v>
+        <v>161.7993636686724</v>
       </c>
       <c r="N31">
         <v>0.84</v>
@@ -3595,7 +3952,7 @@
         <v>0.0452114511707339</v>
       </c>
       <c r="AD31" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="32" spans="1:30">
@@ -3603,13 +3960,13 @@
         <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s">
-        <v>118</v>
+        <v>192</v>
       </c>
       <c r="E32">
         <v>37.20999908447266</v>
@@ -3687,7 +4044,7 @@
         <v>0</v>
       </c>
       <c r="AD32" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="33" spans="1:30">
@@ -3695,13 +4052,13 @@
         <v>61</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="C33" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="D33" t="s">
-        <v>119</v>
+        <v>193</v>
       </c>
       <c r="E33">
         <v>1200.010009765625</v>
@@ -3713,22 +4070,22 @@
         <v>1078.220603027344</v>
       </c>
       <c r="H33">
-        <v>936.2544213867187</v>
+        <v>936.2544197591146</v>
       </c>
       <c r="I33">
-        <v>880.6724224853516</v>
+        <v>880.6724212646484</v>
       </c>
       <c r="J33">
-        <v>827.4175436401367</v>
+        <v>827.4175424194336</v>
       </c>
       <c r="K33">
-        <v>10.43821239471436</v>
+        <v>10.4382152557373</v>
       </c>
       <c r="L33">
         <v>1253.869995117188</v>
       </c>
       <c r="M33">
-        <v>161.0581608512518</v>
+        <v>161.0581606097776</v>
       </c>
       <c r="N33">
         <v>8.800000000000001</v>
@@ -3779,7 +4136,7 @@
         <v>0.3791285637439484</v>
       </c>
       <c r="AD33" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="34" spans="1:30">
@@ -3787,13 +4144,13 @@
         <v>62</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="C34" t="s">
-        <v>87</v>
+        <v>140</v>
       </c>
       <c r="D34" t="s">
-        <v>120</v>
+        <v>194</v>
       </c>
       <c r="E34">
         <v>66.73000335693359</v>
@@ -3871,7 +4228,7 @@
         <v>0.02378390012914335</v>
       </c>
       <c r="AD34" t="s">
-        <v>122</v>
+        <v>241</v>
       </c>
     </row>
     <row r="35" spans="1:30">
@@ -3879,13 +4236,13 @@
         <v>63</v>
       </c>
       <c r="B35" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="D35" t="s">
-        <v>121</v>
+        <v>195</v>
       </c>
       <c r="E35">
         <v>162.9499969482422</v>
@@ -3963,7 +4320,4423 @@
         <v>0.1732075198494099</v>
       </c>
       <c r="AD35" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30">
+      <c r="A36" t="s">
+        <v>64</v>
+      </c>
+      <c r="B36" t="s">
+        <v>113</v>
+      </c>
+      <c r="C36" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" t="s">
+        <v>196</v>
+      </c>
+      <c r="E36">
+        <v>30.89999961853027</v>
+      </c>
+      <c r="F36">
+        <v>673603.3333333334</v>
+      </c>
+      <c r="G36">
+        <v>27.94800010681152</v>
+      </c>
+      <c r="H36">
+        <v>22.96620002746582</v>
+      </c>
+      <c r="I36">
+        <v>21.35530002593994</v>
+      </c>
+      <c r="J36">
+        <v>20.04410002231598</v>
+      </c>
+      <c r="K36">
+        <v>14.09000015258789</v>
+      </c>
+      <c r="L36">
+        <v>38.83000183105469</v>
+      </c>
+      <c r="M36">
+        <v>158.5229664232071</v>
+      </c>
+      <c r="N36">
+        <v>-0.02</v>
+      </c>
+      <c r="O36">
+        <v>-0.41</v>
+      </c>
+      <c r="P36">
+        <v>-0.53</v>
+      </c>
+      <c r="Q36">
+        <v>0.27</v>
+      </c>
+      <c r="R36">
+        <v>-4381000</v>
+      </c>
+      <c r="S36">
+        <v>-116354000</v>
+      </c>
+      <c r="T36">
+        <v>-152466000</v>
+      </c>
+      <c r="U36">
+        <v>79276000</v>
+      </c>
+      <c r="V36">
+        <v>398781000</v>
+      </c>
+      <c r="W36">
+        <v>365431000</v>
+      </c>
+      <c r="X36">
+        <v>375988000</v>
+      </c>
+      <c r="Y36">
+        <v>408563000</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>0.1940361706762482</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30">
+      <c r="A37" t="s">
+        <v>65</v>
+      </c>
+      <c r="B37" t="s">
+        <v>115</v>
+      </c>
+      <c r="C37" t="s">
+        <v>141</v>
+      </c>
+      <c r="D37" t="s">
+        <v>197</v>
+      </c>
+      <c r="E37">
+        <v>179.0200042724609</v>
+      </c>
+      <c r="F37">
+        <v>1248333.333333333</v>
+      </c>
+      <c r="G37">
+        <v>158.1500003051758</v>
+      </c>
+      <c r="H37">
+        <v>140.2303332010905</v>
+      </c>
+      <c r="I37">
+        <v>133.7608498382568</v>
+      </c>
+      <c r="J37">
+        <v>125.6812497711182</v>
+      </c>
+      <c r="K37">
+        <v>0.8299999833106995</v>
+      </c>
+      <c r="L37">
+        <v>179.0200042724609</v>
+      </c>
+      <c r="M37">
+        <v>157.8103098074713</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>2.41</v>
+      </c>
+      <c r="P37">
+        <v>3.16</v>
+      </c>
+      <c r="Q37">
+        <v>3.59</v>
+      </c>
+      <c r="R37">
+        <v>384513000</v>
+      </c>
+      <c r="S37">
+        <v>333786000</v>
+      </c>
+      <c r="T37">
+        <v>404619000</v>
+      </c>
+      <c r="U37">
+        <v>451457000</v>
+      </c>
+      <c r="V37">
+        <v>4357565000</v>
+      </c>
+      <c r="W37">
+        <v>3883314000</v>
+      </c>
+      <c r="X37">
+        <v>4528890000</v>
+      </c>
+      <c r="Y37">
+        <v>4534264000</v>
+      </c>
+      <c r="Z37">
+        <v>0.0882403360592441</v>
+      </c>
+      <c r="AA37">
+        <v>0.08595390431986701</v>
+      </c>
+      <c r="AB37">
+        <v>0.08934175923901884</v>
+      </c>
+      <c r="AC37">
+        <v>0.09956566269630529</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30">
+      <c r="A38" t="s">
+        <v>66</v>
+      </c>
+      <c r="B38" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38" t="s">
         <v>122</v>
+      </c>
+      <c r="D38" t="s">
+        <v>198</v>
+      </c>
+      <c r="E38">
+        <v>75.52999877929688</v>
+      </c>
+      <c r="F38">
+        <v>895146.6666666666</v>
+      </c>
+      <c r="G38">
+        <v>59.67799987792969</v>
+      </c>
+      <c r="H38">
+        <v>52.53223320007324</v>
+      </c>
+      <c r="I38">
+        <v>51.74787492752075</v>
+      </c>
+      <c r="J38">
+        <v>49.09307497024536</v>
+      </c>
+      <c r="K38">
+        <v>16.45000076293945</v>
+      </c>
+      <c r="L38">
+        <v>75.52999877929688</v>
+      </c>
+      <c r="M38">
+        <v>157.4630199428105</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>-0.7</v>
+      </c>
+      <c r="P38">
+        <v>-0.7</v>
+      </c>
+      <c r="Q38">
+        <v>-1.456</v>
+      </c>
+      <c r="R38">
+        <v>-78050000</v>
+      </c>
+      <c r="S38">
+        <v>-60462000</v>
+      </c>
+      <c r="T38">
+        <v>-68339000</v>
+      </c>
+      <c r="U38">
+        <v>-92664000</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30">
+      <c r="A39" t="s">
+        <v>67</v>
+      </c>
+      <c r="B39" t="s">
+        <v>118</v>
+      </c>
+      <c r="C39" t="s">
+        <v>142</v>
+      </c>
+      <c r="D39" t="s">
+        <v>199</v>
+      </c>
+      <c r="E39">
+        <v>43.2599983215332</v>
+      </c>
+      <c r="F39">
+        <v>2700230</v>
+      </c>
+      <c r="G39">
+        <v>38.01844047546387</v>
+      </c>
+      <c r="H39">
+        <v>33.18053857167562</v>
+      </c>
+      <c r="I39">
+        <v>30.8732274723053</v>
+      </c>
+      <c r="J39">
+        <v>29.24686505317688</v>
+      </c>
+      <c r="K39">
+        <v>10.13121604919434</v>
+      </c>
+      <c r="L39">
+        <v>43.2599983215332</v>
+      </c>
+      <c r="M39">
+        <v>156.7497806774429</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>1.71</v>
+      </c>
+      <c r="P39">
+        <v>1.17</v>
+      </c>
+      <c r="Q39">
+        <v>1.25</v>
+      </c>
+      <c r="R39">
+        <v>-246000000</v>
+      </c>
+      <c r="S39">
+        <v>699000000</v>
+      </c>
+      <c r="T39">
+        <v>476000000</v>
+      </c>
+      <c r="U39">
+        <v>502000000</v>
+      </c>
+      <c r="V39">
+        <v>3869000000</v>
+      </c>
+      <c r="W39">
+        <v>4425000000</v>
+      </c>
+      <c r="X39">
+        <v>3189000000</v>
+      </c>
+      <c r="Y39">
+        <v>4086000000</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>0.1579661016949153</v>
+      </c>
+      <c r="AB39">
+        <v>0.1492630918783318</v>
+      </c>
+      <c r="AC39">
+        <v>0.122858541360744</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30">
+      <c r="A40" t="s">
+        <v>68</v>
+      </c>
+      <c r="B40" t="s">
+        <v>115</v>
+      </c>
+      <c r="C40" t="s">
+        <v>143</v>
+      </c>
+      <c r="D40" t="s">
+        <v>200</v>
+      </c>
+      <c r="E40">
+        <v>59.09000015258789</v>
+      </c>
+      <c r="F40">
+        <v>404626.6666666667</v>
+      </c>
+      <c r="G40">
+        <v>55.42371841430664</v>
+      </c>
+      <c r="H40">
+        <v>45.68764488220215</v>
+      </c>
+      <c r="I40">
+        <v>42.30994709968567</v>
+      </c>
+      <c r="J40">
+        <v>39.27762689590454</v>
+      </c>
+      <c r="K40">
+        <v>0.564629077911377</v>
+      </c>
+      <c r="L40">
+        <v>61.68999862670898</v>
+      </c>
+      <c r="M40">
+        <v>156.2444974403169</v>
+      </c>
+      <c r="N40">
+        <v>0.88</v>
+      </c>
+      <c r="O40">
+        <v>-1.17</v>
+      </c>
+      <c r="P40">
+        <v>0.9</v>
+      </c>
+      <c r="Q40">
+        <v>0.79</v>
+      </c>
+      <c r="R40">
+        <v>48702000</v>
+      </c>
+      <c r="S40">
+        <v>-62255000</v>
+      </c>
+      <c r="T40">
+        <v>49205000</v>
+      </c>
+      <c r="U40">
+        <v>41965000</v>
+      </c>
+      <c r="V40">
+        <v>649384000</v>
+      </c>
+      <c r="W40">
+        <v>710984000</v>
+      </c>
+      <c r="X40">
+        <v>683430000</v>
+      </c>
+      <c r="Y40">
+        <v>641385000</v>
+      </c>
+      <c r="Z40">
+        <v>0.07499722814236261</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0.07199713211301816</v>
+      </c>
+      <c r="AC40">
+        <v>0.06542872065919846</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30">
+      <c r="A41" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41" t="s">
+        <v>113</v>
+      </c>
+      <c r="C41" t="s">
+        <v>123</v>
+      </c>
+      <c r="D41" t="s">
+        <v>201</v>
+      </c>
+      <c r="E41">
+        <v>262.9800109863281</v>
+      </c>
+      <c r="F41">
+        <v>1591903.333333333</v>
+      </c>
+      <c r="G41">
+        <v>237.9480001831055</v>
+      </c>
+      <c r="H41">
+        <v>202.3743328857422</v>
+      </c>
+      <c r="I41">
+        <v>189.946499786377</v>
+      </c>
+      <c r="J41">
+        <v>180.8547499084473</v>
+      </c>
+      <c r="K41">
+        <v>13.25</v>
+      </c>
+      <c r="L41">
+        <v>271.9599914550781</v>
+      </c>
+      <c r="M41">
+        <v>156.1125791381686</v>
+      </c>
+      <c r="N41">
+        <v>1.35</v>
+      </c>
+      <c r="O41">
+        <v>1.38</v>
+      </c>
+      <c r="P41">
+        <v>1.55</v>
+      </c>
+      <c r="Q41">
+        <v>1.72</v>
+      </c>
+      <c r="R41">
+        <v>427089000</v>
+      </c>
+      <c r="S41">
+        <v>436473000</v>
+      </c>
+      <c r="T41">
+        <v>491885000</v>
+      </c>
+      <c r="U41">
+        <v>545327000</v>
+      </c>
+      <c r="V41">
+        <v>1275552000</v>
+      </c>
+      <c r="W41">
+        <v>1351351000</v>
+      </c>
+      <c r="X41">
+        <v>1458924000</v>
+      </c>
+      <c r="Y41">
+        <v>1509456000</v>
+      </c>
+      <c r="Z41">
+        <v>0.3348268043952736</v>
+      </c>
+      <c r="AA41">
+        <v>0.3229901039774271</v>
+      </c>
+      <c r="AB41">
+        <v>0.3371560136100304</v>
+      </c>
+      <c r="AC41">
+        <v>0.3612738629016016</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="42" spans="1:30">
+      <c r="A42" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" t="s">
+        <v>112</v>
+      </c>
+      <c r="C42" t="s">
+        <v>122</v>
+      </c>
+      <c r="D42" t="s">
+        <v>202</v>
+      </c>
+      <c r="E42">
+        <v>20.57999992370605</v>
+      </c>
+      <c r="F42">
+        <v>834360</v>
+      </c>
+      <c r="G42">
+        <v>20.02319997787476</v>
+      </c>
+      <c r="H42">
+        <v>16.13776666641235</v>
+      </c>
+      <c r="I42">
+        <v>14.93532499790192</v>
+      </c>
+      <c r="J42">
+        <v>13.56497500896454</v>
+      </c>
+      <c r="K42">
+        <v>0.6290000081062317</v>
+      </c>
+      <c r="L42">
+        <v>24.23999977111816</v>
+      </c>
+      <c r="M42">
+        <v>155.5015336612318</v>
+      </c>
+      <c r="N42">
+        <v>-0.52</v>
+      </c>
+      <c r="O42">
+        <v>-0.45</v>
+      </c>
+      <c r="P42">
+        <v>-0.37</v>
+      </c>
+      <c r="Q42">
+        <v>-0.37</v>
+      </c>
+      <c r="R42">
+        <v>-15692000</v>
+      </c>
+      <c r="S42">
+        <v>-15854000</v>
+      </c>
+      <c r="T42">
+        <v>-14487000</v>
+      </c>
+      <c r="U42">
+        <v>-16448000</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30">
+      <c r="A43" t="s">
+        <v>71</v>
+      </c>
+      <c r="B43" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" t="s">
+        <v>144</v>
+      </c>
+      <c r="D43" t="s">
+        <v>203</v>
+      </c>
+      <c r="E43">
+        <v>287.5899963378906</v>
+      </c>
+      <c r="F43">
+        <v>332513.3333333333</v>
+      </c>
+      <c r="G43">
+        <v>255.983000793457</v>
+      </c>
+      <c r="H43">
+        <v>205.0864575195313</v>
+      </c>
+      <c r="I43">
+        <v>203.2188092803955</v>
+      </c>
+      <c r="J43">
+        <v>194.3775471496582</v>
+      </c>
+      <c r="K43">
+        <v>14.6816463470459</v>
+      </c>
+      <c r="L43">
+        <v>287.5899963378906</v>
+      </c>
+      <c r="M43">
+        <v>155.3610024204277</v>
+      </c>
+      <c r="N43">
+        <v>0.59</v>
+      </c>
+      <c r="O43">
+        <v>0.52</v>
+      </c>
+      <c r="P43">
+        <v>0.54</v>
+      </c>
+      <c r="Q43">
+        <v>0.65</v>
+      </c>
+      <c r="R43">
+        <v>17596000</v>
+      </c>
+      <c r="S43">
+        <v>15669000</v>
+      </c>
+      <c r="T43">
+        <v>16181000</v>
+      </c>
+      <c r="U43">
+        <v>19511000</v>
+      </c>
+      <c r="V43">
+        <v>104867000</v>
+      </c>
+      <c r="W43">
+        <v>108721000</v>
+      </c>
+      <c r="X43">
+        <v>107173000</v>
+      </c>
+      <c r="Y43">
+        <v>117104000</v>
+      </c>
+      <c r="Z43">
+        <v>0.1677934908026357</v>
+      </c>
+      <c r="AA43">
+        <v>0.1441211909382732</v>
+      </c>
+      <c r="AB43">
+        <v>0.1509801909062917</v>
+      </c>
+      <c r="AC43">
+        <v>0.1666125836862959</v>
+      </c>
+      <c r="AD43" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30">
+      <c r="A44" t="s">
+        <v>72</v>
+      </c>
+      <c r="B44" t="s">
+        <v>119</v>
+      </c>
+      <c r="C44" t="s">
+        <v>145</v>
+      </c>
+      <c r="D44" t="s">
+        <v>204</v>
+      </c>
+      <c r="E44">
+        <v>88.15000152587891</v>
+      </c>
+      <c r="F44">
+        <v>2903616.666666667</v>
+      </c>
+      <c r="G44">
+        <v>79.95279968261718</v>
+      </c>
+      <c r="H44">
+        <v>66.91560000101725</v>
+      </c>
+      <c r="I44">
+        <v>63.30834997177124</v>
+      </c>
+      <c r="J44">
+        <v>60.03424995422363</v>
+      </c>
+      <c r="K44">
+        <v>5.215526580810547</v>
+      </c>
+      <c r="L44">
+        <v>88.15000152587891</v>
+      </c>
+      <c r="M44">
+        <v>155.1766287554709</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0.36</v>
+      </c>
+      <c r="P44">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="Q44">
+        <v>1.64</v>
+      </c>
+      <c r="R44">
+        <v>100470000</v>
+      </c>
+      <c r="S44">
+        <v>339994000</v>
+      </c>
+      <c r="T44">
+        <v>861712000</v>
+      </c>
+      <c r="U44">
+        <v>1490126000</v>
+      </c>
+      <c r="V44">
+        <v>2528695000</v>
+      </c>
+      <c r="W44">
+        <v>3127482000</v>
+      </c>
+      <c r="X44">
+        <v>3586660000</v>
+      </c>
+      <c r="Y44">
+        <v>3273140000</v>
+      </c>
+      <c r="Z44">
+        <v>0.03973195660212086</v>
+      </c>
+      <c r="AA44">
+        <v>0.1087117367901718</v>
+      </c>
+      <c r="AB44">
+        <v>0.2402547216630514</v>
+      </c>
+      <c r="AC44">
+        <v>0.4552588645765229</v>
+      </c>
+      <c r="AD44" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30">
+      <c r="A45" t="s">
+        <v>73</v>
+      </c>
+      <c r="B45" t="s">
+        <v>115</v>
+      </c>
+      <c r="C45" t="s">
+        <v>146</v>
+      </c>
+      <c r="D45" t="s">
+        <v>187</v>
+      </c>
+      <c r="E45">
+        <v>58.97000122070312</v>
+      </c>
+      <c r="F45">
+        <v>309623.3333333333</v>
+      </c>
+      <c r="G45">
+        <v>52.98785987854004</v>
+      </c>
+      <c r="H45">
+        <v>45.33593185424805</v>
+      </c>
+      <c r="I45">
+        <v>42.97700508117676</v>
+      </c>
+      <c r="J45">
+        <v>41.14614469528198</v>
+      </c>
+      <c r="K45">
+        <v>0.2025986909866333</v>
+      </c>
+      <c r="L45">
+        <v>58.97000122070312</v>
+      </c>
+      <c r="M45">
+        <v>153.815539739555</v>
+      </c>
+      <c r="N45">
+        <v>0.33</v>
+      </c>
+      <c r="O45">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="P45">
+        <v>1.93</v>
+      </c>
+      <c r="Q45">
+        <v>0.49</v>
+      </c>
+      <c r="R45">
+        <v>46325000</v>
+      </c>
+      <c r="S45">
+        <v>129903000</v>
+      </c>
+      <c r="T45">
+        <v>96106000</v>
+      </c>
+      <c r="U45">
+        <v>24302000</v>
+      </c>
+      <c r="V45">
+        <v>1103322000</v>
+      </c>
+      <c r="W45">
+        <v>1228864000</v>
+      </c>
+      <c r="X45">
+        <v>1193256000</v>
+      </c>
+      <c r="Y45">
+        <v>1086918000</v>
+      </c>
+      <c r="Z45">
+        <v>0.04198683611855832</v>
+      </c>
+      <c r="AA45">
+        <v>0.1057098263111296</v>
+      </c>
+      <c r="AB45">
+        <v>0.08054097360499339</v>
+      </c>
+      <c r="AC45">
+        <v>0.0223586323899319</v>
+      </c>
+      <c r="AD45" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30">
+      <c r="A46" t="s">
+        <v>74</v>
+      </c>
+      <c r="B46" t="s">
+        <v>115</v>
+      </c>
+      <c r="C46" t="s">
+        <v>132</v>
+      </c>
+      <c r="D46" t="s">
+        <v>205</v>
+      </c>
+      <c r="E46">
+        <v>645.3699951171875</v>
+      </c>
+      <c r="F46">
+        <v>689070</v>
+      </c>
+      <c r="G46">
+        <v>545.8429992675781</v>
+      </c>
+      <c r="H46">
+        <v>481.4885998535156</v>
+      </c>
+      <c r="I46">
+        <v>453.0853500366211</v>
+      </c>
+      <c r="J46">
+        <v>432.3840493774414</v>
+      </c>
+      <c r="K46">
+        <v>3.029999971389771</v>
+      </c>
+      <c r="L46">
+        <v>651.6400146484375</v>
+      </c>
+      <c r="M46">
+        <v>153.4190052175755</v>
+      </c>
+      <c r="N46">
+        <v>9.15</v>
+      </c>
+      <c r="O46">
+        <v>6.47</v>
+      </c>
+      <c r="P46">
+        <v>8.58</v>
+      </c>
+      <c r="Q46">
+        <v>10.29</v>
+      </c>
+      <c r="R46">
+        <v>451000000</v>
+      </c>
+      <c r="S46">
+        <v>591000000</v>
+      </c>
+      <c r="T46">
+        <v>703000000</v>
+      </c>
+      <c r="U46">
+        <v>679000000</v>
+      </c>
+      <c r="V46">
+        <v>3285000000</v>
+      </c>
+      <c r="W46">
+        <v>3554000000</v>
+      </c>
+      <c r="X46">
+        <v>3765000000</v>
+      </c>
+      <c r="Y46">
+        <v>3728000000</v>
+      </c>
+      <c r="Z46">
+        <v>0.1372907153729072</v>
+      </c>
+      <c r="AA46">
+        <v>0.1662915025323579</v>
+      </c>
+      <c r="AB46">
+        <v>0.1867197875166003</v>
+      </c>
+      <c r="AC46">
+        <v>0.1821351931330472</v>
+      </c>
+      <c r="AD46" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30">
+      <c r="A47" t="s">
+        <v>75</v>
+      </c>
+      <c r="B47" t="s">
+        <v>116</v>
+      </c>
+      <c r="C47" t="s">
+        <v>131</v>
+      </c>
+      <c r="D47" t="s">
+        <v>206</v>
+      </c>
+      <c r="E47">
+        <v>64.5</v>
+      </c>
+      <c r="F47">
+        <v>579503.3333333334</v>
+      </c>
+      <c r="G47">
+        <v>60.86720024108887</v>
+      </c>
+      <c r="H47">
+        <v>49.8181334177653</v>
+      </c>
+      <c r="I47">
+        <v>46.35630002975464</v>
+      </c>
+      <c r="J47">
+        <v>43.42919998168945</v>
+      </c>
+      <c r="K47">
+        <v>6.285525798797607</v>
+      </c>
+      <c r="L47">
+        <v>69.97000122070312</v>
+      </c>
+      <c r="M47">
+        <v>152.869624404423</v>
+      </c>
+      <c r="N47">
+        <v>1.93</v>
+      </c>
+      <c r="O47">
+        <v>3.51</v>
+      </c>
+      <c r="P47">
+        <v>1.58</v>
+      </c>
+      <c r="Q47">
+        <v>1.64</v>
+      </c>
+      <c r="R47">
+        <v>99654000</v>
+      </c>
+      <c r="S47">
+        <v>182277000</v>
+      </c>
+      <c r="T47">
+        <v>82093000</v>
+      </c>
+      <c r="U47">
+        <v>85382000</v>
+      </c>
+      <c r="V47">
+        <v>344750000</v>
+      </c>
+      <c r="W47">
+        <v>509674000</v>
+      </c>
+      <c r="X47">
+        <v>379660000</v>
+      </c>
+      <c r="Y47">
+        <v>423487000</v>
+      </c>
+      <c r="Z47">
+        <v>0.2890616388687455</v>
+      </c>
+      <c r="AA47">
+        <v>0.3576344879275772</v>
+      </c>
+      <c r="AB47">
+        <v>0.2162276773955644</v>
+      </c>
+      <c r="AC47">
+        <v>0.2016165785490464</v>
+      </c>
+      <c r="AD47" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="48" spans="1:30">
+      <c r="A48" t="s">
+        <v>76</v>
+      </c>
+      <c r="B48" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" t="s">
+        <v>141</v>
+      </c>
+      <c r="D48" t="s">
+        <v>207</v>
+      </c>
+      <c r="E48">
+        <v>41.25</v>
+      </c>
+      <c r="F48">
+        <v>1263806.666666667</v>
+      </c>
+      <c r="G48">
+        <v>38.06539993286133</v>
+      </c>
+      <c r="H48">
+        <v>31.67333343505859</v>
+      </c>
+      <c r="I48">
+        <v>30.37335006713867</v>
+      </c>
+      <c r="J48">
+        <v>28.63785008430481</v>
+      </c>
+      <c r="K48">
+        <v>0.8100000023841858</v>
+      </c>
+      <c r="L48">
+        <v>41.72999954223633</v>
+      </c>
+      <c r="M48">
+        <v>151.1952678073417</v>
+      </c>
+      <c r="N48">
+        <v>0.18</v>
+      </c>
+      <c r="O48">
+        <v>0.54</v>
+      </c>
+      <c r="P48">
+        <v>0.53</v>
+      </c>
+      <c r="Q48">
+        <v>0.67</v>
+      </c>
+      <c r="R48">
+        <v>7511000</v>
+      </c>
+      <c r="S48">
+        <v>33590000</v>
+      </c>
+      <c r="T48">
+        <v>31490000</v>
+      </c>
+      <c r="U48">
+        <v>39207000</v>
+      </c>
+      <c r="V48">
+        <v>340934000</v>
+      </c>
+      <c r="W48">
+        <v>376829000</v>
+      </c>
+      <c r="X48">
+        <v>384934000</v>
+      </c>
+      <c r="Y48">
+        <v>399931000</v>
+      </c>
+      <c r="Z48">
+        <v>0.02203065695999812</v>
+      </c>
+      <c r="AA48">
+        <v>0.0891385747912183</v>
+      </c>
+      <c r="AB48">
+        <v>0.0818062317176451</v>
+      </c>
+      <c r="AC48">
+        <v>0.09803441093588644</v>
+      </c>
+      <c r="AD48" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="49" spans="1:30">
+      <c r="A49" t="s">
+        <v>77</v>
+      </c>
+      <c r="B49" t="s">
+        <v>114</v>
+      </c>
+      <c r="C49" t="s">
+        <v>135</v>
+      </c>
+      <c r="D49" t="s">
+        <v>208</v>
+      </c>
+      <c r="E49">
+        <v>62.65999984741211</v>
+      </c>
+      <c r="F49">
+        <v>1580353.333333333</v>
+      </c>
+      <c r="G49">
+        <v>53.39879981994629</v>
+      </c>
+      <c r="H49">
+        <v>46.90435518900554</v>
+      </c>
+      <c r="I49">
+        <v>45.43036949157715</v>
+      </c>
+      <c r="J49">
+        <v>43.21668104171753</v>
+      </c>
+      <c r="K49">
+        <v>0.01963193342089653</v>
+      </c>
+      <c r="L49">
+        <v>63</v>
+      </c>
+      <c r="M49">
+        <v>151.1878747074209</v>
+      </c>
+      <c r="N49">
+        <v>1.08</v>
+      </c>
+      <c r="O49">
+        <v>1.08</v>
+      </c>
+      <c r="P49">
+        <v>1.24</v>
+      </c>
+      <c r="Q49">
+        <v>1.4</v>
+      </c>
+      <c r="R49">
+        <v>80700000</v>
+      </c>
+      <c r="S49">
+        <v>93493000</v>
+      </c>
+      <c r="T49">
+        <v>107305000</v>
+      </c>
+      <c r="U49">
+        <v>119507000</v>
+      </c>
+      <c r="V49">
+        <v>1049502000</v>
+      </c>
+      <c r="W49">
+        <v>1136089000</v>
+      </c>
+      <c r="X49">
+        <v>1110819000</v>
+      </c>
+      <c r="Y49">
+        <v>1346456000</v>
+      </c>
+      <c r="Z49">
+        <v>0.07689361239902354</v>
+      </c>
+      <c r="AA49">
+        <v>0.08229372874836391</v>
+      </c>
+      <c r="AB49">
+        <v>0.09659989611268803</v>
+      </c>
+      <c r="AC49">
+        <v>0.08875670649467937</v>
+      </c>
+      <c r="AD49" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="50" spans="1:30">
+      <c r="A50" t="s">
+        <v>78</v>
+      </c>
+      <c r="B50" t="s">
+        <v>113</v>
+      </c>
+      <c r="C50" t="s">
+        <v>138</v>
+      </c>
+      <c r="D50" t="s">
+        <v>209</v>
+      </c>
+      <c r="E50">
+        <v>236.0700073242188</v>
+      </c>
+      <c r="F50">
+        <v>548256.6666666666</v>
+      </c>
+      <c r="G50">
+        <v>214.2945993041992</v>
+      </c>
+      <c r="H50">
+        <v>180.6268995157878</v>
+      </c>
+      <c r="I50">
+        <v>171.4376745605469</v>
+      </c>
+      <c r="J50">
+        <v>162.7194245910645</v>
+      </c>
+      <c r="K50">
+        <v>27.38999938964844</v>
+      </c>
+      <c r="L50">
+        <v>237.8699951171875</v>
+      </c>
+      <c r="M50">
+        <v>151.1001963305359</v>
+      </c>
+      <c r="N50">
+        <v>-0.54</v>
+      </c>
+      <c r="O50">
+        <v>-0.85</v>
+      </c>
+      <c r="P50">
+        <v>-0.62</v>
+      </c>
+      <c r="Q50">
+        <v>-0.35</v>
+      </c>
+      <c r="R50">
+        <v>-22204000</v>
+      </c>
+      <c r="S50">
+        <v>-35028000</v>
+      </c>
+      <c r="T50">
+        <v>-25778000</v>
+      </c>
+      <c r="U50">
+        <v>-14609000</v>
+      </c>
+      <c r="V50">
+        <v>169151000</v>
+      </c>
+      <c r="W50">
+        <v>161705000</v>
+      </c>
+      <c r="X50">
+        <v>175843000</v>
+      </c>
+      <c r="Y50">
+        <v>191236000</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>0</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="51" spans="1:30">
+      <c r="A51" t="s">
+        <v>79</v>
+      </c>
+      <c r="B51" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51" t="s">
+        <v>147</v>
+      </c>
+      <c r="D51" t="s">
+        <v>210</v>
+      </c>
+      <c r="E51">
+        <v>16.04999923706055</v>
+      </c>
+      <c r="F51">
+        <v>952150</v>
+      </c>
+      <c r="G51">
+        <v>14.74339998245239</v>
+      </c>
+      <c r="H51">
+        <v>12.82833330154419</v>
+      </c>
+      <c r="I51">
+        <v>12.19192348957062</v>
+      </c>
+      <c r="J51">
+        <v>11.60131481170654</v>
+      </c>
+      <c r="K51">
+        <v>0.3538232743740082</v>
+      </c>
+      <c r="L51">
+        <v>16.04999923706055</v>
+      </c>
+      <c r="M51">
+        <v>150.5435216383999</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>1.0932</v>
+      </c>
+      <c r="P51">
+        <v>1.08812</v>
+      </c>
+      <c r="Q51">
+        <v>1.24</v>
+      </c>
+      <c r="R51">
+        <v>642210000</v>
+      </c>
+      <c r="S51">
+        <v>747212000</v>
+      </c>
+      <c r="T51">
+        <v>743743000</v>
+      </c>
+      <c r="U51">
+        <v>846295000</v>
+      </c>
+      <c r="V51">
+        <v>5932191000</v>
+      </c>
+      <c r="W51">
+        <v>5698369000</v>
+      </c>
+      <c r="X51">
+        <v>6154537000</v>
+      </c>
+      <c r="Y51">
+        <v>6453246000</v>
+      </c>
+      <c r="Z51">
+        <v>0.1082584832484322</v>
+      </c>
+      <c r="AA51">
+        <v>0.1311273453860219</v>
+      </c>
+      <c r="AB51">
+        <v>0.1208446711751022</v>
+      </c>
+      <c r="AC51">
+        <v>0.1311425288916616</v>
+      </c>
+      <c r="AD51" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="52" spans="1:30">
+      <c r="A52" t="s">
+        <v>80</v>
+      </c>
+      <c r="B52" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52" t="s">
+        <v>148</v>
+      </c>
+      <c r="D52" t="s">
+        <v>211</v>
+      </c>
+      <c r="E52">
+        <v>50.56000137329102</v>
+      </c>
+      <c r="F52">
+        <v>5518406.666666667</v>
+      </c>
+      <c r="G52">
+        <v>45.37985809326172</v>
+      </c>
+      <c r="H52">
+        <v>39.56877150217692</v>
+      </c>
+      <c r="I52">
+        <v>36.78701748847961</v>
+      </c>
+      <c r="J52">
+        <v>34.66047563552856</v>
+      </c>
+      <c r="K52">
+        <v>1.243355512619019</v>
+      </c>
+      <c r="L52">
+        <v>50.56000137329102</v>
+      </c>
+      <c r="M52">
+        <v>150.5412301034025</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0.27</v>
+      </c>
+      <c r="P52">
+        <v>0.03</v>
+      </c>
+      <c r="Q52">
+        <v>0.34</v>
+      </c>
+      <c r="R52">
+        <v>-15417000</v>
+      </c>
+      <c r="S52">
+        <v>118969000</v>
+      </c>
+      <c r="T52">
+        <v>13693000</v>
+      </c>
+      <c r="U52">
+        <v>148080000</v>
+      </c>
+      <c r="V52">
+        <v>523729000</v>
+      </c>
+      <c r="W52">
+        <v>686975000</v>
+      </c>
+      <c r="X52">
+        <v>481987000</v>
+      </c>
+      <c r="Y52">
+        <v>575079000</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+      <c r="AA52">
+        <v>0.1731780632482987</v>
+      </c>
+      <c r="AB52">
+        <v>0.02840947992373238</v>
+      </c>
+      <c r="AC52">
+        <v>0.2574950572008368</v>
+      </c>
+      <c r="AD52" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="53" spans="1:30">
+      <c r="A53" t="s">
+        <v>81</v>
+      </c>
+      <c r="B53" t="s">
+        <v>112</v>
+      </c>
+      <c r="C53" t="s">
+        <v>126</v>
+      </c>
+      <c r="D53" t="s">
+        <v>212</v>
+      </c>
+      <c r="E53">
+        <v>91.87000274658203</v>
+      </c>
+      <c r="F53">
+        <v>981263.3333333334</v>
+      </c>
+      <c r="G53">
+        <v>77.61839981079102</v>
+      </c>
+      <c r="H53">
+        <v>73.81619967142741</v>
+      </c>
+      <c r="I53">
+        <v>70.00019971847534</v>
+      </c>
+      <c r="J53">
+        <v>66.03244966506958</v>
+      </c>
+      <c r="K53">
+        <v>14.8100004196167</v>
+      </c>
+      <c r="L53">
+        <v>97.69999694824219</v>
+      </c>
+      <c r="M53">
+        <v>150.1337298252177</v>
+      </c>
+      <c r="N53">
+        <v>-0.66</v>
+      </c>
+      <c r="O53">
+        <v>-0.72</v>
+      </c>
+      <c r="P53">
+        <v>-0.68</v>
+      </c>
+      <c r="Q53">
+        <v>-0.63</v>
+      </c>
+      <c r="R53">
+        <v>-31460000</v>
+      </c>
+      <c r="S53">
+        <v>-34626000</v>
+      </c>
+      <c r="T53">
+        <v>-32812000</v>
+      </c>
+      <c r="U53">
+        <v>-30444000</v>
+      </c>
+      <c r="V53">
+        <v>71227000</v>
+      </c>
+      <c r="W53">
+        <v>73899000</v>
+      </c>
+      <c r="X53">
+        <v>80399000</v>
+      </c>
+      <c r="Y53">
+        <v>78048000</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+      <c r="AA53">
+        <v>0</v>
+      </c>
+      <c r="AB53">
+        <v>0</v>
+      </c>
+      <c r="AC53">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="54" spans="1:30">
+      <c r="A54" t="s">
+        <v>82</v>
+      </c>
+      <c r="B54" t="s">
+        <v>117</v>
+      </c>
+      <c r="C54" t="s">
+        <v>149</v>
+      </c>
+      <c r="D54" t="s">
+        <v>213</v>
+      </c>
+      <c r="E54">
+        <v>56.40999984741211</v>
+      </c>
+      <c r="F54">
+        <v>1077556.666666667</v>
+      </c>
+      <c r="G54">
+        <v>53.84839996337891</v>
+      </c>
+      <c r="H54">
+        <v>44.76759994506836</v>
+      </c>
+      <c r="I54">
+        <v>42.61964994430542</v>
+      </c>
+      <c r="J54">
+        <v>40.52559994697571</v>
+      </c>
+      <c r="K54">
+        <v>14.4399995803833</v>
+      </c>
+      <c r="L54">
+        <v>56.68999862670898</v>
+      </c>
+      <c r="M54">
+        <v>149.8638177500431</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0.33</v>
+      </c>
+      <c r="P54">
+        <v>0.23</v>
+      </c>
+      <c r="Q54">
+        <v>0.33</v>
+      </c>
+      <c r="R54">
+        <v>44200000</v>
+      </c>
+      <c r="S54">
+        <v>30900000</v>
+      </c>
+      <c r="T54">
+        <v>44300000</v>
+      </c>
+      <c r="U54">
+        <v>46100000</v>
+      </c>
+      <c r="V54">
+        <v>362700000</v>
+      </c>
+      <c r="W54">
+        <v>385600000</v>
+      </c>
+      <c r="X54">
+        <v>445900000</v>
+      </c>
+      <c r="Y54">
+        <v>472600000</v>
+      </c>
+      <c r="Z54">
+        <v>0.1218637992831541</v>
+      </c>
+      <c r="AA54">
+        <v>0.08013485477178424</v>
+      </c>
+      <c r="AB54">
+        <v>0.09934962996187487</v>
+      </c>
+      <c r="AC54">
+        <v>0.09754549301735083</v>
+      </c>
+      <c r="AD54" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="55" spans="1:30">
+      <c r="A55" t="s">
+        <v>83</v>
+      </c>
+      <c r="B55" t="s">
+        <v>112</v>
+      </c>
+      <c r="C55" t="s">
+        <v>122</v>
+      </c>
+      <c r="D55" t="s">
+        <v>214</v>
+      </c>
+      <c r="E55">
+        <v>141.6300048828125</v>
+      </c>
+      <c r="F55">
+        <v>424180</v>
+      </c>
+      <c r="G55">
+        <v>120.0959004211426</v>
+      </c>
+      <c r="H55">
+        <v>101.8007000223796</v>
+      </c>
+      <c r="I55">
+        <v>98.59305000305176</v>
+      </c>
+      <c r="J55">
+        <v>94.5056750869751</v>
+      </c>
+      <c r="K55">
+        <v>12.25</v>
+      </c>
+      <c r="L55">
+        <v>182.7599945068359</v>
+      </c>
+      <c r="M55">
+        <v>148.4305195509383</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>-1.98</v>
+      </c>
+      <c r="P55">
+        <v>-2.16</v>
+      </c>
+      <c r="Q55">
+        <v>-2.88</v>
+      </c>
+      <c r="R55">
+        <v>-207418000</v>
+      </c>
+      <c r="S55">
+        <v>-110914000</v>
+      </c>
+      <c r="T55">
+        <v>-121433000</v>
+      </c>
+      <c r="U55">
+        <v>-162223000</v>
+      </c>
+      <c r="V55">
+        <v>22896000</v>
+      </c>
+      <c r="W55">
+        <v>33589000</v>
+      </c>
+      <c r="X55">
+        <v>47393000</v>
+      </c>
+      <c r="Y55">
+        <v>48034000</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+      <c r="AA55">
+        <v>0</v>
+      </c>
+      <c r="AB55">
+        <v>0</v>
+      </c>
+      <c r="AC55">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30">
+      <c r="A56" t="s">
+        <v>84</v>
+      </c>
+      <c r="B56" t="s">
+        <v>115</v>
+      </c>
+      <c r="C56" t="s">
+        <v>150</v>
+      </c>
+      <c r="D56" t="s">
+        <v>215</v>
+      </c>
+      <c r="E56">
+        <v>42.06000137329102</v>
+      </c>
+      <c r="F56">
+        <v>3455056.666666667</v>
+      </c>
+      <c r="G56">
+        <v>38.92879997253418</v>
+      </c>
+      <c r="H56">
+        <v>33.56946670532226</v>
+      </c>
+      <c r="I56">
+        <v>32.00070004463196</v>
+      </c>
+      <c r="J56">
+        <v>30.16670006752014</v>
+      </c>
+      <c r="K56">
+        <v>18.89999961853027</v>
+      </c>
+      <c r="L56">
+        <v>42.22999954223633</v>
+      </c>
+      <c r="M56">
+        <v>148.1423274499962</v>
+      </c>
+      <c r="N56">
+        <v>0.31</v>
+      </c>
+      <c r="O56">
+        <v>0.5</v>
+      </c>
+      <c r="P56">
+        <v>0.66</v>
+      </c>
+      <c r="Q56">
+        <v>0.65</v>
+      </c>
+      <c r="R56">
+        <v>54000000</v>
+      </c>
+      <c r="S56">
+        <v>86000000</v>
+      </c>
+      <c r="T56">
+        <v>110000000</v>
+      </c>
+      <c r="U56">
+        <v>112000000</v>
+      </c>
+      <c r="V56">
+        <v>1374000000</v>
+      </c>
+      <c r="W56">
+        <v>1574000000</v>
+      </c>
+      <c r="X56">
+        <v>1861000000</v>
+      </c>
+      <c r="Y56">
+        <v>1827000000</v>
+      </c>
+      <c r="Z56">
+        <v>0.03930131004366812</v>
+      </c>
+      <c r="AA56">
+        <v>0.05463786531130876</v>
+      </c>
+      <c r="AB56">
+        <v>0.05910800644814616</v>
+      </c>
+      <c r="AC56">
+        <v>0.06130268199233716</v>
+      </c>
+      <c r="AD56" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30">
+      <c r="A57" t="s">
+        <v>85</v>
+      </c>
+      <c r="B57" t="s">
+        <v>114</v>
+      </c>
+      <c r="C57" t="s">
+        <v>133</v>
+      </c>
+      <c r="D57" t="s">
+        <v>216</v>
+      </c>
+      <c r="E57">
+        <v>126.9599990844727</v>
+      </c>
+      <c r="F57">
+        <v>2494853.333333333</v>
+      </c>
+      <c r="G57">
+        <v>120.3387998962402</v>
+      </c>
+      <c r="H57">
+        <v>104.4446663920085</v>
+      </c>
+      <c r="I57">
+        <v>98.48349985122681</v>
+      </c>
+      <c r="J57">
+        <v>92.27574991226196</v>
+      </c>
+      <c r="K57">
+        <v>4.621691703796387</v>
+      </c>
+      <c r="L57">
+        <v>133.7226409912109</v>
+      </c>
+      <c r="M57">
+        <v>147.7153568588353</v>
+      </c>
+      <c r="N57">
+        <v>-1.96</v>
+      </c>
+      <c r="O57">
+        <v>-0.19</v>
+      </c>
+      <c r="P57">
+        <v>1.7</v>
+      </c>
+      <c r="Q57">
+        <v>3.65</v>
+      </c>
+      <c r="R57">
+        <v>-500206000</v>
+      </c>
+      <c r="S57">
+        <v>-47910000</v>
+      </c>
+      <c r="T57">
+        <v>458761000</v>
+      </c>
+      <c r="U57">
+        <v>1009076000</v>
+      </c>
+      <c r="V57">
+        <v>2603992000</v>
+      </c>
+      <c r="W57">
+        <v>2885146000</v>
+      </c>
+      <c r="X57">
+        <v>3522982000</v>
+      </c>
+      <c r="Y57">
+        <v>4160453000</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+      <c r="AA57">
+        <v>0</v>
+      </c>
+      <c r="AB57">
+        <v>0.1302195129012865</v>
+      </c>
+      <c r="AC57">
+        <v>0.2425399349541985</v>
+      </c>
+      <c r="AD57" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30">
+      <c r="A58" t="s">
+        <v>86</v>
+      </c>
+      <c r="B58" t="s">
+        <v>113</v>
+      </c>
+      <c r="C58" t="s">
+        <v>151</v>
+      </c>
+      <c r="D58" t="s">
+        <v>217</v>
+      </c>
+      <c r="E58">
+        <v>771</v>
+      </c>
+      <c r="F58">
+        <v>1125110</v>
+      </c>
+      <c r="G58">
+        <v>709.8597961425781</v>
+      </c>
+      <c r="H58">
+        <v>619.2686661783854</v>
+      </c>
+      <c r="I58">
+        <v>590.3101499938965</v>
+      </c>
+      <c r="J58">
+        <v>561.9340501403808</v>
+      </c>
+      <c r="K58">
+        <v>23.73999977111816</v>
+      </c>
+      <c r="L58">
+        <v>787.239990234375</v>
+      </c>
+      <c r="M58">
+        <v>147.6500966579394</v>
+      </c>
+      <c r="N58">
+        <v>0.74</v>
+      </c>
+      <c r="O58">
+        <v>0.73</v>
+      </c>
+      <c r="P58">
+        <v>5.08</v>
+      </c>
+      <c r="Q58">
+        <v>1.17</v>
+      </c>
+      <c r="R58">
+        <v>150000000</v>
+      </c>
+      <c r="S58">
+        <v>1044000000</v>
+      </c>
+      <c r="T58">
+        <v>242000000</v>
+      </c>
+      <c r="U58">
+        <v>295000000</v>
+      </c>
+      <c r="V58">
+        <v>2096000000</v>
+      </c>
+      <c r="W58">
+        <v>2150000000</v>
+      </c>
+      <c r="X58">
+        <v>2288000000</v>
+      </c>
+      <c r="Y58">
+        <v>2437000000</v>
+      </c>
+      <c r="Z58">
+        <v>0.0715648854961832</v>
+      </c>
+      <c r="AA58">
+        <v>0.4855813953488372</v>
+      </c>
+      <c r="AB58">
+        <v>0.1057692307692308</v>
+      </c>
+      <c r="AC58">
+        <v>0.1210504718916701</v>
+      </c>
+      <c r="AD58" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30">
+      <c r="A59" t="s">
+        <v>87</v>
+      </c>
+      <c r="B59" t="s">
+        <v>114</v>
+      </c>
+      <c r="C59" t="s">
+        <v>135</v>
+      </c>
+      <c r="D59" t="s">
+        <v>187</v>
+      </c>
+      <c r="E59">
+        <v>106.7300033569336</v>
+      </c>
+      <c r="F59">
+        <v>1810360</v>
+      </c>
+      <c r="G59">
+        <v>99.52180007934571</v>
+      </c>
+      <c r="H59">
+        <v>85.49346659342449</v>
+      </c>
+      <c r="I59">
+        <v>81.39769994735718</v>
+      </c>
+      <c r="J59">
+        <v>76.73054988861084</v>
+      </c>
+      <c r="K59">
+        <v>0.1027423962950706</v>
+      </c>
+      <c r="L59">
+        <v>109.2399978637695</v>
+      </c>
+      <c r="M59">
+        <v>147.1635881441495</v>
+      </c>
+      <c r="N59">
+        <v>3.85</v>
+      </c>
+      <c r="O59">
+        <v>2.35</v>
+      </c>
+      <c r="P59">
+        <v>3.21</v>
+      </c>
+      <c r="Q59">
+        <v>2.9</v>
+      </c>
+      <c r="R59">
+        <v>882231000</v>
+      </c>
+      <c r="S59">
+        <v>532259000</v>
+      </c>
+      <c r="T59">
+        <v>720345000</v>
+      </c>
+      <c r="U59">
+        <v>638775000</v>
+      </c>
+      <c r="V59">
+        <v>5171378000</v>
+      </c>
+      <c r="W59">
+        <v>3575641000</v>
+      </c>
+      <c r="X59">
+        <v>4188753000</v>
+      </c>
+      <c r="Y59">
+        <v>4003533000</v>
+      </c>
+      <c r="Z59">
+        <v>0.1705988229829651</v>
+      </c>
+      <c r="AA59">
+        <v>0.1488569462090853</v>
+      </c>
+      <c r="AB59">
+        <v>0.1719712286687709</v>
+      </c>
+      <c r="AC59">
+        <v>0.1595528249673476</v>
+      </c>
+      <c r="AD59" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30">
+      <c r="A60" t="s">
+        <v>88</v>
+      </c>
+      <c r="B60" t="s">
+        <v>114</v>
+      </c>
+      <c r="C60" t="s">
+        <v>152</v>
+      </c>
+      <c r="D60" t="s">
+        <v>218</v>
+      </c>
+      <c r="E60">
+        <v>772.8499755859375</v>
+      </c>
+      <c r="F60">
+        <v>298990</v>
+      </c>
+      <c r="G60">
+        <v>700.8783959960938</v>
+      </c>
+      <c r="H60">
+        <v>595.2000630696615</v>
+      </c>
+      <c r="I60">
+        <v>567.8422471618652</v>
+      </c>
+      <c r="J60">
+        <v>539.7288478088379</v>
+      </c>
+      <c r="K60">
+        <v>0.4583329856395721</v>
+      </c>
+      <c r="L60">
+        <v>774.760009765625</v>
+      </c>
+      <c r="M60">
+        <v>147.0301028020659</v>
+      </c>
+      <c r="N60">
+        <v>10.48</v>
+      </c>
+      <c r="O60">
+        <v>3.46</v>
+      </c>
+      <c r="P60">
+        <v>2.41</v>
+      </c>
+      <c r="Q60">
+        <v>6.82</v>
+      </c>
+      <c r="R60">
+        <v>278662000</v>
+      </c>
+      <c r="S60">
+        <v>91787000</v>
+      </c>
+      <c r="T60">
+        <v>63552000</v>
+      </c>
+      <c r="U60">
+        <v>178547000</v>
+      </c>
+      <c r="V60">
+        <v>1345640000</v>
+      </c>
+      <c r="W60">
+        <v>791571000</v>
+      </c>
+      <c r="X60">
+        <v>675791000</v>
+      </c>
+      <c r="Y60">
+        <v>1091907000</v>
+      </c>
+      <c r="Z60">
+        <v>0.2070851044855979</v>
+      </c>
+      <c r="AA60">
+        <v>0.1159554859892543</v>
+      </c>
+      <c r="AB60">
+        <v>0.09404090909763521</v>
+      </c>
+      <c r="AC60">
+        <v>0.1635185047810848</v>
+      </c>
+      <c r="AD60" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="61" spans="1:30">
+      <c r="A61" t="s">
+        <v>89</v>
+      </c>
+      <c r="B61" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" t="s">
+        <v>153</v>
+      </c>
+      <c r="D61" t="s">
+        <v>219</v>
+      </c>
+      <c r="E61">
+        <v>78.36000061035156</v>
+      </c>
+      <c r="F61">
+        <v>386636.6666666667</v>
+      </c>
+      <c r="G61">
+        <v>74.9642000579834</v>
+      </c>
+      <c r="H61">
+        <v>71.8241332244873</v>
+      </c>
+      <c r="I61">
+        <v>65.24804992675782</v>
+      </c>
+      <c r="J61">
+        <v>61.27864999771118</v>
+      </c>
+      <c r="K61">
+        <v>0.4209107160568237</v>
+      </c>
+      <c r="L61">
+        <v>89.16999816894531</v>
+      </c>
+      <c r="M61">
+        <v>146.1034875981094</v>
+      </c>
+      <c r="N61">
+        <v>1.03</v>
+      </c>
+      <c r="O61">
+        <v>0.64</v>
+      </c>
+      <c r="P61">
+        <v>1.27</v>
+      </c>
+      <c r="Q61">
+        <v>1.26</v>
+      </c>
+      <c r="R61">
+        <v>31725000</v>
+      </c>
+      <c r="S61">
+        <v>19649000</v>
+      </c>
+      <c r="T61">
+        <v>39480000</v>
+      </c>
+      <c r="U61">
+        <v>39353000</v>
+      </c>
+      <c r="V61">
+        <v>291606000</v>
+      </c>
+      <c r="W61">
+        <v>403579000</v>
+      </c>
+      <c r="X61">
+        <v>522325000</v>
+      </c>
+      <c r="Y61">
+        <v>560347000</v>
+      </c>
+      <c r="Z61">
+        <v>0.1087940577354375</v>
+      </c>
+      <c r="AA61">
+        <v>0.04868687419315673</v>
+      </c>
+      <c r="AB61">
+        <v>0.07558512420427894</v>
+      </c>
+      <c r="AC61">
+        <v>0.07022969695563641</v>
+      </c>
+      <c r="AD61" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="62" spans="1:30">
+      <c r="A62" t="s">
+        <v>90</v>
+      </c>
+      <c r="B62" t="s">
+        <v>118</v>
+      </c>
+      <c r="C62" t="s">
+        <v>154</v>
+      </c>
+      <c r="D62" t="s">
+        <v>220</v>
+      </c>
+      <c r="E62">
+        <v>54.25</v>
+      </c>
+      <c r="F62">
+        <v>3033616.666666667</v>
+      </c>
+      <c r="G62">
+        <v>49.73966613769531</v>
+      </c>
+      <c r="H62">
+        <v>42.46516563415528</v>
+      </c>
+      <c r="I62">
+        <v>40.04872654914856</v>
+      </c>
+      <c r="J62">
+        <v>38.11257740020752</v>
+      </c>
+      <c r="K62">
+        <v>7.108533382415771</v>
+      </c>
+      <c r="L62">
+        <v>54.25</v>
+      </c>
+      <c r="M62">
+        <v>145.62423069729</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>-5.82</v>
+      </c>
+      <c r="P62">
+        <v>1.25</v>
+      </c>
+      <c r="Q62">
+        <v>1.41</v>
+      </c>
+      <c r="R62">
+        <v>-1095000000</v>
+      </c>
+      <c r="S62">
+        <v>-1335000000</v>
+      </c>
+      <c r="T62">
+        <v>308000000</v>
+      </c>
+      <c r="U62">
+        <v>343000000</v>
+      </c>
+      <c r="V62">
+        <v>7855000000</v>
+      </c>
+      <c r="W62">
+        <v>7722000000</v>
+      </c>
+      <c r="X62">
+        <v>6348000000</v>
+      </c>
+      <c r="Y62">
+        <v>7946000000</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+      <c r="AA62">
+        <v>0</v>
+      </c>
+      <c r="AB62">
+        <v>0.04851921865154379</v>
+      </c>
+      <c r="AC62">
+        <v>0.04316637301787063</v>
+      </c>
+      <c r="AD62" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="63" spans="1:30">
+      <c r="A63" t="s">
+        <v>91</v>
+      </c>
+      <c r="B63" t="s">
+        <v>115</v>
+      </c>
+      <c r="C63" t="s">
+        <v>155</v>
+      </c>
+      <c r="D63" t="s">
+        <v>221</v>
+      </c>
+      <c r="E63">
+        <v>87.87999725341797</v>
+      </c>
+      <c r="F63">
+        <v>1133663.333333333</v>
+      </c>
+      <c r="G63">
+        <v>85.89679992675781</v>
+      </c>
+      <c r="H63">
+        <v>76.44513343811035</v>
+      </c>
+      <c r="I63">
+        <v>69.18925012588501</v>
+      </c>
+      <c r="J63">
+        <v>63.85015008926391</v>
+      </c>
+      <c r="K63">
+        <v>0.6502050161361694</v>
+      </c>
+      <c r="L63">
+        <v>90.30999755859375</v>
+      </c>
+      <c r="M63">
+        <v>145.3600997909536</v>
+      </c>
+      <c r="N63">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="O63">
+        <v>0.13</v>
+      </c>
+      <c r="P63">
+        <v>0.28</v>
+      </c>
+      <c r="Q63">
+        <v>0.71</v>
+      </c>
+      <c r="R63">
+        <v>-94000000</v>
+      </c>
+      <c r="S63">
+        <v>14000000</v>
+      </c>
+      <c r="T63">
+        <v>33000000</v>
+      </c>
+      <c r="U63">
+        <v>84000000</v>
+      </c>
+      <c r="V63">
+        <v>-2029000000</v>
+      </c>
+      <c r="W63">
+        <v>1907000000</v>
+      </c>
+      <c r="X63">
+        <v>1917000000</v>
+      </c>
+      <c r="Y63">
+        <v>1980000000</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+      <c r="AA63">
+        <v>0.007341373885684321</v>
+      </c>
+      <c r="AB63">
+        <v>0.01721439749608764</v>
+      </c>
+      <c r="AC63">
+        <v>0.04242424242424243</v>
+      </c>
+      <c r="AD63" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="64" spans="1:30">
+      <c r="A64" t="s">
+        <v>92</v>
+      </c>
+      <c r="B64" t="s">
+        <v>112</v>
+      </c>
+      <c r="C64" t="s">
+        <v>126</v>
+      </c>
+      <c r="D64" t="s">
+        <v>222</v>
+      </c>
+      <c r="E64">
+        <v>47.40000152587891</v>
+      </c>
+      <c r="F64">
+        <v>475706.6666666667</v>
+      </c>
+      <c r="G64">
+        <v>41.89300003051758</v>
+      </c>
+      <c r="H64">
+        <v>35.75153326670329</v>
+      </c>
+      <c r="I64">
+        <v>35.00590002059936</v>
+      </c>
+      <c r="J64">
+        <v>33.58205001831055</v>
+      </c>
+      <c r="K64">
+        <v>16.88999938964844</v>
+      </c>
+      <c r="L64">
+        <v>50.65000152587891</v>
+      </c>
+      <c r="M64">
+        <v>145.2547364261373</v>
+      </c>
+      <c r="N64">
+        <v>-0.63</v>
+      </c>
+      <c r="O64">
+        <v>-0.63</v>
+      </c>
+      <c r="P64">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="Q64">
+        <v>-0.51</v>
+      </c>
+      <c r="R64">
+        <v>-28172000</v>
+      </c>
+      <c r="S64">
+        <v>-28484000</v>
+      </c>
+      <c r="T64">
+        <v>-25285000</v>
+      </c>
+      <c r="U64">
+        <v>-24622000</v>
+      </c>
+      <c r="V64">
+        <v>23777000</v>
+      </c>
+      <c r="W64">
+        <v>24404000</v>
+      </c>
+      <c r="X64">
+        <v>33104000</v>
+      </c>
+      <c r="Y64">
+        <v>35102000</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+      <c r="AA64">
+        <v>0</v>
+      </c>
+      <c r="AB64">
+        <v>0</v>
+      </c>
+      <c r="AC64">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="65" spans="1:30">
+      <c r="A65" t="s">
+        <v>93</v>
+      </c>
+      <c r="B65" t="s">
+        <v>113</v>
+      </c>
+      <c r="C65" t="s">
+        <v>138</v>
+      </c>
+      <c r="D65" t="s">
+        <v>223</v>
+      </c>
+      <c r="E65">
+        <v>108.4400024414062</v>
+      </c>
+      <c r="F65">
+        <v>1315236.666666667</v>
+      </c>
+      <c r="G65">
+        <v>103.9804000854492</v>
+      </c>
+      <c r="H65">
+        <v>85.04273325602213</v>
+      </c>
+      <c r="I65">
+        <v>82.08454994201661</v>
+      </c>
+      <c r="J65">
+        <v>79.07294998168945</v>
+      </c>
+      <c r="K65">
+        <v>20</v>
+      </c>
+      <c r="L65">
+        <v>109</v>
+      </c>
+      <c r="M65">
+        <v>145.2453109402834</v>
+      </c>
+      <c r="N65">
+        <v>0.6</v>
+      </c>
+      <c r="O65">
+        <v>0.3</v>
+      </c>
+      <c r="P65">
+        <v>0.54</v>
+      </c>
+      <c r="Q65">
+        <v>0.89</v>
+      </c>
+      <c r="R65">
+        <v>93600000</v>
+      </c>
+      <c r="S65">
+        <v>47300000</v>
+      </c>
+      <c r="T65">
+        <v>82900000</v>
+      </c>
+      <c r="U65">
+        <v>130700000</v>
+      </c>
+      <c r="V65">
+        <v>1039900000</v>
+      </c>
+      <c r="W65">
+        <v>1036000000</v>
+      </c>
+      <c r="X65">
+        <v>1048100000</v>
+      </c>
+      <c r="Y65">
+        <v>1069700000</v>
+      </c>
+      <c r="Z65">
+        <v>0.09000865467833445</v>
+      </c>
+      <c r="AA65">
+        <v>0.04565637065637065</v>
+      </c>
+      <c r="AB65">
+        <v>0.07909550615399294</v>
+      </c>
+      <c r="AC65">
+        <v>0.1221837898476208</v>
+      </c>
+      <c r="AD65" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="66" spans="1:30">
+      <c r="A66" t="s">
+        <v>94</v>
+      </c>
+      <c r="B66" t="s">
+        <v>120</v>
+      </c>
+      <c r="C66" t="s">
+        <v>156</v>
+      </c>
+      <c r="D66" t="s">
+        <v>224</v>
+      </c>
+      <c r="E66">
+        <v>60.70999908447266</v>
+      </c>
+      <c r="F66">
+        <v>506983.3333333333</v>
+      </c>
+      <c r="G66">
+        <v>53.2376001739502</v>
+      </c>
+      <c r="H66">
+        <v>46.04455383300781</v>
+      </c>
+      <c r="I66">
+        <v>43.98065837860108</v>
+      </c>
+      <c r="J66">
+        <v>42.21386005401612</v>
+      </c>
+      <c r="K66">
+        <v>6.980222225189209</v>
+      </c>
+      <c r="L66">
+        <v>73.09423828125</v>
+      </c>
+      <c r="M66">
+        <v>145.1075332777627</v>
+      </c>
+      <c r="N66">
+        <v>4.25</v>
+      </c>
+      <c r="O66">
+        <v>4.9</v>
+      </c>
+      <c r="P66">
+        <v>4.38</v>
+      </c>
+      <c r="Q66">
+        <v>2.35</v>
+      </c>
+      <c r="R66">
+        <v>146427000</v>
+      </c>
+      <c r="S66">
+        <v>169368000</v>
+      </c>
+      <c r="T66">
+        <v>151243000</v>
+      </c>
+      <c r="U66">
+        <v>81366000</v>
+      </c>
+      <c r="V66">
+        <v>367318000</v>
+      </c>
+      <c r="W66">
+        <v>394657000</v>
+      </c>
+      <c r="X66">
+        <v>370646000</v>
+      </c>
+      <c r="Y66">
+        <v>285858000</v>
+      </c>
+      <c r="Z66">
+        <v>0.3986382371677947</v>
+      </c>
+      <c r="AA66">
+        <v>0.4291524032260925</v>
+      </c>
+      <c r="AB66">
+        <v>0.4080524273835412</v>
+      </c>
+      <c r="AC66">
+        <v>0.284637827172932</v>
+      </c>
+      <c r="AD66" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="67" spans="1:30">
+      <c r="A67" t="s">
+        <v>95</v>
+      </c>
+      <c r="B67" t="s">
+        <v>115</v>
+      </c>
+      <c r="C67" t="s">
+        <v>141</v>
+      </c>
+      <c r="D67" t="s">
+        <v>225</v>
+      </c>
+      <c r="E67">
+        <v>14.64999961853027</v>
+      </c>
+      <c r="F67">
+        <v>1539256.666666667</v>
+      </c>
+      <c r="G67">
+        <v>12.52800001144409</v>
+      </c>
+      <c r="H67">
+        <v>11.28319998423258</v>
+      </c>
+      <c r="I67">
+        <v>10.79529999732971</v>
+      </c>
+      <c r="J67">
+        <v>10.35389999389648</v>
+      </c>
+      <c r="K67">
+        <v>8.189999580383301</v>
+      </c>
+      <c r="L67">
+        <v>15.76000022888184</v>
+      </c>
+      <c r="M67">
+        <v>144.9956136454011</v>
+      </c>
+      <c r="N67">
+        <v>0.22</v>
+      </c>
+      <c r="O67">
+        <v>0.18</v>
+      </c>
+      <c r="P67">
+        <v>0.25</v>
+      </c>
+      <c r="Q67">
+        <v>0.25</v>
+      </c>
+      <c r="R67">
+        <v>32713000</v>
+      </c>
+      <c r="S67">
+        <v>25982000</v>
+      </c>
+      <c r="T67">
+        <v>36987000</v>
+      </c>
+      <c r="U67">
+        <v>37000000</v>
+      </c>
+      <c r="V67">
+        <v>279728000</v>
+      </c>
+      <c r="W67">
+        <v>251904000</v>
+      </c>
+      <c r="X67">
+        <v>270611000</v>
+      </c>
+      <c r="Y67">
+        <v>280100000</v>
+      </c>
+      <c r="Z67">
+        <v>0.1169457472973746</v>
+      </c>
+      <c r="AA67">
+        <v>0.1031424669715447</v>
+      </c>
+      <c r="AB67">
+        <v>0.1366795880433538</v>
+      </c>
+      <c r="AC67">
+        <v>0.1320956801142449</v>
+      </c>
+      <c r="AD67" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="68" spans="1:30">
+      <c r="A68" t="s">
+        <v>96</v>
+      </c>
+      <c r="B68" t="s">
+        <v>115</v>
+      </c>
+      <c r="C68" t="s">
+        <v>141</v>
+      </c>
+      <c r="D68" t="s">
+        <v>198</v>
+      </c>
+      <c r="E68">
+        <v>39.9900016784668</v>
+      </c>
+      <c r="F68">
+        <v>1149150</v>
+      </c>
+      <c r="G68">
+        <v>36.35340023040771</v>
+      </c>
+      <c r="H68">
+        <v>32.19513346354167</v>
+      </c>
+      <c r="I68">
+        <v>30.64870006561279</v>
+      </c>
+      <c r="J68">
+        <v>29.21825003623962</v>
+      </c>
+      <c r="K68">
+        <v>15.22000026702881</v>
+      </c>
+      <c r="L68">
+        <v>50.79999923706055</v>
+      </c>
+      <c r="M68">
+        <v>144.9355833703768</v>
+      </c>
+      <c r="N68">
+        <v>-0.17</v>
+      </c>
+      <c r="O68">
+        <v>0.11</v>
+      </c>
+      <c r="P68">
+        <v>0.23</v>
+      </c>
+      <c r="Q68">
+        <v>0.28</v>
+      </c>
+      <c r="R68">
+        <v>-25836000</v>
+      </c>
+      <c r="S68">
+        <v>16273000</v>
+      </c>
+      <c r="T68">
+        <v>34875000</v>
+      </c>
+      <c r="U68">
+        <v>42643000</v>
+      </c>
+      <c r="V68">
+        <v>216259000</v>
+      </c>
+      <c r="W68">
+        <v>377692000</v>
+      </c>
+      <c r="X68">
+        <v>387553000</v>
+      </c>
+      <c r="Y68">
+        <v>388812000</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+      <c r="AA68">
+        <v>0.04308537114897854</v>
+      </c>
+      <c r="AB68">
+        <v>0.0899876920059966</v>
+      </c>
+      <c r="AC68">
+        <v>0.1096751129080378</v>
+      </c>
+      <c r="AD68" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="69" spans="1:30">
+      <c r="A69" t="s">
+        <v>97</v>
+      </c>
+      <c r="B69" t="s">
+        <v>112</v>
+      </c>
+      <c r="C69" t="s">
+        <v>157</v>
+      </c>
+      <c r="D69" t="s">
+        <v>226</v>
+      </c>
+      <c r="E69">
+        <v>660.4299926757812</v>
+      </c>
+      <c r="F69">
+        <v>2704496.666666667</v>
+      </c>
+      <c r="G69">
+        <v>605.2367956542969</v>
+      </c>
+      <c r="H69">
+        <v>560.3068658447265</v>
+      </c>
+      <c r="I69">
+        <v>527.2764492797852</v>
+      </c>
+      <c r="J69">
+        <v>499.0209999084473</v>
+      </c>
+      <c r="K69">
+        <v>0.5143532752990723</v>
+      </c>
+      <c r="L69">
+        <v>660.4299926757812</v>
+      </c>
+      <c r="M69">
+        <v>144.8084077193377</v>
+      </c>
+      <c r="N69">
+        <v>2.039294</v>
+      </c>
+      <c r="O69">
+        <v>1.416777</v>
+      </c>
+      <c r="P69">
+        <v>1.857396</v>
+      </c>
+      <c r="Q69">
+        <v>-0.060465</v>
+      </c>
+      <c r="R69">
+        <v>1937700000</v>
+      </c>
+      <c r="S69">
+        <v>1344900000</v>
+      </c>
+      <c r="T69">
+        <v>1763200000</v>
+      </c>
+      <c r="U69">
+        <v>-57400000</v>
+      </c>
+      <c r="V69">
+        <v>7301800000</v>
+      </c>
+      <c r="W69">
+        <v>6960000000</v>
+      </c>
+      <c r="X69">
+        <v>8312100000</v>
+      </c>
+      <c r="Y69">
+        <v>9498600000</v>
+      </c>
+      <c r="Z69">
+        <v>0.2653729217453231</v>
+      </c>
+      <c r="AA69">
+        <v>0.1932327586206896</v>
+      </c>
+      <c r="AB69">
+        <v>0.2121244932086958</v>
+      </c>
+      <c r="AC69">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="70" spans="1:30">
+      <c r="A70" t="s">
+        <v>98</v>
+      </c>
+      <c r="B70" t="s">
+        <v>121</v>
+      </c>
+      <c r="C70" t="s">
+        <v>158</v>
+      </c>
+      <c r="D70" t="s">
+        <v>227</v>
+      </c>
+      <c r="E70">
+        <v>567.510009765625</v>
+      </c>
+      <c r="F70">
+        <v>5732373.333333333</v>
+      </c>
+      <c r="G70">
+        <v>489.4021990966797</v>
+      </c>
+      <c r="H70">
+        <v>441.6635323079427</v>
+      </c>
+      <c r="I70">
+        <v>424.0709494018554</v>
+      </c>
+      <c r="J70">
+        <v>406.0175997924805</v>
+      </c>
+      <c r="K70">
+        <v>0.372857004404068</v>
+      </c>
+      <c r="L70">
+        <v>691.6900024414062</v>
+      </c>
+      <c r="M70">
+        <v>144.7415781536561</v>
+      </c>
+      <c r="N70">
+        <v>0.12</v>
+      </c>
+      <c r="O70">
+        <v>2.88</v>
+      </c>
+      <c r="P70">
+        <v>3.29</v>
+      </c>
+      <c r="Q70">
+        <v>3.73</v>
+      </c>
+      <c r="R70">
+        <v>1305120000</v>
+      </c>
+      <c r="S70">
+        <v>1487610000</v>
+      </c>
+      <c r="T70">
+        <v>1677422000</v>
+      </c>
+      <c r="U70">
+        <v>937838000</v>
+      </c>
+      <c r="V70">
+        <v>8161503000</v>
+      </c>
+      <c r="W70">
+        <v>8187301000</v>
+      </c>
+      <c r="X70">
+        <v>8541668000</v>
+      </c>
+      <c r="Y70">
+        <v>8832825000</v>
+      </c>
+      <c r="Z70">
+        <v>0.1599117221423554</v>
+      </c>
+      <c r="AA70">
+        <v>0.1816972406413298</v>
+      </c>
+      <c r="AB70">
+        <v>0.1963810815405141</v>
+      </c>
+      <c r="AC70">
+        <v>0.1061764497768268</v>
+      </c>
+      <c r="AD70" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="71" spans="1:30">
+      <c r="A71" t="s">
+        <v>99</v>
+      </c>
+      <c r="B71" t="s">
+        <v>113</v>
+      </c>
+      <c r="C71" t="s">
+        <v>151</v>
+      </c>
+      <c r="D71" t="s">
+        <v>228</v>
+      </c>
+      <c r="E71">
+        <v>94.63999938964844</v>
+      </c>
+      <c r="F71">
+        <v>290743.3333333333</v>
+      </c>
+      <c r="G71">
+        <v>77.74380004882812</v>
+      </c>
+      <c r="H71">
+        <v>72.45846674601238</v>
+      </c>
+      <c r="I71">
+        <v>70.80170011520386</v>
+      </c>
+      <c r="J71">
+        <v>68.53815013885497</v>
+      </c>
+      <c r="K71">
+        <v>7.940000057220459</v>
+      </c>
+      <c r="L71">
+        <v>94.63999938964844</v>
+      </c>
+      <c r="M71">
+        <v>143.9148912566273</v>
+      </c>
+      <c r="N71">
+        <v>-0.98</v>
+      </c>
+      <c r="O71">
+        <v>0.28</v>
+      </c>
+      <c r="P71">
+        <v>0.29</v>
+      </c>
+      <c r="Q71">
+        <v>0.38</v>
+      </c>
+      <c r="R71">
+        <v>-43493000</v>
+      </c>
+      <c r="S71">
+        <v>12629000</v>
+      </c>
+      <c r="T71">
+        <v>13017000</v>
+      </c>
+      <c r="U71">
+        <v>17140000</v>
+      </c>
+      <c r="V71">
+        <v>203478000</v>
+      </c>
+      <c r="W71">
+        <v>198150000</v>
+      </c>
+      <c r="X71">
+        <v>200997000</v>
+      </c>
+      <c r="Y71">
+        <v>216808000</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+      <c r="AA71">
+        <v>0.06373454453696695</v>
+      </c>
+      <c r="AB71">
+        <v>0.06476216062926313</v>
+      </c>
+      <c r="AC71">
+        <v>0.0790561233902808</v>
+      </c>
+      <c r="AD71" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="72" spans="1:30">
+      <c r="A72" t="s">
+        <v>100</v>
+      </c>
+      <c r="B72" t="s">
+        <v>115</v>
+      </c>
+      <c r="C72" t="s">
+        <v>137</v>
+      </c>
+      <c r="D72" t="s">
+        <v>229</v>
+      </c>
+      <c r="E72">
+        <v>137.4700012207031</v>
+      </c>
+      <c r="F72">
+        <v>619980</v>
+      </c>
+      <c r="G72">
+        <v>125.7110813903809</v>
+      </c>
+      <c r="H72">
+        <v>108.1435774739583</v>
+      </c>
+      <c r="I72">
+        <v>106.403408203125</v>
+      </c>
+      <c r="J72">
+        <v>102.8570378494263</v>
+      </c>
+      <c r="K72">
+        <v>2.263161897659302</v>
+      </c>
+      <c r="L72">
+        <v>137.4700012207031</v>
+      </c>
+      <c r="M72">
+        <v>143.9018810855246</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0.8865</v>
+      </c>
+      <c r="P72">
+        <v>6.6195</v>
+      </c>
+      <c r="Q72">
+        <v>0.0645</v>
+      </c>
+      <c r="R72">
+        <v>202100000</v>
+      </c>
+      <c r="S72">
+        <v>-151700000</v>
+      </c>
+      <c r="T72">
+        <v>1515200000</v>
+      </c>
+      <c r="U72">
+        <v>14800000</v>
+      </c>
+      <c r="V72">
+        <v>2312100000</v>
+      </c>
+      <c r="W72">
+        <v>1847000000</v>
+      </c>
+      <c r="X72">
+        <v>4925900000</v>
+      </c>
+      <c r="Y72">
+        <v>2698700000</v>
+      </c>
+      <c r="Z72">
+        <v>0.08740971411271138</v>
+      </c>
+      <c r="AA72">
+        <v>0</v>
+      </c>
+      <c r="AB72">
+        <v>0.3075986114212631</v>
+      </c>
+      <c r="AC72">
+        <v>0.00548412198465928</v>
+      </c>
+      <c r="AD72" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="73" spans="1:30">
+      <c r="A73" t="s">
+        <v>101</v>
+      </c>
+      <c r="B73" t="s">
+        <v>113</v>
+      </c>
+      <c r="C73" t="s">
+        <v>140</v>
+      </c>
+      <c r="D73" t="s">
+        <v>230</v>
+      </c>
+      <c r="E73">
+        <v>294</v>
+      </c>
+      <c r="F73">
+        <v>1214150</v>
+      </c>
+      <c r="G73">
+        <v>272.8342001342774</v>
+      </c>
+      <c r="H73">
+        <v>241.9427336629232</v>
+      </c>
+      <c r="I73">
+        <v>231.4343004608154</v>
+      </c>
+      <c r="J73">
+        <v>222.4578002929688</v>
+      </c>
+      <c r="K73">
+        <v>46.9900016784668</v>
+      </c>
+      <c r="L73">
+        <v>300.8999938964844</v>
+      </c>
+      <c r="M73">
+        <v>143.8129819925551</v>
+      </c>
+      <c r="N73">
+        <v>-0.49</v>
+      </c>
+      <c r="O73">
+        <v>0.00052</v>
+      </c>
+      <c r="P73">
+        <v>0.3</v>
+      </c>
+      <c r="Q73">
+        <v>0.43</v>
+      </c>
+      <c r="R73">
+        <v>-125697000</v>
+      </c>
+      <c r="S73">
+        <v>136000</v>
+      </c>
+      <c r="T73">
+        <v>78660000</v>
+      </c>
+      <c r="U73">
+        <v>113709000</v>
+      </c>
+      <c r="V73">
+        <v>1646260000</v>
+      </c>
+      <c r="W73">
+        <v>1684312000</v>
+      </c>
+      <c r="X73">
+        <v>1786766000</v>
+      </c>
+      <c r="Y73">
+        <v>1865675000</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+      <c r="AA73">
+        <v>8.074513510560989E-05</v>
+      </c>
+      <c r="AB73">
+        <v>0.04402367181824592</v>
+      </c>
+      <c r="AC73">
+        <v>0.06094791429375427</v>
+      </c>
+      <c r="AD73" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="74" spans="1:30">
+      <c r="A74" t="s">
+        <v>102</v>
+      </c>
+      <c r="B74" t="s">
+        <v>120</v>
+      </c>
+      <c r="C74" t="s">
+        <v>159</v>
+      </c>
+      <c r="D74" t="s">
+        <v>231</v>
+      </c>
+      <c r="E74">
+        <v>32.88999938964844</v>
+      </c>
+      <c r="F74">
+        <v>424230</v>
+      </c>
+      <c r="G74">
+        <v>30.6269998550415</v>
+      </c>
+      <c r="H74">
+        <v>28.26013323465983</v>
+      </c>
+      <c r="I74">
+        <v>26.62149994850159</v>
+      </c>
+      <c r="J74">
+        <v>25.47489999771118</v>
+      </c>
+      <c r="K74">
+        <v>1.899999976158142</v>
+      </c>
+      <c r="L74">
+        <v>33.18000030517578</v>
+      </c>
+      <c r="M74">
+        <v>143.7938493633196</v>
+      </c>
+      <c r="N74">
+        <v>0.854055</v>
+      </c>
+      <c r="O74">
+        <v>1.315</v>
+      </c>
+      <c r="P74">
+        <v>0.519</v>
+      </c>
+      <c r="Q74">
+        <v>0.821</v>
+      </c>
+      <c r="R74">
+        <v>75504000</v>
+      </c>
+      <c r="S74">
+        <v>128734000</v>
+      </c>
+      <c r="T74">
+        <v>52181000</v>
+      </c>
+      <c r="U74">
+        <v>83102000</v>
+      </c>
+      <c r="V74">
+        <v>308034000</v>
+      </c>
+      <c r="W74">
+        <v>303213000</v>
+      </c>
+      <c r="X74">
+        <v>230975000</v>
+      </c>
+      <c r="Y74">
+        <v>289686000</v>
+      </c>
+      <c r="Z74">
+        <v>0.2451157989053157</v>
+      </c>
+      <c r="AA74">
+        <v>0.4245662290205235</v>
+      </c>
+      <c r="AB74">
+        <v>0.2259162246996428</v>
+      </c>
+      <c r="AC74">
+        <v>0.2868692308223387</v>
+      </c>
+      <c r="AD74" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="75" spans="1:30">
+      <c r="A75" t="s">
+        <v>103</v>
+      </c>
+      <c r="B75" t="s">
+        <v>113</v>
+      </c>
+      <c r="C75" t="s">
+        <v>151</v>
+      </c>
+      <c r="D75" t="s">
+        <v>232</v>
+      </c>
+      <c r="E75">
+        <v>226.6799926757812</v>
+      </c>
+      <c r="F75">
+        <v>278943.3333333333</v>
+      </c>
+      <c r="G75">
+        <v>185.0336010742188</v>
+      </c>
+      <c r="H75">
+        <v>184.3930675252279</v>
+      </c>
+      <c r="I75">
+        <v>175.3681007385254</v>
+      </c>
+      <c r="J75">
+        <v>168.9734506988525</v>
+      </c>
+      <c r="K75">
+        <v>11.57999992370605</v>
+      </c>
+      <c r="L75">
+        <v>229.6900024414062</v>
+      </c>
+      <c r="M75">
+        <v>143.7512418731264</v>
+      </c>
+      <c r="N75">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="O75">
+        <v>-0.99</v>
+      </c>
+      <c r="P75">
+        <v>-0.53</v>
+      </c>
+      <c r="Q75">
+        <v>0.72</v>
+      </c>
+      <c r="R75">
+        <v>-19700000</v>
+      </c>
+      <c r="S75">
+        <v>-35110000</v>
+      </c>
+      <c r="T75">
+        <v>-18901000</v>
+      </c>
+      <c r="U75">
+        <v>26445000</v>
+      </c>
+      <c r="V75">
+        <v>124058000</v>
+      </c>
+      <c r="W75">
+        <v>136100000</v>
+      </c>
+      <c r="X75">
+        <v>147075000</v>
+      </c>
+      <c r="Y75">
+        <v>165440000</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+      <c r="AA75">
+        <v>0</v>
+      </c>
+      <c r="AB75">
+        <v>0</v>
+      </c>
+      <c r="AC75">
+        <v>0.1598464700193424</v>
+      </c>
+      <c r="AD75" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="76" spans="1:30">
+      <c r="A76" t="s">
+        <v>104</v>
+      </c>
+      <c r="B76" t="s">
+        <v>116</v>
+      </c>
+      <c r="C76" t="s">
+        <v>160</v>
+      </c>
+      <c r="D76" t="s">
+        <v>233</v>
+      </c>
+      <c r="E76">
+        <v>233.8699951171875</v>
+      </c>
+      <c r="F76">
+        <v>251783.3333333333</v>
+      </c>
+      <c r="G76">
+        <v>198.739172668457</v>
+      </c>
+      <c r="H76">
+        <v>182.9257066853841</v>
+      </c>
+      <c r="I76">
+        <v>177.4514108276367</v>
+      </c>
+      <c r="J76">
+        <v>170.6106558227539</v>
+      </c>
+      <c r="K76">
+        <v>2.10910439491272</v>
+      </c>
+      <c r="L76">
+        <v>233.8699951171875</v>
+      </c>
+      <c r="M76">
+        <v>143.3437857392456</v>
+      </c>
+      <c r="N76">
+        <v>2.79</v>
+      </c>
+      <c r="O76">
+        <v>3.4</v>
+      </c>
+      <c r="P76">
+        <v>4.26</v>
+      </c>
+      <c r="Q76">
+        <v>3.72</v>
+      </c>
+      <c r="R76">
+        <v>100356000</v>
+      </c>
+      <c r="S76">
+        <v>120849000</v>
+      </c>
+      <c r="T76">
+        <v>150553000</v>
+      </c>
+      <c r="U76">
+        <v>129138000</v>
+      </c>
+      <c r="V76">
+        <v>470127000</v>
+      </c>
+      <c r="W76">
+        <v>601521000</v>
+      </c>
+      <c r="X76">
+        <v>622236000</v>
+      </c>
+      <c r="Y76">
+        <v>558833000</v>
+      </c>
+      <c r="Z76">
+        <v>0.2134657230918454</v>
+      </c>
+      <c r="AA76">
+        <v>0.200905704040258</v>
+      </c>
+      <c r="AB76">
+        <v>0.2419548210003921</v>
+      </c>
+      <c r="AC76">
+        <v>0.2310851363466367</v>
+      </c>
+      <c r="AD76" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="77" spans="1:30">
+      <c r="A77" t="s">
+        <v>105</v>
+      </c>
+      <c r="B77" t="s">
+        <v>114</v>
+      </c>
+      <c r="C77" t="s">
+        <v>135</v>
+      </c>
+      <c r="D77" t="s">
+        <v>234</v>
+      </c>
+      <c r="E77">
+        <v>101.0299987792969</v>
+      </c>
+      <c r="F77">
+        <v>1302150</v>
+      </c>
+      <c r="G77">
+        <v>96.64032073974609</v>
+      </c>
+      <c r="H77">
+        <v>83.62788981119792</v>
+      </c>
+      <c r="I77">
+        <v>79.63902322769165</v>
+      </c>
+      <c r="J77">
+        <v>75.46564874649047</v>
+      </c>
+      <c r="K77">
+        <v>0.5171800255775452</v>
+      </c>
+      <c r="L77">
+        <v>104.9658050537109</v>
+      </c>
+      <c r="M77">
+        <v>142.9776248934738</v>
+      </c>
+      <c r="N77">
+        <v>1.7</v>
+      </c>
+      <c r="O77">
+        <v>2.85</v>
+      </c>
+      <c r="P77">
+        <v>3.73</v>
+      </c>
+      <c r="Q77">
+        <v>4.11</v>
+      </c>
+      <c r="R77">
+        <v>191530000</v>
+      </c>
+      <c r="S77">
+        <v>320216000</v>
+      </c>
+      <c r="T77">
+        <v>414789000</v>
+      </c>
+      <c r="U77">
+        <v>445536000</v>
+      </c>
+      <c r="V77">
+        <v>1780169000</v>
+      </c>
+      <c r="W77">
+        <v>2506979000</v>
+      </c>
+      <c r="X77">
+        <v>2687642000</v>
+      </c>
+      <c r="Y77">
+        <v>3020147000</v>
+      </c>
+      <c r="Z77">
+        <v>0.1075909085036308</v>
+      </c>
+      <c r="AA77">
+        <v>0.127729829408224</v>
+      </c>
+      <c r="AB77">
+        <v>0.1543319385543164</v>
+      </c>
+      <c r="AC77">
+        <v>0.1475212961488298</v>
+      </c>
+      <c r="AD77" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="78" spans="1:30">
+      <c r="A78" t="s">
+        <v>106</v>
+      </c>
+      <c r="B78" t="s">
+        <v>115</v>
+      </c>
+      <c r="C78" t="s">
+        <v>153</v>
+      </c>
+      <c r="D78" t="s">
+        <v>235</v>
+      </c>
+      <c r="E78">
+        <v>47.2400016784668</v>
+      </c>
+      <c r="F78">
+        <v>267536.6666666667</v>
+      </c>
+      <c r="G78">
+        <v>42.78700035095215</v>
+      </c>
+      <c r="H78">
+        <v>37.73460006713867</v>
+      </c>
+      <c r="I78">
+        <v>35.59125003814697</v>
+      </c>
+      <c r="J78">
+        <v>33.93449995994568</v>
+      </c>
+      <c r="K78">
+        <v>8.170000076293945</v>
+      </c>
+      <c r="L78">
+        <v>47.2400016784668</v>
+      </c>
+      <c r="M78">
+        <v>142.7480580652882</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0.04</v>
+      </c>
+      <c r="P78">
+        <v>-0.11</v>
+      </c>
+      <c r="Q78">
+        <v>0.41</v>
+      </c>
+      <c r="R78">
+        <v>1892000</v>
+      </c>
+      <c r="S78">
+        <v>-5481000</v>
+      </c>
+      <c r="T78">
+        <v>21677000</v>
+      </c>
+      <c r="U78">
+        <v>30913000</v>
+      </c>
+      <c r="V78">
+        <v>341779000</v>
+      </c>
+      <c r="W78">
+        <v>324850000</v>
+      </c>
+      <c r="X78">
+        <v>421893000</v>
+      </c>
+      <c r="Y78">
+        <v>475026000</v>
+      </c>
+      <c r="Z78">
+        <v>0.00553574093200577</v>
+      </c>
+      <c r="AA78">
+        <v>0</v>
+      </c>
+      <c r="AB78">
+        <v>0.05138032629126343</v>
+      </c>
+      <c r="AC78">
+        <v>0.06507643792129272</v>
+      </c>
+      <c r="AD78" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="79" spans="1:30">
+      <c r="A79" t="s">
+        <v>107</v>
+      </c>
+      <c r="B79" t="s">
+        <v>113</v>
+      </c>
+      <c r="C79" t="s">
+        <v>140</v>
+      </c>
+      <c r="D79" t="s">
+        <v>236</v>
+      </c>
+      <c r="E79">
+        <v>283.7999877929688</v>
+      </c>
+      <c r="F79">
+        <v>4978890</v>
+      </c>
+      <c r="G79">
+        <v>259.5511999511719</v>
+      </c>
+      <c r="H79">
+        <v>228.4071329752604</v>
+      </c>
+      <c r="I79">
+        <v>222.7881494903564</v>
+      </c>
+      <c r="J79">
+        <v>214.7438497161865</v>
+      </c>
+      <c r="K79">
+        <v>2.397500038146973</v>
+      </c>
+      <c r="L79">
+        <v>309.9599914550781</v>
+      </c>
+      <c r="M79">
+        <v>142.6384234026285</v>
+      </c>
+      <c r="N79">
+        <v>-0.1</v>
+      </c>
+      <c r="O79">
+        <v>0.2</v>
+      </c>
+      <c r="P79">
+        <v>1.28</v>
+      </c>
+      <c r="Q79">
+        <v>1.25</v>
+      </c>
+      <c r="R79">
+        <v>-98000000</v>
+      </c>
+      <c r="S79">
+        <v>199000000</v>
+      </c>
+      <c r="T79">
+        <v>1267000000</v>
+      </c>
+      <c r="U79">
+        <v>1224000000</v>
+      </c>
+      <c r="V79">
+        <v>8384000000</v>
+      </c>
+      <c r="W79">
+        <v>8247000000</v>
+      </c>
+      <c r="X79">
+        <v>8603000000</v>
+      </c>
+      <c r="Y79">
+        <v>8720000000</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+      <c r="AA79">
+        <v>0.02412998666181642</v>
+      </c>
+      <c r="AB79">
+        <v>0.1472742066720911</v>
+      </c>
+      <c r="AC79">
+        <v>0.1403669724770642</v>
+      </c>
+      <c r="AD79" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="80" spans="1:30">
+      <c r="A80" t="s">
+        <v>108</v>
+      </c>
+      <c r="B80" t="s">
+        <v>121</v>
+      </c>
+      <c r="C80" t="s">
+        <v>158</v>
+      </c>
+      <c r="D80" t="s">
+        <v>237</v>
+      </c>
+      <c r="E80">
+        <v>54.29999923706055</v>
+      </c>
+      <c r="F80">
+        <v>1104623.333333333</v>
+      </c>
+      <c r="G80">
+        <v>48.50319999694824</v>
+      </c>
+      <c r="H80">
+        <v>42.23113327026367</v>
+      </c>
+      <c r="I80">
+        <v>40.80302495002746</v>
+      </c>
+      <c r="J80">
+        <v>39.25722498893738</v>
+      </c>
+      <c r="K80">
+        <v>4.869999885559082</v>
+      </c>
+      <c r="L80">
+        <v>71.40579986572266</v>
+      </c>
+      <c r="M80">
+        <v>142.5078116625839</v>
+      </c>
+      <c r="N80">
+        <v>0.8</v>
+      </c>
+      <c r="O80">
+        <v>1.45</v>
+      </c>
+      <c r="P80">
+        <v>0.6</v>
+      </c>
+      <c r="Q80">
+        <v>-0.12</v>
+      </c>
+      <c r="R80">
+        <v>39145000</v>
+      </c>
+      <c r="S80">
+        <v>70100000</v>
+      </c>
+      <c r="T80">
+        <v>25900000</v>
+      </c>
+      <c r="U80">
+        <v>-5200000</v>
+      </c>
+      <c r="V80">
+        <v>563761000</v>
+      </c>
+      <c r="W80">
+        <v>597300000</v>
+      </c>
+      <c r="X80">
+        <v>542100000</v>
+      </c>
+      <c r="Y80">
+        <v>466900000</v>
+      </c>
+      <c r="Z80">
+        <v>0.06943545225725085</v>
+      </c>
+      <c r="AA80">
+        <v>0.1173614599028964</v>
+      </c>
+      <c r="AB80">
+        <v>0.04777716288507655</v>
+      </c>
+      <c r="AC80">
+        <v>0</v>
+      </c>
+      <c r="AD80" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="81" spans="1:30">
+      <c r="A81" t="s">
+        <v>109</v>
+      </c>
+      <c r="B81" t="s">
+        <v>112</v>
+      </c>
+      <c r="C81" t="s">
+        <v>161</v>
+      </c>
+      <c r="D81" t="s">
+        <v>238</v>
+      </c>
+      <c r="E81">
+        <v>33.47000122070312</v>
+      </c>
+      <c r="F81">
+        <v>424453.3333333333</v>
+      </c>
+      <c r="G81">
+        <v>30.05739990234375</v>
+      </c>
+      <c r="H81">
+        <v>25.20499997456869</v>
+      </c>
+      <c r="I81">
+        <v>24.55999996185303</v>
+      </c>
+      <c r="J81">
+        <v>23.64064995765686</v>
+      </c>
+      <c r="K81">
+        <v>7.590000152587891</v>
+      </c>
+      <c r="L81">
+        <v>33.88999938964844</v>
+      </c>
+      <c r="M81">
+        <v>142.0595524747498</v>
+      </c>
+      <c r="N81">
+        <v>-0.21</v>
+      </c>
+      <c r="O81">
+        <v>-0.51</v>
+      </c>
+      <c r="P81">
+        <v>0.34</v>
+      </c>
+      <c r="Q81">
+        <v>0.53</v>
+      </c>
+      <c r="R81">
+        <v>-7199000</v>
+      </c>
+      <c r="S81">
+        <v>-17426000</v>
+      </c>
+      <c r="T81">
+        <v>13007000</v>
+      </c>
+      <c r="U81">
+        <v>20634000</v>
+      </c>
+      <c r="V81">
+        <v>129620000</v>
+      </c>
+      <c r="W81">
+        <v>144767000</v>
+      </c>
+      <c r="X81">
+        <v>135546000</v>
+      </c>
+      <c r="Y81">
+        <v>136709000</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+      <c r="AA81">
+        <v>0</v>
+      </c>
+      <c r="AB81">
+        <v>0.09596004308500436</v>
+      </c>
+      <c r="AC81">
+        <v>0.1509337351600846</v>
+      </c>
+      <c r="AD81" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="82" spans="1:30">
+      <c r="A82" t="s">
+        <v>110</v>
+      </c>
+      <c r="B82" t="s">
+        <v>113</v>
+      </c>
+      <c r="C82" t="s">
+        <v>151</v>
+      </c>
+      <c r="D82" t="s">
+        <v>239</v>
+      </c>
+      <c r="E82">
+        <v>40.65999984741211</v>
+      </c>
+      <c r="F82">
+        <v>1276730</v>
+      </c>
+      <c r="G82">
+        <v>36.0173999786377</v>
+      </c>
+      <c r="H82">
+        <v>33.5516000366211</v>
+      </c>
+      <c r="I82">
+        <v>33.25224999427795</v>
+      </c>
+      <c r="J82">
+        <v>32.36470002174377</v>
+      </c>
+      <c r="K82">
+        <v>18.28000068664551</v>
+      </c>
+      <c r="L82">
+        <v>47.06000137329102</v>
+      </c>
+      <c r="M82">
+        <v>141.8695021685581</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P82">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q82">
+        <v>0.08</v>
+      </c>
+      <c r="R82">
+        <v>18068000</v>
+      </c>
+      <c r="S82">
+        <v>12175000</v>
+      </c>
+      <c r="T82">
+        <v>12839000</v>
+      </c>
+      <c r="U82">
+        <v>13347000</v>
+      </c>
+      <c r="V82">
+        <v>133636000</v>
+      </c>
+      <c r="W82">
+        <v>122594000</v>
+      </c>
+      <c r="X82">
+        <v>133744000</v>
+      </c>
+      <c r="Y82">
+        <v>143974000</v>
+      </c>
+      <c r="Z82">
+        <v>0.1352030889879972</v>
+      </c>
+      <c r="AA82">
+        <v>0.09931154868916912</v>
+      </c>
+      <c r="AB82">
+        <v>0.09599682976432587</v>
+      </c>
+      <c r="AC82">
+        <v>0.09270423826524234</v>
+      </c>
+      <c r="AD82" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="83" spans="1:30">
+      <c r="A83" t="s">
+        <v>111</v>
+      </c>
+      <c r="B83" t="s">
+        <v>115</v>
+      </c>
+      <c r="C83" t="s">
+        <v>125</v>
+      </c>
+      <c r="D83" t="s">
+        <v>240</v>
+      </c>
+      <c r="E83">
+        <v>240.1399993896484</v>
+      </c>
+      <c r="F83">
+        <v>318033.3333333333</v>
+      </c>
+      <c r="G83">
+        <v>206.4592010498047</v>
+      </c>
+      <c r="H83">
+        <v>179.6670007324219</v>
+      </c>
+      <c r="I83">
+        <v>174.5186004638672</v>
+      </c>
+      <c r="J83">
+        <v>168.7143504333496</v>
+      </c>
+      <c r="K83">
+        <v>7.155714988708496</v>
+      </c>
+      <c r="L83">
+        <v>273.5149841308594</v>
+      </c>
+      <c r="M83">
+        <v>141.3955067910537</v>
+      </c>
+      <c r="N83">
+        <v>2.29</v>
+      </c>
+      <c r="O83">
+        <v>2.57</v>
+      </c>
+      <c r="P83">
+        <v>3.28</v>
+      </c>
+      <c r="Q83">
+        <v>3.21</v>
+      </c>
+      <c r="R83">
+        <v>83200000</v>
+      </c>
+      <c r="S83">
+        <v>105000000</v>
+      </c>
+      <c r="T83">
+        <v>82900000</v>
+      </c>
+      <c r="U83">
+        <v>100600000</v>
+      </c>
+      <c r="V83">
+        <v>943600000</v>
+      </c>
+      <c r="W83">
+        <v>1000300000</v>
+      </c>
+      <c r="X83">
+        <v>1010400000</v>
+      </c>
+      <c r="Y83">
+        <v>934700000</v>
+      </c>
+      <c r="Z83">
+        <v>0.08817295464179738</v>
+      </c>
+      <c r="AA83">
+        <v>0.1049685094471658</v>
+      </c>
+      <c r="AB83">
+        <v>0.08204671417260491</v>
+      </c>
+      <c r="AC83">
+        <v>0.1076281159730395</v>
+      </c>
+      <c r="AD83" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/ScreenResult/ScreenResult.xlsx
+++ b/Screener/ScreenResult/ScreenResult.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="222">
   <si>
     <t>Symbol</t>
   </si>
@@ -55,13 +55,13 @@
     <t>RS Rating</t>
   </si>
   <si>
-    <t>eps_growth_perc_YoY</t>
+    <t>eps_growth_perc_current_YoY</t>
   </si>
   <si>
     <t>eps_growth_perc_last_qtr</t>
   </si>
   <si>
-    <t>eps_growth_perc_yester_qtr</t>
+    <t>eps_growth_perc_last_before_qtr</t>
   </si>
   <si>
     <t>rev_growth_perc_current_qtr</t>
@@ -97,16 +97,19 @@
     <t>MOD</t>
   </si>
   <si>
+    <t>CRWD</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
     <t>CAMT</t>
   </si>
   <si>
-    <t>CRWD</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>CBAY</t>
+    <t>XPO</t>
   </si>
   <si>
     <t>RYTM</t>
@@ -115,112 +118,115 @@
     <t>SKYW</t>
   </si>
   <si>
+    <t>NTNX</t>
+  </si>
+  <si>
     <t>NUVL</t>
   </si>
   <si>
-    <t>NTNX</t>
+    <t>IDYA</t>
+  </si>
+  <si>
+    <t>MRUS</t>
+  </si>
+  <si>
+    <t>CABA</t>
+  </si>
+  <si>
+    <t>GFF</t>
+  </si>
+  <si>
+    <t>MMYT</t>
+  </si>
+  <si>
+    <t>PANW</t>
   </si>
   <si>
     <t>ELF</t>
   </si>
   <si>
-    <t>IDYA</t>
-  </si>
-  <si>
-    <t>MMYT</t>
-  </si>
-  <si>
-    <t>XPO</t>
+    <t>CRNX</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>UBER</t>
   </si>
   <si>
     <t>FTAI</t>
   </si>
   <si>
-    <t>CABA</t>
-  </si>
-  <si>
-    <t>CRNX</t>
-  </si>
-  <si>
-    <t>MRUS</t>
-  </si>
-  <si>
-    <t>UBER</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
     <t>KKR</t>
   </si>
   <si>
+    <t>AZEK</t>
+  </si>
+  <si>
     <t>ANET</t>
   </si>
   <si>
+    <t>BLDR</t>
+  </si>
+  <si>
     <t>SAIA</t>
   </si>
   <si>
     <t>DECK</t>
   </si>
   <si>
+    <t>WING</t>
+  </si>
+  <si>
+    <t>INFA</t>
+  </si>
+  <si>
+    <t>ONTO</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>PGTI</t>
+  </si>
+  <si>
+    <t>GKOS</t>
+  </si>
+  <si>
+    <t>VST</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
     <t>PCVX</t>
   </si>
   <si>
-    <t>WING</t>
-  </si>
-  <si>
-    <t>URI</t>
-  </si>
-  <si>
-    <t>BLDR</t>
-  </si>
-  <si>
-    <t>INFA</t>
-  </si>
-  <si>
-    <t>GFF</t>
-  </si>
-  <si>
-    <t>WSM</t>
-  </si>
-  <si>
-    <t>GKOS</t>
+    <t>BRBR</t>
+  </si>
+  <si>
+    <t>PRCT</t>
+  </si>
+  <si>
+    <t>WOR</t>
+  </si>
+  <si>
+    <t>MDB</t>
   </si>
   <si>
     <t>DELL</t>
   </si>
   <si>
-    <t>ONTO</t>
+    <t>CYBR</t>
   </si>
   <si>
     <t>PTVE</t>
   </si>
   <si>
-    <t>PGTI</t>
-  </si>
-  <si>
-    <t>PRCT</t>
-  </si>
-  <si>
-    <t>WOR</t>
-  </si>
-  <si>
-    <t>VST</t>
-  </si>
-  <si>
-    <t>BRBR</t>
-  </si>
-  <si>
-    <t>CYBR</t>
-  </si>
-  <si>
-    <t>MDB</t>
+    <t>ROAD</t>
   </si>
   <si>
     <t>CNM</t>
@@ -232,72 +238,81 @@
     <t>STRL</t>
   </si>
   <si>
+    <t>FN</t>
+  </si>
+  <si>
     <t>NOW</t>
   </si>
   <si>
+    <t>EXP</t>
+  </si>
+  <si>
+    <t>MATX</t>
+  </si>
+  <si>
     <t>MDC</t>
   </si>
   <si>
-    <t>ROAD</t>
+    <t>FIX</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>CG</t>
+  </si>
+  <si>
+    <t>LRCX</t>
+  </si>
+  <si>
+    <t>APPF</t>
+  </si>
+  <si>
+    <t>PLAY</t>
+  </si>
+  <si>
+    <t>MRVL</t>
+  </si>
+  <si>
+    <t>CCJ</t>
+  </si>
+  <si>
+    <t>GDDY</t>
+  </si>
+  <si>
+    <t>ASND</t>
+  </si>
+  <si>
+    <t>WDAY</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>DV</t>
   </si>
   <si>
     <t>SBS</t>
   </si>
   <si>
-    <t>EXP</t>
-  </si>
-  <si>
-    <t>ASND</t>
-  </si>
-  <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>MATX</t>
-  </si>
-  <si>
-    <t>COLL</t>
-  </si>
-  <si>
-    <t>PLAY</t>
-  </si>
-  <si>
-    <t>FIX</t>
-  </si>
-  <si>
-    <t>VIST</t>
+    <t>CRH</t>
+  </si>
+  <si>
+    <t>NFLX</t>
+  </si>
+  <si>
+    <t>APO</t>
   </si>
   <si>
     <t>PHM</t>
   </si>
   <si>
-    <t>CCJ</t>
-  </si>
-  <si>
-    <t>NRG</t>
-  </si>
-  <si>
-    <t>NFLX</t>
-  </si>
-  <si>
-    <t>LRCX</t>
-  </si>
-  <si>
-    <t>WDAY</t>
-  </si>
-  <si>
-    <t>AZEK</t>
+    <t>GBX</t>
   </si>
   <si>
     <t>JBI</t>
   </si>
   <si>
-    <t>APPF</t>
-  </si>
-  <si>
-    <t>DV</t>
-  </si>
-  <si>
     <t>Technology</t>
   </si>
   <si>
@@ -346,94 +361,97 @@
     <t>Auto Parts</t>
   </si>
   <si>
+    <t>Software - Infrastructure</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
     <t>Semiconductor Equipment &amp; Materials</t>
   </si>
   <si>
-    <t>Software—Infrastructure</t>
-  </si>
-  <si>
-    <t>Semiconductors</t>
+    <t>Trucking</t>
   </si>
   <si>
     <t>Airlines</t>
   </si>
   <si>
+    <t>Conglomerates</t>
+  </si>
+  <si>
+    <t>Travel Services</t>
+  </si>
+  <si>
     <t>Household &amp; Personal Products</t>
   </si>
   <si>
-    <t>Travel Services</t>
-  </si>
-  <si>
-    <t>Trucking</t>
+    <t>Software - Application</t>
   </si>
   <si>
     <t>Rental &amp; Leasing Services</t>
   </si>
   <si>
-    <t>Software—Application</t>
-  </si>
-  <si>
     <t>Asset Management</t>
   </si>
   <si>
+    <t>Building Products &amp; Equipment</t>
+  </si>
+  <si>
     <t>Footwear &amp; Accessories</t>
   </si>
   <si>
     <t>Restaurants</t>
   </si>
   <si>
-    <t>Building Products &amp; Equipment</t>
-  </si>
-  <si>
-    <t>Conglomerates</t>
+    <t>Utilities - Independent Power Producers</t>
   </si>
   <si>
     <t>Specialty Retail</t>
   </si>
   <si>
+    <t>Packaged Foods</t>
+  </si>
+  <si>
+    <t>Metal Fabrication</t>
+  </si>
+  <si>
     <t>Packaging &amp; Containers</t>
   </si>
   <si>
-    <t>Metal Fabrication</t>
-  </si>
-  <si>
-    <t>Utilities—Independent Power Producers</t>
-  </si>
-  <si>
-    <t>Packaged Foods</t>
+    <t>Engineering &amp; Construction</t>
   </si>
   <si>
     <t>Industrial Distribution</t>
   </si>
   <si>
-    <t>Drug Manufacturers—General</t>
-  </si>
-  <si>
-    <t>Engineering &amp; Construction</t>
+    <t>Drug Manufacturers - General</t>
+  </si>
+  <si>
+    <t>Electronic Components</t>
+  </si>
+  <si>
+    <t>Building Materials</t>
+  </si>
+  <si>
+    <t>Marine Shipping</t>
   </si>
   <si>
     <t>Residential Construction</t>
   </si>
   <si>
-    <t>Utilities—Regulated Water</t>
-  </si>
-  <si>
-    <t>Building Materials</t>
-  </si>
-  <si>
-    <t>Marine Shipping</t>
-  </si>
-  <si>
-    <t>Drug Manufacturers—Specialty &amp; Generic</t>
-  </si>
-  <si>
     <t>Entertainment</t>
   </si>
   <si>
+    <t>Uranium</t>
+  </si>
+  <si>
     <t>Oil &amp; Gas E&amp;P</t>
   </si>
   <si>
-    <t>Uranium</t>
+    <t>Utilities - Regulated Water</t>
+  </si>
+  <si>
+    <t>Railroads</t>
   </si>
   <si>
     <t>2007-03-29</t>
@@ -460,16 +478,19 @@
     <t>1982-09-20</t>
   </si>
   <si>
+    <t>2019-06-12</t>
+  </si>
+  <si>
+    <t>1999-01-22</t>
+  </si>
+  <si>
+    <t>2014-02-03</t>
+  </si>
+  <si>
     <t>2000-07-28</t>
   </si>
   <si>
-    <t>2019-06-12</t>
-  </si>
-  <si>
-    <t>1999-01-22</t>
-  </si>
-  <si>
-    <t>2014-02-03</t>
+    <t>2003-10-07</t>
   </si>
   <si>
     <t>2017-10-09</t>
@@ -478,109 +499,109 @@
     <t>1986-06-26</t>
   </si>
   <si>
+    <t>2016-09-30</t>
+  </si>
+  <si>
     <t>2021-07-29</t>
   </si>
   <si>
-    <t>2016-09-30</t>
+    <t>2019-05-23</t>
+  </si>
+  <si>
+    <t>2016-05-19</t>
+  </si>
+  <si>
+    <t>2019-10-25</t>
+  </si>
+  <si>
+    <t>1973-05-03</t>
+  </si>
+  <si>
+    <t>2010-08-12</t>
+  </si>
+  <si>
+    <t>2012-07-20</t>
   </si>
   <si>
     <t>2016-09-22</t>
   </si>
   <si>
-    <t>2019-05-23</t>
-  </si>
-  <si>
-    <t>2010-08-12</t>
-  </si>
-  <si>
-    <t>2003-10-07</t>
+    <t>2018-07-18</t>
+  </si>
+  <si>
+    <t>2009-08-06</t>
+  </si>
+  <si>
+    <t>1980-03-17</t>
+  </si>
+  <si>
+    <t>2019-05-10</t>
   </si>
   <si>
     <t>2015-05-14</t>
   </si>
   <si>
-    <t>2019-10-25</t>
-  </si>
-  <si>
-    <t>2018-07-18</t>
-  </si>
-  <si>
-    <t>2016-05-19</t>
-  </si>
-  <si>
-    <t>2019-05-10</t>
-  </si>
-  <si>
-    <t>2009-08-06</t>
-  </si>
-  <si>
-    <t>1980-03-17</t>
-  </si>
-  <si>
-    <t>2012-07-20</t>
-  </si>
-  <si>
     <t>2010-07-15</t>
   </si>
   <si>
+    <t>2020-06-12</t>
+  </si>
+  <si>
     <t>2014-06-06</t>
   </si>
   <si>
+    <t>2005-06-28</t>
+  </si>
+  <si>
     <t>2002-09-11</t>
   </si>
   <si>
     <t>1993-10-15</t>
   </si>
   <si>
-    <t>2020-06-12</t>
-  </si>
-  <si>
     <t>2015-06-12</t>
   </si>
   <si>
+    <t>2021-10-27</t>
+  </si>
+  <si>
+    <t>2019-10-28</t>
+  </si>
+  <si>
     <t>1997-12-18</t>
   </si>
   <si>
-    <t>2005-06-28</t>
-  </si>
-  <si>
-    <t>2021-10-27</t>
-  </si>
-  <si>
-    <t>1973-05-03</t>
+    <t>2006-06-28</t>
+  </si>
+  <si>
+    <t>2015-06-25</t>
+  </si>
+  <si>
+    <t>2016-10-05</t>
   </si>
   <si>
     <t>1983-07-07</t>
   </si>
   <si>
-    <t>2015-06-25</t>
+    <t>2019-10-18</t>
+  </si>
+  <si>
+    <t>2021-09-15</t>
+  </si>
+  <si>
+    <t>2017-10-19</t>
   </si>
   <si>
     <t>2016-08-17</t>
   </si>
   <si>
-    <t>2019-10-28</t>
+    <t>2014-09-24</t>
   </si>
   <si>
     <t>2020-09-17</t>
   </si>
   <si>
-    <t>2006-06-28</t>
-  </si>
-  <si>
-    <t>2021-09-15</t>
-  </si>
-  <si>
-    <t>2016-10-05</t>
-  </si>
-  <si>
-    <t>2019-10-18</t>
-  </si>
-  <si>
-    <t>2014-09-24</t>
-  </si>
-  <si>
-    <t>2017-10-19</t>
+    <t>2018-05-04</t>
   </si>
   <si>
     <t>2021-07-22</t>
@@ -592,61 +613,73 @@
     <t>1991-07-12</t>
   </si>
   <si>
+    <t>2010-06-25</t>
+  </si>
+  <si>
     <t>2012-06-29</t>
   </si>
   <si>
+    <t>1994-04-12</t>
+  </si>
+  <si>
     <t>1980-03-11</t>
   </si>
   <si>
-    <t>2018-05-04</t>
+    <t>1997-06-27</t>
+  </si>
+  <si>
+    <t>2004-06-23</t>
+  </si>
+  <si>
+    <t>2012-05-03</t>
+  </si>
+  <si>
+    <t>1984-05-04</t>
+  </si>
+  <si>
+    <t>2015-06-26</t>
+  </si>
+  <si>
+    <t>2014-10-10</t>
+  </si>
+  <si>
+    <t>2000-06-30</t>
+  </si>
+  <si>
+    <t>1996-03-14</t>
+  </si>
+  <si>
+    <t>2015-03-31</t>
+  </si>
+  <si>
+    <t>2015-01-28</t>
+  </si>
+  <si>
+    <t>2012-10-12</t>
+  </si>
+  <si>
+    <t>2019-07-26</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
   </si>
   <si>
     <t>2002-05-10</t>
   </si>
   <si>
-    <t>1994-04-12</t>
-  </si>
-  <si>
-    <t>2015-01-28</t>
-  </si>
-  <si>
-    <t>2004-06-23</t>
-  </si>
-  <si>
-    <t>2015-05-07</t>
-  </si>
-  <si>
-    <t>2014-10-10</t>
-  </si>
-  <si>
-    <t>1997-06-27</t>
-  </si>
-  <si>
-    <t>2019-07-26</t>
-  </si>
-  <si>
-    <t>1996-03-14</t>
-  </si>
-  <si>
-    <t>2003-12-02</t>
+    <t>1989-07-13</t>
   </si>
   <si>
     <t>2002-05-23</t>
   </si>
   <si>
-    <t>1984-05-04</t>
-  </si>
-  <si>
-    <t>2012-10-12</t>
+    <t>2011-03-30</t>
+  </si>
+  <si>
+    <t>1994-07-14</t>
   </si>
   <si>
     <t>2019-12-20</t>
-  </si>
-  <si>
-    <t>2015-06-26</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
   </si>
 </sst>
 </file>
@@ -1004,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S76"/>
+  <dimension ref="A1:S81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -1071,58 +1104,58 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E2">
-        <v>681.5900268554688</v>
+        <v>683.5999755859375</v>
       </c>
       <c r="F2">
-        <v>7818080</v>
+        <v>8082150</v>
       </c>
       <c r="G2">
-        <v>353.4799990844726</v>
+        <v>361.4385983276367</v>
       </c>
       <c r="H2">
-        <v>302.3807994588216</v>
+        <v>305.2381326293946</v>
       </c>
       <c r="I2">
-        <v>272.9015994644165</v>
+        <v>275.7829993438721</v>
       </c>
       <c r="J2">
-        <v>238.1897996902466</v>
+        <v>239.3384497451782</v>
       </c>
       <c r="K2">
         <v>3.849999904632568</v>
       </c>
       <c r="L2">
-        <v>681.5900268554688</v>
+        <v>683.5999755859375</v>
       </c>
       <c r="M2">
-        <v>407.7163546963077</v>
+        <v>411.4682431467907</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>71.47239263803682</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>62.9737609329446</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>-2.279202279202269</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>72.900524232051</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-2.983668068586514</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>70.2538619305289</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1130,31 +1163,31 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E3">
-        <v>38.04999923706055</v>
+        <v>37.5099983215332</v>
       </c>
       <c r="F3">
-        <v>1550010</v>
+        <v>1573180</v>
       </c>
       <c r="G3">
-        <v>18.88219989776611</v>
+        <v>19.36219985961914</v>
       </c>
       <c r="H3">
-        <v>16.30946663538615</v>
+        <v>16.45233329137166</v>
       </c>
       <c r="I3">
-        <v>14.69019999027252</v>
+        <v>14.84509998083115</v>
       </c>
       <c r="J3">
-        <v>12.86770001888275</v>
+        <v>12.92650001764297</v>
       </c>
       <c r="K3">
         <v>5.409999847412109</v>
@@ -1163,16 +1196,16 @@
         <v>39.15000152587891</v>
       </c>
       <c r="M3">
-        <v>379.7799497496395</v>
+        <v>369.9886341675686</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>-18.18181818181818</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-2.173913043478263</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>-61.01694915254237</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -1189,31 +1222,31 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E4">
-        <v>20.98999977111816</v>
+        <v>20.57999992370605</v>
       </c>
       <c r="F4">
-        <v>2426893.333333333</v>
+        <v>2436303.333333333</v>
       </c>
       <c r="G4">
-        <v>14.14399997711182</v>
+        <v>14.46979997634888</v>
       </c>
       <c r="H4">
-        <v>8.649299987157185</v>
+        <v>8.741099987030029</v>
       </c>
       <c r="I4">
-        <v>8.496974985599518</v>
+        <v>8.563624985218048</v>
       </c>
       <c r="J4">
-        <v>6.701774998903274</v>
+        <v>6.797574998140335</v>
       </c>
       <c r="K4">
         <v>2.950000047683716</v>
@@ -1222,16 +1255,16 @@
         <v>26.05999946594238</v>
       </c>
       <c r="M4">
-        <v>358.6819966528938</v>
+        <v>346.8778488041254</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>-19.11764705882353</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-15.38461538461538</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>16.07142857142857</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1248,31 +1281,31 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D5" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E5">
-        <v>104.0800018310547</v>
+        <v>103.9599990844727</v>
       </c>
       <c r="F5">
-        <v>1358876.666666667</v>
+        <v>1356533.333333333</v>
       </c>
       <c r="G5">
-        <v>91.4750001525879</v>
+        <v>92.08800018310546</v>
       </c>
       <c r="H5">
-        <v>64.92673337300619</v>
+        <v>65.3790000406901</v>
       </c>
       <c r="I5">
-        <v>56.02365008354187</v>
+        <v>56.42225008010864</v>
       </c>
       <c r="J5">
-        <v>48.43485004425049</v>
+        <v>48.78180005073548</v>
       </c>
       <c r="K5">
         <v>4.195813655853271</v>
@@ -1281,25 +1314,25 @@
         <v>109.4700012207031</v>
       </c>
       <c r="M5">
-        <v>270.5180171814354</v>
+        <v>267.6839556170489</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>18200</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>66.36363636363636</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>182.0512820512821</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>12.94559761371473</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>11.88417620222155</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>-30.32303340351088</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1307,58 +1340,58 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E6">
-        <v>59.11999893188477</v>
+        <v>60.7400016784668</v>
       </c>
       <c r="F6">
-        <v>5339623.333333333</v>
+        <v>5468783.333333333</v>
       </c>
       <c r="G6">
-        <v>49.42820007324219</v>
+        <v>49.78501693725586</v>
       </c>
       <c r="H6">
-        <v>40.2941333770752</v>
+        <v>40.52234619140625</v>
       </c>
       <c r="I6">
-        <v>34.84545002937317</v>
+        <v>35.074614610672</v>
       </c>
       <c r="J6">
-        <v>30.7519000339508</v>
+        <v>30.9173008108139</v>
       </c>
       <c r="K6">
-        <v>5.564881324768066</v>
+        <v>5.557553291320801</v>
       </c>
       <c r="L6">
         <v>61.58000183105469</v>
       </c>
       <c r="M6">
-        <v>252.7092844769693</v>
+        <v>257.1521244203529</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>126.0869565217391</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>13.04347826086956</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>91.66666666666669</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>0.4901678103915575</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>14.00302412727631</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>-8.068415326967243</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1366,31 +1399,31 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E7">
-        <v>47.20999908447266</v>
+        <v>47.2599983215332</v>
       </c>
       <c r="F7">
-        <v>1046263.333333333</v>
+        <v>1008786.666666667</v>
       </c>
       <c r="G7">
-        <v>40.64739994049072</v>
+        <v>40.98379989624024</v>
       </c>
       <c r="H7">
-        <v>29.13419998168945</v>
+        <v>29.29499997456869</v>
       </c>
       <c r="I7">
-        <v>26.42689996242523</v>
+        <v>26.59149995326996</v>
       </c>
       <c r="J7">
-        <v>23.23414999008179</v>
+        <v>23.4056999874115</v>
       </c>
       <c r="K7">
         <v>6.300000190734863</v>
@@ -1399,16 +1432,16 @@
         <v>48.45000076293945</v>
       </c>
       <c r="M7">
-        <v>230.9126927076888</v>
+        <v>231.4271624157234</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>-14.28571428571428</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>13.63636363636363</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>28.15533980582525</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1425,31 +1458,31 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="E8">
-        <v>47.4900016784668</v>
+        <v>47.56000137329102</v>
       </c>
       <c r="F8">
-        <v>493066.6666666667</v>
+        <v>481043.3333333333</v>
       </c>
       <c r="G8">
-        <v>40.3888000869751</v>
+        <v>40.75260009765625</v>
       </c>
       <c r="H8">
-        <v>32.15673334757487</v>
+        <v>32.28766668955485</v>
       </c>
       <c r="I8">
-        <v>30.03297499656677</v>
+        <v>30.18202500343323</v>
       </c>
       <c r="J8">
-        <v>27.05227498054504</v>
+        <v>27.2023249912262</v>
       </c>
       <c r="K8">
         <v>8.970000267028809</v>
@@ -1458,25 +1491,25 @@
         <v>49.79999923706055</v>
       </c>
       <c r="M8">
-        <v>227.1759440294535</v>
+        <v>222.9255021378353</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>-49.18032786885246</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>-20.51282051282051</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>-7.142857142857137</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>6.674675636713119</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>18.98907884956258</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>8.708354052710094</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1484,58 +1517,58 @@
         <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E9">
-        <v>67.90000152587891</v>
+        <v>68.58999633789062</v>
       </c>
       <c r="F9">
-        <v>857686.6666666666</v>
+        <v>862606.6666666666</v>
       </c>
       <c r="G9">
-        <v>59.75080024719238</v>
+        <v>60.08680015563965</v>
       </c>
       <c r="H9">
-        <v>48.69920008341472</v>
+        <v>48.93560005187988</v>
       </c>
       <c r="I9">
-        <v>43.04150010108948</v>
+        <v>43.27820008277893</v>
       </c>
       <c r="J9">
-        <v>38.60705004692078</v>
+        <v>38.79965003967285</v>
       </c>
       <c r="K9">
-        <v>0.5703791379928589</v>
+        <v>0.7788500785827637</v>
       </c>
       <c r="L9">
         <v>71.26000213623047</v>
       </c>
       <c r="M9">
-        <v>220.5531174954706</v>
+        <v>221.525131023993</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>-12.94117647058823</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>-16.85393258426966</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>-9.524576954069298</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>-0.3052699228791774</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>0.695680310629348</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1543,58 +1576,58 @@
         <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E10">
-        <v>77.87999725341797</v>
+        <v>317.7799987792969</v>
       </c>
       <c r="F10">
-        <v>404660</v>
+        <v>3020970</v>
       </c>
       <c r="G10">
-        <v>70.03299995422363</v>
+        <v>266.0943991088867</v>
       </c>
       <c r="H10">
-        <v>58.603466796875</v>
+        <v>200.6727997843425</v>
       </c>
       <c r="I10">
-        <v>51.32535007476807</v>
+        <v>185.8485498428345</v>
       </c>
       <c r="J10">
-        <v>46.2712500667572</v>
+        <v>169.6825000762939</v>
       </c>
       <c r="K10">
-        <v>0.2220596075057983</v>
+        <v>33.0099983215332</v>
       </c>
       <c r="L10">
-        <v>81.34999847412109</v>
+        <v>317.7799987792969</v>
       </c>
       <c r="M10">
-        <v>206.5330704792872</v>
+        <v>213.9219332308575</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>10.81081081081081</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>29.82456140350878</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>7.433852815509563</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>5.637760258742673</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>8.662670015862133</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1602,58 +1635,58 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E11">
-        <v>302.1099853515625</v>
+        <v>700.989990234375</v>
       </c>
       <c r="F11">
-        <v>2947310</v>
+        <v>45059976.66666666</v>
       </c>
       <c r="G11">
-        <v>263.951999206543</v>
+        <v>534.1284185791015</v>
       </c>
       <c r="H11">
-        <v>199.5214664713542</v>
+        <v>478.3397694905599</v>
       </c>
       <c r="I11">
-        <v>184.920899848938</v>
+        <v>446.8623257446289</v>
       </c>
       <c r="J11">
-        <v>168.9863500976562</v>
+        <v>412.9763009643555</v>
       </c>
       <c r="K11">
-        <v>33.0099983215332</v>
+        <v>0.312948614358902</v>
       </c>
       <c r="L11">
-        <v>303.5700073242188</v>
+        <v>700.989990234375</v>
       </c>
       <c r="M11">
-        <v>204.8617785410724</v>
+        <v>208.3368367788274</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>593.103448275862</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>48.88888888888886</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>147.7064220183486</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>34.15266158288295</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>87.8058954393771</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>18.85638737398777</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1661,49 +1694,49 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E12">
-        <v>682.22998046875</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>44249766.66666666</v>
+        <v>1250010</v>
       </c>
       <c r="G12">
-        <v>529.6687994384765</v>
+        <v>22.56819999694824</v>
       </c>
       <c r="H12">
-        <v>476.5264001464844</v>
+        <v>16.99726668675741</v>
       </c>
       <c r="I12">
-        <v>444.7624504089355</v>
+        <v>15.09997502326965</v>
       </c>
       <c r="J12">
-        <v>411.7354006958008</v>
+        <v>13.63802501678467</v>
       </c>
       <c r="K12">
-        <v>0.3134739995002747</v>
+        <v>0.9279999732971191</v>
       </c>
       <c r="L12">
-        <v>693.3200073242188</v>
+        <v>24.5</v>
       </c>
       <c r="M12">
-        <v>203.4819157835435</v>
+        <v>203.5356009403062</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.225806451612906</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>-96.55172413793103</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -1720,58 +1753,58 @@
         <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E13">
-        <v>24.25</v>
+        <v>77.97000122070312</v>
       </c>
       <c r="F13">
-        <v>1271696.666666667</v>
+        <v>388026.6666666667</v>
       </c>
       <c r="G13">
-        <v>22.47020000457764</v>
+        <v>70.30859992980957</v>
       </c>
       <c r="H13">
-        <v>16.91100002288819</v>
+        <v>58.89840014139811</v>
       </c>
       <c r="I13">
-        <v>15.03167502403259</v>
+        <v>51.58515007972717</v>
       </c>
       <c r="J13">
-        <v>13.5605250120163</v>
+        <v>46.49075008392334</v>
       </c>
       <c r="K13">
-        <v>0.9279999732971191</v>
+        <v>0.2303776293992996</v>
       </c>
       <c r="L13">
-        <v>24.5</v>
+        <v>81.34999847412109</v>
       </c>
       <c r="M13">
-        <v>201.5034523222189</v>
+        <v>203.3955798012686</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>6.250000000000005</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>7.142857142857149</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>9.100029827272973</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.795547704155568</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>-11.82598113781564</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1779,58 +1812,58 @@
         <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="D14" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E14">
-        <v>47.63999938964844</v>
+        <v>116.5400009155273</v>
       </c>
       <c r="F14">
-        <v>763926.6666666666</v>
+        <v>1406083.333333333</v>
       </c>
       <c r="G14">
-        <v>41.95260025024414</v>
+        <v>86.89720001220704</v>
       </c>
       <c r="H14">
-        <v>29.79193336486816</v>
+        <v>77.57253346761068</v>
       </c>
       <c r="I14">
-        <v>26.77785004615784</v>
+        <v>70.44790012359618</v>
       </c>
       <c r="J14">
-        <v>24.27720004081726</v>
+        <v>64.86980006217956</v>
       </c>
       <c r="K14">
-        <v>3.119999885559082</v>
+        <v>0.6502050161361694</v>
       </c>
       <c r="L14">
-        <v>49.63999938964844</v>
+        <v>116.5400009155273</v>
       </c>
       <c r="M14">
-        <v>198.083321469365</v>
+        <v>202.5160570697104</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>-21.42857142857142</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>23.94366197183099</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.286384976525822</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>0.5243838489774515</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>-193.9871858058157</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -1838,58 +1871,58 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D15" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E15">
-        <v>59.56999969482422</v>
+        <v>47.79000091552734</v>
       </c>
       <c r="F15">
-        <v>352766.6666666667</v>
+        <v>767670</v>
       </c>
       <c r="G15">
-        <v>50.87579978942871</v>
+        <v>42.21560028076172</v>
       </c>
       <c r="H15">
-        <v>44.95099993387858</v>
+        <v>30.00380003611247</v>
       </c>
       <c r="I15">
-        <v>41.61869995117188</v>
+        <v>26.91280005455017</v>
       </c>
       <c r="J15">
-        <v>38.57254995346069</v>
+        <v>24.40380003929138</v>
       </c>
       <c r="K15">
-        <v>0.4528670310974121</v>
+        <v>3.119999885559082</v>
       </c>
       <c r="L15">
-        <v>65.85888671875</v>
+        <v>49.63999938964844</v>
       </c>
       <c r="M15">
-        <v>191.5827791466122</v>
+        <v>198.6577364790614</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>-3.797468354430383</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>-7.317073170731701</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>-10.86956521739131</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>17.08027678060455</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>67.59089720115092</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>30.47781569965871</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -1897,58 +1930,58 @@
         <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="D16" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E16">
-        <v>79.33000183105469</v>
+        <v>59.33000183105469</v>
       </c>
       <c r="F16">
-        <v>334860</v>
+        <v>364623.3333333333</v>
       </c>
       <c r="G16">
-        <v>73.10840003967286</v>
+        <v>51.13359985351563</v>
       </c>
       <c r="H16">
-        <v>56.92999997456869</v>
+        <v>45.07879994710287</v>
       </c>
       <c r="I16">
-        <v>52.81779993057251</v>
+        <v>41.79429996490479</v>
       </c>
       <c r="J16">
-        <v>47.97309993743897</v>
+        <v>38.73234994888305</v>
       </c>
       <c r="K16">
-        <v>7.400000095367432</v>
+        <v>0.4534777402877808</v>
       </c>
       <c r="L16">
-        <v>80.27999877929688</v>
+        <v>65.85888671875</v>
       </c>
       <c r="M16">
-        <v>187.0863178393401</v>
+        <v>189.1928275008968</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>-193.3333333333333</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>-23.63636363636364</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>5.585115545798692</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>4.887320747407966</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.553919661795683</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -1956,31 +1989,31 @@
         <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="E17">
-        <v>56.54000091552734</v>
+        <v>57.52000045776367</v>
       </c>
       <c r="F17">
-        <v>2484830</v>
+        <v>2446276.666666667</v>
       </c>
       <c r="G17">
-        <v>48.90520011901855</v>
+        <v>49.22940010070801</v>
       </c>
       <c r="H17">
-        <v>38.74096674601237</v>
+        <v>38.93823341369629</v>
       </c>
       <c r="I17">
-        <v>35.78332508087158</v>
+        <v>35.94677508354187</v>
       </c>
       <c r="J17">
-        <v>32.88562502861023</v>
+        <v>32.99537503242492</v>
       </c>
       <c r="K17">
         <v>12.48999977111816</v>
@@ -1989,25 +2022,25 @@
         <v>63.70999908447266</v>
       </c>
       <c r="M17">
-        <v>183.820804584267</v>
+        <v>184.701264163496</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>-270.5882352941176</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.408267740434228</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>10.17185302097057</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>-7.793296950636696</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -2015,49 +2048,49 @@
         <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E18">
-        <v>173.3200073242188</v>
+        <v>78.77999877929688</v>
       </c>
       <c r="F18">
-        <v>1510666.666666667</v>
+        <v>326160</v>
       </c>
       <c r="G18">
-        <v>144.8215997314453</v>
+        <v>73.41819999694825</v>
       </c>
       <c r="H18">
-        <v>124.7060000101725</v>
+        <v>57.18519996643067</v>
       </c>
       <c r="I18">
-        <v>118.2845999908447</v>
+        <v>53.03899991989136</v>
       </c>
       <c r="J18">
-        <v>110.7</v>
+        <v>48.19769993782043</v>
       </c>
       <c r="K18">
-        <v>7.300000190734863</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="L18">
-        <v>173.3200073242188</v>
+        <v>80.27999877929688</v>
       </c>
       <c r="M18">
-        <v>181.286022979877</v>
+        <v>181.2181988979145</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>43.90243902439025</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>15.68627450980391</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>15.90909090909091</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -2074,31 +2107,31 @@
         <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E19">
-        <v>43.18000030517578</v>
+        <v>43.5099983215332</v>
       </c>
       <c r="F19">
-        <v>1094886.666666667</v>
+        <v>1096483.333333333</v>
       </c>
       <c r="G19">
-        <v>36.6298002243042</v>
+        <v>36.86000019073487</v>
       </c>
       <c r="H19">
-        <v>29.74300009409587</v>
+        <v>29.88120007832845</v>
       </c>
       <c r="I19">
-        <v>27.87115008354187</v>
+        <v>28.01405007362366</v>
       </c>
       <c r="J19">
-        <v>25.12215007305145</v>
+        <v>25.23035006999969</v>
       </c>
       <c r="K19">
         <v>3.029999971389771</v>
@@ -2107,25 +2140,25 @@
         <v>44.52999877929688</v>
       </c>
       <c r="M19">
-        <v>181.233784960844</v>
+        <v>180.3569519124598</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>-1250</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>-7.999999999999996</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.040816326530614</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>126.8058690744921</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>-55.0253807106599</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>95.92242665340626</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -2133,58 +2166,58 @@
         <v>37</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E20">
-        <v>56.90000152587891</v>
+        <v>38.06000137329102</v>
       </c>
       <c r="F20">
-        <v>620760</v>
+        <v>491393.3333333333</v>
       </c>
       <c r="G20">
-        <v>47.35219970703125</v>
+        <v>29.5484001159668</v>
       </c>
       <c r="H20">
-        <v>40.37506657918294</v>
+        <v>25.43806664784749</v>
       </c>
       <c r="I20">
-        <v>36.81229994773864</v>
+        <v>24.72594996452332</v>
       </c>
       <c r="J20">
-        <v>34.14130000114441</v>
+        <v>23.2282999420166</v>
       </c>
       <c r="K20">
-        <v>10.89999961853027</v>
+        <v>7.619999885559082</v>
       </c>
       <c r="L20">
-        <v>58.22999954223633</v>
+        <v>38.06000137329102</v>
       </c>
       <c r="M20">
-        <v>176.9623305501541</v>
+        <v>178.6253678430774</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>-18.86792452830189</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>-34.84848484848485</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>-23.25581395348837</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>5.316914852997328</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>-22.39425142603156</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>26.56103506469154</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -2192,49 +2225,49 @@
         <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D21" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E21">
-        <v>98.05000305175781</v>
+        <v>23.59000015258789</v>
       </c>
       <c r="F21">
-        <v>1296793.333333333</v>
+        <v>820003.3333333334</v>
       </c>
       <c r="G21">
-        <v>86.34979995727539</v>
+        <v>20.38639993667602</v>
       </c>
       <c r="H21">
-        <v>77.18533345540365</v>
+        <v>16.41016667048136</v>
       </c>
       <c r="I21">
-        <v>70.08530012130737</v>
+        <v>15.21917499542236</v>
       </c>
       <c r="J21">
-        <v>64.60615005493165</v>
+        <v>13.87647500753403</v>
       </c>
       <c r="K21">
-        <v>0.6502050161361694</v>
+        <v>0.6290000081062317</v>
       </c>
       <c r="L21">
-        <v>98.05000305175781</v>
+        <v>24.23999977111816</v>
       </c>
       <c r="M21">
-        <v>172.4859751604972</v>
+        <v>176.016281847991</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>-5.128205128205133</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>-17.77777777777778</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -2251,58 +2284,58 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D22" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="E22">
-        <v>55.33000183105469</v>
+        <v>67.94000244140625</v>
       </c>
       <c r="F22">
-        <v>691106.6666666666</v>
+        <v>414946.6666666667</v>
       </c>
       <c r="G22">
-        <v>47.11150001525879</v>
+        <v>56.65679969787598</v>
       </c>
       <c r="H22">
-        <v>39.36609992980957</v>
+        <v>46.26557055155436</v>
       </c>
       <c r="I22">
-        <v>36.68934992790222</v>
+        <v>42.98544506072998</v>
       </c>
       <c r="J22">
-        <v>34.23082491874695</v>
+        <v>39.8772172832489</v>
       </c>
       <c r="K22">
-        <v>4.052896976470947</v>
+        <v>0.564629077911377</v>
       </c>
       <c r="L22">
-        <v>56.20999908447266</v>
+        <v>67.94000244140625</v>
       </c>
       <c r="M22">
-        <v>171.6794911716305</v>
+        <v>174.9485683731108</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>24.4186046511628</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>-10.08403361344537</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>-7.751937984496131</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>-6.152056538343357</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>-3.875473990975887</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>9.48591280351841</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -2310,58 +2343,58 @@
         <v>40</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="E23">
-        <v>22.64999961853027</v>
+        <v>56.2599983215332</v>
       </c>
       <c r="F23">
-        <v>810296.6666666666</v>
+        <v>630000</v>
       </c>
       <c r="G23">
-        <v>20.28799993515015</v>
+        <v>47.62799964904785</v>
       </c>
       <c r="H23">
-        <v>16.33363333384196</v>
+        <v>40.57166656494141</v>
       </c>
       <c r="I23">
-        <v>15.14417499542236</v>
+        <v>36.97784994125366</v>
       </c>
       <c r="J23">
-        <v>13.7941250038147</v>
+        <v>34.24395000457763</v>
       </c>
       <c r="K23">
-        <v>0.6290000081062317</v>
+        <v>10.89999961853027</v>
       </c>
       <c r="L23">
-        <v>24.23999977111816</v>
+        <v>58.22999954223633</v>
       </c>
       <c r="M23">
-        <v>170.6121600424204</v>
+        <v>174.6741798174269</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>-683.3333333333333</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>39.99999999999999</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>47.05882352941175</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>26.9879660916474</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>-14.25347301645394</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>32.45827245611791</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -2369,58 +2402,58 @@
         <v>41</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="E24">
-        <v>37.81999969482422</v>
+        <v>364.5</v>
       </c>
       <c r="F24">
-        <v>661296.6666666666</v>
+        <v>3002843.333333333</v>
       </c>
       <c r="G24">
-        <v>35.34420001983643</v>
+        <v>312.5229974365234</v>
       </c>
       <c r="H24">
-        <v>27.53570002873738</v>
+        <v>265.0271989949544</v>
       </c>
       <c r="I24">
-        <v>25.85932505130768</v>
+        <v>252.1508992004395</v>
       </c>
       <c r="J24">
-        <v>23.76302505970001</v>
+        <v>237.7562494659424</v>
       </c>
       <c r="K24">
-        <v>11.52000045776367</v>
+        <v>13.18666744232178</v>
       </c>
       <c r="L24">
-        <v>37.91999816894531</v>
+        <v>364.5</v>
       </c>
       <c r="M24">
-        <v>169.0998326218865</v>
+        <v>174.3361796379824</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>66.26506024096385</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>-4.166666666666671</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>30.90909090909089</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>-3.849895049403573</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>13.50456156662212</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>3.975590598755362</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -2428,58 +2461,58 @@
         <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="D25" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="E25">
-        <v>36.13999938964844</v>
+        <v>164.8200073242188</v>
       </c>
       <c r="F25">
-        <v>500313.3333333333</v>
+        <v>1613770</v>
       </c>
       <c r="G25">
-        <v>29.27000007629395</v>
+        <v>145.8303999328613</v>
       </c>
       <c r="H25">
-        <v>25.36253330230713</v>
+        <v>125.0423333740234</v>
       </c>
       <c r="I25">
-        <v>24.64564995765686</v>
+        <v>118.6253000259399</v>
       </c>
       <c r="J25">
-        <v>23.16224994659424</v>
+        <v>111.0974499511719</v>
       </c>
       <c r="K25">
-        <v>7.619999885559082</v>
+        <v>7.300000190734863</v>
       </c>
       <c r="L25">
-        <v>36.18999862670898</v>
+        <v>173.3200073242188</v>
       </c>
       <c r="M25">
-        <v>166.9664700147367</v>
+        <v>173.4581572376241</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>76.1904761904762</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>-9.756097560975606</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>-0.3845816057206514</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>15.46886425380423</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>27.85644581232044</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -2487,58 +2520,58 @@
         <v>43</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E26">
-        <v>70.47000122070312</v>
+        <v>37.77999877929688</v>
       </c>
       <c r="F26">
-        <v>21283756.66666667</v>
+        <v>646760</v>
       </c>
       <c r="G26">
-        <v>62.01179992675781</v>
+        <v>35.46</v>
       </c>
       <c r="H26">
-        <v>51.50313316345215</v>
+        <v>27.66756668726603</v>
       </c>
       <c r="I26">
-        <v>48.32139990806579</v>
+        <v>25.95897504329681</v>
       </c>
       <c r="J26">
-        <v>44.92944995880127</v>
+        <v>23.87422504901886</v>
       </c>
       <c r="K26">
-        <v>14.81999969482422</v>
+        <v>11.52000045776367</v>
       </c>
       <c r="L26">
-        <v>70.47000122070312</v>
+        <v>37.91999816894531</v>
       </c>
       <c r="M26">
-        <v>165.8416494511974</v>
+        <v>170.607252188801</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>29.48717948717948</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>7.446808510638305</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>10.58823529411764</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>-64.97975708502024</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>-63.12056737588653</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>277.8561354019746</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -2546,58 +2579,58 @@
         <v>44</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E27">
-        <v>1222.650024414062</v>
+        <v>1257.06005859375</v>
       </c>
       <c r="F27">
-        <v>2580013.333333333</v>
+        <v>2602286.666666667</v>
       </c>
       <c r="G27">
-        <v>1094.856999511719</v>
+        <v>1098.967563476562</v>
       </c>
       <c r="H27">
-        <v>948.5318017578124</v>
+        <v>946.3439302571614</v>
       </c>
       <c r="I27">
-        <v>896.0371517944336</v>
+        <v>892.937159729004</v>
       </c>
       <c r="J27">
-        <v>841.1214013671874</v>
+        <v>836.1593408203125</v>
       </c>
       <c r="K27">
-        <v>11.17089080810547</v>
+        <v>10.43821430206299</v>
       </c>
       <c r="L27">
-        <v>1253.869995117188</v>
+        <v>1257.06005859375</v>
       </c>
       <c r="M27">
-        <v>165.7422389680055</v>
+        <v>169.270335927613</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>7.066795740561475</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>4.933586337760924</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>4.720594862550699</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.637467078896141</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>-2.041503084688727</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -2605,31 +2638,31 @@
         <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E28">
-        <v>167.8800048828125</v>
+        <v>170.9400024414062</v>
       </c>
       <c r="F28">
-        <v>84399130</v>
+        <v>85010266.66666667</v>
       </c>
       <c r="G28">
-        <v>146.6925994873047</v>
+        <v>147.6651995849609</v>
       </c>
       <c r="H28">
-        <v>121.141799621582</v>
+        <v>121.5217329915365</v>
       </c>
       <c r="I28">
-        <v>117.6602498245239</v>
+        <v>118.0727998352051</v>
       </c>
       <c r="J28">
-        <v>110.4388999176025</v>
+        <v>110.6837998962402</v>
       </c>
       <c r="K28">
         <v>1.620000004768372</v>
@@ -2638,25 +2671,25 @@
         <v>180.3300018310547</v>
       </c>
       <c r="M28">
-        <v>165.4372277498547</v>
+        <v>168.9926329255467</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>11.59420289855074</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>10.00000000000001</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>20.68965517241379</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>6.344827586206897</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>8.229147228960628</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>0.1120866803661498</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -2664,58 +2697,58 @@
         <v>46</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D29" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E29">
-        <v>341.489990234375</v>
+        <v>70.65000152587891</v>
       </c>
       <c r="F29">
-        <v>2863053.333333333</v>
+        <v>22238230</v>
       </c>
       <c r="G29">
-        <v>310.5545971679687</v>
+        <v>62.31839996337891</v>
       </c>
       <c r="H29">
-        <v>264.3163990275065</v>
+        <v>51.68306650797526</v>
       </c>
       <c r="I29">
-        <v>251.2946492004395</v>
+        <v>48.52049991607666</v>
       </c>
       <c r="J29">
-        <v>237.223599395752</v>
+        <v>45.07504995346069</v>
       </c>
       <c r="K29">
-        <v>13.18666744232178</v>
+        <v>14.81999969482422</v>
       </c>
       <c r="L29">
-        <v>345.8900146484375</v>
+        <v>70.65000152587891</v>
       </c>
       <c r="M29">
-        <v>164.299472130041</v>
+        <v>168.4214225039869</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>127.5862068965518</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>-44.44444444444444</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>0.6717226435536294</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>4.612943443273263</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>2.509585221331474</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -2723,58 +2756,58 @@
         <v>47</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D30" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E30">
-        <v>93.58000183105469</v>
+        <v>53.83000183105469</v>
       </c>
       <c r="F30">
-        <v>2947776.666666667</v>
+        <v>694576.6666666666</v>
       </c>
       <c r="G30">
-        <v>81.28859970092773</v>
+        <v>47.35210006713867</v>
       </c>
       <c r="H30">
-        <v>67.60293329874675</v>
+        <v>39.31432839711507</v>
       </c>
       <c r="I30">
-        <v>63.86654996871948</v>
+        <v>36.53437245368958</v>
       </c>
       <c r="J30">
-        <v>60.50104995727539</v>
+        <v>33.98589563369751</v>
       </c>
       <c r="K30">
-        <v>5.215526580810547</v>
+        <v>3.845682621002197</v>
       </c>
       <c r="L30">
-        <v>93.58000183105469</v>
+        <v>56.20999908447266</v>
       </c>
       <c r="M30">
-        <v>160.8587239761485</v>
+        <v>167.1796227903264</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>-243.4782608695652</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>-28.26086956521739</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>109.0909090909091</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>6.105815670050483</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>-6.27668951004038</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>6.718047620957305</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -2782,58 +2815,58 @@
         <v>48</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C31" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="D31" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="E31">
-        <v>264.8900146484375</v>
+        <v>94.73000335693359</v>
       </c>
       <c r="F31">
-        <v>1661690</v>
+        <v>2991003.333333333</v>
       </c>
       <c r="G31">
-        <v>241.2002005004883</v>
+        <v>81.79919982910157</v>
       </c>
       <c r="H31">
-        <v>204.5723998006185</v>
+        <v>67.74036453247071</v>
       </c>
       <c r="I31">
-        <v>191.6204499053955</v>
+        <v>63.89904949188232</v>
       </c>
       <c r="J31">
-        <v>181.8996999359131</v>
+        <v>60.43292657852173</v>
       </c>
       <c r="K31">
-        <v>13.25</v>
+        <v>5.111276149749756</v>
       </c>
       <c r="L31">
-        <v>273.1000061035156</v>
+        <v>94.73000335693359</v>
       </c>
       <c r="M31">
-        <v>157.7514253662565</v>
+        <v>162.4466252169987</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>-4.347826086956525</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>20.54794520547946</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>-9.876543209876552</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>-8.741280188253137</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>14.6820349405688</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>23.67968458038633</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -2841,58 +2874,58 @@
         <v>49</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C32" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D32" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E32">
-        <v>530.760009765625</v>
+        <v>45.34999847412109</v>
       </c>
       <c r="F32">
-        <v>266536.6666666667</v>
+        <v>1424510</v>
       </c>
       <c r="G32">
-        <v>435.7398010253906</v>
+        <v>37.15300022125244</v>
       </c>
       <c r="H32">
-        <v>412.4156673177083</v>
+        <v>32.49960010528564</v>
       </c>
       <c r="I32">
-        <v>383.4367004394531</v>
+        <v>30.94855005264282</v>
       </c>
       <c r="J32">
-        <v>364.1527003479004</v>
+        <v>29.502350025177</v>
       </c>
       <c r="K32">
-        <v>4.533332824707031</v>
+        <v>15.22000026702881</v>
       </c>
       <c r="L32">
-        <v>534.510009765625</v>
+        <v>50.79999923706055</v>
       </c>
       <c r="M32">
-        <v>156.5049878114011</v>
+        <v>160.9919069898439</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>-211.1111111111111</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>-72.22222222222223</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>0.3248587935069526</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.610857524120183</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>74.64799152867626</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -2900,58 +2933,58 @@
         <v>50</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D33" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="E33">
-        <v>825.3499755859375</v>
+        <v>267.0499877929688</v>
       </c>
       <c r="F33">
-        <v>341310</v>
+        <v>1706196.666666667</v>
       </c>
       <c r="G33">
-        <v>714.1319958496093</v>
+        <v>242.1734002685547</v>
       </c>
       <c r="H33">
-        <v>601.7715962727865</v>
+        <v>205.2881997680664</v>
       </c>
       <c r="I33">
-        <v>573.4475968933106</v>
+        <v>192.1763498687744</v>
       </c>
       <c r="J33">
-        <v>543.3316973876953</v>
+        <v>182.278749923706</v>
       </c>
       <c r="K33">
-        <v>0.4583329856395721</v>
+        <v>13.25</v>
       </c>
       <c r="L33">
-        <v>882.0599975585938</v>
+        <v>273.1000061035156</v>
       </c>
       <c r="M33">
-        <v>155.4590990658935</v>
+        <v>159.2932706766657</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>15.82278481012658</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>10.4895104895105</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.463648551946503</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>7.960404069705058</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>5.942446877900704</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -2959,58 +2992,58 @@
         <v>51</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="D34" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E34">
-        <v>74.83000183105469</v>
+        <v>180.9100036621094</v>
       </c>
       <c r="F34">
-        <v>1003303.333333333</v>
+        <v>1174446.666666667</v>
       </c>
       <c r="G34">
-        <v>61.13959991455078</v>
+        <v>161.8026000976562</v>
       </c>
       <c r="H34">
-        <v>53.04283322652181</v>
+        <v>141.3824664815267</v>
       </c>
       <c r="I34">
-        <v>52.19272493362427</v>
+        <v>135.4508497619629</v>
       </c>
       <c r="J34">
-        <v>49.44872493743897</v>
+        <v>127.2408498001099</v>
       </c>
       <c r="K34">
-        <v>16.45000076293945</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="L34">
-        <v>75.52999877929688</v>
+        <v>180.9100036621094</v>
       </c>
       <c r="M34">
-        <v>155.2101952222008</v>
+        <v>158.0246130163858</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>-18.46153846153846</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>8.997429305912599</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>31.41891891891893</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>0.1186604223109857</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>16.62435744315293</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>-10.88339473995224</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -3018,58 +3051,58 @@
         <v>52</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D35" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E35">
-        <v>286.4800109863281</v>
+        <v>536.02001953125</v>
       </c>
       <c r="F35">
-        <v>322393.3333333333</v>
+        <v>275203.3333333333</v>
       </c>
       <c r="G35">
-        <v>259.2460006713867</v>
+        <v>437.9780017089844</v>
       </c>
       <c r="H35">
-        <v>207.0397004191081</v>
+        <v>413.7476007080078</v>
       </c>
       <c r="I35">
-        <v>204.9595755004883</v>
+        <v>384.7169004821777</v>
       </c>
       <c r="J35">
-        <v>195.6249753570557</v>
+        <v>364.9562504577636</v>
       </c>
       <c r="K35">
-        <v>15.35618686676025</v>
+        <v>4.533332824707031</v>
       </c>
       <c r="L35">
-        <v>287.7699890136719</v>
+        <v>536.02001953125</v>
       </c>
       <c r="M35">
-        <v>155.1354830424837</v>
+        <v>157.5819790571595</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>25.66037735849057</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>-9.264305177111714</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>7.309941520467836</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>11.59220410525437</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>5.160513825913843</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>0.7333855909327981</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -3077,58 +3110,58 @@
         <v>53</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C36" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D36" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="E36">
-        <v>654.5399780273438</v>
+        <v>833.3300170898438</v>
       </c>
       <c r="F36">
-        <v>663483.3333333334</v>
+        <v>346916.6666666667</v>
       </c>
       <c r="G36">
-        <v>556.9001989746093</v>
+        <v>718.0571960449219</v>
       </c>
       <c r="H36">
-        <v>485.6531331380208</v>
+        <v>603.7631962076823</v>
       </c>
       <c r="I36">
-        <v>457.1502499389649</v>
+        <v>575.1808470153809</v>
       </c>
       <c r="J36">
-        <v>434.7596994018555</v>
+        <v>544.6050973510742</v>
       </c>
       <c r="K36">
-        <v>3.029999971389771</v>
+        <v>0.4583329856395721</v>
       </c>
       <c r="L36">
-        <v>654.5399780273438</v>
+        <v>882.0599975585938</v>
       </c>
       <c r="M36">
-        <v>154.9596976669849</v>
+        <v>156.8680274775821</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>44.17938931297709</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>121.5542521994135</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>182.9875518672199</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>42.89742624600813</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>61.57465843729793</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>-14.62660961556196</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -3136,58 +3169,58 @@
         <v>54</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D37" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E37">
-        <v>177.9499969482422</v>
+        <v>292.7900085449219</v>
       </c>
       <c r="F37">
-        <v>1180073.333333333</v>
+        <v>326523.3333333333</v>
       </c>
       <c r="G37">
-        <v>160.8786001586914</v>
+        <v>260.3884008789062</v>
       </c>
       <c r="H37">
-        <v>141.086199798584</v>
+        <v>207.5711375935873</v>
       </c>
       <c r="I37">
-        <v>135.0156497573853</v>
+        <v>205.2209208679199</v>
       </c>
       <c r="J37">
-        <v>126.8356497573853</v>
+        <v>195.662799987793</v>
       </c>
       <c r="K37">
-        <v>0.8299999833106995</v>
+        <v>14.6816463470459</v>
       </c>
       <c r="L37">
-        <v>180.75</v>
+        <v>292.7900085449219</v>
       </c>
       <c r="M37">
-        <v>154.8003579312085</v>
+        <v>156.5528982495269</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>53.33333333333332</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>-3.38983050847458</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>9.266326406837543</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>-1.423827963318954</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>3.675131356861548</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -3195,31 +3228,31 @@
         <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C38" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D38" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E38">
-        <v>30.03000068664551</v>
+        <v>30.20000076293945</v>
       </c>
       <c r="F38">
-        <v>764586.6666666666</v>
+        <v>768456.6666666666</v>
       </c>
       <c r="G38">
-        <v>28.29720008850098</v>
+        <v>28.40800010681152</v>
       </c>
       <c r="H38">
-        <v>23.20720003763835</v>
+        <v>23.28713338216146</v>
       </c>
       <c r="I38">
-        <v>21.5752500295639</v>
+        <v>21.64775003433228</v>
       </c>
       <c r="J38">
-        <v>20.20055001735687</v>
+        <v>20.2584500169754</v>
       </c>
       <c r="K38">
         <v>14.09000015258789</v>
@@ -3228,25 +3261,25 @@
         <v>38.83000183105469</v>
       </c>
       <c r="M38">
-        <v>154.4799850404722</v>
+        <v>156.050235804983</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>50.00000000000001</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>58.82352941176471</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>13.33333333333335</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>8.66384033532985</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.888917470055906</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>-8.362986200445858</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -3254,58 +3287,58 @@
         <v>56</v>
       </c>
       <c r="B39" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C39" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D39" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E39">
-        <v>60.20999908447266</v>
+        <v>158.5200042724609</v>
       </c>
       <c r="F39">
-        <v>400243.3333333333</v>
+        <v>377733.3333333333</v>
       </c>
       <c r="G39">
-        <v>56.23759963989258</v>
+        <v>150.3923986816406</v>
       </c>
       <c r="H39">
-        <v>46.19473320007324</v>
+        <v>131.6141994730631</v>
       </c>
       <c r="I39">
-        <v>43.03119989395142</v>
+        <v>123.6439496231079</v>
       </c>
       <c r="J39">
-        <v>40.19729990959168</v>
+        <v>116.1587998199463</v>
       </c>
       <c r="K39">
-        <v>0.6593880653381348</v>
+        <v>20.81999969482422</v>
       </c>
       <c r="L39">
-        <v>61.68999862670898</v>
+        <v>167.75</v>
       </c>
       <c r="M39">
-        <v>154.4598167148422</v>
+        <v>154.7061182974564</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>-28.8888888888889</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>21.51898734177214</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>-14.1304347826087</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>8.666121198770599</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>-4.269324429493135</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>-21.36257748647688</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -3313,58 +3346,58 @@
         <v>57</v>
       </c>
       <c r="B40" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C40" t="s">
         <v>124</v>
       </c>
       <c r="D40" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E40">
-        <v>204.6900024414062</v>
+        <v>652.72998046875</v>
       </c>
       <c r="F40">
-        <v>680580</v>
+        <v>664780</v>
       </c>
       <c r="G40">
-        <v>199.4498007202149</v>
+        <v>560.6085986328125</v>
       </c>
       <c r="H40">
-        <v>163.4250004577637</v>
+        <v>485.9709497070313</v>
       </c>
       <c r="I40">
-        <v>152.3960004043579</v>
+        <v>457.0511981201172</v>
       </c>
       <c r="J40">
-        <v>143.9802003860474</v>
+        <v>433.687504119873</v>
       </c>
       <c r="K40">
-        <v>0.1974910944700241</v>
+        <v>2.987745523452759</v>
       </c>
       <c r="L40">
-        <v>220.5660552978516</v>
+        <v>654.5399780273438</v>
       </c>
       <c r="M40">
-        <v>153.9544454479188</v>
+        <v>154.3187756622949</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>-4.006820119352094</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>-4.006820119352094</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>-0.9827357237715804</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>5.936972425436128</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>8.188736681887367</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -3372,58 +3405,58 @@
         <v>58</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C41" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="D41" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E41">
-        <v>93.30999755859375</v>
+        <v>41.31000137329102</v>
       </c>
       <c r="F41">
-        <v>914760</v>
+        <v>1123990</v>
       </c>
       <c r="G41">
-        <v>79.34859992980957</v>
+        <v>38.78099998474121</v>
       </c>
       <c r="H41">
-        <v>74.24699968973796</v>
+        <v>32.00346678415934</v>
       </c>
       <c r="I41">
-        <v>70.64569971084595</v>
+        <v>30.67495008468628</v>
       </c>
       <c r="J41">
-        <v>66.49244968414307</v>
+        <v>29.02605008125305</v>
       </c>
       <c r="K41">
-        <v>14.8100004196167</v>
+        <v>0.8100000023841858</v>
       </c>
       <c r="L41">
-        <v>97.69999694824219</v>
+        <v>41.72999954223633</v>
       </c>
       <c r="M41">
-        <v>153.8589642083325</v>
+        <v>153.8025706256185</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>13.79310344827588</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>3.571428571428555</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.895992559763492</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.150842955292719</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>10.52843072266186</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -3431,58 +3464,58 @@
         <v>59</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C42" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D42" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E42">
-        <v>82.68000030517578</v>
+        <v>94.30000305175781</v>
       </c>
       <c r="F42">
-        <v>3712146.666666667</v>
+        <v>895843.3333333334</v>
       </c>
       <c r="G42">
-        <v>76.84139999389649</v>
+        <v>79.97220001220703</v>
       </c>
       <c r="H42">
-        <v>67.8224001566569</v>
+        <v>74.41119972229004</v>
       </c>
       <c r="I42">
-        <v>62.65575008392334</v>
+        <v>70.86934972763062</v>
       </c>
       <c r="J42">
-        <v>58.562200050354</v>
+        <v>66.68414970397949</v>
       </c>
       <c r="K42">
-        <v>11.99751472473145</v>
+        <v>14.8100004196167</v>
       </c>
       <c r="L42">
-        <v>86.31999969482422</v>
+        <v>97.69999694824219</v>
       </c>
       <c r="M42">
-        <v>153.5591556202522</v>
+        <v>153.719325224501</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>-9.090909090909099</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>-6.77966101694914</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>-2.924165723454272</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>8.795788846939741</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>3.751386412455951</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -3490,58 +3523,58 @@
         <v>60</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="C43" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="D43" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E43">
-        <v>155.7700042724609</v>
+        <v>43.7599983215332</v>
       </c>
       <c r="F43">
-        <v>365063.3333333333</v>
+        <v>2986666.666666667</v>
       </c>
       <c r="G43">
-        <v>149.9737985229492</v>
+        <v>38.75550498962402</v>
       </c>
       <c r="H43">
-        <v>131.2894660949707</v>
+        <v>33.65345249176026</v>
       </c>
       <c r="I43">
-        <v>123.264899597168</v>
+        <v>31.27708727836609</v>
       </c>
       <c r="J43">
-        <v>115.872449798584</v>
+        <v>29.54466805458069</v>
       </c>
       <c r="K43">
-        <v>20.81999969482422</v>
+        <v>10.13121700286865</v>
       </c>
       <c r="L43">
-        <v>167.75</v>
+        <v>44.54999923706055</v>
       </c>
       <c r="M43">
-        <v>152.7840169006321</v>
+        <v>153.1882174078707</v>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>-262.5</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>-260.2739726027397</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>-148.3443708609271</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>28.12793979303857</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>-27.93220338983051</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>14.37063840785733</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -3549,58 +3582,58 @@
         <v>61</v>
       </c>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C44" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D44" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E44">
-        <v>14.42000007629395</v>
+        <v>205.5200042724609</v>
       </c>
       <c r="F44">
-        <v>548010</v>
+        <v>682190</v>
       </c>
       <c r="G44">
-        <v>13.5014999961853</v>
+        <v>199.2775250244141</v>
       </c>
       <c r="H44">
-        <v>10.21423332214355</v>
+        <v>162.864963684082</v>
       </c>
       <c r="I44">
-        <v>9.539474990367889</v>
+        <v>151.5057127380371</v>
       </c>
       <c r="J44">
-        <v>8.892824983596801</v>
+        <v>142.8124697113037</v>
       </c>
       <c r="K44">
-        <v>6.869999885559082</v>
+        <v>0.1881471872329712</v>
       </c>
       <c r="L44">
-        <v>18.59381103515625</v>
+        <v>210.5899963378906</v>
       </c>
       <c r="M44">
-        <v>152.5000038296527</v>
+        <v>153.0892743973388</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>-1.612903225806453</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>17.30769230769231</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>32.76595744680851</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>-0.4812591336691338</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>6.104585089529699</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>-28.43887212764041</v>
       </c>
     </row>
     <row r="45" spans="1:19">
@@ -3608,49 +3641,49 @@
         <v>62</v>
       </c>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C45" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="D45" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="E45">
-        <v>41.29999923706055</v>
+        <v>73.45999908447266</v>
       </c>
       <c r="F45">
-        <v>1138226.666666667</v>
+        <v>1004136.666666667</v>
       </c>
       <c r="G45">
-        <v>38.62559997558593</v>
+        <v>61.62219985961914</v>
       </c>
       <c r="H45">
-        <v>31.91533344268799</v>
+        <v>53.20956654866536</v>
       </c>
       <c r="I45">
-        <v>30.5995000743866</v>
+        <v>52.33442493438721</v>
       </c>
       <c r="J45">
-        <v>28.93000008583069</v>
+        <v>49.56282493591308</v>
       </c>
       <c r="K45">
-        <v>0.8100000023841858</v>
+        <v>16.45000076293945</v>
       </c>
       <c r="L45">
-        <v>41.72999954223633</v>
+        <v>75.52999877929688</v>
       </c>
       <c r="M45">
-        <v>152.4065744640128</v>
+        <v>153.0201644598322</v>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>-2.150537634408604</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>30.00000000000001</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -3667,58 +3700,58 @@
         <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C46" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="D46" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E46">
-        <v>49.47999954223633</v>
+        <v>58.65000152587891</v>
       </c>
       <c r="F46">
-        <v>444053.3333333333</v>
+        <v>1196646.666666667</v>
       </c>
       <c r="G46">
-        <v>42.77620002746582</v>
+        <v>54.55220001220703</v>
       </c>
       <c r="H46">
-        <v>36.01973328908284</v>
+        <v>45.3271332804362</v>
       </c>
       <c r="I46">
-        <v>35.19930002212524</v>
+        <v>43.06004995346069</v>
       </c>
       <c r="J46">
-        <v>33.72560001373291</v>
+        <v>40.95104995727539</v>
       </c>
       <c r="K46">
-        <v>16.88999938964844</v>
+        <v>14.4399995803833</v>
       </c>
       <c r="L46">
-        <v>50.65000152587891</v>
+        <v>58.65000152587891</v>
       </c>
       <c r="M46">
-        <v>151.4494213981275</v>
+        <v>152.7325189487613</v>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>26.47058823529411</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>4.878048780487809</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>-8.929327126534067</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>5.987889661359049</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>15.63796680497925</v>
       </c>
     </row>
     <row r="47" spans="1:19">
@@ -3726,58 +3759,58 @@
         <v>64</v>
       </c>
       <c r="B47" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C47" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="D47" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="E47">
-        <v>57.13000106811523</v>
+        <v>49.90000152587891</v>
       </c>
       <c r="F47">
-        <v>274756.6666666667</v>
+        <v>453130</v>
       </c>
       <c r="G47">
-        <v>54.01571983337402</v>
+        <v>43.06720008850098</v>
       </c>
       <c r="H47">
-        <v>45.8901557413737</v>
+        <v>36.10646663665771</v>
       </c>
       <c r="I47">
-        <v>43.6315502166748</v>
+        <v>35.26635002136231</v>
       </c>
       <c r="J47">
-        <v>41.91921356201172</v>
+        <v>33.82510000228882</v>
       </c>
       <c r="K47">
-        <v>0.199247732758522</v>
+        <v>16.88999938964844</v>
       </c>
       <c r="L47">
-        <v>58.97000122070312</v>
+        <v>50.65000152587891</v>
       </c>
       <c r="M47">
-        <v>150.7335135869096</v>
+        <v>152.447642425329</v>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>-8.928571428571436</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>-11.1111111111111</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>6.035524407926535</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>35.64989346008851</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>2.637002144929975</v>
       </c>
     </row>
     <row r="48" spans="1:19">
@@ -3785,43 +3818,43 @@
         <v>65</v>
       </c>
       <c r="B48" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C48" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D48" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="E48">
-        <v>43.2599983215332</v>
+        <v>57.77999877929688</v>
       </c>
       <c r="F48">
-        <v>2950490</v>
+        <v>272450</v>
       </c>
       <c r="G48">
-        <v>38.64379981994629</v>
+        <v>54.35331733703613</v>
       </c>
       <c r="H48">
-        <v>33.74353341420492</v>
+        <v>45.75809611002604</v>
       </c>
       <c r="I48">
-        <v>31.43930005073547</v>
+        <v>43.38622013092041</v>
       </c>
       <c r="J48">
-        <v>29.77625010490418</v>
+        <v>41.57908441543579</v>
       </c>
       <c r="K48">
-        <v>10.74393081665039</v>
+        <v>0.2025985866785049</v>
       </c>
       <c r="L48">
-        <v>44.54999923706055</v>
+        <v>58.97000122070312</v>
       </c>
       <c r="M48">
-        <v>150.6529895448531</v>
+        <v>151.985482495454</v>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>-71.53284671532847</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -3830,13 +3863,13 @@
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>-8.911583097005169</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>-2.897635539815635</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>11.37854588234441</v>
       </c>
     </row>
     <row r="49" spans="1:19">
@@ -3844,58 +3877,58 @@
         <v>66</v>
       </c>
       <c r="B49" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C49" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="D49" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E49">
-        <v>56.84000015258789</v>
+        <v>457.3900146484375</v>
       </c>
       <c r="F49">
-        <v>1178363.333333333</v>
+        <v>1284866.666666667</v>
       </c>
       <c r="G49">
-        <v>54.37819999694824</v>
+        <v>405.9712023925781</v>
       </c>
       <c r="H49">
-        <v>45.17779993693034</v>
+        <v>383.0803668212891</v>
       </c>
       <c r="I49">
-        <v>42.94599994659424</v>
+        <v>366.1866249847412</v>
       </c>
       <c r="J49">
-        <v>40.84774994850159</v>
+        <v>347.2526247406006</v>
       </c>
       <c r="K49">
-        <v>14.4399995803833</v>
+        <v>25.76000022888184</v>
       </c>
       <c r="L49">
-        <v>57.59000015258789</v>
+        <v>585.030029296875</v>
       </c>
       <c r="M49">
-        <v>149.2996725001151</v>
+        <v>151.9233217012739</v>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>68.42105263157896</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>3.225806451612894</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.15837523685024</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>15.0730422504616</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.928527145514126</v>
       </c>
     </row>
     <row r="50" spans="1:19">
@@ -3903,58 +3936,58 @@
         <v>67</v>
       </c>
       <c r="B50" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C50" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D50" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E50">
-        <v>239.8600006103516</v>
+        <v>83.73999786376953</v>
       </c>
       <c r="F50">
-        <v>523416.6666666667</v>
+        <v>3669450</v>
       </c>
       <c r="G50">
-        <v>217.1205993652344</v>
+        <v>76.78235290527344</v>
       </c>
       <c r="H50">
-        <v>182.2894328816732</v>
+        <v>67.54574994405111</v>
       </c>
       <c r="I50">
-        <v>173.0395245361328</v>
+        <v>62.3038849067688</v>
       </c>
       <c r="J50">
-        <v>163.7944745635986</v>
+        <v>58.11147520065308</v>
       </c>
       <c r="K50">
-        <v>27.38999938964844</v>
+        <v>11.32106113433838</v>
       </c>
       <c r="L50">
-        <v>239.8600006103516</v>
+        <v>86.31999969482422</v>
       </c>
       <c r="M50">
-        <v>148.8186333992895</v>
+        <v>151.6864860281966</v>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>-18.26086956521739</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>8.045977011494248</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>32.82442748091602</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>-2.97811110142147</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>9.616671446324442</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>-16.4423499341028</v>
       </c>
     </row>
     <row r="51" spans="1:19">
@@ -3962,58 +3995,58 @@
         <v>68</v>
       </c>
       <c r="B51" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C51" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D51" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E51">
-        <v>443.3099975585938</v>
+        <v>243.1699981689453</v>
       </c>
       <c r="F51">
-        <v>1265783.333333333</v>
+        <v>541016.6666666666</v>
       </c>
       <c r="G51">
-        <v>404.97740234375</v>
+        <v>218.11419921875</v>
       </c>
       <c r="H51">
-        <v>382.7615667724609</v>
+        <v>182.8622328694661</v>
       </c>
       <c r="I51">
-        <v>365.0639749145508</v>
+        <v>173.5610245513916</v>
       </c>
       <c r="J51">
-        <v>346.45932472229</v>
+        <v>164.1586245727539</v>
       </c>
       <c r="K51">
-        <v>25.76000022888184</v>
+        <v>27.38999938964844</v>
       </c>
       <c r="L51">
-        <v>585.030029296875</v>
+        <v>243.1699981689453</v>
       </c>
       <c r="M51">
-        <v>148.3540700897598</v>
+        <v>151.2796321509528</v>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>-117.6470588235294</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>8.753831542910437</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>8.743081537367429</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>-4.401984026106851</v>
       </c>
     </row>
     <row r="52" spans="1:19">
@@ -4021,58 +4054,58 @@
         <v>69</v>
       </c>
       <c r="B52" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C52" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D52" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E52">
-        <v>41.47000122070312</v>
+        <v>14.32999992370605</v>
       </c>
       <c r="F52">
-        <v>3468083.333333333</v>
+        <v>547356.6666666666</v>
       </c>
       <c r="G52">
-        <v>39.37319999694824</v>
+        <v>13.55409997940063</v>
       </c>
       <c r="H52">
-        <v>33.78146672566731</v>
+        <v>10.18428992589315</v>
       </c>
       <c r="I52">
-        <v>32.247200050354</v>
+        <v>9.462855596542358</v>
       </c>
       <c r="J52">
-        <v>30.44030006408691</v>
+        <v>8.791426243782043</v>
       </c>
       <c r="K52">
-        <v>18.89999961853027</v>
+        <v>6.708024024963379</v>
       </c>
       <c r="L52">
-        <v>42.22999954223633</v>
+        <v>16.82963371276855</v>
       </c>
       <c r="M52">
-        <v>147.9933362178913</v>
+        <v>150.795588681398</v>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>113.3333333333334</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>-3.295932678821879</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>-0.3494060097833683</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>-3.048780487804878</v>
       </c>
     </row>
     <row r="53" spans="1:19">
@@ -4080,58 +4113,58 @@
         <v>70</v>
       </c>
       <c r="B53" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C53" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D53" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E53">
-        <v>705.030029296875</v>
+        <v>49.72000122070312</v>
       </c>
       <c r="F53">
-        <v>3110630</v>
+        <v>276936.6666666667</v>
       </c>
       <c r="G53">
-        <v>611.1085974121094</v>
+        <v>43.23400024414062</v>
       </c>
       <c r="H53">
-        <v>564.8667995198567</v>
+        <v>38.18946671803792</v>
       </c>
       <c r="I53">
-        <v>532.094899597168</v>
+        <v>36.04510003089905</v>
       </c>
       <c r="J53">
-        <v>503.3381500244141</v>
+        <v>34.21134998321534</v>
       </c>
       <c r="K53">
-        <v>0.5143532752990723</v>
+        <v>8.170000076293945</v>
       </c>
       <c r="L53">
-        <v>706.2000122070312</v>
+        <v>49.72000122070312</v>
       </c>
       <c r="M53">
-        <v>147.2856644784053</v>
+        <v>149.9088082548701</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>43.90243902439025</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>-472.7272727272727</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>12.59395154695622</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>29.87317223333846</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>-4.953200752533069</v>
       </c>
     </row>
     <row r="54" spans="1:19">
@@ -4139,58 +4172,58 @@
         <v>71</v>
       </c>
       <c r="B54" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C54" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D54" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E54">
-        <v>76.93000030517578</v>
+        <v>42.20999908447266</v>
       </c>
       <c r="F54">
-        <v>380603.3333333333</v>
+        <v>3395010</v>
       </c>
       <c r="G54">
-        <v>75.72460014343261</v>
+        <v>39.5183999633789</v>
       </c>
       <c r="H54">
-        <v>72.23606656392415</v>
+        <v>33.857200050354</v>
       </c>
       <c r="I54">
-        <v>65.84639991760254</v>
+        <v>32.32950004577637</v>
       </c>
       <c r="J54">
-        <v>61.87529998779297</v>
+        <v>30.53700005531311</v>
       </c>
       <c r="K54">
-        <v>0.4209107160568237</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="L54">
-        <v>89.16999816894531</v>
+        <v>42.22999954223633</v>
       </c>
       <c r="M54">
-        <v>146.9600774537036</v>
+        <v>149.7748413973676</v>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>8.955223880597005</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>-2.666666666666669</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>47.05882352941176</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>-1.826974744760881</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>18.23379923761118</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>14.55604075691412</v>
       </c>
     </row>
     <row r="55" spans="1:19">
@@ -4198,58 +4231,58 @@
         <v>72</v>
       </c>
       <c r="B55" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C55" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="D55" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E55">
-        <v>777.4500122070312</v>
+        <v>725.3800048828125</v>
       </c>
       <c r="F55">
-        <v>1142436.666666667</v>
+        <v>3229350</v>
       </c>
       <c r="G55">
-        <v>716.6319970703125</v>
+        <v>613.5941979980469</v>
       </c>
       <c r="H55">
-        <v>623.7397998046876</v>
+        <v>565.8108280436198</v>
       </c>
       <c r="I55">
-        <v>594.9317501831055</v>
+        <v>532.6976466369629</v>
       </c>
       <c r="J55">
-        <v>565.5849000549316</v>
+        <v>503.4685389709473</v>
       </c>
       <c r="K55">
-        <v>23.73999977111816</v>
+        <v>0.5078719854354858</v>
       </c>
       <c r="L55">
-        <v>787.239990234375</v>
+        <v>725.3800048828125</v>
       </c>
       <c r="M55">
-        <v>146.9520880562261</v>
+        <v>149.1239545304081</v>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>19.13875598086126</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>2390</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>-95.260663507109</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>14.27437109755657</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>19.42672413793104</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>-4.681037552384343</v>
       </c>
     </row>
     <row r="56" spans="1:19">
@@ -4257,58 +4290,58 @@
         <v>73</v>
       </c>
       <c r="B56" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C56" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D56" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E56">
-        <v>62.33000183105469</v>
+        <v>79.55999755859375</v>
       </c>
       <c r="F56">
-        <v>1819493.333333333</v>
+        <v>378100</v>
       </c>
       <c r="G56">
-        <v>54.50379989624023</v>
+        <v>76.00800010681152</v>
       </c>
       <c r="H56">
-        <v>47.65860000610351</v>
+        <v>72.37686655680339</v>
       </c>
       <c r="I56">
-        <v>46.38870000839233</v>
+        <v>66.0586999130249</v>
       </c>
       <c r="J56">
-        <v>44.21075004577636</v>
+        <v>62.07124996185303</v>
       </c>
       <c r="K56">
-        <v>0.02175931446254253</v>
+        <v>0.421875</v>
       </c>
       <c r="L56">
-        <v>63</v>
+        <v>89.16999816894531</v>
       </c>
       <c r="M56">
-        <v>146.6259352483625</v>
+        <v>148.750483869228</v>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>22.33009708737864</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>-0.7874015748031503</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>7.279375867515436</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>29.42323559947371</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>38.39872979293979</v>
       </c>
     </row>
     <row r="57" spans="1:19">
@@ -4316,58 +4349,58 @@
         <v>74</v>
       </c>
       <c r="B57" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C57" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D57" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E57">
-        <v>47.93999862670898</v>
+        <v>192.3300018310547</v>
       </c>
       <c r="F57">
-        <v>268780</v>
+        <v>420646.6666666667</v>
       </c>
       <c r="G57">
-        <v>43.10220024108887</v>
+        <v>188.9370001220703</v>
       </c>
       <c r="H57">
-        <v>38.0603333791097</v>
+        <v>162.9968665059407</v>
       </c>
       <c r="I57">
-        <v>35.924850025177</v>
+        <v>149.486249961853</v>
       </c>
       <c r="J57">
-        <v>34.13934997558594</v>
+        <v>139.7895500183105</v>
       </c>
       <c r="K57">
-        <v>8.170000076293945</v>
+        <v>9.350000381469727</v>
       </c>
       <c r="L57">
-        <v>48.7599983215332</v>
+        <v>223.6499938964844</v>
       </c>
       <c r="M57">
-        <v>146.3112679119817</v>
+        <v>148.5168092526375</v>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>9.473684210526324</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>4.000000000000004</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>7.526881720430103</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>3.970519798621981</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>4.513997417175024</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>-1.414439913359919</v>
       </c>
     </row>
     <row r="58" spans="1:19">
@@ -4375,58 +4408,58 @@
         <v>75</v>
       </c>
       <c r="B58" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C58" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D58" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="E58">
-        <v>16.14999961853027</v>
+        <v>790.3900146484375</v>
       </c>
       <c r="F58">
-        <v>892693.3333333334</v>
+        <v>1156390</v>
       </c>
       <c r="G58">
-        <v>14.90339996337891</v>
+        <v>718.961796875</v>
       </c>
       <c r="H58">
-        <v>12.91379996617635</v>
+        <v>625.2373331705729</v>
       </c>
       <c r="I58">
-        <v>12.3003999710083</v>
+        <v>596.5171502685547</v>
       </c>
       <c r="J58">
-        <v>11.72174997806549</v>
+        <v>566.8758999633789</v>
       </c>
       <c r="K58">
-        <v>0.3276619911193848</v>
+        <v>23.73999977111816</v>
       </c>
       <c r="L58">
-        <v>16.14999961853027</v>
+        <v>790.3900146484375</v>
       </c>
       <c r="M58">
-        <v>146.0942816152871</v>
+        <v>147.930531554941</v>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>-0.6849315068493157</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>-6.7524115755627</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>7.241379310344827</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>6.512237762237762</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>6.418604651162791</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>2.576335877862595</v>
       </c>
     </row>
     <row r="59" spans="1:19">
@@ -4434,58 +4467,58 @@
         <v>76</v>
       </c>
       <c r="B59" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C59" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D59" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E59">
-        <v>235.8200073242188</v>
+        <v>240.2799987792969</v>
       </c>
       <c r="F59">
-        <v>258950</v>
+        <v>265880</v>
       </c>
       <c r="G59">
-        <v>202.3079998779297</v>
+        <v>203.4646463012695</v>
       </c>
       <c r="H59">
-        <v>184.1876663208008</v>
+        <v>184.3049637858073</v>
       </c>
       <c r="I59">
-        <v>179.1503997039795</v>
+        <v>179.2731419372559</v>
       </c>
       <c r="J59">
-        <v>171.968999710083</v>
+        <v>171.8820875549316</v>
       </c>
       <c r="K59">
-        <v>2.138945579528809</v>
+        <v>2.10910439491272</v>
       </c>
       <c r="L59">
-        <v>236.2299957275391</v>
+        <v>240.2799987792969</v>
       </c>
       <c r="M59">
-        <v>145.5774203824675</v>
+        <v>147.5343231512931</v>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>16.25</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>-13.08411214953271</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>20.56338028169015</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>-10.18954223156487</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>3.443770042941144</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>27.94861813935384</v>
       </c>
     </row>
     <row r="60" spans="1:19">
@@ -4493,58 +4526,58 @@
         <v>77</v>
       </c>
       <c r="B60" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C60" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="D60" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="E60">
-        <v>140.8399963378906</v>
+        <v>116.6600036621094</v>
       </c>
       <c r="F60">
-        <v>428710</v>
+        <v>252516.6666666667</v>
       </c>
       <c r="G60">
-        <v>122.9667002868652</v>
+        <v>108.2112371826172</v>
       </c>
       <c r="H60">
-        <v>102.8594333394368</v>
+        <v>94.86427505493164</v>
       </c>
       <c r="I60">
-        <v>99.4748749923706</v>
+        <v>88.66610097885132</v>
       </c>
       <c r="J60">
-        <v>94.84327510833741</v>
+        <v>83.26196050643921</v>
       </c>
       <c r="K60">
-        <v>12.25</v>
+        <v>0.3546005487442017</v>
       </c>
       <c r="L60">
-        <v>182.7599945068359</v>
+        <v>120.8598709106445</v>
       </c>
       <c r="M60">
-        <v>143.7982039199218</v>
+        <v>146.4680089625342</v>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>61.9047619047619</v>
       </c>
       <c r="O60">
         <v>0</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>50.44247787610621</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>6.99508663046289</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>9.733257661748015</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>-12.07584830339321</v>
       </c>
     </row>
     <row r="61" spans="1:19">
@@ -4552,58 +4585,58 @@
         <v>78</v>
       </c>
       <c r="B61" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C61" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="D61" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E61">
-        <v>285.8299865722656</v>
+        <v>62.18999862670898</v>
       </c>
       <c r="F61">
-        <v>4938146.666666667</v>
+        <v>1887726.666666667</v>
       </c>
       <c r="G61">
-        <v>263.2773992919922</v>
+        <v>54.40441482543945</v>
       </c>
       <c r="H61">
-        <v>229.9155329386393</v>
+        <v>46.95007705688477</v>
       </c>
       <c r="I61">
-        <v>224.1114994049072</v>
+        <v>45.52091621398926</v>
       </c>
       <c r="J61">
-        <v>215.7577997589111</v>
+        <v>43.19192991256714</v>
       </c>
       <c r="K61">
-        <v>2.397500038146973</v>
+        <v>0.01946010068058968</v>
       </c>
       <c r="L61">
-        <v>309.9599914550781</v>
+        <v>62.4485969543457</v>
       </c>
       <c r="M61">
-        <v>143.7421078393399</v>
+        <v>146.1251380339361</v>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>11.42857142857144</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>12.90322580645161</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>21.21290687321697</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>-2.224297568236291</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>8.250293948939593</v>
       </c>
     </row>
     <row r="62" spans="1:19">
@@ -4611,58 +4644,58 @@
         <v>79</v>
       </c>
       <c r="B62" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C62" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D62" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="E62">
-        <v>114.0299987792969</v>
+        <v>231.9499969482422</v>
       </c>
       <c r="F62">
-        <v>259510</v>
+        <v>256816.6666666667</v>
       </c>
       <c r="G62">
-        <v>108.0985993957519</v>
+        <v>204.2886001586914</v>
       </c>
       <c r="H62">
-        <v>95.08113316853841</v>
+        <v>185.1759404500326</v>
       </c>
       <c r="I62">
-        <v>88.96404993057251</v>
+        <v>177.1289044189453</v>
       </c>
       <c r="J62">
-        <v>83.61860006332398</v>
+        <v>169.4851811981201</v>
       </c>
       <c r="K62">
-        <v>0.2077736556529999</v>
+        <v>1.404735088348389</v>
       </c>
       <c r="L62">
-        <v>124.5500030517578</v>
+        <v>231.9499969482422</v>
       </c>
       <c r="M62">
-        <v>143.2293761855781</v>
+        <v>144.9636868688467</v>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>77.92207792207793</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>41.96891191709846</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>6.301458620982237</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>10.36828304842335</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>5.142554341793861</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -4670,58 +4703,58 @@
         <v>80</v>
       </c>
       <c r="B63" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C63" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="D63" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E63">
-        <v>33.2400016784668</v>
+        <v>288.8399963378906</v>
       </c>
       <c r="F63">
-        <v>397883.3333333333</v>
+        <v>4955153.333333333</v>
       </c>
       <c r="G63">
-        <v>30.49959995269775</v>
+        <v>264.5665991210938</v>
       </c>
       <c r="H63">
-        <v>25.43473331451416</v>
+        <v>230.4156661987305</v>
       </c>
       <c r="I63">
-        <v>24.71154997825623</v>
+        <v>224.5605493927002</v>
       </c>
       <c r="J63">
-        <v>23.75749997138977</v>
+        <v>216.1272997283936</v>
       </c>
       <c r="K63">
-        <v>7.590000152587891</v>
+        <v>2.397500038146973</v>
       </c>
       <c r="L63">
-        <v>33.88999938964844</v>
+        <v>309.9599914550781</v>
       </c>
       <c r="M63">
-        <v>142.4620052165698</v>
+        <v>144.7062246594947</v>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>50.71428571428571</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>-0.4716981132075581</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>25.44378698224853</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>1.359990700918284</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>4.316721231963138</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>-1.634064885496183</v>
       </c>
     </row>
     <row r="64" spans="1:19">
@@ -4729,58 +4762,58 @@
         <v>81</v>
       </c>
       <c r="B64" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C64" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="D64" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E64">
-        <v>54.34999847412109</v>
+        <v>44.2400016784668</v>
       </c>
       <c r="F64">
-        <v>1070903.333333333</v>
+        <v>2167763.333333333</v>
       </c>
       <c r="G64">
-        <v>49.44039993286133</v>
+        <v>39.14420036315918</v>
       </c>
       <c r="H64">
-        <v>42.42099990844726</v>
+        <v>33.57928185780843</v>
       </c>
       <c r="I64">
-        <v>41.10042494773865</v>
+        <v>32.26238916397094</v>
       </c>
       <c r="J64">
-        <v>39.48322497367859</v>
+        <v>31.17191518783569</v>
       </c>
       <c r="K64">
-        <v>4.869999885559082</v>
+        <v>7.637476444244385</v>
       </c>
       <c r="L64">
-        <v>71.40579986572266</v>
+        <v>55.61954116821289</v>
       </c>
       <c r="M64">
-        <v>142.264552832483</v>
+        <v>144.223848067249</v>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>-14.85148514851485</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>-1.149425287356323</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>-1.136363636363637</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>43.51407000686342</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>-31.00236779794791</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>-2.131932643287502</v>
       </c>
     </row>
     <row r="65" spans="1:19">
@@ -4788,58 +4821,58 @@
         <v>82</v>
       </c>
       <c r="B65" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C65" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="D65" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E65">
-        <v>226.5599975585938</v>
+        <v>848.5399780273438</v>
       </c>
       <c r="F65">
-        <v>254750</v>
+        <v>1050356.666666667</v>
       </c>
       <c r="G65">
-        <v>203.6260003662109</v>
+        <v>772.5734167480468</v>
       </c>
       <c r="H65">
-        <v>184.8844668579102</v>
+        <v>690.2345182291666</v>
       </c>
       <c r="I65">
-        <v>176.8939501953125</v>
+        <v>662.4640934753418</v>
       </c>
       <c r="J65">
-        <v>169.4648502349854</v>
+        <v>630.950443725586</v>
       </c>
       <c r="K65">
-        <v>1.419841051101685</v>
+        <v>0.5776801705360413</v>
       </c>
       <c r="L65">
-        <v>231.2899932861328</v>
+        <v>865.5999755859375</v>
       </c>
       <c r="M65">
-        <v>142.2536700390305</v>
+        <v>143.8967274131594</v>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>-29.78524743230627</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>9.781021897810218</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>14.54849498327758</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>7.931995467053716</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>8.568225121965591</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>-17.1159113586035</v>
       </c>
     </row>
     <row r="66" spans="1:19">
@@ -4847,58 +4880,58 @@
         <v>83</v>
       </c>
       <c r="B66" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C66" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D66" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E66">
-        <v>31.95000076293945</v>
+        <v>233.3200073242188</v>
       </c>
       <c r="F66">
-        <v>393196.6666666667</v>
+        <v>292036.6666666667</v>
       </c>
       <c r="G66">
-        <v>30.75819988250732</v>
+        <v>187.5398013305664</v>
       </c>
       <c r="H66">
-        <v>28.41319990793864</v>
+        <v>185.8842010498047</v>
       </c>
       <c r="I66">
-        <v>26.77164996147156</v>
+        <v>177.3041507720947</v>
       </c>
       <c r="J66">
-        <v>25.66635000228882</v>
+        <v>169.9682007217407</v>
       </c>
       <c r="K66">
-        <v>1.899999976158142</v>
+        <v>11.57999992370605</v>
       </c>
       <c r="L66">
-        <v>33.18000030517578</v>
+        <v>233.3200073242188</v>
       </c>
       <c r="M66">
-        <v>142.2198391896674</v>
+        <v>143.4036457148802</v>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>-8900</v>
       </c>
       <c r="O66">
         <v>0</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>46.66666666666667</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>3.86242746615087</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>12.4868264490906</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>8.063923585598824</v>
       </c>
     </row>
     <row r="67" spans="1:19">
@@ -4906,58 +4939,58 @@
         <v>84</v>
       </c>
       <c r="B67" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="C67" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="D67" t="s">
-        <v>166</v>
+        <v>208</v>
       </c>
       <c r="E67">
-        <v>102.5699996948242</v>
+        <v>54.27000045776367</v>
       </c>
       <c r="F67">
-        <v>1825366.666666667</v>
+        <v>1058343.333333333</v>
       </c>
       <c r="G67">
-        <v>100.5097999572754</v>
+        <v>49.7441999053955</v>
       </c>
       <c r="H67">
-        <v>86.03079991658528</v>
+        <v>42.49486658732096</v>
       </c>
       <c r="I67">
-        <v>82.02294994354249</v>
+        <v>41.20182494163513</v>
       </c>
       <c r="J67">
-        <v>77.42259990692139</v>
+        <v>39.55607497215271</v>
       </c>
       <c r="K67">
-        <v>0.1027423962950706</v>
+        <v>4.869999885559082</v>
       </c>
       <c r="L67">
-        <v>109.2399978637695</v>
+        <v>71.40578460693359</v>
       </c>
       <c r="M67">
-        <v>141.5031613548059</v>
+        <v>143.3463264956307</v>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>-115</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>-120</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>-13.87197933960524</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>-9.241587142139629</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>5.949152211664162</v>
       </c>
     </row>
     <row r="68" spans="1:19">
@@ -4965,58 +4998,58 @@
         <v>85</v>
       </c>
       <c r="B68" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C68" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="D68" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E68">
-        <v>47.61999893188477</v>
+        <v>69.37000274658203</v>
       </c>
       <c r="F68">
-        <v>5279240</v>
+        <v>11740030</v>
       </c>
       <c r="G68">
-        <v>45.58679985046387</v>
+        <v>61.60500495910645</v>
       </c>
       <c r="H68">
-        <v>39.966533203125</v>
+        <v>58.06329048156739</v>
       </c>
       <c r="I68">
-        <v>37.17839990615845</v>
+        <v>56.35129058837891</v>
       </c>
       <c r="J68">
-        <v>34.98129990577698</v>
+        <v>53.6153258895874</v>
       </c>
       <c r="K68">
-        <v>1.243403434753418</v>
+        <v>1.828321099281311</v>
       </c>
       <c r="L68">
-        <v>50.56000137329102</v>
+        <v>90.55065155029297</v>
       </c>
       <c r="M68">
-        <v>141.3722306764255</v>
+        <v>143.1047247674147</v>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>-28.07017543859649</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>24.24242424242423</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>6.451612903225811</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>5.794615556715639</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>1.452674585760763</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>-6.824109975326048</v>
       </c>
     </row>
     <row r="69" spans="1:19">
@@ -5024,58 +5057,58 @@
         <v>86</v>
       </c>
       <c r="B69" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C69" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="D69" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E69">
-        <v>53.52000045776367</v>
+        <v>48.04999923706055</v>
       </c>
       <c r="F69">
-        <v>2995700</v>
+        <v>5326610</v>
       </c>
       <c r="G69">
-        <v>50.57399993896485</v>
+        <v>45.64167198181153</v>
       </c>
       <c r="H69">
-        <v>43.3643332417806</v>
+        <v>40.033972752889</v>
       </c>
       <c r="I69">
-        <v>41.00029990196228</v>
+        <v>37.23996558189392</v>
       </c>
       <c r="J69">
-        <v>39.14729990959167</v>
+        <v>35.02679123878479</v>
       </c>
       <c r="K69">
-        <v>7.668580532073975</v>
+        <v>1.243354916572571</v>
       </c>
       <c r="L69">
-        <v>54.72999954223633</v>
+        <v>50.56000137329102</v>
       </c>
       <c r="M69">
-        <v>141.3082040535338</v>
+        <v>143.0406118072495</v>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>966.6666666666667</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>-3300</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>-103.7037037037037</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>19.31421386883879</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>-29.8392226791368</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>31.16993712397061</v>
       </c>
     </row>
     <row r="70" spans="1:19">
@@ -5083,58 +5116,58 @@
         <v>87</v>
       </c>
       <c r="B70" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C70" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="D70" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E70">
-        <v>555.8800048828125</v>
+        <v>112.379997253418</v>
       </c>
       <c r="F70">
-        <v>5727266.666666667</v>
+        <v>1389500</v>
       </c>
       <c r="G70">
-        <v>494.5053991699219</v>
+        <v>105.255</v>
       </c>
       <c r="H70">
-        <v>444.1462658691406</v>
+        <v>85.96919987996419</v>
       </c>
       <c r="I70">
-        <v>427.572999420166</v>
+        <v>82.74279991149902</v>
       </c>
       <c r="J70">
-        <v>408.6622998046875</v>
+        <v>79.62629997253418</v>
       </c>
       <c r="K70">
-        <v>0.372857004404068</v>
+        <v>20</v>
       </c>
       <c r="L70">
-        <v>691.6900024414062</v>
+        <v>112.379997253418</v>
       </c>
       <c r="M70">
-        <v>141.2707086017318</v>
+        <v>142.9043505252912</v>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>42.85714285714286</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>80.00000000000001</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.060872054193302</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>1.167953667953668</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>-0.3750360611597269</v>
       </c>
     </row>
     <row r="71" spans="1:19">
@@ -5142,58 +5175,58 @@
         <v>88</v>
       </c>
       <c r="B71" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C71" t="s">
         <v>110</v>
       </c>
       <c r="D71" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E71">
-        <v>834.6199951171875</v>
+        <v>139.2899932861328</v>
       </c>
       <c r="F71">
-        <v>1039273.333333333</v>
+        <v>431013.3333333333</v>
       </c>
       <c r="G71">
-        <v>770.3786010742188</v>
+        <v>123.9077001953125</v>
       </c>
       <c r="H71">
-        <v>690.718936360677</v>
+        <v>103.2008332824707</v>
       </c>
       <c r="I71">
-        <v>663.3757022094727</v>
+        <v>99.76667495727538</v>
       </c>
       <c r="J71">
-        <v>632.8040524291993</v>
+        <v>95.00132514953613</v>
       </c>
       <c r="K71">
-        <v>0.5958155393600464</v>
+        <v>12.25</v>
       </c>
       <c r="L71">
-        <v>865.5999755859375</v>
+        <v>182.7599945068359</v>
       </c>
       <c r="M71">
-        <v>141.0801897552028</v>
+        <v>142.6530834550017</v>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>-58.37837837837838</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>-46.52777777777777</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>33.33333333333332</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>1.352520414407191</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>41.09678763881032</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>46.70248078266946</v>
       </c>
     </row>
     <row r="72" spans="1:19">
@@ -5201,31 +5234,31 @@
         <v>89</v>
       </c>
       <c r="B72" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C72" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D72" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E72">
-        <v>288.6300048828125</v>
+        <v>294.4200134277344</v>
       </c>
       <c r="F72">
-        <v>1201740</v>
+        <v>1202740</v>
       </c>
       <c r="G72">
-        <v>276.1770004272461</v>
+        <v>277.3332006835938</v>
       </c>
       <c r="H72">
-        <v>243.2594004313151</v>
+        <v>243.7382004801432</v>
       </c>
       <c r="I72">
-        <v>232.9267005157471</v>
+        <v>233.4438505554199</v>
       </c>
       <c r="J72">
-        <v>223.6587502288818</v>
+        <v>224.0976502990723</v>
       </c>
       <c r="K72">
         <v>46.9900016784668</v>
@@ -5234,25 +5267,25 @@
         <v>300.8999938964844</v>
       </c>
       <c r="M72">
-        <v>140.7338743698861</v>
+        <v>142.4065938471842</v>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>6.993006993006999</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>9.160305343511441</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>4.416302974200315</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>6.082839758904527</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>2.311421039204014</v>
       </c>
     </row>
     <row r="73" spans="1:19">
@@ -5260,58 +5293,58 @@
         <v>90</v>
       </c>
       <c r="B73" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C73" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="D73" t="s">
-        <v>172</v>
+        <v>214</v>
       </c>
       <c r="E73">
-        <v>39.59999847412109</v>
+        <v>32.2400016784668</v>
       </c>
       <c r="F73">
-        <v>1260516.666666667</v>
+        <v>387903.3333333333</v>
       </c>
       <c r="G73">
-        <v>36.87520023345947</v>
+        <v>30.76519992828369</v>
       </c>
       <c r="H73">
-        <v>32.39513345082601</v>
+        <v>28.46699991861979</v>
       </c>
       <c r="I73">
-        <v>30.85530006408692</v>
+        <v>26.82734996795654</v>
       </c>
       <c r="J73">
-        <v>29.4269000339508</v>
+        <v>25.72789999961853</v>
       </c>
       <c r="K73">
-        <v>15.22000026702881</v>
+        <v>1.899999976158142</v>
       </c>
       <c r="L73">
-        <v>50.79999923706055</v>
+        <v>33.18000030517578</v>
       </c>
       <c r="M73">
-        <v>140.7223561375927</v>
+        <v>142.3048770110966</v>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>9.333333333333327</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>57.69230769230768</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>-60.60606060606061</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>25.41876826496374</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>-23.824176404046</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>-1.565086970918795</v>
       </c>
     </row>
     <row r="74" spans="1:19">
@@ -5319,58 +5352,58 @@
         <v>91</v>
       </c>
       <c r="B74" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C74" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D74" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E74">
-        <v>14.48999977111816</v>
+        <v>41.47000122070312</v>
       </c>
       <c r="F74">
-        <v>1443063.333333333</v>
+        <v>1302546.666666667</v>
       </c>
       <c r="G74">
-        <v>12.76820001602173</v>
+        <v>36.82040000915527</v>
       </c>
       <c r="H74">
-        <v>11.36273331960042</v>
+        <v>33.62960004170736</v>
       </c>
       <c r="I74">
-        <v>10.87564999580383</v>
+        <v>33.47515000343323</v>
       </c>
       <c r="J74">
-        <v>10.40524999141693</v>
+        <v>32.51240001678467</v>
       </c>
       <c r="K74">
-        <v>8.189999580383301</v>
+        <v>18.28000068664551</v>
       </c>
       <c r="L74">
-        <v>15.76000022888184</v>
+        <v>47.06000137329102</v>
       </c>
       <c r="M74">
-        <v>140.7202362233414</v>
+        <v>142.1797408581503</v>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="P74">
         <v>0</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>7.648941260916378</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>9.095061748535818</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>-8.262743572091352</v>
       </c>
     </row>
     <row r="75" spans="1:19">
@@ -5378,40 +5411,40 @@
         <v>92</v>
       </c>
       <c r="B75" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="C75" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="D75" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E75">
-        <v>227.7200012207031</v>
+        <v>16.1299991607666</v>
       </c>
       <c r="F75">
-        <v>283763.3333333333</v>
+        <v>890670</v>
       </c>
       <c r="G75">
-        <v>186.7376013183594</v>
+        <v>14.9497999382019</v>
       </c>
       <c r="H75">
-        <v>185.4799342854818</v>
+        <v>12.94453329086304</v>
       </c>
       <c r="I75">
-        <v>176.8036507415771</v>
+        <v>12.32517925262451</v>
       </c>
       <c r="J75">
-        <v>169.6872506713867</v>
+        <v>11.71634189128876</v>
       </c>
       <c r="K75">
-        <v>11.57999992370605</v>
+        <v>0.3538231551647186</v>
       </c>
       <c r="L75">
-        <v>229.6900024414062</v>
+        <v>16.14999961853027</v>
       </c>
       <c r="M75">
-        <v>140.7027873935847</v>
+        <v>142.1236756040729</v>
       </c>
       <c r="N75">
         <v>0</v>
@@ -5423,13 +5456,13 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>4.853476386607149</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>8.005237990028375</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>-3.941579089412327</v>
       </c>
     </row>
     <row r="76" spans="1:19">
@@ -5437,40 +5470,40 @@
         <v>93</v>
       </c>
       <c r="B76" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C76" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="D76" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="E76">
-        <v>41.54999923706055</v>
+        <v>74.70999908447266</v>
       </c>
       <c r="F76">
-        <v>1314366.666666667</v>
+        <v>3503523.333333333</v>
       </c>
       <c r="G76">
-        <v>36.63180000305176</v>
+        <v>67.66075218200683</v>
       </c>
       <c r="H76">
-        <v>33.61173337300618</v>
+        <v>59.77672958374023</v>
       </c>
       <c r="I76">
-        <v>33.42029999732971</v>
+        <v>57.16424728393554</v>
       </c>
       <c r="J76">
-        <v>32.47965001106262</v>
+        <v>54.92056552886963</v>
       </c>
       <c r="K76">
-        <v>18.28000068664551</v>
+        <v>1.247950673103333</v>
       </c>
       <c r="L76">
-        <v>47.06000137329102</v>
+        <v>74.70999908447266</v>
       </c>
       <c r="M76">
-        <v>140.3152397738445</v>
+        <v>141.9484793331816</v>
       </c>
       <c r="N76">
         <v>0</v>
@@ -5489,6 +5522,301 @@
       </c>
       <c r="S76">
         <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19">
+      <c r="A77" t="s">
+        <v>94</v>
+      </c>
+      <c r="B77" t="s">
+        <v>107</v>
+      </c>
+      <c r="C77" t="s">
+        <v>141</v>
+      </c>
+      <c r="D77" t="s">
+        <v>218</v>
+      </c>
+      <c r="E77">
+        <v>559.2999877929688</v>
+      </c>
+      <c r="F77">
+        <v>5783110</v>
+      </c>
+      <c r="G77">
+        <v>496.1001989746094</v>
+      </c>
+      <c r="H77">
+        <v>444.9022658284505</v>
+      </c>
+      <c r="I77">
+        <v>428.7295993041992</v>
+      </c>
+      <c r="J77">
+        <v>409.470899810791</v>
+      </c>
+      <c r="K77">
+        <v>0.372857004404068</v>
+      </c>
+      <c r="L77">
+        <v>691.6900024414062</v>
+      </c>
+      <c r="M77">
+        <v>141.8708091249966</v>
+      </c>
+      <c r="N77">
+        <v>1658.333333333333</v>
+      </c>
+      <c r="O77">
+        <v>-43.43163538873995</v>
+      </c>
+      <c r="P77">
+        <v>13.37386018237082</v>
+      </c>
+      <c r="Q77">
+        <v>3.4086667849886</v>
+      </c>
+      <c r="R77">
+        <v>4.328251764531437</v>
+      </c>
+      <c r="S77">
+        <v>0.3160937391066327</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19">
+      <c r="A78" t="s">
+        <v>95</v>
+      </c>
+      <c r="B78" t="s">
+        <v>104</v>
+      </c>
+      <c r="C78" t="s">
+        <v>125</v>
+      </c>
+      <c r="D78" t="s">
+        <v>219</v>
+      </c>
+      <c r="E78">
+        <v>105.9000015258789</v>
+      </c>
+      <c r="F78">
+        <v>2270090</v>
+      </c>
+      <c r="G78">
+        <v>95.30760040283204</v>
+      </c>
+      <c r="H78">
+        <v>88.02434076944986</v>
+      </c>
+      <c r="I78">
+        <v>82.85509580612182</v>
+      </c>
+      <c r="J78">
+        <v>79.06600774765015</v>
+      </c>
+      <c r="K78">
+        <v>3.97672176361084</v>
+      </c>
+      <c r="L78">
+        <v>105.9000015258789</v>
+      </c>
+      <c r="M78">
+        <v>141.4568967138333</v>
+      </c>
+      <c r="N78">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="O78">
+        <v>0.5882352941176475</v>
+      </c>
+      <c r="P78">
+        <v>19.71830985915493</v>
+      </c>
+      <c r="Q78">
+        <v>-81.0611589548971</v>
+      </c>
+      <c r="R78">
+        <v>158.4795321637427</v>
+      </c>
+      <c r="S78">
+        <v>9.479553903345725</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19">
+      <c r="A79" t="s">
+        <v>96</v>
+      </c>
+      <c r="B79" t="s">
+        <v>101</v>
+      </c>
+      <c r="C79" t="s">
+        <v>140</v>
+      </c>
+      <c r="D79" t="s">
+        <v>172</v>
+      </c>
+      <c r="E79">
+        <v>103.0100021362305</v>
+      </c>
+      <c r="F79">
+        <v>1837210</v>
+      </c>
+      <c r="G79">
+        <v>100.7531466674805</v>
+      </c>
+      <c r="H79">
+        <v>86.02768142700195</v>
+      </c>
+      <c r="I79">
+        <v>81.99409641265869</v>
+      </c>
+      <c r="J79">
+        <v>77.39107595443726</v>
+      </c>
+      <c r="K79">
+        <v>0.1045215502381325</v>
+      </c>
+      <c r="L79">
+        <v>109.2399978637695</v>
+      </c>
+      <c r="M79">
+        <v>141.3350482919594</v>
+      </c>
+      <c r="N79">
+        <v>-9.641873278236918</v>
+      </c>
+      <c r="O79">
+        <v>12.71477663230239</v>
+      </c>
+      <c r="P79">
+        <v>-2.999999999999996</v>
+      </c>
+      <c r="Q79">
+        <v>7.246574463105462</v>
+      </c>
+      <c r="R79">
+        <v>-4.421841058663521</v>
+      </c>
+      <c r="S79">
+        <v>17.14691156075232</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19">
+      <c r="A80" t="s">
+        <v>97</v>
+      </c>
+      <c r="B80" t="s">
+        <v>102</v>
+      </c>
+      <c r="C80" t="s">
+        <v>145</v>
+      </c>
+      <c r="D80" t="s">
+        <v>220</v>
+      </c>
+      <c r="E80">
+        <v>47.09000015258789</v>
+      </c>
+      <c r="F80">
+        <v>307313.3333333333</v>
+      </c>
+      <c r="G80">
+        <v>43.3112141418457</v>
+      </c>
+      <c r="H80">
+        <v>41.3860777537028</v>
+      </c>
+      <c r="I80">
+        <v>38.31077602386475</v>
+      </c>
+      <c r="J80">
+        <v>36.74372544288635</v>
+      </c>
+      <c r="K80">
+        <v>1.473910570144653</v>
+      </c>
+      <c r="L80">
+        <v>59.97432327270508</v>
+      </c>
+      <c r="M80">
+        <v>140.5923165255903</v>
+      </c>
+      <c r="N80">
+        <v>1820</v>
+      </c>
+      <c r="O80">
+        <v>4.347826086956514</v>
+      </c>
+      <c r="P80">
+        <v>-9.803921568627448</v>
+      </c>
+      <c r="Q80">
+        <v>-20.50324356202084</v>
+      </c>
+      <c r="R80">
+        <v>-1.994027550332338</v>
+      </c>
+      <c r="S80">
+        <v>-7.477718360071302</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19">
+      <c r="A81" t="s">
+        <v>98</v>
+      </c>
+      <c r="B81" t="s">
+        <v>102</v>
+      </c>
+      <c r="C81" t="s">
+        <v>126</v>
+      </c>
+      <c r="D81" t="s">
+        <v>221</v>
+      </c>
+      <c r="E81">
+        <v>14.64000034332275</v>
+      </c>
+      <c r="F81">
+        <v>1437156.666666667</v>
+      </c>
+      <c r="G81">
+        <v>12.85040002822876</v>
+      </c>
+      <c r="H81">
+        <v>11.39206665674845</v>
+      </c>
+      <c r="I81">
+        <v>10.90299999713898</v>
+      </c>
+      <c r="J81">
+        <v>10.42599999427795</v>
+      </c>
+      <c r="K81">
+        <v>8.189999580383301</v>
+      </c>
+      <c r="L81">
+        <v>15.76000022888184</v>
+      </c>
+      <c r="M81">
+        <v>140.2930427554761</v>
+      </c>
+      <c r="N81">
+        <v>22.72727272727273</v>
+      </c>
+      <c r="O81">
+        <v>8.000000000000007</v>
+      </c>
+      <c r="P81">
+        <v>38.88888888888889</v>
+      </c>
+      <c r="Q81">
+        <v>3.506509343670435</v>
+      </c>
+      <c r="R81">
+        <v>7.426241742886179</v>
+      </c>
+      <c r="S81">
+        <v>-9.946805468169078</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/ScreenResult/ScreenResult.xlsx
+++ b/Screener/ScreenResult/ScreenResult.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
   <si>
     <t>Symbol</t>
   </si>
@@ -91,6 +91,9 @@
     <t>HNI</t>
   </si>
   <si>
+    <t>IDCC</t>
+  </si>
+  <si>
     <t>AX</t>
   </si>
   <si>
@@ -127,6 +130,9 @@
     <t>Business Equipment &amp; Supplies</t>
   </si>
   <si>
+    <t>Software—Application</t>
+  </si>
+  <si>
     <t>Banks - Regional</t>
   </si>
   <si>
@@ -143,6 +149,9 @@
   </si>
   <si>
     <t>1980-03-17</t>
+  </si>
+  <si>
+    <t>1981-11-12</t>
   </si>
   <si>
     <t>2005-03-16</t>
@@ -506,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
@@ -579,40 +588,40 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E2">
-        <v>880.5499877929688</v>
+        <v>1004</v>
       </c>
       <c r="F2">
-        <v>10163993.33333333</v>
+        <v>10952183.33333333</v>
       </c>
       <c r="G2">
-        <v>410.9711978149414</v>
+        <v>425.7241976928711</v>
       </c>
       <c r="H2">
-        <v>322.2733322143555</v>
+        <v>327.0063322957357</v>
       </c>
       <c r="I2">
-        <v>292.7458491897583</v>
+        <v>297.2402991867065</v>
       </c>
       <c r="J2">
-        <v>245.0198997879028</v>
+        <v>246.0443497848511</v>
       </c>
       <c r="K2">
         <v>3.849999904632568</v>
       </c>
       <c r="L2">
-        <v>880.5499877929688</v>
+        <v>1004</v>
       </c>
       <c r="M2">
-        <v>501.9502149887406</v>
+        <v>574.4674227957686</v>
       </c>
       <c r="N2">
         <v>71</v>
@@ -644,40 +653,40 @@
         <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E3">
-        <v>166.7799987792969</v>
+        <v>175.2599945068359</v>
       </c>
       <c r="F3">
-        <v>1717513.333333333</v>
+        <v>1726186.666666667</v>
       </c>
       <c r="G3">
-        <v>150.9815998840332</v>
+        <v>151.9549998474121</v>
       </c>
       <c r="H3">
-        <v>126.9839334106445</v>
+        <v>127.3816000366211</v>
       </c>
       <c r="I3">
-        <v>120.5549000549316</v>
+        <v>120.9676000213623</v>
       </c>
       <c r="J3">
-        <v>113.1099500274658</v>
+        <v>113.4801000595093</v>
       </c>
       <c r="K3">
         <v>7.300000190734863</v>
       </c>
       <c r="L3">
-        <v>174.5200042724609</v>
+        <v>175.2599945068359</v>
       </c>
       <c r="M3">
-        <v>169.9010348832895</v>
+        <v>180.7485579499775</v>
       </c>
       <c r="N3">
         <v>54</v>
@@ -709,31 +718,31 @@
         <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E4">
-        <v>18.39999961853027</v>
+        <v>18.31999969482422</v>
       </c>
       <c r="F4">
-        <v>1155020</v>
+        <v>1127300</v>
       </c>
       <c r="G4">
-        <v>17.99760000228882</v>
+        <v>18.0239999961853</v>
       </c>
       <c r="H4">
-        <v>13.06581509272258</v>
+        <v>13.13076507250468</v>
       </c>
       <c r="I4">
-        <v>11.89673812866211</v>
+        <v>11.95056617259979</v>
       </c>
       <c r="J4">
-        <v>10.90350293159485</v>
+        <v>10.96111566543579</v>
       </c>
       <c r="K4">
         <v>1.793278217315674</v>
@@ -742,7 +751,7 @@
         <v>22.39999961853027</v>
       </c>
       <c r="M4">
-        <v>169.0407875714442</v>
+        <v>172.6082367382666</v>
       </c>
       <c r="N4">
         <v>41</v>
@@ -774,40 +783,40 @@
         <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E5">
-        <v>42.70000076293945</v>
+        <v>43.95000076293945</v>
       </c>
       <c r="F5">
-        <v>237923.3333333333</v>
+        <v>237966.6666666667</v>
       </c>
       <c r="G5">
-        <v>41.21779991149902</v>
+        <v>41.29239990234375</v>
       </c>
       <c r="H5">
-        <v>35.92499713897705</v>
+        <v>36.25113328297933</v>
       </c>
       <c r="I5">
-        <v>33.49428380966187</v>
+        <v>33.91324994087219</v>
       </c>
       <c r="J5">
-        <v>31.91286069869995</v>
+        <v>32.38394992828369</v>
       </c>
       <c r="K5">
-        <v>0.6640231013298035</v>
+        <v>0.3485642671585083</v>
       </c>
       <c r="L5">
-        <v>44.21884918212891</v>
+        <v>47.37138748168945</v>
       </c>
       <c r="M5">
-        <v>133.1526995673106</v>
+        <v>136.672146242307</v>
       </c>
       <c r="N5">
         <v>31</v>
@@ -839,64 +848,64 @@
         <v>25</v>
       </c>
       <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6">
+        <v>116.1500015258789</v>
+      </c>
+      <c r="F6">
+        <v>383806.6666666667</v>
+      </c>
+      <c r="G6">
+        <v>106.1260005187988</v>
+      </c>
+      <c r="H6">
+        <v>92.68060028076172</v>
+      </c>
+      <c r="I6">
+        <v>91.30755020141602</v>
+      </c>
+      <c r="J6">
+        <v>87.899700050354</v>
+      </c>
+      <c r="K6">
+        <v>1.669681549072266</v>
+      </c>
+      <c r="L6">
+        <v>116.1500015258789</v>
+      </c>
+      <c r="M6">
+        <v>136.3204318905187</v>
+      </c>
+      <c r="N6">
         <v>31</v>
       </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6">
-        <v>53.47000122070312</v>
-      </c>
-      <c r="F6">
-        <v>671913.3333333334</v>
-      </c>
-      <c r="G6">
-        <v>52.6402001953125</v>
-      </c>
-      <c r="H6">
-        <v>44.45740000406901</v>
-      </c>
-      <c r="I6">
-        <v>43.21949995040894</v>
-      </c>
-      <c r="J6">
-        <v>41.58699993133545</v>
-      </c>
-      <c r="K6">
-        <v>0.8500000238418579</v>
-      </c>
-      <c r="L6">
-        <v>62.13999938964844</v>
-      </c>
-      <c r="M6">
-        <v>130.5273717485854</v>
-      </c>
-      <c r="N6">
-        <v>94</v>
-      </c>
       <c r="O6">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="P6">
-        <v>52</v>
+        <v>-27</v>
       </c>
       <c r="Q6">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="R6">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="S6">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="T6">
-        <v>4</v>
+        <v>-50</v>
       </c>
       <c r="U6">
-        <v>2</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -907,60 +916,125 @@
         <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7">
+        <v>55.11999893188477</v>
+      </c>
+      <c r="F7">
+        <v>664586.6666666666</v>
+      </c>
+      <c r="G7">
+        <v>52.87160018920898</v>
+      </c>
+      <c r="H7">
+        <v>44.53819999694824</v>
+      </c>
+      <c r="I7">
+        <v>43.29499994277954</v>
+      </c>
+      <c r="J7">
+        <v>41.66369993209839</v>
+      </c>
+      <c r="K7">
+        <v>0.8500000238418579</v>
+      </c>
+      <c r="L7">
+        <v>62.13999938964844</v>
+      </c>
+      <c r="M7">
+        <v>135.733674985963</v>
+      </c>
+      <c r="N7">
+        <v>94</v>
+      </c>
+      <c r="O7">
+        <v>42</v>
+      </c>
+      <c r="P7">
+        <v>52</v>
+      </c>
+      <c r="Q7">
+        <v>28</v>
+      </c>
+      <c r="R7">
+        <v>12</v>
+      </c>
+      <c r="S7">
         <v>44</v>
       </c>
-      <c r="E7">
-        <v>3738.31005859375</v>
-      </c>
-      <c r="F7">
-        <v>245783.3333333333</v>
-      </c>
-      <c r="G7">
-        <v>3504.771787109375</v>
-      </c>
-      <c r="H7">
-        <v>3191.52185546875</v>
-      </c>
-      <c r="I7">
-        <v>3056.814291992187</v>
-      </c>
-      <c r="J7">
-        <v>2959.388244628906</v>
-      </c>
-      <c r="K7">
+      <c r="T7">
+        <v>4</v>
+      </c>
+      <c r="U7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8">
+        <v>3750.659912109375</v>
+      </c>
+      <c r="F8">
+        <v>244776.6666666667</v>
+      </c>
+      <c r="G8">
+        <v>3517.095385742187</v>
+      </c>
+      <c r="H8">
+        <v>3197.629388020833</v>
+      </c>
+      <c r="I8">
+        <v>3062.112141113281</v>
+      </c>
+      <c r="J8">
+        <v>2963.770245361328</v>
+      </c>
+      <c r="K8">
         <v>6.599999904632568</v>
       </c>
-      <c r="L7">
+      <c r="L8">
         <v>3840.219970703125</v>
       </c>
-      <c r="M7">
-        <v>130.2232698255305</v>
-      </c>
-      <c r="N7">
+      <c r="M8">
+        <v>131.2670344561847</v>
+      </c>
+      <c r="N8">
         <v>36</v>
       </c>
-      <c r="O7">
+      <c r="O8">
         <v>97</v>
       </c>
-      <c r="P7">
+      <c r="P8">
         <v>197</v>
       </c>
-      <c r="Q7">
+      <c r="Q8">
         <v>171</v>
       </c>
-      <c r="R7">
+      <c r="R8">
         <v>1856</v>
       </c>
-      <c r="S7">
+      <c r="S8">
         <v>34</v>
       </c>
-      <c r="T7">
+      <c r="T8">
         <v>45</v>
       </c>
-      <c r="U7">
+      <c r="U8">
         <v>-7</v>
       </c>
     </row>

--- a/Screener/ScreenResult/ScreenResult.xlsx
+++ b/Screener/ScreenResult/ScreenResult.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Symbol</t>
   </si>
@@ -79,22 +79,34 @@
     <t>ELF</t>
   </si>
   <si>
+    <t>HTGC</t>
+  </si>
+  <si>
     <t>Technology</t>
   </si>
   <si>
     <t>Consumer Defensive</t>
   </si>
   <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
     <t>Computer Hardware</t>
   </si>
   <si>
     <t>Household &amp; Personal Products</t>
   </si>
   <si>
+    <t>Asset Management</t>
+  </si>
+  <si>
     <t>2007-03-29</t>
   </si>
   <si>
     <t>2016-09-22</t>
+  </si>
+  <si>
+    <t>2005-06-09</t>
   </si>
 </sst>
 </file>
@@ -452,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -519,46 +531,46 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E2">
-        <v>866.1199951171875</v>
+        <v>1085.415649414062</v>
       </c>
       <c r="F2">
-        <v>14772216.66666667</v>
+        <v>14819195.63333333</v>
       </c>
       <c r="G2">
-        <v>528.3253985595703</v>
+        <v>637.4673095703125</v>
       </c>
       <c r="H2">
-        <v>358.9864657592773</v>
+        <v>394.1328362019857</v>
       </c>
       <c r="I2">
-        <v>329.163299331665</v>
+        <v>361.5986769866943</v>
       </c>
       <c r="J2">
-        <v>262.5819494247436</v>
+        <v>282.0150992584229</v>
       </c>
       <c r="K2">
-        <v>89.27999877929688</v>
+        <v>91.75</v>
       </c>
       <c r="L2">
-        <v>1004</v>
+        <v>1159.760009765625</v>
       </c>
       <c r="M2">
-        <v>203.2527010745317</v>
+        <v>323.7422117030001</v>
       </c>
       <c r="N2">
-        <v>785.3316762815909</v>
+        <v>1073.803001065657</v>
       </c>
       <c r="O2">
-        <v>441.3718115269876</v>
+        <v>557.7662072666031</v>
       </c>
       <c r="P2">
         <v>62</v>
@@ -578,46 +590,46 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>208.5299987792969</v>
+        <v>193.6100006103516</v>
       </c>
       <c r="F3">
-        <v>1756746.666666667</v>
+        <v>1440388.8</v>
       </c>
       <c r="G3">
-        <v>162.0811996459961</v>
+        <v>170.4341995239258</v>
       </c>
       <c r="H3">
-        <v>131.8589999389648</v>
+        <v>135.7615998840332</v>
       </c>
       <c r="I3">
-        <v>125.4374499511719</v>
+        <v>129.5238999176025</v>
       </c>
       <c r="J3">
-        <v>116.7663999557495</v>
+        <v>119.4194500350952</v>
       </c>
       <c r="K3">
-        <v>69.56999969482422</v>
+        <v>72.01999664306641</v>
       </c>
       <c r="L3">
-        <v>208.5299987792969</v>
+        <v>217.3999938964844</v>
       </c>
       <c r="M3">
-        <v>76.4362420439728</v>
+        <v>52.56895057709545</v>
       </c>
       <c r="N3">
-        <v>177.3374012612904</v>
+        <v>168.828116682495</v>
       </c>
       <c r="O3">
-        <v>197.3505742430945</v>
+        <v>179.6599058749279</v>
       </c>
       <c r="P3">
         <v>35</v>
@@ -630,6 +642,65 @@
       </c>
       <c r="S3">
         <v>25.889</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4">
+        <v>18.16500091552734</v>
+      </c>
+      <c r="F4">
+        <v>1052424.7</v>
+      </c>
+      <c r="G4">
+        <v>17.23304351806641</v>
+      </c>
+      <c r="H4">
+        <v>15.93628141403198</v>
+      </c>
+      <c r="I4">
+        <v>15.47844623088837</v>
+      </c>
+      <c r="J4">
+        <v>14.88064412593842</v>
+      </c>
+      <c r="K4">
+        <v>10.24463176727295</v>
+      </c>
+      <c r="L4">
+        <v>18.39999961853027</v>
+      </c>
+      <c r="M4">
+        <v>21.68225148065475</v>
+      </c>
+      <c r="N4">
+        <v>71.52562697174625</v>
+      </c>
+      <c r="O4">
+        <v>124.5966768115443</v>
+      </c>
+      <c r="P4">
+        <v>66</v>
+      </c>
+      <c r="Q4">
+        <v>192</v>
+      </c>
+      <c r="R4">
+        <v>171</v>
+      </c>
+      <c r="S4">
+        <v>21.065001</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/ScreenResult/ScreenResult.xlsx
+++ b/Screener/ScreenResult/ScreenResult.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="361">
   <si>
     <t>Symbol</t>
   </si>
@@ -73,40 +73,1030 @@
     <t>ROE</t>
   </si>
   <si>
+    <t>CRBP</t>
+  </si>
+  <si>
+    <t>ROOT</t>
+  </si>
+  <si>
     <t>SMCI</t>
   </si>
   <si>
+    <t>MSTR</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>IMNM</t>
+  </si>
+  <si>
+    <t>CLSK</t>
+  </si>
+  <si>
+    <t>CVNA</t>
+  </si>
+  <si>
+    <t>GBTC</t>
+  </si>
+  <si>
+    <t>YMAB</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>ALPN</t>
+  </si>
+  <si>
+    <t>HARP</t>
+  </si>
+  <si>
+    <t>ETHE</t>
+  </si>
+  <si>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>DWAC</t>
+  </si>
+  <si>
+    <t>MOR</t>
+  </si>
+  <si>
+    <t>MGNX</t>
+  </si>
+  <si>
+    <t>GRPN</t>
+  </si>
+  <si>
+    <t>ANF</t>
+  </si>
+  <si>
+    <t>SLN</t>
+  </si>
+  <si>
+    <t>BHVN</t>
+  </si>
+  <si>
+    <t>DYN</t>
+  </si>
+  <si>
+    <t>POWL</t>
+  </si>
+  <si>
+    <t>EWTX</t>
+  </si>
+  <si>
+    <t>CLS</t>
+  </si>
+  <si>
+    <t>CBAY</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>XPO</t>
+  </si>
+  <si>
+    <t>QUIK</t>
+  </si>
+  <si>
+    <t>KAMN</t>
+  </si>
+  <si>
+    <t>ASPN</t>
+  </si>
+  <si>
+    <t>KURA</t>
+  </si>
+  <si>
+    <t>ACMR</t>
+  </si>
+  <si>
+    <t>EVER</t>
+  </si>
+  <si>
+    <t>CELH</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>BVN</t>
+  </si>
+  <si>
+    <t>VST</t>
+  </si>
+  <si>
+    <t>SKYW</t>
+  </si>
+  <si>
+    <t>PAY</t>
+  </si>
+  <si>
+    <t>MRUS</t>
+  </si>
+  <si>
+    <t>RXST</t>
+  </si>
+  <si>
+    <t>STRL</t>
+  </si>
+  <si>
+    <t>NMM</t>
+  </si>
+  <si>
+    <t>TREE</t>
+  </si>
+  <si>
+    <t>TARS</t>
+  </si>
+  <si>
     <t>ELF</t>
   </si>
   <si>
-    <t>HTGC</t>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>DFH</t>
+  </si>
+  <si>
+    <t>MMYT</t>
+  </si>
+  <si>
+    <t>BMA</t>
+  </si>
+  <si>
+    <t>NTNX</t>
+  </si>
+  <si>
+    <t>CRWD</t>
+  </si>
+  <si>
+    <t>IDYA</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>IBP</t>
+  </si>
+  <si>
+    <t>CGEM</t>
+  </si>
+  <si>
+    <t>HMST</t>
+  </si>
+  <si>
+    <t>FIX</t>
+  </si>
+  <si>
+    <t>WING</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>FTAI</t>
+  </si>
+  <si>
+    <t>GFF</t>
+  </si>
+  <si>
+    <t>SAIA</t>
+  </si>
+  <si>
+    <t>MEDP</t>
+  </si>
+  <si>
+    <t>SWTX</t>
+  </si>
+  <si>
+    <t>AZEK</t>
+  </si>
+  <si>
+    <t>EME</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>FROG</t>
+  </si>
+  <si>
+    <t>NTRA</t>
+  </si>
+  <si>
+    <t>DASH</t>
+  </si>
+  <si>
+    <t>ARHS</t>
+  </si>
+  <si>
+    <t>QTWO</t>
+  </si>
+  <si>
+    <t>TILE</t>
+  </si>
+  <si>
+    <t>PSTG</t>
+  </si>
+  <si>
+    <t>TDW</t>
+  </si>
+  <si>
+    <t>SPOT</t>
+  </si>
+  <si>
+    <t>SFM</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>TOL</t>
+  </si>
+  <si>
+    <t>VITL</t>
+  </si>
+  <si>
+    <t>KRTX</t>
+  </si>
+  <si>
+    <t>FRPT</t>
+  </si>
+  <si>
+    <t>NVO</t>
+  </si>
+  <si>
+    <t>AWI</t>
+  </si>
+  <si>
+    <t>HOOD</t>
+  </si>
+  <si>
+    <t>CYBR</t>
+  </si>
+  <si>
+    <t>ONTO</t>
+  </si>
+  <si>
+    <t>TREX</t>
+  </si>
+  <si>
+    <t>PLAY</t>
+  </si>
+  <si>
+    <t>TRIP</t>
+  </si>
+  <si>
+    <t>BASE</t>
+  </si>
+  <si>
+    <t>GGAL</t>
+  </si>
+  <si>
+    <t>GE</t>
+  </si>
+  <si>
+    <t>ARVN</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>NFLX</t>
+  </si>
+  <si>
+    <t>BLBD</t>
+  </si>
+  <si>
+    <t>COLL</t>
+  </si>
+  <si>
+    <t>LYFT</t>
+  </si>
+  <si>
+    <t>EXP</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>SWBI</t>
+  </si>
+  <si>
+    <t>LRCX</t>
+  </si>
+  <si>
+    <t>TSM</t>
+  </si>
+  <si>
+    <t>ASND</t>
+  </si>
+  <si>
+    <t>RL</t>
+  </si>
+  <si>
+    <t>OWL</t>
+  </si>
+  <si>
+    <t>WDC</t>
+  </si>
+  <si>
+    <t>WIX</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>GNK</t>
+  </si>
+  <si>
+    <t>ASML</t>
+  </si>
+  <si>
+    <t>KLAC</t>
+  </si>
+  <si>
+    <t>ALSN</t>
+  </si>
+  <si>
+    <t>CVLT</t>
+  </si>
+  <si>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t>SPXC</t>
+  </si>
+  <si>
+    <t>ENTG</t>
+  </si>
+  <si>
+    <t>AXON</t>
+  </si>
+  <si>
+    <t>KB</t>
+  </si>
+  <si>
+    <t>ANAB</t>
+  </si>
+  <si>
+    <t>TXRH</t>
+  </si>
+  <si>
+    <t>QCOM</t>
+  </si>
+  <si>
+    <t>ALRM</t>
+  </si>
+  <si>
+    <t>OKTA</t>
+  </si>
+  <si>
+    <t>AXP</t>
+  </si>
+  <si>
+    <t>CAT</t>
+  </si>
+  <si>
+    <t>VCEL</t>
+  </si>
+  <si>
+    <t>RVMD</t>
+  </si>
+  <si>
+    <t>IBKR</t>
+  </si>
+  <si>
+    <t>TFII</t>
+  </si>
+  <si>
+    <t>REVG</t>
+  </si>
+  <si>
+    <t>STEP</t>
+  </si>
+  <si>
+    <t>CTLT</t>
+  </si>
+  <si>
+    <t>TCOM</t>
+  </si>
+  <si>
+    <t>VEEV</t>
+  </si>
+  <si>
+    <t>CI</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
   </si>
   <si>
     <t>Technology</t>
   </si>
   <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
     <t>Consumer Defensive</t>
   </si>
   <si>
-    <t>Financial Services</t>
+    <t>Basic Materials</t>
+  </si>
+  <si>
+    <t>Utilities</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Biotechnology</t>
+  </si>
+  <si>
+    <t>Insurance—Property &amp; Casualty</t>
   </si>
   <si>
     <t>Computer Hardware</t>
   </si>
   <si>
+    <t>Software—Application</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>Auto &amp; Truck Dealerships</t>
+  </si>
+  <si>
+    <t>Financial Data &amp; Stock Exchanges</t>
+  </si>
+  <si>
+    <t>Electrical Equipment &amp; Parts</t>
+  </si>
+  <si>
+    <t>Shell Companies</t>
+  </si>
+  <si>
+    <t>Internet Content &amp; Information</t>
+  </si>
+  <si>
+    <t>Apparel Retail</t>
+  </si>
+  <si>
+    <t>Electronic Components</t>
+  </si>
+  <si>
+    <t>Auto Parts</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Trucking</t>
+  </si>
+  <si>
+    <t>Aerospace &amp; Defense</t>
+  </si>
+  <si>
+    <t>Building Products &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Semiconductor Equipment &amp; Materials</t>
+  </si>
+  <si>
+    <t>Beverages - Non-Alcoholic</t>
+  </si>
+  <si>
+    <t>Other Precious Metals &amp; Mining</t>
+  </si>
+  <si>
+    <t>Utilities - Independent Power Producers</t>
+  </si>
+  <si>
+    <t>Airlines</t>
+  </si>
+  <si>
+    <t>Software—Infrastructure</t>
+  </si>
+  <si>
+    <t>Medical Devices</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Construction</t>
+  </si>
+  <si>
+    <t>Marine Shipping</t>
+  </si>
+  <si>
+    <t>Financial Conglomerates</t>
+  </si>
+  <si>
     <t>Household &amp; Personal Products</t>
   </si>
   <si>
+    <t>Residential Construction</t>
+  </si>
+  <si>
+    <t>Travel Services</t>
+  </si>
+  <si>
+    <t>Banks—Regional</t>
+  </si>
+  <si>
+    <t>Software - Infrastructure</t>
+  </si>
+  <si>
+    <t>Banks - Regional</t>
+  </si>
+  <si>
+    <t>Restaurants</t>
+  </si>
+  <si>
+    <t>Rental &amp; Leasing Services</t>
+  </si>
+  <si>
+    <t>Conglomerates</t>
+  </si>
+  <si>
+    <t>Diagnostics &amp; Research</t>
+  </si>
+  <si>
+    <t>Footwear &amp; Accessories</t>
+  </si>
+  <si>
+    <t>Home Improvement Retail</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Equipment &amp; Services</t>
+  </si>
+  <si>
+    <t>Grocery Stores</t>
+  </si>
+  <si>
+    <t>Farm Products</t>
+  </si>
+  <si>
+    <t>Packaged Foods</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
+    <t>Specialty Industrial Machinery</t>
+  </si>
+  <si>
+    <t>Auto Manufacturers</t>
+  </si>
+  <si>
+    <t>Drug Manufacturers—Specialty &amp; Generic</t>
+  </si>
+  <si>
+    <t>Building Materials</t>
+  </si>
+  <si>
+    <t>Apparel Manufacturing</t>
+  </si>
+  <si>
     <t>Asset Management</t>
   </si>
   <si>
+    <t>Software - Application</t>
+  </si>
+  <si>
+    <t>Credit Services</t>
+  </si>
+  <si>
+    <t>Farm &amp; Heavy Construction Machinery</t>
+  </si>
+  <si>
+    <t>Drug Manufacturers - Specialty &amp; Generic</t>
+  </si>
+  <si>
+    <t>Health Information Services</t>
+  </si>
+  <si>
+    <t>Healthcare Plans</t>
+  </si>
+  <si>
+    <t>2014-10-27</t>
+  </si>
+  <si>
+    <t>2020-10-28</t>
+  </si>
+  <si>
     <t>2007-03-29</t>
   </si>
   <si>
+    <t>1998-06-11</t>
+  </si>
+  <si>
+    <t>2021-05-14</t>
+  </si>
+  <si>
+    <t>2020-10-02</t>
+  </si>
+  <si>
+    <t>2016-11-16</t>
+  </si>
+  <si>
+    <t>2017-04-28</t>
+  </si>
+  <si>
+    <t>2015-05-11</t>
+  </si>
+  <si>
+    <t>2018-09-21</t>
+  </si>
+  <si>
+    <t>2021-04-14</t>
+  </si>
+  <si>
+    <t>2015-06-17</t>
+  </si>
+  <si>
+    <t>2019-02-08</t>
+  </si>
+  <si>
+    <t>2019-06-14</t>
+  </si>
+  <si>
+    <t>2018-08-02</t>
+  </si>
+  <si>
+    <t>2021-09-30</t>
+  </si>
+  <si>
+    <t>2018-04-19</t>
+  </si>
+  <si>
+    <t>2013-10-10</t>
+  </si>
+  <si>
+    <t>2011-11-04</t>
+  </si>
+  <si>
+    <t>1996-09-26</t>
+  </si>
+  <si>
+    <t>2020-09-08</t>
+  </si>
+  <si>
+    <t>2022-09-23</t>
+  </si>
+  <si>
+    <t>2020-09-17</t>
+  </si>
+  <si>
+    <t>1980-03-17</t>
+  </si>
+  <si>
+    <t>2021-03-26</t>
+  </si>
+  <si>
+    <t>1998-06-30</t>
+  </si>
+  <si>
+    <t>2014-02-03</t>
+  </si>
+  <si>
+    <t>2021-04-15</t>
+  </si>
+  <si>
+    <t>1982-09-20</t>
+  </si>
+  <si>
+    <t>1999-01-22</t>
+  </si>
+  <si>
+    <t>2003-10-07</t>
+  </si>
+  <si>
+    <t>1999-10-18</t>
+  </si>
+  <si>
+    <t>2014-06-13</t>
+  </si>
+  <si>
+    <t>2015-09-16</t>
+  </si>
+  <si>
+    <t>2017-11-02</t>
+  </si>
+  <si>
+    <t>2018-06-28</t>
+  </si>
+  <si>
+    <t>2007-01-22</t>
+  </si>
+  <si>
+    <t>2016-08-17</t>
+  </si>
+  <si>
+    <t>1996-05-15</t>
+  </si>
+  <si>
+    <t>2016-10-05</t>
+  </si>
+  <si>
+    <t>1986-06-26</t>
+  </si>
+  <si>
+    <t>2021-05-26</t>
+  </si>
+  <si>
+    <t>2016-05-19</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>1991-07-12</t>
+  </si>
+  <si>
+    <t>2007-11-13</t>
+  </si>
+  <si>
+    <t>2008-08-12</t>
+  </si>
+  <si>
+    <t>2020-10-16</t>
+  </si>
+  <si>
     <t>2016-09-22</t>
   </si>
   <si>
-    <t>2005-06-09</t>
+    <t>2021-01-21</t>
+  </si>
+  <si>
+    <t>2010-08-12</t>
+  </si>
+  <si>
+    <t>2006-03-27</t>
+  </si>
+  <si>
+    <t>2016-09-30</t>
+  </si>
+  <si>
+    <t>2019-06-12</t>
+  </si>
+  <si>
+    <t>2019-05-23</t>
+  </si>
+  <si>
+    <t>2020-09-30</t>
+  </si>
+  <si>
+    <t>2014-02-13</t>
+  </si>
+  <si>
+    <t>2021-01-08</t>
+  </si>
+  <si>
+    <t>2012-02-10</t>
+  </si>
+  <si>
+    <t>1997-06-27</t>
+  </si>
+  <si>
+    <t>2015-06-12</t>
+  </si>
+  <si>
+    <t>2015-05-14</t>
+  </si>
+  <si>
+    <t>1973-05-03</t>
+  </si>
+  <si>
+    <t>2002-09-11</t>
+  </si>
+  <si>
+    <t>2016-08-11</t>
+  </si>
+  <si>
+    <t>2019-09-13</t>
+  </si>
+  <si>
+    <t>2020-06-12</t>
+  </si>
+  <si>
+    <t>1995-01-10</t>
+  </si>
+  <si>
+    <t>1993-10-15</t>
+  </si>
+  <si>
+    <t>2005-06-28</t>
+  </si>
+  <si>
+    <t>2020-09-16</t>
+  </si>
+  <si>
+    <t>2015-07-01</t>
+  </si>
+  <si>
+    <t>2020-12-09</t>
+  </si>
+  <si>
+    <t>2021-11-04</t>
+  </si>
+  <si>
+    <t>2014-03-20</t>
+  </si>
+  <si>
+    <t>1983-04-14</t>
+  </si>
+  <si>
+    <t>2015-10-06</t>
+  </si>
+  <si>
+    <t>2018-04-03</t>
+  </si>
+  <si>
+    <t>2013-08-01</t>
+  </si>
+  <si>
+    <t>2003-12-02</t>
+  </si>
+  <si>
+    <t>1986-07-08</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>2019-06-28</t>
+  </si>
+  <si>
+    <t>2014-11-07</t>
+  </si>
+  <si>
+    <t>1981-04-30</t>
+  </si>
+  <si>
+    <t>2006-10-18</t>
+  </si>
+  <si>
+    <t>2021-07-29</t>
+  </si>
+  <si>
+    <t>2014-09-24</t>
+  </si>
+  <si>
+    <t>2019-10-28</t>
+  </si>
+  <si>
+    <t>1999-04-08</t>
+  </si>
+  <si>
+    <t>2014-10-10</t>
+  </si>
+  <si>
+    <t>2011-12-07</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>2000-07-25</t>
+  </si>
+  <si>
+    <t>1962-01-02</t>
+  </si>
+  <si>
+    <t>2018-09-27</t>
+  </si>
+  <si>
+    <t>1997-12-18</t>
+  </si>
+  <si>
+    <t>2002-05-23</t>
+  </si>
+  <si>
+    <t>2015-05-07</t>
+  </si>
+  <si>
+    <t>2019-03-29</t>
+  </si>
+  <si>
+    <t>1994-04-12</t>
+  </si>
+  <si>
+    <t>2009-08-06</t>
+  </si>
+  <si>
+    <t>1999-08-17</t>
+  </si>
+  <si>
+    <t>1984-05-04</t>
+  </si>
+  <si>
+    <t>1997-10-09</t>
+  </si>
+  <si>
+    <t>2015-01-28</t>
+  </si>
+  <si>
+    <t>1997-06-12</t>
+  </si>
+  <si>
+    <t>2020-12-14</t>
+  </si>
+  <si>
+    <t>1978-10-31</t>
+  </si>
+  <si>
+    <t>2013-11-06</t>
+  </si>
+  <si>
+    <t>2014-07-15</t>
+  </si>
+  <si>
+    <t>1995-03-15</t>
+  </si>
+  <si>
+    <t>1980-10-08</t>
+  </si>
+  <si>
+    <t>2012-03-15</t>
+  </si>
+  <si>
+    <t>2006-09-22</t>
+  </si>
+  <si>
+    <t>2000-07-11</t>
+  </si>
+  <si>
+    <t>2001-06-19</t>
+  </si>
+  <si>
+    <t>2001-11-13</t>
+  </si>
+  <si>
+    <t>2017-01-26</t>
+  </si>
+  <si>
+    <t>2004-10-05</t>
+  </si>
+  <si>
+    <t>1991-12-13</t>
+  </si>
+  <si>
+    <t>2015-06-26</t>
+  </si>
+  <si>
+    <t>2017-04-07</t>
+  </si>
+  <si>
+    <t>1972-06-01</t>
+  </si>
+  <si>
+    <t>1997-02-04</t>
+  </si>
+  <si>
+    <t>2020-02-13</t>
+  </si>
+  <si>
+    <t>2007-05-04</t>
+  </si>
+  <si>
+    <t>2005-11-15</t>
+  </si>
+  <si>
+    <t>2017-01-27</t>
+  </si>
+  <si>
+    <t>2014-07-31</t>
+  </si>
+  <si>
+    <t>2003-12-09</t>
+  </si>
+  <si>
+    <t>2013-10-16</t>
+  </si>
+  <si>
+    <t>1982-03-31</t>
   </si>
 </sst>
 </file>
@@ -464,7 +1454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -531,58 +1521,58 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>162</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>172</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>228</v>
       </c>
       <c r="E2">
-        <v>1085.415649414062</v>
+        <v>44.58000183105469</v>
       </c>
       <c r="F2">
-        <v>14819195.63333333</v>
+        <v>550617.3333333334</v>
       </c>
       <c r="G2">
-        <v>637.4673095703125</v>
+        <v>20.6223999786377</v>
       </c>
       <c r="H2">
-        <v>394.1328362019857</v>
+        <v>10.78762665748596</v>
       </c>
       <c r="I2">
-        <v>361.5986769866943</v>
+        <v>10.08331997871399</v>
       </c>
       <c r="J2">
-        <v>282.0150992584229</v>
+        <v>7.98569498538971</v>
       </c>
       <c r="K2">
-        <v>91.75</v>
+        <v>2.910000085830688</v>
       </c>
       <c r="L2">
-        <v>1159.760009765625</v>
+        <v>44.93000030517578</v>
       </c>
       <c r="M2">
-        <v>323.7422117030001</v>
+        <v>736.397794918866</v>
       </c>
       <c r="N2">
-        <v>1073.803001065657</v>
+        <v>1431.95878062419</v>
       </c>
       <c r="O2">
-        <v>557.7662072666031</v>
+        <v>711.7278402235113</v>
       </c>
       <c r="P2">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>115</v>
+        <v>-9</v>
       </c>
       <c r="R2">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>29.918</v>
+        <v>-224.629</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -590,58 +1580,58 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>173</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>229</v>
       </c>
       <c r="E3">
-        <v>193.6100006103516</v>
+        <v>43.70999908447266</v>
       </c>
       <c r="F3">
-        <v>1440388.8</v>
+        <v>1059819.8</v>
       </c>
       <c r="G3">
-        <v>170.4341995239258</v>
+        <v>16.10260000228882</v>
       </c>
       <c r="H3">
-        <v>135.7615998840332</v>
+        <v>12.06610003153483</v>
       </c>
       <c r="I3">
-        <v>129.5238999176025</v>
+        <v>11.2566250038147</v>
       </c>
       <c r="J3">
-        <v>119.4194500350952</v>
+        <v>9.070125000476837</v>
       </c>
       <c r="K3">
-        <v>72.01999664306641</v>
+        <v>3.539999961853027</v>
       </c>
       <c r="L3">
-        <v>217.3999938964844</v>
+        <v>45.77000045776367</v>
       </c>
       <c r="M3">
-        <v>52.56895057709545</v>
+        <v>308.5046716227429</v>
       </c>
       <c r="N3">
-        <v>168.828116682495</v>
+        <v>1124.369745149233</v>
       </c>
       <c r="O3">
-        <v>179.6599058749279</v>
+        <v>641.2145619888279</v>
       </c>
       <c r="P3">
-        <v>35</v>
+        <v>-60</v>
       </c>
       <c r="Q3">
-        <v>171</v>
+        <v>-51</v>
       </c>
       <c r="R3">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="S3">
-        <v>25.889</v>
+        <v>-44.210997</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -649,58 +1639,8306 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E4">
+        <v>1163</v>
+      </c>
+      <c r="F4">
+        <v>14699776.5</v>
+      </c>
+      <c r="G4">
+        <v>654.7943957519532</v>
+      </c>
+      <c r="H4">
+        <v>399.4962649536133</v>
+      </c>
+      <c r="I4">
+        <v>366.5495986175537</v>
+      </c>
+      <c r="J4">
+        <v>285.4056993103027</v>
+      </c>
+      <c r="K4">
+        <v>91.75</v>
+      </c>
+      <c r="L4">
+        <v>1163</v>
+      </c>
+      <c r="M4">
+        <v>326.5541999027333</v>
+      </c>
+      <c r="N4">
+        <v>1167.574931880109</v>
+      </c>
+      <c r="O4">
+        <v>600.1249239998278</v>
+      </c>
+      <c r="P4">
+        <v>62</v>
+      </c>
+      <c r="Q4">
+        <v>115</v>
+      </c>
+      <c r="R4">
+        <v>73</v>
+      </c>
+      <c r="S4">
+        <v>29.918</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D5" t="s">
+        <v>231</v>
+      </c>
+      <c r="E5">
+        <v>1593.349975585938</v>
+      </c>
+      <c r="F5">
+        <v>2238723.933333333</v>
+      </c>
+      <c r="G5">
+        <v>721.5174005126953</v>
+      </c>
+      <c r="H5">
+        <v>523.6402673339844</v>
+      </c>
+      <c r="I5">
+        <v>482.9678999328613</v>
+      </c>
+      <c r="J5">
+        <v>413.8070500183105</v>
+      </c>
+      <c r="K5">
+        <v>227.5500030517578</v>
+      </c>
+      <c r="L5">
+        <v>1593.349975585938</v>
+      </c>
+      <c r="M5">
+        <v>165.8285818325637</v>
+      </c>
+      <c r="N5">
+        <v>600.2197118070436</v>
+      </c>
+      <c r="O5">
+        <v>439.8682163652454</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>-4</v>
+      </c>
+      <c r="S5">
+        <v>48.166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D6" t="s">
+        <v>232</v>
+      </c>
+      <c r="E6">
+        <v>44.18999862670898</v>
+      </c>
+      <c r="F6">
+        <v>1173467.833333333</v>
+      </c>
+      <c r="G6">
+        <v>33.46899967193603</v>
+      </c>
+      <c r="H6">
+        <v>20.7715332476298</v>
+      </c>
+      <c r="I6">
+        <v>19.20304993391037</v>
+      </c>
+      <c r="J6">
+        <v>15.3780499792099</v>
+      </c>
+      <c r="K6">
+        <v>6.110000133514404</v>
+      </c>
+      <c r="L6">
+        <v>49.13999938964844</v>
+      </c>
+      <c r="M6">
+        <v>222.5547389922141</v>
+      </c>
+      <c r="N6">
+        <v>519.7755668644058</v>
+      </c>
+      <c r="O6">
+        <v>377.2882339330976</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>38</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>-89.59300500000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D7" t="s">
+        <v>233</v>
+      </c>
+      <c r="E7">
+        <v>24.34000015258789</v>
+      </c>
+      <c r="F7">
+        <v>900510.2333333333</v>
+      </c>
+      <c r="G7">
+        <v>19.23200002670288</v>
+      </c>
+      <c r="H7">
+        <v>11.63056667963664</v>
+      </c>
+      <c r="I7">
+        <v>10.37480000019074</v>
+      </c>
+      <c r="J7">
+        <v>8.502574996948242</v>
+      </c>
+      <c r="K7">
+        <v>4.699999809265137</v>
+      </c>
+      <c r="L7">
+        <v>27.34000015258789</v>
+      </c>
+      <c r="M7">
+        <v>214.8771033962464</v>
+      </c>
+      <c r="N7">
+        <v>416.7728228334332</v>
+      </c>
+      <c r="O7">
+        <v>375.1647236545627</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>44</v>
+      </c>
+      <c r="R7">
+        <v>-16</v>
+      </c>
+      <c r="S7">
+        <v>-150.60401</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D8" t="s">
+        <v>234</v>
+      </c>
+      <c r="E8">
+        <v>16.48999977111816</v>
+      </c>
+      <c r="F8">
+        <v>43203608.8</v>
+      </c>
+      <c r="G8">
+        <v>12.46669998168945</v>
+      </c>
+      <c r="H8">
+        <v>7.9014333375295</v>
+      </c>
+      <c r="I8">
+        <v>7.209575003385543</v>
+      </c>
+      <c r="J8">
+        <v>5.890100002288818</v>
+      </c>
+      <c r="K8">
+        <v>2.289999961853027</v>
+      </c>
+      <c r="L8">
+        <v>20.88999938964844</v>
+      </c>
+      <c r="M8">
+        <v>59.47775171928846</v>
+      </c>
+      <c r="N8">
+        <v>620.0873382449644</v>
+      </c>
+      <c r="O8">
+        <v>366.2310721447489</v>
+      </c>
+      <c r="P8">
+        <v>-132</v>
+      </c>
+      <c r="Q8">
+        <v>-1</v>
+      </c>
+      <c r="R8">
+        <v>39</v>
+      </c>
+      <c r="S8">
+        <v>-12.244</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C9" t="s">
+        <v>177</v>
+      </c>
+      <c r="D9" t="s">
+        <v>235</v>
+      </c>
+      <c r="E9">
+        <v>76.27999877929688</v>
+      </c>
+      <c r="F9">
+        <v>8518827.066666666</v>
+      </c>
+      <c r="G9">
+        <v>55.25079986572266</v>
+      </c>
+      <c r="H9">
+        <v>45.04946659088134</v>
+      </c>
+      <c r="I9">
+        <v>41.43889993190766</v>
+      </c>
+      <c r="J9">
+        <v>35.55109991550446</v>
+      </c>
+      <c r="K9">
+        <v>6.929999828338623</v>
+      </c>
+      <c r="L9">
+        <v>85.30000305175781</v>
+      </c>
+      <c r="M9">
+        <v>89.46845990924508</v>
+      </c>
+      <c r="N9">
+        <v>981.9857690152169</v>
+      </c>
+      <c r="O9">
+        <v>361.8132251418559</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>-13</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10" t="s">
         <v>27</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D10" t="s">
+        <v>236</v>
+      </c>
+      <c r="E10">
+        <v>63.66999816894531</v>
+      </c>
+      <c r="F10">
+        <v>16636080.43333333</v>
+      </c>
+      <c r="G10">
+        <v>44.01859977722168</v>
+      </c>
+      <c r="H10">
+        <v>31.23759316762288</v>
+      </c>
+      <c r="I10">
+        <v>27.82099987030029</v>
+      </c>
+      <c r="J10">
+        <v>24.06007489204407</v>
+      </c>
+      <c r="K10">
+        <v>13.10999965667725</v>
+      </c>
+      <c r="L10">
+        <v>64.31999969482422</v>
+      </c>
+      <c r="M10">
+        <v>79.30160850031899</v>
+      </c>
+      <c r="N10">
+        <v>379.804038979478</v>
+      </c>
+      <c r="O10">
+        <v>319.2000518134501</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D11" t="s">
+        <v>237</v>
+      </c>
+      <c r="E11">
+        <v>16.09000015258789</v>
+      </c>
+      <c r="F11">
+        <v>433902.7666666667</v>
+      </c>
+      <c r="G11">
+        <v>12.83840002059937</v>
+      </c>
+      <c r="H11">
+        <v>8.035333344141643</v>
+      </c>
+      <c r="I11">
+        <v>7.810900013446808</v>
+      </c>
+      <c r="J11">
+        <v>6.973850002288819</v>
+      </c>
+      <c r="K11">
+        <v>2.829999923706055</v>
+      </c>
+      <c r="L11">
+        <v>18.69000053405762</v>
+      </c>
+      <c r="M11">
+        <v>127.2598916097942</v>
+      </c>
+      <c r="N11">
+        <v>377.4480919579784</v>
+      </c>
+      <c r="O11">
+        <v>301.1162718045305</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>14</v>
+      </c>
+      <c r="S11">
+        <v>-20.387</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>163</v>
+      </c>
+      <c r="C12" t="s">
+        <v>178</v>
+      </c>
+      <c r="D12" t="s">
+        <v>238</v>
+      </c>
+      <c r="E12">
+        <v>256.1400146484375</v>
+      </c>
+      <c r="F12">
+        <v>15183077.93333333</v>
+      </c>
+      <c r="G12">
+        <v>162.2344010925293</v>
+      </c>
+      <c r="H12">
+        <v>118.6030002848307</v>
+      </c>
+      <c r="I12">
+        <v>108.0596502304077</v>
+      </c>
+      <c r="J12">
+        <v>93.67270011901856</v>
+      </c>
+      <c r="K12">
+        <v>48.4900016784668</v>
+      </c>
+      <c r="L12">
+        <v>256.6199951171875</v>
+      </c>
+      <c r="M12">
+        <v>74.69651014768826</v>
+      </c>
+      <c r="N12">
+        <v>297.3010854638914</v>
+      </c>
+      <c r="O12">
+        <v>297.5214253507081</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>-103</v>
+      </c>
+      <c r="R12">
+        <v>41</v>
+      </c>
+      <c r="S12">
+        <v>1.617</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13" t="s">
         <v>30</v>
       </c>
-      <c r="E4">
-        <v>18.16500091552734</v>
-      </c>
-      <c r="F4">
-        <v>1052424.7</v>
-      </c>
-      <c r="G4">
-        <v>17.23304351806641</v>
-      </c>
-      <c r="H4">
-        <v>15.93628141403198</v>
-      </c>
-      <c r="I4">
-        <v>15.47844623088837</v>
-      </c>
-      <c r="J4">
-        <v>14.88064412593842</v>
-      </c>
-      <c r="K4">
-        <v>10.24463176727295</v>
-      </c>
-      <c r="L4">
-        <v>18.39999961853027</v>
-      </c>
-      <c r="M4">
-        <v>21.68225148065475</v>
-      </c>
-      <c r="N4">
-        <v>71.52562697174625</v>
-      </c>
-      <c r="O4">
-        <v>124.5966768115443</v>
-      </c>
-      <c r="P4">
+      <c r="B13" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" t="s">
+        <v>172</v>
+      </c>
+      <c r="D13" t="s">
+        <v>239</v>
+      </c>
+      <c r="E13">
+        <v>36.45000076293945</v>
+      </c>
+      <c r="F13">
+        <v>1108519.2</v>
+      </c>
+      <c r="G13">
+        <v>27.20419998168945</v>
+      </c>
+      <c r="H13">
+        <v>17.97709997812907</v>
+      </c>
+      <c r="I13">
+        <v>16.298474984169</v>
+      </c>
+      <c r="J13">
+        <v>13.71552499055862</v>
+      </c>
+      <c r="K13">
+        <v>6.840000152587891</v>
+      </c>
+      <c r="L13">
+        <v>38.54999923706055</v>
+      </c>
+      <c r="M13">
+        <v>116.4489336856567</v>
+      </c>
+      <c r="N13">
+        <v>353.3582205955459</v>
+      </c>
+      <c r="O13">
+        <v>297.3941225903973</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>-13</v>
+      </c>
+      <c r="R13">
+        <v>17</v>
+      </c>
+      <c r="S13">
+        <v>-33.17899999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
+        <v>162</v>
+      </c>
+      <c r="C14" t="s">
+        <v>172</v>
+      </c>
+      <c r="D14" t="s">
+        <v>240</v>
+      </c>
+      <c r="E14">
+        <v>23.01000022888184</v>
+      </c>
+      <c r="F14">
+        <v>1565899.466666667</v>
+      </c>
+      <c r="G14">
+        <v>21.17620004653931</v>
+      </c>
+      <c r="H14">
+        <v>12.04872001012166</v>
+      </c>
+      <c r="I14">
+        <v>10.91306000947952</v>
+      </c>
+      <c r="J14">
+        <v>9.328255007266998</v>
+      </c>
+      <c r="K14">
+        <v>3.289999961853027</v>
+      </c>
+      <c r="L14">
+        <v>23.01000022888184</v>
+      </c>
+      <c r="M14">
+        <v>130.1000022888184</v>
+      </c>
+      <c r="N14">
+        <v>238.3823468157166</v>
+      </c>
+      <c r="O14">
+        <v>294.945154330356</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>-44</v>
+      </c>
+      <c r="R14">
+        <v>-78</v>
+      </c>
+      <c r="S14">
+        <v>-284.324</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>241</v>
+      </c>
+      <c r="E15">
+        <v>32.45000076293945</v>
+      </c>
+      <c r="F15">
+        <v>4421308.6</v>
+      </c>
+      <c r="G15">
+        <v>23.06925994873047</v>
+      </c>
+      <c r="H15">
+        <v>16.83450000762939</v>
+      </c>
+      <c r="I15">
+        <v>15.05528500318527</v>
+      </c>
+      <c r="J15">
+        <v>13.10696000814438</v>
+      </c>
+      <c r="K15">
+        <v>7.355000019073486</v>
+      </c>
+      <c r="L15">
+        <v>34.4900016784668</v>
+      </c>
+      <c r="M15">
+        <v>65.64574022554422</v>
+      </c>
+      <c r="N15">
+        <v>325.8530347807031</v>
+      </c>
+      <c r="O15">
+        <v>294.4241404879819</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
+        <v>166</v>
+      </c>
+      <c r="C16" t="s">
+        <v>179</v>
+      </c>
+      <c r="D16" t="s">
+        <v>242</v>
+      </c>
+      <c r="E16">
+        <v>72.31999969482422</v>
+      </c>
+      <c r="F16">
+        <v>8480220.4</v>
+      </c>
+      <c r="G16">
+        <v>58.70979988098144</v>
+      </c>
+      <c r="H16">
+        <v>46.44733332316081</v>
+      </c>
+      <c r="I16">
+        <v>40.95184999465943</v>
+      </c>
+      <c r="J16">
+        <v>35.82805003166199</v>
+      </c>
+      <c r="K16">
+        <v>12.18000030517578</v>
+      </c>
+      <c r="L16">
+        <v>72.31999969482422</v>
+      </c>
+      <c r="M16">
+        <v>53.41535984556061</v>
+      </c>
+      <c r="N16">
+        <v>442.9429530912508</v>
+      </c>
+      <c r="O16">
+        <v>270.3945376166873</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>-3075</v>
+      </c>
+      <c r="R16">
+        <v>7</v>
+      </c>
+      <c r="S16">
+        <v>26.626</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>163</v>
+      </c>
+      <c r="C17" t="s">
+        <v>180</v>
+      </c>
+      <c r="D17" t="s">
+        <v>243</v>
+      </c>
+      <c r="E17">
+        <v>40.18999862670898</v>
+      </c>
+      <c r="F17">
+        <v>2282761.866666667</v>
+      </c>
+      <c r="G17">
+        <v>36.6583999633789</v>
+      </c>
+      <c r="H17">
+        <v>23.00713336308797</v>
+      </c>
+      <c r="I17">
+        <v>20.72550001621246</v>
+      </c>
+      <c r="J17">
+        <v>17.65230002880097</v>
+      </c>
+      <c r="K17">
+        <v>12.46000003814697</v>
+      </c>
+      <c r="L17">
+        <v>50.75</v>
+      </c>
+      <c r="M17">
+        <v>134.0710451259578</v>
+      </c>
+      <c r="N17">
+        <v>221.2629727529688</v>
+      </c>
+      <c r="O17">
+        <v>268.7912220627008</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>250</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C18" t="s">
+        <v>172</v>
+      </c>
+      <c r="D18" t="s">
+        <v>244</v>
+      </c>
+      <c r="E18">
+        <v>18.17000007629395</v>
+      </c>
+      <c r="F18">
+        <v>3292641.666666667</v>
+      </c>
+      <c r="G18">
+        <v>13.89620002746582</v>
+      </c>
+      <c r="H18">
+        <v>9.589833354949951</v>
+      </c>
+      <c r="I18">
+        <v>9.061450021266937</v>
+      </c>
+      <c r="J18">
+        <v>7.866350016593933</v>
+      </c>
+      <c r="K18">
+        <v>3.740000009536743</v>
+      </c>
+      <c r="L18">
+        <v>18.17000007629395</v>
+      </c>
+      <c r="M18">
+        <v>157.7304905632914</v>
+      </c>
+      <c r="N18">
+        <v>385.8288778064624</v>
+      </c>
+      <c r="O18">
+        <v>268.5841388930559</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>-71</v>
+      </c>
+      <c r="R18">
+        <v>20</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C19" t="s">
+        <v>172</v>
+      </c>
+      <c r="D19" t="s">
+        <v>245</v>
+      </c>
+      <c r="E19">
+        <v>17.60000038146973</v>
+      </c>
+      <c r="F19">
+        <v>1686600.066666667</v>
+      </c>
+      <c r="G19">
+        <v>14.96640005111694</v>
+      </c>
+      <c r="H19">
+        <v>9.095000003178914</v>
+      </c>
+      <c r="I19">
+        <v>8.112100009918214</v>
+      </c>
+      <c r="J19">
+        <v>6.957650001049042</v>
+      </c>
+      <c r="K19">
+        <v>4.480000019073486</v>
+      </c>
+      <c r="L19">
+        <v>21.46999931335449</v>
+      </c>
+      <c r="M19">
+        <v>102.0665936209809</v>
+      </c>
+      <c r="N19">
+        <v>177.6025229949825</v>
+      </c>
+      <c r="O19">
+        <v>265.3720101574709</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>-12</v>
+      </c>
+      <c r="S19">
+        <v>-6.1490003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>167</v>
+      </c>
+      <c r="C20" t="s">
+        <v>181</v>
+      </c>
+      <c r="D20" t="s">
+        <v>246</v>
+      </c>
+      <c r="E20">
+        <v>18.57999992370605</v>
+      </c>
+      <c r="F20">
+        <v>711389.3666666667</v>
+      </c>
+      <c r="G20">
+        <v>15.33520004272461</v>
+      </c>
+      <c r="H20">
+        <v>12.97966665267944</v>
+      </c>
+      <c r="I20">
+        <v>11.28889998435974</v>
+      </c>
+      <c r="J20">
+        <v>9.845799987316132</v>
+      </c>
+      <c r="K20">
+        <v>2.970000028610229</v>
+      </c>
+      <c r="L20">
+        <v>18.97999954223633</v>
+      </c>
+      <c r="M20">
+        <v>64.2793919925932</v>
+      </c>
+      <c r="N20">
+        <v>264.3137308067197</v>
+      </c>
+      <c r="O20">
+        <v>265.3218362611832</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>-314</v>
+      </c>
+      <c r="R20">
+        <v>-2</v>
+      </c>
+      <c r="S20">
+        <v>-567.073</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
+        <v>165</v>
+      </c>
+      <c r="C21" t="s">
+        <v>182</v>
+      </c>
+      <c r="D21" t="s">
+        <v>247</v>
+      </c>
+      <c r="E21">
+        <v>120.5599975585938</v>
+      </c>
+      <c r="F21">
+        <v>1859721.4</v>
+      </c>
+      <c r="G21">
+        <v>110.1658003234863</v>
+      </c>
+      <c r="H21">
+        <v>78.45293342590332</v>
+      </c>
+      <c r="I21">
+        <v>67.80880009651185</v>
+      </c>
+      <c r="J21">
+        <v>57.73330009460449</v>
+      </c>
+      <c r="K21">
+        <v>21.82999992370605</v>
+      </c>
+      <c r="L21">
+        <v>139.9499969482422</v>
+      </c>
+      <c r="M21">
+        <v>53.2867072086767</v>
+      </c>
+      <c r="N21">
+        <v>353.2330670287474</v>
+      </c>
+      <c r="O21">
+        <v>264.1936611837056</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>-99</v>
+      </c>
+      <c r="R21">
+        <v>13</v>
+      </c>
+      <c r="S21">
+        <v>38.189998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
+        <v>162</v>
+      </c>
+      <c r="C22" t="s">
+        <v>172</v>
+      </c>
+      <c r="D22" t="s">
+        <v>248</v>
+      </c>
+      <c r="E22">
+        <v>25.89999961853027</v>
+      </c>
+      <c r="F22">
+        <v>300268.6666666667</v>
+      </c>
+      <c r="G22">
+        <v>21.38440002441406</v>
+      </c>
+      <c r="H22">
+        <v>13.88596667925517</v>
+      </c>
+      <c r="I22">
+        <v>11.87607001304626</v>
+      </c>
+      <c r="J22">
+        <v>10.05494502067566</v>
+      </c>
+      <c r="K22">
+        <v>4.610000133514404</v>
+      </c>
+      <c r="L22">
+        <v>26.25</v>
+      </c>
+      <c r="M22">
+        <v>78.62068702434671</v>
+      </c>
+      <c r="N22">
+        <v>182.7510922486267</v>
+      </c>
+      <c r="O22">
+        <v>263.5040013945285</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>-5</v>
+      </c>
+      <c r="R22">
+        <v>-69</v>
+      </c>
+      <c r="S22">
+        <v>-157.468</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" t="s">
+        <v>162</v>
+      </c>
+      <c r="C23" t="s">
+        <v>172</v>
+      </c>
+      <c r="D23" t="s">
+        <v>249</v>
+      </c>
+      <c r="E23">
+        <v>58.58000183105469</v>
+      </c>
+      <c r="F23">
+        <v>1062579.366666667</v>
+      </c>
+      <c r="G23">
+        <v>47.63940002441407</v>
+      </c>
+      <c r="H23">
+        <v>33.60293336232503</v>
+      </c>
+      <c r="I23">
+        <v>30.80594999313355</v>
+      </c>
+      <c r="J23">
+        <v>27.11034993648529</v>
+      </c>
+      <c r="K23">
+        <v>12.64000034332275</v>
+      </c>
+      <c r="L23">
+        <v>58.65000152587891</v>
+      </c>
+      <c r="M23">
+        <v>77.19298063423896</v>
+      </c>
+      <c r="N23">
+        <v>323.8784596572293</v>
+      </c>
+      <c r="O23">
+        <v>258.9260212432711</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>-84.44199999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s">
+        <v>162</v>
+      </c>
+      <c r="C24" t="s">
+        <v>172</v>
+      </c>
+      <c r="D24" t="s">
+        <v>250</v>
+      </c>
+      <c r="E24">
+        <v>27.10000038146973</v>
+      </c>
+      <c r="F24">
+        <v>1427461.933333333</v>
+      </c>
+      <c r="G24">
+        <v>21.231399974823</v>
+      </c>
+      <c r="H24">
+        <v>13.73883334159851</v>
+      </c>
+      <c r="I24">
+        <v>13.23785002470017</v>
+      </c>
+      <c r="J24">
+        <v>12.03957501649857</v>
+      </c>
+      <c r="K24">
+        <v>6.619999885559082</v>
+      </c>
+      <c r="L24">
+        <v>29.1299991607666</v>
+      </c>
+      <c r="M24">
+        <v>142.3971345414345</v>
+      </c>
+      <c r="N24">
+        <v>114.5684888037655</v>
+      </c>
+      <c r="O24">
+        <v>245.9372855730394</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>-137.30999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="A25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" t="s">
+        <v>166</v>
+      </c>
+      <c r="C25" t="s">
+        <v>179</v>
+      </c>
+      <c r="D25" t="s">
+        <v>251</v>
+      </c>
+      <c r="E25">
+        <v>158.9600067138672</v>
+      </c>
+      <c r="F25">
+        <v>399848.9333333333</v>
+      </c>
+      <c r="G25">
+        <v>122.5891636657715</v>
+      </c>
+      <c r="H25">
+        <v>95.67113382975261</v>
+      </c>
+      <c r="I25">
+        <v>87.1725618171692</v>
+      </c>
+      <c r="J25">
+        <v>76.08034343719483</v>
+      </c>
+      <c r="K25">
+        <v>38.53399658203125</v>
+      </c>
+      <c r="L25">
+        <v>185.2400054931641</v>
+      </c>
+      <c r="M25">
+        <v>85.11549324506163</v>
+      </c>
+      <c r="N25">
+        <v>293.8505480961716</v>
+      </c>
+      <c r="O25">
+        <v>245.6092204753607</v>
+      </c>
+      <c r="P25">
+        <v>1880</v>
+      </c>
+      <c r="Q25">
+        <v>291</v>
+      </c>
+      <c r="R25">
+        <v>-7</v>
+      </c>
+      <c r="S25">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" t="s">
+        <v>162</v>
+      </c>
+      <c r="C26" t="s">
+        <v>172</v>
+      </c>
+      <c r="D26" t="s">
+        <v>252</v>
+      </c>
+      <c r="E26">
+        <v>17.71999931335449</v>
+      </c>
+      <c r="F26">
+        <v>760029.5666666667</v>
+      </c>
+      <c r="G26">
+        <v>15.56299997329712</v>
+      </c>
+      <c r="H26">
+        <v>9.726799987157186</v>
+      </c>
+      <c r="I26">
+        <v>9.304849989414215</v>
+      </c>
+      <c r="J26">
+        <v>8.512774984836579</v>
+      </c>
+      <c r="K26">
+        <v>5.510000228881836</v>
+      </c>
+      <c r="L26">
+        <v>19.96999931335449</v>
+      </c>
+      <c r="M26">
+        <v>154.2324224785558</v>
+      </c>
+      <c r="N26">
+        <v>131.6339750647205</v>
+      </c>
+      <c r="O26">
+        <v>245.4377676420069</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>-30.099002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" t="s">
+        <v>164</v>
+      </c>
+      <c r="C27" t="s">
+        <v>183</v>
+      </c>
+      <c r="D27" t="s">
+        <v>253</v>
+      </c>
+      <c r="E27">
+        <v>45.20000076293945</v>
+      </c>
+      <c r="F27">
+        <v>2615862.666666667</v>
+      </c>
+      <c r="G27">
+        <v>36.04579982757569</v>
+      </c>
+      <c r="H27">
+        <v>28.68279993693034</v>
+      </c>
+      <c r="I27">
+        <v>25.38584992408752</v>
+      </c>
+      <c r="J27">
+        <v>22.25159996032715</v>
+      </c>
+      <c r="K27">
+        <v>10.63000011444092</v>
+      </c>
+      <c r="L27">
+        <v>47.36999893188477</v>
+      </c>
+      <c r="M27">
+        <v>66.23758688905832</v>
+      </c>
+      <c r="N27">
+        <v>280.7919224829084</v>
+      </c>
+      <c r="O27">
+        <v>244.8347714704445</v>
+      </c>
+      <c r="P27">
+        <v>100</v>
+      </c>
+      <c r="Q27">
+        <v>72</v>
+      </c>
+      <c r="R27">
+        <v>5</v>
+      </c>
+      <c r="S27">
+        <v>14.195</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
+      <c r="A28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" t="s">
+        <v>162</v>
+      </c>
+      <c r="C28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D28" t="s">
+        <v>254</v>
+      </c>
+      <c r="E28">
+        <v>32.43999862670898</v>
+      </c>
+      <c r="F28">
+        <v>6021907.233333333</v>
+      </c>
+      <c r="G28">
+        <v>27.3315998840332</v>
+      </c>
+      <c r="H28">
+        <v>20.04079998016357</v>
+      </c>
+      <c r="I28">
+        <v>17.59679998874664</v>
+      </c>
+      <c r="J28">
+        <v>15.36202501773834</v>
+      </c>
+      <c r="K28">
+        <v>7.46999979019165</v>
+      </c>
+      <c r="L28">
+        <v>32.43999862670898</v>
+      </c>
+      <c r="M28">
+        <v>55.36398434183636</v>
+      </c>
+      <c r="N28">
+        <v>257.6626209284309</v>
+      </c>
+      <c r="O28">
+        <v>244.4394881174568</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>-18</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>-64.169997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" t="s">
+        <v>164</v>
+      </c>
+      <c r="C29" t="s">
+        <v>175</v>
+      </c>
+      <c r="D29" t="s">
+        <v>255</v>
+      </c>
+      <c r="E29">
+        <v>61.11000061035156</v>
+      </c>
+      <c r="F29">
+        <v>4999079.4</v>
+      </c>
+      <c r="G29">
+        <v>48.98069969177246</v>
+      </c>
+      <c r="H29">
+        <v>42.61863321940104</v>
+      </c>
+      <c r="I29">
+        <v>38.55994987487793</v>
+      </c>
+      <c r="J29">
+        <v>34.74124992370606</v>
+      </c>
+      <c r="K29">
+        <v>13.52000045776367</v>
+      </c>
+      <c r="L29">
+        <v>63.41999816894531</v>
+      </c>
+      <c r="M29">
+        <v>63.57066277300714</v>
+      </c>
+      <c r="N29">
+        <v>349.6688736145056</v>
+      </c>
+      <c r="O29">
+        <v>239.1610190191871</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>-288</v>
+      </c>
+      <c r="R29">
+        <v>10</v>
+      </c>
+      <c r="S29">
+        <v>22.584</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
+      <c r="A30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" t="s">
+        <v>165</v>
+      </c>
+      <c r="C30" t="s">
+        <v>184</v>
+      </c>
+      <c r="D30" t="s">
+        <v>256</v>
+      </c>
+      <c r="E30">
+        <v>84.97000122070312</v>
+      </c>
+      <c r="F30">
+        <v>1089223.033333333</v>
+      </c>
+      <c r="G30">
+        <v>72.99879997253419</v>
+      </c>
+      <c r="H30">
+        <v>55.95793332417806</v>
+      </c>
+      <c r="I30">
+        <v>50.42110004425049</v>
+      </c>
+      <c r="J30">
+        <v>44.05875007629395</v>
+      </c>
+      <c r="K30">
+        <v>19.5</v>
+      </c>
+      <c r="L30">
+        <v>91.69999694824219</v>
+      </c>
+      <c r="M30">
+        <v>59.23913090102062</v>
+      </c>
+      <c r="N30">
+        <v>282.5754377455465</v>
+      </c>
+      <c r="O30">
+        <v>235.2896894731225</v>
+      </c>
+      <c r="P30">
+        <v>80</v>
+      </c>
+      <c r="Q30">
+        <v>79</v>
+      </c>
+      <c r="R30">
+        <v>-10</v>
+      </c>
+      <c r="S30">
+        <v>36.808</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
+      <c r="A31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" t="s">
+        <v>164</v>
+      </c>
+      <c r="C31" t="s">
+        <v>185</v>
+      </c>
+      <c r="D31" t="s">
+        <v>257</v>
+      </c>
+      <c r="E31">
+        <v>919.1300048828125</v>
+      </c>
+      <c r="F31">
+        <v>57359050.36666667</v>
+      </c>
+      <c r="G31">
+        <v>676.380869140625</v>
+      </c>
+      <c r="H31">
+        <v>530.2164552815756</v>
+      </c>
+      <c r="I31">
+        <v>504.3810458374023</v>
+      </c>
+      <c r="J31">
+        <v>453.5312983703614</v>
+      </c>
+      <c r="K31">
+        <v>242.2023010253906</v>
+      </c>
+      <c r="L31">
+        <v>926.6900024414062</v>
+      </c>
+      <c r="M31">
+        <v>93.48568897052532</v>
+      </c>
+      <c r="N31">
+        <v>279.4885519219151</v>
+      </c>
+      <c r="O31">
+        <v>232.031097001016</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>586</v>
+      </c>
+      <c r="R31">
+        <v>22</v>
+      </c>
+      <c r="S31">
+        <v>91.458</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
+      <c r="A32" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" t="s">
+        <v>166</v>
+      </c>
+      <c r="C32" t="s">
+        <v>186</v>
+      </c>
+      <c r="D32" t="s">
+        <v>258</v>
+      </c>
+      <c r="E32">
+        <v>124.9400024414062</v>
+      </c>
+      <c r="F32">
+        <v>1605044.9</v>
+      </c>
+      <c r="G32">
+        <v>102.8153999328613</v>
+      </c>
+      <c r="H32">
+        <v>86.02466674804687</v>
+      </c>
+      <c r="I32">
+        <v>79.07675006866455</v>
+      </c>
+      <c r="J32">
+        <v>71.5879001045227</v>
+      </c>
+      <c r="K32">
+        <v>29.82999992370605</v>
+      </c>
+      <c r="L32">
+        <v>127.9700012207031</v>
+      </c>
+      <c r="M32">
+        <v>52.27300157757835</v>
+      </c>
+      <c r="N32">
+        <v>278.7208126241381</v>
+      </c>
+      <c r="O32">
+        <v>219.9096912329183</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>-72</v>
+      </c>
+      <c r="R32">
+        <v>-2</v>
+      </c>
+      <c r="S32">
+        <v>16.857</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" t="s">
+        <v>185</v>
+      </c>
+      <c r="D33" t="s">
+        <v>259</v>
+      </c>
+      <c r="E33">
+        <v>17.65999984741211</v>
+      </c>
+      <c r="F33">
+        <v>216060.3666666667</v>
+      </c>
+      <c r="G33">
+        <v>13.80259994506836</v>
+      </c>
+      <c r="H33">
+        <v>11.12439997990926</v>
+      </c>
+      <c r="I33">
+        <v>10.34764998197556</v>
+      </c>
+      <c r="J33">
+        <v>9.446699979305267</v>
+      </c>
+      <c r="K33">
+        <v>5.059999942779541</v>
+      </c>
+      <c r="L33">
+        <v>17.65999984741211</v>
+      </c>
+      <c r="M33">
+        <v>49.40778598450497</v>
+      </c>
+      <c r="N33">
+        <v>241.5860655087548</v>
+      </c>
+      <c r="O33">
+        <v>211.1917628258212</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>-40</v>
+      </c>
+      <c r="R33">
+        <v>128</v>
+      </c>
+      <c r="S33">
+        <v>-1.827</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
+      <c r="A34" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" t="s">
+        <v>166</v>
+      </c>
+      <c r="C34" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" t="s">
+        <v>251</v>
+      </c>
+      <c r="E34">
+        <v>45.86999893188477</v>
+      </c>
+      <c r="F34">
+        <v>347149.2666666667</v>
+      </c>
+      <c r="G34">
+        <v>39.54720012664795</v>
+      </c>
+      <c r="H34">
+        <v>26.96927459716797</v>
+      </c>
+      <c r="I34">
+        <v>25.94383862495422</v>
+      </c>
+      <c r="J34">
+        <v>23.56747159957886</v>
+      </c>
+      <c r="K34">
+        <v>17.95781517028809</v>
+      </c>
+      <c r="L34">
+        <v>45.90000152587891</v>
+      </c>
+      <c r="M34">
+        <v>103.8727453618679</v>
+      </c>
+      <c r="N34">
+        <v>116.8406145847196</v>
+      </c>
+      <c r="O34">
+        <v>210.518550738038</v>
+      </c>
+      <c r="P34">
+        <v>-104</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>11</v>
+      </c>
+      <c r="S34">
+        <v>1.158</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19">
+      <c r="A35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" t="s">
+        <v>166</v>
+      </c>
+      <c r="C35" t="s">
+        <v>188</v>
+      </c>
+      <c r="D35" t="s">
+        <v>260</v>
+      </c>
+      <c r="E35">
+        <v>17.48999977111816</v>
+      </c>
+      <c r="F35">
+        <v>1220480.1</v>
+      </c>
+      <c r="G35">
+        <v>14.436399974823</v>
+      </c>
+      <c r="H35">
+        <v>10.67793331464132</v>
+      </c>
+      <c r="I35">
+        <v>9.937450003623962</v>
+      </c>
+      <c r="J35">
+        <v>8.953199996948243</v>
+      </c>
+      <c r="K35">
+        <v>5.510000228881836</v>
+      </c>
+      <c r="L35">
+        <v>17.61000061035156</v>
+      </c>
+      <c r="M35">
+        <v>34.22870398731752</v>
+      </c>
+      <c r="N35">
+        <v>124.2307608132299</v>
+      </c>
+      <c r="O35">
+        <v>205.8072803922142</v>
+      </c>
+      <c r="P35">
+        <v>-95</v>
+      </c>
+      <c r="Q35">
+        <v>-69</v>
+      </c>
+      <c r="R35">
+        <v>39</v>
+      </c>
+      <c r="S35">
+        <v>-9.794</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19">
+      <c r="A36" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" t="s">
+        <v>162</v>
+      </c>
+      <c r="C36" t="s">
+        <v>172</v>
+      </c>
+      <c r="D36" t="s">
+        <v>261</v>
+      </c>
+      <c r="E36">
+        <v>22.30999946594238</v>
+      </c>
+      <c r="F36">
+        <v>1327613.733333333</v>
+      </c>
+      <c r="G36">
+        <v>18.8353999710083</v>
+      </c>
+      <c r="H36">
+        <v>12.8560000260671</v>
+      </c>
+      <c r="I36">
+        <v>12.44162503004074</v>
+      </c>
+      <c r="J36">
+        <v>11.5068750166893</v>
+      </c>
+      <c r="K36">
+        <v>7.579999923706055</v>
+      </c>
+      <c r="L36">
+        <v>23.53000068664551</v>
+      </c>
+      <c r="M36">
+        <v>106.3829657717391</v>
+      </c>
+      <c r="N36">
+        <v>90.84687995524175</v>
+      </c>
+      <c r="O36">
+        <v>204.9305855549465</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>2</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>-37.339002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19">
+      <c r="A37" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" t="s">
+        <v>164</v>
+      </c>
+      <c r="C37" t="s">
+        <v>189</v>
+      </c>
+      <c r="D37" t="s">
+        <v>262</v>
+      </c>
+      <c r="E37">
+        <v>29.35000038146973</v>
+      </c>
+      <c r="F37">
+        <v>2144098.133333333</v>
+      </c>
+      <c r="G37">
+        <v>21.36879989624023</v>
+      </c>
+      <c r="H37">
+        <v>18.3996999613444</v>
+      </c>
+      <c r="I37">
+        <v>16.84037497520447</v>
+      </c>
+      <c r="J37">
+        <v>15.27332497596741</v>
+      </c>
+      <c r="K37">
+        <v>8.880000114440918</v>
+      </c>
+      <c r="L37">
+        <v>33.90999984741211</v>
+      </c>
+      <c r="M37">
+        <v>83.43750238418579</v>
+      </c>
+      <c r="N37">
+        <v>139.5918398487324</v>
+      </c>
+      <c r="O37">
+        <v>204.8533206619469</v>
+      </c>
+      <c r="P37">
+        <v>44</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>1</v>
+      </c>
+      <c r="S37">
+        <v>11.143</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19">
+      <c r="A38" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" t="s">
+        <v>167</v>
+      </c>
+      <c r="C38" t="s">
+        <v>181</v>
+      </c>
+      <c r="D38" t="s">
+        <v>263</v>
+      </c>
+      <c r="E38">
+        <v>18.29999923706055</v>
+      </c>
+      <c r="F38">
+        <v>440829.3666666666</v>
+      </c>
+      <c r="G38">
+        <v>13.82679996490478</v>
+      </c>
+      <c r="H38">
+        <v>9.930033318201701</v>
+      </c>
+      <c r="I38">
+        <v>9.293749980926513</v>
+      </c>
+      <c r="J38">
+        <v>8.424249992370605</v>
+      </c>
+      <c r="K38">
+        <v>5.550000190734863</v>
+      </c>
+      <c r="L38">
+        <v>18.29999923706055</v>
+      </c>
+      <c r="M38">
+        <v>78.3625616844156</v>
+      </c>
+      <c r="N38">
+        <v>39.80136763743764</v>
+      </c>
+      <c r="O38">
+        <v>204.5154620197698</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>1</v>
+      </c>
+      <c r="S38">
+        <v>-54.447</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19">
+      <c r="A39" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" t="s">
+        <v>168</v>
+      </c>
+      <c r="C39" t="s">
+        <v>190</v>
+      </c>
+      <c r="D39" t="s">
+        <v>264</v>
+      </c>
+      <c r="E39">
+        <v>91.06999969482422</v>
+      </c>
+      <c r="F39">
+        <v>5606367.2</v>
+      </c>
+      <c r="G39">
+        <v>63.10339973449707</v>
+      </c>
+      <c r="H39">
+        <v>58.59588882446289</v>
+      </c>
+      <c r="I39">
+        <v>55.91708332061768</v>
+      </c>
+      <c r="J39">
+        <v>52.43343341827393</v>
+      </c>
+      <c r="K39">
+        <v>27.82666778564453</v>
+      </c>
+      <c r="L39">
+        <v>91.06999969482422</v>
+      </c>
+      <c r="M39">
+        <v>78.91944393856613</v>
+      </c>
+      <c r="N39">
+        <v>227.275979992855</v>
+      </c>
+      <c r="O39">
+        <v>204.1747136946859</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>-10</v>
+      </c>
+      <c r="S39">
+        <v>23.225</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19">
+      <c r="A40" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" t="s">
+        <v>164</v>
+      </c>
+      <c r="C40" t="s">
+        <v>174</v>
+      </c>
+      <c r="D40" t="s">
+        <v>265</v>
+      </c>
+      <c r="E40">
+        <v>113.5500030517578</v>
+      </c>
+      <c r="F40">
+        <v>8252561.866666666</v>
+      </c>
+      <c r="G40">
+        <v>88.79320007324219</v>
+      </c>
+      <c r="H40">
+        <v>74.78940022786459</v>
+      </c>
+      <c r="I40">
+        <v>68.9779001045227</v>
+      </c>
+      <c r="J40">
+        <v>63.51670009613037</v>
+      </c>
+      <c r="K40">
+        <v>37.22000122070312</v>
+      </c>
+      <c r="L40">
+        <v>124.5899963378906</v>
+      </c>
+      <c r="M40">
+        <v>65.28385457906951</v>
+      </c>
+      <c r="N40">
+        <v>202.7192965417241</v>
+      </c>
+      <c r="O40">
+        <v>203.0636115769356</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>-54</v>
+      </c>
+      <c r="R40">
+        <v>-3</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19">
+      <c r="A41" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" t="s">
+        <v>169</v>
+      </c>
+      <c r="C41" t="s">
+        <v>191</v>
+      </c>
+      <c r="D41" t="s">
+        <v>266</v>
+      </c>
+      <c r="E41">
+        <v>16.86000061035156</v>
+      </c>
+      <c r="F41">
+        <v>1313922.3</v>
+      </c>
+      <c r="G41">
+        <v>15.2476000213623</v>
+      </c>
+      <c r="H41">
+        <v>11.12479999224345</v>
+      </c>
+      <c r="I41">
+        <v>10.1945499920845</v>
+      </c>
+      <c r="J41">
+        <v>9.3392999958992</v>
+      </c>
+      <c r="K41">
+        <v>6.610000133514404</v>
+      </c>
+      <c r="L41">
+        <v>16.86000061035156</v>
+      </c>
+      <c r="M41">
+        <v>78.6017093198534</v>
+      </c>
+      <c r="N41">
+        <v>106.8711828159816</v>
+      </c>
+      <c r="O41">
+        <v>198.0892801207002</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>-328</v>
+      </c>
+      <c r="R41">
+        <v>22</v>
+      </c>
+      <c r="S41">
+        <v>1.249</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19">
+      <c r="A42" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" t="s">
+        <v>170</v>
+      </c>
+      <c r="C42" t="s">
+        <v>192</v>
+      </c>
+      <c r="D42" t="s">
+        <v>267</v>
+      </c>
+      <c r="E42">
+        <v>60.20000076293945</v>
+      </c>
+      <c r="F42">
+        <v>5572911.266666667</v>
+      </c>
+      <c r="G42">
+        <v>45.25720001220703</v>
+      </c>
+      <c r="H42">
+        <v>37.32820231119792</v>
+      </c>
+      <c r="I42">
+        <v>34.45447940826416</v>
+      </c>
+      <c r="J42">
+        <v>31.57886503219605</v>
+      </c>
+      <c r="K42">
+        <v>22.5151481628418</v>
+      </c>
+      <c r="L42">
+        <v>61.68000030517578</v>
+      </c>
+      <c r="M42">
+        <v>63.80277571884878</v>
+      </c>
+      <c r="N42">
+        <v>153.6029956552136</v>
+      </c>
+      <c r="O42">
+        <v>196.9492149913383</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>-25</v>
+      </c>
+      <c r="S42">
+        <v>29.141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19">
+      <c r="A43" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" t="s">
+        <v>166</v>
+      </c>
+      <c r="C43" t="s">
+        <v>193</v>
+      </c>
+      <c r="D43" t="s">
+        <v>268</v>
+      </c>
+      <c r="E43">
+        <v>67.43000030517578</v>
+      </c>
+      <c r="F43">
+        <v>515353.0666666667</v>
+      </c>
+      <c r="G43">
+        <v>57.20759971618652</v>
+      </c>
+      <c r="H43">
+        <v>48.26966654459635</v>
+      </c>
+      <c r="I43">
+        <v>45.89729990959167</v>
+      </c>
+      <c r="J43">
+        <v>42.33174996376037</v>
+      </c>
+      <c r="K43">
+        <v>17.88999938964844</v>
+      </c>
+      <c r="L43">
+        <v>68.23999786376953</v>
+      </c>
+      <c r="M43">
+        <v>37.58417183121898</v>
+      </c>
+      <c r="N43">
+        <v>266.6666804955497</v>
+      </c>
+      <c r="O43">
+        <v>196.6039858103611</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>-47</v>
+      </c>
+      <c r="R43">
+        <v>-2</v>
+      </c>
+      <c r="S43">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19">
+      <c r="A44" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" t="s">
+        <v>164</v>
+      </c>
+      <c r="C44" t="s">
+        <v>194</v>
+      </c>
+      <c r="D44" t="s">
+        <v>269</v>
+      </c>
+      <c r="E44">
+        <v>23.93000030517578</v>
+      </c>
+      <c r="F44">
+        <v>339319.3666666666</v>
+      </c>
+      <c r="G44">
+        <v>16.7584001159668</v>
+      </c>
+      <c r="H44">
+        <v>16.13233336130778</v>
+      </c>
+      <c r="I44">
+        <v>14.70640003204346</v>
+      </c>
+      <c r="J44">
+        <v>13.89940002918243</v>
+      </c>
+      <c r="K44">
+        <v>7.630000114440918</v>
+      </c>
+      <c r="L44">
+        <v>23.93000030517578</v>
+      </c>
+      <c r="M44">
+        <v>41.59763813803495</v>
+      </c>
+      <c r="N44">
+        <v>205.619419391378</v>
+      </c>
+      <c r="O44">
+        <v>196.5668822304357</v>
+      </c>
+      <c r="P44">
+        <v>1000</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>8</v>
+      </c>
+      <c r="S44">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19">
+      <c r="A45" t="s">
+        <v>62</v>
+      </c>
+      <c r="B45" t="s">
+        <v>162</v>
+      </c>
+      <c r="C45" t="s">
+        <v>172</v>
+      </c>
+      <c r="D45" t="s">
+        <v>270</v>
+      </c>
+      <c r="E45">
+        <v>45.95000076293945</v>
+      </c>
+      <c r="F45">
+        <v>629995.6666666666</v>
+      </c>
+      <c r="G45">
+        <v>39.20860023498535</v>
+      </c>
+      <c r="H45">
+        <v>28.51360001881917</v>
+      </c>
+      <c r="I45">
+        <v>27.69730000495911</v>
+      </c>
+      <c r="J45">
+        <v>25.03719997406006</v>
+      </c>
+      <c r="K45">
+        <v>17.39999961853027</v>
+      </c>
+      <c r="L45">
+        <v>51.81999969482422</v>
+      </c>
+      <c r="M45">
+        <v>92.01838770140343</v>
+      </c>
+      <c r="N45">
+        <v>126.5779053607123</v>
+      </c>
+      <c r="O45">
+        <v>194.2341752477136</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>-19</v>
+      </c>
+      <c r="S45">
+        <v>-51.355</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19">
+      <c r="A46" t="s">
+        <v>63</v>
+      </c>
+      <c r="B46" t="s">
+        <v>162</v>
+      </c>
+      <c r="C46" t="s">
+        <v>195</v>
+      </c>
+      <c r="D46" t="s">
+        <v>271</v>
+      </c>
+      <c r="E46">
+        <v>50.68000030517578</v>
+      </c>
+      <c r="F46">
+        <v>445849.8666666666</v>
+      </c>
+      <c r="G46">
+        <v>48.95900016784668</v>
+      </c>
+      <c r="H46">
+        <v>35.68513341267904</v>
+      </c>
+      <c r="I46">
+        <v>33.93402503013611</v>
+      </c>
+      <c r="J46">
+        <v>30.66792500495911</v>
+      </c>
+      <c r="K46">
+        <v>14.94999980926514</v>
+      </c>
+      <c r="L46">
+        <v>57.91999816894531</v>
+      </c>
+      <c r="M46">
+        <v>44.92421657443906</v>
+      </c>
+      <c r="N46">
+        <v>238.9966618846863</v>
+      </c>
+      <c r="O46">
+        <v>194.0870140961459</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>29</v>
+      </c>
+      <c r="S46">
+        <v>-38.845003</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19">
+      <c r="A47" t="s">
+        <v>64</v>
+      </c>
+      <c r="B47" t="s">
+        <v>166</v>
+      </c>
+      <c r="C47" t="s">
+        <v>196</v>
+      </c>
+      <c r="D47" t="s">
+        <v>272</v>
+      </c>
+      <c r="E47">
+        <v>111.9800033569336</v>
+      </c>
+      <c r="F47">
+        <v>422317.5333333333</v>
+      </c>
+      <c r="G47">
+        <v>86.10800003051757</v>
+      </c>
+      <c r="H47">
+        <v>78.02433326721192</v>
+      </c>
+      <c r="I47">
+        <v>72.34314994812011</v>
+      </c>
+      <c r="J47">
+        <v>66.75214990615845</v>
+      </c>
+      <c r="K47">
+        <v>34.63999938964844</v>
+      </c>
+      <c r="L47">
+        <v>111.9800033569336</v>
+      </c>
+      <c r="M47">
+        <v>61.14549834418308</v>
+      </c>
+      <c r="N47">
+        <v>196.3217799524389</v>
+      </c>
+      <c r="O47">
+        <v>193.910431456638</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>28</v>
+      </c>
+      <c r="R47">
+        <v>-13</v>
+      </c>
+      <c r="S47">
+        <v>25.933</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
+      <c r="A48" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" t="s">
+        <v>166</v>
+      </c>
+      <c r="C48" t="s">
+        <v>197</v>
+      </c>
+      <c r="D48" t="s">
+        <v>273</v>
+      </c>
+      <c r="E48">
+        <v>45.36000061035156</v>
+      </c>
+      <c r="F48">
+        <v>201049.9</v>
+      </c>
+      <c r="G48">
+        <v>31.32940002441406</v>
+      </c>
+      <c r="H48">
+        <v>26.11946666717529</v>
+      </c>
+      <c r="I48">
+        <v>25.07119997024536</v>
+      </c>
+      <c r="J48">
+        <v>23.81829998970032</v>
+      </c>
+      <c r="K48">
+        <v>19.29999923706055</v>
+      </c>
+      <c r="L48">
+        <v>45.36000061035156</v>
+      </c>
+      <c r="M48">
+        <v>77.6733231114989</v>
+      </c>
+      <c r="N48">
+        <v>92.93917553700058</v>
+      </c>
+      <c r="O48">
+        <v>193.6973143901891</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>-16</v>
+      </c>
+      <c r="R48">
+        <v>-7</v>
+      </c>
+      <c r="S48">
+        <v>16.961001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
+      <c r="A49" t="s">
         <v>66</v>
       </c>
-      <c r="Q4">
+      <c r="B49" t="s">
+        <v>163</v>
+      </c>
+      <c r="C49" t="s">
+        <v>198</v>
+      </c>
+      <c r="D49" t="s">
+        <v>274</v>
+      </c>
+      <c r="E49">
+        <v>41.2599983215332</v>
+      </c>
+      <c r="F49">
+        <v>314910.5333333333</v>
+      </c>
+      <c r="G49">
+        <v>33.67319965362549</v>
+      </c>
+      <c r="H49">
+        <v>23.1000665473938</v>
+      </c>
+      <c r="I49">
+        <v>22.98894992351532</v>
+      </c>
+      <c r="J49">
+        <v>21.19709996700287</v>
+      </c>
+      <c r="K49">
+        <v>10.44999980926514</v>
+      </c>
+      <c r="L49">
+        <v>41.63000106811523</v>
+      </c>
+      <c r="M49">
+        <v>73.94603505870927</v>
+      </c>
+      <c r="N49">
+        <v>55.05448092880781</v>
+      </c>
+      <c r="O49">
+        <v>193.1060149177376</v>
+      </c>
+      <c r="P49">
+        <v>-221</v>
+      </c>
+      <c r="Q49">
+        <v>-36</v>
+      </c>
+      <c r="R49">
+        <v>-13</v>
+      </c>
+      <c r="S49">
+        <v>-73.72100400000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19">
+      <c r="A50" t="s">
+        <v>67</v>
+      </c>
+      <c r="B50" t="s">
+        <v>162</v>
+      </c>
+      <c r="C50" t="s">
+        <v>172</v>
+      </c>
+      <c r="D50" t="s">
+        <v>275</v>
+      </c>
+      <c r="E50">
+        <v>30.61000061035156</v>
+      </c>
+      <c r="F50">
+        <v>909871.4</v>
+      </c>
+      <c r="G50">
+        <v>28.38980007171631</v>
+      </c>
+      <c r="H50">
+        <v>20.57560001373291</v>
+      </c>
+      <c r="I50">
+        <v>20.06192504405975</v>
+      </c>
+      <c r="J50">
+        <v>18.2885750246048</v>
+      </c>
+      <c r="K50">
+        <v>11.56999969482422</v>
+      </c>
+      <c r="L50">
+        <v>39.22000122070312</v>
+      </c>
+      <c r="M50">
+        <v>77.03874487862026</v>
+      </c>
+      <c r="N50">
+        <v>122.7802119378093</v>
+      </c>
+      <c r="O50">
+        <v>190.3461226021709</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>599</v>
+      </c>
+      <c r="S50">
+        <v>-69.708997</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19">
+      <c r="A51" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" t="s">
+        <v>168</v>
+      </c>
+      <c r="C51" t="s">
+        <v>199</v>
+      </c>
+      <c r="D51" t="s">
+        <v>276</v>
+      </c>
+      <c r="E51">
+        <v>205.3099975585938</v>
+      </c>
+      <c r="F51">
+        <v>1454412.166666667</v>
+      </c>
+      <c r="G51">
+        <v>171.6455993652344</v>
+      </c>
+      <c r="H51">
+        <v>136.2601332092285</v>
+      </c>
+      <c r="I51">
+        <v>130.1200498962402</v>
+      </c>
+      <c r="J51">
+        <v>119.8097500610352</v>
+      </c>
+      <c r="K51">
+        <v>72.47000122070312</v>
+      </c>
+      <c r="L51">
+        <v>217.3999938964844</v>
+      </c>
+      <c r="M51">
+        <v>61.31845916079774</v>
+      </c>
+      <c r="N51">
+        <v>179.9808979026188</v>
+      </c>
+      <c r="O51">
+        <v>189.9292158237558</v>
+      </c>
+      <c r="P51">
+        <v>35</v>
+      </c>
+      <c r="Q51">
+        <v>171</v>
+      </c>
+      <c r="R51">
+        <v>26</v>
+      </c>
+      <c r="S51">
+        <v>25.889</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19">
+      <c r="A52" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" t="s">
+        <v>167</v>
+      </c>
+      <c r="C52" t="s">
+        <v>181</v>
+      </c>
+      <c r="D52" t="s">
+        <v>229</v>
+      </c>
+      <c r="E52">
+        <v>19.75</v>
+      </c>
+      <c r="F52">
+        <v>332936.5666666667</v>
+      </c>
+      <c r="G52">
+        <v>14.93200002670288</v>
+      </c>
+      <c r="H52">
+        <v>11.18313335418701</v>
+      </c>
+      <c r="I52">
+        <v>10.77145002603531</v>
+      </c>
+      <c r="J52">
+        <v>9.482300026416778</v>
+      </c>
+      <c r="K52">
+        <v>5.360000133514404</v>
+      </c>
+      <c r="L52">
+        <v>21.75</v>
+      </c>
+      <c r="M52">
+        <v>81.35903927780672</v>
+      </c>
+      <c r="N52">
+        <v>42.39365654619039</v>
+      </c>
+      <c r="O52">
+        <v>189.6415014902185</v>
+      </c>
+      <c r="P52">
+        <v>-92</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>57</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19">
+      <c r="A53" t="s">
+        <v>70</v>
+      </c>
+      <c r="B53" t="s">
+        <v>165</v>
+      </c>
+      <c r="C53" t="s">
+        <v>200</v>
+      </c>
+      <c r="D53" t="s">
+        <v>277</v>
+      </c>
+      <c r="E53">
+        <v>40.09999847412109</v>
+      </c>
+      <c r="F53">
+        <v>406011.2666666667</v>
+      </c>
+      <c r="G53">
+        <v>34.15179985046387</v>
+      </c>
+      <c r="H53">
+        <v>28.27706665039063</v>
+      </c>
+      <c r="I53">
+        <v>27.11074999809265</v>
+      </c>
+      <c r="J53">
+        <v>25.13305002689362</v>
+      </c>
+      <c r="K53">
+        <v>11.89999961853027</v>
+      </c>
+      <c r="L53">
+        <v>40.09999847412109</v>
+      </c>
+      <c r="M53">
+        <v>40.89950725261633</v>
+      </c>
+      <c r="N53">
+        <v>236.9747878956125</v>
+      </c>
+      <c r="O53">
+        <v>187.2809527692465</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>27</v>
+      </c>
+      <c r="S53">
+        <v>32.641</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19">
+      <c r="A54" t="s">
+        <v>71</v>
+      </c>
+      <c r="B54" t="s">
+        <v>165</v>
+      </c>
+      <c r="C54" t="s">
+        <v>201</v>
+      </c>
+      <c r="D54" t="s">
+        <v>278</v>
+      </c>
+      <c r="E54">
+        <v>64.43000030517578</v>
+      </c>
+      <c r="F54">
+        <v>896855.6</v>
+      </c>
+      <c r="G54">
+        <v>54.23659950256348</v>
+      </c>
+      <c r="H54">
+        <v>45.13613316853841</v>
+      </c>
+      <c r="I54">
+        <v>40.92604990005493</v>
+      </c>
+      <c r="J54">
+        <v>37.51114992141724</v>
+      </c>
+      <c r="K54">
+        <v>22.51000022888184</v>
+      </c>
+      <c r="L54">
+        <v>64.43000030517578</v>
+      </c>
+      <c r="M54">
+        <v>45.14530567937018</v>
+      </c>
+      <c r="N54">
+        <v>161.0615863390561</v>
+      </c>
+      <c r="O54">
+        <v>187.1415352496705</v>
+      </c>
+      <c r="P54">
+        <v>21900</v>
+      </c>
+      <c r="Q54">
+        <v>-76</v>
+      </c>
+      <c r="R54">
+        <v>27</v>
+      </c>
+      <c r="S54">
+        <v>5.58</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19">
+      <c r="A55" t="s">
+        <v>72</v>
+      </c>
+      <c r="B55" t="s">
+        <v>163</v>
+      </c>
+      <c r="C55" t="s">
+        <v>202</v>
+      </c>
+      <c r="D55" t="s">
+        <v>279</v>
+      </c>
+      <c r="E55">
+        <v>39.9900016784668</v>
+      </c>
+      <c r="F55">
+        <v>356690.5</v>
+      </c>
+      <c r="G55">
+        <v>32.2797998046875</v>
+      </c>
+      <c r="H55">
+        <v>26.13873322804769</v>
+      </c>
+      <c r="I55">
+        <v>25.59674990653992</v>
+      </c>
+      <c r="J55">
+        <v>23.72439990997314</v>
+      </c>
+      <c r="K55">
+        <v>16.79000091552734</v>
+      </c>
+      <c r="L55">
+        <v>40.88000106811523</v>
+      </c>
+      <c r="M55">
+        <v>47.07613421476828</v>
+      </c>
+      <c r="N55">
+        <v>137.8941281913058</v>
+      </c>
+      <c r="O55">
+        <v>185.926699999423</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>-9</v>
+      </c>
+      <c r="R55">
+        <v>34</v>
+      </c>
+      <c r="S55">
+        <v>32.284</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19">
+      <c r="A56" t="s">
+        <v>73</v>
+      </c>
+      <c r="B56" t="s">
+        <v>164</v>
+      </c>
+      <c r="C56" t="s">
+        <v>203</v>
+      </c>
+      <c r="D56" t="s">
+        <v>280</v>
+      </c>
+      <c r="E56">
+        <v>63.81000137329102</v>
+      </c>
+      <c r="F56">
+        <v>3024859.5</v>
+      </c>
+      <c r="G56">
+        <v>56.09820014953613</v>
+      </c>
+      <c r="H56">
+        <v>43.71270011901856</v>
+      </c>
+      <c r="I56">
+        <v>40.03582509994507</v>
+      </c>
+      <c r="J56">
+        <v>36.45662509918213</v>
+      </c>
+      <c r="K56">
+        <v>23.42000007629395</v>
+      </c>
+      <c r="L56">
+        <v>65.84999847412109</v>
+      </c>
+      <c r="M56">
+        <v>38.65710721114548</v>
+      </c>
+      <c r="N56">
+        <v>158.1310806866363</v>
+      </c>
+      <c r="O56">
+        <v>183.9641621785933</v>
+      </c>
+      <c r="P56">
+        <v>-139</v>
+      </c>
+      <c r="Q56">
+        <v>-70</v>
+      </c>
+      <c r="R56">
+        <v>11</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19">
+      <c r="A57" t="s">
+        <v>74</v>
+      </c>
+      <c r="B57" t="s">
+        <v>164</v>
+      </c>
+      <c r="C57" t="s">
+        <v>194</v>
+      </c>
+      <c r="D57" t="s">
+        <v>281</v>
+      </c>
+      <c r="E57">
+        <v>329.2699890136719</v>
+      </c>
+      <c r="F57">
+        <v>4762365.933333334</v>
+      </c>
+      <c r="G57">
+        <v>300.6491983032226</v>
+      </c>
+      <c r="H57">
+        <v>226.4709992472331</v>
+      </c>
+      <c r="I57">
+        <v>207.6639996337891</v>
+      </c>
+      <c r="J57">
+        <v>188.8335499191284</v>
+      </c>
+      <c r="K57">
+        <v>116.7399978637695</v>
+      </c>
+      <c r="L57">
+        <v>334.5499877929688</v>
+      </c>
+      <c r="M57">
+        <v>35.75344665875302</v>
+      </c>
+      <c r="N57">
+        <v>154.616432388654</v>
+      </c>
+      <c r="O57">
+        <v>182.2398916988366</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>-147</v>
+      </c>
+      <c r="R57">
+        <v>8</v>
+      </c>
+      <c r="S57">
+        <v>4.737</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19">
+      <c r="A58" t="s">
+        <v>75</v>
+      </c>
+      <c r="B58" t="s">
+        <v>162</v>
+      </c>
+      <c r="C58" t="s">
+        <v>172</v>
+      </c>
+      <c r="D58" t="s">
+        <v>282</v>
+      </c>
+      <c r="E58">
+        <v>44.7599983215332</v>
+      </c>
+      <c r="F58">
+        <v>736348.8666666667</v>
+      </c>
+      <c r="G58">
+        <v>42.60680023193359</v>
+      </c>
+      <c r="H58">
+        <v>33.45453344980876</v>
+      </c>
+      <c r="I58">
+        <v>30.88325008392334</v>
+      </c>
+      <c r="J58">
+        <v>28.41330006599426</v>
+      </c>
+      <c r="K58">
+        <v>13.32999992370605</v>
+      </c>
+      <c r="L58">
+        <v>47.13000106811523</v>
+      </c>
+      <c r="M58">
+        <v>44.90125997390842</v>
+      </c>
+      <c r="N58">
+        <v>188.9606131885834</v>
+      </c>
+      <c r="O58">
+        <v>181.1611300517403</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>38</v>
+      </c>
+      <c r="R58">
+        <v>-51</v>
+      </c>
+      <c r="S58">
+        <v>-23.278</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19">
+      <c r="A59" t="s">
+        <v>76</v>
+      </c>
+      <c r="B59" t="s">
+        <v>164</v>
+      </c>
+      <c r="C59" t="s">
+        <v>194</v>
+      </c>
+      <c r="D59" t="s">
+        <v>283</v>
+      </c>
+      <c r="E59">
+        <v>24.70000076293945</v>
+      </c>
+      <c r="F59">
+        <v>101192963.7333333</v>
+      </c>
+      <c r="G59">
+        <v>20.52360004425049</v>
+      </c>
+      <c r="H59">
+        <v>18.04160003026326</v>
+      </c>
+      <c r="I59">
+        <v>17.54199998378754</v>
+      </c>
+      <c r="J59">
+        <v>16.03434997797012</v>
+      </c>
+      <c r="K59">
+        <v>7.380000114440918</v>
+      </c>
+      <c r="L59">
+        <v>26.45999908447266</v>
+      </c>
+      <c r="M59">
+        <v>38.9983124741456</v>
+      </c>
+      <c r="N59">
+        <v>212.6582337312067</v>
+      </c>
+      <c r="O59">
+        <v>180.1131082553033</v>
+      </c>
+      <c r="P59">
+        <v>300</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>9</v>
+      </c>
+      <c r="S59">
+        <v>7.008</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19">
+      <c r="A60" t="s">
+        <v>77</v>
+      </c>
+      <c r="B60" t="s">
+        <v>165</v>
+      </c>
+      <c r="C60" t="s">
+        <v>200</v>
+      </c>
+      <c r="D60" t="s">
+        <v>284</v>
+      </c>
+      <c r="E60">
+        <v>240.4799957275391</v>
+      </c>
+      <c r="F60">
+        <v>262866.8333333333</v>
+      </c>
+      <c r="G60">
+        <v>205.2606002807617</v>
+      </c>
+      <c r="H60">
+        <v>161.1549978129069</v>
+      </c>
+      <c r="I60">
+        <v>154.1827989196777</v>
+      </c>
+      <c r="J60">
+        <v>142.85453540802</v>
+      </c>
+      <c r="K60">
+        <v>103.1781387329102</v>
+      </c>
+      <c r="L60">
+        <v>242.1000061035156</v>
+      </c>
+      <c r="M60">
+        <v>46.8938891120142</v>
+      </c>
+      <c r="N60">
+        <v>129.6626755493309</v>
+      </c>
+      <c r="O60">
+        <v>179.4527151278193</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>11</v>
+      </c>
+      <c r="R60">
+        <v>2</v>
+      </c>
+      <c r="S60">
+        <v>41.88</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19">
+      <c r="A61" t="s">
+        <v>78</v>
+      </c>
+      <c r="B61" t="s">
+        <v>162</v>
+      </c>
+      <c r="C61" t="s">
+        <v>172</v>
+      </c>
+      <c r="D61" t="s">
+        <v>285</v>
+      </c>
+      <c r="E61">
+        <v>16.94000053405762</v>
+      </c>
+      <c r="F61">
+        <v>499692.2666666667</v>
+      </c>
+      <c r="G61">
+        <v>15.10299995422363</v>
+      </c>
+      <c r="H61">
+        <v>11.30746663411458</v>
+      </c>
+      <c r="I61">
+        <v>11.26159996986389</v>
+      </c>
+      <c r="J61">
+        <v>10.44394997119904</v>
+      </c>
+      <c r="K61">
+        <v>7.889999866485596</v>
+      </c>
+      <c r="L61">
+        <v>19.02000045776367</v>
+      </c>
+      <c r="M61">
+        <v>108.8779439110127</v>
+      </c>
+      <c r="N61">
+        <v>51.11508007503826</v>
+      </c>
+      <c r="O61">
+        <v>177.4225608563784</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>-257</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>-29.694</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19">
+      <c r="A62" t="s">
+        <v>79</v>
+      </c>
+      <c r="B62" t="s">
+        <v>163</v>
+      </c>
+      <c r="C62" t="s">
+        <v>204</v>
+      </c>
+      <c r="D62" t="s">
+        <v>286</v>
+      </c>
+      <c r="E62">
+        <v>15.39000034332275</v>
+      </c>
+      <c r="F62">
+        <v>254709.6666666667</v>
+      </c>
+      <c r="G62">
+        <v>13.35620006561279</v>
+      </c>
+      <c r="H62">
+        <v>9.575316190719604</v>
+      </c>
+      <c r="I62">
+        <v>8.949402956962585</v>
+      </c>
+      <c r="J62">
+        <v>8.189491260051728</v>
+      </c>
+      <c r="K62">
+        <v>4.440401554107666</v>
+      </c>
+      <c r="L62">
+        <v>19.70642471313477</v>
+      </c>
+      <c r="M62">
+        <v>100.6518929626794</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>177.0119187304219</v>
+      </c>
+      <c r="P62">
+        <v>-140</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>-8</v>
+      </c>
+      <c r="S62">
+        <v>-4.9990002</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19">
+      <c r="A63" t="s">
+        <v>80</v>
+      </c>
+      <c r="B63" t="s">
+        <v>166</v>
+      </c>
+      <c r="C63" t="s">
+        <v>196</v>
+      </c>
+      <c r="D63" t="s">
+        <v>287</v>
+      </c>
+      <c r="E63">
+        <v>302.0299987792969</v>
+      </c>
+      <c r="F63">
+        <v>418322.7666666667</v>
+      </c>
+      <c r="G63">
+        <v>240.4956002807617</v>
+      </c>
+      <c r="H63">
+        <v>202.0894670613607</v>
+      </c>
+      <c r="I63">
+        <v>192.3355500793457</v>
+      </c>
+      <c r="J63">
+        <v>178.9861001586914</v>
+      </c>
+      <c r="K63">
+        <v>129.3099975585938</v>
+      </c>
+      <c r="L63">
+        <v>320.2000122070312</v>
+      </c>
+      <c r="M63">
+        <v>55.67754617335184</v>
+      </c>
+      <c r="N63">
+        <v>121.8851084436752</v>
+      </c>
+      <c r="O63">
+        <v>175.1098605249329</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>-1</v>
+      </c>
+      <c r="S63">
+        <v>28.395998</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19">
+      <c r="A64" t="s">
+        <v>81</v>
+      </c>
+      <c r="B64" t="s">
+        <v>165</v>
+      </c>
+      <c r="C64" t="s">
+        <v>205</v>
+      </c>
+      <c r="D64" t="s">
+        <v>288</v>
+      </c>
+      <c r="E64">
+        <v>349.5700073242188</v>
+      </c>
+      <c r="F64">
+        <v>526906.3</v>
+      </c>
+      <c r="G64">
+        <v>299.9558001708984</v>
+      </c>
+      <c r="H64">
+        <v>231.1457672119141</v>
+      </c>
+      <c r="I64">
+        <v>220.5178255462646</v>
+      </c>
+      <c r="J64">
+        <v>206.9270254516601</v>
+      </c>
+      <c r="K64">
+        <v>151.1999969482422</v>
+      </c>
+      <c r="L64">
+        <v>370.760009765625</v>
+      </c>
+      <c r="M64">
+        <v>41.4232614622412</v>
+      </c>
+      <c r="N64">
+        <v>100.0286211444948</v>
+      </c>
+      <c r="O64">
+        <v>172.1702572554644</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <v>8</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19">
+      <c r="A65" t="s">
+        <v>82</v>
+      </c>
+      <c r="B65" t="s">
+        <v>164</v>
+      </c>
+      <c r="C65" t="s">
+        <v>185</v>
+      </c>
+      <c r="D65" t="s">
+        <v>251</v>
+      </c>
+      <c r="E65">
+        <v>202.7599945068359</v>
+      </c>
+      <c r="F65">
+        <v>73168158.53333333</v>
+      </c>
+      <c r="G65">
+        <v>172.2247991943359</v>
+      </c>
+      <c r="H65">
+        <v>132.5415328979492</v>
+      </c>
+      <c r="I65">
+        <v>128.4612496566772</v>
+      </c>
+      <c r="J65">
+        <v>119.354949836731</v>
+      </c>
+      <c r="K65">
+        <v>81.62000274658203</v>
+      </c>
+      <c r="L65">
+        <v>211.3800048828125</v>
+      </c>
+      <c r="M65">
+        <v>57.27582794495994</v>
+      </c>
+      <c r="N65">
+        <v>126.0927674139781</v>
+      </c>
+      <c r="O65">
+        <v>171.0554607641818</v>
+      </c>
+      <c r="P65">
+        <v>4000</v>
+      </c>
+      <c r="Q65">
+        <v>-37</v>
+      </c>
+      <c r="R65">
+        <v>6</v>
+      </c>
+      <c r="S65">
+        <v>1.544</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19">
+      <c r="A66" t="s">
+        <v>83</v>
+      </c>
+      <c r="B66" t="s">
+        <v>166</v>
+      </c>
+      <c r="C66" t="s">
+        <v>206</v>
+      </c>
+      <c r="D66" t="s">
+        <v>289</v>
+      </c>
+      <c r="E66">
+        <v>57.47999954223633</v>
+      </c>
+      <c r="F66">
+        <v>790993.8</v>
+      </c>
+      <c r="G66">
+        <v>52.51582267761231</v>
+      </c>
+      <c r="H66">
+        <v>42.71240544637044</v>
+      </c>
+      <c r="I66">
+        <v>39.58540149688721</v>
+      </c>
+      <c r="J66">
+        <v>36.75166655540466</v>
+      </c>
+      <c r="K66">
+        <v>22.72007369995117</v>
+      </c>
+      <c r="L66">
+        <v>58.68999862670898</v>
+      </c>
+      <c r="M66">
+        <v>31.70164877508066</v>
+      </c>
+      <c r="N66">
+        <v>152.9921350667091</v>
+      </c>
+      <c r="O66">
+        <v>169.9328127072098</v>
+      </c>
+      <c r="P66">
+        <v>445</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>7</v>
+      </c>
+      <c r="S66">
+        <v>249.704</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19">
+      <c r="A67" t="s">
+        <v>84</v>
+      </c>
+      <c r="B67" t="s">
+        <v>166</v>
+      </c>
+      <c r="C67" t="s">
+        <v>207</v>
+      </c>
+      <c r="D67" t="s">
+        <v>290</v>
+      </c>
+      <c r="E67">
+        <v>68.86000061035156</v>
+      </c>
+      <c r="F67">
+        <v>418249.8</v>
+      </c>
+      <c r="G67">
+        <v>63.67219970703125</v>
+      </c>
+      <c r="H67">
+        <v>50.54006647745769</v>
+      </c>
+      <c r="I67">
+        <v>47.63294986724853</v>
+      </c>
+      <c r="J67">
+        <v>43.82169991493225</v>
+      </c>
+      <c r="K67">
+        <v>27.70000076293945</v>
+      </c>
+      <c r="L67">
+        <v>71.40000152587891</v>
+      </c>
+      <c r="M67">
+        <v>33.94281426713106</v>
+      </c>
+      <c r="N67">
+        <v>127.7869720578153</v>
+      </c>
+      <c r="O67">
+        <v>169.6829575306927</v>
+      </c>
+      <c r="P67">
+        <v>-7</v>
+      </c>
+      <c r="Q67">
+        <v>-138</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>17.513001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19">
+      <c r="A68" t="s">
+        <v>85</v>
+      </c>
+      <c r="B68" t="s">
+        <v>166</v>
+      </c>
+      <c r="C68" t="s">
+        <v>186</v>
+      </c>
+      <c r="D68" t="s">
+        <v>291</v>
+      </c>
+      <c r="E68">
+        <v>596.1099853515625</v>
+      </c>
+      <c r="F68">
+        <v>341482.6333333334</v>
+      </c>
+      <c r="G68">
+        <v>508.2328015136719</v>
+      </c>
+      <c r="H68">
+        <v>440.8593343098958</v>
+      </c>
+      <c r="I68">
+        <v>417.9313507080078</v>
+      </c>
+      <c r="J68">
+        <v>389.0314505004883</v>
+      </c>
+      <c r="K68">
+        <v>248.0599975585938</v>
+      </c>
+      <c r="L68">
+        <v>605.9199829101562</v>
+      </c>
+      <c r="M68">
+        <v>52.263086935265</v>
+      </c>
+      <c r="N68">
+        <v>119.0453271348735</v>
+      </c>
+      <c r="O68">
+        <v>169.6786809995801</v>
+      </c>
+      <c r="P68">
+        <v>26</v>
+      </c>
+      <c r="Q68">
+        <v>-1</v>
+      </c>
+      <c r="R68">
+        <v>-3</v>
+      </c>
+      <c r="S68">
+        <v>20.158</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19">
+      <c r="A69" t="s">
+        <v>86</v>
+      </c>
+      <c r="B69" t="s">
+        <v>162</v>
+      </c>
+      <c r="C69" t="s">
+        <v>208</v>
+      </c>
+      <c r="D69" t="s">
+        <v>292</v>
+      </c>
+      <c r="E69">
+        <v>407.5400085449219</v>
+      </c>
+      <c r="F69">
+        <v>326283.9666666667</v>
+      </c>
+      <c r="G69">
+        <v>338.5960021972656</v>
+      </c>
+      <c r="H69">
+        <v>290.3231673177083</v>
+      </c>
+      <c r="I69">
+        <v>276.0639756011963</v>
+      </c>
+      <c r="J69">
+        <v>256.9167252349853</v>
+      </c>
+      <c r="K69">
+        <v>175.6499938964844</v>
+      </c>
+      <c r="L69">
+        <v>410.1499938964844</v>
+      </c>
+      <c r="M69">
+        <v>43.91045059199941</v>
+      </c>
+      <c r="N69">
+        <v>129.0322597242407</v>
+      </c>
+      <c r="O69">
+        <v>169.5396095630839</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>1</v>
+      </c>
+      <c r="S69">
+        <v>59.83300000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19">
+      <c r="A70" t="s">
+        <v>87</v>
+      </c>
+      <c r="B70" t="s">
+        <v>162</v>
+      </c>
+      <c r="C70" t="s">
+        <v>172</v>
+      </c>
+      <c r="D70" t="s">
+        <v>293</v>
+      </c>
+      <c r="E70">
+        <v>49.75</v>
+      </c>
+      <c r="F70">
+        <v>1455970.033333333</v>
+      </c>
+      <c r="G70">
+        <v>45.16189987182617</v>
+      </c>
+      <c r="H70">
+        <v>32.57369996388753</v>
+      </c>
+      <c r="I70">
+        <v>31.30537495613098</v>
+      </c>
+      <c r="J70">
+        <v>29.05362497329712</v>
+      </c>
+      <c r="K70">
+        <v>18.94000053405762</v>
+      </c>
+      <c r="L70">
+        <v>52.5</v>
+      </c>
+      <c r="M70">
+        <v>57.93650793650793</v>
+      </c>
+      <c r="N70">
+        <v>57.38689983988168</v>
+      </c>
+      <c r="O70">
+        <v>166.5784061538565</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>-54.897</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19">
+      <c r="A71" t="s">
+        <v>88</v>
+      </c>
+      <c r="B71" t="s">
+        <v>166</v>
+      </c>
+      <c r="C71" t="s">
+        <v>188</v>
+      </c>
+      <c r="D71" t="s">
+        <v>294</v>
+      </c>
+      <c r="E71">
+        <v>48.25</v>
+      </c>
+      <c r="F71">
+        <v>1964461.566666667</v>
+      </c>
+      <c r="G71">
+        <v>42.16340019226075</v>
+      </c>
+      <c r="H71">
+        <v>35.00233345031738</v>
+      </c>
+      <c r="I71">
+        <v>33.39725010871887</v>
+      </c>
+      <c r="J71">
+        <v>31.23460006713867</v>
+      </c>
+      <c r="K71">
+        <v>21.63999938964844</v>
+      </c>
+      <c r="L71">
+        <v>49.38000106811523</v>
+      </c>
+      <c r="M71">
+        <v>39.08908016747721</v>
+      </c>
+      <c r="N71">
+        <v>119.7176776483398</v>
+      </c>
+      <c r="O71">
+        <v>166.1614138128882</v>
+      </c>
+      <c r="P71">
+        <v>-200</v>
+      </c>
+      <c r="Q71">
+        <v>-8</v>
+      </c>
+      <c r="R71">
+        <v>-38</v>
+      </c>
+      <c r="S71">
+        <v>8.621999599999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19">
+      <c r="A72" t="s">
+        <v>89</v>
+      </c>
+      <c r="B72" t="s">
+        <v>166</v>
+      </c>
+      <c r="C72" t="s">
+        <v>196</v>
+      </c>
+      <c r="D72" t="s">
+        <v>295</v>
+      </c>
+      <c r="E72">
+        <v>323.2300109863281</v>
+      </c>
+      <c r="F72">
+        <v>502926.7666666667</v>
+      </c>
+      <c r="G72">
+        <v>250.3572009277344</v>
+      </c>
+      <c r="H72">
+        <v>225.3343334960938</v>
+      </c>
+      <c r="I72">
+        <v>215.3946501159668</v>
+      </c>
+      <c r="J72">
+        <v>203.0808501434326</v>
+      </c>
+      <c r="K72">
+        <v>152.8200073242188</v>
+      </c>
+      <c r="L72">
+        <v>325.8399963378906</v>
+      </c>
+      <c r="M72">
+        <v>50.52857887468116</v>
+      </c>
+      <c r="N72">
+        <v>107.3183268514555</v>
+      </c>
+      <c r="O72">
+        <v>166.1426588459036</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>7</v>
+      </c>
+      <c r="S72">
+        <v>28.496</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19">
+      <c r="A73" t="s">
+        <v>90</v>
+      </c>
+      <c r="B73" t="s">
+        <v>165</v>
+      </c>
+      <c r="C73" t="s">
+        <v>209</v>
+      </c>
+      <c r="D73" t="s">
+        <v>296</v>
+      </c>
+      <c r="E73">
+        <v>915.0499877929688</v>
+      </c>
+      <c r="F73">
+        <v>369859.6</v>
+      </c>
+      <c r="G73">
+        <v>805.4165930175782</v>
+      </c>
+      <c r="H73">
+        <v>655.1394624837239</v>
+      </c>
+      <c r="I73">
+        <v>621.3896461486817</v>
+      </c>
+      <c r="J73">
+        <v>580.5690467834472</v>
+      </c>
+      <c r="K73">
+        <v>406.3900146484375</v>
+      </c>
+      <c r="L73">
+        <v>926.5800170898438</v>
+      </c>
+      <c r="M73">
+        <v>31.58991937756044</v>
+      </c>
+      <c r="N73">
+        <v>125.1654703141676</v>
+      </c>
+      <c r="O73">
+        <v>166.0843950950246</v>
+      </c>
+      <c r="P73">
+        <v>44</v>
+      </c>
+      <c r="Q73">
+        <v>19</v>
+      </c>
+      <c r="R73">
+        <v>43</v>
+      </c>
+      <c r="S73">
+        <v>37.373</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19">
+      <c r="A74" t="s">
+        <v>91</v>
+      </c>
+      <c r="B74" t="s">
+        <v>166</v>
+      </c>
+      <c r="C74" t="s">
+        <v>188</v>
+      </c>
+      <c r="D74" t="s">
+        <v>297</v>
+      </c>
+      <c r="E74">
+        <v>199.6600036621094</v>
+      </c>
+      <c r="F74">
+        <v>1263245.633333333</v>
+      </c>
+      <c r="G74">
+        <v>179.8201995849609</v>
+      </c>
+      <c r="H74">
+        <v>149.0400663757324</v>
+      </c>
+      <c r="I74">
+        <v>144.9792496871948</v>
+      </c>
+      <c r="J74">
+        <v>136.8570997619629</v>
+      </c>
+      <c r="K74">
+        <v>79.52999877929688</v>
+      </c>
+      <c r="L74">
+        <v>204.1300048828125</v>
+      </c>
+      <c r="M74">
+        <v>35.17942301114285</v>
+      </c>
+      <c r="N74">
+        <v>151.0499267278809</v>
+      </c>
+      <c r="O74">
+        <v>165.4522040044397</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>-29</v>
+      </c>
+      <c r="R74">
+        <v>-8</v>
+      </c>
+      <c r="S74">
+        <v>31.781</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19">
+      <c r="A75" t="s">
+        <v>92</v>
+      </c>
+      <c r="B75" t="s">
+        <v>164</v>
+      </c>
+      <c r="C75" t="s">
+        <v>175</v>
+      </c>
+      <c r="D75" t="s">
+        <v>298</v>
+      </c>
+      <c r="E75">
+        <v>42.70000076293945</v>
+      </c>
+      <c r="F75">
+        <v>1955978.6</v>
+      </c>
+      <c r="G75">
+        <v>37.49180015563965</v>
+      </c>
+      <c r="H75">
+        <v>30.46913340250651</v>
+      </c>
+      <c r="I75">
+        <v>29.69940008163452</v>
+      </c>
+      <c r="J75">
+        <v>27.5400000667572</v>
+      </c>
+      <c r="K75">
+        <v>17.70000076293945</v>
+      </c>
+      <c r="L75">
+        <v>47.63999938964844</v>
+      </c>
+      <c r="M75">
+        <v>43.43298658500285</v>
+      </c>
+      <c r="N75">
+        <v>127.1276728499259</v>
+      </c>
+      <c r="O75">
+        <v>164.8179902187566</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>-35</v>
+      </c>
+      <c r="R75">
+        <v>10</v>
+      </c>
+      <c r="S75">
+        <v>-9.396000000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19">
+      <c r="A76" t="s">
+        <v>93</v>
+      </c>
+      <c r="B76" t="s">
+        <v>162</v>
+      </c>
+      <c r="C76" t="s">
+        <v>208</v>
+      </c>
+      <c r="D76" t="s">
+        <v>299</v>
+      </c>
+      <c r="E76">
+        <v>90.80999755859375</v>
+      </c>
+      <c r="F76">
+        <v>1439444.566666667</v>
+      </c>
+      <c r="G76">
+        <v>71.25420028686523</v>
+      </c>
+      <c r="H76">
+        <v>57.77186683654785</v>
+      </c>
+      <c r="I76">
+        <v>55.51575019836426</v>
+      </c>
+      <c r="J76">
+        <v>52.71970006942749</v>
+      </c>
+      <c r="K76">
+        <v>37.54999923706055</v>
+      </c>
+      <c r="L76">
+        <v>91.66000366210938</v>
+      </c>
+      <c r="M76">
+        <v>56.16508198745262</v>
+      </c>
+      <c r="N76">
+        <v>59.20406048568907</v>
+      </c>
+      <c r="O76">
+        <v>164.4727339349422</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>-32</v>
+      </c>
+      <c r="R76">
+        <v>16</v>
+      </c>
+      <c r="S76">
+        <v>-59.114</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19">
+      <c r="A77" t="s">
+        <v>94</v>
+      </c>
+      <c r="B77" t="s">
+        <v>167</v>
+      </c>
+      <c r="C77" t="s">
+        <v>181</v>
+      </c>
+      <c r="D77" t="s">
+        <v>300</v>
+      </c>
+      <c r="E77">
+        <v>130.4499969482422</v>
+      </c>
+      <c r="F77">
+        <v>4548637</v>
+      </c>
+      <c r="G77">
+        <v>113.2397999572754</v>
+      </c>
+      <c r="H77">
+        <v>94.54416661580403</v>
+      </c>
+      <c r="I77">
+        <v>90.26857494354248</v>
+      </c>
+      <c r="J77">
+        <v>84.29332494735718</v>
+      </c>
+      <c r="K77">
+        <v>56.81999969482422</v>
+      </c>
+      <c r="L77">
+        <v>133.1999969482422</v>
+      </c>
+      <c r="M77">
+        <v>30.4499969482422</v>
+      </c>
+      <c r="N77">
+        <v>123.105856378967</v>
+      </c>
+      <c r="O77">
+        <v>163.2077820718704</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="R77">
+        <v>6</v>
+      </c>
+      <c r="S77">
+        <v>-8.32</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19">
+      <c r="A78" t="s">
+        <v>95</v>
+      </c>
+      <c r="B78" t="s">
+        <v>165</v>
+      </c>
+      <c r="C78" t="s">
+        <v>210</v>
+      </c>
+      <c r="D78" t="s">
+        <v>301</v>
+      </c>
+      <c r="E78">
+        <v>15.14000034332275</v>
+      </c>
+      <c r="F78">
+        <v>861644.0333333333</v>
+      </c>
+      <c r="G78">
+        <v>12.32200000762939</v>
+      </c>
+      <c r="H78">
+        <v>10.52983333587646</v>
+      </c>
+      <c r="I78">
+        <v>10.36202500104904</v>
+      </c>
+      <c r="J78">
+        <v>9.81644999742508</v>
+      </c>
+      <c r="K78">
+        <v>6.809999942779541</v>
+      </c>
+      <c r="L78">
+        <v>15.14000034332275</v>
+      </c>
+      <c r="M78">
+        <v>61.57951470902705</v>
+      </c>
+      <c r="N78">
+        <v>76.25145604638388</v>
+      </c>
+      <c r="O78">
+        <v>162.3578786680655</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>-9</v>
+      </c>
+      <c r="R78">
+        <v>5</v>
+      </c>
+      <c r="S78">
+        <v>45.547</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19">
+      <c r="A79" t="s">
+        <v>96</v>
+      </c>
+      <c r="B79" t="s">
+        <v>164</v>
+      </c>
+      <c r="C79" t="s">
+        <v>175</v>
+      </c>
+      <c r="D79" t="s">
+        <v>302</v>
+      </c>
+      <c r="E79">
+        <v>50</v>
+      </c>
+      <c r="F79">
+        <v>683454.5666666667</v>
+      </c>
+      <c r="G79">
+        <v>43.84459991455078</v>
+      </c>
+      <c r="H79">
+        <v>37.60806662241618</v>
+      </c>
+      <c r="I79">
+        <v>35.972350025177</v>
+      </c>
+      <c r="J79">
+        <v>33.90145004272461</v>
+      </c>
+      <c r="K79">
+        <v>21.64999961853027</v>
+      </c>
+      <c r="L79">
+        <v>50</v>
+      </c>
+      <c r="M79">
+        <v>31.30251469479819</v>
+      </c>
+      <c r="N79">
+        <v>115.703189567412</v>
+      </c>
+      <c r="O79">
+        <v>162.3056537415601</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79">
+        <v>5</v>
+      </c>
+      <c r="S79">
+        <v>-15.074</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19">
+      <c r="A80" t="s">
+        <v>97</v>
+      </c>
+      <c r="B80" t="s">
+        <v>166</v>
+      </c>
+      <c r="C80" t="s">
+        <v>188</v>
+      </c>
+      <c r="D80" t="s">
+        <v>303</v>
+      </c>
+      <c r="E80">
+        <v>15.32999992370605</v>
+      </c>
+      <c r="F80">
+        <v>264381.8666666666</v>
+      </c>
+      <c r="G80">
+        <v>13.18159997940064</v>
+      </c>
+      <c r="H80">
+        <v>11.13713330586751</v>
+      </c>
+      <c r="I80">
+        <v>10.51354998826981</v>
+      </c>
+      <c r="J80">
+        <v>9.798599984645843</v>
+      </c>
+      <c r="K80">
+        <v>6.619999885559082</v>
+      </c>
+      <c r="L80">
+        <v>15.72000026702881</v>
+      </c>
+      <c r="M80">
+        <v>38.48238795231043</v>
+      </c>
+      <c r="N80">
+        <v>93.56060323271507</v>
+      </c>
+      <c r="O80">
+        <v>162.2499514743791</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>130</v>
+      </c>
+      <c r="R80">
+        <v>5</v>
+      </c>
+      <c r="S80">
+        <v>11.306</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19">
+      <c r="A81" t="s">
+        <v>98</v>
+      </c>
+      <c r="B81" t="s">
+        <v>164</v>
+      </c>
+      <c r="C81" t="s">
+        <v>174</v>
+      </c>
+      <c r="D81" t="s">
+        <v>304</v>
+      </c>
+      <c r="E81">
+        <v>52.36000061035156</v>
+      </c>
+      <c r="F81">
+        <v>4413550.4</v>
+      </c>
+      <c r="G81">
+        <v>42.82520004272461</v>
+      </c>
+      <c r="H81">
+        <v>38.04826681772868</v>
+      </c>
+      <c r="I81">
+        <v>37.57935004234314</v>
+      </c>
+      <c r="J81">
+        <v>35.15340005874634</v>
+      </c>
+      <c r="K81">
+        <v>22.21999931335449</v>
+      </c>
+      <c r="L81">
+        <v>57.15999984741211</v>
+      </c>
+      <c r="M81">
+        <v>57.85349261602452</v>
+      </c>
+      <c r="N81">
+        <v>124.239827644302</v>
+      </c>
+      <c r="O81">
+        <v>161.7192576457285</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>-146</v>
+      </c>
+      <c r="R81">
+        <v>11</v>
+      </c>
+      <c r="S81">
+        <v>5.545</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19">
+      <c r="A82" t="s">
+        <v>99</v>
+      </c>
+      <c r="B82" t="s">
+        <v>171</v>
+      </c>
+      <c r="C82" t="s">
+        <v>211</v>
+      </c>
+      <c r="D82" t="s">
+        <v>251</v>
+      </c>
+      <c r="E82">
+        <v>82.66999816894531</v>
+      </c>
+      <c r="F82">
+        <v>821776.4666666667</v>
+      </c>
+      <c r="G82">
+        <v>70.98360000610352</v>
+      </c>
+      <c r="H82">
+        <v>66.95213333129882</v>
+      </c>
+      <c r="I82">
+        <v>63.58050001144409</v>
+      </c>
+      <c r="J82">
+        <v>60.56665000915527</v>
+      </c>
+      <c r="K82">
+        <v>39.27000045776367</v>
+      </c>
+      <c r="L82">
+        <v>82.66999816894531</v>
+      </c>
+      <c r="M82">
+        <v>40.61914761275482</v>
+      </c>
+      <c r="N82">
+        <v>110.5169269296544</v>
+      </c>
+      <c r="O82">
+        <v>161.3377224618064</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="R82">
+        <v>1</v>
+      </c>
+      <c r="S82">
+        <v>10.045999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19">
+      <c r="A83" t="s">
+        <v>100</v>
+      </c>
+      <c r="B83" t="s">
+        <v>167</v>
+      </c>
+      <c r="C83" t="s">
+        <v>181</v>
+      </c>
+      <c r="D83" t="s">
+        <v>305</v>
+      </c>
+      <c r="E83">
+        <v>258.0899963378906</v>
+      </c>
+      <c r="F83">
+        <v>2224969.033333333</v>
+      </c>
+      <c r="G83">
+        <v>228.0812002563476</v>
+      </c>
+      <c r="H83">
+        <v>185.6242001342773</v>
+      </c>
+      <c r="I83">
+        <v>178.2952499389648</v>
+      </c>
+      <c r="J83">
+        <v>167.159349899292</v>
+      </c>
+      <c r="K83">
+        <v>125.6500015258789</v>
+      </c>
+      <c r="L83">
+        <v>270.3500061035156</v>
+      </c>
+      <c r="M83">
+        <v>30.31557301740719</v>
+      </c>
+      <c r="N83">
+        <v>105.4038943125156</v>
+      </c>
+      <c r="O83">
+        <v>159.2580691423825</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>-7</v>
+      </c>
+      <c r="R83">
+        <v>9</v>
+      </c>
+      <c r="S83">
+        <v>-21.608</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19">
+      <c r="A84" t="s">
+        <v>101</v>
+      </c>
+      <c r="B84" t="s">
+        <v>168</v>
+      </c>
+      <c r="C84" t="s">
+        <v>212</v>
+      </c>
+      <c r="D84" t="s">
+        <v>306</v>
+      </c>
+      <c r="E84">
+        <v>62.72000122070312</v>
+      </c>
+      <c r="F84">
+        <v>1389453.066666667</v>
+      </c>
+      <c r="G84">
+        <v>53.75180007934571</v>
+      </c>
+      <c r="H84">
+        <v>46.05333335876465</v>
+      </c>
+      <c r="I84">
+        <v>43.64419994354248</v>
+      </c>
+      <c r="J84">
+        <v>41.37169988632202</v>
+      </c>
+      <c r="K84">
+        <v>32.31000137329102</v>
+      </c>
+      <c r="L84">
+        <v>63.58000183105469</v>
+      </c>
+      <c r="M84">
+        <v>36.28857148375393</v>
+      </c>
+      <c r="N84">
+        <v>87.22388424090485</v>
+      </c>
+      <c r="O84">
+        <v>159.0177644644925</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>5</v>
+      </c>
+      <c r="R84">
+        <v>-1</v>
+      </c>
+      <c r="S84">
+        <v>23.586</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19">
+      <c r="A85" t="s">
+        <v>102</v>
+      </c>
+      <c r="B85" t="s">
+        <v>170</v>
+      </c>
+      <c r="C85" t="s">
         <v>192</v>
       </c>
-      <c r="R4">
+      <c r="D85" t="s">
+        <v>307</v>
+      </c>
+      <c r="E85">
+        <v>62.29999923706055</v>
+      </c>
+      <c r="F85">
+        <v>3388913.4</v>
+      </c>
+      <c r="G85">
+        <v>53.50570411682129</v>
+      </c>
+      <c r="H85">
+        <v>45.73102811177571</v>
+      </c>
+      <c r="I85">
+        <v>43.09412276268005</v>
+      </c>
+      <c r="J85">
+        <v>40.74576046943665</v>
+      </c>
+      <c r="K85">
+        <v>29.67679786682129</v>
+      </c>
+      <c r="L85">
+        <v>62.29999923706055</v>
+      </c>
+      <c r="M85">
+        <v>31.29894746641928</v>
+      </c>
+      <c r="N85">
+        <v>109.928306674596</v>
+      </c>
+      <c r="O85">
+        <v>158.8381031081887</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>0</v>
+      </c>
+      <c r="R85">
+        <v>-14</v>
+      </c>
+      <c r="S85">
+        <v>-5.999000000000001</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19">
+      <c r="A86" t="s">
+        <v>103</v>
+      </c>
+      <c r="B86" t="s">
+        <v>165</v>
+      </c>
+      <c r="C86" t="s">
+        <v>200</v>
+      </c>
+      <c r="D86" t="s">
+        <v>308</v>
+      </c>
+      <c r="E86">
+        <v>122.1699981689453</v>
+      </c>
+      <c r="F86">
+        <v>1475166.466666667</v>
+      </c>
+      <c r="G86">
+        <v>105.0526000976563</v>
+      </c>
+      <c r="H86">
+        <v>89.16639999389649</v>
+      </c>
+      <c r="I86">
+        <v>86.08420009613037</v>
+      </c>
+      <c r="J86">
+        <v>81.31590005874634</v>
+      </c>
+      <c r="K86">
+        <v>57.41999816894531</v>
+      </c>
+      <c r="L86">
+        <v>122.1699981689453</v>
+      </c>
+      <c r="M86">
+        <v>31.56364135897542</v>
+      </c>
+      <c r="N86">
+        <v>112.7655904994769</v>
+      </c>
+      <c r="O86">
+        <v>158.5170603028344</v>
+      </c>
+      <c r="P86">
+        <v>32</v>
+      </c>
+      <c r="Q86">
+        <v>13</v>
+      </c>
+      <c r="R86">
+        <v>-36</v>
+      </c>
+      <c r="S86">
+        <v>21.430999</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19">
+      <c r="A87" t="s">
+        <v>104</v>
+      </c>
+      <c r="B87" t="s">
+        <v>168</v>
+      </c>
+      <c r="C87" t="s">
+        <v>213</v>
+      </c>
+      <c r="D87" t="s">
+        <v>309</v>
+      </c>
+      <c r="E87">
+        <v>21</v>
+      </c>
+      <c r="F87">
+        <v>344870.1</v>
+      </c>
+      <c r="G87">
+        <v>16.164199924469</v>
+      </c>
+      <c r="H87">
+        <v>13.55029995600382</v>
+      </c>
+      <c r="I87">
+        <v>13.27792495250702</v>
+      </c>
+      <c r="J87">
+        <v>12.9493749666214</v>
+      </c>
+      <c r="K87">
+        <v>10.26000022888184</v>
+      </c>
+      <c r="L87">
+        <v>21</v>
+      </c>
+      <c r="M87">
+        <v>38.06706079770939</v>
+      </c>
+      <c r="N87">
+        <v>44.92753852113742</v>
+      </c>
+      <c r="O87">
+        <v>156.4173239895707</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>0</v>
+      </c>
+      <c r="R87">
+        <v>23</v>
+      </c>
+      <c r="S87">
+        <v>14.567</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19">
+      <c r="A88" t="s">
+        <v>105</v>
+      </c>
+      <c r="B88" t="s">
+        <v>162</v>
+      </c>
+      <c r="C88" t="s">
+        <v>172</v>
+      </c>
+      <c r="D88" t="s">
+        <v>310</v>
+      </c>
+      <c r="E88">
+        <v>322.3200073242188</v>
+      </c>
+      <c r="F88">
+        <v>466161.8</v>
+      </c>
+      <c r="G88">
+        <v>316.652601928711</v>
+      </c>
+      <c r="H88">
+        <v>230.0748006184896</v>
+      </c>
+      <c r="I88">
+        <v>226.7068755340576</v>
+      </c>
+      <c r="J88">
+        <v>216.5566504669189</v>
+      </c>
+      <c r="K88">
+        <v>161.0099945068359</v>
+      </c>
+      <c r="L88">
+        <v>322.3200073242188</v>
+      </c>
+      <c r="M88">
+        <v>56.86198852739241</v>
+      </c>
+      <c r="N88">
+        <v>72.29913652892131</v>
+      </c>
+      <c r="O88">
+        <v>156.3407196509533</v>
+      </c>
+      <c r="P88">
+        <v>36</v>
+      </c>
+      <c r="Q88">
+        <v>34</v>
+      </c>
+      <c r="R88">
+        <v>0</v>
+      </c>
+      <c r="S88">
+        <v>-36.436</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19">
+      <c r="A89" t="s">
+        <v>106</v>
+      </c>
+      <c r="B89" t="s">
+        <v>168</v>
+      </c>
+      <c r="C89" t="s">
+        <v>214</v>
+      </c>
+      <c r="D89" t="s">
+        <v>311</v>
+      </c>
+      <c r="E89">
+        <v>109.9499969482422</v>
+      </c>
+      <c r="F89">
+        <v>741616.8333333334</v>
+      </c>
+      <c r="G89">
+        <v>92.69720016479492</v>
+      </c>
+      <c r="H89">
+        <v>77.73339983622233</v>
+      </c>
+      <c r="I89">
+        <v>74.88569984436035</v>
+      </c>
+      <c r="J89">
+        <v>71.4796997833252</v>
+      </c>
+      <c r="K89">
+        <v>54.65000152587891</v>
+      </c>
+      <c r="L89">
+        <v>113.0299987792969</v>
+      </c>
+      <c r="M89">
+        <v>44.19671730917008</v>
+      </c>
+      <c r="N89">
+        <v>101.1893758066531</v>
+      </c>
+      <c r="O89">
+        <v>156.2048450920742</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>-46</v>
+      </c>
+      <c r="R89">
+        <v>7</v>
+      </c>
+      <c r="S89">
+        <v>-3.387</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19">
+      <c r="A90" t="s">
+        <v>107</v>
+      </c>
+      <c r="B90" t="s">
+        <v>162</v>
+      </c>
+      <c r="C90" t="s">
+        <v>172</v>
+      </c>
+      <c r="D90" t="s">
+        <v>312</v>
+      </c>
+      <c r="E90">
+        <v>135.1100006103516</v>
+      </c>
+      <c r="F90">
+        <v>6296564.133333334</v>
+      </c>
+      <c r="G90">
+        <v>115.9255999755859</v>
+      </c>
+      <c r="H90">
+        <v>103.2131998697917</v>
+      </c>
+      <c r="I90">
+        <v>97.32252494812012</v>
+      </c>
+      <c r="J90">
+        <v>93.16799995422363</v>
+      </c>
+      <c r="K90">
+        <v>69.44499969482422</v>
+      </c>
+      <c r="L90">
+        <v>135.9199981689453</v>
+      </c>
+      <c r="M90">
+        <v>39.80753462714097</v>
+      </c>
+      <c r="N90">
+        <v>91.67258434518331</v>
+      </c>
+      <c r="O90">
+        <v>156.2034993414449</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>52</v>
+      </c>
+      <c r="R90">
+        <v>12</v>
+      </c>
+      <c r="S90">
+        <v>88.066</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19">
+      <c r="A91" t="s">
+        <v>108</v>
+      </c>
+      <c r="B91" t="s">
+        <v>166</v>
+      </c>
+      <c r="C91" t="s">
+        <v>188</v>
+      </c>
+      <c r="D91" t="s">
+        <v>313</v>
+      </c>
+      <c r="E91">
+        <v>121.7200012207031</v>
+      </c>
+      <c r="F91">
+        <v>379330.8333333333</v>
+      </c>
+      <c r="G91">
+        <v>107.0141995239258</v>
+      </c>
+      <c r="H91">
+        <v>88.49579961140951</v>
+      </c>
+      <c r="I91">
+        <v>84.34019971847535</v>
+      </c>
+      <c r="J91">
+        <v>79.17284973144531</v>
+      </c>
+      <c r="K91">
+        <v>62.22999954223633</v>
+      </c>
+      <c r="L91">
+        <v>123.2099990844727</v>
+      </c>
+      <c r="M91">
+        <v>31.93149620891209</v>
+      </c>
+      <c r="N91">
+        <v>76.35469014896113</v>
+      </c>
+      <c r="O91">
+        <v>155.9704954163084</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>0</v>
+      </c>
+      <c r="R91">
+        <v>-10</v>
+      </c>
+      <c r="S91">
+        <v>39.72300000000001</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19">
+      <c r="A92" t="s">
+        <v>109</v>
+      </c>
+      <c r="B92" t="s">
+        <v>163</v>
+      </c>
+      <c r="C92" t="s">
+        <v>176</v>
+      </c>
+      <c r="D92" t="s">
+        <v>314</v>
+      </c>
+      <c r="E92">
+        <v>16.38999938964844</v>
+      </c>
+      <c r="F92">
+        <v>17950625.7</v>
+      </c>
+      <c r="G92">
+        <v>12.89340000152588</v>
+      </c>
+      <c r="H92">
+        <v>11.03543334007263</v>
+      </c>
+      <c r="I92">
+        <v>10.97092498540878</v>
+      </c>
+      <c r="J92">
+        <v>10.31857498884201</v>
+      </c>
+      <c r="K92">
+        <v>7.929999828338623</v>
+      </c>
+      <c r="L92">
+        <v>17</v>
+      </c>
+      <c r="M92">
+        <v>39.72719547543715</v>
+      </c>
+      <c r="N92">
+        <v>78.15217097224713</v>
+      </c>
+      <c r="O92">
+        <v>155.8986468092031</v>
+      </c>
+      <c r="P92">
+        <v>-116</v>
+      </c>
+      <c r="Q92">
+        <v>-48</v>
+      </c>
+      <c r="R92">
+        <v>1</v>
+      </c>
+      <c r="S92">
+        <v>-7.926</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19">
+      <c r="A93" t="s">
+        <v>110</v>
+      </c>
+      <c r="B93" t="s">
+        <v>164</v>
+      </c>
+      <c r="C93" t="s">
+        <v>194</v>
+      </c>
+      <c r="D93" t="s">
+        <v>315</v>
+      </c>
+      <c r="E93">
+        <v>264.739990234375</v>
+      </c>
+      <c r="F93">
+        <v>759190.3666666667</v>
+      </c>
+      <c r="G93">
+        <v>243.2659997558594</v>
+      </c>
+      <c r="H93">
+        <v>198.522566019694</v>
+      </c>
+      <c r="I93">
+        <v>187.8496244049072</v>
+      </c>
+      <c r="J93">
+        <v>175.7272745513916</v>
+      </c>
+      <c r="K93">
+        <v>121.5</v>
+      </c>
+      <c r="L93">
+        <v>281.3099975585938</v>
+      </c>
+      <c r="M93">
+        <v>31.67213441212908</v>
+      </c>
+      <c r="N93">
+        <v>89.96841925581214</v>
+      </c>
+      <c r="O93">
+        <v>155.0791001110591</v>
+      </c>
+      <c r="P93">
+        <v>-137</v>
+      </c>
+      <c r="Q93">
+        <v>-50</v>
+      </c>
+      <c r="R93">
+        <v>9</v>
+      </c>
+      <c r="S93">
+        <v>-9.045000399999999</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19">
+      <c r="A94" t="s">
+        <v>111</v>
+      </c>
+      <c r="B94" t="s">
+        <v>164</v>
+      </c>
+      <c r="C94" t="s">
+        <v>189</v>
+      </c>
+      <c r="D94" t="s">
+        <v>316</v>
+      </c>
+      <c r="E94">
+        <v>182.8600006103516</v>
+      </c>
+      <c r="F94">
+        <v>467601.5</v>
+      </c>
+      <c r="G94">
+        <v>166.1051989746094</v>
+      </c>
+      <c r="H94">
+        <v>141.8595328776042</v>
+      </c>
+      <c r="I94">
+        <v>134.2024995422363</v>
+      </c>
+      <c r="J94">
+        <v>125.0380995559692</v>
+      </c>
+      <c r="K94">
+        <v>78.5</v>
+      </c>
+      <c r="L94">
+        <v>196.6100006103516</v>
+      </c>
+      <c r="M94">
+        <v>31.3649458471922</v>
+      </c>
+      <c r="N94">
+        <v>115.5605288969944</v>
+      </c>
+      <c r="O94">
+        <v>154.9213623586434</v>
+      </c>
+      <c r="P94">
+        <v>-54</v>
+      </c>
+      <c r="Q94">
+        <v>-45</v>
+      </c>
+      <c r="R94">
+        <v>6</v>
+      </c>
+      <c r="S94">
+        <v>7.27</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19">
+      <c r="A95" t="s">
+        <v>112</v>
+      </c>
+      <c r="B95" t="s">
+        <v>166</v>
+      </c>
+      <c r="C95" t="s">
+        <v>188</v>
+      </c>
+      <c r="D95" t="s">
+        <v>317</v>
+      </c>
+      <c r="E95">
+        <v>95.81999969482422</v>
+      </c>
+      <c r="F95">
+        <v>1017796.4</v>
+      </c>
+      <c r="G95">
+        <v>86.87020080566407</v>
+      </c>
+      <c r="H95">
+        <v>73.60480036417643</v>
+      </c>
+      <c r="I95">
+        <v>71.12250022888183</v>
+      </c>
+      <c r="J95">
+        <v>67.42350019454956</v>
+      </c>
+      <c r="K95">
+        <v>46.29000091552734</v>
+      </c>
+      <c r="L95">
+        <v>96.02999877929688</v>
+      </c>
+      <c r="M95">
+        <v>31.33223807182945</v>
+      </c>
+      <c r="N95">
+        <v>98.17994357561565</v>
+      </c>
+      <c r="O95">
+        <v>154.6105466558741</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>15</v>
+      </c>
+      <c r="R95">
+        <v>-36</v>
+      </c>
+      <c r="S95">
+        <v>33.26</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19">
+      <c r="A96" t="s">
+        <v>113</v>
+      </c>
+      <c r="B96" t="s">
+        <v>167</v>
+      </c>
+      <c r="C96" t="s">
+        <v>215</v>
+      </c>
+      <c r="D96" t="s">
+        <v>318</v>
+      </c>
+      <c r="E96">
+        <v>62.54999923706055</v>
+      </c>
+      <c r="F96">
+        <v>821147.6333333333</v>
+      </c>
+      <c r="G96">
+        <v>56.17119995117187</v>
+      </c>
+      <c r="H96">
+        <v>45.01939989725749</v>
+      </c>
+      <c r="I96">
+        <v>44.27177496910095</v>
+      </c>
+      <c r="J96">
+        <v>41.58647492408753</v>
+      </c>
+      <c r="K96">
+        <v>31.92000007629395</v>
+      </c>
+      <c r="L96">
+        <v>63.7400016784668</v>
+      </c>
+      <c r="M96">
+        <v>32.26897446839061</v>
+      </c>
+      <c r="N96">
+        <v>83.97058599135454</v>
+      </c>
+      <c r="O96">
+        <v>154.262989426407</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+      <c r="Q96">
+        <v>26</v>
+      </c>
+      <c r="R96">
+        <v>-14</v>
+      </c>
+      <c r="S96">
+        <v>45.383</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19">
+      <c r="A97" t="s">
+        <v>114</v>
+      </c>
+      <c r="B97" t="s">
+        <v>165</v>
+      </c>
+      <c r="C97" t="s">
+        <v>201</v>
+      </c>
+      <c r="D97" t="s">
+        <v>319</v>
+      </c>
+      <c r="E97">
+        <v>26.76000022888184</v>
+      </c>
+      <c r="F97">
+        <v>3029410.966666667</v>
+      </c>
+      <c r="G97">
+        <v>23.3935998916626</v>
+      </c>
+      <c r="H97">
+        <v>18.99746664047241</v>
+      </c>
+      <c r="I97">
+        <v>18.44250001907348</v>
+      </c>
+      <c r="J97">
+        <v>17.39835003376007</v>
+      </c>
+      <c r="K97">
+        <v>14.28999996185303</v>
+      </c>
+      <c r="L97">
+        <v>27.65999984741211</v>
+      </c>
+      <c r="M97">
+        <v>49.41373789429988</v>
+      </c>
+      <c r="N97">
+        <v>44.88360164438863</v>
+      </c>
+      <c r="O97">
+        <v>153.8791808401862</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>0</v>
+      </c>
+      <c r="R97">
+        <v>-27</v>
+      </c>
+      <c r="S97">
+        <v>1.155</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19">
+      <c r="A98" t="s">
+        <v>115</v>
+      </c>
+      <c r="B98" t="s">
+        <v>164</v>
+      </c>
+      <c r="C98" t="s">
+        <v>203</v>
+      </c>
+      <c r="D98" t="s">
+        <v>320</v>
+      </c>
+      <c r="E98">
+        <v>27.64999961853027</v>
+      </c>
+      <c r="F98">
+        <v>544343.6</v>
+      </c>
+      <c r="G98">
+        <v>25.69259994506836</v>
+      </c>
+      <c r="H98">
+        <v>20.37466668446859</v>
+      </c>
+      <c r="I98">
+        <v>19.37177503108978</v>
+      </c>
+      <c r="J98">
+        <v>18.24947503089905</v>
+      </c>
+      <c r="K98">
+        <v>13.40999984741211</v>
+      </c>
+      <c r="L98">
+        <v>29.26000022888184</v>
+      </c>
+      <c r="M98">
+        <v>35.87223145070683</v>
+      </c>
+      <c r="N98">
+        <v>102.5641054304104</v>
+      </c>
+      <c r="O98">
+        <v>153.230737018593</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <v>-35</v>
+      </c>
+      <c r="R98">
+        <v>6</v>
+      </c>
+      <c r="S98">
+        <v>-57.133996</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19">
+      <c r="A99" t="s">
+        <v>116</v>
+      </c>
+      <c r="B99" t="s">
+        <v>163</v>
+      </c>
+      <c r="C99" t="s">
+        <v>202</v>
+      </c>
+      <c r="D99" t="s">
+        <v>321</v>
+      </c>
+      <c r="E99">
+        <v>22.79000091552734</v>
+      </c>
+      <c r="F99">
+        <v>910458.8</v>
+      </c>
+      <c r="G99">
+        <v>19.65980009078979</v>
+      </c>
+      <c r="H99">
+        <v>16.42860001246135</v>
+      </c>
+      <c r="I99">
+        <v>16.29170004367828</v>
+      </c>
+      <c r="J99">
+        <v>15.30735003948212</v>
+      </c>
+      <c r="K99">
+        <v>10.27999973297119</v>
+      </c>
+      <c r="L99">
+        <v>22.92000007629395</v>
+      </c>
+      <c r="M99">
+        <v>30.22857666015626</v>
+      </c>
+      <c r="N99">
+        <v>121.0475265564986</v>
+      </c>
+      <c r="O99">
+        <v>153.0563326756765</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99">
+        <v>-20</v>
+      </c>
+      <c r="R99">
+        <v>53</v>
+      </c>
+      <c r="S99">
+        <v>25.595</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19">
+      <c r="A100" t="s">
+        <v>117</v>
+      </c>
+      <c r="B100" t="s">
+        <v>166</v>
+      </c>
+      <c r="C100" t="s">
+        <v>216</v>
+      </c>
+      <c r="D100" t="s">
+        <v>322</v>
+      </c>
+      <c r="E100">
+        <v>167.4600067138672</v>
+      </c>
+      <c r="F100">
+        <v>6356742.533333333</v>
+      </c>
+      <c r="G100">
+        <v>141.1469996643066</v>
+      </c>
+      <c r="H100">
+        <v>123.5733213806152</v>
+      </c>
+      <c r="I100">
+        <v>119.7321164321899</v>
+      </c>
+      <c r="J100">
+        <v>114.2493857574463</v>
+      </c>
+      <c r="K100">
+        <v>89.40326690673828</v>
+      </c>
+      <c r="L100">
+        <v>167.9600067138672</v>
+      </c>
+      <c r="M100">
+        <v>38.95444640506081</v>
+      </c>
+      <c r="N100">
+        <v>86.95382872044142</v>
+      </c>
+      <c r="O100">
+        <v>152.5879641494451</v>
+      </c>
+      <c r="P100">
+        <v>0</v>
+      </c>
+      <c r="Q100">
+        <v>0</v>
+      </c>
+      <c r="R100">
+        <v>12</v>
+      </c>
+      <c r="S100">
+        <v>28.445</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19">
+      <c r="A101" t="s">
+        <v>118</v>
+      </c>
+      <c r="B101" t="s">
+        <v>162</v>
+      </c>
+      <c r="C101" t="s">
+        <v>172</v>
+      </c>
+      <c r="D101" t="s">
+        <v>323</v>
+      </c>
+      <c r="E101">
+        <v>45.47999954223633</v>
+      </c>
+      <c r="F101">
+        <v>840909.9</v>
+      </c>
+      <c r="G101">
+        <v>43.82839988708496</v>
+      </c>
+      <c r="H101">
+        <v>30.49966665267944</v>
+      </c>
+      <c r="I101">
+        <v>29.05549999713898</v>
+      </c>
+      <c r="J101">
+        <v>26.70019999980926</v>
+      </c>
+      <c r="K101">
+        <v>14.1899995803833</v>
+      </c>
+      <c r="L101">
+        <v>52.31000137329102</v>
+      </c>
+      <c r="M101">
+        <v>33.13817255675953</v>
+      </c>
+      <c r="N101">
+        <v>53.96072489060187</v>
+      </c>
+      <c r="O101">
+        <v>152.4318570921178</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+      <c r="Q101">
+        <v>0</v>
+      </c>
+      <c r="R101">
+        <v>-225</v>
+      </c>
+      <c r="S101">
+        <v>-59.972</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19">
+      <c r="A102" t="s">
+        <v>119</v>
+      </c>
+      <c r="B102" t="s">
+        <v>166</v>
+      </c>
+      <c r="C102" t="s">
+        <v>206</v>
+      </c>
+      <c r="D102" t="s">
+        <v>324</v>
+      </c>
+      <c r="E102">
+        <v>675.489990234375</v>
+      </c>
+      <c r="F102">
+        <v>515587.7666666667</v>
+      </c>
+      <c r="G102">
+        <v>626.5773999023437</v>
+      </c>
+      <c r="H102">
+        <v>519.6087996419271</v>
+      </c>
+      <c r="I102">
+        <v>495.3646496582031</v>
+      </c>
+      <c r="J102">
+        <v>462.673699798584</v>
+      </c>
+      <c r="K102">
+        <v>326.5299987792969</v>
+      </c>
+      <c r="L102">
+        <v>712.3099975585938</v>
+      </c>
+      <c r="M102">
+        <v>36.44608604322271</v>
+      </c>
+      <c r="N102">
+        <v>71.52251731036785</v>
+      </c>
+      <c r="O102">
+        <v>152.2832200948158</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+      <c r="Q102">
+        <v>19</v>
+      </c>
+      <c r="R102">
+        <v>-1</v>
+      </c>
+      <c r="S102">
+        <v>31.912002</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19">
+      <c r="A103" t="s">
+        <v>120</v>
+      </c>
+      <c r="B103" t="s">
+        <v>167</v>
+      </c>
+      <c r="C103" t="s">
+        <v>215</v>
+      </c>
+      <c r="D103" t="s">
+        <v>325</v>
+      </c>
+      <c r="E103">
+        <v>611.0800170898438</v>
+      </c>
+      <c r="F103">
+        <v>3570276.633333333</v>
+      </c>
+      <c r="G103">
+        <v>549.1252001953125</v>
+      </c>
+      <c r="H103">
+        <v>467.995532836914</v>
+      </c>
+      <c r="I103">
+        <v>457.7713996887207</v>
+      </c>
+      <c r="J103">
+        <v>432.2544995117187</v>
+      </c>
+      <c r="K103">
+        <v>293.8999938964844</v>
+      </c>
+      <c r="L103">
+        <v>619.3400268554688</v>
+      </c>
+      <c r="M103">
+        <v>34.6703111641498</v>
+      </c>
+      <c r="N103">
+        <v>101.1521116236719</v>
+      </c>
+      <c r="O103">
+        <v>151.0261906570812</v>
+      </c>
+      <c r="P103">
+        <v>1658</v>
+      </c>
+      <c r="Q103">
+        <v>21</v>
+      </c>
+      <c r="R103">
+        <v>3</v>
+      </c>
+      <c r="S103">
+        <v>26.147</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19">
+      <c r="A104" t="s">
+        <v>121</v>
+      </c>
+      <c r="B104" t="s">
+        <v>165</v>
+      </c>
+      <c r="C104" t="s">
+        <v>217</v>
+      </c>
+      <c r="D104" t="s">
+        <v>302</v>
+      </c>
+      <c r="E104">
+        <v>32.95999908447266</v>
+      </c>
+      <c r="F104">
+        <v>634548.8333333334</v>
+      </c>
+      <c r="G104">
+        <v>29.49899978637695</v>
+      </c>
+      <c r="H104">
+        <v>23.58406659444173</v>
+      </c>
+      <c r="I104">
+        <v>23.25654993057251</v>
+      </c>
+      <c r="J104">
+        <v>22.19159993171692</v>
+      </c>
+      <c r="K104">
+        <v>17.57999992370605</v>
+      </c>
+      <c r="L104">
+        <v>34.43000030517578</v>
+      </c>
+      <c r="M104">
+        <v>52.73400927247201</v>
+      </c>
+      <c r="N104">
+        <v>64.79999542236328</v>
+      </c>
+      <c r="O104">
+        <v>150.96930638702</v>
+      </c>
+      <c r="P104">
+        <v>-331</v>
+      </c>
+      <c r="Q104">
+        <v>-150</v>
+      </c>
+      <c r="R104">
+        <v>5</v>
+      </c>
+      <c r="S104">
+        <v>184.55901</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19">
+      <c r="A105" t="s">
+        <v>122</v>
+      </c>
+      <c r="B105" t="s">
+        <v>162</v>
+      </c>
+      <c r="C105" t="s">
+        <v>218</v>
+      </c>
+      <c r="D105" t="s">
+        <v>326</v>
+      </c>
+      <c r="E105">
+        <v>37.40000152587891</v>
+      </c>
+      <c r="F105">
+        <v>394934.6333333334</v>
+      </c>
+      <c r="G105">
+        <v>33.88500019073486</v>
+      </c>
+      <c r="H105">
+        <v>27.52073337554932</v>
+      </c>
+      <c r="I105">
+        <v>26.15934999465942</v>
+      </c>
+      <c r="J105">
+        <v>24.91974997520447</v>
+      </c>
+      <c r="K105">
+        <v>21.05999946594238</v>
+      </c>
+      <c r="L105">
+        <v>37.59999847412109</v>
+      </c>
+      <c r="M105">
+        <v>36.84596278918437</v>
+      </c>
+      <c r="N105">
+        <v>58.13954388639912</v>
+      </c>
+      <c r="O105">
+        <v>150.8778437365189</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="Q105">
+        <v>0</v>
+      </c>
+      <c r="R105">
+        <v>10</v>
+      </c>
+      <c r="S105">
+        <v>24.678</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19">
+      <c r="A106" t="s">
+        <v>123</v>
+      </c>
+      <c r="B106" t="s">
+        <v>164</v>
+      </c>
+      <c r="C106" t="s">
+        <v>175</v>
+      </c>
+      <c r="D106" t="s">
+        <v>327</v>
+      </c>
+      <c r="E106">
+        <v>17.70000076293945</v>
+      </c>
+      <c r="F106">
+        <v>24216668.56666667</v>
+      </c>
+      <c r="G106">
+        <v>14.46719993591309</v>
+      </c>
+      <c r="H106">
+        <v>12.39353333791097</v>
+      </c>
+      <c r="I106">
+        <v>11.95350002288818</v>
+      </c>
+      <c r="J106">
+        <v>11.18065002918243</v>
+      </c>
+      <c r="K106">
+        <v>7.989999771118164</v>
+      </c>
+      <c r="L106">
+        <v>19.03000068664551</v>
+      </c>
+      <c r="M106">
+        <v>33.98940735674907</v>
+      </c>
+      <c r="N106">
+        <v>96.88544175277494</v>
+      </c>
+      <c r="O106">
+        <v>150.6403320485977</v>
+      </c>
+      <c r="P106">
+        <v>0</v>
+      </c>
+      <c r="Q106">
+        <v>0</v>
+      </c>
+      <c r="R106">
+        <v>6</v>
+      </c>
+      <c r="S106">
+        <v>-73.172</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19">
+      <c r="A107" t="s">
+        <v>124</v>
+      </c>
+      <c r="B107" t="s">
+        <v>169</v>
+      </c>
+      <c r="C107" t="s">
+        <v>219</v>
+      </c>
+      <c r="D107" t="s">
+        <v>328</v>
+      </c>
+      <c r="E107">
+        <v>254.4600067138672</v>
+      </c>
+      <c r="F107">
+        <v>311159</v>
+      </c>
+      <c r="G107">
+        <v>229.7200003051758</v>
+      </c>
+      <c r="H107">
+        <v>194.2145331827799</v>
+      </c>
+      <c r="I107">
+        <v>190.3735997772217</v>
+      </c>
+      <c r="J107">
+        <v>181.1061496734619</v>
+      </c>
+      <c r="K107">
+        <v>131.6199951171875</v>
+      </c>
+      <c r="L107">
+        <v>259.5700073242188</v>
+      </c>
+      <c r="M107">
+        <v>34.59219824384297</v>
+      </c>
+      <c r="N107">
+        <v>93.32929353728467</v>
+      </c>
+      <c r="O107">
+        <v>150.5933459431767</v>
+      </c>
+      <c r="P107">
+        <v>16</v>
+      </c>
+      <c r="Q107">
+        <v>36</v>
+      </c>
+      <c r="R107">
+        <v>-10</v>
+      </c>
+      <c r="S107">
+        <v>40.093</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19">
+      <c r="A108" t="s">
+        <v>125</v>
+      </c>
+      <c r="B108" t="s">
+        <v>164</v>
+      </c>
+      <c r="C108" t="s">
+        <v>185</v>
+      </c>
+      <c r="D108" t="s">
+        <v>329</v>
+      </c>
+      <c r="E108">
+        <v>1291.880004882812</v>
+      </c>
+      <c r="F108">
+        <v>2988232.866666667</v>
+      </c>
+      <c r="G108">
+        <v>1223.190600585938</v>
+      </c>
+      <c r="H108">
+        <v>1013.758334960938</v>
+      </c>
+      <c r="I108">
+        <v>975.1365515136719</v>
+      </c>
+      <c r="J108">
+        <v>908.9102017211914</v>
+      </c>
+      <c r="K108">
+        <v>610.1599731445312</v>
+      </c>
+      <c r="L108">
+        <v>1407.010009765625</v>
+      </c>
+      <c r="M108">
+        <v>36.80822001302919</v>
+      </c>
+      <c r="N108">
+        <v>106.357429273692</v>
+      </c>
+      <c r="O108">
+        <v>149.9342816289364</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
+      </c>
+      <c r="Q108">
+        <v>0</v>
+      </c>
+      <c r="R108">
+        <v>5</v>
+      </c>
+      <c r="S108">
+        <v>24.749</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19">
+      <c r="A109" t="s">
+        <v>126</v>
+      </c>
+      <c r="B109" t="s">
+        <v>166</v>
+      </c>
+      <c r="C109" t="s">
+        <v>187</v>
+      </c>
+      <c r="D109" t="s">
+        <v>330</v>
+      </c>
+      <c r="E109">
+        <v>17.57999992370605</v>
+      </c>
+      <c r="F109">
+        <v>479212.4</v>
+      </c>
+      <c r="G109">
+        <v>13.63280004501343</v>
+      </c>
+      <c r="H109">
+        <v>13.2276862970988</v>
+      </c>
+      <c r="I109">
+        <v>13.0016982460022</v>
+      </c>
+      <c r="J109">
+        <v>12.75501637935638</v>
+      </c>
+      <c r="K109">
+        <v>10.31051349639893</v>
+      </c>
+      <c r="L109">
+        <v>17.57999992370605</v>
+      </c>
+      <c r="M109">
+        <v>40.66164509110632</v>
+      </c>
+      <c r="N109">
+        <v>64.39245976394825</v>
+      </c>
+      <c r="O109">
+        <v>149.9274922926163</v>
+      </c>
+      <c r="P109">
+        <v>-29</v>
+      </c>
+      <c r="Q109">
+        <v>-80</v>
+      </c>
+      <c r="R109">
+        <v>10</v>
+      </c>
+      <c r="S109">
+        <v>7.014999500000001</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19">
+      <c r="A110" t="s">
+        <v>127</v>
+      </c>
+      <c r="B110" t="s">
+        <v>164</v>
+      </c>
+      <c r="C110" t="s">
+        <v>189</v>
+      </c>
+      <c r="D110" t="s">
+        <v>331</v>
+      </c>
+      <c r="E110">
+        <v>950.8300170898438</v>
+      </c>
+      <c r="F110">
+        <v>1054103.966666667</v>
+      </c>
+      <c r="G110">
+        <v>860.8308020019531</v>
+      </c>
+      <c r="H110">
+        <v>734.3852034505209</v>
+      </c>
+      <c r="I110">
+        <v>710.5146029663086</v>
+      </c>
+      <c r="J110">
+        <v>670.8946520996094</v>
+      </c>
+      <c r="K110">
+        <v>485.0799865722656</v>
+      </c>
+      <c r="L110">
+        <v>994.5700073242188</v>
+      </c>
+      <c r="M110">
+        <v>35.22050716026239</v>
+      </c>
+      <c r="N110">
+        <v>95.2222648435862</v>
+      </c>
+      <c r="O110">
+        <v>149.0119467588387</v>
+      </c>
+      <c r="P110">
+        <v>-33</v>
+      </c>
+      <c r="Q110">
+        <v>1</v>
+      </c>
+      <c r="R110">
+        <v>8</v>
+      </c>
+      <c r="S110">
+        <v>41.849</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19">
+      <c r="A111" t="s">
+        <v>128</v>
+      </c>
+      <c r="B111" t="s">
+        <v>164</v>
+      </c>
+      <c r="C111" t="s">
+        <v>185</v>
+      </c>
+      <c r="D111" t="s">
+        <v>332</v>
+      </c>
+      <c r="E111">
+        <v>144.3999938964844</v>
+      </c>
+      <c r="F111">
+        <v>16727275.23333333</v>
+      </c>
+      <c r="G111">
+        <v>120.4309994506836</v>
+      </c>
+      <c r="H111">
+        <v>102.5241333516439</v>
+      </c>
+      <c r="I111">
+        <v>102.1642001342773</v>
+      </c>
+      <c r="J111">
+        <v>97.48215019226075</v>
+      </c>
+      <c r="K111">
+        <v>82.25</v>
+      </c>
+      <c r="L111">
+        <v>149.1999969482422</v>
+      </c>
+      <c r="M111">
+        <v>43.89635883624172</v>
+      </c>
+      <c r="N111">
+        <v>66.55132523555648</v>
+      </c>
+      <c r="O111">
+        <v>148.1602485169357</v>
+      </c>
+      <c r="P111">
+        <v>-19</v>
+      </c>
+      <c r="Q111">
+        <v>-16</v>
+      </c>
+      <c r="R111">
+        <v>14</v>
+      </c>
+      <c r="S111">
+        <v>26.002002</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19">
+      <c r="A112" t="s">
+        <v>129</v>
+      </c>
+      <c r="B112" t="s">
+        <v>162</v>
+      </c>
+      <c r="C112" t="s">
+        <v>172</v>
+      </c>
+      <c r="D112" t="s">
+        <v>333</v>
+      </c>
+      <c r="E112">
+        <v>153.8000030517578</v>
+      </c>
+      <c r="F112">
+        <v>412867.7</v>
+      </c>
+      <c r="G112">
+        <v>141.1502987670899</v>
+      </c>
+      <c r="H112">
+        <v>112.5028997294108</v>
+      </c>
+      <c r="I112">
+        <v>106.7906748580933</v>
+      </c>
+      <c r="J112">
+        <v>100.7217749404907</v>
+      </c>
+      <c r="K112">
+        <v>69.95999908447266</v>
+      </c>
+      <c r="L112">
+        <v>159.3999938964844</v>
+      </c>
+      <c r="M112">
+        <v>42.81734568205609</v>
+      </c>
+      <c r="N112">
+        <v>41.7250348409262</v>
+      </c>
+      <c r="O112">
+        <v>147.2953158794101</v>
+      </c>
+      <c r="P112">
+        <v>0</v>
+      </c>
+      <c r="Q112">
+        <v>-18</v>
+      </c>
+      <c r="R112">
+        <v>187</v>
+      </c>
+      <c r="S112">
+        <v>-818.432</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19">
+      <c r="A113" t="s">
+        <v>130</v>
+      </c>
+      <c r="B113" t="s">
+        <v>165</v>
+      </c>
+      <c r="C113" t="s">
+        <v>220</v>
+      </c>
+      <c r="D113" t="s">
+        <v>334</v>
+      </c>
+      <c r="E113">
+        <v>180.4499969482422</v>
+      </c>
+      <c r="F113">
+        <v>1188908.966666667</v>
+      </c>
+      <c r="G113">
+        <v>160.3420004272461</v>
+      </c>
+      <c r="H113">
+        <v>133.4188383992513</v>
+      </c>
+      <c r="I113">
+        <v>130.3665879058838</v>
+      </c>
+      <c r="J113">
+        <v>123.1412637329102</v>
+      </c>
+      <c r="K113">
+        <v>104.2125625610352</v>
+      </c>
+      <c r="L113">
+        <v>188.4400024414062</v>
+      </c>
+      <c r="M113">
+        <v>37.66252739055651</v>
+      </c>
+      <c r="N113">
+        <v>65.6126468098586</v>
+      </c>
+      <c r="O113">
+        <v>146.9520472482857</v>
+      </c>
+      <c r="P113">
+        <v>31</v>
+      </c>
+      <c r="Q113">
+        <v>-6</v>
+      </c>
+      <c r="R113">
+        <v>18</v>
+      </c>
+      <c r="S113">
+        <v>23.331</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19">
+      <c r="A114" t="s">
+        <v>131</v>
+      </c>
+      <c r="B114" t="s">
+        <v>163</v>
+      </c>
+      <c r="C114" t="s">
+        <v>221</v>
+      </c>
+      <c r="D114" t="s">
+        <v>335</v>
+      </c>
+      <c r="E114">
+        <v>17.48999977111816</v>
+      </c>
+      <c r="F114">
+        <v>5550334.733333333</v>
+      </c>
+      <c r="G114">
+        <v>16.3992000579834</v>
+      </c>
+      <c r="H114">
+        <v>14.04086668650309</v>
+      </c>
+      <c r="I114">
+        <v>13.40055002689362</v>
+      </c>
+      <c r="J114">
+        <v>12.65260001659393</v>
+      </c>
+      <c r="K114">
+        <v>9.850000381469727</v>
+      </c>
+      <c r="L114">
+        <v>18.10000038146973</v>
+      </c>
+      <c r="M114">
+        <v>31.90044848583706</v>
+      </c>
+      <c r="N114">
+        <v>72.8260866492285</v>
+      </c>
+      <c r="O114">
+        <v>146.5460386950394</v>
+      </c>
+      <c r="P114">
+        <v>0</v>
+      </c>
+      <c r="Q114">
+        <v>0</v>
+      </c>
+      <c r="R114">
+        <v>15</v>
+      </c>
+      <c r="S114">
+        <v>4.077999999999999</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19">
+      <c r="A115" t="s">
+        <v>132</v>
+      </c>
+      <c r="B115" t="s">
+        <v>164</v>
+      </c>
+      <c r="C115" t="s">
+        <v>174</v>
+      </c>
+      <c r="D115" t="s">
+        <v>336</v>
+      </c>
+      <c r="E115">
+        <v>62.97000122070312</v>
+      </c>
+      <c r="F115">
+        <v>6322951.333333333</v>
+      </c>
+      <c r="G115">
+        <v>56.53359992980957</v>
+      </c>
+      <c r="H115">
+        <v>48.83059997558594</v>
+      </c>
+      <c r="I115">
+        <v>46.50204990386963</v>
+      </c>
+      <c r="J115">
+        <v>44.10204986572266</v>
+      </c>
+      <c r="K115">
+        <v>32.09000015258789</v>
+      </c>
+      <c r="L115">
+        <v>64.69999694824219</v>
+      </c>
+      <c r="M115">
+        <v>31.57125035030495</v>
+      </c>
+      <c r="N115">
+        <v>83.10556073943232</v>
+      </c>
+      <c r="O115">
+        <v>146.1456617713687</v>
+      </c>
+      <c r="P115">
+        <v>-35</v>
+      </c>
+      <c r="Q115">
+        <v>-215</v>
+      </c>
+      <c r="R115">
+        <v>10</v>
+      </c>
+      <c r="S115">
+        <v>-19.723</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19">
+      <c r="A116" t="s">
+        <v>133</v>
+      </c>
+      <c r="B116" t="s">
+        <v>164</v>
+      </c>
+      <c r="C116" t="s">
+        <v>194</v>
+      </c>
+      <c r="D116" t="s">
+        <v>337</v>
+      </c>
+      <c r="E116">
+        <v>141.2700042724609</v>
+      </c>
+      <c r="F116">
+        <v>660029.7333333333</v>
+      </c>
+      <c r="G116">
+        <v>129.7421997070313</v>
+      </c>
+      <c r="H116">
+        <v>106.2959665934245</v>
+      </c>
+      <c r="I116">
+        <v>100.1074249649048</v>
+      </c>
+      <c r="J116">
+        <v>94.53032508850097</v>
+      </c>
+      <c r="K116">
+        <v>73.52999877929688</v>
+      </c>
+      <c r="L116">
+        <v>142.7599945068359</v>
+      </c>
+      <c r="M116">
+        <v>36.91607274144819</v>
+      </c>
+      <c r="N116">
+        <v>62.17426619518742</v>
+      </c>
+      <c r="O116">
+        <v>146.0522928181348</v>
+      </c>
+      <c r="P116">
+        <v>-107</v>
+      </c>
+      <c r="Q116">
+        <v>-108</v>
+      </c>
+      <c r="R116">
+        <v>1</v>
+      </c>
+      <c r="S116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19">
+      <c r="A117" t="s">
+        <v>134</v>
+      </c>
+      <c r="B117" t="s">
+        <v>165</v>
+      </c>
+      <c r="C117" t="s">
+        <v>182</v>
+      </c>
+      <c r="D117" t="s">
+        <v>251</v>
+      </c>
+      <c r="E117">
+        <v>37.93000030517578</v>
+      </c>
+      <c r="F117">
+        <v>372571.5666666667</v>
+      </c>
+      <c r="G117">
+        <v>33.6755997467041</v>
+      </c>
+      <c r="H117">
+        <v>29.60358476003011</v>
+      </c>
+      <c r="I117">
+        <v>28.24894425392151</v>
+      </c>
+      <c r="J117">
+        <v>26.72909523010254</v>
+      </c>
+      <c r="K117">
+        <v>17.12530708312988</v>
+      </c>
+      <c r="L117">
+        <v>38.93999862670898</v>
+      </c>
+      <c r="M117">
+        <v>34.37492102546415</v>
+      </c>
+      <c r="N117">
+        <v>63.39501859185064</v>
+      </c>
+      <c r="O117">
+        <v>145.3626354249231</v>
+      </c>
+      <c r="P117">
+        <v>0</v>
+      </c>
+      <c r="Q117">
+        <v>38</v>
+      </c>
+      <c r="R117">
+        <v>10</v>
+      </c>
+      <c r="S117">
+        <v>33.565</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19">
+      <c r="A118" t="s">
+        <v>135</v>
+      </c>
+      <c r="B118" t="s">
+        <v>166</v>
+      </c>
+      <c r="C118" t="s">
+        <v>197</v>
+      </c>
+      <c r="D118" t="s">
+        <v>338</v>
+      </c>
+      <c r="E118">
+        <v>21.18000030517578</v>
+      </c>
+      <c r="F118">
+        <v>808538.2</v>
+      </c>
+      <c r="G118">
+        <v>18.04059999465942</v>
+      </c>
+      <c r="H118">
+        <v>15.48966660817464</v>
+      </c>
+      <c r="I118">
+        <v>15.06344994544983</v>
+      </c>
+      <c r="J118">
+        <v>14.52134994029999</v>
+      </c>
+      <c r="K118">
+        <v>12.40999984741211</v>
+      </c>
+      <c r="L118">
+        <v>21.18000030517578</v>
+      </c>
+      <c r="M118">
+        <v>48.00838353674275</v>
+      </c>
+      <c r="N118">
+        <v>31.14551582325833</v>
+      </c>
+      <c r="O118">
+        <v>145.3529804751247</v>
+      </c>
+      <c r="P118">
+        <v>-84</v>
+      </c>
+      <c r="Q118">
+        <v>-108</v>
+      </c>
+      <c r="R118">
+        <v>39</v>
+      </c>
+      <c r="S118">
+        <v>-1.312</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19">
+      <c r="A119" t="s">
+        <v>136</v>
+      </c>
+      <c r="B119" t="s">
+        <v>164</v>
+      </c>
+      <c r="C119" t="s">
+        <v>189</v>
+      </c>
+      <c r="D119" t="s">
+        <v>339</v>
+      </c>
+      <c r="E119">
+        <v>984.2899780273438</v>
+      </c>
+      <c r="F119">
+        <v>1170076.666666667</v>
+      </c>
+      <c r="G119">
+        <v>865.3316015625001</v>
+      </c>
+      <c r="H119">
+        <v>721.4741345214844</v>
+      </c>
+      <c r="I119">
+        <v>719.9599505615234</v>
+      </c>
+      <c r="J119">
+        <v>689.9769500732422</v>
+      </c>
+      <c r="K119">
+        <v>570.5999755859375</v>
+      </c>
+      <c r="L119">
+        <v>1047.390014648438</v>
+      </c>
+      <c r="M119">
+        <v>41.33365713408812</v>
+      </c>
+      <c r="N119">
+        <v>62.23936014544855</v>
+      </c>
+      <c r="O119">
+        <v>144.7106095465295</v>
+      </c>
+      <c r="P119">
+        <v>0</v>
+      </c>
+      <c r="Q119">
+        <v>41</v>
+      </c>
+      <c r="R119">
+        <v>8</v>
+      </c>
+      <c r="S119">
+        <v>70.42100000000001</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19">
+      <c r="A120" t="s">
+        <v>137</v>
+      </c>
+      <c r="B120" t="s">
+        <v>164</v>
+      </c>
+      <c r="C120" t="s">
+        <v>189</v>
+      </c>
+      <c r="D120" t="s">
+        <v>340</v>
+      </c>
+      <c r="E120">
+        <v>698.4000244140625</v>
+      </c>
+      <c r="F120">
+        <v>980356.6333333333</v>
+      </c>
+      <c r="G120">
+        <v>628.3204028320313</v>
+      </c>
+      <c r="H120">
+        <v>545.7418005371094</v>
+      </c>
+      <c r="I120">
+        <v>527.3049508666992</v>
+      </c>
+      <c r="J120">
+        <v>498.6652005004883</v>
+      </c>
+      <c r="K120">
+        <v>357.3599853515625</v>
+      </c>
+      <c r="L120">
+        <v>723.260009765625</v>
+      </c>
+      <c r="M120">
+        <v>30.68129296361475</v>
+      </c>
+      <c r="N120">
+        <v>88.59874943115879</v>
+      </c>
+      <c r="O120">
+        <v>144.4785359805653</v>
+      </c>
+      <c r="P120">
+        <v>-38</v>
+      </c>
+      <c r="Q120">
+        <v>10</v>
+      </c>
+      <c r="R120">
+        <v>4</v>
+      </c>
+      <c r="S120">
+        <v>95.85299499999999</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19">
+      <c r="A121" t="s">
+        <v>138</v>
+      </c>
+      <c r="B121" t="s">
+        <v>165</v>
+      </c>
+      <c r="C121" t="s">
+        <v>184</v>
+      </c>
+      <c r="D121" t="s">
+        <v>341</v>
+      </c>
+      <c r="E121">
+        <v>75.41999816894531</v>
+      </c>
+      <c r="F121">
+        <v>809874.7666666667</v>
+      </c>
+      <c r="G121">
+        <v>64.51789749145507</v>
+      </c>
+      <c r="H121">
+        <v>59.34460299173991</v>
+      </c>
+      <c r="I121">
+        <v>58.1945619392395</v>
+      </c>
+      <c r="J121">
+        <v>55.60352418899536</v>
+      </c>
+      <c r="K121">
+        <v>41.184326171875</v>
+      </c>
+      <c r="L121">
+        <v>76.23000335693359</v>
+      </c>
+      <c r="M121">
+        <v>37.85958918317971</v>
+      </c>
+      <c r="N121">
+        <v>76.83499094801691</v>
+      </c>
+      <c r="O121">
+        <v>144.3415381442547</v>
+      </c>
+      <c r="P121">
+        <v>26</v>
+      </c>
+      <c r="Q121">
+        <v>34</v>
+      </c>
+      <c r="R121">
+        <v>-6</v>
+      </c>
+      <c r="S121">
+        <v>63.88200000000001</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19">
+      <c r="A122" t="s">
+        <v>139</v>
+      </c>
+      <c r="B122" t="s">
+        <v>164</v>
+      </c>
+      <c r="C122" t="s">
+        <v>222</v>
+      </c>
+      <c r="D122" t="s">
+        <v>342</v>
+      </c>
+      <c r="E122">
+        <v>98.38999938964844</v>
+      </c>
+      <c r="F122">
+        <v>375084.1333333334</v>
+      </c>
+      <c r="G122">
+        <v>88.11979995727539</v>
+      </c>
+      <c r="H122">
+        <v>76.20740005493164</v>
+      </c>
+      <c r="I122">
+        <v>75.34150009155273</v>
+      </c>
+      <c r="J122">
+        <v>72.03955015182495</v>
+      </c>
+      <c r="K122">
+        <v>54.59000015258789</v>
+      </c>
+      <c r="L122">
+        <v>99.76999664306641</v>
+      </c>
+      <c r="M122">
+        <v>30.76821130138065</v>
+      </c>
+      <c r="N122">
+        <v>80.23447355675482</v>
+      </c>
+      <c r="O122">
+        <v>144.2001366603477</v>
+      </c>
+      <c r="P122">
+        <v>-3900</v>
+      </c>
+      <c r="Q122">
+        <v>-213</v>
+      </c>
+      <c r="R122">
+        <v>8</v>
+      </c>
+      <c r="S122">
+        <v>-0.32499998</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19">
+      <c r="A123" t="s">
+        <v>140</v>
+      </c>
+      <c r="B123" t="s">
+        <v>164</v>
+      </c>
+      <c r="C123" t="s">
+        <v>189</v>
+      </c>
+      <c r="D123" t="s">
+        <v>251</v>
+      </c>
+      <c r="E123">
+        <v>204.9400024414062</v>
+      </c>
+      <c r="F123">
+        <v>7203506.966666667</v>
+      </c>
+      <c r="G123">
+        <v>177.7184140014649</v>
+      </c>
+      <c r="H123">
+        <v>155.8669045003255</v>
+      </c>
+      <c r="I123">
+        <v>151.8665753936768</v>
+      </c>
+      <c r="J123">
+        <v>143.6055572128296</v>
+      </c>
+      <c r="K123">
+        <v>109.367561340332</v>
+      </c>
+      <c r="L123">
+        <v>212.6100006103516</v>
+      </c>
+      <c r="M123">
+        <v>38.97056670431955</v>
+      </c>
+      <c r="N123">
+        <v>74.46487359398772</v>
+      </c>
+      <c r="O123">
+        <v>143.8408341198467</v>
+      </c>
+      <c r="P123">
+        <v>19</v>
+      </c>
+      <c r="Q123">
+        <v>0</v>
+      </c>
+      <c r="R123">
+        <v>0</v>
+      </c>
+      <c r="S123">
+        <v>46.40700200000001</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19">
+      <c r="A124" t="s">
+        <v>141</v>
+      </c>
+      <c r="B124" t="s">
+        <v>166</v>
+      </c>
+      <c r="C124" t="s">
+        <v>188</v>
+      </c>
+      <c r="D124" t="s">
+        <v>251</v>
+      </c>
+      <c r="E124">
+        <v>115.4700012207031</v>
+      </c>
+      <c r="F124">
+        <v>247919.6666666667</v>
+      </c>
+      <c r="G124">
+        <v>105.9542002868652</v>
+      </c>
+      <c r="H124">
+        <v>91.12453333536784</v>
+      </c>
+      <c r="I124">
+        <v>88.85719997406005</v>
+      </c>
+      <c r="J124">
+        <v>84.75824993133546</v>
+      </c>
+      <c r="K124">
+        <v>61.68000030517578</v>
+      </c>
+      <c r="L124">
+        <v>117.1900024414062</v>
+      </c>
+      <c r="M124">
+        <v>30.00450531124228</v>
+      </c>
+      <c r="N124">
+        <v>73.37838418355453</v>
+      </c>
+      <c r="O124">
+        <v>142.5362694458422</v>
+      </c>
+      <c r="P124">
+        <v>-212</v>
+      </c>
+      <c r="Q124">
+        <v>0</v>
+      </c>
+      <c r="R124">
+        <v>5</v>
+      </c>
+      <c r="S124">
+        <v>12.728</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19">
+      <c r="A125" t="s">
+        <v>142</v>
+      </c>
+      <c r="B125" t="s">
+        <v>164</v>
+      </c>
+      <c r="C125" t="s">
+        <v>189</v>
+      </c>
+      <c r="D125" t="s">
+        <v>343</v>
+      </c>
+      <c r="E125">
+        <v>142.0299987792969</v>
+      </c>
+      <c r="F125">
+        <v>1588959.4</v>
+      </c>
+      <c r="G125">
+        <v>124.9851992797851</v>
+      </c>
+      <c r="H125">
+        <v>107.7363997395833</v>
+      </c>
+      <c r="I125">
+        <v>107.6254997253418</v>
+      </c>
+      <c r="J125">
+        <v>102.5660999298096</v>
+      </c>
+      <c r="K125">
+        <v>69.37000274658203</v>
+      </c>
+      <c r="L125">
+        <v>145.3699951171875</v>
+      </c>
+      <c r="M125">
+        <v>32.75072587639811</v>
+      </c>
+      <c r="N125">
+        <v>76.06297508752478</v>
+      </c>
+      <c r="O125">
+        <v>142.2900422290517</v>
+      </c>
+      <c r="P125">
+        <v>0</v>
+      </c>
+      <c r="Q125">
+        <v>0</v>
+      </c>
+      <c r="R125">
+        <v>-9</v>
+      </c>
+      <c r="S125">
+        <v>5.4530002</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19">
+      <c r="A126" t="s">
+        <v>143</v>
+      </c>
+      <c r="B126" t="s">
+        <v>166</v>
+      </c>
+      <c r="C126" t="s">
+        <v>187</v>
+      </c>
+      <c r="D126" t="s">
+        <v>344</v>
+      </c>
+      <c r="E126">
+        <v>311.3699951171875</v>
+      </c>
+      <c r="F126">
+        <v>540141.3333333334</v>
+      </c>
+      <c r="G126">
+        <v>269.2010006713867</v>
+      </c>
+      <c r="H126">
+        <v>234.1455331420898</v>
+      </c>
+      <c r="I126">
+        <v>223.3939002227783</v>
+      </c>
+      <c r="J126">
+        <v>215.0705001068115</v>
+      </c>
+      <c r="K126">
+        <v>175.7299957275391</v>
+      </c>
+      <c r="L126">
+        <v>319.8800048828125</v>
+      </c>
+      <c r="M126">
+        <v>31.72433737428508</v>
+      </c>
+      <c r="N126">
+        <v>47.42199006650769</v>
+      </c>
+      <c r="O126">
+        <v>140.8116699402817</v>
+      </c>
+      <c r="P126">
+        <v>0</v>
+      </c>
+      <c r="Q126">
+        <v>0</v>
+      </c>
+      <c r="R126">
+        <v>4</v>
+      </c>
+      <c r="S126">
+        <v>12.097</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19">
+      <c r="A127" t="s">
+        <v>144</v>
+      </c>
+      <c r="B127" t="s">
+        <v>163</v>
+      </c>
+      <c r="C127" t="s">
+        <v>202</v>
+      </c>
+      <c r="D127" t="s">
+        <v>345</v>
+      </c>
+      <c r="E127">
+        <v>54.29999923706055</v>
+      </c>
+      <c r="F127">
+        <v>253465.5333333333</v>
+      </c>
+      <c r="G127">
+        <v>45.14839981079101</v>
+      </c>
+      <c r="H127">
+        <v>42.02019994099935</v>
+      </c>
+      <c r="I127">
+        <v>40.94209991455078</v>
+      </c>
+      <c r="J127">
+        <v>39.64504999160766</v>
+      </c>
+      <c r="K127">
+        <v>35.31000137329102</v>
+      </c>
+      <c r="L127">
+        <v>54.29999923706055</v>
+      </c>
+      <c r="M127">
+        <v>38.16793967226022</v>
+      </c>
+      <c r="N127">
+        <v>49.95857666382854</v>
+      </c>
+      <c r="O127">
+        <v>139.3090297886898</v>
+      </c>
+      <c r="P127">
+        <v>0</v>
+      </c>
+      <c r="Q127">
+        <v>212</v>
+      </c>
+      <c r="R127">
+        <v>-9</v>
+      </c>
+      <c r="S127">
+        <v>8.078000000000001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19">
+      <c r="A128" t="s">
+        <v>145</v>
+      </c>
+      <c r="B128" t="s">
+        <v>162</v>
+      </c>
+      <c r="C128" t="s">
+        <v>172</v>
+      </c>
+      <c r="D128" t="s">
+        <v>346</v>
+      </c>
+      <c r="E128">
+        <v>26.05999946594238</v>
+      </c>
+      <c r="F128">
+        <v>246141.8333333333</v>
+      </c>
+      <c r="G128">
+        <v>23.82060005187988</v>
+      </c>
+      <c r="H128">
+        <v>19.89220005671183</v>
+      </c>
+      <c r="I128">
+        <v>19.69645001888275</v>
+      </c>
+      <c r="J128">
+        <v>19.23910001277924</v>
+      </c>
+      <c r="K128">
+        <v>13.85000038146973</v>
+      </c>
+      <c r="L128">
+        <v>26.46999931335449</v>
+      </c>
+      <c r="M128">
+        <v>59.2909443380661</v>
+      </c>
+      <c r="N128">
+        <v>13.45233019137009</v>
+      </c>
+      <c r="O128">
+        <v>138.9102064719199</v>
+      </c>
+      <c r="P128">
+        <v>0</v>
+      </c>
+      <c r="Q128">
+        <v>33</v>
+      </c>
+      <c r="R128">
         <v>171</v>
       </c>
-      <c r="S4">
-        <v>21.065001</v>
+      <c r="S128">
+        <v>-93.44200000000001</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19">
+      <c r="A129" t="s">
+        <v>146</v>
+      </c>
+      <c r="B129" t="s">
+        <v>165</v>
+      </c>
+      <c r="C129" t="s">
+        <v>205</v>
+      </c>
+      <c r="D129" t="s">
+        <v>347</v>
+      </c>
+      <c r="E129">
+        <v>150.6799926757812</v>
+      </c>
+      <c r="F129">
+        <v>836560.9666666667</v>
+      </c>
+      <c r="G129">
+        <v>132.8715989685059</v>
+      </c>
+      <c r="H129">
+        <v>114.2758664449056</v>
+      </c>
+      <c r="I129">
+        <v>113.5417999267578</v>
+      </c>
+      <c r="J129">
+        <v>109.8996001052856</v>
+      </c>
+      <c r="K129">
+        <v>91.56999969482422</v>
+      </c>
+      <c r="L129">
+        <v>151.5500030517578</v>
+      </c>
+      <c r="M129">
+        <v>32.73431741682889</v>
+      </c>
+      <c r="N129">
+        <v>43.92968684867024</v>
+      </c>
+      <c r="O129">
+        <v>137.7087802007587</v>
+      </c>
+      <c r="P129">
+        <v>21</v>
+      </c>
+      <c r="Q129">
+        <v>14</v>
+      </c>
+      <c r="R129">
+        <v>4</v>
+      </c>
+      <c r="S129">
+        <v>28.709</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19">
+      <c r="A130" t="s">
+        <v>147</v>
+      </c>
+      <c r="B130" t="s">
+        <v>164</v>
+      </c>
+      <c r="C130" t="s">
+        <v>185</v>
+      </c>
+      <c r="D130" t="s">
+        <v>348</v>
+      </c>
+      <c r="E130">
+        <v>173.0800018310547</v>
+      </c>
+      <c r="F130">
+        <v>10049878.56666667</v>
+      </c>
+      <c r="G130">
+        <v>150.4925445556641</v>
+      </c>
+      <c r="H130">
+        <v>128.6492189534505</v>
+      </c>
+      <c r="I130">
+        <v>125.8882687759399</v>
+      </c>
+      <c r="J130">
+        <v>120.4262613677978</v>
+      </c>
+      <c r="K130">
+        <v>100.4379959106445</v>
+      </c>
+      <c r="L130">
+        <v>175.7200012207031</v>
+      </c>
+      <c r="M130">
+        <v>30.82586010466557</v>
+      </c>
+      <c r="N130">
+        <v>53.71846708565886</v>
+      </c>
+      <c r="O130">
+        <v>137.6833345402148</v>
+      </c>
+      <c r="P130">
+        <v>24</v>
+      </c>
+      <c r="Q130">
+        <v>-44</v>
+      </c>
+      <c r="R130">
+        <v>15</v>
+      </c>
+      <c r="S130">
+        <v>37.627998</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19">
+      <c r="A131" t="s">
+        <v>148</v>
+      </c>
+      <c r="B131" t="s">
+        <v>164</v>
+      </c>
+      <c r="C131" t="s">
+        <v>222</v>
+      </c>
+      <c r="D131" t="s">
+        <v>349</v>
+      </c>
+      <c r="E131">
+        <v>74.90000152587891</v>
+      </c>
+      <c r="F131">
+        <v>288996.0666666667</v>
+      </c>
+      <c r="G131">
+        <v>66.55419975280762</v>
+      </c>
+      <c r="H131">
+        <v>60.70049997965495</v>
+      </c>
+      <c r="I131">
+        <v>58.48567495346069</v>
+      </c>
+      <c r="J131">
+        <v>56.05782497406006</v>
+      </c>
+      <c r="K131">
+        <v>45.31999969482422</v>
+      </c>
+      <c r="L131">
+        <v>75.69000244140625</v>
+      </c>
+      <c r="M131">
+        <v>31.47270479372914</v>
+      </c>
+      <c r="N131">
+        <v>51.09945932418369</v>
+      </c>
+      <c r="O131">
+        <v>136.020594064613</v>
+      </c>
+      <c r="P131">
+        <v>0</v>
+      </c>
+      <c r="Q131">
+        <v>43</v>
+      </c>
+      <c r="R131">
+        <v>2</v>
+      </c>
+      <c r="S131">
+        <v>11.923</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19">
+      <c r="A132" t="s">
+        <v>149</v>
+      </c>
+      <c r="B132" t="s">
+        <v>164</v>
+      </c>
+      <c r="C132" t="s">
+        <v>203</v>
+      </c>
+      <c r="D132" t="s">
+        <v>350</v>
+      </c>
+      <c r="E132">
+        <v>107.7200012207031</v>
+      </c>
+      <c r="F132">
+        <v>2859699.933333333</v>
+      </c>
+      <c r="G132">
+        <v>88.93140029907227</v>
+      </c>
+      <c r="H132">
+        <v>81.02750020345051</v>
+      </c>
+      <c r="I132">
+        <v>79.03517505645752</v>
+      </c>
+      <c r="J132">
+        <v>77.12362495422363</v>
+      </c>
+      <c r="K132">
+        <v>65.76000213623047</v>
+      </c>
+      <c r="L132">
+        <v>111.4899978637695</v>
+      </c>
+      <c r="M132">
+        <v>49.59033193321605</v>
+      </c>
+      <c r="N132">
+        <v>29.45559717089834</v>
+      </c>
+      <c r="O132">
+        <v>134.988158413467</v>
+      </c>
+      <c r="P132">
+        <v>-73</v>
+      </c>
+      <c r="Q132">
+        <v>-58</v>
+      </c>
+      <c r="R132">
+        <v>4</v>
+      </c>
+      <c r="S132">
+        <v>-6.252999600000001</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19">
+      <c r="A133" t="s">
+        <v>150</v>
+      </c>
+      <c r="B133" t="s">
+        <v>163</v>
+      </c>
+      <c r="C133" t="s">
+        <v>223</v>
+      </c>
+      <c r="D133" t="s">
+        <v>351</v>
+      </c>
+      <c r="E133">
+        <v>222.6499938964844</v>
+      </c>
+      <c r="F133">
+        <v>3094624.766666667</v>
+      </c>
+      <c r="G133">
+        <v>202.8186056518555</v>
+      </c>
+      <c r="H133">
+        <v>173.6572109985352</v>
+      </c>
+      <c r="I133">
+        <v>172.242216873169</v>
+      </c>
+      <c r="J133">
+        <v>165.6737237548828</v>
+      </c>
+      <c r="K133">
+        <v>140.8549499511719</v>
+      </c>
+      <c r="L133">
+        <v>223.4199981689453</v>
+      </c>
+      <c r="M133">
+        <v>32.61848338432394</v>
+      </c>
+      <c r="N133">
+        <v>41.34905343264468</v>
+      </c>
+      <c r="O133">
+        <v>134.7261674509507</v>
+      </c>
+      <c r="P133">
+        <v>0</v>
+      </c>
+      <c r="Q133">
+        <v>0</v>
+      </c>
+      <c r="R133">
+        <v>3</v>
+      </c>
+      <c r="S133">
+        <v>31.739</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19">
+      <c r="A134" t="s">
+        <v>151</v>
+      </c>
+      <c r="B134" t="s">
+        <v>166</v>
+      </c>
+      <c r="C134" t="s">
+        <v>224</v>
+      </c>
+      <c r="D134" t="s">
+        <v>322</v>
+      </c>
+      <c r="E134">
+        <v>337.239990234375</v>
+      </c>
+      <c r="F134">
+        <v>2408996.5</v>
+      </c>
+      <c r="G134">
+        <v>310.3161956787109</v>
+      </c>
+      <c r="H134">
+        <v>279.5405557250976</v>
+      </c>
+      <c r="I134">
+        <v>270.5357466125488</v>
+      </c>
+      <c r="J134">
+        <v>258.7262649536133</v>
+      </c>
+      <c r="K134">
+        <v>202.7443389892578</v>
+      </c>
+      <c r="L134">
+        <v>340.2200012207031</v>
+      </c>
+      <c r="M134">
+        <v>30.55968378381924</v>
+      </c>
+      <c r="N134">
+        <v>58.38040560804121</v>
+      </c>
+      <c r="O134">
+        <v>134.0723234797668</v>
+      </c>
+      <c r="P134">
+        <v>89</v>
+      </c>
+      <c r="Q134">
+        <v>0</v>
+      </c>
+      <c r="R134">
+        <v>2</v>
+      </c>
+      <c r="S134">
+        <v>58.383</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19">
+      <c r="A135" t="s">
+        <v>152</v>
+      </c>
+      <c r="B135" t="s">
+        <v>162</v>
+      </c>
+      <c r="C135" t="s">
+        <v>172</v>
+      </c>
+      <c r="D135" t="s">
+        <v>352</v>
+      </c>
+      <c r="E135">
+        <v>44.40000152587891</v>
+      </c>
+      <c r="F135">
+        <v>434191.3666666666</v>
+      </c>
+      <c r="G135">
+        <v>42.90260009765625</v>
+      </c>
+      <c r="H135">
+        <v>37.11873346964519</v>
+      </c>
+      <c r="I135">
+        <v>36.7636500453949</v>
+      </c>
+      <c r="J135">
+        <v>35.39195001602173</v>
+      </c>
+      <c r="K135">
+        <v>28.15999984741211</v>
+      </c>
+      <c r="L135">
+        <v>49.5</v>
+      </c>
+      <c r="M135">
+        <v>31.12817698031904</v>
+      </c>
+      <c r="N135">
+        <v>43.64283967991098</v>
+      </c>
+      <c r="O135">
+        <v>133.0280013538284</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+      <c r="Q135">
+        <v>-80</v>
+      </c>
+      <c r="R135">
+        <v>43</v>
+      </c>
+      <c r="S135">
+        <v>-1.52199995</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19">
+      <c r="A136" t="s">
+        <v>153</v>
+      </c>
+      <c r="B136" t="s">
+        <v>162</v>
+      </c>
+      <c r="C136" t="s">
+        <v>172</v>
+      </c>
+      <c r="D136" t="s">
+        <v>353</v>
+      </c>
+      <c r="E136">
+        <v>33.54999923706055</v>
+      </c>
+      <c r="F136">
+        <v>1390316.1</v>
+      </c>
+      <c r="G136">
+        <v>29.18279983520508</v>
+      </c>
+      <c r="H136">
+        <v>27.51303324381511</v>
+      </c>
+      <c r="I136">
+        <v>27.26347493171692</v>
+      </c>
+      <c r="J136">
+        <v>26.74042497634888</v>
+      </c>
+      <c r="K136">
+        <v>18.35000038146973</v>
+      </c>
+      <c r="L136">
+        <v>35.04999923706055</v>
+      </c>
+      <c r="M136">
+        <v>36.43757230123357</v>
+      </c>
+      <c r="N136">
+        <v>45.9965183001722</v>
+      </c>
+      <c r="O136">
+        <v>132.5355119518758</v>
+      </c>
+      <c r="P136">
+        <v>0</v>
+      </c>
+      <c r="Q136">
+        <v>25</v>
+      </c>
+      <c r="R136">
+        <v>0</v>
+      </c>
+      <c r="S136">
+        <v>-34.750998</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19">
+      <c r="A137" t="s">
+        <v>154</v>
+      </c>
+      <c r="B137" t="s">
+        <v>163</v>
+      </c>
+      <c r="C137" t="s">
+        <v>176</v>
+      </c>
+      <c r="D137" t="s">
+        <v>354</v>
+      </c>
+      <c r="E137">
+        <v>109.0999984741211</v>
+      </c>
+      <c r="F137">
+        <v>1089530.933333333</v>
+      </c>
+      <c r="G137">
+        <v>96.91920272827149</v>
+      </c>
+      <c r="H137">
+        <v>89.0804155476888</v>
+      </c>
+      <c r="I137">
+        <v>87.44373523712159</v>
+      </c>
+      <c r="J137">
+        <v>84.29002849578858</v>
+      </c>
+      <c r="K137">
+        <v>71.08221435546875</v>
+      </c>
+      <c r="L137">
+        <v>111.0599975585938</v>
+      </c>
+      <c r="M137">
+        <v>31.32958954047449</v>
+      </c>
+      <c r="N137">
+        <v>44.19563840097223</v>
+      </c>
+      <c r="O137">
+        <v>131.3940745587726</v>
+      </c>
+      <c r="P137">
+        <v>13</v>
+      </c>
+      <c r="Q137">
+        <v>51</v>
+      </c>
+      <c r="R137">
+        <v>3</v>
+      </c>
+      <c r="S137">
+        <v>21.899</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19">
+      <c r="A138" t="s">
+        <v>155</v>
+      </c>
+      <c r="B138" t="s">
+        <v>166</v>
+      </c>
+      <c r="C138" t="s">
+        <v>186</v>
+      </c>
+      <c r="D138" t="s">
+        <v>355</v>
+      </c>
+      <c r="E138">
+        <v>150.5</v>
+      </c>
+      <c r="F138">
+        <v>331427.3333333333</v>
+      </c>
+      <c r="G138">
+        <v>139.7394006347656</v>
+      </c>
+      <c r="H138">
+        <v>128.3545266215006</v>
+      </c>
+      <c r="I138">
+        <v>124.6481527709961</v>
+      </c>
+      <c r="J138">
+        <v>120.5191334533691</v>
+      </c>
+      <c r="K138">
+        <v>100.6677017211914</v>
+      </c>
+      <c r="L138">
+        <v>151.2400054931641</v>
+      </c>
+      <c r="M138">
+        <v>30.90924631841436</v>
+      </c>
+      <c r="N138">
+        <v>28.75914356458715</v>
+      </c>
+      <c r="O138">
+        <v>130.4166413205335</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>-36</v>
+      </c>
+      <c r="R138">
+        <v>3</v>
+      </c>
+      <c r="S138">
+        <v>19.976999</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19">
+      <c r="A139" t="s">
+        <v>156</v>
+      </c>
+      <c r="B139" t="s">
+        <v>166</v>
+      </c>
+      <c r="C139" t="s">
+        <v>224</v>
+      </c>
+      <c r="D139" t="s">
+        <v>356</v>
+      </c>
+      <c r="E139">
+        <v>18.60000038146973</v>
+      </c>
+      <c r="F139">
+        <v>987460.9333333333</v>
+      </c>
+      <c r="G139">
+        <v>17.06797443389893</v>
+      </c>
+      <c r="H139">
+        <v>14.25659464518229</v>
+      </c>
+      <c r="I139">
+        <v>13.3534384727478</v>
+      </c>
+      <c r="J139">
+        <v>12.29333865642548</v>
+      </c>
+      <c r="K139">
+        <v>8.3082275390625</v>
+      </c>
+      <c r="L139">
+        <v>21.02000045776367</v>
+      </c>
+      <c r="M139">
+        <v>34.75125530997016</v>
+      </c>
+      <c r="N139">
+        <v>88.18563454797656</v>
+      </c>
+      <c r="O139">
+        <v>129.743766604058</v>
+      </c>
+      <c r="P139">
+        <v>-1430</v>
+      </c>
+      <c r="Q139">
+        <v>208</v>
+      </c>
+      <c r="R139">
+        <v>-15</v>
+      </c>
+      <c r="S139">
+        <v>51.55800000000001</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19">
+      <c r="A140" t="s">
+        <v>157</v>
+      </c>
+      <c r="B140" t="s">
+        <v>163</v>
+      </c>
+      <c r="C140" t="s">
+        <v>221</v>
+      </c>
+      <c r="D140" t="s">
+        <v>298</v>
+      </c>
+      <c r="E140">
+        <v>33.61999893188477</v>
+      </c>
+      <c r="F140">
+        <v>417236.4666666667</v>
+      </c>
+      <c r="G140">
+        <v>33.53621299743652</v>
+      </c>
+      <c r="H140">
+        <v>30.29132954915364</v>
+      </c>
+      <c r="I140">
+        <v>28.88068963050842</v>
+      </c>
+      <c r="J140">
+        <v>27.53842852592468</v>
+      </c>
+      <c r="K140">
+        <v>20.28377151489258</v>
+      </c>
+      <c r="L140">
+        <v>36.19731140136719</v>
+      </c>
+      <c r="M140">
+        <v>30.06746453494469</v>
+      </c>
+      <c r="N140">
+        <v>45.23623288702314</v>
+      </c>
+      <c r="O140">
+        <v>127.3787196642357</v>
+      </c>
+      <c r="P140">
+        <v>191</v>
+      </c>
+      <c r="Q140">
+        <v>-108</v>
+      </c>
+      <c r="R140">
+        <v>-108</v>
+      </c>
+      <c r="S140">
+        <v>8.674999999999999</v>
+      </c>
+    </row>
+    <row r="141" spans="1:19">
+      <c r="A141" t="s">
+        <v>158</v>
+      </c>
+      <c r="B141" t="s">
+        <v>162</v>
+      </c>
+      <c r="C141" t="s">
+        <v>225</v>
+      </c>
+      <c r="D141" t="s">
+        <v>357</v>
+      </c>
+      <c r="E141">
+        <v>56.5</v>
+      </c>
+      <c r="F141">
+        <v>3826391.433333333</v>
+      </c>
+      <c r="G141">
+        <v>53.47220008850098</v>
+      </c>
+      <c r="H141">
+        <v>46.39600006103515</v>
+      </c>
+      <c r="I141">
+        <v>45.71180006027222</v>
+      </c>
+      <c r="J141">
+        <v>43.93470001220703</v>
+      </c>
+      <c r="K141">
+        <v>31.86000061035156</v>
+      </c>
+      <c r="L141">
+        <v>71.19999694824219</v>
+      </c>
+      <c r="M141">
+        <v>51.96341994686511</v>
+      </c>
+      <c r="N141">
+        <v>0</v>
+      </c>
+      <c r="O141">
+        <v>126.1013692040831</v>
+      </c>
+      <c r="P141">
+        <v>-357</v>
+      </c>
+      <c r="Q141">
+        <v>-152</v>
+      </c>
+      <c r="R141">
+        <v>4</v>
+      </c>
+      <c r="S141">
+        <v>-30.283</v>
+      </c>
+    </row>
+    <row r="142" spans="1:19">
+      <c r="A142" t="s">
+        <v>159</v>
+      </c>
+      <c r="B142" t="s">
+        <v>165</v>
+      </c>
+      <c r="C142" t="s">
+        <v>201</v>
+      </c>
+      <c r="D142" t="s">
+        <v>358</v>
+      </c>
+      <c r="E142">
+        <v>44.27999877929688</v>
+      </c>
+      <c r="F142">
+        <v>4382409.5</v>
+      </c>
+      <c r="G142">
+        <v>39.65799995422363</v>
+      </c>
+      <c r="H142">
+        <v>36.86053339640299</v>
+      </c>
+      <c r="I142">
+        <v>36.63975003242493</v>
+      </c>
+      <c r="J142">
+        <v>35.67705002784729</v>
+      </c>
+      <c r="K142">
+        <v>31.20999908447266</v>
+      </c>
+      <c r="L142">
+        <v>47.34000015258789</v>
+      </c>
+      <c r="M142">
+        <v>34.58965570097783</v>
+      </c>
+      <c r="N142">
+        <v>21.71522121835638</v>
+      </c>
+      <c r="O142">
+        <v>125.9868601205592</v>
+      </c>
+      <c r="P142">
+        <v>0</v>
+      </c>
+      <c r="Q142">
+        <v>-346</v>
+      </c>
+      <c r="R142">
+        <v>22</v>
+      </c>
+      <c r="S142">
+        <v>8.475000400000001</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19">
+      <c r="A143" t="s">
+        <v>160</v>
+      </c>
+      <c r="B143" t="s">
+        <v>162</v>
+      </c>
+      <c r="C143" t="s">
+        <v>226</v>
+      </c>
+      <c r="D143" t="s">
+        <v>359</v>
+      </c>
+      <c r="E143">
+        <v>231.0500030517578</v>
+      </c>
+      <c r="F143">
+        <v>1017797.133333333</v>
+      </c>
+      <c r="G143">
+        <v>211.6693991088867</v>
+      </c>
+      <c r="H143">
+        <v>199.5454665120443</v>
+      </c>
+      <c r="I143">
+        <v>198.6634497070312</v>
+      </c>
+      <c r="J143">
+        <v>193.6416999816894</v>
+      </c>
+      <c r="K143">
+        <v>162.6000061035156</v>
+      </c>
+      <c r="L143">
+        <v>231.0500030517578</v>
+      </c>
+      <c r="M143">
+        <v>33.77916395692342</v>
+      </c>
+      <c r="N143">
+        <v>35.24350737796944</v>
+      </c>
+      <c r="O143">
+        <v>124.3688055239458</v>
+      </c>
+      <c r="P143">
+        <v>0</v>
+      </c>
+      <c r="Q143">
+        <v>14</v>
+      </c>
+      <c r="R143">
+        <v>4</v>
+      </c>
+      <c r="S143">
+        <v>12.575</v>
+      </c>
+    </row>
+    <row r="144" spans="1:19">
+      <c r="A144" t="s">
+        <v>161</v>
+      </c>
+      <c r="B144" t="s">
+        <v>162</v>
+      </c>
+      <c r="C144" t="s">
+        <v>227</v>
+      </c>
+      <c r="D144" t="s">
+        <v>360</v>
+      </c>
+      <c r="E144">
+        <v>343.9400024414062</v>
+      </c>
+      <c r="F144">
+        <v>1712514.033333333</v>
+      </c>
+      <c r="G144">
+        <v>322.5030010986328</v>
+      </c>
+      <c r="H144">
+        <v>300.2588010660807</v>
+      </c>
+      <c r="I144">
+        <v>294.1633006286621</v>
+      </c>
+      <c r="J144">
+        <v>285.7511505889893</v>
+      </c>
+      <c r="K144">
+        <v>242.6399993896484</v>
+      </c>
+      <c r="L144">
+        <v>344.239990234375</v>
+      </c>
+      <c r="M144">
+        <v>32.89799793829458</v>
+      </c>
+      <c r="N144">
+        <v>27.21557222832514</v>
+      </c>
+      <c r="O144">
+        <v>121.7015712551582</v>
+      </c>
+      <c r="P144">
+        <v>0</v>
+      </c>
+      <c r="Q144">
+        <v>0</v>
+      </c>
+      <c r="R144">
+        <v>4</v>
+      </c>
+      <c r="S144">
+        <v>11.793</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/ScreenResult/ScreenResult.xlsx
+++ b/Screener/ScreenResult/ScreenResult.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
   <si>
     <t>Symbol</t>
   </si>
@@ -91,15 +91,9 @@
     <t>ELF</t>
   </si>
   <si>
-    <t>NOW</t>
-  </si>
-  <si>
     <t>WWD</t>
   </si>
   <si>
-    <t>HTGC</t>
-  </si>
-  <si>
     <t>Technology</t>
   </si>
   <si>
@@ -112,9 +106,6 @@
     <t>Consumer Defensive</t>
   </si>
   <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
     <t>Computer Hardware</t>
   </si>
   <si>
@@ -133,15 +124,9 @@
     <t>Household &amp; Personal Products</t>
   </si>
   <si>
-    <t>Software—Application</t>
-  </si>
-  <si>
     <t>Aerospace &amp; Defense</t>
   </si>
   <si>
-    <t>Asset Management</t>
-  </si>
-  <si>
     <t>2007-03-29</t>
   </si>
   <si>
@@ -160,13 +145,7 @@
     <t>2016-09-22</t>
   </si>
   <si>
-    <t>2012-06-29</t>
-  </si>
-  <si>
     <t>1994-04-04</t>
-  </si>
-  <si>
-    <t>2005-06-09</t>
   </si>
 </sst>
 </file>
@@ -524,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -591,31 +570,31 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E2">
-        <v>1130.109985351562</v>
+        <v>1000.679992675781</v>
       </c>
       <c r="F2">
-        <v>14107260</v>
+        <v>14184327.8</v>
       </c>
       <c r="G2">
-        <v>689.7637939453125</v>
+        <v>719.7651928710937</v>
       </c>
       <c r="H2">
-        <v>410.8605978393555</v>
+        <v>421.1136642456055</v>
       </c>
       <c r="I2">
-        <v>376.0102983093262</v>
+        <v>384.0675980377197</v>
       </c>
       <c r="J2">
-        <v>292.7458491897583</v>
+        <v>300.7347492218017</v>
       </c>
       <c r="K2">
         <v>93.27999877929688</v>
@@ -624,13 +603,13 @@
         <v>1188.069946289062</v>
       </c>
       <c r="M2">
-        <v>325.8620063102859</v>
+        <v>239.9048958634272</v>
       </c>
       <c r="N2">
-        <v>1083.361241205825</v>
+        <v>824.4156976219689</v>
       </c>
       <c r="O2">
-        <v>556.4906692325648</v>
+        <v>470.5053010882441</v>
       </c>
       <c r="P2">
         <v>62</v>
@@ -650,46 +629,46 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>162.5599975585938</v>
+        <v>153.6600036621094</v>
       </c>
       <c r="F3">
-        <v>367600</v>
+        <v>400893.6333333334</v>
       </c>
       <c r="G3">
-        <v>125.6609672546387</v>
+        <v>128.6240017700195</v>
       </c>
       <c r="H3">
-        <v>96.84336573282877</v>
+        <v>98.12273401896159</v>
       </c>
       <c r="I3">
-        <v>88.24628536224365</v>
+        <v>89.55160049438477</v>
       </c>
       <c r="J3">
-        <v>77.18783622741699</v>
+        <v>78.70265024185181</v>
       </c>
       <c r="K3">
-        <v>38.53400039672852</v>
+        <v>39.02999877929688</v>
       </c>
       <c r="L3">
         <v>185.2400054931641</v>
       </c>
       <c r="M3">
-        <v>84.54508219190777</v>
+        <v>73.70563560075962</v>
       </c>
       <c r="N3">
-        <v>307.2530855201197</v>
+        <v>266.9930919083317</v>
       </c>
       <c r="O3">
-        <v>246.506696171831</v>
+        <v>231.7309296531739</v>
       </c>
       <c r="P3">
         <v>1880</v>
@@ -709,46 +688,46 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E4">
-        <v>879.4400024414062</v>
+        <v>884.5499877929688</v>
       </c>
       <c r="F4">
-        <v>58650266.66666666</v>
+        <v>60139954.03333333</v>
       </c>
       <c r="G4">
-        <v>692.610185546875</v>
+        <v>708.7809991455078</v>
       </c>
       <c r="H4">
-        <v>536.3253192138671</v>
+        <v>542.577533569336</v>
       </c>
       <c r="I4">
-        <v>509.4775801086426</v>
+        <v>514.4561503601075</v>
       </c>
       <c r="J4">
-        <v>458.0844877624511</v>
+        <v>462.5608003234863</v>
       </c>
       <c r="K4">
-        <v>257.1675415039062</v>
+        <v>261.989990234375</v>
       </c>
       <c r="L4">
         <v>926.6900024414062</v>
       </c>
       <c r="M4">
-        <v>84.54398520240738</v>
+        <v>82.94725704094492</v>
       </c>
       <c r="N4">
-        <v>241.9716179182154</v>
+        <v>237.6273982840545</v>
       </c>
       <c r="O4">
-        <v>220.0467470107713</v>
+        <v>218.7182047434421</v>
       </c>
       <c r="P4">
         <v>1230</v>
@@ -768,46 +747,46 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>63.79000091552734</v>
+        <v>65.13999938964844</v>
       </c>
       <c r="F5">
-        <v>827030</v>
+        <v>801589.2666666667</v>
       </c>
       <c r="G5">
-        <v>54.92379959106445</v>
+        <v>55.65799957275391</v>
       </c>
       <c r="H5">
-        <v>45.52219985961914</v>
+        <v>45.89553319295248</v>
       </c>
       <c r="I5">
-        <v>41.29949990272522</v>
+        <v>41.68324989318847</v>
       </c>
       <c r="J5">
-        <v>37.85804990768433</v>
+        <v>38.21184989929199</v>
       </c>
       <c r="K5">
         <v>22.51000022888184</v>
       </c>
       <c r="L5">
-        <v>64.43000030517578</v>
+        <v>65.13999938964844</v>
       </c>
       <c r="M5">
-        <v>38.88526124903802</v>
+        <v>39.96561690637075</v>
       </c>
       <c r="N5">
-        <v>151.3396494281073</v>
+        <v>159.8324698148951</v>
       </c>
       <c r="O5">
-        <v>187.0096316720907</v>
+        <v>191.6090194799709</v>
       </c>
       <c r="P5">
         <v>21900</v>
@@ -827,31 +806,31 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E6">
-        <v>108.4899978637695</v>
+        <v>106.7600021362305</v>
       </c>
       <c r="F6">
-        <v>406560</v>
+        <v>412367.1333333334</v>
       </c>
       <c r="G6">
-        <v>87.02119995117188</v>
+        <v>88.14360000610351</v>
       </c>
       <c r="H6">
-        <v>78.45479993184408</v>
+        <v>78.81113329569499</v>
       </c>
       <c r="I6">
-        <v>72.96764995574951</v>
+        <v>73.56959999084472</v>
       </c>
       <c r="J6">
-        <v>67.19939990997314</v>
+        <v>67.65309993743897</v>
       </c>
       <c r="K6">
         <v>34.63999938964844</v>
@@ -860,13 +839,13 @@
         <v>111.9800033569336</v>
       </c>
       <c r="M6">
-        <v>47.78639483949068</v>
+        <v>38.90190123398458</v>
       </c>
       <c r="N6">
-        <v>193.7719928709682</v>
+        <v>175.2965587848998</v>
       </c>
       <c r="O6">
-        <v>182.3795809845948</v>
+        <v>179.6448393006261</v>
       </c>
       <c r="P6">
         <v>307</v>
@@ -886,46 +865,46 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E7">
-        <v>200.2899932861328</v>
+        <v>196.8600006103516</v>
       </c>
       <c r="F7">
-        <v>1433456.666666667</v>
+        <v>1464137.066666667</v>
       </c>
       <c r="G7">
-        <v>174.0997991943359</v>
+        <v>176.6357989501953</v>
       </c>
       <c r="H7">
-        <v>137.2215997823079</v>
+        <v>138.0919330342611</v>
       </c>
       <c r="I7">
-        <v>131.1264498519897</v>
+        <v>132.0628498458862</v>
       </c>
       <c r="J7">
-        <v>120.5549000549316</v>
+        <v>121.3788000106811</v>
       </c>
       <c r="K7">
-        <v>72.47000122070312</v>
+        <v>73.11000061035156</v>
       </c>
       <c r="L7">
         <v>217.3999938964844</v>
       </c>
       <c r="M7">
-        <v>52.8114611229779</v>
+        <v>37.46246168654734</v>
       </c>
       <c r="N7">
-        <v>176.3764177071854</v>
+        <v>164.9172481201155</v>
       </c>
       <c r="O7">
-        <v>179.7881235557685</v>
+        <v>177.8155650156492</v>
       </c>
       <c r="P7">
         <v>35</v>
@@ -945,176 +924,58 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8">
+        <v>147.5200042724609</v>
+      </c>
+      <c r="F8">
+        <v>308504.1666666667</v>
+      </c>
+      <c r="G8">
+        <v>139.6373989868164</v>
+      </c>
+      <c r="H8">
+        <v>132.9407996622721</v>
+      </c>
+      <c r="I8">
+        <v>129.3562996292114</v>
+      </c>
+      <c r="J8">
+        <v>125.8575996398926</v>
+      </c>
+      <c r="K8">
+        <v>89.83000183105469</v>
+      </c>
+      <c r="L8">
+        <v>149.4199981689453</v>
+      </c>
+      <c r="M8">
+        <v>8.422759752683362</v>
+      </c>
+      <c r="N8">
+        <v>59.37770977043897</v>
+      </c>
+      <c r="O8">
+        <v>124.9249246962148</v>
+      </c>
+      <c r="P8">
+        <v>198</v>
+      </c>
+      <c r="Q8">
         <v>39</v>
       </c>
-      <c r="D8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8">
-        <v>779.489990234375</v>
-      </c>
-      <c r="F8">
-        <v>1206203.333333333</v>
-      </c>
-      <c r="G8">
-        <v>757.5169995117187</v>
-      </c>
-      <c r="H8">
-        <v>658.6124658203125</v>
-      </c>
-      <c r="I8">
-        <v>634.2110498046875</v>
-      </c>
-      <c r="J8">
-        <v>604.9291000366211</v>
-      </c>
-      <c r="K8">
-        <v>429.0799865722656</v>
-      </c>
-      <c r="L8">
-        <v>812.9400024414062</v>
-      </c>
-      <c r="M8">
-        <v>8.794385256152083</v>
-      </c>
-      <c r="N8">
-        <v>76.75509982638889</v>
-      </c>
-      <c r="O8">
-        <v>135.6356495189992</v>
-      </c>
-      <c r="P8">
-        <v>93</v>
-      </c>
-      <c r="Q8">
-        <v>426</v>
-      </c>
       <c r="R8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S8">
-        <v>27.346</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9">
-        <v>145.1600036621094</v>
-      </c>
-      <c r="F9">
-        <v>306660</v>
-      </c>
-      <c r="G9">
-        <v>139.0381988525391</v>
-      </c>
-      <c r="H9">
-        <v>132.6677996317545</v>
-      </c>
-      <c r="I9">
-        <v>128.9426996231079</v>
-      </c>
-      <c r="J9">
-        <v>125.5397996520996</v>
-      </c>
-      <c r="K9">
-        <v>89.38999938964844</v>
-      </c>
-      <c r="L9">
-        <v>149.4199981689453</v>
-      </c>
-      <c r="M9">
-        <v>6.680382044980404</v>
-      </c>
-      <c r="N9">
-        <v>62.38953423565996</v>
-      </c>
-      <c r="O9">
-        <v>121.4582129236914</v>
-      </c>
-      <c r="P9">
-        <v>198</v>
-      </c>
-      <c r="Q9">
-        <v>39</v>
-      </c>
-      <c r="R9">
-        <v>27</v>
-      </c>
-      <c r="S9">
         <v>14.181</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10">
-        <v>18</v>
-      </c>
-      <c r="F10">
-        <v>1053533.333333333</v>
-      </c>
-      <c r="G10">
-        <v>17.67340003967285</v>
-      </c>
-      <c r="H10">
-        <v>16.58946668624878</v>
-      </c>
-      <c r="I10">
-        <v>16.32935003757477</v>
-      </c>
-      <c r="J10">
-        <v>15.85005004882813</v>
-      </c>
-      <c r="K10">
-        <v>11.85000038146973</v>
-      </c>
-      <c r="L10">
-        <v>18.77000045776367</v>
-      </c>
-      <c r="M10">
-        <v>16.20400429935351</v>
-      </c>
-      <c r="N10">
-        <v>51.26050905052983</v>
-      </c>
-      <c r="O10">
-        <v>120.8366269358796</v>
-      </c>
-      <c r="P10">
-        <v>66</v>
-      </c>
-      <c r="Q10">
-        <v>192</v>
-      </c>
-      <c r="R10">
-        <v>65</v>
-      </c>
-      <c r="S10">
-        <v>21.065001</v>
       </c>
     </row>
   </sheetData>

--- a/Screener/ScreenResult/ScreenResult.xlsx
+++ b/Screener/ScreenResult/ScreenResult.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="130">
   <si>
     <t>Symbol</t>
   </si>
@@ -76,7 +76,13 @@
     <t>SMCI</t>
   </si>
   <si>
-    <t>POWL</t>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>MOD</t>
+  </si>
+  <si>
+    <t>CLS</t>
   </si>
   <si>
     <t>NVDA</t>
@@ -91,13 +97,97 @@
     <t>ELF</t>
   </si>
   <si>
+    <t>UBER</t>
+  </si>
+  <si>
+    <t>VIST</t>
+  </si>
+  <si>
+    <t>AROC</t>
+  </si>
+  <si>
+    <t>AEO</t>
+  </si>
+  <si>
+    <t>WMS</t>
+  </si>
+  <si>
+    <t>WFRD</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>ROAD</t>
+  </si>
+  <si>
+    <t>MCY</t>
+  </si>
+  <si>
+    <t>DVA</t>
+  </si>
+  <si>
+    <t>ALSN</t>
+  </si>
+  <si>
+    <t>ASML</t>
+  </si>
+  <si>
+    <t>PCAR</t>
+  </si>
+  <si>
+    <t>HWM</t>
+  </si>
+  <si>
+    <t>MLM</t>
+  </si>
+  <si>
+    <t>PH</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>SAP</t>
+  </si>
+  <si>
+    <t>HIG</t>
+  </si>
+  <si>
+    <t>HUBB</t>
+  </si>
+  <si>
+    <t>NTAP</t>
+  </si>
+  <si>
     <t>NOW</t>
   </si>
   <si>
+    <t>SHOP</t>
+  </si>
+  <si>
+    <t>GRMN</t>
+  </si>
+  <si>
+    <t>JPM</t>
+  </si>
+  <si>
+    <t>MANH</t>
+  </si>
+  <si>
+    <t>MOH</t>
+  </si>
+  <si>
+    <t>BRO</t>
+  </si>
+  <si>
+    <t>SNPS</t>
+  </si>
+  <si>
     <t>WWD</t>
   </si>
   <si>
-    <t>HTGC</t>
+    <t>ZWS</t>
   </si>
   <si>
     <t>Technology</t>
@@ -112,15 +202,30 @@
     <t>Consumer Defensive</t>
   </si>
   <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>Financial Services</t>
   </si>
   <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Basic Materials</t>
+  </si>
+  <si>
     <t>Computer Hardware</t>
   </si>
   <si>
     <t>Electrical Equipment &amp; Parts</t>
   </si>
   <si>
+    <t>Auto Parts</t>
+  </si>
+  <si>
+    <t>Electronic Components</t>
+  </si>
+  <si>
     <t>Semiconductors</t>
   </si>
   <si>
@@ -136,37 +241,169 @@
     <t>Software—Application</t>
   </si>
   <si>
+    <t>Oil &amp; Gas E&amp;P</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Equipment &amp; Services</t>
+  </si>
+  <si>
+    <t>Apparel Retail</t>
+  </si>
+  <si>
+    <t>Building Products &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Specialty Industrial Machinery</t>
+  </si>
+  <si>
+    <t>Insurance—Property &amp; Casualty</t>
+  </si>
+  <si>
+    <t>Medical Care Facilities</t>
+  </si>
+  <si>
+    <t>Semiconductor Equipment &amp; Materials</t>
+  </si>
+  <si>
+    <t>Farm &amp; Heavy Construction Machinery</t>
+  </si>
+  <si>
     <t>Aerospace &amp; Defense</t>
   </si>
   <si>
-    <t>Asset Management</t>
+    <t>Building Materials</t>
+  </si>
+  <si>
+    <t>Internet Retail</t>
+  </si>
+  <si>
+    <t>Scientific &amp; Technical Instruments</t>
+  </si>
+  <si>
+    <t>Banks—Diversified</t>
+  </si>
+  <si>
+    <t>Healthcare Plans</t>
+  </si>
+  <si>
+    <t>Insurance Brokers</t>
+  </si>
+  <si>
+    <t>Software—Infrastructure</t>
+  </si>
+  <si>
+    <t>Pollution &amp; Treatment Controls</t>
   </si>
   <si>
     <t>2007-03-29</t>
   </si>
   <si>
+    <t>2018-08-02</t>
+  </si>
+  <si>
+    <t>1982-09-20</t>
+  </si>
+  <si>
+    <t>1998-06-30</t>
+  </si>
+  <si>
+    <t>1999-01-22</t>
+  </si>
+  <si>
+    <t>2010-08-12</t>
+  </si>
+  <si>
+    <t>1991-07-12</t>
+  </si>
+  <si>
+    <t>2016-09-22</t>
+  </si>
+  <si>
+    <t>2019-05-10</t>
+  </si>
+  <si>
+    <t>2019-07-26</t>
+  </si>
+  <si>
+    <t>2007-08-21</t>
+  </si>
+  <si>
+    <t>1994-04-14</t>
+  </si>
+  <si>
+    <t>2014-07-25</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>1972-06-01</t>
+  </si>
+  <si>
+    <t>2018-05-04</t>
+  </si>
+  <si>
+    <t>1985-11-20</t>
+  </si>
+  <si>
+    <t>1995-10-31</t>
+  </si>
+  <si>
+    <t>2012-03-15</t>
+  </si>
+  <si>
+    <t>1995-03-15</t>
+  </si>
+  <si>
     <t>1980-03-17</t>
   </si>
   <si>
-    <t>1999-01-22</t>
-  </si>
-  <si>
-    <t>2010-08-12</t>
-  </si>
-  <si>
-    <t>1991-07-12</t>
-  </si>
-  <si>
-    <t>2016-09-22</t>
+    <t>2016-11-01</t>
+  </si>
+  <si>
+    <t>1994-02-17</t>
+  </si>
+  <si>
+    <t>1997-05-15</t>
+  </si>
+  <si>
+    <t>1995-09-18</t>
+  </si>
+  <si>
+    <t>1995-12-15</t>
+  </si>
+  <si>
+    <t>1972-06-05</t>
+  </si>
+  <si>
+    <t>1995-11-21</t>
   </si>
   <si>
     <t>2012-06-29</t>
   </si>
   <si>
+    <t>2015-05-20</t>
+  </si>
+  <si>
+    <t>2000-12-08</t>
+  </si>
+  <si>
+    <t>1998-04-23</t>
+  </si>
+  <si>
+    <t>2003-07-02</t>
+  </si>
+  <si>
+    <t>1981-02-11</t>
+  </si>
+  <si>
+    <t>1992-02-26</t>
+  </si>
+  <si>
     <t>1994-04-04</t>
   </si>
   <si>
-    <t>2005-06-09</t>
+    <t>2012-03-29</t>
   </si>
 </sst>
 </file>
@@ -524,7 +761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -591,31 +828,31 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="E2">
-        <v>1130.109985351562</v>
+        <v>896.469970703125</v>
       </c>
       <c r="F2">
-        <v>14107260</v>
+        <v>13593680</v>
       </c>
       <c r="G2">
-        <v>689.7637939453125</v>
+        <v>743.6657916259766</v>
       </c>
       <c r="H2">
-        <v>410.8605978393555</v>
+        <v>429.6053972371419</v>
       </c>
       <c r="I2">
-        <v>376.0102983093262</v>
+        <v>390.8399977111816</v>
       </c>
       <c r="J2">
-        <v>292.7458491897583</v>
+        <v>306.99169921875</v>
       </c>
       <c r="K2">
         <v>93.27999877929688</v>
@@ -624,13 +861,13 @@
         <v>1188.069946289062</v>
       </c>
       <c r="M2">
-        <v>325.8620063102859</v>
+        <v>178.2426406499555</v>
       </c>
       <c r="N2">
-        <v>1083.361241205825</v>
+        <v>686.377167283443</v>
       </c>
       <c r="O2">
-        <v>556.4906692325648</v>
+        <v>439.245446730372</v>
       </c>
       <c r="P2">
         <v>62</v>
@@ -650,58 +887,58 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="E3">
-        <v>162.5599975585938</v>
+        <v>77.83999633789062</v>
       </c>
       <c r="F3">
-        <v>367600</v>
+        <v>8628510</v>
       </c>
       <c r="G3">
-        <v>125.6609672546387</v>
+        <v>62.18179985046387</v>
       </c>
       <c r="H3">
-        <v>96.84336573282877</v>
+        <v>48.08573331197103</v>
       </c>
       <c r="I3">
-        <v>88.24628536224365</v>
+        <v>42.63484999656677</v>
       </c>
       <c r="J3">
-        <v>77.18783622741699</v>
+        <v>37.25550003528595</v>
       </c>
       <c r="K3">
-        <v>38.53400039672852</v>
+        <v>12.18000030517578</v>
       </c>
       <c r="L3">
-        <v>185.2400054931641</v>
+        <v>77.83999633789062</v>
       </c>
       <c r="M3">
-        <v>84.54508219190777</v>
+        <v>62.84518322238657</v>
       </c>
       <c r="N3">
-        <v>307.2530855201197</v>
+        <v>488.3597810369461</v>
       </c>
       <c r="O3">
-        <v>246.506696171831</v>
+        <v>293.0237150315805</v>
       </c>
       <c r="P3">
-        <v>1880</v>
+        <v>857</v>
       </c>
       <c r="Q3">
-        <v>291</v>
+        <v>3075</v>
       </c>
       <c r="R3">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="S3">
-        <v>23.3</v>
+        <v>26.626</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -709,58 +946,58 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="E4">
-        <v>879.4400024414062</v>
+        <v>99</v>
       </c>
       <c r="F4">
-        <v>58650266.66666666</v>
+        <v>1092100</v>
       </c>
       <c r="G4">
-        <v>692.610185546875</v>
+        <v>76.6597999572754</v>
       </c>
       <c r="H4">
-        <v>536.3253192138671</v>
+        <v>57.71353329976399</v>
       </c>
       <c r="I4">
-        <v>509.4775801086426</v>
+        <v>52.2904000377655</v>
       </c>
       <c r="J4">
-        <v>458.0844877624511</v>
+        <v>45.77190006256104</v>
       </c>
       <c r="K4">
-        <v>257.1675415039062</v>
+        <v>19.5</v>
       </c>
       <c r="L4">
-        <v>926.6900024414062</v>
+        <v>99</v>
       </c>
       <c r="M4">
-        <v>84.54398520240738</v>
+        <v>75.59417900754137</v>
       </c>
       <c r="N4">
-        <v>241.9716179182154</v>
+        <v>344.3446900759747</v>
       </c>
       <c r="O4">
-        <v>220.0467470107713</v>
+        <v>269.0828339926385</v>
       </c>
       <c r="P4">
-        <v>1230</v>
+        <v>80</v>
       </c>
       <c r="Q4">
-        <v>586</v>
+        <v>79</v>
       </c>
       <c r="R4">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>91.458</v>
+        <v>36.808</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -768,58 +1005,58 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="E5">
-        <v>63.79000091552734</v>
+        <v>44.04999923706055</v>
       </c>
       <c r="F5">
-        <v>827030</v>
+        <v>2288293.333333333</v>
       </c>
       <c r="G5">
-        <v>54.92379959106445</v>
+        <v>37.94179973602295</v>
       </c>
       <c r="H5">
-        <v>45.52219985961914</v>
+        <v>29.61059992472331</v>
       </c>
       <c r="I5">
-        <v>41.29949990272522</v>
+        <v>26.33129990577698</v>
       </c>
       <c r="J5">
-        <v>37.85804990768433</v>
+        <v>23.08064994335174</v>
       </c>
       <c r="K5">
-        <v>22.51000022888184</v>
+        <v>10.63000011444092</v>
       </c>
       <c r="L5">
-        <v>64.43000030517578</v>
+        <v>47.36999893188477</v>
       </c>
       <c r="M5">
-        <v>38.88526124903802</v>
+        <v>49.7789849221528</v>
       </c>
       <c r="N5">
-        <v>151.3396494281073</v>
+        <v>254.0996842678614</v>
       </c>
       <c r="O5">
-        <v>187.0096316720907</v>
+        <v>233.0659722969006</v>
       </c>
       <c r="P5">
-        <v>21900</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="R5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>5.58</v>
+        <v>14.195</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -827,58 +1064,58 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="E6">
-        <v>108.4899978637695</v>
+        <v>903.719970703125</v>
       </c>
       <c r="F6">
-        <v>406560</v>
+        <v>59481803.33333334</v>
       </c>
       <c r="G6">
-        <v>87.02119995117188</v>
+        <v>724.4649975585937</v>
       </c>
       <c r="H6">
-        <v>78.45479993184408</v>
+        <v>548.7159999593099</v>
       </c>
       <c r="I6">
-        <v>72.96764995574951</v>
+        <v>519.4898001098633</v>
       </c>
       <c r="J6">
-        <v>67.19939990997314</v>
+        <v>466.6388003540039</v>
       </c>
       <c r="K6">
-        <v>34.63999938964844</v>
+        <v>262.4100036621094</v>
       </c>
       <c r="L6">
-        <v>111.9800033569336</v>
+        <v>926.6900024414062</v>
       </c>
       <c r="M6">
-        <v>47.78639483949068</v>
+        <v>80.46608034221714</v>
       </c>
       <c r="N6">
-        <v>193.7719928709682</v>
+        <v>232.3599567988452</v>
       </c>
       <c r="O6">
-        <v>182.3795809845948</v>
+        <v>231.1826315040106</v>
       </c>
       <c r="P6">
-        <v>307</v>
+        <v>1230</v>
       </c>
       <c r="Q6">
-        <v>28</v>
+        <v>586</v>
       </c>
       <c r="R6">
-        <v>67</v>
+        <v>265</v>
       </c>
       <c r="S6">
-        <v>25.933</v>
+        <v>91.458</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -886,58 +1123,58 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="E7">
-        <v>200.2899932861328</v>
+        <v>67.26000213623047</v>
       </c>
       <c r="F7">
-        <v>1433456.666666667</v>
+        <v>807010</v>
       </c>
       <c r="G7">
-        <v>174.0997991943359</v>
+        <v>56.50439964294434</v>
       </c>
       <c r="H7">
-        <v>137.2215997823079</v>
+        <v>46.28639986673991</v>
       </c>
       <c r="I7">
-        <v>131.1264498519897</v>
+        <v>42.07099989891052</v>
       </c>
       <c r="J7">
-        <v>120.5549000549316</v>
+        <v>38.53859991073608</v>
       </c>
       <c r="K7">
-        <v>72.47000122070312</v>
+        <v>22.51000022888184</v>
       </c>
       <c r="L7">
-        <v>217.3999938964844</v>
+        <v>67.26000213623047</v>
       </c>
       <c r="M7">
-        <v>52.8114611229779</v>
+        <v>43.810137861706</v>
       </c>
       <c r="N7">
-        <v>176.3764177071854</v>
+        <v>176.448838253778</v>
       </c>
       <c r="O7">
-        <v>179.7881235557685</v>
+        <v>202.3363634031878</v>
       </c>
       <c r="P7">
-        <v>35</v>
+        <v>21900</v>
       </c>
       <c r="Q7">
-        <v>171</v>
+        <v>76</v>
       </c>
       <c r="R7">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="S7">
-        <v>25.889</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -945,58 +1182,58 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8">
+        <v>109.6900024414062</v>
+      </c>
+      <c r="F8">
+        <v>411976.6666666667</v>
+      </c>
+      <c r="G8">
+        <v>89.38920013427735</v>
+      </c>
+      <c r="H8">
+        <v>79.18219998677571</v>
+      </c>
+      <c r="I8">
+        <v>74.18185001373291</v>
+      </c>
+      <c r="J8">
+        <v>68.06524991989136</v>
+      </c>
+      <c r="K8">
+        <v>34.63999938964844</v>
+      </c>
+      <c r="L8">
+        <v>111.9800033569336</v>
+      </c>
+      <c r="M8">
+        <v>39.59022637494638</v>
+      </c>
+      <c r="N8">
+        <v>189.4195198554482</v>
+      </c>
+      <c r="O8">
+        <v>183.7415512152612</v>
+      </c>
+      <c r="P8">
+        <v>307</v>
+      </c>
+      <c r="Q8">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8">
-        <v>779.489990234375</v>
-      </c>
-      <c r="F8">
-        <v>1206203.333333333</v>
-      </c>
-      <c r="G8">
-        <v>757.5169995117187</v>
-      </c>
-      <c r="H8">
-        <v>658.6124658203125</v>
-      </c>
-      <c r="I8">
-        <v>634.2110498046875</v>
-      </c>
-      <c r="J8">
-        <v>604.9291000366211</v>
-      </c>
-      <c r="K8">
-        <v>429.0799865722656</v>
-      </c>
-      <c r="L8">
-        <v>812.9400024414062</v>
-      </c>
-      <c r="M8">
-        <v>8.794385256152083</v>
-      </c>
-      <c r="N8">
-        <v>76.75509982638889</v>
-      </c>
-      <c r="O8">
-        <v>135.6356495189992</v>
-      </c>
-      <c r="P8">
-        <v>93</v>
-      </c>
-      <c r="Q8">
-        <v>426</v>
-      </c>
       <c r="R8">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="S8">
-        <v>27.346</v>
+        <v>25.933</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1004,58 +1241,58 @@
         <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="E9">
-        <v>145.1600036621094</v>
+        <v>200.5399932861328</v>
       </c>
       <c r="F9">
-        <v>306660</v>
+        <v>1404836.666666667</v>
       </c>
       <c r="G9">
-        <v>139.0381988525391</v>
+        <v>178.686598815918</v>
       </c>
       <c r="H9">
-        <v>132.6677996317545</v>
+        <v>138.9233996073405</v>
       </c>
       <c r="I9">
-        <v>128.9426996231079</v>
+        <v>132.9602497863769</v>
       </c>
       <c r="J9">
-        <v>125.5397996520996</v>
+        <v>122.1878499984741</v>
       </c>
       <c r="K9">
-        <v>89.38999938964844</v>
+        <v>75.19000244140625</v>
       </c>
       <c r="L9">
-        <v>149.4199981689453</v>
+        <v>217.3999938964844</v>
       </c>
       <c r="M9">
-        <v>6.680382044980404</v>
+        <v>35.70171534892941</v>
       </c>
       <c r="N9">
-        <v>62.38953423565996</v>
+        <v>166.7109812137708</v>
       </c>
       <c r="O9">
-        <v>121.4582129236914</v>
+        <v>181.5074152704412</v>
       </c>
       <c r="P9">
-        <v>198</v>
+        <v>35</v>
       </c>
       <c r="Q9">
-        <v>39</v>
+        <v>171</v>
       </c>
       <c r="R9">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="S9">
-        <v>14.181</v>
+        <v>25.889</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1063,58 +1300,1828 @@
         <v>27</v>
       </c>
       <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10">
+        <v>78.63999938964844</v>
+      </c>
+      <c r="F10">
+        <v>20411926.66666667</v>
+      </c>
+      <c r="G10">
+        <v>72.29660011291504</v>
+      </c>
+      <c r="H10">
+        <v>57.79933326721191</v>
+      </c>
+      <c r="I10">
+        <v>54.40589994430542</v>
+      </c>
+      <c r="J10">
+        <v>50.40714994430542</v>
+      </c>
+      <c r="K10">
+        <v>29.59000015258789</v>
+      </c>
+      <c r="L10">
+        <v>81.38999938964844</v>
+      </c>
+      <c r="M10">
+        <v>27.39348772527062</v>
+      </c>
+      <c r="N10">
+        <v>152.2129525976767</v>
+      </c>
+      <c r="O10">
+        <v>174.0271967096356</v>
+      </c>
+      <c r="P10">
+        <v>128</v>
+      </c>
+      <c r="Q10">
+        <v>119</v>
+      </c>
+      <c r="R10">
+        <v>15</v>
+      </c>
+      <c r="S10">
+        <v>20.353001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11">
+        <v>42.9900016784668</v>
+      </c>
+      <c r="F11">
+        <v>567780</v>
+      </c>
+      <c r="G11">
+        <v>34.3623999786377</v>
+      </c>
+      <c r="H11">
+        <v>30.52693328857422</v>
+      </c>
+      <c r="I11">
+        <v>29.08119996070862</v>
+      </c>
+      <c r="J11">
+        <v>27.38244996070862</v>
+      </c>
+      <c r="K11">
+        <v>16.79000091552734</v>
+      </c>
+      <c r="L11">
+        <v>42.9900016784668</v>
+      </c>
+      <c r="M11">
+        <v>41.22864955395676</v>
+      </c>
+      <c r="N11">
+        <v>150.3785759315265</v>
+      </c>
+      <c r="O11">
+        <v>168.86017272672</v>
+      </c>
+      <c r="P11">
+        <v>54</v>
+      </c>
+      <c r="Q11">
+        <v>407</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>37.967</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12">
+        <v>19.29000091552734</v>
+      </c>
+      <c r="F12">
+        <v>1408093.333333333</v>
+      </c>
+      <c r="G12">
+        <v>16.9820000076294</v>
+      </c>
+      <c r="H12">
+        <v>14.68739998499552</v>
+      </c>
+      <c r="I12">
+        <v>13.73624998092651</v>
+      </c>
+      <c r="J12">
+        <v>12.84669997692108</v>
+      </c>
+      <c r="K12">
+        <v>9</v>
+      </c>
+      <c r="L12">
+        <v>19.29000091552734</v>
+      </c>
+      <c r="M12">
+        <v>24.77361492839578</v>
+      </c>
+      <c r="N12">
+        <v>110.1307219418221</v>
+      </c>
+      <c r="O12">
+        <v>164.9105355520235</v>
+      </c>
+      <c r="P12">
+        <v>657</v>
+      </c>
+      <c r="Q12">
+        <v>139</v>
+      </c>
+      <c r="R12">
+        <v>19</v>
+      </c>
+      <c r="S12">
+        <v>12.126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E13">
+        <v>24.84000015258789</v>
+      </c>
+      <c r="F13">
+        <v>4933140</v>
+      </c>
+      <c r="G13">
+        <v>22.01619998931885</v>
+      </c>
+      <c r="H13">
+        <v>19.22960001627604</v>
+      </c>
+      <c r="I13">
+        <v>17.65579999923706</v>
+      </c>
+      <c r="J13">
+        <v>16.52159999370575</v>
+      </c>
+      <c r="K13">
+        <v>10.17000007629395</v>
+      </c>
+      <c r="L13">
+        <v>24.84000015258789</v>
+      </c>
+      <c r="M13">
+        <v>23.52063350908888</v>
+      </c>
+      <c r="N13">
+        <v>96.05367011058257</v>
+      </c>
+      <c r="O13">
+        <v>164.8632211045166</v>
+      </c>
+      <c r="P13">
+        <v>75</v>
+      </c>
+      <c r="Q13">
+        <v>34</v>
+      </c>
+      <c r="R13">
+        <v>12</v>
+      </c>
+      <c r="S13">
+        <v>10.1940006</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" t="s">
+        <v>105</v>
+      </c>
+      <c r="E14">
+        <v>172.6799926757812</v>
+      </c>
+      <c r="F14">
+        <v>573276.6666666666</v>
+      </c>
+      <c r="G14">
+        <v>150.0152001953125</v>
+      </c>
+      <c r="H14">
+        <v>130.9760003153483</v>
+      </c>
+      <c r="I14">
+        <v>127.7129001617432</v>
+      </c>
+      <c r="J14">
+        <v>120.6059502029419</v>
+      </c>
+      <c r="K14">
+        <v>77.62999725341797</v>
+      </c>
+      <c r="L14">
+        <v>172.6799926757812</v>
+      </c>
+      <c r="M14">
+        <v>26.90525713306577</v>
+      </c>
+      <c r="N14">
+        <v>113.5542806979339</v>
+      </c>
+      <c r="O14">
+        <v>153.5735734716648</v>
+      </c>
+      <c r="P14">
+        <v>35</v>
+      </c>
+      <c r="Q14">
+        <v>93</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>48.973</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" t="s">
         <v>32</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15">
+        <v>116.9100036621094</v>
+      </c>
+      <c r="F15">
+        <v>833890</v>
+      </c>
+      <c r="G15">
+        <v>100.3576007080078</v>
+      </c>
+      <c r="H15">
+        <v>94.91413365681966</v>
+      </c>
+      <c r="I15">
+        <v>89.35590011596679</v>
+      </c>
+      <c r="J15">
+        <v>84.4131000328064</v>
+      </c>
+      <c r="K15">
+        <v>53.47000122070312</v>
+      </c>
+      <c r="L15">
+        <v>116.9100036621094</v>
+      </c>
+      <c r="M15">
+        <v>27.82637746817713</v>
+      </c>
+      <c r="N15">
+        <v>115.3038771726475</v>
+      </c>
+      <c r="O15">
+        <v>151.8327981091966</v>
+      </c>
+      <c r="P15">
+        <v>382</v>
+      </c>
+      <c r="Q15">
+        <v>1472</v>
+      </c>
+      <c r="R15">
+        <v>13</v>
+      </c>
+      <c r="S15">
+        <v>60.964</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16">
+        <v>309.8099975585938</v>
+      </c>
+      <c r="F16">
+        <v>1814770</v>
+      </c>
+      <c r="G16">
+        <v>272.2851986694336</v>
+      </c>
+      <c r="H16">
+        <v>238.6422663370768</v>
+      </c>
+      <c r="I16">
+        <v>229.7257498931885</v>
+      </c>
+      <c r="J16">
+        <v>217.6199002075195</v>
+      </c>
+      <c r="K16">
+        <v>156.25</v>
+      </c>
+      <c r="L16">
+        <v>309.8099975585938</v>
+      </c>
+      <c r="M16">
+        <v>30.6498507903709</v>
+      </c>
+      <c r="N16">
+        <v>88.28856825090443</v>
+      </c>
+      <c r="O16">
+        <v>151.5166803317298</v>
+      </c>
+      <c r="P16">
+        <v>31</v>
+      </c>
+      <c r="Q16">
+        <v>31</v>
+      </c>
+      <c r="R16">
+        <v>11</v>
+      </c>
+      <c r="S16">
+        <v>17.834</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E17">
+        <v>53.02999877929688</v>
+      </c>
+      <c r="F17">
+        <v>366686.6666666667</v>
+      </c>
+      <c r="G17">
+        <v>46.89560020446778</v>
+      </c>
+      <c r="H17">
+        <v>41.67866671244303</v>
+      </c>
+      <c r="I17">
+        <v>39.13110004425049</v>
+      </c>
+      <c r="J17">
+        <v>37.00805003166199</v>
+      </c>
+      <c r="K17">
+        <v>24.36000061035156</v>
+      </c>
+      <c r="L17">
+        <v>53.02999877929688</v>
+      </c>
+      <c r="M17">
+        <v>22.95385454673782</v>
+      </c>
+      <c r="N17">
+        <v>99.43587241437339</v>
+      </c>
+      <c r="O17">
+        <v>150.8113817554991</v>
+      </c>
+      <c r="P17">
+        <v>375</v>
+      </c>
+      <c r="Q17">
+        <v>129</v>
+      </c>
+      <c r="R17">
+        <v>16</v>
+      </c>
+      <c r="S17">
+        <v>11.623</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18">
+        <v>47.88000106811523</v>
+      </c>
+      <c r="F18">
+        <v>253296.6666666667</v>
+      </c>
+      <c r="G18">
+        <v>44.06859970092773</v>
+      </c>
+      <c r="H18">
+        <v>36.6288665898641</v>
+      </c>
+      <c r="I18">
+        <v>35.05529991149902</v>
+      </c>
+      <c r="J18">
+        <v>33.22924993515014</v>
+      </c>
+      <c r="K18">
+        <v>27.70000076293945</v>
+      </c>
+      <c r="L18">
+        <v>50.77000045776367</v>
+      </c>
+      <c r="M18">
+        <v>27.91878353656983</v>
+      </c>
+      <c r="N18">
+        <v>61.86612978907806</v>
+      </c>
+      <c r="O18">
+        <v>147.664210102652</v>
+      </c>
+      <c r="P18">
+        <v>1433</v>
+      </c>
+      <c r="Q18">
+        <v>119</v>
+      </c>
+      <c r="R18">
+        <v>19</v>
+      </c>
+      <c r="S18">
+        <v>6.2750004</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E19">
+        <v>138.7799987792969</v>
+      </c>
+      <c r="F19">
+        <v>1080943.333333333</v>
+      </c>
+      <c r="G19">
+        <v>119.3484004211426</v>
+      </c>
+      <c r="H19">
+        <v>103.4166668192546</v>
+      </c>
+      <c r="I19">
+        <v>103.0755001068115</v>
+      </c>
+      <c r="J19">
+        <v>99.47989997863769</v>
+      </c>
+      <c r="K19">
+        <v>73.19999694824219</v>
+      </c>
+      <c r="L19">
+        <v>139.2100067138672</v>
+      </c>
+      <c r="M19">
+        <v>29.78583969252961</v>
+      </c>
+      <c r="N19">
+        <v>84.44976438007568</v>
+      </c>
+      <c r="O19">
+        <v>146.1299774179572</v>
+      </c>
+      <c r="P19">
+        <v>789</v>
+      </c>
+      <c r="Q19">
+        <v>27</v>
+      </c>
+      <c r="R19">
+        <v>6</v>
+      </c>
+      <c r="S19">
+        <v>38.525</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20">
+        <v>77.65000152587891</v>
+      </c>
+      <c r="F20">
+        <v>820823.3333333334</v>
+      </c>
+      <c r="G20">
+        <v>67.0271996307373</v>
+      </c>
+      <c r="H20">
+        <v>60.32859990437826</v>
+      </c>
+      <c r="I20">
+        <v>59.40624988555908</v>
+      </c>
+      <c r="J20">
+        <v>56.70214996337891</v>
+      </c>
+      <c r="K20">
+        <v>42.77000045776367</v>
+      </c>
+      <c r="L20">
+        <v>77.65000152587891</v>
+      </c>
+      <c r="M20">
+        <v>34.27286714035842</v>
+      </c>
+      <c r="N20">
+        <v>81.55249168762579</v>
+      </c>
+      <c r="O20">
+        <v>145.5842309361661</v>
+      </c>
+      <c r="P20">
+        <v>26</v>
+      </c>
+      <c r="Q20">
+        <v>34</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>63.88200000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" t="s">
+        <v>112</v>
+      </c>
+      <c r="E21">
+        <v>970.9199829101562</v>
+      </c>
+      <c r="F21">
+        <v>1153396.666666667</v>
+      </c>
+      <c r="G21">
+        <v>893.9568029785156</v>
+      </c>
+      <c r="H21">
+        <v>732.9624015299479</v>
+      </c>
+      <c r="I21">
+        <v>726.88955078125</v>
+      </c>
+      <c r="J21">
+        <v>698.4728506469727</v>
+      </c>
+      <c r="K21">
+        <v>570.5999755859375</v>
+      </c>
+      <c r="L21">
+        <v>1047.390014648438</v>
+      </c>
+      <c r="M21">
+        <v>30.8411700003397</v>
+      </c>
+      <c r="N21">
+        <v>46.18766896072333</v>
+      </c>
+      <c r="O21">
+        <v>144.8893435855737</v>
+      </c>
+      <c r="P21">
+        <v>320</v>
+      </c>
+      <c r="Q21">
         <v>41</v>
       </c>
-      <c r="D10" t="s">
+      <c r="R21">
+        <v>13</v>
+      </c>
+      <c r="S21">
+        <v>70.42100000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" t="s">
+        <v>113</v>
+      </c>
+      <c r="E22">
+        <v>121.4499969482422</v>
+      </c>
+      <c r="F22">
+        <v>2310256.666666667</v>
+      </c>
+      <c r="G22">
+        <v>106.731000213623</v>
+      </c>
+      <c r="H22">
+        <v>94.47173355102539</v>
+      </c>
+      <c r="I22">
+        <v>91.5876501083374</v>
+      </c>
+      <c r="J22">
+        <v>87.2935001373291</v>
+      </c>
+      <c r="K22">
+        <v>68.48000335693359</v>
+      </c>
+      <c r="L22">
+        <v>121.4499969482422</v>
+      </c>
+      <c r="M22">
+        <v>26.84072788328167</v>
+      </c>
+      <c r="N22">
+        <v>73.97221199772331</v>
+      </c>
+      <c r="O22">
+        <v>144.1624755239744</v>
+      </c>
+      <c r="P22">
+        <v>53</v>
+      </c>
+      <c r="Q22">
+        <v>52</v>
+      </c>
+      <c r="R22">
+        <v>12</v>
+      </c>
+      <c r="S22">
+        <v>31.68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23">
+        <v>67.52999877929688</v>
+      </c>
+      <c r="F23">
+        <v>3708030</v>
+      </c>
+      <c r="G23">
+        <v>61.3147998046875</v>
+      </c>
+      <c r="H23">
+        <v>53.12666653951009</v>
+      </c>
+      <c r="I23">
+        <v>51.98269992828369</v>
+      </c>
+      <c r="J23">
+        <v>49.71974994659424</v>
+      </c>
+      <c r="K23">
+        <v>40.18999862670898</v>
+      </c>
+      <c r="L23">
+        <v>69.37999725341797</v>
+      </c>
+      <c r="M23">
+        <v>26.95995586167803</v>
+      </c>
+      <c r="N23">
+        <v>68.02687506045</v>
+      </c>
+      <c r="O23">
+        <v>142.7943920177864</v>
+      </c>
+      <c r="P23">
+        <v>492</v>
+      </c>
+      <c r="Q23">
+        <v>65</v>
+      </c>
+      <c r="R23">
+        <v>14</v>
+      </c>
+      <c r="S23">
+        <v>20.031</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" t="s">
+        <v>115</v>
+      </c>
+      <c r="E24">
+        <v>603.6400146484375</v>
+      </c>
+      <c r="F24">
+        <v>508540</v>
+      </c>
+      <c r="G24">
+        <v>543.7805999755859</v>
+      </c>
+      <c r="H24">
+        <v>478.8650004069011</v>
+      </c>
+      <c r="I24">
+        <v>470.7074011230468</v>
+      </c>
+      <c r="J24">
+        <v>452.0413012695312</v>
+      </c>
+      <c r="K24">
+        <v>333.4500122070312</v>
+      </c>
+      <c r="L24">
+        <v>611.9099731445312</v>
+      </c>
+      <c r="M24">
+        <v>23.09386337753825</v>
+      </c>
+      <c r="N24">
+        <v>81.02863774185489</v>
+      </c>
+      <c r="O24">
+        <v>142.057408377519</v>
+      </c>
+      <c r="P24">
+        <v>54</v>
+      </c>
+      <c r="Q24">
+        <v>36</v>
+      </c>
+      <c r="R24">
+        <v>9</v>
+      </c>
+      <c r="S24">
+        <v>15.785</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="A25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25">
+        <v>546.4600219726562</v>
+      </c>
+      <c r="F25">
+        <v>579576.6666666666</v>
+      </c>
+      <c r="G25">
+        <v>507.783998413086</v>
+      </c>
+      <c r="H25">
+        <v>444.6837986246745</v>
+      </c>
+      <c r="I25">
+        <v>431.0207997131347</v>
+      </c>
+      <c r="J25">
+        <v>410.4548500061035</v>
+      </c>
+      <c r="K25">
+        <v>311.6499938964844</v>
+      </c>
+      <c r="L25">
+        <v>546.4600219726562</v>
+      </c>
+      <c r="M25">
+        <v>20.50101076988093</v>
+      </c>
+      <c r="N25">
+        <v>70.54490951636565</v>
+      </c>
+      <c r="O25">
+        <v>139.6274422488626</v>
+      </c>
+      <c r="P25">
+        <v>72</v>
+      </c>
+      <c r="Q25">
+        <v>59</v>
+      </c>
+      <c r="R25">
+        <v>3</v>
+      </c>
+      <c r="S25">
+        <v>25.507</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26">
+        <v>178.1499938964844</v>
+      </c>
+      <c r="F26">
+        <v>42134630</v>
+      </c>
+      <c r="G26">
+        <v>167.397798461914</v>
+      </c>
+      <c r="H26">
+        <v>148.4011331176758</v>
+      </c>
+      <c r="I26">
+        <v>143.9355000305176</v>
+      </c>
+      <c r="J26">
+        <v>137.8724501800537</v>
+      </c>
+      <c r="K26">
+        <v>97.23999786376953</v>
+      </c>
+      <c r="L26">
+        <v>178.75</v>
+      </c>
+      <c r="M26">
+        <v>15.62924996919917</v>
+      </c>
+      <c r="N26">
+        <v>80.47816386263935</v>
+      </c>
+      <c r="O26">
+        <v>138.7637963501963</v>
+      </c>
+      <c r="P26">
+        <v>3233</v>
+      </c>
+      <c r="Q26">
+        <v>1174</v>
+      </c>
+      <c r="R26">
+        <v>14</v>
+      </c>
+      <c r="S26">
+        <v>17.49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" t="s">
+        <v>117</v>
+      </c>
+      <c r="E27">
+        <v>190.3800048828125</v>
+      </c>
+      <c r="F27">
+        <v>650326.6666666666</v>
+      </c>
+      <c r="G27">
+        <v>178.2169998168945</v>
+      </c>
+      <c r="H27">
+        <v>154.0985334269206</v>
+      </c>
+      <c r="I27">
+        <v>149.4903000640869</v>
+      </c>
+      <c r="J27">
+        <v>143.8183499908447</v>
+      </c>
+      <c r="K27">
+        <v>123.25</v>
+      </c>
+      <c r="L27">
+        <v>195.5700073242188</v>
+      </c>
+      <c r="M27">
+        <v>22.90510805961588</v>
+      </c>
+      <c r="N27">
+        <v>53.85486356029334</v>
+      </c>
+      <c r="O27">
+        <v>138.7342883590967</v>
+      </c>
+      <c r="P27">
+        <v>115</v>
+      </c>
+      <c r="Q27">
+        <v>166</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>8.3500005</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
+      <c r="A28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" t="s">
+        <v>118</v>
+      </c>
+      <c r="E28">
+        <v>101.120002746582</v>
+      </c>
+      <c r="F28">
+        <v>1832483.333333333</v>
+      </c>
+      <c r="G28">
+        <v>91.49139938354492</v>
+      </c>
+      <c r="H28">
+        <v>80.25359985351562</v>
+      </c>
+      <c r="I28">
+        <v>78.2484497833252</v>
+      </c>
+      <c r="J28">
+        <v>75.51434986114502</v>
+      </c>
+      <c r="K28">
+        <v>65.79000091552734</v>
+      </c>
+      <c r="L28">
+        <v>101.120002746582</v>
+      </c>
+      <c r="M28">
+        <v>25.67736005119641</v>
+      </c>
+      <c r="N28">
+        <v>53.70117242651735</v>
+      </c>
+      <c r="O28">
+        <v>137.6277629066684</v>
+      </c>
+      <c r="P28">
+        <v>39</v>
+      </c>
+      <c r="Q28">
+        <v>46</v>
+      </c>
+      <c r="R28">
+        <v>8</v>
+      </c>
+      <c r="S28">
+        <v>17.267</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" t="s">
+        <v>119</v>
+      </c>
+      <c r="E29">
+        <v>406.6499938964844</v>
+      </c>
+      <c r="F29">
+        <v>424360.4666666667</v>
+      </c>
+      <c r="G29">
+        <v>359.7169995117188</v>
+      </c>
+      <c r="H29">
+        <v>324.3940667724609</v>
+      </c>
+      <c r="I29">
+        <v>322.9790998840332</v>
+      </c>
+      <c r="J29">
+        <v>312.2045002746582</v>
+      </c>
+      <c r="K29">
+        <v>221.2799987792969</v>
+   